--- a/検査値リファレンス初期データ.xlsx
+++ b/検査値リファレンス初期データ.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30317"/>
   <workbookPr codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="14" documentId="11_52B2971A7EB7CD425C830B15CC34AEF560AA57ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88530DA9-16D2-4595-BE2C-3092D1129855}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="11_52B2971A7EB7CD425C830B15CC34AEF560AA57ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F08513F-0844-4D83-BC8D-B01E733BD977}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="531">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="521">
   <si>
     <t>検査値名</t>
   </si>
@@ -1352,24 +1352,6 @@
     <t>MCHC,赤血球指数,貧血</t>
   </si>
   <si>
-    <t>CK-MB</t>
-  </si>
-  <si>
-    <t>心筋梗塞</t>
-  </si>
-  <si>
-    <t>CK-MB,心筋梗塞</t>
-  </si>
-  <si>
-    <t>トロポニンT</t>
-  </si>
-  <si>
-    <t>TnT</t>
-  </si>
-  <si>
-    <t>トロポニン,トロポニンT,TnT,心筋梗塞</t>
-  </si>
-  <si>
     <t>アミラーゼ（AMY）</t>
   </si>
   <si>
@@ -1439,7 +1421,7 @@
     <t>メルカゾール（チアマゾール）は無顆粒球症の重大な副作用があり、発熱・のどの痛みが出たらすぐ受診するよう指導する。抗がん剤・免疫抑制剤・抗てんかん薬（カルバマゼピンなど）使用中も定期的なモニタリングが必要</t>
   </si>
   <si>
-    <t>甲状腺疾患,てんかん,がん治療薬</t>
+    <t>甲状腺疾患,てんかん</t>
   </si>
   <si>
     <t>白血球,WBC,好中球,感染症,白血病,無顆粒球症,骨髄抑制</t>
@@ -1470,18 +1452,6 @@
   </si>
   <si>
     <t>ナトリウム,Na,電解質,脱水</t>
-  </si>
-  <si>
-    <t>PaCO₂</t>
-  </si>
-  <si>
-    <t>PaCO2</t>
-  </si>
-  <si>
-    <t>COPDなど呼気の障害</t>
-  </si>
-  <si>
-    <t>PaCO2,PaCO₂,二酸化炭素分圧,COPD,呼吸不全</t>
   </si>
   <si>
     <t>疾患名</t>
@@ -2008,7 +1978,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M59"/>
+  <dimension ref="A1:M56"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="4" width="18.875" customWidth="1"/>
@@ -4078,7 +4048,7 @@
         <v>437</v>
       </c>
       <c r="B51" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C51" t="s">
         <v>24</v>
@@ -4090,10 +4060,10 @@
         <v>24</v>
       </c>
       <c r="F51" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="G51" t="s">
-        <v>24</v>
+        <v>440</v>
       </c>
       <c r="H51" t="s">
         <v>24</v>
@@ -4108,7 +4078,7 @@
         <v>24</v>
       </c>
       <c r="L51" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="M51" t="s">
         <v>24</v>
@@ -4116,10 +4086,10 @@
     </row>
     <row r="52" spans="1:13">
       <c r="A52" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B52" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C52" t="s">
         <v>24</v>
@@ -4131,7 +4101,7 @@
         <v>24</v>
       </c>
       <c r="F52" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="G52" t="s">
         <v>24</v>
@@ -4149,7 +4119,7 @@
         <v>24</v>
       </c>
       <c r="L52" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="M52" t="s">
         <v>24</v>
@@ -4157,10 +4127,10 @@
     </row>
     <row r="53" spans="1:13">
       <c r="A53" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="B53" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="C53" t="s">
         <v>24</v>
@@ -4172,10 +4142,10 @@
         <v>24</v>
       </c>
       <c r="F53" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="G53" t="s">
-        <v>446</v>
+        <v>24</v>
       </c>
       <c r="H53" t="s">
         <v>24</v>
@@ -4187,10 +4157,10 @@
         <v>24</v>
       </c>
       <c r="K53" t="s">
-        <v>24</v>
+        <v>117</v>
       </c>
       <c r="L53" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="M53" t="s">
         <v>24</v>
@@ -4198,40 +4168,40 @@
     </row>
     <row r="54" spans="1:13">
       <c r="A54" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B54" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C54" t="s">
-        <v>24</v>
+        <v>452</v>
       </c>
       <c r="D54" t="s">
-        <v>24</v>
+        <v>453</v>
       </c>
       <c r="E54" t="s">
-        <v>24</v>
+        <v>454</v>
       </c>
       <c r="F54" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="G54" t="s">
-        <v>24</v>
+        <v>456</v>
       </c>
       <c r="H54" t="s">
-        <v>24</v>
+        <v>457</v>
       </c>
       <c r="I54" t="s">
-        <v>24</v>
+        <v>458</v>
       </c>
       <c r="J54" t="s">
-        <v>24</v>
+        <v>459</v>
       </c>
       <c r="K54" t="s">
-        <v>24</v>
+        <v>460</v>
       </c>
       <c r="L54" t="s">
-        <v>451</v>
+        <v>461</v>
       </c>
       <c r="M54" t="s">
         <v>24</v>
@@ -4239,10 +4209,10 @@
     </row>
     <row r="55" spans="1:13">
       <c r="A55" t="s">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="B55" t="s">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="C55" t="s">
         <v>24</v>
@@ -4254,7 +4224,7 @@
         <v>24</v>
       </c>
       <c r="F55" t="s">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="G55" t="s">
         <v>24</v>
@@ -4269,10 +4239,10 @@
         <v>24</v>
       </c>
       <c r="K55" t="s">
-        <v>117</v>
+        <v>24</v>
       </c>
       <c r="L55" t="s">
-        <v>455</v>
+        <v>464</v>
       </c>
       <c r="M55" t="s">
         <v>24</v>
@@ -4280,172 +4250,49 @@
     </row>
     <row r="56" spans="1:13">
       <c r="A56" t="s">
-        <v>456</v>
+        <v>465</v>
       </c>
       <c r="B56" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="C56" t="s">
-        <v>458</v>
+        <v>24</v>
       </c>
       <c r="D56" t="s">
-        <v>459</v>
+        <v>24</v>
       </c>
       <c r="E56" t="s">
-        <v>460</v>
+        <v>24</v>
       </c>
       <c r="F56" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="G56" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="H56" t="s">
-        <v>463</v>
+        <v>24</v>
       </c>
       <c r="I56" t="s">
-        <v>464</v>
+        <v>24</v>
       </c>
       <c r="J56" t="s">
-        <v>465</v>
+        <v>24</v>
       </c>
       <c r="K56" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="L56" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="M56" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13">
-      <c r="A57" t="s">
-        <v>468</v>
-      </c>
-      <c r="B57" t="s">
-        <v>468</v>
-      </c>
-      <c r="C57" t="s">
-        <v>24</v>
-      </c>
-      <c r="D57" t="s">
-        <v>24</v>
-      </c>
-      <c r="E57" t="s">
-        <v>24</v>
-      </c>
-      <c r="F57" t="s">
-        <v>469</v>
-      </c>
-      <c r="G57" t="s">
-        <v>24</v>
-      </c>
-      <c r="H57" t="s">
-        <v>24</v>
-      </c>
-      <c r="I57" t="s">
-        <v>24</v>
-      </c>
-      <c r="J57" t="s">
-        <v>24</v>
-      </c>
-      <c r="K57" t="s">
-        <v>24</v>
-      </c>
-      <c r="L57" t="s">
-        <v>470</v>
-      </c>
-      <c r="M57" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13">
-      <c r="A58" t="s">
-        <v>471</v>
-      </c>
-      <c r="B58" t="s">
-        <v>472</v>
-      </c>
-      <c r="C58" t="s">
-        <v>24</v>
-      </c>
-      <c r="D58" t="s">
-        <v>24</v>
-      </c>
-      <c r="E58" t="s">
-        <v>24</v>
-      </c>
-      <c r="F58" t="s">
-        <v>473</v>
-      </c>
-      <c r="G58" t="s">
-        <v>474</v>
-      </c>
-      <c r="H58" t="s">
-        <v>24</v>
-      </c>
-      <c r="I58" t="s">
-        <v>24</v>
-      </c>
-      <c r="J58" t="s">
-        <v>24</v>
-      </c>
-      <c r="K58" t="s">
-        <v>475</v>
-      </c>
-      <c r="L58" t="s">
-        <v>476</v>
-      </c>
-      <c r="M58" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13">
-      <c r="A59" t="s">
-        <v>477</v>
-      </c>
-      <c r="B59" t="s">
-        <v>478</v>
-      </c>
-      <c r="C59" t="s">
-        <v>24</v>
-      </c>
-      <c r="D59" t="s">
-        <v>24</v>
-      </c>
-      <c r="E59" t="s">
-        <v>24</v>
-      </c>
-      <c r="F59" t="s">
-        <v>479</v>
-      </c>
-      <c r="G59" t="s">
-        <v>24</v>
-      </c>
-      <c r="H59" t="s">
-        <v>24</v>
-      </c>
-      <c r="I59" t="s">
-        <v>24</v>
-      </c>
-      <c r="J59" t="s">
-        <v>24</v>
-      </c>
-      <c r="K59" t="s">
-        <v>24</v>
-      </c>
-      <c r="L59" t="s">
-        <v>480</v>
-      </c>
-      <c r="M59" t="s">
         <v>24</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:M3 A5:J5 A4:J4 L4:M4 A7:M8 A6:J6 L6:M6 L5:M5 A11:M37 A9:J9 L9:M9 A10:J10 L10:M10 A42:M59 A41:J41 L41:M41 A39:M40 A38:J38 L38:M38" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:M3 A5:J5 A4:J4 L4:M4 A7:M8 A6:J6 L6:M6 L5:M5 A11:M37 A9:J9 L9:M9 A10:J10 L10:M10 A42:M50 A41:J41 L41:M41 A39:M40 A38:J38 L38:M38 A55:M56 A54:J54 L54:M54 A51:M53" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4462,19 +4309,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>481</v>
+        <v>471</v>
       </c>
       <c r="B1" t="s">
-        <v>482</v>
+        <v>472</v>
       </c>
       <c r="C1" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="D1" t="s">
-        <v>484</v>
+        <v>474</v>
       </c>
       <c r="E1" t="s">
-        <v>485</v>
+        <v>475</v>
       </c>
       <c r="F1" t="s">
         <v>12</v>
@@ -4488,13 +4335,13 @@
         <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="D2" t="s">
-        <v>487</v>
+        <v>477</v>
       </c>
       <c r="E2" t="s">
-        <v>488</v>
+        <v>478</v>
       </c>
       <c r="F2" t="s">
         <v>24</v>
@@ -4502,19 +4349,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>489</v>
+        <v>479</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="D3" t="s">
-        <v>491</v>
+        <v>481</v>
       </c>
       <c r="E3" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="F3" t="s">
         <v>24</v>
@@ -4528,13 +4375,13 @@
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>493</v>
+        <v>483</v>
       </c>
       <c r="D4" t="s">
-        <v>494</v>
+        <v>484</v>
       </c>
       <c r="E4" t="s">
-        <v>495</v>
+        <v>485</v>
       </c>
       <c r="F4" t="s">
         <v>24</v>
@@ -4548,13 +4395,13 @@
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>496</v>
+        <v>486</v>
       </c>
       <c r="D5" t="s">
-        <v>497</v>
+        <v>487</v>
       </c>
       <c r="E5" t="s">
-        <v>498</v>
+        <v>488</v>
       </c>
       <c r="F5" t="s">
         <v>24</v>
@@ -4568,13 +4415,13 @@
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>499</v>
+        <v>489</v>
       </c>
       <c r="D6" t="s">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="E6" t="s">
-        <v>501</v>
+        <v>491</v>
       </c>
       <c r="F6" t="s">
         <v>24</v>
@@ -4588,13 +4435,13 @@
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="D7" t="s">
-        <v>503</v>
+        <v>493</v>
       </c>
       <c r="E7" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="F7" t="s">
         <v>24</v>
@@ -4608,13 +4455,13 @@
         <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>505</v>
+        <v>495</v>
       </c>
       <c r="D8" t="s">
-        <v>506</v>
+        <v>496</v>
       </c>
       <c r="E8" t="s">
-        <v>507</v>
+        <v>497</v>
       </c>
       <c r="F8" t="s">
         <v>24</v>
@@ -4622,19 +4469,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="B9" t="s">
         <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
       <c r="D9" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
       <c r="E9" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="F9" t="s">
         <v>24</v>
@@ -4648,13 +4495,13 @@
         <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
       <c r="D10" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="E10" t="s">
-        <v>513</v>
+        <v>503</v>
       </c>
       <c r="F10" t="s">
         <v>24</v>
@@ -4668,13 +4515,13 @@
         <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>514</v>
+        <v>504</v>
       </c>
       <c r="D11" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="E11" t="s">
-        <v>516</v>
+        <v>506</v>
       </c>
       <c r="F11" t="s">
         <v>24</v>
@@ -4688,13 +4535,13 @@
         <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>517</v>
+        <v>507</v>
       </c>
       <c r="D12" t="s">
-        <v>518</v>
+        <v>508</v>
       </c>
       <c r="E12" t="s">
-        <v>519</v>
+        <v>509</v>
       </c>
       <c r="F12" t="s">
         <v>24</v>
@@ -4702,19 +4549,19 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>520</v>
+        <v>510</v>
       </c>
       <c r="B13" t="s">
         <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>521</v>
+        <v>511</v>
       </c>
       <c r="D13" t="s">
-        <v>522</v>
+        <v>512</v>
       </c>
       <c r="E13" t="s">
-        <v>523</v>
+        <v>513</v>
       </c>
       <c r="F13" t="s">
         <v>24</v>
@@ -4728,13 +4575,13 @@
         <v>24</v>
       </c>
       <c r="C14" t="s">
-        <v>524</v>
+        <v>514</v>
       </c>
       <c r="D14" t="s">
-        <v>525</v>
+        <v>515</v>
       </c>
       <c r="E14" t="s">
-        <v>526</v>
+        <v>516</v>
       </c>
       <c r="F14" t="s">
         <v>24</v>
@@ -4742,19 +4589,19 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="B15" t="s">
         <v>24</v>
       </c>
       <c r="C15" t="s">
-        <v>528</v>
+        <v>518</v>
       </c>
       <c r="D15" t="s">
-        <v>529</v>
+        <v>519</v>
       </c>
       <c r="E15" t="s">
-        <v>530</v>
+        <v>520</v>
       </c>
       <c r="F15" t="s">
         <v>24</v>

--- a/検査値リファレンス初期データ.xlsx
+++ b/検査値リファレンス初期データ.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M69"/>
+  <dimension ref="A1:M80"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -456,169 +456,169 @@
         <v>参考ページ</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" xml:space="preserve">
       <c r="A2" t="str">
-        <v>HbA1c</v>
+        <v>血糖（空腹時・随時）</v>
       </c>
       <c r="B2" t="str">
-        <v>HbA1c</v>
-      </c>
-      <c r="C2" t="str">
-        <v>6.5%未満（NGSP値）</v>
+        <v>BS,Glu</v>
+      </c>
+      <c r="C2" t="str" xml:space="preserve">
+        <v xml:space="preserve">空腹時 70〜109 mg/dL
+（随時血糖は食後に上がるため単独では判断しにくい）</v>
       </c>
       <c r="D2" t="str">
-        <v>過去1〜2か月の平均的な血糖の高さを表す数値</v>
+        <v>採血したその瞬間の血液中のブドウ糖の濃度</v>
       </c>
       <c r="E2" t="str">
-        <v>HbA1cは、この1〜2か月の血糖値の平均を表す数値です。その日の食事や体調に左右されにくいので、普段の血糖コントロールがどれくらいできているかを見るのに使います。数値が高いほど、平均して血糖値が高めだったことを示します。</v>
+        <v>この数値は採血したその瞬間の血糖値です。食事の前後で大きく変わるので、いつ測ったかによって見方が変わります。空腹時に高い場合や、食後を含めた随時血糖で200を超える場合は、糖尿病を疑う目安になります。</v>
       </c>
       <c r="F2" t="str">
-        <v>糖尿病、血糖コントロール不良</v>
+        <v>糖尿病、食後高血糖、ステロイドなど薬剤性高血糖、感染・ストレスによる一時的な上昇</v>
       </c>
       <c r="G2" t="str">
-        <v>主食の量や間食の頻度を見直す、体を動かす機会を増やす。飲み忘れがあれば服薬タイミングを一緒に確認する</v>
+        <v>食後の血糖上昇を抑えるため、早食い・まとめ食いを避け、野菜から食べる順番を意識する</v>
       </c>
       <c r="H2" t="str">
-        <v>低血糖を繰り返している状態</v>
+        <v>低血糖（薬剤性、食事摂取不足、シックデイ時の過量投与など）</v>
       </c>
       <c r="I2" t="str">
-        <v>低血糖を防ぐため、食事の間隔をあけすぎないようにする。ブドウ糖など対処品の携帯を勧める</v>
+        <v>空腹時間が長くならないよう食事を規則正しくとる。冷や汗・動悸・強い空腹感などの低血糖症状が出たらすぐに糖分を摂る</v>
       </c>
       <c r="J2" t="str">
-        <v>貧血・鉄剤補充・妊娠・腎不全などがあると、実際の血糖値とズレて出ることがある。直近の血糖自己測定値と合わせて確認する</v>
+        <v>採血のタイミング（空腹時か食後か）を必ず確認する。SU薬・インスリン使用者では低血糖症状の有無も併せて聞く</v>
       </c>
       <c r="K2" t="str">
         <v>糖尿病,精神疾患（非定型抗精神病薬）</v>
       </c>
       <c r="L2" t="str">
-        <v>HbA1c,ヘモグロビンエーワンシー,グリコヘモグロビン,血糖コントロール,NGSP</v>
+        <v>血糖値,血糖,BS,Glu,グルコース,空腹時血糖,随時血糖,食後血糖</v>
       </c>
       <c r="M2" t="str">
         <v/>
       </c>
     </row>
-    <row r="3" xml:space="preserve">
+    <row r="3">
       <c r="A3" t="str">
-        <v>血糖（空腹時・随時）</v>
+        <v>HbA1c</v>
       </c>
       <c r="B3" t="str">
-        <v>BS,Glu</v>
-      </c>
-      <c r="C3" t="str" xml:space="preserve">
-        <v xml:space="preserve">空腹時 70〜109 mg/dL
-（随時血糖は食後に上がるため単独では判断しにくい）</v>
+        <v>HbA1c</v>
+      </c>
+      <c r="C3" t="str">
+        <v>6.5%未満（NGSP値）</v>
       </c>
       <c r="D3" t="str">
-        <v>採血したその瞬間の血液中のブドウ糖の濃度</v>
+        <v>過去1〜2か月の平均的な血糖の高さを表す数値</v>
       </c>
       <c r="E3" t="str">
-        <v>この数値は採血したその瞬間の血糖値です。食事の前後で大きく変わるので、いつ測ったかによって見方が変わります。空腹時に高い場合や、食後を含めた随時血糖で200を超える場合は、糖尿病を疑う目安になります。</v>
+        <v>HbA1cは、この1〜2か月の血糖値の平均を表す数値です。その日の食事や体調に左右されにくいので、普段の血糖コントロールがどれくらいできているかを見るのに使います。数値が高いほど、平均して血糖値が高めだったことを示します。</v>
       </c>
       <c r="F3" t="str">
-        <v>糖尿病、食後高血糖、ステロイドなど薬剤性高血糖、感染・ストレスによる一時的な上昇</v>
+        <v>糖尿病、血糖コントロール不良</v>
       </c>
       <c r="G3" t="str">
-        <v>食後の血糖上昇を抑えるため、早食い・まとめ食いを避け、野菜から食べる順番を意識する</v>
+        <v>主食の量や間食の頻度を見直す、体を動かす機会を増やす。飲み忘れがあれば服薬タイミングを一緒に確認する</v>
       </c>
       <c r="H3" t="str">
-        <v>低血糖（薬剤性、食事摂取不足、シックデイ時の過量投与など）</v>
+        <v>低血糖を繰り返している状態</v>
       </c>
       <c r="I3" t="str">
-        <v>空腹時間が長くならないよう食事を規則正しくとる。冷や汗・動悸・強い空腹感などの低血糖症状が出たらすぐに糖分を摂る</v>
+        <v>低血糖を防ぐため、食事の間隔をあけすぎないようにする。ブドウ糖など対処品の携帯を勧める</v>
       </c>
       <c r="J3" t="str">
-        <v>採血のタイミング（空腹時か食後か）を必ず確認する。SU薬・インスリン使用者では低血糖症状の有無も併せて聞く</v>
+        <v>貧血・鉄剤補充・妊娠・腎不全などがあると、実際の血糖値とズレて出ることがある。直近の血糖自己測定値と合わせて確認する</v>
       </c>
       <c r="K3" t="str">
         <v>糖尿病,精神疾患（非定型抗精神病薬）</v>
       </c>
       <c r="L3" t="str">
-        <v>血糖値,血糖,BS,Glu,グルコース,空腹時血糖,随時血糖,食後血糖</v>
+        <v>HbA1c,ヘモグロビンエーワンシー,グリコヘモグロビン,血糖コントロール,NGSP</v>
       </c>
       <c r="M3" t="str">
         <v/>
       </c>
     </row>
-    <row r="4" xml:space="preserve">
+    <row r="4">
       <c r="A4" t="str">
+        <v>尿素窒素（BUN）</v>
+      </c>
+      <c r="B4" t="str">
+        <v>BUN,UN</v>
+      </c>
+      <c r="C4" t="str">
+        <v>8〜20 mg/dL</v>
+      </c>
+      <c r="D4" t="str">
+        <v>たんぱく質が分解されてできる老廃物で、腎機能や体の状態を反映する</v>
+      </c>
+      <c r="E4" t="str">
+        <v>BUNはたんぱく質が体の中で使われたあとにできる老廃物のひとつです。腎臓の働きが落ちると排泄されにくくなって数値が上がりますが、脱水や消化管出血、たんぱく質の摂りすぎでも上がることがあります。</v>
+      </c>
+      <c r="F4" t="str">
+        <v>腎機能低下・腎不全、脱水、消化管出血、高たんぱく食、ステロイド使用</v>
+      </c>
+      <c r="G4" t="str">
+        <v>脱水を避けてこまめに水分を摂る。極端な高たんぱく食が続いていないか確認する</v>
+      </c>
+      <c r="H4" t="str">
+        <v>低たんぱく食、肝不全によるたんぱく合成低下、妊娠</v>
+      </c>
+      <c r="I4" t="str">
+        <v/>
+      </c>
+      <c r="J4" t="str">
+        <v>クレアチニンと同時に見る。BUN/Cr比が高ければ脱水や消化管出血を、比が正常で両方高ければ腎性を疑う目安になる</v>
+      </c>
+      <c r="K4" t="str">
+        <v>腎機能,糖尿病,骨粗鬆症,抗凝固療法（心房細動・血栓症）</v>
+      </c>
+      <c r="L4" t="str">
+        <v>BUN,尿素窒素,UN,腎機能</v>
+      </c>
+      <c r="M4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5" xml:space="preserve">
+      <c r="A5" t="str">
         <v>クレアチニン・eGFR</v>
       </c>
-      <c r="B4" t="str">
+      <c r="B5" t="str">
         <v>Cr,eGFR</v>
       </c>
-      <c r="C4" t="str" xml:space="preserve">
+      <c r="C5" t="str" xml:space="preserve">
         <v xml:space="preserve">クレアチニン 男性0.6〜1.1 mg/dL、女性0.4〜0.8 mg/dL
 eGFR 60 mL/分/1.73㎡以上</v>
       </c>
-      <c r="D4" t="str">
+      <c r="D5" t="str">
         <v>腎臓がどれくらい老廃物をろ過できているかを表す指標</v>
       </c>
-      <c r="E4" t="str">
+      <c r="E5" t="str">
         <v>クレアチニンは筋肉から出る老廃物で、腎臓のろ過機能が落ちると血液の中に増えていきます。eGFRはそのクレアチニンの値や年齢から計算した「腎臓の働きの点数」のようなもので、100に近いほど良く、数字が下がるほど腎臓の働きが落ちていることを表します。</v>
       </c>
-      <c r="F4" t="str">
+      <c r="F5" t="str">
         <v>クレアチニン上昇（＝eGFR低下）で考える：腎機能低下、脱水、腎不全、腎毒性のある薬剤の影響</v>
       </c>
-      <c r="G4" t="str">
+      <c r="G5" t="str">
         <v>脱水を避けてこまめに水分を摂る（心不全等で水分制限がある場合を除く）。塩分の摂りすぎに注意する</v>
       </c>
-      <c r="H4" t="str">
+      <c r="H5" t="str">
         <v>クレアチニンが低い場合：筋肉量の低下、高齢・るいそうで見かけ上低く出ることがある</v>
       </c>
-      <c r="I4" t="str">
-        <v/>
-      </c>
-      <c r="J4" t="str" xml:space="preserve">
+      <c r="I5" t="str">
+        <v/>
+      </c>
+      <c r="J5" t="str" xml:space="preserve">
         <v xml:space="preserve">筋肉量に影響されるため、るいそうの強い高齢者では腎機能を過大評価しやすい。eGFR低下時は腎排泄型薬剤の用量調整を確認する。
 CKD重症度分類（GFR区分）の目安：G1 正常または高値(90以上)／G2 正常または軽度低下(60〜89)／G3a 軽度〜中等度低下(45〜59)／G3b 中等度〜高度低下(30〜44)／G4 高度低下(15〜29)／G5 末期腎不全(15未満)。
 eGFRには体表面積1.73㎡に標準化した「標準化eGFR」（CKD病期の判定などに使用）と、実際の体表面積で補正した「個別化eGFR」（標準化eGFR×体表面積÷1.73、薬剤投与量の決定に使用）があり、体格が標準から大きく外れる患者では両者がずれるため、用量調整の場面では個別化eGFRやCCrを優先する</v>
       </c>
-      <c r="K4" t="str">
-        <v>腎機能,糖尿病,骨粗鬆症,抗凝固療法（心房細動・血栓症）</v>
-      </c>
-      <c r="L4" t="str">
-        <v>クレアチニン,Cr,SCr,血清クレアチニン,eGFR,腎機能,GFR,推算糸球体濾過量,CKD重症度分類</v>
-      </c>
-      <c r="M4" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>BUN（尿素窒素）</v>
-      </c>
-      <c r="B5" t="str">
-        <v>BUN,UN</v>
-      </c>
-      <c r="C5" t="str">
-        <v>8〜20 mg/dL</v>
-      </c>
-      <c r="D5" t="str">
-        <v>たんぱく質が分解されてできる老廃物で、腎機能や体の状態を反映する</v>
-      </c>
-      <c r="E5" t="str">
-        <v>BUNはたんぱく質が体の中で使われたあとにできる老廃物のひとつです。腎臓の働きが落ちると排泄されにくくなって数値が上がりますが、脱水や消化管出血、たんぱく質の摂りすぎでも上がることがあります。</v>
-      </c>
-      <c r="F5" t="str">
-        <v>腎機能低下・腎不全、脱水、消化管出血、高たんぱく食、ステロイド使用</v>
-      </c>
-      <c r="G5" t="str">
-        <v>脱水を避けてこまめに水分を摂る。極端な高たんぱく食が続いていないか確認する</v>
-      </c>
-      <c r="H5" t="str">
-        <v>低たんぱく食、肝不全によるたんぱく合成低下、妊娠</v>
-      </c>
-      <c r="I5" t="str">
-        <v/>
-      </c>
-      <c r="J5" t="str">
-        <v>クレアチニンと同時に見る。BUN/Cr比が高ければ脱水や消化管出血を、比が正常で両方高ければ腎性を疑う目安になる</v>
-      </c>
       <c r="K5" t="str">
         <v>腎機能,糖尿病,骨粗鬆症,抗凝固療法（心房細動・血栓症）</v>
       </c>
       <c r="L5" t="str">
-        <v>BUN,尿素窒素,UN,腎機能</v>
+        <v>クレアチニン,Cr,SCr,血清クレアチニン,eGFR,腎機能,GFR,推算糸球体濾過量,CKD重症度分類</v>
       </c>
       <c r="M5" t="str">
         <v/>
@@ -626,7 +626,7 @@
     </row>
     <row r="6" xml:space="preserve">
       <c r="A6" t="str">
-        <v>クレアチニンクリアランス（CCr）</v>
+        <v>CCr（クレアチニンクリアランス）</v>
       </c>
       <c r="B6" t="str">
         <v>CCr</v>
@@ -709,40 +709,40 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>カリウム（K）</v>
+        <v>ナトリウム（Na）</v>
       </c>
       <c r="B8" t="str">
-        <v>K</v>
+        <v>Na</v>
       </c>
       <c r="C8" t="str">
-        <v>3.5〜5.0 mEq/L（5.5 mEq/L以上で高カリウム血症と診断）</v>
+        <v/>
       </c>
       <c r="D8" t="str">
-        <v>心臓や筋肉の働きに関わる電解質で、高すぎても低すぎても不整脈につながる</v>
+        <v/>
       </c>
       <c r="E8" t="str">
-        <v>カリウムは心臓や筋肉が正しく動くために必要なミネラルです。多すぎても少なすぎても脈の乱れにつながることがあるため、腎臓のお薬やお通じのお薬を使っている方は定期的にチェックすることが大切です。</v>
+        <v/>
       </c>
       <c r="F8" t="str">
-        <v>腎不全、アジソン病、ACE阻害薬・ARB・カリウム保持性利尿薬などの薬剤性、溶血による偽高値</v>
+        <v>アルドステロン症、脱水</v>
       </c>
       <c r="G8" t="str">
-        <v>生野菜・果物・芋類などカリウムの多い食品の摂りすぎに注意する（腎機能低下がある場合）</v>
+        <v>水分摂取状況を確認する（脱水が疑われる場合）</v>
       </c>
       <c r="H8" t="str">
-        <v>利尿薬（特にループ・サイアザイド系）、下痢・嘔吐、インスリン投与、甘草含有製剤</v>
+        <v/>
       </c>
       <c r="I8" t="str">
-        <v>利尿薬使用中は下痢・嘔吐が続いていないか確認し、必要に応じてバナナ・芋類などカリウムを含む食品を意識する</v>
+        <v/>
       </c>
       <c r="J8" t="str">
-        <v>高カリウム血症は不整脈・心停止のリスクがあるため脱力感・動悸の有無を確認。RAS阻害薬とカリウム保持性利尿薬の併用時は特に注意</v>
+        <v/>
       </c>
       <c r="K8" t="str">
-        <v>腎機能,電解質</v>
+        <v>電解質</v>
       </c>
       <c r="L8" t="str">
-        <v>カリウム,K,高カリウム血症,低カリウム血症</v>
+        <v>ナトリウム,Na,電解質,脱水</v>
       </c>
       <c r="M8" t="str">
         <v/>
@@ -750,40 +750,40 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>AST（GOT）</v>
+        <v>クロール</v>
       </c>
       <c r="B9" t="str">
-        <v>AST,GOT</v>
+        <v>Cl</v>
       </c>
       <c r="C9" t="str">
-        <v>10〜40 U/L</v>
+        <v>98〜108 mEq/L</v>
       </c>
       <c r="D9" t="str">
-        <v>肝臓や心臓・筋肉の細胞が壊れると血液中に漏れ出す酵素</v>
+        <v>ナトリウムと共に体の水分・酸塩基バランスに関わる電解質</v>
       </c>
       <c r="E9" t="str">
-        <v>ASTは肝臓や心臓、筋肉の細胞の中にある酵素です。これらの細胞がダメージを受けたり壊れたりすると血液中に漏れ出して数値が上がります。肝臓の状態を見るときはALTと一緒に確認します。</v>
+        <v>クロールは、ナトリウムと一緒に体の水分バランスや、体液の性質（酸性・アルカリ性）を保つ働きをしているミネラルです。多くの場合、ナトリウムと同じように変動します。</v>
       </c>
       <c r="F9" t="str">
-        <v>肝炎・肝硬変などの肝疾患、心筋梗塞、筋肉の障害（激しい運動・横紋筋融解症）、薬剤性肝障害</v>
+        <v>脱水、腎不全、代謝性アシドーシス、高ナトリウム血症に伴うもの</v>
       </c>
       <c r="G9" t="str">
-        <v>飲酒量を控える。激しい運動の直後の採血でないかを確認する</v>
+        <v>脱水が疑われる場合はこまめな水分摂取を勧める（水分制限がある場合を除く）</v>
       </c>
       <c r="H9" t="str">
-        <v>臨床的に問題になることは少ない</v>
+        <v>嘔吐・下痢、利尿薬使用、代謝性アルカローシス</v>
       </c>
       <c r="I9" t="str">
-        <v/>
+        <v>利尿薬使用中は嘔吐・下痢が続いていないか確認する</v>
       </c>
       <c r="J9" t="str">
-        <v>ALTとの比率（AST/ALT比）で肝細胞障害か他臓器由来かを推測できる。AST優位はアルコール性・心筋・筋由来を疑う材料になる</v>
+        <v>ナトリウムと同じ方向に動くことが多いが、酸塩基平衡の異常（アシドーシス・アルカローシス）を反映して単独で動くこともある。利尿薬（特にループ利尿薬）使用中は低クロール性アルカローシスに注意</v>
       </c>
       <c r="K9" t="str">
-        <v>肝機能,糖尿病,てんかん,精神疾患（非定型抗精神病薬）</v>
+        <v>電解質,腎機能</v>
       </c>
       <c r="L9" t="str">
-        <v>AST,GOT,肝機能,肝障害</v>
+        <v>クロール,Cl,塩素,電解質,アシドーシス,アルカローシス</v>
       </c>
       <c r="M9" t="str">
         <v/>
@@ -791,493 +791,493 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
+        <v>カリウム（K）</v>
+      </c>
+      <c r="B10" t="str">
+        <v>K</v>
+      </c>
+      <c r="C10" t="str">
+        <v>3.5〜5.0 mEq/L（5.5 mEq/L以上で高カリウム血症と診断）</v>
+      </c>
+      <c r="D10" t="str">
+        <v>心臓や筋肉の働きに関わる電解質で、高すぎても低すぎても不整脈につながる</v>
+      </c>
+      <c r="E10" t="str">
+        <v>カリウムは心臓や筋肉が正しく動くために必要なミネラルです。多すぎても少なすぎても脈の乱れにつながることがあるため、腎臓のお薬やお通じのお薬を使っている方は定期的にチェックすることが大切です。</v>
+      </c>
+      <c r="F10" t="str">
+        <v>腎不全、アジソン病、ACE阻害薬・ARB・カリウム保持性利尿薬などの薬剤性、溶血による偽高値</v>
+      </c>
+      <c r="G10" t="str">
+        <v>生野菜・果物・芋類などカリウムの多い食品の摂りすぎに注意する（腎機能低下がある場合）</v>
+      </c>
+      <c r="H10" t="str">
+        <v>利尿薬（特にループ・サイアザイド系）、下痢・嘔吐、インスリン投与、甘草含有製剤</v>
+      </c>
+      <c r="I10" t="str">
+        <v>利尿薬使用中は下痢・嘔吐が続いていないか確認し、必要に応じてバナナ・芋類などカリウムを含む食品を意識する</v>
+      </c>
+      <c r="J10" t="str">
+        <v>高カリウム血症は不整脈・心停止のリスクがあるため脱力感・動悸の有無を確認。RAS阻害薬とカリウム保持性利尿薬の併用時は特に注意</v>
+      </c>
+      <c r="K10" t="str">
+        <v>腎機能,電解質</v>
+      </c>
+      <c r="L10" t="str">
+        <v>カリウム,K,高カリウム血症,低カリウム血症</v>
+      </c>
+      <c r="M10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>カルシウム（Ca）</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Ca</v>
+      </c>
+      <c r="C11" t="str">
+        <v>8.5〜10.0 mg/dL</v>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v>副甲状腺機能亢進症</v>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v/>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v>電解質,骨粗鬆症</v>
+      </c>
+      <c r="L11" t="str">
+        <v>カルシウム,Ca,電解質</v>
+      </c>
+      <c r="M11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>AST（GOT）</v>
+      </c>
+      <c r="B12" t="str">
+        <v>AST,GOT</v>
+      </c>
+      <c r="C12" t="str">
+        <v>10〜40 U/L</v>
+      </c>
+      <c r="D12" t="str">
+        <v>肝臓や心臓・筋肉の細胞が壊れると血液中に漏れ出す酵素</v>
+      </c>
+      <c r="E12" t="str">
+        <v>ASTは肝臓や心臓、筋肉の細胞の中にある酵素です。これらの細胞がダメージを受けたり壊れたりすると血液中に漏れ出して数値が上がります。肝臓の状態を見るときはALTと一緒に確認します。</v>
+      </c>
+      <c r="F12" t="str">
+        <v>肝炎・肝硬変などの肝疾患、心筋梗塞、筋肉の障害（激しい運動・横紋筋融解症）、薬剤性肝障害</v>
+      </c>
+      <c r="G12" t="str">
+        <v>飲酒量を控える。激しい運動の直後の採血でないかを確認する</v>
+      </c>
+      <c r="H12" t="str">
+        <v>臨床的に問題になることは少ない</v>
+      </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
+      <c r="J12" t="str">
+        <v>ALTとの比率（AST/ALT比）で肝細胞障害か他臓器由来かを推測できる。AST優位はアルコール性・心筋・筋由来を疑う材料になる</v>
+      </c>
+      <c r="K12" t="str">
+        <v>肝機能,糖尿病,てんかん,精神疾患（非定型抗精神病薬）</v>
+      </c>
+      <c r="L12" t="str">
+        <v>AST,GOT,肝機能,肝障害</v>
+      </c>
+      <c r="M12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
         <v>ALT（GPT）</v>
       </c>
-      <c r="B10" t="str">
+      <c r="B13" t="str">
         <v>ALT,GPT</v>
       </c>
-      <c r="C10" t="str">
+      <c r="C13" t="str">
         <v>5〜40 U/L</v>
       </c>
-      <c r="D10" t="str">
+      <c r="D13" t="str">
         <v>主に肝臓の細胞に含まれる酵素で、肝障害の指標として最もよく使われる</v>
       </c>
-      <c r="E10" t="str">
+      <c r="E13" t="str">
         <v>ALTは主に肝臓の細胞の中にある酵素です。肝臓の細胞がダメージを受けると血液中に漏れ出して数値が上がります。ASTよりも肝臓に特異的な数値なので、肝臓の状態を見るときによく使われます。</v>
       </c>
-      <c r="F10" t="str">
+      <c r="F13" t="str">
         <v>脂肪肝、肝炎（ウイルス性・アルコール性・薬剤性）、肝硬変、薬の副作用による肝機能障害</v>
       </c>
-      <c r="G10" t="str">
+      <c r="G13" t="str">
         <v>体重管理と脂質の摂りすぎに注意する（脂肪肝が疑われる場合）。新規薬剤の開始時期と重なっていないか確認する</v>
       </c>
-      <c r="H10" t="str">
+      <c r="H13" t="str">
         <v>臨床的に問題になることは少ない</v>
       </c>
-      <c r="I10" t="str">
-        <v/>
-      </c>
-      <c r="J10" t="str">
+      <c r="I13" t="str">
+        <v/>
+      </c>
+      <c r="J13" t="str">
         <v>新規薬剤開始後の肝障害の指標として重要。健診でALTのみ軽度上昇していることが多く、その場合は脂肪肝（NAFLD）の頻度が高い</v>
       </c>
-      <c r="K10" t="str">
+      <c r="K13" t="str">
         <v>肝機能,糖尿病,てんかん,精神疾患（非定型抗精神病薬）</v>
       </c>
-      <c r="L10" t="str">
+      <c r="L13" t="str">
         <v>ALT,GPT,肝機能,肝障害,脂肪肝</v>
       </c>
-      <c r="M10" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="11" xml:space="preserve">
-      <c r="A11" t="str">
-        <v>γ-GTP（ガンマGTP）</v>
-      </c>
-      <c r="B11" t="str">
+      <c r="M13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>コリンエステラーゼ</v>
+      </c>
+      <c r="B14" t="str">
+        <v>ChE</v>
+      </c>
+      <c r="C14" t="str">
+        <v>男性 240〜486 U/L、女性 201〜421 U/L（施設差あり）</v>
+      </c>
+      <c r="D14" t="str">
+        <v>主に肝臓で作られる酵素。肝臓のたんぱく質を作る力（合成能）を反映する</v>
+      </c>
+      <c r="E14" t="str">
+        <v>コリンエステラーゼは肝臓で作られる酵素です。肝臓がたんぱく質を作る力が落ちると数値が下がり、逆に脂肪肝や栄養状態が良すぎる場合は上がることがあります。</v>
+      </c>
+      <c r="F14" t="str">
+        <v>脂肪肝、ネフローゼ症候群、肥満、甲状腺機能亢進症</v>
+      </c>
+      <c r="G14" t="str">
+        <v>脂肪肝が疑われる場合は食事・運動習慣の見直しを勧める</v>
+      </c>
+      <c r="H14" t="str">
+        <v>肝硬変など肝臓の合成能低下、低栄養、有機リン中毒（農薬など）</v>
+      </c>
+      <c r="I14" t="str">
+        <v/>
+      </c>
+      <c r="J14" t="str">
+        <v>アルブミンと同様に肝臓の「合成能」を見る指標。低栄養か肝硬変かは、アルブミンや血小板数（肝硬変で低下しやすい）と合わせて判断する</v>
+      </c>
+      <c r="K14" t="str">
+        <v>肝機能</v>
+      </c>
+      <c r="L14" t="str">
+        <v>コリンエステラーゼ,ChE,肝合成能,脂肪肝,肝硬変</v>
+      </c>
+      <c r="M14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>アルカリホスファターゼ（ALP）</v>
+      </c>
+      <c r="B15" t="str">
+        <v>ALP</v>
+      </c>
+      <c r="C15" t="str">
+        <v>38〜113 U/L（施設・測定法により大きく異なる）</v>
+      </c>
+      <c r="D15" t="str">
+        <v>骨や肝臓・胆道に多く含まれる酵素で、骨を作る働きの指標にもなる</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v>骨代謝の亢進（骨折治癒過程、骨粗鬆症、骨転移、Paget病）、肝・胆道疾患、成長期の生理的高値</v>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v/>
+      </c>
+      <c r="J15" t="str">
+        <v>骨由来か肝由来かの区別には骨型ALPアイソザイムやγ-GTPとの組み合わせで判断する</v>
+      </c>
+      <c r="K15" t="str">
+        <v>骨粗鬆症,肝機能</v>
+      </c>
+      <c r="L15" t="str">
+        <v>ALP,アルカリホスファターゼ,骨代謝,肝機能</v>
+      </c>
+      <c r="M15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16" xml:space="preserve">
+      <c r="A16" t="str">
+        <v>γ-GTP</v>
+      </c>
+      <c r="B16" t="str">
         <v>γ-GTP,GGT</v>
       </c>
-      <c r="C11" t="str" xml:space="preserve">
+      <c r="C16" t="str" xml:space="preserve">
         <v xml:space="preserve">男性 〜50 U/L、女性 〜30 U/L
 （施設差が大きい）</v>
       </c>
-      <c r="D11" t="str">
+      <c r="D16" t="str">
         <v>アルコールや胆道のトラブルに反応しやすい肝臓の酵素</v>
       </c>
-      <c r="E11" t="str">
+      <c r="E16" t="str">
         <v>γ-GTPは肝臓や胆道の細胞にある酵素で、特にお酒の影響を受けやすいことが知られています。数値が高いときは、アルコールの摂取量や胆道（胆汁の通り道）の状態を確認する目安になります。</v>
       </c>
-      <c r="F11" t="str">
+      <c r="F16" t="str">
         <v>アルコール性肝障害、脂肪肝、胆道系疾患（胆石・胆管閉塞）、薬剤性（酵素誘導）</v>
       </c>
-      <c r="G11" t="str">
+      <c r="G16" t="str">
         <v>飲酒量を控える、休肝日をつくるよう伝える</v>
       </c>
-      <c r="H11" t="str">
+      <c r="H16" t="str">
         <v>臨床的に問題になることは少ない</v>
       </c>
-      <c r="I11" t="str">
-        <v/>
-      </c>
-      <c r="J11" t="str">
+      <c r="I16" t="str">
+        <v/>
+      </c>
+      <c r="J16" t="str">
         <v>飲酒歴の確認に使いやすい数値。断酒・節酒で比較的早く改善するため、生活指導の効果を示す指標としても使える</v>
       </c>
-      <c r="K11" t="str">
+      <c r="K16" t="str">
         <v>肝機能</v>
       </c>
-      <c r="L11" t="str">
+      <c r="L16" t="str">
         <v>ガンマGTP,γ-GTP,GGT,肝機能,飲酒,アルコール</v>
       </c>
-      <c r="M11" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>アルブミン</v>
-      </c>
-      <c r="B12" t="str">
-        <v>Alb</v>
-      </c>
-      <c r="C12" t="str">
-        <v>3.8〜5.2 g/dL</v>
-      </c>
-      <c r="D12" t="str">
-        <v>体の栄養状態を見る目安になるたんぱく質。血液の中で栄養を運ぶ、水分を血管の中に保つという働きをしている。</v>
-      </c>
-      <c r="E12" t="str">
-        <v>アルブミンは栄養の状態を見る数値です。食事量が少なかったり、肝臓や腎臓、腸の働きが弱ると下がることがあります。数値が低いと、むくみが出やすくなります。</v>
-      </c>
-      <c r="F12" t="str">
-        <v>脱水（見かけ上の上昇）</v>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
-        <v>低栄養／肝機能低下／ネフローゼ症候群／クローン病</v>
-      </c>
-      <c r="I12" t="str">
-        <v>主食に偏らず、肉・魚・卵・大豆製品などたんぱく質をしっかり摂るよう伝える。食欲が落ちている場合は少量頻回の食事も提案する</v>
-      </c>
-      <c r="J12" t="str">
-        <v>3前半は注意ライン。食事摂取量を必ず確認</v>
-      </c>
-      <c r="K12" t="str">
-        <v>肝機能,栄養,腎機能</v>
-      </c>
-      <c r="L12" t="str">
-        <v>アルブミン,Alb,むくみ,浮腫,栄養状態</v>
-      </c>
-      <c r="M12" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>BNP</v>
-      </c>
-      <c r="B13" t="str">
-        <v>BNP</v>
-      </c>
-      <c r="C13" t="str">
-        <v>18.4 pg/mL以下</v>
-      </c>
-      <c r="D13" t="str">
-        <v>心臓が無理をしているときに出る物質。心臓は血液を送るポンプだが、負担がかかると「少し助けてほしい」というサインとしてBNPを血液中に出す。</v>
-      </c>
-      <c r="E13" t="str">
-        <v>この検査は、心臓がどれくらい頑張りすぎていないかを見るものです。数値が高いと、心臓に少し負担がかかっているサインになります。</v>
-      </c>
-      <c r="F13" t="str">
-        <v>心不全、心臓に負担がかかっている状態、体に水分がたまりやすいとき</v>
-      </c>
-      <c r="G13" t="str">
-        <v>塩分・水分の摂りすぎに注意し、体重の変化を毎日記録するよう伝える</v>
-      </c>
-      <c r="H13" t="str">
-        <v>心臓の負担は少ない状態</v>
-      </c>
-      <c r="I13" t="str">
-        <v/>
-      </c>
-      <c r="J13" t="str">
-        <v>腎機能が低いとBNPは高めに出ることがある／数値だけで判断せず、症状と合わせて評価する／息切れ、むくみ、体重増加があれば要注意</v>
-      </c>
-      <c r="K13" t="str">
-        <v>心不全</v>
-      </c>
-      <c r="L13" t="str">
-        <v>BNP,心不全,息切れ,むくみ</v>
-      </c>
-      <c r="M13" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="14" xml:space="preserve">
-      <c r="A14" t="str">
+      <c r="M16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>総ビリルビン</v>
+      </c>
+      <c r="B17" t="str">
+        <v>T-Bil</v>
+      </c>
+      <c r="C17" t="str">
+        <v>0.2〜1.2 mg/dL</v>
+      </c>
+      <c r="D17" t="str">
+        <v>赤血球が壊れてできる黄色い色素の総量。肝臓・胆道の状態や黄疸の指標</v>
+      </c>
+      <c r="E17" t="str">
+        <v>ビリルビンは赤血球が寿命を迎えて壊れるときにできる黄色い色素です。肝臓で処理されて排泄されますが、肝臓や胆道にトラブルがあると血液中に増え、皮膚や白目が黄色くなる黄疸として現れます。</v>
+      </c>
+      <c r="F17" t="str">
+        <v>肝炎・肝硬変などの肝疾患、胆道閉塞（胆石・腫瘍など）、溶血性疾患（赤血球の破壊亢進）、体質性黄疸（ジルベール症候群など）</v>
+      </c>
+      <c r="G17" t="str">
+        <v>皮膚や白目の黄染、尿の色が濃くなっていないか確認する</v>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v/>
+      </c>
+      <c r="J17" t="str">
+        <v>直接ビリルビン・間接ビリルビンの内訳で原因を推測できる（直接優位は胆道系、間接優位は溶血・体質性）。AST/ALT/γ-GTPと合わせて評価する</v>
+      </c>
+      <c r="K17" t="str">
+        <v>肝機能</v>
+      </c>
+      <c r="L17" t="str">
+        <v>総ビリルビン,T-Bil,黄疸,ビリルビン,ジルベール症候群</v>
+      </c>
+      <c r="M17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>総タンパク</v>
+      </c>
+      <c r="B18" t="str">
+        <v>TP</v>
+      </c>
+      <c r="C18" t="str">
+        <v>6.6〜8.1 g/dL</v>
+      </c>
+      <c r="D18" t="str">
+        <v>血液中のたんぱく質（アルブミン＋グロブリン）の総量。栄養状態や肝機能、炎症の目安</v>
+      </c>
+      <c r="E18" t="str">
+        <v>総タンパクは、血液中のたんぱく質の合計量です。栄養状態や肝臓の働き、体の炎症の有無などを反映します。</v>
+      </c>
+      <c r="F18" t="str">
+        <v>脱水、多発性骨髄腫など（グロブリン増加）、慢性炎症</v>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v>低栄養、肝機能低下（アルブミン産生低下）、ネフローゼ症候群、消化管からのたんぱく漏出</v>
+      </c>
+      <c r="I18" t="str">
+        <v>食事摂取量（特にたんぱく質）を確認する</v>
+      </c>
+      <c r="J18" t="str">
+        <v>アルブミンとグロブリンの内訳（A/G比）も合わせて確認すると原因の絞り込みに役立つ。低栄養か肝機能低下かはアルブミンの値と合わせて判断する</v>
+      </c>
+      <c r="K18" t="str">
+        <v>肝機能</v>
+      </c>
+      <c r="L18" t="str">
+        <v>総タンパク,TP,総蛋白,栄養状態,A/G比</v>
+      </c>
+      <c r="M18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>中性脂肪（トリグリセリド）</v>
+      </c>
+      <c r="B19" t="str">
+        <v>TG</v>
+      </c>
+      <c r="C19" t="str">
+        <v>150 mg/dL未満（空腹時）</v>
+      </c>
+      <c r="D19" t="str">
+        <v/>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v>脂質異常症</v>
+      </c>
+      <c r="G19" t="str">
+        <v>糖質・アルコールの摂りすぎに注意し、有酸素運動を勧める</v>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v/>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
+        <v>脂質異常症</v>
+      </c>
+      <c r="L19" t="str">
+        <v>中性脂肪,トリグリセリド,TG,脂質異常症</v>
+      </c>
+      <c r="M19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>総コレステロール</v>
+      </c>
+      <c r="B20" t="str">
+        <v>TC,T-cho</v>
+      </c>
+      <c r="C20" t="str">
+        <v>220 mg/dL未満</v>
+      </c>
+      <c r="D20" t="str">
+        <v/>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v>脂質異常症</v>
+      </c>
+      <c r="G20" t="str">
+        <v>動物性脂肪を控え、食物繊維を増やすよう伝える</v>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v/>
+      </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
+      <c r="K20" t="str">
+        <v>脂質異常症</v>
+      </c>
+      <c r="L20" t="str">
+        <v>総コレステロール,TC,コレステロール,脂質異常症</v>
+      </c>
+      <c r="M20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21" xml:space="preserve">
+      <c r="A21" t="str">
         <v>LDLコレステロール</v>
       </c>
-      <c r="B14" t="str">
+      <c r="B21" t="str">
         <v>LDL-C</v>
       </c>
-      <c r="C14" t="str" xml:space="preserve">
+      <c r="C21" t="str" xml:space="preserve">
         <v xml:space="preserve">60〜139 mg/dL
 （140 mg/dL以上で高LDLコレステロール血症）</v>
       </c>
-      <c r="D14" t="str">
+      <c r="D21" t="str">
         <v>いわゆる「悪玉コレステロール」。血管の壁にたまり動脈硬化を進める</v>
       </c>
-      <c r="E14" t="str">
+      <c r="E21" t="str">
         <v>LDLコレステロールは、いわゆる悪玉コレステロールと呼ばれるものです。多いままだと血管の壁にたまって、動脈硬化や心筋梗塞・脳梗塞のリスクを高めます。数値を下げることで、将来の血管のトラブルを防ぐことが目的です。</v>
       </c>
-      <c r="F14" t="str">
+      <c r="F21" t="str">
         <v>脂質異常症、動脈硬化のリスク上昇、家族性高コレステロール血症、甲状腺機能低下症</v>
       </c>
-      <c r="G14" t="str">
+      <c r="G21" t="str">
         <v>動物性脂肪や揚げ物を控え、青魚や食物繊維（野菜・海藻・きのこ）を増やすよう伝える</v>
       </c>
-      <c r="H14" t="str">
+      <c r="H21" t="str">
         <v>低栄養、肝機能低下、甲状腺機能亢進症</v>
       </c>
-      <c r="I14" t="str">
-        <v/>
-      </c>
-      <c r="J14" t="str">
+      <c r="I21" t="str">
+        <v/>
+      </c>
+      <c r="J21" t="str">
         <v>スタチン等の効果判定に使う中心的な数値。目標値は既往疾患（冠動脈疾患・糖尿病等）によって異なるため一律に判断しない</v>
       </c>
-      <c r="K14" t="str">
+      <c r="K21" t="str">
         <v>脂質異常症,精神疾患（非定型抗精神病薬）</v>
       </c>
-      <c r="L14" t="str">
+      <c r="L21" t="str">
         <v>LDL,LDLコレステロール,悪玉コレステロール,脂質異常症</v>
-      </c>
-      <c r="M14" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>尿ケトン体</v>
-      </c>
-      <c r="B15" t="str">
-        <v>尿ケトン,Ket</v>
-      </c>
-      <c r="C15" t="str">
-        <v>陰性（－）</v>
-      </c>
-      <c r="D15" t="str">
-        <v>体がブドウ糖の代わりに脂肪を分解してエネルギーを作っているサイン</v>
-      </c>
-      <c r="E15" t="str">
-        <v>この検査は、体が糖の代わりに脂肪を使ってエネルギーを作っていないかを見るものです。陽性が続くときは、食事や水分、インスリンの使い方を確認する必要があります。</v>
-      </c>
-      <c r="F15" t="str">
-        <v>糖尿病の血糖コントロール不良（シックデイ・インスリン不足）、極端な糖質制限、絶食、嘔吐・下痢による脱水</v>
-      </c>
-      <c r="G15" t="str">
-        <v/>
-      </c>
-      <c r="H15" t="str">
-        <v/>
-      </c>
-      <c r="I15" t="str">
-        <v/>
-      </c>
-      <c r="J15" t="str">
-        <v>陽性かつ高血糖・全身倦怠感が強い場合は糖尿病性ケトアシドーシスの可能性があり緊急性が高い。シックデイルールの説明歴を確認する</v>
-      </c>
-      <c r="K15" t="str">
-        <v>糖尿病</v>
-      </c>
-      <c r="L15" t="str">
-        <v>尿ケトン体,ケトン体,Ket,シックデイ,ケトアシドーシス</v>
-      </c>
-      <c r="M15" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>血清CPR（Cペプチド）</v>
-      </c>
-      <c r="B16" t="str">
-        <v>CPR</v>
-      </c>
-      <c r="C16" t="str">
-        <v>空腹時 0.6〜3.0 ng/mL（施設差あり）</v>
-      </c>
-      <c r="D16" t="str">
-        <v>自分の膵臓がどれくらいインスリンを作れているかを表す指標</v>
-      </c>
-      <c r="E16" t="str">
-        <v>この検査は、ご自身の膵臓がどれくらいインスリンを作る力を持っているかを見るものです。数値が低いほど、体の中で作れるインスリンが少ないことを示します。</v>
-      </c>
-      <c r="F16" t="str">
-        <v>インスリン抵抗性が強い状態（初期の2型糖尿病など）</v>
-      </c>
-      <c r="G16" t="str">
-        <v/>
-      </c>
-      <c r="H16" t="str">
-        <v>膵臓のインスリン分泌能低下（1型糖尿病、糖尿病の進行）</v>
-      </c>
-      <c r="I16" t="str">
-        <v/>
-      </c>
-      <c r="J16" t="str">
-        <v>インスリン分泌能の評価に使われる。数値が低いほどインスリン治療の必要性が高いと判断される目安になる</v>
-      </c>
-      <c r="K16" t="str">
-        <v>糖尿病</v>
-      </c>
-      <c r="L16" t="str">
-        <v>CPR,Cペプチド,インスリン分泌,血清CPR</v>
-      </c>
-      <c r="M16" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>尿蛋白</v>
-      </c>
-      <c r="B17" t="str">
-        <v>尿蛋白,U-pro</v>
-      </c>
-      <c r="C17" t="str">
-        <v>陰性（－）〜弱陽性</v>
-      </c>
-      <c r="D17" t="str">
-        <v>腎臓から本来漏れないはずのたんぱくが尿に出ていないかを見る検査</v>
-      </c>
-      <c r="E17" t="str">
-        <v>この検査は、腎臓のろ過機能に負担がかかっていないかを見るものです。本来、たんぱく質は尿にほとんど出ませんが、腎臓に負担がかかると漏れ出るようになります。</v>
-      </c>
-      <c r="F17" t="str">
-        <v>糖尿病性腎症、腎炎、高血圧性腎硬化症、発熱・運動後の一過性のもの</v>
-      </c>
-      <c r="G17" t="str">
-        <v/>
-      </c>
-      <c r="H17" t="str">
-        <v/>
-      </c>
-      <c r="I17" t="str">
-        <v/>
-      </c>
-      <c r="J17" t="str">
-        <v>発熱・激しい運動・起立性蛋白尿など生理的な要因でも陽性になることがある。持続する場合に腎症の進行を疑う</v>
-      </c>
-      <c r="K17" t="str">
-        <v>糖尿病,腎機能</v>
-      </c>
-      <c r="L17" t="str">
-        <v>尿蛋白,U-pro,腎症,たんぱく尿</v>
-      </c>
-      <c r="M17" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>尿中微量アルブミン</v>
-      </c>
-      <c r="B18" t="str">
-        <v>U-Alb,MAU</v>
-      </c>
-      <c r="C18" t="str">
-        <v>30 mg/gCr未満（尿中アルブミン/クレアチニン比）</v>
-      </c>
-      <c r="D18" t="str">
-        <v>通常の尿蛋白検査では見つからない、ごく早期の腎症のサイン</v>
-      </c>
-      <c r="E18" t="str">
-        <v>この検査は、通常の尿検査ではまだ分からないくらい早い段階の腎臓の変化を見つけるためのものです。数値が高いと、腎症の初期のサインである可能性があります。</v>
-      </c>
-      <c r="F18" t="str">
-        <v>糖尿病性腎症の早期段階、高血圧</v>
-      </c>
-      <c r="G18" t="str">
-        <v/>
-      </c>
-      <c r="H18" t="str">
-        <v/>
-      </c>
-      <c r="I18" t="str">
-        <v/>
-      </c>
-      <c r="J18" t="str">
-        <v>糖尿病腎症の早期発見に重要な検査。血糖・血圧コントロールで改善しうる段階なので、早期介入の意義を伝える</v>
-      </c>
-      <c r="K18" t="str">
-        <v>糖尿病,腎機能</v>
-      </c>
-      <c r="L18" t="str">
-        <v>微量アルブミン,U-Alb,MAU,糖尿病性腎症,早期腎症</v>
-      </c>
-      <c r="M18" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>血清鉄（Fe）</v>
-      </c>
-      <c r="B19" t="str">
-        <v>Fe</v>
-      </c>
-      <c r="C19" t="str">
-        <v>60〜200 μg/dL（施設差あり）</v>
-      </c>
-      <c r="D19" t="str">
-        <v>血液中を流れている鉄の量</v>
-      </c>
-      <c r="E19" t="str">
-        <v>この検査は、今血液の中を流れている鉄の量を見るものです。低いと、体の中で鉄が不足している可能性があります。</v>
-      </c>
-      <c r="F19" t="str">
-        <v>鉄剤の過剰摂取、溶血、肝疾患</v>
-      </c>
-      <c r="G19" t="str">
-        <v/>
-      </c>
-      <c r="H19" t="str">
-        <v>鉄欠乏性貧血、慢性炎症、出血</v>
-      </c>
-      <c r="I19" t="str">
-        <v>鉄分の多い食品（レバー・赤身肉・魚・ほうれん草など）を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える</v>
-      </c>
-      <c r="J19" t="str">
-        <v>血清鉄は日内変動が大きい。単独で判断せず総鉄結合能・フェリチンと合わせて評価する</v>
-      </c>
-      <c r="K19" t="str">
-        <v>鉄欠乏性貧血</v>
-      </c>
-      <c r="L19" t="str">
-        <v>血清鉄,Fe,鉄欠乏性貧血</v>
-      </c>
-      <c r="M19" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>総鉄結合能（TIBC）</v>
-      </c>
-      <c r="B20" t="str">
-        <v>TIBC</v>
-      </c>
-      <c r="C20" t="str">
-        <v>250〜360 μg/dL（施設差あり）</v>
-      </c>
-      <c r="D20" t="str">
-        <v>血液中のトランスフェリンが鉄と結合できる総量</v>
-      </c>
-      <c r="E20" t="str">
-        <v/>
-      </c>
-      <c r="F20" t="str">
-        <v>鉄欠乏性貧血（＞360 μg/dLが目安）</v>
-      </c>
-      <c r="G20" t="str">
-        <v/>
-      </c>
-      <c r="H20" t="str">
-        <v>慢性炎症、肝疾患、ネフローゼ症候群</v>
-      </c>
-      <c r="I20" t="str">
-        <v/>
-      </c>
-      <c r="J20" t="str">
-        <v>鉄が不足すると、体はより多く運ぼうとしてTIBCが上昇する。UIBC・血清鉄と併せて評価する</v>
-      </c>
-      <c r="K20" t="str">
-        <v>鉄欠乏性貧血</v>
-      </c>
-      <c r="L20" t="str">
-        <v>TIBC,総鉄結合能,鉄欠乏性貧血</v>
-      </c>
-      <c r="M20" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>不飽和鉄結合能（UIBC）</v>
-      </c>
-      <c r="B21" t="str">
-        <v>UIBC</v>
-      </c>
-      <c r="C21" t="str">
-        <v>170〜300 μg/dL（施設差あり）</v>
-      </c>
-      <c r="D21" t="str">
-        <v>トランスフェリンのうち、まだ鉄と結合していない余力の部分（UIBC＝TIBC－血清鉄）</v>
-      </c>
-      <c r="E21" t="str">
-        <v/>
-      </c>
-      <c r="F21" t="str">
-        <v>鉄欠乏性貧血（＞300 μg/dLが目安）</v>
-      </c>
-      <c r="G21" t="str">
-        <v/>
-      </c>
-      <c r="H21" t="str">
-        <v>慢性炎症、鉄過剰状態</v>
-      </c>
-      <c r="I21" t="str">
-        <v/>
-      </c>
-      <c r="J21" t="str">
-        <v>TIBCと同じ方向に動くことが多い。血清鉄・TIBCとあわせて鉄欠乏性貧血と二次性貧血の鑑別に使う</v>
-      </c>
-      <c r="K21" t="str">
-        <v>鉄欠乏性貧血</v>
-      </c>
-      <c r="L21" t="str">
-        <v>UIBC,不飽和鉄結合能,鉄欠乏性貧血</v>
       </c>
       <c r="M21" t="str">
         <v/>
@@ -1285,40 +1285,40 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>トランスフェリン飽和度</v>
+        <v>nonHDLコレステロール</v>
       </c>
       <c r="B22" t="str">
-        <v>TSAT</v>
+        <v>non-HDL-C</v>
       </c>
       <c r="C22" t="str">
-        <v>16〜50%程度（施設差あり）</v>
+        <v>90〜149 mg/dL（150 mg/dL以上で高値）</v>
       </c>
       <c r="D22" t="str">
-        <v>鉄を運ぶ役割のトランスフェリンのうち、実際に鉄を運んでいる割合（血清鉄÷総鉄結合能）</v>
+        <v>総コレステロールからHDL（善玉）を除いた、動脈硬化を進めるすべての脂質の合計</v>
       </c>
       <c r="E22" t="str">
-        <v/>
+        <v>nonHDLコレステロールは、総コレステロールから善玉のHDLを引いた数値で、LDL（悪玉）を含む、動脈硬化を進めるすべてのコレステロールの合計を表します。中性脂肪が高くLDLだけでは評価しにくい方でも、こちらで動脈硬化のリスクを評価できます。</v>
       </c>
       <c r="F22" t="str">
-        <v>鉄過剰症（ヘモクロマトーシスなど）</v>
+        <v>脂質異常症、動脈硬化のリスク上昇（特に中性脂肪が高い場合にLDL-Cより実態を反映しやすい）</v>
       </c>
       <c r="G22" t="str">
-        <v/>
+        <v>動物性脂肪や揚げ物を控え、青魚や食物繊維（野菜・海藻・きのこ）を増やすよう伝える</v>
       </c>
       <c r="H22" t="str">
-        <v>鉄欠乏性貧血（＜16%が目安）</v>
+        <v/>
       </c>
       <c r="I22" t="str">
         <v/>
       </c>
       <c r="J22" t="str">
-        <v>血清鉄をTIBCで割って計算される。鉄剤補充の効果判定にも使われる</v>
+        <v>中性脂肪（TG）が400 mg/dL以上などLDL-Cの計算式（Friedewald式）が不正確になる場合に、LDL-Cの代わりに用いられる。目標値はLDL-Cの目標値＋30 mg/dLが目安</v>
       </c>
       <c r="K22" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>脂質異常症</v>
       </c>
       <c r="L22" t="str">
-        <v>トランスフェリン飽和度,TSAT,鉄欠乏性貧血</v>
+        <v>nonHDL,non-HDLコレステロール,動脈硬化,中性脂肪,LDL計算式</v>
       </c>
       <c r="M22" t="str">
         <v/>
@@ -1326,40 +1326,40 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>血清フェリチン</v>
+        <v>HDLコレステロール</v>
       </c>
       <c r="B23" t="str">
-        <v>Ferritin</v>
+        <v>HDL-C</v>
       </c>
       <c r="C23" t="str">
-        <v>男性 20〜250 ng/mL、女性 10〜120 ng/mL（施設差あり）</v>
+        <v>40 mg/dL以上</v>
       </c>
       <c r="D23" t="str">
-        <v>体に貯蔵されている鉄の量を反映する指標。貧血の症状が出るより早い段階で低下する</v>
+        <v/>
       </c>
       <c r="E23" t="str">
-        <v>フェリチンは、体に蓄えられている鉄の「貯金」の量を見る検査です。この数値が下がるのは、貧血の症状が出るよりも前の、とても早い段階のサインになります。</v>
+        <v/>
       </c>
       <c r="F23" t="str">
-        <v>炎症性疾患、肝疾患、悪性腫瘍、鉄過剰症（フェリチンは炎症でも上昇するため、貧血の評価では注意が必要）</v>
+        <v/>
       </c>
       <c r="G23" t="str">
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>鉄欠乏状態（貧血の症状が出る前の早期段階から低下する）</v>
+        <v>脂質異常症（低HDL血症）</v>
       </c>
       <c r="I23" t="str">
-        <v>鉄分の多い食品を意識するとともに、貯蔵鉄を補うため治療は数値が正常化してからも継続が必要なことを伝える</v>
+        <v>適度な運動習慣、禁煙を勧める</v>
       </c>
       <c r="J23" t="str">
-        <v>貯蔵鉄の指標で鉄欠乏を最も早期に反映する。ただし炎症があると鉄欠乏があっても正常〜高値に出ることがあり、CRP等の炎症所見と合わせて評価する。二次性貧血との鑑別に重要</v>
+        <v/>
       </c>
       <c r="K23" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>脂質異常症</v>
       </c>
       <c r="L23" t="str">
-        <v>フェリチン,Ferritin,貯蔵鉄,鉄欠乏</v>
+        <v>HDL,HDLコレステロール,善玉コレステロール,脂質異常症</v>
       </c>
       <c r="M23" t="str">
         <v/>
@@ -1367,40 +1367,40 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>尿中尿酸/クレアチニン比（UUA/UCr）</v>
+        <v>CK（クレアチンフォスフォキナーゼ）</v>
       </c>
       <c r="B24" t="str">
-        <v>UUA/UCr</v>
+        <v>CK,CPK</v>
       </c>
       <c r="C24" t="str">
-        <v>0.4〜0.8程度が混合型の目安</v>
+        <v>男性 60〜250 U/L、女性 50〜170 U/L</v>
       </c>
       <c r="D24" t="str">
-        <v>尿酸が「作られすぎ」か「排泄できていない」かを見分ける比の値</v>
+        <v/>
       </c>
       <c r="E24" t="str">
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>尿酸産生過剰型（0.8以上が目安）</v>
+        <v>心筋梗塞、横紋筋融解症などで上昇</v>
       </c>
       <c r="G24" t="str">
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>尿酸排泄低下型（0.4以下が目安）</v>
+        <v/>
       </c>
       <c r="I24" t="str">
         <v/>
       </c>
       <c r="J24" t="str">
-        <v>高尿酸血症は尿酸産生過剰型・排泄低下型・混合型に分類され、この比が目安になる。病型によって使う薬剤（尿酸生成抑制薬か尿酸排泄促進薬か）の選択が変わる</v>
+        <v/>
       </c>
       <c r="K24" t="str">
-        <v>高尿酸血症</v>
+        <v/>
       </c>
       <c r="L24" t="str">
-        <v>UUA,UCr,尿酸クリアランス,CUA,EUA,尿酸産生過剰型,尿酸排泄低下型</v>
+        <v>CK,CPK,クレアチンキナーゼ,横紋筋融解症</v>
       </c>
       <c r="M24" t="str">
         <v/>
@@ -1408,40 +1408,40 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>リン（P）</v>
+        <v>尿蛋白</v>
       </c>
       <c r="B25" t="str">
-        <v>P,IP</v>
+        <v>尿蛋白,U-pro</v>
       </c>
       <c r="C25" t="str">
-        <v>2.5〜4.5 mg/dL</v>
+        <v>陰性（－）〜弱陽性</v>
       </c>
       <c r="D25" t="str">
-        <v>カルシウムとともに骨を作る主要なミネラル</v>
+        <v>腎臓から本来漏れないはずのたんぱくが尿に出ていないかを見る検査</v>
       </c>
       <c r="E25" t="str">
-        <v/>
+        <v>この検査は、腎臓のろ過機能に負担がかかっていないかを見るものです。本来、たんぱく質は尿にほとんど出ませんが、腎臓に負担がかかると漏れ出るようになります。</v>
       </c>
       <c r="F25" t="str">
-        <v>腎不全、副甲状腺機能低下症</v>
+        <v>糖尿病性腎症、腎炎、高血圧性腎硬化症、発熱・運動後の一過性のもの</v>
       </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>副甲状腺機能亢進症、骨軟化症、ビタミンD欠乏</v>
+        <v/>
       </c>
       <c r="I25" t="str">
         <v/>
       </c>
       <c r="J25" t="str">
-        <v>カルシウムと逆方向に動くことが多い（副甲状腺機能亢進症ではCa上昇・P低下）。骨粗鬆症の二次性原因の除外に用いられる</v>
+        <v>発熱・激しい運動・起立性蛋白尿など生理的な要因でも陽性になることがある。持続する場合に腎症の進行を疑う</v>
       </c>
       <c r="K25" t="str">
-        <v>骨粗鬆症,電解質</v>
+        <v>糖尿病,腎機能</v>
       </c>
       <c r="L25" t="str">
-        <v>リン,P,IP,無機リン</v>
+        <v>尿蛋白,U-pro,腎症,たんぱく尿</v>
       </c>
       <c r="M25" t="str">
         <v/>
@@ -1449,40 +1449,40 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>アルカリホスファターゼ（ALP）</v>
+        <v>尿クレアチニン（随時尿）</v>
       </c>
       <c r="B26" t="str">
-        <v>ALP</v>
+        <v>尿CRE</v>
       </c>
       <c r="C26" t="str">
-        <v>38〜113 U/L（施設・測定法により大きく異なる）</v>
+        <v>随時尿は主に他項目の濃度補正に利用（単独の基準値は設けにくい）</v>
       </c>
       <c r="D26" t="str">
-        <v>骨や肝臓・胆道に多く含まれる酵素で、骨を作る働きの指標にもなる</v>
+        <v>随時尿中のクレアチニン濃度。他の尿検査項目を薄まり具合で補正するための基準として使う</v>
       </c>
       <c r="E26" t="str">
-        <v/>
+        <v>この数値は、尿がどれくらい薄まっているかを確認するための基準として使われます。他の尿検査の結果（蛋白やアルブミンなど）をこの値で割って補正することで、水分摂取量による影響を減らして正確に評価できます。</v>
       </c>
       <c r="F26" t="str">
-        <v>骨代謝の亢進（骨折治癒過程、骨粗鬆症、骨転移、Paget病）、肝・胆道疾患、成長期の生理的高値</v>
+        <v/>
       </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v/>
+        <v>尿が薄い（水分摂取が多い、腎機能低下）状態</v>
       </c>
       <c r="I26" t="str">
         <v/>
       </c>
       <c r="J26" t="str">
-        <v>骨由来か肝由来かの区別には骨型ALPアイソザイムやγ-GTPとの組み合わせで判断する</v>
+        <v>尿中アルブミン/Cr比、尿蛋白/Cr比など、他項目の補正計算に使われる。単独の高低に臨床的意味は乏しい</v>
       </c>
       <c r="K26" t="str">
-        <v>骨粗鬆症,肝機能</v>
+        <v>腎機能</v>
       </c>
       <c r="L26" t="str">
-        <v>ALP,アルカリホスファターゼ,骨代謝,肝機能</v>
+        <v>尿CRE,尿クレアチニン,随時尿,補正,蛋白クレアチニン比</v>
       </c>
       <c r="M26" t="str">
         <v/>
@@ -1490,40 +1490,40 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>PTH（副甲状腺ホルモン）</v>
+        <v>白血球（WBC）</v>
       </c>
       <c r="B27" t="str">
-        <v>PTH</v>
+        <v>WBC</v>
       </c>
       <c r="C27" t="str">
-        <v>10〜65 pg/mL（施設差あり）</v>
+        <v>3,300〜8,600 /μL程度（施設差あり）</v>
       </c>
       <c r="D27" t="str">
-        <v>血液中のカルシウム濃度を調節するホルモン</v>
+        <v>体を細菌やウイルスから守る免疫細胞の数で、感染や炎症、薬剤の影響を反映する</v>
       </c>
       <c r="E27" t="str">
-        <v/>
+        <v>白血球は体に入ってきた細菌やウイルスと戦う免疫細胞です。感染症や炎症があると増え、逆に一部のお薬の副作用や骨髄の働きが落ちると減ることがあります。</v>
       </c>
       <c r="F27" t="str">
-        <v>原発性・二次性副甲状腺機能亢進症（腎不全に伴うものなど）</v>
+        <v>感染症、炎症、ステロイド使用、喫煙、白血病などの血液疾患</v>
       </c>
       <c r="G27" t="str">
-        <v/>
+        <v>発熱や体の痛みなど感染症状がないか確認する</v>
       </c>
       <c r="H27" t="str">
-        <v>副甲状腺機能低下症</v>
+        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、メルカゾールなど薬剤性の無顆粒球症、再生不良性貧血、ウイルス感染</v>
       </c>
       <c r="I27" t="str">
-        <v/>
+        <v>発熱、のどの痛みなど感染症状の初期サインがないか確認する。人混みを避け、手洗い・うがいを徹底するよう伝える</v>
       </c>
       <c r="J27" t="str">
-        <v>骨粗鬆症の二次性原因（副甲状腺機能亢進症）を除外するための検査。カルシウム・リンと合わせて評価する</v>
+        <v>メルカゾール（チアマゾール）は無顆粒球症の重大な副作用があり、発熱・のどの痛みが出たらすぐ受診するよう指導する。抗がん剤・免疫抑制剤・抗てんかん薬（カルバマゼピンなど）使用中も定期的なモニタリングが必要</v>
       </c>
       <c r="K27" t="str">
-        <v>骨粗鬆症</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L27" t="str">
-        <v>PTH,副甲状腺ホルモン,パラトルモン</v>
+        <v>白血球,WBC,好中球,感染症,白血病,無顆粒球症,骨髄抑制</v>
       </c>
       <c r="M27" t="str">
         <v/>
@@ -1531,22 +1531,22 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>カルシトニン</v>
+        <v>RDW-SD</v>
       </c>
       <c r="B28" t="str">
-        <v>CT</v>
+        <v>RDW-SD</v>
       </c>
       <c r="C28" t="str">
-        <v>男性 9.52 pg/mL未満、女性 6.40 pg/mL未満（施設差あり）</v>
+        <v>39〜46 fL程度（施設差あり）</v>
       </c>
       <c r="D28" t="str">
-        <v>血液中のカルシウムを下げる方向に働くホルモン</v>
+        <v>赤血球の大きさのばらつきを表す指標(絶対値)。鉄欠乏性貧血などの初期変化を捉えやすい</v>
       </c>
       <c r="E28" t="str">
-        <v/>
+        <v>RDW-SDは、赤血球の大きさがどれくらいバラバラになっているかを表す数値です。貧血の原因を調べる際、鉄が足りなくなり始めた早い段階での変化を捉えるのに役立ちます。</v>
       </c>
       <c r="F28" t="str">
-        <v>甲状腺髄様癌、腎不全</v>
+        <v>鉄欠乏性貧血の初期、混合性貧血（複数の原因が重なっている状態）、赤血球産生の乱れ</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1558,13 +1558,13 @@
         <v/>
       </c>
       <c r="J28" t="str">
-        <v>骨粗鬆症の二次性原因の除外目的で測定されることがある検査値。同名の薬剤（カルシトニン製剤）と混同しないよう注意</v>
+        <v>MCVが正常範囲でもRDWが上昇している場合、鉄欠乏の初期段階を示唆することがある。MCV・MCHと合わせて評価する</v>
       </c>
       <c r="K28" t="str">
-        <v>骨粗鬆症</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="L28" t="str">
-        <v>カルシトニン,CT</v>
+        <v>RDW-SD,赤血球分布幅,貧血,鉄欠乏</v>
       </c>
       <c r="M28" t="str">
         <v/>
@@ -1572,40 +1572,40 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>尿中NTX</v>
+        <v>RDW-CV</v>
       </c>
       <c r="B29" t="str">
-        <v>NTX</v>
+        <v>RDW-CV</v>
       </c>
       <c r="C29" t="str">
-        <v>施設差が大きく一律の記載が難しい（尿中）</v>
+        <v>11.5〜14.5%程度（施設差あり）</v>
       </c>
       <c r="D29" t="str">
-        <v>骨が壊されるときに出る、骨吸収マーカーのひとつ</v>
+        <v>赤血球の大きさのばらつきを割合(%)で表した指標</v>
       </c>
       <c r="E29" t="str">
-        <v/>
+        <v>RDW-CVもRDW-SDと同じく、赤血球の大きさのばらつきを表す数値ですが、こちらは割合(%)で示されます。貧血のタイプを見分ける手がかりになります。</v>
       </c>
       <c r="F29" t="str">
-        <v>骨代謝回転の亢進（骨粗鬆症、閉経後など）</v>
+        <v>鉄欠乏性貧血、ビタミンB12・葉酸欠乏性貧血、混合性貧血</v>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>骨吸収抑制薬（ビスホスホネート等）による治療効果</v>
+        <v/>
       </c>
       <c r="I29" t="str">
         <v/>
       </c>
       <c r="J29" t="str">
-        <v>治療開始後3〜6か月で再検し、薬の効果判定に使われる。TRACP-5bと同じ「骨を壊す側」の指標</v>
+        <v>RDW-SDと同様の意味を持つ指標。MCVが小さくRDWが高ければ鉄欠乏性貧血、MCVが大きくRDWが高ければビタミンB12・葉酸欠乏を疑う手がかりになる</v>
       </c>
       <c r="K29" t="str">
-        <v>骨粗鬆症</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="L29" t="str">
-        <v>NTX,尿中NTX,骨吸収マーカー</v>
+        <v>RDW-CV,赤血球分布幅,貧血,ビタミンB12,葉酸</v>
       </c>
       <c r="M29" t="str">
         <v/>
@@ -1613,40 +1613,40 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>DPD（デオキシピリジノリン）</v>
+        <v>好中球</v>
       </c>
       <c r="B30" t="str">
-        <v>DPD</v>
+        <v>Neutro,Neut%</v>
       </c>
       <c r="C30" t="str">
-        <v>施設差が大きく一律の記載が難しい（尿中）</v>
+        <v>40〜75%程度（施設差あり）</v>
       </c>
       <c r="D30" t="str">
-        <v>骨のコラーゲンが壊れるときに出る、骨吸収マーカーのひとつ</v>
+        <v>白血球の中で最も多くを占め、細菌感染と戦う主力の免疫細胞の割合</v>
       </c>
       <c r="E30" t="str">
-        <v/>
+        <v>好中球は、白血球の中で最も数が多く、細菌が体に入ってきたときに真っ先に戦ってくれる免疫細胞です。感染症や炎症があると増え、逆に薬の副作用などで減ることがあります。</v>
       </c>
       <c r="F30" t="str">
-        <v>骨代謝回転の亢進（骨粗鬆症など）</v>
+        <v>細菌感染症、炎症、ストレス、ステロイド使用</v>
       </c>
       <c r="G30" t="str">
-        <v/>
+        <v>発熱や炎症症状がないか確認する</v>
       </c>
       <c r="H30" t="str">
-        <v>骨吸収抑制薬による治療効果</v>
+        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、ウイルス感染、メルカゾールなど薬剤性の無顆粒球症</v>
       </c>
       <c r="I30" t="str">
-        <v/>
+        <v>発熱やのどの痛みなど感染症状の初期サインがないか確認する</v>
       </c>
       <c r="J30" t="str">
-        <v>NTX・CTXと同じ「骨を壊す側」の指標。食事の影響を受けにくいとされる</v>
+        <v>好中球の絶対数（好中球実数値）が500/μL未満になると重篤な感染症のリスクが高まる。割合(%)だけでなく実数値も合わせて確認する</v>
       </c>
       <c r="K30" t="str">
-        <v>骨粗鬆症</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L30" t="str">
-        <v>DPD,デオキシピリジノリン,骨吸収マーカー</v>
+        <v>好中球,Neutro,Neut,感染症,無顆粒球症</v>
       </c>
       <c r="M30" t="str">
         <v/>
@@ -1654,40 +1654,40 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>CTX</v>
+        <v>好中球実数値</v>
       </c>
       <c r="B31" t="str">
-        <v>CTX</v>
+        <v>Neutro#,ANC</v>
       </c>
       <c r="C31" t="str">
-        <v>施設差が大きく一律の記載が難しい（血清・尿中）</v>
+        <v>2,000〜7,500 /μL程度（施設差あり、白血球数×好中球%で算出）</v>
       </c>
       <c r="D31" t="str">
-        <v>骨のコラーゲンが壊れるときに出る、骨吸収マーカーのひとつ</v>
+        <v>好中球の絶対数。感染症リスクを判断する上で割合(%)より重要な指標</v>
       </c>
       <c r="E31" t="str">
-        <v/>
+        <v>これは好中球の実際の数を表す数値です。割合(%)だけでなく、実際の数がどれくらいあるかを見ることで、感染症にかかりやすい状態かどうかをより正確に判断できます。</v>
       </c>
       <c r="F31" t="str">
-        <v>骨代謝回転の亢進（骨粗鬆症など）</v>
+        <v>細菌感染症、炎症、ステロイド使用</v>
       </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>骨吸収抑制薬による治療効果</v>
+        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、メルカゾールなど薬剤性の無顆粒球症（1,000/μL未満で好中球減少症、500/μL未満で重症感染リスクが著しく上昇）</v>
       </c>
       <c r="I31" t="str">
-        <v/>
+        <v>発熱、のどの痛みなど感染症状の初期サインがないか確認する。人混みを避け、手洗い・うがいを徹底するよう伝える</v>
       </c>
       <c r="J31" t="str">
-        <v>NTX・DPDと同じ「骨を壊す側」の指標。血清・尿中いずれでも測定されることがある</v>
+        <v>抗がん剤・メルカゾール・カルバマゼピンなど骨髄抑制のリスクがある薬剤使用中は特に重視すべき数値。500/μL未満は発熱性好中球減少症のリスクが高く緊急性が高い</v>
       </c>
       <c r="K31" t="str">
-        <v>骨粗鬆症</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L31" t="str">
-        <v>CTX,骨吸収マーカー</v>
+        <v>好中球実数値,好中球数,ANC,無顆粒球症,発熱性好中球減少症</v>
       </c>
       <c r="M31" t="str">
         <v/>
@@ -1695,40 +1695,40 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>P1NP</v>
+        <v>好酸球</v>
       </c>
       <c r="B32" t="str">
-        <v>P1NP</v>
+        <v>Eosino,Eos%</v>
       </c>
       <c r="C32" t="str">
-        <v>施設差が大きく一律の記載が難しい（血清）</v>
+        <v>1〜5%程度（施設差あり）</v>
       </c>
       <c r="D32" t="str">
-        <v>骨が新しく作られるときに出る、骨形成マーカーのひとつ</v>
+        <v>アレルギー反応や寄生虫感染に関わる白血球の一種の割合</v>
       </c>
       <c r="E32" t="str">
-        <v/>
+        <v>好酸球は、アレルギー反応や寄生虫感染と関係が深い免疫細胞です。アレルギー性の病気や薬の副作用（薬疹など）で増えることがあります。</v>
       </c>
       <c r="F32" t="str">
-        <v>骨代謝回転の亢進、骨形成促進薬による治療効果</v>
+        <v>アレルギー性疾患（気管支喘息、アトピー性皮膚炎など）、薬剤アレルギー、寄生虫感染</v>
       </c>
       <c r="G32" t="str">
-        <v/>
+        <v>新しく始めた薬がないか確認する。皮疹やかゆみなどアレルギー症状の有無を確認する</v>
       </c>
       <c r="H32" t="str">
-        <v>骨形成の低下</v>
+        <v/>
       </c>
       <c r="I32" t="str">
         <v/>
       </c>
       <c r="J32" t="str">
-        <v>TRACP-5b等「骨を壊す側」の指標とは逆の、「骨を作る側」の指標。骨形成促進薬（テリパラチド等）の効果判定に使われる</v>
+        <v>薬剤性の好酸球増多は、原因薬剤の中止で改善することが多い。新規薬剤開始後の皮疹・発熱と合わせて薬剤性過敏症症候群(DIHS)を疑う材料になる</v>
       </c>
       <c r="K32" t="str">
-        <v>骨粗鬆症</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L32" t="str">
-        <v>P1NP,骨形成マーカー</v>
+        <v>好酸球,Eosino,Eos,アレルギー,薬疹,DIHS</v>
       </c>
       <c r="M32" t="str">
         <v/>
@@ -1736,25 +1736,25 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>ucOC（低カルボキシル化オステオカルシン）</v>
+        <v>好酸球実数値</v>
       </c>
       <c r="B33" t="str">
-        <v>ucOC</v>
+        <v>Eosino#</v>
       </c>
       <c r="C33" t="str">
-        <v>4.5 ng/mL未満（施設差あり）</v>
+        <v>100〜500 /μL程度（施設差あり）</v>
       </c>
       <c r="D33" t="str">
-        <v>ビタミンKが不足していないかを反映する骨の指標</v>
+        <v>好酸球の絶対数。アレルギーや薬剤反応の程度をより正確に評価できる</v>
       </c>
       <c r="E33" t="str">
-        <v/>
+        <v>これは好酸球の実際の数を表す数値です。割合(%)だけでなく実数を見ることで、アレルギー反応の強さをより正確に把握できます。</v>
       </c>
       <c r="F33" t="str">
-        <v>ビタミンK不足状態</v>
+        <v>アレルギー性疾患、薬剤アレルギー、寄生虫感染</v>
       </c>
       <c r="G33" t="str">
-        <v/>
+        <v>新しく始めた薬がないか確認する</v>
       </c>
       <c r="H33" t="str">
         <v/>
@@ -1763,13 +1763,13 @@
         <v/>
       </c>
       <c r="J33" t="str">
-        <v>ビタミンK2製剤（骨粗鬆症治療薬）の適応判断や効果判定に使われる</v>
+        <v>薬剤性過敏症症候群(DIHS)などでは著明な好酸球増多を認めることがあり、原因薬剤の特定に役立つ</v>
       </c>
       <c r="K33" t="str">
-        <v>骨粗鬆症</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L33" t="str">
-        <v>ucOC,オステオカルシン,ビタミンK</v>
+        <v>好酸球実数値,好酸球数,アレルギー,DIHS</v>
       </c>
       <c r="M33" t="str">
         <v/>
@@ -1777,22 +1777,22 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>抗甲状腺マイクロゾーム抗体（抗TPO抗体）</v>
+        <v>好塩基球</v>
       </c>
       <c r="B34" t="str">
-        <v>TPOAb</v>
+        <v>Baso,Baso%</v>
       </c>
       <c r="C34" t="str">
-        <v>陰性（16 IU/mL未満程度、施設差あり）</v>
+        <v>0〜2%程度（施設差あり）</v>
       </c>
       <c r="D34" t="str">
-        <v>自分の甲状腺を攻撃する抗体が出ていないかを見る検査</v>
+        <v>白血球の中で最も数が少なく、アレルギー反応に関わる細胞の割合</v>
       </c>
       <c r="E34" t="str">
-        <v>この検査は、体の中に自分の甲状腺を誤って攻撃してしまう抗体がないかを見るものです。陽性の場合、橋本病（慢性甲状腺炎）など甲状腺の自己免疫的な炎症が背景にある可能性があります。</v>
+        <v>好塩基球は白血球の中で最も数が少ない種類で、アレルギー反応や炎症に関わっています。数値の変動が病気の診断に直接使われることは少ない検査です。</v>
       </c>
       <c r="F34" t="str">
-        <v>橋本病（慢性甲状腺炎）、バセドウ病などの自己免疫性甲状腺疾患</v>
+        <v>慢性骨髄性白血病などの血液疾患、アレルギー性疾患、甲状腺機能低下症</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1804,13 +1804,13 @@
         <v/>
       </c>
       <c r="J34" t="str">
-        <v>陽性でも必ずしも甲状腺機能異常があるとは限らない。TSH・FT4など甲状腺ホルモンの数値と合わせて評価する</v>
+        <v>単独での臨床的意義は乏しいが、著明な増加は血液疾患（慢性骨髄性白血病等）の可能性があり他の血球指標と合わせて評価する</v>
       </c>
       <c r="K34" t="str">
-        <v>甲状腺疾患</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L34" t="str">
-        <v>抗TPO抗体,抗甲状腺マイクロゾーム抗体,TPOAb,橋本病</v>
+        <v>好塩基球,Baso,アレルギー,白血病</v>
       </c>
       <c r="M34" t="str">
         <v/>
@@ -1818,22 +1818,22 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>抗サイログロブリン抗体</v>
+        <v>好塩基球実数値</v>
       </c>
       <c r="B35" t="str">
-        <v>TgAb</v>
+        <v>Baso#</v>
       </c>
       <c r="C35" t="str">
-        <v>陰性（28 IU/mL未満程度、施設差あり）</v>
+        <v>0〜100 /μL程度（施設差あり）</v>
       </c>
       <c r="D35" t="str">
-        <v>甲状腺のたんぱく質（サイログロブリン）への抗体が出ていないかを見る検査</v>
+        <v>好塩基球の絶対数</v>
       </c>
       <c r="E35" t="str">
-        <v>この検査も、抗TPO抗体と同じく、甲状腺に対する自己免疫の有無を見るものです。あわせて調べることで橋本病などの診断の参考にします。</v>
+        <v>これは好塩基球の実際の数を表す数値です。数がとても少ない種類の血球なので、通常は大きな変動を示すことは多くありません。</v>
       </c>
       <c r="F35" t="str">
-        <v>橋本病（慢性甲状腺炎）、バセドウ病などの自己免疫性甲状腺疾患</v>
+        <v>慢性骨髄性白血病などの血液疾患、アレルギー性疾患</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1845,13 +1845,13 @@
         <v/>
       </c>
       <c r="J35" t="str">
-        <v>抗TPO抗体とあわせて測定されることが多い。単独の高値だけで治療方針が決まるわけではない</v>
+        <v>単独での臨床的意義は乏しく、他の血球指標（白血球分画全体）と合わせて評価する</v>
       </c>
       <c r="K35" t="str">
-        <v>甲状腺疾患</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L35" t="str">
-        <v>抗サイログロブリン抗体,TgAb,橋本病</v>
+        <v>好塩基球実数値,好塩基球数</v>
       </c>
       <c r="M35" t="str">
         <v/>
@@ -1859,40 +1859,40 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>TSH（甲状腺刺激ホルモン）</v>
+        <v>リンパ球</v>
       </c>
       <c r="B36" t="str">
-        <v>TSH</v>
+        <v>Lympho,Lym%</v>
       </c>
       <c r="C36" t="str">
-        <v>0.5〜5.0 μIU/mL程度（施設差あり）</v>
+        <v>18〜49%程度（施設差あり）</v>
       </c>
       <c r="D36" t="str">
-        <v>甲状腺の働きが多いか少ないかを最も敏感に反映するホルモン</v>
+        <v>ウイルス感染と戦い、免疫の記憶を担う白血球の割合</v>
       </c>
       <c r="E36" t="str">
-        <v>TSHは脳の下垂体から出て、甲状腺に「もっと働いて」と指令を送るホルモンです。甲状腺の働きが弱っていると体が指令を強めるためTSHは上がり、逆に甲状腺が働きすぎているとTSHは下がります。甲状腺の状態を最初に確認する数値としてよく使われます。</v>
+        <v>リンパ球は、ウイルスと戦ったり、一度かかった病気を記憶して免疫をつくったりする細胞です。ウイルス感染で増え、抗がん剤の副作用や強いストレスで減ることがあります。</v>
       </c>
       <c r="F36" t="str">
-        <v>甲状腺機能低下症（橋本病など）、チラーヂンSなど甲状腺ホルモン薬の量不足</v>
+        <v>ウイルス感染症、リンパ性白血病などの血液疾患、百日咳</v>
       </c>
       <c r="G36" t="str">
-        <v>だるさ、むくみ、体重増加、寒がりなどの症状がないか確認する。服薬状況（飲み忘れ、他の薬との飲み合わせ）を確認する</v>
+        <v/>
       </c>
       <c r="H36" t="str">
-        <v>甲状腺機能亢進症（バセドウ病など）、チラーヂンSなど甲状腺ホルモン薬の過量</v>
+        <v>抗がん剤・免疫抑制剤・ステロイドの使用、強いストレス、AIDSなどの免疫不全</v>
       </c>
       <c r="I36" t="str">
-        <v>動悸、体重減少、暑がり、手のふるえなどの症状がないか確認する</v>
+        <v>免疫が下がっている可能性があるため、感染予防（手洗い・うがい、人混みを避ける）を意識するよう伝える</v>
       </c>
       <c r="J36" t="str">
-        <v>チラーヂンS服用中はTSHが治療目標域に収まっているかで用量調整の目安にする。メルカゾール服用中はTSH・FT4に加えて無顆粒球症の初期症状（発熱・のどの痛み）の有無や白血球数も確認する</v>
+        <v>ステロイド・免疫抑制剤使用中はリンパ球減少による易感染性に注意。好中球と逆方向に動くことが多い（ウイルス感染ではリンパ球優位、細菌感染では好中球優位になりやすい）</v>
       </c>
       <c r="K36" t="str">
-        <v>甲状腺疾患</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L36" t="str">
-        <v>TSH,甲状腺刺激ホルモン,甲状腺機能,橋本病,バセドウ病,チラーヂン,メルカゾール</v>
+        <v>リンパ球,Lympho,Lym,ウイルス感染,免疫抑制剤,ステロイド</v>
       </c>
       <c r="M36" t="str">
         <v/>
@@ -1900,40 +1900,40 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>FT4（遊離サイロキシン）</v>
+        <v>リンパ球実数値</v>
       </c>
       <c r="B37" t="str">
-        <v>FT4</v>
+        <v>Lympho#,ALC</v>
       </c>
       <c r="C37" t="str">
-        <v>0.9〜1.7 ng/dL程度（施設差あり）</v>
+        <v>1,000〜3,600 /μL程度（施設差あり）</v>
       </c>
       <c r="D37" t="str">
-        <v>甲状腺が実際に分泌しているホルモンの量そのものを表す数値</v>
+        <v>リンパ球の絶対数。免疫力の目安として使われる</v>
       </c>
       <c r="E37" t="str">
-        <v>FT4は甲状腺そのものが作っているホルモンの量です。TSHが「指令の強さ」だとすると、FT4は「実際に出ている量」にあたります。2つをあわせて見ることで、甲状腺の働きが今どういう状態かを詳しく判断できます。</v>
+        <v>これはリンパ球の実際の数を表す数値です。免疫力の目安の一つとして使われ、抗がん剤や免疫抑制剤の副作用モニタリングにも用いられます。</v>
       </c>
       <c r="F37" t="str">
-        <v>甲状腺機能亢進症（バセドウ病など）</v>
+        <v>ウイルス感染症、リンパ性白血病などの血液疾患</v>
       </c>
       <c r="G37" t="str">
-        <v>動悸、体重減少、暑がり、手のふるえなどの症状がないか確認する</v>
+        <v/>
       </c>
       <c r="H37" t="str">
-        <v>甲状腺機能低下症（橋本病など）</v>
+        <v>抗がん剤・免疫抑制剤・ステロイドの使用、強いストレス、AIDSなどの免疫不全</v>
       </c>
       <c r="I37" t="str">
-        <v>だるさ、むくみ、体重増加、寒がりなどの症状がないか確認する</v>
+        <v>感染予防（手洗い・うがい、人混みを避ける）を意識するよう伝える</v>
       </c>
       <c r="J37" t="str">
-        <v>TSHと逆方向に動くのが基本だが、下垂体性の異常など例外もある。TSHと合わせて評価し、片方だけで判断しない</v>
+        <v>免疫抑制剤・抗がん剤治療中のモニタリング指標としても使われる。著明な低下時は日和見感染のリスクが高まる</v>
       </c>
       <c r="K37" t="str">
-        <v>甲状腺疾患</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L37" t="str">
-        <v>FT4,遊離サイロキシン,甲状腺ホルモン,甲状腺機能</v>
+        <v>リンパ球実数値,リンパ球数,ALC,免疫抑制剤,日和見感染</v>
       </c>
       <c r="M37" t="str">
         <v/>
@@ -1941,40 +1941,40 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>血小板（Plt）</v>
+        <v>単球</v>
       </c>
       <c r="B38" t="str">
-        <v>Plt</v>
+        <v>Mono,Mono%</v>
       </c>
       <c r="C38" t="str">
-        <v>15.0〜35.0万/μL程度（施設差あり）</v>
+        <v>2〜10%程度（施設差あり）</v>
       </c>
       <c r="D38" t="str">
-        <v>出血を止める働きをする血液成分で、少なすぎると出血しやすくなる</v>
+        <v>感染や炎症の後始末をする白血球の一種の割合</v>
       </c>
       <c r="E38" t="str">
-        <v>血小板は、血管が傷ついたときに集まって血を止める役割をする血液の成分です。数が少ないとあざができやすくなったり、出血が止まりにくくなったりします。抗血小板薬や抗がん剤を使っている方では、定期的にチェックすることが大切です。</v>
+        <v>単球は、細菌などを取り込んで処理したり、組織の修復に関わったりする免疫細胞です。慢性的な炎症や感染症の回復期に増えることがあります。</v>
       </c>
       <c r="F38" t="str">
-        <v>炎症性疾患、鉄欠乏性貧血、脾摘後、骨髄増殖性疾患</v>
+        <v>慢性感染症（結核など）、炎症性疾患、血液疾患、感染症の回復期</v>
       </c>
       <c r="G38" t="str">
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、肝硬変・脾機能亢進、再生不良性貧血、抗てんかん薬（バルプロ酸など）の副作用、ITP（特発性血小板減少性紫斑病）</v>
+        <v/>
       </c>
       <c r="I38" t="str">
-        <v>あざができやすい、歯ぐきや鼻からの出血が増えていないか確認する。強い運動や転倒によるけがに注意するよう伝える</v>
+        <v/>
       </c>
       <c r="J38" t="str">
-        <v>抗血小板薬・抗凝固薬使用中に血小板減少があると出血リスクがさらに高まる。抗がん剤・バルプロ酸・カルバマゼピンなど骨髄抑制のリスクがある薬剤使用中は定期採血の実施状況を確認する</v>
+        <v>単独での臨床的意義は乏しく、他の血球指標や炎症マーカー(CRPなど)と合わせて評価する</v>
       </c>
       <c r="K38" t="str">
-        <v>てんかん,抗血小板療法</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L38" t="str">
-        <v>血小板,Plt,platelet,出血,あざ,紫斑,骨髄抑制</v>
+        <v>単球,Mono,慢性感染症,結核,炎症</v>
       </c>
       <c r="M38" t="str">
         <v/>
@@ -1982,40 +1982,40 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>PT-INR（プロトロンビン時間国際標準比）</v>
+        <v>単球実数値</v>
       </c>
       <c r="B39" t="str">
-        <v>PT-INR,INR</v>
+        <v>Mono#</v>
       </c>
       <c r="C39" t="str">
-        <v>治療域の目安 1.6〜3.0（ワルファリン服用時。年齢・疾患により異なる）</v>
+        <v>200〜600 /μL程度（施設差あり）</v>
       </c>
       <c r="D39" t="str">
-        <v>血液の固まりやすさを表す数値で、ワルファリンの効き具合を確認するために使う</v>
+        <v>単球の絶対数</v>
       </c>
       <c r="E39" t="str">
-        <v>PT-INRは血液が固まるまでの時間をもとにした数値で、ワルファリンというお薬を飲んでいる方の効き具合を確認するために測ります。数値が高いほど血液が固まりにくく出血しやすい状態、低いほど血栓ができやすい状態を示します。</v>
+        <v>これは単球の実際の数を表す数値です。慢性的な炎症や感染症の状態を把握する材料の一つになります。</v>
       </c>
       <c r="F39" t="str">
-        <v>ワルファリンの効きすぎ、肝機能低下、ビタミンK不足、納豆・青汁など摂取量の変化</v>
+        <v>慢性感染症、炎症性疾患、血液疾患</v>
       </c>
       <c r="G39" t="str">
-        <v>歯ぐきや鼻からの出血、あざ、黒い便などの出血症状がないか確認する。納豆・クロレラ・青汁などビタミンKを多く含む食品の摂取状況を確認する</v>
+        <v/>
       </c>
       <c r="H39" t="str">
-        <v>ワルファリンの効き不足、飲み忘れ、ビタミンK摂取量の急激な増加</v>
+        <v/>
       </c>
       <c r="I39" t="str">
-        <v>服薬状況（飲み忘れ）を確認する。片側のむくみ・しびれ・胸痛など血栓症状がないか確認する</v>
+        <v/>
       </c>
       <c r="J39" t="str">
-        <v>治療域は疾患・年齢によって異なる（例：非弁膜症性心房細動の高齢者では1.6〜2.6が目安になることが多い）。多くの薬剤・食品と相互作用があるため新規薬剤追加時は必ず確認する。DOAC（エリキュース、リクシアナ、プラザキサなど）ではPT-INRのモニタリングは不要</v>
+        <v>単独での臨床的意義は乏しく、他の血球指標と合わせて評価する</v>
       </c>
       <c r="K39" t="str">
-        <v>抗凝固療法（心房細動・血栓症）</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L39" t="str">
-        <v>PT-INR,INR,プロトロンビン時間,ワルファリン,ワーファリン,抗凝固</v>
+        <v>単球実数値,単球数</v>
       </c>
       <c r="M39" t="str">
         <v/>
@@ -2023,40 +2023,40 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>血中薬物濃度（TDM）</v>
+        <v>ヘモグロビン濃度</v>
       </c>
       <c r="B40" t="str">
-        <v>TDM</v>
+        <v>Hb</v>
       </c>
       <c r="C40" t="str">
-        <v>薬剤ごとに有効域が異なる（例：カルバマゼピン 4〜12 μg/mL、バルプロ酸 40〜100 μg/mL、フェニトイン 10〜20 μg/mL）</v>
+        <v>男性 13.5〜17.5 g/dL、女性 11.5〜15.0 g/dL</v>
       </c>
       <c r="D40" t="str">
-        <v>治療域が狭い薬剤で、血液中の薬の濃度が効果域・中毒域のどちらにあるかを確認する検査</v>
+        <v>血液の中で酸素を運ぶ役割をしている。この値が低い状態が貧血。</v>
       </c>
       <c r="E40" t="str">
-        <v>この薬は効く量と副作用が出る量が近いため、血液中の薬の濃度を定期的に測って、ちょうどよい範囲に入っているかを確認します。数値が低いと効果が不十分になり、高いと副作用が出やすくなります。</v>
+        <v>血の数値が良くなっても、体の中の鉄はまだ十分ではないことがあります。そのため、しばらく続けて飲むことが大切です。</v>
       </c>
       <c r="F40" t="str">
-        <v>過量投与、代謝を妨げる薬剤との併用、肝機能低下による代謝低下</v>
+        <v/>
       </c>
       <c r="G40" t="str">
-        <v>ふらつき、眠気、めまい、物が二重に見えるなどの中毒症状がないか確認する</v>
+        <v/>
       </c>
       <c r="H40" t="str">
-        <v>飲み忘れ、自己判断による減量、代謝を促進する薬剤との併用（相互作用）</v>
+        <v>鉄欠乏性貧血、出血、腎性貧血、骨髄の造血機能低下</v>
       </c>
       <c r="I40" t="str">
-        <v>発作やてんかん症状の再発がないか確認し、飲み忘れがないか一緒に確認する</v>
+        <v>鉄分の多い食品（レバー・赤身肉・魚・ほうれん草など）を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える</v>
       </c>
       <c r="J40" t="str">
-        <v>採血のタイミング（トラフ値かどうか）で数値の解釈が変わるため採血時点を確認する。カルバマゼピンは自己誘導により長期使用で濃度が下がることがある点にも注意</v>
+        <v>原因（出血・食事量低下など）の確認が重要。腎機能低下がある場合は鉄不足以外が原因のこともある。鉄剤はヘモグロビンが正常化した後も2〜3か月程度は継続することが多い（鉄の貯蔵分を補うため。途中でやめると再び貧血になりやすい）</v>
       </c>
       <c r="K40" t="str">
-        <v>てんかん</v>
+        <v>鉄欠乏性貧血,抗血小板療法,抗凝固療法（心房細動・血栓症）</v>
       </c>
       <c r="L40" t="str">
-        <v>TDM,血中薬物濃度,治療域,中毒域,カルバマゼピン,フェニトイン,バルプロ酸,抗てんかん薬</v>
+        <v>ヘモグロビン,Hb,貧血,鉄剤,鉄欠乏性貧血</v>
       </c>
       <c r="M40" t="str">
         <v/>
@@ -2064,40 +2064,40 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ヘモグロビン</v>
+        <v>ヘマトクリット値</v>
       </c>
       <c r="B41" t="str">
-        <v>Hb</v>
+        <v>Ht,Hct</v>
       </c>
       <c r="C41" t="str">
-        <v>男性 13.5〜17.5 g/dL、女性 11.5〜15.0 g/dL</v>
+        <v>男性 40〜50%、女性 35〜45%</v>
       </c>
       <c r="D41" t="str">
-        <v>血液の中で酸素を運ぶ役割をしている。この値が低い状態が貧血。</v>
+        <v>血液全体のうち赤血球が占める体積の割合。貧血・脱水の指標</v>
       </c>
       <c r="E41" t="str">
-        <v>血の数値が良くなっても、体の中の鉄はまだ十分ではないことがあります。そのため、しばらく続けて飲むことが大切です。</v>
+        <v>ヘマトクリットは、血液全体のうち赤血球が占める割合を表す数値です。この値が低いと貧血、高いと脱水や血液が濃くなっている状態が疑われます。</v>
       </c>
       <c r="F41" t="str">
-        <v/>
+        <v>脱水、多血症（真性多血症、二次性多血症）、喫煙</v>
       </c>
       <c r="G41" t="str">
-        <v/>
+        <v>脱水が疑われる場合はこまめな水分摂取を勧める（水分制限がある場合を除く）</v>
       </c>
       <c r="H41" t="str">
-        <v>鉄欠乏性貧血、出血、腎性貧血、骨髄の造血機能低下</v>
+        <v>貧血（鉄欠乏性貧血、腎性貧血など）、出血</v>
       </c>
       <c r="I41" t="str">
-        <v>鉄分の多い食品（レバー・赤身肉・魚・ほうれん草など）を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える</v>
+        <v>ヘモグロビンと同様に、出血や食事量低下がないか確認する</v>
       </c>
       <c r="J41" t="str">
-        <v>原因（出血・食事量低下など）の確認が重要。腎機能低下がある場合は鉄不足以外が原因のこともある。鉄剤はヘモグロビンが正常化した後も2〜3か月程度は継続することが多い（鉄の貯蔵分を補うため。途中でやめると再び貧血になりやすい）</v>
+        <v>ヘモグロビン・赤血球数と合わせて評価する。3つの値は同じ方向に動くことが多く、脱水があると貧血が見かけ上隠れることがある</v>
       </c>
       <c r="K41" t="str">
-        <v>鉄欠乏性貧血,抗血小板療法,抗凝固療法（心房細動・血栓症）</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="L41" t="str">
-        <v>ヘモグロビン,Hb,貧血,鉄剤,鉄欠乏性貧血</v>
+        <v>ヘマトクリット,Ht,Hct,貧血,脱水,多血症</v>
       </c>
       <c r="M41" t="str">
         <v/>
@@ -2105,40 +2105,40 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>骨型酒石酸抵抗性フォスファターゼ（TRACP-5b）</v>
+        <v>MCV</v>
       </c>
       <c r="B42" t="str">
-        <v>TRACP-5b</v>
+        <v>MCV</v>
       </c>
       <c r="C42" t="str">
-        <v>120〜420 mU/dL</v>
+        <v>79〜100 fL</v>
       </c>
       <c r="D42" t="str">
-        <v>骨がどれくらい壊されているかを見る検査。骨は「古い骨を壊して新しい骨を作る」入れ替えを繰り返しており、骨を壊す細胞が活発だとこの物質が血液中に増える。</v>
+        <v>赤血球1個の大きさ</v>
       </c>
       <c r="E42" t="str">
-        <v>この検査は、骨がどれくらい早く減っていないかを見るものです。数値が高いと、骨が弱くなりやすい状態の目安になります。</v>
+        <v/>
       </c>
       <c r="F42" t="str">
-        <v>骨粗鬆症、骨代謝回転（骨がこわれるスピード）が活発な状態</v>
+        <v/>
       </c>
       <c r="G42" t="str">
-        <v>カルシウム・ビタミンDの摂取や、適度な荷重運動（ウォーキングなど）を意識するよう伝える</v>
+        <v/>
       </c>
       <c r="H42" t="str">
-        <v/>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="I42" t="str">
-        <v/>
+        <v>鉄分の多い食事を意識する（ヘモグロビンの項目を参照）</v>
       </c>
       <c r="J42" t="str">
-        <v>「骨を壊す側」の指標。「骨を作る側」の検査と合わせて評価する。数値だけで診断はしない</v>
+        <v/>
       </c>
       <c r="K42" t="str">
-        <v>骨粗鬆症</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="L42" t="str">
-        <v>TRACP-5b,骨型酒石酸抵抗性フォスファターゼ,骨粗鬆症,骨代謝</v>
+        <v>MCV,赤血球指数,貧血</v>
       </c>
       <c r="M42" t="str">
         <v/>
@@ -2146,40 +2146,40 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>カルシウム（Ca）</v>
+        <v>MCH</v>
       </c>
       <c r="B43" t="str">
-        <v>Ca</v>
+        <v>MCH</v>
       </c>
       <c r="C43" t="str">
-        <v>8.5〜10.0 mg/dL</v>
+        <v>26.3〜34.3 pg</v>
       </c>
       <c r="D43" t="str">
-        <v/>
+        <v>赤血球1個に含まれるヘモグロビン量</v>
       </c>
       <c r="E43" t="str">
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>副甲状腺機能亢進症</v>
+        <v/>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v/>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="I43" t="str">
-        <v/>
+        <v>鉄分の多い食事を意識する（ヘモグロビンの項目を参照）</v>
       </c>
       <c r="J43" t="str">
         <v/>
       </c>
       <c r="K43" t="str">
-        <v>電解質,骨粗鬆症</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="L43" t="str">
-        <v>カルシウム,Ca,電解質</v>
+        <v>MCH,赤血球指数,貧血</v>
       </c>
       <c r="M43" t="str">
         <v/>
@@ -2187,40 +2187,40 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>CK（クレアチンキナーゼ）</v>
+        <v>MCHC</v>
       </c>
       <c r="B44" t="str">
-        <v>CK,CPK</v>
+        <v>MCHC</v>
       </c>
       <c r="C44" t="str">
-        <v>男性 60〜250 U/L、女性 50〜170 U/L</v>
+        <v>31.6〜36.6 %</v>
       </c>
       <c r="D44" t="str">
-        <v/>
+        <v>単位容積あたりの赤血球に含まれるヘモグロビン濃度</v>
       </c>
       <c r="E44" t="str">
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>心筋梗塞、横紋筋融解症などで上昇</v>
+        <v/>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v/>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="I44" t="str">
-        <v/>
+        <v>鉄分の多い食事を意識する（ヘモグロビンの項目を参照）</v>
       </c>
       <c r="J44" t="str">
         <v/>
       </c>
       <c r="K44" t="str">
-        <v/>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="L44" t="str">
-        <v>CK,CPK,クレアチンキナーゼ,横紋筋融解症</v>
+        <v>MCHC,赤血球指数,貧血</v>
       </c>
       <c r="M44" t="str">
         <v/>
@@ -2228,40 +2228,40 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>中性脂肪（トリグリセリド）</v>
+        <v>血小板数</v>
       </c>
       <c r="B45" t="str">
-        <v>TG</v>
+        <v>Plt</v>
       </c>
       <c r="C45" t="str">
-        <v>150 mg/dL未満（空腹時）</v>
+        <v>15.0〜35.0万/μL程度（施設差あり）</v>
       </c>
       <c r="D45" t="str">
-        <v/>
+        <v>出血を止める働きをする血液成分で、少なすぎると出血しやすくなる</v>
       </c>
       <c r="E45" t="str">
-        <v/>
+        <v>血小板は、血管が傷ついたときに集まって血を止める役割をする血液の成分です。数が少ないとあざができやすくなったり、出血が止まりにくくなったりします。抗血小板薬や抗がん剤を使っている方では、定期的にチェックすることが大切です。</v>
       </c>
       <c r="F45" t="str">
-        <v>脂質異常症</v>
+        <v>炎症性疾患、鉄欠乏性貧血、脾摘後、骨髄増殖性疾患</v>
       </c>
       <c r="G45" t="str">
-        <v>糖質・アルコールの摂りすぎに注意し、有酸素運動を勧める</v>
+        <v/>
       </c>
       <c r="H45" t="str">
-        <v/>
+        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、肝硬変・脾機能亢進、再生不良性貧血、抗てんかん薬（バルプロ酸など）の副作用、ITP（特発性血小板減少性紫斑病）</v>
       </c>
       <c r="I45" t="str">
-        <v/>
+        <v>あざができやすい、歯ぐきや鼻からの出血が増えていないか確認する。強い運動や転倒によるけがに注意するよう伝える</v>
       </c>
       <c r="J45" t="str">
-        <v/>
+        <v>抗血小板薬・抗凝固薬使用中に血小板減少があると出血リスクがさらに高まる。抗がん剤・バルプロ酸・カルバマゼピンなど骨髄抑制のリスクがある薬剤使用中は定期採血の実施状況を確認する</v>
       </c>
       <c r="K45" t="str">
-        <v>脂質異常症</v>
+        <v>てんかん,抗血小板療法</v>
       </c>
       <c r="L45" t="str">
-        <v>中性脂肪,トリグリセリド,TG,脂質異常症</v>
+        <v>血小板,Plt,platelet,出血,あざ,紫斑,骨髄抑制</v>
       </c>
       <c r="M45" t="str">
         <v/>
@@ -2269,40 +2269,40 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>HDLコレステロール</v>
+        <v>尿pH</v>
       </c>
       <c r="B46" t="str">
-        <v>HDL-C</v>
+        <v>尿pH</v>
       </c>
       <c r="C46" t="str">
-        <v>40 mg/dL以上</v>
+        <v>4.5〜7.5程度（弱酸性が多い）</v>
       </c>
       <c r="D46" t="str">
-        <v/>
+        <v>尿の酸性・アルカリ性の度合い。食事や感染症、体の状態を反映する</v>
       </c>
       <c r="E46" t="str">
-        <v/>
+        <v>尿のpHは酸性・アルカリ性のバランスを表します。食事の内容や感染症、体の代謝状態によって変化します。単独で大きな問題を示すことは少ない検査です。</v>
       </c>
       <c r="F46" t="str">
-        <v/>
+        <v>尿路感染症（尿素分解菌によるもの）、野菜中心の食事、過換気</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>脂質異常症（低HDL血症）</v>
+        <v>高たんぱく食、糖尿病性ケトアシドーシス、痛風発作時（酸性尿は尿酸結石のリスクを高める）</v>
       </c>
       <c r="I46" t="str">
-        <v>適度な運動習慣、禁煙を勧める</v>
+        <v>痛風・尿酸結石がある場合は、野菜など尿をアルカリ化する食品を意識するとよいことを伝える</v>
       </c>
       <c r="J46" t="str">
-        <v/>
+        <v>高尿酸血症・尿酸結石の患者では尿pHが酸性に傾いていないか確認する。尿アルカリ化薬（ウラリットなど）の効果判定にも使う</v>
       </c>
       <c r="K46" t="str">
-        <v>脂質異常症</v>
+        <v>高尿酸血症</v>
       </c>
       <c r="L46" t="str">
-        <v>HDL,HDLコレステロール,善玉コレステロール,脂質異常症</v>
+        <v>尿pH,尿酸性度,尿アルカリ化,ウラリット</v>
       </c>
       <c r="M46" t="str">
         <v/>
@@ -2310,40 +2310,40 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>総コレステロール</v>
+        <v>ウロビリノーゲン</v>
       </c>
       <c r="B47" t="str">
-        <v>TC,T-cho</v>
+        <v>Uro</v>
       </c>
       <c r="C47" t="str">
-        <v>220 mg/dL未満</v>
+        <v>正常（±）程度</v>
       </c>
       <c r="D47" t="str">
-        <v/>
+        <v>肝臓や胆道、赤血球の壊れ方の状態を反映する尿検査項目</v>
       </c>
       <c r="E47" t="str">
-        <v/>
+        <v>ウロビリノーゲンは、赤血球やビリルビンが体の中で処理される過程でできる物質です。肝臓の働きが悪くなったり、赤血球が壊れやすくなったりすると、尿の中の量が変化します。</v>
       </c>
       <c r="F47" t="str">
-        <v>脂質異常症</v>
+        <v>溶血性疾患（赤血球の破壊亢進）、肝機能障害</v>
       </c>
       <c r="G47" t="str">
-        <v>動物性脂肪を控え、食物繊維を増やすよう伝える</v>
+        <v/>
       </c>
       <c r="H47" t="str">
-        <v/>
+        <v>胆道閉塞（胆汁が腸に流れず、ウロビリノーゲンが作られない状態）</v>
       </c>
       <c r="I47" t="str">
         <v/>
       </c>
       <c r="J47" t="str">
-        <v/>
+        <v>完全に陰性の場合は胆道閉塞を疑う所見の一つ。肝機能（AST/ALT/ビリルビン）と合わせて評価する</v>
       </c>
       <c r="K47" t="str">
-        <v>脂質異常症</v>
+        <v>肝機能</v>
       </c>
       <c r="L47" t="str">
-        <v>総コレステロール,TC,コレステロール,脂質異常症</v>
+        <v>ウロビリノーゲン,Uro,溶血,胆道閉塞,肝機能</v>
       </c>
       <c r="M47" t="str">
         <v/>
@@ -2351,40 +2351,40 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>MCV</v>
+        <v>尿ケトン体</v>
       </c>
       <c r="B48" t="str">
-        <v>MCV</v>
+        <v>尿ケトン,Ket</v>
       </c>
       <c r="C48" t="str">
-        <v>79〜100 fL</v>
+        <v>陰性（－）</v>
       </c>
       <c r="D48" t="str">
-        <v>赤血球1個の大きさ</v>
+        <v>体がブドウ糖の代わりに脂肪を分解してエネルギーを作っているサイン</v>
       </c>
       <c r="E48" t="str">
-        <v/>
+        <v>この検査は、体が糖の代わりに脂肪を使ってエネルギーを作っていないかを見るものです。陽性が続くときは、食事や水分、インスリンの使い方を確認する必要があります。</v>
       </c>
       <c r="F48" t="str">
-        <v/>
+        <v>糖尿病の血糖コントロール不良（シックデイ・インスリン不足）、極端な糖質制限、絶食、嘔吐・下痢による脱水</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v/>
       </c>
       <c r="I48" t="str">
-        <v>鉄分の多い食事を意識する（ヘモグロビンの項目を参照）</v>
+        <v/>
       </c>
       <c r="J48" t="str">
-        <v/>
+        <v>陽性かつ高血糖・全身倦怠感が強い場合は糖尿病性ケトアシドーシスの可能性があり緊急性が高い。シックデイルールの説明歴を確認する</v>
       </c>
       <c r="K48" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>糖尿病</v>
       </c>
       <c r="L48" t="str">
-        <v>MCV,赤血球指数,貧血</v>
+        <v>尿ケトン体,ケトン体,Ket,シックデイ,ケトアシドーシス</v>
       </c>
       <c r="M48" t="str">
         <v/>
@@ -2392,40 +2392,40 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>MCH</v>
+        <v>尿潜血反応</v>
       </c>
       <c r="B49" t="str">
-        <v>MCH</v>
+        <v>尿潜血,U-OB</v>
       </c>
       <c r="C49" t="str">
-        <v>26.3〜34.3 pg</v>
+        <v>陰性（－）</v>
       </c>
       <c r="D49" t="str">
-        <v>赤血球1個に含まれるヘモグロビン量</v>
+        <v>尿に血液（赤血球）が混じっていないかを見る検査</v>
       </c>
       <c r="E49" t="str">
-        <v/>
+        <v>この検査は、尿に目に見えないくらいの微量の血液が混じっていないかを調べるものです。陽性の場合、腎臓や膀胱、尿路のどこかに炎症や結石などがある可能性があります。</v>
       </c>
       <c r="F49" t="str">
-        <v/>
+        <v>尿路結石、膀胱炎などの尿路感染症、腎炎、腫瘍、月経血の混入、激しい運動後</v>
       </c>
       <c r="G49" t="str">
-        <v/>
+        <v>排尿時の痛みや頻尿、目に見える血尿の有無を確認する。女性は月経の時期と重なっていないか確認する</v>
       </c>
       <c r="H49" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v/>
       </c>
       <c r="I49" t="str">
-        <v>鉄分の多い食事を意識する（ヘモグロビンの項目を参照）</v>
+        <v/>
       </c>
       <c r="J49" t="str">
-        <v/>
+        <v>陽性でも尿沈渣で赤血球が確認されない場合は偽陽性（ミオグロビン尿など）のこともある。持続する場合は泌尿器科的な精査が必要</v>
       </c>
       <c r="K49" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>腎機能</v>
       </c>
       <c r="L49" t="str">
-        <v>MCH,赤血球指数,貧血</v>
+        <v>尿潜血,潜血反応,U-OB,血尿,尿路結石,膀胱炎</v>
       </c>
       <c r="M49" t="str">
         <v/>
@@ -2433,40 +2433,40 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>MCHC</v>
+        <v>尿糖（半定量）</v>
       </c>
       <c r="B50" t="str">
-        <v>MCHC</v>
+        <v>尿糖,U-Glu</v>
       </c>
       <c r="C50" t="str">
-        <v>31.6〜36.6 %</v>
+        <v>陰性（－）</v>
       </c>
       <c r="D50" t="str">
-        <v>単位容積あたりの赤血球に含まれるヘモグロビン濃度</v>
+        <v>尿に糖が漏れ出ていないかを見る検査。血糖値がかなり高いと陽性になる</v>
       </c>
       <c r="E50" t="str">
-        <v/>
+        <v>通常、糖は尿にはほとんど出ませんが、血糖値がかなり高くなると尿にあふれ出るようになります。血糖コントロールの目安の一つです。</v>
       </c>
       <c r="F50" t="str">
-        <v/>
+        <v>糖尿病（血糖値が腎臓で再吸収できる量を超えている状態）、腎性糖尿（血糖値が正常でも体質的に出ることがある）、SGLT2阻害薬服用中（薬の作用で意図的に糖を排泄するため陽性になるのが正常）</v>
       </c>
       <c r="G50" t="str">
-        <v/>
+        <v>SGLT2阻害薬（フォシーガ、ジャディアンスなど）服用中は、陽性が薬の効果によるものであることを説明する。脱水や尿路感染の症状がないかも確認する</v>
       </c>
       <c r="H50" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v/>
       </c>
       <c r="I50" t="str">
-        <v>鉄分の多い食事を意識する（ヘモグロビンの項目を参照）</v>
+        <v/>
       </c>
       <c r="J50" t="str">
-        <v/>
+        <v>SGLT2阻害薬服用中は尿糖陽性が治療効果として想定内であることを患者に伝える。血糖値・HbA1cと合わせて評価する</v>
       </c>
       <c r="K50" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>糖尿病</v>
       </c>
       <c r="L50" t="str">
-        <v>MCHC,赤血球指数,貧血</v>
+        <v>尿糖,糖半定量,U-Glu,腎性糖尿,SGLT2</v>
       </c>
       <c r="M50" t="str">
         <v/>
@@ -2474,25 +2474,25 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>アミラーゼ（AMY）</v>
+        <v>尿蛋白定量（随時尿）</v>
       </c>
       <c r="B51" t="str">
-        <v>AMY</v>
+        <v>U-Pro定量,蛋白/Cr比</v>
       </c>
       <c r="C51" t="str">
-        <v/>
+        <v>0.15 g/gCr未満</v>
       </c>
       <c r="D51" t="str">
-        <v/>
+        <v>随時尿から尿蛋白の量を具体的な数値として評価する検査。ネフローゼ等の重症度判定に使う</v>
       </c>
       <c r="E51" t="str">
-        <v/>
+        <v>これは、尿に出ているたんぱくの量を具体的な数値で見る検査です。試験紙での陽性・陰性の判定だけでなく、実際にどれくらいの量が出ているかを把握できます。</v>
       </c>
       <c r="F51" t="str">
-        <v>急性膵炎</v>
+        <v>腎症の進行（糖尿病性腎症、慢性腎臓病など）、ネフローゼ症候群（3.5 g/gCr以上が目安）</v>
       </c>
       <c r="G51" t="str">
-        <v>飲酒を控える、脂っこい食事を避けるよう伝える</v>
+        <v/>
       </c>
       <c r="H51" t="str">
         <v/>
@@ -2501,13 +2501,13 @@
         <v/>
       </c>
       <c r="J51" t="str">
-        <v/>
+        <v>CKD診療ガイドラインの重症度分類（尿蛋白量による区分）にも使われる定量指標。試験紙法の半定量結果より治療効果判定に適する</v>
       </c>
       <c r="K51" t="str">
-        <v/>
+        <v>腎機能,糖尿病</v>
       </c>
       <c r="L51" t="str">
-        <v>アミラーゼ,AMY,膵炎,急性膵炎</v>
+        <v>尿蛋白,随時尿,定量,蛋白クレアチニン比,ネフローゼ</v>
       </c>
       <c r="M51" t="str">
         <v/>
@@ -2515,40 +2515,40 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>間接ビリルビン</v>
+        <v>アルブミン</v>
       </c>
       <c r="B52" t="str">
-        <v>I-Bil</v>
+        <v>Alb</v>
       </c>
       <c r="C52" t="str">
-        <v/>
+        <v>3.8〜5.2 g/dL</v>
       </c>
       <c r="D52" t="str">
-        <v/>
+        <v>体の栄養状態を見る目安になるたんぱく質。血液の中で栄養を運ぶ、水分を血管の中に保つという働きをしている。</v>
       </c>
       <c r="E52" t="str">
-        <v/>
+        <v>アルブミンは栄養の状態を見る数値です。食事量が少なかったり、肝臓や腎臓、腸の働きが弱ると下がることがあります。数値が低いと、むくみが出やすくなります。</v>
       </c>
       <c r="F52" t="str">
-        <v>血液型不適合輸血などによる溶血</v>
+        <v>脱水（見かけ上の上昇）</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v/>
+        <v>低栄養／肝機能低下／ネフローゼ症候群／クローン病</v>
       </c>
       <c r="I52" t="str">
-        <v/>
+        <v>主食に偏らず、肉・魚・卵・大豆製品などたんぱく質をしっかり摂るよう伝える。食欲が落ちている場合は少量頻回の食事も提案する</v>
       </c>
       <c r="J52" t="str">
-        <v/>
+        <v>3前半は注意ライン。食事摂取量を必ず確認</v>
       </c>
       <c r="K52" t="str">
-        <v/>
+        <v>肝機能,栄養,腎機能</v>
       </c>
       <c r="L52" t="str">
-        <v>間接ビリルビン,I-Bil,溶血</v>
+        <v>アルブミン,Alb,むくみ,浮腫,栄養状態</v>
       </c>
       <c r="M52" t="str">
         <v/>
@@ -2556,40 +2556,40 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>直接ビリルビン</v>
+        <v>BNP</v>
       </c>
       <c r="B53" t="str">
-        <v>D-Bil</v>
+        <v>BNP</v>
       </c>
       <c r="C53" t="str">
-        <v/>
+        <v>18.4 pg/mL以下</v>
       </c>
       <c r="D53" t="str">
-        <v/>
+        <v>心臓が無理をしているときに出る物質。心臓は血液を送るポンプだが、負担がかかると「少し助けてほしい」というサインとしてBNPを血液中に出す。</v>
       </c>
       <c r="E53" t="str">
-        <v/>
+        <v>この検査は、心臓がどれくらい頑張りすぎていないかを見るものです。数値が高いと、心臓に少し負担がかかっているサインになります。</v>
       </c>
       <c r="F53" t="str">
-        <v>肝疾患、胆石など胆道の閉塞</v>
+        <v>心不全、心臓に負担がかかっている状態、体に水分がたまりやすいとき</v>
       </c>
       <c r="G53" t="str">
-        <v/>
+        <v>塩分・水分の摂りすぎに注意し、体重の変化を毎日記録するよう伝える</v>
       </c>
       <c r="H53" t="str">
-        <v/>
+        <v>心臓の負担は少ない状態</v>
       </c>
       <c r="I53" t="str">
         <v/>
       </c>
       <c r="J53" t="str">
-        <v/>
+        <v>腎機能が低いとBNPは高めに出ることがある／数値だけで判断せず、症状と合わせて評価する／息切れ、むくみ、体重増加があれば要注意</v>
       </c>
       <c r="K53" t="str">
-        <v>肝機能</v>
+        <v>心不全</v>
       </c>
       <c r="L53" t="str">
-        <v>直接ビリルビン,D-Bil,胆石,胆道閉塞</v>
+        <v>BNP,心不全,息切れ,むくみ</v>
       </c>
       <c r="M53" t="str">
         <v/>
@@ -2597,40 +2597,40 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>白血球（WBC）</v>
+        <v>血清CPR（Cペプチド）</v>
       </c>
       <c r="B54" t="str">
-        <v>WBC</v>
+        <v>CPR</v>
       </c>
       <c r="C54" t="str">
-        <v>3,300〜8,600 /μL程度（施設差あり）</v>
+        <v>空腹時 0.6〜3.0 ng/mL（施設差あり）</v>
       </c>
       <c r="D54" t="str">
-        <v>体を細菌やウイルスから守る免疫細胞の数で、感染や炎症、薬剤の影響を反映する</v>
+        <v>自分の膵臓がどれくらいインスリンを作れているかを表す指標</v>
       </c>
       <c r="E54" t="str">
-        <v>白血球は体に入ってきた細菌やウイルスと戦う免疫細胞です。感染症や炎症があると増え、逆に一部のお薬の副作用や骨髄の働きが落ちると減ることがあります。</v>
+        <v>この検査は、ご自身の膵臓がどれくらいインスリンを作る力を持っているかを見るものです。数値が低いほど、体の中で作れるインスリンが少ないことを示します。</v>
       </c>
       <c r="F54" t="str">
-        <v>感染症、炎症、ステロイド使用、喫煙、白血病などの血液疾患</v>
+        <v>インスリン抵抗性が強い状態（初期の2型糖尿病など）</v>
       </c>
       <c r="G54" t="str">
-        <v>発熱や体の痛みなど感染症状がないか確認する</v>
+        <v/>
       </c>
       <c r="H54" t="str">
-        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、メルカゾールなど薬剤性の無顆粒球症、再生不良性貧血、ウイルス感染</v>
+        <v>膵臓のインスリン分泌能低下（1型糖尿病、糖尿病の進行）</v>
       </c>
       <c r="I54" t="str">
-        <v>発熱、のどの痛みなど感染症状の初期サインがないか確認する。人混みを避け、手洗い・うがいを徹底するよう伝える</v>
+        <v/>
       </c>
       <c r="J54" t="str">
-        <v>メルカゾール（チアマゾール）は無顆粒球症の重大な副作用があり、発熱・のどの痛みが出たらすぐ受診するよう指導する。抗がん剤・免疫抑制剤・抗てんかん薬（カルバマゼピンなど）使用中も定期的なモニタリングが必要</v>
+        <v>インスリン分泌能の評価に使われる。数値が低いほどインスリン治療の必要性が高いと判断される目安になる</v>
       </c>
       <c r="K54" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>糖尿病</v>
       </c>
       <c r="L54" t="str">
-        <v>白血球,WBC,好中球,感染症,白血病,無顆粒球症,骨髄抑制</v>
+        <v>CPR,Cペプチド,インスリン分泌,血清CPR</v>
       </c>
       <c r="M54" t="str">
         <v/>
@@ -2638,22 +2638,22 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>CRP</v>
+        <v>尿中微量アルブミン</v>
       </c>
       <c r="B55" t="str">
-        <v>CRP</v>
+        <v>U-Alb,MAU</v>
       </c>
       <c r="C55" t="str">
-        <v/>
+        <v>30 mg/gCr未満（尿中アルブミン/クレアチニン比）</v>
       </c>
       <c r="D55" t="str">
-        <v/>
+        <v>通常の尿蛋白検査では見つからない、ごく早期の腎症のサイン</v>
       </c>
       <c r="E55" t="str">
-        <v/>
+        <v>この検査は、通常の尿検査ではまだ分からないくらい早い段階の腎臓の変化を見つけるためのものです。数値が高いと、腎症の初期のサインである可能性があります。</v>
       </c>
       <c r="F55" t="str">
-        <v>炎症や感染</v>
+        <v>糖尿病性腎症の早期段階、高血圧</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2665,13 +2665,13 @@
         <v/>
       </c>
       <c r="J55" t="str">
-        <v/>
+        <v>糖尿病腎症の早期発見に重要な検査。血糖・血圧コントロールで改善しうる段階なので、早期介入の意義を伝える</v>
       </c>
       <c r="K55" t="str">
-        <v/>
+        <v>糖尿病,腎機能</v>
       </c>
       <c r="L55" t="str">
-        <v>CRP,炎症,感染</v>
+        <v>微量アルブミン,U-Alb,MAU,糖尿病性腎症,早期腎症</v>
       </c>
       <c r="M55" t="str">
         <v/>
@@ -2679,40 +2679,40 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ナトリウム（Na）</v>
+        <v>血清鉄（Fe）</v>
       </c>
       <c r="B56" t="str">
-        <v>Na</v>
+        <v>Fe</v>
       </c>
       <c r="C56" t="str">
-        <v/>
+        <v>60〜200 μg/dL（施設差あり）</v>
       </c>
       <c r="D56" t="str">
-        <v/>
+        <v>血液中を流れている鉄の量</v>
       </c>
       <c r="E56" t="str">
-        <v/>
+        <v>この検査は、今血液の中を流れている鉄の量を見るものです。低いと、体の中で鉄が不足している可能性があります。</v>
       </c>
       <c r="F56" t="str">
-        <v>アルドステロン症、脱水</v>
+        <v>鉄剤の過剰摂取、溶血、肝疾患</v>
       </c>
       <c r="G56" t="str">
-        <v>水分摂取状況を確認する（脱水が疑われる場合）</v>
+        <v/>
       </c>
       <c r="H56" t="str">
-        <v/>
+        <v>鉄欠乏性貧血、慢性炎症、出血</v>
       </c>
       <c r="I56" t="str">
-        <v/>
+        <v>鉄分の多い食品（レバー・赤身肉・魚・ほうれん草など）を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える</v>
       </c>
       <c r="J56" t="str">
-        <v/>
+        <v>血清鉄は日内変動が大きい。単独で判断せず総鉄結合能・フェリチンと合わせて評価する</v>
       </c>
       <c r="K56" t="str">
-        <v>電解質</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="L56" t="str">
-        <v>ナトリウム,Na,電解質,脱水</v>
+        <v>血清鉄,Fe,鉄欠乏性貧血</v>
       </c>
       <c r="M56" t="str">
         <v/>
@@ -2720,40 +2720,40 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>PaCO₂</v>
+        <v>総鉄結合能（TIBC）</v>
       </c>
       <c r="B57" t="str">
-        <v>PaCO2</v>
+        <v>TIBC</v>
       </c>
       <c r="C57" t="str">
-        <v/>
+        <v>250〜360 μg/dL（施設差あり）</v>
       </c>
       <c r="D57" t="str">
-        <v/>
+        <v>血液中のトランスフェリンが鉄と結合できる総量</v>
       </c>
       <c r="E57" t="str">
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>COPDなど呼気の障害</v>
+        <v>鉄欠乏性貧血（＞360 μg/dLが目安）</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v/>
+        <v>慢性炎症、肝疾患、ネフローゼ症候群</v>
       </c>
       <c r="I57" t="str">
         <v/>
       </c>
       <c r="J57" t="str">
-        <v/>
+        <v>鉄が不足すると、体はより多く運ぼうとしてTIBCが上昇する。UIBC・血清鉄と併せて評価する</v>
       </c>
       <c r="K57" t="str">
-        <v/>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="L57" t="str">
-        <v>PaCO2,PaCO₂,二酸化炭素分圧,COPD,呼吸不全</v>
+        <v>TIBC,総鉄結合能,鉄欠乏性貧血</v>
       </c>
       <c r="M57" t="str">
         <v/>
@@ -2761,40 +2761,40 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ヘマトクリット値</v>
+        <v>不飽和鉄結合能（UIBC）</v>
       </c>
       <c r="B58" t="str">
-        <v>Ht,Hct</v>
+        <v>UIBC</v>
       </c>
       <c r="C58" t="str">
-        <v>男性 40〜50%、女性 35〜45%</v>
+        <v>170〜300 μg/dL（施設差あり）</v>
       </c>
       <c r="D58" t="str">
-        <v>血液全体のうち赤血球が占める体積の割合。貧血・脱水の指標</v>
+        <v>トランスフェリンのうち、まだ鉄と結合していない余力の部分（UIBC＝TIBC－血清鉄）</v>
       </c>
       <c r="E58" t="str">
-        <v>ヘマトクリットは、血液全体のうち赤血球が占める割合を表す数値です。この値が低いと貧血、高いと脱水や血液が濃くなっている状態が疑われます。</v>
+        <v/>
       </c>
       <c r="F58" t="str">
-        <v>脱水、多血症（真性多血症、二次性多血症）、喫煙</v>
+        <v>鉄欠乏性貧血（＞300 μg/dLが目安）</v>
       </c>
       <c r="G58" t="str">
-        <v>脱水が疑われる場合はこまめな水分摂取を勧める（水分制限がある場合を除く）</v>
+        <v/>
       </c>
       <c r="H58" t="str">
-        <v>貧血（鉄欠乏性貧血、腎性貧血など）、出血</v>
+        <v>慢性炎症、鉄過剰状態</v>
       </c>
       <c r="I58" t="str">
-        <v>ヘモグロビンと同様に、出血や食事量低下がないか確認する</v>
+        <v/>
       </c>
       <c r="J58" t="str">
-        <v>ヘモグロビン・赤血球数と合わせて評価する。3つの値は同じ方向に動くことが多く、脱水があると貧血が見かけ上隠れることがある</v>
+        <v>TIBCと同じ方向に動くことが多い。血清鉄・TIBCとあわせて鉄欠乏性貧血と二次性貧血の鑑別に使う</v>
       </c>
       <c r="K58" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
       <c r="L58" t="str">
-        <v>ヘマトクリット,Ht,Hct,貧血,脱水,多血症</v>
+        <v>UIBC,不飽和鉄結合能,鉄欠乏性貧血</v>
       </c>
       <c r="M58" t="str">
         <v/>
@@ -2802,40 +2802,40 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>尿糖（半定量）</v>
+        <v>トランスフェリン飽和度</v>
       </c>
       <c r="B59" t="str">
-        <v>尿糖,U-Glu</v>
+        <v>TSAT</v>
       </c>
       <c r="C59" t="str">
-        <v>陰性（－）</v>
+        <v>16〜50%程度（施設差あり）</v>
       </c>
       <c r="D59" t="str">
-        <v>尿に糖が漏れ出ていないかを見る検査。血糖値がかなり高いと陽性になる</v>
+        <v>鉄を運ぶ役割のトランスフェリンのうち、実際に鉄を運んでいる割合（血清鉄÷総鉄結合能）</v>
       </c>
       <c r="E59" t="str">
-        <v>通常、糖は尿にはほとんど出ませんが、血糖値がかなり高くなると尿にあふれ出るようになります。血糖コントロールの目安の一つです。</v>
+        <v/>
       </c>
       <c r="F59" t="str">
-        <v>糖尿病（血糖値が腎臓で再吸収できる量を超えている状態）、腎性糖尿（血糖値が正常でも体質的に出ることがある）、SGLT2阻害薬服用中（薬の作用で意図的に糖を排泄するため陽性になるのが正常）</v>
+        <v>鉄過剰症（ヘモクロマトーシスなど）</v>
       </c>
       <c r="G59" t="str">
-        <v>SGLT2阻害薬（フォシーガ、ジャディアンスなど）服用中は、陽性が薬の効果によるものであることを説明する。脱水や尿路感染の症状がないかも確認する</v>
+        <v/>
       </c>
       <c r="H59" t="str">
-        <v/>
+        <v>鉄欠乏性貧血（＜16%が目安）</v>
       </c>
       <c r="I59" t="str">
         <v/>
       </c>
       <c r="J59" t="str">
-        <v>SGLT2阻害薬服用中は尿糖陽性が治療効果として想定内であることを患者に伝える。血糖値・HbA1cと合わせて評価する</v>
+        <v>血清鉄をTIBCで割って計算される。鉄剤補充の効果判定にも使われる</v>
       </c>
       <c r="K59" t="str">
-        <v>糖尿病</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="L59" t="str">
-        <v>尿糖,糖半定量,U-Glu,腎性糖尿,SGLT2</v>
+        <v>トランスフェリン飽和度,TSAT,鉄欠乏性貧血</v>
       </c>
       <c r="M59" t="str">
         <v/>
@@ -2843,40 +2843,40 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>尿潜血反応</v>
+        <v>血清フェリチン</v>
       </c>
       <c r="B60" t="str">
-        <v>尿潜血,U-OB</v>
+        <v>Ferritin</v>
       </c>
       <c r="C60" t="str">
-        <v>陰性（－）</v>
+        <v>男性 20〜250 ng/mL、女性 10〜120 ng/mL（施設差あり）</v>
       </c>
       <c r="D60" t="str">
-        <v>尿に血液（赤血球）が混じっていないかを見る検査</v>
+        <v>体に貯蔵されている鉄の量を反映する指標。貧血の症状が出るより早い段階で低下する</v>
       </c>
       <c r="E60" t="str">
-        <v>この検査は、尿に目に見えないくらいの微量の血液が混じっていないかを調べるものです。陽性の場合、腎臓や膀胱、尿路のどこかに炎症や結石などがある可能性があります。</v>
+        <v>フェリチンは、体に蓄えられている鉄の「貯金」の量を見る検査です。この数値が下がるのは、貧血の症状が出るよりも前の、とても早い段階のサインになります。</v>
       </c>
       <c r="F60" t="str">
-        <v>尿路結石、膀胱炎などの尿路感染症、腎炎、腫瘍、月経血の混入、激しい運動後</v>
+        <v>炎症性疾患、肝疾患、悪性腫瘍、鉄過剰症（フェリチンは炎症でも上昇するため、貧血の評価では注意が必要）</v>
       </c>
       <c r="G60" t="str">
-        <v>排尿時の痛みや頻尿、目に見える血尿の有無を確認する。女性は月経の時期と重なっていないか確認する</v>
+        <v/>
       </c>
       <c r="H60" t="str">
-        <v/>
+        <v>鉄欠乏状態（貧血の症状が出る前の早期段階から低下する）</v>
       </c>
       <c r="I60" t="str">
-        <v/>
+        <v>鉄分の多い食品を意識するとともに、貯蔵鉄を補うため治療は数値が正常化してからも継続が必要なことを伝える</v>
       </c>
       <c r="J60" t="str">
-        <v>陽性でも尿沈渣で赤血球が確認されない場合は偽陽性（ミオグロビン尿など）のこともある。持続する場合は泌尿器科的な精査が必要</v>
+        <v>貯蔵鉄の指標で鉄欠乏を最も早期に反映する。ただし炎症があると鉄欠乏があっても正常〜高値に出ることがあり、CRP等の炎症所見と合わせて評価する。二次性貧血との鑑別に重要</v>
       </c>
       <c r="K60" t="str">
-        <v>腎機能</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="L60" t="str">
-        <v>尿潜血,潜血反応,U-OB,血尿,尿路結石,膀胱炎</v>
+        <v>フェリチン,Ferritin,貯蔵鉄,鉄欠乏</v>
       </c>
       <c r="M60" t="str">
         <v/>
@@ -2884,40 +2884,40 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>ウロビリノーゲン</v>
+        <v>尿中尿酸/クレアチニン比（UUA/UCr）</v>
       </c>
       <c r="B61" t="str">
-        <v>Uro</v>
+        <v>UUA/UCr</v>
       </c>
       <c r="C61" t="str">
-        <v>正常（±）程度</v>
+        <v>0.4〜0.8程度が混合型の目安</v>
       </c>
       <c r="D61" t="str">
-        <v>肝臓や胆道、赤血球の壊れ方の状態を反映する尿検査項目</v>
+        <v>尿酸が「作られすぎ」か「排泄できていない」かを見分ける比の値</v>
       </c>
       <c r="E61" t="str">
-        <v>ウロビリノーゲンは、赤血球やビリルビンが体の中で処理される過程でできる物質です。肝臓の働きが悪くなったり、赤血球が壊れやすくなったりすると、尿の中の量が変化します。</v>
+        <v/>
       </c>
       <c r="F61" t="str">
-        <v>溶血性疾患（赤血球の破壊亢進）、肝機能障害</v>
+        <v>尿酸産生過剰型（0.8以上が目安）</v>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>胆道閉塞（胆汁が腸に流れず、ウロビリノーゲンが作られない状態）</v>
+        <v>尿酸排泄低下型（0.4以下が目安）</v>
       </c>
       <c r="I61" t="str">
         <v/>
       </c>
       <c r="J61" t="str">
-        <v>完全に陰性の場合は胆道閉塞を疑う所見の一つ。肝機能（AST/ALT/ビリルビン）と合わせて評価する</v>
+        <v>高尿酸血症は尿酸産生過剰型・排泄低下型・混合型に分類され、この比が目安になる。病型によって使う薬剤（尿酸生成抑制薬か尿酸排泄促進薬か）の選択が変わる</v>
       </c>
       <c r="K61" t="str">
-        <v>肝機能</v>
+        <v>高尿酸血症</v>
       </c>
       <c r="L61" t="str">
-        <v>ウロビリノーゲン,Uro,溶血,胆道閉塞,肝機能</v>
+        <v>UUA,UCr,尿酸クリアランス,CUA,EUA,尿酸産生過剰型,尿酸排泄低下型</v>
       </c>
       <c r="M61" t="str">
         <v/>
@@ -2925,40 +2925,40 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>尿pH</v>
+        <v>ucOC（低カルボキシル化オステオカルシン）</v>
       </c>
       <c r="B62" t="str">
-        <v>尿pH</v>
+        <v>ucOC</v>
       </c>
       <c r="C62" t="str">
-        <v>4.5〜7.5程度（弱酸性が多い）</v>
+        <v>4.5 ng/mL未満（施設差あり）</v>
       </c>
       <c r="D62" t="str">
-        <v>尿の酸性・アルカリ性の度合い。食事や感染症、体の状態を反映する</v>
+        <v>ビタミンKが不足していないかを反映する骨の指標</v>
       </c>
       <c r="E62" t="str">
-        <v>尿のpHは酸性・アルカリ性のバランスを表します。食事の内容や感染症、体の代謝状態によって変化します。単独で大きな問題を示すことは少ない検査です。</v>
+        <v/>
       </c>
       <c r="F62" t="str">
-        <v>尿路感染症（尿素分解菌によるもの）、野菜中心の食事、過換気</v>
+        <v>ビタミンK不足状態</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>高たんぱく食、糖尿病性ケトアシドーシス、痛風発作時（酸性尿は尿酸結石のリスクを高める）</v>
+        <v/>
       </c>
       <c r="I62" t="str">
-        <v>痛風・尿酸結石がある場合は、野菜など尿をアルカリ化する食品を意識するとよいことを伝える</v>
+        <v/>
       </c>
       <c r="J62" t="str">
-        <v>高尿酸血症・尿酸結石の患者では尿pHが酸性に傾いていないか確認する。尿アルカリ化薬（ウラリットなど）の効果判定にも使う</v>
+        <v>ビタミンK2製剤（骨粗鬆症治療薬）の適応判断や効果判定に使われる</v>
       </c>
       <c r="K62" t="str">
-        <v>高尿酸血症</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="L62" t="str">
-        <v>尿pH,尿酸性度,尿アルカリ化,ウラリット</v>
+        <v>ucOC,オステオカルシン,ビタミンK</v>
       </c>
       <c r="M62" t="str">
         <v/>
@@ -2966,40 +2966,40 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>尿クレアチニン（随時尿）</v>
+        <v>リン（P）</v>
       </c>
       <c r="B63" t="str">
-        <v>尿CRE</v>
+        <v>P,IP</v>
       </c>
       <c r="C63" t="str">
-        <v>随時尿は主に他項目の濃度補正に利用（単独の基準値は設けにくい）</v>
+        <v>2.5〜4.5 mg/dL</v>
       </c>
       <c r="D63" t="str">
-        <v>随時尿中のクレアチニン濃度。他の尿検査項目を薄まり具合で補正するための基準として使う</v>
+        <v>カルシウムとともに骨を作る主要なミネラル</v>
       </c>
       <c r="E63" t="str">
-        <v>この数値は、尿がどれくらい薄まっているかを確認するための基準として使われます。他の尿検査の結果（蛋白やアルブミンなど）をこの値で割って補正することで、水分摂取量による影響を減らして正確に評価できます。</v>
+        <v/>
       </c>
       <c r="F63" t="str">
-        <v/>
+        <v>腎不全、副甲状腺機能低下症</v>
       </c>
       <c r="G63" t="str">
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>尿が薄い（水分摂取が多い、腎機能低下）状態</v>
+        <v>副甲状腺機能亢進症、骨軟化症、ビタミンD欠乏</v>
       </c>
       <c r="I63" t="str">
         <v/>
       </c>
       <c r="J63" t="str">
-        <v>尿中アルブミン/Cr比、尿蛋白/Cr比など、他項目の補正計算に使われる。単独の高低に臨床的意味は乏しい</v>
+        <v>カルシウムと逆方向に動くことが多い（副甲状腺機能亢進症ではCa上昇・P低下）。骨粗鬆症の二次性原因の除外に用いられる</v>
       </c>
       <c r="K63" t="str">
-        <v>腎機能</v>
+        <v>骨粗鬆症,電解質</v>
       </c>
       <c r="L63" t="str">
-        <v>尿CRE,尿クレアチニン,随時尿,補正,蛋白クレアチニン比</v>
+        <v>リン,P,IP,無機リン</v>
       </c>
       <c r="M63" t="str">
         <v/>
@@ -3007,40 +3007,40 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>尿蛋白定量（随時尿）</v>
+        <v>PTH（副甲状腺ホルモン）</v>
       </c>
       <c r="B64" t="str">
-        <v>U-Pro定量,蛋白/Cr比</v>
+        <v>PTH</v>
       </c>
       <c r="C64" t="str">
-        <v>0.15 g/gCr未満</v>
+        <v>10〜65 pg/mL（施設差あり）</v>
       </c>
       <c r="D64" t="str">
-        <v>随時尿から尿蛋白の量を具体的な数値として評価する検査。ネフローゼ等の重症度判定に使う</v>
+        <v>血液中のカルシウム濃度を調節するホルモン</v>
       </c>
       <c r="E64" t="str">
-        <v>これは、尿に出ているたんぱくの量を具体的な数値で見る検査です。試験紙での陽性・陰性の判定だけでなく、実際にどれくらいの量が出ているかを把握できます。</v>
+        <v/>
       </c>
       <c r="F64" t="str">
-        <v>腎症の進行（糖尿病性腎症、慢性腎臓病など）、ネフローゼ症候群（3.5 g/gCr以上が目安）</v>
+        <v>原発性・二次性副甲状腺機能亢進症（腎不全に伴うものなど）</v>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v/>
+        <v>副甲状腺機能低下症</v>
       </c>
       <c r="I64" t="str">
         <v/>
       </c>
       <c r="J64" t="str">
-        <v>CKD診療ガイドラインの重症度分類（尿蛋白量による区分）にも使われる定量指標。試験紙法の半定量結果より治療効果判定に適する</v>
+        <v>骨粗鬆症の二次性原因（副甲状腺機能亢進症）を除外するための検査。カルシウム・リンと合わせて評価する</v>
       </c>
       <c r="K64" t="str">
-        <v>腎機能,糖尿病</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="L64" t="str">
-        <v>尿蛋白,随時尿,定量,蛋白クレアチニン比,ネフローゼ</v>
+        <v>PTH,副甲状腺ホルモン,パラトルモン</v>
       </c>
       <c r="M64" t="str">
         <v/>
@@ -3048,40 +3048,40 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>総タンパク</v>
+        <v>骨型酒石酸抵抗性フォスファターゼ（TRACP-5b）</v>
       </c>
       <c r="B65" t="str">
-        <v>TP</v>
+        <v>TRACP-5b</v>
       </c>
       <c r="C65" t="str">
-        <v>6.6〜8.1 g/dL</v>
+        <v>120〜420 mU/dL</v>
       </c>
       <c r="D65" t="str">
-        <v>血液中のたんぱく質（アルブミン＋グロブリン）の総量。栄養状態や肝機能、炎症の目安</v>
+        <v>骨がどれくらい壊されているかを見る検査。骨は「古い骨を壊して新しい骨を作る」入れ替えを繰り返しており、骨を壊す細胞が活発だとこの物質が血液中に増える。</v>
       </c>
       <c r="E65" t="str">
-        <v>総タンパクは、血液中のたんぱく質の合計量です。栄養状態や肝臓の働き、体の炎症の有無などを反映します。</v>
+        <v>この検査は、骨がどれくらい早く減っていないかを見るものです。数値が高いと、骨が弱くなりやすい状態の目安になります。</v>
       </c>
       <c r="F65" t="str">
-        <v>脱水、多発性骨髄腫など（グロブリン増加）、慢性炎症</v>
+        <v>骨粗鬆症、骨代謝回転（骨がこわれるスピード）が活発な状態</v>
       </c>
       <c r="G65" t="str">
-        <v/>
+        <v>カルシウム・ビタミンDの摂取や、適度な荷重運動（ウォーキングなど）を意識するよう伝える</v>
       </c>
       <c r="H65" t="str">
-        <v>低栄養、肝機能低下（アルブミン産生低下）、ネフローゼ症候群、消化管からのたんぱく漏出</v>
+        <v/>
       </c>
       <c r="I65" t="str">
-        <v>食事摂取量（特にたんぱく質）を確認する</v>
+        <v/>
       </c>
       <c r="J65" t="str">
-        <v>アルブミンとグロブリンの内訳（A/G比）も合わせて確認すると原因の絞り込みに役立つ。低栄養か肝機能低下かはアルブミンの値と合わせて判断する</v>
+        <v>「骨を壊す側」の指標。「骨を作る側」の検査と合わせて評価する。数値だけで診断はしない</v>
       </c>
       <c r="K65" t="str">
-        <v>肝機能</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="L65" t="str">
-        <v>総タンパク,TP,総蛋白,栄養状態,A/G比</v>
+        <v>TRACP-5b,骨型酒石酸抵抗性フォスファターゼ,骨粗鬆症,骨代謝</v>
       </c>
       <c r="M65" t="str">
         <v/>
@@ -3089,25 +3089,25 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>総ビリルビン</v>
+        <v>カルシトニン</v>
       </c>
       <c r="B66" t="str">
-        <v>T-Bil</v>
+        <v>CT</v>
       </c>
       <c r="C66" t="str">
-        <v>0.2〜1.2 mg/dL</v>
+        <v>男性 9.52 pg/mL未満、女性 6.40 pg/mL未満（施設差あり）</v>
       </c>
       <c r="D66" t="str">
-        <v>赤血球が壊れてできる黄色い色素の総量。肝臓・胆道の状態や黄疸の指標</v>
+        <v>血液中のカルシウムを下げる方向に働くホルモン</v>
       </c>
       <c r="E66" t="str">
-        <v>ビリルビンは赤血球が寿命を迎えて壊れるときにできる黄色い色素です。肝臓で処理されて排泄されますが、肝臓や胆道にトラブルがあると血液中に増え、皮膚や白目が黄色くなる黄疸として現れます。</v>
+        <v/>
       </c>
       <c r="F66" t="str">
-        <v>肝炎・肝硬変などの肝疾患、胆道閉塞（胆石・腫瘍など）、溶血性疾患（赤血球の破壊亢進）、体質性黄疸（ジルベール症候群など）</v>
+        <v>甲状腺髄様癌、腎不全</v>
       </c>
       <c r="G66" t="str">
-        <v>皮膚や白目の黄染、尿の色が濃くなっていないか確認する</v>
+        <v/>
       </c>
       <c r="H66" t="str">
         <v/>
@@ -3116,13 +3116,13 @@
         <v/>
       </c>
       <c r="J66" t="str">
-        <v>直接ビリルビン・間接ビリルビンの内訳で原因を推測できる（直接優位は胆道系、間接優位は溶血・体質性）。AST/ALT/γ-GTPと合わせて評価する</v>
+        <v>骨粗鬆症の二次性原因の除外目的で測定されることがある検査値。同名の薬剤（カルシトニン製剤）と混同しないよう注意</v>
       </c>
       <c r="K66" t="str">
-        <v>肝機能</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="L66" t="str">
-        <v>総ビリルビン,T-Bil,黄疸,ビリルビン,ジルベール症候群</v>
+        <v>カルシトニン,CT</v>
       </c>
       <c r="M66" t="str">
         <v/>
@@ -3130,40 +3130,40 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>コリンエステラーゼ</v>
+        <v>尿中NTX</v>
       </c>
       <c r="B67" t="str">
-        <v>ChE</v>
+        <v>NTX</v>
       </c>
       <c r="C67" t="str">
-        <v>男性 240〜486 U/L、女性 201〜421 U/L（施設差あり）</v>
+        <v>施設差が大きく一律の記載が難しい（尿中）</v>
       </c>
       <c r="D67" t="str">
-        <v>主に肝臓で作られる酵素。肝臓のたんぱく質を作る力（合成能）を反映する</v>
+        <v>骨が壊されるときに出る、骨吸収マーカーのひとつ</v>
       </c>
       <c r="E67" t="str">
-        <v>コリンエステラーゼは肝臓で作られる酵素です。肝臓がたんぱく質を作る力が落ちると数値が下がり、逆に脂肪肝や栄養状態が良すぎる場合は上がることがあります。</v>
+        <v/>
       </c>
       <c r="F67" t="str">
-        <v>脂肪肝、ネフローゼ症候群、肥満、甲状腺機能亢進症</v>
+        <v>骨代謝回転の亢進（骨粗鬆症、閉経後など）</v>
       </c>
       <c r="G67" t="str">
-        <v>脂肪肝が疑われる場合は食事・運動習慣の見直しを勧める</v>
+        <v/>
       </c>
       <c r="H67" t="str">
-        <v>肝硬変など肝臓の合成能低下、低栄養、有機リン中毒（農薬など）</v>
+        <v>骨吸収抑制薬（ビスホスホネート等）による治療効果</v>
       </c>
       <c r="I67" t="str">
         <v/>
       </c>
       <c r="J67" t="str">
-        <v>アルブミンと同様に肝臓の「合成能」を見る指標。低栄養か肝硬変かは、アルブミンや血小板数（肝硬変で低下しやすい）と合わせて判断する</v>
+        <v>治療開始後3〜6か月で再検し、薬の効果判定に使われる。TRACP-5bと同じ「骨を壊す側」の指標</v>
       </c>
       <c r="K67" t="str">
-        <v>肝機能</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="L67" t="str">
-        <v>コリンエステラーゼ,ChE,肝合成能,脂肪肝,肝硬変</v>
+        <v>NTX,尿中NTX,骨吸収マーカー</v>
       </c>
       <c r="M67" t="str">
         <v/>
@@ -3171,40 +3171,40 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>クロール</v>
+        <v>DPD（デオキシピリジノリン）</v>
       </c>
       <c r="B68" t="str">
-        <v>Cl</v>
+        <v>DPD</v>
       </c>
       <c r="C68" t="str">
-        <v>98〜108 mEq/L</v>
+        <v>施設差が大きく一律の記載が難しい（尿中）</v>
       </c>
       <c r="D68" t="str">
-        <v>ナトリウムと共に体の水分・酸塩基バランスに関わる電解質</v>
+        <v>骨のコラーゲンが壊れるときに出る、骨吸収マーカーのひとつ</v>
       </c>
       <c r="E68" t="str">
-        <v>クロールは、ナトリウムと一緒に体の水分バランスや、体液の性質（酸性・アルカリ性）を保つ働きをしているミネラルです。多くの場合、ナトリウムと同じように変動します。</v>
+        <v/>
       </c>
       <c r="F68" t="str">
-        <v>脱水、腎不全、代謝性アシドーシス、高ナトリウム血症に伴うもの</v>
+        <v>骨代謝回転の亢進（骨粗鬆症など）</v>
       </c>
       <c r="G68" t="str">
-        <v>脱水が疑われる場合はこまめな水分摂取を勧める（水分制限がある場合を除く）</v>
+        <v/>
       </c>
       <c r="H68" t="str">
-        <v>嘔吐・下痢、利尿薬使用、代謝性アルカローシス</v>
+        <v>骨吸収抑制薬による治療効果</v>
       </c>
       <c r="I68" t="str">
-        <v>利尿薬使用中は嘔吐・下痢が続いていないか確認する</v>
+        <v/>
       </c>
       <c r="J68" t="str">
-        <v>ナトリウムと同じ方向に動くことが多いが、酸塩基平衡の異常（アシドーシス・アルカローシス）を反映して単独で動くこともある。利尿薬（特にループ利尿薬）使用中は低クロール性アルカローシスに注意</v>
+        <v>NTX・CTXと同じ「骨を壊す側」の指標。食事の影響を受けにくいとされる</v>
       </c>
       <c r="K68" t="str">
-        <v>電解質,腎機能</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="L68" t="str">
-        <v>クロール,Cl,塩素,電解質,アシドーシス,アルカローシス</v>
+        <v>DPD,デオキシピリジノリン,骨吸収マーカー</v>
       </c>
       <c r="M68" t="str">
         <v/>
@@ -3212,48 +3212,499 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>nonHDLコレステロール</v>
+        <v>CTX</v>
       </c>
       <c r="B69" t="str">
-        <v>non-HDL-C</v>
+        <v>CTX</v>
       </c>
       <c r="C69" t="str">
-        <v>90〜149 mg/dL（150 mg/dL以上で高値）</v>
+        <v>施設差が大きく一律の記載が難しい（血清・尿中）</v>
       </c>
       <c r="D69" t="str">
-        <v>総コレステロールからHDL（善玉）を除いた、動脈硬化を進めるすべての脂質の合計</v>
+        <v>骨のコラーゲンが壊れるときに出る、骨吸収マーカーのひとつ</v>
       </c>
       <c r="E69" t="str">
-        <v>nonHDLコレステロールは、総コレステロールから善玉のHDLを引いた数値で、LDL（悪玉）を含む、動脈硬化を進めるすべてのコレステロールの合計を表します。中性脂肪が高くLDLだけでは評価しにくい方でも、こちらで動脈硬化のリスクを評価できます。</v>
+        <v/>
       </c>
       <c r="F69" t="str">
-        <v>脂質異常症、動脈硬化のリスク上昇（特に中性脂肪が高い場合にLDL-Cより実態を反映しやすい）</v>
+        <v>骨代謝回転の亢進（骨粗鬆症など）</v>
       </c>
       <c r="G69" t="str">
-        <v>動物性脂肪や揚げ物を控え、青魚や食物繊維（野菜・海藻・きのこ）を増やすよう伝える</v>
+        <v/>
       </c>
       <c r="H69" t="str">
-        <v/>
+        <v>骨吸収抑制薬による治療効果</v>
       </c>
       <c r="I69" t="str">
         <v/>
       </c>
       <c r="J69" t="str">
-        <v>中性脂肪（TG）が400 mg/dL以上などLDL-Cの計算式（Friedewald式）が不正確になる場合に、LDL-Cの代わりに用いられる。目標値はLDL-Cの目標値＋30 mg/dLが目安</v>
+        <v>NTX・DPDと同じ「骨を壊す側」の指標。血清・尿中いずれでも測定されることがある</v>
       </c>
       <c r="K69" t="str">
-        <v>脂質異常症</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="L69" t="str">
-        <v>nonHDL,non-HDLコレステロール,動脈硬化,中性脂肪,LDL計算式</v>
+        <v>CTX,骨吸収マーカー</v>
       </c>
       <c r="M69" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>P1NP</v>
+      </c>
+      <c r="B70" t="str">
+        <v>P1NP</v>
+      </c>
+      <c r="C70" t="str">
+        <v>施設差が大きく一律の記載が難しい（血清）</v>
+      </c>
+      <c r="D70" t="str">
+        <v>骨が新しく作られるときに出る、骨形成マーカーのひとつ</v>
+      </c>
+      <c r="E70" t="str">
+        <v/>
+      </c>
+      <c r="F70" t="str">
+        <v>骨代謝回転の亢進、骨形成促進薬による治療効果</v>
+      </c>
+      <c r="G70" t="str">
+        <v/>
+      </c>
+      <c r="H70" t="str">
+        <v>骨形成の低下</v>
+      </c>
+      <c r="I70" t="str">
+        <v/>
+      </c>
+      <c r="J70" t="str">
+        <v>TRACP-5b等「骨を壊す側」の指標とは逆の、「骨を作る側」の指標。骨形成促進薬（テリパラチド等）の効果判定に使われる</v>
+      </c>
+      <c r="K70" t="str">
+        <v>骨粗鬆症</v>
+      </c>
+      <c r="L70" t="str">
+        <v>P1NP,骨形成マーカー</v>
+      </c>
+      <c r="M70" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>抗甲状腺マイクロゾーム抗体（抗TPO抗体）</v>
+      </c>
+      <c r="B71" t="str">
+        <v>TPOAb</v>
+      </c>
+      <c r="C71" t="str">
+        <v>陰性（16 IU/mL未満程度、施設差あり）</v>
+      </c>
+      <c r="D71" t="str">
+        <v>自分の甲状腺を攻撃する抗体が出ていないかを見る検査</v>
+      </c>
+      <c r="E71" t="str">
+        <v>この検査は、体の中に自分の甲状腺を誤って攻撃してしまう抗体がないかを見るものです。陽性の場合、橋本病（慢性甲状腺炎）など甲状腺の自己免疫的な炎症が背景にある可能性があります。</v>
+      </c>
+      <c r="F71" t="str">
+        <v>橋本病（慢性甲状腺炎）、バセドウ病などの自己免疫性甲状腺疾患</v>
+      </c>
+      <c r="G71" t="str">
+        <v/>
+      </c>
+      <c r="H71" t="str">
+        <v/>
+      </c>
+      <c r="I71" t="str">
+        <v/>
+      </c>
+      <c r="J71" t="str">
+        <v>陽性でも必ずしも甲状腺機能異常があるとは限らない。TSH・FT4など甲状腺ホルモンの数値と合わせて評価する</v>
+      </c>
+      <c r="K71" t="str">
+        <v>甲状腺疾患</v>
+      </c>
+      <c r="L71" t="str">
+        <v>抗TPO抗体,抗甲状腺マイクロゾーム抗体,TPOAb,橋本病</v>
+      </c>
+      <c r="M71" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>抗サイログロブリン抗体</v>
+      </c>
+      <c r="B72" t="str">
+        <v>TgAb</v>
+      </c>
+      <c r="C72" t="str">
+        <v>陰性（28 IU/mL未満程度、施設差あり）</v>
+      </c>
+      <c r="D72" t="str">
+        <v>甲状腺のたんぱく質（サイログロブリン）への抗体が出ていないかを見る検査</v>
+      </c>
+      <c r="E72" t="str">
+        <v>この検査も、抗TPO抗体と同じく、甲状腺に対する自己免疫の有無を見るものです。あわせて調べることで橋本病などの診断の参考にします。</v>
+      </c>
+      <c r="F72" t="str">
+        <v>橋本病（慢性甲状腺炎）、バセドウ病などの自己免疫性甲状腺疾患</v>
+      </c>
+      <c r="G72" t="str">
+        <v/>
+      </c>
+      <c r="H72" t="str">
+        <v/>
+      </c>
+      <c r="I72" t="str">
+        <v/>
+      </c>
+      <c r="J72" t="str">
+        <v>抗TPO抗体とあわせて測定されることが多い。単独の高値だけで治療方針が決まるわけではない</v>
+      </c>
+      <c r="K72" t="str">
+        <v>甲状腺疾患</v>
+      </c>
+      <c r="L72" t="str">
+        <v>抗サイログロブリン抗体,TgAb,橋本病</v>
+      </c>
+      <c r="M72" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>TSH（甲状腺刺激ホルモン）</v>
+      </c>
+      <c r="B73" t="str">
+        <v>TSH</v>
+      </c>
+      <c r="C73" t="str">
+        <v>0.5〜5.0 μIU/mL程度（施設差あり）</v>
+      </c>
+      <c r="D73" t="str">
+        <v>甲状腺の働きが多いか少ないかを最も敏感に反映するホルモン</v>
+      </c>
+      <c r="E73" t="str">
+        <v>TSHは脳の下垂体から出て、甲状腺に「もっと働いて」と指令を送るホルモンです。甲状腺の働きが弱っていると体が指令を強めるためTSHは上がり、逆に甲状腺が働きすぎているとTSHは下がります。甲状腺の状態を最初に確認する数値としてよく使われます。</v>
+      </c>
+      <c r="F73" t="str">
+        <v>甲状腺機能低下症（橋本病など）、チラーヂンSなど甲状腺ホルモン薬の量不足</v>
+      </c>
+      <c r="G73" t="str">
+        <v>だるさ、むくみ、体重増加、寒がりなどの症状がないか確認する。服薬状況（飲み忘れ、他の薬との飲み合わせ）を確認する</v>
+      </c>
+      <c r="H73" t="str">
+        <v>甲状腺機能亢進症（バセドウ病など）、チラーヂンSなど甲状腺ホルモン薬の過量</v>
+      </c>
+      <c r="I73" t="str">
+        <v>動悸、体重減少、暑がり、手のふるえなどの症状がないか確認する</v>
+      </c>
+      <c r="J73" t="str">
+        <v>チラーヂンS服用中はTSHが治療目標域に収まっているかで用量調整の目安にする。メルカゾール服用中はTSH・FT4に加えて無顆粒球症の初期症状（発熱・のどの痛み）の有無や白血球数も確認する</v>
+      </c>
+      <c r="K73" t="str">
+        <v>甲状腺疾患</v>
+      </c>
+      <c r="L73" t="str">
+        <v>TSH,甲状腺刺激ホルモン,甲状腺機能,橋本病,バセドウ病,チラーヂン,メルカゾール</v>
+      </c>
+      <c r="M73" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>FT4（遊離サイロキシン）</v>
+      </c>
+      <c r="B74" t="str">
+        <v>FT4</v>
+      </c>
+      <c r="C74" t="str">
+        <v>0.9〜1.7 ng/dL程度（施設差あり）</v>
+      </c>
+      <c r="D74" t="str">
+        <v>甲状腺が実際に分泌しているホルモンの量そのものを表す数値</v>
+      </c>
+      <c r="E74" t="str">
+        <v>FT4は甲状腺そのものが作っているホルモンの量です。TSHが「指令の強さ」だとすると、FT4は「実際に出ている量」にあたります。2つをあわせて見ることで、甲状腺の働きが今どういう状態かを詳しく判断できます。</v>
+      </c>
+      <c r="F74" t="str">
+        <v>甲状腺機能亢進症（バセドウ病など）</v>
+      </c>
+      <c r="G74" t="str">
+        <v>動悸、体重減少、暑がり、手のふるえなどの症状がないか確認する</v>
+      </c>
+      <c r="H74" t="str">
+        <v>甲状腺機能低下症（橋本病など）</v>
+      </c>
+      <c r="I74" t="str">
+        <v>だるさ、むくみ、体重増加、寒がりなどの症状がないか確認する</v>
+      </c>
+      <c r="J74" t="str">
+        <v>TSHと逆方向に動くのが基本だが、下垂体性の異常など例外もある。TSHと合わせて評価し、片方だけで判断しない</v>
+      </c>
+      <c r="K74" t="str">
+        <v>甲状腺疾患</v>
+      </c>
+      <c r="L74" t="str">
+        <v>FT4,遊離サイロキシン,甲状腺ホルモン,甲状腺機能</v>
+      </c>
+      <c r="M74" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>PT-INR（プロトロンビン時間国際標準比）</v>
+      </c>
+      <c r="B75" t="str">
+        <v>PT-INR,INR</v>
+      </c>
+      <c r="C75" t="str">
+        <v>治療域の目安 1.6〜3.0（ワルファリン服用時。年齢・疾患により異なる）</v>
+      </c>
+      <c r="D75" t="str">
+        <v>血液の固まりやすさを表す数値で、ワルファリンの効き具合を確認するために使う</v>
+      </c>
+      <c r="E75" t="str">
+        <v>PT-INRは血液が固まるまでの時間をもとにした数値で、ワルファリンというお薬を飲んでいる方の効き具合を確認するために測ります。数値が高いほど血液が固まりにくく出血しやすい状態、低いほど血栓ができやすい状態を示します。</v>
+      </c>
+      <c r="F75" t="str">
+        <v>ワルファリンの効きすぎ、肝機能低下、ビタミンK不足、納豆・青汁など摂取量の変化</v>
+      </c>
+      <c r="G75" t="str">
+        <v>歯ぐきや鼻からの出血、あざ、黒い便などの出血症状がないか確認する。納豆・クロレラ・青汁などビタミンKを多く含む食品の摂取状況を確認する</v>
+      </c>
+      <c r="H75" t="str">
+        <v>ワルファリンの効き不足、飲み忘れ、ビタミンK摂取量の急激な増加</v>
+      </c>
+      <c r="I75" t="str">
+        <v>服薬状況（飲み忘れ）を確認する。片側のむくみ・しびれ・胸痛など血栓症状がないか確認する</v>
+      </c>
+      <c r="J75" t="str">
+        <v>治療域は疾患・年齢によって異なる（例：非弁膜症性心房細動の高齢者では1.6〜2.6が目安になることが多い）。多くの薬剤・食品と相互作用があるため新規薬剤追加時は必ず確認する。DOAC（エリキュース、リクシアナ、プラザキサなど）ではPT-INRのモニタリングは不要</v>
+      </c>
+      <c r="K75" t="str">
+        <v>抗凝固療法（心房細動・血栓症）</v>
+      </c>
+      <c r="L75" t="str">
+        <v>PT-INR,INR,プロトロンビン時間,ワルファリン,ワーファリン,抗凝固</v>
+      </c>
+      <c r="M75" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>血中薬物濃度（TDM）</v>
+      </c>
+      <c r="B76" t="str">
+        <v>TDM</v>
+      </c>
+      <c r="C76" t="str">
+        <v>薬剤ごとに有効域が異なる（例：カルバマゼピン 4〜12 μg/mL、バルプロ酸 40〜100 μg/mL、フェニトイン 10〜20 μg/mL）</v>
+      </c>
+      <c r="D76" t="str">
+        <v>治療域が狭い薬剤で、血液中の薬の濃度が効果域・中毒域のどちらにあるかを確認する検査</v>
+      </c>
+      <c r="E76" t="str">
+        <v>この薬は効く量と副作用が出る量が近いため、血液中の薬の濃度を定期的に測って、ちょうどよい範囲に入っているかを確認します。数値が低いと効果が不十分になり、高いと副作用が出やすくなります。</v>
+      </c>
+      <c r="F76" t="str">
+        <v>過量投与、代謝を妨げる薬剤との併用、肝機能低下による代謝低下</v>
+      </c>
+      <c r="G76" t="str">
+        <v>ふらつき、眠気、めまい、物が二重に見えるなどの中毒症状がないか確認する</v>
+      </c>
+      <c r="H76" t="str">
+        <v>飲み忘れ、自己判断による減量、代謝を促進する薬剤との併用（相互作用）</v>
+      </c>
+      <c r="I76" t="str">
+        <v>発作やてんかん症状の再発がないか確認し、飲み忘れがないか一緒に確認する</v>
+      </c>
+      <c r="J76" t="str">
+        <v>採血のタイミング（トラフ値かどうか）で数値の解釈が変わるため採血時点を確認する。カルバマゼピンは自己誘導により長期使用で濃度が下がることがある点にも注意</v>
+      </c>
+      <c r="K76" t="str">
+        <v>てんかん</v>
+      </c>
+      <c r="L76" t="str">
+        <v>TDM,血中薬物濃度,治療域,中毒域,カルバマゼピン,フェニトイン,バルプロ酸,抗てんかん薬</v>
+      </c>
+      <c r="M76" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>アミラーゼ（AMY）</v>
+      </c>
+      <c r="B77" t="str">
+        <v>AMY</v>
+      </c>
+      <c r="C77" t="str">
+        <v/>
+      </c>
+      <c r="D77" t="str">
+        <v/>
+      </c>
+      <c r="E77" t="str">
+        <v/>
+      </c>
+      <c r="F77" t="str">
+        <v>急性膵炎</v>
+      </c>
+      <c r="G77" t="str">
+        <v>飲酒を控える、脂っこい食事を避けるよう伝える</v>
+      </c>
+      <c r="H77" t="str">
+        <v/>
+      </c>
+      <c r="I77" t="str">
+        <v/>
+      </c>
+      <c r="J77" t="str">
+        <v/>
+      </c>
+      <c r="K77" t="str">
+        <v/>
+      </c>
+      <c r="L77" t="str">
+        <v>アミラーゼ,AMY,膵炎,急性膵炎</v>
+      </c>
+      <c r="M77" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>間接ビリルビン</v>
+      </c>
+      <c r="B78" t="str">
+        <v>I-Bil</v>
+      </c>
+      <c r="C78" t="str">
+        <v/>
+      </c>
+      <c r="D78" t="str">
+        <v/>
+      </c>
+      <c r="E78" t="str">
+        <v/>
+      </c>
+      <c r="F78" t="str">
+        <v>血液型不適合輸血などによる溶血</v>
+      </c>
+      <c r="G78" t="str">
+        <v/>
+      </c>
+      <c r="H78" t="str">
+        <v/>
+      </c>
+      <c r="I78" t="str">
+        <v/>
+      </c>
+      <c r="J78" t="str">
+        <v/>
+      </c>
+      <c r="K78" t="str">
+        <v/>
+      </c>
+      <c r="L78" t="str">
+        <v>間接ビリルビン,I-Bil,溶血</v>
+      </c>
+      <c r="M78" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>直接ビリルビン</v>
+      </c>
+      <c r="B79" t="str">
+        <v>D-Bil</v>
+      </c>
+      <c r="C79" t="str">
+        <v/>
+      </c>
+      <c r="D79" t="str">
+        <v/>
+      </c>
+      <c r="E79" t="str">
+        <v/>
+      </c>
+      <c r="F79" t="str">
+        <v>肝疾患、胆石など胆道の閉塞</v>
+      </c>
+      <c r="G79" t="str">
+        <v/>
+      </c>
+      <c r="H79" t="str">
+        <v/>
+      </c>
+      <c r="I79" t="str">
+        <v/>
+      </c>
+      <c r="J79" t="str">
+        <v/>
+      </c>
+      <c r="K79" t="str">
+        <v>肝機能</v>
+      </c>
+      <c r="L79" t="str">
+        <v>直接ビリルビン,D-Bil,胆石,胆道閉塞</v>
+      </c>
+      <c r="M79" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>CRP</v>
+      </c>
+      <c r="B80" t="str">
+        <v>CRP</v>
+      </c>
+      <c r="C80" t="str">
+        <v/>
+      </c>
+      <c r="D80" t="str">
+        <v/>
+      </c>
+      <c r="E80" t="str">
+        <v/>
+      </c>
+      <c r="F80" t="str">
+        <v>炎症や感染</v>
+      </c>
+      <c r="G80" t="str">
+        <v/>
+      </c>
+      <c r="H80" t="str">
+        <v/>
+      </c>
+      <c r="I80" t="str">
+        <v/>
+      </c>
+      <c r="J80" t="str">
+        <v/>
+      </c>
+      <c r="K80" t="str">
+        <v/>
+      </c>
+      <c r="L80" t="str">
+        <v>CRP,炎症,感染</v>
+      </c>
+      <c r="M80" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M69"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M80"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3312,19 +3763,19 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>腎機能</v>
+        <v>脂質異常症</v>
       </c>
       <c r="B3" t="str">
         <v/>
       </c>
       <c r="C3" t="str">
-        <v>足のむくみやだるさが増えていませんか／尿の量や回数に変化はありませんか／血圧の薬や痛み止めを新しく使い始めていませんか</v>
+        <v>揚げ物や脂っこい食事、間食の頻度はどれくらいですか／運動の習慣はありますか／お薬の飲み忘れはどのくらいありますか</v>
       </c>
       <c r="D3" t="str">
-        <v>【数値が悪化した時】お薬の量や飲み合わせを一度確認しますね。むくみや体重の変化はありませんか　【数値が安定している時】今のペースを維持できています。水分の摂り方や塩分は今のままで大丈夫そうです</v>
+        <v>【悪化した時】食事や運動で最近変わったことはありますか。一緒に見直してみましょう　【改善した時】数値が良くなってきています。今の生活習慣を続けていきましょう</v>
       </c>
       <c r="E3" t="str">
-        <v>腎排泄型薬剤の用量調整が必要ないか。NSAIDsや造影剤など腎機能に影響する薬剤の使用歴。脱水を起こしやすい状況（下痢・嘔吐・猛暑）がないか</v>
+        <v>LDLの目標値は既往疾患（冠動脈疾患・糖尿病など）によって異なる。スタチンの副作用（筋肉痛・脱力感）の有無</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -3332,19 +3783,19 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>心不全</v>
+        <v>精神疾患（非定型抗精神病薬）</v>
       </c>
       <c r="B4" t="str">
         <v/>
       </c>
       <c r="C4" t="str">
-        <v>階段や坂道で息切れしやすくなっていませんか／足や靴がきつくなるようなむくみはありませんか／体重は増えていませんか／夜、横になると苦しくて起き上がることはありませんか</v>
+        <v>体重の増減はありませんか／のどの渇きや尿量の変化はありませんか／だるさや動きにくさが増えていませんか</v>
       </c>
       <c r="D4" t="str">
-        <v>【数値が悪化した時】少し心臓に負担がかかっているサインかもしれません。むくみや体重の増減はありましたか　【数値が安定している時】今のところ落ち着いています。塩分と水分のとり方は今のままで大丈夫そうです</v>
+        <v>【体重増加や口渇がある時】念のため血糖や脂質の数値を確認しますね　【安定している時】今のところ大きな変化はなさそうです</v>
       </c>
       <c r="E4" t="str">
-        <v>体重の日々の変化（急な増加は水分貯留のサイン）。塩分・水分制限の理解度。NSAIDsなど心不全を悪化させうる薬剤の使用</v>
+        <v>非定型抗精神病薬（アリピプラゾール、クエチアピン、リスペリドン等）による代謝異常（高血糖・脂質異常・体重増加）は自覚症状に乏しく、定期的な血糖・脂質・肝機能のチェックが重要なこと。糖尿病がある場合オランザピン・クエチアピンは原則禁忌</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -3352,19 +3803,19 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>肝機能</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="B5" t="str">
         <v/>
       </c>
       <c r="C5" t="str">
-        <v>お酒を飲む量や頻度に変化はありますか／新しく始めたお薬やサプリメントはありますか／だるさや黄疸（白目や皮膚が黄色くなること）のような症状はありませんか</v>
+        <v>転倒やつまずきが増えていませんか／日光を浴びる機会や運動の習慣はありますか／カルシウムや乳製品を摂る頻度はどれくらいですか</v>
       </c>
       <c r="D5" t="str">
-        <v>【悪化した時】最近、お酒の量やお薬で変わったことはありますか。少し肝臓に負担がかかっているようです　【改善した時】数値が落ち着いてきています。今の生活を続けていきましょう</v>
+        <v>【悪化した時】骨密度や数値が気になるところです。日光を浴びる時間や運動は取れていますか　【改善した時】治療の効果が出てきています。このまま続けていきましょう</v>
       </c>
       <c r="E5" t="str">
-        <v>新規開始薬剤による薬剤性肝障害の可能性。市販薬・サプリメント・健康食品の使用歴。飲酒量の申告は過小になりやすい</v>
+        <v>骨粗鬆症治療薬（ビスホスホネート等）の服用方法（起床時空腹時服用、服用後30分は横にならない、等）の再確認。転倒リスクとなる他剤（睡眠薬等）の併用</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -3372,19 +3823,19 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>脂質異常症</v>
+        <v>腎機能</v>
       </c>
       <c r="B6" t="str">
         <v/>
       </c>
       <c r="C6" t="str">
-        <v>揚げ物や脂っこい食事、間食の頻度はどれくらいですか／運動の習慣はありますか／お薬の飲み忘れはどのくらいありますか</v>
+        <v>足のむくみやだるさが増えていませんか／尿の量や回数に変化はありませんか／血圧の薬や痛み止めを新しく使い始めていませんか</v>
       </c>
       <c r="D6" t="str">
-        <v>【悪化した時】食事や運動で最近変わったことはありますか。一緒に見直してみましょう　【改善した時】数値が良くなってきています。今の生活習慣を続けていきましょう</v>
+        <v>【数値が悪化した時】お薬の量や飲み合わせを一度確認しますね。むくみや体重の変化はありませんか　【数値が安定している時】今のペースを維持できています。水分の摂り方や塩分は今のままで大丈夫そうです</v>
       </c>
       <c r="E6" t="str">
-        <v>LDLの目標値は既往疾患（冠動脈疾患・糖尿病など）によって異なる。スタチンの副作用（筋肉痛・脱力感）の有無</v>
+        <v>腎排泄型薬剤の用量調整が必要ないか。NSAIDsや造影剤など腎機能に影響する薬剤の使用歴。脱水を起こしやすい状況（下痢・嘔吐・猛暑）がないか</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -3392,19 +3843,19 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>高尿酸血症</v>
+        <v>肝機能</v>
       </c>
       <c r="B7" t="str">
         <v/>
       </c>
       <c r="C7" t="str">
-        <v>お酒（特にビール）を飲む量はどれくらいですか／プリン体の多い食品（レバー・魚卵・干物など）をよく摂りますか／関節の痛みや腫れが出たことはありますか</v>
+        <v>お酒を飲む量や頻度に変化はありますか／新しく始めたお薬やサプリメントはありますか／だるさや黄疸（白目や皮膚が黄色くなること）のような症状はありませんか</v>
       </c>
       <c r="D7" t="str">
-        <v>【悪化した時】最近、お酒や食事で変わったことはありますか。水分を多めに摂ることも意識してみてください　【改善した時】数値が落ち着いています。今のペースを続けましょう</v>
+        <v>【悪化した時】最近、お酒の量やお薬で変わったことはありますか。少し肝臓に負担がかかっているようです　【改善した時】数値が落ち着いてきています。今の生活を続けていきましょう</v>
       </c>
       <c r="E7" t="str">
-        <v>尿酸降下薬を急に開始・増量すると痛風発作が誘発されることがある。水分摂取量、尿路結石の既往</v>
+        <v>新規開始薬剤による薬剤性肝障害の可能性。市販薬・サプリメント・健康食品の使用歴。飲酒量の申告は過小になりやすい</v>
       </c>
       <c r="F7" t="str">
         <v/>
@@ -3412,19 +3863,19 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>抗凝固療法（心房細動・血栓症）</v>
       </c>
       <c r="B8" t="str">
         <v/>
       </c>
       <c r="C8" t="str">
-        <v>立ちくらみやめまい、動悸、息切れはありませんか／食事量や偏りはありますか／黒い便や月経量の変化など、出血を疑う症状はありませんか</v>
+        <v>あざや出血が増えていませんか／歯ぐきや鼻からの出血、黒っぽい便はありませんか／新しく始めたお薬やサプリメント、納豆・青汁の摂取に変化はありませんか</v>
       </c>
       <c r="D8" t="str">
-        <v>【悪化した時】ふらつきや動悸は増えていませんか。原因を確認させてください　【改善した時】数値が良くなってきています。鉄剤は数値が戻ってからもしばらく続けることが大切です</v>
+        <v>【出血傾向がある時】念のため出血の状況を詳しく確認させてください　【安定している時】今のところ大きな変化はなさそうです。飲み合わせだけ念のため確認しますね</v>
       </c>
       <c r="E8" t="str">
-        <v>鉄剤は自己判断で早期中断されやすい。出血源（消化管出血・月経過多等）の精査が済んでいるか</v>
+        <v>ワルファリンはPT-INRのモニタリングと納豆・ビタミンK摂取の変動に注意。DOAC（エリキュース、リクシアナ、プラザキサ等）は腎排泄が多く腎機能低下時の用量調整が必要。NSAIDsとの併用による出血リスク増大</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -3432,19 +3883,19 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>電解質</v>
+        <v>抗血小板療法</v>
       </c>
       <c r="B9" t="str">
         <v/>
       </c>
       <c r="C9" t="str">
-        <v>下痢や嘔吐、大量の汗をかくことはありましたか／お通じの薬や利尿薬を新しく使い始めていませんか／脱力感やしびれ、動悸はありませんか</v>
+        <v>あざや出血が増えていませんか／歯ぐきの出血や鼻血が出やすくなっていませんか／手術や抜歯の予定はありませんか</v>
       </c>
       <c r="D9" t="str">
-        <v>【悪化した時】最近、体調やお薬で変わったことはありますか。むくみや脱力感はありませんか　【改善した時】数値は落ち着いています。水分やお食事は今のままで大丈夫そうです</v>
+        <v>【出血傾向がある時】あざや出血の状況を詳しく確認させてください　【安定している時】今のところ大きな変化はなさそうです</v>
       </c>
       <c r="E9" t="str">
-        <v>利尿薬・下剤・NSAIDsなど電解質に影響する薬剤の併用。高カリウム血症は自覚症状に乏しく数値での早期発見が重要</v>
+        <v>手術・抜歯前の休薬指示の有無（自己判断で中止しないよう説明）。他の抗血小板薬・抗凝固薬・NSAIDsとの併用による出血リスク増大</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -3452,19 +3903,19 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>骨粗鬆症</v>
+        <v>高尿酸血症</v>
       </c>
       <c r="B10" t="str">
         <v/>
       </c>
       <c r="C10" t="str">
-        <v>転倒やつまずきが増えていませんか／日光を浴びる機会や運動の習慣はありますか／カルシウムや乳製品を摂る頻度はどれくらいですか</v>
+        <v>お酒（特にビール）を飲む量はどれくらいですか／プリン体の多い食品（レバー・魚卵・干物など）をよく摂りますか／関節の痛みや腫れが出たことはありますか</v>
       </c>
       <c r="D10" t="str">
-        <v>【悪化した時】骨密度や数値が気になるところです。日光を浴びる時間や運動は取れていますか　【改善した時】治療の効果が出てきています。このまま続けていきましょう</v>
+        <v>【悪化した時】最近、お酒や食事で変わったことはありますか。水分を多めに摂ることも意識してみてください　【改善した時】数値が落ち着いています。今のペースを続けましょう</v>
       </c>
       <c r="E10" t="str">
-        <v>骨粗鬆症治療薬（ビスホスホネート等）の服用方法（起床時空腹時服用、服用後30分は横にならない、等）の再確認。転倒リスクとなる他剤（睡眠薬等）の併用</v>
+        <v>尿酸降下薬を急に開始・増量すると痛風発作が誘発されることがある。水分摂取量、尿路結石の既往</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -3492,19 +3943,19 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>抗凝固療法（心房細動・血栓症）</v>
+        <v>心不全</v>
       </c>
       <c r="B12" t="str">
         <v/>
       </c>
       <c r="C12" t="str">
-        <v>あざや出血が増えていませんか／歯ぐきや鼻からの出血、黒っぽい便はありませんか／新しく始めたお薬やサプリメント、納豆・青汁の摂取に変化はありませんか</v>
+        <v>階段や坂道で息切れしやすくなっていませんか／足や靴がきつくなるようなむくみはありませんか／体重は増えていませんか／夜、横になると苦しくて起き上がることはありませんか</v>
       </c>
       <c r="D12" t="str">
-        <v>【出血傾向がある時】念のため出血の状況を詳しく確認させてください　【安定している時】今のところ大きな変化はなさそうです。飲み合わせだけ念のため確認しますね</v>
+        <v>【数値が悪化した時】少し心臓に負担がかかっているサインかもしれません。むくみや体重の増減はありましたか　【数値が安定している時】今のところ落ち着いています。塩分と水分のとり方は今のままで大丈夫そうです</v>
       </c>
       <c r="E12" t="str">
-        <v>ワルファリンはPT-INRのモニタリングと納豆・ビタミンK摂取の変動に注意。DOAC（エリキュース、リクシアナ、プラザキサ等）は腎排泄が多く腎機能低下時の用量調整が必要。NSAIDsとの併用による出血リスク増大</v>
+        <v>体重の日々の変化（急な増加は水分貯留のサイン）。塩分・水分制限の理解度。NSAIDsなど心不全を悪化させうる薬剤の使用</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -3512,19 +3963,19 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>抗血小板療法</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="B13" t="str">
         <v/>
       </c>
       <c r="C13" t="str">
-        <v>あざや出血が増えていませんか／歯ぐきの出血や鼻血が出やすくなっていませんか／手術や抜歯の予定はありませんか</v>
+        <v>立ちくらみやめまい、動悸、息切れはありませんか／食事量や偏りはありますか／黒い便や月経量の変化など、出血を疑う症状はありませんか</v>
       </c>
       <c r="D13" t="str">
-        <v>【出血傾向がある時】あざや出血の状況を詳しく確認させてください　【安定している時】今のところ大きな変化はなさそうです</v>
+        <v>【悪化した時】ふらつきや動悸は増えていませんか。原因を確認させてください　【改善した時】数値が良くなってきています。鉄剤は数値が戻ってからもしばらく続けることが大切です</v>
       </c>
       <c r="E13" t="str">
-        <v>手術・抜歯前の休薬指示の有無（自己判断で中止しないよう説明）。他の抗血小板薬・抗凝固薬・NSAIDsとの併用による出血リスク増大</v>
+        <v>鉄剤は自己判断で早期中断されやすい。出血源（消化管出血・月経過多等）の精査が済んでいるか</v>
       </c>
       <c r="F13" t="str">
         <v/>
@@ -3552,19 +4003,19 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>精神疾患（非定型抗精神病薬）</v>
+        <v>電解質</v>
       </c>
       <c r="B15" t="str">
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>体重の増減はありませんか／のどの渇きや尿量の変化はありませんか／だるさや動きにくさが増えていませんか</v>
+        <v>下痢や嘔吐、大量の汗をかくことはありましたか／お通じの薬や利尿薬を新しく使い始めていませんか／脱力感やしびれ、動悸はありませんか</v>
       </c>
       <c r="D15" t="str">
-        <v>【体重増加や口渇がある時】念のため血糖や脂質の数値を確認しますね　【安定している時】今のところ大きな変化はなさそうです</v>
+        <v>【悪化した時】最近、体調やお薬で変わったことはありますか。むくみや脱力感はありませんか　【改善した時】数値は落ち着いています。水分やお食事は今のままで大丈夫そうです</v>
       </c>
       <c r="E15" t="str">
-        <v>非定型抗精神病薬（アリピプラゾール、クエチアピン、リスペリドン等）による代謝異常（高血糖・脂質異常・体重増加）は自覚症状に乏しく、定期的な血糖・脂質・肝機能のチェックが重要なこと。糖尿病がある場合オランザピン・クエチアピンは原則禁忌</v>
+        <v>利尿薬・下剤・NSAIDsなど電解質に影響する薬剤の併用。高カリウム血症は自覚症状に乏しく数値での早期発見が重要</v>
       </c>
       <c r="F15" t="str">
         <v/>

--- a/検査値リファレンス初期データ.xlsx
+++ b/検査値リファレンス初期データ.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M80"/>
+  <dimension ref="A1:M81"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -715,34 +715,34 @@
         <v>Na</v>
       </c>
       <c r="C8" t="str">
-        <v/>
+        <v>135〜145 mEq/L</v>
       </c>
       <c r="D8" t="str">
-        <v/>
+        <v>体内の水分バランスや神経・筋肉の働きに関わる、血液中に最も多い電解質</v>
       </c>
       <c r="E8" t="str">
-        <v/>
+        <v>ナトリウムは、体の中の水分バランスを保ったり、神経や筋肉が正しく働くために欠かせないミネラルです。多すぎても少なすぎても、意識障害やけいれんなど重い症状につながることがあります。</v>
       </c>
       <c r="F8" t="str">
-        <v>アルドステロン症、脱水</v>
+        <v>脱水、アルドステロン症、水分摂取不足、下痢・嘔吐による水分喪失</v>
       </c>
       <c r="G8" t="str">
         <v>水分摂取状況を確認する（脱水が疑われる場合）</v>
       </c>
       <c r="H8" t="str">
-        <v/>
+        <v>利尿薬（特にサイアザイド系）、SIADH（抗利尿ホルモン不適合分泌症候群）、嘔吐・下痢、心不全・肝硬変によるむくみ</v>
       </c>
       <c r="I8" t="str">
-        <v/>
+        <v>利尿薬使用中は嘔吐・下痢が続いていないか確認する。意識がぼんやりする、頭痛などの症状がないか確認する</v>
       </c>
       <c r="J8" t="str">
-        <v/>
+        <v>低ナトリウム血症は高齢者に多く、意識障害や転倒の原因になりうる。利尿薬（特にサイアザイド系）、SSRI、カルバマゼピンなどSIADHを起こしうる薬剤の使用歴を確認する</v>
       </c>
       <c r="K8" t="str">
         <v>電解質</v>
       </c>
       <c r="L8" t="str">
-        <v>ナトリウム,Na,電解質,脱水</v>
+        <v>ナトリウム,Na,電解質,脱水,SIADH,低ナトリウム血症</v>
       </c>
       <c r="M8" t="str">
         <v/>
@@ -841,25 +841,25 @@
         <v>8.5〜10.0 mg/dL</v>
       </c>
       <c r="D11" t="str">
-        <v/>
+        <v>骨や歯の材料であると同時に、神経・筋肉・血液凝固にも関わるミネラル</v>
       </c>
       <c r="E11" t="str">
-        <v/>
+        <v>カルシウムは骨や歯の材料になるだけでなく、神経の伝達や筋肉の収縮、血液を固める働きにも関わっている重要なミネラルです。副甲状腺ホルモンやビタミンDによって血液中の濃度が細かく調整されています。</v>
       </c>
       <c r="F11" t="str">
-        <v>副甲状腺機能亢進症</v>
+        <v>副甲状腺機能亢進症、悪性腫瘍（骨転移など）、ビタミンD過剰、活性型ビタミンD3製剤の過量</v>
       </c>
       <c r="G11" t="str">
-        <v/>
+        <v>吐き気、便秘、多尿、意識がぼんやりするなどの高カルシウム血症の症状がないか確認する。活性型ビタミンD3製剤使用中は過量になっていないか確認する</v>
       </c>
       <c r="H11" t="str">
-        <v/>
+        <v>副甲状腺機能低下症、ビタミンD欠乏、腎不全、低アルブミン血症（見かけ上の低下）</v>
       </c>
       <c r="I11" t="str">
-        <v/>
+        <v>手足のしびれやこむら返りなど低カルシウム血症の症状がないか確認する</v>
       </c>
       <c r="J11" t="str">
-        <v/>
+        <v>アルブミンが低いと見かけ上低く出るため、補正カルシウム値（Ca+(4-Alb)）で評価する。骨粗鬆症治療薬（活性型ビタミンD3製剤、デノスマブなど）使用中は高カルシウム血症の副作用に注意</v>
       </c>
       <c r="K11" t="str">
         <v>電解質,骨粗鬆症</v>
@@ -1008,7 +1008,7 @@
         <v>骨や肝臓・胆道に多く含まれる酵素で、骨を作る働きの指標にもなる</v>
       </c>
       <c r="E15" t="str">
-        <v/>
+        <v>ALPは骨や肝臓、胆道に多く含まれる酵素です。骨を作る働きが活発なとき（骨の成長期や骨折の治癒過程など）や、肝臓・胆道にトラブルがあるときに数値が上がります。</v>
       </c>
       <c r="F15" t="str">
         <v>骨代謝の亢進（骨折治癒過程、骨粗鬆症、骨転移、Paget病）、肝・胆道疾患、成長期の生理的高値</v>
@@ -1170,25 +1170,25 @@
         <v>150 mg/dL未満（空腹時）</v>
       </c>
       <c r="D19" t="str">
-        <v/>
+        <v>脂質異常症で高値になりやすい脂質で、食事の影響を強く受ける</v>
       </c>
       <c r="E19" t="str">
-        <v/>
+        <v>中性脂肪は、食事から摂った脂肪や糖質が体に蓄えられる形になったものです。食後は誰でも一時的に上がるため、正確に評価するには空腹時に採血することが大切です。高い状態が続くと動脈硬化や急性膵炎のリスクが高まります。</v>
       </c>
       <c r="F19" t="str">
-        <v>脂質異常症</v>
+        <v>脂質異常症、糖質・アルコールの摂りすぎ、肥満、糖尿病のコントロール不良</v>
       </c>
       <c r="G19" t="str">
         <v>糖質・アルコールの摂りすぎに注意し、有酸素運動を勧める</v>
       </c>
       <c r="H19" t="str">
-        <v/>
+        <v>低栄養、甲状腺機能亢進症</v>
       </c>
       <c r="I19" t="str">
         <v/>
       </c>
       <c r="J19" t="str">
-        <v/>
+        <v>採血が食後か空腹時かで数値が大きく変わるため必ず確認する。500 mg/dL以上では急性膵炎のリスクが高まるため注意。フィブラート系・EPA製剤などの効果判定に使う</v>
       </c>
       <c r="K19" t="str">
         <v>脂質異常症</v>
@@ -1211,25 +1211,25 @@
         <v>220 mg/dL未満</v>
       </c>
       <c r="D20" t="str">
-        <v/>
+        <v>LDL・HDLなどすべてのコレステロールを合わせた総量</v>
       </c>
       <c r="E20" t="str">
-        <v/>
+        <v>総コレステロールは、体の中にあるコレステロールをすべて合わせた数値です。ただし、悪玉(LDL)が多いのか善玉(HDL)が多いのかまでは分からないため、実際の評価にはLDLコレステロールの値がより重視されます。</v>
       </c>
       <c r="F20" t="str">
-        <v>脂質異常症</v>
+        <v>脂質異常症、家族性高コレステロール血症、甲状腺機能低下症</v>
       </c>
       <c r="G20" t="str">
         <v>動物性脂肪を控え、食物繊維を増やすよう伝える</v>
       </c>
       <c r="H20" t="str">
-        <v/>
+        <v>低栄養、肝機能低下、甲状腺機能亢進症</v>
       </c>
       <c r="I20" t="str">
         <v/>
       </c>
       <c r="J20" t="str">
-        <v/>
+        <v>現在はLDLコレステロールでの評価が主流。総コレステロールだけでは悪玉・善玉の内訳が分からないため、LDL・HDL・中性脂肪と合わせて評価する</v>
       </c>
       <c r="K20" t="str">
         <v>脂質異常症</v>
@@ -1335,10 +1335,10 @@
         <v>40 mg/dL以上</v>
       </c>
       <c r="D23" t="str">
-        <v/>
+        <v>いわゆる「善玉コレステロール」。血管にたまった余分なコレステロールを回収する</v>
       </c>
       <c r="E23" t="str">
-        <v/>
+        <v>HDLコレステロールは、いわゆる善玉コレステロールと呼ばれるものです。血管の壁にたまった余分なコレステロールを回収して肝臓に戻す働きがあり、数値が高いほど動脈硬化を防ぐ方向に働きます。</v>
       </c>
       <c r="F23" t="str">
         <v/>
@@ -1353,7 +1353,7 @@
         <v>適度な運動習慣、禁煙を勧める</v>
       </c>
       <c r="J23" t="str">
-        <v/>
+        <v>喫煙、運動不足、肥満で低下しやすい。禁煙・運動習慣の改善で上昇が期待できる。低HDLは動脈硬化のリスク因子として単独でも重視される</v>
       </c>
       <c r="K23" t="str">
         <v>脂質異常症</v>
@@ -1376,16 +1376,16 @@
         <v>男性 60〜250 U/L、女性 50〜170 U/L</v>
       </c>
       <c r="D24" t="str">
-        <v/>
+        <v>主に骨格筋・心筋に含まれる酵素。筋肉の損傷で血液中に漏れ出す</v>
       </c>
       <c r="E24" t="str">
-        <v/>
+        <v>CKは筋肉の中にある酵素で、激しい運動や筋肉の病気、心筋梗塞などで筋肉の細胞がダメージを受けると血液中に漏れ出して数値が上がります。スタチン系のお薬の副作用（横紋筋融解症）のチェックにも使われます。</v>
       </c>
       <c r="F24" t="str">
-        <v>心筋梗塞、横紋筋融解症などで上昇</v>
+        <v>心筋梗塞、横紋筋融解症（スタチン系薬剤の副作用など）、激しい運動、筋肉注射直後、甲状腺機能低下症</v>
       </c>
       <c r="G24" t="str">
-        <v/>
+        <v>筋肉痛・脱力感・褐色尿（横紋筋融解症の症状）がないか確認する。スタチン系薬剤服用中は特に注意する。激しい運動の直後の採血でないかも確認する</v>
       </c>
       <c r="H24" t="str">
         <v/>
@@ -1394,7 +1394,7 @@
         <v/>
       </c>
       <c r="J24" t="str">
-        <v/>
+        <v>スタチン系薬剤の重大な副作用である横紋筋融解症の指標。筋肉痛・脱力感・褐色尿の有無を必ず確認し、著明高値では服薬継続の可否を医師に相談する</v>
       </c>
       <c r="K24" t="str">
         <v/>
@@ -1408,7 +1408,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>尿蛋白</v>
+        <v>尿蛋白（随時尿）</v>
       </c>
       <c r="B25" t="str">
         <v>尿蛋白,U-pro</v>
@@ -1531,40 +1531,40 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>RDW-SD</v>
+        <v>赤血球</v>
       </c>
       <c r="B28" t="str">
-        <v>RDW-SD</v>
+        <v>RBC</v>
       </c>
       <c r="C28" t="str">
-        <v>39〜46 fL程度（施設差あり）</v>
+        <v>男性 435〜555万/μL、女性 386〜492万/μL程度（施設差あり）</v>
       </c>
       <c r="D28" t="str">
-        <v>赤血球の大きさのばらつきを表す指標(絶対値)。鉄欠乏性貧血などの初期変化を捉えやすい</v>
+        <v>血液中で酸素を運ぶ細胞の数。ヘモグロビン・ヘマトクリットと合わせて貧血・多血症を評価する</v>
       </c>
       <c r="E28" t="str">
-        <v>RDW-SDは、赤血球の大きさがどれくらいバラバラになっているかを表す数値です。貧血の原因を調べる際、鉄が足りなくなり始めた早い段階での変化を捉えるのに役立ちます。</v>
+        <v>赤血球は、肺で受け取った酸素を全身に運ぶ血液の細胞です。数が少ないと貧血、多いと多血症が疑われます。ヘモグロビンやヘマトクリットと合わせて総合的に評価します。</v>
       </c>
       <c r="F28" t="str">
-        <v>鉄欠乏性貧血の初期、混合性貧血（複数の原因が重なっている状態）、赤血球産生の乱れ</v>
+        <v>脱水、多血症（真性多血症、二次性多血症）、喫煙</v>
       </c>
       <c r="G28" t="str">
-        <v/>
+        <v>脱水が疑われる場合はこまめな水分摂取を勧める（水分制限がある場合を除く）</v>
       </c>
       <c r="H28" t="str">
-        <v/>
+        <v>貧血（鉄欠乏性貧血、腎性貧血など）、出血</v>
       </c>
       <c r="I28" t="str">
-        <v/>
+        <v>ヘモグロビンと同様に、出血や食事量低下がないか確認する</v>
       </c>
       <c r="J28" t="str">
-        <v>MCVが正常範囲でもRDWが上昇している場合、鉄欠乏の初期段階を示唆することがある。MCV・MCHと合わせて評価する</v>
+        <v>ヘモグロビン・ヘマトクリットと同じ方向に動くことが多い。赤血球数だけでなくMCV・MCH・MCHCと合わせて貧血のタイプ(小球性・正球性・大球性)を判断する</v>
       </c>
       <c r="K28" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
       <c r="L28" t="str">
-        <v>RDW-SD,赤血球分布幅,貧血,鉄欠乏</v>
+        <v>赤血球,RBC,貧血,多血症</v>
       </c>
       <c r="M28" t="str">
         <v/>
@@ -1572,40 +1572,40 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>RDW-CV</v>
+        <v>ヘモグロビン濃度</v>
       </c>
       <c r="B29" t="str">
-        <v>RDW-CV</v>
+        <v>Hb</v>
       </c>
       <c r="C29" t="str">
-        <v>11.5〜14.5%程度（施設差あり）</v>
+        <v>男性 13.5〜17.5 g/dL、女性 11.5〜15.0 g/dL</v>
       </c>
       <c r="D29" t="str">
-        <v>赤血球の大きさのばらつきを割合(%)で表した指標</v>
+        <v>血液の中で酸素を運ぶ役割をしている。この値が低い状態が貧血。</v>
       </c>
       <c r="E29" t="str">
-        <v>RDW-CVもRDW-SDと同じく、赤血球の大きさのばらつきを表す数値ですが、こちらは割合(%)で示されます。貧血のタイプを見分ける手がかりになります。</v>
+        <v>血の数値が良くなっても、体の中の鉄はまだ十分ではないことがあります。そのため、しばらく続けて飲むことが大切です。</v>
       </c>
       <c r="F29" t="str">
-        <v>鉄欠乏性貧血、ビタミンB12・葉酸欠乏性貧血、混合性貧血</v>
+        <v/>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v/>
+        <v>鉄欠乏性貧血、出血、腎性貧血、骨髄の造血機能低下</v>
       </c>
       <c r="I29" t="str">
-        <v/>
+        <v>鉄分の多い食品（レバー・赤身肉・魚・ほうれん草など）を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える</v>
       </c>
       <c r="J29" t="str">
-        <v>RDW-SDと同様の意味を持つ指標。MCVが小さくRDWが高ければ鉄欠乏性貧血、MCVが大きくRDWが高ければビタミンB12・葉酸欠乏を疑う手がかりになる</v>
+        <v>原因（出血・食事量低下など）の確認が重要。腎機能低下がある場合は鉄不足以外が原因のこともある。鉄剤はヘモグロビンが正常化した後も2〜3か月程度は継続することが多い（鉄の貯蔵分を補うため。途中でやめると再び貧血になりやすい）</v>
       </c>
       <c r="K29" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>鉄欠乏性貧血,抗血小板療法,抗凝固療法（心房細動・血栓症）</v>
       </c>
       <c r="L29" t="str">
-        <v>RDW-CV,赤血球分布幅,貧血,ビタミンB12,葉酸</v>
+        <v>ヘモグロビン,Hb,貧血,鉄剤,鉄欠乏性貧血</v>
       </c>
       <c r="M29" t="str">
         <v/>
@@ -1613,40 +1613,40 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>好中球</v>
+        <v>ヘマトクリット値</v>
       </c>
       <c r="B30" t="str">
-        <v>Neutro,Neut%</v>
+        <v>Ht,Hct</v>
       </c>
       <c r="C30" t="str">
-        <v>40〜75%程度（施設差あり）</v>
+        <v>男性 40〜50%、女性 35〜45%</v>
       </c>
       <c r="D30" t="str">
-        <v>白血球の中で最も多くを占め、細菌感染と戦う主力の免疫細胞の割合</v>
+        <v>血液全体のうち赤血球が占める体積の割合。貧血・脱水の指標</v>
       </c>
       <c r="E30" t="str">
-        <v>好中球は、白血球の中で最も数が多く、細菌が体に入ってきたときに真っ先に戦ってくれる免疫細胞です。感染症や炎症があると増え、逆に薬の副作用などで減ることがあります。</v>
+        <v>ヘマトクリットは、血液全体のうち赤血球が占める割合を表す数値です。この値が低いと貧血、高いと脱水や血液が濃くなっている状態が疑われます。</v>
       </c>
       <c r="F30" t="str">
-        <v>細菌感染症、炎症、ストレス、ステロイド使用</v>
+        <v>脱水、多血症（真性多血症、二次性多血症）、喫煙</v>
       </c>
       <c r="G30" t="str">
-        <v>発熱や炎症症状がないか確認する</v>
+        <v>脱水が疑われる場合はこまめな水分摂取を勧める（水分制限がある場合を除く）</v>
       </c>
       <c r="H30" t="str">
-        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、ウイルス感染、メルカゾールなど薬剤性の無顆粒球症</v>
+        <v>貧血（鉄欠乏性貧血、腎性貧血など）、出血</v>
       </c>
       <c r="I30" t="str">
-        <v>発熱やのどの痛みなど感染症状の初期サインがないか確認する</v>
+        <v>ヘモグロビンと同様に、出血や食事量低下がないか確認する</v>
       </c>
       <c r="J30" t="str">
-        <v>好中球の絶対数（好中球実数値）が500/μL未満になると重篤な感染症のリスクが高まる。割合(%)だけでなく実数値も合わせて確認する</v>
+        <v>ヘモグロビン・赤血球数と合わせて評価する。3つの値は同じ方向に動くことが多く、脱水があると貧血が見かけ上隠れることがある</v>
       </c>
       <c r="K30" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="L30" t="str">
-        <v>好中球,Neutro,Neut,感染症,無顆粒球症</v>
+        <v>ヘマトクリット,Ht,Hct,貧血,脱水,多血症</v>
       </c>
       <c r="M30" t="str">
         <v/>
@@ -1654,40 +1654,40 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>好中球実数値</v>
+        <v>MCV</v>
       </c>
       <c r="B31" t="str">
-        <v>Neutro#,ANC</v>
+        <v>MCV</v>
       </c>
       <c r="C31" t="str">
-        <v>2,000〜7,500 /μL程度（施設差あり、白血球数×好中球%で算出）</v>
+        <v>79〜100 fL</v>
       </c>
       <c r="D31" t="str">
-        <v>好中球の絶対数。感染症リスクを判断する上で割合(%)より重要な指標</v>
+        <v>赤血球1個の大きさ</v>
       </c>
       <c r="E31" t="str">
-        <v>これは好中球の実際の数を表す数値です。割合(%)だけでなく、実際の数がどれくらいあるかを見ることで、感染症にかかりやすい状態かどうかをより正確に判断できます。</v>
+        <v>MCVは赤血球1個あたりの大きさを表す数値です。貧血があるとき、この数値で「小さい貧血」か「大きい貧血」かを見分けることができ、原因を絞り込む手がかりになります。</v>
       </c>
       <c r="F31" t="str">
-        <v>細菌感染症、炎症、ステロイド使用</v>
+        <v/>
       </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、メルカゾールなど薬剤性の無顆粒球症（1,000/μL未満で好中球減少症、500/μL未満で重症感染リスクが著しく上昇）</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="I31" t="str">
-        <v>発熱、のどの痛みなど感染症状の初期サインがないか確認する。人混みを避け、手洗い・うがいを徹底するよう伝える</v>
+        <v>鉄分の多い食事を意識する（ヘモグロビンの項目を参照）</v>
       </c>
       <c r="J31" t="str">
-        <v>抗がん剤・メルカゾール・カルバマゼピンなど骨髄抑制のリスクがある薬剤使用中は特に重視すべき数値。500/μL未満は発熱性好中球減少症のリスクが高く緊急性が高い</v>
+        <v/>
       </c>
       <c r="K31" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="L31" t="str">
-        <v>好中球実数値,好中球数,ANC,無顆粒球症,発熱性好中球減少症</v>
+        <v>MCV,赤血球指数,貧血</v>
       </c>
       <c r="M31" t="str">
         <v/>
@@ -1695,40 +1695,40 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>好酸球</v>
+        <v>MCH</v>
       </c>
       <c r="B32" t="str">
-        <v>Eosino,Eos%</v>
+        <v>MCH</v>
       </c>
       <c r="C32" t="str">
-        <v>1〜5%程度（施設差あり）</v>
+        <v>26.3〜34.3 pg</v>
       </c>
       <c r="D32" t="str">
-        <v>アレルギー反応や寄生虫感染に関わる白血球の一種の割合</v>
+        <v>赤血球1個に含まれるヘモグロビン量</v>
       </c>
       <c r="E32" t="str">
-        <v>好酸球は、アレルギー反応や寄生虫感染と関係が深い免疫細胞です。アレルギー性の病気や薬の副作用（薬疹など）で増えることがあります。</v>
+        <v>MCHは赤血球1個の中に含まれるヘモグロビン（酸素を運ぶ色素）の量を表す数値です。MCVと同じく、貧血の種類を見分けるのに使われます。</v>
       </c>
       <c r="F32" t="str">
-        <v>アレルギー性疾患（気管支喘息、アトピー性皮膚炎など）、薬剤アレルギー、寄生虫感染</v>
+        <v/>
       </c>
       <c r="G32" t="str">
-        <v>新しく始めた薬がないか確認する。皮疹やかゆみなどアレルギー症状の有無を確認する</v>
+        <v/>
       </c>
       <c r="H32" t="str">
-        <v/>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="I32" t="str">
-        <v/>
+        <v>鉄分の多い食事を意識する（ヘモグロビンの項目を参照）</v>
       </c>
       <c r="J32" t="str">
-        <v>薬剤性の好酸球増多は、原因薬剤の中止で改善することが多い。新規薬剤開始後の皮疹・発熱と合わせて薬剤性過敏症症候群(DIHS)を疑う材料になる</v>
+        <v/>
       </c>
       <c r="K32" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="L32" t="str">
-        <v>好酸球,Eosino,Eos,アレルギー,薬疹,DIHS</v>
+        <v>MCH,赤血球指数,貧血</v>
       </c>
       <c r="M32" t="str">
         <v/>
@@ -1736,40 +1736,40 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>好酸球実数値</v>
+        <v>MCHC</v>
       </c>
       <c r="B33" t="str">
-        <v>Eosino#</v>
+        <v>MCHC</v>
       </c>
       <c r="C33" t="str">
-        <v>100〜500 /μL程度（施設差あり）</v>
+        <v>31.6〜36.6 %</v>
       </c>
       <c r="D33" t="str">
-        <v>好酸球の絶対数。アレルギーや薬剤反応の程度をより正確に評価できる</v>
+        <v>単位容積あたりの赤血球に含まれるヘモグロビン濃度</v>
       </c>
       <c r="E33" t="str">
-        <v>これは好酸球の実際の数を表す数値です。割合(%)だけでなく実数を見ることで、アレルギー反応の強さをより正確に把握できます。</v>
+        <v>MCHCは、赤血球の中にヘモグロビンがどれくらい濃く詰まっているかを表す数値です。鉄が不足すると、この濃度も薄くなる傾向があります。</v>
       </c>
       <c r="F33" t="str">
-        <v>アレルギー性疾患、薬剤アレルギー、寄生虫感染</v>
+        <v/>
       </c>
       <c r="G33" t="str">
-        <v>新しく始めた薬がないか確認する</v>
+        <v/>
       </c>
       <c r="H33" t="str">
-        <v/>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="I33" t="str">
-        <v/>
+        <v>鉄分の多い食事を意識する（ヘモグロビンの項目を参照）</v>
       </c>
       <c r="J33" t="str">
-        <v>薬剤性過敏症症候群(DIHS)などでは著明な好酸球増多を認めることがあり、原因薬剤の特定に役立つ</v>
+        <v/>
       </c>
       <c r="K33" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="L33" t="str">
-        <v>好酸球実数値,好酸球数,アレルギー,DIHS</v>
+        <v>MCHC,赤血球指数,貧血</v>
       </c>
       <c r="M33" t="str">
         <v/>
@@ -1777,40 +1777,40 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>好塩基球</v>
+        <v>血小板数</v>
       </c>
       <c r="B34" t="str">
-        <v>Baso,Baso%</v>
+        <v>Plt</v>
       </c>
       <c r="C34" t="str">
-        <v>0〜2%程度（施設差あり）</v>
+        <v>15.0〜35.0万/μL程度（施設差あり）</v>
       </c>
       <c r="D34" t="str">
-        <v>白血球の中で最も数が少なく、アレルギー反応に関わる細胞の割合</v>
+        <v>出血を止める働きをする血液成分で、少なすぎると出血しやすくなる</v>
       </c>
       <c r="E34" t="str">
-        <v>好塩基球は白血球の中で最も数が少ない種類で、アレルギー反応や炎症に関わっています。数値の変動が病気の診断に直接使われることは少ない検査です。</v>
+        <v>血小板は、血管が傷ついたときに集まって血を止める役割をする血液の成分です。数が少ないとあざができやすくなったり、出血が止まりにくくなったりします。抗血小板薬や抗がん剤を使っている方では、定期的にチェックすることが大切です。</v>
       </c>
       <c r="F34" t="str">
-        <v>慢性骨髄性白血病などの血液疾患、アレルギー性疾患、甲状腺機能低下症</v>
+        <v>炎症性疾患、鉄欠乏性貧血、脾摘後、骨髄増殖性疾患</v>
       </c>
       <c r="G34" t="str">
         <v/>
       </c>
       <c r="H34" t="str">
-        <v/>
+        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、肝硬変・脾機能亢進、再生不良性貧血、抗てんかん薬（バルプロ酸など）の副作用、ITP（特発性血小板減少性紫斑病）</v>
       </c>
       <c r="I34" t="str">
-        <v/>
+        <v>あざができやすい、歯ぐきや鼻からの出血が増えていないか確認する。強い運動や転倒によるけがに注意するよう伝える</v>
       </c>
       <c r="J34" t="str">
-        <v>単独での臨床的意義は乏しいが、著明な増加は血液疾患（慢性骨髄性白血病等）の可能性があり他の血球指標と合わせて評価する</v>
+        <v>抗血小板薬・抗凝固薬使用中に血小板減少があると出血リスクがさらに高まる。抗がん剤・バルプロ酸・カルバマゼピンなど骨髄抑制のリスクがある薬剤使用中は定期採血の実施状況を確認する</v>
       </c>
       <c r="K34" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>てんかん,抗血小板療法</v>
       </c>
       <c r="L34" t="str">
-        <v>好塩基球,Baso,アレルギー,白血病</v>
+        <v>血小板,Plt,platelet,出血,あざ,紫斑,骨髄抑制</v>
       </c>
       <c r="M34" t="str">
         <v/>
@@ -1818,22 +1818,22 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>好塩基球実数値</v>
+        <v>RDW-SD</v>
       </c>
       <c r="B35" t="str">
-        <v>Baso#</v>
+        <v>RDW-SD</v>
       </c>
       <c r="C35" t="str">
-        <v>0〜100 /μL程度（施設差あり）</v>
+        <v>39〜46 fL程度（施設差あり）</v>
       </c>
       <c r="D35" t="str">
-        <v>好塩基球の絶対数</v>
+        <v>赤血球の大きさのばらつきを表す指標(絶対値)。鉄欠乏性貧血などの初期変化を捉えやすい</v>
       </c>
       <c r="E35" t="str">
-        <v>これは好塩基球の実際の数を表す数値です。数がとても少ない種類の血球なので、通常は大きな変動を示すことは多くありません。</v>
+        <v>RDW-SDは、赤血球の大きさがどれくらいバラバラになっているかを表す数値です。貧血の原因を調べる際、鉄が足りなくなり始めた早い段階での変化を捉えるのに役立ちます。</v>
       </c>
       <c r="F35" t="str">
-        <v>慢性骨髄性白血病などの血液疾患、アレルギー性疾患</v>
+        <v>鉄欠乏性貧血の初期、混合性貧血（複数の原因が重なっている状態）、赤血球産生の乱れ</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1845,13 +1845,13 @@
         <v/>
       </c>
       <c r="J35" t="str">
-        <v>単独での臨床的意義は乏しく、他の血球指標（白血球分画全体）と合わせて評価する</v>
+        <v>MCVが正常範囲でもRDWが上昇している場合、鉄欠乏の初期段階を示唆することがある。MCV・MCHと合わせて評価する</v>
       </c>
       <c r="K35" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="L35" t="str">
-        <v>好塩基球実数値,好塩基球数</v>
+        <v>RDW-SD,赤血球分布幅,貧血,鉄欠乏</v>
       </c>
       <c r="M35" t="str">
         <v/>
@@ -1859,40 +1859,40 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>リンパ球</v>
+        <v>RDW-CV</v>
       </c>
       <c r="B36" t="str">
-        <v>Lympho,Lym%</v>
+        <v>RDW-CV</v>
       </c>
       <c r="C36" t="str">
-        <v>18〜49%程度（施設差あり）</v>
+        <v>11.5〜14.5%程度（施設差あり）</v>
       </c>
       <c r="D36" t="str">
-        <v>ウイルス感染と戦い、免疫の記憶を担う白血球の割合</v>
+        <v>赤血球の大きさのばらつきを割合(%)で表した指標</v>
       </c>
       <c r="E36" t="str">
-        <v>リンパ球は、ウイルスと戦ったり、一度かかった病気を記憶して免疫をつくったりする細胞です。ウイルス感染で増え、抗がん剤の副作用や強いストレスで減ることがあります。</v>
+        <v>RDW-CVもRDW-SDと同じく、赤血球の大きさのばらつきを表す数値ですが、こちらは割合(%)で示されます。貧血のタイプを見分ける手がかりになります。</v>
       </c>
       <c r="F36" t="str">
-        <v>ウイルス感染症、リンパ性白血病などの血液疾患、百日咳</v>
+        <v>鉄欠乏性貧血、ビタミンB12・葉酸欠乏性貧血、混合性貧血</v>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>抗がん剤・免疫抑制剤・ステロイドの使用、強いストレス、AIDSなどの免疫不全</v>
+        <v/>
       </c>
       <c r="I36" t="str">
-        <v>免疫が下がっている可能性があるため、感染予防（手洗い・うがい、人混みを避ける）を意識するよう伝える</v>
+        <v/>
       </c>
       <c r="J36" t="str">
-        <v>ステロイド・免疫抑制剤使用中はリンパ球減少による易感染性に注意。好中球と逆方向に動くことが多い（ウイルス感染ではリンパ球優位、細菌感染では好中球優位になりやすい）</v>
+        <v>RDW-SDと同様の意味を持つ指標。MCVが小さくRDWが高ければ鉄欠乏性貧血、MCVが大きくRDWが高ければビタミンB12・葉酸欠乏を疑う手がかりになる</v>
       </c>
       <c r="K36" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="L36" t="str">
-        <v>リンパ球,Lympho,Lym,ウイルス感染,免疫抑制剤,ステロイド</v>
+        <v>RDW-CV,赤血球分布幅,貧血,ビタミンB12,葉酸</v>
       </c>
       <c r="M36" t="str">
         <v/>
@@ -1900,40 +1900,40 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>リンパ球実数値</v>
+        <v>好中球実数値</v>
       </c>
       <c r="B37" t="str">
-        <v>Lympho#,ALC</v>
+        <v>Neutro#,ANC</v>
       </c>
       <c r="C37" t="str">
-        <v>1,000〜3,600 /μL程度（施設差あり）</v>
+        <v>2,000〜7,500 /μL程度（施設差あり、白血球数×好中球%で算出）</v>
       </c>
       <c r="D37" t="str">
-        <v>リンパ球の絶対数。免疫力の目安として使われる</v>
+        <v>好中球の絶対数。感染症リスクを判断する上で割合(%)より重要な指標</v>
       </c>
       <c r="E37" t="str">
-        <v>これはリンパ球の実際の数を表す数値です。免疫力の目安の一つとして使われ、抗がん剤や免疫抑制剤の副作用モニタリングにも用いられます。</v>
+        <v>これは好中球の実際の数を表す数値です。割合(%)だけでなく、実際の数がどれくらいあるかを見ることで、感染症にかかりやすい状態かどうかをより正確に判断できます。</v>
       </c>
       <c r="F37" t="str">
-        <v>ウイルス感染症、リンパ性白血病などの血液疾患</v>
+        <v>細菌感染症、炎症、ステロイド使用</v>
       </c>
       <c r="G37" t="str">
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>抗がん剤・免疫抑制剤・ステロイドの使用、強いストレス、AIDSなどの免疫不全</v>
+        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、メルカゾールなど薬剤性の無顆粒球症（1,000/μL未満で好中球減少症、500/μL未満で重症感染リスクが著しく上昇）</v>
       </c>
       <c r="I37" t="str">
-        <v>感染予防（手洗い・うがい、人混みを避ける）を意識するよう伝える</v>
+        <v>発熱、のどの痛みなど感染症状の初期サインがないか確認する。人混みを避け、手洗い・うがいを徹底するよう伝える</v>
       </c>
       <c r="J37" t="str">
-        <v>免疫抑制剤・抗がん剤治療中のモニタリング指標としても使われる。著明な低下時は日和見感染のリスクが高まる</v>
+        <v>抗がん剤・メルカゾール・カルバマゼピンなど骨髄抑制のリスクがある薬剤使用中は特に重視すべき数値。500/μL未満は発熱性好中球減少症のリスクが高く緊急性が高い</v>
       </c>
       <c r="K37" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L37" t="str">
-        <v>リンパ球実数値,リンパ球数,ALC,免疫抑制剤,日和見感染</v>
+        <v>好中球実数値,好中球数,ANC,無顆粒球症,発熱性好中球減少症</v>
       </c>
       <c r="M37" t="str">
         <v/>
@@ -1941,25 +1941,25 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>単球</v>
+        <v>好酸球実数値</v>
       </c>
       <c r="B38" t="str">
-        <v>Mono,Mono%</v>
+        <v>Eosino#</v>
       </c>
       <c r="C38" t="str">
-        <v>2〜10%程度（施設差あり）</v>
+        <v>100〜500 /μL程度（施設差あり）</v>
       </c>
       <c r="D38" t="str">
-        <v>感染や炎症の後始末をする白血球の一種の割合</v>
+        <v>好酸球の絶対数。アレルギーや薬剤反応の程度をより正確に評価できる</v>
       </c>
       <c r="E38" t="str">
-        <v>単球は、細菌などを取り込んで処理したり、組織の修復に関わったりする免疫細胞です。慢性的な炎症や感染症の回復期に増えることがあります。</v>
+        <v>これは好酸球の実際の数を表す数値です。割合(%)だけでなく実数を見ることで、アレルギー反応の強さをより正確に把握できます。</v>
       </c>
       <c r="F38" t="str">
-        <v>慢性感染症（結核など）、炎症性疾患、血液疾患、感染症の回復期</v>
+        <v>アレルギー性疾患、薬剤アレルギー、寄生虫感染</v>
       </c>
       <c r="G38" t="str">
-        <v/>
+        <v>新しく始めた薬がないか確認する</v>
       </c>
       <c r="H38" t="str">
         <v/>
@@ -1968,13 +1968,13 @@
         <v/>
       </c>
       <c r="J38" t="str">
-        <v>単独での臨床的意義は乏しく、他の血球指標や炎症マーカー(CRPなど)と合わせて評価する</v>
+        <v>薬剤性過敏症症候群(DIHS)などでは著明な好酸球増多を認めることがあり、原因薬剤の特定に役立つ</v>
       </c>
       <c r="K38" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L38" t="str">
-        <v>単球,Mono,慢性感染症,結核,炎症</v>
+        <v>好酸球実数値,好酸球数,アレルギー,DIHS</v>
       </c>
       <c r="M38" t="str">
         <v/>
@@ -1982,22 +1982,22 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>単球実数値</v>
+        <v>好塩基球実数値</v>
       </c>
       <c r="B39" t="str">
-        <v>Mono#</v>
+        <v>Baso#</v>
       </c>
       <c r="C39" t="str">
-        <v>200〜600 /μL程度（施設差あり）</v>
+        <v>0〜100 /μL程度（施設差あり）</v>
       </c>
       <c r="D39" t="str">
-        <v>単球の絶対数</v>
+        <v>好塩基球の絶対数</v>
       </c>
       <c r="E39" t="str">
-        <v>これは単球の実際の数を表す数値です。慢性的な炎症や感染症の状態を把握する材料の一つになります。</v>
+        <v>これは好塩基球の実際の数を表す数値です。数がとても少ない種類の血球なので、通常は大きな変動を示すことは多くありません。</v>
       </c>
       <c r="F39" t="str">
-        <v>慢性感染症、炎症性疾患、血液疾患</v>
+        <v>慢性骨髄性白血病などの血液疾患、アレルギー性疾患</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="J39" t="str">
-        <v>単独での臨床的意義は乏しく、他の血球指標と合わせて評価する</v>
+        <v>単独での臨床的意義は乏しく、他の血球指標（白血球分画全体）と合わせて評価する</v>
       </c>
       <c r="K39" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L39" t="str">
-        <v>単球実数値,単球数</v>
+        <v>好塩基球実数値,好塩基球数</v>
       </c>
       <c r="M39" t="str">
         <v/>
@@ -2023,40 +2023,40 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ヘモグロビン濃度</v>
+        <v>リンパ球実数値</v>
       </c>
       <c r="B40" t="str">
-        <v>Hb</v>
+        <v>Lympho#,ALC</v>
       </c>
       <c r="C40" t="str">
-        <v>男性 13.5〜17.5 g/dL、女性 11.5〜15.0 g/dL</v>
+        <v>1,000〜3,600 /μL程度（施設差あり）</v>
       </c>
       <c r="D40" t="str">
-        <v>血液の中で酸素を運ぶ役割をしている。この値が低い状態が貧血。</v>
+        <v>リンパ球の絶対数。免疫力の目安として使われる</v>
       </c>
       <c r="E40" t="str">
-        <v>血の数値が良くなっても、体の中の鉄はまだ十分ではないことがあります。そのため、しばらく続けて飲むことが大切です。</v>
+        <v>これはリンパ球の実際の数を表す数値です。免疫力の目安の一つとして使われ、抗がん剤や免疫抑制剤の副作用モニタリングにも用いられます。</v>
       </c>
       <c r="F40" t="str">
-        <v/>
+        <v>ウイルス感染症、リンパ性白血病などの血液疾患</v>
       </c>
       <c r="G40" t="str">
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>鉄欠乏性貧血、出血、腎性貧血、骨髄の造血機能低下</v>
+        <v>抗がん剤・免疫抑制剤・ステロイドの使用、強いストレス、AIDSなどの免疫不全</v>
       </c>
       <c r="I40" t="str">
-        <v>鉄分の多い食品（レバー・赤身肉・魚・ほうれん草など）を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える</v>
+        <v>感染予防（手洗い・うがい、人混みを避ける）を意識するよう伝える</v>
       </c>
       <c r="J40" t="str">
-        <v>原因（出血・食事量低下など）の確認が重要。腎機能低下がある場合は鉄不足以外が原因のこともある。鉄剤はヘモグロビンが正常化した後も2〜3か月程度は継続することが多い（鉄の貯蔵分を補うため。途中でやめると再び貧血になりやすい）</v>
+        <v>免疫抑制剤・抗がん剤治療中のモニタリング指標としても使われる。著明な低下時は日和見感染のリスクが高まる</v>
       </c>
       <c r="K40" t="str">
-        <v>鉄欠乏性貧血,抗血小板療法,抗凝固療法（心房細動・血栓症）</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L40" t="str">
-        <v>ヘモグロビン,Hb,貧血,鉄剤,鉄欠乏性貧血</v>
+        <v>リンパ球実数値,リンパ球数,ALC,免疫抑制剤,日和見感染</v>
       </c>
       <c r="M40" t="str">
         <v/>
@@ -2064,40 +2064,40 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ヘマトクリット値</v>
+        <v>単球実数値</v>
       </c>
       <c r="B41" t="str">
-        <v>Ht,Hct</v>
+        <v>Mono#</v>
       </c>
       <c r="C41" t="str">
-        <v>男性 40〜50%、女性 35〜45%</v>
+        <v>200〜600 /μL程度（施設差あり）</v>
       </c>
       <c r="D41" t="str">
-        <v>血液全体のうち赤血球が占める体積の割合。貧血・脱水の指標</v>
+        <v>単球の絶対数</v>
       </c>
       <c r="E41" t="str">
-        <v>ヘマトクリットは、血液全体のうち赤血球が占める割合を表す数値です。この値が低いと貧血、高いと脱水や血液が濃くなっている状態が疑われます。</v>
+        <v>これは単球の実際の数を表す数値です。慢性的な炎症や感染症の状態を把握する材料の一つになります。</v>
       </c>
       <c r="F41" t="str">
-        <v>脱水、多血症（真性多血症、二次性多血症）、喫煙</v>
+        <v>慢性感染症、炎症性疾患、血液疾患</v>
       </c>
       <c r="G41" t="str">
-        <v>脱水が疑われる場合はこまめな水分摂取を勧める（水分制限がある場合を除く）</v>
+        <v/>
       </c>
       <c r="H41" t="str">
-        <v>貧血（鉄欠乏性貧血、腎性貧血など）、出血</v>
+        <v/>
       </c>
       <c r="I41" t="str">
-        <v>ヘモグロビンと同様に、出血や食事量低下がないか確認する</v>
+        <v/>
       </c>
       <c r="J41" t="str">
-        <v>ヘモグロビン・赤血球数と合わせて評価する。3つの値は同じ方向に動くことが多く、脱水があると貧血が見かけ上隠れることがある</v>
+        <v>単独での臨床的意義は乏しく、他の血球指標と合わせて評価する</v>
       </c>
       <c r="K41" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L41" t="str">
-        <v>ヘマトクリット,Ht,Hct,貧血,脱水,多血症</v>
+        <v>単球実数値,単球数</v>
       </c>
       <c r="M41" t="str">
         <v/>
@@ -2105,40 +2105,40 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>MCV</v>
+        <v>好中球</v>
       </c>
       <c r="B42" t="str">
-        <v>MCV</v>
+        <v>Neutro,Neut%</v>
       </c>
       <c r="C42" t="str">
-        <v>79〜100 fL</v>
+        <v>40〜75%程度（施設差あり）</v>
       </c>
       <c r="D42" t="str">
-        <v>赤血球1個の大きさ</v>
+        <v>白血球の中で最も多くを占め、細菌感染と戦う主力の免疫細胞の割合</v>
       </c>
       <c r="E42" t="str">
-        <v/>
+        <v>好中球は、白血球の中で最も数が多く、細菌が体に入ってきたときに真っ先に戦ってくれる免疫細胞です。感染症や炎症があると増え、逆に薬の副作用などで減ることがあります。</v>
       </c>
       <c r="F42" t="str">
-        <v/>
+        <v>細菌感染症、炎症、ストレス、ステロイド使用</v>
       </c>
       <c r="G42" t="str">
-        <v/>
+        <v>発熱や炎症症状がないか確認する</v>
       </c>
       <c r="H42" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、ウイルス感染、メルカゾールなど薬剤性の無顆粒球症</v>
       </c>
       <c r="I42" t="str">
-        <v>鉄分の多い食事を意識する（ヘモグロビンの項目を参照）</v>
+        <v>発熱やのどの痛みなど感染症状の初期サインがないか確認する</v>
       </c>
       <c r="J42" t="str">
-        <v/>
+        <v>好中球の絶対数（好中球実数値）が500/μL未満になると重篤な感染症のリスクが高まる。割合(%)だけでなく実数値も合わせて確認する</v>
       </c>
       <c r="K42" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L42" t="str">
-        <v>MCV,赤血球指数,貧血</v>
+        <v>好中球,Neutro,Neut,感染症,無顆粒球症</v>
       </c>
       <c r="M42" t="str">
         <v/>
@@ -2146,40 +2146,40 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>MCH</v>
+        <v>好酸球</v>
       </c>
       <c r="B43" t="str">
-        <v>MCH</v>
+        <v>Eosino,Eos%</v>
       </c>
       <c r="C43" t="str">
-        <v>26.3〜34.3 pg</v>
+        <v>1〜5%程度（施設差あり）</v>
       </c>
       <c r="D43" t="str">
-        <v>赤血球1個に含まれるヘモグロビン量</v>
+        <v>アレルギー反応や寄生虫感染に関わる白血球の一種の割合</v>
       </c>
       <c r="E43" t="str">
-        <v/>
+        <v>好酸球は、アレルギー反応や寄生虫感染と関係が深い免疫細胞です。アレルギー性の病気や薬の副作用（薬疹など）で増えることがあります。</v>
       </c>
       <c r="F43" t="str">
-        <v/>
+        <v>アレルギー性疾患（気管支喘息、アトピー性皮膚炎など）、薬剤アレルギー、寄生虫感染</v>
       </c>
       <c r="G43" t="str">
-        <v/>
+        <v>新しく始めた薬がないか確認する。皮疹やかゆみなどアレルギー症状の有無を確認する</v>
       </c>
       <c r="H43" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v/>
       </c>
       <c r="I43" t="str">
-        <v>鉄分の多い食事を意識する（ヘモグロビンの項目を参照）</v>
+        <v/>
       </c>
       <c r="J43" t="str">
-        <v/>
+        <v>薬剤性の好酸球増多は、原因薬剤の中止で改善することが多い。新規薬剤開始後の皮疹・発熱と合わせて薬剤性過敏症症候群(DIHS)を疑う材料になる</v>
       </c>
       <c r="K43" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L43" t="str">
-        <v>MCH,赤血球指数,貧血</v>
+        <v>好酸球,Eosino,Eos,アレルギー,薬疹,DIHS</v>
       </c>
       <c r="M43" t="str">
         <v/>
@@ -2187,40 +2187,40 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>MCHC</v>
+        <v>好塩基球</v>
       </c>
       <c r="B44" t="str">
-        <v>MCHC</v>
+        <v>Baso,Baso%</v>
       </c>
       <c r="C44" t="str">
-        <v>31.6〜36.6 %</v>
+        <v>0〜2%程度（施設差あり）</v>
       </c>
       <c r="D44" t="str">
-        <v>単位容積あたりの赤血球に含まれるヘモグロビン濃度</v>
+        <v>白血球の中で最も数が少なく、アレルギー反応に関わる細胞の割合</v>
       </c>
       <c r="E44" t="str">
-        <v/>
+        <v>好塩基球は白血球の中で最も数が少ない種類で、アレルギー反応や炎症に関わっています。数値の変動が病気の診断に直接使われることは少ない検査です。</v>
       </c>
       <c r="F44" t="str">
-        <v/>
+        <v>慢性骨髄性白血病などの血液疾患、アレルギー性疾患、甲状腺機能低下症</v>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v/>
       </c>
       <c r="I44" t="str">
-        <v>鉄分の多い食事を意識する（ヘモグロビンの項目を参照）</v>
+        <v/>
       </c>
       <c r="J44" t="str">
-        <v/>
+        <v>単独での臨床的意義は乏しいが、著明な増加は血液疾患（慢性骨髄性白血病等）の可能性があり他の血球指標と合わせて評価する</v>
       </c>
       <c r="K44" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L44" t="str">
-        <v>MCHC,赤血球指数,貧血</v>
+        <v>好塩基球,Baso,アレルギー,白血病</v>
       </c>
       <c r="M44" t="str">
         <v/>
@@ -2228,40 +2228,40 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>血小板数</v>
+        <v>リンパ球</v>
       </c>
       <c r="B45" t="str">
-        <v>Plt</v>
+        <v>Lympho,Lym%</v>
       </c>
       <c r="C45" t="str">
-        <v>15.0〜35.0万/μL程度（施設差あり）</v>
+        <v>18〜49%程度（施設差あり）</v>
       </c>
       <c r="D45" t="str">
-        <v>出血を止める働きをする血液成分で、少なすぎると出血しやすくなる</v>
+        <v>ウイルス感染と戦い、免疫の記憶を担う白血球の割合</v>
       </c>
       <c r="E45" t="str">
-        <v>血小板は、血管が傷ついたときに集まって血を止める役割をする血液の成分です。数が少ないとあざができやすくなったり、出血が止まりにくくなったりします。抗血小板薬や抗がん剤を使っている方では、定期的にチェックすることが大切です。</v>
+        <v>リンパ球は、ウイルスと戦ったり、一度かかった病気を記憶して免疫をつくったりする細胞です。ウイルス感染で増え、抗がん剤の副作用や強いストレスで減ることがあります。</v>
       </c>
       <c r="F45" t="str">
-        <v>炎症性疾患、鉄欠乏性貧血、脾摘後、骨髄増殖性疾患</v>
+        <v>ウイルス感染症、リンパ性白血病などの血液疾患、百日咳</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、肝硬変・脾機能亢進、再生不良性貧血、抗てんかん薬（バルプロ酸など）の副作用、ITP（特発性血小板減少性紫斑病）</v>
+        <v>抗がん剤・免疫抑制剤・ステロイドの使用、強いストレス、AIDSなどの免疫不全</v>
       </c>
       <c r="I45" t="str">
-        <v>あざができやすい、歯ぐきや鼻からの出血が増えていないか確認する。強い運動や転倒によるけがに注意するよう伝える</v>
+        <v>免疫が下がっている可能性があるため、感染予防（手洗い・うがい、人混みを避ける）を意識するよう伝える</v>
       </c>
       <c r="J45" t="str">
-        <v>抗血小板薬・抗凝固薬使用中に血小板減少があると出血リスクがさらに高まる。抗がん剤・バルプロ酸・カルバマゼピンなど骨髄抑制のリスクがある薬剤使用中は定期採血の実施状況を確認する</v>
+        <v>ステロイド・免疫抑制剤使用中はリンパ球減少による易感染性に注意。好中球と逆方向に動くことが多い（ウイルス感染ではリンパ球優位、細菌感染では好中球優位になりやすい）</v>
       </c>
       <c r="K45" t="str">
-        <v>てんかん,抗血小板療法</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L45" t="str">
-        <v>血小板,Plt,platelet,出血,あざ,紫斑,骨髄抑制</v>
+        <v>リンパ球,Lympho,Lym,ウイルス感染,免疫抑制剤,ステロイド</v>
       </c>
       <c r="M45" t="str">
         <v/>
@@ -2269,40 +2269,40 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>尿pH</v>
+        <v>単球</v>
       </c>
       <c r="B46" t="str">
-        <v>尿pH</v>
+        <v>Mono,Mono%</v>
       </c>
       <c r="C46" t="str">
-        <v>4.5〜7.5程度（弱酸性が多い）</v>
+        <v>2〜10%程度（施設差あり）</v>
       </c>
       <c r="D46" t="str">
-        <v>尿の酸性・アルカリ性の度合い。食事や感染症、体の状態を反映する</v>
+        <v>感染や炎症の後始末をする白血球の一種の割合</v>
       </c>
       <c r="E46" t="str">
-        <v>尿のpHは酸性・アルカリ性のバランスを表します。食事の内容や感染症、体の代謝状態によって変化します。単独で大きな問題を示すことは少ない検査です。</v>
+        <v>単球は、細菌などを取り込んで処理したり、組織の修復に関わったりする免疫細胞です。慢性的な炎症や感染症の回復期に増えることがあります。</v>
       </c>
       <c r="F46" t="str">
-        <v>尿路感染症（尿素分解菌によるもの）、野菜中心の食事、過換気</v>
+        <v>慢性感染症（結核など）、炎症性疾患、血液疾患、感染症の回復期</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>高たんぱく食、糖尿病性ケトアシドーシス、痛風発作時（酸性尿は尿酸結石のリスクを高める）</v>
+        <v/>
       </c>
       <c r="I46" t="str">
-        <v>痛風・尿酸結石がある場合は、野菜など尿をアルカリ化する食品を意識するとよいことを伝える</v>
+        <v/>
       </c>
       <c r="J46" t="str">
-        <v>高尿酸血症・尿酸結石の患者では尿pHが酸性に傾いていないか確認する。尿アルカリ化薬（ウラリットなど）の効果判定にも使う</v>
+        <v>単独での臨床的意義は乏しく、他の血球指標や炎症マーカー(CRPなど)と合わせて評価する</v>
       </c>
       <c r="K46" t="str">
-        <v>高尿酸血症</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L46" t="str">
-        <v>尿pH,尿酸性度,尿アルカリ化,ウラリット</v>
+        <v>単球,Mono,慢性感染症,結核,炎症</v>
       </c>
       <c r="M46" t="str">
         <v/>
@@ -2310,40 +2310,40 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ウロビリノーゲン</v>
+        <v>尿pH</v>
       </c>
       <c r="B47" t="str">
-        <v>Uro</v>
+        <v>尿pH</v>
       </c>
       <c r="C47" t="str">
-        <v>正常（±）程度</v>
+        <v>4.5〜7.5程度（弱酸性が多い）</v>
       </c>
       <c r="D47" t="str">
-        <v>肝臓や胆道、赤血球の壊れ方の状態を反映する尿検査項目</v>
+        <v>尿の酸性・アルカリ性の度合い。食事や感染症、体の状態を反映する</v>
       </c>
       <c r="E47" t="str">
-        <v>ウロビリノーゲンは、赤血球やビリルビンが体の中で処理される過程でできる物質です。肝臓の働きが悪くなったり、赤血球が壊れやすくなったりすると、尿の中の量が変化します。</v>
+        <v>尿のpHは酸性・アルカリ性のバランスを表します。食事の内容や感染症、体の代謝状態によって変化します。単独で大きな問題を示すことは少ない検査です。</v>
       </c>
       <c r="F47" t="str">
-        <v>溶血性疾患（赤血球の破壊亢進）、肝機能障害</v>
+        <v>尿路感染症（尿素分解菌によるもの）、野菜中心の食事、過換気</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>胆道閉塞（胆汁が腸に流れず、ウロビリノーゲンが作られない状態）</v>
+        <v>高たんぱく食、糖尿病性ケトアシドーシス、痛風発作時（酸性尿は尿酸結石のリスクを高める）</v>
       </c>
       <c r="I47" t="str">
-        <v/>
+        <v>痛風・尿酸結石がある場合は、野菜など尿をアルカリ化する食品を意識するとよいことを伝える</v>
       </c>
       <c r="J47" t="str">
-        <v>完全に陰性の場合は胆道閉塞を疑う所見の一つ。肝機能（AST/ALT/ビリルビン）と合わせて評価する</v>
+        <v>高尿酸血症・尿酸結石の患者では尿pHが酸性に傾いていないか確認する。尿アルカリ化薬（ウラリットなど）の効果判定にも使う</v>
       </c>
       <c r="K47" t="str">
-        <v>肝機能</v>
+        <v>高尿酸血症</v>
       </c>
       <c r="L47" t="str">
-        <v>ウロビリノーゲン,Uro,溶血,胆道閉塞,肝機能</v>
+        <v>尿pH,尿酸性度,尿アルカリ化,ウラリット</v>
       </c>
       <c r="M47" t="str">
         <v/>
@@ -2351,40 +2351,40 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>尿ケトン体</v>
+        <v>ウロビリノーゲン</v>
       </c>
       <c r="B48" t="str">
-        <v>尿ケトン,Ket</v>
+        <v>Uro</v>
       </c>
       <c r="C48" t="str">
-        <v>陰性（－）</v>
+        <v>正常（±）程度</v>
       </c>
       <c r="D48" t="str">
-        <v>体がブドウ糖の代わりに脂肪を分解してエネルギーを作っているサイン</v>
+        <v>肝臓や胆道、赤血球の壊れ方の状態を反映する尿検査項目</v>
       </c>
       <c r="E48" t="str">
-        <v>この検査は、体が糖の代わりに脂肪を使ってエネルギーを作っていないかを見るものです。陽性が続くときは、食事や水分、インスリンの使い方を確認する必要があります。</v>
+        <v>ウロビリノーゲンは、赤血球やビリルビンが体の中で処理される過程でできる物質です。肝臓の働きが悪くなったり、赤血球が壊れやすくなったりすると、尿の中の量が変化します。</v>
       </c>
       <c r="F48" t="str">
-        <v>糖尿病の血糖コントロール不良（シックデイ・インスリン不足）、極端な糖質制限、絶食、嘔吐・下痢による脱水</v>
+        <v>溶血性疾患（赤血球の破壊亢進）、肝機能障害</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v/>
+        <v>胆道閉塞（胆汁が腸に流れず、ウロビリノーゲンが作られない状態）</v>
       </c>
       <c r="I48" t="str">
         <v/>
       </c>
       <c r="J48" t="str">
-        <v>陽性かつ高血糖・全身倦怠感が強い場合は糖尿病性ケトアシドーシスの可能性があり緊急性が高い。シックデイルールの説明歴を確認する</v>
+        <v>完全に陰性の場合は胆道閉塞を疑う所見の一つ。肝機能（AST/ALT/ビリルビン）と合わせて評価する</v>
       </c>
       <c r="K48" t="str">
-        <v>糖尿病</v>
+        <v>肝機能</v>
       </c>
       <c r="L48" t="str">
-        <v>尿ケトン体,ケトン体,Ket,シックデイ,ケトアシドーシス</v>
+        <v>ウロビリノーゲン,Uro,溶血,胆道閉塞,肝機能</v>
       </c>
       <c r="M48" t="str">
         <v/>
@@ -2433,25 +2433,25 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>尿糖（半定量）</v>
+        <v>尿ケトン体</v>
       </c>
       <c r="B50" t="str">
-        <v>尿糖,U-Glu</v>
+        <v>尿ケトン,Ket</v>
       </c>
       <c r="C50" t="str">
         <v>陰性（－）</v>
       </c>
       <c r="D50" t="str">
-        <v>尿に糖が漏れ出ていないかを見る検査。血糖値がかなり高いと陽性になる</v>
+        <v>体がブドウ糖の代わりに脂肪を分解してエネルギーを作っているサイン</v>
       </c>
       <c r="E50" t="str">
-        <v>通常、糖は尿にはほとんど出ませんが、血糖値がかなり高くなると尿にあふれ出るようになります。血糖コントロールの目安の一つです。</v>
+        <v>この検査は、体が糖の代わりに脂肪を使ってエネルギーを作っていないかを見るものです。陽性が続くときは、食事や水分、インスリンの使い方を確認する必要があります。</v>
       </c>
       <c r="F50" t="str">
-        <v>糖尿病（血糖値が腎臓で再吸収できる量を超えている状態）、腎性糖尿（血糖値が正常でも体質的に出ることがある）、SGLT2阻害薬服用中（薬の作用で意図的に糖を排泄するため陽性になるのが正常）</v>
+        <v>糖尿病の血糖コントロール不良（シックデイ・インスリン不足）、極端な糖質制限、絶食、嘔吐・下痢による脱水</v>
       </c>
       <c r="G50" t="str">
-        <v>SGLT2阻害薬（フォシーガ、ジャディアンスなど）服用中は、陽性が薬の効果によるものであることを説明する。脱水や尿路感染の症状がないかも確認する</v>
+        <v/>
       </c>
       <c r="H50" t="str">
         <v/>
@@ -2460,13 +2460,13 @@
         <v/>
       </c>
       <c r="J50" t="str">
-        <v>SGLT2阻害薬服用中は尿糖陽性が治療効果として想定内であることを患者に伝える。血糖値・HbA1cと合わせて評価する</v>
+        <v>陽性かつ高血糖・全身倦怠感が強い場合は糖尿病性ケトアシドーシスの可能性があり緊急性が高い。シックデイルールの説明歴を確認する</v>
       </c>
       <c r="K50" t="str">
         <v>糖尿病</v>
       </c>
       <c r="L50" t="str">
-        <v>尿糖,糖半定量,U-Glu,腎性糖尿,SGLT2</v>
+        <v>尿ケトン体,ケトン体,Ket,シックデイ,ケトアシドーシス</v>
       </c>
       <c r="M50" t="str">
         <v/>
@@ -2474,25 +2474,25 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>尿蛋白定量（随時尿）</v>
+        <v>尿糖（半定量）</v>
       </c>
       <c r="B51" t="str">
-        <v>U-Pro定量,蛋白/Cr比</v>
+        <v>尿糖,U-Glu</v>
       </c>
       <c r="C51" t="str">
-        <v>0.15 g/gCr未満</v>
+        <v>陰性（－）</v>
       </c>
       <c r="D51" t="str">
-        <v>随時尿から尿蛋白の量を具体的な数値として評価する検査。ネフローゼ等の重症度判定に使う</v>
+        <v>尿に糖が漏れ出ていないかを見る検査。血糖値がかなり高いと陽性になる</v>
       </c>
       <c r="E51" t="str">
-        <v>これは、尿に出ているたんぱくの量を具体的な数値で見る検査です。試験紙での陽性・陰性の判定だけでなく、実際にどれくらいの量が出ているかを把握できます。</v>
+        <v>通常、糖は尿にはほとんど出ませんが、血糖値がかなり高くなると尿にあふれ出るようになります。血糖コントロールの目安の一つです。</v>
       </c>
       <c r="F51" t="str">
-        <v>腎症の進行（糖尿病性腎症、慢性腎臓病など）、ネフローゼ症候群（3.5 g/gCr以上が目安）</v>
+        <v>糖尿病（血糖値が腎臓で再吸収できる量を超えている状態）、腎性糖尿（血糖値が正常でも体質的に出ることがある）、SGLT2阻害薬服用中（薬の作用で意図的に糖を排泄するため陽性になるのが正常）</v>
       </c>
       <c r="G51" t="str">
-        <v/>
+        <v>SGLT2阻害薬（フォシーガ、ジャディアンスなど）服用中は、陽性が薬の効果によるものであることを説明する。脱水や尿路感染の症状がないかも確認する</v>
       </c>
       <c r="H51" t="str">
         <v/>
@@ -2501,13 +2501,13 @@
         <v/>
       </c>
       <c r="J51" t="str">
-        <v>CKD診療ガイドラインの重症度分類（尿蛋白量による区分）にも使われる定量指標。試験紙法の半定量結果より治療効果判定に適する</v>
+        <v>SGLT2阻害薬服用中は尿糖陽性が治療効果として想定内であることを患者に伝える。血糖値・HbA1cと合わせて評価する</v>
       </c>
       <c r="K51" t="str">
-        <v>腎機能,糖尿病</v>
+        <v>糖尿病</v>
       </c>
       <c r="L51" t="str">
-        <v>尿蛋白,随時尿,定量,蛋白クレアチニン比,ネフローゼ</v>
+        <v>尿糖,糖半定量,U-Glu,腎性糖尿,SGLT2</v>
       </c>
       <c r="M51" t="str">
         <v/>
@@ -2515,40 +2515,40 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>アルブミン</v>
+        <v>尿蛋白定量</v>
       </c>
       <c r="B52" t="str">
-        <v>Alb</v>
+        <v>U-Pro定量,蛋白/Cr比</v>
       </c>
       <c r="C52" t="str">
-        <v>3.8〜5.2 g/dL</v>
+        <v>0.15 g/gCr未満</v>
       </c>
       <c r="D52" t="str">
-        <v>体の栄養状態を見る目安になるたんぱく質。血液の中で栄養を運ぶ、水分を血管の中に保つという働きをしている。</v>
+        <v>随時尿から尿蛋白の量を具体的な数値として評価する検査。ネフローゼ等の重症度判定に使う</v>
       </c>
       <c r="E52" t="str">
-        <v>アルブミンは栄養の状態を見る数値です。食事量が少なかったり、肝臓や腎臓、腸の働きが弱ると下がることがあります。数値が低いと、むくみが出やすくなります。</v>
+        <v>これは、尿に出ているたんぱくの量を具体的な数値で見る検査です。試験紙での陽性・陰性の判定だけでなく、実際にどれくらいの量が出ているかを把握できます。</v>
       </c>
       <c r="F52" t="str">
-        <v>脱水（見かけ上の上昇）</v>
+        <v>腎症の進行（糖尿病性腎症、慢性腎臓病など）、ネフローゼ症候群（3.5 g/gCr以上が目安）</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>低栄養／肝機能低下／ネフローゼ症候群／クローン病</v>
+        <v/>
       </c>
       <c r="I52" t="str">
-        <v>主食に偏らず、肉・魚・卵・大豆製品などたんぱく質をしっかり摂るよう伝える。食欲が落ちている場合は少量頻回の食事も提案する</v>
+        <v/>
       </c>
       <c r="J52" t="str">
-        <v>3前半は注意ライン。食事摂取量を必ず確認</v>
+        <v>CKD診療ガイドラインの重症度分類（尿蛋白量による区分）にも使われる定量指標。試験紙法の半定量結果より治療効果判定に適する</v>
       </c>
       <c r="K52" t="str">
-        <v>肝機能,栄養,腎機能</v>
+        <v>腎機能,糖尿病</v>
       </c>
       <c r="L52" t="str">
-        <v>アルブミン,Alb,むくみ,浮腫,栄養状態</v>
+        <v>尿蛋白,随時尿,定量,蛋白クレアチニン比,ネフローゼ</v>
       </c>
       <c r="M52" t="str">
         <v/>
@@ -2556,40 +2556,40 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>BNP</v>
+        <v>アルブミン</v>
       </c>
       <c r="B53" t="str">
-        <v>BNP</v>
+        <v>Alb</v>
       </c>
       <c r="C53" t="str">
-        <v>18.4 pg/mL以下</v>
+        <v>3.8〜5.2 g/dL</v>
       </c>
       <c r="D53" t="str">
-        <v>心臓が無理をしているときに出る物質。心臓は血液を送るポンプだが、負担がかかると「少し助けてほしい」というサインとしてBNPを血液中に出す。</v>
+        <v>体の栄養状態を見る目安になるたんぱく質。血液の中で栄養を運ぶ、水分を血管の中に保つという働きをしている。</v>
       </c>
       <c r="E53" t="str">
-        <v>この検査は、心臓がどれくらい頑張りすぎていないかを見るものです。数値が高いと、心臓に少し負担がかかっているサインになります。</v>
+        <v>アルブミンは栄養の状態を見る数値です。食事量が少なかったり、肝臓や腎臓、腸の働きが弱ると下がることがあります。数値が低いと、むくみが出やすくなります。</v>
       </c>
       <c r="F53" t="str">
-        <v>心不全、心臓に負担がかかっている状態、体に水分がたまりやすいとき</v>
+        <v>脱水（見かけ上の上昇）</v>
       </c>
       <c r="G53" t="str">
-        <v>塩分・水分の摂りすぎに注意し、体重の変化を毎日記録するよう伝える</v>
+        <v/>
       </c>
       <c r="H53" t="str">
-        <v>心臓の負担は少ない状態</v>
+        <v>低栄養／肝機能低下／ネフローゼ症候群／クローン病</v>
       </c>
       <c r="I53" t="str">
-        <v/>
+        <v>主食に偏らず、肉・魚・卵・大豆製品などたんぱく質をしっかり摂るよう伝える。食欲が落ちている場合は少量頻回の食事も提案する</v>
       </c>
       <c r="J53" t="str">
-        <v>腎機能が低いとBNPは高めに出ることがある／数値だけで判断せず、症状と合わせて評価する／息切れ、むくみ、体重増加があれば要注意</v>
+        <v>3前半は注意ライン。食事摂取量を必ず確認</v>
       </c>
       <c r="K53" t="str">
-        <v>心不全</v>
+        <v>肝機能,栄養,腎機能</v>
       </c>
       <c r="L53" t="str">
-        <v>BNP,心不全,息切れ,むくみ</v>
+        <v>アルブミン,Alb,むくみ,浮腫,栄養状態</v>
       </c>
       <c r="M53" t="str">
         <v/>
@@ -2597,40 +2597,40 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>血清CPR（Cペプチド）</v>
+        <v>BNP</v>
       </c>
       <c r="B54" t="str">
-        <v>CPR</v>
+        <v>BNP</v>
       </c>
       <c r="C54" t="str">
-        <v>空腹時 0.6〜3.0 ng/mL（施設差あり）</v>
+        <v>18.4 pg/mL以下</v>
       </c>
       <c r="D54" t="str">
-        <v>自分の膵臓がどれくらいインスリンを作れているかを表す指標</v>
+        <v>心臓が無理をしているときに出る物質。心臓は血液を送るポンプだが、負担がかかると「少し助けてほしい」というサインとしてBNPを血液中に出す。</v>
       </c>
       <c r="E54" t="str">
-        <v>この検査は、ご自身の膵臓がどれくらいインスリンを作る力を持っているかを見るものです。数値が低いほど、体の中で作れるインスリンが少ないことを示します。</v>
+        <v>この検査は、心臓がどれくらい頑張りすぎていないかを見るものです。数値が高いと、心臓に少し負担がかかっているサインになります。</v>
       </c>
       <c r="F54" t="str">
-        <v>インスリン抵抗性が強い状態（初期の2型糖尿病など）</v>
+        <v>心不全、心臓に負担がかかっている状態、体に水分がたまりやすいとき</v>
       </c>
       <c r="G54" t="str">
-        <v/>
+        <v>塩分・水分の摂りすぎに注意し、体重の変化を毎日記録するよう伝える</v>
       </c>
       <c r="H54" t="str">
-        <v>膵臓のインスリン分泌能低下（1型糖尿病、糖尿病の進行）</v>
+        <v>心臓の負担は少ない状態</v>
       </c>
       <c r="I54" t="str">
         <v/>
       </c>
       <c r="J54" t="str">
-        <v>インスリン分泌能の評価に使われる。数値が低いほどインスリン治療の必要性が高いと判断される目安になる</v>
+        <v>腎機能が低いとBNPは高めに出ることがある／数値だけで判断せず、症状と合わせて評価する／息切れ、むくみ、体重増加があれば要注意</v>
       </c>
       <c r="K54" t="str">
-        <v>糖尿病</v>
+        <v>心不全</v>
       </c>
       <c r="L54" t="str">
-        <v>CPR,Cペプチド,インスリン分泌,血清CPR</v>
+        <v>BNP,心不全,息切れ,むくみ</v>
       </c>
       <c r="M54" t="str">
         <v/>
@@ -2638,40 +2638,40 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>尿中微量アルブミン</v>
+        <v>血清CPR（Cペプチド）</v>
       </c>
       <c r="B55" t="str">
-        <v>U-Alb,MAU</v>
+        <v>CPR</v>
       </c>
       <c r="C55" t="str">
-        <v>30 mg/gCr未満（尿中アルブミン/クレアチニン比）</v>
+        <v>空腹時 0.6〜3.0 ng/mL（施設差あり）</v>
       </c>
       <c r="D55" t="str">
-        <v>通常の尿蛋白検査では見つからない、ごく早期の腎症のサイン</v>
+        <v>自分の膵臓がどれくらいインスリンを作れているかを表す指標</v>
       </c>
       <c r="E55" t="str">
-        <v>この検査は、通常の尿検査ではまだ分からないくらい早い段階の腎臓の変化を見つけるためのものです。数値が高いと、腎症の初期のサインである可能性があります。</v>
+        <v>この検査は、ご自身の膵臓がどれくらいインスリンを作る力を持っているかを見るものです。数値が低いほど、体の中で作れるインスリンが少ないことを示します。</v>
       </c>
       <c r="F55" t="str">
-        <v>糖尿病性腎症の早期段階、高血圧</v>
+        <v>インスリン抵抗性が強い状態（初期の2型糖尿病など）</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v/>
+        <v>膵臓のインスリン分泌能低下（1型糖尿病、糖尿病の進行）</v>
       </c>
       <c r="I55" t="str">
         <v/>
       </c>
       <c r="J55" t="str">
-        <v>糖尿病腎症の早期発見に重要な検査。血糖・血圧コントロールで改善しうる段階なので、早期介入の意義を伝える</v>
+        <v>インスリン分泌能の評価に使われる。数値が低いほどインスリン治療の必要性が高いと判断される目安になる</v>
       </c>
       <c r="K55" t="str">
-        <v>糖尿病,腎機能</v>
+        <v>糖尿病</v>
       </c>
       <c r="L55" t="str">
-        <v>微量アルブミン,U-Alb,MAU,糖尿病性腎症,早期腎症</v>
+        <v>CPR,Cペプチド,インスリン分泌,血清CPR</v>
       </c>
       <c r="M55" t="str">
         <v/>
@@ -2679,40 +2679,40 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>血清鉄（Fe）</v>
+        <v>尿中微量アルブミン</v>
       </c>
       <c r="B56" t="str">
-        <v>Fe</v>
+        <v>U-Alb,MAU</v>
       </c>
       <c r="C56" t="str">
-        <v>60〜200 μg/dL（施設差あり）</v>
+        <v>30 mg/gCr未満（尿中アルブミン/クレアチニン比）</v>
       </c>
       <c r="D56" t="str">
-        <v>血液中を流れている鉄の量</v>
+        <v>通常の尿蛋白検査では見つからない、ごく早期の腎症のサイン</v>
       </c>
       <c r="E56" t="str">
-        <v>この検査は、今血液の中を流れている鉄の量を見るものです。低いと、体の中で鉄が不足している可能性があります。</v>
+        <v>この検査は、通常の尿検査ではまだ分からないくらい早い段階の腎臓の変化を見つけるためのものです。数値が高いと、腎症の初期のサインである可能性があります。</v>
       </c>
       <c r="F56" t="str">
-        <v>鉄剤の過剰摂取、溶血、肝疾患</v>
+        <v>糖尿病性腎症の早期段階、高血圧</v>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>鉄欠乏性貧血、慢性炎症、出血</v>
+        <v/>
       </c>
       <c r="I56" t="str">
-        <v>鉄分の多い食品（レバー・赤身肉・魚・ほうれん草など）を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える</v>
+        <v/>
       </c>
       <c r="J56" t="str">
-        <v>血清鉄は日内変動が大きい。単独で判断せず総鉄結合能・フェリチンと合わせて評価する</v>
+        <v>糖尿病腎症の早期発見に重要な検査。血糖・血圧コントロールで改善しうる段階なので、早期介入の意義を伝える</v>
       </c>
       <c r="K56" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>糖尿病,腎機能</v>
       </c>
       <c r="L56" t="str">
-        <v>血清鉄,Fe,鉄欠乏性貧血</v>
+        <v>微量アルブミン,U-Alb,MAU,糖尿病性腎症,早期腎症</v>
       </c>
       <c r="M56" t="str">
         <v/>
@@ -2720,40 +2720,40 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>総鉄結合能（TIBC）</v>
+        <v>血清鉄（Fe）</v>
       </c>
       <c r="B57" t="str">
-        <v>TIBC</v>
+        <v>Fe</v>
       </c>
       <c r="C57" t="str">
-        <v>250〜360 μg/dL（施設差あり）</v>
+        <v>60〜200 μg/dL（施設差あり）</v>
       </c>
       <c r="D57" t="str">
-        <v>血液中のトランスフェリンが鉄と結合できる総量</v>
+        <v>血液中を流れている鉄の量</v>
       </c>
       <c r="E57" t="str">
-        <v/>
+        <v>この検査は、今血液の中を流れている鉄の量を見るものです。低いと、体の中で鉄が不足している可能性があります。</v>
       </c>
       <c r="F57" t="str">
-        <v>鉄欠乏性貧血（＞360 μg/dLが目安）</v>
+        <v>鉄剤の過剰摂取、溶血、肝疾患</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>慢性炎症、肝疾患、ネフローゼ症候群</v>
+        <v>鉄欠乏性貧血、慢性炎症、出血</v>
       </c>
       <c r="I57" t="str">
-        <v/>
+        <v>鉄分の多い食品（レバー・赤身肉・魚・ほうれん草など）を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える</v>
       </c>
       <c r="J57" t="str">
-        <v>鉄が不足すると、体はより多く運ぼうとしてTIBCが上昇する。UIBC・血清鉄と併せて評価する</v>
+        <v>血清鉄は日内変動が大きい。単独で判断せず総鉄結合能・フェリチンと合わせて評価する</v>
       </c>
       <c r="K57" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
       <c r="L57" t="str">
-        <v>TIBC,総鉄結合能,鉄欠乏性貧血</v>
+        <v>血清鉄,Fe,鉄欠乏性貧血</v>
       </c>
       <c r="M57" t="str">
         <v/>
@@ -2761,40 +2761,40 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>不飽和鉄結合能（UIBC）</v>
+        <v>総鉄結合能（TIBC）</v>
       </c>
       <c r="B58" t="str">
-        <v>UIBC</v>
+        <v>TIBC</v>
       </c>
       <c r="C58" t="str">
-        <v>170〜300 μg/dL（施設差あり）</v>
+        <v>250〜360 μg/dL（施設差あり）</v>
       </c>
       <c r="D58" t="str">
-        <v>トランスフェリンのうち、まだ鉄と結合していない余力の部分（UIBC＝TIBC－血清鉄）</v>
+        <v>血液中のトランスフェリンが鉄と結合できる総量</v>
       </c>
       <c r="E58" t="str">
-        <v/>
+        <v>TIBCは、血液中でトランスフェリンという物質が鉄を運べる最大量を表します。体の中の鉄が不足すると、少しでも多く鉄を運ぼうとしてこの数値が上がる性質があります。</v>
       </c>
       <c r="F58" t="str">
-        <v>鉄欠乏性貧血（＞300 μg/dLが目安）</v>
+        <v>鉄欠乏性貧血（＞360 μg/dLが目安）</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>慢性炎症、鉄過剰状態</v>
+        <v>慢性炎症、肝疾患、ネフローゼ症候群</v>
       </c>
       <c r="I58" t="str">
         <v/>
       </c>
       <c r="J58" t="str">
-        <v>TIBCと同じ方向に動くことが多い。血清鉄・TIBCとあわせて鉄欠乏性貧血と二次性貧血の鑑別に使う</v>
+        <v>鉄が不足すると、体はより多く運ぼうとしてTIBCが上昇する。UIBC・血清鉄と併せて評価する</v>
       </c>
       <c r="K58" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
       <c r="L58" t="str">
-        <v>UIBC,不飽和鉄結合能,鉄欠乏性貧血</v>
+        <v>TIBC,総鉄結合能,鉄欠乏性貧血</v>
       </c>
       <c r="M58" t="str">
         <v/>
@@ -2802,40 +2802,40 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>トランスフェリン飽和度</v>
+        <v>不飽和鉄結合能（UIBC）</v>
       </c>
       <c r="B59" t="str">
-        <v>TSAT</v>
+        <v>UIBC</v>
       </c>
       <c r="C59" t="str">
-        <v>16〜50%程度（施設差あり）</v>
+        <v>170〜300 μg/dL（施設差あり）</v>
       </c>
       <c r="D59" t="str">
-        <v>鉄を運ぶ役割のトランスフェリンのうち、実際に鉄を運んでいる割合（血清鉄÷総鉄結合能）</v>
+        <v>トランスフェリンのうち、まだ鉄と結合していない余力の部分（UIBC＝TIBC－血清鉄）</v>
       </c>
       <c r="E59" t="str">
-        <v/>
+        <v>UIBCは、トランスフェリンのうち、まだ鉄と結合していない「空き容量」の部分を表します。鉄が不足しているときほど、この空き容量は大きくなります。</v>
       </c>
       <c r="F59" t="str">
-        <v>鉄過剰症（ヘモクロマトーシスなど）</v>
+        <v>鉄欠乏性貧血（＞300 μg/dLが目安）</v>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>鉄欠乏性貧血（＜16%が目安）</v>
+        <v>慢性炎症、鉄過剰状態</v>
       </c>
       <c r="I59" t="str">
         <v/>
       </c>
       <c r="J59" t="str">
-        <v>血清鉄をTIBCで割って計算される。鉄剤補充の効果判定にも使われる</v>
+        <v>TIBCと同じ方向に動くことが多い。血清鉄・TIBCとあわせて鉄欠乏性貧血と二次性貧血の鑑別に使う</v>
       </c>
       <c r="K59" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
       <c r="L59" t="str">
-        <v>トランスフェリン飽和度,TSAT,鉄欠乏性貧血</v>
+        <v>UIBC,不飽和鉄結合能,鉄欠乏性貧血</v>
       </c>
       <c r="M59" t="str">
         <v/>
@@ -2843,40 +2843,40 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>血清フェリチン</v>
+        <v>トランスフェリン飽和度</v>
       </c>
       <c r="B60" t="str">
-        <v>Ferritin</v>
+        <v>TSAT</v>
       </c>
       <c r="C60" t="str">
-        <v>男性 20〜250 ng/mL、女性 10〜120 ng/mL（施設差あり）</v>
+        <v>16〜50%程度（施設差あり）</v>
       </c>
       <c r="D60" t="str">
-        <v>体に貯蔵されている鉄の量を反映する指標。貧血の症状が出るより早い段階で低下する</v>
+        <v>鉄を運ぶ役割のトランスフェリンのうち、実際に鉄を運んでいる割合（血清鉄÷総鉄結合能）</v>
       </c>
       <c r="E60" t="str">
-        <v>フェリチンは、体に蓄えられている鉄の「貯金」の量を見る検査です。この数値が下がるのは、貧血の症状が出るよりも前の、とても早い段階のサインになります。</v>
+        <v>トランスフェリン飽和度は、鉄を運ぶトランスフェリンのうち、実際にどれくらいが鉄を運んでいるかを割合で表したものです。鉄欠乏性貧血では低くなり、鉄が過剰にたまる病気では高くなります。</v>
       </c>
       <c r="F60" t="str">
-        <v>炎症性疾患、肝疾患、悪性腫瘍、鉄過剰症（フェリチンは炎症でも上昇するため、貧血の評価では注意が必要）</v>
+        <v>鉄過剰症（ヘモクロマトーシスなど）</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>鉄欠乏状態（貧血の症状が出る前の早期段階から低下する）</v>
+        <v>鉄欠乏性貧血（＜16%が目安）</v>
       </c>
       <c r="I60" t="str">
-        <v>鉄分の多い食品を意識するとともに、貯蔵鉄を補うため治療は数値が正常化してからも継続が必要なことを伝える</v>
+        <v/>
       </c>
       <c r="J60" t="str">
-        <v>貯蔵鉄の指標で鉄欠乏を最も早期に反映する。ただし炎症があると鉄欠乏があっても正常〜高値に出ることがあり、CRP等の炎症所見と合わせて評価する。二次性貧血との鑑別に重要</v>
+        <v>血清鉄をTIBCで割って計算される。鉄剤補充の効果判定にも使われる</v>
       </c>
       <c r="K60" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
       <c r="L60" t="str">
-        <v>フェリチン,Ferritin,貯蔵鉄,鉄欠乏</v>
+        <v>トランスフェリン飽和度,TSAT,鉄欠乏性貧血</v>
       </c>
       <c r="M60" t="str">
         <v/>
@@ -2884,40 +2884,40 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>尿中尿酸/クレアチニン比（UUA/UCr）</v>
+        <v>血清フェリチン</v>
       </c>
       <c r="B61" t="str">
-        <v>UUA/UCr</v>
+        <v>Ferritin</v>
       </c>
       <c r="C61" t="str">
-        <v>0.4〜0.8程度が混合型の目安</v>
+        <v>男性 20〜250 ng/mL、女性 10〜120 ng/mL（施設差あり）</v>
       </c>
       <c r="D61" t="str">
-        <v>尿酸が「作られすぎ」か「排泄できていない」かを見分ける比の値</v>
+        <v>体に貯蔵されている鉄の量を反映する指標。貧血の症状が出るより早い段階で低下する</v>
       </c>
       <c r="E61" t="str">
-        <v/>
+        <v>フェリチンは、体に蓄えられている鉄の「貯金」の量を見る検査です。この数値が下がるのは、貧血の症状が出るよりも前の、とても早い段階のサインになります。</v>
       </c>
       <c r="F61" t="str">
-        <v>尿酸産生過剰型（0.8以上が目安）</v>
+        <v>炎症性疾患、肝疾患、悪性腫瘍、鉄過剰症（フェリチンは炎症でも上昇するため、貧血の評価では注意が必要）</v>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>尿酸排泄低下型（0.4以下が目安）</v>
+        <v>鉄欠乏状態（貧血の症状が出る前の早期段階から低下する）</v>
       </c>
       <c r="I61" t="str">
-        <v/>
+        <v>鉄分の多い食品を意識するとともに、貯蔵鉄を補うため治療は数値が正常化してからも継続が必要なことを伝える</v>
       </c>
       <c r="J61" t="str">
-        <v>高尿酸血症は尿酸産生過剰型・排泄低下型・混合型に分類され、この比が目安になる。病型によって使う薬剤（尿酸生成抑制薬か尿酸排泄促進薬か）の選択が変わる</v>
+        <v>貯蔵鉄の指標で鉄欠乏を最も早期に反映する。ただし炎症があると鉄欠乏があっても正常〜高値に出ることがあり、CRP等の炎症所見と合わせて評価する。二次性貧血との鑑別に重要</v>
       </c>
       <c r="K61" t="str">
-        <v>高尿酸血症</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="L61" t="str">
-        <v>UUA,UCr,尿酸クリアランス,CUA,EUA,尿酸産生過剰型,尿酸排泄低下型</v>
+        <v>フェリチン,Ferritin,貯蔵鉄,鉄欠乏</v>
       </c>
       <c r="M61" t="str">
         <v/>
@@ -2925,40 +2925,40 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>ucOC（低カルボキシル化オステオカルシン）</v>
+        <v>尿中尿酸/クレアチニン比（UUA/UCr）</v>
       </c>
       <c r="B62" t="str">
-        <v>ucOC</v>
+        <v>UUA/UCr</v>
       </c>
       <c r="C62" t="str">
-        <v>4.5 ng/mL未満（施設差あり）</v>
+        <v>0.4〜0.8程度が混合型の目安</v>
       </c>
       <c r="D62" t="str">
-        <v>ビタミンKが不足していないかを反映する骨の指標</v>
+        <v>尿酸が「作られすぎ」か「排泄できていない」かを見分ける比の値</v>
       </c>
       <c r="E62" t="str">
-        <v/>
+        <v>この数値は、体の中で尿酸が「作られすぎている」のか、それとも「うまく排泄できていない」のかを見分けるために使う比の値です。高尿酸血症の治療薬を選ぶときの参考になります。</v>
       </c>
       <c r="F62" t="str">
-        <v>ビタミンK不足状態</v>
+        <v>尿酸産生過剰型（0.8以上が目安）</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v/>
+        <v>尿酸排泄低下型（0.4以下が目安）</v>
       </c>
       <c r="I62" t="str">
         <v/>
       </c>
       <c r="J62" t="str">
-        <v>ビタミンK2製剤（骨粗鬆症治療薬）の適応判断や効果判定に使われる</v>
+        <v>高尿酸血症は尿酸産生過剰型・排泄低下型・混合型に分類され、この比が目安になる。病型によって使う薬剤（尿酸生成抑制薬か尿酸排泄促進薬か）の選択が変わる</v>
       </c>
       <c r="K62" t="str">
-        <v>骨粗鬆症</v>
+        <v>高尿酸血症</v>
       </c>
       <c r="L62" t="str">
-        <v>ucOC,オステオカルシン,ビタミンK</v>
+        <v>UUA,UCr,尿酸クリアランス,CUA,EUA,尿酸産生過剰型,尿酸排泄低下型</v>
       </c>
       <c r="M62" t="str">
         <v/>
@@ -2966,40 +2966,40 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>リン（P）</v>
+        <v>ucOC（低カルボキシル化オステオカルシン）</v>
       </c>
       <c r="B63" t="str">
-        <v>P,IP</v>
+        <v>ucOC</v>
       </c>
       <c r="C63" t="str">
-        <v>2.5〜4.5 mg/dL</v>
+        <v>4.5 ng/mL未満（施設差あり）</v>
       </c>
       <c r="D63" t="str">
-        <v>カルシウムとともに骨を作る主要なミネラル</v>
+        <v>ビタミンKが不足していないかを反映する骨の指標</v>
       </c>
       <c r="E63" t="str">
-        <v/>
+        <v>ucOCは、骨を作るために必要なビタミンKが体の中で足りているかどうかを反映する検査です。数値が高いとビタミンK不足が疑われます。</v>
       </c>
       <c r="F63" t="str">
-        <v>腎不全、副甲状腺機能低下症</v>
+        <v>ビタミンK不足状態</v>
       </c>
       <c r="G63" t="str">
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>副甲状腺機能亢進症、骨軟化症、ビタミンD欠乏</v>
+        <v/>
       </c>
       <c r="I63" t="str">
         <v/>
       </c>
       <c r="J63" t="str">
-        <v>カルシウムと逆方向に動くことが多い（副甲状腺機能亢進症ではCa上昇・P低下）。骨粗鬆症の二次性原因の除外に用いられる</v>
+        <v>ビタミンK2製剤（骨粗鬆症治療薬）の適応判断や効果判定に使われる</v>
       </c>
       <c r="K63" t="str">
-        <v>骨粗鬆症,電解質</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="L63" t="str">
-        <v>リン,P,IP,無機リン</v>
+        <v>ucOC,オステオカルシン,ビタミンK</v>
       </c>
       <c r="M63" t="str">
         <v/>
@@ -3007,40 +3007,40 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>PTH（副甲状腺ホルモン）</v>
+        <v>リン（P）</v>
       </c>
       <c r="B64" t="str">
-        <v>PTH</v>
+        <v>P,IP</v>
       </c>
       <c r="C64" t="str">
-        <v>10〜65 pg/mL（施設差あり）</v>
+        <v>2.5〜4.5 mg/dL</v>
       </c>
       <c r="D64" t="str">
-        <v>血液中のカルシウム濃度を調節するホルモン</v>
+        <v>カルシウムとともに骨を作る主要なミネラル</v>
       </c>
       <c r="E64" t="str">
-        <v/>
+        <v>リンはカルシウムと一緒に骨や歯を作る材料になるミネラルです。カルシウムと逆方向に動くことが多く、腎臓の働きやホルモンのバランスによっても変動します。</v>
       </c>
       <c r="F64" t="str">
-        <v>原発性・二次性副甲状腺機能亢進症（腎不全に伴うものなど）</v>
+        <v>腎不全、副甲状腺機能低下症</v>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>副甲状腺機能低下症</v>
+        <v>副甲状腺機能亢進症、骨軟化症、ビタミンD欠乏</v>
       </c>
       <c r="I64" t="str">
         <v/>
       </c>
       <c r="J64" t="str">
-        <v>骨粗鬆症の二次性原因（副甲状腺機能亢進症）を除外するための検査。カルシウム・リンと合わせて評価する</v>
+        <v>カルシウムと逆方向に動くことが多い（副甲状腺機能亢進症ではCa上昇・P低下）。骨粗鬆症の二次性原因の除外に用いられる</v>
       </c>
       <c r="K64" t="str">
-        <v>骨粗鬆症</v>
+        <v>骨粗鬆症,電解質</v>
       </c>
       <c r="L64" t="str">
-        <v>PTH,副甲状腺ホルモン,パラトルモン</v>
+        <v>リン,P,IP,無機リン</v>
       </c>
       <c r="M64" t="str">
         <v/>
@@ -3048,40 +3048,40 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>骨型酒石酸抵抗性フォスファターゼ（TRACP-5b）</v>
+        <v>PTH（副甲状腺ホルモン）</v>
       </c>
       <c r="B65" t="str">
-        <v>TRACP-5b</v>
+        <v>PTH</v>
       </c>
       <c r="C65" t="str">
-        <v>120〜420 mU/dL</v>
+        <v>10〜65 pg/mL（施設差あり）</v>
       </c>
       <c r="D65" t="str">
-        <v>骨がどれくらい壊されているかを見る検査。骨は「古い骨を壊して新しい骨を作る」入れ替えを繰り返しており、骨を壊す細胞が活発だとこの物質が血液中に増える。</v>
+        <v>血液中のカルシウム濃度を調節するホルモン</v>
       </c>
       <c r="E65" t="str">
-        <v>この検査は、骨がどれくらい早く減っていないかを見るものです。数値が高いと、骨が弱くなりやすい状態の目安になります。</v>
+        <v>PTHは、血液中のカルシウム濃度を一定に保つために働くホルモンです。カルシウムが低くなると分泌が増え、骨からカルシウムを取り出したり、腎臓での再吸収を促したりして数値を戻そうとします。</v>
       </c>
       <c r="F65" t="str">
-        <v>骨粗鬆症、骨代謝回転（骨がこわれるスピード）が活発な状態</v>
+        <v>原発性・二次性副甲状腺機能亢進症（腎不全に伴うものなど）</v>
       </c>
       <c r="G65" t="str">
-        <v>カルシウム・ビタミンDの摂取や、適度な荷重運動（ウォーキングなど）を意識するよう伝える</v>
+        <v/>
       </c>
       <c r="H65" t="str">
-        <v/>
+        <v>副甲状腺機能低下症</v>
       </c>
       <c r="I65" t="str">
         <v/>
       </c>
       <c r="J65" t="str">
-        <v>「骨を壊す側」の指標。「骨を作る側」の検査と合わせて評価する。数値だけで診断はしない</v>
+        <v>骨粗鬆症の二次性原因（副甲状腺機能亢進症）を除外するための検査。カルシウム・リンと合わせて評価する</v>
       </c>
       <c r="K65" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="L65" t="str">
-        <v>TRACP-5b,骨型酒石酸抵抗性フォスファターゼ,骨粗鬆症,骨代謝</v>
+        <v>PTH,副甲状腺ホルモン,パラトルモン</v>
       </c>
       <c r="M65" t="str">
         <v/>
@@ -3089,25 +3089,25 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>カルシトニン</v>
+        <v>骨型酒石酸抵抗性フォスファターゼ（TRACP-5b）</v>
       </c>
       <c r="B66" t="str">
-        <v>CT</v>
+        <v>TRACP-5b</v>
       </c>
       <c r="C66" t="str">
-        <v>男性 9.52 pg/mL未満、女性 6.40 pg/mL未満（施設差あり）</v>
+        <v>120〜420 mU/dL</v>
       </c>
       <c r="D66" t="str">
-        <v>血液中のカルシウムを下げる方向に働くホルモン</v>
+        <v>骨がどれくらい壊されているかを見る検査。骨は「古い骨を壊して新しい骨を作る」入れ替えを繰り返しており、骨を壊す細胞が活発だとこの物質が血液中に増える。</v>
       </c>
       <c r="E66" t="str">
-        <v/>
+        <v>この検査は、骨がどれくらい早く減っていないかを見るものです。数値が高いと、骨が弱くなりやすい状態の目安になります。</v>
       </c>
       <c r="F66" t="str">
-        <v>甲状腺髄様癌、腎不全</v>
+        <v>骨粗鬆症、骨代謝回転（骨がこわれるスピード）が活発な状態</v>
       </c>
       <c r="G66" t="str">
-        <v/>
+        <v>カルシウム・ビタミンDの摂取や、適度な荷重運動（ウォーキングなど）を意識するよう伝える</v>
       </c>
       <c r="H66" t="str">
         <v/>
@@ -3116,13 +3116,13 @@
         <v/>
       </c>
       <c r="J66" t="str">
-        <v>骨粗鬆症の二次性原因の除外目的で測定されることがある検査値。同名の薬剤（カルシトニン製剤）と混同しないよう注意</v>
+        <v>「骨を壊す側」の指標。「骨を作る側」の検査と合わせて評価する。数値だけで診断はしない</v>
       </c>
       <c r="K66" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="L66" t="str">
-        <v>カルシトニン,CT</v>
+        <v>TRACP-5b,骨型酒石酸抵抗性フォスファターゼ,骨粗鬆症,骨代謝</v>
       </c>
       <c r="M66" t="str">
         <v/>
@@ -3130,40 +3130,40 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>尿中NTX</v>
+        <v>カルシトニン</v>
       </c>
       <c r="B67" t="str">
-        <v>NTX</v>
+        <v>CT</v>
       </c>
       <c r="C67" t="str">
-        <v>施設差が大きく一律の記載が難しい（尿中）</v>
+        <v>男性 9.52 pg/mL未満、女性 6.40 pg/mL未満（施設差あり）</v>
       </c>
       <c r="D67" t="str">
-        <v>骨が壊されるときに出る、骨吸収マーカーのひとつ</v>
+        <v>血液中のカルシウムを下げる方向に働くホルモン</v>
       </c>
       <c r="E67" t="str">
-        <v/>
+        <v>カルシトニンは、PTHとは逆に血液中のカルシウムを下げる方向に働くホルモンです。特定の甲状腺の病気（甲状腺髄様癌）がないかを調べる際にも使われます。</v>
       </c>
       <c r="F67" t="str">
-        <v>骨代謝回転の亢進（骨粗鬆症、閉経後など）</v>
+        <v>甲状腺髄様癌、腎不全</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>骨吸収抑制薬（ビスホスホネート等）による治療効果</v>
+        <v/>
       </c>
       <c r="I67" t="str">
         <v/>
       </c>
       <c r="J67" t="str">
-        <v>治療開始後3〜6か月で再検し、薬の効果判定に使われる。TRACP-5bと同じ「骨を壊す側」の指標</v>
+        <v>骨粗鬆症の二次性原因の除外目的で測定されることがある検査値。同名の薬剤（カルシトニン製剤）と混同しないよう注意</v>
       </c>
       <c r="K67" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="L67" t="str">
-        <v>NTX,尿中NTX,骨吸収マーカー</v>
+        <v>カルシトニン,CT</v>
       </c>
       <c r="M67" t="str">
         <v/>
@@ -3171,40 +3171,40 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>DPD（デオキシピリジノリン）</v>
+        <v>尿中NTX</v>
       </c>
       <c r="B68" t="str">
-        <v>DPD</v>
+        <v>NTX</v>
       </c>
       <c r="C68" t="str">
         <v>施設差が大きく一律の記載が難しい（尿中）</v>
       </c>
       <c r="D68" t="str">
-        <v>骨のコラーゲンが壊れるときに出る、骨吸収マーカーのひとつ</v>
+        <v>骨が壊されるときに出る、骨吸収マーカーのひとつ</v>
       </c>
       <c r="E68" t="str">
-        <v/>
+        <v>NTXは、骨が壊される（吸収される）ときに尿の中に出てくる物質です。骨粗鬆症の治療薬がどれくらい効いているかを確認するために使われます。</v>
       </c>
       <c r="F68" t="str">
-        <v>骨代謝回転の亢進（骨粗鬆症など）</v>
+        <v>骨代謝回転の亢進（骨粗鬆症、閉経後など）</v>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>骨吸収抑制薬による治療効果</v>
+        <v>骨吸収抑制薬（ビスホスホネート等）による治療効果</v>
       </c>
       <c r="I68" t="str">
         <v/>
       </c>
       <c r="J68" t="str">
-        <v>NTX・CTXと同じ「骨を壊す側」の指標。食事の影響を受けにくいとされる</v>
+        <v>治療開始後3〜6か月で再検し、薬の効果判定に使われる。TRACP-5bと同じ「骨を壊す側」の指標</v>
       </c>
       <c r="K68" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="L68" t="str">
-        <v>DPD,デオキシピリジノリン,骨吸収マーカー</v>
+        <v>NTX,尿中NTX,骨吸収マーカー</v>
       </c>
       <c r="M68" t="str">
         <v/>
@@ -3212,19 +3212,19 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>CTX</v>
+        <v>DPD（デオキシピリジノリン）</v>
       </c>
       <c r="B69" t="str">
-        <v>CTX</v>
+        <v>DPD</v>
       </c>
       <c r="C69" t="str">
-        <v>施設差が大きく一律の記載が難しい（血清・尿中）</v>
+        <v>施設差が大きく一律の記載が難しい（尿中）</v>
       </c>
       <c r="D69" t="str">
         <v>骨のコラーゲンが壊れるときに出る、骨吸収マーカーのひとつ</v>
       </c>
       <c r="E69" t="str">
-        <v/>
+        <v>DPDも、骨が壊されるときに尿に出てくる物質の一つです。NTXと同じように、骨粗鬆症治療薬の効果を確認するために使われます。</v>
       </c>
       <c r="F69" t="str">
         <v>骨代謝回転の亢進（骨粗鬆症など）</v>
@@ -3239,13 +3239,13 @@
         <v/>
       </c>
       <c r="J69" t="str">
-        <v>NTX・DPDと同じ「骨を壊す側」の指標。血清・尿中いずれでも測定されることがある</v>
+        <v>NTX・CTXと同じ「骨を壊す側」の指標。食事の影響を受けにくいとされる</v>
       </c>
       <c r="K69" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="L69" t="str">
-        <v>CTX,骨吸収マーカー</v>
+        <v>DPD,デオキシピリジノリン,骨吸収マーカー</v>
       </c>
       <c r="M69" t="str">
         <v/>
@@ -3253,40 +3253,40 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>P1NP</v>
+        <v>CTX</v>
       </c>
       <c r="B70" t="str">
-        <v>P1NP</v>
+        <v>CTX</v>
       </c>
       <c r="C70" t="str">
-        <v>施設差が大きく一律の記載が難しい（血清）</v>
+        <v>施設差が大きく一律の記載が難しい（血清・尿中）</v>
       </c>
       <c r="D70" t="str">
-        <v>骨が新しく作られるときに出る、骨形成マーカーのひとつ</v>
+        <v>骨のコラーゲンが壊れるときに出る、骨吸収マーカーのひとつ</v>
       </c>
       <c r="E70" t="str">
-        <v/>
+        <v>CTXも、骨が壊されるときに血液や尿に出てくる物質です。骨粗鬆症治療薬（骨を壊すのを抑える薬）の効果を確認するために使われます。</v>
       </c>
       <c r="F70" t="str">
-        <v>骨代謝回転の亢進、骨形成促進薬による治療効果</v>
+        <v>骨代謝回転の亢進（骨粗鬆症など）</v>
       </c>
       <c r="G70" t="str">
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>骨形成の低下</v>
+        <v>骨吸収抑制薬による治療効果</v>
       </c>
       <c r="I70" t="str">
         <v/>
       </c>
       <c r="J70" t="str">
-        <v>TRACP-5b等「骨を壊す側」の指標とは逆の、「骨を作る側」の指標。骨形成促進薬（テリパラチド等）の効果判定に使われる</v>
+        <v>NTX・DPDと同じ「骨を壊す側」の指標。血清・尿中いずれでも測定されることがある</v>
       </c>
       <c r="K70" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="L70" t="str">
-        <v>P1NP,骨形成マーカー</v>
+        <v>CTX,骨吸収マーカー</v>
       </c>
       <c r="M70" t="str">
         <v/>
@@ -3294,40 +3294,40 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>抗甲状腺マイクロゾーム抗体（抗TPO抗体）</v>
+        <v>P1NP</v>
       </c>
       <c r="B71" t="str">
-        <v>TPOAb</v>
+        <v>P1NP</v>
       </c>
       <c r="C71" t="str">
-        <v>陰性（16 IU/mL未満程度、施設差あり）</v>
+        <v>施設差が大きく一律の記載が難しい（血清）</v>
       </c>
       <c r="D71" t="str">
-        <v>自分の甲状腺を攻撃する抗体が出ていないかを見る検査</v>
+        <v>骨が新しく作られるときに出る、骨形成マーカーのひとつ</v>
       </c>
       <c r="E71" t="str">
-        <v>この検査は、体の中に自分の甲状腺を誤って攻撃してしまう抗体がないかを見るものです。陽性の場合、橋本病（慢性甲状腺炎）など甲状腺の自己免疫的な炎症が背景にある可能性があります。</v>
+        <v>P1NPは、CTXなどとは逆に、骨が新しく作られるときに血液中に出てくる物質です。骨を作る力を高める薬（テリパラチドなど）の効果を確認するために使われます。</v>
       </c>
       <c r="F71" t="str">
-        <v>橋本病（慢性甲状腺炎）、バセドウ病などの自己免疫性甲状腺疾患</v>
+        <v>骨代謝回転の亢進、骨形成促進薬による治療効果</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v/>
+        <v>骨形成の低下</v>
       </c>
       <c r="I71" t="str">
         <v/>
       </c>
       <c r="J71" t="str">
-        <v>陽性でも必ずしも甲状腺機能異常があるとは限らない。TSH・FT4など甲状腺ホルモンの数値と合わせて評価する</v>
+        <v>TRACP-5b等「骨を壊す側」の指標とは逆の、「骨を作る側」の指標。骨形成促進薬（テリパラチド等）の効果判定に使われる</v>
       </c>
       <c r="K71" t="str">
-        <v>甲状腺疾患</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="L71" t="str">
-        <v>抗TPO抗体,抗甲状腺マイクロゾーム抗体,TPOAb,橋本病</v>
+        <v>P1NP,骨形成マーカー</v>
       </c>
       <c r="M71" t="str">
         <v/>
@@ -3335,19 +3335,19 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>抗サイログロブリン抗体</v>
+        <v>抗甲状腺マイクロゾーム抗体（抗TPO抗体）</v>
       </c>
       <c r="B72" t="str">
-        <v>TgAb</v>
+        <v>TPOAb</v>
       </c>
       <c r="C72" t="str">
-        <v>陰性（28 IU/mL未満程度、施設差あり）</v>
+        <v>陰性（16 IU/mL未満程度、施設差あり）</v>
       </c>
       <c r="D72" t="str">
-        <v>甲状腺のたんぱく質（サイログロブリン）への抗体が出ていないかを見る検査</v>
+        <v>自分の甲状腺を攻撃する抗体が出ていないかを見る検査</v>
       </c>
       <c r="E72" t="str">
-        <v>この検査も、抗TPO抗体と同じく、甲状腺に対する自己免疫の有無を見るものです。あわせて調べることで橋本病などの診断の参考にします。</v>
+        <v>この検査は、体の中に自分の甲状腺を誤って攻撃してしまう抗体がないかを見るものです。陽性の場合、橋本病（慢性甲状腺炎）など甲状腺の自己免疫的な炎症が背景にある可能性があります。</v>
       </c>
       <c r="F72" t="str">
         <v>橋本病（慢性甲状腺炎）、バセドウ病などの自己免疫性甲状腺疾患</v>
@@ -3362,13 +3362,13 @@
         <v/>
       </c>
       <c r="J72" t="str">
-        <v>抗TPO抗体とあわせて測定されることが多い。単独の高値だけで治療方針が決まるわけではない</v>
+        <v>陽性でも必ずしも甲状腺機能異常があるとは限らない。TSH・FT4など甲状腺ホルモンの数値と合わせて評価する</v>
       </c>
       <c r="K72" t="str">
         <v>甲状腺疾患</v>
       </c>
       <c r="L72" t="str">
-        <v>抗サイログロブリン抗体,TgAb,橋本病</v>
+        <v>抗TPO抗体,抗甲状腺マイクロゾーム抗体,TPOAb,橋本病</v>
       </c>
       <c r="M72" t="str">
         <v/>
@@ -3376,40 +3376,40 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>TSH（甲状腺刺激ホルモン）</v>
+        <v>抗サイログロブリン抗体</v>
       </c>
       <c r="B73" t="str">
-        <v>TSH</v>
+        <v>TgAb</v>
       </c>
       <c r="C73" t="str">
-        <v>0.5〜5.0 μIU/mL程度（施設差あり）</v>
+        <v>陰性（28 IU/mL未満程度、施設差あり）</v>
       </c>
       <c r="D73" t="str">
-        <v>甲状腺の働きが多いか少ないかを最も敏感に反映するホルモン</v>
+        <v>甲状腺のたんぱく質（サイログロブリン）への抗体が出ていないかを見る検査</v>
       </c>
       <c r="E73" t="str">
-        <v>TSHは脳の下垂体から出て、甲状腺に「もっと働いて」と指令を送るホルモンです。甲状腺の働きが弱っていると体が指令を強めるためTSHは上がり、逆に甲状腺が働きすぎているとTSHは下がります。甲状腺の状態を最初に確認する数値としてよく使われます。</v>
+        <v>この検査も、抗TPO抗体と同じく、甲状腺に対する自己免疫の有無を見るものです。あわせて調べることで橋本病などの診断の参考にします。</v>
       </c>
       <c r="F73" t="str">
-        <v>甲状腺機能低下症（橋本病など）、チラーヂンSなど甲状腺ホルモン薬の量不足</v>
+        <v>橋本病（慢性甲状腺炎）、バセドウ病などの自己免疫性甲状腺疾患</v>
       </c>
       <c r="G73" t="str">
-        <v>だるさ、むくみ、体重増加、寒がりなどの症状がないか確認する。服薬状況（飲み忘れ、他の薬との飲み合わせ）を確認する</v>
+        <v/>
       </c>
       <c r="H73" t="str">
-        <v>甲状腺機能亢進症（バセドウ病など）、チラーヂンSなど甲状腺ホルモン薬の過量</v>
+        <v/>
       </c>
       <c r="I73" t="str">
-        <v>動悸、体重減少、暑がり、手のふるえなどの症状がないか確認する</v>
+        <v/>
       </c>
       <c r="J73" t="str">
-        <v>チラーヂンS服用中はTSHが治療目標域に収まっているかで用量調整の目安にする。メルカゾール服用中はTSH・FT4に加えて無顆粒球症の初期症状（発熱・のどの痛み）の有無や白血球数も確認する</v>
+        <v>抗TPO抗体とあわせて測定されることが多い。単独の高値だけで治療方針が決まるわけではない</v>
       </c>
       <c r="K73" t="str">
         <v>甲状腺疾患</v>
       </c>
       <c r="L73" t="str">
-        <v>TSH,甲状腺刺激ホルモン,甲状腺機能,橋本病,バセドウ病,チラーヂン,メルカゾール</v>
+        <v>抗サイログロブリン抗体,TgAb,橋本病</v>
       </c>
       <c r="M73" t="str">
         <v/>
@@ -3417,40 +3417,40 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>FT4（遊離サイロキシン）</v>
+        <v>TSH（甲状腺刺激ホルモン）</v>
       </c>
       <c r="B74" t="str">
-        <v>FT4</v>
+        <v>TSH</v>
       </c>
       <c r="C74" t="str">
-        <v>0.9〜1.7 ng/dL程度（施設差あり）</v>
+        <v>0.5〜5.0 μIU/mL程度（施設差あり）</v>
       </c>
       <c r="D74" t="str">
-        <v>甲状腺が実際に分泌しているホルモンの量そのものを表す数値</v>
+        <v>甲状腺の働きが多いか少ないかを最も敏感に反映するホルモン</v>
       </c>
       <c r="E74" t="str">
-        <v>FT4は甲状腺そのものが作っているホルモンの量です。TSHが「指令の強さ」だとすると、FT4は「実際に出ている量」にあたります。2つをあわせて見ることで、甲状腺の働きが今どういう状態かを詳しく判断できます。</v>
+        <v>TSHは脳の下垂体から出て、甲状腺に「もっと働いて」と指令を送るホルモンです。甲状腺の働きが弱っていると体が指令を強めるためTSHは上がり、逆に甲状腺が働きすぎているとTSHは下がります。甲状腺の状態を最初に確認する数値としてよく使われます。</v>
       </c>
       <c r="F74" t="str">
-        <v>甲状腺機能亢進症（バセドウ病など）</v>
+        <v>甲状腺機能低下症（橋本病など）、チラーヂンSなど甲状腺ホルモン薬の量不足</v>
       </c>
       <c r="G74" t="str">
+        <v>だるさ、むくみ、体重増加、寒がりなどの症状がないか確認する。服薬状況（飲み忘れ、他の薬との飲み合わせ）を確認する</v>
+      </c>
+      <c r="H74" t="str">
+        <v>甲状腺機能亢進症（バセドウ病など）、チラーヂンSなど甲状腺ホルモン薬の過量</v>
+      </c>
+      <c r="I74" t="str">
         <v>動悸、体重減少、暑がり、手のふるえなどの症状がないか確認する</v>
       </c>
-      <c r="H74" t="str">
-        <v>甲状腺機能低下症（橋本病など）</v>
-      </c>
-      <c r="I74" t="str">
-        <v>だるさ、むくみ、体重増加、寒がりなどの症状がないか確認する</v>
-      </c>
       <c r="J74" t="str">
-        <v>TSHと逆方向に動くのが基本だが、下垂体性の異常など例外もある。TSHと合わせて評価し、片方だけで判断しない</v>
+        <v>チラーヂンS服用中はTSHが治療目標域に収まっているかで用量調整の目安にする。メルカゾール服用中はTSH・FT4に加えて無顆粒球症の初期症状（発熱・のどの痛み）の有無や白血球数も確認する</v>
       </c>
       <c r="K74" t="str">
         <v>甲状腺疾患</v>
       </c>
       <c r="L74" t="str">
-        <v>FT4,遊離サイロキシン,甲状腺ホルモン,甲状腺機能</v>
+        <v>TSH,甲状腺刺激ホルモン,甲状腺機能,橋本病,バセドウ病,チラーヂン,メルカゾール</v>
       </c>
       <c r="M74" t="str">
         <v/>
@@ -3458,40 +3458,40 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>PT-INR（プロトロンビン時間国際標準比）</v>
+        <v>FT4（遊離サイロキシン）</v>
       </c>
       <c r="B75" t="str">
-        <v>PT-INR,INR</v>
+        <v>FT4</v>
       </c>
       <c r="C75" t="str">
-        <v>治療域の目安 1.6〜3.0（ワルファリン服用時。年齢・疾患により異なる）</v>
+        <v>0.9〜1.7 ng/dL程度（施設差あり）</v>
       </c>
       <c r="D75" t="str">
-        <v>血液の固まりやすさを表す数値で、ワルファリンの効き具合を確認するために使う</v>
+        <v>甲状腺が実際に分泌しているホルモンの量そのものを表す数値</v>
       </c>
       <c r="E75" t="str">
-        <v>PT-INRは血液が固まるまでの時間をもとにした数値で、ワルファリンというお薬を飲んでいる方の効き具合を確認するために測ります。数値が高いほど血液が固まりにくく出血しやすい状態、低いほど血栓ができやすい状態を示します。</v>
+        <v>FT4は甲状腺そのものが作っているホルモンの量です。TSHが「指令の強さ」だとすると、FT4は「実際に出ている量」にあたります。2つをあわせて見ることで、甲状腺の働きが今どういう状態かを詳しく判断できます。</v>
       </c>
       <c r="F75" t="str">
-        <v>ワルファリンの効きすぎ、肝機能低下、ビタミンK不足、納豆・青汁など摂取量の変化</v>
+        <v>甲状腺機能亢進症（バセドウ病など）</v>
       </c>
       <c r="G75" t="str">
-        <v>歯ぐきや鼻からの出血、あざ、黒い便などの出血症状がないか確認する。納豆・クロレラ・青汁などビタミンKを多く含む食品の摂取状況を確認する</v>
+        <v>動悸、体重減少、暑がり、手のふるえなどの症状がないか確認する</v>
       </c>
       <c r="H75" t="str">
-        <v>ワルファリンの効き不足、飲み忘れ、ビタミンK摂取量の急激な増加</v>
+        <v>甲状腺機能低下症（橋本病など）</v>
       </c>
       <c r="I75" t="str">
-        <v>服薬状況（飲み忘れ）を確認する。片側のむくみ・しびれ・胸痛など血栓症状がないか確認する</v>
+        <v>だるさ、むくみ、体重増加、寒がりなどの症状がないか確認する</v>
       </c>
       <c r="J75" t="str">
-        <v>治療域は疾患・年齢によって異なる（例：非弁膜症性心房細動の高齢者では1.6〜2.6が目安になることが多い）。多くの薬剤・食品と相互作用があるため新規薬剤追加時は必ず確認する。DOAC（エリキュース、リクシアナ、プラザキサなど）ではPT-INRのモニタリングは不要</v>
+        <v>TSHと逆方向に動くのが基本だが、下垂体性の異常など例外もある。TSHと合わせて評価し、片方だけで判断しない</v>
       </c>
       <c r="K75" t="str">
-        <v>抗凝固療法（心房細動・血栓症）</v>
+        <v>甲状腺疾患</v>
       </c>
       <c r="L75" t="str">
-        <v>PT-INR,INR,プロトロンビン時間,ワルファリン,ワーファリン,抗凝固</v>
+        <v>FT4,遊離サイロキシン,甲状腺ホルモン,甲状腺機能</v>
       </c>
       <c r="M75" t="str">
         <v/>
@@ -3499,40 +3499,40 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>血中薬物濃度（TDM）</v>
+        <v>PT-INR（プロトロンビン時間国際標準比）</v>
       </c>
       <c r="B76" t="str">
-        <v>TDM</v>
+        <v>PT-INR,INR</v>
       </c>
       <c r="C76" t="str">
-        <v>薬剤ごとに有効域が異なる（例：カルバマゼピン 4〜12 μg/mL、バルプロ酸 40〜100 μg/mL、フェニトイン 10〜20 μg/mL）</v>
+        <v>治療域の目安 1.6〜3.0（ワルファリン服用時。年齢・疾患により異なる）</v>
       </c>
       <c r="D76" t="str">
-        <v>治療域が狭い薬剤で、血液中の薬の濃度が効果域・中毒域のどちらにあるかを確認する検査</v>
+        <v>血液の固まりやすさを表す数値で、ワルファリンの効き具合を確認するために使う</v>
       </c>
       <c r="E76" t="str">
-        <v>この薬は効く量と副作用が出る量が近いため、血液中の薬の濃度を定期的に測って、ちょうどよい範囲に入っているかを確認します。数値が低いと効果が不十分になり、高いと副作用が出やすくなります。</v>
+        <v>PT-INRは血液が固まるまでの時間をもとにした数値で、ワルファリンというお薬を飲んでいる方の効き具合を確認するために測ります。数値が高いほど血液が固まりにくく出血しやすい状態、低いほど血栓ができやすい状態を示します。</v>
       </c>
       <c r="F76" t="str">
-        <v>過量投与、代謝を妨げる薬剤との併用、肝機能低下による代謝低下</v>
+        <v>ワルファリンの効きすぎ、肝機能低下、ビタミンK不足、納豆・青汁など摂取量の変化</v>
       </c>
       <c r="G76" t="str">
-        <v>ふらつき、眠気、めまい、物が二重に見えるなどの中毒症状がないか確認する</v>
+        <v>歯ぐきや鼻からの出血、あざ、黒い便などの出血症状がないか確認する。納豆・クロレラ・青汁などビタミンKを多く含む食品の摂取状況を確認する</v>
       </c>
       <c r="H76" t="str">
-        <v>飲み忘れ、自己判断による減量、代謝を促進する薬剤との併用（相互作用）</v>
+        <v>ワルファリンの効き不足、飲み忘れ、ビタミンK摂取量の急激な増加</v>
       </c>
       <c r="I76" t="str">
-        <v>発作やてんかん症状の再発がないか確認し、飲み忘れがないか一緒に確認する</v>
+        <v>服薬状況（飲み忘れ）を確認する。片側のむくみ・しびれ・胸痛など血栓症状がないか確認する</v>
       </c>
       <c r="J76" t="str">
-        <v>採血のタイミング（トラフ値かどうか）で数値の解釈が変わるため採血時点を確認する。カルバマゼピンは自己誘導により長期使用で濃度が下がることがある点にも注意</v>
+        <v>治療域は疾患・年齢によって異なる（例：非弁膜症性心房細動の高齢者では1.6〜2.6が目安になることが多い）。多くの薬剤・食品と相互作用があるため新規薬剤追加時は必ず確認する。DOAC（エリキュース、リクシアナ、プラザキサなど）ではPT-INRのモニタリングは不要</v>
       </c>
       <c r="K76" t="str">
-        <v>てんかん</v>
+        <v>抗凝固療法（心房細動・血栓症）</v>
       </c>
       <c r="L76" t="str">
-        <v>TDM,血中薬物濃度,治療域,中毒域,カルバマゼピン,フェニトイン,バルプロ酸,抗てんかん薬</v>
+        <v>PT-INR,INR,プロトロンビン時間,ワルファリン,ワーファリン,抗凝固</v>
       </c>
       <c r="M76" t="str">
         <v/>
@@ -3540,40 +3540,40 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>アミラーゼ（AMY）</v>
+        <v>血中薬物濃度（TDM）</v>
       </c>
       <c r="B77" t="str">
-        <v>AMY</v>
+        <v>TDM</v>
       </c>
       <c r="C77" t="str">
-        <v/>
+        <v>薬剤ごとに有効域が異なる（例：カルバマゼピン 4〜12 μg/mL、バルプロ酸 40〜100 μg/mL、フェニトイン 10〜20 μg/mL）</v>
       </c>
       <c r="D77" t="str">
-        <v/>
+        <v>治療域が狭い薬剤で、血液中の薬の濃度が効果域・中毒域のどちらにあるかを確認する検査</v>
       </c>
       <c r="E77" t="str">
-        <v/>
+        <v>この薬は効く量と副作用が出る量が近いため、血液中の薬の濃度を定期的に測って、ちょうどよい範囲に入っているかを確認します。数値が低いと効果が不十分になり、高いと副作用が出やすくなります。</v>
       </c>
       <c r="F77" t="str">
-        <v>急性膵炎</v>
+        <v>過量投与、代謝を妨げる薬剤との併用、肝機能低下による代謝低下</v>
       </c>
       <c r="G77" t="str">
-        <v>飲酒を控える、脂っこい食事を避けるよう伝える</v>
+        <v>ふらつき、眠気、めまい、物が二重に見えるなどの中毒症状がないか確認する</v>
       </c>
       <c r="H77" t="str">
-        <v/>
+        <v>飲み忘れ、自己判断による減量、代謝を促進する薬剤との併用（相互作用）</v>
       </c>
       <c r="I77" t="str">
-        <v/>
+        <v>発作やてんかん症状の再発がないか確認し、飲み忘れがないか一緒に確認する</v>
       </c>
       <c r="J77" t="str">
-        <v/>
+        <v>採血のタイミング（トラフ値かどうか）で数値の解釈が変わるため採血時点を確認する。カルバマゼピンは自己誘導により長期使用で濃度が下がることがある点にも注意</v>
       </c>
       <c r="K77" t="str">
-        <v/>
+        <v>てんかん</v>
       </c>
       <c r="L77" t="str">
-        <v>アミラーゼ,AMY,膵炎,急性膵炎</v>
+        <v>TDM,血中薬物濃度,治療域,中毒域,カルバマゼピン,フェニトイン,バルプロ酸,抗てんかん薬</v>
       </c>
       <c r="M77" t="str">
         <v/>
@@ -3581,40 +3581,40 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>間接ビリルビン</v>
+        <v>アミラーゼ（AMY）</v>
       </c>
       <c r="B78" t="str">
-        <v>I-Bil</v>
+        <v>AMY</v>
       </c>
       <c r="C78" t="str">
-        <v/>
+        <v>44〜132 U/L（施設差あり）</v>
       </c>
       <c r="D78" t="str">
-        <v/>
+        <v>膵臓や唾液腺から出る消化酵素。膵炎などで血液中に漏れ出す</v>
       </c>
       <c r="E78" t="str">
-        <v/>
+        <v>アミラーゼは、でんぷんを分解する消化酵素で、主に膵臓と唾液腺から作られます。膵臓に炎症が起きると血液中に漏れ出して数値が上がるため、膵炎の診断や経過観察に使われます。</v>
       </c>
       <c r="F78" t="str">
-        <v>血液型不適合輸血などによる溶血</v>
+        <v>急性膵炎、慢性膵炎の急性増悪、耳下腺炎（おたふくかぜ）、腎不全</v>
       </c>
       <c r="G78" t="str">
-        <v/>
+        <v>飲酒を控える、脂っこい食事を避けるよう伝える</v>
       </c>
       <c r="H78" t="str">
-        <v/>
+        <v>慢性膵炎の進行期（膵臓の機能低下）</v>
       </c>
       <c r="I78" t="str">
         <v/>
       </c>
       <c r="J78" t="str">
-        <v/>
+        <v>膵臓由来か唾液腺由来かを区別するには膵型アミラーゼ(P-AMY)を確認する。急性膵炎では強い腹痛・背部痛を伴うことが多く、飲酒歴の確認も重要</v>
       </c>
       <c r="K78" t="str">
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>間接ビリルビン,I-Bil,溶血</v>
+        <v>アミラーゼ,AMY,膵炎,急性膵炎</v>
       </c>
       <c r="M78" t="str">
         <v/>
@@ -3622,25 +3622,25 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>直接ビリルビン</v>
+        <v>間接ビリルビン</v>
       </c>
       <c r="B79" t="str">
-        <v>D-Bil</v>
+        <v>I-Bil</v>
       </c>
       <c r="C79" t="str">
-        <v/>
+        <v>0.2〜0.8 mg/dL程度（施設差あり）</v>
       </c>
       <c r="D79" t="str">
-        <v/>
+        <v>赤血球が壊れてできるビリルビンのうち、肝臓で処理される前の形</v>
       </c>
       <c r="E79" t="str">
-        <v/>
+        <v>間接ビリルビンは、赤血球が壊れてできたビリルビンが、まだ肝臓で処理される前の状態です。この値が高い場合、赤血球が通常より多く壊れている(溶血)か、肝臓での処理能力に生まれつきの体質差(体質性黄疸)がある可能性が考えられます。</v>
       </c>
       <c r="F79" t="str">
-        <v>肝疾患、胆石など胆道の閉塞</v>
+        <v>溶血性疾患（自己免疫性溶血性貧血、血液型不適合輸血など）、体質性黄疸（ジルベール症候群）、新生児黄疸</v>
       </c>
       <c r="G79" t="str">
-        <v/>
+        <v>皮膚や白目の黄染、尿の色の変化がないか確認する</v>
       </c>
       <c r="H79" t="str">
         <v/>
@@ -3649,13 +3649,13 @@
         <v/>
       </c>
       <c r="J79" t="str">
-        <v/>
+        <v>直接ビリルビンとの比率で原因を推測する（間接優位は溶血・体質性、直接優位は胆道系）。総ビリルビン・AST/ALTと合わせて評価する</v>
       </c>
       <c r="K79" t="str">
         <v>肝機能</v>
       </c>
       <c r="L79" t="str">
-        <v>直接ビリルビン,D-Bil,胆石,胆道閉塞</v>
+        <v>間接ビリルビン,I-Bil,溶血</v>
       </c>
       <c r="M79" t="str">
         <v/>
@@ -3663,48 +3663,89 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
+        <v>直接ビリルビン</v>
+      </c>
+      <c r="B80" t="str">
+        <v>D-Bil</v>
+      </c>
+      <c r="C80" t="str">
+        <v>0.0〜0.3 mg/dL程度（施設差あり）</v>
+      </c>
+      <c r="D80" t="str">
+        <v>肝臓で処理された後のビリルビン。胆道の詰まりで血液中に増える</v>
+      </c>
+      <c r="E80" t="str">
+        <v>直接ビリルビンは、肝臓で処理された後のビリルビンです。胆石や腫瘍などで胆汁の通り道（胆道）が詰まると、行き場を失って血液中に増え、皮膚や白目が黄色くなる黄疸として現れます。</v>
+      </c>
+      <c r="F80" t="str">
+        <v>肝疾患、胆石など胆道の閉塞</v>
+      </c>
+      <c r="G80" t="str">
+        <v>皮膚や白目の黄染、白っぽい便、濃い茶色の尿がないか確認する</v>
+      </c>
+      <c r="H80" t="str">
+        <v/>
+      </c>
+      <c r="I80" t="str">
+        <v/>
+      </c>
+      <c r="J80" t="str">
+        <v>直接優位の上昇は胆道系（胆石、腫瘍による閉塞）を、間接優位の上昇は溶血・体質性を疑う手がかりになる。γ-GTP・ALPと合わせて胆道系疾患を評価する</v>
+      </c>
+      <c r="K80" t="str">
+        <v>肝機能</v>
+      </c>
+      <c r="L80" t="str">
+        <v>直接ビリルビン,D-Bil,胆石,胆道閉塞</v>
+      </c>
+      <c r="M80" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
         <v>CRP</v>
       </c>
-      <c r="B80" t="str">
+      <c r="B81" t="str">
         <v>CRP</v>
       </c>
-      <c r="C80" t="str">
-        <v/>
-      </c>
-      <c r="D80" t="str">
-        <v/>
-      </c>
-      <c r="E80" t="str">
-        <v/>
-      </c>
-      <c r="F80" t="str">
-        <v>炎症や感染</v>
-      </c>
-      <c r="G80" t="str">
-        <v/>
-      </c>
-      <c r="H80" t="str">
-        <v/>
-      </c>
-      <c r="I80" t="str">
-        <v/>
-      </c>
-      <c r="J80" t="str">
-        <v/>
-      </c>
-      <c r="K80" t="str">
-        <v/>
-      </c>
-      <c r="L80" t="str">
+      <c r="C81" t="str">
+        <v>0.3 mg/dL未満（施設差あり）</v>
+      </c>
+      <c r="D81" t="str">
+        <v>体のどこかに炎症や感染が起きていないかを鋭敏に反映する数値</v>
+      </c>
+      <c r="E81" t="str">
+        <v>CRPは、体に炎症や感染が起きると数時間〜半日程度で急激に上昇する数値です。風邪のようなウイルス感染から細菌感染、体のどこかの炎症まで、幅広く反応するため、体調の変化を早期に捉える手がかりになります。</v>
+      </c>
+      <c r="F81" t="str">
+        <v>細菌感染症、ウイルス感染症、自己免疫疾患（関節リウマチなど）、悪性腫瘍、組織の損傷（術後・心筋梗塞など）</v>
+      </c>
+      <c r="G81" t="str">
+        <v>発熱、痛み、腫れなど炎症症状の有無を確認する</v>
+      </c>
+      <c r="H81" t="str">
+        <v/>
+      </c>
+      <c r="I81" t="str">
+        <v/>
+      </c>
+      <c r="J81" t="str">
+        <v>白血球数と合わせて感染・炎症の程度を評価する。上昇・低下のタイミングは白血球より半日〜1日程度遅れる傾向があるため、経過を追う際は採血のタイミングに注意</v>
+      </c>
+      <c r="K81" t="str">
+        <v/>
+      </c>
+      <c r="L81" t="str">
         <v>CRP,炎症,感染</v>
       </c>
-      <c r="M80" t="str">
+      <c r="M81" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M80"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M81"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/検査値リファレンス初期データ.xlsx
+++ b/検査値リファレンス初期データ.xlsx
@@ -495,7 +495,7 @@
         <v>血糖値,血糖,BS,Glu,グルコース,空腹時血糖,随時血糖,食後血糖</v>
       </c>
       <c r="M2" t="str">
-        <v/>
+        <v>食事と栄養 p.18（炭水化物）／p.106-131（第2部 糖尿病）</v>
       </c>
     </row>
     <row r="3">
@@ -536,7 +536,7 @@
         <v>HbA1c,ヘモグロビンエーワンシー,グリコヘモグロビン,血糖コントロール,NGSP</v>
       </c>
       <c r="M3" t="str">
-        <v/>
+        <v>食事と栄養 p.18（炭水化物）／p.106-131（第2部 糖尿病）</v>
       </c>
     </row>
     <row r="4">
@@ -577,7 +577,7 @@
         <v>BUN,尿素窒素,UN,腎機能</v>
       </c>
       <c r="M4" t="str">
-        <v/>
+        <v>食事と栄養 p.199-215（第2部 腎機能低下）</v>
       </c>
     </row>
     <row r="5" xml:space="preserve">
@@ -621,7 +621,7 @@
         <v>クレアチニン,Cr,SCr,血清クレアチニン,eGFR,腎機能,GFR,推算糸球体濾過量,CKD重症度分類</v>
       </c>
       <c r="M5" t="str">
-        <v/>
+        <v>食事と栄養 p.199-215（第2部 腎機能低下）／p.243（フレイルQ111 クレアチニン値が低い場合）</v>
       </c>
     </row>
     <row r="6" xml:space="preserve">
@@ -663,7 +663,7 @@
         <v>CCr,クレアチニンクリアランス,クレアチニン・クリアランス,creatinine clearance,コッククロフトゴート,Cockcroft-Gault,腎機能</v>
       </c>
       <c r="M6" t="str">
-        <v/>
+        <v>食事と栄養 p.199-215（第2部 腎機能低下）</v>
       </c>
     </row>
     <row r="7">
@@ -704,7 +704,7 @@
         <v>尿酸,UA,痛風,高尿酸血症</v>
       </c>
       <c r="M7" t="str">
-        <v/>
+        <v>食事と栄養 p.180-189（第2部 痛風・高尿酸血症）</v>
       </c>
     </row>
     <row r="8">
@@ -745,7 +745,7 @@
         <v>ナトリウム,Na,電解質,脱水,SIADH,低ナトリウム血症</v>
       </c>
       <c r="M8" t="str">
-        <v/>
+        <v>食事と栄養 p.81（ナトリウム）</v>
       </c>
     </row>
     <row r="9">
@@ -827,7 +827,7 @@
         <v>カリウム,K,高カリウム血症,低カリウム血症</v>
       </c>
       <c r="M10" t="str">
-        <v/>
+        <v>食事と栄養 p.72（カリウム）／p.199-215（第2部 腎機能低下 Q80-82 カリウム制限）</v>
       </c>
     </row>
     <row r="11">
@@ -868,7 +868,7 @@
         <v>カルシウム,Ca,電解質</v>
       </c>
       <c r="M11" t="str">
-        <v/>
+        <v>食事と栄養 p.75（カルシウム）／p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="12">
@@ -1032,7 +1032,7 @@
         <v>ALP,アルカリホスファターゼ,骨代謝,肝機能</v>
       </c>
       <c r="M15" t="str">
-        <v/>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="16" xml:space="preserve">
@@ -1156,7 +1156,7 @@
         <v>総タンパク,TP,総蛋白,栄養状態,A/G比</v>
       </c>
       <c r="M18" t="str">
-        <v/>
+        <v>食事と栄養 p.23（たんぱく質）</v>
       </c>
     </row>
     <row r="19">
@@ -1197,7 +1197,7 @@
         <v>中性脂肪,トリグリセリド,TG,脂質異常症</v>
       </c>
       <c r="M19" t="str">
-        <v/>
+        <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
       </c>
     </row>
     <row r="20">
@@ -1238,7 +1238,7 @@
         <v>総コレステロール,TC,コレステロール,脂質異常症</v>
       </c>
       <c r="M20" t="str">
-        <v/>
+        <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
       </c>
     </row>
     <row r="21" xml:space="preserve">
@@ -1280,7 +1280,7 @@
         <v>LDL,LDLコレステロール,悪玉コレステロール,脂質異常症</v>
       </c>
       <c r="M21" t="str">
-        <v/>
+        <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
       </c>
     </row>
     <row r="22">
@@ -1321,7 +1321,7 @@
         <v>nonHDL,non-HDLコレステロール,動脈硬化,中性脂肪,LDL計算式</v>
       </c>
       <c r="M22" t="str">
-        <v/>
+        <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
       </c>
     </row>
     <row r="23">
@@ -1362,7 +1362,7 @@
         <v>HDL,HDLコレステロール,善玉コレステロール,脂質異常症</v>
       </c>
       <c r="M23" t="str">
-        <v/>
+        <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
       </c>
     </row>
     <row r="24">
@@ -1567,7 +1567,7 @@
         <v>赤血球,RBC,貧血,多血症</v>
       </c>
       <c r="M28" t="str">
-        <v/>
+        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="29">
@@ -1608,7 +1608,7 @@
         <v>ヘモグロビン,Hb,貧血,鉄剤,鉄欠乏性貧血</v>
       </c>
       <c r="M29" t="str">
-        <v/>
+        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="30">
@@ -1649,7 +1649,7 @@
         <v>ヘマトクリット,Ht,Hct,貧血,脱水,多血症</v>
       </c>
       <c r="M30" t="str">
-        <v/>
+        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="31">
@@ -1690,7 +1690,7 @@
         <v>MCV,赤血球指数,貧血</v>
       </c>
       <c r="M31" t="str">
-        <v/>
+        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="32">
@@ -1731,7 +1731,7 @@
         <v>MCH,赤血球指数,貧血</v>
       </c>
       <c r="M32" t="str">
-        <v/>
+        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="33">
@@ -1772,7 +1772,7 @@
         <v>MCHC,赤血球指数,貧血</v>
       </c>
       <c r="M33" t="str">
-        <v/>
+        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="34">
@@ -1854,7 +1854,7 @@
         <v>RDW-SD,赤血球分布幅,貧血,鉄欠乏</v>
       </c>
       <c r="M35" t="str">
-        <v/>
+        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="36">
@@ -1895,7 +1895,7 @@
         <v>RDW-CV,赤血球分布幅,貧血,ビタミンB12,葉酸</v>
       </c>
       <c r="M36" t="str">
-        <v/>
+        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="37">
@@ -2592,7 +2592,7 @@
         <v>アルブミン,Alb,むくみ,浮腫,栄養状態</v>
       </c>
       <c r="M53" t="str">
-        <v/>
+        <v>食事と栄養 p.23（たんぱく質）／p.242（フレイルQ110 アルブミン値を上げる食事指導）</v>
       </c>
     </row>
     <row r="54">
@@ -2633,7 +2633,7 @@
         <v>BNP,心不全,息切れ,むくみ</v>
       </c>
       <c r="M54" t="str">
-        <v/>
+        <v>食事と栄養 p.216-222（第2部 心疾患）</v>
       </c>
     </row>
     <row r="55">
@@ -2756,7 +2756,7 @@
         <v>血清鉄,Fe,鉄欠乏性貧血</v>
       </c>
       <c r="M57" t="str">
-        <v/>
+        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="58">
@@ -2797,7 +2797,7 @@
         <v>TIBC,総鉄結合能,鉄欠乏性貧血</v>
       </c>
       <c r="M58" t="str">
-        <v/>
+        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="59">
@@ -2838,7 +2838,7 @@
         <v>UIBC,不飽和鉄結合能,鉄欠乏性貧血</v>
       </c>
       <c r="M59" t="str">
-        <v/>
+        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="60">
@@ -2879,7 +2879,7 @@
         <v>トランスフェリン飽和度,TSAT,鉄欠乏性貧血</v>
       </c>
       <c r="M60" t="str">
-        <v/>
+        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="61">
@@ -2920,7 +2920,7 @@
         <v>フェリチン,Ferritin,貯蔵鉄,鉄欠乏</v>
       </c>
       <c r="M61" t="str">
-        <v/>
+        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="62">
@@ -2961,7 +2961,7 @@
         <v>UUA,UCr,尿酸クリアランス,CUA,EUA,尿酸産生過剰型,尿酸排泄低下型</v>
       </c>
       <c r="M62" t="str">
-        <v/>
+        <v>食事と栄養 p.180-189（第2部 痛風・高尿酸血症）</v>
       </c>
     </row>
     <row r="63">
@@ -3002,7 +3002,7 @@
         <v>ucOC,オステオカルシン,ビタミンK</v>
       </c>
       <c r="M63" t="str">
-        <v/>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="64">
@@ -3043,7 +3043,7 @@
         <v>リン,P,IP,無機リン</v>
       </c>
       <c r="M64" t="str">
-        <v/>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）／p.199-215（第2部 腎機能低下 Q83 リン制限）</v>
       </c>
     </row>
     <row r="65">
@@ -3084,7 +3084,7 @@
         <v>PTH,副甲状腺ホルモン,パラトルモン</v>
       </c>
       <c r="M65" t="str">
-        <v/>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="66">
@@ -3166,7 +3166,7 @@
         <v>カルシトニン,CT</v>
       </c>
       <c r="M67" t="str">
-        <v/>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="68">
@@ -3207,7 +3207,7 @@
         <v>NTX,尿中NTX,骨吸収マーカー</v>
       </c>
       <c r="M68" t="str">
-        <v/>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="69">
@@ -3248,7 +3248,7 @@
         <v>DPD,デオキシピリジノリン,骨吸収マーカー</v>
       </c>
       <c r="M69" t="str">
-        <v/>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="70">
@@ -3289,7 +3289,7 @@
         <v>CTX,骨吸収マーカー</v>
       </c>
       <c r="M70" t="str">
-        <v/>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="71">
@@ -3330,7 +3330,7 @@
         <v>P1NP,骨形成マーカー</v>
       </c>
       <c r="M71" t="str">
-        <v/>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="72">
@@ -3371,7 +3371,7 @@
         <v>抗TPO抗体,抗甲状腺マイクロゾーム抗体,TPOAb,橋本病</v>
       </c>
       <c r="M72" t="str">
-        <v/>
+        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
       </c>
     </row>
     <row r="73">
@@ -3412,7 +3412,7 @@
         <v>抗サイログロブリン抗体,TgAb,橋本病</v>
       </c>
       <c r="M73" t="str">
-        <v/>
+        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
       </c>
     </row>
     <row r="74">
@@ -3453,7 +3453,7 @@
         <v>TSH,甲状腺刺激ホルモン,甲状腺機能,橋本病,バセドウ病,チラーヂン,メルカゾール</v>
       </c>
       <c r="M74" t="str">
-        <v/>
+        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
       </c>
     </row>
     <row r="75">
@@ -3494,7 +3494,7 @@
         <v>FT4,遊離サイロキシン,甲状腺ホルモン,甲状腺機能</v>
       </c>
       <c r="M75" t="str">
-        <v/>
+        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
       </c>
     </row>
     <row r="76">
@@ -3535,7 +3535,7 @@
         <v>PT-INR,INR,プロトロンビン時間,ワルファリン,ワーファリン,抗凝固</v>
       </c>
       <c r="M76" t="str">
-        <v/>
+        <v>食事と栄養 p.221（心疾患Q93 ワルファリン服用中のビタミンK摂取）</v>
       </c>
     </row>
     <row r="77">
@@ -3799,7 +3799,7 @@
         <v>腎機能・脂質・眼科受診の有無。シックデイ対応を説明済みか</v>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>食事と栄養 p.106-131（第2部 糖尿病 Q11-26）</v>
       </c>
     </row>
     <row r="3">
@@ -3819,7 +3819,7 @@
         <v>LDLの目標値は既往疾患（冠動脈疾患・糖尿病など）によって異なる。スタチンの副作用（筋肉痛・脱力感）の有無</v>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>食事と栄養 p.132-150（第2部 脂質異常症 Q27-40）</v>
       </c>
     </row>
     <row r="4">
@@ -3859,7 +3859,7 @@
         <v>骨粗鬆症治療薬（ビスホスホネート等）の服用方法（起床時空腹時服用、服用後30分は横にならない、等）の再確認。転倒リスクとなる他剤（睡眠薬等）の併用</v>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症 Q51-60）</v>
       </c>
     </row>
     <row r="6">
@@ -3879,7 +3879,7 @@
         <v>腎排泄型薬剤の用量調整が必要ないか。NSAIDsや造影剤など腎機能に影響する薬剤の使用歴。脱水を起こしやすい状況（下痢・嘔吐・猛暑）がないか</v>
       </c>
       <c r="F6" t="str">
-        <v/>
+        <v>食事と栄養 p.190-215（第2部 尿路結石 Q70-77／腎機能低下 Q78-89）</v>
       </c>
     </row>
     <row r="7">
@@ -3959,7 +3959,7 @@
         <v>尿酸降下薬を急に開始・増量すると痛風発作が誘発されることがある。水分摂取量、尿路結石の既往</v>
       </c>
       <c r="F10" t="str">
-        <v/>
+        <v>食事と栄養 p.180-189（第2部 痛風・高尿酸血症 Q61-69）</v>
       </c>
     </row>
     <row r="11">
@@ -3999,7 +3999,7 @@
         <v>体重の日々の変化（急な増加は水分貯留のサイン）。塩分・水分制限の理解度。NSAIDsなど心不全を悪化させうる薬剤の使用</v>
       </c>
       <c r="F12" t="str">
-        <v/>
+        <v>食事と栄養 p.216-222（第2部 心疾患 Q90-94）</v>
       </c>
     </row>
     <row r="13">
@@ -4019,7 +4019,7 @@
         <v>鉄剤は自己判断で早期中断されやすい。出血源（消化管出血・月経過多等）の精査が済んでいるか</v>
       </c>
       <c r="F13" t="str">
-        <v/>
+        <v>食事と栄養 p.151-164（第2部 貧血 Q41-50）</v>
       </c>
     </row>
     <row r="14">
@@ -4039,7 +4039,7 @@
         <v>チラーヂンSは食後だと吸収が落ちやすく、起床時空腹での服用が基本であること。メルカゾールは無顆粒球症の初期症状（発熱・のどの痛み）が出たらすぐ受診が必要なこと</v>
       </c>
       <c r="F14" t="str">
-        <v/>
+        <v>食事と栄養 p.224-228（第2部 甲状腺疾患 Q95-98）</v>
       </c>
     </row>
     <row r="15">
@@ -4059,7 +4059,7 @@
         <v>利尿薬・下剤・NSAIDsなど電解質に影響する薬剤の併用。高カリウム血症は自覚症状に乏しく数値での早期発見が重要</v>
       </c>
       <c r="F15" t="str">
-        <v/>
+        <v>食事と栄養 p.72（カリウム）・p.81（ナトリウム）／p.199-215（第2部 腎機能低下 Q80-82）</v>
       </c>
     </row>
   </sheetData>

--- a/検査値リファレンス初期データ.xlsx
+++ b/検査値リファレンス初期データ.xlsx
@@ -873,66 +873,66 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>AST（GOT）</v>
+        <v>リン（P）</v>
       </c>
       <c r="B12" t="str">
-        <v>AST,GOT</v>
+        <v>P,IP</v>
       </c>
       <c r="C12" t="str">
-        <v>10〜40 U/L</v>
+        <v>2.5〜4.5 mg/dL</v>
       </c>
       <c r="D12" t="str">
-        <v>肝臓や心臓・筋肉の細胞が壊れると血液中に漏れ出す酵素</v>
+        <v>カルシウムとともに骨を作る主要なミネラル</v>
       </c>
       <c r="E12" t="str">
-        <v>ASTは肝臓や心臓、筋肉の細胞の中にある酵素です。これらの細胞がダメージを受けたり壊れたりすると血液中に漏れ出して数値が上がります。肝臓の状態を見るときはALTと一緒に確認します。</v>
+        <v>リンはカルシウムと一緒に骨や歯を作る材料になるミネラルです。カルシウムと逆方向に動くことが多く、腎臓の働きやホルモンのバランスによっても変動します。</v>
       </c>
       <c r="F12" t="str">
-        <v>肝炎・肝硬変などの肝疾患、心筋梗塞、筋肉の障害（激しい運動・横紋筋融解症）、薬剤性肝障害</v>
+        <v>腎不全、副甲状腺機能低下症</v>
       </c>
       <c r="G12" t="str">
-        <v>飲酒量を控える。激しい運動の直後の採血でないかを確認する</v>
+        <v/>
       </c>
       <c r="H12" t="str">
-        <v>臨床的に問題になることは少ない</v>
+        <v>副甲状腺機能亢進症、骨軟化症、ビタミンD欠乏</v>
       </c>
       <c r="I12" t="str">
         <v/>
       </c>
       <c r="J12" t="str">
-        <v>ALTとの比率（AST/ALT比）で肝細胞障害か他臓器由来かを推測できる。AST優位はアルコール性・心筋・筋由来を疑う材料になる</v>
+        <v>カルシウムと逆方向に動くことが多い（副甲状腺機能亢進症ではCa上昇・P低下）。骨粗鬆症の二次性原因の除外に用いられる</v>
       </c>
       <c r="K12" t="str">
-        <v>肝機能,糖尿病,てんかん,精神疾患（非定型抗精神病薬）</v>
+        <v>骨粗鬆症,電解質</v>
       </c>
       <c r="L12" t="str">
-        <v>AST,GOT,肝機能,肝障害</v>
+        <v>リン,P,IP,無機リン</v>
       </c>
       <c r="M12" t="str">
-        <v/>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）／p.199-215（第2部 腎機能低下 Q83 リン制限）</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ALT（GPT）</v>
+        <v>AST（GOT）</v>
       </c>
       <c r="B13" t="str">
-        <v>ALT,GPT</v>
+        <v>AST,GOT</v>
       </c>
       <c r="C13" t="str">
-        <v>5〜40 U/L</v>
+        <v>10〜40 U/L</v>
       </c>
       <c r="D13" t="str">
-        <v>主に肝臓の細胞に含まれる酵素で、肝障害の指標として最もよく使われる</v>
+        <v>肝臓や心臓・筋肉の細胞が壊れると血液中に漏れ出す酵素</v>
       </c>
       <c r="E13" t="str">
-        <v>ALTは主に肝臓の細胞の中にある酵素です。肝臓の細胞がダメージを受けると血液中に漏れ出して数値が上がります。ASTよりも肝臓に特異的な数値なので、肝臓の状態を見るときによく使われます。</v>
+        <v>ASTは肝臓や心臓、筋肉の細胞の中にある酵素です。これらの細胞がダメージを受けたり壊れたりすると血液中に漏れ出して数値が上がります。肝臓の状態を見るときはALTと一緒に確認します。</v>
       </c>
       <c r="F13" t="str">
-        <v>脂肪肝、肝炎（ウイルス性・アルコール性・薬剤性）、肝硬変、薬の副作用による肝機能障害</v>
+        <v>肝炎・肝硬変などの肝疾患、心筋梗塞、筋肉の障害（激しい運動・横紋筋融解症）、薬剤性肝障害</v>
       </c>
       <c r="G13" t="str">
-        <v>体重管理と脂質の摂りすぎに注意する（脂肪肝が疑われる場合）。新規薬剤の開始時期と重なっていないか確認する</v>
+        <v>飲酒量を控える。激しい運動の直後の採血でないかを確認する</v>
       </c>
       <c r="H13" t="str">
         <v>臨床的に問題になることは少ない</v>
@@ -941,13 +941,13 @@
         <v/>
       </c>
       <c r="J13" t="str">
-        <v>新規薬剤開始後の肝障害の指標として重要。健診でALTのみ軽度上昇していることが多く、その場合は脂肪肝（NAFLD）の頻度が高い</v>
+        <v>ALTとの比率（AST/ALT比）で肝細胞障害か他臓器由来かを推測できる。AST優位はアルコール性・心筋・筋由来を疑う材料になる</v>
       </c>
       <c r="K13" t="str">
         <v>肝機能,糖尿病,てんかん,精神疾患（非定型抗精神病薬）</v>
       </c>
       <c r="L13" t="str">
-        <v>ALT,GPT,肝機能,肝障害,脂肪肝</v>
+        <v>AST,GOT,肝機能,肝障害</v>
       </c>
       <c r="M13" t="str">
         <v/>
@@ -955,40 +955,40 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>コリンエステラーゼ</v>
+        <v>ALT（GPT）</v>
       </c>
       <c r="B14" t="str">
-        <v>ChE</v>
+        <v>ALT,GPT</v>
       </c>
       <c r="C14" t="str">
-        <v>男性 240〜486 U/L、女性 201〜421 U/L（施設差あり）</v>
+        <v>5〜40 U/L</v>
       </c>
       <c r="D14" t="str">
-        <v>主に肝臓で作られる酵素。肝臓のたんぱく質を作る力（合成能）を反映する</v>
+        <v>主に肝臓の細胞に含まれる酵素で、肝障害の指標として最もよく使われる</v>
       </c>
       <c r="E14" t="str">
-        <v>コリンエステラーゼは肝臓で作られる酵素です。肝臓がたんぱく質を作る力が落ちると数値が下がり、逆に脂肪肝や栄養状態が良すぎる場合は上がることがあります。</v>
+        <v>ALTは主に肝臓の細胞の中にある酵素です。肝臓の細胞がダメージを受けると血液中に漏れ出して数値が上がります。ASTよりも肝臓に特異的な数値なので、肝臓の状態を見るときによく使われます。</v>
       </c>
       <c r="F14" t="str">
-        <v>脂肪肝、ネフローゼ症候群、肥満、甲状腺機能亢進症</v>
+        <v>脂肪肝、肝炎（ウイルス性・アルコール性・薬剤性）、肝硬変、薬の副作用による肝機能障害</v>
       </c>
       <c r="G14" t="str">
-        <v>脂肪肝が疑われる場合は食事・運動習慣の見直しを勧める</v>
+        <v>体重管理と脂質の摂りすぎに注意する（脂肪肝が疑われる場合）。新規薬剤の開始時期と重なっていないか確認する</v>
       </c>
       <c r="H14" t="str">
-        <v>肝硬変など肝臓の合成能低下、低栄養、有機リン中毒（農薬など）</v>
+        <v>臨床的に問題になることは少ない</v>
       </c>
       <c r="I14" t="str">
         <v/>
       </c>
       <c r="J14" t="str">
-        <v>アルブミンと同様に肝臓の「合成能」を見る指標。低栄養か肝硬変かは、アルブミンや血小板数（肝硬変で低下しやすい）と合わせて判断する</v>
+        <v>新規薬剤開始後の肝障害の指標として重要。健診でALTのみ軽度上昇していることが多く、その場合は脂肪肝（NAFLD）の頻度が高い</v>
       </c>
       <c r="K14" t="str">
-        <v>肝機能</v>
+        <v>肝機能,糖尿病,てんかん,精神疾患（非定型抗精神病薬）</v>
       </c>
       <c r="L14" t="str">
-        <v>コリンエステラーゼ,ChE,肝合成能,脂肪肝,肝硬変</v>
+        <v>ALT,GPT,肝機能,肝障害,脂肪肝</v>
       </c>
       <c r="M14" t="str">
         <v/>
@@ -996,123 +996,123 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
+        <v>コリンエステラーゼ</v>
+      </c>
+      <c r="B15" t="str">
+        <v>ChE</v>
+      </c>
+      <c r="C15" t="str">
+        <v>男性 240〜486 U/L、女性 201〜421 U/L（施設差あり）</v>
+      </c>
+      <c r="D15" t="str">
+        <v>主に肝臓で作られる酵素。肝臓のたんぱく質を作る力（合成能）を反映する</v>
+      </c>
+      <c r="E15" t="str">
+        <v>コリンエステラーゼは肝臓で作られる酵素です。肝臓がたんぱく質を作る力が落ちると数値が下がり、逆に脂肪肝や栄養状態が良すぎる場合は上がることがあります。</v>
+      </c>
+      <c r="F15" t="str">
+        <v>脂肪肝、ネフローゼ症候群、肥満、甲状腺機能亢進症</v>
+      </c>
+      <c r="G15" t="str">
+        <v>脂肪肝が疑われる場合は食事・運動習慣の見直しを勧める</v>
+      </c>
+      <c r="H15" t="str">
+        <v>肝硬変など肝臓の合成能低下、低栄養、有機リン中毒（農薬など）</v>
+      </c>
+      <c r="I15" t="str">
+        <v/>
+      </c>
+      <c r="J15" t="str">
+        <v>アルブミンと同様に肝臓の「合成能」を見る指標。低栄養か肝硬変かは、アルブミンや血小板数（肝硬変で低下しやすい）と合わせて判断する</v>
+      </c>
+      <c r="K15" t="str">
+        <v>肝機能</v>
+      </c>
+      <c r="L15" t="str">
+        <v>コリンエステラーゼ,ChE,肝合成能,脂肪肝,肝硬変</v>
+      </c>
+      <c r="M15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
         <v>アルカリホスファターゼ（ALP）</v>
       </c>
-      <c r="B15" t="str">
+      <c r="B16" t="str">
         <v>ALP</v>
       </c>
-      <c r="C15" t="str">
+      <c r="C16" t="str">
         <v>38〜113 U/L（施設・測定法により大きく異なる）</v>
       </c>
-      <c r="D15" t="str">
+      <c r="D16" t="str">
         <v>骨や肝臓・胆道に多く含まれる酵素で、骨を作る働きの指標にもなる</v>
       </c>
-      <c r="E15" t="str">
+      <c r="E16" t="str">
         <v>ALPは骨や肝臓、胆道に多く含まれる酵素です。骨を作る働きが活発なとき（骨の成長期や骨折の治癒過程など）や、肝臓・胆道にトラブルがあるときに数値が上がります。</v>
       </c>
-      <c r="F15" t="str">
+      <c r="F16" t="str">
         <v>骨代謝の亢進（骨折治癒過程、骨粗鬆症、骨転移、Paget病）、肝・胆道疾患、成長期の生理的高値</v>
       </c>
-      <c r="G15" t="str">
-        <v/>
-      </c>
-      <c r="H15" t="str">
-        <v/>
-      </c>
-      <c r="I15" t="str">
-        <v/>
-      </c>
-      <c r="J15" t="str">
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v/>
+      </c>
+      <c r="J16" t="str">
         <v>骨由来か肝由来かの区別には骨型ALPアイソザイムやγ-GTPとの組み合わせで判断する</v>
       </c>
-      <c r="K15" t="str">
+      <c r="K16" t="str">
         <v>骨粗鬆症,肝機能</v>
       </c>
-      <c r="L15" t="str">
+      <c r="L16" t="str">
         <v>ALP,アルカリホスファターゼ,骨代謝,肝機能</v>
       </c>
-      <c r="M15" t="str">
+      <c r="M16" t="str">
         <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
-    <row r="16" xml:space="preserve">
-      <c r="A16" t="str">
+    <row r="17" xml:space="preserve">
+      <c r="A17" t="str">
         <v>γ-GTP</v>
       </c>
-      <c r="B16" t="str">
+      <c r="B17" t="str">
         <v>γ-GTP,GGT</v>
       </c>
-      <c r="C16" t="str" xml:space="preserve">
+      <c r="C17" t="str" xml:space="preserve">
         <v xml:space="preserve">男性 〜50 U/L、女性 〜30 U/L
 （施設差が大きい）</v>
       </c>
-      <c r="D16" t="str">
+      <c r="D17" t="str">
         <v>アルコールや胆道のトラブルに反応しやすい肝臓の酵素</v>
       </c>
-      <c r="E16" t="str">
+      <c r="E17" t="str">
         <v>γ-GTPは肝臓や胆道の細胞にある酵素で、特にお酒の影響を受けやすいことが知られています。数値が高いときは、アルコールの摂取量や胆道（胆汁の通り道）の状態を確認する目安になります。</v>
       </c>
-      <c r="F16" t="str">
+      <c r="F17" t="str">
         <v>アルコール性肝障害、脂肪肝、胆道系疾患（胆石・胆管閉塞）、薬剤性（酵素誘導）</v>
       </c>
-      <c r="G16" t="str">
+      <c r="G17" t="str">
         <v>飲酒量を控える、休肝日をつくるよう伝える</v>
       </c>
-      <c r="H16" t="str">
+      <c r="H17" t="str">
         <v>臨床的に問題になることは少ない</v>
       </c>
-      <c r="I16" t="str">
-        <v/>
-      </c>
-      <c r="J16" t="str">
+      <c r="I17" t="str">
+        <v/>
+      </c>
+      <c r="J17" t="str">
         <v>飲酒歴の確認に使いやすい数値。断酒・節酒で比較的早く改善するため、生活指導の効果を示す指標としても使える</v>
-      </c>
-      <c r="K16" t="str">
-        <v>肝機能</v>
-      </c>
-      <c r="L16" t="str">
-        <v>ガンマGTP,γ-GTP,GGT,肝機能,飲酒,アルコール</v>
-      </c>
-      <c r="M16" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>総ビリルビン</v>
-      </c>
-      <c r="B17" t="str">
-        <v>T-Bil</v>
-      </c>
-      <c r="C17" t="str">
-        <v>0.2〜1.2 mg/dL</v>
-      </c>
-      <c r="D17" t="str">
-        <v>赤血球が壊れてできる黄色い色素の総量。肝臓・胆道の状態や黄疸の指標</v>
-      </c>
-      <c r="E17" t="str">
-        <v>ビリルビンは赤血球が寿命を迎えて壊れるときにできる黄色い色素です。肝臓で処理されて排泄されますが、肝臓や胆道にトラブルがあると血液中に増え、皮膚や白目が黄色くなる黄疸として現れます。</v>
-      </c>
-      <c r="F17" t="str">
-        <v>肝炎・肝硬変などの肝疾患、胆道閉塞（胆石・腫瘍など）、溶血性疾患（赤血球の破壊亢進）、体質性黄疸（ジルベール症候群など）</v>
-      </c>
-      <c r="G17" t="str">
-        <v>皮膚や白目の黄染、尿の色が濃くなっていないか確認する</v>
-      </c>
-      <c r="H17" t="str">
-        <v/>
-      </c>
-      <c r="I17" t="str">
-        <v/>
-      </c>
-      <c r="J17" t="str">
-        <v>直接ビリルビン・間接ビリルビンの内訳で原因を推測できる（直接優位は胆道系、間接優位は溶血・体質性）。AST/ALT/γ-GTPと合わせて評価する</v>
       </c>
       <c r="K17" t="str">
         <v>肝機能</v>
       </c>
       <c r="L17" t="str">
-        <v>総ビリルビン,T-Bil,黄疸,ビリルビン,ジルベール症候群</v>
+        <v>ガンマGTP,γ-GTP,GGT,肝機能,飲酒,アルコール</v>
       </c>
       <c r="M17" t="str">
         <v/>
@@ -1120,246 +1120,246 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>総タンパク</v>
+        <v>総ビリルビン</v>
       </c>
       <c r="B18" t="str">
-        <v>TP</v>
+        <v>T-Bil</v>
       </c>
       <c r="C18" t="str">
-        <v>6.6〜8.1 g/dL</v>
+        <v>0.2〜1.2 mg/dL</v>
       </c>
       <c r="D18" t="str">
-        <v>血液中のたんぱく質（アルブミン＋グロブリン）の総量。栄養状態や肝機能、炎症の目安</v>
+        <v>赤血球が壊れてできる黄色い色素の総量。肝臓・胆道の状態や黄疸の指標</v>
       </c>
       <c r="E18" t="str">
-        <v>総タンパクは、血液中のたんぱく質の合計量です。栄養状態や肝臓の働き、体の炎症の有無などを反映します。</v>
+        <v>ビリルビンは赤血球が寿命を迎えて壊れるときにできる黄色い色素です。肝臓で処理されて排泄されますが、肝臓や胆道にトラブルがあると血液中に増え、皮膚や白目が黄色くなる黄疸として現れます。</v>
       </c>
       <c r="F18" t="str">
-        <v>脱水、多発性骨髄腫など（グロブリン増加）、慢性炎症</v>
+        <v>肝炎・肝硬変などの肝疾患、胆道閉塞（胆石・腫瘍など）、溶血性疾患（赤血球の破壊亢進）、体質性黄疸（ジルベール症候群など）</v>
       </c>
       <c r="G18" t="str">
-        <v/>
+        <v>皮膚や白目の黄染、尿の色が濃くなっていないか確認する</v>
       </c>
       <c r="H18" t="str">
-        <v>低栄養、肝機能低下（アルブミン産生低下）、ネフローゼ症候群、消化管からのたんぱく漏出</v>
+        <v/>
       </c>
       <c r="I18" t="str">
-        <v>食事摂取量（特にたんぱく質）を確認する</v>
+        <v/>
       </c>
       <c r="J18" t="str">
-        <v>アルブミンとグロブリンの内訳（A/G比）も合わせて確認すると原因の絞り込みに役立つ。低栄養か肝機能低下かはアルブミンの値と合わせて判断する</v>
+        <v>直接ビリルビン・間接ビリルビンの内訳で原因を推測できる（直接優位は胆道系、間接優位は溶血・体質性）。AST/ALT/γ-GTPと合わせて評価する</v>
       </c>
       <c r="K18" t="str">
         <v>肝機能</v>
       </c>
       <c r="L18" t="str">
-        <v>総タンパク,TP,総蛋白,栄養状態,A/G比</v>
+        <v>総ビリルビン,T-Bil,黄疸,ビリルビン,ジルベール症候群</v>
       </c>
       <c r="M18" t="str">
-        <v>食事と栄養 p.23（たんぱく質）</v>
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>中性脂肪（トリグリセリド）</v>
+        <v>総タンパク</v>
       </c>
       <c r="B19" t="str">
-        <v>TG</v>
+        <v>TP</v>
       </c>
       <c r="C19" t="str">
-        <v>150 mg/dL未満（空腹時）</v>
+        <v>6.6〜8.1 g/dL</v>
       </c>
       <c r="D19" t="str">
-        <v>脂質異常症で高値になりやすい脂質で、食事の影響を強く受ける</v>
+        <v>血液中のたんぱく質（アルブミン＋グロブリン）の総量。栄養状態や肝機能、炎症の目安</v>
       </c>
       <c r="E19" t="str">
-        <v>中性脂肪は、食事から摂った脂肪や糖質が体に蓄えられる形になったものです。食後は誰でも一時的に上がるため、正確に評価するには空腹時に採血することが大切です。高い状態が続くと動脈硬化や急性膵炎のリスクが高まります。</v>
+        <v>総タンパクは、血液中のたんぱく質の合計量です。栄養状態や肝臓の働き、体の炎症の有無などを反映します。</v>
       </c>
       <c r="F19" t="str">
-        <v>脂質異常症、糖質・アルコールの摂りすぎ、肥満、糖尿病のコントロール不良</v>
+        <v>脱水、多発性骨髄腫など（グロブリン増加）、慢性炎症</v>
       </c>
       <c r="G19" t="str">
-        <v>糖質・アルコールの摂りすぎに注意し、有酸素運動を勧める</v>
+        <v/>
       </c>
       <c r="H19" t="str">
-        <v>低栄養、甲状腺機能亢進症</v>
+        <v>低栄養、肝機能低下（アルブミン産生低下）、ネフローゼ症候群、消化管からのたんぱく漏出</v>
       </c>
       <c r="I19" t="str">
-        <v/>
+        <v>食事摂取量（特にたんぱく質）を確認する</v>
       </c>
       <c r="J19" t="str">
-        <v>採血が食後か空腹時かで数値が大きく変わるため必ず確認する。500 mg/dL以上では急性膵炎のリスクが高まるため注意。フィブラート系・EPA製剤などの効果判定に使う</v>
+        <v>アルブミンとグロブリンの内訳（A/G比）も合わせて確認すると原因の絞り込みに役立つ。低栄養か肝機能低下かはアルブミンの値と合わせて判断する</v>
       </c>
       <c r="K19" t="str">
-        <v>脂質異常症</v>
+        <v>肝機能</v>
       </c>
       <c r="L19" t="str">
-        <v>中性脂肪,トリグリセリド,TG,脂質異常症</v>
+        <v>総タンパク,TP,総蛋白,栄養状態,A/G比</v>
       </c>
       <c r="M19" t="str">
-        <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
+        <v>食事と栄養 p.23（たんぱく質）</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
+        <v>アルブミン</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Alb</v>
+      </c>
+      <c r="C20" t="str">
+        <v>3.8〜5.2 g/dL</v>
+      </c>
+      <c r="D20" t="str">
+        <v>体の栄養状態を見る目安になるたんぱく質。血液の中で栄養を運ぶ、水分を血管の中に保つという働きをしている。</v>
+      </c>
+      <c r="E20" t="str">
+        <v>アルブミンは栄養の状態を見る数値です。食事量が少なかったり、肝臓や腎臓、腸の働きが弱ると下がることがあります。数値が低いと、むくみが出やすくなります。</v>
+      </c>
+      <c r="F20" t="str">
+        <v>脱水（見かけ上の上昇）</v>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v>低栄養／肝機能低下／ネフローゼ症候群／クローン病</v>
+      </c>
+      <c r="I20" t="str">
+        <v>主食に偏らず、肉・魚・卵・大豆製品などたんぱく質をしっかり摂るよう伝える。食欲が落ちている場合は少量頻回の食事も提案する</v>
+      </c>
+      <c r="J20" t="str">
+        <v>3前半は注意ライン。食事摂取量を必ず確認</v>
+      </c>
+      <c r="K20" t="str">
+        <v>肝機能,栄養,腎機能</v>
+      </c>
+      <c r="L20" t="str">
+        <v>アルブミン,Alb,むくみ,浮腫,栄養状態</v>
+      </c>
+      <c r="M20" t="str">
+        <v>食事と栄養 p.23（たんぱく質）／p.242（フレイルQ110 アルブミン値を上げる食事指導）</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>中性脂肪（トリグリセリド）</v>
+      </c>
+      <c r="B21" t="str">
+        <v>TG</v>
+      </c>
+      <c r="C21" t="str">
+        <v>150 mg/dL未満（空腹時）</v>
+      </c>
+      <c r="D21" t="str">
+        <v>脂質異常症で高値になりやすい脂質で、食事の影響を強く受ける</v>
+      </c>
+      <c r="E21" t="str">
+        <v>中性脂肪は、食事から摂った脂肪や糖質が体に蓄えられる形になったものです。食後は誰でも一時的に上がるため、正確に評価するには空腹時に採血することが大切です。高い状態が続くと動脈硬化や急性膵炎のリスクが高まります。</v>
+      </c>
+      <c r="F21" t="str">
+        <v>脂質異常症、糖質・アルコールの摂りすぎ、肥満、糖尿病のコントロール不良</v>
+      </c>
+      <c r="G21" t="str">
+        <v>糖質・アルコールの摂りすぎに注意し、有酸素運動を勧める</v>
+      </c>
+      <c r="H21" t="str">
+        <v>低栄養、甲状腺機能亢進症</v>
+      </c>
+      <c r="I21" t="str">
+        <v/>
+      </c>
+      <c r="J21" t="str">
+        <v>採血が食後か空腹時かで数値が大きく変わるため必ず確認する。500 mg/dL以上では急性膵炎のリスクが高まるため注意。フィブラート系・EPA製剤などの効果判定に使う</v>
+      </c>
+      <c r="K21" t="str">
+        <v>脂質異常症</v>
+      </c>
+      <c r="L21" t="str">
+        <v>中性脂肪,トリグリセリド,TG,脂質異常症</v>
+      </c>
+      <c r="M21" t="str">
+        <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
         <v>総コレステロール</v>
       </c>
-      <c r="B20" t="str">
+      <c r="B22" t="str">
         <v>TC,T-cho</v>
       </c>
-      <c r="C20" t="str">
+      <c r="C22" t="str">
         <v>220 mg/dL未満</v>
       </c>
-      <c r="D20" t="str">
+      <c r="D22" t="str">
         <v>LDL・HDLなどすべてのコレステロールを合わせた総量</v>
       </c>
-      <c r="E20" t="str">
+      <c r="E22" t="str">
         <v>総コレステロールは、体の中にあるコレステロールをすべて合わせた数値です。ただし、悪玉(LDL)が多いのか善玉(HDL)が多いのかまでは分からないため、実際の評価にはLDLコレステロールの値がより重視されます。</v>
       </c>
-      <c r="F20" t="str">
+      <c r="F22" t="str">
         <v>脂質異常症、家族性高コレステロール血症、甲状腺機能低下症</v>
       </c>
-      <c r="G20" t="str">
+      <c r="G22" t="str">
         <v>動物性脂肪を控え、食物繊維を増やすよう伝える</v>
       </c>
-      <c r="H20" t="str">
+      <c r="H22" t="str">
         <v>低栄養、肝機能低下、甲状腺機能亢進症</v>
       </c>
-      <c r="I20" t="str">
-        <v/>
-      </c>
-      <c r="J20" t="str">
+      <c r="I22" t="str">
+        <v/>
+      </c>
+      <c r="J22" t="str">
         <v>現在はLDLコレステロールでの評価が主流。総コレステロールだけでは悪玉・善玉の内訳が分からないため、LDL・HDL・中性脂肪と合わせて評価する</v>
       </c>
-      <c r="K20" t="str">
+      <c r="K22" t="str">
         <v>脂質異常症</v>
       </c>
-      <c r="L20" t="str">
+      <c r="L22" t="str">
         <v>総コレステロール,TC,コレステロール,脂質異常症</v>
       </c>
-      <c r="M20" t="str">
+      <c r="M22" t="str">
         <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
       </c>
     </row>
-    <row r="21" xml:space="preserve">
-      <c r="A21" t="str">
+    <row r="23" xml:space="preserve">
+      <c r="A23" t="str">
         <v>LDLコレステロール</v>
       </c>
-      <c r="B21" t="str">
+      <c r="B23" t="str">
         <v>LDL-C</v>
       </c>
-      <c r="C21" t="str" xml:space="preserve">
+      <c r="C23" t="str" xml:space="preserve">
         <v xml:space="preserve">60〜139 mg/dL
 （140 mg/dL以上で高LDLコレステロール血症）</v>
       </c>
-      <c r="D21" t="str">
+      <c r="D23" t="str">
         <v>いわゆる「悪玉コレステロール」。血管の壁にたまり動脈硬化を進める</v>
       </c>
-      <c r="E21" t="str">
+      <c r="E23" t="str">
         <v>LDLコレステロールは、いわゆる悪玉コレステロールと呼ばれるものです。多いままだと血管の壁にたまって、動脈硬化や心筋梗塞・脳梗塞のリスクを高めます。数値を下げることで、将来の血管のトラブルを防ぐことが目的です。</v>
       </c>
-      <c r="F21" t="str">
+      <c r="F23" t="str">
         <v>脂質異常症、動脈硬化のリスク上昇、家族性高コレステロール血症、甲状腺機能低下症</v>
       </c>
-      <c r="G21" t="str">
+      <c r="G23" t="str">
         <v>動物性脂肪や揚げ物を控え、青魚や食物繊維（野菜・海藻・きのこ）を増やすよう伝える</v>
       </c>
-      <c r="H21" t="str">
+      <c r="H23" t="str">
         <v>低栄養、肝機能低下、甲状腺機能亢進症</v>
       </c>
-      <c r="I21" t="str">
-        <v/>
-      </c>
-      <c r="J21" t="str">
+      <c r="I23" t="str">
+        <v/>
+      </c>
+      <c r="J23" t="str">
         <v>スタチン等の効果判定に使う中心的な数値。目標値は既往疾患（冠動脈疾患・糖尿病等）によって異なるため一律に判断しない</v>
       </c>
-      <c r="K21" t="str">
+      <c r="K23" t="str">
         <v>脂質異常症,精神疾患（非定型抗精神病薬）</v>
       </c>
-      <c r="L21" t="str">
+      <c r="L23" t="str">
         <v>LDL,LDLコレステロール,悪玉コレステロール,脂質異常症</v>
-      </c>
-      <c r="M21" t="str">
-        <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>nonHDLコレステロール</v>
-      </c>
-      <c r="B22" t="str">
-        <v>non-HDL-C</v>
-      </c>
-      <c r="C22" t="str">
-        <v>90〜149 mg/dL（150 mg/dL以上で高値）</v>
-      </c>
-      <c r="D22" t="str">
-        <v>総コレステロールからHDL（善玉）を除いた、動脈硬化を進めるすべての脂質の合計</v>
-      </c>
-      <c r="E22" t="str">
-        <v>nonHDLコレステロールは、総コレステロールから善玉のHDLを引いた数値で、LDL（悪玉）を含む、動脈硬化を進めるすべてのコレステロールの合計を表します。中性脂肪が高くLDLだけでは評価しにくい方でも、こちらで動脈硬化のリスクを評価できます。</v>
-      </c>
-      <c r="F22" t="str">
-        <v>脂質異常症、動脈硬化のリスク上昇（特に中性脂肪が高い場合にLDL-Cより実態を反映しやすい）</v>
-      </c>
-      <c r="G22" t="str">
-        <v>動物性脂肪や揚げ物を控え、青魚や食物繊維（野菜・海藻・きのこ）を増やすよう伝える</v>
-      </c>
-      <c r="H22" t="str">
-        <v/>
-      </c>
-      <c r="I22" t="str">
-        <v/>
-      </c>
-      <c r="J22" t="str">
-        <v>中性脂肪（TG）が400 mg/dL以上などLDL-Cの計算式（Friedewald式）が不正確になる場合に、LDL-Cの代わりに用いられる。目標値はLDL-Cの目標値＋30 mg/dLが目安</v>
-      </c>
-      <c r="K22" t="str">
-        <v>脂質異常症</v>
-      </c>
-      <c r="L22" t="str">
-        <v>nonHDL,non-HDLコレステロール,動脈硬化,中性脂肪,LDL計算式</v>
-      </c>
-      <c r="M22" t="str">
-        <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>HDLコレステロール</v>
-      </c>
-      <c r="B23" t="str">
-        <v>HDL-C</v>
-      </c>
-      <c r="C23" t="str">
-        <v>40 mg/dL以上</v>
-      </c>
-      <c r="D23" t="str">
-        <v>いわゆる「善玉コレステロール」。血管にたまった余分なコレステロールを回収する</v>
-      </c>
-      <c r="E23" t="str">
-        <v>HDLコレステロールは、いわゆる善玉コレステロールと呼ばれるものです。血管の壁にたまった余分なコレステロールを回収して肝臓に戻す働きがあり、数値が高いほど動脈硬化を防ぐ方向に働きます。</v>
-      </c>
-      <c r="F23" t="str">
-        <v/>
-      </c>
-      <c r="G23" t="str">
-        <v/>
-      </c>
-      <c r="H23" t="str">
-        <v>脂質異常症（低HDL血症）</v>
-      </c>
-      <c r="I23" t="str">
-        <v>適度な運動習慣、禁煙を勧める</v>
-      </c>
-      <c r="J23" t="str">
-        <v>喫煙、運動不足、肥満で低下しやすい。禁煙・運動習慣の改善で上昇が期待できる。低HDLは動脈硬化のリスク因子として単独でも重視される</v>
-      </c>
-      <c r="K23" t="str">
-        <v>脂質異常症</v>
-      </c>
-      <c r="L23" t="str">
-        <v>HDL,HDLコレステロール,善玉コレステロール,脂質異常症</v>
       </c>
       <c r="M23" t="str">
         <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
@@ -1367,25 +1367,25 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>CK（クレアチンフォスフォキナーゼ）</v>
+        <v>nonHDLコレステロール</v>
       </c>
       <c r="B24" t="str">
-        <v>CK,CPK</v>
+        <v>non-HDL-C</v>
       </c>
       <c r="C24" t="str">
-        <v>男性 60〜250 U/L、女性 50〜170 U/L</v>
+        <v>90〜149 mg/dL（150 mg/dL以上で高値）</v>
       </c>
       <c r="D24" t="str">
-        <v>主に骨格筋・心筋に含まれる酵素。筋肉の損傷で血液中に漏れ出す</v>
+        <v>総コレステロールからHDL（善玉）を除いた、動脈硬化を進めるすべての脂質の合計</v>
       </c>
       <c r="E24" t="str">
-        <v>CKは筋肉の中にある酵素で、激しい運動や筋肉の病気、心筋梗塞などで筋肉の細胞がダメージを受けると血液中に漏れ出して数値が上がります。スタチン系のお薬の副作用（横紋筋融解症）のチェックにも使われます。</v>
+        <v>nonHDLコレステロールは、総コレステロールから善玉のHDLを引いた数値で、LDL（悪玉）を含む、動脈硬化を進めるすべてのコレステロールの合計を表します。中性脂肪が高くLDLだけでは評価しにくい方でも、こちらで動脈硬化のリスクを評価できます。</v>
       </c>
       <c r="F24" t="str">
-        <v>心筋梗塞、横紋筋融解症（スタチン系薬剤の副作用など）、激しい運動、筋肉注射直後、甲状腺機能低下症</v>
+        <v>脂質異常症、動脈硬化のリスク上昇（特に中性脂肪が高い場合にLDL-Cより実態を反映しやすい）</v>
       </c>
       <c r="G24" t="str">
-        <v>筋肉痛・脱力感・褐色尿（横紋筋融解症の症状）がないか確認する。スタチン系薬剤服用中は特に注意する。激しい運動の直後の採血でないかも確認する</v>
+        <v>動物性脂肪や揚げ物を控え、青魚や食物繊維（野菜・海藻・きのこ）を増やすよう伝える</v>
       </c>
       <c r="H24" t="str">
         <v/>
@@ -1394,95 +1394,95 @@
         <v/>
       </c>
       <c r="J24" t="str">
-        <v>スタチン系薬剤の重大な副作用である横紋筋融解症の指標。筋肉痛・脱力感・褐色尿の有無を必ず確認し、著明高値では服薬継続の可否を医師に相談する</v>
+        <v>中性脂肪（TG）が400 mg/dL以上などLDL-Cの計算式（Friedewald式）が不正確になる場合に、LDL-Cの代わりに用いられる。目標値はLDL-Cの目標値＋30 mg/dLが目安</v>
       </c>
       <c r="K24" t="str">
-        <v/>
+        <v>脂質異常症</v>
       </c>
       <c r="L24" t="str">
-        <v>CK,CPK,クレアチンキナーゼ,横紋筋融解症</v>
+        <v>nonHDL,non-HDLコレステロール,動脈硬化,中性脂肪,LDL計算式</v>
       </c>
       <c r="M24" t="str">
-        <v/>
+        <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>尿蛋白（随時尿）</v>
+        <v>HDLコレステロール</v>
       </c>
       <c r="B25" t="str">
-        <v>尿蛋白,U-pro</v>
+        <v>HDL-C</v>
       </c>
       <c r="C25" t="str">
-        <v>陰性（－）〜弱陽性</v>
+        <v>40 mg/dL以上</v>
       </c>
       <c r="D25" t="str">
-        <v>腎臓から本来漏れないはずのたんぱくが尿に出ていないかを見る検査</v>
+        <v>いわゆる「善玉コレステロール」。血管にたまった余分なコレステロールを回収する</v>
       </c>
       <c r="E25" t="str">
-        <v>この検査は、腎臓のろ過機能に負担がかかっていないかを見るものです。本来、たんぱく質は尿にほとんど出ませんが、腎臓に負担がかかると漏れ出るようになります。</v>
+        <v>HDLコレステロールは、いわゆる善玉コレステロールと呼ばれるものです。血管の壁にたまった余分なコレステロールを回収して肝臓に戻す働きがあり、数値が高いほど動脈硬化を防ぐ方向に働きます。</v>
       </c>
       <c r="F25" t="str">
-        <v>糖尿病性腎症、腎炎、高血圧性腎硬化症、発熱・運動後の一過性のもの</v>
+        <v/>
       </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v/>
+        <v>脂質異常症（低HDL血症）</v>
       </c>
       <c r="I25" t="str">
-        <v/>
+        <v>適度な運動習慣、禁煙を勧める</v>
       </c>
       <c r="J25" t="str">
-        <v>発熱・激しい運動・起立性蛋白尿など生理的な要因でも陽性になることがある。持続する場合に腎症の進行を疑う</v>
+        <v>喫煙、運動不足、肥満で低下しやすい。禁煙・運動習慣の改善で上昇が期待できる。低HDLは動脈硬化のリスク因子として単独でも重視される</v>
       </c>
       <c r="K25" t="str">
-        <v>糖尿病,腎機能</v>
+        <v>脂質異常症</v>
       </c>
       <c r="L25" t="str">
-        <v>尿蛋白,U-pro,腎症,たんぱく尿</v>
+        <v>HDL,HDLコレステロール,善玉コレステロール,脂質異常症</v>
       </c>
       <c r="M25" t="str">
-        <v/>
+        <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>尿クレアチニン（随時尿）</v>
+        <v>CK（クレアチンフォスフォキナーゼ）</v>
       </c>
       <c r="B26" t="str">
-        <v>尿CRE</v>
+        <v>CK,CPK</v>
       </c>
       <c r="C26" t="str">
-        <v>随時尿は主に他項目の濃度補正に利用（単独の基準値は設けにくい）</v>
+        <v>男性 60〜250 U/L、女性 50〜170 U/L</v>
       </c>
       <c r="D26" t="str">
-        <v>随時尿中のクレアチニン濃度。他の尿検査項目を薄まり具合で補正するための基準として使う</v>
+        <v>主に骨格筋・心筋に含まれる酵素。筋肉の損傷で血液中に漏れ出す</v>
       </c>
       <c r="E26" t="str">
-        <v>この数値は、尿がどれくらい薄まっているかを確認するための基準として使われます。他の尿検査の結果（蛋白やアルブミンなど）をこの値で割って補正することで、水分摂取量による影響を減らして正確に評価できます。</v>
+        <v>CKは筋肉の中にある酵素で、激しい運動や筋肉の病気、心筋梗塞などで筋肉の細胞がダメージを受けると血液中に漏れ出して数値が上がります。スタチン系のお薬の副作用（横紋筋融解症）のチェックにも使われます。</v>
       </c>
       <c r="F26" t="str">
-        <v/>
+        <v>心筋梗塞、横紋筋融解症（スタチン系薬剤の副作用など）、激しい運動、筋肉注射直後、甲状腺機能低下症</v>
       </c>
       <c r="G26" t="str">
-        <v/>
+        <v>筋肉痛・脱力感・褐色尿（横紋筋融解症の症状）がないか確認する。スタチン系薬剤服用中は特に注意する。激しい運動の直後の採血でないかも確認する</v>
       </c>
       <c r="H26" t="str">
-        <v>尿が薄い（水分摂取が多い、腎機能低下）状態</v>
+        <v/>
       </c>
       <c r="I26" t="str">
         <v/>
       </c>
       <c r="J26" t="str">
-        <v>尿中アルブミン/Cr比、尿蛋白/Cr比など、他項目の補正計算に使われる。単独の高低に臨床的意味は乏しい</v>
+        <v>スタチン系薬剤の重大な副作用である横紋筋融解症の指標。筋肉痛・脱力感・褐色尿の有無を必ず確認し、著明高値では服薬継続の可否を医師に相談する</v>
       </c>
       <c r="K26" t="str">
-        <v>腎機能</v>
+        <v/>
       </c>
       <c r="L26" t="str">
-        <v>尿CRE,尿クレアチニン,随時尿,補正,蛋白クレアチニン比</v>
+        <v>CK,CPK,クレアチンキナーゼ,横紋筋融解症</v>
       </c>
       <c r="M26" t="str">
         <v/>
@@ -1490,245 +1490,245 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>白血球（WBC）</v>
+        <v>TSH（甲状腺刺激ホルモン）</v>
       </c>
       <c r="B27" t="str">
-        <v>WBC</v>
+        <v>TSH</v>
       </c>
       <c r="C27" t="str">
-        <v>3,300〜8,600 /μL程度（施設差あり）</v>
+        <v>0.5〜5.0 μIU/mL程度（施設差あり）</v>
       </c>
       <c r="D27" t="str">
-        <v>体を細菌やウイルスから守る免疫細胞の数で、感染や炎症、薬剤の影響を反映する</v>
+        <v>甲状腺の働きが多いか少ないかを最も敏感に反映するホルモン</v>
       </c>
       <c r="E27" t="str">
-        <v>白血球は体に入ってきた細菌やウイルスと戦う免疫細胞です。感染症や炎症があると増え、逆に一部のお薬の副作用や骨髄の働きが落ちると減ることがあります。</v>
+        <v>TSHは脳の下垂体から出て、甲状腺に「もっと働いて」と指令を送るホルモンです。甲状腺の働きが弱っていると体が指令を強めるためTSHは上がり、逆に甲状腺が働きすぎているとTSHは下がります。甲状腺の状態を最初に確認する数値としてよく使われます。</v>
       </c>
       <c r="F27" t="str">
-        <v>感染症、炎症、ステロイド使用、喫煙、白血病などの血液疾患</v>
+        <v>甲状腺機能低下症（橋本病など）、チラーヂンSなど甲状腺ホルモン薬の量不足</v>
       </c>
       <c r="G27" t="str">
-        <v>発熱や体の痛みなど感染症状がないか確認する</v>
+        <v>だるさ、むくみ、体重増加、寒がりなどの症状がないか確認する。服薬状況（飲み忘れ、他の薬との飲み合わせ）を確認する</v>
       </c>
       <c r="H27" t="str">
-        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、メルカゾールなど薬剤性の無顆粒球症、再生不良性貧血、ウイルス感染</v>
+        <v>甲状腺機能亢進症（バセドウ病など）、チラーヂンSなど甲状腺ホルモン薬の過量</v>
       </c>
       <c r="I27" t="str">
-        <v>発熱、のどの痛みなど感染症状の初期サインがないか確認する。人混みを避け、手洗い・うがいを徹底するよう伝える</v>
+        <v>動悸、体重減少、暑がり、手のふるえなどの症状がないか確認する</v>
       </c>
       <c r="J27" t="str">
-        <v>メルカゾール（チアマゾール）は無顆粒球症の重大な副作用があり、発熱・のどの痛みが出たらすぐ受診するよう指導する。抗がん剤・免疫抑制剤・抗てんかん薬（カルバマゼピンなど）使用中も定期的なモニタリングが必要</v>
+        <v>チラーヂンS服用中はTSHが治療目標域に収まっているかで用量調整の目安にする。メルカゾール服用中はTSH・FT4に加えて無顆粒球症の初期症状（発熱・のどの痛み）の有無や白血球数も確認する</v>
       </c>
       <c r="K27" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>甲状腺疾患</v>
       </c>
       <c r="L27" t="str">
-        <v>白血球,WBC,好中球,感染症,白血病,無顆粒球症,骨髄抑制</v>
+        <v>TSH,甲状腺刺激ホルモン,甲状腺機能,橋本病,バセドウ病,チラーヂン,メルカゾール</v>
       </c>
       <c r="M27" t="str">
-        <v/>
+        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>赤血球</v>
+        <v>FT4（遊離サイロキシン）</v>
       </c>
       <c r="B28" t="str">
-        <v>RBC</v>
+        <v>FT4</v>
       </c>
       <c r="C28" t="str">
-        <v>男性 435〜555万/μL、女性 386〜492万/μL程度（施設差あり）</v>
+        <v>0.9〜1.7 ng/dL程度（施設差あり）</v>
       </c>
       <c r="D28" t="str">
-        <v>血液中で酸素を運ぶ細胞の数。ヘモグロビン・ヘマトクリットと合わせて貧血・多血症を評価する</v>
+        <v>甲状腺が実際に分泌しているホルモンの量そのものを表す数値</v>
       </c>
       <c r="E28" t="str">
-        <v>赤血球は、肺で受け取った酸素を全身に運ぶ血液の細胞です。数が少ないと貧血、多いと多血症が疑われます。ヘモグロビンやヘマトクリットと合わせて総合的に評価します。</v>
+        <v>FT4は甲状腺そのものが作っているホルモンの量です。TSHが「指令の強さ」だとすると、FT4は「実際に出ている量」にあたります。2つをあわせて見ることで、甲状腺の働きが今どういう状態かを詳しく判断できます。</v>
       </c>
       <c r="F28" t="str">
-        <v>脱水、多血症（真性多血症、二次性多血症）、喫煙</v>
+        <v>甲状腺機能亢進症（バセドウ病など）</v>
       </c>
       <c r="G28" t="str">
-        <v>脱水が疑われる場合はこまめな水分摂取を勧める（水分制限がある場合を除く）</v>
+        <v>動悸、体重減少、暑がり、手のふるえなどの症状がないか確認する</v>
       </c>
       <c r="H28" t="str">
-        <v>貧血（鉄欠乏性貧血、腎性貧血など）、出血</v>
+        <v>甲状腺機能低下症（橋本病など）</v>
       </c>
       <c r="I28" t="str">
-        <v>ヘモグロビンと同様に、出血や食事量低下がないか確認する</v>
+        <v>だるさ、むくみ、体重増加、寒がりなどの症状がないか確認する</v>
       </c>
       <c r="J28" t="str">
-        <v>ヘモグロビン・ヘマトクリットと同じ方向に動くことが多い。赤血球数だけでなくMCV・MCH・MCHCと合わせて貧血のタイプ(小球性・正球性・大球性)を判断する</v>
+        <v>TSHと逆方向に動くのが基本だが、下垂体性の異常など例外もある。TSHと合わせて評価し、片方だけで判断しない</v>
       </c>
       <c r="K28" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>甲状腺疾患</v>
       </c>
       <c r="L28" t="str">
-        <v>赤血球,RBC,貧血,多血症</v>
+        <v>FT4,遊離サイロキシン,甲状腺ホルモン,甲状腺機能</v>
       </c>
       <c r="M28" t="str">
-        <v>食事と栄養 p.151-164（第2部 貧血）</v>
+        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ヘモグロビン濃度</v>
+        <v>尿蛋白（随時尿）</v>
       </c>
       <c r="B29" t="str">
-        <v>Hb</v>
+        <v>尿蛋白,U-pro</v>
       </c>
       <c r="C29" t="str">
-        <v>男性 13.5〜17.5 g/dL、女性 11.5〜15.0 g/dL</v>
+        <v>陰性（－）〜弱陽性</v>
       </c>
       <c r="D29" t="str">
-        <v>血液の中で酸素を運ぶ役割をしている。この値が低い状態が貧血。</v>
+        <v>腎臓から本来漏れないはずのたんぱくが尿に出ていないかを見る検査</v>
       </c>
       <c r="E29" t="str">
-        <v>血の数値が良くなっても、体の中の鉄はまだ十分ではないことがあります。そのため、しばらく続けて飲むことが大切です。</v>
+        <v>この検査は、腎臓のろ過機能に負担がかかっていないかを見るものです。本来、たんぱく質は尿にほとんど出ませんが、腎臓に負担がかかると漏れ出るようになります。</v>
       </c>
       <c r="F29" t="str">
-        <v/>
+        <v>糖尿病性腎症、腎炎、高血圧性腎硬化症、発熱・運動後の一過性のもの</v>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>鉄欠乏性貧血、出血、腎性貧血、骨髄の造血機能低下</v>
+        <v/>
       </c>
       <c r="I29" t="str">
-        <v>鉄分の多い食品（レバー・赤身肉・魚・ほうれん草など）を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える</v>
+        <v/>
       </c>
       <c r="J29" t="str">
-        <v>原因（出血・食事量低下など）の確認が重要。腎機能低下がある場合は鉄不足以外が原因のこともある。鉄剤はヘモグロビンが正常化した後も2〜3か月程度は継続することが多い（鉄の貯蔵分を補うため。途中でやめると再び貧血になりやすい）</v>
+        <v>発熱・激しい運動・起立性蛋白尿など生理的な要因でも陽性になることがある。持続する場合に腎症の進行を疑う</v>
       </c>
       <c r="K29" t="str">
-        <v>鉄欠乏性貧血,抗血小板療法,抗凝固療法（心房細動・血栓症）</v>
+        <v>糖尿病,腎機能</v>
       </c>
       <c r="L29" t="str">
-        <v>ヘモグロビン,Hb,貧血,鉄剤,鉄欠乏性貧血</v>
+        <v>尿蛋白,U-pro,腎症,たんぱく尿</v>
       </c>
       <c r="M29" t="str">
-        <v>食事と栄養 p.151-164（第2部 貧血）</v>
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ヘマトクリット値</v>
+        <v>尿クレアチニン（随時尿）</v>
       </c>
       <c r="B30" t="str">
-        <v>Ht,Hct</v>
+        <v>尿CRE</v>
       </c>
       <c r="C30" t="str">
-        <v>男性 40〜50%、女性 35〜45%</v>
+        <v>随時尿は主に他項目の濃度補正に利用（単独の基準値は設けにくい）</v>
       </c>
       <c r="D30" t="str">
-        <v>血液全体のうち赤血球が占める体積の割合。貧血・脱水の指標</v>
+        <v>随時尿中のクレアチニン濃度。他の尿検査項目を薄まり具合で補正するための基準として使う</v>
       </c>
       <c r="E30" t="str">
-        <v>ヘマトクリットは、血液全体のうち赤血球が占める割合を表す数値です。この値が低いと貧血、高いと脱水や血液が濃くなっている状態が疑われます。</v>
+        <v>この数値は、尿がどれくらい薄まっているかを確認するための基準として使われます。他の尿検査の結果（蛋白やアルブミンなど）をこの値で割って補正することで、水分摂取量による影響を減らして正確に評価できます。</v>
       </c>
       <c r="F30" t="str">
-        <v>脱水、多血症（真性多血症、二次性多血症）、喫煙</v>
+        <v/>
       </c>
       <c r="G30" t="str">
-        <v>脱水が疑われる場合はこまめな水分摂取を勧める（水分制限がある場合を除く）</v>
+        <v/>
       </c>
       <c r="H30" t="str">
-        <v>貧血（鉄欠乏性貧血、腎性貧血など）、出血</v>
+        <v>尿が薄い（水分摂取が多い、腎機能低下）状態</v>
       </c>
       <c r="I30" t="str">
-        <v>ヘモグロビンと同様に、出血や食事量低下がないか確認する</v>
+        <v/>
       </c>
       <c r="J30" t="str">
-        <v>ヘモグロビン・赤血球数と合わせて評価する。3つの値は同じ方向に動くことが多く、脱水があると貧血が見かけ上隠れることがある</v>
+        <v>尿中アルブミン/Cr比、尿蛋白/Cr比など、他項目の補正計算に使われる。単独の高低に臨床的意味は乏しい</v>
       </c>
       <c r="K30" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>腎機能</v>
       </c>
       <c r="L30" t="str">
-        <v>ヘマトクリット,Ht,Hct,貧血,脱水,多血症</v>
+        <v>尿CRE,尿クレアチニン,随時尿,補正,蛋白クレアチニン比</v>
       </c>
       <c r="M30" t="str">
-        <v>食事と栄養 p.151-164（第2部 貧血）</v>
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>MCV</v>
+        <v>白血球（WBC）</v>
       </c>
       <c r="B31" t="str">
-        <v>MCV</v>
+        <v>WBC</v>
       </c>
       <c r="C31" t="str">
-        <v>79〜100 fL</v>
+        <v>3,300〜8,600 /μL程度（施設差あり）</v>
       </c>
       <c r="D31" t="str">
-        <v>赤血球1個の大きさ</v>
+        <v>体を細菌やウイルスから守る免疫細胞の数で、感染や炎症、薬剤の影響を反映する</v>
       </c>
       <c r="E31" t="str">
-        <v>MCVは赤血球1個あたりの大きさを表す数値です。貧血があるとき、この数値で「小さい貧血」か「大きい貧血」かを見分けることができ、原因を絞り込む手がかりになります。</v>
+        <v>白血球は体に入ってきた細菌やウイルスと戦う免疫細胞です。感染症や炎症があると増え、逆に一部のお薬の副作用や骨髄の働きが落ちると減ることがあります。</v>
       </c>
       <c r="F31" t="str">
-        <v/>
+        <v>感染症、炎症、ステロイド使用、喫煙、白血病などの血液疾患</v>
       </c>
       <c r="G31" t="str">
-        <v/>
+        <v>発熱や体の痛みなど感染症状がないか確認する</v>
       </c>
       <c r="H31" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、メルカゾールなど薬剤性の無顆粒球症、再生不良性貧血、ウイルス感染</v>
       </c>
       <c r="I31" t="str">
-        <v>鉄分の多い食事を意識する（ヘモグロビンの項目を参照）</v>
+        <v>発熱、のどの痛みなど感染症状の初期サインがないか確認する。人混みを避け、手洗い・うがいを徹底するよう伝える</v>
       </c>
       <c r="J31" t="str">
-        <v/>
+        <v>メルカゾール（チアマゾール）は無顆粒球症の重大な副作用があり、発熱・のどの痛みが出たらすぐ受診するよう指導する。抗がん剤・免疫抑制剤・抗てんかん薬（カルバマゼピンなど）使用中も定期的なモニタリングが必要</v>
       </c>
       <c r="K31" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L31" t="str">
-        <v>MCV,赤血球指数,貧血</v>
+        <v>白血球,WBC,好中球,感染症,白血病,無顆粒球症,骨髄抑制</v>
       </c>
       <c r="M31" t="str">
-        <v>食事と栄養 p.151-164（第2部 貧血）</v>
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>MCH</v>
+        <v>赤血球</v>
       </c>
       <c r="B32" t="str">
-        <v>MCH</v>
+        <v>RBC</v>
       </c>
       <c r="C32" t="str">
-        <v>26.3〜34.3 pg</v>
+        <v>男性 435〜555万/μL、女性 386〜492万/μL程度（施設差あり）</v>
       </c>
       <c r="D32" t="str">
-        <v>赤血球1個に含まれるヘモグロビン量</v>
+        <v>血液中で酸素を運ぶ細胞の数。ヘモグロビン・ヘマトクリットと合わせて貧血・多血症を評価する</v>
       </c>
       <c r="E32" t="str">
-        <v>MCHは赤血球1個の中に含まれるヘモグロビン（酸素を運ぶ色素）の量を表す数値です。MCVと同じく、貧血の種類を見分けるのに使われます。</v>
+        <v>赤血球は、肺で受け取った酸素を全身に運ぶ血液の細胞です。数が少ないと貧血、多いと多血症が疑われます。ヘモグロビンやヘマトクリットと合わせて総合的に評価します。</v>
       </c>
       <c r="F32" t="str">
-        <v/>
+        <v>脱水、多血症（真性多血症、二次性多血症）、喫煙</v>
       </c>
       <c r="G32" t="str">
-        <v/>
+        <v>脱水が疑われる場合はこまめな水分摂取を勧める（水分制限がある場合を除く）</v>
       </c>
       <c r="H32" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>貧血（鉄欠乏性貧血、腎性貧血など）、出血</v>
       </c>
       <c r="I32" t="str">
-        <v>鉄分の多い食事を意識する（ヘモグロビンの項目を参照）</v>
+        <v>ヘモグロビンと同様に、出血や食事量低下がないか確認する</v>
       </c>
       <c r="J32" t="str">
-        <v/>
+        <v>ヘモグロビン・ヘマトクリットと同じ方向に動くことが多い。赤血球数だけでなくMCV・MCH・MCHCと合わせて貧血のタイプ(小球性・正球性・大球性)を判断する</v>
       </c>
       <c r="K32" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
       <c r="L32" t="str">
-        <v>MCH,赤血球指数,貧血</v>
+        <v>赤血球,RBC,貧血,多血症</v>
       </c>
       <c r="M32" t="str">
         <v>食事と栄養 p.151-164（第2部 貧血）</v>
@@ -1736,19 +1736,19 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>MCHC</v>
+        <v>ヘモグロビン濃度</v>
       </c>
       <c r="B33" t="str">
-        <v>MCHC</v>
+        <v>Hb</v>
       </c>
       <c r="C33" t="str">
-        <v>31.6〜36.6 %</v>
+        <v>男性 13.5〜17.5 g/dL、女性 11.5〜15.0 g/dL</v>
       </c>
       <c r="D33" t="str">
-        <v>単位容積あたりの赤血球に含まれるヘモグロビン濃度</v>
+        <v>血液の中で酸素を運ぶ役割をしている。この値が低い状態が貧血。</v>
       </c>
       <c r="E33" t="str">
-        <v>MCHCは、赤血球の中にヘモグロビンがどれくらい濃く詰まっているかを表す数値です。鉄が不足すると、この濃度も薄くなる傾向があります。</v>
+        <v>血の数値が良くなっても、体の中の鉄はまだ十分ではないことがあります。そのため、しばらく続けて飲むことが大切です。</v>
       </c>
       <c r="F33" t="str">
         <v/>
@@ -1757,19 +1757,19 @@
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>鉄欠乏性貧血、出血、腎性貧血、骨髄の造血機能低下</v>
       </c>
       <c r="I33" t="str">
-        <v>鉄分の多い食事を意識する（ヘモグロビンの項目を参照）</v>
+        <v>鉄分の多い食品（レバー・赤身肉・魚・ほうれん草など）を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える</v>
       </c>
       <c r="J33" t="str">
-        <v/>
+        <v>原因（出血・食事量低下など）の確認が重要。腎機能低下がある場合は鉄不足以外が原因のこともある。鉄剤はヘモグロビンが正常化した後も2〜3か月程度は継続することが多い（鉄の貯蔵分を補うため。途中でやめると再び貧血になりやすい）</v>
       </c>
       <c r="K33" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>鉄欠乏性貧血,抗血小板療法,抗凝固療法（心房細動・血栓症）</v>
       </c>
       <c r="L33" t="str">
-        <v>MCHC,赤血球指数,貧血</v>
+        <v>ヘモグロビン,Hb,貧血,鉄剤,鉄欠乏性貧血</v>
       </c>
       <c r="M33" t="str">
         <v>食事と栄養 p.151-164（第2部 貧血）</v>
@@ -1777,81 +1777,81 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>血小板数</v>
+        <v>ヘマトクリット値</v>
       </c>
       <c r="B34" t="str">
-        <v>Plt</v>
+        <v>Ht,Hct</v>
       </c>
       <c r="C34" t="str">
-        <v>15.0〜35.0万/μL程度（施設差あり）</v>
+        <v>男性 40〜50%、女性 35〜45%</v>
       </c>
       <c r="D34" t="str">
-        <v>出血を止める働きをする血液成分で、少なすぎると出血しやすくなる</v>
+        <v>血液全体のうち赤血球が占める体積の割合。貧血・脱水の指標</v>
       </c>
       <c r="E34" t="str">
-        <v>血小板は、血管が傷ついたときに集まって血を止める役割をする血液の成分です。数が少ないとあざができやすくなったり、出血が止まりにくくなったりします。抗血小板薬や抗がん剤を使っている方では、定期的にチェックすることが大切です。</v>
+        <v>ヘマトクリットは、血液全体のうち赤血球が占める割合を表す数値です。この値が低いと貧血、高いと脱水や血液が濃くなっている状態が疑われます。</v>
       </c>
       <c r="F34" t="str">
-        <v>炎症性疾患、鉄欠乏性貧血、脾摘後、骨髄増殖性疾患</v>
+        <v>脱水、多血症（真性多血症、二次性多血症）、喫煙</v>
       </c>
       <c r="G34" t="str">
-        <v/>
+        <v>脱水が疑われる場合はこまめな水分摂取を勧める（水分制限がある場合を除く）</v>
       </c>
       <c r="H34" t="str">
-        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、肝硬変・脾機能亢進、再生不良性貧血、抗てんかん薬（バルプロ酸など）の副作用、ITP（特発性血小板減少性紫斑病）</v>
+        <v>貧血（鉄欠乏性貧血、腎性貧血など）、出血</v>
       </c>
       <c r="I34" t="str">
-        <v>あざができやすい、歯ぐきや鼻からの出血が増えていないか確認する。強い運動や転倒によるけがに注意するよう伝える</v>
+        <v>ヘモグロビンと同様に、出血や食事量低下がないか確認する</v>
       </c>
       <c r="J34" t="str">
-        <v>抗血小板薬・抗凝固薬使用中に血小板減少があると出血リスクがさらに高まる。抗がん剤・バルプロ酸・カルバマゼピンなど骨髄抑制のリスクがある薬剤使用中は定期採血の実施状況を確認する</v>
+        <v>ヘモグロビン・赤血球数と合わせて評価する。3つの値は同じ方向に動くことが多く、脱水があると貧血が見かけ上隠れることがある</v>
       </c>
       <c r="K34" t="str">
-        <v>てんかん,抗血小板療法</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="L34" t="str">
-        <v>血小板,Plt,platelet,出血,あざ,紫斑,骨髄抑制</v>
+        <v>ヘマトクリット,Ht,Hct,貧血,脱水,多血症</v>
       </c>
       <c r="M34" t="str">
-        <v/>
+        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>RDW-SD</v>
+        <v>MCV</v>
       </c>
       <c r="B35" t="str">
-        <v>RDW-SD</v>
+        <v>MCV</v>
       </c>
       <c r="C35" t="str">
-        <v>39〜46 fL程度（施設差あり）</v>
+        <v>79〜100 fL</v>
       </c>
       <c r="D35" t="str">
-        <v>赤血球の大きさのばらつきを表す指標(絶対値)。鉄欠乏性貧血などの初期変化を捉えやすい</v>
+        <v>赤血球1個の大きさ</v>
       </c>
       <c r="E35" t="str">
-        <v>RDW-SDは、赤血球の大きさがどれくらいバラバラになっているかを表す数値です。貧血の原因を調べる際、鉄が足りなくなり始めた早い段階での変化を捉えるのに役立ちます。</v>
+        <v>MCVは赤血球1個あたりの大きさを表す数値です。貧血があるとき、この数値で「小さい貧血」か「大きい貧血」かを見分けることができ、原因を絞り込む手がかりになります。</v>
       </c>
       <c r="F35" t="str">
-        <v>鉄欠乏性貧血の初期、混合性貧血（複数の原因が重なっている状態）、赤血球産生の乱れ</v>
+        <v/>
       </c>
       <c r="G35" t="str">
         <v/>
       </c>
       <c r="H35" t="str">
-        <v/>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="I35" t="str">
-        <v/>
+        <v>鉄分の多い食事を意識する（ヘモグロビンの項目を参照）</v>
       </c>
       <c r="J35" t="str">
-        <v>MCVが正常範囲でもRDWが上昇している場合、鉄欠乏の初期段階を示唆することがある。MCV・MCHと合わせて評価する</v>
+        <v/>
       </c>
       <c r="K35" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
       <c r="L35" t="str">
-        <v>RDW-SD,赤血球分布幅,貧血,鉄欠乏</v>
+        <v>MCV,赤血球指数,貧血</v>
       </c>
       <c r="M35" t="str">
         <v>食事と栄養 p.151-164（第2部 貧血）</v>
@@ -1859,40 +1859,40 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>RDW-CV</v>
+        <v>MCH</v>
       </c>
       <c r="B36" t="str">
-        <v>RDW-CV</v>
+        <v>MCH</v>
       </c>
       <c r="C36" t="str">
-        <v>11.5〜14.5%程度（施設差あり）</v>
+        <v>26.3〜34.3 pg</v>
       </c>
       <c r="D36" t="str">
-        <v>赤血球の大きさのばらつきを割合(%)で表した指標</v>
+        <v>赤血球1個に含まれるヘモグロビン量</v>
       </c>
       <c r="E36" t="str">
-        <v>RDW-CVもRDW-SDと同じく、赤血球の大きさのばらつきを表す数値ですが、こちらは割合(%)で示されます。貧血のタイプを見分ける手がかりになります。</v>
+        <v>MCHは赤血球1個の中に含まれるヘモグロビン（酸素を運ぶ色素）の量を表す数値です。MCVと同じく、貧血の種類を見分けるのに使われます。</v>
       </c>
       <c r="F36" t="str">
-        <v>鉄欠乏性貧血、ビタミンB12・葉酸欠乏性貧血、混合性貧血</v>
+        <v/>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v/>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="I36" t="str">
-        <v/>
+        <v>鉄分の多い食事を意識する（ヘモグロビンの項目を参照）</v>
       </c>
       <c r="J36" t="str">
-        <v>RDW-SDと同様の意味を持つ指標。MCVが小さくRDWが高ければ鉄欠乏性貧血、MCVが大きくRDWが高ければビタミンB12・葉酸欠乏を疑う手がかりになる</v>
+        <v/>
       </c>
       <c r="K36" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
       <c r="L36" t="str">
-        <v>RDW-CV,赤血球分布幅,貧血,ビタミンB12,葉酸</v>
+        <v>MCH,赤血球指数,貧血</v>
       </c>
       <c r="M36" t="str">
         <v>食事と栄養 p.151-164（第2部 貧血）</v>
@@ -1900,81 +1900,81 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>好中球実数値</v>
+        <v>MCHC</v>
       </c>
       <c r="B37" t="str">
-        <v>Neutro#,ANC</v>
+        <v>MCHC</v>
       </c>
       <c r="C37" t="str">
-        <v>2,000〜7,500 /μL程度（施設差あり、白血球数×好中球%で算出）</v>
+        <v>31.6〜36.6 %</v>
       </c>
       <c r="D37" t="str">
-        <v>好中球の絶対数。感染症リスクを判断する上で割合(%)より重要な指標</v>
+        <v>単位容積あたりの赤血球に含まれるヘモグロビン濃度</v>
       </c>
       <c r="E37" t="str">
-        <v>これは好中球の実際の数を表す数値です。割合(%)だけでなく、実際の数がどれくらいあるかを見ることで、感染症にかかりやすい状態かどうかをより正確に判断できます。</v>
+        <v>MCHCは、赤血球の中にヘモグロビンがどれくらい濃く詰まっているかを表す数値です。鉄が不足すると、この濃度も薄くなる傾向があります。</v>
       </c>
       <c r="F37" t="str">
-        <v>細菌感染症、炎症、ステロイド使用</v>
+        <v/>
       </c>
       <c r="G37" t="str">
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、メルカゾールなど薬剤性の無顆粒球症（1,000/μL未満で好中球減少症、500/μL未満で重症感染リスクが著しく上昇）</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="I37" t="str">
-        <v>発熱、のどの痛みなど感染症状の初期サインがないか確認する。人混みを避け、手洗い・うがいを徹底するよう伝える</v>
+        <v>鉄分の多い食事を意識する（ヘモグロビンの項目を参照）</v>
       </c>
       <c r="J37" t="str">
-        <v>抗がん剤・メルカゾール・カルバマゼピンなど骨髄抑制のリスクがある薬剤使用中は特に重視すべき数値。500/μL未満は発熱性好中球減少症のリスクが高く緊急性が高い</v>
+        <v/>
       </c>
       <c r="K37" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="L37" t="str">
-        <v>好中球実数値,好中球数,ANC,無顆粒球症,発熱性好中球減少症</v>
+        <v>MCHC,赤血球指数,貧血</v>
       </c>
       <c r="M37" t="str">
-        <v/>
+        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>好酸球実数値</v>
+        <v>血小板数</v>
       </c>
       <c r="B38" t="str">
-        <v>Eosino#</v>
+        <v>Plt</v>
       </c>
       <c r="C38" t="str">
-        <v>100〜500 /μL程度（施設差あり）</v>
+        <v>15.0〜35.0万/μL程度（施設差あり）</v>
       </c>
       <c r="D38" t="str">
-        <v>好酸球の絶対数。アレルギーや薬剤反応の程度をより正確に評価できる</v>
+        <v>出血を止める働きをする血液成分で、少なすぎると出血しやすくなる</v>
       </c>
       <c r="E38" t="str">
-        <v>これは好酸球の実際の数を表す数値です。割合(%)だけでなく実数を見ることで、アレルギー反応の強さをより正確に把握できます。</v>
+        <v>血小板は、血管が傷ついたときに集まって血を止める役割をする血液の成分です。数が少ないとあざができやすくなったり、出血が止まりにくくなったりします。抗血小板薬や抗がん剤を使っている方では、定期的にチェックすることが大切です。</v>
       </c>
       <c r="F38" t="str">
-        <v>アレルギー性疾患、薬剤アレルギー、寄生虫感染</v>
+        <v>炎症性疾患、鉄欠乏性貧血、脾摘後、骨髄増殖性疾患</v>
       </c>
       <c r="G38" t="str">
-        <v>新しく始めた薬がないか確認する</v>
+        <v/>
       </c>
       <c r="H38" t="str">
-        <v/>
+        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、肝硬変・脾機能亢進、再生不良性貧血、抗てんかん薬（バルプロ酸など）の副作用、ITP（特発性血小板減少性紫斑病）</v>
       </c>
       <c r="I38" t="str">
-        <v/>
+        <v>あざができやすい、歯ぐきや鼻からの出血が増えていないか確認する。強い運動や転倒によるけがに注意するよう伝える</v>
       </c>
       <c r="J38" t="str">
-        <v>薬剤性過敏症症候群(DIHS)などでは著明な好酸球増多を認めることがあり、原因薬剤の特定に役立つ</v>
+        <v>抗血小板薬・抗凝固薬使用中に血小板減少があると出血リスクがさらに高まる。抗がん剤・バルプロ酸・カルバマゼピンなど骨髄抑制のリスクがある薬剤使用中は定期採血の実施状況を確認する</v>
       </c>
       <c r="K38" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>てんかん,抗血小板療法</v>
       </c>
       <c r="L38" t="str">
-        <v>好酸球実数値,好酸球数,アレルギー,DIHS</v>
+        <v>血小板,Plt,platelet,出血,あざ,紫斑,骨髄抑制</v>
       </c>
       <c r="M38" t="str">
         <v/>
@@ -1982,22 +1982,22 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>好塩基球実数値</v>
+        <v>RDW-SD</v>
       </c>
       <c r="B39" t="str">
-        <v>Baso#</v>
+        <v>RDW-SD</v>
       </c>
       <c r="C39" t="str">
-        <v>0〜100 /μL程度（施設差あり）</v>
+        <v>39〜46 fL程度（施設差あり）</v>
       </c>
       <c r="D39" t="str">
-        <v>好塩基球の絶対数</v>
+        <v>赤血球の大きさのばらつきを表す指標(絶対値)。鉄欠乏性貧血などの初期変化を捉えやすい</v>
       </c>
       <c r="E39" t="str">
-        <v>これは好塩基球の実際の数を表す数値です。数がとても少ない種類の血球なので、通常は大きな変動を示すことは多くありません。</v>
+        <v>RDW-SDは、赤血球の大きさがどれくらいバラバラになっているかを表す数値です。貧血の原因を調べる際、鉄が足りなくなり始めた早い段階での変化を捉えるのに役立ちます。</v>
       </c>
       <c r="F39" t="str">
-        <v>慢性骨髄性白血病などの血液疾患、アレルギー性疾患</v>
+        <v>鉄欠乏性貧血の初期、混合性貧血（複数の原因が重なっている状態）、赤血球産生の乱れ</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -2009,95 +2009,95 @@
         <v/>
       </c>
       <c r="J39" t="str">
-        <v>単独での臨床的意義は乏しく、他の血球指標（白血球分画全体）と合わせて評価する</v>
+        <v>MCVが正常範囲でもRDWが上昇している場合、鉄欠乏の初期段階を示唆することがある。MCV・MCHと合わせて評価する</v>
       </c>
       <c r="K39" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="L39" t="str">
-        <v>好塩基球実数値,好塩基球数</v>
+        <v>RDW-SD,赤血球分布幅,貧血,鉄欠乏</v>
       </c>
       <c r="M39" t="str">
-        <v/>
+        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>リンパ球実数値</v>
+        <v>RDW-CV</v>
       </c>
       <c r="B40" t="str">
-        <v>Lympho#,ALC</v>
+        <v>RDW-CV</v>
       </c>
       <c r="C40" t="str">
-        <v>1,000〜3,600 /μL程度（施設差あり）</v>
+        <v>11.5〜14.5%程度（施設差あり）</v>
       </c>
       <c r="D40" t="str">
-        <v>リンパ球の絶対数。免疫力の目安として使われる</v>
+        <v>赤血球の大きさのばらつきを割合(%)で表した指標</v>
       </c>
       <c r="E40" t="str">
-        <v>これはリンパ球の実際の数を表す数値です。免疫力の目安の一つとして使われ、抗がん剤や免疫抑制剤の副作用モニタリングにも用いられます。</v>
+        <v>RDW-CVもRDW-SDと同じく、赤血球の大きさのばらつきを表す数値ですが、こちらは割合(%)で示されます。貧血のタイプを見分ける手がかりになります。</v>
       </c>
       <c r="F40" t="str">
-        <v>ウイルス感染症、リンパ性白血病などの血液疾患</v>
+        <v>鉄欠乏性貧血、ビタミンB12・葉酸欠乏性貧血、混合性貧血</v>
       </c>
       <c r="G40" t="str">
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>抗がん剤・免疫抑制剤・ステロイドの使用、強いストレス、AIDSなどの免疫不全</v>
+        <v/>
       </c>
       <c r="I40" t="str">
-        <v>感染予防（手洗い・うがい、人混みを避ける）を意識するよう伝える</v>
+        <v/>
       </c>
       <c r="J40" t="str">
-        <v>免疫抑制剤・抗がん剤治療中のモニタリング指標としても使われる。著明な低下時は日和見感染のリスクが高まる</v>
+        <v>RDW-SDと同様の意味を持つ指標。MCVが小さくRDWが高ければ鉄欠乏性貧血、MCVが大きくRDWが高ければビタミンB12・葉酸欠乏を疑う手がかりになる</v>
       </c>
       <c r="K40" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="L40" t="str">
-        <v>リンパ球実数値,リンパ球数,ALC,免疫抑制剤,日和見感染</v>
+        <v>RDW-CV,赤血球分布幅,貧血,ビタミンB12,葉酸</v>
       </c>
       <c r="M40" t="str">
-        <v/>
+        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>単球実数値</v>
+        <v>好中球実数値</v>
       </c>
       <c r="B41" t="str">
-        <v>Mono#</v>
+        <v>Neutro#,ANC</v>
       </c>
       <c r="C41" t="str">
-        <v>200〜600 /μL程度（施設差あり）</v>
+        <v>2,000〜7,500 /μL程度（施設差あり、白血球数×好中球%で算出）</v>
       </c>
       <c r="D41" t="str">
-        <v>単球の絶対数</v>
+        <v>好中球の絶対数。感染症リスクを判断する上で割合(%)より重要な指標</v>
       </c>
       <c r="E41" t="str">
-        <v>これは単球の実際の数を表す数値です。慢性的な炎症や感染症の状態を把握する材料の一つになります。</v>
+        <v>これは好中球の実際の数を表す数値です。割合(%)だけでなく、実際の数がどれくらいあるかを見ることで、感染症にかかりやすい状態かどうかをより正確に判断できます。</v>
       </c>
       <c r="F41" t="str">
-        <v>慢性感染症、炎症性疾患、血液疾患</v>
+        <v>細菌感染症、炎症、ステロイド使用</v>
       </c>
       <c r="G41" t="str">
         <v/>
       </c>
       <c r="H41" t="str">
-        <v/>
+        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、メルカゾールなど薬剤性の無顆粒球症（1,000/μL未満で好中球減少症、500/μL未満で重症感染リスクが著しく上昇）</v>
       </c>
       <c r="I41" t="str">
-        <v/>
+        <v>発熱、のどの痛みなど感染症状の初期サインがないか確認する。人混みを避け、手洗い・うがいを徹底するよう伝える</v>
       </c>
       <c r="J41" t="str">
-        <v>単独での臨床的意義は乏しく、他の血球指標と合わせて評価する</v>
+        <v>抗がん剤・メルカゾール・カルバマゼピンなど骨髄抑制のリスクがある薬剤使用中は特に重視すべき数値。500/μL未満は発熱性好中球減少症のリスクが高く緊急性が高い</v>
       </c>
       <c r="K41" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L41" t="str">
-        <v>単球実数値,単球数</v>
+        <v>好中球実数値,好中球数,ANC,無顆粒球症,発熱性好中球減少症</v>
       </c>
       <c r="M41" t="str">
         <v/>
@@ -2105,40 +2105,40 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>好中球</v>
+        <v>好酸球実数値</v>
       </c>
       <c r="B42" t="str">
-        <v>Neutro,Neut%</v>
+        <v>Eosino#</v>
       </c>
       <c r="C42" t="str">
-        <v>40〜75%程度（施設差あり）</v>
+        <v>100〜500 /μL程度（施設差あり）</v>
       </c>
       <c r="D42" t="str">
-        <v>白血球の中で最も多くを占め、細菌感染と戦う主力の免疫細胞の割合</v>
+        <v>好酸球の絶対数。アレルギーや薬剤反応の程度をより正確に評価できる</v>
       </c>
       <c r="E42" t="str">
-        <v>好中球は、白血球の中で最も数が多く、細菌が体に入ってきたときに真っ先に戦ってくれる免疫細胞です。感染症や炎症があると増え、逆に薬の副作用などで減ることがあります。</v>
+        <v>これは好酸球の実際の数を表す数値です。割合(%)だけでなく実数を見ることで、アレルギー反応の強さをより正確に把握できます。</v>
       </c>
       <c r="F42" t="str">
-        <v>細菌感染症、炎症、ストレス、ステロイド使用</v>
+        <v>アレルギー性疾患、薬剤アレルギー、寄生虫感染</v>
       </c>
       <c r="G42" t="str">
-        <v>発熱や炎症症状がないか確認する</v>
+        <v>新しく始めた薬がないか確認する</v>
       </c>
       <c r="H42" t="str">
-        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、ウイルス感染、メルカゾールなど薬剤性の無顆粒球症</v>
+        <v/>
       </c>
       <c r="I42" t="str">
-        <v>発熱やのどの痛みなど感染症状の初期サインがないか確認する</v>
+        <v/>
       </c>
       <c r="J42" t="str">
-        <v>好中球の絶対数（好中球実数値）が500/μL未満になると重篤な感染症のリスクが高まる。割合(%)だけでなく実数値も合わせて確認する</v>
+        <v>薬剤性過敏症症候群(DIHS)などでは著明な好酸球増多を認めることがあり、原因薬剤の特定に役立つ</v>
       </c>
       <c r="K42" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L42" t="str">
-        <v>好中球,Neutro,Neut,感染症,無顆粒球症</v>
+        <v>好酸球実数値,好酸球数,アレルギー,DIHS</v>
       </c>
       <c r="M42" t="str">
         <v/>
@@ -2146,25 +2146,25 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>好酸球</v>
+        <v>好塩基球実数値</v>
       </c>
       <c r="B43" t="str">
-        <v>Eosino,Eos%</v>
+        <v>Baso#</v>
       </c>
       <c r="C43" t="str">
-        <v>1〜5%程度（施設差あり）</v>
+        <v>0〜100 /μL程度（施設差あり）</v>
       </c>
       <c r="D43" t="str">
-        <v>アレルギー反応や寄生虫感染に関わる白血球の一種の割合</v>
+        <v>好塩基球の絶対数</v>
       </c>
       <c r="E43" t="str">
-        <v>好酸球は、アレルギー反応や寄生虫感染と関係が深い免疫細胞です。アレルギー性の病気や薬の副作用（薬疹など）で増えることがあります。</v>
+        <v>これは好塩基球の実際の数を表す数値です。数がとても少ない種類の血球なので、通常は大きな変動を示すことは多くありません。</v>
       </c>
       <c r="F43" t="str">
-        <v>アレルギー性疾患（気管支喘息、アトピー性皮膚炎など）、薬剤アレルギー、寄生虫感染</v>
+        <v>慢性骨髄性白血病などの血液疾患、アレルギー性疾患</v>
       </c>
       <c r="G43" t="str">
-        <v>新しく始めた薬がないか確認する。皮疹やかゆみなどアレルギー症状の有無を確認する</v>
+        <v/>
       </c>
       <c r="H43" t="str">
         <v/>
@@ -2173,13 +2173,13 @@
         <v/>
       </c>
       <c r="J43" t="str">
-        <v>薬剤性の好酸球増多は、原因薬剤の中止で改善することが多い。新規薬剤開始後の皮疹・発熱と合わせて薬剤性過敏症症候群(DIHS)を疑う材料になる</v>
+        <v>単独での臨床的意義は乏しく、他の血球指標（白血球分画全体）と合わせて評価する</v>
       </c>
       <c r="K43" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L43" t="str">
-        <v>好酸球,Eosino,Eos,アレルギー,薬疹,DIHS</v>
+        <v>好塩基球実数値,好塩基球数</v>
       </c>
       <c r="M43" t="str">
         <v/>
@@ -2187,40 +2187,40 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>好塩基球</v>
+        <v>リンパ球実数値</v>
       </c>
       <c r="B44" t="str">
-        <v>Baso,Baso%</v>
+        <v>Lympho#,ALC</v>
       </c>
       <c r="C44" t="str">
-        <v>0〜2%程度（施設差あり）</v>
+        <v>1,000〜3,600 /μL程度（施設差あり）</v>
       </c>
       <c r="D44" t="str">
-        <v>白血球の中で最も数が少なく、アレルギー反応に関わる細胞の割合</v>
+        <v>リンパ球の絶対数。免疫力の目安として使われる</v>
       </c>
       <c r="E44" t="str">
-        <v>好塩基球は白血球の中で最も数が少ない種類で、アレルギー反応や炎症に関わっています。数値の変動が病気の診断に直接使われることは少ない検査です。</v>
+        <v>これはリンパ球の実際の数を表す数値です。免疫力の目安の一つとして使われ、抗がん剤や免疫抑制剤の副作用モニタリングにも用いられます。</v>
       </c>
       <c r="F44" t="str">
-        <v>慢性骨髄性白血病などの血液疾患、アレルギー性疾患、甲状腺機能低下症</v>
+        <v>ウイルス感染症、リンパ性白血病などの血液疾患</v>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v/>
+        <v>抗がん剤・免疫抑制剤・ステロイドの使用、強いストレス、AIDSなどの免疫不全</v>
       </c>
       <c r="I44" t="str">
-        <v/>
+        <v>感染予防（手洗い・うがい、人混みを避ける）を意識するよう伝える</v>
       </c>
       <c r="J44" t="str">
-        <v>単独での臨床的意義は乏しいが、著明な増加は血液疾患（慢性骨髄性白血病等）の可能性があり他の血球指標と合わせて評価する</v>
+        <v>免疫抑制剤・抗がん剤治療中のモニタリング指標としても使われる。著明な低下時は日和見感染のリスクが高まる</v>
       </c>
       <c r="K44" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L44" t="str">
-        <v>好塩基球,Baso,アレルギー,白血病</v>
+        <v>リンパ球実数値,リンパ球数,ALC,免疫抑制剤,日和見感染</v>
       </c>
       <c r="M44" t="str">
         <v/>
@@ -2228,40 +2228,40 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>リンパ球</v>
+        <v>単球実数値</v>
       </c>
       <c r="B45" t="str">
-        <v>Lympho,Lym%</v>
+        <v>Mono#</v>
       </c>
       <c r="C45" t="str">
-        <v>18〜49%程度（施設差あり）</v>
+        <v>200〜600 /μL程度（施設差あり）</v>
       </c>
       <c r="D45" t="str">
-        <v>ウイルス感染と戦い、免疫の記憶を担う白血球の割合</v>
+        <v>単球の絶対数</v>
       </c>
       <c r="E45" t="str">
-        <v>リンパ球は、ウイルスと戦ったり、一度かかった病気を記憶して免疫をつくったりする細胞です。ウイルス感染で増え、抗がん剤の副作用や強いストレスで減ることがあります。</v>
+        <v>これは単球の実際の数を表す数値です。慢性的な炎症や感染症の状態を把握する材料の一つになります。</v>
       </c>
       <c r="F45" t="str">
-        <v>ウイルス感染症、リンパ性白血病などの血液疾患、百日咳</v>
+        <v>慢性感染症、炎症性疾患、血液疾患</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>抗がん剤・免疫抑制剤・ステロイドの使用、強いストレス、AIDSなどの免疫不全</v>
+        <v/>
       </c>
       <c r="I45" t="str">
-        <v>免疫が下がっている可能性があるため、感染予防（手洗い・うがい、人混みを避ける）を意識するよう伝える</v>
+        <v/>
       </c>
       <c r="J45" t="str">
-        <v>ステロイド・免疫抑制剤使用中はリンパ球減少による易感染性に注意。好中球と逆方向に動くことが多い（ウイルス感染ではリンパ球優位、細菌感染では好中球優位になりやすい）</v>
+        <v>単独での臨床的意義は乏しく、他の血球指標と合わせて評価する</v>
       </c>
       <c r="K45" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L45" t="str">
-        <v>リンパ球,Lympho,Lym,ウイルス感染,免疫抑制剤,ステロイド</v>
+        <v>単球実数値,単球数</v>
       </c>
       <c r="M45" t="str">
         <v/>
@@ -2269,40 +2269,40 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>単球</v>
+        <v>好中球</v>
       </c>
       <c r="B46" t="str">
-        <v>Mono,Mono%</v>
+        <v>Neutro,Neut%</v>
       </c>
       <c r="C46" t="str">
-        <v>2〜10%程度（施設差あり）</v>
+        <v>40〜75%程度（施設差あり）</v>
       </c>
       <c r="D46" t="str">
-        <v>感染や炎症の後始末をする白血球の一種の割合</v>
+        <v>白血球の中で最も多くを占め、細菌感染と戦う主力の免疫細胞の割合</v>
       </c>
       <c r="E46" t="str">
-        <v>単球は、細菌などを取り込んで処理したり、組織の修復に関わったりする免疫細胞です。慢性的な炎症や感染症の回復期に増えることがあります。</v>
+        <v>好中球は、白血球の中で最も数が多く、細菌が体に入ってきたときに真っ先に戦ってくれる免疫細胞です。感染症や炎症があると増え、逆に薬の副作用などで減ることがあります。</v>
       </c>
       <c r="F46" t="str">
-        <v>慢性感染症（結核など）、炎症性疾患、血液疾患、感染症の回復期</v>
+        <v>細菌感染症、炎症、ストレス、ステロイド使用</v>
       </c>
       <c r="G46" t="str">
-        <v/>
+        <v>発熱や炎症症状がないか確認する</v>
       </c>
       <c r="H46" t="str">
-        <v/>
+        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、ウイルス感染、メルカゾールなど薬剤性の無顆粒球症</v>
       </c>
       <c r="I46" t="str">
-        <v/>
+        <v>発熱やのどの痛みなど感染症状の初期サインがないか確認する</v>
       </c>
       <c r="J46" t="str">
-        <v>単独での臨床的意義は乏しく、他の血球指標や炎症マーカー(CRPなど)と合わせて評価する</v>
+        <v>好中球の絶対数（好中球実数値）が500/μL未満になると重篤な感染症のリスクが高まる。割合(%)だけでなく実数値も合わせて確認する</v>
       </c>
       <c r="K46" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L46" t="str">
-        <v>単球,Mono,慢性感染症,結核,炎症</v>
+        <v>好中球,Neutro,Neut,感染症,無顆粒球症</v>
       </c>
       <c r="M46" t="str">
         <v/>
@@ -2310,40 +2310,40 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>尿pH</v>
+        <v>好酸球</v>
       </c>
       <c r="B47" t="str">
-        <v>尿pH</v>
+        <v>Eosino,Eos%</v>
       </c>
       <c r="C47" t="str">
-        <v>4.5〜7.5程度（弱酸性が多い）</v>
+        <v>1〜5%程度（施設差あり）</v>
       </c>
       <c r="D47" t="str">
-        <v>尿の酸性・アルカリ性の度合い。食事や感染症、体の状態を反映する</v>
+        <v>アレルギー反応や寄生虫感染に関わる白血球の一種の割合</v>
       </c>
       <c r="E47" t="str">
-        <v>尿のpHは酸性・アルカリ性のバランスを表します。食事の内容や感染症、体の代謝状態によって変化します。単独で大きな問題を示すことは少ない検査です。</v>
+        <v>好酸球は、アレルギー反応や寄生虫感染と関係が深い免疫細胞です。アレルギー性の病気や薬の副作用（薬疹など）で増えることがあります。</v>
       </c>
       <c r="F47" t="str">
-        <v>尿路感染症（尿素分解菌によるもの）、野菜中心の食事、過換気</v>
+        <v>アレルギー性疾患（気管支喘息、アトピー性皮膚炎など）、薬剤アレルギー、寄生虫感染</v>
       </c>
       <c r="G47" t="str">
-        <v/>
+        <v>新しく始めた薬がないか確認する。皮疹やかゆみなどアレルギー症状の有無を確認する</v>
       </c>
       <c r="H47" t="str">
-        <v>高たんぱく食、糖尿病性ケトアシドーシス、痛風発作時（酸性尿は尿酸結石のリスクを高める）</v>
+        <v/>
       </c>
       <c r="I47" t="str">
-        <v>痛風・尿酸結石がある場合は、野菜など尿をアルカリ化する食品を意識するとよいことを伝える</v>
+        <v/>
       </c>
       <c r="J47" t="str">
-        <v>高尿酸血症・尿酸結石の患者では尿pHが酸性に傾いていないか確認する。尿アルカリ化薬（ウラリットなど）の効果判定にも使う</v>
+        <v>薬剤性の好酸球増多は、原因薬剤の中止で改善することが多い。新規薬剤開始後の皮疹・発熱と合わせて薬剤性過敏症症候群(DIHS)を疑う材料になる</v>
       </c>
       <c r="K47" t="str">
-        <v>高尿酸血症</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L47" t="str">
-        <v>尿pH,尿酸性度,尿アルカリ化,ウラリット</v>
+        <v>好酸球,Eosino,Eos,アレルギー,薬疹,DIHS</v>
       </c>
       <c r="M47" t="str">
         <v/>
@@ -2351,40 +2351,40 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ウロビリノーゲン</v>
+        <v>好塩基球</v>
       </c>
       <c r="B48" t="str">
-        <v>Uro</v>
+        <v>Baso,Baso%</v>
       </c>
       <c r="C48" t="str">
-        <v>正常（±）程度</v>
+        <v>0〜2%程度（施設差あり）</v>
       </c>
       <c r="D48" t="str">
-        <v>肝臓や胆道、赤血球の壊れ方の状態を反映する尿検査項目</v>
+        <v>白血球の中で最も数が少なく、アレルギー反応に関わる細胞の割合</v>
       </c>
       <c r="E48" t="str">
-        <v>ウロビリノーゲンは、赤血球やビリルビンが体の中で処理される過程でできる物質です。肝臓の働きが悪くなったり、赤血球が壊れやすくなったりすると、尿の中の量が変化します。</v>
+        <v>好塩基球は白血球の中で最も数が少ない種類で、アレルギー反応や炎症に関わっています。数値の変動が病気の診断に直接使われることは少ない検査です。</v>
       </c>
       <c r="F48" t="str">
-        <v>溶血性疾患（赤血球の破壊亢進）、肝機能障害</v>
+        <v>慢性骨髄性白血病などの血液疾患、アレルギー性疾患、甲状腺機能低下症</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>胆道閉塞（胆汁が腸に流れず、ウロビリノーゲンが作られない状態）</v>
+        <v/>
       </c>
       <c r="I48" t="str">
         <v/>
       </c>
       <c r="J48" t="str">
-        <v>完全に陰性の場合は胆道閉塞を疑う所見の一つ。肝機能（AST/ALT/ビリルビン）と合わせて評価する</v>
+        <v>単独での臨床的意義は乏しいが、著明な増加は血液疾患（慢性骨髄性白血病等）の可能性があり他の血球指標と合わせて評価する</v>
       </c>
       <c r="K48" t="str">
-        <v>肝機能</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L48" t="str">
-        <v>ウロビリノーゲン,Uro,溶血,胆道閉塞,肝機能</v>
+        <v>好塩基球,Baso,アレルギー,白血病</v>
       </c>
       <c r="M48" t="str">
         <v/>
@@ -2392,40 +2392,40 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>尿潜血反応</v>
+        <v>リンパ球</v>
       </c>
       <c r="B49" t="str">
-        <v>尿潜血,U-OB</v>
+        <v>Lympho,Lym%</v>
       </c>
       <c r="C49" t="str">
-        <v>陰性（－）</v>
+        <v>18〜49%程度（施設差あり）</v>
       </c>
       <c r="D49" t="str">
-        <v>尿に血液（赤血球）が混じっていないかを見る検査</v>
+        <v>ウイルス感染と戦い、免疫の記憶を担う白血球の割合</v>
       </c>
       <c r="E49" t="str">
-        <v>この検査は、尿に目に見えないくらいの微量の血液が混じっていないかを調べるものです。陽性の場合、腎臓や膀胱、尿路のどこかに炎症や結石などがある可能性があります。</v>
+        <v>リンパ球は、ウイルスと戦ったり、一度かかった病気を記憶して免疫をつくったりする細胞です。ウイルス感染で増え、抗がん剤の副作用や強いストレスで減ることがあります。</v>
       </c>
       <c r="F49" t="str">
-        <v>尿路結石、膀胱炎などの尿路感染症、腎炎、腫瘍、月経血の混入、激しい運動後</v>
+        <v>ウイルス感染症、リンパ性白血病などの血液疾患、百日咳</v>
       </c>
       <c r="G49" t="str">
-        <v>排尿時の痛みや頻尿、目に見える血尿の有無を確認する。女性は月経の時期と重なっていないか確認する</v>
+        <v/>
       </c>
       <c r="H49" t="str">
-        <v/>
+        <v>抗がん剤・免疫抑制剤・ステロイドの使用、強いストレス、AIDSなどの免疫不全</v>
       </c>
       <c r="I49" t="str">
-        <v/>
+        <v>免疫が下がっている可能性があるため、感染予防（手洗い・うがい、人混みを避ける）を意識するよう伝える</v>
       </c>
       <c r="J49" t="str">
-        <v>陽性でも尿沈渣で赤血球が確認されない場合は偽陽性（ミオグロビン尿など）のこともある。持続する場合は泌尿器科的な精査が必要</v>
+        <v>ステロイド・免疫抑制剤使用中はリンパ球減少による易感染性に注意。好中球と逆方向に動くことが多い（ウイルス感染ではリンパ球優位、細菌感染では好中球優位になりやすい）</v>
       </c>
       <c r="K49" t="str">
-        <v>腎機能</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L49" t="str">
-        <v>尿潜血,潜血反応,U-OB,血尿,尿路結石,膀胱炎</v>
+        <v>リンパ球,Lympho,Lym,ウイルス感染,免疫抑制剤,ステロイド</v>
       </c>
       <c r="M49" t="str">
         <v/>
@@ -2433,22 +2433,22 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>尿ケトン体</v>
+        <v>単球</v>
       </c>
       <c r="B50" t="str">
-        <v>尿ケトン,Ket</v>
+        <v>Mono,Mono%</v>
       </c>
       <c r="C50" t="str">
-        <v>陰性（－）</v>
+        <v>2〜10%程度（施設差あり）</v>
       </c>
       <c r="D50" t="str">
-        <v>体がブドウ糖の代わりに脂肪を分解してエネルギーを作っているサイン</v>
+        <v>感染や炎症の後始末をする白血球の一種の割合</v>
       </c>
       <c r="E50" t="str">
-        <v>この検査は、体が糖の代わりに脂肪を使ってエネルギーを作っていないかを見るものです。陽性が続くときは、食事や水分、インスリンの使い方を確認する必要があります。</v>
+        <v>単球は、細菌などを取り込んで処理したり、組織の修復に関わったりする免疫細胞です。慢性的な炎症や感染症の回復期に増えることがあります。</v>
       </c>
       <c r="F50" t="str">
-        <v>糖尿病の血糖コントロール不良（シックデイ・インスリン不足）、極端な糖質制限、絶食、嘔吐・下痢による脱水</v>
+        <v>慢性感染症（結核など）、炎症性疾患、血液疾患、感染症の回復期</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2460,13 +2460,13 @@
         <v/>
       </c>
       <c r="J50" t="str">
-        <v>陽性かつ高血糖・全身倦怠感が強い場合は糖尿病性ケトアシドーシスの可能性があり緊急性が高い。シックデイルールの説明歴を確認する</v>
+        <v>単独での臨床的意義は乏しく、他の血球指標や炎症マーカー(CRPなど)と合わせて評価する</v>
       </c>
       <c r="K50" t="str">
-        <v>糖尿病</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L50" t="str">
-        <v>尿ケトン体,ケトン体,Ket,シックデイ,ケトアシドーシス</v>
+        <v>単球,Mono,慢性感染症,結核,炎症</v>
       </c>
       <c r="M50" t="str">
         <v/>
@@ -2474,40 +2474,40 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>尿糖（半定量）</v>
+        <v>尿pH</v>
       </c>
       <c r="B51" t="str">
-        <v>尿糖,U-Glu</v>
+        <v>尿pH</v>
       </c>
       <c r="C51" t="str">
-        <v>陰性（－）</v>
+        <v>4.5〜7.5程度（弱酸性が多い）</v>
       </c>
       <c r="D51" t="str">
-        <v>尿に糖が漏れ出ていないかを見る検査。血糖値がかなり高いと陽性になる</v>
+        <v>尿の酸性・アルカリ性の度合い。食事や感染症、体の状態を反映する</v>
       </c>
       <c r="E51" t="str">
-        <v>通常、糖は尿にはほとんど出ませんが、血糖値がかなり高くなると尿にあふれ出るようになります。血糖コントロールの目安の一つです。</v>
+        <v>尿のpHは酸性・アルカリ性のバランスを表します。食事の内容や感染症、体の代謝状態によって変化します。単独で大きな問題を示すことは少ない検査です。</v>
       </c>
       <c r="F51" t="str">
-        <v>糖尿病（血糖値が腎臓で再吸収できる量を超えている状態）、腎性糖尿（血糖値が正常でも体質的に出ることがある）、SGLT2阻害薬服用中（薬の作用で意図的に糖を排泄するため陽性になるのが正常）</v>
+        <v>尿路感染症（尿素分解菌によるもの）、野菜中心の食事、過換気</v>
       </c>
       <c r="G51" t="str">
-        <v>SGLT2阻害薬（フォシーガ、ジャディアンスなど）服用中は、陽性が薬の効果によるものであることを説明する。脱水や尿路感染の症状がないかも確認する</v>
+        <v/>
       </c>
       <c r="H51" t="str">
-        <v/>
+        <v>高たんぱく食、糖尿病性ケトアシドーシス、痛風発作時（酸性尿は尿酸結石のリスクを高める）</v>
       </c>
       <c r="I51" t="str">
-        <v/>
+        <v>痛風・尿酸結石がある場合は、野菜など尿をアルカリ化する食品を意識するとよいことを伝える</v>
       </c>
       <c r="J51" t="str">
-        <v>SGLT2阻害薬服用中は尿糖陽性が治療効果として想定内であることを患者に伝える。血糖値・HbA1cと合わせて評価する</v>
+        <v>高尿酸血症・尿酸結石の患者では尿pHが酸性に傾いていないか確認する。尿アルカリ化薬（ウラリットなど）の効果判定にも使う</v>
       </c>
       <c r="K51" t="str">
-        <v>糖尿病</v>
+        <v>高尿酸血症</v>
       </c>
       <c r="L51" t="str">
-        <v>尿糖,糖半定量,U-Glu,腎性糖尿,SGLT2</v>
+        <v>尿pH,尿酸性度,尿アルカリ化,ウラリット</v>
       </c>
       <c r="M51" t="str">
         <v/>
@@ -2515,22 +2515,22 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>尿蛋白定量</v>
+        <v>尿ケトン体</v>
       </c>
       <c r="B52" t="str">
-        <v>U-Pro定量,蛋白/Cr比</v>
+        <v>尿ケトン,Ket</v>
       </c>
       <c r="C52" t="str">
-        <v>0.15 g/gCr未満</v>
+        <v>陰性（－）</v>
       </c>
       <c r="D52" t="str">
-        <v>随時尿から尿蛋白の量を具体的な数値として評価する検査。ネフローゼ等の重症度判定に使う</v>
+        <v>体がブドウ糖の代わりに脂肪を分解してエネルギーを作っているサイン</v>
       </c>
       <c r="E52" t="str">
-        <v>これは、尿に出ているたんぱくの量を具体的な数値で見る検査です。試験紙での陽性・陰性の判定だけでなく、実際にどれくらいの量が出ているかを把握できます。</v>
+        <v>この検査は、体が糖の代わりに脂肪を使ってエネルギーを作っていないかを見るものです。陽性が続くときは、食事や水分、インスリンの使い方を確認する必要があります。</v>
       </c>
       <c r="F52" t="str">
-        <v>腎症の進行（糖尿病性腎症、慢性腎臓病など）、ネフローゼ症候群（3.5 g/gCr以上が目安）</v>
+        <v>糖尿病の血糖コントロール不良（シックデイ・インスリン不足）、極端な糖質制限、絶食、嘔吐・下痢による脱水</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2542,13 +2542,13 @@
         <v/>
       </c>
       <c r="J52" t="str">
-        <v>CKD診療ガイドラインの重症度分類（尿蛋白量による区分）にも使われる定量指標。試験紙法の半定量結果より治療効果判定に適する</v>
+        <v>陽性かつ高血糖・全身倦怠感が強い場合は糖尿病性ケトアシドーシスの可能性があり緊急性が高い。シックデイルールの説明歴を確認する</v>
       </c>
       <c r="K52" t="str">
-        <v>腎機能,糖尿病</v>
+        <v>糖尿病</v>
       </c>
       <c r="L52" t="str">
-        <v>尿蛋白,随時尿,定量,蛋白クレアチニン比,ネフローゼ</v>
+        <v>尿ケトン体,ケトン体,Ket,シックデイ,ケトアシドーシス</v>
       </c>
       <c r="M52" t="str">
         <v/>
@@ -2556,122 +2556,122 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>アルブミン</v>
+        <v>ウロビリノーゲン</v>
       </c>
       <c r="B53" t="str">
-        <v>Alb</v>
+        <v>Uro</v>
       </c>
       <c r="C53" t="str">
-        <v>3.8〜5.2 g/dL</v>
+        <v>正常（±）程度</v>
       </c>
       <c r="D53" t="str">
-        <v>体の栄養状態を見る目安になるたんぱく質。血液の中で栄養を運ぶ、水分を血管の中に保つという働きをしている。</v>
+        <v>肝臓や胆道、赤血球の壊れ方の状態を反映する尿検査項目</v>
       </c>
       <c r="E53" t="str">
-        <v>アルブミンは栄養の状態を見る数値です。食事量が少なかったり、肝臓や腎臓、腸の働きが弱ると下がることがあります。数値が低いと、むくみが出やすくなります。</v>
+        <v>ウロビリノーゲンは、赤血球やビリルビンが体の中で処理される過程でできる物質です。肝臓の働きが悪くなったり、赤血球が壊れやすくなったりすると、尿の中の量が変化します。</v>
       </c>
       <c r="F53" t="str">
-        <v>脱水（見かけ上の上昇）</v>
+        <v>溶血性疾患（赤血球の破壊亢進）、肝機能障害</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>低栄養／肝機能低下／ネフローゼ症候群／クローン病</v>
+        <v>胆道閉塞（胆汁が腸に流れず、ウロビリノーゲンが作られない状態）</v>
       </c>
       <c r="I53" t="str">
-        <v>主食に偏らず、肉・魚・卵・大豆製品などたんぱく質をしっかり摂るよう伝える。食欲が落ちている場合は少量頻回の食事も提案する</v>
+        <v/>
       </c>
       <c r="J53" t="str">
-        <v>3前半は注意ライン。食事摂取量を必ず確認</v>
+        <v>完全に陰性の場合は胆道閉塞を疑う所見の一つ。肝機能（AST/ALT/ビリルビン）と合わせて評価する</v>
       </c>
       <c r="K53" t="str">
-        <v>肝機能,栄養,腎機能</v>
+        <v>肝機能</v>
       </c>
       <c r="L53" t="str">
-        <v>アルブミン,Alb,むくみ,浮腫,栄養状態</v>
+        <v>ウロビリノーゲン,Uro,溶血,胆道閉塞,肝機能</v>
       </c>
       <c r="M53" t="str">
-        <v>食事と栄養 p.23（たんぱく質）／p.242（フレイルQ110 アルブミン値を上げる食事指導）</v>
+        <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>BNP</v>
+        <v>尿潜血反応</v>
       </c>
       <c r="B54" t="str">
-        <v>BNP</v>
+        <v>尿潜血,U-OB</v>
       </c>
       <c r="C54" t="str">
-        <v>18.4 pg/mL以下</v>
+        <v>陰性（－）</v>
       </c>
       <c r="D54" t="str">
-        <v>心臓が無理をしているときに出る物質。心臓は血液を送るポンプだが、負担がかかると「少し助けてほしい」というサインとしてBNPを血液中に出す。</v>
+        <v>尿に血液（赤血球）が混じっていないかを見る検査</v>
       </c>
       <c r="E54" t="str">
-        <v>この検査は、心臓がどれくらい頑張りすぎていないかを見るものです。数値が高いと、心臓に少し負担がかかっているサインになります。</v>
+        <v>この検査は、尿に目に見えないくらいの微量の血液が混じっていないかを調べるものです。陽性の場合、腎臓や膀胱、尿路のどこかに炎症や結石などがある可能性があります。</v>
       </c>
       <c r="F54" t="str">
-        <v>心不全、心臓に負担がかかっている状態、体に水分がたまりやすいとき</v>
+        <v>尿路結石、膀胱炎などの尿路感染症、腎炎、腫瘍、月経血の混入、激しい運動後</v>
       </c>
       <c r="G54" t="str">
-        <v>塩分・水分の摂りすぎに注意し、体重の変化を毎日記録するよう伝える</v>
+        <v>排尿時の痛みや頻尿、目に見える血尿の有無を確認する。女性は月経の時期と重なっていないか確認する</v>
       </c>
       <c r="H54" t="str">
-        <v>心臓の負担は少ない状態</v>
+        <v/>
       </c>
       <c r="I54" t="str">
         <v/>
       </c>
       <c r="J54" t="str">
-        <v>腎機能が低いとBNPは高めに出ることがある／数値だけで判断せず、症状と合わせて評価する／息切れ、むくみ、体重増加があれば要注意</v>
+        <v>陽性でも尿沈渣で赤血球が確認されない場合は偽陽性（ミオグロビン尿など）のこともある。持続する場合は泌尿器科的な精査が必要</v>
       </c>
       <c r="K54" t="str">
-        <v>心不全</v>
+        <v>腎機能</v>
       </c>
       <c r="L54" t="str">
-        <v>BNP,心不全,息切れ,むくみ</v>
+        <v>尿潜血,潜血反応,U-OB,血尿,尿路結石,膀胱炎</v>
       </c>
       <c r="M54" t="str">
-        <v>食事と栄養 p.216-222（第2部 心疾患）</v>
+        <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>血清CPR（Cペプチド）</v>
+        <v>尿糖（半定量）</v>
       </c>
       <c r="B55" t="str">
-        <v>CPR</v>
+        <v>尿糖,U-Glu</v>
       </c>
       <c r="C55" t="str">
-        <v>空腹時 0.6〜3.0 ng/mL（施設差あり）</v>
+        <v>陰性（－）</v>
       </c>
       <c r="D55" t="str">
-        <v>自分の膵臓がどれくらいインスリンを作れているかを表す指標</v>
+        <v>尿に糖が漏れ出ていないかを見る検査。血糖値がかなり高いと陽性になる</v>
       </c>
       <c r="E55" t="str">
-        <v>この検査は、ご自身の膵臓がどれくらいインスリンを作る力を持っているかを見るものです。数値が低いほど、体の中で作れるインスリンが少ないことを示します。</v>
+        <v>通常、糖は尿にはほとんど出ませんが、血糖値がかなり高くなると尿にあふれ出るようになります。血糖コントロールの目安の一つです。</v>
       </c>
       <c r="F55" t="str">
-        <v>インスリン抵抗性が強い状態（初期の2型糖尿病など）</v>
+        <v>糖尿病（血糖値が腎臓で再吸収できる量を超えている状態）、腎性糖尿（血糖値が正常でも体質的に出ることがある）、SGLT2阻害薬服用中（薬の作用で意図的に糖を排泄するため陽性になるのが正常）</v>
       </c>
       <c r="G55" t="str">
-        <v/>
+        <v>SGLT2阻害薬（フォシーガ、ジャディアンスなど）服用中は、陽性が薬の効果によるものであることを説明する。脱水や尿路感染の症状がないかも確認する</v>
       </c>
       <c r="H55" t="str">
-        <v>膵臓のインスリン分泌能低下（1型糖尿病、糖尿病の進行）</v>
+        <v/>
       </c>
       <c r="I55" t="str">
         <v/>
       </c>
       <c r="J55" t="str">
-        <v>インスリン分泌能の評価に使われる。数値が低いほどインスリン治療の必要性が高いと判断される目安になる</v>
+        <v>SGLT2阻害薬服用中は尿糖陽性が治療効果として想定内であることを患者に伝える。血糖値・HbA1cと合わせて評価する</v>
       </c>
       <c r="K55" t="str">
         <v>糖尿病</v>
       </c>
       <c r="L55" t="str">
-        <v>CPR,Cペプチド,インスリン分泌,血清CPR</v>
+        <v>尿糖,糖半定量,U-Glu,腎性糖尿,SGLT2</v>
       </c>
       <c r="M55" t="str">
         <v/>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>尿中微量アルブミン</v>
+        <v>尿蛋白定量</v>
       </c>
       <c r="B56" t="str">
-        <v>U-Alb,MAU</v>
+        <v>U-Pro定量,蛋白/Cr比</v>
       </c>
       <c r="C56" t="str">
-        <v>30 mg/gCr未満（尿中アルブミン/クレアチニン比）</v>
+        <v>0.15 g/gCr未満</v>
       </c>
       <c r="D56" t="str">
-        <v>通常の尿蛋白検査では見つからない、ごく早期の腎症のサイン</v>
+        <v>随時尿から尿蛋白の量を具体的な数値として評価する検査。ネフローゼ等の重症度判定に使う</v>
       </c>
       <c r="E56" t="str">
-        <v>この検査は、通常の尿検査ではまだ分からないくらい早い段階の腎臓の変化を見つけるためのものです。数値が高いと、腎症の初期のサインである可能性があります。</v>
+        <v>これは、尿に出ているたんぱくの量を具体的な数値で見る検査です。試験紙での陽性・陰性の判定だけでなく、実際にどれくらいの量が出ているかを把握できます。</v>
       </c>
       <c r="F56" t="str">
-        <v>糖尿病性腎症の早期段階、高血圧</v>
+        <v>腎症の進行（糖尿病性腎症、慢性腎臓病など）、ネフローゼ症候群（3.5 g/gCr以上が目安）</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2706,13 +2706,13 @@
         <v/>
       </c>
       <c r="J56" t="str">
-        <v>糖尿病腎症の早期発見に重要な検査。血糖・血圧コントロールで改善しうる段階なので、早期介入の意義を伝える</v>
+        <v>CKD診療ガイドラインの重症度分類（尿蛋白量による区分）にも使われる定量指標。試験紙法の半定量結果より治療効果判定に適する</v>
       </c>
       <c r="K56" t="str">
-        <v>糖尿病,腎機能</v>
+        <v>腎機能,糖尿病</v>
       </c>
       <c r="L56" t="str">
-        <v>微量アルブミン,U-Alb,MAU,糖尿病性腎症,早期腎症</v>
+        <v>尿蛋白,随時尿,定量,蛋白クレアチニン比,ネフローゼ</v>
       </c>
       <c r="M56" t="str">
         <v/>
@@ -2720,163 +2720,163 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>血清鉄（Fe）</v>
+        <v>BNP</v>
       </c>
       <c r="B57" t="str">
-        <v>Fe</v>
+        <v>BNP</v>
       </c>
       <c r="C57" t="str">
-        <v>60〜200 μg/dL（施設差あり）</v>
+        <v>18.4 pg/mL以下</v>
       </c>
       <c r="D57" t="str">
-        <v>血液中を流れている鉄の量</v>
+        <v>心臓が無理をしているときに出る物質。心臓は血液を送るポンプだが、負担がかかると「少し助けてほしい」というサインとしてBNPを血液中に出す。</v>
       </c>
       <c r="E57" t="str">
-        <v>この検査は、今血液の中を流れている鉄の量を見るものです。低いと、体の中で鉄が不足している可能性があります。</v>
+        <v>この検査は、心臓がどれくらい頑張りすぎていないかを見るものです。数値が高いと、心臓に少し負担がかかっているサインになります。</v>
       </c>
       <c r="F57" t="str">
-        <v>鉄剤の過剰摂取、溶血、肝疾患</v>
+        <v>心不全、心臓に負担がかかっている状態、体に水分がたまりやすいとき</v>
       </c>
       <c r="G57" t="str">
-        <v/>
+        <v>塩分・水分の摂りすぎに注意し、体重の変化を毎日記録するよう伝える</v>
       </c>
       <c r="H57" t="str">
-        <v>鉄欠乏性貧血、慢性炎症、出血</v>
+        <v>心臓の負担は少ない状態</v>
       </c>
       <c r="I57" t="str">
-        <v>鉄分の多い食品（レバー・赤身肉・魚・ほうれん草など）を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える</v>
+        <v/>
       </c>
       <c r="J57" t="str">
-        <v>血清鉄は日内変動が大きい。単独で判断せず総鉄結合能・フェリチンと合わせて評価する</v>
+        <v>腎機能が低いとBNPは高めに出ることがある／数値だけで判断せず、症状と合わせて評価する／息切れ、むくみ、体重増加があれば要注意</v>
       </c>
       <c r="K57" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>心不全</v>
       </c>
       <c r="L57" t="str">
-        <v>血清鉄,Fe,鉄欠乏性貧血</v>
+        <v>BNP,心不全,息切れ,むくみ</v>
       </c>
       <c r="M57" t="str">
-        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
+        <v>食事と栄養 p.216-222（第2部 心疾患）</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>総鉄結合能（TIBC）</v>
+        <v>血清CPR（Cペプチド）</v>
       </c>
       <c r="B58" t="str">
-        <v>TIBC</v>
+        <v>CPR</v>
       </c>
       <c r="C58" t="str">
-        <v>250〜360 μg/dL（施設差あり）</v>
+        <v>空腹時 0.6〜3.0 ng/mL（施設差あり）</v>
       </c>
       <c r="D58" t="str">
-        <v>血液中のトランスフェリンが鉄と結合できる総量</v>
+        <v>自分の膵臓がどれくらいインスリンを作れているかを表す指標</v>
       </c>
       <c r="E58" t="str">
-        <v>TIBCは、血液中でトランスフェリンという物質が鉄を運べる最大量を表します。体の中の鉄が不足すると、少しでも多く鉄を運ぼうとしてこの数値が上がる性質があります。</v>
+        <v>この検査は、ご自身の膵臓がどれくらいインスリンを作る力を持っているかを見るものです。数値が低いほど、体の中で作れるインスリンが少ないことを示します。</v>
       </c>
       <c r="F58" t="str">
-        <v>鉄欠乏性貧血（＞360 μg/dLが目安）</v>
+        <v>インスリン抵抗性が強い状態（初期の2型糖尿病など）</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>慢性炎症、肝疾患、ネフローゼ症候群</v>
+        <v>膵臓のインスリン分泌能低下（1型糖尿病、糖尿病の進行）</v>
       </c>
       <c r="I58" t="str">
         <v/>
       </c>
       <c r="J58" t="str">
-        <v>鉄が不足すると、体はより多く運ぼうとしてTIBCが上昇する。UIBC・血清鉄と併せて評価する</v>
+        <v>インスリン分泌能の評価に使われる。数値が低いほどインスリン治療の必要性が高いと判断される目安になる</v>
       </c>
       <c r="K58" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>糖尿病</v>
       </c>
       <c r="L58" t="str">
-        <v>TIBC,総鉄結合能,鉄欠乏性貧血</v>
+        <v>CPR,Cペプチド,インスリン分泌,血清CPR</v>
       </c>
       <c r="M58" t="str">
-        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>不飽和鉄結合能（UIBC）</v>
+        <v>尿中微量アルブミン</v>
       </c>
       <c r="B59" t="str">
-        <v>UIBC</v>
+        <v>U-Alb,MAU</v>
       </c>
       <c r="C59" t="str">
-        <v>170〜300 μg/dL（施設差あり）</v>
+        <v>30 mg/gCr未満（尿中アルブミン/クレアチニン比）</v>
       </c>
       <c r="D59" t="str">
-        <v>トランスフェリンのうち、まだ鉄と結合していない余力の部分（UIBC＝TIBC－血清鉄）</v>
+        <v>通常の尿蛋白検査では見つからない、ごく早期の腎症のサイン</v>
       </c>
       <c r="E59" t="str">
-        <v>UIBCは、トランスフェリンのうち、まだ鉄と結合していない「空き容量」の部分を表します。鉄が不足しているときほど、この空き容量は大きくなります。</v>
+        <v>この検査は、通常の尿検査ではまだ分からないくらい早い段階の腎臓の変化を見つけるためのものです。数値が高いと、腎症の初期のサインである可能性があります。</v>
       </c>
       <c r="F59" t="str">
-        <v>鉄欠乏性貧血（＞300 μg/dLが目安）</v>
+        <v>糖尿病性腎症の早期段階、高血圧</v>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>慢性炎症、鉄過剰状態</v>
+        <v/>
       </c>
       <c r="I59" t="str">
         <v/>
       </c>
       <c r="J59" t="str">
-        <v>TIBCと同じ方向に動くことが多い。血清鉄・TIBCとあわせて鉄欠乏性貧血と二次性貧血の鑑別に使う</v>
+        <v>糖尿病腎症の早期発見に重要な検査。血糖・血圧コントロールで改善しうる段階なので、早期介入の意義を伝える</v>
       </c>
       <c r="K59" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>糖尿病,腎機能</v>
       </c>
       <c r="L59" t="str">
-        <v>UIBC,不飽和鉄結合能,鉄欠乏性貧血</v>
+        <v>微量アルブミン,U-Alb,MAU,糖尿病性腎症,早期腎症</v>
       </c>
       <c r="M59" t="str">
-        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
+        <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>トランスフェリン飽和度</v>
+        <v>血清鉄（Fe）</v>
       </c>
       <c r="B60" t="str">
-        <v>TSAT</v>
+        <v>Fe</v>
       </c>
       <c r="C60" t="str">
-        <v>16〜50%程度（施設差あり）</v>
+        <v>60〜200 μg/dL（施設差あり）</v>
       </c>
       <c r="D60" t="str">
-        <v>鉄を運ぶ役割のトランスフェリンのうち、実際に鉄を運んでいる割合（血清鉄÷総鉄結合能）</v>
+        <v>血液中を流れている鉄の量</v>
       </c>
       <c r="E60" t="str">
-        <v>トランスフェリン飽和度は、鉄を運ぶトランスフェリンのうち、実際にどれくらいが鉄を運んでいるかを割合で表したものです。鉄欠乏性貧血では低くなり、鉄が過剰にたまる病気では高くなります。</v>
+        <v>この検査は、今血液の中を流れている鉄の量を見るものです。低いと、体の中で鉄が不足している可能性があります。</v>
       </c>
       <c r="F60" t="str">
-        <v>鉄過剰症（ヘモクロマトーシスなど）</v>
+        <v>鉄剤の過剰摂取、溶血、肝疾患</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>鉄欠乏性貧血（＜16%が目安）</v>
+        <v>鉄欠乏性貧血、慢性炎症、出血</v>
       </c>
       <c r="I60" t="str">
-        <v/>
+        <v>鉄分の多い食品（レバー・赤身肉・魚・ほうれん草など）を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える</v>
       </c>
       <c r="J60" t="str">
-        <v>血清鉄をTIBCで割って計算される。鉄剤補充の効果判定にも使われる</v>
+        <v>血清鉄は日内変動が大きい。単独で判断せず総鉄結合能・フェリチンと合わせて評価する</v>
       </c>
       <c r="K60" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
       <c r="L60" t="str">
-        <v>トランスフェリン飽和度,TSAT,鉄欠乏性貧血</v>
+        <v>血清鉄,Fe,鉄欠乏性貧血</v>
       </c>
       <c r="M60" t="str">
         <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
@@ -2884,40 +2884,40 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>血清フェリチン</v>
+        <v>総鉄結合能（TIBC）</v>
       </c>
       <c r="B61" t="str">
-        <v>Ferritin</v>
+        <v>TIBC</v>
       </c>
       <c r="C61" t="str">
-        <v>男性 20〜250 ng/mL、女性 10〜120 ng/mL（施設差あり）</v>
+        <v>250〜360 μg/dL（施設差あり）</v>
       </c>
       <c r="D61" t="str">
-        <v>体に貯蔵されている鉄の量を反映する指標。貧血の症状が出るより早い段階で低下する</v>
+        <v>血液中のトランスフェリンが鉄と結合できる総量</v>
       </c>
       <c r="E61" t="str">
-        <v>フェリチンは、体に蓄えられている鉄の「貯金」の量を見る検査です。この数値が下がるのは、貧血の症状が出るよりも前の、とても早い段階のサインになります。</v>
+        <v>TIBCは、血液中でトランスフェリンという物質が鉄を運べる最大量を表します。体の中の鉄が不足すると、少しでも多く鉄を運ぼうとしてこの数値が上がる性質があります。</v>
       </c>
       <c r="F61" t="str">
-        <v>炎症性疾患、肝疾患、悪性腫瘍、鉄過剰症（フェリチンは炎症でも上昇するため、貧血の評価では注意が必要）</v>
+        <v>鉄欠乏性貧血（＞360 μg/dLが目安）</v>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>鉄欠乏状態（貧血の症状が出る前の早期段階から低下する）</v>
+        <v>慢性炎症、肝疾患、ネフローゼ症候群</v>
       </c>
       <c r="I61" t="str">
-        <v>鉄分の多い食品を意識するとともに、貯蔵鉄を補うため治療は数値が正常化してからも継続が必要なことを伝える</v>
+        <v/>
       </c>
       <c r="J61" t="str">
-        <v>貯蔵鉄の指標で鉄欠乏を最も早期に反映する。ただし炎症があると鉄欠乏があっても正常〜高値に出ることがあり、CRP等の炎症所見と合わせて評価する。二次性貧血との鑑別に重要</v>
+        <v>鉄が不足すると、体はより多く運ぼうとしてTIBCが上昇する。UIBC・血清鉄と併せて評価する</v>
       </c>
       <c r="K61" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
       <c r="L61" t="str">
-        <v>フェリチン,Ferritin,貯蔵鉄,鉄欠乏</v>
+        <v>TIBC,総鉄結合能,鉄欠乏性貧血</v>
       </c>
       <c r="M61" t="str">
         <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
@@ -2925,66 +2925,66 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>尿中尿酸/クレアチニン比（UUA/UCr）</v>
+        <v>不飽和鉄結合能（UIBC）</v>
       </c>
       <c r="B62" t="str">
-        <v>UUA/UCr</v>
+        <v>UIBC</v>
       </c>
       <c r="C62" t="str">
-        <v>0.4〜0.8程度が混合型の目安</v>
+        <v>170〜300 μg/dL（施設差あり）</v>
       </c>
       <c r="D62" t="str">
-        <v>尿酸が「作られすぎ」か「排泄できていない」かを見分ける比の値</v>
+        <v>トランスフェリンのうち、まだ鉄と結合していない余力の部分（UIBC＝TIBC－血清鉄）</v>
       </c>
       <c r="E62" t="str">
-        <v>この数値は、体の中で尿酸が「作られすぎている」のか、それとも「うまく排泄できていない」のかを見分けるために使う比の値です。高尿酸血症の治療薬を選ぶときの参考になります。</v>
+        <v>UIBCは、トランスフェリンのうち、まだ鉄と結合していない「空き容量」の部分を表します。鉄が不足しているときほど、この空き容量は大きくなります。</v>
       </c>
       <c r="F62" t="str">
-        <v>尿酸産生過剰型（0.8以上が目安）</v>
+        <v>鉄欠乏性貧血（＞300 μg/dLが目安）</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>尿酸排泄低下型（0.4以下が目安）</v>
+        <v>慢性炎症、鉄過剰状態</v>
       </c>
       <c r="I62" t="str">
         <v/>
       </c>
       <c r="J62" t="str">
-        <v>高尿酸血症は尿酸産生過剰型・排泄低下型・混合型に分類され、この比が目安になる。病型によって使う薬剤（尿酸生成抑制薬か尿酸排泄促進薬か）の選択が変わる</v>
+        <v>TIBCと同じ方向に動くことが多い。血清鉄・TIBCとあわせて鉄欠乏性貧血と二次性貧血の鑑別に使う</v>
       </c>
       <c r="K62" t="str">
-        <v>高尿酸血症</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="L62" t="str">
-        <v>UUA,UCr,尿酸クリアランス,CUA,EUA,尿酸産生過剰型,尿酸排泄低下型</v>
+        <v>UIBC,不飽和鉄結合能,鉄欠乏性貧血</v>
       </c>
       <c r="M62" t="str">
-        <v>食事と栄養 p.180-189（第2部 痛風・高尿酸血症）</v>
+        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>ucOC（低カルボキシル化オステオカルシン）</v>
+        <v>骨型酒石酸抵抗性フォスファターゼ（TRACP-5b）</v>
       </c>
       <c r="B63" t="str">
-        <v>ucOC</v>
+        <v>TRACP-5b</v>
       </c>
       <c r="C63" t="str">
-        <v>4.5 ng/mL未満（施設差あり）</v>
+        <v>120〜420 mU/dL</v>
       </c>
       <c r="D63" t="str">
-        <v>ビタミンKが不足していないかを反映する骨の指標</v>
+        <v>骨がどれくらい壊されているかを見る検査。骨は「古い骨を壊して新しい骨を作る」入れ替えを繰り返しており、骨を壊す細胞が活発だとこの物質が血液中に増える。</v>
       </c>
       <c r="E63" t="str">
-        <v>ucOCは、骨を作るために必要なビタミンKが体の中で足りているかどうかを反映する検査です。数値が高いとビタミンK不足が疑われます。</v>
+        <v>この検査は、骨がどれくらい早く減っていないかを見るものです。数値が高いと、骨が弱くなりやすい状態の目安になります。</v>
       </c>
       <c r="F63" t="str">
-        <v>ビタミンK不足状態</v>
+        <v>骨粗鬆症、骨代謝回転（骨がこわれるスピード）が活発な状態</v>
       </c>
       <c r="G63" t="str">
-        <v/>
+        <v>カルシウム・ビタミンDの摂取や、適度な荷重運動（ウォーキングなど）を意識するよう伝える</v>
       </c>
       <c r="H63" t="str">
         <v/>
@@ -2993,159 +2993,159 @@
         <v/>
       </c>
       <c r="J63" t="str">
-        <v>ビタミンK2製剤（骨粗鬆症治療薬）の適応判断や効果判定に使われる</v>
+        <v>「骨を壊す側」の指標。「骨を作る側」の検査と合わせて評価する。数値だけで診断はしない</v>
       </c>
       <c r="K63" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="L63" t="str">
-        <v>ucOC,オステオカルシン,ビタミンK</v>
+        <v>TRACP-5b,骨型酒石酸抵抗性フォスファターゼ,骨粗鬆症,骨代謝</v>
       </c>
       <c r="M63" t="str">
-        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
+        <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>リン（P）</v>
+        <v>トランスフェリン飽和度</v>
       </c>
       <c r="B64" t="str">
-        <v>P,IP</v>
+        <v>TSAT</v>
       </c>
       <c r="C64" t="str">
-        <v>2.5〜4.5 mg/dL</v>
+        <v>16〜50%程度（施設差あり）</v>
       </c>
       <c r="D64" t="str">
-        <v>カルシウムとともに骨を作る主要なミネラル</v>
+        <v>鉄を運ぶ役割のトランスフェリンのうち、実際に鉄を運んでいる割合（血清鉄÷総鉄結合能）</v>
       </c>
       <c r="E64" t="str">
-        <v>リンはカルシウムと一緒に骨や歯を作る材料になるミネラルです。カルシウムと逆方向に動くことが多く、腎臓の働きやホルモンのバランスによっても変動します。</v>
+        <v>トランスフェリン飽和度は、鉄を運ぶトランスフェリンのうち、実際にどれくらいが鉄を運んでいるかを割合で表したものです。鉄欠乏性貧血では低くなり、鉄が過剰にたまる病気では高くなります。</v>
       </c>
       <c r="F64" t="str">
-        <v>腎不全、副甲状腺機能低下症</v>
+        <v>鉄過剰症（ヘモクロマトーシスなど）</v>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>副甲状腺機能亢進症、骨軟化症、ビタミンD欠乏</v>
+        <v>鉄欠乏性貧血（＜16%が目安）</v>
       </c>
       <c r="I64" t="str">
         <v/>
       </c>
       <c r="J64" t="str">
-        <v>カルシウムと逆方向に動くことが多い（副甲状腺機能亢進症ではCa上昇・P低下）。骨粗鬆症の二次性原因の除外に用いられる</v>
+        <v>血清鉄をTIBCで割って計算される。鉄剤補充の効果判定にも使われる</v>
       </c>
       <c r="K64" t="str">
-        <v>骨粗鬆症,電解質</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="L64" t="str">
-        <v>リン,P,IP,無機リン</v>
+        <v>トランスフェリン飽和度,TSAT,鉄欠乏性貧血</v>
       </c>
       <c r="M64" t="str">
-        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）／p.199-215（第2部 腎機能低下 Q83 リン制限）</v>
+        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>PTH（副甲状腺ホルモン）</v>
+        <v>血清フェリチン</v>
       </c>
       <c r="B65" t="str">
-        <v>PTH</v>
+        <v>Ferritin</v>
       </c>
       <c r="C65" t="str">
-        <v>10〜65 pg/mL（施設差あり）</v>
+        <v>男性 20〜250 ng/mL、女性 10〜120 ng/mL（施設差あり）</v>
       </c>
       <c r="D65" t="str">
-        <v>血液中のカルシウム濃度を調節するホルモン</v>
+        <v>体に貯蔵されている鉄の量を反映する指標。貧血の症状が出るより早い段階で低下する</v>
       </c>
       <c r="E65" t="str">
-        <v>PTHは、血液中のカルシウム濃度を一定に保つために働くホルモンです。カルシウムが低くなると分泌が増え、骨からカルシウムを取り出したり、腎臓での再吸収を促したりして数値を戻そうとします。</v>
+        <v>フェリチンは、体に蓄えられている鉄の「貯金」の量を見る検査です。この数値が下がるのは、貧血の症状が出るよりも前の、とても早い段階のサインになります。</v>
       </c>
       <c r="F65" t="str">
-        <v>原発性・二次性副甲状腺機能亢進症（腎不全に伴うものなど）</v>
+        <v>炎症性疾患、肝疾患、悪性腫瘍、鉄過剰症（フェリチンは炎症でも上昇するため、貧血の評価では注意が必要）</v>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>副甲状腺機能低下症</v>
+        <v>鉄欠乏状態（貧血の症状が出る前の早期段階から低下する）</v>
       </c>
       <c r="I65" t="str">
-        <v/>
+        <v>鉄分の多い食品を意識するとともに、貯蔵鉄を補うため治療は数値が正常化してからも継続が必要なことを伝える</v>
       </c>
       <c r="J65" t="str">
-        <v>骨粗鬆症の二次性原因（副甲状腺機能亢進症）を除外するための検査。カルシウム・リンと合わせて評価する</v>
+        <v>貯蔵鉄の指標で鉄欠乏を最も早期に反映する。ただし炎症があると鉄欠乏があっても正常〜高値に出ることがあり、CRP等の炎症所見と合わせて評価する。二次性貧血との鑑別に重要</v>
       </c>
       <c r="K65" t="str">
-        <v>骨粗鬆症</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="L65" t="str">
-        <v>PTH,副甲状腺ホルモン,パラトルモン</v>
+        <v>フェリチン,Ferritin,貯蔵鉄,鉄欠乏</v>
       </c>
       <c r="M65" t="str">
-        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
+        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>骨型酒石酸抵抗性フォスファターゼ（TRACP-5b）</v>
+        <v>尿中尿酸/クレアチニン比（UUA/UCr）</v>
       </c>
       <c r="B66" t="str">
-        <v>TRACP-5b</v>
+        <v>UUA/UCr</v>
       </c>
       <c r="C66" t="str">
-        <v>120〜420 mU/dL</v>
+        <v>0.4〜0.8程度が混合型の目安</v>
       </c>
       <c r="D66" t="str">
-        <v>骨がどれくらい壊されているかを見る検査。骨は「古い骨を壊して新しい骨を作る」入れ替えを繰り返しており、骨を壊す細胞が活発だとこの物質が血液中に増える。</v>
+        <v>尿酸が「作られすぎ」か「排泄できていない」かを見分ける比の値</v>
       </c>
       <c r="E66" t="str">
-        <v>この検査は、骨がどれくらい早く減っていないかを見るものです。数値が高いと、骨が弱くなりやすい状態の目安になります。</v>
+        <v>この数値は、体の中で尿酸が「作られすぎている」のか、それとも「うまく排泄できていない」のかを見分けるために使う比の値です。高尿酸血症の治療薬を選ぶときの参考になります。</v>
       </c>
       <c r="F66" t="str">
-        <v>骨粗鬆症、骨代謝回転（骨がこわれるスピード）が活発な状態</v>
+        <v>尿酸産生過剰型（0.8以上が目安）</v>
       </c>
       <c r="G66" t="str">
-        <v>カルシウム・ビタミンDの摂取や、適度な荷重運動（ウォーキングなど）を意識するよう伝える</v>
+        <v/>
       </c>
       <c r="H66" t="str">
-        <v/>
+        <v>尿酸排泄低下型（0.4以下が目安）</v>
       </c>
       <c r="I66" t="str">
         <v/>
       </c>
       <c r="J66" t="str">
-        <v>「骨を壊す側」の指標。「骨を作る側」の検査と合わせて評価する。数値だけで診断はしない</v>
+        <v>高尿酸血症は尿酸産生過剰型・排泄低下型・混合型に分類され、この比が目安になる。病型によって使う薬剤（尿酸生成抑制薬か尿酸排泄促進薬か）の選択が変わる</v>
       </c>
       <c r="K66" t="str">
-        <v>骨粗鬆症</v>
+        <v>高尿酸血症</v>
       </c>
       <c r="L66" t="str">
-        <v>TRACP-5b,骨型酒石酸抵抗性フォスファターゼ,骨粗鬆症,骨代謝</v>
+        <v>UUA,UCr,尿酸クリアランス,CUA,EUA,尿酸産生過剰型,尿酸排泄低下型</v>
       </c>
       <c r="M66" t="str">
-        <v/>
+        <v>食事と栄養 p.180-189（第2部 痛風・高尿酸血症）</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>カルシトニン</v>
+        <v>ucOC（低カルボキシル化オステオカルシン）</v>
       </c>
       <c r="B67" t="str">
-        <v>CT</v>
+        <v>ucOC</v>
       </c>
       <c r="C67" t="str">
-        <v>男性 9.52 pg/mL未満、女性 6.40 pg/mL未満（施設差あり）</v>
+        <v>4.5 ng/mL未満（施設差あり）</v>
       </c>
       <c r="D67" t="str">
-        <v>血液中のカルシウムを下げる方向に働くホルモン</v>
+        <v>ビタミンKが不足していないかを反映する骨の指標</v>
       </c>
       <c r="E67" t="str">
-        <v>カルシトニンは、PTHとは逆に血液中のカルシウムを下げる方向に働くホルモンです。特定の甲状腺の病気（甲状腺髄様癌）がないかを調べる際にも使われます。</v>
+        <v>ucOCは、骨を作るために必要なビタミンKが体の中で足りているかどうかを反映する検査です。数値が高いとビタミンK不足が疑われます。</v>
       </c>
       <c r="F67" t="str">
-        <v>甲状腺髄様癌、腎不全</v>
+        <v>ビタミンK不足状態</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -3157,13 +3157,13 @@
         <v/>
       </c>
       <c r="J67" t="str">
-        <v>骨粗鬆症の二次性原因の除外目的で測定されることがある検査値。同名の薬剤（カルシトニン製剤）と混同しないよう注意</v>
+        <v>ビタミンK2製剤（骨粗鬆症治療薬）の適応判断や効果判定に使われる</v>
       </c>
       <c r="K67" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="L67" t="str">
-        <v>カルシトニン,CT</v>
+        <v>ucOC,オステオカルシン,ビタミンK</v>
       </c>
       <c r="M67" t="str">
         <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
@@ -3171,40 +3171,40 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>尿中NTX</v>
+        <v>PTH（副甲状腺ホルモン）</v>
       </c>
       <c r="B68" t="str">
-        <v>NTX</v>
+        <v>PTH</v>
       </c>
       <c r="C68" t="str">
-        <v>施設差が大きく一律の記載が難しい（尿中）</v>
+        <v>10〜65 pg/mL（施設差あり）</v>
       </c>
       <c r="D68" t="str">
-        <v>骨が壊されるときに出る、骨吸収マーカーのひとつ</v>
+        <v>血液中のカルシウム濃度を調節するホルモン</v>
       </c>
       <c r="E68" t="str">
-        <v>NTXは、骨が壊される（吸収される）ときに尿の中に出てくる物質です。骨粗鬆症の治療薬がどれくらい効いているかを確認するために使われます。</v>
+        <v>PTHは、血液中のカルシウム濃度を一定に保つために働くホルモンです。カルシウムが低くなると分泌が増え、骨からカルシウムを取り出したり、腎臓での再吸収を促したりして数値を戻そうとします。</v>
       </c>
       <c r="F68" t="str">
-        <v>骨代謝回転の亢進（骨粗鬆症、閉経後など）</v>
+        <v>原発性・二次性副甲状腺機能亢進症（腎不全に伴うものなど）</v>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>骨吸収抑制薬（ビスホスホネート等）による治療効果</v>
+        <v>副甲状腺機能低下症</v>
       </c>
       <c r="I68" t="str">
         <v/>
       </c>
       <c r="J68" t="str">
-        <v>治療開始後3〜6か月で再検し、薬の効果判定に使われる。TRACP-5bと同じ「骨を壊す側」の指標</v>
+        <v>骨粗鬆症の二次性原因（副甲状腺機能亢進症）を除外するための検査。カルシウム・リンと合わせて評価する</v>
       </c>
       <c r="K68" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="L68" t="str">
-        <v>NTX,尿中NTX,骨吸収マーカー</v>
+        <v>PTH,副甲状腺ホルモン,パラトルモン</v>
       </c>
       <c r="M68" t="str">
         <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
@@ -3212,40 +3212,40 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>DPD（デオキシピリジノリン）</v>
+        <v>尿中NTX</v>
       </c>
       <c r="B69" t="str">
-        <v>DPD</v>
+        <v>NTX</v>
       </c>
       <c r="C69" t="str">
         <v>施設差が大きく一律の記載が難しい（尿中）</v>
       </c>
       <c r="D69" t="str">
-        <v>骨のコラーゲンが壊れるときに出る、骨吸収マーカーのひとつ</v>
+        <v>骨が壊されるときに出る、骨吸収マーカーのひとつ</v>
       </c>
       <c r="E69" t="str">
-        <v>DPDも、骨が壊されるときに尿に出てくる物質の一つです。NTXと同じように、骨粗鬆症治療薬の効果を確認するために使われます。</v>
+        <v>NTXは、骨が壊される（吸収される）ときに尿の中に出てくる物質です。骨粗鬆症の治療薬がどれくらい効いているかを確認するために使われます。</v>
       </c>
       <c r="F69" t="str">
-        <v>骨代謝回転の亢進（骨粗鬆症など）</v>
+        <v>骨代謝回転の亢進（骨粗鬆症、閉経後など）</v>
       </c>
       <c r="G69" t="str">
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>骨吸収抑制薬による治療効果</v>
+        <v>骨吸収抑制薬（ビスホスホネート等）による治療効果</v>
       </c>
       <c r="I69" t="str">
         <v/>
       </c>
       <c r="J69" t="str">
-        <v>NTX・CTXと同じ「骨を壊す側」の指標。食事の影響を受けにくいとされる</v>
+        <v>治療開始後3〜6か月で再検し、薬の効果判定に使われる。TRACP-5bと同じ「骨を壊す側」の指標</v>
       </c>
       <c r="K69" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="L69" t="str">
-        <v>DPD,デオキシピリジノリン,骨吸収マーカー</v>
+        <v>NTX,尿中NTX,骨吸収マーカー</v>
       </c>
       <c r="M69" t="str">
         <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
@@ -3253,40 +3253,40 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>CTX</v>
+        <v>カルシトニン</v>
       </c>
       <c r="B70" t="str">
-        <v>CTX</v>
+        <v>CT</v>
       </c>
       <c r="C70" t="str">
-        <v>施設差が大きく一律の記載が難しい（血清・尿中）</v>
+        <v>男性 9.52 pg/mL未満、女性 6.40 pg/mL未満（施設差あり）</v>
       </c>
       <c r="D70" t="str">
-        <v>骨のコラーゲンが壊れるときに出る、骨吸収マーカーのひとつ</v>
+        <v>血液中のカルシウムを下げる方向に働くホルモン</v>
       </c>
       <c r="E70" t="str">
-        <v>CTXも、骨が壊されるときに血液や尿に出てくる物質です。骨粗鬆症治療薬（骨を壊すのを抑える薬）の効果を確認するために使われます。</v>
+        <v>カルシトニンは、PTHとは逆に血液中のカルシウムを下げる方向に働くホルモンです。特定の甲状腺の病気（甲状腺髄様癌）がないかを調べる際にも使われます。</v>
       </c>
       <c r="F70" t="str">
-        <v>骨代謝回転の亢進（骨粗鬆症など）</v>
+        <v>甲状腺髄様癌、腎不全</v>
       </c>
       <c r="G70" t="str">
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>骨吸収抑制薬による治療効果</v>
+        <v/>
       </c>
       <c r="I70" t="str">
         <v/>
       </c>
       <c r="J70" t="str">
-        <v>NTX・DPDと同じ「骨を壊す側」の指標。血清・尿中いずれでも測定されることがある</v>
+        <v>骨粗鬆症の二次性原因の除外目的で測定されることがある検査値。同名の薬剤（カルシトニン製剤）と混同しないよう注意</v>
       </c>
       <c r="K70" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="L70" t="str">
-        <v>CTX,骨吸収マーカー</v>
+        <v>カルシトニン,CT</v>
       </c>
       <c r="M70" t="str">
         <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
@@ -3294,40 +3294,40 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>P1NP</v>
+        <v>DPD（デオキシピリジノリン）</v>
       </c>
       <c r="B71" t="str">
-        <v>P1NP</v>
+        <v>DPD</v>
       </c>
       <c r="C71" t="str">
-        <v>施設差が大きく一律の記載が難しい（血清）</v>
+        <v>施設差が大きく一律の記載が難しい（尿中）</v>
       </c>
       <c r="D71" t="str">
-        <v>骨が新しく作られるときに出る、骨形成マーカーのひとつ</v>
+        <v>骨のコラーゲンが壊れるときに出る、骨吸収マーカーのひとつ</v>
       </c>
       <c r="E71" t="str">
-        <v>P1NPは、CTXなどとは逆に、骨が新しく作られるときに血液中に出てくる物質です。骨を作る力を高める薬（テリパラチドなど）の効果を確認するために使われます。</v>
+        <v>DPDも、骨が壊されるときに尿に出てくる物質の一つです。NTXと同じように、骨粗鬆症治療薬の効果を確認するために使われます。</v>
       </c>
       <c r="F71" t="str">
-        <v>骨代謝回転の亢進、骨形成促進薬による治療効果</v>
+        <v>骨代謝回転の亢進（骨粗鬆症など）</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>骨形成の低下</v>
+        <v>骨吸収抑制薬による治療効果</v>
       </c>
       <c r="I71" t="str">
         <v/>
       </c>
       <c r="J71" t="str">
-        <v>TRACP-5b等「骨を壊す側」の指標とは逆の、「骨を作る側」の指標。骨形成促進薬（テリパラチド等）の効果判定に使われる</v>
+        <v>NTX・CTXと同じ「骨を壊す側」の指標。食事の影響を受けにくいとされる</v>
       </c>
       <c r="K71" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="L71" t="str">
-        <v>P1NP,骨形成マーカー</v>
+        <v>DPD,デオキシピリジノリン,骨吸収マーカー</v>
       </c>
       <c r="M71" t="str">
         <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
@@ -3335,122 +3335,122 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>抗甲状腺マイクロゾーム抗体（抗TPO抗体）</v>
+        <v>CTX</v>
       </c>
       <c r="B72" t="str">
-        <v>TPOAb</v>
+        <v>CTX</v>
       </c>
       <c r="C72" t="str">
-        <v>陰性（16 IU/mL未満程度、施設差あり）</v>
+        <v>施設差が大きく一律の記載が難しい（血清・尿中）</v>
       </c>
       <c r="D72" t="str">
-        <v>自分の甲状腺を攻撃する抗体が出ていないかを見る検査</v>
+        <v>骨のコラーゲンが壊れるときに出る、骨吸収マーカーのひとつ</v>
       </c>
       <c r="E72" t="str">
-        <v>この検査は、体の中に自分の甲状腺を誤って攻撃してしまう抗体がないかを見るものです。陽性の場合、橋本病（慢性甲状腺炎）など甲状腺の自己免疫的な炎症が背景にある可能性があります。</v>
+        <v>CTXも、骨が壊されるときに血液や尿に出てくる物質です。骨粗鬆症治療薬（骨を壊すのを抑える薬）の効果を確認するために使われます。</v>
       </c>
       <c r="F72" t="str">
-        <v>橋本病（慢性甲状腺炎）、バセドウ病などの自己免疫性甲状腺疾患</v>
+        <v>骨代謝回転の亢進（骨粗鬆症など）</v>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" t="str">
-        <v/>
+        <v>骨吸収抑制薬による治療効果</v>
       </c>
       <c r="I72" t="str">
         <v/>
       </c>
       <c r="J72" t="str">
-        <v>陽性でも必ずしも甲状腺機能異常があるとは限らない。TSH・FT4など甲状腺ホルモンの数値と合わせて評価する</v>
+        <v>NTX・DPDと同じ「骨を壊す側」の指標。血清・尿中いずれでも測定されることがある</v>
       </c>
       <c r="K72" t="str">
-        <v>甲状腺疾患</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="L72" t="str">
-        <v>抗TPO抗体,抗甲状腺マイクロゾーム抗体,TPOAb,橋本病</v>
+        <v>CTX,骨吸収マーカー</v>
       </c>
       <c r="M72" t="str">
-        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>抗サイログロブリン抗体</v>
+        <v>P1NP</v>
       </c>
       <c r="B73" t="str">
-        <v>TgAb</v>
+        <v>P1NP</v>
       </c>
       <c r="C73" t="str">
-        <v>陰性（28 IU/mL未満程度、施設差あり）</v>
+        <v>施設差が大きく一律の記載が難しい（血清）</v>
       </c>
       <c r="D73" t="str">
-        <v>甲状腺のたんぱく質（サイログロブリン）への抗体が出ていないかを見る検査</v>
+        <v>骨が新しく作られるときに出る、骨形成マーカーのひとつ</v>
       </c>
       <c r="E73" t="str">
-        <v>この検査も、抗TPO抗体と同じく、甲状腺に対する自己免疫の有無を見るものです。あわせて調べることで橋本病などの診断の参考にします。</v>
+        <v>P1NPは、CTXなどとは逆に、骨が新しく作られるときに血液中に出てくる物質です。骨を作る力を高める薬（テリパラチドなど）の効果を確認するために使われます。</v>
       </c>
       <c r="F73" t="str">
-        <v>橋本病（慢性甲状腺炎）、バセドウ病などの自己免疫性甲状腺疾患</v>
+        <v>骨代謝回転の亢進、骨形成促進薬による治療効果</v>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v/>
+        <v>骨形成の低下</v>
       </c>
       <c r="I73" t="str">
         <v/>
       </c>
       <c r="J73" t="str">
-        <v>抗TPO抗体とあわせて測定されることが多い。単独の高値だけで治療方針が決まるわけではない</v>
+        <v>TRACP-5b等「骨を壊す側」の指標とは逆の、「骨を作る側」の指標。骨形成促進薬（テリパラチド等）の効果判定に使われる</v>
       </c>
       <c r="K73" t="str">
-        <v>甲状腺疾患</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="L73" t="str">
-        <v>抗サイログロブリン抗体,TgAb,橋本病</v>
+        <v>P1NP,骨形成マーカー</v>
       </c>
       <c r="M73" t="str">
-        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>TSH（甲状腺刺激ホルモン）</v>
+        <v>抗甲状腺マイクロゾーム抗体（抗TPO抗体）</v>
       </c>
       <c r="B74" t="str">
-        <v>TSH</v>
+        <v>TPOAb</v>
       </c>
       <c r="C74" t="str">
-        <v>0.5〜5.0 μIU/mL程度（施設差あり）</v>
+        <v>陰性（16 IU/mL未満程度、施設差あり）</v>
       </c>
       <c r="D74" t="str">
-        <v>甲状腺の働きが多いか少ないかを最も敏感に反映するホルモン</v>
+        <v>自分の甲状腺を攻撃する抗体が出ていないかを見る検査</v>
       </c>
       <c r="E74" t="str">
-        <v>TSHは脳の下垂体から出て、甲状腺に「もっと働いて」と指令を送るホルモンです。甲状腺の働きが弱っていると体が指令を強めるためTSHは上がり、逆に甲状腺が働きすぎているとTSHは下がります。甲状腺の状態を最初に確認する数値としてよく使われます。</v>
+        <v>この検査は、体の中に自分の甲状腺を誤って攻撃してしまう抗体がないかを見るものです。陽性の場合、橋本病（慢性甲状腺炎）など甲状腺の自己免疫的な炎症が背景にある可能性があります。</v>
       </c>
       <c r="F74" t="str">
-        <v>甲状腺機能低下症（橋本病など）、チラーヂンSなど甲状腺ホルモン薬の量不足</v>
+        <v>橋本病（慢性甲状腺炎）、バセドウ病などの自己免疫性甲状腺疾患</v>
       </c>
       <c r="G74" t="str">
-        <v>だるさ、むくみ、体重増加、寒がりなどの症状がないか確認する。服薬状況（飲み忘れ、他の薬との飲み合わせ）を確認する</v>
+        <v/>
       </c>
       <c r="H74" t="str">
-        <v>甲状腺機能亢進症（バセドウ病など）、チラーヂンSなど甲状腺ホルモン薬の過量</v>
+        <v/>
       </c>
       <c r="I74" t="str">
-        <v>動悸、体重減少、暑がり、手のふるえなどの症状がないか確認する</v>
+        <v/>
       </c>
       <c r="J74" t="str">
-        <v>チラーヂンS服用中はTSHが治療目標域に収まっているかで用量調整の目安にする。メルカゾール服用中はTSH・FT4に加えて無顆粒球症の初期症状（発熱・のどの痛み）の有無や白血球数も確認する</v>
+        <v>陽性でも必ずしも甲状腺機能異常があるとは限らない。TSH・FT4など甲状腺ホルモンの数値と合わせて評価する</v>
       </c>
       <c r="K74" t="str">
         <v>甲状腺疾患</v>
       </c>
       <c r="L74" t="str">
-        <v>TSH,甲状腺刺激ホルモン,甲状腺機能,橋本病,バセドウ病,チラーヂン,メルカゾール</v>
+        <v>抗TPO抗体,抗甲状腺マイクロゾーム抗体,TPOAb,橋本病</v>
       </c>
       <c r="M74" t="str">
         <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
@@ -3458,40 +3458,40 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>FT4（遊離サイロキシン）</v>
+        <v>抗サイログロブリン抗体</v>
       </c>
       <c r="B75" t="str">
-        <v>FT4</v>
+        <v>TgAb</v>
       </c>
       <c r="C75" t="str">
-        <v>0.9〜1.7 ng/dL程度（施設差あり）</v>
+        <v>陰性（28 IU/mL未満程度、施設差あり）</v>
       </c>
       <c r="D75" t="str">
-        <v>甲状腺が実際に分泌しているホルモンの量そのものを表す数値</v>
+        <v>甲状腺のたんぱく質（サイログロブリン）への抗体が出ていないかを見る検査</v>
       </c>
       <c r="E75" t="str">
-        <v>FT4は甲状腺そのものが作っているホルモンの量です。TSHが「指令の強さ」だとすると、FT4は「実際に出ている量」にあたります。2つをあわせて見ることで、甲状腺の働きが今どういう状態かを詳しく判断できます。</v>
+        <v>この検査も、抗TPO抗体と同じく、甲状腺に対する自己免疫の有無を見るものです。あわせて調べることで橋本病などの診断の参考にします。</v>
       </c>
       <c r="F75" t="str">
-        <v>甲状腺機能亢進症（バセドウ病など）</v>
+        <v>橋本病（慢性甲状腺炎）、バセドウ病などの自己免疫性甲状腺疾患</v>
       </c>
       <c r="G75" t="str">
-        <v>動悸、体重減少、暑がり、手のふるえなどの症状がないか確認する</v>
+        <v/>
       </c>
       <c r="H75" t="str">
-        <v>甲状腺機能低下症（橋本病など）</v>
+        <v/>
       </c>
       <c r="I75" t="str">
-        <v>だるさ、むくみ、体重増加、寒がりなどの症状がないか確認する</v>
+        <v/>
       </c>
       <c r="J75" t="str">
-        <v>TSHと逆方向に動くのが基本だが、下垂体性の異常など例外もある。TSHと合わせて評価し、片方だけで判断しない</v>
+        <v>抗TPO抗体とあわせて測定されることが多い。単独の高値だけで治療方針が決まるわけではない</v>
       </c>
       <c r="K75" t="str">
         <v>甲状腺疾患</v>
       </c>
       <c r="L75" t="str">
-        <v>FT4,遊離サイロキシン,甲状腺ホルモン,甲状腺機能</v>
+        <v>抗サイログロブリン抗体,TgAb,橋本病</v>
       </c>
       <c r="M75" t="str">
         <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
@@ -3804,42 +3804,42 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>脂質異常症</v>
+        <v>精神疾患（非定型抗精神病薬）</v>
       </c>
       <c r="B3" t="str">
         <v/>
       </c>
       <c r="C3" t="str">
-        <v>揚げ物や脂っこい食事、間食の頻度はどれくらいですか／運動の習慣はありますか／お薬の飲み忘れはどのくらいありますか</v>
+        <v>体重の増減はありませんか／のどの渇きや尿量の変化はありませんか／だるさや動きにくさが増えていませんか</v>
       </c>
       <c r="D3" t="str">
-        <v>【悪化した時】食事や運動で最近変わったことはありますか。一緒に見直してみましょう　【改善した時】数値が良くなってきています。今の生活習慣を続けていきましょう</v>
+        <v>【体重増加や口渇がある時】念のため血糖や脂質の数値を確認しますね　【安定している時】今のところ大きな変化はなさそうです</v>
       </c>
       <c r="E3" t="str">
-        <v>LDLの目標値は既往疾患（冠動脈疾患・糖尿病など）によって異なる。スタチンの副作用（筋肉痛・脱力感）の有無</v>
+        <v>非定型抗精神病薬（アリピプラゾール、クエチアピン、リスペリドン等）による代謝異常（高血糖・脂質異常・体重増加）は自覚症状に乏しく、定期的な血糖・脂質・肝機能のチェックが重要なこと。糖尿病がある場合オランザピン・クエチアピンは原則禁忌</v>
       </c>
       <c r="F3" t="str">
-        <v>食事と栄養 p.132-150（第2部 脂質異常症 Q27-40）</v>
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>精神疾患（非定型抗精神病薬）</v>
+        <v>腎機能</v>
       </c>
       <c r="B4" t="str">
         <v/>
       </c>
       <c r="C4" t="str">
-        <v>体重の増減はありませんか／のどの渇きや尿量の変化はありませんか／だるさや動きにくさが増えていませんか</v>
+        <v>足のむくみやだるさが増えていませんか／尿の量や回数に変化はありませんか／血圧の薬や痛み止めを新しく使い始めていませんか</v>
       </c>
       <c r="D4" t="str">
-        <v>【体重増加や口渇がある時】念のため血糖や脂質の数値を確認しますね　【安定している時】今のところ大きな変化はなさそうです</v>
+        <v>【数値が悪化した時】お薬の量や飲み合わせを一度確認しますね。むくみや体重の変化はありませんか　【数値が安定している時】今のペースを維持できています。水分の摂り方や塩分は今のままで大丈夫そうです</v>
       </c>
       <c r="E4" t="str">
-        <v>非定型抗精神病薬（アリピプラゾール、クエチアピン、リスペリドン等）による代謝異常（高血糖・脂質異常・体重増加）は自覚症状に乏しく、定期的な血糖・脂質・肝機能のチェックが重要なこと。糖尿病がある場合オランザピン・クエチアピンは原則禁忌</v>
+        <v>腎排泄型薬剤の用量調整が必要ないか。NSAIDsや造影剤など腎機能に影響する薬剤の使用歴。脱水を起こしやすい状況（下痢・嘔吐・猛暑）がないか</v>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>食事と栄養 p.190-215（第2部 尿路結石 Q70-77／腎機能低下 Q78-89）</v>
       </c>
     </row>
     <row r="5">
@@ -3864,79 +3864,79 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>腎機能</v>
+        <v>抗凝固療法（心房細動・血栓症）</v>
       </c>
       <c r="B6" t="str">
         <v/>
       </c>
       <c r="C6" t="str">
-        <v>足のむくみやだるさが増えていませんか／尿の量や回数に変化はありませんか／血圧の薬や痛み止めを新しく使い始めていませんか</v>
+        <v>あざや出血が増えていませんか／歯ぐきや鼻からの出血、黒っぽい便はありませんか／新しく始めたお薬やサプリメント、納豆・青汁の摂取に変化はありませんか</v>
       </c>
       <c r="D6" t="str">
-        <v>【数値が悪化した時】お薬の量や飲み合わせを一度確認しますね。むくみや体重の変化はありませんか　【数値が安定している時】今のペースを維持できています。水分の摂り方や塩分は今のままで大丈夫そうです</v>
+        <v>【出血傾向がある時】念のため出血の状況を詳しく確認させてください　【安定している時】今のところ大きな変化はなさそうです。飲み合わせだけ念のため確認しますね</v>
       </c>
       <c r="E6" t="str">
-        <v>腎排泄型薬剤の用量調整が必要ないか。NSAIDsや造影剤など腎機能に影響する薬剤の使用歴。脱水を起こしやすい状況（下痢・嘔吐・猛暑）がないか</v>
+        <v>ワルファリンはPT-INRのモニタリングと納豆・ビタミンK摂取の変動に注意。DOAC（エリキュース、リクシアナ、プラザキサ等）は腎排泄が多く腎機能低下時の用量調整が必要。NSAIDsとの併用による出血リスク増大</v>
       </c>
       <c r="F6" t="str">
-        <v>食事と栄養 p.190-215（第2部 尿路結石 Q70-77／腎機能低下 Q78-89）</v>
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>肝機能</v>
+        <v>高尿酸血症</v>
       </c>
       <c r="B7" t="str">
         <v/>
       </c>
       <c r="C7" t="str">
-        <v>お酒を飲む量や頻度に変化はありますか／新しく始めたお薬やサプリメントはありますか／だるさや黄疸（白目や皮膚が黄色くなること）のような症状はありませんか</v>
+        <v>お酒（特にビール）を飲む量はどれくらいですか／プリン体の多い食品（レバー・魚卵・干物など）をよく摂りますか／関節の痛みや腫れが出たことはありますか</v>
       </c>
       <c r="D7" t="str">
-        <v>【悪化した時】最近、お酒の量やお薬で変わったことはありますか。少し肝臓に負担がかかっているようです　【改善した時】数値が落ち着いてきています。今の生活を続けていきましょう</v>
+        <v>【悪化した時】最近、お酒や食事で変わったことはありますか。水分を多めに摂ることも意識してみてください　【改善した時】数値が落ち着いています。今のペースを続けましょう</v>
       </c>
       <c r="E7" t="str">
-        <v>新規開始薬剤による薬剤性肝障害の可能性。市販薬・サプリメント・健康食品の使用歴。飲酒量の申告は過小になりやすい</v>
+        <v>尿酸降下薬を急に開始・増量すると痛風発作が誘発されることがある。水分摂取量、尿路結石の既往</v>
       </c>
       <c r="F7" t="str">
-        <v/>
+        <v>食事と栄養 p.180-189（第2部 痛風・高尿酸血症 Q61-69）</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>抗凝固療法（心房細動・血栓症）</v>
+        <v>電解質</v>
       </c>
       <c r="B8" t="str">
         <v/>
       </c>
       <c r="C8" t="str">
-        <v>あざや出血が増えていませんか／歯ぐきや鼻からの出血、黒っぽい便はありませんか／新しく始めたお薬やサプリメント、納豆・青汁の摂取に変化はありませんか</v>
+        <v>下痢や嘔吐、大量の汗をかくことはありましたか／お通じの薬や利尿薬を新しく使い始めていませんか／脱力感やしびれ、動悸はありませんか</v>
       </c>
       <c r="D8" t="str">
-        <v>【出血傾向がある時】念のため出血の状況を詳しく確認させてください　【安定している時】今のところ大きな変化はなさそうです。飲み合わせだけ念のため確認しますね</v>
+        <v>【悪化した時】最近、体調やお薬で変わったことはありますか。むくみや脱力感はありませんか　【改善した時】数値は落ち着いています。水分やお食事は今のままで大丈夫そうです</v>
       </c>
       <c r="E8" t="str">
-        <v>ワルファリンはPT-INRのモニタリングと納豆・ビタミンK摂取の変動に注意。DOAC（エリキュース、リクシアナ、プラザキサ等）は腎排泄が多く腎機能低下時の用量調整が必要。NSAIDsとの併用による出血リスク増大</v>
+        <v>利尿薬・下剤・NSAIDsなど電解質に影響する薬剤の併用。高カリウム血症は自覚症状に乏しく数値での早期発見が重要</v>
       </c>
       <c r="F8" t="str">
-        <v/>
+        <v>食事と栄養 p.72（カリウム）・p.81（ナトリウム）／p.199-215（第2部 腎機能低下 Q80-82）</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>抗血小板療法</v>
+        <v>肝機能</v>
       </c>
       <c r="B9" t="str">
         <v/>
       </c>
       <c r="C9" t="str">
-        <v>あざや出血が増えていませんか／歯ぐきの出血や鼻血が出やすくなっていませんか／手術や抜歯の予定はありませんか</v>
+        <v>お酒を飲む量や頻度に変化はありますか／新しく始めたお薬やサプリメントはありますか／だるさや黄疸（白目や皮膚が黄色くなること）のような症状はありませんか</v>
       </c>
       <c r="D9" t="str">
-        <v>【出血傾向がある時】あざや出血の状況を詳しく確認させてください　【安定している時】今のところ大きな変化はなさそうです</v>
+        <v>【悪化した時】最近、お酒の量やお薬で変わったことはありますか。少し肝臓に負担がかかっているようです　【改善した時】数値が落ち着いてきています。今の生活を続けていきましょう</v>
       </c>
       <c r="E9" t="str">
-        <v>手術・抜歯前の休薬指示の有無（自己判断で中止しないよう説明）。他の抗血小板薬・抗凝固薬・NSAIDsとの併用による出血リスク増大</v>
+        <v>新規開始薬剤による薬剤性肝障害の可能性。市販薬・サプリメント・健康食品の使用歴。飲酒量の申告は過小になりやすい</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -3944,62 +3944,62 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>高尿酸血症</v>
+        <v>てんかん</v>
       </c>
       <c r="B10" t="str">
         <v/>
       </c>
       <c r="C10" t="str">
-        <v>お酒（特にビール）を飲む量はどれくらいですか／プリン体の多い食品（レバー・魚卵・干物など）をよく摂りますか／関節の痛みや腫れが出たことはありますか</v>
+        <v>発作の頻度や様子に変化はありますか／めまい・ふらつき・眠気が強く出ていませんか／お薬を飲み忘れることはありますか</v>
       </c>
       <c r="D10" t="str">
-        <v>【悪化した時】最近、お酒や食事で変わったことはありますか。水分を多めに摂ることも意識してみてください　【改善した時】数値が落ち着いています。今のペースを続けましょう</v>
+        <v>【発作が増えた時】飲み忘れや体調の変化がなかったか一緒に確認しましょう　【安定している時】今の血中濃度・量が体に合っているようです。このまま続けましょう</v>
       </c>
       <c r="E10" t="str">
-        <v>尿酸降下薬を急に開始・増量すると痛風発作が誘発されることがある。水分摂取量、尿路結石の既往</v>
+        <v>治療域が狭く、少量の飲み忘れや併用薬の変化で血中濃度が大きく動くこと。カルバマゼピン・バルプロ酸は肝障害や血球減少（白血球・血小板）の定期チェックが必要なこと。眠気を伴う他剤との併用</v>
       </c>
       <c r="F10" t="str">
-        <v>食事と栄養 p.180-189（第2部 痛風・高尿酸血症 Q61-69）</v>
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>てんかん</v>
+        <v>脂質異常症</v>
       </c>
       <c r="B11" t="str">
         <v/>
       </c>
       <c r="C11" t="str">
-        <v>発作の頻度や様子に変化はありますか／めまい・ふらつき・眠気が強く出ていませんか／お薬を飲み忘れることはありますか</v>
+        <v>揚げ物や脂っこい食事、間食の頻度はどれくらいですか／運動の習慣はありますか／お薬の飲み忘れはどのくらいありますか</v>
       </c>
       <c r="D11" t="str">
-        <v>【発作が増えた時】飲み忘れや体調の変化がなかったか一緒に確認しましょう　【安定している時】今の血中濃度・量が体に合っているようです。このまま続けましょう</v>
+        <v>【悪化した時】食事や運動で最近変わったことはありますか。一緒に見直してみましょう　【改善した時】数値が良くなってきています。今の生活習慣を続けていきましょう</v>
       </c>
       <c r="E11" t="str">
-        <v>治療域が狭く、少量の飲み忘れや併用薬の変化で血中濃度が大きく動くこと。カルバマゼピン・バルプロ酸は肝障害や血球減少（白血球・血小板）の定期チェックが必要なこと。眠気を伴う他剤との併用</v>
+        <v>LDLの目標値は既往疾患（冠動脈疾患・糖尿病など）によって異なる。スタチンの副作用（筋肉痛・脱力感）の有無</v>
       </c>
       <c r="F11" t="str">
-        <v/>
+        <v>食事と栄養 p.132-150（第2部 脂質異常症 Q27-40）</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>心不全</v>
+        <v>甲状腺疾患</v>
       </c>
       <c r="B12" t="str">
         <v/>
       </c>
       <c r="C12" t="str">
-        <v>階段や坂道で息切れしやすくなっていませんか／足や靴がきつくなるようなむくみはありませんか／体重は増えていませんか／夜、横になると苦しくて起き上がることはありませんか</v>
+        <v>動悸や体重の増減はありませんか／だるさやむくみ、逆に暑がり・手のふるえはありませんか／薬の量が変わってから体調の変化はありますか</v>
       </c>
       <c r="D12" t="str">
-        <v>【数値が悪化した時】少し心臓に負担がかかっているサインかもしれません。むくみや体重の増減はありましたか　【数値が安定している時】今のところ落ち着いています。塩分と水分のとり方は今のままで大丈夫そうです</v>
+        <v>【機能低下気味の時】だるさやむくみはありませんか。お薬の量を確認しますね　【機能亢進気味の時】動悸や体重減少はありませんか。念のため数値を確認しましょう</v>
       </c>
       <c r="E12" t="str">
-        <v>体重の日々の変化（急な増加は水分貯留のサイン）。塩分・水分制限の理解度。NSAIDsなど心不全を悪化させうる薬剤の使用</v>
+        <v>チラーヂンSは食後だと吸収が落ちやすく、起床時空腹での服用が基本であること。メルカゾールは無顆粒球症の初期症状（発熱・のどの痛み）が出たらすぐ受診が必要なこと</v>
       </c>
       <c r="F12" t="str">
-        <v>食事と栄養 p.216-222（第2部 心疾患 Q90-94）</v>
+        <v>食事と栄養 p.224-228（第2部 甲状腺疾患 Q95-98）</v>
       </c>
     </row>
     <row r="13">
@@ -4024,42 +4024,42 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>甲状腺疾患</v>
+        <v>抗血小板療法</v>
       </c>
       <c r="B14" t="str">
         <v/>
       </c>
       <c r="C14" t="str">
-        <v>動悸や体重の増減はありませんか／だるさやむくみ、逆に暑がり・手のふるえはありませんか／薬の量が変わってから体調の変化はありますか</v>
+        <v>あざや出血が増えていませんか／歯ぐきの出血や鼻血が出やすくなっていませんか／手術や抜歯の予定はありませんか</v>
       </c>
       <c r="D14" t="str">
-        <v>【機能低下気味の時】だるさやむくみはありませんか。お薬の量を確認しますね　【機能亢進気味の時】動悸や体重減少はありませんか。念のため数値を確認しましょう</v>
+        <v>【出血傾向がある時】あざや出血の状況を詳しく確認させてください　【安定している時】今のところ大きな変化はなさそうです</v>
       </c>
       <c r="E14" t="str">
-        <v>チラーヂンSは食後だと吸収が落ちやすく、起床時空腹での服用が基本であること。メルカゾールは無顆粒球症の初期症状（発熱・のどの痛み）が出たらすぐ受診が必要なこと</v>
+        <v>手術・抜歯前の休薬指示の有無（自己判断で中止しないよう説明）。他の抗血小板薬・抗凝固薬・NSAIDsとの併用による出血リスク増大</v>
       </c>
       <c r="F14" t="str">
-        <v>食事と栄養 p.224-228（第2部 甲状腺疾患 Q95-98）</v>
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>電解質</v>
+        <v>心不全</v>
       </c>
       <c r="B15" t="str">
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>下痢や嘔吐、大量の汗をかくことはありましたか／お通じの薬や利尿薬を新しく使い始めていませんか／脱力感やしびれ、動悸はありませんか</v>
+        <v>階段や坂道で息切れしやすくなっていませんか／足や靴がきつくなるようなむくみはありませんか／体重は増えていませんか／夜、横になると苦しくて起き上がることはありませんか</v>
       </c>
       <c r="D15" t="str">
-        <v>【悪化した時】最近、体調やお薬で変わったことはありますか。むくみや脱力感はありませんか　【改善した時】数値は落ち着いています。水分やお食事は今のままで大丈夫そうです</v>
+        <v>【数値が悪化した時】少し心臓に負担がかかっているサインかもしれません。むくみや体重の増減はありましたか　【数値が安定している時】今のところ落ち着いています。塩分と水分のとり方は今のままで大丈夫そうです</v>
       </c>
       <c r="E15" t="str">
-        <v>利尿薬・下剤・NSAIDsなど電解質に影響する薬剤の併用。高カリウム血症は自覚症状に乏しく数値での早期発見が重要</v>
+        <v>体重の日々の変化（急な増加は水分貯留のサイン）。塩分・水分制限の理解度。NSAIDsなど心不全を悪化させうる薬剤の使用</v>
       </c>
       <c r="F15" t="str">
-        <v>食事と栄養 p.72（カリウム）・p.81（ナトリウム）／p.199-215（第2部 腎機能低下 Q80-82）</v>
+        <v>食事と栄養 p.216-222（第2部 心疾患 Q90-94）</v>
       </c>
     </row>
   </sheetData>

--- a/検査値リファレンス初期データ.xlsx
+++ b/検査値リファレンス初期データ.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M81"/>
+  <dimension ref="A1:M83"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -3704,48 +3704,130 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
+        <v>黄疸</v>
+      </c>
+      <c r="B81" t="str">
+        <v>黄疸,Jaundice</v>
+      </c>
+      <c r="C81" t="str">
+        <v>所見なし（皮膚・眼球結膜の黄染がなければ正常）</v>
+      </c>
+      <c r="D81" t="str">
+        <v>ビリルビンが体にたまり、皮膚や白目が黄色くなる状態。単独の検査値ではなく、ビリルビン上昇によって表れる身体所見</v>
+      </c>
+      <c r="E81" t="str">
+        <v>黄疸は、体の中にビリルビンという黄色い色素がたまることで、皮膚や白目が黄色く見える状態です。肝臓や胆道のトラブル、赤血球が壊れやすくなる病気（溶血）などが原因となります。</v>
+      </c>
+      <c r="F81" t="str">
+        <v>肝炎・肝硬変などの肝疾患、胆石・腫瘍による胆道閉塞、溶血性疾患、体質性黄疸（ジルベール症候群）、新生児黄疸</v>
+      </c>
+      <c r="G81" t="str">
+        <v>白目や皮膚の黄染に気づいたら、尿の色（濃い茶色）や便の色（白っぽい）の変化も確認し、早めの受診を勧める</v>
+      </c>
+      <c r="H81" t="str">
+        <v/>
+      </c>
+      <c r="I81" t="str">
+        <v/>
+      </c>
+      <c r="J81" t="str">
+        <v>黄疸は検査値そのものではなく身体所見。原因を調べる際は総ビリルビン・直接ビリルビン・間接ビリルビンの内訳とAST/ALT/γ-GTPを確認する。直接優位なら胆道系、間接優位なら溶血・体質性を疑う</v>
+      </c>
+      <c r="K81" t="str">
+        <v>肝機能</v>
+      </c>
+      <c r="L81" t="str">
+        <v>黄疸,ジョンダイス,Jaundice,ビリルビン,皮膚黄染,白目</v>
+      </c>
+      <c r="M81" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>溶血</v>
+      </c>
+      <c r="B82" t="str">
+        <v>溶血,Hemolysis</v>
+      </c>
+      <c r="C82" t="str">
+        <v>所見なし（溶血を示唆する検査値異常がなければ正常）</v>
+      </c>
+      <c r="D82" t="str">
+        <v>赤血球が通常より早く壊れる状態。単独の検査値ではなく、複数の検査値の組み合わせで疑う病態</v>
+      </c>
+      <c r="E82" t="str">
+        <v>溶血とは、赤血球が通常よりも早いペースで壊れてしまう状態のことです。壊れた赤血球からビリルビンなどが放出されるため、貧血や黄疸の原因になることがあります。</v>
+      </c>
+      <c r="F82" t="str">
+        <v>自己免疫性溶血性貧血、血液型不適合輸血、G6PD欠損症などの遺伝性疾患、機械弁など人工物による物理的破壊、薬剤性溶血</v>
+      </c>
+      <c r="G82" t="str">
+        <v>倦怠感、黄疸、尿の色が濃くなるなどの症状がないか確認する</v>
+      </c>
+      <c r="H82" t="str">
+        <v/>
+      </c>
+      <c r="I82" t="str">
+        <v/>
+      </c>
+      <c r="J82" t="str">
+        <v>溶血を疑う際は、間接ビリルビン上昇・LDH上昇・ハプトグロビン低下・網状赤血球増加のパターンを確認する。ヘモグロビン・MCV・MCHCの変化と合わせて総合的に判断する</v>
+      </c>
+      <c r="K82" t="str">
+        <v>鉄欠乏性貧血</v>
+      </c>
+      <c r="L82" t="str">
+        <v>溶血,Hemolysis,溶血性貧血,G6PD,ハプトグロビン</v>
+      </c>
+      <c r="M82" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
         <v>CRP</v>
       </c>
-      <c r="B81" t="str">
+      <c r="B83" t="str">
         <v>CRP</v>
       </c>
-      <c r="C81" t="str">
+      <c r="C83" t="str">
         <v>0.3 mg/dL未満（施設差あり）</v>
       </c>
-      <c r="D81" t="str">
+      <c r="D83" t="str">
         <v>体のどこかに炎症や感染が起きていないかを鋭敏に反映する数値</v>
       </c>
-      <c r="E81" t="str">
+      <c r="E83" t="str">
         <v>CRPは、体に炎症や感染が起きると数時間〜半日程度で急激に上昇する数値です。風邪のようなウイルス感染から細菌感染、体のどこかの炎症まで、幅広く反応するため、体調の変化を早期に捉える手がかりになります。</v>
       </c>
-      <c r="F81" t="str">
+      <c r="F83" t="str">
         <v>細菌感染症、ウイルス感染症、自己免疫疾患（関節リウマチなど）、悪性腫瘍、組織の損傷（術後・心筋梗塞など）</v>
       </c>
-      <c r="G81" t="str">
+      <c r="G83" t="str">
         <v>発熱、痛み、腫れなど炎症症状の有無を確認する</v>
       </c>
-      <c r="H81" t="str">
-        <v/>
-      </c>
-      <c r="I81" t="str">
-        <v/>
-      </c>
-      <c r="J81" t="str">
+      <c r="H83" t="str">
+        <v/>
+      </c>
+      <c r="I83" t="str">
+        <v/>
+      </c>
+      <c r="J83" t="str">
         <v>白血球数と合わせて感染・炎症の程度を評価する。上昇・低下のタイミングは白血球より半日〜1日程度遅れる傾向があるため、経過を追う際は採血のタイミングに注意</v>
       </c>
-      <c r="K81" t="str">
-        <v/>
-      </c>
-      <c r="L81" t="str">
+      <c r="K83" t="str">
+        <v/>
+      </c>
+      <c r="L83" t="str">
         <v>CRP,炎症,感染</v>
       </c>
-      <c r="M81" t="str">
+      <c r="M83" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M81"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M83"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/検査値リファレンス初期データ.xlsx
+++ b/検査値リファレンス初期データ.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M83"/>
+  <dimension ref="A1:M92"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -3786,48 +3786,417 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
+        <v>乳び</v>
+      </c>
+      <c r="B83" t="str">
+        <v>乳び,Lipemia</v>
+      </c>
+      <c r="C83" t="str">
+        <v>所見なし（血清が白濁していなければ正常）</v>
+      </c>
+      <c r="D83" t="str">
+        <v>中性脂肪が非常に多いため、血清が白く濁って見える状態。検査値そのものではなく検体の外観所見</v>
+      </c>
+      <c r="E83" t="str">
+        <v>乳びとは、血液中の中性脂肪が非常に多いために、採血した血液（血清）が白く濁って見える状態のことです。多くの場合、食後の採血や、著しい脂質異常症が背景にあります。</v>
+      </c>
+      <c r="F83" t="str">
+        <v>著しい高中性脂肪血症、食後採血（一時的なもの）、原発性高カイロミクロン血症などの脂質代謝異常</v>
+      </c>
+      <c r="G83" t="str">
+        <v>採血が空腹時だったかを確認する。食後採血であれば次回は空腹時の再検を提案する</v>
+      </c>
+      <c r="H83" t="str">
+        <v/>
+      </c>
+      <c r="I83" t="str">
+        <v/>
+      </c>
+      <c r="J83" t="str">
+        <v>血清の白濁により一部の検査項目（電解質など）の測定値に誤差が出ることがある（偽性低ナトリウム血症など）。中性脂肪値と合わせて評価する</v>
+      </c>
+      <c r="K83" t="str">
+        <v>脂質異常症</v>
+      </c>
+      <c r="L83" t="str">
+        <v>乳び,乳び血清,Lipemia,高中性脂肪血症</v>
+      </c>
+      <c r="M83" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>亜鉛（Zn）</v>
+      </c>
+      <c r="B84" t="str">
+        <v>Zn</v>
+      </c>
+      <c r="C84" t="str">
+        <v>80〜130 μg/dL程度（施設差あり）</v>
+      </c>
+      <c r="D84" t="str">
+        <v>味覚や皮膚、免疫に関わる微量ミネラル。高齢者や低栄養で不足しやすい</v>
+      </c>
+      <c r="E84" t="str">
+        <v>亜鉛は、味を感じる働きや皮膚・粘膜の健康、免疫の働きに関わる微量ミネラルです。不足すると、味がわかりにくくなったり（味覚障害）、傷が治りにくくなったりすることがあります。</v>
+      </c>
+      <c r="F84" t="str">
+        <v/>
+      </c>
+      <c r="G84" t="str">
+        <v/>
+      </c>
+      <c r="H84" t="str">
+        <v>低栄養、高齢による摂取不足、消化器手術後、亜鉛の吸収を妨げる薬剤（PPI、キレート形成する薬剤など）との併用</v>
+      </c>
+      <c r="I84" t="str">
+        <v>味覚の変化（味を感じにくい、金属味がするなど）がないか確認する。牡蠣、赤身肉、レバーなど亜鉛を多く含む食品を意識するとよいことを伝える</v>
+      </c>
+      <c r="J84" t="str">
+        <v>薬剤性の亜鉛欠乏（PPI長期使用、D-ペニシラミン、一部の降圧薬など）に注意。亜鉛欠乏による味覚障害は原因薬剤の中止・亜鉛補充で改善することがある</v>
+      </c>
+      <c r="K84" t="str">
+        <v/>
+      </c>
+      <c r="L84" t="str">
+        <v>亜鉛,Zn,味覚障害,亜鉛欠乏</v>
+      </c>
+      <c r="M84" t="str">
+        <v>食事と栄養 p.78（亜鉛）</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>マグネシウム（Mg）</v>
+      </c>
+      <c r="B85" t="str">
+        <v>Mg</v>
+      </c>
+      <c r="C85" t="str">
+        <v>1.8〜2.6 mg/dL程度（施設差あり）</v>
+      </c>
+      <c r="D85" t="str">
+        <v>骨や筋肉、神経の働きに関わるミネラル。低栄養や利尿薬で不足しやすい</v>
+      </c>
+      <c r="E85" t="str">
+        <v>マグネシウムは、骨や筋肉、神経の働きを支えるミネラルです。不足すると、こむら返りや不整脈、だるさなどの症状が出ることがあります。</v>
+      </c>
+      <c r="F85" t="str">
+        <v>腎不全、マグネシウム製剤（酸化マグネシウムなど）の過量投与</v>
+      </c>
+      <c r="G85" t="str">
+        <v>腎機能低下がある患者で酸化マグネシウムなどの緩下剤を使用中は、傾眠・血圧低下などの高マグネシウム血症の症状がないか確認する</v>
+      </c>
+      <c r="H85" t="str">
+        <v>低栄養、利尿薬の使用、慢性的な下痢、アルコール多飲、PPI長期使用</v>
+      </c>
+      <c r="I85" t="str">
+        <v>こむら返りや動悸などの症状がないか確認する</v>
+      </c>
+      <c r="J85" t="str">
+        <v>腎機能低下患者への酸化マグネシウム投与は高マグネシウム血症のリスクがあるため定期的なモニタリングが必要。PPI長期使用も低マグネシウム血症のリスク因子として知られる</v>
+      </c>
+      <c r="K85" t="str">
+        <v>腎機能</v>
+      </c>
+      <c r="L85" t="str">
+        <v>マグネシウム,Mg,酸化マグネシウム,こむら返り</v>
+      </c>
+      <c r="M85" t="str">
+        <v>食事と栄養 p.84（マグネシウム）</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>乳酸脱水素酵素（LDH）</v>
+      </c>
+      <c r="B86" t="str">
+        <v>LDH</v>
+      </c>
+      <c r="C86" t="str">
+        <v>120〜245 U/L程度（施設差あり）</v>
+      </c>
+      <c r="D86" t="str">
+        <v>全身のさまざまな組織に含まれる酵素で、細胞が壊れると幅広く上昇する</v>
+      </c>
+      <c r="E86" t="str">
+        <v>LDHは全身の細胞の中にある酵素で、肝臓、心臓、筋肉、血液など、いろいろな組織の細胞がダメージを受けると血液中に漏れ出します。どの臓器が原因かを絞り込むには、他の検査値と組み合わせて評価します。</v>
+      </c>
+      <c r="F86" t="str">
+        <v>肝疾患、心筋梗塞、溶血性疾患、悪性腫瘍、筋肉の障害（横紋筋融解症など）、肺疾患</v>
+      </c>
+      <c r="G86" t="str">
+        <v/>
+      </c>
+      <c r="H86" t="str">
+        <v/>
+      </c>
+      <c r="I86" t="str">
+        <v/>
+      </c>
+      <c r="J86" t="str">
+        <v>臓器特異性が低いため単独では原因を特定しにくい。AST/ALT(肝)、CK(筋)、ビリルビン・ハプトグロビン(溶血)など他の検査値と組み合わせて原因臓器を推定する</v>
+      </c>
+      <c r="K86" t="str">
+        <v/>
+      </c>
+      <c r="L86" t="str">
+        <v>LDH,乳酸脱水素酵素,溶血,心筋梗塞,悪性腫瘍</v>
+      </c>
+      <c r="M86" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>LDH/AST比</v>
+      </c>
+      <c r="B87" t="str">
+        <v>LDH/AST</v>
+      </c>
+      <c r="C87" t="str">
+        <v>目安として使われる比率（施設差・カットオフ値の設定により異なる）</v>
+      </c>
+      <c r="D87" t="str">
+        <v>LDHとASTの両方が上昇したときに、原因が肝臓か、それ以外（溶血・心筋・骨格筋）かを見分ける目安になる比</v>
+      </c>
+      <c r="E87" t="str">
+        <v>これは、肝臓の数値（AST）と、全身に広く分布する酵素（LDH）の比率を見るもので、両方の数値が上がっているときに、原因が肝臓なのか、それとも血液や筋肉など他の場所なのかを見分ける手がかりになります。</v>
+      </c>
+      <c r="F87" t="str">
+        <v>溶血性疾患、心筋梗塞、骨格筋の障害（比が高いほど肝臓以外が原因の可能性）</v>
+      </c>
+      <c r="G87" t="str">
+        <v/>
+      </c>
+      <c r="H87" t="str">
+        <v>急性肝炎などの肝細胞障害（比が低い、つまりASTに対してLDHが相対的に低い場合は肝性が示唆される）</v>
+      </c>
+      <c r="I87" t="str">
+        <v/>
+      </c>
+      <c r="J87" t="str">
+        <v>AST・LDHが同時に上昇した際の鑑別に使う目安の一つ。単独の検査値ではなく計算上の比率であり、確定診断には他の検査（ビリルビン、CK、心筋マーカーなど）と合わせた評価が必要</v>
+      </c>
+      <c r="K87" t="str">
+        <v/>
+      </c>
+      <c r="L87" t="str">
+        <v>LDH/AST,LDH,AST,溶血,心筋梗塞,肝炎</v>
+      </c>
+      <c r="M87" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>CK/AST比</v>
+      </c>
+      <c r="B88" t="str">
+        <v>CK/AST</v>
+      </c>
+      <c r="C88" t="str">
+        <v>目安として使われる比率（施設差・カットオフ値の設定により異なる）</v>
+      </c>
+      <c r="D88" t="str">
+        <v>ASTが上昇したときに、原因が筋肉（CKも上昇）か、それ以外（肝臓など）かを見分ける目安になる比</v>
+      </c>
+      <c r="E88" t="str">
+        <v>これは、筋肉の数値（CK）と肝臓の数値（AST）を比べることで、ASTの上昇が筋肉由来なのか、肝臓由来なのかを見分ける手がかりになる比率です。</v>
+      </c>
+      <c r="F88" t="str">
+        <v>横紋筋融解症、心筋梗塞、激しい運動など筋肉由来のAST上昇（CKも同時に高値）</v>
+      </c>
+      <c r="G88" t="str">
+        <v>筋肉痛や脱力感、褐色尿などの症状がないか確認する</v>
+      </c>
+      <c r="H88" t="str">
+        <v/>
+      </c>
+      <c r="I88" t="str">
+        <v/>
+      </c>
+      <c r="J88" t="str">
+        <v>ASTのみ上昇しCKが正常であれば肝臓由来を、両方上昇していれば筋肉由来を疑う手がかりになる。スタチン系薬剤による横紋筋融解症が疑われる場面での鑑別に有用</v>
+      </c>
+      <c r="K88" t="str">
+        <v/>
+      </c>
+      <c r="L88" t="str">
+        <v>CK/AST,CK,AST,横紋筋融解症,スタチン</v>
+      </c>
+      <c r="M88" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>BUN/CRE比</v>
+      </c>
+      <c r="B89" t="str">
+        <v>BUN/Cr</v>
+      </c>
+      <c r="C89" t="str">
+        <v>10前後が目安（施設差あり）</v>
+      </c>
+      <c r="D89" t="str">
+        <v>BUNとクレアチニンの比率。腎前性（脱水・出血など）か腎性かを見分ける目安になる</v>
+      </c>
+      <c r="E89" t="str">
+        <v>これは、BUN（尿素窒素）とクレアチニンという2つの腎機能に関わる検査値を比較したもので、腎臓そのものに問題があるのか、それとも脱水や出血など腎臓の外側に原因があるのかを見分ける手がかりになります。</v>
+      </c>
+      <c r="F89" t="str">
+        <v>脱水、消化管出血、高たんぱく食、心不全（腎臓への血流低下）</v>
+      </c>
+      <c r="G89" t="str">
+        <v>脱水が疑われる場合はこまめな水分摂取を勧める。黒い便など消化管出血を示唆する症状がないか確認する</v>
+      </c>
+      <c r="H89" t="str">
+        <v>低たんぱく食、肝不全、妊娠</v>
+      </c>
+      <c r="I89" t="str">
+        <v/>
+      </c>
+      <c r="J89" t="str">
+        <v>比が高い（目安20以上）場合は脱水や消化管出血など腎前性の要因を、比が正常範囲で両方高値なら腎性の障害を疑う。BUN単独やクレアチニン単独よりも病態の絞り込みに役立つ</v>
+      </c>
+      <c r="K89" t="str">
+        <v>腎機能</v>
+      </c>
+      <c r="L89" t="str">
+        <v>BUN/CRE,BUN/Cr,尿素窒素,クレアチニン,脱水,腎前性</v>
+      </c>
+      <c r="M89" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>Na-Cl（ナトリウム・クロール差）</v>
+      </c>
+      <c r="B90" t="str">
+        <v>Na-Cl</v>
+      </c>
+      <c r="C90" t="str">
+        <v>36前後が目安（施設差あり）</v>
+      </c>
+      <c r="D90" t="str">
+        <v>ナトリウムからクロールを引いた値。アニオンギャップの簡易的な目安として使われる</v>
+      </c>
+      <c r="E90" t="str">
+        <v>この数値は、ナトリウムとクロールの検査値の差から計算されるもので、体の中に通常とは違う酸（アニオン）がたまっていないかを大まかに見積もるために使われます。</v>
+      </c>
+      <c r="F90" t="str">
+        <v>代謝性アシドーシス（乳酸アシドーシス、糖尿病性ケトアシドーシス、腎不全など、体内に有機酸がたまる病態）</v>
+      </c>
+      <c r="G90" t="str">
+        <v/>
+      </c>
+      <c r="H90" t="str">
+        <v/>
+      </c>
+      <c r="I90" t="str">
+        <v/>
+      </c>
+      <c r="J90" t="str">
+        <v>本来のアニオンギャップ(Na-(Cl+HCO3))の簡易代用として使われることがあるが、重炭酸(HCO3)を用いた計算の方が正確。メトホルミン使用中の乳酸アシドーシスが疑われる場面などで参考にする</v>
+      </c>
+      <c r="K90" t="str">
+        <v>電解質</v>
+      </c>
+      <c r="L90" t="str">
+        <v>Na-Cl,アニオンギャップ,AG,代謝性アシドーシス,乳酸アシドーシス</v>
+      </c>
+      <c r="M90" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>CONUT値</v>
+      </c>
+      <c r="B91" t="str">
+        <v>CONUT</v>
+      </c>
+      <c r="C91" t="str">
+        <v>0〜1点：正常、2〜4点：軽度低栄養、5〜8点：中等度低栄養、9〜12点：高度低栄養</v>
+      </c>
+      <c r="D91" t="str">
+        <v>アルブミン・総リンパ球数・総コレステロールの3項目から算出する栄養状態の評価スコア</v>
+      </c>
+      <c r="E91" t="str">
+        <v>CONUT値は、血液検査（アルブミン、リンパ球数、コレステロール）の結果から計算される、栄養状態を数値化したスコアです。点数が高いほど低栄養の状態が疑われます。</v>
+      </c>
+      <c r="F91" t="str">
+        <v>低栄養状態（点数が高いほど重度）</v>
+      </c>
+      <c r="G91" t="str">
+        <v>食事摂取量や体重の変化を確認する。必要に応じて栄養補助食品の活用を提案する</v>
+      </c>
+      <c r="H91" t="str">
+        <v/>
+      </c>
+      <c r="I91" t="str">
+        <v/>
+      </c>
+      <c r="J91" t="str">
+        <v>アルブミン・総リンパ球数・総コレステロールの3項目それぞれに配点があり、合計点で評価する客観的栄養指標。フレイル・サルコペニアの評価やポリファーマシー対策の一環としての栄養状態把握に有用</v>
+      </c>
+      <c r="K91" t="str">
+        <v/>
+      </c>
+      <c r="L91" t="str">
+        <v>CONUT,CONUT値,栄養評価,低栄養,フレイル</v>
+      </c>
+      <c r="M91" t="str">
+        <v>食事と栄養 p.240（フレイルQ108 低栄養や食事量の評価）</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
         <v>CRP</v>
       </c>
-      <c r="B83" t="str">
+      <c r="B92" t="str">
         <v>CRP</v>
       </c>
-      <c r="C83" t="str">
+      <c r="C92" t="str">
         <v>0.3 mg/dL未満（施設差あり）</v>
       </c>
-      <c r="D83" t="str">
+      <c r="D92" t="str">
         <v>体のどこかに炎症や感染が起きていないかを鋭敏に反映する数値</v>
       </c>
-      <c r="E83" t="str">
+      <c r="E92" t="str">
         <v>CRPは、体に炎症や感染が起きると数時間〜半日程度で急激に上昇する数値です。風邪のようなウイルス感染から細菌感染、体のどこかの炎症まで、幅広く反応するため、体調の変化を早期に捉える手がかりになります。</v>
       </c>
-      <c r="F83" t="str">
+      <c r="F92" t="str">
         <v>細菌感染症、ウイルス感染症、自己免疫疾患（関節リウマチなど）、悪性腫瘍、組織の損傷（術後・心筋梗塞など）</v>
       </c>
-      <c r="G83" t="str">
+      <c r="G92" t="str">
         <v>発熱、痛み、腫れなど炎症症状の有無を確認する</v>
       </c>
-      <c r="H83" t="str">
-        <v/>
-      </c>
-      <c r="I83" t="str">
-        <v/>
-      </c>
-      <c r="J83" t="str">
+      <c r="H92" t="str">
+        <v/>
+      </c>
+      <c r="I92" t="str">
+        <v/>
+      </c>
+      <c r="J92" t="str">
         <v>白血球数と合わせて感染・炎症の程度を評価する。上昇・低下のタイミングは白血球より半日〜1日程度遅れる傾向があるため、経過を追う際は採血のタイミングに注意</v>
       </c>
-      <c r="K83" t="str">
-        <v/>
-      </c>
-      <c r="L83" t="str">
+      <c r="K92" t="str">
+        <v/>
+      </c>
+      <c r="L92" t="str">
         <v>CRP,炎症,感染</v>
       </c>
-      <c r="M83" t="str">
+      <c r="M92" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M83"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M92"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/検査値リファレンス初期データ.xlsx
+++ b/検査値リファレンス初期データ.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M92"/>
+  <dimension ref="A1:M97"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -873,122 +873,122 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>リン（P）</v>
+        <v>補正カルシウム（参考値）</v>
       </c>
       <c r="B12" t="str">
-        <v>P,IP</v>
+        <v>Corrected Ca,補正Ca</v>
       </c>
       <c r="C12" t="str">
-        <v>2.5〜4.5 mg/dL</v>
+        <v>実測カルシウム値と同じ基準値を用いる（8.5〜10.0 mg/dL）</v>
       </c>
       <c r="D12" t="str">
-        <v>カルシウムとともに骨を作る主要なミネラル</v>
+        <v>アルブミンが低い患者で、見かけ上のカルシウム値を実際の値に近づけるための補正値</v>
       </c>
       <c r="E12" t="str">
-        <v>リンはカルシウムと一緒に骨や歯を作る材料になるミネラルです。カルシウムと逆方向に動くことが多く、腎臓の働きやホルモンのバランスによっても変動します。</v>
+        <v>血液中のカルシウムの多くはアルブミンというたんぱく質にくっついて存在しています。アルブミンが少ないと、実際のカルシウムの量が変わらなくても検査値上は低く出てしまうことがあるため、その影響を補正した数値がこの「補正カルシウム」です。</v>
       </c>
       <c r="F12" t="str">
-        <v>腎不全、副甲状腺機能低下症</v>
+        <v>（実測カルシウムの高値と同様）副甲状腺機能亢進症、悪性腫瘍（骨転移など）、ビタミンD過剰</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>副甲状腺機能亢進症、骨軟化症、ビタミンD欠乏</v>
+        <v>（実測カルシウムの低値と同様）副甲状腺機能低下症、ビタミンD欠乏、腎不全</v>
       </c>
       <c r="I12" t="str">
         <v/>
       </c>
       <c r="J12" t="str">
-        <v>カルシウムと逆方向に動くことが多い（副甲状腺機能亢進症ではCa上昇・P低下）。骨粗鬆症の二次性原因の除外に用いられる</v>
+        <v>補正カルシウム(mg/dL) = 実測カルシウム + (4 − アルブミン値)の式で計算する。アルブミンが4.0 g/dL未満の低栄養患者やネフローゼ症候群の患者では、実測カルシウムだけで判断すると誤りやすいため、この補正値で評価する</v>
       </c>
       <c r="K12" t="str">
-        <v>骨粗鬆症,電解質</v>
+        <v>電解質,骨粗鬆症</v>
       </c>
       <c r="L12" t="str">
-        <v>リン,P,IP,無機リン</v>
+        <v>補正カルシウム,Corrected Calcium,アルブミン補正,低アルブミン血症</v>
       </c>
       <c r="M12" t="str">
-        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）／p.199-215（第2部 腎機能低下 Q83 リン制限）</v>
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>AST（GOT）</v>
+        <v>リン（P）</v>
       </c>
       <c r="B13" t="str">
-        <v>AST,GOT</v>
+        <v>P,IP</v>
       </c>
       <c r="C13" t="str">
-        <v>10〜40 U/L</v>
+        <v>2.5〜4.5 mg/dL</v>
       </c>
       <c r="D13" t="str">
-        <v>肝臓や心臓・筋肉の細胞が壊れると血液中に漏れ出す酵素</v>
+        <v>カルシウムとともに骨を作る主要なミネラル</v>
       </c>
       <c r="E13" t="str">
-        <v>ASTは肝臓や心臓、筋肉の細胞の中にある酵素です。これらの細胞がダメージを受けたり壊れたりすると血液中に漏れ出して数値が上がります。肝臓の状態を見るときはALTと一緒に確認します。</v>
+        <v>リンはカルシウムと一緒に骨や歯を作る材料になるミネラルです。カルシウムと逆方向に動くことが多く、腎臓の働きやホルモンのバランスによっても変動します。</v>
       </c>
       <c r="F13" t="str">
-        <v>肝炎・肝硬変などの肝疾患、心筋梗塞、筋肉の障害（激しい運動・横紋筋融解症）、薬剤性肝障害</v>
+        <v>腎不全、副甲状腺機能低下症</v>
       </c>
       <c r="G13" t="str">
-        <v>飲酒量を控える。激しい運動の直後の採血でないかを確認する</v>
+        <v/>
       </c>
       <c r="H13" t="str">
-        <v>臨床的に問題になることは少ない</v>
+        <v>副甲状腺機能亢進症、骨軟化症、ビタミンD欠乏</v>
       </c>
       <c r="I13" t="str">
         <v/>
       </c>
       <c r="J13" t="str">
-        <v>ALTとの比率（AST/ALT比）で肝細胞障害か他臓器由来かを推測できる。AST優位はアルコール性・心筋・筋由来を疑う材料になる</v>
+        <v>カルシウムと逆方向に動くことが多い（副甲状腺機能亢進症ではCa上昇・P低下）。骨粗鬆症の二次性原因の除外に用いられる</v>
       </c>
       <c r="K13" t="str">
-        <v>肝機能,糖尿病,てんかん,精神疾患（非定型抗精神病薬）</v>
+        <v>骨粗鬆症,電解質</v>
       </c>
       <c r="L13" t="str">
-        <v>AST,GOT,肝機能,肝障害</v>
+        <v>リン,P,IP,無機リン</v>
       </c>
       <c r="M13" t="str">
-        <v/>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）／p.199-215（第2部 腎機能低下 Q83 リン制限）</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ALT（GPT）</v>
+        <v>乳酸脱水素酵素（LDH）</v>
       </c>
       <c r="B14" t="str">
-        <v>ALT,GPT</v>
+        <v>LDH</v>
       </c>
       <c r="C14" t="str">
-        <v>5〜40 U/L</v>
+        <v>120〜245 U/L程度（施設差あり）</v>
       </c>
       <c r="D14" t="str">
-        <v>主に肝臓の細胞に含まれる酵素で、肝障害の指標として最もよく使われる</v>
+        <v>全身のさまざまな組織に含まれる酵素で、細胞が壊れると幅広く上昇する</v>
       </c>
       <c r="E14" t="str">
-        <v>ALTは主に肝臓の細胞の中にある酵素です。肝臓の細胞がダメージを受けると血液中に漏れ出して数値が上がります。ASTよりも肝臓に特異的な数値なので、肝臓の状態を見るときによく使われます。</v>
+        <v>LDHは全身の細胞の中にある酵素で、肝臓、心臓、筋肉、血液など、いろいろな組織の細胞がダメージを受けると血液中に漏れ出します。どの臓器が原因かを絞り込むには、他の検査値と組み合わせて評価します。</v>
       </c>
       <c r="F14" t="str">
-        <v>脂肪肝、肝炎（ウイルス性・アルコール性・薬剤性）、肝硬変、薬の副作用による肝機能障害</v>
+        <v>肝疾患、心筋梗塞、溶血性疾患、悪性腫瘍、筋肉の障害（横紋筋融解症など）、肺疾患</v>
       </c>
       <c r="G14" t="str">
-        <v>体重管理と脂質の摂りすぎに注意する（脂肪肝が疑われる場合）。新規薬剤の開始時期と重なっていないか確認する</v>
+        <v/>
       </c>
       <c r="H14" t="str">
-        <v>臨床的に問題になることは少ない</v>
+        <v/>
       </c>
       <c r="I14" t="str">
         <v/>
       </c>
       <c r="J14" t="str">
-        <v>新規薬剤開始後の肝障害の指標として重要。健診でALTのみ軽度上昇していることが多く、その場合は脂肪肝（NAFLD）の頻度が高い</v>
+        <v>臓器特異性が低いため単独では原因を特定しにくい。AST/ALT(肝)、CK(筋)、ビリルビン・ハプトグロビン(溶血)など他の検査値と組み合わせて原因臓器を推定する</v>
       </c>
       <c r="K14" t="str">
-        <v>肝機能,糖尿病,てんかん,精神疾患（非定型抗精神病薬）</v>
+        <v/>
       </c>
       <c r="L14" t="str">
-        <v>ALT,GPT,肝機能,肝障害,脂肪肝</v>
+        <v>LDH,乳酸脱水素酵素,溶血,心筋梗塞,悪性腫瘍</v>
       </c>
       <c r="M14" t="str">
         <v/>
@@ -996,40 +996,40 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>コリンエステラーゼ</v>
+        <v>AST（GOT）</v>
       </c>
       <c r="B15" t="str">
-        <v>ChE</v>
+        <v>AST,GOT</v>
       </c>
       <c r="C15" t="str">
-        <v>男性 240〜486 U/L、女性 201〜421 U/L（施設差あり）</v>
+        <v>10〜40 U/L</v>
       </c>
       <c r="D15" t="str">
-        <v>主に肝臓で作られる酵素。肝臓のたんぱく質を作る力（合成能）を反映する</v>
+        <v>肝臓や心臓・筋肉の細胞が壊れると血液中に漏れ出す酵素</v>
       </c>
       <c r="E15" t="str">
-        <v>コリンエステラーゼは肝臓で作られる酵素です。肝臓がたんぱく質を作る力が落ちると数値が下がり、逆に脂肪肝や栄養状態が良すぎる場合は上がることがあります。</v>
+        <v>ASTは肝臓や心臓、筋肉の細胞の中にある酵素です。これらの細胞がダメージを受けたり壊れたりすると血液中に漏れ出して数値が上がります。肝臓の状態を見るときはALTと一緒に確認します。</v>
       </c>
       <c r="F15" t="str">
-        <v>脂肪肝、ネフローゼ症候群、肥満、甲状腺機能亢進症</v>
+        <v>肝炎・肝硬変などの肝疾患、心筋梗塞、筋肉の障害（激しい運動・横紋筋融解症）、薬剤性肝障害</v>
       </c>
       <c r="G15" t="str">
-        <v>脂肪肝が疑われる場合は食事・運動習慣の見直しを勧める</v>
+        <v>飲酒量を控える。激しい運動の直後の採血でないかを確認する</v>
       </c>
       <c r="H15" t="str">
-        <v>肝硬変など肝臓の合成能低下、低栄養、有機リン中毒（農薬など）</v>
+        <v>臨床的に問題になることは少ない</v>
       </c>
       <c r="I15" t="str">
         <v/>
       </c>
       <c r="J15" t="str">
-        <v>アルブミンと同様に肝臓の「合成能」を見る指標。低栄養か肝硬変かは、アルブミンや血小板数（肝硬変で低下しやすい）と合わせて判断する</v>
+        <v>ALTとの比率（AST/ALT比）で肝細胞障害か他臓器由来かを推測できる。AST優位はアルコール性・心筋・筋由来を疑う材料になる</v>
       </c>
       <c r="K15" t="str">
-        <v>肝機能</v>
+        <v>肝機能,糖尿病,てんかん,精神疾患（非定型抗精神病薬）</v>
       </c>
       <c r="L15" t="str">
-        <v>コリンエステラーゼ,ChE,肝合成能,脂肪肝,肝硬変</v>
+        <v>AST,GOT,肝機能,肝障害</v>
       </c>
       <c r="M15" t="str">
         <v/>
@@ -1037,944 +1037,944 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
+        <v>ALT（GPT）</v>
+      </c>
+      <c r="B16" t="str">
+        <v>ALT,GPT</v>
+      </c>
+      <c r="C16" t="str">
+        <v>5〜40 U/L</v>
+      </c>
+      <c r="D16" t="str">
+        <v>主に肝臓の細胞に含まれる酵素で、肝障害の指標として最もよく使われる</v>
+      </c>
+      <c r="E16" t="str">
+        <v>ALTは主に肝臓の細胞の中にある酵素です。肝臓の細胞がダメージを受けると血液中に漏れ出して数値が上がります。ASTよりも肝臓に特異的な数値なので、肝臓の状態を見るときによく使われます。</v>
+      </c>
+      <c r="F16" t="str">
+        <v>脂肪肝、肝炎（ウイルス性・アルコール性・薬剤性）、肝硬変、薬の副作用による肝機能障害</v>
+      </c>
+      <c r="G16" t="str">
+        <v>体重管理と脂質の摂りすぎに注意する（脂肪肝が疑われる場合）。新規薬剤の開始時期と重なっていないか確認する</v>
+      </c>
+      <c r="H16" t="str">
+        <v>臨床的に問題になることは少ない</v>
+      </c>
+      <c r="I16" t="str">
+        <v/>
+      </c>
+      <c r="J16" t="str">
+        <v>新規薬剤開始後の肝障害の指標として重要。健診でALTのみ軽度上昇していることが多く、その場合は脂肪肝（NAFLD）の頻度が高い</v>
+      </c>
+      <c r="K16" t="str">
+        <v>肝機能,糖尿病,てんかん,精神疾患（非定型抗精神病薬）</v>
+      </c>
+      <c r="L16" t="str">
+        <v>ALT,GPT,肝機能,肝障害,脂肪肝</v>
+      </c>
+      <c r="M16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>コリンエステラーゼ</v>
+      </c>
+      <c r="B17" t="str">
+        <v>ChE</v>
+      </c>
+      <c r="C17" t="str">
+        <v>男性 240〜486 U/L、女性 201〜421 U/L（施設差あり）</v>
+      </c>
+      <c r="D17" t="str">
+        <v>主に肝臓で作られる酵素。肝臓のたんぱく質を作る力（合成能）を反映する</v>
+      </c>
+      <c r="E17" t="str">
+        <v>コリンエステラーゼは肝臓で作られる酵素です。肝臓がたんぱく質を作る力が落ちると数値が下がり、逆に脂肪肝や栄養状態が良すぎる場合は上がることがあります。</v>
+      </c>
+      <c r="F17" t="str">
+        <v>脂肪肝、ネフローゼ症候群、肥満、甲状腺機能亢進症</v>
+      </c>
+      <c r="G17" t="str">
+        <v>脂肪肝が疑われる場合は食事・運動習慣の見直しを勧める</v>
+      </c>
+      <c r="H17" t="str">
+        <v>肝硬変など肝臓の合成能低下、低栄養、有機リン中毒（農薬など）</v>
+      </c>
+      <c r="I17" t="str">
+        <v/>
+      </c>
+      <c r="J17" t="str">
+        <v>アルブミンと同様に肝臓の「合成能」を見る指標。低栄養か肝硬変かは、アルブミンや血小板数（肝硬変で低下しやすい）と合わせて判断する</v>
+      </c>
+      <c r="K17" t="str">
+        <v>肝機能</v>
+      </c>
+      <c r="L17" t="str">
+        <v>コリンエステラーゼ,ChE,肝合成能,脂肪肝,肝硬変</v>
+      </c>
+      <c r="M17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
         <v>アルカリホスファターゼ（ALP）</v>
       </c>
-      <c r="B16" t="str">
+      <c r="B18" t="str">
         <v>ALP</v>
       </c>
-      <c r="C16" t="str">
+      <c r="C18" t="str">
         <v>38〜113 U/L（施設・測定法により大きく異なる）</v>
       </c>
-      <c r="D16" t="str">
+      <c r="D18" t="str">
         <v>骨や肝臓・胆道に多く含まれる酵素で、骨を作る働きの指標にもなる</v>
       </c>
-      <c r="E16" t="str">
+      <c r="E18" t="str">
         <v>ALPは骨や肝臓、胆道に多く含まれる酵素です。骨を作る働きが活発なとき（骨の成長期や骨折の治癒過程など）や、肝臓・胆道にトラブルがあるときに数値が上がります。</v>
       </c>
-      <c r="F16" t="str">
+      <c r="F18" t="str">
         <v>骨代謝の亢進（骨折治癒過程、骨粗鬆症、骨転移、Paget病）、肝・胆道疾患、成長期の生理的高値</v>
       </c>
-      <c r="G16" t="str">
-        <v/>
-      </c>
-      <c r="H16" t="str">
-        <v/>
-      </c>
-      <c r="I16" t="str">
-        <v/>
-      </c>
-      <c r="J16" t="str">
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v/>
+      </c>
+      <c r="J18" t="str">
         <v>骨由来か肝由来かの区別には骨型ALPアイソザイムやγ-GTPとの組み合わせで判断する</v>
       </c>
-      <c r="K16" t="str">
+      <c r="K18" t="str">
         <v>骨粗鬆症,肝機能</v>
       </c>
-      <c r="L16" t="str">
+      <c r="L18" t="str">
         <v>ALP,アルカリホスファターゼ,骨代謝,肝機能</v>
       </c>
-      <c r="M16" t="str">
+      <c r="M18" t="str">
         <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
-    <row r="17" xml:space="preserve">
-      <c r="A17" t="str">
+    <row r="19" xml:space="preserve">
+      <c r="A19" t="str">
         <v>γ-GTP</v>
       </c>
-      <c r="B17" t="str">
+      <c r="B19" t="str">
         <v>γ-GTP,GGT</v>
       </c>
-      <c r="C17" t="str" xml:space="preserve">
+      <c r="C19" t="str" xml:space="preserve">
         <v xml:space="preserve">男性 〜50 U/L、女性 〜30 U/L
 （施設差が大きい）</v>
       </c>
-      <c r="D17" t="str">
+      <c r="D19" t="str">
         <v>アルコールや胆道のトラブルに反応しやすい肝臓の酵素</v>
       </c>
-      <c r="E17" t="str">
+      <c r="E19" t="str">
         <v>γ-GTPは肝臓や胆道の細胞にある酵素で、特にお酒の影響を受けやすいことが知られています。数値が高いときは、アルコールの摂取量や胆道（胆汁の通り道）の状態を確認する目安になります。</v>
       </c>
-      <c r="F17" t="str">
+      <c r="F19" t="str">
         <v>アルコール性肝障害、脂肪肝、胆道系疾患（胆石・胆管閉塞）、薬剤性（酵素誘導）</v>
       </c>
-      <c r="G17" t="str">
+      <c r="G19" t="str">
         <v>飲酒量を控える、休肝日をつくるよう伝える</v>
       </c>
-      <c r="H17" t="str">
+      <c r="H19" t="str">
         <v>臨床的に問題になることは少ない</v>
       </c>
-      <c r="I17" t="str">
-        <v/>
-      </c>
-      <c r="J17" t="str">
+      <c r="I19" t="str">
+        <v/>
+      </c>
+      <c r="J19" t="str">
         <v>飲酒歴の確認に使いやすい数値。断酒・節酒で比較的早く改善するため、生活指導の効果を示す指標としても使える</v>
-      </c>
-      <c r="K17" t="str">
-        <v>肝機能</v>
-      </c>
-      <c r="L17" t="str">
-        <v>ガンマGTP,γ-GTP,GGT,肝機能,飲酒,アルコール</v>
-      </c>
-      <c r="M17" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>総ビリルビン</v>
-      </c>
-      <c r="B18" t="str">
-        <v>T-Bil</v>
-      </c>
-      <c r="C18" t="str">
-        <v>0.2〜1.2 mg/dL</v>
-      </c>
-      <c r="D18" t="str">
-        <v>赤血球が壊れてできる黄色い色素の総量。肝臓・胆道の状態や黄疸の指標</v>
-      </c>
-      <c r="E18" t="str">
-        <v>ビリルビンは赤血球が寿命を迎えて壊れるときにできる黄色い色素です。肝臓で処理されて排泄されますが、肝臓や胆道にトラブルがあると血液中に増え、皮膚や白目が黄色くなる黄疸として現れます。</v>
-      </c>
-      <c r="F18" t="str">
-        <v>肝炎・肝硬変などの肝疾患、胆道閉塞（胆石・腫瘍など）、溶血性疾患（赤血球の破壊亢進）、体質性黄疸（ジルベール症候群など）</v>
-      </c>
-      <c r="G18" t="str">
-        <v>皮膚や白目の黄染、尿の色が濃くなっていないか確認する</v>
-      </c>
-      <c r="H18" t="str">
-        <v/>
-      </c>
-      <c r="I18" t="str">
-        <v/>
-      </c>
-      <c r="J18" t="str">
-        <v>直接ビリルビン・間接ビリルビンの内訳で原因を推測できる（直接優位は胆道系、間接優位は溶血・体質性）。AST/ALT/γ-GTPと合わせて評価する</v>
-      </c>
-      <c r="K18" t="str">
-        <v>肝機能</v>
-      </c>
-      <c r="L18" t="str">
-        <v>総ビリルビン,T-Bil,黄疸,ビリルビン,ジルベール症候群</v>
-      </c>
-      <c r="M18" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>総タンパク</v>
-      </c>
-      <c r="B19" t="str">
-        <v>TP</v>
-      </c>
-      <c r="C19" t="str">
-        <v>6.6〜8.1 g/dL</v>
-      </c>
-      <c r="D19" t="str">
-        <v>血液中のたんぱく質（アルブミン＋グロブリン）の総量。栄養状態や肝機能、炎症の目安</v>
-      </c>
-      <c r="E19" t="str">
-        <v>総タンパクは、血液中のたんぱく質の合計量です。栄養状態や肝臓の働き、体の炎症の有無などを反映します。</v>
-      </c>
-      <c r="F19" t="str">
-        <v>脱水、多発性骨髄腫など（グロブリン増加）、慢性炎症</v>
-      </c>
-      <c r="G19" t="str">
-        <v/>
-      </c>
-      <c r="H19" t="str">
-        <v>低栄養、肝機能低下（アルブミン産生低下）、ネフローゼ症候群、消化管からのたんぱく漏出</v>
-      </c>
-      <c r="I19" t="str">
-        <v>食事摂取量（特にたんぱく質）を確認する</v>
-      </c>
-      <c r="J19" t="str">
-        <v>アルブミンとグロブリンの内訳（A/G比）も合わせて確認すると原因の絞り込みに役立つ。低栄養か肝機能低下かはアルブミンの値と合わせて判断する</v>
       </c>
       <c r="K19" t="str">
         <v>肝機能</v>
       </c>
       <c r="L19" t="str">
-        <v>総タンパク,TP,総蛋白,栄養状態,A/G比</v>
+        <v>ガンマGTP,γ-GTP,GGT,肝機能,飲酒,アルコール</v>
       </c>
       <c r="M19" t="str">
-        <v>食事と栄養 p.23（たんぱく質）</v>
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>アルブミン</v>
+        <v>総ビリルビン</v>
       </c>
       <c r="B20" t="str">
-        <v>Alb</v>
+        <v>T-Bil</v>
       </c>
       <c r="C20" t="str">
-        <v>3.8〜5.2 g/dL</v>
+        <v>0.2〜1.2 mg/dL</v>
       </c>
       <c r="D20" t="str">
-        <v>体の栄養状態を見る目安になるたんぱく質。血液の中で栄養を運ぶ、水分を血管の中に保つという働きをしている。</v>
+        <v>赤血球が壊れてできる黄色い色素の総量。肝臓・胆道の状態や黄疸の指標</v>
       </c>
       <c r="E20" t="str">
-        <v>アルブミンは栄養の状態を見る数値です。食事量が少なかったり、肝臓や腎臓、腸の働きが弱ると下がることがあります。数値が低いと、むくみが出やすくなります。</v>
+        <v>ビリルビンは赤血球が寿命を迎えて壊れるときにできる黄色い色素です。肝臓で処理されて排泄されますが、肝臓や胆道にトラブルがあると血液中に増え、皮膚や白目が黄色くなる黄疸として現れます。</v>
       </c>
       <c r="F20" t="str">
-        <v>脱水（見かけ上の上昇）</v>
+        <v>肝炎・肝硬変などの肝疾患、胆道閉塞（胆石・腫瘍など）、溶血性疾患（赤血球の破壊亢進）、体質性黄疸（ジルベール症候群など）</v>
       </c>
       <c r="G20" t="str">
-        <v/>
+        <v>皮膚や白目の黄染、尿の色が濃くなっていないか確認する</v>
       </c>
       <c r="H20" t="str">
-        <v>低栄養／肝機能低下／ネフローゼ症候群／クローン病</v>
+        <v/>
       </c>
       <c r="I20" t="str">
-        <v>主食に偏らず、肉・魚・卵・大豆製品などたんぱく質をしっかり摂るよう伝える。食欲が落ちている場合は少量頻回の食事も提案する</v>
+        <v/>
       </c>
       <c r="J20" t="str">
-        <v>3前半は注意ライン。食事摂取量を必ず確認</v>
+        <v>直接ビリルビン・間接ビリルビンの内訳で原因を推測できる（直接優位は胆道系、間接優位は溶血・体質性）。AST/ALT/γ-GTPと合わせて評価する</v>
       </c>
       <c r="K20" t="str">
-        <v>肝機能,栄養,腎機能</v>
+        <v>肝機能</v>
       </c>
       <c r="L20" t="str">
-        <v>アルブミン,Alb,むくみ,浮腫,栄養状態</v>
+        <v>総ビリルビン,T-Bil,黄疸,ビリルビン,ジルベール症候群</v>
       </c>
       <c r="M20" t="str">
-        <v>食事と栄養 p.23（たんぱく質）／p.242（フレイルQ110 アルブミン値を上げる食事指導）</v>
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>中性脂肪（トリグリセリド）</v>
+        <v>総タンパク</v>
       </c>
       <c r="B21" t="str">
-        <v>TG</v>
+        <v>TP</v>
       </c>
       <c r="C21" t="str">
-        <v>150 mg/dL未満（空腹時）</v>
+        <v>6.6〜8.1 g/dL</v>
       </c>
       <c r="D21" t="str">
-        <v>脂質異常症で高値になりやすい脂質で、食事の影響を強く受ける</v>
+        <v>血液中のたんぱく質（アルブミン＋グロブリン）の総量。栄養状態や肝機能、炎症の目安</v>
       </c>
       <c r="E21" t="str">
-        <v>中性脂肪は、食事から摂った脂肪や糖質が体に蓄えられる形になったものです。食後は誰でも一時的に上がるため、正確に評価するには空腹時に採血することが大切です。高い状態が続くと動脈硬化や急性膵炎のリスクが高まります。</v>
+        <v>総タンパクは、血液中のたんぱく質の合計量です。栄養状態や肝臓の働き、体の炎症の有無などを反映します。</v>
       </c>
       <c r="F21" t="str">
-        <v>脂質異常症、糖質・アルコールの摂りすぎ、肥満、糖尿病のコントロール不良</v>
+        <v>脱水、多発性骨髄腫など（グロブリン増加）、慢性炎症</v>
       </c>
       <c r="G21" t="str">
-        <v>糖質・アルコールの摂りすぎに注意し、有酸素運動を勧める</v>
+        <v/>
       </c>
       <c r="H21" t="str">
-        <v>低栄養、甲状腺機能亢進症</v>
+        <v>低栄養、肝機能低下（アルブミン産生低下）、ネフローゼ症候群、消化管からのたんぱく漏出</v>
       </c>
       <c r="I21" t="str">
-        <v/>
+        <v>食事摂取量（特にたんぱく質）を確認する</v>
       </c>
       <c r="J21" t="str">
-        <v>採血が食後か空腹時かで数値が大きく変わるため必ず確認する。500 mg/dL以上では急性膵炎のリスクが高まるため注意。フィブラート系・EPA製剤などの効果判定に使う</v>
+        <v>アルブミンとグロブリンの内訳（A/G比）も合わせて確認すると原因の絞り込みに役立つ。低栄養か肝機能低下かはアルブミンの値と合わせて判断する</v>
       </c>
       <c r="K21" t="str">
-        <v>脂質異常症</v>
+        <v>肝機能</v>
       </c>
       <c r="L21" t="str">
-        <v>中性脂肪,トリグリセリド,TG,脂質異常症</v>
+        <v>総タンパク,TP,総蛋白,栄養状態,A/G比</v>
       </c>
       <c r="M21" t="str">
-        <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
+        <v>食事と栄養 p.23（たんぱく質）</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
+        <v>アルブミン</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Alb</v>
+      </c>
+      <c r="C22" t="str">
+        <v>3.8〜5.2 g/dL</v>
+      </c>
+      <c r="D22" t="str">
+        <v>体の栄養状態を見る目安になるたんぱく質。血液の中で栄養を運ぶ、水分を血管の中に保つという働きをしている。</v>
+      </c>
+      <c r="E22" t="str">
+        <v>アルブミンは栄養の状態を見る数値です。食事量が少なかったり、肝臓や腎臓、腸の働きが弱ると下がることがあります。数値が低いと、むくみが出やすくなります。</v>
+      </c>
+      <c r="F22" t="str">
+        <v>脱水（見かけ上の上昇）</v>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <v>低栄養／肝機能低下／ネフローゼ症候群／クローン病</v>
+      </c>
+      <c r="I22" t="str">
+        <v>主食に偏らず、肉・魚・卵・大豆製品などたんぱく質をしっかり摂るよう伝える。食欲が落ちている場合は少量頻回の食事も提案する</v>
+      </c>
+      <c r="J22" t="str">
+        <v>3前半は注意ライン。食事摂取量を必ず確認</v>
+      </c>
+      <c r="K22" t="str">
+        <v>肝機能,栄養,腎機能</v>
+      </c>
+      <c r="L22" t="str">
+        <v>アルブミン,Alb,むくみ,浮腫,栄養状態</v>
+      </c>
+      <c r="M22" t="str">
+        <v>食事と栄養 p.23（たんぱく質）／p.242（フレイルQ110 アルブミン値を上げる食事指導）</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>BUN/CRE比</v>
+      </c>
+      <c r="B23" t="str">
+        <v>BUN/Cr</v>
+      </c>
+      <c r="C23" t="str">
+        <v>10前後が目安（施設差あり）</v>
+      </c>
+      <c r="D23" t="str">
+        <v>BUNとクレアチニンの比率。腎前性（脱水・出血など）か腎性かを見分ける目安になる</v>
+      </c>
+      <c r="E23" t="str">
+        <v>これは、BUN（尿素窒素）とクレアチニンという2つの腎機能に関わる検査値を比較したもので、腎臓そのものに問題があるのか、それとも脱水や出血など腎臓の外側に原因があるのかを見分ける手がかりになります。</v>
+      </c>
+      <c r="F23" t="str">
+        <v>脱水、消化管出血、高たんぱく食、心不全（腎臓への血流低下）</v>
+      </c>
+      <c r="G23" t="str">
+        <v>脱水が疑われる場合はこまめな水分摂取を勧める。黒い便など消化管出血を示唆する症状がないか確認する</v>
+      </c>
+      <c r="H23" t="str">
+        <v>低たんぱく食、肝不全、妊娠</v>
+      </c>
+      <c r="I23" t="str">
+        <v/>
+      </c>
+      <c r="J23" t="str">
+        <v>比が高い（目安20以上）場合は脱水や消化管出血など腎前性の要因を、比が正常範囲で両方高値なら腎性の障害を疑う。BUN単独やクレアチニン単独よりも病態の絞り込みに役立つ</v>
+      </c>
+      <c r="K23" t="str">
+        <v>腎機能</v>
+      </c>
+      <c r="L23" t="str">
+        <v>BUN/CRE,BUN/Cr,尿素窒素,クレアチニン,脱水,腎前性</v>
+      </c>
+      <c r="M23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>Na-Cl（ナトリウム・クロール差）</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Na-Cl</v>
+      </c>
+      <c r="C24" t="str">
+        <v>36前後が目安（施設差あり）</v>
+      </c>
+      <c r="D24" t="str">
+        <v>ナトリウムからクロールを引いた値。アニオンギャップの簡易的な目安として使われる</v>
+      </c>
+      <c r="E24" t="str">
+        <v>この数値は、ナトリウムとクロールの検査値の差から計算されるもので、体の中に通常とは違う酸（アニオン）がたまっていないかを大まかに見積もるために使われます。</v>
+      </c>
+      <c r="F24" t="str">
+        <v>代謝性アシドーシス（乳酸アシドーシス、糖尿病性ケトアシドーシス、腎不全など、体内に有機酸がたまる病態）</v>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v/>
+      </c>
+      <c r="J24" t="str">
+        <v>本来のアニオンギャップ(Na-(Cl+HCO3))の簡易代用として使われることがあるが、重炭酸(HCO3)を用いた計算の方が正確。メトホルミン使用中の乳酸アシドーシスが疑われる場面などで参考にする</v>
+      </c>
+      <c r="K24" t="str">
+        <v>電解質</v>
+      </c>
+      <c r="L24" t="str">
+        <v>Na-Cl,アニオンギャップ,AG,代謝性アシドーシス,乳酸アシドーシス</v>
+      </c>
+      <c r="M24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>AST/ALT</v>
+      </c>
+      <c r="B25" t="str">
+        <v>AST/ALT,De Ritis比</v>
+      </c>
+      <c r="C25" t="str">
+        <v>1未満が目安（施設・病態により異なる）</v>
+      </c>
+      <c r="D25" t="str">
+        <v>ASTとALTの比率（De Ritis比）。肝疾患の種類を推測する手がかりになる</v>
+      </c>
+      <c r="E25" t="str">
+        <v>これは、肝臓に関わる2つの数値（ASTとALT）の比率を見るもので、肝臓のどのようなタイプのトラブルが起きているかを推測する手がかりになります。</v>
+      </c>
+      <c r="F25" t="str">
+        <v>アルコール性肝障害、肝硬変、心筋梗塞・筋疾患の合併（比が2以上でアルコール性を強く示唆）</v>
+      </c>
+      <c r="G25" t="str">
+        <v>飲酒量や頻度を確認する</v>
+      </c>
+      <c r="H25" t="str">
+        <v>急性ウイルス性肝炎、脂肪肝（比が1未満で肝細胞の急性障害を示唆することが多い）</v>
+      </c>
+      <c r="I25" t="str">
+        <v/>
+      </c>
+      <c r="J25" t="str">
+        <v>De Ritis比とも呼ばれる。比が2以上はアルコール性肝障害や肝硬変を、1未満は急性ウイルス性肝炎や脂肪肝を示唆する目安になるが、確定診断には他の検査所見と合わせた評価が必要</v>
+      </c>
+      <c r="K25" t="str">
+        <v>肝機能</v>
+      </c>
+      <c r="L25" t="str">
+        <v>AST/ALT,De Ritis比,デリティス比,アルコール性肝障害,肝硬変</v>
+      </c>
+      <c r="M25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>AST比/ALP比</v>
+      </c>
+      <c r="B26" t="str">
+        <v>R比,R-factor</v>
+      </c>
+      <c r="C26" t="str">
+        <v>R比 5以上：肝細胞障害型、2以下：胆汁うっ滞型、2〜5：混合型（報告により定義が異なる）</v>
+      </c>
+      <c r="D26" t="str">
+        <v>肝障害のパターンを「肝細胞障害型」か「胆汁うっ滞型」かに分類するための指標（R比）</v>
+      </c>
+      <c r="E26" t="str">
+        <v>これは、肝臓の数値の上がり方のパターンから、肝臓の細胞そのものが傷んでいるタイプなのか、胆汁の流れが滞っているタイプなのかを見分けるための指標です。</v>
+      </c>
+      <c r="F26" t="str">
+        <v>肝細胞障害型（ウイルス性肝炎、薬剤性肝障害の肝細胞障害型など）：AST/ALT優位の上昇</v>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+      <c r="H26" t="str">
+        <v>胆汁うっ滞型（胆石、胆道腫瘍、薬剤性肝障害の胆汁うっ滞型など）：ALP優位の上昇</v>
+      </c>
+      <c r="I26" t="str">
+        <v/>
+      </c>
+      <c r="J26" t="str">
+        <v>R比＝(ALTの基準値上限に対する倍率)÷(ALPの基準値上限に対する倍率)で算出する。薬剤性肝障害(DILI)の病型分類（肝細胞障害型・胆汁うっ滞型・混合型）に用いられる考え方で、原因薬剤の推定や重症度評価の参考になる</v>
+      </c>
+      <c r="K26" t="str">
+        <v>肝機能</v>
+      </c>
+      <c r="L26" t="str">
+        <v>R比,R-factor,肝細胞障害型,胆汁うっ滞型,薬剤性肝障害,DILI</v>
+      </c>
+      <c r="M26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>乳び</v>
+      </c>
+      <c r="B27" t="str">
+        <v>乳び,Lipemia</v>
+      </c>
+      <c r="C27" t="str">
+        <v>所見なし（血清が白濁していなければ正常）</v>
+      </c>
+      <c r="D27" t="str">
+        <v>中性脂肪が非常に多いため、血清が白く濁って見える状態。検査値そのものではなく検体の外観所見</v>
+      </c>
+      <c r="E27" t="str">
+        <v>乳びとは、血液中の中性脂肪が非常に多いために、採血した血液（血清）が白く濁って見える状態のことです。多くの場合、食後の採血や、著しい脂質異常症が背景にあります。</v>
+      </c>
+      <c r="F27" t="str">
+        <v>著しい高中性脂肪血症、食後採血（一時的なもの）、原発性高カイロミクロン血症などの脂質代謝異常</v>
+      </c>
+      <c r="G27" t="str">
+        <v>採血が空腹時だったかを確認する。食後採血であれば次回は空腹時の再検を提案する</v>
+      </c>
+      <c r="H27" t="str">
+        <v/>
+      </c>
+      <c r="I27" t="str">
+        <v/>
+      </c>
+      <c r="J27" t="str">
+        <v>血清の白濁により一部の検査項目（電解質など）の測定値に誤差が出ることがある（偽性低ナトリウム血症など）。中性脂肪値と合わせて評価する</v>
+      </c>
+      <c r="K27" t="str">
+        <v>脂質異常症</v>
+      </c>
+      <c r="L27" t="str">
+        <v>乳び,乳び血清,Lipemia,高中性脂肪血症</v>
+      </c>
+      <c r="M27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>溶血</v>
+      </c>
+      <c r="B28" t="str">
+        <v>溶血,Hemolysis</v>
+      </c>
+      <c r="C28" t="str">
+        <v>所見なし（溶血を示唆する検査値異常がなければ正常）</v>
+      </c>
+      <c r="D28" t="str">
+        <v>赤血球が通常より早く壊れる状態。単独の検査値ではなく、複数の検査値の組み合わせで疑う病態</v>
+      </c>
+      <c r="E28" t="str">
+        <v>溶血とは、赤血球が通常よりも早いペースで壊れてしまう状態のことです。壊れた赤血球からビリルビンなどが放出されるため、貧血や黄疸の原因になることがあります。</v>
+      </c>
+      <c r="F28" t="str">
+        <v>自己免疫性溶血性貧血、血液型不適合輸血、G6PD欠損症などの遺伝性疾患、機械弁など人工物による物理的破壊、薬剤性溶血</v>
+      </c>
+      <c r="G28" t="str">
+        <v>倦怠感、黄疸、尿の色が濃くなるなどの症状がないか確認する</v>
+      </c>
+      <c r="H28" t="str">
+        <v/>
+      </c>
+      <c r="I28" t="str">
+        <v/>
+      </c>
+      <c r="J28" t="str">
+        <v>溶血を疑う際は、間接ビリルビン上昇・LDH上昇・ハプトグロビン低下・網状赤血球増加のパターンを確認する。ヘモグロビン・MCV・MCHCの変化と合わせて総合的に判断する</v>
+      </c>
+      <c r="K28" t="str">
+        <v>鉄欠乏性貧血</v>
+      </c>
+      <c r="L28" t="str">
+        <v>溶血,Hemolysis,溶血性貧血,G6PD,ハプトグロビン</v>
+      </c>
+      <c r="M28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>黄疸</v>
+      </c>
+      <c r="B29" t="str">
+        <v>黄疸,Jaundice</v>
+      </c>
+      <c r="C29" t="str">
+        <v>所見なし（皮膚・眼球結膜の黄染がなければ正常）</v>
+      </c>
+      <c r="D29" t="str">
+        <v>ビリルビンが体にたまり、皮膚や白目が黄色くなる状態。単独の検査値ではなく、ビリルビン上昇によって表れる身体所見</v>
+      </c>
+      <c r="E29" t="str">
+        <v>黄疸は、体の中にビリルビンという黄色い色素がたまることで、皮膚や白目が黄色く見える状態です。肝臓や胆道のトラブル、赤血球が壊れやすくなる病気（溶血）などが原因となります。</v>
+      </c>
+      <c r="F29" t="str">
+        <v>肝炎・肝硬変などの肝疾患、胆石・腫瘍による胆道閉塞、溶血性疾患、体質性黄疸（ジルベール症候群）、新生児黄疸</v>
+      </c>
+      <c r="G29" t="str">
+        <v>白目や皮膚の黄染に気づいたら、尿の色（濃い茶色）や便の色（白っぽい）の変化も確認し、早めの受診を勧める</v>
+      </c>
+      <c r="H29" t="str">
+        <v/>
+      </c>
+      <c r="I29" t="str">
+        <v/>
+      </c>
+      <c r="J29" t="str">
+        <v>黄疸は検査値そのものではなく身体所見。原因を調べる際は総ビリルビン・直接ビリルビン・間接ビリルビンの内訳とAST/ALT/γ-GTPを確認する。直接優位なら胆道系、間接優位なら溶血・体質性を疑う</v>
+      </c>
+      <c r="K29" t="str">
+        <v>肝機能</v>
+      </c>
+      <c r="L29" t="str">
+        <v>黄疸,ジョンダイス,Jaundice,ビリルビン,皮膚黄染,白目</v>
+      </c>
+      <c r="M29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>中性脂肪（トリグリセリド）</v>
+      </c>
+      <c r="B30" t="str">
+        <v>TG</v>
+      </c>
+      <c r="C30" t="str">
+        <v>150 mg/dL未満（空腹時）</v>
+      </c>
+      <c r="D30" t="str">
+        <v>脂質異常症で高値になりやすい脂質で、食事の影響を強く受ける</v>
+      </c>
+      <c r="E30" t="str">
+        <v>中性脂肪は、食事から摂った脂肪や糖質が体に蓄えられる形になったものです。食後は誰でも一時的に上がるため、正確に評価するには空腹時に採血することが大切です。高い状態が続くと動脈硬化や急性膵炎のリスクが高まります。</v>
+      </c>
+      <c r="F30" t="str">
+        <v>脂質異常症、糖質・アルコールの摂りすぎ、肥満、糖尿病のコントロール不良</v>
+      </c>
+      <c r="G30" t="str">
+        <v>糖質・アルコールの摂りすぎに注意し、有酸素運動を勧める</v>
+      </c>
+      <c r="H30" t="str">
+        <v>低栄養、甲状腺機能亢進症</v>
+      </c>
+      <c r="I30" t="str">
+        <v/>
+      </c>
+      <c r="J30" t="str">
+        <v>採血が食後か空腹時かで数値が大きく変わるため必ず確認する。500 mg/dL以上では急性膵炎のリスクが高まるため注意。フィブラート系・EPA製剤などの効果判定に使う</v>
+      </c>
+      <c r="K30" t="str">
+        <v>脂質異常症</v>
+      </c>
+      <c r="L30" t="str">
+        <v>中性脂肪,トリグリセリド,TG,脂質異常症</v>
+      </c>
+      <c r="M30" t="str">
+        <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
         <v>総コレステロール</v>
       </c>
-      <c r="B22" t="str">
+      <c r="B31" t="str">
         <v>TC,T-cho</v>
       </c>
-      <c r="C22" t="str">
+      <c r="C31" t="str">
         <v>220 mg/dL未満</v>
       </c>
-      <c r="D22" t="str">
+      <c r="D31" t="str">
         <v>LDL・HDLなどすべてのコレステロールを合わせた総量</v>
       </c>
-      <c r="E22" t="str">
+      <c r="E31" t="str">
         <v>総コレステロールは、体の中にあるコレステロールをすべて合わせた数値です。ただし、悪玉(LDL)が多いのか善玉(HDL)が多いのかまでは分からないため、実際の評価にはLDLコレステロールの値がより重視されます。</v>
       </c>
-      <c r="F22" t="str">
+      <c r="F31" t="str">
         <v>脂質異常症、家族性高コレステロール血症、甲状腺機能低下症</v>
       </c>
-      <c r="G22" t="str">
+      <c r="G31" t="str">
         <v>動物性脂肪を控え、食物繊維を増やすよう伝える</v>
       </c>
-      <c r="H22" t="str">
+      <c r="H31" t="str">
         <v>低栄養、肝機能低下、甲状腺機能亢進症</v>
       </c>
-      <c r="I22" t="str">
-        <v/>
-      </c>
-      <c r="J22" t="str">
+      <c r="I31" t="str">
+        <v/>
+      </c>
+      <c r="J31" t="str">
         <v>現在はLDLコレステロールでの評価が主流。総コレステロールだけでは悪玉・善玉の内訳が分からないため、LDL・HDL・中性脂肪と合わせて評価する</v>
       </c>
-      <c r="K22" t="str">
+      <c r="K31" t="str">
         <v>脂質異常症</v>
       </c>
-      <c r="L22" t="str">
+      <c r="L31" t="str">
         <v>総コレステロール,TC,コレステロール,脂質異常症</v>
       </c>
-      <c r="M22" t="str">
+      <c r="M31" t="str">
         <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
       </c>
     </row>
-    <row r="23" xml:space="preserve">
-      <c r="A23" t="str">
+    <row r="32" xml:space="preserve">
+      <c r="A32" t="str">
         <v>LDLコレステロール</v>
       </c>
-      <c r="B23" t="str">
+      <c r="B32" t="str">
         <v>LDL-C</v>
       </c>
-      <c r="C23" t="str" xml:space="preserve">
+      <c r="C32" t="str" xml:space="preserve">
         <v xml:space="preserve">60〜139 mg/dL
 （140 mg/dL以上で高LDLコレステロール血症）</v>
       </c>
-      <c r="D23" t="str">
+      <c r="D32" t="str">
         <v>いわゆる「悪玉コレステロール」。血管の壁にたまり動脈硬化を進める</v>
       </c>
-      <c r="E23" t="str">
+      <c r="E32" t="str">
         <v>LDLコレステロールは、いわゆる悪玉コレステロールと呼ばれるものです。多いままだと血管の壁にたまって、動脈硬化や心筋梗塞・脳梗塞のリスクを高めます。数値を下げることで、将来の血管のトラブルを防ぐことが目的です。</v>
       </c>
-      <c r="F23" t="str">
+      <c r="F32" t="str">
         <v>脂質異常症、動脈硬化のリスク上昇、家族性高コレステロール血症、甲状腺機能低下症</v>
       </c>
-      <c r="G23" t="str">
+      <c r="G32" t="str">
         <v>動物性脂肪や揚げ物を控え、青魚や食物繊維（野菜・海藻・きのこ）を増やすよう伝える</v>
       </c>
-      <c r="H23" t="str">
+      <c r="H32" t="str">
         <v>低栄養、肝機能低下、甲状腺機能亢進症</v>
       </c>
-      <c r="I23" t="str">
-        <v/>
-      </c>
-      <c r="J23" t="str">
+      <c r="I32" t="str">
+        <v/>
+      </c>
+      <c r="J32" t="str">
         <v>スタチン等の効果判定に使う中心的な数値。目標値は既往疾患（冠動脈疾患・糖尿病等）によって異なるため一律に判断しない</v>
       </c>
-      <c r="K23" t="str">
+      <c r="K32" t="str">
         <v>脂質異常症,精神疾患（非定型抗精神病薬）</v>
       </c>
-      <c r="L23" t="str">
+      <c r="L32" t="str">
         <v>LDL,LDLコレステロール,悪玉コレステロール,脂質異常症</v>
       </c>
-      <c r="M23" t="str">
+      <c r="M32" t="str">
         <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>nonHDLコレステロール</v>
-      </c>
-      <c r="B24" t="str">
-        <v>non-HDL-C</v>
-      </c>
-      <c r="C24" t="str">
-        <v>90〜149 mg/dL（150 mg/dL以上で高値）</v>
-      </c>
-      <c r="D24" t="str">
-        <v>総コレステロールからHDL（善玉）を除いた、動脈硬化を進めるすべての脂質の合計</v>
-      </c>
-      <c r="E24" t="str">
-        <v>nonHDLコレステロールは、総コレステロールから善玉のHDLを引いた数値で、LDL（悪玉）を含む、動脈硬化を進めるすべてのコレステロールの合計を表します。中性脂肪が高くLDLだけでは評価しにくい方でも、こちらで動脈硬化のリスクを評価できます。</v>
-      </c>
-      <c r="F24" t="str">
-        <v>脂質異常症、動脈硬化のリスク上昇（特に中性脂肪が高い場合にLDL-Cより実態を反映しやすい）</v>
-      </c>
-      <c r="G24" t="str">
-        <v>動物性脂肪や揚げ物を控え、青魚や食物繊維（野菜・海藻・きのこ）を増やすよう伝える</v>
-      </c>
-      <c r="H24" t="str">
-        <v/>
-      </c>
-      <c r="I24" t="str">
-        <v/>
-      </c>
-      <c r="J24" t="str">
-        <v>中性脂肪（TG）が400 mg/dL以上などLDL-Cの計算式（Friedewald式）が不正確になる場合に、LDL-Cの代わりに用いられる。目標値はLDL-Cの目標値＋30 mg/dLが目安</v>
-      </c>
-      <c r="K24" t="str">
-        <v>脂質異常症</v>
-      </c>
-      <c r="L24" t="str">
-        <v>nonHDL,non-HDLコレステロール,動脈硬化,中性脂肪,LDL計算式</v>
-      </c>
-      <c r="M24" t="str">
-        <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>HDLコレステロール</v>
-      </c>
-      <c r="B25" t="str">
-        <v>HDL-C</v>
-      </c>
-      <c r="C25" t="str">
-        <v>40 mg/dL以上</v>
-      </c>
-      <c r="D25" t="str">
-        <v>いわゆる「善玉コレステロール」。血管にたまった余分なコレステロールを回収する</v>
-      </c>
-      <c r="E25" t="str">
-        <v>HDLコレステロールは、いわゆる善玉コレステロールと呼ばれるものです。血管の壁にたまった余分なコレステロールを回収して肝臓に戻す働きがあり、数値が高いほど動脈硬化を防ぐ方向に働きます。</v>
-      </c>
-      <c r="F25" t="str">
-        <v/>
-      </c>
-      <c r="G25" t="str">
-        <v/>
-      </c>
-      <c r="H25" t="str">
-        <v>脂質異常症（低HDL血症）</v>
-      </c>
-      <c r="I25" t="str">
-        <v>適度な運動習慣、禁煙を勧める</v>
-      </c>
-      <c r="J25" t="str">
-        <v>喫煙、運動不足、肥満で低下しやすい。禁煙・運動習慣の改善で上昇が期待できる。低HDLは動脈硬化のリスク因子として単独でも重視される</v>
-      </c>
-      <c r="K25" t="str">
-        <v>脂質異常症</v>
-      </c>
-      <c r="L25" t="str">
-        <v>HDL,HDLコレステロール,善玉コレステロール,脂質異常症</v>
-      </c>
-      <c r="M25" t="str">
-        <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>CK（クレアチンフォスフォキナーゼ）</v>
-      </c>
-      <c r="B26" t="str">
-        <v>CK,CPK</v>
-      </c>
-      <c r="C26" t="str">
-        <v>男性 60〜250 U/L、女性 50〜170 U/L</v>
-      </c>
-      <c r="D26" t="str">
-        <v>主に骨格筋・心筋に含まれる酵素。筋肉の損傷で血液中に漏れ出す</v>
-      </c>
-      <c r="E26" t="str">
-        <v>CKは筋肉の中にある酵素で、激しい運動や筋肉の病気、心筋梗塞などで筋肉の細胞がダメージを受けると血液中に漏れ出して数値が上がります。スタチン系のお薬の副作用（横紋筋融解症）のチェックにも使われます。</v>
-      </c>
-      <c r="F26" t="str">
-        <v>心筋梗塞、横紋筋融解症（スタチン系薬剤の副作用など）、激しい運動、筋肉注射直後、甲状腺機能低下症</v>
-      </c>
-      <c r="G26" t="str">
-        <v>筋肉痛・脱力感・褐色尿（横紋筋融解症の症状）がないか確認する。スタチン系薬剤服用中は特に注意する。激しい運動の直後の採血でないかも確認する</v>
-      </c>
-      <c r="H26" t="str">
-        <v/>
-      </c>
-      <c r="I26" t="str">
-        <v/>
-      </c>
-      <c r="J26" t="str">
-        <v>スタチン系薬剤の重大な副作用である横紋筋融解症の指標。筋肉痛・脱力感・褐色尿の有無を必ず確認し、著明高値では服薬継続の可否を医師に相談する</v>
-      </c>
-      <c r="K26" t="str">
-        <v/>
-      </c>
-      <c r="L26" t="str">
-        <v>CK,CPK,クレアチンキナーゼ,横紋筋融解症</v>
-      </c>
-      <c r="M26" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <v>TSH（甲状腺刺激ホルモン）</v>
-      </c>
-      <c r="B27" t="str">
-        <v>TSH</v>
-      </c>
-      <c r="C27" t="str">
-        <v>0.5〜5.0 μIU/mL程度（施設差あり）</v>
-      </c>
-      <c r="D27" t="str">
-        <v>甲状腺の働きが多いか少ないかを最も敏感に反映するホルモン</v>
-      </c>
-      <c r="E27" t="str">
-        <v>TSHは脳の下垂体から出て、甲状腺に「もっと働いて」と指令を送るホルモンです。甲状腺の働きが弱っていると体が指令を強めるためTSHは上がり、逆に甲状腺が働きすぎているとTSHは下がります。甲状腺の状態を最初に確認する数値としてよく使われます。</v>
-      </c>
-      <c r="F27" t="str">
-        <v>甲状腺機能低下症（橋本病など）、チラーヂンSなど甲状腺ホルモン薬の量不足</v>
-      </c>
-      <c r="G27" t="str">
-        <v>だるさ、むくみ、体重増加、寒がりなどの症状がないか確認する。服薬状況（飲み忘れ、他の薬との飲み合わせ）を確認する</v>
-      </c>
-      <c r="H27" t="str">
-        <v>甲状腺機能亢進症（バセドウ病など）、チラーヂンSなど甲状腺ホルモン薬の過量</v>
-      </c>
-      <c r="I27" t="str">
-        <v>動悸、体重減少、暑がり、手のふるえなどの症状がないか確認する</v>
-      </c>
-      <c r="J27" t="str">
-        <v>チラーヂンS服用中はTSHが治療目標域に収まっているかで用量調整の目安にする。メルカゾール服用中はTSH・FT4に加えて無顆粒球症の初期症状（発熱・のどの痛み）の有無や白血球数も確認する</v>
-      </c>
-      <c r="K27" t="str">
-        <v>甲状腺疾患</v>
-      </c>
-      <c r="L27" t="str">
-        <v>TSH,甲状腺刺激ホルモン,甲状腺機能,橋本病,バセドウ病,チラーヂン,メルカゾール</v>
-      </c>
-      <c r="M27" t="str">
-        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v>FT4（遊離サイロキシン）</v>
-      </c>
-      <c r="B28" t="str">
-        <v>FT4</v>
-      </c>
-      <c r="C28" t="str">
-        <v>0.9〜1.7 ng/dL程度（施設差あり）</v>
-      </c>
-      <c r="D28" t="str">
-        <v>甲状腺が実際に分泌しているホルモンの量そのものを表す数値</v>
-      </c>
-      <c r="E28" t="str">
-        <v>FT4は甲状腺そのものが作っているホルモンの量です。TSHが「指令の強さ」だとすると、FT4は「実際に出ている量」にあたります。2つをあわせて見ることで、甲状腺の働きが今どういう状態かを詳しく判断できます。</v>
-      </c>
-      <c r="F28" t="str">
-        <v>甲状腺機能亢進症（バセドウ病など）</v>
-      </c>
-      <c r="G28" t="str">
-        <v>動悸、体重減少、暑がり、手のふるえなどの症状がないか確認する</v>
-      </c>
-      <c r="H28" t="str">
-        <v>甲状腺機能低下症（橋本病など）</v>
-      </c>
-      <c r="I28" t="str">
-        <v>だるさ、むくみ、体重増加、寒がりなどの症状がないか確認する</v>
-      </c>
-      <c r="J28" t="str">
-        <v>TSHと逆方向に動くのが基本だが、下垂体性の異常など例外もある。TSHと合わせて評価し、片方だけで判断しない</v>
-      </c>
-      <c r="K28" t="str">
-        <v>甲状腺疾患</v>
-      </c>
-      <c r="L28" t="str">
-        <v>FT4,遊離サイロキシン,甲状腺ホルモン,甲状腺機能</v>
-      </c>
-      <c r="M28" t="str">
-        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="str">
-        <v>尿蛋白（随時尿）</v>
-      </c>
-      <c r="B29" t="str">
-        <v>尿蛋白,U-pro</v>
-      </c>
-      <c r="C29" t="str">
-        <v>陰性（－）〜弱陽性</v>
-      </c>
-      <c r="D29" t="str">
-        <v>腎臓から本来漏れないはずのたんぱくが尿に出ていないかを見る検査</v>
-      </c>
-      <c r="E29" t="str">
-        <v>この検査は、腎臓のろ過機能に負担がかかっていないかを見るものです。本来、たんぱく質は尿にほとんど出ませんが、腎臓に負担がかかると漏れ出るようになります。</v>
-      </c>
-      <c r="F29" t="str">
-        <v>糖尿病性腎症、腎炎、高血圧性腎硬化症、発熱・運動後の一過性のもの</v>
-      </c>
-      <c r="G29" t="str">
-        <v/>
-      </c>
-      <c r="H29" t="str">
-        <v/>
-      </c>
-      <c r="I29" t="str">
-        <v/>
-      </c>
-      <c r="J29" t="str">
-        <v>発熱・激しい運動・起立性蛋白尿など生理的な要因でも陽性になることがある。持続する場合に腎症の進行を疑う</v>
-      </c>
-      <c r="K29" t="str">
-        <v>糖尿病,腎機能</v>
-      </c>
-      <c r="L29" t="str">
-        <v>尿蛋白,U-pro,腎症,たんぱく尿</v>
-      </c>
-      <c r="M29" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="str">
-        <v>尿クレアチニン（随時尿）</v>
-      </c>
-      <c r="B30" t="str">
-        <v>尿CRE</v>
-      </c>
-      <c r="C30" t="str">
-        <v>随時尿は主に他項目の濃度補正に利用（単独の基準値は設けにくい）</v>
-      </c>
-      <c r="D30" t="str">
-        <v>随時尿中のクレアチニン濃度。他の尿検査項目を薄まり具合で補正するための基準として使う</v>
-      </c>
-      <c r="E30" t="str">
-        <v>この数値は、尿がどれくらい薄まっているかを確認するための基準として使われます。他の尿検査の結果（蛋白やアルブミンなど）をこの値で割って補正することで、水分摂取量による影響を減らして正確に評価できます。</v>
-      </c>
-      <c r="F30" t="str">
-        <v/>
-      </c>
-      <c r="G30" t="str">
-        <v/>
-      </c>
-      <c r="H30" t="str">
-        <v>尿が薄い（水分摂取が多い、腎機能低下）状態</v>
-      </c>
-      <c r="I30" t="str">
-        <v/>
-      </c>
-      <c r="J30" t="str">
-        <v>尿中アルブミン/Cr比、尿蛋白/Cr比など、他項目の補正計算に使われる。単独の高低に臨床的意味は乏しい</v>
-      </c>
-      <c r="K30" t="str">
-        <v>腎機能</v>
-      </c>
-      <c r="L30" t="str">
-        <v>尿CRE,尿クレアチニン,随時尿,補正,蛋白クレアチニン比</v>
-      </c>
-      <c r="M30" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="str">
-        <v>白血球（WBC）</v>
-      </c>
-      <c r="B31" t="str">
-        <v>WBC</v>
-      </c>
-      <c r="C31" t="str">
-        <v>3,300〜8,600 /μL程度（施設差あり）</v>
-      </c>
-      <c r="D31" t="str">
-        <v>体を細菌やウイルスから守る免疫細胞の数で、感染や炎症、薬剤の影響を反映する</v>
-      </c>
-      <c r="E31" t="str">
-        <v>白血球は体に入ってきた細菌やウイルスと戦う免疫細胞です。感染症や炎症があると増え、逆に一部のお薬の副作用や骨髄の働きが落ちると減ることがあります。</v>
-      </c>
-      <c r="F31" t="str">
-        <v>感染症、炎症、ステロイド使用、喫煙、白血病などの血液疾患</v>
-      </c>
-      <c r="G31" t="str">
-        <v>発熱や体の痛みなど感染症状がないか確認する</v>
-      </c>
-      <c r="H31" t="str">
-        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、メルカゾールなど薬剤性の無顆粒球症、再生不良性貧血、ウイルス感染</v>
-      </c>
-      <c r="I31" t="str">
-        <v>発熱、のどの痛みなど感染症状の初期サインがないか確認する。人混みを避け、手洗い・うがいを徹底するよう伝える</v>
-      </c>
-      <c r="J31" t="str">
-        <v>メルカゾール（チアマゾール）は無顆粒球症の重大な副作用があり、発熱・のどの痛みが出たらすぐ受診するよう指導する。抗がん剤・免疫抑制剤・抗てんかん薬（カルバマゼピンなど）使用中も定期的なモニタリングが必要</v>
-      </c>
-      <c r="K31" t="str">
-        <v>甲状腺疾患,てんかん</v>
-      </c>
-      <c r="L31" t="str">
-        <v>白血球,WBC,好中球,感染症,白血病,無顆粒球症,骨髄抑制</v>
-      </c>
-      <c r="M31" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="str">
-        <v>赤血球</v>
-      </c>
-      <c r="B32" t="str">
-        <v>RBC</v>
-      </c>
-      <c r="C32" t="str">
-        <v>男性 435〜555万/μL、女性 386〜492万/μL程度（施設差あり）</v>
-      </c>
-      <c r="D32" t="str">
-        <v>血液中で酸素を運ぶ細胞の数。ヘモグロビン・ヘマトクリットと合わせて貧血・多血症を評価する</v>
-      </c>
-      <c r="E32" t="str">
-        <v>赤血球は、肺で受け取った酸素を全身に運ぶ血液の細胞です。数が少ないと貧血、多いと多血症が疑われます。ヘモグロビンやヘマトクリットと合わせて総合的に評価します。</v>
-      </c>
-      <c r="F32" t="str">
-        <v>脱水、多血症（真性多血症、二次性多血症）、喫煙</v>
-      </c>
-      <c r="G32" t="str">
-        <v>脱水が疑われる場合はこまめな水分摂取を勧める（水分制限がある場合を除く）</v>
-      </c>
-      <c r="H32" t="str">
-        <v>貧血（鉄欠乏性貧血、腎性貧血など）、出血</v>
-      </c>
-      <c r="I32" t="str">
-        <v>ヘモグロビンと同様に、出血や食事量低下がないか確認する</v>
-      </c>
-      <c r="J32" t="str">
-        <v>ヘモグロビン・ヘマトクリットと同じ方向に動くことが多い。赤血球数だけでなくMCV・MCH・MCHCと合わせて貧血のタイプ(小球性・正球性・大球性)を判断する</v>
-      </c>
-      <c r="K32" t="str">
-        <v>鉄欠乏性貧血</v>
-      </c>
-      <c r="L32" t="str">
-        <v>赤血球,RBC,貧血,多血症</v>
-      </c>
-      <c r="M32" t="str">
-        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>ヘモグロビン濃度</v>
+        <v>nonHDLコレステロール</v>
       </c>
       <c r="B33" t="str">
-        <v>Hb</v>
+        <v>non-HDL-C</v>
       </c>
       <c r="C33" t="str">
-        <v>男性 13.5〜17.5 g/dL、女性 11.5〜15.0 g/dL</v>
+        <v>90〜149 mg/dL（150 mg/dL以上で高値）</v>
       </c>
       <c r="D33" t="str">
-        <v>血液の中で酸素を運ぶ役割をしている。この値が低い状態が貧血。</v>
+        <v>総コレステロールからHDL（善玉）を除いた、動脈硬化を進めるすべての脂質の合計</v>
       </c>
       <c r="E33" t="str">
-        <v>血の数値が良くなっても、体の中の鉄はまだ十分ではないことがあります。そのため、しばらく続けて飲むことが大切です。</v>
+        <v>nonHDLコレステロールは、総コレステロールから善玉のHDLを引いた数値で、LDL（悪玉）を含む、動脈硬化を進めるすべてのコレステロールの合計を表します。中性脂肪が高くLDLだけでは評価しにくい方でも、こちらで動脈硬化のリスクを評価できます。</v>
       </c>
       <c r="F33" t="str">
-        <v/>
+        <v>脂質異常症、動脈硬化のリスク上昇（特に中性脂肪が高い場合にLDL-Cより実態を反映しやすい）</v>
       </c>
       <c r="G33" t="str">
-        <v/>
+        <v>動物性脂肪や揚げ物を控え、青魚や食物繊維（野菜・海藻・きのこ）を増やすよう伝える</v>
       </c>
       <c r="H33" t="str">
-        <v>鉄欠乏性貧血、出血、腎性貧血、骨髄の造血機能低下</v>
+        <v/>
       </c>
       <c r="I33" t="str">
-        <v>鉄分の多い食品（レバー・赤身肉・魚・ほうれん草など）を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える</v>
+        <v/>
       </c>
       <c r="J33" t="str">
-        <v>原因（出血・食事量低下など）の確認が重要。腎機能低下がある場合は鉄不足以外が原因のこともある。鉄剤はヘモグロビンが正常化した後も2〜3か月程度は継続することが多い（鉄の貯蔵分を補うため。途中でやめると再び貧血になりやすい）</v>
+        <v>中性脂肪（TG）が400 mg/dL以上などLDL-Cの計算式（Friedewald式）が不正確になる場合に、LDL-Cの代わりに用いられる。目標値はLDL-Cの目標値＋30 mg/dLが目安</v>
       </c>
       <c r="K33" t="str">
-        <v>鉄欠乏性貧血,抗血小板療法,抗凝固療法（心房細動・血栓症）</v>
+        <v>脂質異常症</v>
       </c>
       <c r="L33" t="str">
-        <v>ヘモグロビン,Hb,貧血,鉄剤,鉄欠乏性貧血</v>
+        <v>nonHDL,non-HDLコレステロール,動脈硬化,中性脂肪,LDL計算式</v>
       </c>
       <c r="M33" t="str">
-        <v>食事と栄養 p.151-164（第2部 貧血）</v>
+        <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ヘマトクリット値</v>
+        <v>HDLコレステロール</v>
       </c>
       <c r="B34" t="str">
-        <v>Ht,Hct</v>
+        <v>HDL-C</v>
       </c>
       <c r="C34" t="str">
-        <v>男性 40〜50%、女性 35〜45%</v>
+        <v>40 mg/dL以上</v>
       </c>
       <c r="D34" t="str">
-        <v>血液全体のうち赤血球が占める体積の割合。貧血・脱水の指標</v>
+        <v>いわゆる「善玉コレステロール」。血管にたまった余分なコレステロールを回収する</v>
       </c>
       <c r="E34" t="str">
-        <v>ヘマトクリットは、血液全体のうち赤血球が占める割合を表す数値です。この値が低いと貧血、高いと脱水や血液が濃くなっている状態が疑われます。</v>
+        <v>HDLコレステロールは、いわゆる善玉コレステロールと呼ばれるものです。血管の壁にたまった余分なコレステロールを回収して肝臓に戻す働きがあり、数値が高いほど動脈硬化を防ぐ方向に働きます。</v>
       </c>
       <c r="F34" t="str">
-        <v>脱水、多血症（真性多血症、二次性多血症）、喫煙</v>
+        <v/>
       </c>
       <c r="G34" t="str">
-        <v>脱水が疑われる場合はこまめな水分摂取を勧める（水分制限がある場合を除く）</v>
+        <v/>
       </c>
       <c r="H34" t="str">
-        <v>貧血（鉄欠乏性貧血、腎性貧血など）、出血</v>
+        <v>脂質異常症（低HDL血症）</v>
       </c>
       <c r="I34" t="str">
-        <v>ヘモグロビンと同様に、出血や食事量低下がないか確認する</v>
+        <v>適度な運動習慣、禁煙を勧める</v>
       </c>
       <c r="J34" t="str">
-        <v>ヘモグロビン・赤血球数と合わせて評価する。3つの値は同じ方向に動くことが多く、脱水があると貧血が見かけ上隠れることがある</v>
+        <v>喫煙、運動不足、肥満で低下しやすい。禁煙・運動習慣の改善で上昇が期待できる。低HDLは動脈硬化のリスク因子として単独でも重視される</v>
       </c>
       <c r="K34" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>脂質異常症</v>
       </c>
       <c r="L34" t="str">
-        <v>ヘマトクリット,Ht,Hct,貧血,脱水,多血症</v>
+        <v>HDL,HDLコレステロール,善玉コレステロール,脂質異常症</v>
       </c>
       <c r="M34" t="str">
-        <v>食事と栄養 p.151-164（第2部 貧血）</v>
+        <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>MCV</v>
+        <v>CK（クレアチンフォスフォキナーゼ）</v>
       </c>
       <c r="B35" t="str">
-        <v>MCV</v>
+        <v>CK,CPK</v>
       </c>
       <c r="C35" t="str">
-        <v>79〜100 fL</v>
+        <v>男性 60〜250 U/L、女性 50〜170 U/L</v>
       </c>
       <c r="D35" t="str">
-        <v>赤血球1個の大きさ</v>
+        <v>主に骨格筋・心筋に含まれる酵素。筋肉の損傷で血液中に漏れ出す</v>
       </c>
       <c r="E35" t="str">
-        <v>MCVは赤血球1個あたりの大きさを表す数値です。貧血があるとき、この数値で「小さい貧血」か「大きい貧血」かを見分けることができ、原因を絞り込む手がかりになります。</v>
+        <v>CKは筋肉の中にある酵素で、激しい運動や筋肉の病気、心筋梗塞などで筋肉の細胞がダメージを受けると血液中に漏れ出して数値が上がります。スタチン系のお薬の副作用（横紋筋融解症）のチェックにも使われます。</v>
       </c>
       <c r="F35" t="str">
-        <v/>
+        <v>心筋梗塞、横紋筋融解症（スタチン系薬剤の副作用など）、激しい運動、筋肉注射直後、甲状腺機能低下症</v>
       </c>
       <c r="G35" t="str">
-        <v/>
+        <v>筋肉痛・脱力感・褐色尿（横紋筋融解症の症状）がないか確認する。スタチン系薬剤服用中は特に注意する。激しい運動の直後の採血でないかも確認する</v>
       </c>
       <c r="H35" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v/>
       </c>
       <c r="I35" t="str">
-        <v>鉄分の多い食事を意識する（ヘモグロビンの項目を参照）</v>
+        <v/>
       </c>
       <c r="J35" t="str">
-        <v/>
+        <v>スタチン系薬剤の重大な副作用である横紋筋融解症の指標。筋肉痛・脱力感・褐色尿の有無を必ず確認し、著明高値では服薬継続の可否を医師に相談する</v>
       </c>
       <c r="K35" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v/>
       </c>
       <c r="L35" t="str">
-        <v>MCV,赤血球指数,貧血</v>
+        <v>CK,CPK,クレアチンキナーゼ,横紋筋融解症</v>
       </c>
       <c r="M35" t="str">
-        <v>食事と栄養 p.151-164（第2部 貧血）</v>
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>MCH</v>
+        <v>TSH（甲状腺刺激ホルモン）</v>
       </c>
       <c r="B36" t="str">
-        <v>MCH</v>
+        <v>TSH</v>
       </c>
       <c r="C36" t="str">
-        <v>26.3〜34.3 pg</v>
+        <v>0.5〜5.0 μIU/mL程度（施設差あり）</v>
       </c>
       <c r="D36" t="str">
-        <v>赤血球1個に含まれるヘモグロビン量</v>
+        <v>甲状腺の働きが多いか少ないかを最も敏感に反映するホルモン</v>
       </c>
       <c r="E36" t="str">
-        <v>MCHは赤血球1個の中に含まれるヘモグロビン（酸素を運ぶ色素）の量を表す数値です。MCVと同じく、貧血の種類を見分けるのに使われます。</v>
+        <v>TSHは脳の下垂体から出て、甲状腺に「もっと働いて」と指令を送るホルモンです。甲状腺の働きが弱っていると体が指令を強めるためTSHは上がり、逆に甲状腺が働きすぎているとTSHは下がります。甲状腺の状態を最初に確認する数値としてよく使われます。</v>
       </c>
       <c r="F36" t="str">
-        <v/>
+        <v>甲状腺機能低下症（橋本病など）、チラーヂンSなど甲状腺ホルモン薬の量不足</v>
       </c>
       <c r="G36" t="str">
-        <v/>
+        <v>だるさ、むくみ、体重増加、寒がりなどの症状がないか確認する。服薬状況（飲み忘れ、他の薬との飲み合わせ）を確認する</v>
       </c>
       <c r="H36" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>甲状腺機能亢進症（バセドウ病など）、チラーヂンSなど甲状腺ホルモン薬の過量</v>
       </c>
       <c r="I36" t="str">
-        <v>鉄分の多い食事を意識する（ヘモグロビンの項目を参照）</v>
+        <v>動悸、体重減少、暑がり、手のふるえなどの症状がないか確認する</v>
       </c>
       <c r="J36" t="str">
-        <v/>
+        <v>チラーヂンS服用中はTSHが治療目標域に収まっているかで用量調整の目安にする。メルカゾール服用中はTSH・FT4に加えて無顆粒球症の初期症状（発熱・のどの痛み）の有無や白血球数も確認する</v>
       </c>
       <c r="K36" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>甲状腺疾患</v>
       </c>
       <c r="L36" t="str">
-        <v>MCH,赤血球指数,貧血</v>
+        <v>TSH,甲状腺刺激ホルモン,甲状腺機能,橋本病,バセドウ病,チラーヂン,メルカゾール</v>
       </c>
       <c r="M36" t="str">
-        <v>食事と栄養 p.151-164（第2部 貧血）</v>
+        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>MCHC</v>
+        <v>FT4（遊離サイロキシン）</v>
       </c>
       <c r="B37" t="str">
-        <v>MCHC</v>
+        <v>FT4</v>
       </c>
       <c r="C37" t="str">
-        <v>31.6〜36.6 %</v>
+        <v>0.9〜1.7 ng/dL程度（施設差あり）</v>
       </c>
       <c r="D37" t="str">
-        <v>単位容積あたりの赤血球に含まれるヘモグロビン濃度</v>
+        <v>甲状腺が実際に分泌しているホルモンの量そのものを表す数値</v>
       </c>
       <c r="E37" t="str">
-        <v>MCHCは、赤血球の中にヘモグロビンがどれくらい濃く詰まっているかを表す数値です。鉄が不足すると、この濃度も薄くなる傾向があります。</v>
+        <v>FT4は甲状腺そのものが作っているホルモンの量です。TSHが「指令の強さ」だとすると、FT4は「実際に出ている量」にあたります。2つをあわせて見ることで、甲状腺の働きが今どういう状態かを詳しく判断できます。</v>
       </c>
       <c r="F37" t="str">
-        <v/>
+        <v>甲状腺機能亢進症（バセドウ病など）</v>
       </c>
       <c r="G37" t="str">
-        <v/>
+        <v>動悸、体重減少、暑がり、手のふるえなどの症状がないか確認する</v>
       </c>
       <c r="H37" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>甲状腺機能低下症（橋本病など）</v>
       </c>
       <c r="I37" t="str">
-        <v>鉄分の多い食事を意識する（ヘモグロビンの項目を参照）</v>
+        <v>だるさ、むくみ、体重増加、寒がりなどの症状がないか確認する</v>
       </c>
       <c r="J37" t="str">
-        <v/>
+        <v>TSHと逆方向に動くのが基本だが、下垂体性の異常など例外もある。TSHと合わせて評価し、片方だけで判断しない</v>
       </c>
       <c r="K37" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>甲状腺疾患</v>
       </c>
       <c r="L37" t="str">
-        <v>MCHC,赤血球指数,貧血</v>
+        <v>FT4,遊離サイロキシン,甲状腺ホルモン,甲状腺機能</v>
       </c>
       <c r="M37" t="str">
-        <v>食事と栄養 p.151-164（第2部 貧血）</v>
+        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>血小板数</v>
+        <v>尿蛋白（随時尿）</v>
       </c>
       <c r="B38" t="str">
-        <v>Plt</v>
+        <v>尿蛋白,U-pro</v>
       </c>
       <c r="C38" t="str">
-        <v>15.0〜35.0万/μL程度（施設差あり）</v>
+        <v>陰性（－）〜弱陽性</v>
       </c>
       <c r="D38" t="str">
-        <v>出血を止める働きをする血液成分で、少なすぎると出血しやすくなる</v>
+        <v>腎臓から本来漏れないはずのたんぱくが尿に出ていないかを見る検査</v>
       </c>
       <c r="E38" t="str">
-        <v>血小板は、血管が傷ついたときに集まって血を止める役割をする血液の成分です。数が少ないとあざができやすくなったり、出血が止まりにくくなったりします。抗血小板薬や抗がん剤を使っている方では、定期的にチェックすることが大切です。</v>
+        <v>この検査は、腎臓のろ過機能に負担がかかっていないかを見るものです。本来、たんぱく質は尿にほとんど出ませんが、腎臓に負担がかかると漏れ出るようになります。</v>
       </c>
       <c r="F38" t="str">
-        <v>炎症性疾患、鉄欠乏性貧血、脾摘後、骨髄増殖性疾患</v>
+        <v>糖尿病性腎症、腎炎、高血圧性腎硬化症、発熱・運動後の一過性のもの</v>
       </c>
       <c r="G38" t="str">
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、肝硬変・脾機能亢進、再生不良性貧血、抗てんかん薬（バルプロ酸など）の副作用、ITP（特発性血小板減少性紫斑病）</v>
+        <v/>
       </c>
       <c r="I38" t="str">
-        <v>あざができやすい、歯ぐきや鼻からの出血が増えていないか確認する。強い運動や転倒によるけがに注意するよう伝える</v>
+        <v/>
       </c>
       <c r="J38" t="str">
-        <v>抗血小板薬・抗凝固薬使用中に血小板減少があると出血リスクがさらに高まる。抗がん剤・バルプロ酸・カルバマゼピンなど骨髄抑制のリスクがある薬剤使用中は定期採血の実施状況を確認する</v>
+        <v>発熱・激しい運動・起立性蛋白尿など生理的な要因でも陽性になることがある。持続する場合に腎症の進行を疑う</v>
       </c>
       <c r="K38" t="str">
-        <v>てんかん,抗血小板療法</v>
+        <v>糖尿病,腎機能</v>
       </c>
       <c r="L38" t="str">
-        <v>血小板,Plt,platelet,出血,あざ,紫斑,骨髄抑制</v>
+        <v>尿蛋白,U-pro,腎症,たんぱく尿</v>
       </c>
       <c r="M38" t="str">
         <v/>
@@ -1982,368 +1982,368 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>RDW-SD</v>
+        <v>尿クレアチニン（随時尿）</v>
       </c>
       <c r="B39" t="str">
-        <v>RDW-SD</v>
+        <v>尿CRE</v>
       </c>
       <c r="C39" t="str">
-        <v>39〜46 fL程度（施設差あり）</v>
+        <v>随時尿は主に他項目の濃度補正に利用（単独の基準値は設けにくい）</v>
       </c>
       <c r="D39" t="str">
-        <v>赤血球の大きさのばらつきを表す指標(絶対値)。鉄欠乏性貧血などの初期変化を捉えやすい</v>
+        <v>随時尿中のクレアチニン濃度。他の尿検査項目を薄まり具合で補正するための基準として使う</v>
       </c>
       <c r="E39" t="str">
-        <v>RDW-SDは、赤血球の大きさがどれくらいバラバラになっているかを表す数値です。貧血の原因を調べる際、鉄が足りなくなり始めた早い段階での変化を捉えるのに役立ちます。</v>
+        <v>この数値は、尿がどれくらい薄まっているかを確認するための基準として使われます。他の尿検査の結果（蛋白やアルブミンなど）をこの値で割って補正することで、水分摂取量による影響を減らして正確に評価できます。</v>
       </c>
       <c r="F39" t="str">
-        <v>鉄欠乏性貧血の初期、混合性貧血（複数の原因が重なっている状態）、赤血球産生の乱れ</v>
+        <v/>
       </c>
       <c r="G39" t="str">
         <v/>
       </c>
       <c r="H39" t="str">
-        <v/>
+        <v>尿が薄い（水分摂取が多い、腎機能低下）状態</v>
       </c>
       <c r="I39" t="str">
         <v/>
       </c>
       <c r="J39" t="str">
-        <v>MCVが正常範囲でもRDWが上昇している場合、鉄欠乏の初期段階を示唆することがある。MCV・MCHと合わせて評価する</v>
+        <v>尿中アルブミン/Cr比、尿蛋白/Cr比など、他項目の補正計算に使われる。単独の高低に臨床的意味は乏しい</v>
       </c>
       <c r="K39" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>腎機能</v>
       </c>
       <c r="L39" t="str">
-        <v>RDW-SD,赤血球分布幅,貧血,鉄欠乏</v>
+        <v>尿CRE,尿クレアチニン,随時尿,補正,蛋白クレアチニン比</v>
       </c>
       <c r="M39" t="str">
-        <v>食事と栄養 p.151-164（第2部 貧血）</v>
+        <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>RDW-CV</v>
+        <v>白血球（WBC）</v>
       </c>
       <c r="B40" t="str">
-        <v>RDW-CV</v>
+        <v>WBC</v>
       </c>
       <c r="C40" t="str">
-        <v>11.5〜14.5%程度（施設差あり）</v>
+        <v>3,300〜8,600 /μL程度（施設差あり）</v>
       </c>
       <c r="D40" t="str">
-        <v>赤血球の大きさのばらつきを割合(%)で表した指標</v>
+        <v>体を細菌やウイルスから守る免疫細胞の数で、感染や炎症、薬剤の影響を反映する</v>
       </c>
       <c r="E40" t="str">
-        <v>RDW-CVもRDW-SDと同じく、赤血球の大きさのばらつきを表す数値ですが、こちらは割合(%)で示されます。貧血のタイプを見分ける手がかりになります。</v>
+        <v>白血球は体に入ってきた細菌やウイルスと戦う免疫細胞です。感染症や炎症があると増え、逆に一部のお薬の副作用や骨髄の働きが落ちると減ることがあります。</v>
       </c>
       <c r="F40" t="str">
-        <v>鉄欠乏性貧血、ビタミンB12・葉酸欠乏性貧血、混合性貧血</v>
+        <v>感染症、炎症、ステロイド使用、喫煙、白血病などの血液疾患</v>
       </c>
       <c r="G40" t="str">
-        <v/>
+        <v>発熱や体の痛みなど感染症状がないか確認する</v>
       </c>
       <c r="H40" t="str">
-        <v/>
+        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、メルカゾールなど薬剤性の無顆粒球症、再生不良性貧血、ウイルス感染</v>
       </c>
       <c r="I40" t="str">
-        <v/>
+        <v>発熱、のどの痛みなど感染症状の初期サインがないか確認する。人混みを避け、手洗い・うがいを徹底するよう伝える</v>
       </c>
       <c r="J40" t="str">
-        <v>RDW-SDと同様の意味を持つ指標。MCVが小さくRDWが高ければ鉄欠乏性貧血、MCVが大きくRDWが高ければビタミンB12・葉酸欠乏を疑う手がかりになる</v>
+        <v>メルカゾール（チアマゾール）は無顆粒球症の重大な副作用があり、発熱・のどの痛みが出たらすぐ受診するよう指導する。抗がん剤・免疫抑制剤・抗てんかん薬（カルバマゼピンなど）使用中も定期的なモニタリングが必要</v>
       </c>
       <c r="K40" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L40" t="str">
-        <v>RDW-CV,赤血球分布幅,貧血,ビタミンB12,葉酸</v>
+        <v>白血球,WBC,好中球,感染症,白血病,無顆粒球症,骨髄抑制</v>
       </c>
       <c r="M40" t="str">
-        <v>食事と栄養 p.151-164（第2部 貧血）</v>
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>好中球実数値</v>
+        <v>赤血球</v>
       </c>
       <c r="B41" t="str">
-        <v>Neutro#,ANC</v>
+        <v>RBC</v>
       </c>
       <c r="C41" t="str">
-        <v>2,000〜7,500 /μL程度（施設差あり、白血球数×好中球%で算出）</v>
+        <v>男性 435〜555万/μL、女性 386〜492万/μL程度（施設差あり）</v>
       </c>
       <c r="D41" t="str">
-        <v>好中球の絶対数。感染症リスクを判断する上で割合(%)より重要な指標</v>
+        <v>血液中で酸素を運ぶ細胞の数。ヘモグロビン・ヘマトクリットと合わせて貧血・多血症を評価する</v>
       </c>
       <c r="E41" t="str">
-        <v>これは好中球の実際の数を表す数値です。割合(%)だけでなく、実際の数がどれくらいあるかを見ることで、感染症にかかりやすい状態かどうかをより正確に判断できます。</v>
+        <v>赤血球は、肺で受け取った酸素を全身に運ぶ血液の細胞です。数が少ないと貧血、多いと多血症が疑われます。ヘモグロビンやヘマトクリットと合わせて総合的に評価します。</v>
       </c>
       <c r="F41" t="str">
-        <v>細菌感染症、炎症、ステロイド使用</v>
+        <v>脱水、多血症（真性多血症、二次性多血症）、喫煙</v>
       </c>
       <c r="G41" t="str">
-        <v/>
+        <v>脱水が疑われる場合はこまめな水分摂取を勧める（水分制限がある場合を除く）</v>
       </c>
       <c r="H41" t="str">
-        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、メルカゾールなど薬剤性の無顆粒球症（1,000/μL未満で好中球減少症、500/μL未満で重症感染リスクが著しく上昇）</v>
+        <v>貧血（鉄欠乏性貧血、腎性貧血など）、出血</v>
       </c>
       <c r="I41" t="str">
-        <v>発熱、のどの痛みなど感染症状の初期サインがないか確認する。人混みを避け、手洗い・うがいを徹底するよう伝える</v>
+        <v>ヘモグロビンと同様に、出血や食事量低下がないか確認する</v>
       </c>
       <c r="J41" t="str">
-        <v>抗がん剤・メルカゾール・カルバマゼピンなど骨髄抑制のリスクがある薬剤使用中は特に重視すべき数値。500/μL未満は発熱性好中球減少症のリスクが高く緊急性が高い</v>
+        <v>ヘモグロビン・ヘマトクリットと同じ方向に動くことが多い。赤血球数だけでなくMCV・MCH・MCHCと合わせて貧血のタイプ(小球性・正球性・大球性)を判断する</v>
       </c>
       <c r="K41" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="L41" t="str">
-        <v>好中球実数値,好中球数,ANC,無顆粒球症,発熱性好中球減少症</v>
+        <v>赤血球,RBC,貧血,多血症</v>
       </c>
       <c r="M41" t="str">
-        <v/>
+        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>好酸球実数値</v>
+        <v>ヘモグロビン濃度</v>
       </c>
       <c r="B42" t="str">
-        <v>Eosino#</v>
+        <v>Hb</v>
       </c>
       <c r="C42" t="str">
-        <v>100〜500 /μL程度（施設差あり）</v>
+        <v>男性 13.5〜17.5 g/dL、女性 11.5〜15.0 g/dL</v>
       </c>
       <c r="D42" t="str">
-        <v>好酸球の絶対数。アレルギーや薬剤反応の程度をより正確に評価できる</v>
+        <v>血液の中で酸素を運ぶ役割をしている。この値が低い状態が貧血。</v>
       </c>
       <c r="E42" t="str">
-        <v>これは好酸球の実際の数を表す数値です。割合(%)だけでなく実数を見ることで、アレルギー反応の強さをより正確に把握できます。</v>
+        <v>血の数値が良くなっても、体の中の鉄はまだ十分ではないことがあります。そのため、しばらく続けて飲むことが大切です。</v>
       </c>
       <c r="F42" t="str">
-        <v>アレルギー性疾患、薬剤アレルギー、寄生虫感染</v>
+        <v/>
       </c>
       <c r="G42" t="str">
-        <v>新しく始めた薬がないか確認する</v>
+        <v/>
       </c>
       <c r="H42" t="str">
-        <v/>
+        <v>鉄欠乏性貧血、出血、腎性貧血、骨髄の造血機能低下</v>
       </c>
       <c r="I42" t="str">
-        <v/>
+        <v>鉄分の多い食品（レバー・赤身肉・魚・ほうれん草など）を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える</v>
       </c>
       <c r="J42" t="str">
-        <v>薬剤性過敏症症候群(DIHS)などでは著明な好酸球増多を認めることがあり、原因薬剤の特定に役立つ</v>
+        <v>原因（出血・食事量低下など）の確認が重要。腎機能低下がある場合は鉄不足以外が原因のこともある。鉄剤はヘモグロビンが正常化した後も2〜3か月程度は継続することが多い（鉄の貯蔵分を補うため。途中でやめると再び貧血になりやすい）</v>
       </c>
       <c r="K42" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>鉄欠乏性貧血,抗血小板療法,抗凝固療法（心房細動・血栓症）</v>
       </c>
       <c r="L42" t="str">
-        <v>好酸球実数値,好酸球数,アレルギー,DIHS</v>
+        <v>ヘモグロビン,Hb,貧血,鉄剤,鉄欠乏性貧血</v>
       </c>
       <c r="M42" t="str">
-        <v/>
+        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>好塩基球実数値</v>
+        <v>ヘマトクリット値</v>
       </c>
       <c r="B43" t="str">
-        <v>Baso#</v>
+        <v>Ht,Hct</v>
       </c>
       <c r="C43" t="str">
-        <v>0〜100 /μL程度（施設差あり）</v>
+        <v>男性 40〜50%、女性 35〜45%</v>
       </c>
       <c r="D43" t="str">
-        <v>好塩基球の絶対数</v>
+        <v>血液全体のうち赤血球が占める体積の割合。貧血・脱水の指標</v>
       </c>
       <c r="E43" t="str">
-        <v>これは好塩基球の実際の数を表す数値です。数がとても少ない種類の血球なので、通常は大きな変動を示すことは多くありません。</v>
+        <v>ヘマトクリットは、血液全体のうち赤血球が占める割合を表す数値です。この値が低いと貧血、高いと脱水や血液が濃くなっている状態が疑われます。</v>
       </c>
       <c r="F43" t="str">
-        <v>慢性骨髄性白血病などの血液疾患、アレルギー性疾患</v>
+        <v>脱水、多血症（真性多血症、二次性多血症）、喫煙</v>
       </c>
       <c r="G43" t="str">
-        <v/>
+        <v>脱水が疑われる場合はこまめな水分摂取を勧める（水分制限がある場合を除く）</v>
       </c>
       <c r="H43" t="str">
-        <v/>
+        <v>貧血（鉄欠乏性貧血、腎性貧血など）、出血</v>
       </c>
       <c r="I43" t="str">
-        <v/>
+        <v>ヘモグロビンと同様に、出血や食事量低下がないか確認する</v>
       </c>
       <c r="J43" t="str">
-        <v>単独での臨床的意義は乏しく、他の血球指標（白血球分画全体）と合わせて評価する</v>
+        <v>ヘモグロビン・赤血球数と合わせて評価する。3つの値は同じ方向に動くことが多く、脱水があると貧血が見かけ上隠れることがある</v>
       </c>
       <c r="K43" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="L43" t="str">
-        <v>好塩基球実数値,好塩基球数</v>
+        <v>ヘマトクリット,Ht,Hct,貧血,脱水,多血症</v>
       </c>
       <c r="M43" t="str">
-        <v/>
+        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>リンパ球実数値</v>
+        <v>MCV</v>
       </c>
       <c r="B44" t="str">
-        <v>Lympho#,ALC</v>
+        <v>MCV</v>
       </c>
       <c r="C44" t="str">
-        <v>1,000〜3,600 /μL程度（施設差あり）</v>
+        <v>79〜100 fL</v>
       </c>
       <c r="D44" t="str">
-        <v>リンパ球の絶対数。免疫力の目安として使われる</v>
+        <v>赤血球1個の大きさ</v>
       </c>
       <c r="E44" t="str">
-        <v>これはリンパ球の実際の数を表す数値です。免疫力の目安の一つとして使われ、抗がん剤や免疫抑制剤の副作用モニタリングにも用いられます。</v>
+        <v>MCVは赤血球1個あたりの大きさを表す数値です。貧血があるとき、この数値で「小さい貧血」か「大きい貧血」かを見分けることができ、原因を絞り込む手がかりになります。</v>
       </c>
       <c r="F44" t="str">
-        <v>ウイルス感染症、リンパ性白血病などの血液疾患</v>
+        <v/>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>抗がん剤・免疫抑制剤・ステロイドの使用、強いストレス、AIDSなどの免疫不全</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="I44" t="str">
-        <v>感染予防（手洗い・うがい、人混みを避ける）を意識するよう伝える</v>
+        <v>鉄分の多い食事を意識する（ヘモグロビンの項目を参照）</v>
       </c>
       <c r="J44" t="str">
-        <v>免疫抑制剤・抗がん剤治療中のモニタリング指標としても使われる。著明な低下時は日和見感染のリスクが高まる</v>
+        <v/>
       </c>
       <c r="K44" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="L44" t="str">
-        <v>リンパ球実数値,リンパ球数,ALC,免疫抑制剤,日和見感染</v>
+        <v>MCV,赤血球指数,貧血</v>
       </c>
       <c r="M44" t="str">
-        <v/>
+        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>単球実数値</v>
+        <v>MCH</v>
       </c>
       <c r="B45" t="str">
-        <v>Mono#</v>
+        <v>MCH</v>
       </c>
       <c r="C45" t="str">
-        <v>200〜600 /μL程度（施設差あり）</v>
+        <v>26.3〜34.3 pg</v>
       </c>
       <c r="D45" t="str">
-        <v>単球の絶対数</v>
+        <v>赤血球1個に含まれるヘモグロビン量</v>
       </c>
       <c r="E45" t="str">
-        <v>これは単球の実際の数を表す数値です。慢性的な炎症や感染症の状態を把握する材料の一つになります。</v>
+        <v>MCHは赤血球1個の中に含まれるヘモグロビン（酸素を運ぶ色素）の量を表す数値です。MCVと同じく、貧血の種類を見分けるのに使われます。</v>
       </c>
       <c r="F45" t="str">
-        <v>慢性感染症、炎症性疾患、血液疾患</v>
+        <v/>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v/>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="I45" t="str">
-        <v/>
+        <v>鉄分の多い食事を意識する（ヘモグロビンの項目を参照）</v>
       </c>
       <c r="J45" t="str">
-        <v>単独での臨床的意義は乏しく、他の血球指標と合わせて評価する</v>
+        <v/>
       </c>
       <c r="K45" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="L45" t="str">
-        <v>単球実数値,単球数</v>
+        <v>MCH,赤血球指数,貧血</v>
       </c>
       <c r="M45" t="str">
-        <v/>
+        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>好中球</v>
+        <v>MCHC</v>
       </c>
       <c r="B46" t="str">
-        <v>Neutro,Neut%</v>
+        <v>MCHC</v>
       </c>
       <c r="C46" t="str">
-        <v>40〜75%程度（施設差あり）</v>
+        <v>31.6〜36.6 %</v>
       </c>
       <c r="D46" t="str">
-        <v>白血球の中で最も多くを占め、細菌感染と戦う主力の免疫細胞の割合</v>
+        <v>単位容積あたりの赤血球に含まれるヘモグロビン濃度</v>
       </c>
       <c r="E46" t="str">
-        <v>好中球は、白血球の中で最も数が多く、細菌が体に入ってきたときに真っ先に戦ってくれる免疫細胞です。感染症や炎症があると増え、逆に薬の副作用などで減ることがあります。</v>
+        <v>MCHCは、赤血球の中にヘモグロビンがどれくらい濃く詰まっているかを表す数値です。鉄が不足すると、この濃度も薄くなる傾向があります。</v>
       </c>
       <c r="F46" t="str">
-        <v>細菌感染症、炎症、ストレス、ステロイド使用</v>
+        <v/>
       </c>
       <c r="G46" t="str">
-        <v>発熱や炎症症状がないか確認する</v>
+        <v/>
       </c>
       <c r="H46" t="str">
-        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、ウイルス感染、メルカゾールなど薬剤性の無顆粒球症</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="I46" t="str">
-        <v>発熱やのどの痛みなど感染症状の初期サインがないか確認する</v>
+        <v>鉄分の多い食事を意識する（ヘモグロビンの項目を参照）</v>
       </c>
       <c r="J46" t="str">
-        <v>好中球の絶対数（好中球実数値）が500/μL未満になると重篤な感染症のリスクが高まる。割合(%)だけでなく実数値も合わせて確認する</v>
+        <v/>
       </c>
       <c r="K46" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="L46" t="str">
-        <v>好中球,Neutro,Neut,感染症,無顆粒球症</v>
+        <v>MCHC,赤血球指数,貧血</v>
       </c>
       <c r="M46" t="str">
-        <v/>
+        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>好酸球</v>
+        <v>血小板数</v>
       </c>
       <c r="B47" t="str">
-        <v>Eosino,Eos%</v>
+        <v>Plt</v>
       </c>
       <c r="C47" t="str">
-        <v>1〜5%程度（施設差あり）</v>
+        <v>15.0〜35.0万/μL程度（施設差あり）</v>
       </c>
       <c r="D47" t="str">
-        <v>アレルギー反応や寄生虫感染に関わる白血球の一種の割合</v>
+        <v>出血を止める働きをする血液成分で、少なすぎると出血しやすくなる</v>
       </c>
       <c r="E47" t="str">
-        <v>好酸球は、アレルギー反応や寄生虫感染と関係が深い免疫細胞です。アレルギー性の病気や薬の副作用（薬疹など）で増えることがあります。</v>
+        <v>血小板は、血管が傷ついたときに集まって血を止める役割をする血液の成分です。数が少ないとあざができやすくなったり、出血が止まりにくくなったりします。抗血小板薬や抗がん剤を使っている方では、定期的にチェックすることが大切です。</v>
       </c>
       <c r="F47" t="str">
-        <v>アレルギー性疾患（気管支喘息、アトピー性皮膚炎など）、薬剤アレルギー、寄生虫感染</v>
+        <v>炎症性疾患、鉄欠乏性貧血、脾摘後、骨髄増殖性疾患</v>
       </c>
       <c r="G47" t="str">
-        <v>新しく始めた薬がないか確認する。皮疹やかゆみなどアレルギー症状の有無を確認する</v>
+        <v/>
       </c>
       <c r="H47" t="str">
-        <v/>
+        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、肝硬変・脾機能亢進、再生不良性貧血、抗てんかん薬（バルプロ酸など）の副作用、ITP（特発性血小板減少性紫斑病）</v>
       </c>
       <c r="I47" t="str">
-        <v/>
+        <v>あざができやすい、歯ぐきや鼻からの出血が増えていないか確認する。強い運動や転倒によるけがに注意するよう伝える</v>
       </c>
       <c r="J47" t="str">
-        <v>薬剤性の好酸球増多は、原因薬剤の中止で改善することが多い。新規薬剤開始後の皮疹・発熱と合わせて薬剤性過敏症症候群(DIHS)を疑う材料になる</v>
+        <v>抗血小板薬・抗凝固薬使用中に血小板減少があると出血リスクがさらに高まる。抗がん剤・バルプロ酸・カルバマゼピンなど骨髄抑制のリスクがある薬剤使用中は定期採血の実施状況を確認する</v>
       </c>
       <c r="K47" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>てんかん,抗血小板療法</v>
       </c>
       <c r="L47" t="str">
-        <v>好酸球,Eosino,Eos,アレルギー,薬疹,DIHS</v>
+        <v>血小板,Plt,platelet,出血,あざ,紫斑,骨髄抑制</v>
       </c>
       <c r="M47" t="str">
         <v/>
@@ -2351,22 +2351,22 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>好塩基球</v>
+        <v>RDW-SD</v>
       </c>
       <c r="B48" t="str">
-        <v>Baso,Baso%</v>
+        <v>RDW-SD</v>
       </c>
       <c r="C48" t="str">
-        <v>0〜2%程度（施設差あり）</v>
+        <v>39〜46 fL程度（施設差あり）</v>
       </c>
       <c r="D48" t="str">
-        <v>白血球の中で最も数が少なく、アレルギー反応に関わる細胞の割合</v>
+        <v>赤血球の大きさのばらつきを表す指標(絶対値)。鉄欠乏性貧血などの初期変化を捉えやすい</v>
       </c>
       <c r="E48" t="str">
-        <v>好塩基球は白血球の中で最も数が少ない種類で、アレルギー反応や炎症に関わっています。数値の変動が病気の診断に直接使われることは少ない検査です。</v>
+        <v>RDW-SDは、赤血球の大きさがどれくらいバラバラになっているかを表す数値です。貧血の原因を調べる際、鉄が足りなくなり始めた早い段階での変化を捉えるのに役立ちます。</v>
       </c>
       <c r="F48" t="str">
-        <v>慢性骨髄性白血病などの血液疾患、アレルギー性疾患、甲状腺機能低下症</v>
+        <v>鉄欠乏性貧血の初期、混合性貧血（複数の原因が重なっている状態）、赤血球産生の乱れ</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2378,95 +2378,95 @@
         <v/>
       </c>
       <c r="J48" t="str">
-        <v>単独での臨床的意義は乏しいが、著明な増加は血液疾患（慢性骨髄性白血病等）の可能性があり他の血球指標と合わせて評価する</v>
+        <v>MCVが正常範囲でもRDWが上昇している場合、鉄欠乏の初期段階を示唆することがある。MCV・MCHと合わせて評価する</v>
       </c>
       <c r="K48" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="L48" t="str">
-        <v>好塩基球,Baso,アレルギー,白血病</v>
+        <v>RDW-SD,赤血球分布幅,貧血,鉄欠乏</v>
       </c>
       <c r="M48" t="str">
-        <v/>
+        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>リンパ球</v>
+        <v>RDW-CV</v>
       </c>
       <c r="B49" t="str">
-        <v>Lympho,Lym%</v>
+        <v>RDW-CV</v>
       </c>
       <c r="C49" t="str">
-        <v>18〜49%程度（施設差あり）</v>
+        <v>11.5〜14.5%程度（施設差あり）</v>
       </c>
       <c r="D49" t="str">
-        <v>ウイルス感染と戦い、免疫の記憶を担う白血球の割合</v>
+        <v>赤血球の大きさのばらつきを割合(%)で表した指標</v>
       </c>
       <c r="E49" t="str">
-        <v>リンパ球は、ウイルスと戦ったり、一度かかった病気を記憶して免疫をつくったりする細胞です。ウイルス感染で増え、抗がん剤の副作用や強いストレスで減ることがあります。</v>
+        <v>RDW-CVもRDW-SDと同じく、赤血球の大きさのばらつきを表す数値ですが、こちらは割合(%)で示されます。貧血のタイプを見分ける手がかりになります。</v>
       </c>
       <c r="F49" t="str">
-        <v>ウイルス感染症、リンパ性白血病などの血液疾患、百日咳</v>
+        <v>鉄欠乏性貧血、ビタミンB12・葉酸欠乏性貧血、混合性貧血</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>抗がん剤・免疫抑制剤・ステロイドの使用、強いストレス、AIDSなどの免疫不全</v>
+        <v/>
       </c>
       <c r="I49" t="str">
-        <v>免疫が下がっている可能性があるため、感染予防（手洗い・うがい、人混みを避ける）を意識するよう伝える</v>
+        <v/>
       </c>
       <c r="J49" t="str">
-        <v>ステロイド・免疫抑制剤使用中はリンパ球減少による易感染性に注意。好中球と逆方向に動くことが多い（ウイルス感染ではリンパ球優位、細菌感染では好中球優位になりやすい）</v>
+        <v>RDW-SDと同様の意味を持つ指標。MCVが小さくRDWが高ければ鉄欠乏性貧血、MCVが大きくRDWが高ければビタミンB12・葉酸欠乏を疑う手がかりになる</v>
       </c>
       <c r="K49" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="L49" t="str">
-        <v>リンパ球,Lympho,Lym,ウイルス感染,免疫抑制剤,ステロイド</v>
+        <v>RDW-CV,赤血球分布幅,貧血,ビタミンB12,葉酸</v>
       </c>
       <c r="M49" t="str">
-        <v/>
+        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>単球</v>
+        <v>好中球実数値</v>
       </c>
       <c r="B50" t="str">
-        <v>Mono,Mono%</v>
+        <v>Neutro#,ANC</v>
       </c>
       <c r="C50" t="str">
-        <v>2〜10%程度（施設差あり）</v>
+        <v>2,000〜7,500 /μL程度（施設差あり、白血球数×好中球%で算出）</v>
       </c>
       <c r="D50" t="str">
-        <v>感染や炎症の後始末をする白血球の一種の割合</v>
+        <v>好中球の絶対数。感染症リスクを判断する上で割合(%)より重要な指標</v>
       </c>
       <c r="E50" t="str">
-        <v>単球は、細菌などを取り込んで処理したり、組織の修復に関わったりする免疫細胞です。慢性的な炎症や感染症の回復期に増えることがあります。</v>
+        <v>これは好中球の実際の数を表す数値です。割合(%)だけでなく、実際の数がどれくらいあるかを見ることで、感染症にかかりやすい状態かどうかをより正確に判断できます。</v>
       </c>
       <c r="F50" t="str">
-        <v>慢性感染症（結核など）、炎症性疾患、血液疾患、感染症の回復期</v>
+        <v>細菌感染症、炎症、ステロイド使用</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v/>
+        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、メルカゾールなど薬剤性の無顆粒球症（1,000/μL未満で好中球減少症、500/μL未満で重症感染リスクが著しく上昇）</v>
       </c>
       <c r="I50" t="str">
-        <v/>
+        <v>発熱、のどの痛みなど感染症状の初期サインがないか確認する。人混みを避け、手洗い・うがいを徹底するよう伝える</v>
       </c>
       <c r="J50" t="str">
-        <v>単独での臨床的意義は乏しく、他の血球指標や炎症マーカー(CRPなど)と合わせて評価する</v>
+        <v>抗がん剤・メルカゾール・カルバマゼピンなど骨髄抑制のリスクがある薬剤使用中は特に重視すべき数値。500/μL未満は発熱性好中球減少症のリスクが高く緊急性が高い</v>
       </c>
       <c r="K50" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L50" t="str">
-        <v>単球,Mono,慢性感染症,結核,炎症</v>
+        <v>好中球実数値,好中球数,ANC,無顆粒球症,発熱性好中球減少症</v>
       </c>
       <c r="M50" t="str">
         <v/>
@@ -2474,40 +2474,40 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>尿pH</v>
+        <v>好酸球実数値</v>
       </c>
       <c r="B51" t="str">
-        <v>尿pH</v>
+        <v>Eosino#</v>
       </c>
       <c r="C51" t="str">
-        <v>4.5〜7.5程度（弱酸性が多い）</v>
+        <v>100〜500 /μL程度（施設差あり）</v>
       </c>
       <c r="D51" t="str">
-        <v>尿の酸性・アルカリ性の度合い。食事や感染症、体の状態を反映する</v>
+        <v>好酸球の絶対数。アレルギーや薬剤反応の程度をより正確に評価できる</v>
       </c>
       <c r="E51" t="str">
-        <v>尿のpHは酸性・アルカリ性のバランスを表します。食事の内容や感染症、体の代謝状態によって変化します。単独で大きな問題を示すことは少ない検査です。</v>
+        <v>これは好酸球の実際の数を表す数値です。割合(%)だけでなく実数を見ることで、アレルギー反応の強さをより正確に把握できます。</v>
       </c>
       <c r="F51" t="str">
-        <v>尿路感染症（尿素分解菌によるもの）、野菜中心の食事、過換気</v>
+        <v>アレルギー性疾患、薬剤アレルギー、寄生虫感染</v>
       </c>
       <c r="G51" t="str">
-        <v/>
+        <v>新しく始めた薬がないか確認する</v>
       </c>
       <c r="H51" t="str">
-        <v>高たんぱく食、糖尿病性ケトアシドーシス、痛風発作時（酸性尿は尿酸結石のリスクを高める）</v>
+        <v/>
       </c>
       <c r="I51" t="str">
-        <v>痛風・尿酸結石がある場合は、野菜など尿をアルカリ化する食品を意識するとよいことを伝える</v>
+        <v/>
       </c>
       <c r="J51" t="str">
-        <v>高尿酸血症・尿酸結石の患者では尿pHが酸性に傾いていないか確認する。尿アルカリ化薬（ウラリットなど）の効果判定にも使う</v>
+        <v>薬剤性過敏症症候群(DIHS)などでは著明な好酸球増多を認めることがあり、原因薬剤の特定に役立つ</v>
       </c>
       <c r="K51" t="str">
-        <v>高尿酸血症</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L51" t="str">
-        <v>尿pH,尿酸性度,尿アルカリ化,ウラリット</v>
+        <v>好酸球実数値,好酸球数,アレルギー,DIHS</v>
       </c>
       <c r="M51" t="str">
         <v/>
@@ -2515,22 +2515,22 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>尿ケトン体</v>
+        <v>好塩基球実数値</v>
       </c>
       <c r="B52" t="str">
-        <v>尿ケトン,Ket</v>
+        <v>Baso#</v>
       </c>
       <c r="C52" t="str">
-        <v>陰性（－）</v>
+        <v>0〜100 /μL程度（施設差あり）</v>
       </c>
       <c r="D52" t="str">
-        <v>体がブドウ糖の代わりに脂肪を分解してエネルギーを作っているサイン</v>
+        <v>好塩基球の絶対数</v>
       </c>
       <c r="E52" t="str">
-        <v>この検査は、体が糖の代わりに脂肪を使ってエネルギーを作っていないかを見るものです。陽性が続くときは、食事や水分、インスリンの使い方を確認する必要があります。</v>
+        <v>これは好塩基球の実際の数を表す数値です。数がとても少ない種類の血球なので、通常は大きな変動を示すことは多くありません。</v>
       </c>
       <c r="F52" t="str">
-        <v>糖尿病の血糖コントロール不良（シックデイ・インスリン不足）、極端な糖質制限、絶食、嘔吐・下痢による脱水</v>
+        <v>慢性骨髄性白血病などの血液疾患、アレルギー性疾患</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2542,13 +2542,13 @@
         <v/>
       </c>
       <c r="J52" t="str">
-        <v>陽性かつ高血糖・全身倦怠感が強い場合は糖尿病性ケトアシドーシスの可能性があり緊急性が高い。シックデイルールの説明歴を確認する</v>
+        <v>単独での臨床的意義は乏しく、他の血球指標（白血球分画全体）と合わせて評価する</v>
       </c>
       <c r="K52" t="str">
-        <v>糖尿病</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L52" t="str">
-        <v>尿ケトン体,ケトン体,Ket,シックデイ,ケトアシドーシス</v>
+        <v>好塩基球実数値,好塩基球数</v>
       </c>
       <c r="M52" t="str">
         <v/>
@@ -2556,40 +2556,40 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ウロビリノーゲン</v>
+        <v>リンパ球実数値</v>
       </c>
       <c r="B53" t="str">
-        <v>Uro</v>
+        <v>Lympho#,ALC</v>
       </c>
       <c r="C53" t="str">
-        <v>正常（±）程度</v>
+        <v>1,000〜3,600 /μL程度（施設差あり）</v>
       </c>
       <c r="D53" t="str">
-        <v>肝臓や胆道、赤血球の壊れ方の状態を反映する尿検査項目</v>
+        <v>リンパ球の絶対数。免疫力の目安として使われる</v>
       </c>
       <c r="E53" t="str">
-        <v>ウロビリノーゲンは、赤血球やビリルビンが体の中で処理される過程でできる物質です。肝臓の働きが悪くなったり、赤血球が壊れやすくなったりすると、尿の中の量が変化します。</v>
+        <v>これはリンパ球の実際の数を表す数値です。免疫力の目安の一つとして使われ、抗がん剤や免疫抑制剤の副作用モニタリングにも用いられます。</v>
       </c>
       <c r="F53" t="str">
-        <v>溶血性疾患（赤血球の破壊亢進）、肝機能障害</v>
+        <v>ウイルス感染症、リンパ性白血病などの血液疾患</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>胆道閉塞（胆汁が腸に流れず、ウロビリノーゲンが作られない状態）</v>
+        <v>抗がん剤・免疫抑制剤・ステロイドの使用、強いストレス、AIDSなどの免疫不全</v>
       </c>
       <c r="I53" t="str">
-        <v/>
+        <v>感染予防（手洗い・うがい、人混みを避ける）を意識するよう伝える</v>
       </c>
       <c r="J53" t="str">
-        <v>完全に陰性の場合は胆道閉塞を疑う所見の一つ。肝機能（AST/ALT/ビリルビン）と合わせて評価する</v>
+        <v>免疫抑制剤・抗がん剤治療中のモニタリング指標としても使われる。著明な低下時は日和見感染のリスクが高まる</v>
       </c>
       <c r="K53" t="str">
-        <v>肝機能</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L53" t="str">
-        <v>ウロビリノーゲン,Uro,溶血,胆道閉塞,肝機能</v>
+        <v>リンパ球実数値,リンパ球数,ALC,免疫抑制剤,日和見感染</v>
       </c>
       <c r="M53" t="str">
         <v/>
@@ -2597,25 +2597,25 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>尿潜血反応</v>
+        <v>単球実数値</v>
       </c>
       <c r="B54" t="str">
-        <v>尿潜血,U-OB</v>
+        <v>Mono#</v>
       </c>
       <c r="C54" t="str">
-        <v>陰性（－）</v>
+        <v>200〜600 /μL程度（施設差あり）</v>
       </c>
       <c r="D54" t="str">
-        <v>尿に血液（赤血球）が混じっていないかを見る検査</v>
+        <v>単球の絶対数</v>
       </c>
       <c r="E54" t="str">
-        <v>この検査は、尿に目に見えないくらいの微量の血液が混じっていないかを調べるものです。陽性の場合、腎臓や膀胱、尿路のどこかに炎症や結石などがある可能性があります。</v>
+        <v>これは単球の実際の数を表す数値です。慢性的な炎症や感染症の状態を把握する材料の一つになります。</v>
       </c>
       <c r="F54" t="str">
-        <v>尿路結石、膀胱炎などの尿路感染症、腎炎、腫瘍、月経血の混入、激しい運動後</v>
+        <v>慢性感染症、炎症性疾患、血液疾患</v>
       </c>
       <c r="G54" t="str">
-        <v>排尿時の痛みや頻尿、目に見える血尿の有無を確認する。女性は月経の時期と重なっていないか確認する</v>
+        <v/>
       </c>
       <c r="H54" t="str">
         <v/>
@@ -2624,13 +2624,13 @@
         <v/>
       </c>
       <c r="J54" t="str">
-        <v>陽性でも尿沈渣で赤血球が確認されない場合は偽陽性（ミオグロビン尿など）のこともある。持続する場合は泌尿器科的な精査が必要</v>
+        <v>単独での臨床的意義は乏しく、他の血球指標と合わせて評価する</v>
       </c>
       <c r="K54" t="str">
-        <v>腎機能</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L54" t="str">
-        <v>尿潜血,潜血反応,U-OB,血尿,尿路結石,膀胱炎</v>
+        <v>単球実数値,単球数</v>
       </c>
       <c r="M54" t="str">
         <v/>
@@ -2638,40 +2638,40 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>尿糖（半定量）</v>
+        <v>好中球</v>
       </c>
       <c r="B55" t="str">
-        <v>尿糖,U-Glu</v>
+        <v>Neutro,Neut%</v>
       </c>
       <c r="C55" t="str">
-        <v>陰性（－）</v>
+        <v>40〜75%程度（施設差あり）</v>
       </c>
       <c r="D55" t="str">
-        <v>尿に糖が漏れ出ていないかを見る検査。血糖値がかなり高いと陽性になる</v>
+        <v>白血球の中で最も多くを占め、細菌感染と戦う主力の免疫細胞の割合</v>
       </c>
       <c r="E55" t="str">
-        <v>通常、糖は尿にはほとんど出ませんが、血糖値がかなり高くなると尿にあふれ出るようになります。血糖コントロールの目安の一つです。</v>
+        <v>好中球は、白血球の中で最も数が多く、細菌が体に入ってきたときに真っ先に戦ってくれる免疫細胞です。感染症や炎症があると増え、逆に薬の副作用などで減ることがあります。</v>
       </c>
       <c r="F55" t="str">
-        <v>糖尿病（血糖値が腎臓で再吸収できる量を超えている状態）、腎性糖尿（血糖値が正常でも体質的に出ることがある）、SGLT2阻害薬服用中（薬の作用で意図的に糖を排泄するため陽性になるのが正常）</v>
+        <v>細菌感染症、炎症、ストレス、ステロイド使用</v>
       </c>
       <c r="G55" t="str">
-        <v>SGLT2阻害薬（フォシーガ、ジャディアンスなど）服用中は、陽性が薬の効果によるものであることを説明する。脱水や尿路感染の症状がないかも確認する</v>
+        <v>発熱や炎症症状がないか確認する</v>
       </c>
       <c r="H55" t="str">
-        <v/>
+        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、ウイルス感染、メルカゾールなど薬剤性の無顆粒球症</v>
       </c>
       <c r="I55" t="str">
-        <v/>
+        <v>発熱やのどの痛みなど感染症状の初期サインがないか確認する</v>
       </c>
       <c r="J55" t="str">
-        <v>SGLT2阻害薬服用中は尿糖陽性が治療効果として想定内であることを患者に伝える。血糖値・HbA1cと合わせて評価する</v>
+        <v>好中球の絶対数（好中球実数値）が500/μL未満になると重篤な感染症のリスクが高まる。割合(%)だけでなく実数値も合わせて確認する</v>
       </c>
       <c r="K55" t="str">
-        <v>糖尿病</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L55" t="str">
-        <v>尿糖,糖半定量,U-Glu,腎性糖尿,SGLT2</v>
+        <v>好中球,Neutro,Neut,感染症,無顆粒球症</v>
       </c>
       <c r="M55" t="str">
         <v/>
@@ -2679,25 +2679,25 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>尿蛋白定量</v>
+        <v>好酸球</v>
       </c>
       <c r="B56" t="str">
-        <v>U-Pro定量,蛋白/Cr比</v>
+        <v>Eosino,Eos%</v>
       </c>
       <c r="C56" t="str">
-        <v>0.15 g/gCr未満</v>
+        <v>1〜5%程度（施設差あり）</v>
       </c>
       <c r="D56" t="str">
-        <v>随時尿から尿蛋白の量を具体的な数値として評価する検査。ネフローゼ等の重症度判定に使う</v>
+        <v>アレルギー反応や寄生虫感染に関わる白血球の一種の割合</v>
       </c>
       <c r="E56" t="str">
-        <v>これは、尿に出ているたんぱくの量を具体的な数値で見る検査です。試験紙での陽性・陰性の判定だけでなく、実際にどれくらいの量が出ているかを把握できます。</v>
+        <v>好酸球は、アレルギー反応や寄生虫感染と関係が深い免疫細胞です。アレルギー性の病気や薬の副作用（薬疹など）で増えることがあります。</v>
       </c>
       <c r="F56" t="str">
-        <v>腎症の進行（糖尿病性腎症、慢性腎臓病など）、ネフローゼ症候群（3.5 g/gCr以上が目安）</v>
+        <v>アレルギー性疾患（気管支喘息、アトピー性皮膚炎など）、薬剤アレルギー、寄生虫感染</v>
       </c>
       <c r="G56" t="str">
-        <v/>
+        <v>新しく始めた薬がないか確認する。皮疹やかゆみなどアレルギー症状の有無を確認する</v>
       </c>
       <c r="H56" t="str">
         <v/>
@@ -2706,13 +2706,13 @@
         <v/>
       </c>
       <c r="J56" t="str">
-        <v>CKD診療ガイドラインの重症度分類（尿蛋白量による区分）にも使われる定量指標。試験紙法の半定量結果より治療効果判定に適する</v>
+        <v>薬剤性の好酸球増多は、原因薬剤の中止で改善することが多い。新規薬剤開始後の皮疹・発熱と合わせて薬剤性過敏症症候群(DIHS)を疑う材料になる</v>
       </c>
       <c r="K56" t="str">
-        <v>腎機能,糖尿病</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L56" t="str">
-        <v>尿蛋白,随時尿,定量,蛋白クレアチニン比,ネフローゼ</v>
+        <v>好酸球,Eosino,Eos,アレルギー,薬疹,DIHS</v>
       </c>
       <c r="M56" t="str">
         <v/>
@@ -2720,81 +2720,81 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>BNP</v>
+        <v>好塩基球</v>
       </c>
       <c r="B57" t="str">
-        <v>BNP</v>
+        <v>Baso,Baso%</v>
       </c>
       <c r="C57" t="str">
-        <v>18.4 pg/mL以下</v>
+        <v>0〜2%程度（施設差あり）</v>
       </c>
       <c r="D57" t="str">
-        <v>心臓が無理をしているときに出る物質。心臓は血液を送るポンプだが、負担がかかると「少し助けてほしい」というサインとしてBNPを血液中に出す。</v>
+        <v>白血球の中で最も数が少なく、アレルギー反応に関わる細胞の割合</v>
       </c>
       <c r="E57" t="str">
-        <v>この検査は、心臓がどれくらい頑張りすぎていないかを見るものです。数値が高いと、心臓に少し負担がかかっているサインになります。</v>
+        <v>好塩基球は白血球の中で最も数が少ない種類で、アレルギー反応や炎症に関わっています。数値の変動が病気の診断に直接使われることは少ない検査です。</v>
       </c>
       <c r="F57" t="str">
-        <v>心不全、心臓に負担がかかっている状態、体に水分がたまりやすいとき</v>
+        <v>慢性骨髄性白血病などの血液疾患、アレルギー性疾患、甲状腺機能低下症</v>
       </c>
       <c r="G57" t="str">
-        <v>塩分・水分の摂りすぎに注意し、体重の変化を毎日記録するよう伝える</v>
+        <v/>
       </c>
       <c r="H57" t="str">
-        <v>心臓の負担は少ない状態</v>
+        <v/>
       </c>
       <c r="I57" t="str">
         <v/>
       </c>
       <c r="J57" t="str">
-        <v>腎機能が低いとBNPは高めに出ることがある／数値だけで判断せず、症状と合わせて評価する／息切れ、むくみ、体重増加があれば要注意</v>
+        <v>単独での臨床的意義は乏しいが、著明な増加は血液疾患（慢性骨髄性白血病等）の可能性があり他の血球指標と合わせて評価する</v>
       </c>
       <c r="K57" t="str">
-        <v>心不全</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L57" t="str">
-        <v>BNP,心不全,息切れ,むくみ</v>
+        <v>好塩基球,Baso,アレルギー,白血病</v>
       </c>
       <c r="M57" t="str">
-        <v>食事と栄養 p.216-222（第2部 心疾患）</v>
+        <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>血清CPR（Cペプチド）</v>
+        <v>リンパ球</v>
       </c>
       <c r="B58" t="str">
-        <v>CPR</v>
+        <v>Lympho,Lym%</v>
       </c>
       <c r="C58" t="str">
-        <v>空腹時 0.6〜3.0 ng/mL（施設差あり）</v>
+        <v>18〜49%程度（施設差あり）</v>
       </c>
       <c r="D58" t="str">
-        <v>自分の膵臓がどれくらいインスリンを作れているかを表す指標</v>
+        <v>ウイルス感染と戦い、免疫の記憶を担う白血球の割合</v>
       </c>
       <c r="E58" t="str">
-        <v>この検査は、ご自身の膵臓がどれくらいインスリンを作る力を持っているかを見るものです。数値が低いほど、体の中で作れるインスリンが少ないことを示します。</v>
+        <v>リンパ球は、ウイルスと戦ったり、一度かかった病気を記憶して免疫をつくったりする細胞です。ウイルス感染で増え、抗がん剤の副作用や強いストレスで減ることがあります。</v>
       </c>
       <c r="F58" t="str">
-        <v>インスリン抵抗性が強い状態（初期の2型糖尿病など）</v>
+        <v>ウイルス感染症、リンパ性白血病などの血液疾患、百日咳</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>膵臓のインスリン分泌能低下（1型糖尿病、糖尿病の進行）</v>
+        <v>抗がん剤・免疫抑制剤・ステロイドの使用、強いストレス、AIDSなどの免疫不全</v>
       </c>
       <c r="I58" t="str">
-        <v/>
+        <v>免疫が下がっている可能性があるため、感染予防（手洗い・うがい、人混みを避ける）を意識するよう伝える</v>
       </c>
       <c r="J58" t="str">
-        <v>インスリン分泌能の評価に使われる。数値が低いほどインスリン治療の必要性が高いと判断される目安になる</v>
+        <v>ステロイド・免疫抑制剤使用中はリンパ球減少による易感染性に注意。好中球と逆方向に動くことが多い（ウイルス感染ではリンパ球優位、細菌感染では好中球優位になりやすい）</v>
       </c>
       <c r="K58" t="str">
-        <v>糖尿病</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L58" t="str">
-        <v>CPR,Cペプチド,インスリン分泌,血清CPR</v>
+        <v>リンパ球,Lympho,Lym,ウイルス感染,免疫抑制剤,ステロイド</v>
       </c>
       <c r="M58" t="str">
         <v/>
@@ -2802,22 +2802,22 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>尿中微量アルブミン</v>
+        <v>単球</v>
       </c>
       <c r="B59" t="str">
-        <v>U-Alb,MAU</v>
+        <v>Mono,Mono%</v>
       </c>
       <c r="C59" t="str">
-        <v>30 mg/gCr未満（尿中アルブミン/クレアチニン比）</v>
+        <v>2〜10%程度（施設差あり）</v>
       </c>
       <c r="D59" t="str">
-        <v>通常の尿蛋白検査では見つからない、ごく早期の腎症のサイン</v>
+        <v>感染や炎症の後始末をする白血球の一種の割合</v>
       </c>
       <c r="E59" t="str">
-        <v>この検査は、通常の尿検査ではまだ分からないくらい早い段階の腎臓の変化を見つけるためのものです。数値が高いと、腎症の初期のサインである可能性があります。</v>
+        <v>単球は、細菌などを取り込んで処理したり、組織の修復に関わったりする免疫細胞です。慢性的な炎症や感染症の回復期に増えることがあります。</v>
       </c>
       <c r="F59" t="str">
-        <v>糖尿病性腎症の早期段階、高血圧</v>
+        <v>慢性感染症（結核など）、炎症性疾患、血液疾患、感染症の回復期</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2829,13 +2829,13 @@
         <v/>
       </c>
       <c r="J59" t="str">
-        <v>糖尿病腎症の早期発見に重要な検査。血糖・血圧コントロールで改善しうる段階なので、早期介入の意義を伝える</v>
+        <v>単独での臨床的意義は乏しく、他の血球指標や炎症マーカー(CRPなど)と合わせて評価する</v>
       </c>
       <c r="K59" t="str">
-        <v>糖尿病,腎機能</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L59" t="str">
-        <v>微量アルブミン,U-Alb,MAU,糖尿病性腎症,早期腎症</v>
+        <v>単球,Mono,慢性感染症,結核,炎症</v>
       </c>
       <c r="M59" t="str">
         <v/>
@@ -2843,312 +2843,312 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>血清鉄（Fe）</v>
+        <v>C反応性蛋白（CRP）</v>
       </c>
       <c r="B60" t="str">
-        <v>Fe</v>
+        <v>CRP</v>
       </c>
       <c r="C60" t="str">
-        <v>60〜200 μg/dL（施設差あり）</v>
+        <v>0.3 mg/dL未満（施設差あり）</v>
       </c>
       <c r="D60" t="str">
-        <v>血液中を流れている鉄の量</v>
+        <v>体のどこかに炎症や感染が起きていないかを鋭敏に反映する数値</v>
       </c>
       <c r="E60" t="str">
-        <v>この検査は、今血液の中を流れている鉄の量を見るものです。低いと、体の中で鉄が不足している可能性があります。</v>
+        <v>CRPは、体に炎症や感染が起きると数時間〜半日程度で急激に上昇する数値です。風邪のようなウイルス感染から細菌感染、体のどこかの炎症まで、幅広く反応するため、体調の変化を早期に捉える手がかりになります。</v>
       </c>
       <c r="F60" t="str">
-        <v>鉄剤の過剰摂取、溶血、肝疾患</v>
+        <v>細菌感染症、ウイルス感染症、自己免疫疾患（関節リウマチなど）、悪性腫瘍、組織の損傷（術後・心筋梗塞など）</v>
       </c>
       <c r="G60" t="str">
-        <v/>
+        <v>発熱、痛み、腫れなど炎症症状の有無を確認する</v>
       </c>
       <c r="H60" t="str">
-        <v>鉄欠乏性貧血、慢性炎症、出血</v>
+        <v/>
       </c>
       <c r="I60" t="str">
-        <v>鉄分の多い食品（レバー・赤身肉・魚・ほうれん草など）を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える</v>
+        <v/>
       </c>
       <c r="J60" t="str">
-        <v>血清鉄は日内変動が大きい。単独で判断せず総鉄結合能・フェリチンと合わせて評価する</v>
+        <v>白血球数と合わせて感染・炎症の程度を評価する。上昇・低下のタイミングは白血球より半日〜1日程度遅れる傾向があるため、経過を追う際は採血のタイミングに注意</v>
       </c>
       <c r="K60" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v/>
       </c>
       <c r="L60" t="str">
-        <v>血清鉄,Fe,鉄欠乏性貧血</v>
+        <v>CRP,炎症,感染</v>
       </c>
       <c r="M60" t="str">
-        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
+        <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>総鉄結合能（TIBC）</v>
+        <v>骨型酒石酸抵抗性フォスファターゼ（TRACP-5b）</v>
       </c>
       <c r="B61" t="str">
-        <v>TIBC</v>
+        <v>TRACP-5b</v>
       </c>
       <c r="C61" t="str">
-        <v>250〜360 μg/dL（施設差あり）</v>
+        <v>120〜420 mU/dL</v>
       </c>
       <c r="D61" t="str">
-        <v>血液中のトランスフェリンが鉄と結合できる総量</v>
+        <v>骨がどれくらい壊されているかを見る検査。骨は「古い骨を壊して新しい骨を作る」入れ替えを繰り返しており、骨を壊す細胞が活発だとこの物質が血液中に増える。</v>
       </c>
       <c r="E61" t="str">
-        <v>TIBCは、血液中でトランスフェリンという物質が鉄を運べる最大量を表します。体の中の鉄が不足すると、少しでも多く鉄を運ぼうとしてこの数値が上がる性質があります。</v>
+        <v>この検査は、骨がどれくらい早く減っていないかを見るものです。数値が高いと、骨が弱くなりやすい状態の目安になります。</v>
       </c>
       <c r="F61" t="str">
-        <v>鉄欠乏性貧血（＞360 μg/dLが目安）</v>
+        <v>骨粗鬆症、骨代謝回転（骨がこわれるスピード）が活発な状態</v>
       </c>
       <c r="G61" t="str">
-        <v/>
+        <v>カルシウム・ビタミンDの摂取や、適度な荷重運動（ウォーキングなど）を意識するよう伝える</v>
       </c>
       <c r="H61" t="str">
-        <v>慢性炎症、肝疾患、ネフローゼ症候群</v>
+        <v/>
       </c>
       <c r="I61" t="str">
         <v/>
       </c>
       <c r="J61" t="str">
-        <v>鉄が不足すると、体はより多く運ぼうとしてTIBCが上昇する。UIBC・血清鉄と併せて評価する</v>
+        <v>「骨を壊す側」の指標。「骨を作る側」の検査と合わせて評価する。数値だけで診断はしない</v>
       </c>
       <c r="K61" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="L61" t="str">
-        <v>TIBC,総鉄結合能,鉄欠乏性貧血</v>
+        <v>TRACP-5b,骨型酒石酸抵抗性フォスファターゼ,骨粗鬆症,骨代謝</v>
       </c>
       <c r="M61" t="str">
-        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
+        <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>不飽和鉄結合能（UIBC）</v>
+        <v>骨型アルカリフォスファターゼ</v>
       </c>
       <c r="B62" t="str">
-        <v>UIBC</v>
+        <v>BAP</v>
       </c>
       <c r="C62" t="str">
-        <v>170〜300 μg/dL（施設差あり）</v>
+        <v>男性 3.7〜20.9 μg/L、女性（閉経前）2.9〜14.5 μg/L（施設差あり）</v>
       </c>
       <c r="D62" t="str">
-        <v>トランスフェリンのうち、まだ鉄と結合していない余力の部分（UIBC＝TIBC－血清鉄）</v>
+        <v>ALPのうち骨に由来する成分だけを測定し、骨が作られる勢い（骨形成）を反映する</v>
       </c>
       <c r="E62" t="str">
-        <v>UIBCは、トランスフェリンのうち、まだ鉄と結合していない「空き容量」の部分を表します。鉄が不足しているときほど、この空き容量は大きくなります。</v>
+        <v>骨型ALPは、通常のALP（アルカリホスファターゼ）の中でも、骨で作られる成分だけを選んで測定するものです。骨を新しく作る働きがどれくらい活発かを見る指標として、骨粗鬆症の治療効果判定などに使われます。</v>
       </c>
       <c r="F62" t="str">
-        <v>鉄欠乏性貧血（＞300 μg/dLが目安）</v>
+        <v>骨代謝回転の亢進（骨粗鬆症、骨折治癒過程、骨形成促進薬による治療効果、Paget病、骨転移）</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>慢性炎症、鉄過剰状態</v>
+        <v>骨形成の低下</v>
       </c>
       <c r="I62" t="str">
         <v/>
       </c>
       <c r="J62" t="str">
-        <v>TIBCと同じ方向に動くことが多い。血清鉄・TIBCとあわせて鉄欠乏性貧血と二次性貧血の鑑別に使う</v>
+        <v>通常のALPと異なり肝臓の影響を受けにくいため、肝機能異常がある患者でも骨代謝を評価しやすい。P1NPと同じ「骨を作る側」の指標で、骨形成促進薬（テリパラチド等）の効果判定に使われる</v>
       </c>
       <c r="K62" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="L62" t="str">
-        <v>UIBC,不飽和鉄結合能,鉄欠乏性貧血</v>
+        <v>骨型ALP,BAP,骨型アルカリフォスファターゼ,骨形成マーカー</v>
       </c>
       <c r="M62" t="str">
-        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
+        <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>骨型酒石酸抵抗性フォスファターゼ（TRACP-5b）</v>
+        <v>25-ヒドロキシビタミンD</v>
       </c>
       <c r="B63" t="str">
-        <v>TRACP-5b</v>
+        <v>25(OH)D</v>
       </c>
       <c r="C63" t="str">
-        <v>120〜420 mU/dL</v>
+        <v>30 ng/mL以上：充足、20〜30 ng/mL：不足、20 ng/mL未満：欠乏（施設差あり）</v>
       </c>
       <c r="D63" t="str">
-        <v>骨がどれくらい壊されているかを見る検査。骨は「古い骨を壊して新しい骨を作る」入れ替えを繰り返しており、骨を壊す細胞が活発だとこの物質が血液中に増える。</v>
+        <v>体内のビタミンDの蓄え具合を反映する指標。カルシウムの吸収や骨の健康に関わる</v>
       </c>
       <c r="E63" t="str">
-        <v>この検査は、骨がどれくらい早く減っていないかを見るものです。数値が高いと、骨が弱くなりやすい状態の目安になります。</v>
+        <v>この検査は、体の中にビタミンDがどれくらい蓄えられているかを見るものです。ビタミンDは、食事から摂ったカルシウムを腸で吸収するのを助ける働きがあり、不足すると骨がもろくなりやすくなります。</v>
       </c>
       <c r="F63" t="str">
-        <v>骨粗鬆症、骨代謝回転（骨がこわれるスピード）が活発な状態</v>
+        <v>ビタミンD製剤の過剰摂取</v>
       </c>
       <c r="G63" t="str">
-        <v>カルシウム・ビタミンDの摂取や、適度な荷重運動（ウォーキングなど）を意識するよう伝える</v>
+        <v>活性型ビタミンD3製剤やサプリメントの摂取量を確認する。高カルシウム血症の症状（吐き気、便秘、多尿など）がないか確認する</v>
       </c>
       <c r="H63" t="str">
-        <v/>
+        <v>日光暴露不足、食事摂取不足、高齢、腸疾患による吸収不良、肝・腎機能低下（活性化障害）</v>
       </c>
       <c r="I63" t="str">
-        <v/>
+        <v>適度な日光浴、魚類・きのこ類などビタミンDを多く含む食品の摂取を意識するとよいことを伝える</v>
       </c>
       <c r="J63" t="str">
-        <v>「骨を壊す側」の指標。「骨を作る側」の検査と合わせて評価する。数値だけで診断はしない</v>
+        <v>骨粗鬆症治療における活性型ビタミンD3製剤の効果判定や、投与量調整の参考に用いられる。腎機能低下患者では活性化障害により25(OH)Dが正常でも活性型が不足することがある点に注意</v>
       </c>
       <c r="K63" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="L63" t="str">
-        <v>TRACP-5b,骨型酒石酸抵抗性フォスファターゼ,骨粗鬆症,骨代謝</v>
+        <v>25(OH)D,ビタミンD,25-ヒドロキシビタミンD,ビタミンD欠乏,骨粗鬆症</v>
       </c>
       <c r="M63" t="str">
-        <v/>
+        <v>食事と栄養 p.38（ビタミンD）</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>トランスフェリン飽和度</v>
+        <v>尿pH</v>
       </c>
       <c r="B64" t="str">
-        <v>TSAT</v>
+        <v>尿pH</v>
       </c>
       <c r="C64" t="str">
-        <v>16〜50%程度（施設差あり）</v>
+        <v>4.5〜7.5程度（弱酸性が多い）</v>
       </c>
       <c r="D64" t="str">
-        <v>鉄を運ぶ役割のトランスフェリンのうち、実際に鉄を運んでいる割合（血清鉄÷総鉄結合能）</v>
+        <v>尿の酸性・アルカリ性の度合い。食事や感染症、体の状態を反映する</v>
       </c>
       <c r="E64" t="str">
-        <v>トランスフェリン飽和度は、鉄を運ぶトランスフェリンのうち、実際にどれくらいが鉄を運んでいるかを割合で表したものです。鉄欠乏性貧血では低くなり、鉄が過剰にたまる病気では高くなります。</v>
+        <v>尿のpHは酸性・アルカリ性のバランスを表します。食事の内容や感染症、体の代謝状態によって変化します。単独で大きな問題を示すことは少ない検査です。</v>
       </c>
       <c r="F64" t="str">
-        <v>鉄過剰症（ヘモクロマトーシスなど）</v>
+        <v>尿路感染症（尿素分解菌によるもの）、野菜中心の食事、過換気</v>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>鉄欠乏性貧血（＜16%が目安）</v>
+        <v>高たんぱく食、糖尿病性ケトアシドーシス、痛風発作時（酸性尿は尿酸結石のリスクを高める）</v>
       </c>
       <c r="I64" t="str">
-        <v/>
+        <v>痛風・尿酸結石がある場合は、野菜など尿をアルカリ化する食品を意識するとよいことを伝える</v>
       </c>
       <c r="J64" t="str">
-        <v>血清鉄をTIBCで割って計算される。鉄剤補充の効果判定にも使われる</v>
+        <v>高尿酸血症・尿酸結石の患者では尿pHが酸性に傾いていないか確認する。尿アルカリ化薬（ウラリットなど）の効果判定にも使う</v>
       </c>
       <c r="K64" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>高尿酸血症</v>
       </c>
       <c r="L64" t="str">
-        <v>トランスフェリン飽和度,TSAT,鉄欠乏性貧血</v>
+        <v>尿pH,尿酸性度,尿アルカリ化,ウラリット</v>
       </c>
       <c r="M64" t="str">
-        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
+        <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>血清フェリチン</v>
+        <v>尿ケトン体</v>
       </c>
       <c r="B65" t="str">
-        <v>Ferritin</v>
+        <v>尿ケトン,Ket</v>
       </c>
       <c r="C65" t="str">
-        <v>男性 20〜250 ng/mL、女性 10〜120 ng/mL（施設差あり）</v>
+        <v>陰性（－）</v>
       </c>
       <c r="D65" t="str">
-        <v>体に貯蔵されている鉄の量を反映する指標。貧血の症状が出るより早い段階で低下する</v>
+        <v>体がブドウ糖の代わりに脂肪を分解してエネルギーを作っているサイン</v>
       </c>
       <c r="E65" t="str">
-        <v>フェリチンは、体に蓄えられている鉄の「貯金」の量を見る検査です。この数値が下がるのは、貧血の症状が出るよりも前の、とても早い段階のサインになります。</v>
+        <v>この検査は、体が糖の代わりに脂肪を使ってエネルギーを作っていないかを見るものです。陽性が続くときは、食事や水分、インスリンの使い方を確認する必要があります。</v>
       </c>
       <c r="F65" t="str">
-        <v>炎症性疾患、肝疾患、悪性腫瘍、鉄過剰症（フェリチンは炎症でも上昇するため、貧血の評価では注意が必要）</v>
+        <v>糖尿病の血糖コントロール不良（シックデイ・インスリン不足）、極端な糖質制限、絶食、嘔吐・下痢による脱水</v>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>鉄欠乏状態（貧血の症状が出る前の早期段階から低下する）</v>
+        <v/>
       </c>
       <c r="I65" t="str">
-        <v>鉄分の多い食品を意識するとともに、貯蔵鉄を補うため治療は数値が正常化してからも継続が必要なことを伝える</v>
+        <v/>
       </c>
       <c r="J65" t="str">
-        <v>貯蔵鉄の指標で鉄欠乏を最も早期に反映する。ただし炎症があると鉄欠乏があっても正常〜高値に出ることがあり、CRP等の炎症所見と合わせて評価する。二次性貧血との鑑別に重要</v>
+        <v>陽性かつ高血糖・全身倦怠感が強い場合は糖尿病性ケトアシドーシスの可能性があり緊急性が高い。シックデイルールの説明歴を確認する</v>
       </c>
       <c r="K65" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>糖尿病</v>
       </c>
       <c r="L65" t="str">
-        <v>フェリチン,Ferritin,貯蔵鉄,鉄欠乏</v>
+        <v>尿ケトン体,ケトン体,Ket,シックデイ,ケトアシドーシス</v>
       </c>
       <c r="M65" t="str">
-        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
+        <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>尿中尿酸/クレアチニン比（UUA/UCr）</v>
+        <v>ウロビリノーゲン</v>
       </c>
       <c r="B66" t="str">
-        <v>UUA/UCr</v>
+        <v>Uro</v>
       </c>
       <c r="C66" t="str">
-        <v>0.4〜0.8程度が混合型の目安</v>
+        <v>正常（±）程度</v>
       </c>
       <c r="D66" t="str">
-        <v>尿酸が「作られすぎ」か「排泄できていない」かを見分ける比の値</v>
+        <v>肝臓や胆道、赤血球の壊れ方の状態を反映する尿検査項目</v>
       </c>
       <c r="E66" t="str">
-        <v>この数値は、体の中で尿酸が「作られすぎている」のか、それとも「うまく排泄できていない」のかを見分けるために使う比の値です。高尿酸血症の治療薬を選ぶときの参考になります。</v>
+        <v>ウロビリノーゲンは、赤血球やビリルビンが体の中で処理される過程でできる物質です。肝臓の働きが悪くなったり、赤血球が壊れやすくなったりすると、尿の中の量が変化します。</v>
       </c>
       <c r="F66" t="str">
-        <v>尿酸産生過剰型（0.8以上が目安）</v>
+        <v>溶血性疾患（赤血球の破壊亢進）、肝機能障害</v>
       </c>
       <c r="G66" t="str">
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>尿酸排泄低下型（0.4以下が目安）</v>
+        <v>胆道閉塞（胆汁が腸に流れず、ウロビリノーゲンが作られない状態）</v>
       </c>
       <c r="I66" t="str">
         <v/>
       </c>
       <c r="J66" t="str">
-        <v>高尿酸血症は尿酸産生過剰型・排泄低下型・混合型に分類され、この比が目安になる。病型によって使う薬剤（尿酸生成抑制薬か尿酸排泄促進薬か）の選択が変わる</v>
+        <v>完全に陰性の場合は胆道閉塞を疑う所見の一つ。肝機能（AST/ALT/ビリルビン）と合わせて評価する</v>
       </c>
       <c r="K66" t="str">
-        <v>高尿酸血症</v>
+        <v>肝機能</v>
       </c>
       <c r="L66" t="str">
-        <v>UUA,UCr,尿酸クリアランス,CUA,EUA,尿酸産生過剰型,尿酸排泄低下型</v>
+        <v>ウロビリノーゲン,Uro,溶血,胆道閉塞,肝機能</v>
       </c>
       <c r="M66" t="str">
-        <v>食事と栄養 p.180-189（第2部 痛風・高尿酸血症）</v>
+        <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>ucOC（低カルボキシル化オステオカルシン）</v>
+        <v>尿潜血反応</v>
       </c>
       <c r="B67" t="str">
-        <v>ucOC</v>
+        <v>尿潜血,U-OB</v>
       </c>
       <c r="C67" t="str">
-        <v>4.5 ng/mL未満（施設差あり）</v>
+        <v>陰性（－）</v>
       </c>
       <c r="D67" t="str">
-        <v>ビタミンKが不足していないかを反映する骨の指標</v>
+        <v>尿に血液（赤血球）が混じっていないかを見る検査</v>
       </c>
       <c r="E67" t="str">
-        <v>ucOCは、骨を作るために必要なビタミンKが体の中で足りているかどうかを反映する検査です。数値が高いとビタミンK不足が疑われます。</v>
+        <v>この検査は、尿に目に見えないくらいの微量の血液が混じっていないかを調べるものです。陽性の場合、腎臓や膀胱、尿路のどこかに炎症や結石などがある可能性があります。</v>
       </c>
       <c r="F67" t="str">
-        <v>ビタミンK不足状態</v>
+        <v>尿路結石、膀胱炎などの尿路感染症、腎炎、腫瘍、月経血の混入、激しい運動後</v>
       </c>
       <c r="G67" t="str">
-        <v/>
+        <v>排尿時の痛みや頻尿、目に見える血尿の有無を確認する。女性は月経の時期と重なっていないか確認する</v>
       </c>
       <c r="H67" t="str">
         <v/>
@@ -3157,490 +3157,490 @@
         <v/>
       </c>
       <c r="J67" t="str">
-        <v>ビタミンK2製剤（骨粗鬆症治療薬）の適応判断や効果判定に使われる</v>
+        <v>陽性でも尿沈渣で赤血球が確認されない場合は偽陽性（ミオグロビン尿など）のこともある。持続する場合は泌尿器科的な精査が必要</v>
       </c>
       <c r="K67" t="str">
-        <v>骨粗鬆症</v>
+        <v>腎機能</v>
       </c>
       <c r="L67" t="str">
-        <v>ucOC,オステオカルシン,ビタミンK</v>
+        <v>尿潜血,潜血反応,U-OB,血尿,尿路結石,膀胱炎</v>
       </c>
       <c r="M67" t="str">
-        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
+        <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>PTH（副甲状腺ホルモン）</v>
+        <v>尿糖（半定量）</v>
       </c>
       <c r="B68" t="str">
-        <v>PTH</v>
+        <v>尿糖,U-Glu</v>
       </c>
       <c r="C68" t="str">
-        <v>10〜65 pg/mL（施設差あり）</v>
+        <v>陰性（－）</v>
       </c>
       <c r="D68" t="str">
-        <v>血液中のカルシウム濃度を調節するホルモン</v>
+        <v>尿に糖が漏れ出ていないかを見る検査。血糖値がかなり高いと陽性になる</v>
       </c>
       <c r="E68" t="str">
-        <v>PTHは、血液中のカルシウム濃度を一定に保つために働くホルモンです。カルシウムが低くなると分泌が増え、骨からカルシウムを取り出したり、腎臓での再吸収を促したりして数値を戻そうとします。</v>
+        <v>通常、糖は尿にはほとんど出ませんが、血糖値がかなり高くなると尿にあふれ出るようになります。血糖コントロールの目安の一つです。</v>
       </c>
       <c r="F68" t="str">
-        <v>原発性・二次性副甲状腺機能亢進症（腎不全に伴うものなど）</v>
+        <v>糖尿病（血糖値が腎臓で再吸収できる量を超えている状態）、腎性糖尿（血糖値が正常でも体質的に出ることがある）、SGLT2阻害薬服用中（薬の作用で意図的に糖を排泄するため陽性になるのが正常）</v>
       </c>
       <c r="G68" t="str">
-        <v/>
+        <v>SGLT2阻害薬（フォシーガ、ジャディアンスなど）服用中は、陽性が薬の効果によるものであることを説明する。脱水や尿路感染の症状がないかも確認する</v>
       </c>
       <c r="H68" t="str">
-        <v>副甲状腺機能低下症</v>
+        <v/>
       </c>
       <c r="I68" t="str">
         <v/>
       </c>
       <c r="J68" t="str">
-        <v>骨粗鬆症の二次性原因（副甲状腺機能亢進症）を除外するための検査。カルシウム・リンと合わせて評価する</v>
+        <v>SGLT2阻害薬服用中は尿糖陽性が治療効果として想定内であることを患者に伝える。血糖値・HbA1cと合わせて評価する</v>
       </c>
       <c r="K68" t="str">
-        <v>骨粗鬆症</v>
+        <v>糖尿病</v>
       </c>
       <c r="L68" t="str">
-        <v>PTH,副甲状腺ホルモン,パラトルモン</v>
+        <v>尿糖,糖半定量,U-Glu,腎性糖尿,SGLT2</v>
       </c>
       <c r="M68" t="str">
-        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
+        <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>尿中NTX</v>
+        <v>尿蛋白定量</v>
       </c>
       <c r="B69" t="str">
-        <v>NTX</v>
+        <v>U-Pro定量,蛋白/Cr比</v>
       </c>
       <c r="C69" t="str">
-        <v>施設差が大きく一律の記載が難しい（尿中）</v>
+        <v>0.15 g/gCr未満</v>
       </c>
       <c r="D69" t="str">
-        <v>骨が壊されるときに出る、骨吸収マーカーのひとつ</v>
+        <v>随時尿から尿蛋白の量を具体的な数値として評価する検査。ネフローゼ等の重症度判定に使う</v>
       </c>
       <c r="E69" t="str">
-        <v>NTXは、骨が壊される（吸収される）ときに尿の中に出てくる物質です。骨粗鬆症の治療薬がどれくらい効いているかを確認するために使われます。</v>
+        <v>これは、尿に出ているたんぱくの量を具体的な数値で見る検査です。試験紙での陽性・陰性の判定だけでなく、実際にどれくらいの量が出ているかを把握できます。</v>
       </c>
       <c r="F69" t="str">
-        <v>骨代謝回転の亢進（骨粗鬆症、閉経後など）</v>
+        <v>腎症の進行（糖尿病性腎症、慢性腎臓病など）、ネフローゼ症候群（3.5 g/gCr以上が目安）</v>
       </c>
       <c r="G69" t="str">
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>骨吸収抑制薬（ビスホスホネート等）による治療効果</v>
+        <v/>
       </c>
       <c r="I69" t="str">
         <v/>
       </c>
       <c r="J69" t="str">
-        <v>治療開始後3〜6か月で再検し、薬の効果判定に使われる。TRACP-5bと同じ「骨を壊す側」の指標</v>
+        <v>CKD診療ガイドラインの重症度分類（尿蛋白量による区分）にも使われる定量指標。試験紙法の半定量結果より治療効果判定に適する</v>
       </c>
       <c r="K69" t="str">
-        <v>骨粗鬆症</v>
+        <v>腎機能,糖尿病</v>
       </c>
       <c r="L69" t="str">
-        <v>NTX,尿中NTX,骨吸収マーカー</v>
+        <v>尿蛋白,随時尿,定量,蛋白クレアチニン比,ネフローゼ</v>
       </c>
       <c r="M69" t="str">
-        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
+        <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>カルシトニン</v>
+        <v>BNP</v>
       </c>
       <c r="B70" t="str">
-        <v>CT</v>
+        <v>BNP</v>
       </c>
       <c r="C70" t="str">
-        <v>男性 9.52 pg/mL未満、女性 6.40 pg/mL未満（施設差あり）</v>
+        <v>18.4 pg/mL以下</v>
       </c>
       <c r="D70" t="str">
-        <v>血液中のカルシウムを下げる方向に働くホルモン</v>
+        <v>心臓が無理をしているときに出る物質。心臓は血液を送るポンプだが、負担がかかると「少し助けてほしい」というサインとしてBNPを血液中に出す。</v>
       </c>
       <c r="E70" t="str">
-        <v>カルシトニンは、PTHとは逆に血液中のカルシウムを下げる方向に働くホルモンです。特定の甲状腺の病気（甲状腺髄様癌）がないかを調べる際にも使われます。</v>
+        <v>この検査は、心臓がどれくらい頑張りすぎていないかを見るものです。数値が高いと、心臓に少し負担がかかっているサインになります。</v>
       </c>
       <c r="F70" t="str">
-        <v>甲状腺髄様癌、腎不全</v>
+        <v>心不全、心臓に負担がかかっている状態、体に水分がたまりやすいとき</v>
       </c>
       <c r="G70" t="str">
-        <v/>
+        <v>塩分・水分の摂りすぎに注意し、体重の変化を毎日記録するよう伝える</v>
       </c>
       <c r="H70" t="str">
-        <v/>
+        <v>心臓の負担は少ない状態</v>
       </c>
       <c r="I70" t="str">
         <v/>
       </c>
       <c r="J70" t="str">
-        <v>骨粗鬆症の二次性原因の除外目的で測定されることがある検査値。同名の薬剤（カルシトニン製剤）と混同しないよう注意</v>
+        <v>腎機能が低いとBNPは高めに出ることがある／数値だけで判断せず、症状と合わせて評価する／息切れ、むくみ、体重増加があれば要注意</v>
       </c>
       <c r="K70" t="str">
-        <v>骨粗鬆症</v>
+        <v>心不全</v>
       </c>
       <c r="L70" t="str">
-        <v>カルシトニン,CT</v>
+        <v>BNP,心不全,息切れ,むくみ</v>
       </c>
       <c r="M70" t="str">
-        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
+        <v>食事と栄養 p.216-222（第2部 心疾患）</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>DPD（デオキシピリジノリン）</v>
+        <v>血清CPR（Cペプチド）</v>
       </c>
       <c r="B71" t="str">
-        <v>DPD</v>
+        <v>CPR</v>
       </c>
       <c r="C71" t="str">
-        <v>施設差が大きく一律の記載が難しい（尿中）</v>
+        <v>空腹時 0.6〜3.0 ng/mL（施設差あり）</v>
       </c>
       <c r="D71" t="str">
-        <v>骨のコラーゲンが壊れるときに出る、骨吸収マーカーのひとつ</v>
+        <v>自分の膵臓がどれくらいインスリンを作れているかを表す指標</v>
       </c>
       <c r="E71" t="str">
-        <v>DPDも、骨が壊されるときに尿に出てくる物質の一つです。NTXと同じように、骨粗鬆症治療薬の効果を確認するために使われます。</v>
+        <v>この検査は、ご自身の膵臓がどれくらいインスリンを作る力を持っているかを見るものです。数値が低いほど、体の中で作れるインスリンが少ないことを示します。</v>
       </c>
       <c r="F71" t="str">
-        <v>骨代謝回転の亢進（骨粗鬆症など）</v>
+        <v>インスリン抵抗性が強い状態（初期の2型糖尿病など）</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>骨吸収抑制薬による治療効果</v>
+        <v>膵臓のインスリン分泌能低下（1型糖尿病、糖尿病の進行）</v>
       </c>
       <c r="I71" t="str">
         <v/>
       </c>
       <c r="J71" t="str">
-        <v>NTX・CTXと同じ「骨を壊す側」の指標。食事の影響を受けにくいとされる</v>
+        <v>インスリン分泌能の評価に使われる。数値が低いほどインスリン治療の必要性が高いと判断される目安になる</v>
       </c>
       <c r="K71" t="str">
-        <v>骨粗鬆症</v>
+        <v>糖尿病</v>
       </c>
       <c r="L71" t="str">
-        <v>DPD,デオキシピリジノリン,骨吸収マーカー</v>
+        <v>CPR,Cペプチド,インスリン分泌,血清CPR</v>
       </c>
       <c r="M71" t="str">
-        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
+        <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>CTX</v>
+        <v>尿中微量アルブミン</v>
       </c>
       <c r="B72" t="str">
-        <v>CTX</v>
+        <v>U-Alb,MAU</v>
       </c>
       <c r="C72" t="str">
-        <v>施設差が大きく一律の記載が難しい（血清・尿中）</v>
+        <v>30 mg/gCr未満（尿中アルブミン/クレアチニン比）</v>
       </c>
       <c r="D72" t="str">
-        <v>骨のコラーゲンが壊れるときに出る、骨吸収マーカーのひとつ</v>
+        <v>通常の尿蛋白検査では見つからない、ごく早期の腎症のサイン</v>
       </c>
       <c r="E72" t="str">
-        <v>CTXも、骨が壊されるときに血液や尿に出てくる物質です。骨粗鬆症治療薬（骨を壊すのを抑える薬）の効果を確認するために使われます。</v>
+        <v>この検査は、通常の尿検査ではまだ分からないくらい早い段階の腎臓の変化を見つけるためのものです。数値が高いと、腎症の初期のサインである可能性があります。</v>
       </c>
       <c r="F72" t="str">
-        <v>骨代謝回転の亢進（骨粗鬆症など）</v>
+        <v>糖尿病性腎症の早期段階、高血圧</v>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>骨吸収抑制薬による治療効果</v>
+        <v/>
       </c>
       <c r="I72" t="str">
         <v/>
       </c>
       <c r="J72" t="str">
-        <v>NTX・DPDと同じ「骨を壊す側」の指標。血清・尿中いずれでも測定されることがある</v>
+        <v>糖尿病腎症の早期発見に重要な検査。血糖・血圧コントロールで改善しうる段階なので、早期介入の意義を伝える</v>
       </c>
       <c r="K72" t="str">
-        <v>骨粗鬆症</v>
+        <v>糖尿病,腎機能</v>
       </c>
       <c r="L72" t="str">
-        <v>CTX,骨吸収マーカー</v>
+        <v>微量アルブミン,U-Alb,MAU,糖尿病性腎症,早期腎症</v>
       </c>
       <c r="M72" t="str">
-        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
+        <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>P1NP</v>
+        <v>血清鉄（Fe）</v>
       </c>
       <c r="B73" t="str">
-        <v>P1NP</v>
+        <v>Fe</v>
       </c>
       <c r="C73" t="str">
-        <v>施設差が大きく一律の記載が難しい（血清）</v>
+        <v>60〜200 μg/dL（施設差あり）</v>
       </c>
       <c r="D73" t="str">
-        <v>骨が新しく作られるときに出る、骨形成マーカーのひとつ</v>
+        <v>血液中を流れている鉄の量</v>
       </c>
       <c r="E73" t="str">
-        <v>P1NPは、CTXなどとは逆に、骨が新しく作られるときに血液中に出てくる物質です。骨を作る力を高める薬（テリパラチドなど）の効果を確認するために使われます。</v>
+        <v>この検査は、今血液の中を流れている鉄の量を見るものです。低いと、体の中で鉄が不足している可能性があります。</v>
       </c>
       <c r="F73" t="str">
-        <v>骨代謝回転の亢進、骨形成促進薬による治療効果</v>
+        <v>鉄剤の過剰摂取、溶血、肝疾患</v>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>骨形成の低下</v>
+        <v>鉄欠乏性貧血、慢性炎症、出血</v>
       </c>
       <c r="I73" t="str">
-        <v/>
+        <v>鉄分の多い食品（レバー・赤身肉・魚・ほうれん草など）を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える</v>
       </c>
       <c r="J73" t="str">
-        <v>TRACP-5b等「骨を壊す側」の指標とは逆の、「骨を作る側」の指標。骨形成促進薬（テリパラチド等）の効果判定に使われる</v>
+        <v>血清鉄は日内変動が大きい。単独で判断せず総鉄結合能・フェリチンと合わせて評価する</v>
       </c>
       <c r="K73" t="str">
-        <v>骨粗鬆症</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="L73" t="str">
-        <v>P1NP,骨形成マーカー</v>
+        <v>血清鉄,Fe,鉄欠乏性貧血</v>
       </c>
       <c r="M73" t="str">
-        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
+        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>抗甲状腺マイクロゾーム抗体（抗TPO抗体）</v>
+        <v>総鉄結合能（TIBC）</v>
       </c>
       <c r="B74" t="str">
-        <v>TPOAb</v>
+        <v>TIBC</v>
       </c>
       <c r="C74" t="str">
-        <v>陰性（16 IU/mL未満程度、施設差あり）</v>
+        <v>250〜360 μg/dL（施設差あり）</v>
       </c>
       <c r="D74" t="str">
-        <v>自分の甲状腺を攻撃する抗体が出ていないかを見る検査</v>
+        <v>血液中のトランスフェリンが鉄と結合できる総量</v>
       </c>
       <c r="E74" t="str">
-        <v>この検査は、体の中に自分の甲状腺を誤って攻撃してしまう抗体がないかを見るものです。陽性の場合、橋本病（慢性甲状腺炎）など甲状腺の自己免疫的な炎症が背景にある可能性があります。</v>
+        <v>TIBCは、血液中でトランスフェリンという物質が鉄を運べる最大量を表します。体の中の鉄が不足すると、少しでも多く鉄を運ぼうとしてこの数値が上がる性質があります。</v>
       </c>
       <c r="F74" t="str">
-        <v>橋本病（慢性甲状腺炎）、バセドウ病などの自己免疫性甲状腺疾患</v>
+        <v>鉄欠乏性貧血（＞360 μg/dLが目安）</v>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v/>
+        <v>慢性炎症、肝疾患、ネフローゼ症候群</v>
       </c>
       <c r="I74" t="str">
         <v/>
       </c>
       <c r="J74" t="str">
-        <v>陽性でも必ずしも甲状腺機能異常があるとは限らない。TSH・FT4など甲状腺ホルモンの数値と合わせて評価する</v>
+        <v>鉄が不足すると、体はより多く運ぼうとしてTIBCが上昇する。UIBC・血清鉄と併せて評価する</v>
       </c>
       <c r="K74" t="str">
-        <v>甲状腺疾患</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="L74" t="str">
-        <v>抗TPO抗体,抗甲状腺マイクロゾーム抗体,TPOAb,橋本病</v>
+        <v>TIBC,総鉄結合能,鉄欠乏性貧血</v>
       </c>
       <c r="M74" t="str">
-        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
+        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>抗サイログロブリン抗体</v>
+        <v>不飽和鉄結合能（UIBC）</v>
       </c>
       <c r="B75" t="str">
-        <v>TgAb</v>
+        <v>UIBC</v>
       </c>
       <c r="C75" t="str">
-        <v>陰性（28 IU/mL未満程度、施設差あり）</v>
+        <v>170〜300 μg/dL（施設差あり）</v>
       </c>
       <c r="D75" t="str">
-        <v>甲状腺のたんぱく質（サイログロブリン）への抗体が出ていないかを見る検査</v>
+        <v>トランスフェリンのうち、まだ鉄と結合していない余力の部分（UIBC＝TIBC－血清鉄）</v>
       </c>
       <c r="E75" t="str">
-        <v>この検査も、抗TPO抗体と同じく、甲状腺に対する自己免疫の有無を見るものです。あわせて調べることで橋本病などの診断の参考にします。</v>
+        <v>UIBCは、トランスフェリンのうち、まだ鉄と結合していない「空き容量」の部分を表します。鉄が不足しているときほど、この空き容量は大きくなります。</v>
       </c>
       <c r="F75" t="str">
-        <v>橋本病（慢性甲状腺炎）、バセドウ病などの自己免疫性甲状腺疾患</v>
+        <v>鉄欠乏性貧血（＞300 μg/dLが目安）</v>
       </c>
       <c r="G75" t="str">
         <v/>
       </c>
       <c r="H75" t="str">
-        <v/>
+        <v>慢性炎症、鉄過剰状態</v>
       </c>
       <c r="I75" t="str">
         <v/>
       </c>
       <c r="J75" t="str">
-        <v>抗TPO抗体とあわせて測定されることが多い。単独の高値だけで治療方針が決まるわけではない</v>
+        <v>TIBCと同じ方向に動くことが多い。血清鉄・TIBCとあわせて鉄欠乏性貧血と二次性貧血の鑑別に使う</v>
       </c>
       <c r="K75" t="str">
-        <v>甲状腺疾患</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="L75" t="str">
-        <v>抗サイログロブリン抗体,TgAb,橋本病</v>
+        <v>UIBC,不飽和鉄結合能,鉄欠乏性貧血</v>
       </c>
       <c r="M75" t="str">
-        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
+        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>PT-INR（プロトロンビン時間国際標準比）</v>
+        <v>トランスフェリン飽和度</v>
       </c>
       <c r="B76" t="str">
-        <v>PT-INR,INR</v>
+        <v>TSAT</v>
       </c>
       <c r="C76" t="str">
-        <v>治療域の目安 1.6〜3.0（ワルファリン服用時。年齢・疾患により異なる）</v>
+        <v>16〜50%程度（施設差あり）</v>
       </c>
       <c r="D76" t="str">
-        <v>血液の固まりやすさを表す数値で、ワルファリンの効き具合を確認するために使う</v>
+        <v>鉄を運ぶ役割のトランスフェリンのうち、実際に鉄を運んでいる割合（血清鉄÷総鉄結合能）</v>
       </c>
       <c r="E76" t="str">
-        <v>PT-INRは血液が固まるまでの時間をもとにした数値で、ワルファリンというお薬を飲んでいる方の効き具合を確認するために測ります。数値が高いほど血液が固まりにくく出血しやすい状態、低いほど血栓ができやすい状態を示します。</v>
+        <v>トランスフェリン飽和度は、鉄を運ぶトランスフェリンのうち、実際にどれくらいが鉄を運んでいるかを割合で表したものです。鉄欠乏性貧血では低くなり、鉄が過剰にたまる病気では高くなります。</v>
       </c>
       <c r="F76" t="str">
-        <v>ワルファリンの効きすぎ、肝機能低下、ビタミンK不足、納豆・青汁など摂取量の変化</v>
+        <v>鉄過剰症（ヘモクロマトーシスなど）</v>
       </c>
       <c r="G76" t="str">
-        <v>歯ぐきや鼻からの出血、あざ、黒い便などの出血症状がないか確認する。納豆・クロレラ・青汁などビタミンKを多く含む食品の摂取状況を確認する</v>
+        <v/>
       </c>
       <c r="H76" t="str">
-        <v>ワルファリンの効き不足、飲み忘れ、ビタミンK摂取量の急激な増加</v>
+        <v>鉄欠乏性貧血（＜16%が目安）</v>
       </c>
       <c r="I76" t="str">
-        <v>服薬状況（飲み忘れ）を確認する。片側のむくみ・しびれ・胸痛など血栓症状がないか確認する</v>
+        <v/>
       </c>
       <c r="J76" t="str">
-        <v>治療域は疾患・年齢によって異なる（例：非弁膜症性心房細動の高齢者では1.6〜2.6が目安になることが多い）。多くの薬剤・食品と相互作用があるため新規薬剤追加時は必ず確認する。DOAC（エリキュース、リクシアナ、プラザキサなど）ではPT-INRのモニタリングは不要</v>
+        <v>血清鉄をTIBCで割って計算される。鉄剤補充の効果判定にも使われる</v>
       </c>
       <c r="K76" t="str">
-        <v>抗凝固療法（心房細動・血栓症）</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="L76" t="str">
-        <v>PT-INR,INR,プロトロンビン時間,ワルファリン,ワーファリン,抗凝固</v>
+        <v>トランスフェリン飽和度,TSAT,鉄欠乏性貧血</v>
       </c>
       <c r="M76" t="str">
-        <v>食事と栄養 p.221（心疾患Q93 ワルファリン服用中のビタミンK摂取）</v>
+        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>血中薬物濃度（TDM）</v>
+        <v>血清フェリチン</v>
       </c>
       <c r="B77" t="str">
-        <v>TDM</v>
+        <v>Ferritin</v>
       </c>
       <c r="C77" t="str">
-        <v>薬剤ごとに有効域が異なる（例：カルバマゼピン 4〜12 μg/mL、バルプロ酸 40〜100 μg/mL、フェニトイン 10〜20 μg/mL）</v>
+        <v>男性 20〜250 ng/mL、女性 10〜120 ng/mL（施設差あり）</v>
       </c>
       <c r="D77" t="str">
-        <v>治療域が狭い薬剤で、血液中の薬の濃度が効果域・中毒域のどちらにあるかを確認する検査</v>
+        <v>体に貯蔵されている鉄の量を反映する指標。貧血の症状が出るより早い段階で低下する</v>
       </c>
       <c r="E77" t="str">
-        <v>この薬は効く量と副作用が出る量が近いため、血液中の薬の濃度を定期的に測って、ちょうどよい範囲に入っているかを確認します。数値が低いと効果が不十分になり、高いと副作用が出やすくなります。</v>
+        <v>フェリチンは、体に蓄えられている鉄の「貯金」の量を見る検査です。この数値が下がるのは、貧血の症状が出るよりも前の、とても早い段階のサインになります。</v>
       </c>
       <c r="F77" t="str">
-        <v>過量投与、代謝を妨げる薬剤との併用、肝機能低下による代謝低下</v>
+        <v>炎症性疾患、肝疾患、悪性腫瘍、鉄過剰症（フェリチンは炎症でも上昇するため、貧血の評価では注意が必要）</v>
       </c>
       <c r="G77" t="str">
-        <v>ふらつき、眠気、めまい、物が二重に見えるなどの中毒症状がないか確認する</v>
+        <v/>
       </c>
       <c r="H77" t="str">
-        <v>飲み忘れ、自己判断による減量、代謝を促進する薬剤との併用（相互作用）</v>
+        <v>鉄欠乏状態（貧血の症状が出る前の早期段階から低下する）</v>
       </c>
       <c r="I77" t="str">
-        <v>発作やてんかん症状の再発がないか確認し、飲み忘れがないか一緒に確認する</v>
+        <v>鉄分の多い食品を意識するとともに、貯蔵鉄を補うため治療は数値が正常化してからも継続が必要なことを伝える</v>
       </c>
       <c r="J77" t="str">
-        <v>採血のタイミング（トラフ値かどうか）で数値の解釈が変わるため採血時点を確認する。カルバマゼピンは自己誘導により長期使用で濃度が下がることがある点にも注意</v>
+        <v>貯蔵鉄の指標で鉄欠乏を最も早期に反映する。ただし炎症があると鉄欠乏があっても正常〜高値に出ることがあり、CRP等の炎症所見と合わせて評価する。二次性貧血との鑑別に重要</v>
       </c>
       <c r="K77" t="str">
-        <v>てんかん</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="L77" t="str">
-        <v>TDM,血中薬物濃度,治療域,中毒域,カルバマゼピン,フェニトイン,バルプロ酸,抗てんかん薬</v>
+        <v>フェリチン,Ferritin,貯蔵鉄,鉄欠乏</v>
       </c>
       <c r="M77" t="str">
-        <v/>
+        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>アミラーゼ（AMY）</v>
+        <v>尿中尿酸/クレアチニン比（UUA/UCr）</v>
       </c>
       <c r="B78" t="str">
-        <v>AMY</v>
+        <v>UUA/UCr</v>
       </c>
       <c r="C78" t="str">
-        <v>44〜132 U/L（施設差あり）</v>
+        <v>0.4〜0.8程度が混合型の目安</v>
       </c>
       <c r="D78" t="str">
-        <v>膵臓や唾液腺から出る消化酵素。膵炎などで血液中に漏れ出す</v>
+        <v>尿酸が「作られすぎ」か「排泄できていない」かを見分ける比の値</v>
       </c>
       <c r="E78" t="str">
-        <v>アミラーゼは、でんぷんを分解する消化酵素で、主に膵臓と唾液腺から作られます。膵臓に炎症が起きると血液中に漏れ出して数値が上がるため、膵炎の診断や経過観察に使われます。</v>
+        <v>この数値は、体の中で尿酸が「作られすぎている」のか、それとも「うまく排泄できていない」のかを見分けるために使う比の値です。高尿酸血症の治療薬を選ぶときの参考になります。</v>
       </c>
       <c r="F78" t="str">
-        <v>急性膵炎、慢性膵炎の急性増悪、耳下腺炎（おたふくかぜ）、腎不全</v>
+        <v>尿酸産生過剰型（0.8以上が目安）</v>
       </c>
       <c r="G78" t="str">
-        <v>飲酒を控える、脂っこい食事を避けるよう伝える</v>
+        <v/>
       </c>
       <c r="H78" t="str">
-        <v>慢性膵炎の進行期（膵臓の機能低下）</v>
+        <v>尿酸排泄低下型（0.4以下が目安）</v>
       </c>
       <c r="I78" t="str">
         <v/>
       </c>
       <c r="J78" t="str">
-        <v>膵臓由来か唾液腺由来かを区別するには膵型アミラーゼ(P-AMY)を確認する。急性膵炎では強い腹痛・背部痛を伴うことが多く、飲酒歴の確認も重要</v>
+        <v>高尿酸血症は尿酸産生過剰型・排泄低下型・混合型に分類され、この比が目安になる。病型によって使う薬剤（尿酸生成抑制薬か尿酸排泄促進薬か）の選択が変わる</v>
       </c>
       <c r="K78" t="str">
-        <v/>
+        <v>高尿酸血症</v>
       </c>
       <c r="L78" t="str">
-        <v>アミラーゼ,AMY,膵炎,急性膵炎</v>
+        <v>UUA,UCr,尿酸クリアランス,CUA,EUA,尿酸産生過剰型,尿酸排泄低下型</v>
       </c>
       <c r="M78" t="str">
-        <v/>
+        <v>食事と栄養 p.180-189（第2部 痛風・高尿酸血症）</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>間接ビリルビン</v>
+        <v>ucOC（低カルボキシル化オステオカルシン）</v>
       </c>
       <c r="B79" t="str">
-        <v>I-Bil</v>
+        <v>ucOC</v>
       </c>
       <c r="C79" t="str">
-        <v>0.2〜0.8 mg/dL程度（施設差あり）</v>
+        <v>4.5 ng/mL未満（施設差あり）</v>
       </c>
       <c r="D79" t="str">
-        <v>赤血球が壊れてできるビリルビンのうち、肝臓で処理される前の形</v>
+        <v>ビタミンKが不足していないかを反映する骨の指標</v>
       </c>
       <c r="E79" t="str">
-        <v>間接ビリルビンは、赤血球が壊れてできたビリルビンが、まだ肝臓で処理される前の状態です。この値が高い場合、赤血球が通常より多く壊れている(溶血)か、肝臓での処理能力に生まれつきの体質差(体質性黄疸)がある可能性が考えられます。</v>
+        <v>ucOCは、骨を作るために必要なビタミンKが体の中で足りているかどうかを反映する検査です。数値が高いとビタミンK不足が疑われます。</v>
       </c>
       <c r="F79" t="str">
-        <v>溶血性疾患（自己免疫性溶血性貧血、血液型不適合輸血など）、体質性黄疸（ジルベール症候群）、新生児黄疸</v>
+        <v>ビタミンK不足状態</v>
       </c>
       <c r="G79" t="str">
-        <v>皮膚や白目の黄染、尿の色の変化がないか確認する</v>
+        <v/>
       </c>
       <c r="H79" t="str">
         <v/>
@@ -3649,121 +3649,121 @@
         <v/>
       </c>
       <c r="J79" t="str">
-        <v>直接ビリルビンとの比率で原因を推測する（間接優位は溶血・体質性、直接優位は胆道系）。総ビリルビン・AST/ALTと合わせて評価する</v>
+        <v>ビタミンK2製剤（骨粗鬆症治療薬）の適応判断や効果判定に使われる</v>
       </c>
       <c r="K79" t="str">
-        <v>肝機能</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="L79" t="str">
-        <v>間接ビリルビン,I-Bil,溶血</v>
+        <v>ucOC,オステオカルシン,ビタミンK</v>
       </c>
       <c r="M79" t="str">
-        <v/>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>直接ビリルビン</v>
+        <v>PTH（副甲状腺ホルモン）</v>
       </c>
       <c r="B80" t="str">
-        <v>D-Bil</v>
+        <v>PTH</v>
       </c>
       <c r="C80" t="str">
-        <v>0.0〜0.3 mg/dL程度（施設差あり）</v>
+        <v>10〜65 pg/mL（施設差あり）</v>
       </c>
       <c r="D80" t="str">
-        <v>肝臓で処理された後のビリルビン。胆道の詰まりで血液中に増える</v>
+        <v>血液中のカルシウム濃度を調節するホルモン</v>
       </c>
       <c r="E80" t="str">
-        <v>直接ビリルビンは、肝臓で処理された後のビリルビンです。胆石や腫瘍などで胆汁の通り道（胆道）が詰まると、行き場を失って血液中に増え、皮膚や白目が黄色くなる黄疸として現れます。</v>
+        <v>PTHは、血液中のカルシウム濃度を一定に保つために働くホルモンです。カルシウムが低くなると分泌が増え、骨からカルシウムを取り出したり、腎臓での再吸収を促したりして数値を戻そうとします。</v>
       </c>
       <c r="F80" t="str">
-        <v>肝疾患、胆石など胆道の閉塞</v>
+        <v>原発性・二次性副甲状腺機能亢進症（腎不全に伴うものなど）</v>
       </c>
       <c r="G80" t="str">
-        <v>皮膚や白目の黄染、白っぽい便、濃い茶色の尿がないか確認する</v>
+        <v/>
       </c>
       <c r="H80" t="str">
-        <v/>
+        <v>副甲状腺機能低下症</v>
       </c>
       <c r="I80" t="str">
         <v/>
       </c>
       <c r="J80" t="str">
-        <v>直接優位の上昇は胆道系（胆石、腫瘍による閉塞）を、間接優位の上昇は溶血・体質性を疑う手がかりになる。γ-GTP・ALPと合わせて胆道系疾患を評価する</v>
+        <v>骨粗鬆症の二次性原因（副甲状腺機能亢進症）を除外するための検査。カルシウム・リンと合わせて評価する</v>
       </c>
       <c r="K80" t="str">
-        <v>肝機能</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="L80" t="str">
-        <v>直接ビリルビン,D-Bil,胆石,胆道閉塞</v>
+        <v>PTH,副甲状腺ホルモン,パラトルモン</v>
       </c>
       <c r="M80" t="str">
-        <v/>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>黄疸</v>
+        <v>尿中NTX</v>
       </c>
       <c r="B81" t="str">
-        <v>黄疸,Jaundice</v>
+        <v>NTX</v>
       </c>
       <c r="C81" t="str">
-        <v>所見なし（皮膚・眼球結膜の黄染がなければ正常）</v>
+        <v>施設差が大きく一律の記載が難しい（尿中）</v>
       </c>
       <c r="D81" t="str">
-        <v>ビリルビンが体にたまり、皮膚や白目が黄色くなる状態。単独の検査値ではなく、ビリルビン上昇によって表れる身体所見</v>
+        <v>骨が壊されるときに出る、骨吸収マーカーのひとつ</v>
       </c>
       <c r="E81" t="str">
-        <v>黄疸は、体の中にビリルビンという黄色い色素がたまることで、皮膚や白目が黄色く見える状態です。肝臓や胆道のトラブル、赤血球が壊れやすくなる病気（溶血）などが原因となります。</v>
+        <v>NTXは、骨が壊される（吸収される）ときに尿の中に出てくる物質です。骨粗鬆症の治療薬がどれくらい効いているかを確認するために使われます。</v>
       </c>
       <c r="F81" t="str">
-        <v>肝炎・肝硬変などの肝疾患、胆石・腫瘍による胆道閉塞、溶血性疾患、体質性黄疸（ジルベール症候群）、新生児黄疸</v>
+        <v>骨代謝回転の亢進（骨粗鬆症、閉経後など）</v>
       </c>
       <c r="G81" t="str">
-        <v>白目や皮膚の黄染に気づいたら、尿の色（濃い茶色）や便の色（白っぽい）の変化も確認し、早めの受診を勧める</v>
+        <v/>
       </c>
       <c r="H81" t="str">
-        <v/>
+        <v>骨吸収抑制薬（ビスホスホネート等）による治療効果</v>
       </c>
       <c r="I81" t="str">
         <v/>
       </c>
       <c r="J81" t="str">
-        <v>黄疸は検査値そのものではなく身体所見。原因を調べる際は総ビリルビン・直接ビリルビン・間接ビリルビンの内訳とAST/ALT/γ-GTPを確認する。直接優位なら胆道系、間接優位なら溶血・体質性を疑う</v>
+        <v>治療開始後3〜6か月で再検し、薬の効果判定に使われる。TRACP-5bと同じ「骨を壊す側」の指標</v>
       </c>
       <c r="K81" t="str">
-        <v>肝機能</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="L81" t="str">
-        <v>黄疸,ジョンダイス,Jaundice,ビリルビン,皮膚黄染,白目</v>
+        <v>NTX,尿中NTX,骨吸収マーカー</v>
       </c>
       <c r="M81" t="str">
-        <v/>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>溶血</v>
+        <v>カルシトニン</v>
       </c>
       <c r="B82" t="str">
-        <v>溶血,Hemolysis</v>
+        <v>CT</v>
       </c>
       <c r="C82" t="str">
-        <v>所見なし（溶血を示唆する検査値異常がなければ正常）</v>
+        <v>男性 9.52 pg/mL未満、女性 6.40 pg/mL未満（施設差あり）</v>
       </c>
       <c r="D82" t="str">
-        <v>赤血球が通常より早く壊れる状態。単独の検査値ではなく、複数の検査値の組み合わせで疑う病態</v>
+        <v>血液中のカルシウムを下げる方向に働くホルモン</v>
       </c>
       <c r="E82" t="str">
-        <v>溶血とは、赤血球が通常よりも早いペースで壊れてしまう状態のことです。壊れた赤血球からビリルビンなどが放出されるため、貧血や黄疸の原因になることがあります。</v>
+        <v>カルシトニンは、PTHとは逆に血液中のカルシウムを下げる方向に働くホルモンです。特定の甲状腺の病気（甲状腺髄様癌）がないかを調べる際にも使われます。</v>
       </c>
       <c r="F82" t="str">
-        <v>自己免疫性溶血性貧血、血液型不適合輸血、G6PD欠損症などの遺伝性疾患、機械弁など人工物による物理的破壊、薬剤性溶血</v>
+        <v>甲状腺髄様癌、腎不全</v>
       </c>
       <c r="G82" t="str">
-        <v>倦怠感、黄疸、尿の色が濃くなるなどの症状がないか確認する</v>
+        <v/>
       </c>
       <c r="H82" t="str">
         <v/>
@@ -3772,159 +3772,159 @@
         <v/>
       </c>
       <c r="J82" t="str">
-        <v>溶血を疑う際は、間接ビリルビン上昇・LDH上昇・ハプトグロビン低下・網状赤血球増加のパターンを確認する。ヘモグロビン・MCV・MCHCの変化と合わせて総合的に判断する</v>
+        <v>骨粗鬆症の二次性原因の除外目的で測定されることがある検査値。同名の薬剤（カルシトニン製剤）と混同しないよう注意</v>
       </c>
       <c r="K82" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="L82" t="str">
-        <v>溶血,Hemolysis,溶血性貧血,G6PD,ハプトグロビン</v>
+        <v>カルシトニン,CT</v>
       </c>
       <c r="M82" t="str">
-        <v/>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>乳び</v>
+        <v>DPD（デオキシピリジノリン）</v>
       </c>
       <c r="B83" t="str">
-        <v>乳び,Lipemia</v>
+        <v>DPD</v>
       </c>
       <c r="C83" t="str">
-        <v>所見なし（血清が白濁していなければ正常）</v>
+        <v>施設差が大きく一律の記載が難しい（尿中）</v>
       </c>
       <c r="D83" t="str">
-        <v>中性脂肪が非常に多いため、血清が白く濁って見える状態。検査値そのものではなく検体の外観所見</v>
+        <v>骨のコラーゲンが壊れるときに出る、骨吸収マーカーのひとつ</v>
       </c>
       <c r="E83" t="str">
-        <v>乳びとは、血液中の中性脂肪が非常に多いために、採血した血液（血清）が白く濁って見える状態のことです。多くの場合、食後の採血や、著しい脂質異常症が背景にあります。</v>
+        <v>DPDも、骨が壊されるときに尿に出てくる物質の一つです。NTXと同じように、骨粗鬆症治療薬の効果を確認するために使われます。</v>
       </c>
       <c r="F83" t="str">
-        <v>著しい高中性脂肪血症、食後採血（一時的なもの）、原発性高カイロミクロン血症などの脂質代謝異常</v>
+        <v>骨代謝回転の亢進（骨粗鬆症など）</v>
       </c>
       <c r="G83" t="str">
-        <v>採血が空腹時だったかを確認する。食後採血であれば次回は空腹時の再検を提案する</v>
+        <v/>
       </c>
       <c r="H83" t="str">
-        <v/>
+        <v>骨吸収抑制薬による治療効果</v>
       </c>
       <c r="I83" t="str">
         <v/>
       </c>
       <c r="J83" t="str">
-        <v>血清の白濁により一部の検査項目（電解質など）の測定値に誤差が出ることがある（偽性低ナトリウム血症など）。中性脂肪値と合わせて評価する</v>
+        <v>NTX・CTXと同じ「骨を壊す側」の指標。食事の影響を受けにくいとされる</v>
       </c>
       <c r="K83" t="str">
-        <v>脂質異常症</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="L83" t="str">
-        <v>乳び,乳び血清,Lipemia,高中性脂肪血症</v>
+        <v>DPD,デオキシピリジノリン,骨吸収マーカー</v>
       </c>
       <c r="M83" t="str">
-        <v/>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>亜鉛（Zn）</v>
+        <v>CTX</v>
       </c>
       <c r="B84" t="str">
-        <v>Zn</v>
+        <v>CTX</v>
       </c>
       <c r="C84" t="str">
-        <v>80〜130 μg/dL程度（施設差あり）</v>
+        <v>施設差が大きく一律の記載が難しい（血清・尿中）</v>
       </c>
       <c r="D84" t="str">
-        <v>味覚や皮膚、免疫に関わる微量ミネラル。高齢者や低栄養で不足しやすい</v>
+        <v>骨のコラーゲンが壊れるときに出る、骨吸収マーカーのひとつ</v>
       </c>
       <c r="E84" t="str">
-        <v>亜鉛は、味を感じる働きや皮膚・粘膜の健康、免疫の働きに関わる微量ミネラルです。不足すると、味がわかりにくくなったり（味覚障害）、傷が治りにくくなったりすることがあります。</v>
+        <v>CTXも、骨が壊されるときに血液や尿に出てくる物質です。骨粗鬆症治療薬（骨を壊すのを抑える薬）の効果を確認するために使われます。</v>
       </c>
       <c r="F84" t="str">
-        <v/>
+        <v>骨代謝回転の亢進（骨粗鬆症など）</v>
       </c>
       <c r="G84" t="str">
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>低栄養、高齢による摂取不足、消化器手術後、亜鉛の吸収を妨げる薬剤（PPI、キレート形成する薬剤など）との併用</v>
+        <v>骨吸収抑制薬による治療効果</v>
       </c>
       <c r="I84" t="str">
-        <v>味覚の変化（味を感じにくい、金属味がするなど）がないか確認する。牡蠣、赤身肉、レバーなど亜鉛を多く含む食品を意識するとよいことを伝える</v>
+        <v/>
       </c>
       <c r="J84" t="str">
-        <v>薬剤性の亜鉛欠乏（PPI長期使用、D-ペニシラミン、一部の降圧薬など）に注意。亜鉛欠乏による味覚障害は原因薬剤の中止・亜鉛補充で改善することがある</v>
+        <v>NTX・DPDと同じ「骨を壊す側」の指標。血清・尿中いずれでも測定されることがある</v>
       </c>
       <c r="K84" t="str">
-        <v/>
+        <v>骨粗鬆症</v>
       </c>
       <c r="L84" t="str">
-        <v>亜鉛,Zn,味覚障害,亜鉛欠乏</v>
+        <v>CTX,骨吸収マーカー</v>
       </c>
       <c r="M84" t="str">
-        <v>食事と栄養 p.78（亜鉛）</v>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>マグネシウム（Mg）</v>
+        <v>P1NP</v>
       </c>
       <c r="B85" t="str">
-        <v>Mg</v>
+        <v>P1NP</v>
       </c>
       <c r="C85" t="str">
-        <v>1.8〜2.6 mg/dL程度（施設差あり）</v>
+        <v>施設差が大きく一律の記載が難しい（血清）</v>
       </c>
       <c r="D85" t="str">
-        <v>骨や筋肉、神経の働きに関わるミネラル。低栄養や利尿薬で不足しやすい</v>
+        <v>骨が新しく作られるときに出る、骨形成マーカーのひとつ</v>
       </c>
       <c r="E85" t="str">
-        <v>マグネシウムは、骨や筋肉、神経の働きを支えるミネラルです。不足すると、こむら返りや不整脈、だるさなどの症状が出ることがあります。</v>
+        <v>P1NPは、CTXなどとは逆に、骨が新しく作られるときに血液中に出てくる物質です。骨を作る力を高める薬（テリパラチドなど）の効果を確認するために使われます。</v>
       </c>
       <c r="F85" t="str">
-        <v>腎不全、マグネシウム製剤（酸化マグネシウムなど）の過量投与</v>
+        <v>骨代謝回転の亢進、骨形成促進薬による治療効果</v>
       </c>
       <c r="G85" t="str">
-        <v>腎機能低下がある患者で酸化マグネシウムなどの緩下剤を使用中は、傾眠・血圧低下などの高マグネシウム血症の症状がないか確認する</v>
+        <v/>
       </c>
       <c r="H85" t="str">
-        <v>低栄養、利尿薬の使用、慢性的な下痢、アルコール多飲、PPI長期使用</v>
+        <v>骨形成の低下</v>
       </c>
       <c r="I85" t="str">
-        <v>こむら返りや動悸などの症状がないか確認する</v>
+        <v/>
       </c>
       <c r="J85" t="str">
-        <v>腎機能低下患者への酸化マグネシウム投与は高マグネシウム血症のリスクがあるため定期的なモニタリングが必要。PPI長期使用も低マグネシウム血症のリスク因子として知られる</v>
+        <v>TRACP-5b等「骨を壊す側」の指標とは逆の、「骨を作る側」の指標。骨形成促進薬（テリパラチド等）の効果判定に使われる</v>
       </c>
       <c r="K85" t="str">
-        <v>腎機能</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="L85" t="str">
-        <v>マグネシウム,Mg,酸化マグネシウム,こむら返り</v>
+        <v>P1NP,骨形成マーカー</v>
       </c>
       <c r="M85" t="str">
-        <v>食事と栄養 p.84（マグネシウム）</v>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>乳酸脱水素酵素（LDH）</v>
+        <v>抗甲状腺マイクロゾーム抗体（抗TPO抗体）</v>
       </c>
       <c r="B86" t="str">
-        <v>LDH</v>
+        <v>TPOAb</v>
       </c>
       <c r="C86" t="str">
-        <v>120〜245 U/L程度（施設差あり）</v>
+        <v>陰性（16 IU/mL未満程度、施設差あり）</v>
       </c>
       <c r="D86" t="str">
-        <v>全身のさまざまな組織に含まれる酵素で、細胞が壊れると幅広く上昇する</v>
+        <v>自分の甲状腺を攻撃する抗体が出ていないかを見る検査</v>
       </c>
       <c r="E86" t="str">
-        <v>LDHは全身の細胞の中にある酵素で、肝臓、心臓、筋肉、血液など、いろいろな組織の細胞がダメージを受けると血液中に漏れ出します。どの臓器が原因かを絞り込むには、他の検査値と組み合わせて評価します。</v>
+        <v>この検査は、体の中に自分の甲状腺を誤って攻撃してしまう抗体がないかを見るものです。陽性の場合、橋本病（慢性甲状腺炎）など甲状腺の自己免疫的な炎症が背景にある可能性があります。</v>
       </c>
       <c r="F86" t="str">
-        <v>肝疾患、心筋梗塞、溶血性疾患、悪性腫瘍、筋肉の障害（横紋筋融解症など）、肺疾患</v>
+        <v>橋本病（慢性甲状腺炎）、バセドウ病などの自己免疫性甲状腺疾患</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -3936,136 +3936,136 @@
         <v/>
       </c>
       <c r="J86" t="str">
-        <v>臓器特異性が低いため単独では原因を特定しにくい。AST/ALT(肝)、CK(筋)、ビリルビン・ハプトグロビン(溶血)など他の検査値と組み合わせて原因臓器を推定する</v>
+        <v>陽性でも必ずしも甲状腺機能異常があるとは限らない。TSH・FT4など甲状腺ホルモンの数値と合わせて評価する</v>
       </c>
       <c r="K86" t="str">
-        <v/>
+        <v>甲状腺疾患</v>
       </c>
       <c r="L86" t="str">
-        <v>LDH,乳酸脱水素酵素,溶血,心筋梗塞,悪性腫瘍</v>
+        <v>抗TPO抗体,抗甲状腺マイクロゾーム抗体,TPOAb,橋本病</v>
       </c>
       <c r="M86" t="str">
-        <v/>
+        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>LDH/AST比</v>
+        <v>抗サイログロブリン抗体</v>
       </c>
       <c r="B87" t="str">
-        <v>LDH/AST</v>
+        <v>TgAb</v>
       </c>
       <c r="C87" t="str">
-        <v>目安として使われる比率（施設差・カットオフ値の設定により異なる）</v>
+        <v>陰性（28 IU/mL未満程度、施設差あり）</v>
       </c>
       <c r="D87" t="str">
-        <v>LDHとASTの両方が上昇したときに、原因が肝臓か、それ以外（溶血・心筋・骨格筋）かを見分ける目安になる比</v>
+        <v>甲状腺のたんぱく質（サイログロブリン）への抗体が出ていないかを見る検査</v>
       </c>
       <c r="E87" t="str">
-        <v>これは、肝臓の数値（AST）と、全身に広く分布する酵素（LDH）の比率を見るもので、両方の数値が上がっているときに、原因が肝臓なのか、それとも血液や筋肉など他の場所なのかを見分ける手がかりになります。</v>
+        <v>この検査も、抗TPO抗体と同じく、甲状腺に対する自己免疫の有無を見るものです。あわせて調べることで橋本病などの診断の参考にします。</v>
       </c>
       <c r="F87" t="str">
-        <v>溶血性疾患、心筋梗塞、骨格筋の障害（比が高いほど肝臓以外が原因の可能性）</v>
+        <v>橋本病（慢性甲状腺炎）、バセドウ病などの自己免疫性甲状腺疾患</v>
       </c>
       <c r="G87" t="str">
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>急性肝炎などの肝細胞障害（比が低い、つまりASTに対してLDHが相対的に低い場合は肝性が示唆される）</v>
+        <v/>
       </c>
       <c r="I87" t="str">
         <v/>
       </c>
       <c r="J87" t="str">
-        <v>AST・LDHが同時に上昇した際の鑑別に使う目安の一つ。単独の検査値ではなく計算上の比率であり、確定診断には他の検査（ビリルビン、CK、心筋マーカーなど）と合わせた評価が必要</v>
+        <v>抗TPO抗体とあわせて測定されることが多い。単独の高値だけで治療方針が決まるわけではない</v>
       </c>
       <c r="K87" t="str">
-        <v/>
+        <v>甲状腺疾患</v>
       </c>
       <c r="L87" t="str">
-        <v>LDH/AST,LDH,AST,溶血,心筋梗塞,肝炎</v>
+        <v>抗サイログロブリン抗体,TgAb,橋本病</v>
       </c>
       <c r="M87" t="str">
-        <v/>
+        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>CK/AST比</v>
+        <v>PT-INR（プロトロンビン時間国際標準比）</v>
       </c>
       <c r="B88" t="str">
-        <v>CK/AST</v>
+        <v>PT-INR,INR</v>
       </c>
       <c r="C88" t="str">
-        <v>目安として使われる比率（施設差・カットオフ値の設定により異なる）</v>
+        <v>治療域の目安 1.6〜3.0（ワルファリン服用時。年齢・疾患により異なる）</v>
       </c>
       <c r="D88" t="str">
-        <v>ASTが上昇したときに、原因が筋肉（CKも上昇）か、それ以外（肝臓など）かを見分ける目安になる比</v>
+        <v>血液の固まりやすさを表す数値で、ワルファリンの効き具合を確認するために使う</v>
       </c>
       <c r="E88" t="str">
-        <v>これは、筋肉の数値（CK）と肝臓の数値（AST）を比べることで、ASTの上昇が筋肉由来なのか、肝臓由来なのかを見分ける手がかりになる比率です。</v>
+        <v>PT-INRは血液が固まるまでの時間をもとにした数値で、ワルファリンというお薬を飲んでいる方の効き具合を確認するために測ります。数値が高いほど血液が固まりにくく出血しやすい状態、低いほど血栓ができやすい状態を示します。</v>
       </c>
       <c r="F88" t="str">
-        <v>横紋筋融解症、心筋梗塞、激しい運動など筋肉由来のAST上昇（CKも同時に高値）</v>
+        <v>ワルファリンの効きすぎ、肝機能低下、ビタミンK不足、納豆・青汁など摂取量の変化</v>
       </c>
       <c r="G88" t="str">
-        <v>筋肉痛や脱力感、褐色尿などの症状がないか確認する</v>
+        <v>歯ぐきや鼻からの出血、あざ、黒い便などの出血症状がないか確認する。納豆・クロレラ・青汁などビタミンKを多く含む食品の摂取状況を確認する</v>
       </c>
       <c r="H88" t="str">
-        <v/>
+        <v>ワルファリンの効き不足、飲み忘れ、ビタミンK摂取量の急激な増加</v>
       </c>
       <c r="I88" t="str">
-        <v/>
+        <v>服薬状況（飲み忘れ）を確認する。片側のむくみ・しびれ・胸痛など血栓症状がないか確認する</v>
       </c>
       <c r="J88" t="str">
-        <v>ASTのみ上昇しCKが正常であれば肝臓由来を、両方上昇していれば筋肉由来を疑う手がかりになる。スタチン系薬剤による横紋筋融解症が疑われる場面での鑑別に有用</v>
+        <v>治療域は疾患・年齢によって異なる（例：非弁膜症性心房細動の高齢者では1.6〜2.6が目安になることが多い）。多くの薬剤・食品と相互作用があるため新規薬剤追加時は必ず確認する。DOAC（エリキュース、リクシアナ、プラザキサなど）ではPT-INRのモニタリングは不要</v>
       </c>
       <c r="K88" t="str">
-        <v/>
+        <v>抗凝固療法（心房細動・血栓症）</v>
       </c>
       <c r="L88" t="str">
-        <v>CK/AST,CK,AST,横紋筋融解症,スタチン</v>
+        <v>PT-INR,INR,プロトロンビン時間,ワルファリン,ワーファリン,抗凝固</v>
       </c>
       <c r="M88" t="str">
-        <v/>
+        <v>食事と栄養 p.221（心疾患Q93 ワルファリン服用中のビタミンK摂取）</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>BUN/CRE比</v>
+        <v>血中薬物濃度（TDM）</v>
       </c>
       <c r="B89" t="str">
-        <v>BUN/Cr</v>
+        <v>TDM</v>
       </c>
       <c r="C89" t="str">
-        <v>10前後が目安（施設差あり）</v>
+        <v>薬剤ごとに有効域が異なる（例：カルバマゼピン 4〜12 μg/mL、バルプロ酸 40〜100 μg/mL、フェニトイン 10〜20 μg/mL）</v>
       </c>
       <c r="D89" t="str">
-        <v>BUNとクレアチニンの比率。腎前性（脱水・出血など）か腎性かを見分ける目安になる</v>
+        <v>治療域が狭い薬剤で、血液中の薬の濃度が効果域・中毒域のどちらにあるかを確認する検査</v>
       </c>
       <c r="E89" t="str">
-        <v>これは、BUN（尿素窒素）とクレアチニンという2つの腎機能に関わる検査値を比較したもので、腎臓そのものに問題があるのか、それとも脱水や出血など腎臓の外側に原因があるのかを見分ける手がかりになります。</v>
+        <v>この薬は効く量と副作用が出る量が近いため、血液中の薬の濃度を定期的に測って、ちょうどよい範囲に入っているかを確認します。数値が低いと効果が不十分になり、高いと副作用が出やすくなります。</v>
       </c>
       <c r="F89" t="str">
-        <v>脱水、消化管出血、高たんぱく食、心不全（腎臓への血流低下）</v>
+        <v>過量投与、代謝を妨げる薬剤との併用、肝機能低下による代謝低下</v>
       </c>
       <c r="G89" t="str">
-        <v>脱水が疑われる場合はこまめな水分摂取を勧める。黒い便など消化管出血を示唆する症状がないか確認する</v>
+        <v>ふらつき、眠気、めまい、物が二重に見えるなどの中毒症状がないか確認する</v>
       </c>
       <c r="H89" t="str">
-        <v>低たんぱく食、肝不全、妊娠</v>
+        <v>飲み忘れ、自己判断による減量、代謝を促進する薬剤との併用（相互作用）</v>
       </c>
       <c r="I89" t="str">
-        <v/>
+        <v>発作やてんかん症状の再発がないか確認し、飲み忘れがないか一緒に確認する</v>
       </c>
       <c r="J89" t="str">
-        <v>比が高い（目安20以上）場合は脱水や消化管出血など腎前性の要因を、比が正常範囲で両方高値なら腎性の障害を疑う。BUN単独やクレアチニン単独よりも病態の絞り込みに役立つ</v>
+        <v>採血のタイミング（トラフ値かどうか）で数値の解釈が変わるため採血時点を確認する。カルバマゼピンは自己誘導により長期使用で濃度が下がることがある点にも注意</v>
       </c>
       <c r="K89" t="str">
-        <v>腎機能</v>
+        <v>てんかん</v>
       </c>
       <c r="L89" t="str">
-        <v>BUN/CRE,BUN/Cr,尿素窒素,クレアチニン,脱水,腎前性</v>
+        <v>TDM,血中薬物濃度,治療域,中毒域,カルバマゼピン,フェニトイン,バルプロ酸,抗てんかん薬</v>
       </c>
       <c r="M89" t="str">
         <v/>
@@ -4073,40 +4073,40 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Na-Cl（ナトリウム・クロール差）</v>
+        <v>アミラーゼ（AMY）</v>
       </c>
       <c r="B90" t="str">
-        <v>Na-Cl</v>
+        <v>AMY</v>
       </c>
       <c r="C90" t="str">
-        <v>36前後が目安（施設差あり）</v>
+        <v>44〜132 U/L（施設差あり）</v>
       </c>
       <c r="D90" t="str">
-        <v>ナトリウムからクロールを引いた値。アニオンギャップの簡易的な目安として使われる</v>
+        <v>膵臓や唾液腺から出る消化酵素。膵炎などで血液中に漏れ出す</v>
       </c>
       <c r="E90" t="str">
-        <v>この数値は、ナトリウムとクロールの検査値の差から計算されるもので、体の中に通常とは違う酸（アニオン）がたまっていないかを大まかに見積もるために使われます。</v>
+        <v>アミラーゼは、でんぷんを分解する消化酵素で、主に膵臓と唾液腺から作られます。膵臓に炎症が起きると血液中に漏れ出して数値が上がるため、膵炎の診断や経過観察に使われます。</v>
       </c>
       <c r="F90" t="str">
-        <v>代謝性アシドーシス（乳酸アシドーシス、糖尿病性ケトアシドーシス、腎不全など、体内に有機酸がたまる病態）</v>
+        <v>急性膵炎、慢性膵炎の急性増悪、耳下腺炎（おたふくかぜ）、腎不全</v>
       </c>
       <c r="G90" t="str">
-        <v/>
+        <v>飲酒を控える、脂っこい食事を避けるよう伝える</v>
       </c>
       <c r="H90" t="str">
-        <v/>
+        <v>慢性膵炎の進行期（膵臓の機能低下）</v>
       </c>
       <c r="I90" t="str">
         <v/>
       </c>
       <c r="J90" t="str">
-        <v>本来のアニオンギャップ(Na-(Cl+HCO3))の簡易代用として使われることがあるが、重炭酸(HCO3)を用いた計算の方が正確。メトホルミン使用中の乳酸アシドーシスが疑われる場面などで参考にする</v>
+        <v>膵臓由来か唾液腺由来かを区別するには膵型アミラーゼ(P-AMY)を確認する。急性膵炎では強い腹痛・背部痛を伴うことが多く、飲酒歴の確認も重要</v>
       </c>
       <c r="K90" t="str">
-        <v>電解質</v>
+        <v/>
       </c>
       <c r="L90" t="str">
-        <v>Na-Cl,アニオンギャップ,AG,代謝性アシドーシス,乳酸アシドーシス</v>
+        <v>アミラーゼ,AMY,膵炎,急性膵炎</v>
       </c>
       <c r="M90" t="str">
         <v/>
@@ -4155,25 +4155,25 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>CRP</v>
+        <v>間接ビリルビン</v>
       </c>
       <c r="B92" t="str">
-        <v>CRP</v>
+        <v>I-Bil</v>
       </c>
       <c r="C92" t="str">
-        <v>0.3 mg/dL未満（施設差あり）</v>
+        <v>0.2〜0.8 mg/dL程度（施設差あり）</v>
       </c>
       <c r="D92" t="str">
-        <v>体のどこかに炎症や感染が起きていないかを鋭敏に反映する数値</v>
+        <v>赤血球が壊れてできるビリルビンのうち、肝臓で処理される前の形</v>
       </c>
       <c r="E92" t="str">
-        <v>CRPは、体に炎症や感染が起きると数時間〜半日程度で急激に上昇する数値です。風邪のようなウイルス感染から細菌感染、体のどこかの炎症まで、幅広く反応するため、体調の変化を早期に捉える手がかりになります。</v>
+        <v>間接ビリルビンは、赤血球が壊れてできたビリルビンが、まだ肝臓で処理される前の状態です。この値が高い場合、赤血球が通常より多く壊れている(溶血)か、肝臓での処理能力に生まれつきの体質差(体質性黄疸)がある可能性が考えられます。</v>
       </c>
       <c r="F92" t="str">
-        <v>細菌感染症、ウイルス感染症、自己免疫疾患（関節リウマチなど）、悪性腫瘍、組織の損傷（術後・心筋梗塞など）</v>
+        <v>溶血性疾患（自己免疫性溶血性貧血、血液型不適合輸血など）、体質性黄疸（ジルベール症候群）、新生児黄疸</v>
       </c>
       <c r="G92" t="str">
-        <v>発熱、痛み、腫れなど炎症症状の有無を確認する</v>
+        <v>皮膚や白目の黄染、尿の色の変化がないか確認する</v>
       </c>
       <c r="H92" t="str">
         <v/>
@@ -4182,21 +4182,226 @@
         <v/>
       </c>
       <c r="J92" t="str">
-        <v>白血球数と合わせて感染・炎症の程度を評価する。上昇・低下のタイミングは白血球より半日〜1日程度遅れる傾向があるため、経過を追う際は採血のタイミングに注意</v>
+        <v>直接ビリルビンとの比率で原因を推測する（間接優位は溶血・体質性、直接優位は胆道系）。総ビリルビン・AST/ALTと合わせて評価する</v>
       </c>
       <c r="K92" t="str">
-        <v/>
+        <v>肝機能</v>
       </c>
       <c r="L92" t="str">
-        <v>CRP,炎症,感染</v>
+        <v>間接ビリルビン,I-Bil,溶血</v>
       </c>
       <c r="M92" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>直接ビリルビン</v>
+      </c>
+      <c r="B93" t="str">
+        <v>D-Bil</v>
+      </c>
+      <c r="C93" t="str">
+        <v>0.0〜0.3 mg/dL程度（施設差あり）</v>
+      </c>
+      <c r="D93" t="str">
+        <v>肝臓で処理された後のビリルビン。胆道の詰まりで血液中に増える</v>
+      </c>
+      <c r="E93" t="str">
+        <v>直接ビリルビンは、肝臓で処理された後のビリルビンです。胆石や腫瘍などで胆汁の通り道（胆道）が詰まると、行き場を失って血液中に増え、皮膚や白目が黄色くなる黄疸として現れます。</v>
+      </c>
+      <c r="F93" t="str">
+        <v>肝疾患、胆石など胆道の閉塞</v>
+      </c>
+      <c r="G93" t="str">
+        <v>皮膚や白目の黄染、白っぽい便、濃い茶色の尿がないか確認する</v>
+      </c>
+      <c r="H93" t="str">
+        <v/>
+      </c>
+      <c r="I93" t="str">
+        <v/>
+      </c>
+      <c r="J93" t="str">
+        <v>直接優位の上昇は胆道系（胆石、腫瘍による閉塞）を、間接優位の上昇は溶血・体質性を疑う手がかりになる。γ-GTP・ALPと合わせて胆道系疾患を評価する</v>
+      </c>
+      <c r="K93" t="str">
+        <v>肝機能</v>
+      </c>
+      <c r="L93" t="str">
+        <v>直接ビリルビン,D-Bil,胆石,胆道閉塞</v>
+      </c>
+      <c r="M93" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>LDH/AST比</v>
+      </c>
+      <c r="B94" t="str">
+        <v>LDH/AST</v>
+      </c>
+      <c r="C94" t="str">
+        <v>目安として使われる比率（施設差・カットオフ値の設定により異なる）</v>
+      </c>
+      <c r="D94" t="str">
+        <v>LDHとASTの両方が上昇したときに、原因が肝臓か、それ以外（溶血・心筋・骨格筋）かを見分ける目安になる比</v>
+      </c>
+      <c r="E94" t="str">
+        <v>これは、肝臓の数値（AST）と、全身に広く分布する酵素（LDH）の比率を見るもので、両方の数値が上がっているときに、原因が肝臓なのか、それとも血液や筋肉など他の場所なのかを見分ける手がかりになります。</v>
+      </c>
+      <c r="F94" t="str">
+        <v>溶血性疾患、心筋梗塞、骨格筋の障害（比が高いほど肝臓以外が原因の可能性）</v>
+      </c>
+      <c r="G94" t="str">
+        <v/>
+      </c>
+      <c r="H94" t="str">
+        <v>急性肝炎などの肝細胞障害（比が低い、つまりASTに対してLDHが相対的に低い場合は肝性が示唆される）</v>
+      </c>
+      <c r="I94" t="str">
+        <v/>
+      </c>
+      <c r="J94" t="str">
+        <v>AST・LDHが同時に上昇した際の鑑別に使う目安の一つ。単独の検査値ではなく計算上の比率であり、確定診断には他の検査（ビリルビン、CK、心筋マーカーなど）と合わせた評価が必要</v>
+      </c>
+      <c r="K94" t="str">
+        <v/>
+      </c>
+      <c r="L94" t="str">
+        <v>LDH/AST,LDH,AST,溶血,心筋梗塞,肝炎</v>
+      </c>
+      <c r="M94" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>亜鉛（Zn）</v>
+      </c>
+      <c r="B95" t="str">
+        <v>Zn</v>
+      </c>
+      <c r="C95" t="str">
+        <v>80〜130 μg/dL程度（施設差あり）</v>
+      </c>
+      <c r="D95" t="str">
+        <v>味覚や皮膚、免疫に関わる微量ミネラル。高齢者や低栄養で不足しやすい</v>
+      </c>
+      <c r="E95" t="str">
+        <v>亜鉛は、味を感じる働きや皮膚・粘膜の健康、免疫の働きに関わる微量ミネラルです。不足すると、味がわかりにくくなったり（味覚障害）、傷が治りにくくなったりすることがあります。</v>
+      </c>
+      <c r="F95" t="str">
+        <v/>
+      </c>
+      <c r="G95" t="str">
+        <v/>
+      </c>
+      <c r="H95" t="str">
+        <v>低栄養、高齢による摂取不足、消化器手術後、亜鉛の吸収を妨げる薬剤（PPI、キレート形成する薬剤など）との併用</v>
+      </c>
+      <c r="I95" t="str">
+        <v>味覚の変化（味を感じにくい、金属味がするなど）がないか確認する。牡蠣、赤身肉、レバーなど亜鉛を多く含む食品を意識するとよいことを伝える</v>
+      </c>
+      <c r="J95" t="str">
+        <v>薬剤性の亜鉛欠乏（PPI長期使用、D-ペニシラミン、一部の降圧薬など）に注意。亜鉛欠乏による味覚障害は原因薬剤の中止・亜鉛補充で改善することがある</v>
+      </c>
+      <c r="K95" t="str">
+        <v/>
+      </c>
+      <c r="L95" t="str">
+        <v>亜鉛,Zn,味覚障害,亜鉛欠乏</v>
+      </c>
+      <c r="M95" t="str">
+        <v>食事と栄養 p.78（亜鉛）</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>マグネシウム（Mg）</v>
+      </c>
+      <c r="B96" t="str">
+        <v>Mg</v>
+      </c>
+      <c r="C96" t="str">
+        <v>1.8〜2.6 mg/dL程度（施設差あり）</v>
+      </c>
+      <c r="D96" t="str">
+        <v>骨や筋肉、神経の働きに関わるミネラル。低栄養や利尿薬で不足しやすい</v>
+      </c>
+      <c r="E96" t="str">
+        <v>マグネシウムは、骨や筋肉、神経の働きを支えるミネラルです。不足すると、こむら返りや不整脈、だるさなどの症状が出ることがあります。</v>
+      </c>
+      <c r="F96" t="str">
+        <v>腎不全、マグネシウム製剤（酸化マグネシウムなど）の過量投与</v>
+      </c>
+      <c r="G96" t="str">
+        <v>腎機能低下がある患者で酸化マグネシウムなどの緩下剤を使用中は、傾眠・血圧低下などの高マグネシウム血症の症状がないか確認する</v>
+      </c>
+      <c r="H96" t="str">
+        <v>低栄養、利尿薬の使用、慢性的な下痢、アルコール多飲、PPI長期使用</v>
+      </c>
+      <c r="I96" t="str">
+        <v>こむら返りや動悸などの症状がないか確認する</v>
+      </c>
+      <c r="J96" t="str">
+        <v>腎機能低下患者への酸化マグネシウム投与は高マグネシウム血症のリスクがあるため定期的なモニタリングが必要。PPI長期使用も低マグネシウム血症のリスク因子として知られる</v>
+      </c>
+      <c r="K96" t="str">
+        <v>腎機能</v>
+      </c>
+      <c r="L96" t="str">
+        <v>マグネシウム,Mg,酸化マグネシウム,こむら返り</v>
+      </c>
+      <c r="M96" t="str">
+        <v>食事と栄養 p.84（マグネシウム）</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>CK/AST比</v>
+      </c>
+      <c r="B97" t="str">
+        <v>CK/AST</v>
+      </c>
+      <c r="C97" t="str">
+        <v>目安として使われる比率（施設差・カットオフ値の設定により異なる）</v>
+      </c>
+      <c r="D97" t="str">
+        <v>ASTが上昇したときに、原因が筋肉（CKも上昇）か、それ以外（肝臓など）かを見分ける目安になる比</v>
+      </c>
+      <c r="E97" t="str">
+        <v>これは、筋肉の数値（CK）と肝臓の数値（AST）を比べることで、ASTの上昇が筋肉由来なのか、肝臓由来なのかを見分ける手がかりになる比率です。</v>
+      </c>
+      <c r="F97" t="str">
+        <v>横紋筋融解症、心筋梗塞、激しい運動など筋肉由来のAST上昇（CKも同時に高値）</v>
+      </c>
+      <c r="G97" t="str">
+        <v>筋肉痛や脱力感、褐色尿などの症状がないか確認する</v>
+      </c>
+      <c r="H97" t="str">
+        <v/>
+      </c>
+      <c r="I97" t="str">
+        <v/>
+      </c>
+      <c r="J97" t="str">
+        <v>ASTのみ上昇しCKが正常であれば肝臓由来を、両方上昇していれば筋肉由来を疑う手がかりになる。スタチン系薬剤による横紋筋融解症が疑われる場面での鑑別に有用</v>
+      </c>
+      <c r="K97" t="str">
+        <v/>
+      </c>
+      <c r="L97" t="str">
+        <v>CK/AST,CK,AST,横紋筋融解症,スタチン</v>
+      </c>
+      <c r="M97" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M92"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M97"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/検査値リファレンス初期データ.xlsx
+++ b/検査値リファレンス初期データ.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M97"/>
+  <dimension ref="A1:M99"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -1325,40 +1325,40 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>BUN/CRE比</v>
+        <v>アンモニア</v>
       </c>
       <c r="B23" t="str">
-        <v>BUN/Cr</v>
+        <v>NH3</v>
       </c>
       <c r="C23" t="str">
-        <v>10前後が目安（施設差あり）</v>
+        <v>12〜66 μg/dL（施設差あり／空腹時採血が望ましい）</v>
       </c>
       <c r="D23" t="str">
-        <v>BUNとクレアチニンの比率。腎前性（脱水・出血など）か腎性かを見分ける目安になる</v>
+        <v>肝機能低下や門脈シャントなどで代謝・排泄が低下すると上昇し、意識障害（肝性脳症）の原因となる</v>
       </c>
       <c r="E23" t="str">
-        <v>これは、BUN（尿素窒素）とクレアチニンという2つの腎機能に関わる検査値を比較したもので、腎臓そのものに問題があるのか、それとも脱水や出血など腎臓の外側に原因があるのかを見分ける手がかりになります。</v>
+        <v>アンモニアは体の中でタンパク質が分解されるときにできる老廃物で、通常は肝臓で無害な尿素に変えられて尿として排泄されます。肝臓の働きが弱っていたり血液の流れ道に変化があると、アンモニアがうまく処理されず血液中にたまり、頭がぼんやりしたり意識がもうろうとする原因になることがあります。</v>
       </c>
       <c r="F23" t="str">
-        <v>脱水、消化管出血、高たんぱく食、心不全（腎臓への血流低下）</v>
+        <v>肝硬変・肝不全（門脈-大循環シャント含む）、劇症肝炎、消化管出血、便秘、脱水、高たんぱく食、尿素サイクル異常症、一部薬剤（バルプロ酸など）</v>
       </c>
       <c r="G23" t="str">
-        <v>脱水が疑われる場合はこまめな水分摂取を勧める。黒い便など消化管出血を示唆する症状がないか確認する</v>
+        <v>便秘の解消（排便コントロール）を心がける。ラクツロースやリファキシミンなど肝性脳症治療薬の服薬状況を確認する</v>
       </c>
       <c r="H23" t="str">
-        <v>低たんぱく食、肝不全、妊娠</v>
+        <v>通常、臨床的意義は乏しい</v>
       </c>
       <c r="I23" t="str">
         <v/>
       </c>
       <c r="J23" t="str">
-        <v>比が高い（目安20以上）場合は脱水や消化管出血など腎前性の要因を、比が正常範囲で両方高値なら腎性の障害を疑う。BUN単独やクレアチニン単独よりも病態の絞り込みに役立つ</v>
+        <v>バルプロ酸(デパケン等)は肝疾患の既往がなくても高アンモニア血症を起こすことがあり、意識障害・傾眠が出現した場合は薬剤性を疑ってアンモニア値を確認する。採血後は室温放置で見かけ上上昇するため測定条件にも注意。ラクツロース・リファキシミンは腸管内でのアンモニア産生・吸収を抑える目的で使用される</v>
       </c>
       <c r="K23" t="str">
-        <v>腎機能</v>
+        <v>肝機能</v>
       </c>
       <c r="L23" t="str">
-        <v>BUN/CRE,BUN/Cr,尿素窒素,クレアチニン,脱水,腎前性</v>
+        <v>アンモニア,NH3,肝性脳症,バルプロ酸,門脈シャント</v>
       </c>
       <c r="M23" t="str">
         <v/>
@@ -1366,148 +1366,149 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Na-Cl（ナトリウム・クロール差）</v>
+        <v>中性脂肪（トリグリセリド）</v>
       </c>
       <c r="B24" t="str">
-        <v>Na-Cl</v>
+        <v>TG</v>
       </c>
       <c r="C24" t="str">
-        <v>36前後が目安（施設差あり）</v>
+        <v>150 mg/dL未満（空腹時）</v>
       </c>
       <c r="D24" t="str">
-        <v>ナトリウムからクロールを引いた値。アニオンギャップの簡易的な目安として使われる</v>
+        <v>脂質異常症で高値になりやすい脂質で、食事の影響を強く受ける</v>
       </c>
       <c r="E24" t="str">
-        <v>この数値は、ナトリウムとクロールの検査値の差から計算されるもので、体の中に通常とは違う酸（アニオン）がたまっていないかを大まかに見積もるために使われます。</v>
+        <v>中性脂肪は、食事から摂った脂肪や糖質が体に蓄えられる形になったものです。食後は誰でも一時的に上がるため、正確に評価するには空腹時に採血することが大切です。高い状態が続くと動脈硬化や急性膵炎のリスクが高まります。</v>
       </c>
       <c r="F24" t="str">
-        <v>代謝性アシドーシス（乳酸アシドーシス、糖尿病性ケトアシドーシス、腎不全など、体内に有機酸がたまる病態）</v>
+        <v>脂質異常症、糖質・アルコールの摂りすぎ、肥満、糖尿病のコントロール不良</v>
       </c>
       <c r="G24" t="str">
-        <v/>
+        <v>糖質・アルコールの摂りすぎに注意し、有酸素運動を勧める</v>
       </c>
       <c r="H24" t="str">
-        <v/>
+        <v>低栄養、甲状腺機能亢進症</v>
       </c>
       <c r="I24" t="str">
         <v/>
       </c>
       <c r="J24" t="str">
-        <v>本来のアニオンギャップ(Na-(Cl+HCO3))の簡易代用として使われることがあるが、重炭酸(HCO3)を用いた計算の方が正確。メトホルミン使用中の乳酸アシドーシスが疑われる場面などで参考にする</v>
+        <v>採血が食後か空腹時かで数値が大きく変わるため必ず確認する。500 mg/dL以上では急性膵炎のリスクが高まるため注意。フィブラート系・EPA製剤などの効果判定に使う</v>
       </c>
       <c r="K24" t="str">
-        <v>電解質</v>
+        <v>脂質異常症</v>
       </c>
       <c r="L24" t="str">
-        <v>Na-Cl,アニオンギャップ,AG,代謝性アシドーシス,乳酸アシドーシス</v>
+        <v>中性脂肪,トリグリセリド,TG,脂質異常症</v>
       </c>
       <c r="M24" t="str">
-        <v/>
+        <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>AST/ALT</v>
+        <v>総コレステロール</v>
       </c>
       <c r="B25" t="str">
-        <v>AST/ALT,De Ritis比</v>
+        <v>TC,T-cho</v>
       </c>
       <c r="C25" t="str">
-        <v>1未満が目安（施設・病態により異なる）</v>
+        <v>220 mg/dL未満</v>
       </c>
       <c r="D25" t="str">
-        <v>ASTとALTの比率（De Ritis比）。肝疾患の種類を推測する手がかりになる</v>
+        <v>LDL・HDLなどすべてのコレステロールを合わせた総量</v>
       </c>
       <c r="E25" t="str">
-        <v>これは、肝臓に関わる2つの数値（ASTとALT）の比率を見るもので、肝臓のどのようなタイプのトラブルが起きているかを推測する手がかりになります。</v>
+        <v>総コレステロールは、体の中にあるコレステロールをすべて合わせた数値です。ただし、悪玉(LDL)が多いのか善玉(HDL)が多いのかまでは分からないため、実際の評価にはLDLコレステロールの値がより重視されます。</v>
       </c>
       <c r="F25" t="str">
-        <v>アルコール性肝障害、肝硬変、心筋梗塞・筋疾患の合併（比が2以上でアルコール性を強く示唆）</v>
+        <v>脂質異常症、家族性高コレステロール血症、甲状腺機能低下症</v>
       </c>
       <c r="G25" t="str">
-        <v>飲酒量や頻度を確認する</v>
+        <v>動物性脂肪を控え、食物繊維を増やすよう伝える</v>
       </c>
       <c r="H25" t="str">
-        <v>急性ウイルス性肝炎、脂肪肝（比が1未満で肝細胞の急性障害を示唆することが多い）</v>
+        <v>低栄養、肝機能低下、甲状腺機能亢進症</v>
       </c>
       <c r="I25" t="str">
         <v/>
       </c>
       <c r="J25" t="str">
-        <v>De Ritis比とも呼ばれる。比が2以上はアルコール性肝障害や肝硬変を、1未満は急性ウイルス性肝炎や脂肪肝を示唆する目安になるが、確定診断には他の検査所見と合わせた評価が必要</v>
+        <v>現在はLDLコレステロールでの評価が主流。総コレステロールだけでは悪玉・善玉の内訳が分からないため、LDL・HDL・中性脂肪と合わせて評価する</v>
       </c>
       <c r="K25" t="str">
-        <v>肝機能</v>
+        <v>脂質異常症</v>
       </c>
       <c r="L25" t="str">
-        <v>AST/ALT,De Ritis比,デリティス比,アルコール性肝障害,肝硬変</v>
+        <v>総コレステロール,TC,コレステロール,脂質異常症</v>
       </c>
       <c r="M25" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="26">
+        <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
+      </c>
+    </row>
+    <row r="26" xml:space="preserve">
       <c r="A26" t="str">
-        <v>AST比/ALP比</v>
+        <v>LDLコレステロール</v>
       </c>
       <c r="B26" t="str">
-        <v>R比,R-factor</v>
-      </c>
-      <c r="C26" t="str">
-        <v>R比 5以上：肝細胞障害型、2以下：胆汁うっ滞型、2〜5：混合型（報告により定義が異なる）</v>
+        <v>LDL-C</v>
+      </c>
+      <c r="C26" t="str" xml:space="preserve">
+        <v xml:space="preserve">60〜139 mg/dL
+（140 mg/dL以上で高LDLコレステロール血症）</v>
       </c>
       <c r="D26" t="str">
-        <v>肝障害のパターンを「肝細胞障害型」か「胆汁うっ滞型」かに分類するための指標（R比）</v>
+        <v>いわゆる「悪玉コレステロール」。血管の壁にたまり動脈硬化を進める</v>
       </c>
       <c r="E26" t="str">
-        <v>これは、肝臓の数値の上がり方のパターンから、肝臓の細胞そのものが傷んでいるタイプなのか、胆汁の流れが滞っているタイプなのかを見分けるための指標です。</v>
+        <v>LDLコレステロールは、いわゆる悪玉コレステロールと呼ばれるものです。多いままだと血管の壁にたまって、動脈硬化や心筋梗塞・脳梗塞のリスクを高めます。数値を下げることで、将来の血管のトラブルを防ぐことが目的です。</v>
       </c>
       <c r="F26" t="str">
-        <v>肝細胞障害型（ウイルス性肝炎、薬剤性肝障害の肝細胞障害型など）：AST/ALT優位の上昇</v>
+        <v>脂質異常症、動脈硬化のリスク上昇、家族性高コレステロール血症、甲状腺機能低下症</v>
       </c>
       <c r="G26" t="str">
-        <v/>
+        <v>動物性脂肪や揚げ物を控え、青魚や食物繊維（野菜・海藻・きのこ）を増やすよう伝える</v>
       </c>
       <c r="H26" t="str">
-        <v>胆汁うっ滞型（胆石、胆道腫瘍、薬剤性肝障害の胆汁うっ滞型など）：ALP優位の上昇</v>
+        <v>低栄養、肝機能低下、甲状腺機能亢進症</v>
       </c>
       <c r="I26" t="str">
         <v/>
       </c>
       <c r="J26" t="str">
-        <v>R比＝(ALTの基準値上限に対する倍率)÷(ALPの基準値上限に対する倍率)で算出する。薬剤性肝障害(DILI)の病型分類（肝細胞障害型・胆汁うっ滞型・混合型）に用いられる考え方で、原因薬剤の推定や重症度評価の参考になる</v>
+        <v>スタチン等の効果判定に使う中心的な数値。目標値は既往疾患（冠動脈疾患・糖尿病等）によって異なるため一律に判断しない</v>
       </c>
       <c r="K26" t="str">
-        <v>肝機能</v>
+        <v>脂質異常症,精神疾患（非定型抗精神病薬）</v>
       </c>
       <c r="L26" t="str">
-        <v>R比,R-factor,肝細胞障害型,胆汁うっ滞型,薬剤性肝障害,DILI</v>
+        <v>LDL,LDLコレステロール,悪玉コレステロール,脂質異常症</v>
       </c>
       <c r="M26" t="str">
-        <v/>
+        <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>乳び</v>
+        <v>nonHDLコレステロール</v>
       </c>
       <c r="B27" t="str">
-        <v>乳び,Lipemia</v>
+        <v>non-HDL-C</v>
       </c>
       <c r="C27" t="str">
-        <v>所見なし（血清が白濁していなければ正常）</v>
+        <v>90〜149 mg/dL（150 mg/dL以上で高値）</v>
       </c>
       <c r="D27" t="str">
-        <v>中性脂肪が非常に多いため、血清が白く濁って見える状態。検査値そのものではなく検体の外観所見</v>
+        <v>総コレステロールからHDL（善玉）を除いた、動脈硬化を進めるすべての脂質の合計</v>
       </c>
       <c r="E27" t="str">
-        <v>乳びとは、血液中の中性脂肪が非常に多いために、採血した血液（血清）が白く濁って見える状態のことです。多くの場合、食後の採血や、著しい脂質異常症が背景にあります。</v>
+        <v>nonHDLコレステロールは、総コレステロールから善玉のHDLを引いた数値で、LDL（悪玉）を含む、動脈硬化を進めるすべてのコレステロールの合計を表します。中性脂肪が高くLDLだけでは評価しにくい方でも、こちらで動脈硬化のリスクを評価できます。</v>
       </c>
       <c r="F27" t="str">
-        <v>著しい高中性脂肪血症、食後採血（一時的なもの）、原発性高カイロミクロン血症などの脂質代謝異常</v>
+        <v>脂質異常症、動脈硬化のリスク上昇（特に中性脂肪が高い場合にLDL-Cより実態を反映しやすい）</v>
       </c>
       <c r="G27" t="str">
-        <v>採血が空腹時だったかを確認する。食後採血であれば次回は空腹時の再検を提案する</v>
+        <v>動物性脂肪や揚げ物を控え、青魚や食物繊維（野菜・海藻・きのこ）を増やすよう伝える</v>
       </c>
       <c r="H27" t="str">
         <v/>
@@ -1516,80 +1517,80 @@
         <v/>
       </c>
       <c r="J27" t="str">
-        <v>血清の白濁により一部の検査項目（電解質など）の測定値に誤差が出ることがある（偽性低ナトリウム血症など）。中性脂肪値と合わせて評価する</v>
+        <v>中性脂肪（TG）が400 mg/dL以上などLDL-Cの計算式（Friedewald式）が不正確になる場合に、LDL-Cの代わりに用いられる。目標値はLDL-Cの目標値＋30 mg/dLが目安</v>
       </c>
       <c r="K27" t="str">
         <v>脂質異常症</v>
       </c>
       <c r="L27" t="str">
-        <v>乳び,乳び血清,Lipemia,高中性脂肪血症</v>
+        <v>nonHDL,non-HDLコレステロール,動脈硬化,中性脂肪,LDL計算式</v>
       </c>
       <c r="M27" t="str">
-        <v/>
+        <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>溶血</v>
+        <v>HDLコレステロール</v>
       </c>
       <c r="B28" t="str">
-        <v>溶血,Hemolysis</v>
+        <v>HDL-C</v>
       </c>
       <c r="C28" t="str">
-        <v>所見なし（溶血を示唆する検査値異常がなければ正常）</v>
+        <v>40 mg/dL以上</v>
       </c>
       <c r="D28" t="str">
-        <v>赤血球が通常より早く壊れる状態。単独の検査値ではなく、複数の検査値の組み合わせで疑う病態</v>
+        <v>いわゆる「善玉コレステロール」。血管にたまった余分なコレステロールを回収する</v>
       </c>
       <c r="E28" t="str">
-        <v>溶血とは、赤血球が通常よりも早いペースで壊れてしまう状態のことです。壊れた赤血球からビリルビンなどが放出されるため、貧血や黄疸の原因になることがあります。</v>
+        <v>HDLコレステロールは、いわゆる善玉コレステロールと呼ばれるものです。血管の壁にたまった余分なコレステロールを回収して肝臓に戻す働きがあり、数値が高いほど動脈硬化を防ぐ方向に働きます。</v>
       </c>
       <c r="F28" t="str">
-        <v>自己免疫性溶血性貧血、血液型不適合輸血、G6PD欠損症などの遺伝性疾患、機械弁など人工物による物理的破壊、薬剤性溶血</v>
+        <v/>
       </c>
       <c r="G28" t="str">
-        <v>倦怠感、黄疸、尿の色が濃くなるなどの症状がないか確認する</v>
+        <v/>
       </c>
       <c r="H28" t="str">
-        <v/>
+        <v>脂質異常症（低HDL血症）</v>
       </c>
       <c r="I28" t="str">
-        <v/>
+        <v>適度な運動習慣、禁煙を勧める</v>
       </c>
       <c r="J28" t="str">
-        <v>溶血を疑う際は、間接ビリルビン上昇・LDH上昇・ハプトグロビン低下・網状赤血球増加のパターンを確認する。ヘモグロビン・MCV・MCHCの変化と合わせて総合的に判断する</v>
+        <v>喫煙、運動不足、肥満で低下しやすい。禁煙・運動習慣の改善で上昇が期待できる。低HDLは動脈硬化のリスク因子として単独でも重視される</v>
       </c>
       <c r="K28" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>脂質異常症</v>
       </c>
       <c r="L28" t="str">
-        <v>溶血,Hemolysis,溶血性貧血,G6PD,ハプトグロビン</v>
+        <v>HDL,HDLコレステロール,善玉コレステロール,脂質異常症</v>
       </c>
       <c r="M28" t="str">
-        <v/>
+        <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>黄疸</v>
+        <v>CK（クレアチンフォスフォキナーゼ）</v>
       </c>
       <c r="B29" t="str">
-        <v>黄疸,Jaundice</v>
+        <v>CK,CPK</v>
       </c>
       <c r="C29" t="str">
-        <v>所見なし（皮膚・眼球結膜の黄染がなければ正常）</v>
+        <v>男性 60〜250 U/L、女性 50〜170 U/L</v>
       </c>
       <c r="D29" t="str">
-        <v>ビリルビンが体にたまり、皮膚や白目が黄色くなる状態。単独の検査値ではなく、ビリルビン上昇によって表れる身体所見</v>
+        <v>主に骨格筋・心筋に含まれる酵素。筋肉の損傷で血液中に漏れ出す</v>
       </c>
       <c r="E29" t="str">
-        <v>黄疸は、体の中にビリルビンという黄色い色素がたまることで、皮膚や白目が黄色く見える状態です。肝臓や胆道のトラブル、赤血球が壊れやすくなる病気（溶血）などが原因となります。</v>
+        <v>CKは筋肉の中にある酵素で、激しい運動や筋肉の病気、心筋梗塞などで筋肉の細胞がダメージを受けると血液中に漏れ出して数値が上がります。スタチン系のお薬の副作用（横紋筋融解症）のチェックにも使われます。</v>
       </c>
       <c r="F29" t="str">
-        <v>肝炎・肝硬変などの肝疾患、胆石・腫瘍による胆道閉塞、溶血性疾患、体質性黄疸（ジルベール症候群）、新生児黄疸</v>
+        <v>心筋梗塞、横紋筋融解症（スタチン系薬剤の副作用など）、激しい運動、筋肉注射直後、甲状腺機能低下症</v>
       </c>
       <c r="G29" t="str">
-        <v>白目や皮膚の黄染に気づいたら、尿の色（濃い茶色）や便の色（白っぽい）の変化も確認し、早めの受診を勧める</v>
+        <v>筋肉痛・脱力感・褐色尿（横紋筋融解症の症状）がないか確認する。スタチン系薬剤服用中は特に注意する。激しい運動の直後の採血でないかも確認する</v>
       </c>
       <c r="H29" t="str">
         <v/>
@@ -1598,13 +1599,13 @@
         <v/>
       </c>
       <c r="J29" t="str">
-        <v>黄疸は検査値そのものではなく身体所見。原因を調べる際は総ビリルビン・直接ビリルビン・間接ビリルビンの内訳とAST/ALT/γ-GTPを確認する。直接優位なら胆道系、間接優位なら溶血・体質性を疑う</v>
+        <v>スタチン系薬剤の重大な副作用である横紋筋融解症の指標。筋肉痛・脱力感・褐色尿の有無を必ず確認し、著明高値では服薬継続の可否を医師に相談する</v>
       </c>
       <c r="K29" t="str">
-        <v>肝機能</v>
+        <v/>
       </c>
       <c r="L29" t="str">
-        <v>黄疸,ジョンダイス,Jaundice,ビリルビン,皮膚黄染,白目</v>
+        <v>CK,CPK,クレアチンキナーゼ,横紋筋融解症</v>
       </c>
       <c r="M29" t="str">
         <v/>
@@ -1612,149 +1613,148 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>中性脂肪（トリグリセリド）</v>
+        <v>BUN/CRE比</v>
       </c>
       <c r="B30" t="str">
-        <v>TG</v>
+        <v>BUN/Cr</v>
       </c>
       <c r="C30" t="str">
-        <v>150 mg/dL未満（空腹時）</v>
+        <v>10前後が目安（施設差あり）</v>
       </c>
       <c r="D30" t="str">
-        <v>脂質異常症で高値になりやすい脂質で、食事の影響を強く受ける</v>
+        <v>BUNとクレアチニンの比率。腎前性（脱水・出血など）か腎性かを見分ける目安になる</v>
       </c>
       <c r="E30" t="str">
-        <v>中性脂肪は、食事から摂った脂肪や糖質が体に蓄えられる形になったものです。食後は誰でも一時的に上がるため、正確に評価するには空腹時に採血することが大切です。高い状態が続くと動脈硬化や急性膵炎のリスクが高まります。</v>
+        <v>これは、BUN（尿素窒素）とクレアチニンという2つの腎機能に関わる検査値を比較したもので、腎臓そのものに問題があるのか、それとも脱水や出血など腎臓の外側に原因があるのかを見分ける手がかりになります。</v>
       </c>
       <c r="F30" t="str">
-        <v>脂質異常症、糖質・アルコールの摂りすぎ、肥満、糖尿病のコントロール不良</v>
+        <v>脱水、消化管出血、高たんぱく食、心不全（腎臓への血流低下）</v>
       </c>
       <c r="G30" t="str">
-        <v>糖質・アルコールの摂りすぎに注意し、有酸素運動を勧める</v>
+        <v>脱水が疑われる場合はこまめな水分摂取を勧める。黒い便など消化管出血を示唆する症状がないか確認する</v>
       </c>
       <c r="H30" t="str">
-        <v>低栄養、甲状腺機能亢進症</v>
+        <v>低たんぱく食、肝不全、妊娠</v>
       </c>
       <c r="I30" t="str">
         <v/>
       </c>
       <c r="J30" t="str">
-        <v>採血が食後か空腹時かで数値が大きく変わるため必ず確認する。500 mg/dL以上では急性膵炎のリスクが高まるため注意。フィブラート系・EPA製剤などの効果判定に使う</v>
+        <v>比が高い（目安20以上）場合は脱水や消化管出血など腎前性の要因を、比が正常範囲で両方高値なら腎性の障害を疑う。BUN単独やクレアチニン単独よりも病態の絞り込みに役立つ</v>
       </c>
       <c r="K30" t="str">
-        <v>脂質異常症</v>
+        <v>腎機能</v>
       </c>
       <c r="L30" t="str">
-        <v>中性脂肪,トリグリセリド,TG,脂質異常症</v>
+        <v>BUN/CRE,BUN/Cr,尿素窒素,クレアチニン,脱水,腎前性</v>
       </c>
       <c r="M30" t="str">
-        <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>総コレステロール</v>
+        <v>CK/AST比</v>
       </c>
       <c r="B31" t="str">
-        <v>TC,T-cho</v>
+        <v>CK/AST</v>
       </c>
       <c r="C31" t="str">
-        <v>220 mg/dL未満</v>
+        <v>目安として使われる比率（施設差・カットオフ値の設定により異なる）</v>
       </c>
       <c r="D31" t="str">
-        <v>LDL・HDLなどすべてのコレステロールを合わせた総量</v>
+        <v>ASTが上昇したときに、原因が筋肉（CKも上昇）か、それ以外（肝臓など）かを見分ける目安になる比</v>
       </c>
       <c r="E31" t="str">
-        <v>総コレステロールは、体の中にあるコレステロールをすべて合わせた数値です。ただし、悪玉(LDL)が多いのか善玉(HDL)が多いのかまでは分からないため、実際の評価にはLDLコレステロールの値がより重視されます。</v>
+        <v>これは、筋肉の数値（CK）と肝臓の数値（AST）を比べることで、ASTの上昇が筋肉由来なのか、肝臓由来なのかを見分ける手がかりになる比率です。</v>
       </c>
       <c r="F31" t="str">
-        <v>脂質異常症、家族性高コレステロール血症、甲状腺機能低下症</v>
+        <v>横紋筋融解症、心筋梗塞、激しい運動など筋肉由来のAST上昇（CKも同時に高値）</v>
       </c>
       <c r="G31" t="str">
-        <v>動物性脂肪を控え、食物繊維を増やすよう伝える</v>
+        <v>筋肉痛や脱力感、褐色尿などの症状がないか確認する</v>
       </c>
       <c r="H31" t="str">
-        <v>低栄養、肝機能低下、甲状腺機能亢進症</v>
+        <v/>
       </c>
       <c r="I31" t="str">
         <v/>
       </c>
       <c r="J31" t="str">
-        <v>現在はLDLコレステロールでの評価が主流。総コレステロールだけでは悪玉・善玉の内訳が分からないため、LDL・HDL・中性脂肪と合わせて評価する</v>
+        <v>ASTのみ上昇しCKが正常であれば肝臓由来を、両方上昇していれば筋肉由来を疑う手がかりになる。スタチン系薬剤による横紋筋融解症が疑われる場面での鑑別に有用</v>
       </c>
       <c r="K31" t="str">
-        <v>脂質異常症</v>
+        <v/>
       </c>
       <c r="L31" t="str">
-        <v>総コレステロール,TC,コレステロール,脂質異常症</v>
+        <v>CK/AST,CK,AST,横紋筋融解症,スタチン</v>
       </c>
       <c r="M31" t="str">
-        <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
-      </c>
-    </row>
-    <row r="32" xml:space="preserve">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
       <c r="A32" t="str">
-        <v>LDLコレステロール</v>
+        <v>LDH/AST比</v>
       </c>
       <c r="B32" t="str">
-        <v>LDL-C</v>
-      </c>
-      <c r="C32" t="str" xml:space="preserve">
-        <v xml:space="preserve">60〜139 mg/dL
-（140 mg/dL以上で高LDLコレステロール血症）</v>
+        <v>LDH/AST</v>
+      </c>
+      <c r="C32" t="str">
+        <v>目安として使われる比率（施設差・カットオフ値の設定により異なる）</v>
       </c>
       <c r="D32" t="str">
-        <v>いわゆる「悪玉コレステロール」。血管の壁にたまり動脈硬化を進める</v>
+        <v>LDHとASTの両方が上昇したときに、原因が肝臓か、それ以外（溶血・心筋・骨格筋）かを見分ける目安になる比</v>
       </c>
       <c r="E32" t="str">
-        <v>LDLコレステロールは、いわゆる悪玉コレステロールと呼ばれるものです。多いままだと血管の壁にたまって、動脈硬化や心筋梗塞・脳梗塞のリスクを高めます。数値を下げることで、将来の血管のトラブルを防ぐことが目的です。</v>
+        <v>これは、肝臓の数値（AST）と、全身に広く分布する酵素（LDH）の比率を見るもので、両方の数値が上がっているときに、原因が肝臓なのか、それとも血液や筋肉など他の場所なのかを見分ける手がかりになります。</v>
       </c>
       <c r="F32" t="str">
-        <v>脂質異常症、動脈硬化のリスク上昇、家族性高コレステロール血症、甲状腺機能低下症</v>
+        <v>溶血性疾患、心筋梗塞、骨格筋の障害（比が高いほど肝臓以外が原因の可能性）</v>
       </c>
       <c r="G32" t="str">
-        <v>動物性脂肪や揚げ物を控え、青魚や食物繊維（野菜・海藻・きのこ）を増やすよう伝える</v>
+        <v/>
       </c>
       <c r="H32" t="str">
-        <v>低栄養、肝機能低下、甲状腺機能亢進症</v>
+        <v>急性肝炎などの肝細胞障害（比が低い、つまりASTに対してLDHが相対的に低い場合は肝性が示唆される）</v>
       </c>
       <c r="I32" t="str">
         <v/>
       </c>
       <c r="J32" t="str">
-        <v>スタチン等の効果判定に使う中心的な数値。目標値は既往疾患（冠動脈疾患・糖尿病等）によって異なるため一律に判断しない</v>
+        <v>AST・LDHが同時に上昇した際の鑑別に使う目安の一つ。単独の検査値ではなく計算上の比率であり、確定診断には他の検査（ビリルビン、CK、心筋マーカーなど）と合わせた評価が必要</v>
       </c>
       <c r="K32" t="str">
-        <v>脂質異常症,精神疾患（非定型抗精神病薬）</v>
+        <v/>
       </c>
       <c r="L32" t="str">
-        <v>LDL,LDLコレステロール,悪玉コレステロール,脂質異常症</v>
+        <v>LDH/AST,LDH,AST,溶血,心筋梗塞,肝炎</v>
       </c>
       <c r="M32" t="str">
-        <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>nonHDLコレステロール</v>
+        <v>Na-Cl（ナトリウム・クロール差）</v>
       </c>
       <c r="B33" t="str">
-        <v>non-HDL-C</v>
+        <v>Na-Cl</v>
       </c>
       <c r="C33" t="str">
-        <v>90〜149 mg/dL（150 mg/dL以上で高値）</v>
+        <v>36前後が目安（施設差あり）</v>
       </c>
       <c r="D33" t="str">
-        <v>総コレステロールからHDL（善玉）を除いた、動脈硬化を進めるすべての脂質の合計</v>
+        <v>ナトリウムからクロールを引いた値。アニオンギャップの簡易的な目安として使われる</v>
       </c>
       <c r="E33" t="str">
-        <v>nonHDLコレステロールは、総コレステロールから善玉のHDLを引いた数値で、LDL（悪玉）を含む、動脈硬化を進めるすべてのコレステロールの合計を表します。中性脂肪が高くLDLだけでは評価しにくい方でも、こちらで動脈硬化のリスクを評価できます。</v>
+        <v>この数値は、ナトリウムとクロールの検査値の差から計算されるもので、体の中に通常とは違う酸（アニオン）がたまっていないかを大まかに見積もるために使われます。</v>
       </c>
       <c r="F33" t="str">
-        <v>脂質異常症、動脈硬化のリスク上昇（特に中性脂肪が高い場合にLDL-Cより実態を反映しやすい）</v>
+        <v>代謝性アシドーシス（乳酸アシドーシス、糖尿病性ケトアシドーシス、腎不全など、体内に有機酸がたまる病態）</v>
       </c>
       <c r="G33" t="str">
-        <v>動物性脂肪や揚げ物を控え、青魚や食物繊維（野菜・海藻・きのこ）を増やすよう伝える</v>
+        <v/>
       </c>
       <c r="H33" t="str">
         <v/>
@@ -1763,95 +1763,95 @@
         <v/>
       </c>
       <c r="J33" t="str">
-        <v>中性脂肪（TG）が400 mg/dL以上などLDL-Cの計算式（Friedewald式）が不正確になる場合に、LDL-Cの代わりに用いられる。目標値はLDL-Cの目標値＋30 mg/dLが目安</v>
+        <v>本来のアニオンギャップ(Na-(Cl+HCO3))の簡易代用として使われることがあるが、重炭酸(HCO3)を用いた計算の方が正確。メトホルミン使用中の乳酸アシドーシスが疑われる場面などで参考にする</v>
       </c>
       <c r="K33" t="str">
-        <v>脂質異常症</v>
+        <v>電解質</v>
       </c>
       <c r="L33" t="str">
-        <v>nonHDL,non-HDLコレステロール,動脈硬化,中性脂肪,LDL計算式</v>
+        <v>Na-Cl,アニオンギャップ,AG,代謝性アシドーシス,乳酸アシドーシス</v>
       </c>
       <c r="M33" t="str">
-        <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>HDLコレステロール</v>
+        <v>AST/ALT</v>
       </c>
       <c r="B34" t="str">
-        <v>HDL-C</v>
+        <v>AST/ALT,De Ritis比</v>
       </c>
       <c r="C34" t="str">
-        <v>40 mg/dL以上</v>
+        <v>1未満が目安（施設・病態により異なる）</v>
       </c>
       <c r="D34" t="str">
-        <v>いわゆる「善玉コレステロール」。血管にたまった余分なコレステロールを回収する</v>
+        <v>ASTとALTの比率（De Ritis比）。肝疾患の種類を推測する手がかりになる</v>
       </c>
       <c r="E34" t="str">
-        <v>HDLコレステロールは、いわゆる善玉コレステロールと呼ばれるものです。血管の壁にたまった余分なコレステロールを回収して肝臓に戻す働きがあり、数値が高いほど動脈硬化を防ぐ方向に働きます。</v>
+        <v>これは、肝臓に関わる2つの数値（ASTとALT）の比率を見るもので、肝臓のどのようなタイプのトラブルが起きているかを推測する手がかりになります。</v>
       </c>
       <c r="F34" t="str">
-        <v/>
+        <v>アルコール性肝障害、肝硬変、心筋梗塞・筋疾患の合併（比が2以上でアルコール性を強く示唆）</v>
       </c>
       <c r="G34" t="str">
-        <v/>
+        <v>飲酒量や頻度を確認する</v>
       </c>
       <c r="H34" t="str">
-        <v>脂質異常症（低HDL血症）</v>
+        <v>急性ウイルス性肝炎、脂肪肝（比が1未満で肝細胞の急性障害を示唆することが多い）</v>
       </c>
       <c r="I34" t="str">
-        <v>適度な運動習慣、禁煙を勧める</v>
+        <v/>
       </c>
       <c r="J34" t="str">
-        <v>喫煙、運動不足、肥満で低下しやすい。禁煙・運動習慣の改善で上昇が期待できる。低HDLは動脈硬化のリスク因子として単独でも重視される</v>
+        <v>De Ritis比とも呼ばれる。比が2以上はアルコール性肝障害や肝硬変を、1未満は急性ウイルス性肝炎や脂肪肝を示唆する目安になるが、確定診断には他の検査所見と合わせた評価が必要</v>
       </c>
       <c r="K34" t="str">
-        <v>脂質異常症</v>
+        <v>肝機能</v>
       </c>
       <c r="L34" t="str">
-        <v>HDL,HDLコレステロール,善玉コレステロール,脂質異常症</v>
+        <v>AST/ALT,De Ritis比,デリティス比,アルコール性肝障害,肝硬変</v>
       </c>
       <c r="M34" t="str">
-        <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>CK（クレアチンフォスフォキナーゼ）</v>
+        <v>ALT比ALP</v>
       </c>
       <c r="B35" t="str">
-        <v>CK,CPK</v>
+        <v>ALT比/ALP比,R比,R-factor</v>
       </c>
       <c r="C35" t="str">
-        <v>男性 60〜250 U/L、女性 50〜170 U/L</v>
+        <v>R値 5以上：肝細胞障害型、2以下：胆汁うっ滞型、2〜5：混合型</v>
       </c>
       <c r="D35" t="str">
-        <v>主に骨格筋・心筋に含まれる酵素。筋肉の損傷で血液中に漏れ出す</v>
+        <v>薬剤性肝障害(DILI)などで、肝障害のパターンを「肝細胞障害型」か「胆汁うっ滞型」かに分類するための指標(R値)</v>
       </c>
       <c r="E35" t="str">
-        <v>CKは筋肉の中にある酵素で、激しい運動や筋肉の病気、心筋梗塞などで筋肉の細胞がダメージを受けると血液中に漏れ出して数値が上がります。スタチン系のお薬の副作用（横紋筋融解症）のチェックにも使われます。</v>
+        <v>肝臓に関する数値はいくつかありますが、その組み合わせ方によって「肝臓の細胞自体が傷んでいるタイプ」か「胆汁の流れが悪くなっているタイプ」かをある程度見分けることができます。この指標はその判定に使われます。</v>
       </c>
       <c r="F35" t="str">
-        <v>心筋梗塞、横紋筋融解症（スタチン系薬剤の副作用など）、激しい運動、筋肉注射直後、甲状腺機能低下症</v>
+        <v>R値5以上：肝細胞障害型（ウイルス性肝炎、薬剤性肝障害の肝細胞障害型、虚血性肝障害など）</v>
       </c>
       <c r="G35" t="str">
-        <v>筋肉痛・脱力感・褐色尿（横紋筋融解症の症状）がないか確認する。スタチン系薬剤服用中は特に注意する。激しい運動の直後の採血でないかも確認する</v>
+        <v/>
       </c>
       <c r="H35" t="str">
-        <v/>
+        <v>R値2以下：胆汁うっ滞型（閉塞性黄疸、薬剤性肝障害の胆汁うっ滞型など）</v>
       </c>
       <c r="I35" t="str">
         <v/>
       </c>
       <c r="J35" t="str">
-        <v>スタチン系薬剤の重大な副作用である横紋筋融解症の指標。筋肉痛・脱力感・褐色尿の有無を必ず確認し、著明高値では服薬継続の可否を医師に相談する</v>
+        <v>R値＝(ALTの基準値上限に対する倍率)÷(ALPの基準値上限に対する倍率)で算出する。薬剤性肝障害(DILI)の病型分類(肝細胞障害型/胆汁うっ滞型/混合型)に用いられ、被疑薬の休薬・変更の判断材料になる</v>
       </c>
       <c r="K35" t="str">
-        <v/>
+        <v>肝機能</v>
       </c>
       <c r="L35" t="str">
-        <v>CK,CPK,クレアチンキナーゼ,横紋筋融解症</v>
+        <v>ALT比ALP,ALT/ALP比,R値,R-factor,DILI,薬剤性肝障害</v>
       </c>
       <c r="M35" t="str">
         <v/>
@@ -1859,107 +1859,107 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>TSH（甲状腺刺激ホルモン）</v>
+        <v>AST比/ALP比</v>
       </c>
       <c r="B36" t="str">
-        <v>TSH</v>
+        <v>R比,R-factor</v>
       </c>
       <c r="C36" t="str">
-        <v>0.5〜5.0 μIU/mL程度（施設差あり）</v>
+        <v>R比 5以上：肝細胞障害型、2以下：胆汁うっ滞型、2〜5：混合型（報告により定義が異なる）</v>
       </c>
       <c r="D36" t="str">
-        <v>甲状腺の働きが多いか少ないかを最も敏感に反映するホルモン</v>
+        <v>肝障害のパターンを「肝細胞障害型」か「胆汁うっ滞型」かに分類するための指標（R比）</v>
       </c>
       <c r="E36" t="str">
-        <v>TSHは脳の下垂体から出て、甲状腺に「もっと働いて」と指令を送るホルモンです。甲状腺の働きが弱っていると体が指令を強めるためTSHは上がり、逆に甲状腺が働きすぎているとTSHは下がります。甲状腺の状態を最初に確認する数値としてよく使われます。</v>
+        <v>これは、肝臓の数値の上がり方のパターンから、肝臓の細胞そのものが傷んでいるタイプなのか、胆汁の流れが滞っているタイプなのかを見分けるための指標です。</v>
       </c>
       <c r="F36" t="str">
-        <v>甲状腺機能低下症（橋本病など）、チラーヂンSなど甲状腺ホルモン薬の量不足</v>
+        <v>肝細胞障害型（ウイルス性肝炎、薬剤性肝障害の肝細胞障害型など）：AST/ALT優位の上昇</v>
       </c>
       <c r="G36" t="str">
-        <v>だるさ、むくみ、体重増加、寒がりなどの症状がないか確認する。服薬状況（飲み忘れ、他の薬との飲み合わせ）を確認する</v>
+        <v/>
       </c>
       <c r="H36" t="str">
-        <v>甲状腺機能亢進症（バセドウ病など）、チラーヂンSなど甲状腺ホルモン薬の過量</v>
+        <v>胆汁うっ滞型（胆石、胆道腫瘍、薬剤性肝障害の胆汁うっ滞型など）：ALP優位の上昇</v>
       </c>
       <c r="I36" t="str">
-        <v>動悸、体重減少、暑がり、手のふるえなどの症状がないか確認する</v>
+        <v/>
       </c>
       <c r="J36" t="str">
-        <v>チラーヂンS服用中はTSHが治療目標域に収まっているかで用量調整の目安にする。メルカゾール服用中はTSH・FT4に加えて無顆粒球症の初期症状（発熱・のどの痛み）の有無や白血球数も確認する</v>
+        <v>R比＝(ALTの基準値上限に対する倍率)÷(ALPの基準値上限に対する倍率)で算出する。薬剤性肝障害(DILI)の病型分類（肝細胞障害型・胆汁うっ滞型・混合型）に用いられる考え方で、原因薬剤の推定や重症度評価の参考になる</v>
       </c>
       <c r="K36" t="str">
-        <v>甲状腺疾患</v>
+        <v>肝機能</v>
       </c>
       <c r="L36" t="str">
-        <v>TSH,甲状腺刺激ホルモン,甲状腺機能,橋本病,バセドウ病,チラーヂン,メルカゾール</v>
+        <v>R比,R-factor,肝細胞障害型,胆汁うっ滞型,薬剤性肝障害,DILI</v>
       </c>
       <c r="M36" t="str">
-        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
+        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>FT4（遊離サイロキシン）</v>
+        <v>CONUT値</v>
       </c>
       <c r="B37" t="str">
-        <v>FT4</v>
+        <v>CONUT</v>
       </c>
       <c r="C37" t="str">
-        <v>0.9〜1.7 ng/dL程度（施設差あり）</v>
+        <v>0〜1点：正常、2〜4点：軽度低栄養、5〜8点：中等度低栄養、9〜12点：高度低栄養</v>
       </c>
       <c r="D37" t="str">
-        <v>甲状腺が実際に分泌しているホルモンの量そのものを表す数値</v>
+        <v>アルブミン・総リンパ球数・総コレステロールの3項目から算出する栄養状態の評価スコア</v>
       </c>
       <c r="E37" t="str">
-        <v>FT4は甲状腺そのものが作っているホルモンの量です。TSHが「指令の強さ」だとすると、FT4は「実際に出ている量」にあたります。2つをあわせて見ることで、甲状腺の働きが今どういう状態かを詳しく判断できます。</v>
+        <v>CONUT値は、血液検査（アルブミン、リンパ球数、コレステロール）の結果から計算される、栄養状態を数値化したスコアです。点数が高いほど低栄養の状態が疑われます。</v>
       </c>
       <c r="F37" t="str">
-        <v>甲状腺機能亢進症（バセドウ病など）</v>
+        <v>低栄養状態（点数が高いほど重度）</v>
       </c>
       <c r="G37" t="str">
-        <v>動悸、体重減少、暑がり、手のふるえなどの症状がないか確認する</v>
+        <v>食事摂取量や体重の変化を確認する。必要に応じて栄養補助食品の活用を提案する</v>
       </c>
       <c r="H37" t="str">
-        <v>甲状腺機能低下症（橋本病など）</v>
+        <v/>
       </c>
       <c r="I37" t="str">
-        <v>だるさ、むくみ、体重増加、寒がりなどの症状がないか確認する</v>
+        <v/>
       </c>
       <c r="J37" t="str">
-        <v>TSHと逆方向に動くのが基本だが、下垂体性の異常など例外もある。TSHと合わせて評価し、片方だけで判断しない</v>
+        <v>アルブミン・総リンパ球数・総コレステロールの3項目それぞれに配点があり、合計点で評価する客観的栄養指標。フレイル・サルコペニアの評価やポリファーマシー対策の一環としての栄養状態把握に有用</v>
       </c>
       <c r="K37" t="str">
-        <v>甲状腺疾患</v>
+        <v/>
       </c>
       <c r="L37" t="str">
-        <v>FT4,遊離サイロキシン,甲状腺ホルモン,甲状腺機能</v>
+        <v>CONUT,CONUT値,栄養評価,低栄養,フレイル</v>
       </c>
       <c r="M37" t="str">
-        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
+        <v>食事と栄養 p.240（フレイルQ108 低栄養や食事量の評価）</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>尿蛋白（随時尿）</v>
+        <v>乳び</v>
       </c>
       <c r="B38" t="str">
-        <v>尿蛋白,U-pro</v>
+        <v>乳び,Lipemia</v>
       </c>
       <c r="C38" t="str">
-        <v>陰性（－）〜弱陽性</v>
+        <v>所見なし（血清が白濁していなければ正常）</v>
       </c>
       <c r="D38" t="str">
-        <v>腎臓から本来漏れないはずのたんぱくが尿に出ていないかを見る検査</v>
+        <v>中性脂肪が非常に多いため、血清が白く濁って見える状態。検査値そのものではなく検体の外観所見</v>
       </c>
       <c r="E38" t="str">
-        <v>この検査は、腎臓のろ過機能に負担がかかっていないかを見るものです。本来、たんぱく質は尿にほとんど出ませんが、腎臓に負担がかかると漏れ出るようになります。</v>
+        <v>乳びとは、血液中の中性脂肪が非常に多いために、採血した血液（血清）が白く濁って見える状態のことです。多くの場合、食後の採血や、著しい脂質異常症が背景にあります。</v>
       </c>
       <c r="F38" t="str">
-        <v>糖尿病性腎症、腎炎、高血圧性腎硬化症、発熱・運動後の一過性のもの</v>
+        <v>著しい高中性脂肪血症、食後採血（一時的なもの）、原発性高カイロミクロン血症などの脂質代謝異常</v>
       </c>
       <c r="G38" t="str">
-        <v/>
+        <v>採血が空腹時だったかを確認する。食後採血であれば次回は空腹時の再検を提案する</v>
       </c>
       <c r="H38" t="str">
         <v/>
@@ -1968,13 +1968,13 @@
         <v/>
       </c>
       <c r="J38" t="str">
-        <v>発熱・激しい運動・起立性蛋白尿など生理的な要因でも陽性になることがある。持続する場合に腎症の進行を疑う</v>
+        <v>血清の白濁により一部の検査項目（電解質など）の測定値に誤差が出ることがある（偽性低ナトリウム血症など）。中性脂肪値と合わせて評価する</v>
       </c>
       <c r="K38" t="str">
-        <v>糖尿病,腎機能</v>
+        <v>脂質異常症</v>
       </c>
       <c r="L38" t="str">
-        <v>尿蛋白,U-pro,腎症,たんぱく尿</v>
+        <v>乳び,乳び血清,Lipemia,高中性脂肪血症</v>
       </c>
       <c r="M38" t="str">
         <v/>
@@ -1982,40 +1982,40 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>尿クレアチニン（随時尿）</v>
+        <v>溶血</v>
       </c>
       <c r="B39" t="str">
-        <v>尿CRE</v>
+        <v>溶血,Hemolysis</v>
       </c>
       <c r="C39" t="str">
-        <v>随時尿は主に他項目の濃度補正に利用（単独の基準値は設けにくい）</v>
+        <v>所見なし（溶血を示唆する検査値異常がなければ正常）</v>
       </c>
       <c r="D39" t="str">
-        <v>随時尿中のクレアチニン濃度。他の尿検査項目を薄まり具合で補正するための基準として使う</v>
+        <v>赤血球が通常より早く壊れる状態。単独の検査値ではなく、複数の検査値の組み合わせで疑う病態</v>
       </c>
       <c r="E39" t="str">
-        <v>この数値は、尿がどれくらい薄まっているかを確認するための基準として使われます。他の尿検査の結果（蛋白やアルブミンなど）をこの値で割って補正することで、水分摂取量による影響を減らして正確に評価できます。</v>
+        <v>溶血とは、赤血球が通常よりも早いペースで壊れてしまう状態のことです。壊れた赤血球からビリルビンなどが放出されるため、貧血や黄疸の原因になることがあります。</v>
       </c>
       <c r="F39" t="str">
-        <v/>
+        <v>自己免疫性溶血性貧血、血液型不適合輸血、G6PD欠損症などの遺伝性疾患、機械弁など人工物による物理的破壊、薬剤性溶血</v>
       </c>
       <c r="G39" t="str">
-        <v/>
+        <v>倦怠感、黄疸、尿の色が濃くなるなどの症状がないか確認する</v>
       </c>
       <c r="H39" t="str">
-        <v>尿が薄い（水分摂取が多い、腎機能低下）状態</v>
+        <v/>
       </c>
       <c r="I39" t="str">
         <v/>
       </c>
       <c r="J39" t="str">
-        <v>尿中アルブミン/Cr比、尿蛋白/Cr比など、他項目の補正計算に使われる。単独の高低に臨床的意味は乏しい</v>
+        <v>溶血を疑う際は、間接ビリルビン上昇・LDH上昇・ハプトグロビン低下・網状赤血球増加のパターンを確認する。ヘモグロビン・MCV・MCHCの変化と合わせて総合的に判断する</v>
       </c>
       <c r="K39" t="str">
-        <v>腎機能</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="L39" t="str">
-        <v>尿CRE,尿クレアチニン,随時尿,補正,蛋白クレアチニン比</v>
+        <v>溶血,Hemolysis,溶血性貧血,G6PD,ハプトグロビン</v>
       </c>
       <c r="M39" t="str">
         <v/>
@@ -2023,40 +2023,40 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>白血球（WBC）</v>
+        <v>黄疸</v>
       </c>
       <c r="B40" t="str">
-        <v>WBC</v>
+        <v>黄疸,Jaundice</v>
       </c>
       <c r="C40" t="str">
-        <v>3,300〜8,600 /μL程度（施設差あり）</v>
+        <v>所見なし（皮膚・眼球結膜の黄染がなければ正常）</v>
       </c>
       <c r="D40" t="str">
-        <v>体を細菌やウイルスから守る免疫細胞の数で、感染や炎症、薬剤の影響を反映する</v>
+        <v>ビリルビンが体にたまり、皮膚や白目が黄色くなる状態。単独の検査値ではなく、ビリルビン上昇によって表れる身体所見</v>
       </c>
       <c r="E40" t="str">
-        <v>白血球は体に入ってきた細菌やウイルスと戦う免疫細胞です。感染症や炎症があると増え、逆に一部のお薬の副作用や骨髄の働きが落ちると減ることがあります。</v>
+        <v>黄疸は、体の中にビリルビンという黄色い色素がたまることで、皮膚や白目が黄色く見える状態です。肝臓や胆道のトラブル、赤血球が壊れやすくなる病気（溶血）などが原因となります。</v>
       </c>
       <c r="F40" t="str">
-        <v>感染症、炎症、ステロイド使用、喫煙、白血病などの血液疾患</v>
+        <v>肝炎・肝硬変などの肝疾患、胆石・腫瘍による胆道閉塞、溶血性疾患、体質性黄疸（ジルベール症候群）、新生児黄疸</v>
       </c>
       <c r="G40" t="str">
-        <v>発熱や体の痛みなど感染症状がないか確認する</v>
+        <v>白目や皮膚の黄染に気づいたら、尿の色（濃い茶色）や便の色（白っぽい）の変化も確認し、早めの受診を勧める</v>
       </c>
       <c r="H40" t="str">
-        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、メルカゾールなど薬剤性の無顆粒球症、再生不良性貧血、ウイルス感染</v>
+        <v/>
       </c>
       <c r="I40" t="str">
-        <v>発熱、のどの痛みなど感染症状の初期サインがないか確認する。人混みを避け、手洗い・うがいを徹底するよう伝える</v>
+        <v/>
       </c>
       <c r="J40" t="str">
-        <v>メルカゾール（チアマゾール）は無顆粒球症の重大な副作用があり、発熱・のどの痛みが出たらすぐ受診するよう指導する。抗がん剤・免疫抑制剤・抗てんかん薬（カルバマゼピンなど）使用中も定期的なモニタリングが必要</v>
+        <v>黄疸は検査値そのものではなく身体所見。原因を調べる際は総ビリルビン・直接ビリルビン・間接ビリルビンの内訳とAST/ALT/γ-GTPを確認する。直接優位なら胆道系、間接優位なら溶血・体質性を疑う</v>
       </c>
       <c r="K40" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>肝機能</v>
       </c>
       <c r="L40" t="str">
-        <v>白血球,WBC,好中球,感染症,白血病,無顆粒球症,骨髄抑制</v>
+        <v>黄疸,ジョンダイス,Jaundice,ビリルビン,皮膚黄染,白目</v>
       </c>
       <c r="M40" t="str">
         <v/>
@@ -2064,142 +2064,142 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>赤血球</v>
+        <v>TSH（甲状腺刺激ホルモン）</v>
       </c>
       <c r="B41" t="str">
-        <v>RBC</v>
+        <v>TSH</v>
       </c>
       <c r="C41" t="str">
-        <v>男性 435〜555万/μL、女性 386〜492万/μL程度（施設差あり）</v>
+        <v>0.5〜5.0 μIU/mL程度（施設差あり）</v>
       </c>
       <c r="D41" t="str">
-        <v>血液中で酸素を運ぶ細胞の数。ヘモグロビン・ヘマトクリットと合わせて貧血・多血症を評価する</v>
+        <v>甲状腺の働きが多いか少ないかを最も敏感に反映するホルモン</v>
       </c>
       <c r="E41" t="str">
-        <v>赤血球は、肺で受け取った酸素を全身に運ぶ血液の細胞です。数が少ないと貧血、多いと多血症が疑われます。ヘモグロビンやヘマトクリットと合わせて総合的に評価します。</v>
+        <v>TSHは脳の下垂体から出て、甲状腺に「もっと働いて」と指令を送るホルモンです。甲状腺の働きが弱っていると体が指令を強めるためTSHは上がり、逆に甲状腺が働きすぎているとTSHは下がります。甲状腺の状態を最初に確認する数値としてよく使われます。</v>
       </c>
       <c r="F41" t="str">
-        <v>脱水、多血症（真性多血症、二次性多血症）、喫煙</v>
+        <v>甲状腺機能低下症（橋本病など）、チラーヂンSなど甲状腺ホルモン薬の量不足</v>
       </c>
       <c r="G41" t="str">
-        <v>脱水が疑われる場合はこまめな水分摂取を勧める（水分制限がある場合を除く）</v>
+        <v>だるさ、むくみ、体重増加、寒がりなどの症状がないか確認する。服薬状況（飲み忘れ、他の薬との飲み合わせ）を確認する</v>
       </c>
       <c r="H41" t="str">
-        <v>貧血（鉄欠乏性貧血、腎性貧血など）、出血</v>
+        <v>甲状腺機能亢進症（バセドウ病など）、チラーヂンSなど甲状腺ホルモン薬の過量</v>
       </c>
       <c r="I41" t="str">
-        <v>ヘモグロビンと同様に、出血や食事量低下がないか確認する</v>
+        <v>動悸、体重減少、暑がり、手のふるえなどの症状がないか確認する</v>
       </c>
       <c r="J41" t="str">
-        <v>ヘモグロビン・ヘマトクリットと同じ方向に動くことが多い。赤血球数だけでなくMCV・MCH・MCHCと合わせて貧血のタイプ(小球性・正球性・大球性)を判断する</v>
+        <v>チラーヂンS服用中はTSHが治療目標域に収まっているかで用量調整の目安にする。メルカゾール服用中はTSH・FT4に加えて無顆粒球症の初期症状（発熱・のどの痛み）の有無や白血球数も確認する</v>
       </c>
       <c r="K41" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>甲状腺疾患</v>
       </c>
       <c r="L41" t="str">
-        <v>赤血球,RBC,貧血,多血症</v>
+        <v>TSH,甲状腺刺激ホルモン,甲状腺機能,橋本病,バセドウ病,チラーヂン,メルカゾール</v>
       </c>
       <c r="M41" t="str">
-        <v>食事と栄養 p.151-164（第2部 貧血）</v>
+        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ヘモグロビン濃度</v>
+        <v>FT4（遊離サイロキシン）</v>
       </c>
       <c r="B42" t="str">
-        <v>Hb</v>
+        <v>FT4</v>
       </c>
       <c r="C42" t="str">
-        <v>男性 13.5〜17.5 g/dL、女性 11.5〜15.0 g/dL</v>
+        <v>0.9〜1.7 ng/dL程度（施設差あり）</v>
       </c>
       <c r="D42" t="str">
-        <v>血液の中で酸素を運ぶ役割をしている。この値が低い状態が貧血。</v>
+        <v>甲状腺が実際に分泌しているホルモンの量そのものを表す数値</v>
       </c>
       <c r="E42" t="str">
-        <v>血の数値が良くなっても、体の中の鉄はまだ十分ではないことがあります。そのため、しばらく続けて飲むことが大切です。</v>
+        <v>FT4は甲状腺そのものが作っているホルモンの量です。TSHが「指令の強さ」だとすると、FT4は「実際に出ている量」にあたります。2つをあわせて見ることで、甲状腺の働きが今どういう状態かを詳しく判断できます。</v>
       </c>
       <c r="F42" t="str">
-        <v/>
+        <v>甲状腺機能亢進症（バセドウ病など）</v>
       </c>
       <c r="G42" t="str">
-        <v/>
+        <v>動悸、体重減少、暑がり、手のふるえなどの症状がないか確認する</v>
       </c>
       <c r="H42" t="str">
-        <v>鉄欠乏性貧血、出血、腎性貧血、骨髄の造血機能低下</v>
+        <v>甲状腺機能低下症（橋本病など）</v>
       </c>
       <c r="I42" t="str">
-        <v>鉄分の多い食品（レバー・赤身肉・魚・ほうれん草など）を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える</v>
+        <v>だるさ、むくみ、体重増加、寒がりなどの症状がないか確認する</v>
       </c>
       <c r="J42" t="str">
-        <v>原因（出血・食事量低下など）の確認が重要。腎機能低下がある場合は鉄不足以外が原因のこともある。鉄剤はヘモグロビンが正常化した後も2〜3か月程度は継続することが多い（鉄の貯蔵分を補うため。途中でやめると再び貧血になりやすい）</v>
+        <v>TSHと逆方向に動くのが基本だが、下垂体性の異常など例外もある。TSHと合わせて評価し、片方だけで判断しない</v>
       </c>
       <c r="K42" t="str">
-        <v>鉄欠乏性貧血,抗血小板療法,抗凝固療法（心房細動・血栓症）</v>
+        <v>甲状腺疾患</v>
       </c>
       <c r="L42" t="str">
-        <v>ヘモグロビン,Hb,貧血,鉄剤,鉄欠乏性貧血</v>
+        <v>FT4,遊離サイロキシン,甲状腺ホルモン,甲状腺機能</v>
       </c>
       <c r="M42" t="str">
-        <v>食事と栄養 p.151-164（第2部 貧血）</v>
+        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ヘマトクリット値</v>
+        <v>尿蛋白（随時尿）</v>
       </c>
       <c r="B43" t="str">
-        <v>Ht,Hct</v>
+        <v>尿蛋白,U-pro</v>
       </c>
       <c r="C43" t="str">
-        <v>男性 40〜50%、女性 35〜45%</v>
+        <v>陰性（－）〜弱陽性</v>
       </c>
       <c r="D43" t="str">
-        <v>血液全体のうち赤血球が占める体積の割合。貧血・脱水の指標</v>
+        <v>腎臓から本来漏れないはずのたんぱくが尿に出ていないかを見る検査</v>
       </c>
       <c r="E43" t="str">
-        <v>ヘマトクリットは、血液全体のうち赤血球が占める割合を表す数値です。この値が低いと貧血、高いと脱水や血液が濃くなっている状態が疑われます。</v>
+        <v>この検査は、腎臓のろ過機能に負担がかかっていないかを見るものです。本来、たんぱく質は尿にほとんど出ませんが、腎臓に負担がかかると漏れ出るようになります。</v>
       </c>
       <c r="F43" t="str">
-        <v>脱水、多血症（真性多血症、二次性多血症）、喫煙</v>
+        <v>糖尿病性腎症、腎炎、高血圧性腎硬化症、発熱・運動後の一過性のもの</v>
       </c>
       <c r="G43" t="str">
-        <v>脱水が疑われる場合はこまめな水分摂取を勧める（水分制限がある場合を除く）</v>
+        <v/>
       </c>
       <c r="H43" t="str">
-        <v>貧血（鉄欠乏性貧血、腎性貧血など）、出血</v>
+        <v/>
       </c>
       <c r="I43" t="str">
-        <v>ヘモグロビンと同様に、出血や食事量低下がないか確認する</v>
+        <v/>
       </c>
       <c r="J43" t="str">
-        <v>ヘモグロビン・赤血球数と合わせて評価する。3つの値は同じ方向に動くことが多く、脱水があると貧血が見かけ上隠れることがある</v>
+        <v>発熱・激しい運動・起立性蛋白尿など生理的な要因でも陽性になることがある。持続する場合に腎症の進行を疑う</v>
       </c>
       <c r="K43" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>糖尿病,腎機能</v>
       </c>
       <c r="L43" t="str">
-        <v>ヘマトクリット,Ht,Hct,貧血,脱水,多血症</v>
+        <v>尿蛋白,U-pro,腎症,たんぱく尿</v>
       </c>
       <c r="M43" t="str">
-        <v>食事と栄養 p.151-164（第2部 貧血）</v>
+        <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>MCV</v>
+        <v>尿クレアチニン（随時尿）</v>
       </c>
       <c r="B44" t="str">
-        <v>MCV</v>
+        <v>尿CRE</v>
       </c>
       <c r="C44" t="str">
-        <v>79〜100 fL</v>
+        <v>随時尿は主に他項目の濃度補正に利用（単独の基準値は設けにくい）</v>
       </c>
       <c r="D44" t="str">
-        <v>赤血球1個の大きさ</v>
+        <v>随時尿中のクレアチニン濃度。他の尿検査項目を薄まり具合で補正するための基準として使う</v>
       </c>
       <c r="E44" t="str">
-        <v>MCVは赤血球1個あたりの大きさを表す数値です。貧血があるとき、この数値で「小さい貧血」か「大きい貧血」かを見分けることができ、原因を絞り込む手がかりになります。</v>
+        <v>この数値は、尿がどれくらい薄まっているかを確認するための基準として使われます。他の尿検査の結果（蛋白やアルブミンなど）をこの値で割って補正することで、水分摂取量による影響を減らして正確に評価できます。</v>
       </c>
       <c r="F44" t="str">
         <v/>
@@ -2208,101 +2208,101 @@
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>尿が薄い（水分摂取が多い、腎機能低下）状態</v>
       </c>
       <c r="I44" t="str">
-        <v>鉄分の多い食事を意識する（ヘモグロビンの項目を参照）</v>
+        <v/>
       </c>
       <c r="J44" t="str">
-        <v/>
+        <v>尿中アルブミン/Cr比、尿蛋白/Cr比など、他項目の補正計算に使われる。単独の高低に臨床的意味は乏しい</v>
       </c>
       <c r="K44" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>腎機能</v>
       </c>
       <c r="L44" t="str">
-        <v>MCV,赤血球指数,貧血</v>
+        <v>尿CRE,尿クレアチニン,随時尿,補正,蛋白クレアチニン比</v>
       </c>
       <c r="M44" t="str">
-        <v>食事と栄養 p.151-164（第2部 貧血）</v>
+        <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>MCH</v>
+        <v>白血球（WBC）</v>
       </c>
       <c r="B45" t="str">
-        <v>MCH</v>
+        <v>WBC</v>
       </c>
       <c r="C45" t="str">
-        <v>26.3〜34.3 pg</v>
+        <v>3,300〜8,600 /μL程度（施設差あり）</v>
       </c>
       <c r="D45" t="str">
-        <v>赤血球1個に含まれるヘモグロビン量</v>
+        <v>体を細菌やウイルスから守る免疫細胞の数で、感染や炎症、薬剤の影響を反映する</v>
       </c>
       <c r="E45" t="str">
-        <v>MCHは赤血球1個の中に含まれるヘモグロビン（酸素を運ぶ色素）の量を表す数値です。MCVと同じく、貧血の種類を見分けるのに使われます。</v>
+        <v>白血球は体に入ってきた細菌やウイルスと戦う免疫細胞です。感染症や炎症があると増え、逆に一部のお薬の副作用や骨髄の働きが落ちると減ることがあります。</v>
       </c>
       <c r="F45" t="str">
-        <v/>
+        <v>感染症、炎症、ステロイド使用、喫煙、白血病などの血液疾患</v>
       </c>
       <c r="G45" t="str">
-        <v/>
+        <v>発熱や体の痛みなど感染症状がないか確認する</v>
       </c>
       <c r="H45" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、メルカゾールなど薬剤性の無顆粒球症、再生不良性貧血、ウイルス感染</v>
       </c>
       <c r="I45" t="str">
-        <v>鉄分の多い食事を意識する（ヘモグロビンの項目を参照）</v>
+        <v>発熱、のどの痛みなど感染症状の初期サインがないか確認する。人混みを避け、手洗い・うがいを徹底するよう伝える</v>
       </c>
       <c r="J45" t="str">
-        <v/>
+        <v>メルカゾール（チアマゾール）は無顆粒球症の重大な副作用があり、発熱・のどの痛みが出たらすぐ受診するよう指導する。抗がん剤・免疫抑制剤・抗てんかん薬（カルバマゼピンなど）使用中も定期的なモニタリングが必要</v>
       </c>
       <c r="K45" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L45" t="str">
-        <v>MCH,赤血球指数,貧血</v>
+        <v>白血球,WBC,好中球,感染症,白血病,無顆粒球症,骨髄抑制</v>
       </c>
       <c r="M45" t="str">
-        <v>食事と栄養 p.151-164（第2部 貧血）</v>
+        <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>MCHC</v>
+        <v>赤血球</v>
       </c>
       <c r="B46" t="str">
-        <v>MCHC</v>
+        <v>RBC</v>
       </c>
       <c r="C46" t="str">
-        <v>31.6〜36.6 %</v>
+        <v>男性 435〜555万/μL、女性 386〜492万/μL程度（施設差あり）</v>
       </c>
       <c r="D46" t="str">
-        <v>単位容積あたりの赤血球に含まれるヘモグロビン濃度</v>
+        <v>血液中で酸素を運ぶ細胞の数。ヘモグロビン・ヘマトクリットと合わせて貧血・多血症を評価する</v>
       </c>
       <c r="E46" t="str">
-        <v>MCHCは、赤血球の中にヘモグロビンがどれくらい濃く詰まっているかを表す数値です。鉄が不足すると、この濃度も薄くなる傾向があります。</v>
+        <v>赤血球は、肺で受け取った酸素を全身に運ぶ血液の細胞です。数が少ないと貧血、多いと多血症が疑われます。ヘモグロビンやヘマトクリットと合わせて総合的に評価します。</v>
       </c>
       <c r="F46" t="str">
-        <v/>
+        <v>脱水、多血症（真性多血症、二次性多血症）、喫煙</v>
       </c>
       <c r="G46" t="str">
-        <v/>
+        <v>脱水が疑われる場合はこまめな水分摂取を勧める（水分制限がある場合を除く）</v>
       </c>
       <c r="H46" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>貧血（鉄欠乏性貧血、腎性貧血など）、出血</v>
       </c>
       <c r="I46" t="str">
-        <v>鉄分の多い食事を意識する（ヘモグロビンの項目を参照）</v>
+        <v>ヘモグロビンと同様に、出血や食事量低下がないか確認する</v>
       </c>
       <c r="J46" t="str">
-        <v/>
+        <v>ヘモグロビン・ヘマトクリットと同じ方向に動くことが多い。赤血球数だけでなくMCV・MCH・MCHCと合わせて貧血のタイプ(小球性・正球性・大球性)を判断する</v>
       </c>
       <c r="K46" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
       <c r="L46" t="str">
-        <v>MCHC,赤血球指数,貧血</v>
+        <v>赤血球,RBC,貧血,多血症</v>
       </c>
       <c r="M46" t="str">
         <v>食事と栄養 p.151-164（第2部 貧血）</v>
@@ -2310,81 +2310,81 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>血小板数</v>
+        <v>ヘモグロビン濃度</v>
       </c>
       <c r="B47" t="str">
-        <v>Plt</v>
+        <v>Hb</v>
       </c>
       <c r="C47" t="str">
-        <v>15.0〜35.0万/μL程度（施設差あり）</v>
+        <v>男性 13.5〜17.5 g/dL、女性 11.5〜15.0 g/dL</v>
       </c>
       <c r="D47" t="str">
-        <v>出血を止める働きをする血液成分で、少なすぎると出血しやすくなる</v>
+        <v>血液の中で酸素を運ぶ役割をしている。この値が低い状態が貧血。</v>
       </c>
       <c r="E47" t="str">
-        <v>血小板は、血管が傷ついたときに集まって血を止める役割をする血液の成分です。数が少ないとあざができやすくなったり、出血が止まりにくくなったりします。抗血小板薬や抗がん剤を使っている方では、定期的にチェックすることが大切です。</v>
+        <v>血の数値が良くなっても、体の中の鉄はまだ十分ではないことがあります。そのため、しばらく続けて飲むことが大切です。</v>
       </c>
       <c r="F47" t="str">
-        <v>炎症性疾患、鉄欠乏性貧血、脾摘後、骨髄増殖性疾患</v>
+        <v/>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、肝硬変・脾機能亢進、再生不良性貧血、抗てんかん薬（バルプロ酸など）の副作用、ITP（特発性血小板減少性紫斑病）</v>
+        <v>鉄欠乏性貧血、出血、腎性貧血、骨髄の造血機能低下</v>
       </c>
       <c r="I47" t="str">
-        <v>あざができやすい、歯ぐきや鼻からの出血が増えていないか確認する。強い運動や転倒によるけがに注意するよう伝える</v>
+        <v>鉄分の多い食品（レバー・赤身肉・魚・ほうれん草など）を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える</v>
       </c>
       <c r="J47" t="str">
-        <v>抗血小板薬・抗凝固薬使用中に血小板減少があると出血リスクがさらに高まる。抗がん剤・バルプロ酸・カルバマゼピンなど骨髄抑制のリスクがある薬剤使用中は定期採血の実施状況を確認する</v>
+        <v>原因（出血・食事量低下など）の確認が重要。腎機能低下がある場合は鉄不足以外が原因のこともある。鉄剤はヘモグロビンが正常化した後も2〜3か月程度は継続することが多い（鉄の貯蔵分を補うため。途中でやめると再び貧血になりやすい）</v>
       </c>
       <c r="K47" t="str">
-        <v>てんかん,抗血小板療法</v>
+        <v>鉄欠乏性貧血,抗血小板療法,抗凝固療法（心房細動・血栓症）</v>
       </c>
       <c r="L47" t="str">
-        <v>血小板,Plt,platelet,出血,あざ,紫斑,骨髄抑制</v>
+        <v>ヘモグロビン,Hb,貧血,鉄剤,鉄欠乏性貧血</v>
       </c>
       <c r="M47" t="str">
-        <v/>
+        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>RDW-SD</v>
+        <v>ヘマトクリット値</v>
       </c>
       <c r="B48" t="str">
-        <v>RDW-SD</v>
+        <v>Ht,Hct</v>
       </c>
       <c r="C48" t="str">
-        <v>39〜46 fL程度（施設差あり）</v>
+        <v>男性 40〜50%、女性 35〜45%</v>
       </c>
       <c r="D48" t="str">
-        <v>赤血球の大きさのばらつきを表す指標(絶対値)。鉄欠乏性貧血などの初期変化を捉えやすい</v>
+        <v>血液全体のうち赤血球が占める体積の割合。貧血・脱水の指標</v>
       </c>
       <c r="E48" t="str">
-        <v>RDW-SDは、赤血球の大きさがどれくらいバラバラになっているかを表す数値です。貧血の原因を調べる際、鉄が足りなくなり始めた早い段階での変化を捉えるのに役立ちます。</v>
+        <v>ヘマトクリットは、血液全体のうち赤血球が占める割合を表す数値です。この値が低いと貧血、高いと脱水や血液が濃くなっている状態が疑われます。</v>
       </c>
       <c r="F48" t="str">
-        <v>鉄欠乏性貧血の初期、混合性貧血（複数の原因が重なっている状態）、赤血球産生の乱れ</v>
+        <v>脱水、多血症（真性多血症、二次性多血症）、喫煙</v>
       </c>
       <c r="G48" t="str">
-        <v/>
+        <v>脱水が疑われる場合はこまめな水分摂取を勧める（水分制限がある場合を除く）</v>
       </c>
       <c r="H48" t="str">
-        <v/>
+        <v>貧血（鉄欠乏性貧血、腎性貧血など）、出血</v>
       </c>
       <c r="I48" t="str">
-        <v/>
+        <v>ヘモグロビンと同様に、出血や食事量低下がないか確認する</v>
       </c>
       <c r="J48" t="str">
-        <v>MCVが正常範囲でもRDWが上昇している場合、鉄欠乏の初期段階を示唆することがある。MCV・MCHと合わせて評価する</v>
+        <v>ヘモグロビン・赤血球数と合わせて評価する。3つの値は同じ方向に動くことが多く、脱水があると貧血が見かけ上隠れることがある</v>
       </c>
       <c r="K48" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
       <c r="L48" t="str">
-        <v>RDW-SD,赤血球分布幅,貧血,鉄欠乏</v>
+        <v>ヘマトクリット,Ht,Hct,貧血,脱水,多血症</v>
       </c>
       <c r="M48" t="str">
         <v>食事と栄養 p.151-164（第2部 貧血）</v>
@@ -2392,40 +2392,40 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>RDW-CV</v>
+        <v>MCV</v>
       </c>
       <c r="B49" t="str">
-        <v>RDW-CV</v>
+        <v>MCV</v>
       </c>
       <c r="C49" t="str">
-        <v>11.5〜14.5%程度（施設差あり）</v>
+        <v>79〜100 fL</v>
       </c>
       <c r="D49" t="str">
-        <v>赤血球の大きさのばらつきを割合(%)で表した指標</v>
+        <v>赤血球1個の大きさ</v>
       </c>
       <c r="E49" t="str">
-        <v>RDW-CVもRDW-SDと同じく、赤血球の大きさのばらつきを表す数値ですが、こちらは割合(%)で示されます。貧血のタイプを見分ける手がかりになります。</v>
+        <v>MCVは赤血球1個あたりの大きさを表す数値です。貧血があるとき、この数値で「小さい貧血」か「大きい貧血」かを見分けることができ、原因を絞り込む手がかりになります。</v>
       </c>
       <c r="F49" t="str">
-        <v>鉄欠乏性貧血、ビタミンB12・葉酸欠乏性貧血、混合性貧血</v>
+        <v/>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v/>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="I49" t="str">
-        <v/>
+        <v>鉄分の多い食事を意識する（ヘモグロビンの項目を参照）</v>
       </c>
       <c r="J49" t="str">
-        <v>RDW-SDと同様の意味を持つ指標。MCVが小さくRDWが高ければ鉄欠乏性貧血、MCVが大きくRDWが高ければビタミンB12・葉酸欠乏を疑う手がかりになる</v>
+        <v/>
       </c>
       <c r="K49" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
       <c r="L49" t="str">
-        <v>RDW-CV,赤血球分布幅,貧血,ビタミンB12,葉酸</v>
+        <v>MCV,赤血球指数,貧血</v>
       </c>
       <c r="M49" t="str">
         <v>食事と栄養 p.151-164（第2部 貧血）</v>
@@ -2433,122 +2433,122 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>好中球実数値</v>
+        <v>MCH</v>
       </c>
       <c r="B50" t="str">
-        <v>Neutro#,ANC</v>
+        <v>MCH</v>
       </c>
       <c r="C50" t="str">
-        <v>2,000〜7,500 /μL程度（施設差あり、白血球数×好中球%で算出）</v>
+        <v>26.3〜34.3 pg</v>
       </c>
       <c r="D50" t="str">
-        <v>好中球の絶対数。感染症リスクを判断する上で割合(%)より重要な指標</v>
+        <v>赤血球1個に含まれるヘモグロビン量</v>
       </c>
       <c r="E50" t="str">
-        <v>これは好中球の実際の数を表す数値です。割合(%)だけでなく、実際の数がどれくらいあるかを見ることで、感染症にかかりやすい状態かどうかをより正確に判断できます。</v>
+        <v>MCHは赤血球1個の中に含まれるヘモグロビン（酸素を運ぶ色素）の量を表す数値です。MCVと同じく、貧血の種類を見分けるのに使われます。</v>
       </c>
       <c r="F50" t="str">
-        <v>細菌感染症、炎症、ステロイド使用</v>
+        <v/>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、メルカゾールなど薬剤性の無顆粒球症（1,000/μL未満で好中球減少症、500/μL未満で重症感染リスクが著しく上昇）</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="I50" t="str">
-        <v>発熱、のどの痛みなど感染症状の初期サインがないか確認する。人混みを避け、手洗い・うがいを徹底するよう伝える</v>
+        <v>鉄分の多い食事を意識する（ヘモグロビンの項目を参照）</v>
       </c>
       <c r="J50" t="str">
-        <v>抗がん剤・メルカゾール・カルバマゼピンなど骨髄抑制のリスクがある薬剤使用中は特に重視すべき数値。500/μL未満は発熱性好中球減少症のリスクが高く緊急性が高い</v>
+        <v/>
       </c>
       <c r="K50" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="L50" t="str">
-        <v>好中球実数値,好中球数,ANC,無顆粒球症,発熱性好中球減少症</v>
+        <v>MCH,赤血球指数,貧血</v>
       </c>
       <c r="M50" t="str">
-        <v/>
+        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>好酸球実数値</v>
+        <v>MCHC</v>
       </c>
       <c r="B51" t="str">
-        <v>Eosino#</v>
+        <v>MCHC</v>
       </c>
       <c r="C51" t="str">
-        <v>100〜500 /μL程度（施設差あり）</v>
+        <v>31.6〜36.6 %</v>
       </c>
       <c r="D51" t="str">
-        <v>好酸球の絶対数。アレルギーや薬剤反応の程度をより正確に評価できる</v>
+        <v>単位容積あたりの赤血球に含まれるヘモグロビン濃度</v>
       </c>
       <c r="E51" t="str">
-        <v>これは好酸球の実際の数を表す数値です。割合(%)だけでなく実数を見ることで、アレルギー反応の強さをより正確に把握できます。</v>
+        <v>MCHCは、赤血球の中にヘモグロビンがどれくらい濃く詰まっているかを表す数値です。鉄が不足すると、この濃度も薄くなる傾向があります。</v>
       </c>
       <c r="F51" t="str">
-        <v>アレルギー性疾患、薬剤アレルギー、寄生虫感染</v>
+        <v/>
       </c>
       <c r="G51" t="str">
-        <v>新しく始めた薬がないか確認する</v>
+        <v/>
       </c>
       <c r="H51" t="str">
-        <v/>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="I51" t="str">
-        <v/>
+        <v>鉄分の多い食事を意識する（ヘモグロビンの項目を参照）</v>
       </c>
       <c r="J51" t="str">
-        <v>薬剤性過敏症症候群(DIHS)などでは著明な好酸球増多を認めることがあり、原因薬剤の特定に役立つ</v>
+        <v/>
       </c>
       <c r="K51" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="L51" t="str">
-        <v>好酸球実数値,好酸球数,アレルギー,DIHS</v>
+        <v>MCHC,赤血球指数,貧血</v>
       </c>
       <c r="M51" t="str">
-        <v/>
+        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>好塩基球実数値</v>
+        <v>血小板数</v>
       </c>
       <c r="B52" t="str">
-        <v>Baso#</v>
+        <v>Plt</v>
       </c>
       <c r="C52" t="str">
-        <v>0〜100 /μL程度（施設差あり）</v>
+        <v>15.0〜35.0万/μL程度（施設差あり）</v>
       </c>
       <c r="D52" t="str">
-        <v>好塩基球の絶対数</v>
+        <v>出血を止める働きをする血液成分で、少なすぎると出血しやすくなる</v>
       </c>
       <c r="E52" t="str">
-        <v>これは好塩基球の実際の数を表す数値です。数がとても少ない種類の血球なので、通常は大きな変動を示すことは多くありません。</v>
+        <v>血小板は、血管が傷ついたときに集まって血を止める役割をする血液の成分です。数が少ないとあざができやすくなったり、出血が止まりにくくなったりします。抗血小板薬や抗がん剤を使っている方では、定期的にチェックすることが大切です。</v>
       </c>
       <c r="F52" t="str">
-        <v>慢性骨髄性白血病などの血液疾患、アレルギー性疾患</v>
+        <v>炎症性疾患、鉄欠乏性貧血、脾摘後、骨髄増殖性疾患</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v/>
+        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、肝硬変・脾機能亢進、再生不良性貧血、抗てんかん薬（バルプロ酸など）の副作用、ITP（特発性血小板減少性紫斑病）</v>
       </c>
       <c r="I52" t="str">
-        <v/>
+        <v>あざができやすい、歯ぐきや鼻からの出血が増えていないか確認する。強い運動や転倒によるけがに注意するよう伝える</v>
       </c>
       <c r="J52" t="str">
-        <v>単独での臨床的意義は乏しく、他の血球指標（白血球分画全体）と合わせて評価する</v>
+        <v>抗血小板薬・抗凝固薬使用中に血小板減少があると出血リスクがさらに高まる。抗がん剤・バルプロ酸・カルバマゼピンなど骨髄抑制のリスクがある薬剤使用中は定期採血の実施状況を確認する</v>
       </c>
       <c r="K52" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>てんかん,抗血小板療法</v>
       </c>
       <c r="L52" t="str">
-        <v>好塩基球実数値,好塩基球数</v>
+        <v>血小板,Plt,platelet,出血,あざ,紫斑,骨髄抑制</v>
       </c>
       <c r="M52" t="str">
         <v/>
@@ -2556,63 +2556,63 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>リンパ球実数値</v>
+        <v>RDW-SD</v>
       </c>
       <c r="B53" t="str">
-        <v>Lympho#,ALC</v>
+        <v>RDW-SD</v>
       </c>
       <c r="C53" t="str">
-        <v>1,000〜3,600 /μL程度（施設差あり）</v>
+        <v>39〜46 fL程度（施設差あり）</v>
       </c>
       <c r="D53" t="str">
-        <v>リンパ球の絶対数。免疫力の目安として使われる</v>
+        <v>赤血球の大きさのばらつきを表す指標(絶対値)。鉄欠乏性貧血などの初期変化を捉えやすい</v>
       </c>
       <c r="E53" t="str">
-        <v>これはリンパ球の実際の数を表す数値です。免疫力の目安の一つとして使われ、抗がん剤や免疫抑制剤の副作用モニタリングにも用いられます。</v>
+        <v>RDW-SDは、赤血球の大きさがどれくらいバラバラになっているかを表す数値です。貧血の原因を調べる際、鉄が足りなくなり始めた早い段階での変化を捉えるのに役立ちます。</v>
       </c>
       <c r="F53" t="str">
-        <v>ウイルス感染症、リンパ性白血病などの血液疾患</v>
+        <v>鉄欠乏性貧血の初期、混合性貧血（複数の原因が重なっている状態）、赤血球産生の乱れ</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>抗がん剤・免疫抑制剤・ステロイドの使用、強いストレス、AIDSなどの免疫不全</v>
+        <v/>
       </c>
       <c r="I53" t="str">
-        <v>感染予防（手洗い・うがい、人混みを避ける）を意識するよう伝える</v>
+        <v/>
       </c>
       <c r="J53" t="str">
-        <v>免疫抑制剤・抗がん剤治療中のモニタリング指標としても使われる。著明な低下時は日和見感染のリスクが高まる</v>
+        <v>MCVが正常範囲でもRDWが上昇している場合、鉄欠乏の初期段階を示唆することがある。MCV・MCHと合わせて評価する</v>
       </c>
       <c r="K53" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="L53" t="str">
-        <v>リンパ球実数値,リンパ球数,ALC,免疫抑制剤,日和見感染</v>
+        <v>RDW-SD,赤血球分布幅,貧血,鉄欠乏</v>
       </c>
       <c r="M53" t="str">
-        <v/>
+        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>単球実数値</v>
+        <v>RDW-CV</v>
       </c>
       <c r="B54" t="str">
-        <v>Mono#</v>
+        <v>RDW-CV</v>
       </c>
       <c r="C54" t="str">
-        <v>200〜600 /μL程度（施設差あり）</v>
+        <v>11.5〜14.5%程度（施設差あり）</v>
       </c>
       <c r="D54" t="str">
-        <v>単球の絶対数</v>
+        <v>赤血球の大きさのばらつきを割合(%)で表した指標</v>
       </c>
       <c r="E54" t="str">
-        <v>これは単球の実際の数を表す数値です。慢性的な炎症や感染症の状態を把握する材料の一つになります。</v>
+        <v>RDW-CVもRDW-SDと同じく、赤血球の大きさのばらつきを表す数値ですが、こちらは割合(%)で示されます。貧血のタイプを見分ける手がかりになります。</v>
       </c>
       <c r="F54" t="str">
-        <v>慢性感染症、炎症性疾患、血液疾患</v>
+        <v>鉄欠乏性貧血、ビタミンB12・葉酸欠乏性貧血、混合性貧血</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2624,54 +2624,54 @@
         <v/>
       </c>
       <c r="J54" t="str">
-        <v>単独での臨床的意義は乏しく、他の血球指標と合わせて評価する</v>
+        <v>RDW-SDと同様の意味を持つ指標。MCVが小さくRDWが高ければ鉄欠乏性貧血、MCVが大きくRDWが高ければビタミンB12・葉酸欠乏を疑う手がかりになる</v>
       </c>
       <c r="K54" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="L54" t="str">
-        <v>単球実数値,単球数</v>
+        <v>RDW-CV,赤血球分布幅,貧血,ビタミンB12,葉酸</v>
       </c>
       <c r="M54" t="str">
-        <v/>
+        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>好中球</v>
+        <v>好中球実数値</v>
       </c>
       <c r="B55" t="str">
-        <v>Neutro,Neut%</v>
+        <v>Neutro#,ANC</v>
       </c>
       <c r="C55" t="str">
-        <v>40〜75%程度（施設差あり）</v>
+        <v>2,000〜7,500 /μL程度（施設差あり、白血球数×好中球%で算出）</v>
       </c>
       <c r="D55" t="str">
-        <v>白血球の中で最も多くを占め、細菌感染と戦う主力の免疫細胞の割合</v>
+        <v>好中球の絶対数。感染症リスクを判断する上で割合(%)より重要な指標</v>
       </c>
       <c r="E55" t="str">
-        <v>好中球は、白血球の中で最も数が多く、細菌が体に入ってきたときに真っ先に戦ってくれる免疫細胞です。感染症や炎症があると増え、逆に薬の副作用などで減ることがあります。</v>
+        <v>これは好中球の実際の数を表す数値です。割合(%)だけでなく、実際の数がどれくらいあるかを見ることで、感染症にかかりやすい状態かどうかをより正確に判断できます。</v>
       </c>
       <c r="F55" t="str">
-        <v>細菌感染症、炎症、ストレス、ステロイド使用</v>
+        <v>細菌感染症、炎症、ステロイド使用</v>
       </c>
       <c r="G55" t="str">
-        <v>発熱や炎症症状がないか確認する</v>
+        <v/>
       </c>
       <c r="H55" t="str">
-        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、ウイルス感染、メルカゾールなど薬剤性の無顆粒球症</v>
+        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、メルカゾールなど薬剤性の無顆粒球症（1,000/μL未満で好中球減少症、500/μL未満で重症感染リスクが著しく上昇）</v>
       </c>
       <c r="I55" t="str">
-        <v>発熱やのどの痛みなど感染症状の初期サインがないか確認する</v>
+        <v>発熱、のどの痛みなど感染症状の初期サインがないか確認する。人混みを避け、手洗い・うがいを徹底するよう伝える</v>
       </c>
       <c r="J55" t="str">
-        <v>好中球の絶対数（好中球実数値）が500/μL未満になると重篤な感染症のリスクが高まる。割合(%)だけでなく実数値も合わせて確認する</v>
+        <v>抗がん剤・メルカゾール・カルバマゼピンなど骨髄抑制のリスクがある薬剤使用中は特に重視すべき数値。500/μL未満は発熱性好中球減少症のリスクが高く緊急性が高い</v>
       </c>
       <c r="K55" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L55" t="str">
-        <v>好中球,Neutro,Neut,感染症,無顆粒球症</v>
+        <v>好中球実数値,好中球数,ANC,無顆粒球症,発熱性好中球減少症</v>
       </c>
       <c r="M55" t="str">
         <v/>
@@ -2679,25 +2679,25 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>好酸球</v>
+        <v>好酸球実数値</v>
       </c>
       <c r="B56" t="str">
-        <v>Eosino,Eos%</v>
+        <v>Eosino#</v>
       </c>
       <c r="C56" t="str">
-        <v>1〜5%程度（施設差あり）</v>
+        <v>100〜500 /μL程度（施設差あり）</v>
       </c>
       <c r="D56" t="str">
-        <v>アレルギー反応や寄生虫感染に関わる白血球の一種の割合</v>
+        <v>好酸球の絶対数。アレルギーや薬剤反応の程度をより正確に評価できる</v>
       </c>
       <c r="E56" t="str">
-        <v>好酸球は、アレルギー反応や寄生虫感染と関係が深い免疫細胞です。アレルギー性の病気や薬の副作用（薬疹など）で増えることがあります。</v>
+        <v>これは好酸球の実際の数を表す数値です。割合(%)だけでなく実数を見ることで、アレルギー反応の強さをより正確に把握できます。</v>
       </c>
       <c r="F56" t="str">
-        <v>アレルギー性疾患（気管支喘息、アトピー性皮膚炎など）、薬剤アレルギー、寄生虫感染</v>
+        <v>アレルギー性疾患、薬剤アレルギー、寄生虫感染</v>
       </c>
       <c r="G56" t="str">
-        <v>新しく始めた薬がないか確認する。皮疹やかゆみなどアレルギー症状の有無を確認する</v>
+        <v>新しく始めた薬がないか確認する</v>
       </c>
       <c r="H56" t="str">
         <v/>
@@ -2706,13 +2706,13 @@
         <v/>
       </c>
       <c r="J56" t="str">
-        <v>薬剤性の好酸球増多は、原因薬剤の中止で改善することが多い。新規薬剤開始後の皮疹・発熱と合わせて薬剤性過敏症症候群(DIHS)を疑う材料になる</v>
+        <v>薬剤性過敏症症候群(DIHS)などでは著明な好酸球増多を認めることがあり、原因薬剤の特定に役立つ</v>
       </c>
       <c r="K56" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L56" t="str">
-        <v>好酸球,Eosino,Eos,アレルギー,薬疹,DIHS</v>
+        <v>好酸球実数値,好酸球数,アレルギー,DIHS</v>
       </c>
       <c r="M56" t="str">
         <v/>
@@ -2720,22 +2720,22 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>好塩基球</v>
+        <v>好塩基球実数値</v>
       </c>
       <c r="B57" t="str">
-        <v>Baso,Baso%</v>
+        <v>Baso#</v>
       </c>
       <c r="C57" t="str">
-        <v>0〜2%程度（施設差あり）</v>
+        <v>0〜100 /μL程度（施設差あり）</v>
       </c>
       <c r="D57" t="str">
-        <v>白血球の中で最も数が少なく、アレルギー反応に関わる細胞の割合</v>
+        <v>好塩基球の絶対数</v>
       </c>
       <c r="E57" t="str">
-        <v>好塩基球は白血球の中で最も数が少ない種類で、アレルギー反応や炎症に関わっています。数値の変動が病気の診断に直接使われることは少ない検査です。</v>
+        <v>これは好塩基球の実際の数を表す数値です。数がとても少ない種類の血球なので、通常は大きな変動を示すことは多くありません。</v>
       </c>
       <c r="F57" t="str">
-        <v>慢性骨髄性白血病などの血液疾患、アレルギー性疾患、甲状腺機能低下症</v>
+        <v>慢性骨髄性白血病などの血液疾患、アレルギー性疾患</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2747,13 +2747,13 @@
         <v/>
       </c>
       <c r="J57" t="str">
-        <v>単独での臨床的意義は乏しいが、著明な増加は血液疾患（慢性骨髄性白血病等）の可能性があり他の血球指標と合わせて評価する</v>
+        <v>単独での臨床的意義は乏しく、他の血球指標（白血球分画全体）と合わせて評価する</v>
       </c>
       <c r="K57" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L57" t="str">
-        <v>好塩基球,Baso,アレルギー,白血病</v>
+        <v>好塩基球実数値,好塩基球数</v>
       </c>
       <c r="M57" t="str">
         <v/>
@@ -2761,22 +2761,22 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>リンパ球</v>
+        <v>リンパ球実数値</v>
       </c>
       <c r="B58" t="str">
-        <v>Lympho,Lym%</v>
+        <v>Lympho#,ALC</v>
       </c>
       <c r="C58" t="str">
-        <v>18〜49%程度（施設差あり）</v>
+        <v>1,000〜3,600 /μL程度（施設差あり）</v>
       </c>
       <c r="D58" t="str">
-        <v>ウイルス感染と戦い、免疫の記憶を担う白血球の割合</v>
+        <v>リンパ球の絶対数。免疫力の目安として使われる</v>
       </c>
       <c r="E58" t="str">
-        <v>リンパ球は、ウイルスと戦ったり、一度かかった病気を記憶して免疫をつくったりする細胞です。ウイルス感染で増え、抗がん剤の副作用や強いストレスで減ることがあります。</v>
+        <v>これはリンパ球の実際の数を表す数値です。免疫力の目安の一つとして使われ、抗がん剤や免疫抑制剤の副作用モニタリングにも用いられます。</v>
       </c>
       <c r="F58" t="str">
-        <v>ウイルス感染症、リンパ性白血病などの血液疾患、百日咳</v>
+        <v>ウイルス感染症、リンパ性白血病などの血液疾患</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2785,16 +2785,16 @@
         <v>抗がん剤・免疫抑制剤・ステロイドの使用、強いストレス、AIDSなどの免疫不全</v>
       </c>
       <c r="I58" t="str">
-        <v>免疫が下がっている可能性があるため、感染予防（手洗い・うがい、人混みを避ける）を意識するよう伝える</v>
+        <v>感染予防（手洗い・うがい、人混みを避ける）を意識するよう伝える</v>
       </c>
       <c r="J58" t="str">
-        <v>ステロイド・免疫抑制剤使用中はリンパ球減少による易感染性に注意。好中球と逆方向に動くことが多い（ウイルス感染ではリンパ球優位、細菌感染では好中球優位になりやすい）</v>
+        <v>免疫抑制剤・抗がん剤治療中のモニタリング指標としても使われる。著明な低下時は日和見感染のリスクが高まる</v>
       </c>
       <c r="K58" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L58" t="str">
-        <v>リンパ球,Lympho,Lym,ウイルス感染,免疫抑制剤,ステロイド</v>
+        <v>リンパ球実数値,リンパ球数,ALC,免疫抑制剤,日和見感染</v>
       </c>
       <c r="M58" t="str">
         <v/>
@@ -2802,22 +2802,22 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>単球</v>
+        <v>単球実数値</v>
       </c>
       <c r="B59" t="str">
-        <v>Mono,Mono%</v>
+        <v>Mono#</v>
       </c>
       <c r="C59" t="str">
-        <v>2〜10%程度（施設差あり）</v>
+        <v>200〜600 /μL程度（施設差あり）</v>
       </c>
       <c r="D59" t="str">
-        <v>感染や炎症の後始末をする白血球の一種の割合</v>
+        <v>単球の絶対数</v>
       </c>
       <c r="E59" t="str">
-        <v>単球は、細菌などを取り込んで処理したり、組織の修復に関わったりする免疫細胞です。慢性的な炎症や感染症の回復期に増えることがあります。</v>
+        <v>これは単球の実際の数を表す数値です。慢性的な炎症や感染症の状態を把握する材料の一つになります。</v>
       </c>
       <c r="F59" t="str">
-        <v>慢性感染症（結核など）、炎症性疾患、血液疾患、感染症の回復期</v>
+        <v>慢性感染症、炎症性疾患、血液疾患</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2829,13 +2829,13 @@
         <v/>
       </c>
       <c r="J59" t="str">
-        <v>単独での臨床的意義は乏しく、他の血球指標や炎症マーカー(CRPなど)と合わせて評価する</v>
+        <v>単独での臨床的意義は乏しく、他の血球指標と合わせて評価する</v>
       </c>
       <c r="K59" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L59" t="str">
-        <v>単球,Mono,慢性感染症,結核,炎症</v>
+        <v>単球実数値,単球数</v>
       </c>
       <c r="M59" t="str">
         <v/>
@@ -2843,40 +2843,40 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>C反応性蛋白（CRP）</v>
+        <v>好中球</v>
       </c>
       <c r="B60" t="str">
-        <v>CRP</v>
+        <v>Neutro,Neut%</v>
       </c>
       <c r="C60" t="str">
-        <v>0.3 mg/dL未満（施設差あり）</v>
+        <v>40〜75%程度（施設差あり）</v>
       </c>
       <c r="D60" t="str">
-        <v>体のどこかに炎症や感染が起きていないかを鋭敏に反映する数値</v>
+        <v>白血球の中で最も多くを占め、細菌感染と戦う主力の免疫細胞の割合</v>
       </c>
       <c r="E60" t="str">
-        <v>CRPは、体に炎症や感染が起きると数時間〜半日程度で急激に上昇する数値です。風邪のようなウイルス感染から細菌感染、体のどこかの炎症まで、幅広く反応するため、体調の変化を早期に捉える手がかりになります。</v>
+        <v>好中球は、白血球の中で最も数が多く、細菌が体に入ってきたときに真っ先に戦ってくれる免疫細胞です。感染症や炎症があると増え、逆に薬の副作用などで減ることがあります。</v>
       </c>
       <c r="F60" t="str">
-        <v>細菌感染症、ウイルス感染症、自己免疫疾患（関節リウマチなど）、悪性腫瘍、組織の損傷（術後・心筋梗塞など）</v>
+        <v>細菌感染症、炎症、ストレス、ステロイド使用</v>
       </c>
       <c r="G60" t="str">
-        <v>発熱、痛み、腫れなど炎症症状の有無を確認する</v>
+        <v>発熱や炎症症状がないか確認する</v>
       </c>
       <c r="H60" t="str">
-        <v/>
+        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、ウイルス感染、メルカゾールなど薬剤性の無顆粒球症</v>
       </c>
       <c r="I60" t="str">
-        <v/>
+        <v>発熱やのどの痛みなど感染症状の初期サインがないか確認する</v>
       </c>
       <c r="J60" t="str">
-        <v>白血球数と合わせて感染・炎症の程度を評価する。上昇・低下のタイミングは白血球より半日〜1日程度遅れる傾向があるため、経過を追う際は採血のタイミングに注意</v>
+        <v>好中球の絶対数（好中球実数値）が500/μL未満になると重篤な感染症のリスクが高まる。割合(%)だけでなく実数値も合わせて確認する</v>
       </c>
       <c r="K60" t="str">
-        <v/>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L60" t="str">
-        <v>CRP,炎症,感染</v>
+        <v>好中球,Neutro,Neut,感染症,無顆粒球症</v>
       </c>
       <c r="M60" t="str">
         <v/>
@@ -2884,25 +2884,25 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>骨型酒石酸抵抗性フォスファターゼ（TRACP-5b）</v>
+        <v>好酸球</v>
       </c>
       <c r="B61" t="str">
-        <v>TRACP-5b</v>
+        <v>Eosino,Eos%</v>
       </c>
       <c r="C61" t="str">
-        <v>120〜420 mU/dL</v>
+        <v>1〜5%程度（施設差あり）</v>
       </c>
       <c r="D61" t="str">
-        <v>骨がどれくらい壊されているかを見る検査。骨は「古い骨を壊して新しい骨を作る」入れ替えを繰り返しており、骨を壊す細胞が活発だとこの物質が血液中に増える。</v>
+        <v>アレルギー反応や寄生虫感染に関わる白血球の一種の割合</v>
       </c>
       <c r="E61" t="str">
-        <v>この検査は、骨がどれくらい早く減っていないかを見るものです。数値が高いと、骨が弱くなりやすい状態の目安になります。</v>
+        <v>好酸球は、アレルギー反応や寄生虫感染と関係が深い免疫細胞です。アレルギー性の病気や薬の副作用（薬疹など）で増えることがあります。</v>
       </c>
       <c r="F61" t="str">
-        <v>骨粗鬆症、骨代謝回転（骨がこわれるスピード）が活発な状態</v>
+        <v>アレルギー性疾患（気管支喘息、アトピー性皮膚炎など）、薬剤アレルギー、寄生虫感染</v>
       </c>
       <c r="G61" t="str">
-        <v>カルシウム・ビタミンDの摂取や、適度な荷重運動（ウォーキングなど）を意識するよう伝える</v>
+        <v>新しく始めた薬がないか確認する。皮疹やかゆみなどアレルギー症状の有無を確認する</v>
       </c>
       <c r="H61" t="str">
         <v/>
@@ -2911,13 +2911,13 @@
         <v/>
       </c>
       <c r="J61" t="str">
-        <v>「骨を壊す側」の指標。「骨を作る側」の検査と合わせて評価する。数値だけで診断はしない</v>
+        <v>薬剤性の好酸球増多は、原因薬剤の中止で改善することが多い。新規薬剤開始後の皮疹・発熱と合わせて薬剤性過敏症症候群(DIHS)を疑う材料になる</v>
       </c>
       <c r="K61" t="str">
-        <v>骨粗鬆症</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L61" t="str">
-        <v>TRACP-5b,骨型酒石酸抵抗性フォスファターゼ,骨粗鬆症,骨代謝</v>
+        <v>好酸球,Eosino,Eos,アレルギー,薬疹,DIHS</v>
       </c>
       <c r="M61" t="str">
         <v/>
@@ -2925,40 +2925,40 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>骨型アルカリフォスファターゼ</v>
+        <v>好塩基球</v>
       </c>
       <c r="B62" t="str">
-        <v>BAP</v>
+        <v>Baso,Baso%</v>
       </c>
       <c r="C62" t="str">
-        <v>男性 3.7〜20.9 μg/L、女性（閉経前）2.9〜14.5 μg/L（施設差あり）</v>
+        <v>0〜2%程度（施設差あり）</v>
       </c>
       <c r="D62" t="str">
-        <v>ALPのうち骨に由来する成分だけを測定し、骨が作られる勢い（骨形成）を反映する</v>
+        <v>白血球の中で最も数が少なく、アレルギー反応に関わる細胞の割合</v>
       </c>
       <c r="E62" t="str">
-        <v>骨型ALPは、通常のALP（アルカリホスファターゼ）の中でも、骨で作られる成分だけを選んで測定するものです。骨を新しく作る働きがどれくらい活発かを見る指標として、骨粗鬆症の治療効果判定などに使われます。</v>
+        <v>好塩基球は白血球の中で最も数が少ない種類で、アレルギー反応や炎症に関わっています。数値の変動が病気の診断に直接使われることは少ない検査です。</v>
       </c>
       <c r="F62" t="str">
-        <v>骨代謝回転の亢進（骨粗鬆症、骨折治癒過程、骨形成促進薬による治療効果、Paget病、骨転移）</v>
+        <v>慢性骨髄性白血病などの血液疾患、アレルギー性疾患、甲状腺機能低下症</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>骨形成の低下</v>
+        <v/>
       </c>
       <c r="I62" t="str">
         <v/>
       </c>
       <c r="J62" t="str">
-        <v>通常のALPと異なり肝臓の影響を受けにくいため、肝機能異常がある患者でも骨代謝を評価しやすい。P1NPと同じ「骨を作る側」の指標で、骨形成促進薬（テリパラチド等）の効果判定に使われる</v>
+        <v>単独での臨床的意義は乏しいが、著明な増加は血液疾患（慢性骨髄性白血病等）の可能性があり他の血球指標と合わせて評価する</v>
       </c>
       <c r="K62" t="str">
-        <v>骨粗鬆症</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L62" t="str">
-        <v>骨型ALP,BAP,骨型アルカリフォスファターゼ,骨形成マーカー</v>
+        <v>好塩基球,Baso,アレルギー,白血病</v>
       </c>
       <c r="M62" t="str">
         <v/>
@@ -2966,81 +2966,81 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>25-ヒドロキシビタミンD</v>
+        <v>リンパ球</v>
       </c>
       <c r="B63" t="str">
-        <v>25(OH)D</v>
+        <v>Lympho,Lym%</v>
       </c>
       <c r="C63" t="str">
-        <v>30 ng/mL以上：充足、20〜30 ng/mL：不足、20 ng/mL未満：欠乏（施設差あり）</v>
+        <v>18〜49%程度（施設差あり）</v>
       </c>
       <c r="D63" t="str">
-        <v>体内のビタミンDの蓄え具合を反映する指標。カルシウムの吸収や骨の健康に関わる</v>
+        <v>ウイルス感染と戦い、免疫の記憶を担う白血球の割合</v>
       </c>
       <c r="E63" t="str">
-        <v>この検査は、体の中にビタミンDがどれくらい蓄えられているかを見るものです。ビタミンDは、食事から摂ったカルシウムを腸で吸収するのを助ける働きがあり、不足すると骨がもろくなりやすくなります。</v>
+        <v>リンパ球は、ウイルスと戦ったり、一度かかった病気を記憶して免疫をつくったりする細胞です。ウイルス感染で増え、抗がん剤の副作用や強いストレスで減ることがあります。</v>
       </c>
       <c r="F63" t="str">
-        <v>ビタミンD製剤の過剰摂取</v>
+        <v>ウイルス感染症、リンパ性白血病などの血液疾患、百日咳</v>
       </c>
       <c r="G63" t="str">
-        <v>活性型ビタミンD3製剤やサプリメントの摂取量を確認する。高カルシウム血症の症状（吐き気、便秘、多尿など）がないか確認する</v>
+        <v/>
       </c>
       <c r="H63" t="str">
-        <v>日光暴露不足、食事摂取不足、高齢、腸疾患による吸収不良、肝・腎機能低下（活性化障害）</v>
+        <v>抗がん剤・免疫抑制剤・ステロイドの使用、強いストレス、AIDSなどの免疫不全</v>
       </c>
       <c r="I63" t="str">
-        <v>適度な日光浴、魚類・きのこ類などビタミンDを多く含む食品の摂取を意識するとよいことを伝える</v>
+        <v>免疫が下がっている可能性があるため、感染予防（手洗い・うがい、人混みを避ける）を意識するよう伝える</v>
       </c>
       <c r="J63" t="str">
-        <v>骨粗鬆症治療における活性型ビタミンD3製剤の効果判定や、投与量調整の参考に用いられる。腎機能低下患者では活性化障害により25(OH)Dが正常でも活性型が不足することがある点に注意</v>
+        <v>ステロイド・免疫抑制剤使用中はリンパ球減少による易感染性に注意。好中球と逆方向に動くことが多い（ウイルス感染ではリンパ球優位、細菌感染では好中球優位になりやすい）</v>
       </c>
       <c r="K63" t="str">
-        <v>骨粗鬆症</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L63" t="str">
-        <v>25(OH)D,ビタミンD,25-ヒドロキシビタミンD,ビタミンD欠乏,骨粗鬆症</v>
+        <v>リンパ球,Lympho,Lym,ウイルス感染,免疫抑制剤,ステロイド</v>
       </c>
       <c r="M63" t="str">
-        <v>食事と栄養 p.38（ビタミンD）</v>
+        <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>尿pH</v>
+        <v>単球</v>
       </c>
       <c r="B64" t="str">
-        <v>尿pH</v>
+        <v>Mono,Mono%</v>
       </c>
       <c r="C64" t="str">
-        <v>4.5〜7.5程度（弱酸性が多い）</v>
+        <v>2〜10%程度（施設差あり）</v>
       </c>
       <c r="D64" t="str">
-        <v>尿の酸性・アルカリ性の度合い。食事や感染症、体の状態を反映する</v>
+        <v>感染や炎症の後始末をする白血球の一種の割合</v>
       </c>
       <c r="E64" t="str">
-        <v>尿のpHは酸性・アルカリ性のバランスを表します。食事の内容や感染症、体の代謝状態によって変化します。単独で大きな問題を示すことは少ない検査です。</v>
+        <v>単球は、細菌などを取り込んで処理したり、組織の修復に関わったりする免疫細胞です。慢性的な炎症や感染症の回復期に増えることがあります。</v>
       </c>
       <c r="F64" t="str">
-        <v>尿路感染症（尿素分解菌によるもの）、野菜中心の食事、過換気</v>
+        <v>慢性感染症（結核など）、炎症性疾患、血液疾患、感染症の回復期</v>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>高たんぱく食、糖尿病性ケトアシドーシス、痛風発作時（酸性尿は尿酸結石のリスクを高める）</v>
+        <v/>
       </c>
       <c r="I64" t="str">
-        <v>痛風・尿酸結石がある場合は、野菜など尿をアルカリ化する食品を意識するとよいことを伝える</v>
+        <v/>
       </c>
       <c r="J64" t="str">
-        <v>高尿酸血症・尿酸結石の患者では尿pHが酸性に傾いていないか確認する。尿アルカリ化薬（ウラリットなど）の効果判定にも使う</v>
+        <v>単独での臨床的意義は乏しく、他の血球指標や炎症マーカー(CRPなど)と合わせて評価する</v>
       </c>
       <c r="K64" t="str">
-        <v>高尿酸血症</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L64" t="str">
-        <v>尿pH,尿酸性度,尿アルカリ化,ウラリット</v>
+        <v>単球,Mono,慢性感染症,結核,炎症</v>
       </c>
       <c r="M64" t="str">
         <v/>
@@ -3048,81 +3048,81 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>尿ケトン体</v>
+        <v>PT-INR（プロトロンビン時間国際標準比）</v>
       </c>
       <c r="B65" t="str">
-        <v>尿ケトン,Ket</v>
+        <v>PT-INR,INR</v>
       </c>
       <c r="C65" t="str">
-        <v>陰性（－）</v>
+        <v>治療域の目安 1.6〜3.0（ワルファリン服用時。年齢・疾患により異なる）</v>
       </c>
       <c r="D65" t="str">
-        <v>体がブドウ糖の代わりに脂肪を分解してエネルギーを作っているサイン</v>
+        <v>血液の固まりやすさを表す数値で、ワルファリンの効き具合を確認するために使う</v>
       </c>
       <c r="E65" t="str">
-        <v>この検査は、体が糖の代わりに脂肪を使ってエネルギーを作っていないかを見るものです。陽性が続くときは、食事や水分、インスリンの使い方を確認する必要があります。</v>
+        <v>PT-INRは血液が固まるまでの時間をもとにした数値で、ワルファリンというお薬を飲んでいる方の効き具合を確認するために測ります。数値が高いほど血液が固まりにくく出血しやすい状態、低いほど血栓ができやすい状態を示します。</v>
       </c>
       <c r="F65" t="str">
-        <v>糖尿病の血糖コントロール不良（シックデイ・インスリン不足）、極端な糖質制限、絶食、嘔吐・下痢による脱水</v>
+        <v>ワルファリンの効きすぎ、肝機能低下、ビタミンK不足、納豆・青汁など摂取量の変化</v>
       </c>
       <c r="G65" t="str">
-        <v/>
+        <v>歯ぐきや鼻からの出血、あざ、黒い便などの出血症状がないか確認する。納豆・クロレラ・青汁などビタミンKを多く含む食品の摂取状況を確認する</v>
       </c>
       <c r="H65" t="str">
-        <v/>
+        <v>ワルファリンの効き不足、飲み忘れ、ビタミンK摂取量の急激な増加</v>
       </c>
       <c r="I65" t="str">
-        <v/>
+        <v>服薬状況（飲み忘れ）を確認する。片側のむくみ・しびれ・胸痛など血栓症状がないか確認する</v>
       </c>
       <c r="J65" t="str">
-        <v>陽性かつ高血糖・全身倦怠感が強い場合は糖尿病性ケトアシドーシスの可能性があり緊急性が高い。シックデイルールの説明歴を確認する</v>
+        <v>治療域は疾患・年齢によって異なる（例：非弁膜症性心房細動の高齢者では1.6〜2.6が目安になることが多い）。多くの薬剤・食品と相互作用があるため新規薬剤追加時は必ず確認する。DOAC（エリキュース、リクシアナ、プラザキサなど）ではPT-INRのモニタリングは不要</v>
       </c>
       <c r="K65" t="str">
-        <v>糖尿病</v>
+        <v>抗凝固療法（心房細動・血栓症）</v>
       </c>
       <c r="L65" t="str">
-        <v>尿ケトン体,ケトン体,Ket,シックデイ,ケトアシドーシス</v>
+        <v>PT-INR,INR,プロトロンビン時間,ワルファリン,ワーファリン,抗凝固</v>
       </c>
       <c r="M65" t="str">
-        <v/>
+        <v>食事と栄養 p.221（心疾患Q93 ワルファリン服用中のビタミンK摂取）</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>ウロビリノーゲン</v>
+        <v>C反応性蛋白（CRP）</v>
       </c>
       <c r="B66" t="str">
-        <v>Uro</v>
+        <v>CRP</v>
       </c>
       <c r="C66" t="str">
-        <v>正常（±）程度</v>
+        <v>0.3 mg/dL未満（施設差あり）</v>
       </c>
       <c r="D66" t="str">
-        <v>肝臓や胆道、赤血球の壊れ方の状態を反映する尿検査項目</v>
+        <v>体のどこかに炎症や感染が起きていないかを鋭敏に反映する数値</v>
       </c>
       <c r="E66" t="str">
-        <v>ウロビリノーゲンは、赤血球やビリルビンが体の中で処理される過程でできる物質です。肝臓の働きが悪くなったり、赤血球が壊れやすくなったりすると、尿の中の量が変化します。</v>
+        <v>CRPは、体に炎症や感染が起きると数時間〜半日程度で急激に上昇する数値です。風邪のようなウイルス感染から細菌感染、体のどこかの炎症まで、幅広く反応するため、体調の変化を早期に捉える手がかりになります。</v>
       </c>
       <c r="F66" t="str">
-        <v>溶血性疾患（赤血球の破壊亢進）、肝機能障害</v>
+        <v>細菌感染症、ウイルス感染症、自己免疫疾患（関節リウマチなど）、悪性腫瘍、組織の損傷（術後・心筋梗塞など）</v>
       </c>
       <c r="G66" t="str">
-        <v/>
+        <v>発熱、痛み、腫れなど炎症症状の有無を確認する</v>
       </c>
       <c r="H66" t="str">
-        <v>胆道閉塞（胆汁が腸に流れず、ウロビリノーゲンが作られない状態）</v>
+        <v/>
       </c>
       <c r="I66" t="str">
         <v/>
       </c>
       <c r="J66" t="str">
-        <v>完全に陰性の場合は胆道閉塞を疑う所見の一つ。肝機能（AST/ALT/ビリルビン）と合わせて評価する</v>
+        <v>白血球数と合わせて感染・炎症の程度を評価する。上昇・低下のタイミングは白血球より半日〜1日程度遅れる傾向があるため、経過を追う際は採血のタイミングに注意</v>
       </c>
       <c r="K66" t="str">
-        <v>肝機能</v>
+        <v/>
       </c>
       <c r="L66" t="str">
-        <v>ウロビリノーゲン,Uro,溶血,胆道閉塞,肝機能</v>
+        <v>CRP,炎症,感染</v>
       </c>
       <c r="M66" t="str">
         <v/>
@@ -3130,25 +3130,25 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>尿潜血反応</v>
+        <v>骨型酒石酸抵抗性フォスファターゼ（TRACP-5b）</v>
       </c>
       <c r="B67" t="str">
-        <v>尿潜血,U-OB</v>
+        <v>TRACP-5b</v>
       </c>
       <c r="C67" t="str">
-        <v>陰性（－）</v>
+        <v>120〜420 mU/dL</v>
       </c>
       <c r="D67" t="str">
-        <v>尿に血液（赤血球）が混じっていないかを見る検査</v>
+        <v>骨がどれくらい壊されているかを見る検査。骨は「古い骨を壊して新しい骨を作る」入れ替えを繰り返しており、骨を壊す細胞が活発だとこの物質が血液中に増える。</v>
       </c>
       <c r="E67" t="str">
-        <v>この検査は、尿に目に見えないくらいの微量の血液が混じっていないかを調べるものです。陽性の場合、腎臓や膀胱、尿路のどこかに炎症や結石などがある可能性があります。</v>
+        <v>この検査は、骨がどれくらい早く減っていないかを見るものです。数値が高いと、骨が弱くなりやすい状態の目安になります。</v>
       </c>
       <c r="F67" t="str">
-        <v>尿路結石、膀胱炎などの尿路感染症、腎炎、腫瘍、月経血の混入、激しい運動後</v>
+        <v>骨粗鬆症、骨代謝回転（骨がこわれるスピード）が活発な状態</v>
       </c>
       <c r="G67" t="str">
-        <v>排尿時の痛みや頻尿、目に見える血尿の有無を確認する。女性は月経の時期と重なっていないか確認する</v>
+        <v>カルシウム・ビタミンDの摂取や、適度な荷重運動（ウォーキングなど）を意識するよう伝える</v>
       </c>
       <c r="H67" t="str">
         <v/>
@@ -3157,13 +3157,13 @@
         <v/>
       </c>
       <c r="J67" t="str">
-        <v>陽性でも尿沈渣で赤血球が確認されない場合は偽陽性（ミオグロビン尿など）のこともある。持続する場合は泌尿器科的な精査が必要</v>
+        <v>「骨を壊す側」の指標。「骨を作る側」の検査と合わせて評価する。数値だけで診断はしない</v>
       </c>
       <c r="K67" t="str">
-        <v>腎機能</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="L67" t="str">
-        <v>尿潜血,潜血反応,U-OB,血尿,尿路結石,膀胱炎</v>
+        <v>TRACP-5b,骨型酒石酸抵抗性フォスファターゼ,骨粗鬆症,骨代謝</v>
       </c>
       <c r="M67" t="str">
         <v/>
@@ -3171,40 +3171,40 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>尿糖（半定量）</v>
+        <v>骨型アルカリフォスファターゼ</v>
       </c>
       <c r="B68" t="str">
-        <v>尿糖,U-Glu</v>
+        <v>BAP</v>
       </c>
       <c r="C68" t="str">
-        <v>陰性（－）</v>
+        <v>男性 3.7〜20.9 μg/L、女性（閉経前）2.9〜14.5 μg/L（施設差あり）</v>
       </c>
       <c r="D68" t="str">
-        <v>尿に糖が漏れ出ていないかを見る検査。血糖値がかなり高いと陽性になる</v>
+        <v>ALPのうち骨に由来する成分だけを測定し、骨が作られる勢い（骨形成）を反映する</v>
       </c>
       <c r="E68" t="str">
-        <v>通常、糖は尿にはほとんど出ませんが、血糖値がかなり高くなると尿にあふれ出るようになります。血糖コントロールの目安の一つです。</v>
+        <v>骨型ALPは、通常のALP（アルカリホスファターゼ）の中でも、骨で作られる成分だけを選んで測定するものです。骨を新しく作る働きがどれくらい活発かを見る指標として、骨粗鬆症の治療効果判定などに使われます。</v>
       </c>
       <c r="F68" t="str">
-        <v>糖尿病（血糖値が腎臓で再吸収できる量を超えている状態）、腎性糖尿（血糖値が正常でも体質的に出ることがある）、SGLT2阻害薬服用中（薬の作用で意図的に糖を排泄するため陽性になるのが正常）</v>
+        <v>骨代謝回転の亢進（骨粗鬆症、骨折治癒過程、骨形成促進薬による治療効果、Paget病、骨転移）</v>
       </c>
       <c r="G68" t="str">
-        <v>SGLT2阻害薬（フォシーガ、ジャディアンスなど）服用中は、陽性が薬の効果によるものであることを説明する。脱水や尿路感染の症状がないかも確認する</v>
+        <v/>
       </c>
       <c r="H68" t="str">
-        <v/>
+        <v>骨形成の低下</v>
       </c>
       <c r="I68" t="str">
         <v/>
       </c>
       <c r="J68" t="str">
-        <v>SGLT2阻害薬服用中は尿糖陽性が治療効果として想定内であることを患者に伝える。血糖値・HbA1cと合わせて評価する</v>
+        <v>通常のALPと異なり肝臓の影響を受けにくいため、肝機能異常がある患者でも骨代謝を評価しやすい。P1NPと同じ「骨を作る側」の指標で、骨形成促進薬（テリパラチド等）の効果判定に使われる</v>
       </c>
       <c r="K68" t="str">
-        <v>糖尿病</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="L68" t="str">
-        <v>尿糖,糖半定量,U-Glu,腎性糖尿,SGLT2</v>
+        <v>骨型ALP,BAP,骨型アルカリフォスファターゼ,骨形成マーカー</v>
       </c>
       <c r="M68" t="str">
         <v/>
@@ -3212,122 +3212,122 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>尿蛋白定量</v>
+        <v>25-ヒドロキシビタミンD</v>
       </c>
       <c r="B69" t="str">
-        <v>U-Pro定量,蛋白/Cr比</v>
+        <v>25(OH)D</v>
       </c>
       <c r="C69" t="str">
-        <v>0.15 g/gCr未満</v>
+        <v>30 ng/mL以上：充足、20〜30 ng/mL：不足、20 ng/mL未満：欠乏（施設差あり）</v>
       </c>
       <c r="D69" t="str">
-        <v>随時尿から尿蛋白の量を具体的な数値として評価する検査。ネフローゼ等の重症度判定に使う</v>
+        <v>体内のビタミンDの蓄え具合を反映する指標。カルシウムの吸収や骨の健康に関わる</v>
       </c>
       <c r="E69" t="str">
-        <v>これは、尿に出ているたんぱくの量を具体的な数値で見る検査です。試験紙での陽性・陰性の判定だけでなく、実際にどれくらいの量が出ているかを把握できます。</v>
+        <v>この検査は、体の中にビタミンDがどれくらい蓄えられているかを見るものです。ビタミンDは、食事から摂ったカルシウムを腸で吸収するのを助ける働きがあり、不足すると骨がもろくなりやすくなります。</v>
       </c>
       <c r="F69" t="str">
-        <v>腎症の進行（糖尿病性腎症、慢性腎臓病など）、ネフローゼ症候群（3.5 g/gCr以上が目安）</v>
+        <v>ビタミンD製剤の過剰摂取</v>
       </c>
       <c r="G69" t="str">
-        <v/>
+        <v>活性型ビタミンD3製剤やサプリメントの摂取量を確認する。高カルシウム血症の症状（吐き気、便秘、多尿など）がないか確認する</v>
       </c>
       <c r="H69" t="str">
-        <v/>
+        <v>日光暴露不足、食事摂取不足、高齢、腸疾患による吸収不良、肝・腎機能低下（活性化障害）</v>
       </c>
       <c r="I69" t="str">
-        <v/>
+        <v>適度な日光浴、魚類・きのこ類などビタミンDを多く含む食品の摂取を意識するとよいことを伝える</v>
       </c>
       <c r="J69" t="str">
-        <v>CKD診療ガイドラインの重症度分類（尿蛋白量による区分）にも使われる定量指標。試験紙法の半定量結果より治療効果判定に適する</v>
+        <v>骨粗鬆症治療における活性型ビタミンD3製剤の効果判定や、投与量調整の参考に用いられる。腎機能低下患者では活性化障害により25(OH)Dが正常でも活性型が不足することがある点に注意</v>
       </c>
       <c r="K69" t="str">
-        <v>腎機能,糖尿病</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="L69" t="str">
-        <v>尿蛋白,随時尿,定量,蛋白クレアチニン比,ネフローゼ</v>
+        <v>25(OH)D,ビタミンD,25-ヒドロキシビタミンD,ビタミンD欠乏,骨粗鬆症</v>
       </c>
       <c r="M69" t="str">
-        <v/>
+        <v>食事と栄養 p.38（ビタミンD）</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>BNP</v>
+        <v>尿pH</v>
       </c>
       <c r="B70" t="str">
-        <v>BNP</v>
+        <v>尿pH</v>
       </c>
       <c r="C70" t="str">
-        <v>18.4 pg/mL以下</v>
+        <v>4.5〜7.5程度（弱酸性が多い）</v>
       </c>
       <c r="D70" t="str">
-        <v>心臓が無理をしているときに出る物質。心臓は血液を送るポンプだが、負担がかかると「少し助けてほしい」というサインとしてBNPを血液中に出す。</v>
+        <v>尿の酸性・アルカリ性の度合い。食事や感染症、体の状態を反映する</v>
       </c>
       <c r="E70" t="str">
-        <v>この検査は、心臓がどれくらい頑張りすぎていないかを見るものです。数値が高いと、心臓に少し負担がかかっているサインになります。</v>
+        <v>尿のpHは酸性・アルカリ性のバランスを表します。食事の内容や感染症、体の代謝状態によって変化します。単独で大きな問題を示すことは少ない検査です。</v>
       </c>
       <c r="F70" t="str">
-        <v>心不全、心臓に負担がかかっている状態、体に水分がたまりやすいとき</v>
+        <v>尿路感染症（尿素分解菌によるもの）、野菜中心の食事、過換気</v>
       </c>
       <c r="G70" t="str">
-        <v>塩分・水分の摂りすぎに注意し、体重の変化を毎日記録するよう伝える</v>
+        <v/>
       </c>
       <c r="H70" t="str">
-        <v>心臓の負担は少ない状態</v>
+        <v>高たんぱく食、糖尿病性ケトアシドーシス、痛風発作時（酸性尿は尿酸結石のリスクを高める）</v>
       </c>
       <c r="I70" t="str">
-        <v/>
+        <v>痛風・尿酸結石がある場合は、野菜など尿をアルカリ化する食品を意識するとよいことを伝える</v>
       </c>
       <c r="J70" t="str">
-        <v>腎機能が低いとBNPは高めに出ることがある／数値だけで判断せず、症状と合わせて評価する／息切れ、むくみ、体重増加があれば要注意</v>
+        <v>高尿酸血症・尿酸結石の患者では尿pHが酸性に傾いていないか確認する。尿アルカリ化薬（ウラリットなど）の効果判定にも使う</v>
       </c>
       <c r="K70" t="str">
-        <v>心不全</v>
+        <v>高尿酸血症</v>
       </c>
       <c r="L70" t="str">
-        <v>BNP,心不全,息切れ,むくみ</v>
+        <v>尿pH,尿酸性度,尿アルカリ化,ウラリット</v>
       </c>
       <c r="M70" t="str">
-        <v>食事と栄養 p.216-222（第2部 心疾患）</v>
+        <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>血清CPR（Cペプチド）</v>
+        <v>尿ケトン体</v>
       </c>
       <c r="B71" t="str">
-        <v>CPR</v>
+        <v>尿ケトン,Ket</v>
       </c>
       <c r="C71" t="str">
-        <v>空腹時 0.6〜3.0 ng/mL（施設差あり）</v>
+        <v>陰性（－）</v>
       </c>
       <c r="D71" t="str">
-        <v>自分の膵臓がどれくらいインスリンを作れているかを表す指標</v>
+        <v>体がブドウ糖の代わりに脂肪を分解してエネルギーを作っているサイン</v>
       </c>
       <c r="E71" t="str">
-        <v>この検査は、ご自身の膵臓がどれくらいインスリンを作る力を持っているかを見るものです。数値が低いほど、体の中で作れるインスリンが少ないことを示します。</v>
+        <v>この検査は、体が糖の代わりに脂肪を使ってエネルギーを作っていないかを見るものです。陽性が続くときは、食事や水分、インスリンの使い方を確認する必要があります。</v>
       </c>
       <c r="F71" t="str">
-        <v>インスリン抵抗性が強い状態（初期の2型糖尿病など）</v>
+        <v>糖尿病の血糖コントロール不良（シックデイ・インスリン不足）、極端な糖質制限、絶食、嘔吐・下痢による脱水</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>膵臓のインスリン分泌能低下（1型糖尿病、糖尿病の進行）</v>
+        <v/>
       </c>
       <c r="I71" t="str">
         <v/>
       </c>
       <c r="J71" t="str">
-        <v>インスリン分泌能の評価に使われる。数値が低いほどインスリン治療の必要性が高いと判断される目安になる</v>
+        <v>陽性かつ高血糖・全身倦怠感が強い場合は糖尿病性ケトアシドーシスの可能性があり緊急性が高い。シックデイルールの説明歴を確認する</v>
       </c>
       <c r="K71" t="str">
         <v>糖尿病</v>
       </c>
       <c r="L71" t="str">
-        <v>CPR,Cペプチド,インスリン分泌,血清CPR</v>
+        <v>尿ケトン体,ケトン体,Ket,シックデイ,ケトアシドーシス</v>
       </c>
       <c r="M71" t="str">
         <v/>
@@ -3335,40 +3335,40 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>尿中微量アルブミン</v>
+        <v>ウロビリノーゲン</v>
       </c>
       <c r="B72" t="str">
-        <v>U-Alb,MAU</v>
+        <v>Uro</v>
       </c>
       <c r="C72" t="str">
-        <v>30 mg/gCr未満（尿中アルブミン/クレアチニン比）</v>
+        <v>正常（±）程度</v>
       </c>
       <c r="D72" t="str">
-        <v>通常の尿蛋白検査では見つからない、ごく早期の腎症のサイン</v>
+        <v>肝臓や胆道、赤血球の壊れ方の状態を反映する尿検査項目</v>
       </c>
       <c r="E72" t="str">
-        <v>この検査は、通常の尿検査ではまだ分からないくらい早い段階の腎臓の変化を見つけるためのものです。数値が高いと、腎症の初期のサインである可能性があります。</v>
+        <v>ウロビリノーゲンは、赤血球やビリルビンが体の中で処理される過程でできる物質です。肝臓の働きが悪くなったり、赤血球が壊れやすくなったりすると、尿の中の量が変化します。</v>
       </c>
       <c r="F72" t="str">
-        <v>糖尿病性腎症の早期段階、高血圧</v>
+        <v>溶血性疾患（赤血球の破壊亢進）、肝機能障害</v>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" t="str">
-        <v/>
+        <v>胆道閉塞（胆汁が腸に流れず、ウロビリノーゲンが作られない状態）</v>
       </c>
       <c r="I72" t="str">
         <v/>
       </c>
       <c r="J72" t="str">
-        <v>糖尿病腎症の早期発見に重要な検査。血糖・血圧コントロールで改善しうる段階なので、早期介入の意義を伝える</v>
+        <v>完全に陰性の場合は胆道閉塞を疑う所見の一つ。肝機能（AST/ALT/ビリルビン）と合わせて評価する</v>
       </c>
       <c r="K72" t="str">
-        <v>糖尿病,腎機能</v>
+        <v>肝機能</v>
       </c>
       <c r="L72" t="str">
-        <v>微量アルブミン,U-Alb,MAU,糖尿病性腎症,早期腎症</v>
+        <v>ウロビリノーゲン,Uro,溶血,胆道閉塞,肝機能</v>
       </c>
       <c r="M72" t="str">
         <v/>
@@ -3376,532 +3376,532 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>血清鉄（Fe）</v>
+        <v>尿潜血反応</v>
       </c>
       <c r="B73" t="str">
-        <v>Fe</v>
+        <v>尿潜血,U-OB</v>
       </c>
       <c r="C73" t="str">
-        <v>60〜200 μg/dL（施設差あり）</v>
+        <v>陰性（－）</v>
       </c>
       <c r="D73" t="str">
-        <v>血液中を流れている鉄の量</v>
+        <v>尿に血液（赤血球）が混じっていないかを見る検査</v>
       </c>
       <c r="E73" t="str">
-        <v>この検査は、今血液の中を流れている鉄の量を見るものです。低いと、体の中で鉄が不足している可能性があります。</v>
+        <v>この検査は、尿に目に見えないくらいの微量の血液が混じっていないかを調べるものです。陽性の場合、腎臓や膀胱、尿路のどこかに炎症や結石などがある可能性があります。</v>
       </c>
       <c r="F73" t="str">
-        <v>鉄剤の過剰摂取、溶血、肝疾患</v>
+        <v>尿路結石、膀胱炎などの尿路感染症、腎炎、腫瘍、月経血の混入、激しい運動後</v>
       </c>
       <c r="G73" t="str">
-        <v/>
+        <v>排尿時の痛みや頻尿、目に見える血尿の有無を確認する。女性は月経の時期と重なっていないか確認する</v>
       </c>
       <c r="H73" t="str">
-        <v>鉄欠乏性貧血、慢性炎症、出血</v>
+        <v/>
       </c>
       <c r="I73" t="str">
-        <v>鉄分の多い食品（レバー・赤身肉・魚・ほうれん草など）を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える</v>
+        <v/>
       </c>
       <c r="J73" t="str">
-        <v>血清鉄は日内変動が大きい。単独で判断せず総鉄結合能・フェリチンと合わせて評価する</v>
+        <v>陽性でも尿沈渣で赤血球が確認されない場合は偽陽性（ミオグロビン尿など）のこともある。持続する場合は泌尿器科的な精査が必要</v>
       </c>
       <c r="K73" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>腎機能</v>
       </c>
       <c r="L73" t="str">
-        <v>血清鉄,Fe,鉄欠乏性貧血</v>
+        <v>尿潜血,潜血反応,U-OB,血尿,尿路結石,膀胱炎</v>
       </c>
       <c r="M73" t="str">
-        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
+        <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>総鉄結合能（TIBC）</v>
+        <v>尿糖（半定量）</v>
       </c>
       <c r="B74" t="str">
-        <v>TIBC</v>
+        <v>尿糖,U-Glu</v>
       </c>
       <c r="C74" t="str">
-        <v>250〜360 μg/dL（施設差あり）</v>
+        <v>陰性（－）</v>
       </c>
       <c r="D74" t="str">
-        <v>血液中のトランスフェリンが鉄と結合できる総量</v>
+        <v>尿に糖が漏れ出ていないかを見る検査。血糖値がかなり高いと陽性になる</v>
       </c>
       <c r="E74" t="str">
-        <v>TIBCは、血液中でトランスフェリンという物質が鉄を運べる最大量を表します。体の中の鉄が不足すると、少しでも多く鉄を運ぼうとしてこの数値が上がる性質があります。</v>
+        <v>通常、糖は尿にはほとんど出ませんが、血糖値がかなり高くなると尿にあふれ出るようになります。血糖コントロールの目安の一つです。</v>
       </c>
       <c r="F74" t="str">
-        <v>鉄欠乏性貧血（＞360 μg/dLが目安）</v>
+        <v>糖尿病（血糖値が腎臓で再吸収できる量を超えている状態）、腎性糖尿（血糖値が正常でも体質的に出ることがある）、SGLT2阻害薬服用中（薬の作用で意図的に糖を排泄するため陽性になるのが正常）</v>
       </c>
       <c r="G74" t="str">
-        <v/>
+        <v>SGLT2阻害薬（フォシーガ、ジャディアンスなど）服用中は、陽性が薬の効果によるものであることを説明する。脱水や尿路感染の症状がないかも確認する</v>
       </c>
       <c r="H74" t="str">
-        <v>慢性炎症、肝疾患、ネフローゼ症候群</v>
+        <v/>
       </c>
       <c r="I74" t="str">
         <v/>
       </c>
       <c r="J74" t="str">
-        <v>鉄が不足すると、体はより多く運ぼうとしてTIBCが上昇する。UIBC・血清鉄と併せて評価する</v>
+        <v>SGLT2阻害薬服用中は尿糖陽性が治療効果として想定内であることを患者に伝える。血糖値・HbA1cと合わせて評価する</v>
       </c>
       <c r="K74" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>糖尿病</v>
       </c>
       <c r="L74" t="str">
-        <v>TIBC,総鉄結合能,鉄欠乏性貧血</v>
+        <v>尿糖,糖半定量,U-Glu,腎性糖尿,SGLT2</v>
       </c>
       <c r="M74" t="str">
-        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
+        <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>不飽和鉄結合能（UIBC）</v>
+        <v>尿蛋白定量</v>
       </c>
       <c r="B75" t="str">
-        <v>UIBC</v>
+        <v>U-Pro定量,蛋白/Cr比</v>
       </c>
       <c r="C75" t="str">
-        <v>170〜300 μg/dL（施設差あり）</v>
+        <v>0.15 g/gCr未満</v>
       </c>
       <c r="D75" t="str">
-        <v>トランスフェリンのうち、まだ鉄と結合していない余力の部分（UIBC＝TIBC－血清鉄）</v>
+        <v>随時尿から尿蛋白の量を具体的な数値として評価する検査。ネフローゼ等の重症度判定に使う</v>
       </c>
       <c r="E75" t="str">
-        <v>UIBCは、トランスフェリンのうち、まだ鉄と結合していない「空き容量」の部分を表します。鉄が不足しているときほど、この空き容量は大きくなります。</v>
+        <v>これは、尿に出ているたんぱくの量を具体的な数値で見る検査です。試験紙での陽性・陰性の判定だけでなく、実際にどれくらいの量が出ているかを把握できます。</v>
       </c>
       <c r="F75" t="str">
-        <v>鉄欠乏性貧血（＞300 μg/dLが目安）</v>
+        <v>腎症の進行（糖尿病性腎症、慢性腎臓病など）、ネフローゼ症候群（3.5 g/gCr以上が目安）</v>
       </c>
       <c r="G75" t="str">
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>慢性炎症、鉄過剰状態</v>
+        <v/>
       </c>
       <c r="I75" t="str">
         <v/>
       </c>
       <c r="J75" t="str">
-        <v>TIBCと同じ方向に動くことが多い。血清鉄・TIBCとあわせて鉄欠乏性貧血と二次性貧血の鑑別に使う</v>
+        <v>CKD診療ガイドラインの重症度分類（尿蛋白量による区分）にも使われる定量指標。試験紙法の半定量結果より治療効果判定に適する</v>
       </c>
       <c r="K75" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>腎機能,糖尿病</v>
       </c>
       <c r="L75" t="str">
-        <v>UIBC,不飽和鉄結合能,鉄欠乏性貧血</v>
+        <v>尿蛋白,随時尿,定量,蛋白クレアチニン比,ネフローゼ</v>
       </c>
       <c r="M75" t="str">
-        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
+        <v/>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>トランスフェリン飽和度</v>
+        <v>BNP</v>
       </c>
       <c r="B76" t="str">
-        <v>TSAT</v>
+        <v>BNP</v>
       </c>
       <c r="C76" t="str">
-        <v>16〜50%程度（施設差あり）</v>
+        <v>18.4 pg/mL以下</v>
       </c>
       <c r="D76" t="str">
-        <v>鉄を運ぶ役割のトランスフェリンのうち、実際に鉄を運んでいる割合（血清鉄÷総鉄結合能）</v>
+        <v>心臓が無理をしているときに出る物質。心臓は血液を送るポンプだが、負担がかかると「少し助けてほしい」というサインとしてBNPを血液中に出す。</v>
       </c>
       <c r="E76" t="str">
-        <v>トランスフェリン飽和度は、鉄を運ぶトランスフェリンのうち、実際にどれくらいが鉄を運んでいるかを割合で表したものです。鉄欠乏性貧血では低くなり、鉄が過剰にたまる病気では高くなります。</v>
+        <v>この検査は、心臓がどれくらい頑張りすぎていないかを見るものです。数値が高いと、心臓に少し負担がかかっているサインになります。</v>
       </c>
       <c r="F76" t="str">
-        <v>鉄過剰症（ヘモクロマトーシスなど）</v>
+        <v>心不全、心臓に負担がかかっている状態、体に水分がたまりやすいとき</v>
       </c>
       <c r="G76" t="str">
-        <v/>
+        <v>塩分・水分の摂りすぎに注意し、体重の変化を毎日記録するよう伝える</v>
       </c>
       <c r="H76" t="str">
-        <v>鉄欠乏性貧血（＜16%が目安）</v>
+        <v>心臓の負担は少ない状態</v>
       </c>
       <c r="I76" t="str">
         <v/>
       </c>
       <c r="J76" t="str">
-        <v>血清鉄をTIBCで割って計算される。鉄剤補充の効果判定にも使われる</v>
+        <v>腎機能が低いとBNPは高めに出ることがある／数値だけで判断せず、症状と合わせて評価する／息切れ、むくみ、体重増加があれば要注意</v>
       </c>
       <c r="K76" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>心不全</v>
       </c>
       <c r="L76" t="str">
-        <v>トランスフェリン飽和度,TSAT,鉄欠乏性貧血</v>
+        <v>BNP,心不全,息切れ,むくみ</v>
       </c>
       <c r="M76" t="str">
-        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
+        <v>食事と栄養 p.216-222（第2部 心疾患）</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>血清フェリチン</v>
+        <v>血清CPR（Cペプチド）</v>
       </c>
       <c r="B77" t="str">
-        <v>Ferritin</v>
+        <v>CPR</v>
       </c>
       <c r="C77" t="str">
-        <v>男性 20〜250 ng/mL、女性 10〜120 ng/mL（施設差あり）</v>
+        <v>空腹時 0.6〜3.0 ng/mL（施設差あり）</v>
       </c>
       <c r="D77" t="str">
-        <v>体に貯蔵されている鉄の量を反映する指標。貧血の症状が出るより早い段階で低下する</v>
+        <v>自分の膵臓がどれくらいインスリンを作れているかを表す指標</v>
       </c>
       <c r="E77" t="str">
-        <v>フェリチンは、体に蓄えられている鉄の「貯金」の量を見る検査です。この数値が下がるのは、貧血の症状が出るよりも前の、とても早い段階のサインになります。</v>
+        <v>この検査は、ご自身の膵臓がどれくらいインスリンを作る力を持っているかを見るものです。数値が低いほど、体の中で作れるインスリンが少ないことを示します。</v>
       </c>
       <c r="F77" t="str">
-        <v>炎症性疾患、肝疾患、悪性腫瘍、鉄過剰症（フェリチンは炎症でも上昇するため、貧血の評価では注意が必要）</v>
+        <v>インスリン抵抗性が強い状態（初期の2型糖尿病など）</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>鉄欠乏状態（貧血の症状が出る前の早期段階から低下する）</v>
+        <v>膵臓のインスリン分泌能低下（1型糖尿病、糖尿病の進行）</v>
       </c>
       <c r="I77" t="str">
-        <v>鉄分の多い食品を意識するとともに、貯蔵鉄を補うため治療は数値が正常化してからも継続が必要なことを伝える</v>
+        <v/>
       </c>
       <c r="J77" t="str">
-        <v>貯蔵鉄の指標で鉄欠乏を最も早期に反映する。ただし炎症があると鉄欠乏があっても正常〜高値に出ることがあり、CRP等の炎症所見と合わせて評価する。二次性貧血との鑑別に重要</v>
+        <v>インスリン分泌能の評価に使われる。数値が低いほどインスリン治療の必要性が高いと判断される目安になる</v>
       </c>
       <c r="K77" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>糖尿病</v>
       </c>
       <c r="L77" t="str">
-        <v>フェリチン,Ferritin,貯蔵鉄,鉄欠乏</v>
+        <v>CPR,Cペプチド,インスリン分泌,血清CPR</v>
       </c>
       <c r="M77" t="str">
-        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
+        <v/>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>尿中尿酸/クレアチニン比（UUA/UCr）</v>
+        <v>尿中微量アルブミン</v>
       </c>
       <c r="B78" t="str">
-        <v>UUA/UCr</v>
+        <v>U-Alb,MAU</v>
       </c>
       <c r="C78" t="str">
-        <v>0.4〜0.8程度が混合型の目安</v>
+        <v>30 mg/gCr未満（尿中アルブミン/クレアチニン比）</v>
       </c>
       <c r="D78" t="str">
-        <v>尿酸が「作られすぎ」か「排泄できていない」かを見分ける比の値</v>
+        <v>通常の尿蛋白検査では見つからない、ごく早期の腎症のサイン</v>
       </c>
       <c r="E78" t="str">
-        <v>この数値は、体の中で尿酸が「作られすぎている」のか、それとも「うまく排泄できていない」のかを見分けるために使う比の値です。高尿酸血症の治療薬を選ぶときの参考になります。</v>
+        <v>この検査は、通常の尿検査ではまだ分からないくらい早い段階の腎臓の変化を見つけるためのものです。数値が高いと、腎症の初期のサインである可能性があります。</v>
       </c>
       <c r="F78" t="str">
-        <v>尿酸産生過剰型（0.8以上が目安）</v>
+        <v>糖尿病性腎症の早期段階、高血圧</v>
       </c>
       <c r="G78" t="str">
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>尿酸排泄低下型（0.4以下が目安）</v>
+        <v/>
       </c>
       <c r="I78" t="str">
         <v/>
       </c>
       <c r="J78" t="str">
-        <v>高尿酸血症は尿酸産生過剰型・排泄低下型・混合型に分類され、この比が目安になる。病型によって使う薬剤（尿酸生成抑制薬か尿酸排泄促進薬か）の選択が変わる</v>
+        <v>糖尿病腎症の早期発見に重要な検査。血糖・血圧コントロールで改善しうる段階なので、早期介入の意義を伝える</v>
       </c>
       <c r="K78" t="str">
-        <v>高尿酸血症</v>
+        <v>糖尿病,腎機能</v>
       </c>
       <c r="L78" t="str">
-        <v>UUA,UCr,尿酸クリアランス,CUA,EUA,尿酸産生過剰型,尿酸排泄低下型</v>
+        <v>微量アルブミン,U-Alb,MAU,糖尿病性腎症,早期腎症</v>
       </c>
       <c r="M78" t="str">
-        <v>食事と栄養 p.180-189（第2部 痛風・高尿酸血症）</v>
+        <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>ucOC（低カルボキシル化オステオカルシン）</v>
+        <v>血清鉄（Fe）</v>
       </c>
       <c r="B79" t="str">
-        <v>ucOC</v>
+        <v>Fe</v>
       </c>
       <c r="C79" t="str">
-        <v>4.5 ng/mL未満（施設差あり）</v>
+        <v>60〜200 μg/dL（施設差あり）</v>
       </c>
       <c r="D79" t="str">
-        <v>ビタミンKが不足していないかを反映する骨の指標</v>
+        <v>血液中を流れている鉄の量</v>
       </c>
       <c r="E79" t="str">
-        <v>ucOCは、骨を作るために必要なビタミンKが体の中で足りているかどうかを反映する検査です。数値が高いとビタミンK不足が疑われます。</v>
+        <v>この検査は、今血液の中を流れている鉄の量を見るものです。低いと、体の中で鉄が不足している可能性があります。</v>
       </c>
       <c r="F79" t="str">
-        <v>ビタミンK不足状態</v>
+        <v>鉄剤の過剰摂取、溶血、肝疾患</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v/>
+        <v>鉄欠乏性貧血、慢性炎症、出血</v>
       </c>
       <c r="I79" t="str">
-        <v/>
+        <v>鉄分の多い食品（レバー・赤身肉・魚・ほうれん草など）を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える</v>
       </c>
       <c r="J79" t="str">
-        <v>ビタミンK2製剤（骨粗鬆症治療薬）の適応判断や効果判定に使われる</v>
+        <v>血清鉄は日内変動が大きい。単独で判断せず総鉄結合能・フェリチンと合わせて評価する</v>
       </c>
       <c r="K79" t="str">
-        <v>骨粗鬆症</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="L79" t="str">
-        <v>ucOC,オステオカルシン,ビタミンK</v>
+        <v>血清鉄,Fe,鉄欠乏性貧血</v>
       </c>
       <c r="M79" t="str">
-        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
+        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>PTH（副甲状腺ホルモン）</v>
+        <v>総鉄結合能（TIBC）</v>
       </c>
       <c r="B80" t="str">
-        <v>PTH</v>
+        <v>TIBC</v>
       </c>
       <c r="C80" t="str">
-        <v>10〜65 pg/mL（施設差あり）</v>
+        <v>250〜360 μg/dL（施設差あり）</v>
       </c>
       <c r="D80" t="str">
-        <v>血液中のカルシウム濃度を調節するホルモン</v>
+        <v>血液中のトランスフェリンが鉄と結合できる総量</v>
       </c>
       <c r="E80" t="str">
-        <v>PTHは、血液中のカルシウム濃度を一定に保つために働くホルモンです。カルシウムが低くなると分泌が増え、骨からカルシウムを取り出したり、腎臓での再吸収を促したりして数値を戻そうとします。</v>
+        <v>TIBCは、血液中でトランスフェリンという物質が鉄を運べる最大量を表します。体の中の鉄が不足すると、少しでも多く鉄を運ぼうとしてこの数値が上がる性質があります。</v>
       </c>
       <c r="F80" t="str">
-        <v>原発性・二次性副甲状腺機能亢進症（腎不全に伴うものなど）</v>
+        <v>鉄欠乏性貧血（＞360 μg/dLが目安）</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>副甲状腺機能低下症</v>
+        <v>慢性炎症、肝疾患、ネフローゼ症候群</v>
       </c>
       <c r="I80" t="str">
         <v/>
       </c>
       <c r="J80" t="str">
-        <v>骨粗鬆症の二次性原因（副甲状腺機能亢進症）を除外するための検査。カルシウム・リンと合わせて評価する</v>
+        <v>鉄が不足すると、体はより多く運ぼうとしてTIBCが上昇する。UIBC・血清鉄と併せて評価する</v>
       </c>
       <c r="K80" t="str">
-        <v>骨粗鬆症</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="L80" t="str">
-        <v>PTH,副甲状腺ホルモン,パラトルモン</v>
+        <v>TIBC,総鉄結合能,鉄欠乏性貧血</v>
       </c>
       <c r="M80" t="str">
-        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
+        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>尿中NTX</v>
+        <v>不飽和鉄結合能（UIBC）</v>
       </c>
       <c r="B81" t="str">
-        <v>NTX</v>
+        <v>UIBC</v>
       </c>
       <c r="C81" t="str">
-        <v>施設差が大きく一律の記載が難しい（尿中）</v>
+        <v>170〜300 μg/dL（施設差あり）</v>
       </c>
       <c r="D81" t="str">
-        <v>骨が壊されるときに出る、骨吸収マーカーのひとつ</v>
+        <v>トランスフェリンのうち、まだ鉄と結合していない余力の部分（UIBC＝TIBC－血清鉄）</v>
       </c>
       <c r="E81" t="str">
-        <v>NTXは、骨が壊される（吸収される）ときに尿の中に出てくる物質です。骨粗鬆症の治療薬がどれくらい効いているかを確認するために使われます。</v>
+        <v>UIBCは、トランスフェリンのうち、まだ鉄と結合していない「空き容量」の部分を表します。鉄が不足しているときほど、この空き容量は大きくなります。</v>
       </c>
       <c r="F81" t="str">
-        <v>骨代謝回転の亢進（骨粗鬆症、閉経後など）</v>
+        <v>鉄欠乏性貧血（＞300 μg/dLが目安）</v>
       </c>
       <c r="G81" t="str">
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>骨吸収抑制薬（ビスホスホネート等）による治療効果</v>
+        <v>慢性炎症、鉄過剰状態</v>
       </c>
       <c r="I81" t="str">
         <v/>
       </c>
       <c r="J81" t="str">
-        <v>治療開始後3〜6か月で再検し、薬の効果判定に使われる。TRACP-5bと同じ「骨を壊す側」の指標</v>
+        <v>TIBCと同じ方向に動くことが多い。血清鉄・TIBCとあわせて鉄欠乏性貧血と二次性貧血の鑑別に使う</v>
       </c>
       <c r="K81" t="str">
-        <v>骨粗鬆症</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="L81" t="str">
-        <v>NTX,尿中NTX,骨吸収マーカー</v>
+        <v>UIBC,不飽和鉄結合能,鉄欠乏性貧血</v>
       </c>
       <c r="M81" t="str">
-        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
+        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>カルシトニン</v>
+        <v>トランスフェリン飽和度</v>
       </c>
       <c r="B82" t="str">
-        <v>CT</v>
+        <v>TSAT</v>
       </c>
       <c r="C82" t="str">
-        <v>男性 9.52 pg/mL未満、女性 6.40 pg/mL未満（施設差あり）</v>
+        <v>16〜50%程度（施設差あり）</v>
       </c>
       <c r="D82" t="str">
-        <v>血液中のカルシウムを下げる方向に働くホルモン</v>
+        <v>鉄を運ぶ役割のトランスフェリンのうち、実際に鉄を運んでいる割合（血清鉄÷総鉄結合能）</v>
       </c>
       <c r="E82" t="str">
-        <v>カルシトニンは、PTHとは逆に血液中のカルシウムを下げる方向に働くホルモンです。特定の甲状腺の病気（甲状腺髄様癌）がないかを調べる際にも使われます。</v>
+        <v>トランスフェリン飽和度は、鉄を運ぶトランスフェリンのうち、実際にどれくらいが鉄を運んでいるかを割合で表したものです。鉄欠乏性貧血では低くなり、鉄が過剰にたまる病気では高くなります。</v>
       </c>
       <c r="F82" t="str">
-        <v>甲状腺髄様癌、腎不全</v>
+        <v>鉄過剰症（ヘモクロマトーシスなど）</v>
       </c>
       <c r="G82" t="str">
         <v/>
       </c>
       <c r="H82" t="str">
-        <v/>
+        <v>鉄欠乏性貧血（＜16%が目安）</v>
       </c>
       <c r="I82" t="str">
         <v/>
       </c>
       <c r="J82" t="str">
-        <v>骨粗鬆症の二次性原因の除外目的で測定されることがある検査値。同名の薬剤（カルシトニン製剤）と混同しないよう注意</v>
+        <v>血清鉄をTIBCで割って計算される。鉄剤補充の効果判定にも使われる</v>
       </c>
       <c r="K82" t="str">
-        <v>骨粗鬆症</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="L82" t="str">
-        <v>カルシトニン,CT</v>
+        <v>トランスフェリン飽和度,TSAT,鉄欠乏性貧血</v>
       </c>
       <c r="M82" t="str">
-        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
+        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>DPD（デオキシピリジノリン）</v>
+        <v>血清フェリチン</v>
       </c>
       <c r="B83" t="str">
-        <v>DPD</v>
+        <v>Ferritin</v>
       </c>
       <c r="C83" t="str">
-        <v>施設差が大きく一律の記載が難しい（尿中）</v>
+        <v>男性 20〜250 ng/mL、女性 10〜120 ng/mL（施設差あり）</v>
       </c>
       <c r="D83" t="str">
-        <v>骨のコラーゲンが壊れるときに出る、骨吸収マーカーのひとつ</v>
+        <v>体に貯蔵されている鉄の量を反映する指標。貧血の症状が出るより早い段階で低下する</v>
       </c>
       <c r="E83" t="str">
-        <v>DPDも、骨が壊されるときに尿に出てくる物質の一つです。NTXと同じように、骨粗鬆症治療薬の効果を確認するために使われます。</v>
+        <v>フェリチンは、体に蓄えられている鉄の「貯金」の量を見る検査です。この数値が下がるのは、貧血の症状が出るよりも前の、とても早い段階のサインになります。</v>
       </c>
       <c r="F83" t="str">
-        <v>骨代謝回転の亢進（骨粗鬆症など）</v>
+        <v>炎症性疾患、肝疾患、悪性腫瘍、鉄過剰症（フェリチンは炎症でも上昇するため、貧血の評価では注意が必要）</v>
       </c>
       <c r="G83" t="str">
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>骨吸収抑制薬による治療効果</v>
+        <v>鉄欠乏状態（貧血の症状が出る前の早期段階から低下する）</v>
       </c>
       <c r="I83" t="str">
-        <v/>
+        <v>鉄分の多い食品を意識するとともに、貯蔵鉄を補うため治療は数値が正常化してからも継続が必要なことを伝える</v>
       </c>
       <c r="J83" t="str">
-        <v>NTX・CTXと同じ「骨を壊す側」の指標。食事の影響を受けにくいとされる</v>
+        <v>貯蔵鉄の指標で鉄欠乏を最も早期に反映する。ただし炎症があると鉄欠乏があっても正常〜高値に出ることがあり、CRP等の炎症所見と合わせて評価する。二次性貧血との鑑別に重要</v>
       </c>
       <c r="K83" t="str">
-        <v>骨粗鬆症</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="L83" t="str">
-        <v>DPD,デオキシピリジノリン,骨吸収マーカー</v>
+        <v>フェリチン,Ferritin,貯蔵鉄,鉄欠乏</v>
       </c>
       <c r="M83" t="str">
-        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
+        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>CTX</v>
+        <v>尿中尿酸/クレアチニン比（UUA/UCr）</v>
       </c>
       <c r="B84" t="str">
-        <v>CTX</v>
+        <v>UUA/UCr</v>
       </c>
       <c r="C84" t="str">
-        <v>施設差が大きく一律の記載が難しい（血清・尿中）</v>
+        <v>0.4〜0.8程度が混合型の目安</v>
       </c>
       <c r="D84" t="str">
-        <v>骨のコラーゲンが壊れるときに出る、骨吸収マーカーのひとつ</v>
+        <v>尿酸が「作られすぎ」か「排泄できていない」かを見分ける比の値</v>
       </c>
       <c r="E84" t="str">
-        <v>CTXも、骨が壊されるときに血液や尿に出てくる物質です。骨粗鬆症治療薬（骨を壊すのを抑える薬）の効果を確認するために使われます。</v>
+        <v>この数値は、体の中で尿酸が「作られすぎている」のか、それとも「うまく排泄できていない」のかを見分けるために使う比の値です。高尿酸血症の治療薬を選ぶときの参考になります。</v>
       </c>
       <c r="F84" t="str">
-        <v>骨代謝回転の亢進（骨粗鬆症など）</v>
+        <v>尿酸産生過剰型（0.8以上が目安）</v>
       </c>
       <c r="G84" t="str">
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>骨吸収抑制薬による治療効果</v>
+        <v>尿酸排泄低下型（0.4以下が目安）</v>
       </c>
       <c r="I84" t="str">
         <v/>
       </c>
       <c r="J84" t="str">
-        <v>NTX・DPDと同じ「骨を壊す側」の指標。血清・尿中いずれでも測定されることがある</v>
+        <v>高尿酸血症は尿酸産生過剰型・排泄低下型・混合型に分類され、この比が目安になる。病型によって使う薬剤（尿酸生成抑制薬か尿酸排泄促進薬か）の選択が変わる</v>
       </c>
       <c r="K84" t="str">
-        <v>骨粗鬆症</v>
+        <v>高尿酸血症</v>
       </c>
       <c r="L84" t="str">
-        <v>CTX,骨吸収マーカー</v>
+        <v>UUA,UCr,尿酸クリアランス,CUA,EUA,尿酸産生過剰型,尿酸排泄低下型</v>
       </c>
       <c r="M84" t="str">
-        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
+        <v>食事と栄養 p.180-189（第2部 痛風・高尿酸血症）</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>P1NP</v>
+        <v>ucOC（低カルボキシル化オステオカルシン）</v>
       </c>
       <c r="B85" t="str">
-        <v>P1NP</v>
+        <v>ucOC</v>
       </c>
       <c r="C85" t="str">
-        <v>施設差が大きく一律の記載が難しい（血清）</v>
+        <v>4.5 ng/mL未満（施設差あり）</v>
       </c>
       <c r="D85" t="str">
-        <v>骨が新しく作られるときに出る、骨形成マーカーのひとつ</v>
+        <v>ビタミンKが不足していないかを反映する骨の指標</v>
       </c>
       <c r="E85" t="str">
-        <v>P1NPは、CTXなどとは逆に、骨が新しく作られるときに血液中に出てくる物質です。骨を作る力を高める薬（テリパラチドなど）の効果を確認するために使われます。</v>
+        <v>ucOCは、骨を作るために必要なビタミンKが体の中で足りているかどうかを反映する検査です。数値が高いとビタミンK不足が疑われます。</v>
       </c>
       <c r="F85" t="str">
-        <v>骨代謝回転の亢進、骨形成促進薬による治療効果</v>
+        <v>ビタミンK不足状態</v>
       </c>
       <c r="G85" t="str">
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>骨形成の低下</v>
+        <v/>
       </c>
       <c r="I85" t="str">
         <v/>
       </c>
       <c r="J85" t="str">
-        <v>TRACP-5b等「骨を壊す側」の指標とは逆の、「骨を作る側」の指標。骨形成促進薬（テリパラチド等）の効果判定に使われる</v>
+        <v>ビタミンK2製剤（骨粗鬆症治療薬）の適応判断や効果判定に使われる</v>
       </c>
       <c r="K85" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="L85" t="str">
-        <v>P1NP,骨形成マーカー</v>
+        <v>ucOC,オステオカルシン,ビタミンK</v>
       </c>
       <c r="M85" t="str">
         <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
@@ -3909,271 +3909,271 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>抗甲状腺マイクロゾーム抗体（抗TPO抗体）</v>
+        <v>PTH（副甲状腺ホルモン）</v>
       </c>
       <c r="B86" t="str">
-        <v>TPOAb</v>
+        <v>PTH</v>
       </c>
       <c r="C86" t="str">
-        <v>陰性（16 IU/mL未満程度、施設差あり）</v>
+        <v>10〜65 pg/mL（施設差あり）</v>
       </c>
       <c r="D86" t="str">
-        <v>自分の甲状腺を攻撃する抗体が出ていないかを見る検査</v>
+        <v>血液中のカルシウム濃度を調節するホルモン</v>
       </c>
       <c r="E86" t="str">
-        <v>この検査は、体の中に自分の甲状腺を誤って攻撃してしまう抗体がないかを見るものです。陽性の場合、橋本病（慢性甲状腺炎）など甲状腺の自己免疫的な炎症が背景にある可能性があります。</v>
+        <v>PTHは、血液中のカルシウム濃度を一定に保つために働くホルモンです。カルシウムが低くなると分泌が増え、骨からカルシウムを取り出したり、腎臓での再吸収を促したりして数値を戻そうとします。</v>
       </c>
       <c r="F86" t="str">
-        <v>橋本病（慢性甲状腺炎）、バセドウ病などの自己免疫性甲状腺疾患</v>
+        <v>原発性・二次性副甲状腺機能亢進症（腎不全に伴うものなど）</v>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v/>
+        <v>副甲状腺機能低下症</v>
       </c>
       <c r="I86" t="str">
         <v/>
       </c>
       <c r="J86" t="str">
-        <v>陽性でも必ずしも甲状腺機能異常があるとは限らない。TSH・FT4など甲状腺ホルモンの数値と合わせて評価する</v>
+        <v>骨粗鬆症の二次性原因（副甲状腺機能亢進症）を除外するための検査。カルシウム・リンと合わせて評価する</v>
       </c>
       <c r="K86" t="str">
-        <v>甲状腺疾患</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="L86" t="str">
-        <v>抗TPO抗体,抗甲状腺マイクロゾーム抗体,TPOAb,橋本病</v>
+        <v>PTH,副甲状腺ホルモン,パラトルモン</v>
       </c>
       <c r="M86" t="str">
-        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>抗サイログロブリン抗体</v>
+        <v>尿中NTX</v>
       </c>
       <c r="B87" t="str">
-        <v>TgAb</v>
+        <v>NTX</v>
       </c>
       <c r="C87" t="str">
-        <v>陰性（28 IU/mL未満程度、施設差あり）</v>
+        <v>施設差が大きく一律の記載が難しい（尿中）</v>
       </c>
       <c r="D87" t="str">
-        <v>甲状腺のたんぱく質（サイログロブリン）への抗体が出ていないかを見る検査</v>
+        <v>骨が壊されるときに出る、骨吸収マーカーのひとつ</v>
       </c>
       <c r="E87" t="str">
-        <v>この検査も、抗TPO抗体と同じく、甲状腺に対する自己免疫の有無を見るものです。あわせて調べることで橋本病などの診断の参考にします。</v>
+        <v>NTXは、骨が壊される（吸収される）ときに尿の中に出てくる物質です。骨粗鬆症の治療薬がどれくらい効いているかを確認するために使われます。</v>
       </c>
       <c r="F87" t="str">
-        <v>橋本病（慢性甲状腺炎）、バセドウ病などの自己免疫性甲状腺疾患</v>
+        <v>骨代謝回転の亢進（骨粗鬆症、閉経後など）</v>
       </c>
       <c r="G87" t="str">
         <v/>
       </c>
       <c r="H87" t="str">
-        <v/>
+        <v>骨吸収抑制薬（ビスホスホネート等）による治療効果</v>
       </c>
       <c r="I87" t="str">
         <v/>
       </c>
       <c r="J87" t="str">
-        <v>抗TPO抗体とあわせて測定されることが多い。単独の高値だけで治療方針が決まるわけではない</v>
+        <v>治療開始後3〜6か月で再検し、薬の効果判定に使われる。TRACP-5bと同じ「骨を壊す側」の指標</v>
       </c>
       <c r="K87" t="str">
-        <v>甲状腺疾患</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="L87" t="str">
-        <v>抗サイログロブリン抗体,TgAb,橋本病</v>
+        <v>NTX,尿中NTX,骨吸収マーカー</v>
       </c>
       <c r="M87" t="str">
-        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>PT-INR（プロトロンビン時間国際標準比）</v>
+        <v>カルシトニン</v>
       </c>
       <c r="B88" t="str">
-        <v>PT-INR,INR</v>
+        <v>CT</v>
       </c>
       <c r="C88" t="str">
-        <v>治療域の目安 1.6〜3.0（ワルファリン服用時。年齢・疾患により異なる）</v>
+        <v>男性 9.52 pg/mL未満、女性 6.40 pg/mL未満（施設差あり）</v>
       </c>
       <c r="D88" t="str">
-        <v>血液の固まりやすさを表す数値で、ワルファリンの効き具合を確認するために使う</v>
+        <v>血液中のカルシウムを下げる方向に働くホルモン</v>
       </c>
       <c r="E88" t="str">
-        <v>PT-INRは血液が固まるまでの時間をもとにした数値で、ワルファリンというお薬を飲んでいる方の効き具合を確認するために測ります。数値が高いほど血液が固まりにくく出血しやすい状態、低いほど血栓ができやすい状態を示します。</v>
+        <v>カルシトニンは、PTHとは逆に血液中のカルシウムを下げる方向に働くホルモンです。特定の甲状腺の病気（甲状腺髄様癌）がないかを調べる際にも使われます。</v>
       </c>
       <c r="F88" t="str">
-        <v>ワルファリンの効きすぎ、肝機能低下、ビタミンK不足、納豆・青汁など摂取量の変化</v>
+        <v>甲状腺髄様癌、腎不全</v>
       </c>
       <c r="G88" t="str">
-        <v>歯ぐきや鼻からの出血、あざ、黒い便などの出血症状がないか確認する。納豆・クロレラ・青汁などビタミンKを多く含む食品の摂取状況を確認する</v>
+        <v/>
       </c>
       <c r="H88" t="str">
-        <v>ワルファリンの効き不足、飲み忘れ、ビタミンK摂取量の急激な増加</v>
+        <v/>
       </c>
       <c r="I88" t="str">
-        <v>服薬状況（飲み忘れ）を確認する。片側のむくみ・しびれ・胸痛など血栓症状がないか確認する</v>
+        <v/>
       </c>
       <c r="J88" t="str">
-        <v>治療域は疾患・年齢によって異なる（例：非弁膜症性心房細動の高齢者では1.6〜2.6が目安になることが多い）。多くの薬剤・食品と相互作用があるため新規薬剤追加時は必ず確認する。DOAC（エリキュース、リクシアナ、プラザキサなど）ではPT-INRのモニタリングは不要</v>
+        <v>骨粗鬆症の二次性原因の除外目的で測定されることがある検査値。同名の薬剤（カルシトニン製剤）と混同しないよう注意</v>
       </c>
       <c r="K88" t="str">
-        <v>抗凝固療法（心房細動・血栓症）</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="L88" t="str">
-        <v>PT-INR,INR,プロトロンビン時間,ワルファリン,ワーファリン,抗凝固</v>
+        <v>カルシトニン,CT</v>
       </c>
       <c r="M88" t="str">
-        <v>食事と栄養 p.221（心疾患Q93 ワルファリン服用中のビタミンK摂取）</v>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>血中薬物濃度（TDM）</v>
+        <v>DPD（デオキシピリジノリン）</v>
       </c>
       <c r="B89" t="str">
-        <v>TDM</v>
+        <v>DPD</v>
       </c>
       <c r="C89" t="str">
-        <v>薬剤ごとに有効域が異なる（例：カルバマゼピン 4〜12 μg/mL、バルプロ酸 40〜100 μg/mL、フェニトイン 10〜20 μg/mL）</v>
+        <v>施設差が大きく一律の記載が難しい（尿中）</v>
       </c>
       <c r="D89" t="str">
-        <v>治療域が狭い薬剤で、血液中の薬の濃度が効果域・中毒域のどちらにあるかを確認する検査</v>
+        <v>骨のコラーゲンが壊れるときに出る、骨吸収マーカーのひとつ</v>
       </c>
       <c r="E89" t="str">
-        <v>この薬は効く量と副作用が出る量が近いため、血液中の薬の濃度を定期的に測って、ちょうどよい範囲に入っているかを確認します。数値が低いと効果が不十分になり、高いと副作用が出やすくなります。</v>
+        <v>DPDも、骨が壊されるときに尿に出てくる物質の一つです。NTXと同じように、骨粗鬆症治療薬の効果を確認するために使われます。</v>
       </c>
       <c r="F89" t="str">
-        <v>過量投与、代謝を妨げる薬剤との併用、肝機能低下による代謝低下</v>
+        <v>骨代謝回転の亢進（骨粗鬆症など）</v>
       </c>
       <c r="G89" t="str">
-        <v>ふらつき、眠気、めまい、物が二重に見えるなどの中毒症状がないか確認する</v>
+        <v/>
       </c>
       <c r="H89" t="str">
-        <v>飲み忘れ、自己判断による減量、代謝を促進する薬剤との併用（相互作用）</v>
+        <v>骨吸収抑制薬による治療効果</v>
       </c>
       <c r="I89" t="str">
-        <v>発作やてんかん症状の再発がないか確認し、飲み忘れがないか一緒に確認する</v>
+        <v/>
       </c>
       <c r="J89" t="str">
-        <v>採血のタイミング（トラフ値かどうか）で数値の解釈が変わるため採血時点を確認する。カルバマゼピンは自己誘導により長期使用で濃度が下がることがある点にも注意</v>
+        <v>NTX・CTXと同じ「骨を壊す側」の指標。食事の影響を受けにくいとされる</v>
       </c>
       <c r="K89" t="str">
-        <v>てんかん</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="L89" t="str">
-        <v>TDM,血中薬物濃度,治療域,中毒域,カルバマゼピン,フェニトイン,バルプロ酸,抗てんかん薬</v>
+        <v>DPD,デオキシピリジノリン,骨吸収マーカー</v>
       </c>
       <c r="M89" t="str">
-        <v/>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>アミラーゼ（AMY）</v>
+        <v>CTX</v>
       </c>
       <c r="B90" t="str">
-        <v>AMY</v>
+        <v>CTX</v>
       </c>
       <c r="C90" t="str">
-        <v>44〜132 U/L（施設差あり）</v>
+        <v>施設差が大きく一律の記載が難しい（血清・尿中）</v>
       </c>
       <c r="D90" t="str">
-        <v>膵臓や唾液腺から出る消化酵素。膵炎などで血液中に漏れ出す</v>
+        <v>骨のコラーゲンが壊れるときに出る、骨吸収マーカーのひとつ</v>
       </c>
       <c r="E90" t="str">
-        <v>アミラーゼは、でんぷんを分解する消化酵素で、主に膵臓と唾液腺から作られます。膵臓に炎症が起きると血液中に漏れ出して数値が上がるため、膵炎の診断や経過観察に使われます。</v>
+        <v>CTXも、骨が壊されるときに血液や尿に出てくる物質です。骨粗鬆症治療薬（骨を壊すのを抑える薬）の効果を確認するために使われます。</v>
       </c>
       <c r="F90" t="str">
-        <v>急性膵炎、慢性膵炎の急性増悪、耳下腺炎（おたふくかぜ）、腎不全</v>
+        <v>骨代謝回転の亢進（骨粗鬆症など）</v>
       </c>
       <c r="G90" t="str">
-        <v>飲酒を控える、脂っこい食事を避けるよう伝える</v>
+        <v/>
       </c>
       <c r="H90" t="str">
-        <v>慢性膵炎の進行期（膵臓の機能低下）</v>
+        <v>骨吸収抑制薬による治療効果</v>
       </c>
       <c r="I90" t="str">
         <v/>
       </c>
       <c r="J90" t="str">
-        <v>膵臓由来か唾液腺由来かを区別するには膵型アミラーゼ(P-AMY)を確認する。急性膵炎では強い腹痛・背部痛を伴うことが多く、飲酒歴の確認も重要</v>
+        <v>NTX・DPDと同じ「骨を壊す側」の指標。血清・尿中いずれでも測定されることがある</v>
       </c>
       <c r="K90" t="str">
-        <v/>
+        <v>骨粗鬆症</v>
       </c>
       <c r="L90" t="str">
-        <v>アミラーゼ,AMY,膵炎,急性膵炎</v>
+        <v>CTX,骨吸収マーカー</v>
       </c>
       <c r="M90" t="str">
-        <v/>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>CONUT値</v>
+        <v>P1NP</v>
       </c>
       <c r="B91" t="str">
-        <v>CONUT</v>
+        <v>P1NP</v>
       </c>
       <c r="C91" t="str">
-        <v>0〜1点：正常、2〜4点：軽度低栄養、5〜8点：中等度低栄養、9〜12点：高度低栄養</v>
+        <v>施設差が大きく一律の記載が難しい（血清）</v>
       </c>
       <c r="D91" t="str">
-        <v>アルブミン・総リンパ球数・総コレステロールの3項目から算出する栄養状態の評価スコア</v>
+        <v>骨が新しく作られるときに出る、骨形成マーカーのひとつ</v>
       </c>
       <c r="E91" t="str">
-        <v>CONUT値は、血液検査（アルブミン、リンパ球数、コレステロール）の結果から計算される、栄養状態を数値化したスコアです。点数が高いほど低栄養の状態が疑われます。</v>
+        <v>P1NPは、CTXなどとは逆に、骨が新しく作られるときに血液中に出てくる物質です。骨を作る力を高める薬（テリパラチドなど）の効果を確認するために使われます。</v>
       </c>
       <c r="F91" t="str">
-        <v>低栄養状態（点数が高いほど重度）</v>
+        <v>骨代謝回転の亢進、骨形成促進薬による治療効果</v>
       </c>
       <c r="G91" t="str">
-        <v>食事摂取量や体重の変化を確認する。必要に応じて栄養補助食品の活用を提案する</v>
+        <v/>
       </c>
       <c r="H91" t="str">
-        <v/>
+        <v>骨形成の低下</v>
       </c>
       <c r="I91" t="str">
         <v/>
       </c>
       <c r="J91" t="str">
-        <v>アルブミン・総リンパ球数・総コレステロールの3項目それぞれに配点があり、合計点で評価する客観的栄養指標。フレイル・サルコペニアの評価やポリファーマシー対策の一環としての栄養状態把握に有用</v>
+        <v>TRACP-5b等「骨を壊す側」の指標とは逆の、「骨を作る側」の指標。骨形成促進薬（テリパラチド等）の効果判定に使われる</v>
       </c>
       <c r="K91" t="str">
-        <v/>
+        <v>骨粗鬆症</v>
       </c>
       <c r="L91" t="str">
-        <v>CONUT,CONUT値,栄養評価,低栄養,フレイル</v>
+        <v>P1NP,骨形成マーカー</v>
       </c>
       <c r="M91" t="str">
-        <v>食事と栄養 p.240（フレイルQ108 低栄養や食事量の評価）</v>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>間接ビリルビン</v>
+        <v>抗甲状腺マイクロゾーム抗体（抗TPO抗体）</v>
       </c>
       <c r="B92" t="str">
-        <v>I-Bil</v>
+        <v>TPOAb</v>
       </c>
       <c r="C92" t="str">
-        <v>0.2〜0.8 mg/dL程度（施設差あり）</v>
+        <v>陰性（16 IU/mL未満程度、施設差あり）</v>
       </c>
       <c r="D92" t="str">
-        <v>赤血球が壊れてできるビリルビンのうち、肝臓で処理される前の形</v>
+        <v>自分の甲状腺を攻撃する抗体が出ていないかを見る検査</v>
       </c>
       <c r="E92" t="str">
-        <v>間接ビリルビンは、赤血球が壊れてできたビリルビンが、まだ肝臓で処理される前の状態です。この値が高い場合、赤血球が通常より多く壊れている(溶血)か、肝臓での処理能力に生まれつきの体質差(体質性黄疸)がある可能性が考えられます。</v>
+        <v>この検査は、体の中に自分の甲状腺を誤って攻撃してしまう抗体がないかを見るものです。陽性の場合、橋本病（慢性甲状腺炎）など甲状腺の自己免疫的な炎症が背景にある可能性があります。</v>
       </c>
       <c r="F92" t="str">
-        <v>溶血性疾患（自己免疫性溶血性貧血、血液型不適合輸血など）、体質性黄疸（ジルベール症候群）、新生児黄疸</v>
+        <v>橋本病（慢性甲状腺炎）、バセドウ病などの自己免疫性甲状腺疾患</v>
       </c>
       <c r="G92" t="str">
-        <v>皮膚や白目の黄染、尿の色の変化がないか確認する</v>
+        <v/>
       </c>
       <c r="H92" t="str">
         <v/>
@@ -4182,39 +4182,39 @@
         <v/>
       </c>
       <c r="J92" t="str">
-        <v>直接ビリルビンとの比率で原因を推測する（間接優位は溶血・体質性、直接優位は胆道系）。総ビリルビン・AST/ALTと合わせて評価する</v>
+        <v>陽性でも必ずしも甲状腺機能異常があるとは限らない。TSH・FT4など甲状腺ホルモンの数値と合わせて評価する</v>
       </c>
       <c r="K92" t="str">
-        <v>肝機能</v>
+        <v>甲状腺疾患</v>
       </c>
       <c r="L92" t="str">
-        <v>間接ビリルビン,I-Bil,溶血</v>
+        <v>抗TPO抗体,抗甲状腺マイクロゾーム抗体,TPOAb,橋本病</v>
       </c>
       <c r="M92" t="str">
-        <v/>
+        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>直接ビリルビン</v>
+        <v>抗サイログロブリン抗体</v>
       </c>
       <c r="B93" t="str">
-        <v>D-Bil</v>
+        <v>TgAb</v>
       </c>
       <c r="C93" t="str">
-        <v>0.0〜0.3 mg/dL程度（施設差あり）</v>
+        <v>陰性（28 IU/mL未満程度、施設差あり）</v>
       </c>
       <c r="D93" t="str">
-        <v>肝臓で処理された後のビリルビン。胆道の詰まりで血液中に増える</v>
+        <v>甲状腺のたんぱく質（サイログロブリン）への抗体が出ていないかを見る検査</v>
       </c>
       <c r="E93" t="str">
-        <v>直接ビリルビンは、肝臓で処理された後のビリルビンです。胆石や腫瘍などで胆汁の通り道（胆道）が詰まると、行き場を失って血液中に増え、皮膚や白目が黄色くなる黄疸として現れます。</v>
+        <v>この検査も、抗TPO抗体と同じく、甲状腺に対する自己免疫の有無を見るものです。あわせて調べることで橋本病などの診断の参考にします。</v>
       </c>
       <c r="F93" t="str">
-        <v>肝疾患、胆石など胆道の閉塞</v>
+        <v>橋本病（慢性甲状腺炎）、バセドウ病などの自己免疫性甲状腺疾患</v>
       </c>
       <c r="G93" t="str">
-        <v>皮膚や白目の黄染、白っぽい便、濃い茶色の尿がないか確認する</v>
+        <v/>
       </c>
       <c r="H93" t="str">
         <v/>
@@ -4223,54 +4223,54 @@
         <v/>
       </c>
       <c r="J93" t="str">
-        <v>直接優位の上昇は胆道系（胆石、腫瘍による閉塞）を、間接優位の上昇は溶血・体質性を疑う手がかりになる。γ-GTP・ALPと合わせて胆道系疾患を評価する</v>
+        <v>抗TPO抗体とあわせて測定されることが多い。単独の高値だけで治療方針が決まるわけではない</v>
       </c>
       <c r="K93" t="str">
-        <v>肝機能</v>
+        <v>甲状腺疾患</v>
       </c>
       <c r="L93" t="str">
-        <v>直接ビリルビン,D-Bil,胆石,胆道閉塞</v>
+        <v>抗サイログロブリン抗体,TgAb,橋本病</v>
       </c>
       <c r="M93" t="str">
-        <v/>
+        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>LDH/AST比</v>
+        <v>血中薬物濃度（TDM）</v>
       </c>
       <c r="B94" t="str">
-        <v>LDH/AST</v>
+        <v>TDM</v>
       </c>
       <c r="C94" t="str">
-        <v>目安として使われる比率（施設差・カットオフ値の設定により異なる）</v>
+        <v>薬剤ごとに有効域が異なる（例：カルバマゼピン 4〜12 μg/mL、バルプロ酸 40〜100 μg/mL、フェニトイン 10〜20 μg/mL）</v>
       </c>
       <c r="D94" t="str">
-        <v>LDHとASTの両方が上昇したときに、原因が肝臓か、それ以外（溶血・心筋・骨格筋）かを見分ける目安になる比</v>
+        <v>治療域が狭い薬剤で、血液中の薬の濃度が効果域・中毒域のどちらにあるかを確認する検査</v>
       </c>
       <c r="E94" t="str">
-        <v>これは、肝臓の数値（AST）と、全身に広く分布する酵素（LDH）の比率を見るもので、両方の数値が上がっているときに、原因が肝臓なのか、それとも血液や筋肉など他の場所なのかを見分ける手がかりになります。</v>
+        <v>この薬は効く量と副作用が出る量が近いため、血液中の薬の濃度を定期的に測って、ちょうどよい範囲に入っているかを確認します。数値が低いと効果が不十分になり、高いと副作用が出やすくなります。</v>
       </c>
       <c r="F94" t="str">
-        <v>溶血性疾患、心筋梗塞、骨格筋の障害（比が高いほど肝臓以外が原因の可能性）</v>
+        <v>過量投与、代謝を妨げる薬剤との併用、肝機能低下による代謝低下</v>
       </c>
       <c r="G94" t="str">
-        <v/>
+        <v>ふらつき、眠気、めまい、物が二重に見えるなどの中毒症状がないか確認する</v>
       </c>
       <c r="H94" t="str">
-        <v>急性肝炎などの肝細胞障害（比が低い、つまりASTに対してLDHが相対的に低い場合は肝性が示唆される）</v>
+        <v>飲み忘れ、自己判断による減量、代謝を促進する薬剤との併用（相互作用）</v>
       </c>
       <c r="I94" t="str">
-        <v/>
+        <v>発作やてんかん症状の再発がないか確認し、飲み忘れがないか一緒に確認する</v>
       </c>
       <c r="J94" t="str">
-        <v>AST・LDHが同時に上昇した際の鑑別に使う目安の一つ。単独の検査値ではなく計算上の比率であり、確定診断には他の検査（ビリルビン、CK、心筋マーカーなど）と合わせた評価が必要</v>
+        <v>採血のタイミング（トラフ値かどうか）で数値の解釈が変わるため採血時点を確認する。カルバマゼピンは自己誘導により長期使用で濃度が下がることがある点にも注意</v>
       </c>
       <c r="K94" t="str">
-        <v/>
+        <v>てんかん</v>
       </c>
       <c r="L94" t="str">
-        <v>LDH/AST,LDH,AST,溶血,心筋梗塞,肝炎</v>
+        <v>TDM,血中薬物濃度,治療域,中毒域,カルバマゼピン,フェニトイン,バルプロ酸,抗てんかん薬</v>
       </c>
       <c r="M94" t="str">
         <v/>
@@ -4278,107 +4278,107 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>亜鉛（Zn）</v>
+        <v>アミラーゼ（AMY）</v>
       </c>
       <c r="B95" t="str">
-        <v>Zn</v>
+        <v>AMY</v>
       </c>
       <c r="C95" t="str">
-        <v>80〜130 μg/dL程度（施設差あり）</v>
+        <v>44〜132 U/L（施設差あり）</v>
       </c>
       <c r="D95" t="str">
-        <v>味覚や皮膚、免疫に関わる微量ミネラル。高齢者や低栄養で不足しやすい</v>
+        <v>膵臓や唾液腺から出る消化酵素。膵炎などで血液中に漏れ出す</v>
       </c>
       <c r="E95" t="str">
-        <v>亜鉛は、味を感じる働きや皮膚・粘膜の健康、免疫の働きに関わる微量ミネラルです。不足すると、味がわかりにくくなったり（味覚障害）、傷が治りにくくなったりすることがあります。</v>
+        <v>アミラーゼは、でんぷんを分解する消化酵素で、主に膵臓と唾液腺から作られます。膵臓に炎症が起きると血液中に漏れ出して数値が上がるため、膵炎の診断や経過観察に使われます。</v>
       </c>
       <c r="F95" t="str">
-        <v/>
+        <v>急性膵炎、慢性膵炎の急性増悪、耳下腺炎（おたふくかぜ）、腎不全</v>
       </c>
       <c r="G95" t="str">
-        <v/>
+        <v>飲酒を控える、脂っこい食事を避けるよう伝える</v>
       </c>
       <c r="H95" t="str">
-        <v>低栄養、高齢による摂取不足、消化器手術後、亜鉛の吸収を妨げる薬剤（PPI、キレート形成する薬剤など）との併用</v>
+        <v>慢性膵炎の進行期（膵臓の機能低下）</v>
       </c>
       <c r="I95" t="str">
-        <v>味覚の変化（味を感じにくい、金属味がするなど）がないか確認する。牡蠣、赤身肉、レバーなど亜鉛を多く含む食品を意識するとよいことを伝える</v>
+        <v/>
       </c>
       <c r="J95" t="str">
-        <v>薬剤性の亜鉛欠乏（PPI長期使用、D-ペニシラミン、一部の降圧薬など）に注意。亜鉛欠乏による味覚障害は原因薬剤の中止・亜鉛補充で改善することがある</v>
+        <v>膵臓由来か唾液腺由来かを区別するには膵型アミラーゼ(P-AMY)を確認する。急性膵炎では強い腹痛・背部痛を伴うことが多く、飲酒歴の確認も重要</v>
       </c>
       <c r="K95" t="str">
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>亜鉛,Zn,味覚障害,亜鉛欠乏</v>
+        <v>アミラーゼ,AMY,膵炎,急性膵炎</v>
       </c>
       <c r="M95" t="str">
-        <v>食事と栄養 p.78（亜鉛）</v>
+        <v/>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>マグネシウム（Mg）</v>
+        <v>間接ビリルビン</v>
       </c>
       <c r="B96" t="str">
-        <v>Mg</v>
+        <v>I-Bil</v>
       </c>
       <c r="C96" t="str">
-        <v>1.8〜2.6 mg/dL程度（施設差あり）</v>
+        <v>0.2〜0.8 mg/dL程度（施設差あり）</v>
       </c>
       <c r="D96" t="str">
-        <v>骨や筋肉、神経の働きに関わるミネラル。低栄養や利尿薬で不足しやすい</v>
+        <v>赤血球が壊れてできるビリルビンのうち、肝臓で処理される前の形</v>
       </c>
       <c r="E96" t="str">
-        <v>マグネシウムは、骨や筋肉、神経の働きを支えるミネラルです。不足すると、こむら返りや不整脈、だるさなどの症状が出ることがあります。</v>
+        <v>間接ビリルビンは、赤血球が壊れてできたビリルビンが、まだ肝臓で処理される前の状態です。この値が高い場合、赤血球が通常より多く壊れている(溶血)か、肝臓での処理能力に生まれつきの体質差(体質性黄疸)がある可能性が考えられます。</v>
       </c>
       <c r="F96" t="str">
-        <v>腎不全、マグネシウム製剤（酸化マグネシウムなど）の過量投与</v>
+        <v>溶血性疾患（自己免疫性溶血性貧血、血液型不適合輸血など）、体質性黄疸（ジルベール症候群）、新生児黄疸</v>
       </c>
       <c r="G96" t="str">
-        <v>腎機能低下がある患者で酸化マグネシウムなどの緩下剤を使用中は、傾眠・血圧低下などの高マグネシウム血症の症状がないか確認する</v>
+        <v>皮膚や白目の黄染、尿の色の変化がないか確認する</v>
       </c>
       <c r="H96" t="str">
-        <v>低栄養、利尿薬の使用、慢性的な下痢、アルコール多飲、PPI長期使用</v>
+        <v/>
       </c>
       <c r="I96" t="str">
-        <v>こむら返りや動悸などの症状がないか確認する</v>
+        <v/>
       </c>
       <c r="J96" t="str">
-        <v>腎機能低下患者への酸化マグネシウム投与は高マグネシウム血症のリスクがあるため定期的なモニタリングが必要。PPI長期使用も低マグネシウム血症のリスク因子として知られる</v>
+        <v>直接ビリルビンとの比率で原因を推測する（間接優位は溶血・体質性、直接優位は胆道系）。総ビリルビン・AST/ALTと合わせて評価する</v>
       </c>
       <c r="K96" t="str">
-        <v>腎機能</v>
+        <v>肝機能</v>
       </c>
       <c r="L96" t="str">
-        <v>マグネシウム,Mg,酸化マグネシウム,こむら返り</v>
+        <v>間接ビリルビン,I-Bil,溶血</v>
       </c>
       <c r="M96" t="str">
-        <v>食事と栄養 p.84（マグネシウム）</v>
+        <v/>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>CK/AST比</v>
+        <v>直接ビリルビン</v>
       </c>
       <c r="B97" t="str">
-        <v>CK/AST</v>
+        <v>D-Bil</v>
       </c>
       <c r="C97" t="str">
-        <v>目安として使われる比率（施設差・カットオフ値の設定により異なる）</v>
+        <v>0.0〜0.3 mg/dL程度（施設差あり）</v>
       </c>
       <c r="D97" t="str">
-        <v>ASTが上昇したときに、原因が筋肉（CKも上昇）か、それ以外（肝臓など）かを見分ける目安になる比</v>
+        <v>肝臓で処理された後のビリルビン。胆道の詰まりで血液中に増える</v>
       </c>
       <c r="E97" t="str">
-        <v>これは、筋肉の数値（CK）と肝臓の数値（AST）を比べることで、ASTの上昇が筋肉由来なのか、肝臓由来なのかを見分ける手がかりになる比率です。</v>
+        <v>直接ビリルビンは、肝臓で処理された後のビリルビンです。胆石や腫瘍などで胆汁の通り道（胆道）が詰まると、行き場を失って血液中に増え、皮膚や白目が黄色くなる黄疸として現れます。</v>
       </c>
       <c r="F97" t="str">
-        <v>横紋筋融解症、心筋梗塞、激しい運動など筋肉由来のAST上昇（CKも同時に高値）</v>
+        <v>肝疾患、胆石など胆道の閉塞</v>
       </c>
       <c r="G97" t="str">
-        <v>筋肉痛や脱力感、褐色尿などの症状がないか確認する</v>
+        <v>皮膚や白目の黄染、白っぽい便、濃い茶色の尿がないか確認する</v>
       </c>
       <c r="H97" t="str">
         <v/>
@@ -4387,21 +4387,103 @@
         <v/>
       </c>
       <c r="J97" t="str">
-        <v>ASTのみ上昇しCKが正常であれば肝臓由来を、両方上昇していれば筋肉由来を疑う手がかりになる。スタチン系薬剤による横紋筋融解症が疑われる場面での鑑別に有用</v>
+        <v>直接優位の上昇は胆道系（胆石、腫瘍による閉塞）を、間接優位の上昇は溶血・体質性を疑う手がかりになる。γ-GTP・ALPと合わせて胆道系疾患を評価する</v>
       </c>
       <c r="K97" t="str">
-        <v/>
+        <v>肝機能</v>
       </c>
       <c r="L97" t="str">
-        <v>CK/AST,CK,AST,横紋筋融解症,スタチン</v>
+        <v>直接ビリルビン,D-Bil,胆石,胆道閉塞</v>
       </c>
       <c r="M97" t="str">
         <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>亜鉛（Zn）</v>
+      </c>
+      <c r="B98" t="str">
+        <v>Zn</v>
+      </c>
+      <c r="C98" t="str">
+        <v>80〜130 μg/dL程度（施設差あり）</v>
+      </c>
+      <c r="D98" t="str">
+        <v>味覚や皮膚、免疫に関わる微量ミネラル。高齢者や低栄養で不足しやすい</v>
+      </c>
+      <c r="E98" t="str">
+        <v>亜鉛は、味を感じる働きや皮膚・粘膜の健康、免疫の働きに関わる微量ミネラルです。不足すると、味がわかりにくくなったり（味覚障害）、傷が治りにくくなったりすることがあります。</v>
+      </c>
+      <c r="F98" t="str">
+        <v/>
+      </c>
+      <c r="G98" t="str">
+        <v/>
+      </c>
+      <c r="H98" t="str">
+        <v>低栄養、高齢による摂取不足、消化器手術後、亜鉛の吸収を妨げる薬剤（PPI、キレート形成する薬剤など）との併用</v>
+      </c>
+      <c r="I98" t="str">
+        <v>味覚の変化（味を感じにくい、金属味がするなど）がないか確認する。牡蠣、赤身肉、レバーなど亜鉛を多く含む食品を意識するとよいことを伝える</v>
+      </c>
+      <c r="J98" t="str">
+        <v>薬剤性の亜鉛欠乏（PPI長期使用、D-ペニシラミン、一部の降圧薬など）に注意。亜鉛欠乏による味覚障害は原因薬剤の中止・亜鉛補充で改善することがある</v>
+      </c>
+      <c r="K98" t="str">
+        <v/>
+      </c>
+      <c r="L98" t="str">
+        <v>亜鉛,Zn,味覚障害,亜鉛欠乏</v>
+      </c>
+      <c r="M98" t="str">
+        <v>食事と栄養 p.78（亜鉛）</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>マグネシウム（Mg）</v>
+      </c>
+      <c r="B99" t="str">
+        <v>Mg</v>
+      </c>
+      <c r="C99" t="str">
+        <v>1.8〜2.6 mg/dL程度（施設差あり）</v>
+      </c>
+      <c r="D99" t="str">
+        <v>骨や筋肉、神経の働きに関わるミネラル。低栄養や利尿薬で不足しやすい</v>
+      </c>
+      <c r="E99" t="str">
+        <v>マグネシウムは、骨や筋肉、神経の働きを支えるミネラルです。不足すると、こむら返りや不整脈、だるさなどの症状が出ることがあります。</v>
+      </c>
+      <c r="F99" t="str">
+        <v>腎不全、マグネシウム製剤（酸化マグネシウムなど）の過量投与</v>
+      </c>
+      <c r="G99" t="str">
+        <v>腎機能低下がある患者で酸化マグネシウムなどの緩下剤を使用中は、傾眠・血圧低下などの高マグネシウム血症の症状がないか確認する</v>
+      </c>
+      <c r="H99" t="str">
+        <v>低栄養、利尿薬の使用、慢性的な下痢、アルコール多飲、PPI長期使用</v>
+      </c>
+      <c r="I99" t="str">
+        <v>こむら返りや動悸などの症状がないか確認する</v>
+      </c>
+      <c r="J99" t="str">
+        <v>腎機能低下患者への酸化マグネシウム投与は高マグネシウム血症のリスクがあるため定期的なモニタリングが必要。PPI長期使用も低マグネシウム血症のリスク因子として知られる</v>
+      </c>
+      <c r="K99" t="str">
+        <v>腎機能</v>
+      </c>
+      <c r="L99" t="str">
+        <v>マグネシウム,Mg,酸化マグネシウム,こむら返り</v>
+      </c>
+      <c r="M99" t="str">
+        <v>食事と栄養 p.84（マグネシウム）</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M97"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M99"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/検査値リファレンス初期データ.xlsx
+++ b/検査値リファレンス初期データ.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M99"/>
+  <dimension ref="A1:M98"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -1859,66 +1859,66 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>AST比/ALP比</v>
+        <v>CONUT値</v>
       </c>
       <c r="B36" t="str">
-        <v>R比,R-factor</v>
+        <v>CONUT</v>
       </c>
       <c r="C36" t="str">
-        <v>R比 5以上：肝細胞障害型、2以下：胆汁うっ滞型、2〜5：混合型（報告により定義が異なる）</v>
+        <v>0〜1点：正常、2〜4点：軽度低栄養、5〜8点：中等度低栄養、9〜12点：高度低栄養</v>
       </c>
       <c r="D36" t="str">
-        <v>肝障害のパターンを「肝細胞障害型」か「胆汁うっ滞型」かに分類するための指標（R比）</v>
+        <v>アルブミン・総リンパ球数・総コレステロールの3項目から算出する栄養状態の評価スコア</v>
       </c>
       <c r="E36" t="str">
-        <v>これは、肝臓の数値の上がり方のパターンから、肝臓の細胞そのものが傷んでいるタイプなのか、胆汁の流れが滞っているタイプなのかを見分けるための指標です。</v>
+        <v>CONUT値は、血液検査（アルブミン、リンパ球数、コレステロール）の結果から計算される、栄養状態を数値化したスコアです。点数が高いほど低栄養の状態が疑われます。</v>
       </c>
       <c r="F36" t="str">
-        <v>肝細胞障害型（ウイルス性肝炎、薬剤性肝障害の肝細胞障害型など）：AST/ALT優位の上昇</v>
+        <v>低栄養状態（点数が高いほど重度）</v>
       </c>
       <c r="G36" t="str">
-        <v/>
+        <v>食事摂取量や体重の変化を確認する。必要に応じて栄養補助食品の活用を提案する</v>
       </c>
       <c r="H36" t="str">
-        <v>胆汁うっ滞型（胆石、胆道腫瘍、薬剤性肝障害の胆汁うっ滞型など）：ALP優位の上昇</v>
+        <v/>
       </c>
       <c r="I36" t="str">
         <v/>
       </c>
       <c r="J36" t="str">
-        <v>R比＝(ALTの基準値上限に対する倍率)÷(ALPの基準値上限に対する倍率)で算出する。薬剤性肝障害(DILI)の病型分類（肝細胞障害型・胆汁うっ滞型・混合型）に用いられる考え方で、原因薬剤の推定や重症度評価の参考になる</v>
+        <v>アルブミン・総リンパ球数・総コレステロールの3項目それぞれに配点があり、合計点で評価する客観的栄養指標。フレイル・サルコペニアの評価やポリファーマシー対策の一環としての栄養状態把握に有用</v>
       </c>
       <c r="K36" t="str">
-        <v>肝機能</v>
+        <v/>
       </c>
       <c r="L36" t="str">
-        <v>R比,R-factor,肝細胞障害型,胆汁うっ滞型,薬剤性肝障害,DILI</v>
+        <v>CONUT,CONUT値,栄養評価,低栄養,フレイル</v>
       </c>
       <c r="M36" t="str">
-        <v/>
+        <v>食事と栄養 p.240（フレイルQ108 低栄養や食事量の評価）</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>CONUT値</v>
+        <v>乳び</v>
       </c>
       <c r="B37" t="str">
-        <v>CONUT</v>
+        <v>乳び,Lipemia</v>
       </c>
       <c r="C37" t="str">
-        <v>0〜1点：正常、2〜4点：軽度低栄養、5〜8点：中等度低栄養、9〜12点：高度低栄養</v>
+        <v>所見なし（血清が白濁していなければ正常）</v>
       </c>
       <c r="D37" t="str">
-        <v>アルブミン・総リンパ球数・総コレステロールの3項目から算出する栄養状態の評価スコア</v>
+        <v>中性脂肪が非常に多いため、血清が白く濁って見える状態。検査値そのものではなく検体の外観所見</v>
       </c>
       <c r="E37" t="str">
-        <v>CONUT値は、血液検査（アルブミン、リンパ球数、コレステロール）の結果から計算される、栄養状態を数値化したスコアです。点数が高いほど低栄養の状態が疑われます。</v>
+        <v>乳びとは、血液中の中性脂肪が非常に多いために、採血した血液（血清）が白く濁って見える状態のことです。多くの場合、食後の採血や、著しい脂質異常症が背景にあります。</v>
       </c>
       <c r="F37" t="str">
-        <v>低栄養状態（点数が高いほど重度）</v>
+        <v>著しい高中性脂肪血症、食後採血（一時的なもの）、原発性高カイロミクロン血症などの脂質代謝異常</v>
       </c>
       <c r="G37" t="str">
-        <v>食事摂取量や体重の変化を確認する。必要に応じて栄養補助食品の活用を提案する</v>
+        <v>採血が空腹時だったかを確認する。食後採血であれば次回は空腹時の再検を提案する</v>
       </c>
       <c r="H37" t="str">
         <v/>
@@ -1927,39 +1927,39 @@
         <v/>
       </c>
       <c r="J37" t="str">
-        <v>アルブミン・総リンパ球数・総コレステロールの3項目それぞれに配点があり、合計点で評価する客観的栄養指標。フレイル・サルコペニアの評価やポリファーマシー対策の一環としての栄養状態把握に有用</v>
+        <v>血清の白濁により一部の検査項目（電解質など）の測定値に誤差が出ることがある（偽性低ナトリウム血症など）。中性脂肪値と合わせて評価する</v>
       </c>
       <c r="K37" t="str">
-        <v/>
+        <v>脂質異常症</v>
       </c>
       <c r="L37" t="str">
-        <v>CONUT,CONUT値,栄養評価,低栄養,フレイル</v>
+        <v>乳び,乳び血清,Lipemia,高中性脂肪血症</v>
       </c>
       <c r="M37" t="str">
-        <v>食事と栄養 p.240（フレイルQ108 低栄養や食事量の評価）</v>
+        <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>乳び</v>
+        <v>溶血</v>
       </c>
       <c r="B38" t="str">
-        <v>乳び,Lipemia</v>
+        <v>溶血,Hemolysis</v>
       </c>
       <c r="C38" t="str">
-        <v>所見なし（血清が白濁していなければ正常）</v>
+        <v>所見なし（溶血を示唆する検査値異常がなければ正常）</v>
       </c>
       <c r="D38" t="str">
-        <v>中性脂肪が非常に多いため、血清が白く濁って見える状態。検査値そのものではなく検体の外観所見</v>
+        <v>赤血球が通常より早く壊れる状態。単独の検査値ではなく、複数の検査値の組み合わせで疑う病態</v>
       </c>
       <c r="E38" t="str">
-        <v>乳びとは、血液中の中性脂肪が非常に多いために、採血した血液（血清）が白く濁って見える状態のことです。多くの場合、食後の採血や、著しい脂質異常症が背景にあります。</v>
+        <v>溶血とは、赤血球が通常よりも早いペースで壊れてしまう状態のことです。壊れた赤血球からビリルビンなどが放出されるため、貧血や黄疸の原因になることがあります。</v>
       </c>
       <c r="F38" t="str">
-        <v>著しい高中性脂肪血症、食後採血（一時的なもの）、原発性高カイロミクロン血症などの脂質代謝異常</v>
+        <v>自己免疫性溶血性貧血、血液型不適合輸血、G6PD欠損症などの遺伝性疾患、機械弁など人工物による物理的破壊、薬剤性溶血</v>
       </c>
       <c r="G38" t="str">
-        <v>採血が空腹時だったかを確認する。食後採血であれば次回は空腹時の再検を提案する</v>
+        <v>倦怠感、黄疸、尿の色が濃くなるなどの症状がないか確認する</v>
       </c>
       <c r="H38" t="str">
         <v/>
@@ -1968,13 +1968,13 @@
         <v/>
       </c>
       <c r="J38" t="str">
-        <v>血清の白濁により一部の検査項目（電解質など）の測定値に誤差が出ることがある（偽性低ナトリウム血症など）。中性脂肪値と合わせて評価する</v>
+        <v>溶血を疑う際は、間接ビリルビン上昇・LDH上昇・ハプトグロビン低下・網状赤血球増加のパターンを確認する。ヘモグロビン・MCV・MCHCの変化と合わせて総合的に判断する</v>
       </c>
       <c r="K38" t="str">
-        <v>脂質異常症</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="L38" t="str">
-        <v>乳び,乳び血清,Lipemia,高中性脂肪血症</v>
+        <v>溶血,Hemolysis,溶血性貧血,G6PD,ハプトグロビン</v>
       </c>
       <c r="M38" t="str">
         <v/>
@@ -1982,25 +1982,25 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>溶血</v>
+        <v>黄疸</v>
       </c>
       <c r="B39" t="str">
-        <v>溶血,Hemolysis</v>
+        <v>黄疸,Jaundice</v>
       </c>
       <c r="C39" t="str">
-        <v>所見なし（溶血を示唆する検査値異常がなければ正常）</v>
+        <v>所見なし（皮膚・眼球結膜の黄染がなければ正常）</v>
       </c>
       <c r="D39" t="str">
-        <v>赤血球が通常より早く壊れる状態。単独の検査値ではなく、複数の検査値の組み合わせで疑う病態</v>
+        <v>ビリルビンが体にたまり、皮膚や白目が黄色くなる状態。単独の検査値ではなく、ビリルビン上昇によって表れる身体所見</v>
       </c>
       <c r="E39" t="str">
-        <v>溶血とは、赤血球が通常よりも早いペースで壊れてしまう状態のことです。壊れた赤血球からビリルビンなどが放出されるため、貧血や黄疸の原因になることがあります。</v>
+        <v>黄疸は、体の中にビリルビンという黄色い色素がたまることで、皮膚や白目が黄色く見える状態です。肝臓や胆道のトラブル、赤血球が壊れやすくなる病気（溶血）などが原因となります。</v>
       </c>
       <c r="F39" t="str">
-        <v>自己免疫性溶血性貧血、血液型不適合輸血、G6PD欠損症などの遺伝性疾患、機械弁など人工物による物理的破壊、薬剤性溶血</v>
+        <v>肝炎・肝硬変などの肝疾患、胆石・腫瘍による胆道閉塞、溶血性疾患、体質性黄疸（ジルベール症候群）、新生児黄疸</v>
       </c>
       <c r="G39" t="str">
-        <v>倦怠感、黄疸、尿の色が濃くなるなどの症状がないか確認する</v>
+        <v>白目や皮膚の黄染に気づいたら、尿の色（濃い茶色）や便の色（白っぽい）の変化も確認し、早めの受診を勧める</v>
       </c>
       <c r="H39" t="str">
         <v/>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="J39" t="str">
-        <v>溶血を疑う際は、間接ビリルビン上昇・LDH上昇・ハプトグロビン低下・網状赤血球増加のパターンを確認する。ヘモグロビン・MCV・MCHCの変化と合わせて総合的に判断する</v>
+        <v>黄疸は検査値そのものではなく身体所見。原因を調べる際は総ビリルビン・直接ビリルビン・間接ビリルビンの内訳とAST/ALT/γ-GTPを確認する。直接優位なら胆道系、間接優位なら溶血・体質性を疑う</v>
       </c>
       <c r="K39" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>肝機能</v>
       </c>
       <c r="L39" t="str">
-        <v>溶血,Hemolysis,溶血性貧血,G6PD,ハプトグロビン</v>
+        <v>黄疸,ジョンダイス,Jaundice,ビリルビン,皮膚黄染,白目</v>
       </c>
       <c r="M39" t="str">
         <v/>
@@ -2023,81 +2023,81 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>黄疸</v>
+        <v>TSH（甲状腺刺激ホルモン）</v>
       </c>
       <c r="B40" t="str">
-        <v>黄疸,Jaundice</v>
+        <v>TSH</v>
       </c>
       <c r="C40" t="str">
-        <v>所見なし（皮膚・眼球結膜の黄染がなければ正常）</v>
+        <v>0.5〜5.0 μIU/mL程度（施設差あり）</v>
       </c>
       <c r="D40" t="str">
-        <v>ビリルビンが体にたまり、皮膚や白目が黄色くなる状態。単独の検査値ではなく、ビリルビン上昇によって表れる身体所見</v>
+        <v>甲状腺の働きが多いか少ないかを最も敏感に反映するホルモン</v>
       </c>
       <c r="E40" t="str">
-        <v>黄疸は、体の中にビリルビンという黄色い色素がたまることで、皮膚や白目が黄色く見える状態です。肝臓や胆道のトラブル、赤血球が壊れやすくなる病気（溶血）などが原因となります。</v>
+        <v>TSHは脳の下垂体から出て、甲状腺に「もっと働いて」と指令を送るホルモンです。甲状腺の働きが弱っていると体が指令を強めるためTSHは上がり、逆に甲状腺が働きすぎているとTSHは下がります。甲状腺の状態を最初に確認する数値としてよく使われます。</v>
       </c>
       <c r="F40" t="str">
-        <v>肝炎・肝硬変などの肝疾患、胆石・腫瘍による胆道閉塞、溶血性疾患、体質性黄疸（ジルベール症候群）、新生児黄疸</v>
+        <v>甲状腺機能低下症（橋本病など）、チラーヂンSなど甲状腺ホルモン薬の量不足</v>
       </c>
       <c r="G40" t="str">
-        <v>白目や皮膚の黄染に気づいたら、尿の色（濃い茶色）や便の色（白っぽい）の変化も確認し、早めの受診を勧める</v>
+        <v>だるさ、むくみ、体重増加、寒がりなどの症状がないか確認する。服薬状況（飲み忘れ、他の薬との飲み合わせ）を確認する</v>
       </c>
       <c r="H40" t="str">
-        <v/>
+        <v>甲状腺機能亢進症（バセドウ病など）、チラーヂンSなど甲状腺ホルモン薬の過量</v>
       </c>
       <c r="I40" t="str">
-        <v/>
+        <v>動悸、体重減少、暑がり、手のふるえなどの症状がないか確認する</v>
       </c>
       <c r="J40" t="str">
-        <v>黄疸は検査値そのものではなく身体所見。原因を調べる際は総ビリルビン・直接ビリルビン・間接ビリルビンの内訳とAST/ALT/γ-GTPを確認する。直接優位なら胆道系、間接優位なら溶血・体質性を疑う</v>
+        <v>チラーヂンS服用中はTSHが治療目標域に収まっているかで用量調整の目安にする。メルカゾール服用中はTSH・FT4に加えて無顆粒球症の初期症状（発熱・のどの痛み）の有無や白血球数も確認する</v>
       </c>
       <c r="K40" t="str">
-        <v>肝機能</v>
+        <v>甲状腺疾患</v>
       </c>
       <c r="L40" t="str">
-        <v>黄疸,ジョンダイス,Jaundice,ビリルビン,皮膚黄染,白目</v>
+        <v>TSH,甲状腺刺激ホルモン,甲状腺機能,橋本病,バセドウ病,チラーヂン,メルカゾール</v>
       </c>
       <c r="M40" t="str">
-        <v/>
+        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>TSH（甲状腺刺激ホルモン）</v>
+        <v>FT4（遊離サイロキシン）</v>
       </c>
       <c r="B41" t="str">
-        <v>TSH</v>
+        <v>FT4</v>
       </c>
       <c r="C41" t="str">
-        <v>0.5〜5.0 μIU/mL程度（施設差あり）</v>
+        <v>0.9〜1.7 ng/dL程度（施設差あり）</v>
       </c>
       <c r="D41" t="str">
-        <v>甲状腺の働きが多いか少ないかを最も敏感に反映するホルモン</v>
+        <v>甲状腺が実際に分泌しているホルモンの量そのものを表す数値</v>
       </c>
       <c r="E41" t="str">
-        <v>TSHは脳の下垂体から出て、甲状腺に「もっと働いて」と指令を送るホルモンです。甲状腺の働きが弱っていると体が指令を強めるためTSHは上がり、逆に甲状腺が働きすぎているとTSHは下がります。甲状腺の状態を最初に確認する数値としてよく使われます。</v>
+        <v>FT4は甲状腺そのものが作っているホルモンの量です。TSHが「指令の強さ」だとすると、FT4は「実際に出ている量」にあたります。2つをあわせて見ることで、甲状腺の働きが今どういう状態かを詳しく判断できます。</v>
       </c>
       <c r="F41" t="str">
-        <v>甲状腺機能低下症（橋本病など）、チラーヂンSなど甲状腺ホルモン薬の量不足</v>
+        <v>甲状腺機能亢進症（バセドウ病など）</v>
       </c>
       <c r="G41" t="str">
-        <v>だるさ、むくみ、体重増加、寒がりなどの症状がないか確認する。服薬状況（飲み忘れ、他の薬との飲み合わせ）を確認する</v>
+        <v>動悸、体重減少、暑がり、手のふるえなどの症状がないか確認する</v>
       </c>
       <c r="H41" t="str">
-        <v>甲状腺機能亢進症（バセドウ病など）、チラーヂンSなど甲状腺ホルモン薬の過量</v>
+        <v>甲状腺機能低下症（橋本病など）</v>
       </c>
       <c r="I41" t="str">
-        <v>動悸、体重減少、暑がり、手のふるえなどの症状がないか確認する</v>
+        <v>だるさ、むくみ、体重増加、寒がりなどの症状がないか確認する</v>
       </c>
       <c r="J41" t="str">
-        <v>チラーヂンS服用中はTSHが治療目標域に収まっているかで用量調整の目安にする。メルカゾール服用中はTSH・FT4に加えて無顆粒球症の初期症状（発熱・のどの痛み）の有無や白血球数も確認する</v>
+        <v>TSHと逆方向に動くのが基本だが、下垂体性の異常など例外もある。TSHと合わせて評価し、片方だけで判断しない</v>
       </c>
       <c r="K41" t="str">
         <v>甲状腺疾患</v>
       </c>
       <c r="L41" t="str">
-        <v>TSH,甲状腺刺激ホルモン,甲状腺機能,橋本病,バセドウ病,チラーヂン,メルカゾール</v>
+        <v>FT4,遊離サイロキシン,甲状腺ホルモン,甲状腺機能</v>
       </c>
       <c r="M41" t="str">
         <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
@@ -2105,81 +2105,81 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>FT4（遊離サイロキシン）</v>
+        <v>尿蛋白（随時尿）</v>
       </c>
       <c r="B42" t="str">
-        <v>FT4</v>
+        <v>尿蛋白,U-pro</v>
       </c>
       <c r="C42" t="str">
-        <v>0.9〜1.7 ng/dL程度（施設差あり）</v>
+        <v>陰性（－）〜弱陽性</v>
       </c>
       <c r="D42" t="str">
-        <v>甲状腺が実際に分泌しているホルモンの量そのものを表す数値</v>
+        <v>腎臓から本来漏れないはずのたんぱくが尿に出ていないかを見る検査</v>
       </c>
       <c r="E42" t="str">
-        <v>FT4は甲状腺そのものが作っているホルモンの量です。TSHが「指令の強さ」だとすると、FT4は「実際に出ている量」にあたります。2つをあわせて見ることで、甲状腺の働きが今どういう状態かを詳しく判断できます。</v>
+        <v>この検査は、腎臓のろ過機能に負担がかかっていないかを見るものです。本来、たんぱく質は尿にほとんど出ませんが、腎臓に負担がかかると漏れ出るようになります。</v>
       </c>
       <c r="F42" t="str">
-        <v>甲状腺機能亢進症（バセドウ病など）</v>
+        <v>糖尿病性腎症、腎炎、高血圧性腎硬化症、発熱・運動後の一過性のもの</v>
       </c>
       <c r="G42" t="str">
-        <v>動悸、体重減少、暑がり、手のふるえなどの症状がないか確認する</v>
+        <v/>
       </c>
       <c r="H42" t="str">
-        <v>甲状腺機能低下症（橋本病など）</v>
+        <v/>
       </c>
       <c r="I42" t="str">
-        <v>だるさ、むくみ、体重増加、寒がりなどの症状がないか確認する</v>
+        <v/>
       </c>
       <c r="J42" t="str">
-        <v>TSHと逆方向に動くのが基本だが、下垂体性の異常など例外もある。TSHと合わせて評価し、片方だけで判断しない</v>
+        <v>発熱・激しい運動・起立性蛋白尿など生理的な要因でも陽性になることがある。持続する場合に腎症の進行を疑う</v>
       </c>
       <c r="K42" t="str">
-        <v>甲状腺疾患</v>
+        <v>糖尿病,腎機能</v>
       </c>
       <c r="L42" t="str">
-        <v>FT4,遊離サイロキシン,甲状腺ホルモン,甲状腺機能</v>
+        <v>尿蛋白,U-pro,腎症,たんぱく尿</v>
       </c>
       <c r="M42" t="str">
-        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
+        <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>尿蛋白（随時尿）</v>
+        <v>尿クレアチニン（随時尿）</v>
       </c>
       <c r="B43" t="str">
-        <v>尿蛋白,U-pro</v>
+        <v>尿CRE</v>
       </c>
       <c r="C43" t="str">
-        <v>陰性（－）〜弱陽性</v>
+        <v>随時尿は主に他項目の濃度補正に利用（単独の基準値は設けにくい）</v>
       </c>
       <c r="D43" t="str">
-        <v>腎臓から本来漏れないはずのたんぱくが尿に出ていないかを見る検査</v>
+        <v>随時尿中のクレアチニン濃度。他の尿検査項目を薄まり具合で補正するための基準として使う</v>
       </c>
       <c r="E43" t="str">
-        <v>この検査は、腎臓のろ過機能に負担がかかっていないかを見るものです。本来、たんぱく質は尿にほとんど出ませんが、腎臓に負担がかかると漏れ出るようになります。</v>
+        <v>この数値は、尿がどれくらい薄まっているかを確認するための基準として使われます。他の尿検査の結果（蛋白やアルブミンなど）をこの値で割って補正することで、水分摂取量による影響を減らして正確に評価できます。</v>
       </c>
       <c r="F43" t="str">
-        <v>糖尿病性腎症、腎炎、高血圧性腎硬化症、発熱・運動後の一過性のもの</v>
+        <v/>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v/>
+        <v>尿が薄い（水分摂取が多い、腎機能低下）状態</v>
       </c>
       <c r="I43" t="str">
         <v/>
       </c>
       <c r="J43" t="str">
-        <v>発熱・激しい運動・起立性蛋白尿など生理的な要因でも陽性になることがある。持続する場合に腎症の進行を疑う</v>
+        <v>尿中アルブミン/Cr比、尿蛋白/Cr比など、他項目の補正計算に使われる。単独の高低に臨床的意味は乏しい</v>
       </c>
       <c r="K43" t="str">
-        <v>糖尿病,腎機能</v>
+        <v>腎機能</v>
       </c>
       <c r="L43" t="str">
-        <v>尿蛋白,U-pro,腎症,たんぱく尿</v>
+        <v>尿CRE,尿クレアチニン,随時尿,補正,蛋白クレアチニン比</v>
       </c>
       <c r="M43" t="str">
         <v/>
@@ -2187,40 +2187,40 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>尿クレアチニン（随時尿）</v>
+        <v>白血球（WBC）</v>
       </c>
       <c r="B44" t="str">
-        <v>尿CRE</v>
+        <v>WBC</v>
       </c>
       <c r="C44" t="str">
-        <v>随時尿は主に他項目の濃度補正に利用（単独の基準値は設けにくい）</v>
+        <v>3,300〜8,600 /μL程度（施設差あり）</v>
       </c>
       <c r="D44" t="str">
-        <v>随時尿中のクレアチニン濃度。他の尿検査項目を薄まり具合で補正するための基準として使う</v>
+        <v>体を細菌やウイルスから守る免疫細胞の数で、感染や炎症、薬剤の影響を反映する</v>
       </c>
       <c r="E44" t="str">
-        <v>この数値は、尿がどれくらい薄まっているかを確認するための基準として使われます。他の尿検査の結果（蛋白やアルブミンなど）をこの値で割って補正することで、水分摂取量による影響を減らして正確に評価できます。</v>
+        <v>白血球は体に入ってきた細菌やウイルスと戦う免疫細胞です。感染症や炎症があると増え、逆に一部のお薬の副作用や骨髄の働きが落ちると減ることがあります。</v>
       </c>
       <c r="F44" t="str">
-        <v/>
+        <v>感染症、炎症、ステロイド使用、喫煙、白血病などの血液疾患</v>
       </c>
       <c r="G44" t="str">
-        <v/>
+        <v>発熱や体の痛みなど感染症状がないか確認する</v>
       </c>
       <c r="H44" t="str">
-        <v>尿が薄い（水分摂取が多い、腎機能低下）状態</v>
+        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、メルカゾールなど薬剤性の無顆粒球症、再生不良性貧血、ウイルス感染</v>
       </c>
       <c r="I44" t="str">
-        <v/>
+        <v>発熱、のどの痛みなど感染症状の初期サインがないか確認する。人混みを避け、手洗い・うがいを徹底するよう伝える</v>
       </c>
       <c r="J44" t="str">
-        <v>尿中アルブミン/Cr比、尿蛋白/Cr比など、他項目の補正計算に使われる。単独の高低に臨床的意味は乏しい</v>
+        <v>メルカゾール（チアマゾール）は無顆粒球症の重大な副作用があり、発熱・のどの痛みが出たらすぐ受診するよう指導する。抗がん剤・免疫抑制剤・抗てんかん薬（カルバマゼピンなど）使用中も定期的なモニタリングが必要</v>
       </c>
       <c r="K44" t="str">
-        <v>腎機能</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L44" t="str">
-        <v>尿CRE,尿クレアチニン,随時尿,補正,蛋白クレアチニン比</v>
+        <v>白血球,WBC,好中球,感染症,白血病,無顆粒球症,骨髄抑制</v>
       </c>
       <c r="M44" t="str">
         <v/>
@@ -2228,81 +2228,81 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>白血球（WBC）</v>
+        <v>赤血球</v>
       </c>
       <c r="B45" t="str">
-        <v>WBC</v>
+        <v>RBC</v>
       </c>
       <c r="C45" t="str">
-        <v>3,300〜8,600 /μL程度（施設差あり）</v>
+        <v>男性 435〜555万/μL、女性 386〜492万/μL程度（施設差あり）</v>
       </c>
       <c r="D45" t="str">
-        <v>体を細菌やウイルスから守る免疫細胞の数で、感染や炎症、薬剤の影響を反映する</v>
+        <v>血液中で酸素を運ぶ細胞の数。ヘモグロビン・ヘマトクリットと合わせて貧血・多血症を評価する</v>
       </c>
       <c r="E45" t="str">
-        <v>白血球は体に入ってきた細菌やウイルスと戦う免疫細胞です。感染症や炎症があると増え、逆に一部のお薬の副作用や骨髄の働きが落ちると減ることがあります。</v>
+        <v>赤血球は、肺で受け取った酸素を全身に運ぶ血液の細胞です。数が少ないと貧血、多いと多血症が疑われます。ヘモグロビンやヘマトクリットと合わせて総合的に評価します。</v>
       </c>
       <c r="F45" t="str">
-        <v>感染症、炎症、ステロイド使用、喫煙、白血病などの血液疾患</v>
+        <v>脱水、多血症（真性多血症、二次性多血症）、喫煙</v>
       </c>
       <c r="G45" t="str">
-        <v>発熱や体の痛みなど感染症状がないか確認する</v>
+        <v>脱水が疑われる場合はこまめな水分摂取を勧める（水分制限がある場合を除く）</v>
       </c>
       <c r="H45" t="str">
-        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、メルカゾールなど薬剤性の無顆粒球症、再生不良性貧血、ウイルス感染</v>
+        <v>貧血（鉄欠乏性貧血、腎性貧血など）、出血</v>
       </c>
       <c r="I45" t="str">
-        <v>発熱、のどの痛みなど感染症状の初期サインがないか確認する。人混みを避け、手洗い・うがいを徹底するよう伝える</v>
+        <v>ヘモグロビンと同様に、出血や食事量低下がないか確認する</v>
       </c>
       <c r="J45" t="str">
-        <v>メルカゾール（チアマゾール）は無顆粒球症の重大な副作用があり、発熱・のどの痛みが出たらすぐ受診するよう指導する。抗がん剤・免疫抑制剤・抗てんかん薬（カルバマゼピンなど）使用中も定期的なモニタリングが必要</v>
+        <v>ヘモグロビン・ヘマトクリットと同じ方向に動くことが多い。赤血球数だけでなくMCV・MCH・MCHCと合わせて貧血のタイプ(小球性・正球性・大球性)を判断する</v>
       </c>
       <c r="K45" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="L45" t="str">
-        <v>白血球,WBC,好中球,感染症,白血病,無顆粒球症,骨髄抑制</v>
+        <v>赤血球,RBC,貧血,多血症</v>
       </c>
       <c r="M45" t="str">
-        <v/>
+        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>赤血球</v>
+        <v>ヘモグロビン濃度</v>
       </c>
       <c r="B46" t="str">
-        <v>RBC</v>
+        <v>Hb</v>
       </c>
       <c r="C46" t="str">
-        <v>男性 435〜555万/μL、女性 386〜492万/μL程度（施設差あり）</v>
+        <v>男性 13.5〜17.5 g/dL、女性 11.5〜15.0 g/dL</v>
       </c>
       <c r="D46" t="str">
-        <v>血液中で酸素を運ぶ細胞の数。ヘモグロビン・ヘマトクリットと合わせて貧血・多血症を評価する</v>
+        <v>血液の中で酸素を運ぶ役割をしている。この値が低い状態が貧血。</v>
       </c>
       <c r="E46" t="str">
-        <v>赤血球は、肺で受け取った酸素を全身に運ぶ血液の細胞です。数が少ないと貧血、多いと多血症が疑われます。ヘモグロビンやヘマトクリットと合わせて総合的に評価します。</v>
+        <v>血の数値が良くなっても、体の中の鉄はまだ十分ではないことがあります。そのため、しばらく続けて飲むことが大切です。</v>
       </c>
       <c r="F46" t="str">
-        <v>脱水、多血症（真性多血症、二次性多血症）、喫煙</v>
+        <v/>
       </c>
       <c r="G46" t="str">
-        <v>脱水が疑われる場合はこまめな水分摂取を勧める（水分制限がある場合を除く）</v>
+        <v/>
       </c>
       <c r="H46" t="str">
-        <v>貧血（鉄欠乏性貧血、腎性貧血など）、出血</v>
+        <v>鉄欠乏性貧血、出血、腎性貧血、骨髄の造血機能低下</v>
       </c>
       <c r="I46" t="str">
-        <v>ヘモグロビンと同様に、出血や食事量低下がないか確認する</v>
+        <v>鉄分の多い食品（レバー・赤身肉・魚・ほうれん草など）を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える</v>
       </c>
       <c r="J46" t="str">
-        <v>ヘモグロビン・ヘマトクリットと同じ方向に動くことが多い。赤血球数だけでなくMCV・MCH・MCHCと合わせて貧血のタイプ(小球性・正球性・大球性)を判断する</v>
+        <v>原因（出血・食事量低下など）の確認が重要。腎機能低下がある場合は鉄不足以外が原因のこともある。鉄剤はヘモグロビンが正常化した後も2〜3か月程度は継続することが多い（鉄の貯蔵分を補うため。途中でやめると再び貧血になりやすい）</v>
       </c>
       <c r="K46" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>鉄欠乏性貧血,抗血小板療法,抗凝固療法（心房細動・血栓症）</v>
       </c>
       <c r="L46" t="str">
-        <v>赤血球,RBC,貧血,多血症</v>
+        <v>ヘモグロビン,Hb,貧血,鉄剤,鉄欠乏性貧血</v>
       </c>
       <c r="M46" t="str">
         <v>食事と栄養 p.151-164（第2部 貧血）</v>
@@ -2310,40 +2310,40 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ヘモグロビン濃度</v>
+        <v>ヘマトクリット値</v>
       </c>
       <c r="B47" t="str">
-        <v>Hb</v>
+        <v>Ht,Hct</v>
       </c>
       <c r="C47" t="str">
-        <v>男性 13.5〜17.5 g/dL、女性 11.5〜15.0 g/dL</v>
+        <v>男性 40〜50%、女性 35〜45%</v>
       </c>
       <c r="D47" t="str">
-        <v>血液の中で酸素を運ぶ役割をしている。この値が低い状態が貧血。</v>
+        <v>血液全体のうち赤血球が占める体積の割合。貧血・脱水の指標</v>
       </c>
       <c r="E47" t="str">
-        <v>血の数値が良くなっても、体の中の鉄はまだ十分ではないことがあります。そのため、しばらく続けて飲むことが大切です。</v>
+        <v>ヘマトクリットは、血液全体のうち赤血球が占める割合を表す数値です。この値が低いと貧血、高いと脱水や血液が濃くなっている状態が疑われます。</v>
       </c>
       <c r="F47" t="str">
-        <v/>
+        <v>脱水、多血症（真性多血症、二次性多血症）、喫煙</v>
       </c>
       <c r="G47" t="str">
-        <v/>
+        <v>脱水が疑われる場合はこまめな水分摂取を勧める（水分制限がある場合を除く）</v>
       </c>
       <c r="H47" t="str">
-        <v>鉄欠乏性貧血、出血、腎性貧血、骨髄の造血機能低下</v>
+        <v>貧血（鉄欠乏性貧血、腎性貧血など）、出血</v>
       </c>
       <c r="I47" t="str">
-        <v>鉄分の多い食品（レバー・赤身肉・魚・ほうれん草など）を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える</v>
+        <v>ヘモグロビンと同様に、出血や食事量低下がないか確認する</v>
       </c>
       <c r="J47" t="str">
-        <v>原因（出血・食事量低下など）の確認が重要。腎機能低下がある場合は鉄不足以外が原因のこともある。鉄剤はヘモグロビンが正常化した後も2〜3か月程度は継続することが多い（鉄の貯蔵分を補うため。途中でやめると再び貧血になりやすい）</v>
+        <v>ヘモグロビン・赤血球数と合わせて評価する。3つの値は同じ方向に動くことが多く、脱水があると貧血が見かけ上隠れることがある</v>
       </c>
       <c r="K47" t="str">
-        <v>鉄欠乏性貧血,抗血小板療法,抗凝固療法（心房細動・血栓症）</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="L47" t="str">
-        <v>ヘモグロビン,Hb,貧血,鉄剤,鉄欠乏性貧血</v>
+        <v>ヘマトクリット,Ht,Hct,貧血,脱水,多血症</v>
       </c>
       <c r="M47" t="str">
         <v>食事と栄養 p.151-164（第2部 貧血）</v>
@@ -2351,40 +2351,40 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ヘマトクリット値</v>
+        <v>MCV</v>
       </c>
       <c r="B48" t="str">
-        <v>Ht,Hct</v>
+        <v>MCV</v>
       </c>
       <c r="C48" t="str">
-        <v>男性 40〜50%、女性 35〜45%</v>
+        <v>79〜100 fL</v>
       </c>
       <c r="D48" t="str">
-        <v>血液全体のうち赤血球が占める体積の割合。貧血・脱水の指標</v>
+        <v>赤血球1個の大きさ</v>
       </c>
       <c r="E48" t="str">
-        <v>ヘマトクリットは、血液全体のうち赤血球が占める割合を表す数値です。この値が低いと貧血、高いと脱水や血液が濃くなっている状態が疑われます。</v>
+        <v>MCVは赤血球1個あたりの大きさを表す数値です。貧血があるとき、この数値で「小さい貧血」か「大きい貧血」かを見分けることができ、原因を絞り込む手がかりになります。</v>
       </c>
       <c r="F48" t="str">
-        <v>脱水、多血症（真性多血症、二次性多血症）、喫煙</v>
+        <v/>
       </c>
       <c r="G48" t="str">
-        <v>脱水が疑われる場合はこまめな水分摂取を勧める（水分制限がある場合を除く）</v>
+        <v/>
       </c>
       <c r="H48" t="str">
-        <v>貧血（鉄欠乏性貧血、腎性貧血など）、出血</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="I48" t="str">
-        <v>ヘモグロビンと同様に、出血や食事量低下がないか確認する</v>
+        <v>鉄分の多い食事を意識する（ヘモグロビンの項目を参照）</v>
       </c>
       <c r="J48" t="str">
-        <v>ヘモグロビン・赤血球数と合わせて評価する。3つの値は同じ方向に動くことが多く、脱水があると貧血が見かけ上隠れることがある</v>
+        <v/>
       </c>
       <c r="K48" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
       <c r="L48" t="str">
-        <v>ヘマトクリット,Ht,Hct,貧血,脱水,多血症</v>
+        <v>MCV,赤血球指数,貧血</v>
       </c>
       <c r="M48" t="str">
         <v>食事と栄養 p.151-164（第2部 貧血）</v>
@@ -2392,19 +2392,19 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>MCV</v>
+        <v>MCH</v>
       </c>
       <c r="B49" t="str">
-        <v>MCV</v>
+        <v>MCH</v>
       </c>
       <c r="C49" t="str">
-        <v>79〜100 fL</v>
+        <v>26.3〜34.3 pg</v>
       </c>
       <c r="D49" t="str">
-        <v>赤血球1個の大きさ</v>
+        <v>赤血球1個に含まれるヘモグロビン量</v>
       </c>
       <c r="E49" t="str">
-        <v>MCVは赤血球1個あたりの大きさを表す数値です。貧血があるとき、この数値で「小さい貧血」か「大きい貧血」かを見分けることができ、原因を絞り込む手がかりになります。</v>
+        <v>MCHは赤血球1個の中に含まれるヘモグロビン（酸素を運ぶ色素）の量を表す数値です。MCVと同じく、貧血の種類を見分けるのに使われます。</v>
       </c>
       <c r="F49" t="str">
         <v/>
@@ -2425,7 +2425,7 @@
         <v>鉄欠乏性貧血</v>
       </c>
       <c r="L49" t="str">
-        <v>MCV,赤血球指数,貧血</v>
+        <v>MCH,赤血球指数,貧血</v>
       </c>
       <c r="M49" t="str">
         <v>食事と栄養 p.151-164（第2部 貧血）</v>
@@ -2433,19 +2433,19 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>MCH</v>
+        <v>MCHC</v>
       </c>
       <c r="B50" t="str">
-        <v>MCH</v>
+        <v>MCHC</v>
       </c>
       <c r="C50" t="str">
-        <v>26.3〜34.3 pg</v>
+        <v>31.6〜36.6 %</v>
       </c>
       <c r="D50" t="str">
-        <v>赤血球1個に含まれるヘモグロビン量</v>
+        <v>単位容積あたりの赤血球に含まれるヘモグロビン濃度</v>
       </c>
       <c r="E50" t="str">
-        <v>MCHは赤血球1個の中に含まれるヘモグロビン（酸素を運ぶ色素）の量を表す数値です。MCVと同じく、貧血の種類を見分けるのに使われます。</v>
+        <v>MCHCは、赤血球の中にヘモグロビンがどれくらい濃く詰まっているかを表す数値です。鉄が不足すると、この濃度も薄くなる傾向があります。</v>
       </c>
       <c r="F50" t="str">
         <v/>
@@ -2466,7 +2466,7 @@
         <v>鉄欠乏性貧血</v>
       </c>
       <c r="L50" t="str">
-        <v>MCH,赤血球指数,貧血</v>
+        <v>MCHC,赤血球指数,貧血</v>
       </c>
       <c r="M50" t="str">
         <v>食事と栄養 p.151-164（第2部 貧血）</v>
@@ -2474,104 +2474,104 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>MCHC</v>
+        <v>血小板数</v>
       </c>
       <c r="B51" t="str">
-        <v>MCHC</v>
+        <v>Plt</v>
       </c>
       <c r="C51" t="str">
-        <v>31.6〜36.6 %</v>
+        <v>15.0〜35.0万/μL程度（施設差あり）</v>
       </c>
       <c r="D51" t="str">
-        <v>単位容積あたりの赤血球に含まれるヘモグロビン濃度</v>
+        <v>出血を止める働きをする血液成分で、少なすぎると出血しやすくなる</v>
       </c>
       <c r="E51" t="str">
-        <v>MCHCは、赤血球の中にヘモグロビンがどれくらい濃く詰まっているかを表す数値です。鉄が不足すると、この濃度も薄くなる傾向があります。</v>
+        <v>血小板は、血管が傷ついたときに集まって血を止める役割をする血液の成分です。数が少ないとあざができやすくなったり、出血が止まりにくくなったりします。抗血小板薬や抗がん剤を使っている方では、定期的にチェックすることが大切です。</v>
       </c>
       <c r="F51" t="str">
-        <v/>
+        <v>炎症性疾患、鉄欠乏性貧血、脾摘後、骨髄増殖性疾患</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、肝硬変・脾機能亢進、再生不良性貧血、抗てんかん薬（バルプロ酸など）の副作用、ITP（特発性血小板減少性紫斑病）</v>
       </c>
       <c r="I51" t="str">
-        <v>鉄分の多い食事を意識する（ヘモグロビンの項目を参照）</v>
+        <v>あざができやすい、歯ぐきや鼻からの出血が増えていないか確認する。強い運動や転倒によるけがに注意するよう伝える</v>
       </c>
       <c r="J51" t="str">
-        <v/>
+        <v>抗血小板薬・抗凝固薬使用中に血小板減少があると出血リスクがさらに高まる。抗がん剤・バルプロ酸・カルバマゼピンなど骨髄抑制のリスクがある薬剤使用中は定期採血の実施状況を確認する</v>
       </c>
       <c r="K51" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>てんかん,抗血小板療法</v>
       </c>
       <c r="L51" t="str">
-        <v>MCHC,赤血球指数,貧血</v>
+        <v>血小板,Plt,platelet,出血,あざ,紫斑,骨髄抑制</v>
       </c>
       <c r="M51" t="str">
-        <v>食事と栄養 p.151-164（第2部 貧血）</v>
+        <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>血小板数</v>
+        <v>RDW-SD</v>
       </c>
       <c r="B52" t="str">
-        <v>Plt</v>
+        <v>RDW-SD</v>
       </c>
       <c r="C52" t="str">
-        <v>15.0〜35.0万/μL程度（施設差あり）</v>
+        <v>39〜46 fL程度（施設差あり）</v>
       </c>
       <c r="D52" t="str">
-        <v>出血を止める働きをする血液成分で、少なすぎると出血しやすくなる</v>
+        <v>赤血球の大きさのばらつきを表す指標(絶対値)。鉄欠乏性貧血などの初期変化を捉えやすい</v>
       </c>
       <c r="E52" t="str">
-        <v>血小板は、血管が傷ついたときに集まって血を止める役割をする血液の成分です。数が少ないとあざができやすくなったり、出血が止まりにくくなったりします。抗血小板薬や抗がん剤を使っている方では、定期的にチェックすることが大切です。</v>
+        <v>RDW-SDは、赤血球の大きさがどれくらいバラバラになっているかを表す数値です。貧血の原因を調べる際、鉄が足りなくなり始めた早い段階での変化を捉えるのに役立ちます。</v>
       </c>
       <c r="F52" t="str">
-        <v>炎症性疾患、鉄欠乏性貧血、脾摘後、骨髄増殖性疾患</v>
+        <v>鉄欠乏性貧血の初期、混合性貧血（複数の原因が重なっている状態）、赤血球産生の乱れ</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、肝硬変・脾機能亢進、再生不良性貧血、抗てんかん薬（バルプロ酸など）の副作用、ITP（特発性血小板減少性紫斑病）</v>
+        <v/>
       </c>
       <c r="I52" t="str">
-        <v>あざができやすい、歯ぐきや鼻からの出血が増えていないか確認する。強い運動や転倒によるけがに注意するよう伝える</v>
+        <v/>
       </c>
       <c r="J52" t="str">
-        <v>抗血小板薬・抗凝固薬使用中に血小板減少があると出血リスクがさらに高まる。抗がん剤・バルプロ酸・カルバマゼピンなど骨髄抑制のリスクがある薬剤使用中は定期採血の実施状況を確認する</v>
+        <v>MCVが正常範囲でもRDWが上昇している場合、鉄欠乏の初期段階を示唆することがある。MCV・MCHと合わせて評価する</v>
       </c>
       <c r="K52" t="str">
-        <v>てんかん,抗血小板療法</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="L52" t="str">
-        <v>血小板,Plt,platelet,出血,あざ,紫斑,骨髄抑制</v>
+        <v>RDW-SD,赤血球分布幅,貧血,鉄欠乏</v>
       </c>
       <c r="M52" t="str">
-        <v/>
+        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>RDW-SD</v>
+        <v>RDW-CV</v>
       </c>
       <c r="B53" t="str">
-        <v>RDW-SD</v>
+        <v>RDW-CV</v>
       </c>
       <c r="C53" t="str">
-        <v>39〜46 fL程度（施設差あり）</v>
+        <v>11.5〜14.5%程度（施設差あり）</v>
       </c>
       <c r="D53" t="str">
-        <v>赤血球の大きさのばらつきを表す指標(絶対値)。鉄欠乏性貧血などの初期変化を捉えやすい</v>
+        <v>赤血球の大きさのばらつきを割合(%)で表した指標</v>
       </c>
       <c r="E53" t="str">
-        <v>RDW-SDは、赤血球の大きさがどれくらいバラバラになっているかを表す数値です。貧血の原因を調べる際、鉄が足りなくなり始めた早い段階での変化を捉えるのに役立ちます。</v>
+        <v>RDW-CVもRDW-SDと同じく、赤血球の大きさのばらつきを表す数値ですが、こちらは割合(%)で示されます。貧血のタイプを見分ける手がかりになります。</v>
       </c>
       <c r="F53" t="str">
-        <v>鉄欠乏性貧血の初期、混合性貧血（複数の原因が重なっている状態）、赤血球産生の乱れ</v>
+        <v>鉄欠乏性貧血、ビタミンB12・葉酸欠乏性貧血、混合性貧血</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2583,13 +2583,13 @@
         <v/>
       </c>
       <c r="J53" t="str">
-        <v>MCVが正常範囲でもRDWが上昇している場合、鉄欠乏の初期段階を示唆することがある。MCV・MCHと合わせて評価する</v>
+        <v>RDW-SDと同様の意味を持つ指標。MCVが小さくRDWが高ければ鉄欠乏性貧血、MCVが大きくRDWが高ければビタミンB12・葉酸欠乏を疑う手がかりになる</v>
       </c>
       <c r="K53" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
       <c r="L53" t="str">
-        <v>RDW-SD,赤血球分布幅,貧血,鉄欠乏</v>
+        <v>RDW-CV,赤血球分布幅,貧血,ビタミンB12,葉酸</v>
       </c>
       <c r="M53" t="str">
         <v>食事と栄養 p.151-164（第2部 貧血）</v>
@@ -2597,81 +2597,81 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>RDW-CV</v>
+        <v>好中球実数値</v>
       </c>
       <c r="B54" t="str">
-        <v>RDW-CV</v>
+        <v>Neutro#,ANC</v>
       </c>
       <c r="C54" t="str">
-        <v>11.5〜14.5%程度（施設差あり）</v>
+        <v>2,000〜7,500 /μL程度（施設差あり、白血球数×好中球%で算出）</v>
       </c>
       <c r="D54" t="str">
-        <v>赤血球の大きさのばらつきを割合(%)で表した指標</v>
+        <v>好中球の絶対数。感染症リスクを判断する上で割合(%)より重要な指標</v>
       </c>
       <c r="E54" t="str">
-        <v>RDW-CVもRDW-SDと同じく、赤血球の大きさのばらつきを表す数値ですが、こちらは割合(%)で示されます。貧血のタイプを見分ける手がかりになります。</v>
+        <v>これは好中球の実際の数を表す数値です。割合(%)だけでなく、実際の数がどれくらいあるかを見ることで、感染症にかかりやすい状態かどうかをより正確に判断できます。</v>
       </c>
       <c r="F54" t="str">
-        <v>鉄欠乏性貧血、ビタミンB12・葉酸欠乏性貧血、混合性貧血</v>
+        <v>細菌感染症、炎症、ステロイド使用</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v/>
+        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、メルカゾールなど薬剤性の無顆粒球症（1,000/μL未満で好中球減少症、500/μL未満で重症感染リスクが著しく上昇）</v>
       </c>
       <c r="I54" t="str">
-        <v/>
+        <v>発熱、のどの痛みなど感染症状の初期サインがないか確認する。人混みを避け、手洗い・うがいを徹底するよう伝える</v>
       </c>
       <c r="J54" t="str">
-        <v>RDW-SDと同様の意味を持つ指標。MCVが小さくRDWが高ければ鉄欠乏性貧血、MCVが大きくRDWが高ければビタミンB12・葉酸欠乏を疑う手がかりになる</v>
+        <v>抗がん剤・メルカゾール・カルバマゼピンなど骨髄抑制のリスクがある薬剤使用中は特に重視すべき数値。500/μL未満は発熱性好中球減少症のリスクが高く緊急性が高い</v>
       </c>
       <c r="K54" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L54" t="str">
-        <v>RDW-CV,赤血球分布幅,貧血,ビタミンB12,葉酸</v>
+        <v>好中球実数値,好中球数,ANC,無顆粒球症,発熱性好中球減少症</v>
       </c>
       <c r="M54" t="str">
-        <v>食事と栄養 p.151-164（第2部 貧血）</v>
+        <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>好中球実数値</v>
+        <v>好酸球実数値</v>
       </c>
       <c r="B55" t="str">
-        <v>Neutro#,ANC</v>
+        <v>Eosino#</v>
       </c>
       <c r="C55" t="str">
-        <v>2,000〜7,500 /μL程度（施設差あり、白血球数×好中球%で算出）</v>
+        <v>100〜500 /μL程度（施設差あり）</v>
       </c>
       <c r="D55" t="str">
-        <v>好中球の絶対数。感染症リスクを判断する上で割合(%)より重要な指標</v>
+        <v>好酸球の絶対数。アレルギーや薬剤反応の程度をより正確に評価できる</v>
       </c>
       <c r="E55" t="str">
-        <v>これは好中球の実際の数を表す数値です。割合(%)だけでなく、実際の数がどれくらいあるかを見ることで、感染症にかかりやすい状態かどうかをより正確に判断できます。</v>
+        <v>これは好酸球の実際の数を表す数値です。割合(%)だけでなく実数を見ることで、アレルギー反応の強さをより正確に把握できます。</v>
       </c>
       <c r="F55" t="str">
-        <v>細菌感染症、炎症、ステロイド使用</v>
+        <v>アレルギー性疾患、薬剤アレルギー、寄生虫感染</v>
       </c>
       <c r="G55" t="str">
-        <v/>
+        <v>新しく始めた薬がないか確認する</v>
       </c>
       <c r="H55" t="str">
-        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、メルカゾールなど薬剤性の無顆粒球症（1,000/μL未満で好中球減少症、500/μL未満で重症感染リスクが著しく上昇）</v>
+        <v/>
       </c>
       <c r="I55" t="str">
-        <v>発熱、のどの痛みなど感染症状の初期サインがないか確認する。人混みを避け、手洗い・うがいを徹底するよう伝える</v>
+        <v/>
       </c>
       <c r="J55" t="str">
-        <v>抗がん剤・メルカゾール・カルバマゼピンなど骨髄抑制のリスクがある薬剤使用中は特に重視すべき数値。500/μL未満は発熱性好中球減少症のリスクが高く緊急性が高い</v>
+        <v>薬剤性過敏症症候群(DIHS)などでは著明な好酸球増多を認めることがあり、原因薬剤の特定に役立つ</v>
       </c>
       <c r="K55" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L55" t="str">
-        <v>好中球実数値,好中球数,ANC,無顆粒球症,発熱性好中球減少症</v>
+        <v>好酸球実数値,好酸球数,アレルギー,DIHS</v>
       </c>
       <c r="M55" t="str">
         <v/>
@@ -2679,25 +2679,25 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>好酸球実数値</v>
+        <v>好塩基球実数値</v>
       </c>
       <c r="B56" t="str">
-        <v>Eosino#</v>
+        <v>Baso#</v>
       </c>
       <c r="C56" t="str">
-        <v>100〜500 /μL程度（施設差あり）</v>
+        <v>0〜100 /μL程度（施設差あり）</v>
       </c>
       <c r="D56" t="str">
-        <v>好酸球の絶対数。アレルギーや薬剤反応の程度をより正確に評価できる</v>
+        <v>好塩基球の絶対数</v>
       </c>
       <c r="E56" t="str">
-        <v>これは好酸球の実際の数を表す数値です。割合(%)だけでなく実数を見ることで、アレルギー反応の強さをより正確に把握できます。</v>
+        <v>これは好塩基球の実際の数を表す数値です。数がとても少ない種類の血球なので、通常は大きな変動を示すことは多くありません。</v>
       </c>
       <c r="F56" t="str">
-        <v>アレルギー性疾患、薬剤アレルギー、寄生虫感染</v>
+        <v>慢性骨髄性白血病などの血液疾患、アレルギー性疾患</v>
       </c>
       <c r="G56" t="str">
-        <v>新しく始めた薬がないか確認する</v>
+        <v/>
       </c>
       <c r="H56" t="str">
         <v/>
@@ -2706,13 +2706,13 @@
         <v/>
       </c>
       <c r="J56" t="str">
-        <v>薬剤性過敏症症候群(DIHS)などでは著明な好酸球増多を認めることがあり、原因薬剤の特定に役立つ</v>
+        <v>単独での臨床的意義は乏しく、他の血球指標（白血球分画全体）と合わせて評価する</v>
       </c>
       <c r="K56" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L56" t="str">
-        <v>好酸球実数値,好酸球数,アレルギー,DIHS</v>
+        <v>好塩基球実数値,好塩基球数</v>
       </c>
       <c r="M56" t="str">
         <v/>
@@ -2720,40 +2720,40 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>好塩基球実数値</v>
+        <v>リンパ球実数値</v>
       </c>
       <c r="B57" t="str">
-        <v>Baso#</v>
+        <v>Lympho#,ALC</v>
       </c>
       <c r="C57" t="str">
-        <v>0〜100 /μL程度（施設差あり）</v>
+        <v>1,000〜3,600 /μL程度（施設差あり）</v>
       </c>
       <c r="D57" t="str">
-        <v>好塩基球の絶対数</v>
+        <v>リンパ球の絶対数。免疫力の目安として使われる</v>
       </c>
       <c r="E57" t="str">
-        <v>これは好塩基球の実際の数を表す数値です。数がとても少ない種類の血球なので、通常は大きな変動を示すことは多くありません。</v>
+        <v>これはリンパ球の実際の数を表す数値です。免疫力の目安の一つとして使われ、抗がん剤や免疫抑制剤の副作用モニタリングにも用いられます。</v>
       </c>
       <c r="F57" t="str">
-        <v>慢性骨髄性白血病などの血液疾患、アレルギー性疾患</v>
+        <v>ウイルス感染症、リンパ性白血病などの血液疾患</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v/>
+        <v>抗がん剤・免疫抑制剤・ステロイドの使用、強いストレス、AIDSなどの免疫不全</v>
       </c>
       <c r="I57" t="str">
-        <v/>
+        <v>感染予防（手洗い・うがい、人混みを避ける）を意識するよう伝える</v>
       </c>
       <c r="J57" t="str">
-        <v>単独での臨床的意義は乏しく、他の血球指標（白血球分画全体）と合わせて評価する</v>
+        <v>免疫抑制剤・抗がん剤治療中のモニタリング指標としても使われる。著明な低下時は日和見感染のリスクが高まる</v>
       </c>
       <c r="K57" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L57" t="str">
-        <v>好塩基球実数値,好塩基球数</v>
+        <v>リンパ球実数値,リンパ球数,ALC,免疫抑制剤,日和見感染</v>
       </c>
       <c r="M57" t="str">
         <v/>
@@ -2761,40 +2761,40 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>リンパ球実数値</v>
+        <v>単球実数値</v>
       </c>
       <c r="B58" t="str">
-        <v>Lympho#,ALC</v>
+        <v>Mono#</v>
       </c>
       <c r="C58" t="str">
-        <v>1,000〜3,600 /μL程度（施設差あり）</v>
+        <v>200〜600 /μL程度（施設差あり）</v>
       </c>
       <c r="D58" t="str">
-        <v>リンパ球の絶対数。免疫力の目安として使われる</v>
+        <v>単球の絶対数</v>
       </c>
       <c r="E58" t="str">
-        <v>これはリンパ球の実際の数を表す数値です。免疫力の目安の一つとして使われ、抗がん剤や免疫抑制剤の副作用モニタリングにも用いられます。</v>
+        <v>これは単球の実際の数を表す数値です。慢性的な炎症や感染症の状態を把握する材料の一つになります。</v>
       </c>
       <c r="F58" t="str">
-        <v>ウイルス感染症、リンパ性白血病などの血液疾患</v>
+        <v>慢性感染症、炎症性疾患、血液疾患</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>抗がん剤・免疫抑制剤・ステロイドの使用、強いストレス、AIDSなどの免疫不全</v>
+        <v/>
       </c>
       <c r="I58" t="str">
-        <v>感染予防（手洗い・うがい、人混みを避ける）を意識するよう伝える</v>
+        <v/>
       </c>
       <c r="J58" t="str">
-        <v>免疫抑制剤・抗がん剤治療中のモニタリング指標としても使われる。著明な低下時は日和見感染のリスクが高まる</v>
+        <v>単独での臨床的意義は乏しく、他の血球指標と合わせて評価する</v>
       </c>
       <c r="K58" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L58" t="str">
-        <v>リンパ球実数値,リンパ球数,ALC,免疫抑制剤,日和見感染</v>
+        <v>単球実数値,単球数</v>
       </c>
       <c r="M58" t="str">
         <v/>
@@ -2802,40 +2802,40 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>単球実数値</v>
+        <v>好中球</v>
       </c>
       <c r="B59" t="str">
-        <v>Mono#</v>
+        <v>Neutro,Neut%</v>
       </c>
       <c r="C59" t="str">
-        <v>200〜600 /μL程度（施設差あり）</v>
+        <v>40〜75%程度（施設差あり）</v>
       </c>
       <c r="D59" t="str">
-        <v>単球の絶対数</v>
+        <v>白血球の中で最も多くを占め、細菌感染と戦う主力の免疫細胞の割合</v>
       </c>
       <c r="E59" t="str">
-        <v>これは単球の実際の数を表す数値です。慢性的な炎症や感染症の状態を把握する材料の一つになります。</v>
+        <v>好中球は、白血球の中で最も数が多く、細菌が体に入ってきたときに真っ先に戦ってくれる免疫細胞です。感染症や炎症があると増え、逆に薬の副作用などで減ることがあります。</v>
       </c>
       <c r="F59" t="str">
-        <v>慢性感染症、炎症性疾患、血液疾患</v>
+        <v>細菌感染症、炎症、ストレス、ステロイド使用</v>
       </c>
       <c r="G59" t="str">
-        <v/>
+        <v>発熱や炎症症状がないか確認する</v>
       </c>
       <c r="H59" t="str">
-        <v/>
+        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、ウイルス感染、メルカゾールなど薬剤性の無顆粒球症</v>
       </c>
       <c r="I59" t="str">
-        <v/>
+        <v>発熱やのどの痛みなど感染症状の初期サインがないか確認する</v>
       </c>
       <c r="J59" t="str">
-        <v>単独での臨床的意義は乏しく、他の血球指標と合わせて評価する</v>
+        <v>好中球の絶対数（好中球実数値）が500/μL未満になると重篤な感染症のリスクが高まる。割合(%)だけでなく実数値も合わせて確認する</v>
       </c>
       <c r="K59" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L59" t="str">
-        <v>単球実数値,単球数</v>
+        <v>好中球,Neutro,Neut,感染症,無顆粒球症</v>
       </c>
       <c r="M59" t="str">
         <v/>
@@ -2843,40 +2843,40 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>好中球</v>
+        <v>好酸球</v>
       </c>
       <c r="B60" t="str">
-        <v>Neutro,Neut%</v>
+        <v>Eosino,Eos%</v>
       </c>
       <c r="C60" t="str">
-        <v>40〜75%程度（施設差あり）</v>
+        <v>1〜5%程度（施設差あり）</v>
       </c>
       <c r="D60" t="str">
-        <v>白血球の中で最も多くを占め、細菌感染と戦う主力の免疫細胞の割合</v>
+        <v>アレルギー反応や寄生虫感染に関わる白血球の一種の割合</v>
       </c>
       <c r="E60" t="str">
-        <v>好中球は、白血球の中で最も数が多く、細菌が体に入ってきたときに真っ先に戦ってくれる免疫細胞です。感染症や炎症があると増え、逆に薬の副作用などで減ることがあります。</v>
+        <v>好酸球は、アレルギー反応や寄生虫感染と関係が深い免疫細胞です。アレルギー性の病気や薬の副作用（薬疹など）で増えることがあります。</v>
       </c>
       <c r="F60" t="str">
-        <v>細菌感染症、炎症、ストレス、ステロイド使用</v>
+        <v>アレルギー性疾患（気管支喘息、アトピー性皮膚炎など）、薬剤アレルギー、寄生虫感染</v>
       </c>
       <c r="G60" t="str">
-        <v>発熱や炎症症状がないか確認する</v>
+        <v>新しく始めた薬がないか確認する。皮疹やかゆみなどアレルギー症状の有無を確認する</v>
       </c>
       <c r="H60" t="str">
-        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、ウイルス感染、メルカゾールなど薬剤性の無顆粒球症</v>
+        <v/>
       </c>
       <c r="I60" t="str">
-        <v>発熱やのどの痛みなど感染症状の初期サインがないか確認する</v>
+        <v/>
       </c>
       <c r="J60" t="str">
-        <v>好中球の絶対数（好中球実数値）が500/μL未満になると重篤な感染症のリスクが高まる。割合(%)だけでなく実数値も合わせて確認する</v>
+        <v>薬剤性の好酸球増多は、原因薬剤の中止で改善することが多い。新規薬剤開始後の皮疹・発熱と合わせて薬剤性過敏症症候群(DIHS)を疑う材料になる</v>
       </c>
       <c r="K60" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L60" t="str">
-        <v>好中球,Neutro,Neut,感染症,無顆粒球症</v>
+        <v>好酸球,Eosino,Eos,アレルギー,薬疹,DIHS</v>
       </c>
       <c r="M60" t="str">
         <v/>
@@ -2884,25 +2884,25 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>好酸球</v>
+        <v>好塩基球</v>
       </c>
       <c r="B61" t="str">
-        <v>Eosino,Eos%</v>
+        <v>Baso,Baso%</v>
       </c>
       <c r="C61" t="str">
-        <v>1〜5%程度（施設差あり）</v>
+        <v>0〜2%程度（施設差あり）</v>
       </c>
       <c r="D61" t="str">
-        <v>アレルギー反応や寄生虫感染に関わる白血球の一種の割合</v>
+        <v>白血球の中で最も数が少なく、アレルギー反応に関わる細胞の割合</v>
       </c>
       <c r="E61" t="str">
-        <v>好酸球は、アレルギー反応や寄生虫感染と関係が深い免疫細胞です。アレルギー性の病気や薬の副作用（薬疹など）で増えることがあります。</v>
+        <v>好塩基球は白血球の中で最も数が少ない種類で、アレルギー反応や炎症に関わっています。数値の変動が病気の診断に直接使われることは少ない検査です。</v>
       </c>
       <c r="F61" t="str">
-        <v>アレルギー性疾患（気管支喘息、アトピー性皮膚炎など）、薬剤アレルギー、寄生虫感染</v>
+        <v>慢性骨髄性白血病などの血液疾患、アレルギー性疾患、甲状腺機能低下症</v>
       </c>
       <c r="G61" t="str">
-        <v>新しく始めた薬がないか確認する。皮疹やかゆみなどアレルギー症状の有無を確認する</v>
+        <v/>
       </c>
       <c r="H61" t="str">
         <v/>
@@ -2911,13 +2911,13 @@
         <v/>
       </c>
       <c r="J61" t="str">
-        <v>薬剤性の好酸球増多は、原因薬剤の中止で改善することが多い。新規薬剤開始後の皮疹・発熱と合わせて薬剤性過敏症症候群(DIHS)を疑う材料になる</v>
+        <v>単独での臨床的意義は乏しいが、著明な増加は血液疾患（慢性骨髄性白血病等）の可能性があり他の血球指標と合わせて評価する</v>
       </c>
       <c r="K61" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L61" t="str">
-        <v>好酸球,Eosino,Eos,アレルギー,薬疹,DIHS</v>
+        <v>好塩基球,Baso,アレルギー,白血病</v>
       </c>
       <c r="M61" t="str">
         <v/>
@@ -2925,40 +2925,40 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>好塩基球</v>
+        <v>リンパ球</v>
       </c>
       <c r="B62" t="str">
-        <v>Baso,Baso%</v>
+        <v>Lympho,Lym%</v>
       </c>
       <c r="C62" t="str">
-        <v>0〜2%程度（施設差あり）</v>
+        <v>18〜49%程度（施設差あり）</v>
       </c>
       <c r="D62" t="str">
-        <v>白血球の中で最も数が少なく、アレルギー反応に関わる細胞の割合</v>
+        <v>ウイルス感染と戦い、免疫の記憶を担う白血球の割合</v>
       </c>
       <c r="E62" t="str">
-        <v>好塩基球は白血球の中で最も数が少ない種類で、アレルギー反応や炎症に関わっています。数値の変動が病気の診断に直接使われることは少ない検査です。</v>
+        <v>リンパ球は、ウイルスと戦ったり、一度かかった病気を記憶して免疫をつくったりする細胞です。ウイルス感染で増え、抗がん剤の副作用や強いストレスで減ることがあります。</v>
       </c>
       <c r="F62" t="str">
-        <v>慢性骨髄性白血病などの血液疾患、アレルギー性疾患、甲状腺機能低下症</v>
+        <v>ウイルス感染症、リンパ性白血病などの血液疾患、百日咳</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v/>
+        <v>抗がん剤・免疫抑制剤・ステロイドの使用、強いストレス、AIDSなどの免疫不全</v>
       </c>
       <c r="I62" t="str">
-        <v/>
+        <v>免疫が下がっている可能性があるため、感染予防（手洗い・うがい、人混みを避ける）を意識するよう伝える</v>
       </c>
       <c r="J62" t="str">
-        <v>単独での臨床的意義は乏しいが、著明な増加は血液疾患（慢性骨髄性白血病等）の可能性があり他の血球指標と合わせて評価する</v>
+        <v>ステロイド・免疫抑制剤使用中はリンパ球減少による易感染性に注意。好中球と逆方向に動くことが多い（ウイルス感染ではリンパ球優位、細菌感染では好中球優位になりやすい）</v>
       </c>
       <c r="K62" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L62" t="str">
-        <v>好塩基球,Baso,アレルギー,白血病</v>
+        <v>リンパ球,Lympho,Lym,ウイルス感染,免疫抑制剤,ステロイド</v>
       </c>
       <c r="M62" t="str">
         <v/>
@@ -2966,40 +2966,40 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>リンパ球</v>
+        <v>単球</v>
       </c>
       <c r="B63" t="str">
-        <v>Lympho,Lym%</v>
+        <v>Mono,Mono%</v>
       </c>
       <c r="C63" t="str">
-        <v>18〜49%程度（施設差あり）</v>
+        <v>2〜10%程度（施設差あり）</v>
       </c>
       <c r="D63" t="str">
-        <v>ウイルス感染と戦い、免疫の記憶を担う白血球の割合</v>
+        <v>感染や炎症の後始末をする白血球の一種の割合</v>
       </c>
       <c r="E63" t="str">
-        <v>リンパ球は、ウイルスと戦ったり、一度かかった病気を記憶して免疫をつくったりする細胞です。ウイルス感染で増え、抗がん剤の副作用や強いストレスで減ることがあります。</v>
+        <v>単球は、細菌などを取り込んで処理したり、組織の修復に関わったりする免疫細胞です。慢性的な炎症や感染症の回復期に増えることがあります。</v>
       </c>
       <c r="F63" t="str">
-        <v>ウイルス感染症、リンパ性白血病などの血液疾患、百日咳</v>
+        <v>慢性感染症（結核など）、炎症性疾患、血液疾患、感染症の回復期</v>
       </c>
       <c r="G63" t="str">
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>抗がん剤・免疫抑制剤・ステロイドの使用、強いストレス、AIDSなどの免疫不全</v>
+        <v/>
       </c>
       <c r="I63" t="str">
-        <v>免疫が下がっている可能性があるため、感染予防（手洗い・うがい、人混みを避ける）を意識するよう伝える</v>
+        <v/>
       </c>
       <c r="J63" t="str">
-        <v>ステロイド・免疫抑制剤使用中はリンパ球減少による易感染性に注意。好中球と逆方向に動くことが多い（ウイルス感染ではリンパ球優位、細菌感染では好中球優位になりやすい）</v>
+        <v>単独での臨床的意義は乏しく、他の血球指標や炎症マーカー(CRPなど)と合わせて評価する</v>
       </c>
       <c r="K63" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="L63" t="str">
-        <v>リンパ球,Lympho,Lym,ウイルス感染,免疫抑制剤,ステロイド</v>
+        <v>単球,Mono,慢性感染症,結核,炎症</v>
       </c>
       <c r="M63" t="str">
         <v/>
@@ -3007,107 +3007,107 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>単球</v>
+        <v>PT-INR（プロトロンビン時間国際標準比）</v>
       </c>
       <c r="B64" t="str">
-        <v>Mono,Mono%</v>
+        <v>PT-INR,INR</v>
       </c>
       <c r="C64" t="str">
-        <v>2〜10%程度（施設差あり）</v>
+        <v>治療域の目安 1.6〜3.0（ワルファリン服用時。年齢・疾患により異なる）</v>
       </c>
       <c r="D64" t="str">
-        <v>感染や炎症の後始末をする白血球の一種の割合</v>
+        <v>血液の固まりやすさを表す数値で、ワルファリンの効き具合を確認するために使う</v>
       </c>
       <c r="E64" t="str">
-        <v>単球は、細菌などを取り込んで処理したり、組織の修復に関わったりする免疫細胞です。慢性的な炎症や感染症の回復期に増えることがあります。</v>
+        <v>PT-INRは血液が固まるまでの時間をもとにした数値で、ワルファリンというお薬を飲んでいる方の効き具合を確認するために測ります。数値が高いほど血液が固まりにくく出血しやすい状態、低いほど血栓ができやすい状態を示します。</v>
       </c>
       <c r="F64" t="str">
-        <v>慢性感染症（結核など）、炎症性疾患、血液疾患、感染症の回復期</v>
+        <v>ワルファリンの効きすぎ、肝機能低下、ビタミンK不足、納豆・青汁など摂取量の変化</v>
       </c>
       <c r="G64" t="str">
-        <v/>
+        <v>歯ぐきや鼻からの出血、あざ、黒い便などの出血症状がないか確認する。納豆・クロレラ・青汁などビタミンKを多く含む食品の摂取状況を確認する</v>
       </c>
       <c r="H64" t="str">
-        <v/>
+        <v>ワルファリンの効き不足、飲み忘れ、ビタミンK摂取量の急激な増加</v>
       </c>
       <c r="I64" t="str">
-        <v/>
+        <v>服薬状況（飲み忘れ）を確認する。片側のむくみ・しびれ・胸痛など血栓症状がないか確認する</v>
       </c>
       <c r="J64" t="str">
-        <v>単独での臨床的意義は乏しく、他の血球指標や炎症マーカー(CRPなど)と合わせて評価する</v>
+        <v>治療域は疾患・年齢によって異なる（例：非弁膜症性心房細動の高齢者では1.6〜2.6が目安になることが多い）。多くの薬剤・食品と相互作用があるため新規薬剤追加時は必ず確認する。DOAC（エリキュース、リクシアナ、プラザキサなど）ではPT-INRのモニタリングは不要</v>
       </c>
       <c r="K64" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>抗凝固療法（心房細動・血栓症）</v>
       </c>
       <c r="L64" t="str">
-        <v>単球,Mono,慢性感染症,結核,炎症</v>
+        <v>PT-INR,INR,プロトロンビン時間,ワルファリン,ワーファリン,抗凝固</v>
       </c>
       <c r="M64" t="str">
-        <v/>
+        <v>食事と栄養 p.221（心疾患Q93 ワルファリン服用中のビタミンK摂取）</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>PT-INR（プロトロンビン時間国際標準比）</v>
+        <v>C反応性蛋白（CRP）</v>
       </c>
       <c r="B65" t="str">
-        <v>PT-INR,INR</v>
+        <v>CRP</v>
       </c>
       <c r="C65" t="str">
-        <v>治療域の目安 1.6〜3.0（ワルファリン服用時。年齢・疾患により異なる）</v>
+        <v>0.3 mg/dL未満（施設差あり）</v>
       </c>
       <c r="D65" t="str">
-        <v>血液の固まりやすさを表す数値で、ワルファリンの効き具合を確認するために使う</v>
+        <v>体のどこかに炎症や感染が起きていないかを鋭敏に反映する数値</v>
       </c>
       <c r="E65" t="str">
-        <v>PT-INRは血液が固まるまでの時間をもとにした数値で、ワルファリンというお薬を飲んでいる方の効き具合を確認するために測ります。数値が高いほど血液が固まりにくく出血しやすい状態、低いほど血栓ができやすい状態を示します。</v>
+        <v>CRPは、体に炎症や感染が起きると数時間〜半日程度で急激に上昇する数値です。風邪のようなウイルス感染から細菌感染、体のどこかの炎症まで、幅広く反応するため、体調の変化を早期に捉える手がかりになります。</v>
       </c>
       <c r="F65" t="str">
-        <v>ワルファリンの効きすぎ、肝機能低下、ビタミンK不足、納豆・青汁など摂取量の変化</v>
+        <v>細菌感染症、ウイルス感染症、自己免疫疾患（関節リウマチなど）、悪性腫瘍、組織の損傷（術後・心筋梗塞など）</v>
       </c>
       <c r="G65" t="str">
-        <v>歯ぐきや鼻からの出血、あざ、黒い便などの出血症状がないか確認する。納豆・クロレラ・青汁などビタミンKを多く含む食品の摂取状況を確認する</v>
+        <v>発熱、痛み、腫れなど炎症症状の有無を確認する</v>
       </c>
       <c r="H65" t="str">
-        <v>ワルファリンの効き不足、飲み忘れ、ビタミンK摂取量の急激な増加</v>
+        <v/>
       </c>
       <c r="I65" t="str">
-        <v>服薬状況（飲み忘れ）を確認する。片側のむくみ・しびれ・胸痛など血栓症状がないか確認する</v>
+        <v/>
       </c>
       <c r="J65" t="str">
-        <v>治療域は疾患・年齢によって異なる（例：非弁膜症性心房細動の高齢者では1.6〜2.6が目安になることが多い）。多くの薬剤・食品と相互作用があるため新規薬剤追加時は必ず確認する。DOAC（エリキュース、リクシアナ、プラザキサなど）ではPT-INRのモニタリングは不要</v>
+        <v>白血球数と合わせて感染・炎症の程度を評価する。上昇・低下のタイミングは白血球より半日〜1日程度遅れる傾向があるため、経過を追う際は採血のタイミングに注意</v>
       </c>
       <c r="K65" t="str">
-        <v>抗凝固療法（心房細動・血栓症）</v>
+        <v/>
       </c>
       <c r="L65" t="str">
-        <v>PT-INR,INR,プロトロンビン時間,ワルファリン,ワーファリン,抗凝固</v>
+        <v>CRP,炎症,感染</v>
       </c>
       <c r="M65" t="str">
-        <v>食事と栄養 p.221（心疾患Q93 ワルファリン服用中のビタミンK摂取）</v>
+        <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>C反応性蛋白（CRP）</v>
+        <v>骨型酒石酸抵抗性フォスファターゼ（TRACP-5b）</v>
       </c>
       <c r="B66" t="str">
-        <v>CRP</v>
+        <v>TRACP-5b</v>
       </c>
       <c r="C66" t="str">
-        <v>0.3 mg/dL未満（施設差あり）</v>
+        <v>120〜420 mU/dL</v>
       </c>
       <c r="D66" t="str">
-        <v>体のどこかに炎症や感染が起きていないかを鋭敏に反映する数値</v>
+        <v>骨がどれくらい壊されているかを見る検査。骨は「古い骨を壊して新しい骨を作る」入れ替えを繰り返しており、骨を壊す細胞が活発だとこの物質が血液中に増える。</v>
       </c>
       <c r="E66" t="str">
-        <v>CRPは、体に炎症や感染が起きると数時間〜半日程度で急激に上昇する数値です。風邪のようなウイルス感染から細菌感染、体のどこかの炎症まで、幅広く反応するため、体調の変化を早期に捉える手がかりになります。</v>
+        <v>この検査は、骨がどれくらい早く減っていないかを見るものです。数値が高いと、骨が弱くなりやすい状態の目安になります。</v>
       </c>
       <c r="F66" t="str">
-        <v>細菌感染症、ウイルス感染症、自己免疫疾患（関節リウマチなど）、悪性腫瘍、組織の損傷（術後・心筋梗塞など）</v>
+        <v>骨粗鬆症、骨代謝回転（骨がこわれるスピード）が活発な状態</v>
       </c>
       <c r="G66" t="str">
-        <v>発熱、痛み、腫れなど炎症症状の有無を確認する</v>
+        <v>カルシウム・ビタミンDの摂取や、適度な荷重運動（ウォーキングなど）を意識するよう伝える</v>
       </c>
       <c r="H66" t="str">
         <v/>
@@ -3116,13 +3116,13 @@
         <v/>
       </c>
       <c r="J66" t="str">
-        <v>白血球数と合わせて感染・炎症の程度を評価する。上昇・低下のタイミングは白血球より半日〜1日程度遅れる傾向があるため、経過を追う際は採血のタイミングに注意</v>
+        <v>「骨を壊す側」の指標。「骨を作る側」の検査と合わせて評価する。数値だけで診断はしない</v>
       </c>
       <c r="K66" t="str">
-        <v/>
+        <v>骨粗鬆症</v>
       </c>
       <c r="L66" t="str">
-        <v>CRP,炎症,感染</v>
+        <v>TRACP-5b,骨型酒石酸抵抗性フォスファターゼ,骨粗鬆症,骨代謝</v>
       </c>
       <c r="M66" t="str">
         <v/>
@@ -3130,40 +3130,40 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>骨型酒石酸抵抗性フォスファターゼ（TRACP-5b）</v>
+        <v>骨型アルカリフォスファターゼ</v>
       </c>
       <c r="B67" t="str">
-        <v>TRACP-5b</v>
+        <v>BAP</v>
       </c>
       <c r="C67" t="str">
-        <v>120〜420 mU/dL</v>
+        <v>男性 3.7〜20.9 μg/L、女性（閉経前）2.9〜14.5 μg/L（施設差あり）</v>
       </c>
       <c r="D67" t="str">
-        <v>骨がどれくらい壊されているかを見る検査。骨は「古い骨を壊して新しい骨を作る」入れ替えを繰り返しており、骨を壊す細胞が活発だとこの物質が血液中に増える。</v>
+        <v>ALPのうち骨に由来する成分だけを測定し、骨が作られる勢い（骨形成）を反映する</v>
       </c>
       <c r="E67" t="str">
-        <v>この検査は、骨がどれくらい早く減っていないかを見るものです。数値が高いと、骨が弱くなりやすい状態の目安になります。</v>
+        <v>骨型ALPは、通常のALP（アルカリホスファターゼ）の中でも、骨で作られる成分だけを選んで測定するものです。骨を新しく作る働きがどれくらい活発かを見る指標として、骨粗鬆症の治療効果判定などに使われます。</v>
       </c>
       <c r="F67" t="str">
-        <v>骨粗鬆症、骨代謝回転（骨がこわれるスピード）が活発な状態</v>
+        <v>骨代謝回転の亢進（骨粗鬆症、骨折治癒過程、骨形成促進薬による治療効果、Paget病、骨転移）</v>
       </c>
       <c r="G67" t="str">
-        <v>カルシウム・ビタミンDの摂取や、適度な荷重運動（ウォーキングなど）を意識するよう伝える</v>
+        <v/>
       </c>
       <c r="H67" t="str">
-        <v/>
+        <v>骨形成の低下</v>
       </c>
       <c r="I67" t="str">
         <v/>
       </c>
       <c r="J67" t="str">
-        <v>「骨を壊す側」の指標。「骨を作る側」の検査と合わせて評価する。数値だけで診断はしない</v>
+        <v>通常のALPと異なり肝臓の影響を受けにくいため、肝機能異常がある患者でも骨代謝を評価しやすい。P1NPと同じ「骨を作る側」の指標で、骨形成促進薬（テリパラチド等）の効果判定に使われる</v>
       </c>
       <c r="K67" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="L67" t="str">
-        <v>TRACP-5b,骨型酒石酸抵抗性フォスファターゼ,骨粗鬆症,骨代謝</v>
+        <v>骨型ALP,BAP,骨型アルカリフォスファターゼ,骨形成マーカー</v>
       </c>
       <c r="M67" t="str">
         <v/>
@@ -3171,122 +3171,122 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>骨型アルカリフォスファターゼ</v>
+        <v>25-ヒドロキシビタミンD</v>
       </c>
       <c r="B68" t="str">
-        <v>BAP</v>
+        <v>25(OH)D</v>
       </c>
       <c r="C68" t="str">
-        <v>男性 3.7〜20.9 μg/L、女性（閉経前）2.9〜14.5 μg/L（施設差あり）</v>
+        <v>30 ng/mL以上：充足、20〜30 ng/mL：不足、20 ng/mL未満：欠乏（施設差あり）</v>
       </c>
       <c r="D68" t="str">
-        <v>ALPのうち骨に由来する成分だけを測定し、骨が作られる勢い（骨形成）を反映する</v>
+        <v>体内のビタミンDの蓄え具合を反映する指標。カルシウムの吸収や骨の健康に関わる</v>
       </c>
       <c r="E68" t="str">
-        <v>骨型ALPは、通常のALP（アルカリホスファターゼ）の中でも、骨で作られる成分だけを選んで測定するものです。骨を新しく作る働きがどれくらい活発かを見る指標として、骨粗鬆症の治療効果判定などに使われます。</v>
+        <v>この検査は、体の中にビタミンDがどれくらい蓄えられているかを見るものです。ビタミンDは、食事から摂ったカルシウムを腸で吸収するのを助ける働きがあり、不足すると骨がもろくなりやすくなります。</v>
       </c>
       <c r="F68" t="str">
-        <v>骨代謝回転の亢進（骨粗鬆症、骨折治癒過程、骨形成促進薬による治療効果、Paget病、骨転移）</v>
+        <v>ビタミンD製剤の過剰摂取</v>
       </c>
       <c r="G68" t="str">
-        <v/>
+        <v>活性型ビタミンD3製剤やサプリメントの摂取量を確認する。高カルシウム血症の症状（吐き気、便秘、多尿など）がないか確認する</v>
       </c>
       <c r="H68" t="str">
-        <v>骨形成の低下</v>
+        <v>日光暴露不足、食事摂取不足、高齢、腸疾患による吸収不良、肝・腎機能低下（活性化障害）</v>
       </c>
       <c r="I68" t="str">
-        <v/>
+        <v>適度な日光浴、魚類・きのこ類などビタミンDを多く含む食品の摂取を意識するとよいことを伝える</v>
       </c>
       <c r="J68" t="str">
-        <v>通常のALPと異なり肝臓の影響を受けにくいため、肝機能異常がある患者でも骨代謝を評価しやすい。P1NPと同じ「骨を作る側」の指標で、骨形成促進薬（テリパラチド等）の効果判定に使われる</v>
+        <v>骨粗鬆症治療における活性型ビタミンD3製剤の効果判定や、投与量調整の参考に用いられる。腎機能低下患者では活性化障害により25(OH)Dが正常でも活性型が不足することがある点に注意</v>
       </c>
       <c r="K68" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="L68" t="str">
-        <v>骨型ALP,BAP,骨型アルカリフォスファターゼ,骨形成マーカー</v>
+        <v>25(OH)D,ビタミンD,25-ヒドロキシビタミンD,ビタミンD欠乏,骨粗鬆症</v>
       </c>
       <c r="M68" t="str">
-        <v/>
+        <v>食事と栄養 p.38（ビタミンD）</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>25-ヒドロキシビタミンD</v>
+        <v>尿pH</v>
       </c>
       <c r="B69" t="str">
-        <v>25(OH)D</v>
+        <v>尿pH</v>
       </c>
       <c r="C69" t="str">
-        <v>30 ng/mL以上：充足、20〜30 ng/mL：不足、20 ng/mL未満：欠乏（施設差あり）</v>
+        <v>4.5〜7.5程度（弱酸性が多い）</v>
       </c>
       <c r="D69" t="str">
-        <v>体内のビタミンDの蓄え具合を反映する指標。カルシウムの吸収や骨の健康に関わる</v>
+        <v>尿の酸性・アルカリ性の度合い。食事や感染症、体の状態を反映する</v>
       </c>
       <c r="E69" t="str">
-        <v>この検査は、体の中にビタミンDがどれくらい蓄えられているかを見るものです。ビタミンDは、食事から摂ったカルシウムを腸で吸収するのを助ける働きがあり、不足すると骨がもろくなりやすくなります。</v>
+        <v>尿のpHは酸性・アルカリ性のバランスを表します。食事の内容や感染症、体の代謝状態によって変化します。単独で大きな問題を示すことは少ない検査です。</v>
       </c>
       <c r="F69" t="str">
-        <v>ビタミンD製剤の過剰摂取</v>
+        <v>尿路感染症（尿素分解菌によるもの）、野菜中心の食事、過換気</v>
       </c>
       <c r="G69" t="str">
-        <v>活性型ビタミンD3製剤やサプリメントの摂取量を確認する。高カルシウム血症の症状（吐き気、便秘、多尿など）がないか確認する</v>
+        <v/>
       </c>
       <c r="H69" t="str">
-        <v>日光暴露不足、食事摂取不足、高齢、腸疾患による吸収不良、肝・腎機能低下（活性化障害）</v>
+        <v>高たんぱく食、糖尿病性ケトアシドーシス、痛風発作時（酸性尿は尿酸結石のリスクを高める）</v>
       </c>
       <c r="I69" t="str">
-        <v>適度な日光浴、魚類・きのこ類などビタミンDを多く含む食品の摂取を意識するとよいことを伝える</v>
+        <v>痛風・尿酸結石がある場合は、野菜など尿をアルカリ化する食品を意識するとよいことを伝える</v>
       </c>
       <c r="J69" t="str">
-        <v>骨粗鬆症治療における活性型ビタミンD3製剤の効果判定や、投与量調整の参考に用いられる。腎機能低下患者では活性化障害により25(OH)Dが正常でも活性型が不足することがある点に注意</v>
+        <v>高尿酸血症・尿酸結石の患者では尿pHが酸性に傾いていないか確認する。尿アルカリ化薬（ウラリットなど）の効果判定にも使う</v>
       </c>
       <c r="K69" t="str">
-        <v>骨粗鬆症</v>
+        <v>高尿酸血症</v>
       </c>
       <c r="L69" t="str">
-        <v>25(OH)D,ビタミンD,25-ヒドロキシビタミンD,ビタミンD欠乏,骨粗鬆症</v>
+        <v>尿pH,尿酸性度,尿アルカリ化,ウラリット</v>
       </c>
       <c r="M69" t="str">
-        <v>食事と栄養 p.38（ビタミンD）</v>
+        <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>尿pH</v>
+        <v>尿ケトン体</v>
       </c>
       <c r="B70" t="str">
-        <v>尿pH</v>
+        <v>尿ケトン,Ket</v>
       </c>
       <c r="C70" t="str">
-        <v>4.5〜7.5程度（弱酸性が多い）</v>
+        <v>陰性（－）</v>
       </c>
       <c r="D70" t="str">
-        <v>尿の酸性・アルカリ性の度合い。食事や感染症、体の状態を反映する</v>
+        <v>体がブドウ糖の代わりに脂肪を分解してエネルギーを作っているサイン</v>
       </c>
       <c r="E70" t="str">
-        <v>尿のpHは酸性・アルカリ性のバランスを表します。食事の内容や感染症、体の代謝状態によって変化します。単独で大きな問題を示すことは少ない検査です。</v>
+        <v>この検査は、体が糖の代わりに脂肪を使ってエネルギーを作っていないかを見るものです。陽性が続くときは、食事や水分、インスリンの使い方を確認する必要があります。</v>
       </c>
       <c r="F70" t="str">
-        <v>尿路感染症（尿素分解菌によるもの）、野菜中心の食事、過換気</v>
+        <v>糖尿病の血糖コントロール不良（シックデイ・インスリン不足）、極端な糖質制限、絶食、嘔吐・下痢による脱水</v>
       </c>
       <c r="G70" t="str">
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>高たんぱく食、糖尿病性ケトアシドーシス、痛風発作時（酸性尿は尿酸結石のリスクを高める）</v>
+        <v/>
       </c>
       <c r="I70" t="str">
-        <v>痛風・尿酸結石がある場合は、野菜など尿をアルカリ化する食品を意識するとよいことを伝える</v>
+        <v/>
       </c>
       <c r="J70" t="str">
-        <v>高尿酸血症・尿酸結石の患者では尿pHが酸性に傾いていないか確認する。尿アルカリ化薬（ウラリットなど）の効果判定にも使う</v>
+        <v>陽性かつ高血糖・全身倦怠感が強い場合は糖尿病性ケトアシドーシスの可能性があり緊急性が高い。シックデイルールの説明歴を確認する</v>
       </c>
       <c r="K70" t="str">
-        <v>高尿酸血症</v>
+        <v>糖尿病</v>
       </c>
       <c r="L70" t="str">
-        <v>尿pH,尿酸性度,尿アルカリ化,ウラリット</v>
+        <v>尿ケトン体,ケトン体,Ket,シックデイ,ケトアシドーシス</v>
       </c>
       <c r="M70" t="str">
         <v/>
@@ -3294,40 +3294,40 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>尿ケトン体</v>
+        <v>ウロビリノーゲン</v>
       </c>
       <c r="B71" t="str">
-        <v>尿ケトン,Ket</v>
+        <v>Uro</v>
       </c>
       <c r="C71" t="str">
-        <v>陰性（－）</v>
+        <v>正常（±）程度</v>
       </c>
       <c r="D71" t="str">
-        <v>体がブドウ糖の代わりに脂肪を分解してエネルギーを作っているサイン</v>
+        <v>肝臓や胆道、赤血球の壊れ方の状態を反映する尿検査項目</v>
       </c>
       <c r="E71" t="str">
-        <v>この検査は、体が糖の代わりに脂肪を使ってエネルギーを作っていないかを見るものです。陽性が続くときは、食事や水分、インスリンの使い方を確認する必要があります。</v>
+        <v>ウロビリノーゲンは、赤血球やビリルビンが体の中で処理される過程でできる物質です。肝臓の働きが悪くなったり、赤血球が壊れやすくなったりすると、尿の中の量が変化します。</v>
       </c>
       <c r="F71" t="str">
-        <v>糖尿病の血糖コントロール不良（シックデイ・インスリン不足）、極端な糖質制限、絶食、嘔吐・下痢による脱水</v>
+        <v>溶血性疾患（赤血球の破壊亢進）、肝機能障害</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v/>
+        <v>胆道閉塞（胆汁が腸に流れず、ウロビリノーゲンが作られない状態）</v>
       </c>
       <c r="I71" t="str">
         <v/>
       </c>
       <c r="J71" t="str">
-        <v>陽性かつ高血糖・全身倦怠感が強い場合は糖尿病性ケトアシドーシスの可能性があり緊急性が高い。シックデイルールの説明歴を確認する</v>
+        <v>完全に陰性の場合は胆道閉塞を疑う所見の一つ。肝機能（AST/ALT/ビリルビン）と合わせて評価する</v>
       </c>
       <c r="K71" t="str">
-        <v>糖尿病</v>
+        <v>肝機能</v>
       </c>
       <c r="L71" t="str">
-        <v>尿ケトン体,ケトン体,Ket,シックデイ,ケトアシドーシス</v>
+        <v>ウロビリノーゲン,Uro,溶血,胆道閉塞,肝機能</v>
       </c>
       <c r="M71" t="str">
         <v/>
@@ -3335,40 +3335,40 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>ウロビリノーゲン</v>
+        <v>尿潜血反応</v>
       </c>
       <c r="B72" t="str">
-        <v>Uro</v>
+        <v>尿潜血,U-OB</v>
       </c>
       <c r="C72" t="str">
-        <v>正常（±）程度</v>
+        <v>陰性（－）</v>
       </c>
       <c r="D72" t="str">
-        <v>肝臓や胆道、赤血球の壊れ方の状態を反映する尿検査項目</v>
+        <v>尿に血液（赤血球）が混じっていないかを見る検査</v>
       </c>
       <c r="E72" t="str">
-        <v>ウロビリノーゲンは、赤血球やビリルビンが体の中で処理される過程でできる物質です。肝臓の働きが悪くなったり、赤血球が壊れやすくなったりすると、尿の中の量が変化します。</v>
+        <v>この検査は、尿に目に見えないくらいの微量の血液が混じっていないかを調べるものです。陽性の場合、腎臓や膀胱、尿路のどこかに炎症や結石などがある可能性があります。</v>
       </c>
       <c r="F72" t="str">
-        <v>溶血性疾患（赤血球の破壊亢進）、肝機能障害</v>
+        <v>尿路結石、膀胱炎などの尿路感染症、腎炎、腫瘍、月経血の混入、激しい運動後</v>
       </c>
       <c r="G72" t="str">
-        <v/>
+        <v>排尿時の痛みや頻尿、目に見える血尿の有無を確認する。女性は月経の時期と重なっていないか確認する</v>
       </c>
       <c r="H72" t="str">
-        <v>胆道閉塞（胆汁が腸に流れず、ウロビリノーゲンが作られない状態）</v>
+        <v/>
       </c>
       <c r="I72" t="str">
         <v/>
       </c>
       <c r="J72" t="str">
-        <v>完全に陰性の場合は胆道閉塞を疑う所見の一つ。肝機能（AST/ALT/ビリルビン）と合わせて評価する</v>
+        <v>陽性でも尿沈渣で赤血球が確認されない場合は偽陽性（ミオグロビン尿など）のこともある。持続する場合は泌尿器科的な精査が必要</v>
       </c>
       <c r="K72" t="str">
-        <v>肝機能</v>
+        <v>腎機能</v>
       </c>
       <c r="L72" t="str">
-        <v>ウロビリノーゲン,Uro,溶血,胆道閉塞,肝機能</v>
+        <v>尿潜血,潜血反応,U-OB,血尿,尿路結石,膀胱炎</v>
       </c>
       <c r="M72" t="str">
         <v/>
@@ -3376,25 +3376,25 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>尿潜血反応</v>
+        <v>尿糖（半定量）</v>
       </c>
       <c r="B73" t="str">
-        <v>尿潜血,U-OB</v>
+        <v>尿糖,U-Glu</v>
       </c>
       <c r="C73" t="str">
         <v>陰性（－）</v>
       </c>
       <c r="D73" t="str">
-        <v>尿に血液（赤血球）が混じっていないかを見る検査</v>
+        <v>尿に糖が漏れ出ていないかを見る検査。血糖値がかなり高いと陽性になる</v>
       </c>
       <c r="E73" t="str">
-        <v>この検査は、尿に目に見えないくらいの微量の血液が混じっていないかを調べるものです。陽性の場合、腎臓や膀胱、尿路のどこかに炎症や結石などがある可能性があります。</v>
+        <v>通常、糖は尿にはほとんど出ませんが、血糖値がかなり高くなると尿にあふれ出るようになります。血糖コントロールの目安の一つです。</v>
       </c>
       <c r="F73" t="str">
-        <v>尿路結石、膀胱炎などの尿路感染症、腎炎、腫瘍、月経血の混入、激しい運動後</v>
+        <v>糖尿病（血糖値が腎臓で再吸収できる量を超えている状態）、腎性糖尿（血糖値が正常でも体質的に出ることがある）、SGLT2阻害薬服用中（薬の作用で意図的に糖を排泄するため陽性になるのが正常）</v>
       </c>
       <c r="G73" t="str">
-        <v>排尿時の痛みや頻尿、目に見える血尿の有無を確認する。女性は月経の時期と重なっていないか確認する</v>
+        <v>SGLT2阻害薬（フォシーガ、ジャディアンスなど）服用中は、陽性が薬の効果によるものであることを説明する。脱水や尿路感染の症状がないかも確認する</v>
       </c>
       <c r="H73" t="str">
         <v/>
@@ -3403,13 +3403,13 @@
         <v/>
       </c>
       <c r="J73" t="str">
-        <v>陽性でも尿沈渣で赤血球が確認されない場合は偽陽性（ミオグロビン尿など）のこともある。持続する場合は泌尿器科的な精査が必要</v>
+        <v>SGLT2阻害薬服用中は尿糖陽性が治療効果として想定内であることを患者に伝える。血糖値・HbA1cと合わせて評価する</v>
       </c>
       <c r="K73" t="str">
-        <v>腎機能</v>
+        <v>糖尿病</v>
       </c>
       <c r="L73" t="str">
-        <v>尿潜血,潜血反応,U-OB,血尿,尿路結石,膀胱炎</v>
+        <v>尿糖,糖半定量,U-Glu,腎性糖尿,SGLT2</v>
       </c>
       <c r="M73" t="str">
         <v/>
@@ -3417,25 +3417,25 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>尿糖（半定量）</v>
+        <v>尿蛋白定量</v>
       </c>
       <c r="B74" t="str">
-        <v>尿糖,U-Glu</v>
+        <v>U-Pro定量,蛋白/Cr比</v>
       </c>
       <c r="C74" t="str">
-        <v>陰性（－）</v>
+        <v>0.15 g/gCr未満</v>
       </c>
       <c r="D74" t="str">
-        <v>尿に糖が漏れ出ていないかを見る検査。血糖値がかなり高いと陽性になる</v>
+        <v>随時尿から尿蛋白の量を具体的な数値として評価する検査。ネフローゼ等の重症度判定に使う</v>
       </c>
       <c r="E74" t="str">
-        <v>通常、糖は尿にはほとんど出ませんが、血糖値がかなり高くなると尿にあふれ出るようになります。血糖コントロールの目安の一つです。</v>
+        <v>これは、尿に出ているたんぱくの量を具体的な数値で見る検査です。試験紙での陽性・陰性の判定だけでなく、実際にどれくらいの量が出ているかを把握できます。</v>
       </c>
       <c r="F74" t="str">
-        <v>糖尿病（血糖値が腎臓で再吸収できる量を超えている状態）、腎性糖尿（血糖値が正常でも体質的に出ることがある）、SGLT2阻害薬服用中（薬の作用で意図的に糖を排泄するため陽性になるのが正常）</v>
+        <v>腎症の進行（糖尿病性腎症、慢性腎臓病など）、ネフローゼ症候群（3.5 g/gCr以上が目安）</v>
       </c>
       <c r="G74" t="str">
-        <v>SGLT2阻害薬（フォシーガ、ジャディアンスなど）服用中は、陽性が薬の効果によるものであることを説明する。脱水や尿路感染の症状がないかも確認する</v>
+        <v/>
       </c>
       <c r="H74" t="str">
         <v/>
@@ -3444,13 +3444,13 @@
         <v/>
       </c>
       <c r="J74" t="str">
-        <v>SGLT2阻害薬服用中は尿糖陽性が治療効果として想定内であることを患者に伝える。血糖値・HbA1cと合わせて評価する</v>
+        <v>CKD診療ガイドラインの重症度分類（尿蛋白量による区分）にも使われる定量指標。試験紙法の半定量結果より治療効果判定に適する</v>
       </c>
       <c r="K74" t="str">
-        <v>糖尿病</v>
+        <v>腎機能,糖尿病</v>
       </c>
       <c r="L74" t="str">
-        <v>尿糖,糖半定量,U-Glu,腎性糖尿,SGLT2</v>
+        <v>尿蛋白,随時尿,定量,蛋白クレアチニン比,ネフローゼ</v>
       </c>
       <c r="M74" t="str">
         <v/>
@@ -3458,122 +3458,122 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>尿蛋白定量</v>
+        <v>BNP</v>
       </c>
       <c r="B75" t="str">
-        <v>U-Pro定量,蛋白/Cr比</v>
+        <v>BNP</v>
       </c>
       <c r="C75" t="str">
-        <v>0.15 g/gCr未満</v>
+        <v>18.4 pg/mL以下</v>
       </c>
       <c r="D75" t="str">
-        <v>随時尿から尿蛋白の量を具体的な数値として評価する検査。ネフローゼ等の重症度判定に使う</v>
+        <v>心臓が無理をしているときに出る物質。心臓は血液を送るポンプだが、負担がかかると「少し助けてほしい」というサインとしてBNPを血液中に出す。</v>
       </c>
       <c r="E75" t="str">
-        <v>これは、尿に出ているたんぱくの量を具体的な数値で見る検査です。試験紙での陽性・陰性の判定だけでなく、実際にどれくらいの量が出ているかを把握できます。</v>
+        <v>この検査は、心臓がどれくらい頑張りすぎていないかを見るものです。数値が高いと、心臓に少し負担がかかっているサインになります。</v>
       </c>
       <c r="F75" t="str">
-        <v>腎症の進行（糖尿病性腎症、慢性腎臓病など）、ネフローゼ症候群（3.5 g/gCr以上が目安）</v>
+        <v>心不全、心臓に負担がかかっている状態、体に水分がたまりやすいとき</v>
       </c>
       <c r="G75" t="str">
-        <v/>
+        <v>塩分・水分の摂りすぎに注意し、体重の変化を毎日記録するよう伝える</v>
       </c>
       <c r="H75" t="str">
-        <v/>
+        <v>心臓の負担は少ない状態</v>
       </c>
       <c r="I75" t="str">
         <v/>
       </c>
       <c r="J75" t="str">
-        <v>CKD診療ガイドラインの重症度分類（尿蛋白量による区分）にも使われる定量指標。試験紙法の半定量結果より治療効果判定に適する</v>
+        <v>腎機能が低いとBNPは高めに出ることがある／数値だけで判断せず、症状と合わせて評価する／息切れ、むくみ、体重増加があれば要注意</v>
       </c>
       <c r="K75" t="str">
-        <v>腎機能,糖尿病</v>
+        <v>心不全</v>
       </c>
       <c r="L75" t="str">
-        <v>尿蛋白,随時尿,定量,蛋白クレアチニン比,ネフローゼ</v>
+        <v>BNP,心不全,息切れ,むくみ</v>
       </c>
       <c r="M75" t="str">
-        <v/>
+        <v>食事と栄養 p.216-222（第2部 心疾患）</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>BNP</v>
+        <v>血清CPR（Cペプチド）</v>
       </c>
       <c r="B76" t="str">
-        <v>BNP</v>
+        <v>CPR</v>
       </c>
       <c r="C76" t="str">
-        <v>18.4 pg/mL以下</v>
+        <v>空腹時 0.6〜3.0 ng/mL（施設差あり）</v>
       </c>
       <c r="D76" t="str">
-        <v>心臓が無理をしているときに出る物質。心臓は血液を送るポンプだが、負担がかかると「少し助けてほしい」というサインとしてBNPを血液中に出す。</v>
+        <v>自分の膵臓がどれくらいインスリンを作れているかを表す指標</v>
       </c>
       <c r="E76" t="str">
-        <v>この検査は、心臓がどれくらい頑張りすぎていないかを見るものです。数値が高いと、心臓に少し負担がかかっているサインになります。</v>
+        <v>この検査は、ご自身の膵臓がどれくらいインスリンを作る力を持っているかを見るものです。数値が低いほど、体の中で作れるインスリンが少ないことを示します。</v>
       </c>
       <c r="F76" t="str">
-        <v>心不全、心臓に負担がかかっている状態、体に水分がたまりやすいとき</v>
+        <v>インスリン抵抗性が強い状態（初期の2型糖尿病など）</v>
       </c>
       <c r="G76" t="str">
-        <v>塩分・水分の摂りすぎに注意し、体重の変化を毎日記録するよう伝える</v>
+        <v/>
       </c>
       <c r="H76" t="str">
-        <v>心臓の負担は少ない状態</v>
+        <v>膵臓のインスリン分泌能低下（1型糖尿病、糖尿病の進行）</v>
       </c>
       <c r="I76" t="str">
         <v/>
       </c>
       <c r="J76" t="str">
-        <v>腎機能が低いとBNPは高めに出ることがある／数値だけで判断せず、症状と合わせて評価する／息切れ、むくみ、体重増加があれば要注意</v>
+        <v>インスリン分泌能の評価に使われる。数値が低いほどインスリン治療の必要性が高いと判断される目安になる</v>
       </c>
       <c r="K76" t="str">
-        <v>心不全</v>
+        <v>糖尿病</v>
       </c>
       <c r="L76" t="str">
-        <v>BNP,心不全,息切れ,むくみ</v>
+        <v>CPR,Cペプチド,インスリン分泌,血清CPR</v>
       </c>
       <c r="M76" t="str">
-        <v>食事と栄養 p.216-222（第2部 心疾患）</v>
+        <v/>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>血清CPR（Cペプチド）</v>
+        <v>尿中微量アルブミン</v>
       </c>
       <c r="B77" t="str">
-        <v>CPR</v>
+        <v>U-Alb,MAU</v>
       </c>
       <c r="C77" t="str">
-        <v>空腹時 0.6〜3.0 ng/mL（施設差あり）</v>
+        <v>30 mg/gCr未満（尿中アルブミン/クレアチニン比）</v>
       </c>
       <c r="D77" t="str">
-        <v>自分の膵臓がどれくらいインスリンを作れているかを表す指標</v>
+        <v>通常の尿蛋白検査では見つからない、ごく早期の腎症のサイン</v>
       </c>
       <c r="E77" t="str">
-        <v>この検査は、ご自身の膵臓がどれくらいインスリンを作る力を持っているかを見るものです。数値が低いほど、体の中で作れるインスリンが少ないことを示します。</v>
+        <v>この検査は、通常の尿検査ではまだ分からないくらい早い段階の腎臓の変化を見つけるためのものです。数値が高いと、腎症の初期のサインである可能性があります。</v>
       </c>
       <c r="F77" t="str">
-        <v>インスリン抵抗性が強い状態（初期の2型糖尿病など）</v>
+        <v>糖尿病性腎症の早期段階、高血圧</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>膵臓のインスリン分泌能低下（1型糖尿病、糖尿病の進行）</v>
+        <v/>
       </c>
       <c r="I77" t="str">
         <v/>
       </c>
       <c r="J77" t="str">
-        <v>インスリン分泌能の評価に使われる。数値が低いほどインスリン治療の必要性が高いと判断される目安になる</v>
+        <v>糖尿病腎症の早期発見に重要な検査。血糖・血圧コントロールで改善しうる段階なので、早期介入の意義を伝える</v>
       </c>
       <c r="K77" t="str">
-        <v>糖尿病</v>
+        <v>糖尿病,腎機能</v>
       </c>
       <c r="L77" t="str">
-        <v>CPR,Cペプチド,インスリン分泌,血清CPR</v>
+        <v>微量アルブミン,U-Alb,MAU,糖尿病性腎症,早期腎症</v>
       </c>
       <c r="M77" t="str">
         <v/>
@@ -3581,81 +3581,81 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>尿中微量アルブミン</v>
+        <v>血清鉄（Fe）</v>
       </c>
       <c r="B78" t="str">
-        <v>U-Alb,MAU</v>
+        <v>Fe</v>
       </c>
       <c r="C78" t="str">
-        <v>30 mg/gCr未満（尿中アルブミン/クレアチニン比）</v>
+        <v>60〜200 μg/dL（施設差あり）</v>
       </c>
       <c r="D78" t="str">
-        <v>通常の尿蛋白検査では見つからない、ごく早期の腎症のサイン</v>
+        <v>血液中を流れている鉄の量</v>
       </c>
       <c r="E78" t="str">
-        <v>この検査は、通常の尿検査ではまだ分からないくらい早い段階の腎臓の変化を見つけるためのものです。数値が高いと、腎症の初期のサインである可能性があります。</v>
+        <v>この検査は、今血液の中を流れている鉄の量を見るものです。低いと、体の中で鉄が不足している可能性があります。</v>
       </c>
       <c r="F78" t="str">
-        <v>糖尿病性腎症の早期段階、高血圧</v>
+        <v>鉄剤の過剰摂取、溶血、肝疾患</v>
       </c>
       <c r="G78" t="str">
         <v/>
       </c>
       <c r="H78" t="str">
-        <v/>
+        <v>鉄欠乏性貧血、慢性炎症、出血</v>
       </c>
       <c r="I78" t="str">
-        <v/>
+        <v>鉄分の多い食品（レバー・赤身肉・魚・ほうれん草など）を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える</v>
       </c>
       <c r="J78" t="str">
-        <v>糖尿病腎症の早期発見に重要な検査。血糖・血圧コントロールで改善しうる段階なので、早期介入の意義を伝える</v>
+        <v>血清鉄は日内変動が大きい。単独で判断せず総鉄結合能・フェリチンと合わせて評価する</v>
       </c>
       <c r="K78" t="str">
-        <v>糖尿病,腎機能</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="L78" t="str">
-        <v>微量アルブミン,U-Alb,MAU,糖尿病性腎症,早期腎症</v>
+        <v>血清鉄,Fe,鉄欠乏性貧血</v>
       </c>
       <c r="M78" t="str">
-        <v/>
+        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>血清鉄（Fe）</v>
+        <v>総鉄結合能（TIBC）</v>
       </c>
       <c r="B79" t="str">
-        <v>Fe</v>
+        <v>TIBC</v>
       </c>
       <c r="C79" t="str">
-        <v>60〜200 μg/dL（施設差あり）</v>
+        <v>250〜360 μg/dL（施設差あり）</v>
       </c>
       <c r="D79" t="str">
-        <v>血液中を流れている鉄の量</v>
+        <v>血液中のトランスフェリンが鉄と結合できる総量</v>
       </c>
       <c r="E79" t="str">
-        <v>この検査は、今血液の中を流れている鉄の量を見るものです。低いと、体の中で鉄が不足している可能性があります。</v>
+        <v>TIBCは、血液中でトランスフェリンという物質が鉄を運べる最大量を表します。体の中の鉄が不足すると、少しでも多く鉄を運ぼうとしてこの数値が上がる性質があります。</v>
       </c>
       <c r="F79" t="str">
-        <v>鉄剤の過剰摂取、溶血、肝疾患</v>
+        <v>鉄欠乏性貧血（＞360 μg/dLが目安）</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>鉄欠乏性貧血、慢性炎症、出血</v>
+        <v>慢性炎症、肝疾患、ネフローゼ症候群</v>
       </c>
       <c r="I79" t="str">
-        <v>鉄分の多い食品（レバー・赤身肉・魚・ほうれん草など）を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える</v>
+        <v/>
       </c>
       <c r="J79" t="str">
-        <v>血清鉄は日内変動が大きい。単独で判断せず総鉄結合能・フェリチンと合わせて評価する</v>
+        <v>鉄が不足すると、体はより多く運ぼうとしてTIBCが上昇する。UIBC・血清鉄と併せて評価する</v>
       </c>
       <c r="K79" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
       <c r="L79" t="str">
-        <v>血清鉄,Fe,鉄欠乏性貧血</v>
+        <v>TIBC,総鉄結合能,鉄欠乏性貧血</v>
       </c>
       <c r="M79" t="str">
         <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
@@ -3663,40 +3663,40 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>総鉄結合能（TIBC）</v>
+        <v>不飽和鉄結合能（UIBC）</v>
       </c>
       <c r="B80" t="str">
-        <v>TIBC</v>
+        <v>UIBC</v>
       </c>
       <c r="C80" t="str">
-        <v>250〜360 μg/dL（施設差あり）</v>
+        <v>170〜300 μg/dL（施設差あり）</v>
       </c>
       <c r="D80" t="str">
-        <v>血液中のトランスフェリンが鉄と結合できる総量</v>
+        <v>トランスフェリンのうち、まだ鉄と結合していない余力の部分（UIBC＝TIBC－血清鉄）</v>
       </c>
       <c r="E80" t="str">
-        <v>TIBCは、血液中でトランスフェリンという物質が鉄を運べる最大量を表します。体の中の鉄が不足すると、少しでも多く鉄を運ぼうとしてこの数値が上がる性質があります。</v>
+        <v>UIBCは、トランスフェリンのうち、まだ鉄と結合していない「空き容量」の部分を表します。鉄が不足しているときほど、この空き容量は大きくなります。</v>
       </c>
       <c r="F80" t="str">
-        <v>鉄欠乏性貧血（＞360 μg/dLが目安）</v>
+        <v>鉄欠乏性貧血（＞300 μg/dLが目安）</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>慢性炎症、肝疾患、ネフローゼ症候群</v>
+        <v>慢性炎症、鉄過剰状態</v>
       </c>
       <c r="I80" t="str">
         <v/>
       </c>
       <c r="J80" t="str">
-        <v>鉄が不足すると、体はより多く運ぼうとしてTIBCが上昇する。UIBC・血清鉄と併せて評価する</v>
+        <v>TIBCと同じ方向に動くことが多い。血清鉄・TIBCとあわせて鉄欠乏性貧血と二次性貧血の鑑別に使う</v>
       </c>
       <c r="K80" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
       <c r="L80" t="str">
-        <v>TIBC,総鉄結合能,鉄欠乏性貧血</v>
+        <v>UIBC,不飽和鉄結合能,鉄欠乏性貧血</v>
       </c>
       <c r="M80" t="str">
         <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
@@ -3704,40 +3704,40 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>不飽和鉄結合能（UIBC）</v>
+        <v>トランスフェリン飽和度</v>
       </c>
       <c r="B81" t="str">
-        <v>UIBC</v>
+        <v>TSAT</v>
       </c>
       <c r="C81" t="str">
-        <v>170〜300 μg/dL（施設差あり）</v>
+        <v>16〜50%程度（施設差あり）</v>
       </c>
       <c r="D81" t="str">
-        <v>トランスフェリンのうち、まだ鉄と結合していない余力の部分（UIBC＝TIBC－血清鉄）</v>
+        <v>鉄を運ぶ役割のトランスフェリンのうち、実際に鉄を運んでいる割合（血清鉄÷総鉄結合能）</v>
       </c>
       <c r="E81" t="str">
-        <v>UIBCは、トランスフェリンのうち、まだ鉄と結合していない「空き容量」の部分を表します。鉄が不足しているときほど、この空き容量は大きくなります。</v>
+        <v>トランスフェリン飽和度は、鉄を運ぶトランスフェリンのうち、実際にどれくらいが鉄を運んでいるかを割合で表したものです。鉄欠乏性貧血では低くなり、鉄が過剰にたまる病気では高くなります。</v>
       </c>
       <c r="F81" t="str">
-        <v>鉄欠乏性貧血（＞300 μg/dLが目安）</v>
+        <v>鉄過剰症（ヘモクロマトーシスなど）</v>
       </c>
       <c r="G81" t="str">
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>慢性炎症、鉄過剰状態</v>
+        <v>鉄欠乏性貧血（＜16%が目安）</v>
       </c>
       <c r="I81" t="str">
         <v/>
       </c>
       <c r="J81" t="str">
-        <v>TIBCと同じ方向に動くことが多い。血清鉄・TIBCとあわせて鉄欠乏性貧血と二次性貧血の鑑別に使う</v>
+        <v>血清鉄をTIBCで割って計算される。鉄剤補充の効果判定にも使われる</v>
       </c>
       <c r="K81" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
       <c r="L81" t="str">
-        <v>UIBC,不飽和鉄結合能,鉄欠乏性貧血</v>
+        <v>トランスフェリン飽和度,TSAT,鉄欠乏性貧血</v>
       </c>
       <c r="M81" t="str">
         <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
@@ -3745,40 +3745,40 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>トランスフェリン飽和度</v>
+        <v>血清フェリチン</v>
       </c>
       <c r="B82" t="str">
-        <v>TSAT</v>
+        <v>Ferritin</v>
       </c>
       <c r="C82" t="str">
-        <v>16〜50%程度（施設差あり）</v>
+        <v>男性 20〜250 ng/mL、女性 10〜120 ng/mL（施設差あり）</v>
       </c>
       <c r="D82" t="str">
-        <v>鉄を運ぶ役割のトランスフェリンのうち、実際に鉄を運んでいる割合（血清鉄÷総鉄結合能）</v>
+        <v>体に貯蔵されている鉄の量を反映する指標。貧血の症状が出るより早い段階で低下する</v>
       </c>
       <c r="E82" t="str">
-        <v>トランスフェリン飽和度は、鉄を運ぶトランスフェリンのうち、実際にどれくらいが鉄を運んでいるかを割合で表したものです。鉄欠乏性貧血では低くなり、鉄が過剰にたまる病気では高くなります。</v>
+        <v>フェリチンは、体に蓄えられている鉄の「貯金」の量を見る検査です。この数値が下がるのは、貧血の症状が出るよりも前の、とても早い段階のサインになります。</v>
       </c>
       <c r="F82" t="str">
-        <v>鉄過剰症（ヘモクロマトーシスなど）</v>
+        <v>炎症性疾患、肝疾患、悪性腫瘍、鉄過剰症（フェリチンは炎症でも上昇するため、貧血の評価では注意が必要）</v>
       </c>
       <c r="G82" t="str">
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>鉄欠乏性貧血（＜16%が目安）</v>
+        <v>鉄欠乏状態（貧血の症状が出る前の早期段階から低下する）</v>
       </c>
       <c r="I82" t="str">
-        <v/>
+        <v>鉄分の多い食品を意識するとともに、貯蔵鉄を補うため治療は数値が正常化してからも継続が必要なことを伝える</v>
       </c>
       <c r="J82" t="str">
-        <v>血清鉄をTIBCで割って計算される。鉄剤補充の効果判定にも使われる</v>
+        <v>貯蔵鉄の指標で鉄欠乏を最も早期に反映する。ただし炎症があると鉄欠乏があっても正常〜高値に出ることがあり、CRP等の炎症所見と合わせて評価する。二次性貧血との鑑別に重要</v>
       </c>
       <c r="K82" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
       <c r="L82" t="str">
-        <v>トランスフェリン飽和度,TSAT,鉄欠乏性貧血</v>
+        <v>フェリチン,Ferritin,貯蔵鉄,鉄欠乏</v>
       </c>
       <c r="M82" t="str">
         <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
@@ -3786,122 +3786,122 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>血清フェリチン</v>
+        <v>尿中尿酸/クレアチニン比（UUA/UCr）</v>
       </c>
       <c r="B83" t="str">
-        <v>Ferritin</v>
+        <v>UUA/UCr</v>
       </c>
       <c r="C83" t="str">
-        <v>男性 20〜250 ng/mL、女性 10〜120 ng/mL（施設差あり）</v>
+        <v>0.4〜0.8程度が混合型の目安</v>
       </c>
       <c r="D83" t="str">
-        <v>体に貯蔵されている鉄の量を反映する指標。貧血の症状が出るより早い段階で低下する</v>
+        <v>尿酸が「作られすぎ」か「排泄できていない」かを見分ける比の値</v>
       </c>
       <c r="E83" t="str">
-        <v>フェリチンは、体に蓄えられている鉄の「貯金」の量を見る検査です。この数値が下がるのは、貧血の症状が出るよりも前の、とても早い段階のサインになります。</v>
+        <v>この数値は、体の中で尿酸が「作られすぎている」のか、それとも「うまく排泄できていない」のかを見分けるために使う比の値です。高尿酸血症の治療薬を選ぶときの参考になります。</v>
       </c>
       <c r="F83" t="str">
-        <v>炎症性疾患、肝疾患、悪性腫瘍、鉄過剰症（フェリチンは炎症でも上昇するため、貧血の評価では注意が必要）</v>
+        <v>尿酸産生過剰型（0.8以上が目安）</v>
       </c>
       <c r="G83" t="str">
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>鉄欠乏状態（貧血の症状が出る前の早期段階から低下する）</v>
+        <v>尿酸排泄低下型（0.4以下が目安）</v>
       </c>
       <c r="I83" t="str">
-        <v>鉄分の多い食品を意識するとともに、貯蔵鉄を補うため治療は数値が正常化してからも継続が必要なことを伝える</v>
+        <v/>
       </c>
       <c r="J83" t="str">
-        <v>貯蔵鉄の指標で鉄欠乏を最も早期に反映する。ただし炎症があると鉄欠乏があっても正常〜高値に出ることがあり、CRP等の炎症所見と合わせて評価する。二次性貧血との鑑別に重要</v>
+        <v>高尿酸血症は尿酸産生過剰型・排泄低下型・混合型に分類され、この比が目安になる。病型によって使う薬剤（尿酸生成抑制薬か尿酸排泄促進薬か）の選択が変わる</v>
       </c>
       <c r="K83" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>高尿酸血症</v>
       </c>
       <c r="L83" t="str">
-        <v>フェリチン,Ferritin,貯蔵鉄,鉄欠乏</v>
+        <v>UUA,UCr,尿酸クリアランス,CUA,EUA,尿酸産生過剰型,尿酸排泄低下型</v>
       </c>
       <c r="M83" t="str">
-        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
+        <v>食事と栄養 p.180-189（第2部 痛風・高尿酸血症）</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>尿中尿酸/クレアチニン比（UUA/UCr）</v>
+        <v>ucOC（低カルボキシル化オステオカルシン）</v>
       </c>
       <c r="B84" t="str">
-        <v>UUA/UCr</v>
+        <v>ucOC</v>
       </c>
       <c r="C84" t="str">
-        <v>0.4〜0.8程度が混合型の目安</v>
+        <v>4.5 ng/mL未満（施設差あり）</v>
       </c>
       <c r="D84" t="str">
-        <v>尿酸が「作られすぎ」か「排泄できていない」かを見分ける比の値</v>
+        <v>ビタミンKが不足していないかを反映する骨の指標</v>
       </c>
       <c r="E84" t="str">
-        <v>この数値は、体の中で尿酸が「作られすぎている」のか、それとも「うまく排泄できていない」のかを見分けるために使う比の値です。高尿酸血症の治療薬を選ぶときの参考になります。</v>
+        <v>ucOCは、骨を作るために必要なビタミンKが体の中で足りているかどうかを反映する検査です。数値が高いとビタミンK不足が疑われます。</v>
       </c>
       <c r="F84" t="str">
-        <v>尿酸産生過剰型（0.8以上が目安）</v>
+        <v>ビタミンK不足状態</v>
       </c>
       <c r="G84" t="str">
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>尿酸排泄低下型（0.4以下が目安）</v>
+        <v/>
       </c>
       <c r="I84" t="str">
         <v/>
       </c>
       <c r="J84" t="str">
-        <v>高尿酸血症は尿酸産生過剰型・排泄低下型・混合型に分類され、この比が目安になる。病型によって使う薬剤（尿酸生成抑制薬か尿酸排泄促進薬か）の選択が変わる</v>
+        <v>ビタミンK2製剤（骨粗鬆症治療薬）の適応判断や効果判定に使われる</v>
       </c>
       <c r="K84" t="str">
-        <v>高尿酸血症</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="L84" t="str">
-        <v>UUA,UCr,尿酸クリアランス,CUA,EUA,尿酸産生過剰型,尿酸排泄低下型</v>
+        <v>ucOC,オステオカルシン,ビタミンK</v>
       </c>
       <c r="M84" t="str">
-        <v>食事と栄養 p.180-189（第2部 痛風・高尿酸血症）</v>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>ucOC（低カルボキシル化オステオカルシン）</v>
+        <v>PTH（副甲状腺ホルモン）</v>
       </c>
       <c r="B85" t="str">
-        <v>ucOC</v>
+        <v>PTH</v>
       </c>
       <c r="C85" t="str">
-        <v>4.5 ng/mL未満（施設差あり）</v>
+        <v>10〜65 pg/mL（施設差あり）</v>
       </c>
       <c r="D85" t="str">
-        <v>ビタミンKが不足していないかを反映する骨の指標</v>
+        <v>血液中のカルシウム濃度を調節するホルモン</v>
       </c>
       <c r="E85" t="str">
-        <v>ucOCは、骨を作るために必要なビタミンKが体の中で足りているかどうかを反映する検査です。数値が高いとビタミンK不足が疑われます。</v>
+        <v>PTHは、血液中のカルシウム濃度を一定に保つために働くホルモンです。カルシウムが低くなると分泌が増え、骨からカルシウムを取り出したり、腎臓での再吸収を促したりして数値を戻そうとします。</v>
       </c>
       <c r="F85" t="str">
-        <v>ビタミンK不足状態</v>
+        <v>原発性・二次性副甲状腺機能亢進症（腎不全に伴うものなど）</v>
       </c>
       <c r="G85" t="str">
         <v/>
       </c>
       <c r="H85" t="str">
-        <v/>
+        <v>副甲状腺機能低下症</v>
       </c>
       <c r="I85" t="str">
         <v/>
       </c>
       <c r="J85" t="str">
-        <v>ビタミンK2製剤（骨粗鬆症治療薬）の適応判断や効果判定に使われる</v>
+        <v>骨粗鬆症の二次性原因（副甲状腺機能亢進症）を除外するための検査。カルシウム・リンと合わせて評価する</v>
       </c>
       <c r="K85" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="L85" t="str">
-        <v>ucOC,オステオカルシン,ビタミンK</v>
+        <v>PTH,副甲状腺ホルモン,パラトルモン</v>
       </c>
       <c r="M85" t="str">
         <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
@@ -3909,40 +3909,40 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>PTH（副甲状腺ホルモン）</v>
+        <v>尿中NTX</v>
       </c>
       <c r="B86" t="str">
-        <v>PTH</v>
+        <v>NTX</v>
       </c>
       <c r="C86" t="str">
-        <v>10〜65 pg/mL（施設差あり）</v>
+        <v>施設差が大きく一律の記載が難しい（尿中）</v>
       </c>
       <c r="D86" t="str">
-        <v>血液中のカルシウム濃度を調節するホルモン</v>
+        <v>骨が壊されるときに出る、骨吸収マーカーのひとつ</v>
       </c>
       <c r="E86" t="str">
-        <v>PTHは、血液中のカルシウム濃度を一定に保つために働くホルモンです。カルシウムが低くなると分泌が増え、骨からカルシウムを取り出したり、腎臓での再吸収を促したりして数値を戻そうとします。</v>
+        <v>NTXは、骨が壊される（吸収される）ときに尿の中に出てくる物質です。骨粗鬆症の治療薬がどれくらい効いているかを確認するために使われます。</v>
       </c>
       <c r="F86" t="str">
-        <v>原発性・二次性副甲状腺機能亢進症（腎不全に伴うものなど）</v>
+        <v>骨代謝回転の亢進（骨粗鬆症、閉経後など）</v>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>副甲状腺機能低下症</v>
+        <v>骨吸収抑制薬（ビスホスホネート等）による治療効果</v>
       </c>
       <c r="I86" t="str">
         <v/>
       </c>
       <c r="J86" t="str">
-        <v>骨粗鬆症の二次性原因（副甲状腺機能亢進症）を除外するための検査。カルシウム・リンと合わせて評価する</v>
+        <v>治療開始後3〜6か月で再検し、薬の効果判定に使われる。TRACP-5bと同じ「骨を壊す側」の指標</v>
       </c>
       <c r="K86" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="L86" t="str">
-        <v>PTH,副甲状腺ホルモン,パラトルモン</v>
+        <v>NTX,尿中NTX,骨吸収マーカー</v>
       </c>
       <c r="M86" t="str">
         <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
@@ -3950,40 +3950,40 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>尿中NTX</v>
+        <v>カルシトニン</v>
       </c>
       <c r="B87" t="str">
-        <v>NTX</v>
+        <v>CT</v>
       </c>
       <c r="C87" t="str">
-        <v>施設差が大きく一律の記載が難しい（尿中）</v>
+        <v>男性 9.52 pg/mL未満、女性 6.40 pg/mL未満（施設差あり）</v>
       </c>
       <c r="D87" t="str">
-        <v>骨が壊されるときに出る、骨吸収マーカーのひとつ</v>
+        <v>血液中のカルシウムを下げる方向に働くホルモン</v>
       </c>
       <c r="E87" t="str">
-        <v>NTXは、骨が壊される（吸収される）ときに尿の中に出てくる物質です。骨粗鬆症の治療薬がどれくらい効いているかを確認するために使われます。</v>
+        <v>カルシトニンは、PTHとは逆に血液中のカルシウムを下げる方向に働くホルモンです。特定の甲状腺の病気（甲状腺髄様癌）がないかを調べる際にも使われます。</v>
       </c>
       <c r="F87" t="str">
-        <v>骨代謝回転の亢進（骨粗鬆症、閉経後など）</v>
+        <v>甲状腺髄様癌、腎不全</v>
       </c>
       <c r="G87" t="str">
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>骨吸収抑制薬（ビスホスホネート等）による治療効果</v>
+        <v/>
       </c>
       <c r="I87" t="str">
         <v/>
       </c>
       <c r="J87" t="str">
-        <v>治療開始後3〜6か月で再検し、薬の効果判定に使われる。TRACP-5bと同じ「骨を壊す側」の指標</v>
+        <v>骨粗鬆症の二次性原因の除外目的で測定されることがある検査値。同名の薬剤（カルシトニン製剤）と混同しないよう注意</v>
       </c>
       <c r="K87" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="L87" t="str">
-        <v>NTX,尿中NTX,骨吸収マーカー</v>
+        <v>カルシトニン,CT</v>
       </c>
       <c r="M87" t="str">
         <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
@@ -3991,40 +3991,40 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>カルシトニン</v>
+        <v>DPD（デオキシピリジノリン）</v>
       </c>
       <c r="B88" t="str">
-        <v>CT</v>
+        <v>DPD</v>
       </c>
       <c r="C88" t="str">
-        <v>男性 9.52 pg/mL未満、女性 6.40 pg/mL未満（施設差あり）</v>
+        <v>施設差が大きく一律の記載が難しい（尿中）</v>
       </c>
       <c r="D88" t="str">
-        <v>血液中のカルシウムを下げる方向に働くホルモン</v>
+        <v>骨のコラーゲンが壊れるときに出る、骨吸収マーカーのひとつ</v>
       </c>
       <c r="E88" t="str">
-        <v>カルシトニンは、PTHとは逆に血液中のカルシウムを下げる方向に働くホルモンです。特定の甲状腺の病気（甲状腺髄様癌）がないかを調べる際にも使われます。</v>
+        <v>DPDも、骨が壊されるときに尿に出てくる物質の一つです。NTXと同じように、骨粗鬆症治療薬の効果を確認するために使われます。</v>
       </c>
       <c r="F88" t="str">
-        <v>甲状腺髄様癌、腎不全</v>
+        <v>骨代謝回転の亢進（骨粗鬆症など）</v>
       </c>
       <c r="G88" t="str">
         <v/>
       </c>
       <c r="H88" t="str">
-        <v/>
+        <v>骨吸収抑制薬による治療効果</v>
       </c>
       <c r="I88" t="str">
         <v/>
       </c>
       <c r="J88" t="str">
-        <v>骨粗鬆症の二次性原因の除外目的で測定されることがある検査値。同名の薬剤（カルシトニン製剤）と混同しないよう注意</v>
+        <v>NTX・CTXと同じ「骨を壊す側」の指標。食事の影響を受けにくいとされる</v>
       </c>
       <c r="K88" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="L88" t="str">
-        <v>カルシトニン,CT</v>
+        <v>DPD,デオキシピリジノリン,骨吸収マーカー</v>
       </c>
       <c r="M88" t="str">
         <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
@@ -4032,19 +4032,19 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>DPD（デオキシピリジノリン）</v>
+        <v>CTX</v>
       </c>
       <c r="B89" t="str">
-        <v>DPD</v>
+        <v>CTX</v>
       </c>
       <c r="C89" t="str">
-        <v>施設差が大きく一律の記載が難しい（尿中）</v>
+        <v>施設差が大きく一律の記載が難しい（血清・尿中）</v>
       </c>
       <c r="D89" t="str">
         <v>骨のコラーゲンが壊れるときに出る、骨吸収マーカーのひとつ</v>
       </c>
       <c r="E89" t="str">
-        <v>DPDも、骨が壊されるときに尿に出てくる物質の一つです。NTXと同じように、骨粗鬆症治療薬の効果を確認するために使われます。</v>
+        <v>CTXも、骨が壊されるときに血液や尿に出てくる物質です。骨粗鬆症治療薬（骨を壊すのを抑える薬）の効果を確認するために使われます。</v>
       </c>
       <c r="F89" t="str">
         <v>骨代謝回転の亢進（骨粗鬆症など）</v>
@@ -4059,13 +4059,13 @@
         <v/>
       </c>
       <c r="J89" t="str">
-        <v>NTX・CTXと同じ「骨を壊す側」の指標。食事の影響を受けにくいとされる</v>
+        <v>NTX・DPDと同じ「骨を壊す側」の指標。血清・尿中いずれでも測定されることがある</v>
       </c>
       <c r="K89" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="L89" t="str">
-        <v>DPD,デオキシピリジノリン,骨吸収マーカー</v>
+        <v>CTX,骨吸収マーカー</v>
       </c>
       <c r="M89" t="str">
         <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
@@ -4073,40 +4073,40 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>CTX</v>
+        <v>P1NP</v>
       </c>
       <c r="B90" t="str">
-        <v>CTX</v>
+        <v>P1NP</v>
       </c>
       <c r="C90" t="str">
-        <v>施設差が大きく一律の記載が難しい（血清・尿中）</v>
+        <v>施設差が大きく一律の記載が難しい（血清）</v>
       </c>
       <c r="D90" t="str">
-        <v>骨のコラーゲンが壊れるときに出る、骨吸収マーカーのひとつ</v>
+        <v>骨が新しく作られるときに出る、骨形成マーカーのひとつ</v>
       </c>
       <c r="E90" t="str">
-        <v>CTXも、骨が壊されるときに血液や尿に出てくる物質です。骨粗鬆症治療薬（骨を壊すのを抑える薬）の効果を確認するために使われます。</v>
+        <v>P1NPは、CTXなどとは逆に、骨が新しく作られるときに血液中に出てくる物質です。骨を作る力を高める薬（テリパラチドなど）の効果を確認するために使われます。</v>
       </c>
       <c r="F90" t="str">
-        <v>骨代謝回転の亢進（骨粗鬆症など）</v>
+        <v>骨代謝回転の亢進、骨形成促進薬による治療効果</v>
       </c>
       <c r="G90" t="str">
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>骨吸収抑制薬による治療効果</v>
+        <v>骨形成の低下</v>
       </c>
       <c r="I90" t="str">
         <v/>
       </c>
       <c r="J90" t="str">
-        <v>NTX・DPDと同じ「骨を壊す側」の指標。血清・尿中いずれでも測定されることがある</v>
+        <v>TRACP-5b等「骨を壊す側」の指標とは逆の、「骨を作る側」の指標。骨形成促進薬（テリパラチド等）の効果判定に使われる</v>
       </c>
       <c r="K90" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="L90" t="str">
-        <v>CTX,骨吸収マーカー</v>
+        <v>P1NP,骨形成マーカー</v>
       </c>
       <c r="M90" t="str">
         <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
@@ -4114,60 +4114,60 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>P1NP</v>
+        <v>抗甲状腺マイクロゾーム抗体（抗TPO抗体）</v>
       </c>
       <c r="B91" t="str">
-        <v>P1NP</v>
+        <v>TPOAb</v>
       </c>
       <c r="C91" t="str">
-        <v>施設差が大きく一律の記載が難しい（血清）</v>
+        <v>陰性（16 IU/mL未満程度、施設差あり）</v>
       </c>
       <c r="D91" t="str">
-        <v>骨が新しく作られるときに出る、骨形成マーカーのひとつ</v>
+        <v>自分の甲状腺を攻撃する抗体が出ていないかを見る検査</v>
       </c>
       <c r="E91" t="str">
-        <v>P1NPは、CTXなどとは逆に、骨が新しく作られるときに血液中に出てくる物質です。骨を作る力を高める薬（テリパラチドなど）の効果を確認するために使われます。</v>
+        <v>この検査は、体の中に自分の甲状腺を誤って攻撃してしまう抗体がないかを見るものです。陽性の場合、橋本病（慢性甲状腺炎）など甲状腺の自己免疫的な炎症が背景にある可能性があります。</v>
       </c>
       <c r="F91" t="str">
-        <v>骨代謝回転の亢進、骨形成促進薬による治療効果</v>
+        <v>橋本病（慢性甲状腺炎）、バセドウ病などの自己免疫性甲状腺疾患</v>
       </c>
       <c r="G91" t="str">
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>骨形成の低下</v>
+        <v/>
       </c>
       <c r="I91" t="str">
         <v/>
       </c>
       <c r="J91" t="str">
-        <v>TRACP-5b等「骨を壊す側」の指標とは逆の、「骨を作る側」の指標。骨形成促進薬（テリパラチド等）の効果判定に使われる</v>
+        <v>陽性でも必ずしも甲状腺機能異常があるとは限らない。TSH・FT4など甲状腺ホルモンの数値と合わせて評価する</v>
       </c>
       <c r="K91" t="str">
-        <v>骨粗鬆症</v>
+        <v>甲状腺疾患</v>
       </c>
       <c r="L91" t="str">
-        <v>P1NP,骨形成マーカー</v>
+        <v>抗TPO抗体,抗甲状腺マイクロゾーム抗体,TPOAb,橋本病</v>
       </c>
       <c r="M91" t="str">
-        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
+        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>抗甲状腺マイクロゾーム抗体（抗TPO抗体）</v>
+        <v>抗サイログロブリン抗体</v>
       </c>
       <c r="B92" t="str">
-        <v>TPOAb</v>
+        <v>TgAb</v>
       </c>
       <c r="C92" t="str">
-        <v>陰性（16 IU/mL未満程度、施設差あり）</v>
+        <v>陰性（28 IU/mL未満程度、施設差あり）</v>
       </c>
       <c r="D92" t="str">
-        <v>自分の甲状腺を攻撃する抗体が出ていないかを見る検査</v>
+        <v>甲状腺のたんぱく質（サイログロブリン）への抗体が出ていないかを見る検査</v>
       </c>
       <c r="E92" t="str">
-        <v>この検査は、体の中に自分の甲状腺を誤って攻撃してしまう抗体がないかを見るものです。陽性の場合、橋本病（慢性甲状腺炎）など甲状腺の自己免疫的な炎症が背景にある可能性があります。</v>
+        <v>この検査も、抗TPO抗体と同じく、甲状腺に対する自己免疫の有無を見るものです。あわせて調べることで橋本病などの診断の参考にします。</v>
       </c>
       <c r="F92" t="str">
         <v>橋本病（慢性甲状腺炎）、バセドウ病などの自己免疫性甲状腺疾患</v>
@@ -4182,13 +4182,13 @@
         <v/>
       </c>
       <c r="J92" t="str">
-        <v>陽性でも必ずしも甲状腺機能異常があるとは限らない。TSH・FT4など甲状腺ホルモンの数値と合わせて評価する</v>
+        <v>抗TPO抗体とあわせて測定されることが多い。単独の高値だけで治療方針が決まるわけではない</v>
       </c>
       <c r="K92" t="str">
         <v>甲状腺疾患</v>
       </c>
       <c r="L92" t="str">
-        <v>抗TPO抗体,抗甲状腺マイクロゾーム抗体,TPOAb,橋本病</v>
+        <v>抗サイログロブリン抗体,TgAb,橋本病</v>
       </c>
       <c r="M92" t="str">
         <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
@@ -4196,81 +4196,81 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>抗サイログロブリン抗体</v>
+        <v>血中薬物濃度（TDM）</v>
       </c>
       <c r="B93" t="str">
-        <v>TgAb</v>
+        <v>TDM</v>
       </c>
       <c r="C93" t="str">
-        <v>陰性（28 IU/mL未満程度、施設差あり）</v>
+        <v>薬剤ごとに有効域が異なる（例：カルバマゼピン 4〜12 μg/mL、バルプロ酸 40〜100 μg/mL、フェニトイン 10〜20 μg/mL）</v>
       </c>
       <c r="D93" t="str">
-        <v>甲状腺のたんぱく質（サイログロブリン）への抗体が出ていないかを見る検査</v>
+        <v>治療域が狭い薬剤で、血液中の薬の濃度が効果域・中毒域のどちらにあるかを確認する検査</v>
       </c>
       <c r="E93" t="str">
-        <v>この検査も、抗TPO抗体と同じく、甲状腺に対する自己免疫の有無を見るものです。あわせて調べることで橋本病などの診断の参考にします。</v>
+        <v>この薬は効く量と副作用が出る量が近いため、血液中の薬の濃度を定期的に測って、ちょうどよい範囲に入っているかを確認します。数値が低いと効果が不十分になり、高いと副作用が出やすくなります。</v>
       </c>
       <c r="F93" t="str">
-        <v>橋本病（慢性甲状腺炎）、バセドウ病などの自己免疫性甲状腺疾患</v>
+        <v>過量投与、代謝を妨げる薬剤との併用、肝機能低下による代謝低下</v>
       </c>
       <c r="G93" t="str">
-        <v/>
+        <v>ふらつき、眠気、めまい、物が二重に見えるなどの中毒症状がないか確認する</v>
       </c>
       <c r="H93" t="str">
-        <v/>
+        <v>飲み忘れ、自己判断による減量、代謝を促進する薬剤との併用（相互作用）</v>
       </c>
       <c r="I93" t="str">
-        <v/>
+        <v>発作やてんかん症状の再発がないか確認し、飲み忘れがないか一緒に確認する</v>
       </c>
       <c r="J93" t="str">
-        <v>抗TPO抗体とあわせて測定されることが多い。単独の高値だけで治療方針が決まるわけではない</v>
+        <v>採血のタイミング（トラフ値かどうか）で数値の解釈が変わるため採血時点を確認する。カルバマゼピンは自己誘導により長期使用で濃度が下がることがある点にも注意</v>
       </c>
       <c r="K93" t="str">
-        <v>甲状腺疾患</v>
+        <v>てんかん</v>
       </c>
       <c r="L93" t="str">
-        <v>抗サイログロブリン抗体,TgAb,橋本病</v>
+        <v>TDM,血中薬物濃度,治療域,中毒域,カルバマゼピン,フェニトイン,バルプロ酸,抗てんかん薬</v>
       </c>
       <c r="M93" t="str">
-        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
+        <v/>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>血中薬物濃度（TDM）</v>
+        <v>アミラーゼ（AMY）</v>
       </c>
       <c r="B94" t="str">
-        <v>TDM</v>
+        <v>AMY</v>
       </c>
       <c r="C94" t="str">
-        <v>薬剤ごとに有効域が異なる（例：カルバマゼピン 4〜12 μg/mL、バルプロ酸 40〜100 μg/mL、フェニトイン 10〜20 μg/mL）</v>
+        <v>44〜132 U/L（施設差あり）</v>
       </c>
       <c r="D94" t="str">
-        <v>治療域が狭い薬剤で、血液中の薬の濃度が効果域・中毒域のどちらにあるかを確認する検査</v>
+        <v>膵臓や唾液腺から出る消化酵素。膵炎などで血液中に漏れ出す</v>
       </c>
       <c r="E94" t="str">
-        <v>この薬は効く量と副作用が出る量が近いため、血液中の薬の濃度を定期的に測って、ちょうどよい範囲に入っているかを確認します。数値が低いと効果が不十分になり、高いと副作用が出やすくなります。</v>
+        <v>アミラーゼは、でんぷんを分解する消化酵素で、主に膵臓と唾液腺から作られます。膵臓に炎症が起きると血液中に漏れ出して数値が上がるため、膵炎の診断や経過観察に使われます。</v>
       </c>
       <c r="F94" t="str">
-        <v>過量投与、代謝を妨げる薬剤との併用、肝機能低下による代謝低下</v>
+        <v>急性膵炎、慢性膵炎の急性増悪、耳下腺炎（おたふくかぜ）、腎不全</v>
       </c>
       <c r="G94" t="str">
-        <v>ふらつき、眠気、めまい、物が二重に見えるなどの中毒症状がないか確認する</v>
+        <v>飲酒を控える、脂っこい食事を避けるよう伝える</v>
       </c>
       <c r="H94" t="str">
-        <v>飲み忘れ、自己判断による減量、代謝を促進する薬剤との併用（相互作用）</v>
+        <v>慢性膵炎の進行期（膵臓の機能低下）</v>
       </c>
       <c r="I94" t="str">
-        <v>発作やてんかん症状の再発がないか確認し、飲み忘れがないか一緒に確認する</v>
+        <v/>
       </c>
       <c r="J94" t="str">
-        <v>採血のタイミング（トラフ値かどうか）で数値の解釈が変わるため採血時点を確認する。カルバマゼピンは自己誘導により長期使用で濃度が下がることがある点にも注意</v>
+        <v>膵臓由来か唾液腺由来かを区別するには膵型アミラーゼ(P-AMY)を確認する。急性膵炎では強い腹痛・背部痛を伴うことが多く、飲酒歴の確認も重要</v>
       </c>
       <c r="K94" t="str">
-        <v>てんかん</v>
+        <v/>
       </c>
       <c r="L94" t="str">
-        <v>TDM,血中薬物濃度,治療域,中毒域,カルバマゼピン,フェニトイン,バルプロ酸,抗てんかん薬</v>
+        <v>アミラーゼ,AMY,膵炎,急性膵炎</v>
       </c>
       <c r="M94" t="str">
         <v/>
@@ -4278,40 +4278,40 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>アミラーゼ（AMY）</v>
+        <v>間接ビリルビン</v>
       </c>
       <c r="B95" t="str">
-        <v>AMY</v>
+        <v>I-Bil</v>
       </c>
       <c r="C95" t="str">
-        <v>44〜132 U/L（施設差あり）</v>
+        <v>0.2〜0.8 mg/dL程度（施設差あり）</v>
       </c>
       <c r="D95" t="str">
-        <v>膵臓や唾液腺から出る消化酵素。膵炎などで血液中に漏れ出す</v>
+        <v>赤血球が壊れてできるビリルビンのうち、肝臓で処理される前の形</v>
       </c>
       <c r="E95" t="str">
-        <v>アミラーゼは、でんぷんを分解する消化酵素で、主に膵臓と唾液腺から作られます。膵臓に炎症が起きると血液中に漏れ出して数値が上がるため、膵炎の診断や経過観察に使われます。</v>
+        <v>間接ビリルビンは、赤血球が壊れてできたビリルビンが、まだ肝臓で処理される前の状態です。この値が高い場合、赤血球が通常より多く壊れている(溶血)か、肝臓での処理能力に生まれつきの体質差(体質性黄疸)がある可能性が考えられます。</v>
       </c>
       <c r="F95" t="str">
-        <v>急性膵炎、慢性膵炎の急性増悪、耳下腺炎（おたふくかぜ）、腎不全</v>
+        <v>溶血性疾患（自己免疫性溶血性貧血、血液型不適合輸血など）、体質性黄疸（ジルベール症候群）、新生児黄疸</v>
       </c>
       <c r="G95" t="str">
-        <v>飲酒を控える、脂っこい食事を避けるよう伝える</v>
+        <v>皮膚や白目の黄染、尿の色の変化がないか確認する</v>
       </c>
       <c r="H95" t="str">
-        <v>慢性膵炎の進行期（膵臓の機能低下）</v>
+        <v/>
       </c>
       <c r="I95" t="str">
         <v/>
       </c>
       <c r="J95" t="str">
-        <v>膵臓由来か唾液腺由来かを区別するには膵型アミラーゼ(P-AMY)を確認する。急性膵炎では強い腹痛・背部痛を伴うことが多く、飲酒歴の確認も重要</v>
+        <v>直接ビリルビンとの比率で原因を推測する（間接優位は溶血・体質性、直接優位は胆道系）。総ビリルビン・AST/ALTと合わせて評価する</v>
       </c>
       <c r="K95" t="str">
-        <v/>
+        <v>肝機能</v>
       </c>
       <c r="L95" t="str">
-        <v>アミラーゼ,AMY,膵炎,急性膵炎</v>
+        <v>間接ビリルビン,I-Bil,溶血</v>
       </c>
       <c r="M95" t="str">
         <v/>
@@ -4319,25 +4319,25 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>間接ビリルビン</v>
+        <v>直接ビリルビン</v>
       </c>
       <c r="B96" t="str">
-        <v>I-Bil</v>
+        <v>D-Bil</v>
       </c>
       <c r="C96" t="str">
-        <v>0.2〜0.8 mg/dL程度（施設差あり）</v>
+        <v>0.0〜0.3 mg/dL程度（施設差あり）</v>
       </c>
       <c r="D96" t="str">
-        <v>赤血球が壊れてできるビリルビンのうち、肝臓で処理される前の形</v>
+        <v>肝臓で処理された後のビリルビン。胆道の詰まりで血液中に増える</v>
       </c>
       <c r="E96" t="str">
-        <v>間接ビリルビンは、赤血球が壊れてできたビリルビンが、まだ肝臓で処理される前の状態です。この値が高い場合、赤血球が通常より多く壊れている(溶血)か、肝臓での処理能力に生まれつきの体質差(体質性黄疸)がある可能性が考えられます。</v>
+        <v>直接ビリルビンは、肝臓で処理された後のビリルビンです。胆石や腫瘍などで胆汁の通り道（胆道）が詰まると、行き場を失って血液中に増え、皮膚や白目が黄色くなる黄疸として現れます。</v>
       </c>
       <c r="F96" t="str">
-        <v>溶血性疾患（自己免疫性溶血性貧血、血液型不適合輸血など）、体質性黄疸（ジルベール症候群）、新生児黄疸</v>
+        <v>肝疾患、胆石など胆道の閉塞</v>
       </c>
       <c r="G96" t="str">
-        <v>皮膚や白目の黄染、尿の色の変化がないか確認する</v>
+        <v>皮膚や白目の黄染、白っぽい便、濃い茶色の尿がないか確認する</v>
       </c>
       <c r="H96" t="str">
         <v/>
@@ -4346,13 +4346,13 @@
         <v/>
       </c>
       <c r="J96" t="str">
-        <v>直接ビリルビンとの比率で原因を推測する（間接優位は溶血・体質性、直接優位は胆道系）。総ビリルビン・AST/ALTと合わせて評価する</v>
+        <v>直接優位の上昇は胆道系（胆石、腫瘍による閉塞）を、間接優位の上昇は溶血・体質性を疑う手がかりになる。γ-GTP・ALPと合わせて胆道系疾患を評価する</v>
       </c>
       <c r="K96" t="str">
         <v>肝機能</v>
       </c>
       <c r="L96" t="str">
-        <v>間接ビリルビン,I-Bil,溶血</v>
+        <v>直接ビリルビン,D-Bil,胆石,胆道閉塞</v>
       </c>
       <c r="M96" t="str">
         <v/>
@@ -4360,130 +4360,89 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>直接ビリルビン</v>
+        <v>亜鉛（Zn）</v>
       </c>
       <c r="B97" t="str">
-        <v>D-Bil</v>
+        <v>Zn</v>
       </c>
       <c r="C97" t="str">
-        <v>0.0〜0.3 mg/dL程度（施設差あり）</v>
+        <v>80〜130 μg/dL程度（施設差あり）</v>
       </c>
       <c r="D97" t="str">
-        <v>肝臓で処理された後のビリルビン。胆道の詰まりで血液中に増える</v>
+        <v>味覚や皮膚、免疫に関わる微量ミネラル。高齢者や低栄養で不足しやすい</v>
       </c>
       <c r="E97" t="str">
-        <v>直接ビリルビンは、肝臓で処理された後のビリルビンです。胆石や腫瘍などで胆汁の通り道（胆道）が詰まると、行き場を失って血液中に増え、皮膚や白目が黄色くなる黄疸として現れます。</v>
+        <v>亜鉛は、味を感じる働きや皮膚・粘膜の健康、免疫の働きに関わる微量ミネラルです。不足すると、味がわかりにくくなったり（味覚障害）、傷が治りにくくなったりすることがあります。</v>
       </c>
       <c r="F97" t="str">
-        <v>肝疾患、胆石など胆道の閉塞</v>
+        <v/>
       </c>
       <c r="G97" t="str">
-        <v>皮膚や白目の黄染、白っぽい便、濃い茶色の尿がないか確認する</v>
+        <v/>
       </c>
       <c r="H97" t="str">
-        <v/>
+        <v>低栄養、高齢による摂取不足、消化器手術後、亜鉛の吸収を妨げる薬剤（PPI、キレート形成する薬剤など）との併用</v>
       </c>
       <c r="I97" t="str">
-        <v/>
+        <v>味覚の変化（味を感じにくい、金属味がするなど）がないか確認する。牡蠣、赤身肉、レバーなど亜鉛を多く含む食品を意識するとよいことを伝える</v>
       </c>
       <c r="J97" t="str">
-        <v>直接優位の上昇は胆道系（胆石、腫瘍による閉塞）を、間接優位の上昇は溶血・体質性を疑う手がかりになる。γ-GTP・ALPと合わせて胆道系疾患を評価する</v>
+        <v>薬剤性の亜鉛欠乏（PPI長期使用、D-ペニシラミン、一部の降圧薬など）に注意。亜鉛欠乏による味覚障害は原因薬剤の中止・亜鉛補充で改善することがある</v>
       </c>
       <c r="K97" t="str">
-        <v>肝機能</v>
+        <v/>
       </c>
       <c r="L97" t="str">
-        <v>直接ビリルビン,D-Bil,胆石,胆道閉塞</v>
+        <v>亜鉛,Zn,味覚障害,亜鉛欠乏</v>
       </c>
       <c r="M97" t="str">
-        <v/>
+        <v>食事と栄養 p.78（亜鉛）</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>亜鉛（Zn）</v>
+        <v>マグネシウム（Mg）</v>
       </c>
       <c r="B98" t="str">
-        <v>Zn</v>
+        <v>Mg</v>
       </c>
       <c r="C98" t="str">
-        <v>80〜130 μg/dL程度（施設差あり）</v>
+        <v>1.8〜2.6 mg/dL程度（施設差あり）</v>
       </c>
       <c r="D98" t="str">
-        <v>味覚や皮膚、免疫に関わる微量ミネラル。高齢者や低栄養で不足しやすい</v>
+        <v>骨や筋肉、神経の働きに関わるミネラル。低栄養や利尿薬で不足しやすい</v>
       </c>
       <c r="E98" t="str">
-        <v>亜鉛は、味を感じる働きや皮膚・粘膜の健康、免疫の働きに関わる微量ミネラルです。不足すると、味がわかりにくくなったり（味覚障害）、傷が治りにくくなったりすることがあります。</v>
+        <v>マグネシウムは、骨や筋肉、神経の働きを支えるミネラルです。不足すると、こむら返りや不整脈、だるさなどの症状が出ることがあります。</v>
       </c>
       <c r="F98" t="str">
-        <v/>
+        <v>腎不全、マグネシウム製剤（酸化マグネシウムなど）の過量投与</v>
       </c>
       <c r="G98" t="str">
-        <v/>
+        <v>腎機能低下がある患者で酸化マグネシウムなどの緩下剤を使用中は、傾眠・血圧低下などの高マグネシウム血症の症状がないか確認する</v>
       </c>
       <c r="H98" t="str">
-        <v>低栄養、高齢による摂取不足、消化器手術後、亜鉛の吸収を妨げる薬剤（PPI、キレート形成する薬剤など）との併用</v>
+        <v>低栄養、利尿薬の使用、慢性的な下痢、アルコール多飲、PPI長期使用</v>
       </c>
       <c r="I98" t="str">
-        <v>味覚の変化（味を感じにくい、金属味がするなど）がないか確認する。牡蠣、赤身肉、レバーなど亜鉛を多く含む食品を意識するとよいことを伝える</v>
+        <v>こむら返りや動悸などの症状がないか確認する</v>
       </c>
       <c r="J98" t="str">
-        <v>薬剤性の亜鉛欠乏（PPI長期使用、D-ペニシラミン、一部の降圧薬など）に注意。亜鉛欠乏による味覚障害は原因薬剤の中止・亜鉛補充で改善することがある</v>
+        <v>腎機能低下患者への酸化マグネシウム投与は高マグネシウム血症のリスクがあるため定期的なモニタリングが必要。PPI長期使用も低マグネシウム血症のリスク因子として知られる</v>
       </c>
       <c r="K98" t="str">
-        <v/>
+        <v>腎機能</v>
       </c>
       <c r="L98" t="str">
-        <v>亜鉛,Zn,味覚障害,亜鉛欠乏</v>
+        <v>マグネシウム,Mg,酸化マグネシウム,こむら返り</v>
       </c>
       <c r="M98" t="str">
-        <v>食事と栄養 p.78（亜鉛）</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="str">
-        <v>マグネシウム（Mg）</v>
-      </c>
-      <c r="B99" t="str">
-        <v>Mg</v>
-      </c>
-      <c r="C99" t="str">
-        <v>1.8〜2.6 mg/dL程度（施設差あり）</v>
-      </c>
-      <c r="D99" t="str">
-        <v>骨や筋肉、神経の働きに関わるミネラル。低栄養や利尿薬で不足しやすい</v>
-      </c>
-      <c r="E99" t="str">
-        <v>マグネシウムは、骨や筋肉、神経の働きを支えるミネラルです。不足すると、こむら返りや不整脈、だるさなどの症状が出ることがあります。</v>
-      </c>
-      <c r="F99" t="str">
-        <v>腎不全、マグネシウム製剤（酸化マグネシウムなど）の過量投与</v>
-      </c>
-      <c r="G99" t="str">
-        <v>腎機能低下がある患者で酸化マグネシウムなどの緩下剤を使用中は、傾眠・血圧低下などの高マグネシウム血症の症状がないか確認する</v>
-      </c>
-      <c r="H99" t="str">
-        <v>低栄養、利尿薬の使用、慢性的な下痢、アルコール多飲、PPI長期使用</v>
-      </c>
-      <c r="I99" t="str">
-        <v>こむら返りや動悸などの症状がないか確認する</v>
-      </c>
-      <c r="J99" t="str">
-        <v>腎機能低下患者への酸化マグネシウム投与は高マグネシウム血症のリスクがあるため定期的なモニタリングが必要。PPI長期使用も低マグネシウム血症のリスク因子として知られる</v>
-      </c>
-      <c r="K99" t="str">
-        <v>腎機能</v>
-      </c>
-      <c r="L99" t="str">
-        <v>マグネシウム,Mg,酸化マグネシウム,こむら返り</v>
-      </c>
-      <c r="M99" t="str">
         <v>食事と栄養 p.84（マグネシウム）</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M99"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M98"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/検査値リファレンス初期データ.xlsx
+++ b/検査値リファレンス初期データ.xlsx
@@ -955,40 +955,40 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>乳酸脱水素酵素（LDH）</v>
+        <v>AST（GOT）</v>
       </c>
       <c r="B14" t="str">
-        <v>LDH</v>
+        <v>AST,GOT</v>
       </c>
       <c r="C14" t="str">
-        <v>120〜245 U/L程度（施設差あり）</v>
+        <v>10〜40 U/L</v>
       </c>
       <c r="D14" t="str">
-        <v>全身のさまざまな組織に含まれる酵素で、細胞が壊れると幅広く上昇する</v>
+        <v>肝臓や心臓・筋肉の細胞が壊れると血液中に漏れ出す酵素</v>
       </c>
       <c r="E14" t="str">
-        <v>LDHは全身の細胞の中にある酵素で、肝臓、心臓、筋肉、血液など、いろいろな組織の細胞がダメージを受けると血液中に漏れ出します。どの臓器が原因かを絞り込むには、他の検査値と組み合わせて評価します。</v>
+        <v>ASTは肝臓や心臓、筋肉の細胞の中にある酵素です。これらの細胞がダメージを受けたり壊れたりすると血液中に漏れ出して数値が上がります。肝臓の状態を見るときはALTと一緒に確認します。</v>
       </c>
       <c r="F14" t="str">
-        <v>肝疾患、心筋梗塞、溶血性疾患、悪性腫瘍、筋肉の障害（横紋筋融解症など）、肺疾患</v>
+        <v>肝炎・肝硬変などの肝疾患、心筋梗塞、筋肉の障害（激しい運動・横紋筋融解症）、薬剤性肝障害</v>
       </c>
       <c r="G14" t="str">
-        <v/>
+        <v>飲酒量を控える。激しい運動の直後の採血でないかを確認する</v>
       </c>
       <c r="H14" t="str">
-        <v/>
+        <v>臨床的に問題になることは少ない</v>
       </c>
       <c r="I14" t="str">
         <v/>
       </c>
       <c r="J14" t="str">
-        <v>臓器特異性が低いため単独では原因を特定しにくい。AST/ALT(肝)、CK(筋)、ビリルビン・ハプトグロビン(溶血)など他の検査値と組み合わせて原因臓器を推定する</v>
+        <v>ALTとの比率（AST/ALT比）で肝細胞障害か他臓器由来かを推測できる。AST優位はアルコール性・心筋・筋由来を疑う材料になる</v>
       </c>
       <c r="K14" t="str">
-        <v/>
+        <v>肝機能,糖尿病,てんかん,精神疾患（非定型抗精神病薬）</v>
       </c>
       <c r="L14" t="str">
-        <v>LDH,乳酸脱水素酵素,溶血,心筋梗塞,悪性腫瘍</v>
+        <v>AST,GOT,肝機能,肝障害</v>
       </c>
       <c r="M14" t="str">
         <v/>
@@ -996,25 +996,25 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>AST（GOT）</v>
+        <v>ALT（GPT）</v>
       </c>
       <c r="B15" t="str">
-        <v>AST,GOT</v>
+        <v>ALT,GPT</v>
       </c>
       <c r="C15" t="str">
-        <v>10〜40 U/L</v>
+        <v>5〜40 U/L</v>
       </c>
       <c r="D15" t="str">
-        <v>肝臓や心臓・筋肉の細胞が壊れると血液中に漏れ出す酵素</v>
+        <v>主に肝臓の細胞に含まれる酵素で、肝障害の指標として最もよく使われる</v>
       </c>
       <c r="E15" t="str">
-        <v>ASTは肝臓や心臓、筋肉の細胞の中にある酵素です。これらの細胞がダメージを受けたり壊れたりすると血液中に漏れ出して数値が上がります。肝臓の状態を見るときはALTと一緒に確認します。</v>
+        <v>ALTは主に肝臓の細胞の中にある酵素です。肝臓の細胞がダメージを受けると血液中に漏れ出して数値が上がります。ASTよりも肝臓に特異的な数値なので、肝臓の状態を見るときによく使われます。</v>
       </c>
       <c r="F15" t="str">
-        <v>肝炎・肝硬変などの肝疾患、心筋梗塞、筋肉の障害（激しい運動・横紋筋融解症）、薬剤性肝障害</v>
+        <v>脂肪肝、肝炎（ウイルス性・アルコール性・薬剤性）、肝硬変、薬の副作用による肝機能障害</v>
       </c>
       <c r="G15" t="str">
-        <v>飲酒量を控える。激しい運動の直後の採血でないかを確認する</v>
+        <v>体重管理と脂質の摂りすぎに注意する（脂肪肝が疑われる場合）。新規薬剤の開始時期と重なっていないか確認する</v>
       </c>
       <c r="H15" t="str">
         <v>臨床的に問題になることは少ない</v>
@@ -1023,13 +1023,13 @@
         <v/>
       </c>
       <c r="J15" t="str">
-        <v>ALTとの比率（AST/ALT比）で肝細胞障害か他臓器由来かを推測できる。AST優位はアルコール性・心筋・筋由来を疑う材料になる</v>
+        <v>新規薬剤開始後の肝障害の指標として重要。健診でALTのみ軽度上昇していることが多く、その場合は脂肪肝（NAFLD）の頻度が高い</v>
       </c>
       <c r="K15" t="str">
         <v>肝機能,糖尿病,てんかん,精神疾患（非定型抗精神病薬）</v>
       </c>
       <c r="L15" t="str">
-        <v>AST,GOT,肝機能,肝障害</v>
+        <v>ALT,GPT,肝機能,肝障害,脂肪肝</v>
       </c>
       <c r="M15" t="str">
         <v/>
@@ -1037,40 +1037,40 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ALT（GPT）</v>
+        <v>乳酸脱水素酵素（LDH）</v>
       </c>
       <c r="B16" t="str">
-        <v>ALT,GPT</v>
+        <v>LDH</v>
       </c>
       <c r="C16" t="str">
-        <v>5〜40 U/L</v>
+        <v>120〜245 U/L程度（施設差あり）</v>
       </c>
       <c r="D16" t="str">
-        <v>主に肝臓の細胞に含まれる酵素で、肝障害の指標として最もよく使われる</v>
+        <v>全身のさまざまな組織に含まれる酵素で、細胞が壊れると幅広く上昇する</v>
       </c>
       <c r="E16" t="str">
-        <v>ALTは主に肝臓の細胞の中にある酵素です。肝臓の細胞がダメージを受けると血液中に漏れ出して数値が上がります。ASTよりも肝臓に特異的な数値なので、肝臓の状態を見るときによく使われます。</v>
+        <v>LDHは全身の細胞の中にある酵素で、肝臓、心臓、筋肉、血液など、いろいろな組織の細胞がダメージを受けると血液中に漏れ出します。どの臓器が原因かを絞り込むには、他の検査値と組み合わせて評価します。</v>
       </c>
       <c r="F16" t="str">
-        <v>脂肪肝、肝炎（ウイルス性・アルコール性・薬剤性）、肝硬変、薬の副作用による肝機能障害</v>
+        <v>肝疾患、心筋梗塞、溶血性疾患、悪性腫瘍、筋肉の障害（横紋筋融解症など）、肺疾患</v>
       </c>
       <c r="G16" t="str">
-        <v>体重管理と脂質の摂りすぎに注意する（脂肪肝が疑われる場合）。新規薬剤の開始時期と重なっていないか確認する</v>
+        <v/>
       </c>
       <c r="H16" t="str">
-        <v>臨床的に問題になることは少ない</v>
+        <v/>
       </c>
       <c r="I16" t="str">
         <v/>
       </c>
       <c r="J16" t="str">
-        <v>新規薬剤開始後の肝障害の指標として重要。健診でALTのみ軽度上昇していることが多く、その場合は脂肪肝（NAFLD）の頻度が高い</v>
+        <v>臓器特異性が低いため単独では原因を特定しにくい。AST/ALT(肝)、CK(筋)、ビリルビン・ハプトグロビン(溶血)など他の検査値と組み合わせて原因臓器を推定する</v>
       </c>
       <c r="K16" t="str">
-        <v>肝機能,糖尿病,てんかん,精神疾患（非定型抗精神病薬）</v>
+        <v/>
       </c>
       <c r="L16" t="str">
-        <v>ALT,GPT,肝機能,肝障害,脂肪肝</v>
+        <v>LDH,乳酸脱水素酵素,溶血,心筋梗塞,悪性腫瘍</v>
       </c>
       <c r="M16" t="str">
         <v/>
@@ -4681,42 +4681,42 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>甲状腺疾患</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="B12" t="str">
         <v/>
       </c>
       <c r="C12" t="str">
-        <v>動悸や体重の増減はありませんか／だるさやむくみ、逆に暑がり・手のふるえはありませんか／薬の量が変わってから体調の変化はありますか</v>
+        <v>立ちくらみやめまい、動悸、息切れはありませんか／食事量や偏りはありますか／黒い便や月経量の変化など、出血を疑う症状はありませんか</v>
       </c>
       <c r="D12" t="str">
-        <v>【機能低下気味の時】だるさやむくみはありませんか。お薬の量を確認しますね　【機能亢進気味の時】動悸や体重減少はありませんか。念のため数値を確認しましょう</v>
+        <v>【悪化した時】ふらつきや動悸は増えていませんか。原因を確認させてください　【改善した時】数値が良くなってきています。鉄剤は数値が戻ってからもしばらく続けることが大切です</v>
       </c>
       <c r="E12" t="str">
-        <v>チラーヂンSは食後だと吸収が落ちやすく、起床時空腹での服用が基本であること。メルカゾールは無顆粒球症の初期症状（発熱・のどの痛み）が出たらすぐ受診が必要なこと</v>
+        <v>鉄剤は自己判断で早期中断されやすい。出血源（消化管出血・月経過多等）の精査が済んでいるか</v>
       </c>
       <c r="F12" t="str">
-        <v>食事と栄養 p.224-228（第2部 甲状腺疾患 Q95-98）</v>
+        <v>食事と栄養 p.151-164（第2部 貧血 Q41-50）</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>甲状腺疾患</v>
       </c>
       <c r="B13" t="str">
         <v/>
       </c>
       <c r="C13" t="str">
-        <v>立ちくらみやめまい、動悸、息切れはありませんか／食事量や偏りはありますか／黒い便や月経量の変化など、出血を疑う症状はありませんか</v>
+        <v>動悸や体重の増減はありませんか／だるさやむくみ、逆に暑がり・手のふるえはありませんか／薬の量が変わってから体調の変化はありますか</v>
       </c>
       <c r="D13" t="str">
-        <v>【悪化した時】ふらつきや動悸は増えていませんか。原因を確認させてください　【改善した時】数値が良くなってきています。鉄剤は数値が戻ってからもしばらく続けることが大切です</v>
+        <v>【機能低下気味の時】だるさやむくみはありませんか。お薬の量を確認しますね　【機能亢進気味の時】動悸や体重減少はありませんか。念のため数値を確認しましょう</v>
       </c>
       <c r="E13" t="str">
-        <v>鉄剤は自己判断で早期中断されやすい。出血源（消化管出血・月経過多等）の精査が済んでいるか</v>
+        <v>チラーヂンSは食後だと吸収が落ちやすく、起床時空腹での服用が基本であること。メルカゾールは無顆粒球症の初期症状（発熱・のどの痛み）が出たらすぐ受診が必要なこと</v>
       </c>
       <c r="F13" t="str">
-        <v>食事と栄養 p.151-164（第2部 貧血 Q41-50）</v>
+        <v>食事と栄養 p.224-228（第2部 甲状腺疾患 Q95-98）</v>
       </c>
     </row>
     <row r="14">

--- a/検査値リファレンス初期データ.xlsx
+++ b/検査値リファレンス初期データ.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M98"/>
+  <dimension ref="A1:N100"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -408,11 +408,12 @@
     <col min="6" max="6" width="18.83203125" customWidth="1"/>
     <col min="7" max="7" width="32.83203125" customWidth="1"/>
     <col min="8" max="8" width="18.83203125" customWidth="1"/>
-    <col min="9" max="9" width="32.83203125" customWidth="1"/>
-    <col min="10" max="10" width="35.83203125" customWidth="1"/>
-    <col min="11" max="11" width="18.83203125" customWidth="1"/>
+    <col min="9" max="9" width="18.83203125" customWidth="1"/>
+    <col min="10" max="10" width="32.83203125" customWidth="1"/>
+    <col min="11" max="11" width="35.83203125" customWidth="1"/>
     <col min="12" max="12" width="18.83203125" customWidth="1"/>
-    <col min="13" max="13" width="14.83203125" customWidth="1"/>
+    <col min="13" max="13" width="18.83203125" customWidth="1"/>
+    <col min="14" max="14" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -438,21 +439,24 @@
         <v>高値の時のアドバイス</v>
       </c>
       <c r="H1" t="str">
+        <v>高値の時に注意する薬</v>
+      </c>
+      <c r="I1" t="str">
         <v>低値で考えること</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>低値の時のアドバイス</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>薬剤師補足</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>疾患タグ</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>検索キーワード</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
         <v>参考ページ</v>
       </c>
     </row>
@@ -480,21 +484,24 @@
         <v>食後の血糖上昇を抑えるため、早食い・まとめ食いを避け、野菜から食べる順番を意識する</v>
       </c>
       <c r="H2" t="str">
+        <v>ステロイド、サイアザイド系利尿薬、非定型抗精神病薬(オランザピン・クエチアピン)、タクロリムス・シクロスポリン、β遮断薬、高カロリー輸液</v>
+      </c>
+      <c r="I2" t="str">
         <v>低血糖（薬剤性、食事摂取不足、シックデイ時の過量投与など）</v>
       </c>
-      <c r="I2" t="str">
+      <c r="J2" t="str">
         <v>空腹時間が長くならないよう食事を規則正しくとる。冷や汗・動悸・強い空腹感などの低血糖症状が出たらすぐに糖分を摂る</v>
       </c>
-      <c r="J2" t="str">
+      <c r="K2" t="str">
         <v>採血のタイミング（空腹時か食後か）を必ず確認する。SU薬・インスリン使用者では低血糖症状の有無も併せて聞く</v>
       </c>
-      <c r="K2" t="str">
+      <c r="L2" t="str">
         <v>糖尿病,精神疾患（非定型抗精神病薬）</v>
       </c>
-      <c r="L2" t="str">
+      <c r="M2" t="str">
         <v>血糖値,血糖,BS,Glu,グルコース,空腹時血糖,随時血糖,食後血糖</v>
       </c>
-      <c r="M2" t="str">
+      <c r="N2" t="str">
         <v>食事と栄養 p.18（炭水化物）／p.106-131（第2部 糖尿病）</v>
       </c>
     </row>
@@ -521,21 +528,24 @@
         <v>主食の量や間食の頻度を見直す、体を動かす機会を増やす。飲み忘れがあれば服薬タイミングを一緒に確認する</v>
       </c>
       <c r="H3" t="str">
+        <v>血糖と同様(ステロイド、非定型抗精神病薬、サイアザイド系利尿薬など)。SU薬・インスリンを使用中なら低血糖の有無も確認</v>
+      </c>
+      <c r="I3" t="str">
         <v>低血糖を繰り返している状態</v>
       </c>
-      <c r="I3" t="str">
+      <c r="J3" t="str">
         <v>低血糖を防ぐため、食事の間隔をあけすぎないようにする。ブドウ糖など対処品の携帯を勧める</v>
       </c>
-      <c r="J3" t="str">
+      <c r="K3" t="str">
         <v>貧血・鉄剤補充・妊娠・腎不全などがあると、実際の血糖値とズレて出ることがある。直近の血糖自己測定値と合わせて確認する</v>
       </c>
-      <c r="K3" t="str">
+      <c r="L3" t="str">
         <v>糖尿病,精神疾患（非定型抗精神病薬）</v>
       </c>
-      <c r="L3" t="str">
+      <c r="M3" t="str">
         <v>HbA1c,ヘモグロビンエーワンシー,グリコヘモグロビン,血糖コントロール,NGSP</v>
       </c>
-      <c r="M3" t="str">
+      <c r="N3" t="str">
         <v>食事と栄養 p.18（炭水化物）／p.106-131（第2部 糖尿病）</v>
       </c>
     </row>
@@ -562,21 +572,24 @@
         <v>脱水を避けてこまめに水分を摂る。極端な高たんぱく食が続いていないか確認する</v>
       </c>
       <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
         <v>低たんぱく食、肝不全によるたんぱく合成低下、妊娠</v>
       </c>
-      <c r="I4" t="str">
-        <v/>
-      </c>
       <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
         <v>クレアチニンと同時に見る。BUN/Cr比が高ければ脱水や消化管出血を、比が正常で両方高ければ腎性を疑う目安になる</v>
       </c>
-      <c r="K4" t="str">
+      <c r="L4" t="str">
         <v>腎機能,糖尿病,骨粗鬆症,抗凝固療法（心房細動・血栓症）</v>
       </c>
-      <c r="L4" t="str">
+      <c r="M4" t="str">
         <v>BUN,尿素窒素,UN,腎機能</v>
       </c>
-      <c r="M4" t="str">
+      <c r="N4" t="str">
         <v>食事と栄養 p.199-215（第2部 腎機能低下）</v>
       </c>
     </row>
@@ -604,23 +617,26 @@
         <v>脱水を避けてこまめに水分を摂る（心不全等で水分制限がある場合を除く）。塩分の摂りすぎに注意する</v>
       </c>
       <c r="H5" t="str">
+        <v>腎排泄型薬剤の減量要否を確認(ジゴキシン、NOAC、メトホルミン、アミノグリコシド系、バンコマイシン等)。悪化させうる代表薬はNSAIDs・ARB/ACE阻害薬・利尿薬・造影剤・アミノグリコシド系</v>
+      </c>
+      <c r="I5" t="str">
         <v>クレアチニンが低い場合：筋肉量の低下、高齢・るいそうで見かけ上低く出ることがある</v>
       </c>
-      <c r="I5" t="str">
-        <v/>
-      </c>
-      <c r="J5" t="str" xml:space="preserve">
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str" xml:space="preserve">
         <v xml:space="preserve">筋肉量に影響されるため、るいそうの強い高齢者では腎機能を過大評価しやすい。eGFR低下時は腎排泄型薬剤の用量調整を確認する。
 CKD重症度分類（GFR区分）の目安：G1 正常または高値(90以上)／G2 正常または軽度低下(60〜89)／G3a 軽度〜中等度低下(45〜59)／G3b 中等度〜高度低下(30〜44)／G4 高度低下(15〜29)／G5 末期腎不全(15未満)。
 eGFRには体表面積1.73㎡に標準化した「標準化eGFR」（CKD病期の判定などに使用）と、実際の体表面積で補正した「個別化eGFR」（標準化eGFR×体表面積÷1.73、薬剤投与量の決定に使用）があり、体格が標準から大きく外れる患者では両者がずれるため、用量調整の場面では個別化eGFRやCCrを優先する</v>
       </c>
-      <c r="K5" t="str">
+      <c r="L5" t="str">
         <v>腎機能,糖尿病,骨粗鬆症,抗凝固療法（心房細動・血栓症）</v>
       </c>
-      <c r="L5" t="str">
+      <c r="M5" t="str">
         <v>クレアチニン,Cr,SCr,血清クレアチニン,eGFR,腎機能,GFR,推算糸球体濾過量,CKD重症度分類</v>
       </c>
-      <c r="M5" t="str">
+      <c r="N5" t="str">
         <v>食事と栄養 p.199-215（第2部 腎機能低下）／p.243（フレイルQ111 クレアチニン値が低い場合）</v>
       </c>
     </row>
@@ -647,22 +663,25 @@
         <v/>
       </c>
       <c r="H6" t="str">
+        <v>添付文書のCCr基準で減量が必要な薬剤(NOAC、ST合剤、アシクロビル等)の用量を確認</v>
+      </c>
+      <c r="I6" t="str">
         <v>腎機能の低下（数値が低いほどろ過機能の低下を示す）、脱水、加齢に伴う腎機能低下、糖尿病性腎症など</v>
       </c>
-      <c r="I6" t="str">
+      <c r="J6" t="str">
         <v>脱水を避けてこまめに水分を摂る（水分制限がある場合を除く）。腎排泄型の薬剤は減量や投与間隔の延長が必要になることがあるため、お薬手帳を最新の状態に保つ</v>
       </c>
-      <c r="J6" t="str" xml:space="preserve">
+      <c r="K6" t="str" xml:space="preserve">
         <v xml:space="preserve">Cockcroft-Gault式［(140−年齢)×体重(kg)÷(72×血清Cr)、女性は×0.85］で算出した推算CCrが、多くの薬剤の添付文書における腎機能別用量調整の基準に使われる。eGFRは体表面積1.73㎡で標準化した値のため、実際の体格が標準から離れる患者（高齢・るいそう・肥満など）では、添付文書のCCr基準にそのまま当てはめると過大・過小評価になりうる点に注意。
 血清Cr(mg/dL)からのおおまかな対応の目安：0.7〜1.4→CCr100±20（正常・健常）／1.4〜2.4→61〜99（日常生活に支障なし）／2.5〜4.9→24〜60（日常生活に多少の支障）／5.0〜7.9→12〜23（日常生活に支障あり）／8.0〜12.0→7〜12（日常生活の規制）／12.0超→6未満（昏睡・見当識障害）</v>
       </c>
-      <c r="K6" t="str">
+      <c r="L6" t="str">
         <v>腎機能,糖尿病,骨粗鬆症,抗凝固療法（心房細動・血栓症）</v>
       </c>
-      <c r="L6" t="str">
+      <c r="M6" t="str">
         <v>CCr,クレアチニンクリアランス,クレアチニン・クリアランス,creatinine clearance,コッククロフトゴート,Cockcroft-Gault,腎機能</v>
       </c>
-      <c r="M6" t="str">
+      <c r="N6" t="str">
         <v>食事と栄養 p.199-215（第2部 腎機能低下）</v>
       </c>
     </row>
@@ -689,21 +708,24 @@
         <v>プリン体の多い食品（レバー・魚卵・干物・ビールなど）を控えめにし、水分を多めに摂る</v>
       </c>
       <c r="H7" t="str">
+        <v>サイアザイド系利尿薬、ループ利尿薬、少量アスピリン、ピラジナミド、シクロスポリンは上昇させうる。尿酸降下薬(アロプリノール等)服用中はコントロール状況も確認</v>
+      </c>
+      <c r="I7" t="str">
         <v>尿酸排泄促進薬の効果、まれに特発性腎性低尿酸血症</v>
       </c>
-      <c r="I7" t="str">
-        <v/>
-      </c>
       <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
         <v>利尿薬（サイアザイド系など）は尿酸を上げやすい。急激に尿酸を下げる治療の開始直後は痛風発作が誘発されることがある</v>
       </c>
-      <c r="K7" t="str">
+      <c r="L7" t="str">
         <v>高尿酸血症,糖尿病</v>
       </c>
-      <c r="L7" t="str">
+      <c r="M7" t="str">
         <v>尿酸,UA,痛風,高尿酸血症</v>
       </c>
-      <c r="M7" t="str">
+      <c r="N7" t="str">
         <v>食事と栄養 p.180-189（第2部 痛風・高尿酸血症）</v>
       </c>
     </row>
@@ -730,21 +752,24 @@
         <v>水分摂取状況を確認する（脱水が疑われる場合）</v>
       </c>
       <c r="H8" t="str">
+        <v>高張輸液、浸透圧利尿薬(グリセオール等)、抗利尿ホルモン分泌を低下させる薬(炭酸リチウム等)</v>
+      </c>
+      <c r="I8" t="str">
         <v>利尿薬（特にサイアザイド系）、SIADH（抗利尿ホルモン不適合分泌症候群）、嘔吐・下痢、心不全・肝硬変によるむくみ</v>
       </c>
-      <c r="I8" t="str">
+      <c r="J8" t="str">
         <v>利尿薬使用中は嘔吐・下痢が続いていないか確認する。意識がぼんやりする、頭痛などの症状がないか確認する</v>
       </c>
-      <c r="J8" t="str">
+      <c r="K8" t="str">
         <v>低ナトリウム血症は高齢者に多く、意識障害や転倒の原因になりうる。利尿薬（特にサイアザイド系）、SSRI、カルバマゼピンなどSIADHを起こしうる薬剤の使用歴を確認する</v>
       </c>
-      <c r="K8" t="str">
+      <c r="L8" t="str">
         <v>電解質</v>
       </c>
-      <c r="L8" t="str">
+      <c r="M8" t="str">
         <v>ナトリウム,Na,電解質,脱水,SIADH,低ナトリウム血症</v>
       </c>
-      <c r="M8" t="str">
+      <c r="N8" t="str">
         <v>食事と栄養 p.81（ナトリウム）</v>
       </c>
     </row>
@@ -771,21 +796,24 @@
         <v>脱水が疑われる場合はこまめな水分摂取を勧める（水分制限がある場合を除く）</v>
       </c>
       <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
         <v>嘔吐・下痢、利尿薬使用、代謝性アルカローシス</v>
       </c>
-      <c r="I9" t="str">
+      <c r="J9" t="str">
         <v>利尿薬使用中は嘔吐・下痢が続いていないか確認する</v>
       </c>
-      <c r="J9" t="str">
+      <c r="K9" t="str">
         <v>ナトリウムと同じ方向に動くことが多いが、酸塩基平衡の異常（アシドーシス・アルカローシス）を反映して単独で動くこともある。利尿薬（特にループ利尿薬）使用中は低クロール性アルカローシスに注意</v>
       </c>
-      <c r="K9" t="str">
+      <c r="L9" t="str">
         <v>電解質,腎機能</v>
       </c>
-      <c r="L9" t="str">
+      <c r="M9" t="str">
         <v>クロール,Cl,塩素,電解質,アシドーシス,アルカローシス</v>
       </c>
-      <c r="M9" t="str">
+      <c r="N9" t="str">
         <v/>
       </c>
     </row>
@@ -812,21 +840,24 @@
         <v>生野菜・果物・芋類などカリウムの多い食品の摂りすぎに注意する（腎機能低下がある場合）</v>
       </c>
       <c r="H10" t="str">
+        <v>ACE阻害薬、ARB、カリウム保持性利尿薬(スピロノラクトン等)、NSAIDs、ST合剤、ヘパリン。β遮断薬は細胞内への取り込みを阻害し上昇させうる</v>
+      </c>
+      <c r="I10" t="str">
         <v>利尿薬（特にループ・サイアザイド系）、下痢・嘔吐、インスリン投与、甘草含有製剤</v>
       </c>
-      <c r="I10" t="str">
+      <c r="J10" t="str">
         <v>利尿薬使用中は下痢・嘔吐が続いていないか確認し、必要に応じてバナナ・芋類などカリウムを含む食品を意識する</v>
       </c>
-      <c r="J10" t="str">
+      <c r="K10" t="str">
         <v>高カリウム血症は不整脈・心停止のリスクがあるため脱力感・動悸の有無を確認。RAS阻害薬とカリウム保持性利尿薬の併用時は特に注意</v>
       </c>
-      <c r="K10" t="str">
+      <c r="L10" t="str">
         <v>腎機能,電解質</v>
       </c>
-      <c r="L10" t="str">
+      <c r="M10" t="str">
         <v>カリウム,K,高カリウム血症,低カリウム血症</v>
       </c>
-      <c r="M10" t="str">
+      <c r="N10" t="str">
         <v>食事と栄養 p.72（カリウム）／p.199-215（第2部 腎機能低下 Q80-82 カリウム制限）</v>
       </c>
     </row>
@@ -853,21 +884,24 @@
         <v>吐き気、便秘、多尿、意識がぼんやりするなどの高カルシウム血症の症状がないか確認する。活性型ビタミンD3製剤使用中は過量になっていないか確認する</v>
       </c>
       <c r="H11" t="str">
+        <v>活性型ビタミンD製剤、サイアザイド系利尿薬、炭酸リチウム、カルシウム含有薬(炭酸カルシウム等)</v>
+      </c>
+      <c r="I11" t="str">
         <v>副甲状腺機能低下症、ビタミンD欠乏、腎不全、低アルブミン血症（見かけ上の低下）</v>
       </c>
-      <c r="I11" t="str">
+      <c r="J11" t="str">
         <v>手足のしびれやこむら返りなど低カルシウム血症の症状がないか確認する</v>
       </c>
-      <c r="J11" t="str">
+      <c r="K11" t="str">
         <v>アルブミンが低いと見かけ上低く出るため、補正カルシウム値（Ca+(4-Alb)）で評価する。骨粗鬆症治療薬（活性型ビタミンD3製剤、デノスマブなど）使用中は高カルシウム血症の副作用に注意</v>
       </c>
-      <c r="K11" t="str">
+      <c r="L11" t="str">
         <v>電解質,骨粗鬆症</v>
       </c>
-      <c r="L11" t="str">
+      <c r="M11" t="str">
         <v>カルシウム,Ca,電解質</v>
       </c>
-      <c r="M11" t="str">
+      <c r="N11" t="str">
         <v>食事と栄養 p.75（カルシウム）／p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
@@ -894,21 +928,24 @@
         <v/>
       </c>
       <c r="H12" t="str">
+        <v>(実測カルシウムに準ずる)活性型ビタミンD製剤、サイアザイド系利尿薬、炭酸リチウム</v>
+      </c>
+      <c r="I12" t="str">
         <v>（実測カルシウムの低値と同様）副甲状腺機能低下症、ビタミンD欠乏、腎不全</v>
       </c>
-      <c r="I12" t="str">
-        <v/>
-      </c>
       <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
         <v>補正カルシウム(mg/dL) = 実測カルシウム + (4 − アルブミン値)の式で計算する。アルブミンが4.0 g/dL未満の低栄養患者やネフローゼ症候群の患者では、実測カルシウムだけで判断すると誤りやすいため、この補正値で評価する</v>
       </c>
-      <c r="K12" t="str">
+      <c r="L12" t="str">
         <v>電解質,骨粗鬆症</v>
       </c>
-      <c r="L12" t="str">
+      <c r="M12" t="str">
         <v>補正カルシウム,Corrected Calcium,アルブミン補正,低アルブミン血症</v>
       </c>
-      <c r="M12" t="str">
+      <c r="N12" t="str">
         <v/>
       </c>
     </row>
@@ -935,21 +972,24 @@
         <v/>
       </c>
       <c r="H13" t="str">
+        <v>活性型ビタミンD製剤、リン含有製剤。腎機能低下患者では特に注意</v>
+      </c>
+      <c r="I13" t="str">
         <v>副甲状腺機能亢進症、骨軟化症、ビタミンD欠乏</v>
       </c>
-      <c r="I13" t="str">
-        <v/>
-      </c>
       <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
         <v>カルシウムと逆方向に動くことが多い（副甲状腺機能亢進症ではCa上昇・P低下）。骨粗鬆症の二次性原因の除外に用いられる</v>
       </c>
-      <c r="K13" t="str">
+      <c r="L13" t="str">
         <v>骨粗鬆症,電解質</v>
       </c>
-      <c r="L13" t="str">
+      <c r="M13" t="str">
         <v>リン,P,IP,無機リン</v>
       </c>
-      <c r="M13" t="str">
+      <c r="N13" t="str">
         <v>食事と栄養 p.165-178（第2部 骨粗鬆症）／p.199-215（第2部 腎機能低下 Q83 リン制限）</v>
       </c>
     </row>
@@ -976,21 +1016,24 @@
         <v>飲酒量を控える。激しい運動の直後の採血でないかを確認する</v>
       </c>
       <c r="H14" t="str">
+        <v>アセトアミノフェン(過量)、スタチン系、抗結核薬(イソニアジド・リファンピシン)、バルプロ酸、NSAIDs、メトトレキサート</v>
+      </c>
+      <c r="I14" t="str">
         <v>臨床的に問題になることは少ない</v>
       </c>
-      <c r="I14" t="str">
-        <v/>
-      </c>
       <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
         <v>ALTとの比率（AST/ALT比）で肝細胞障害か他臓器由来かを推測できる。AST優位はアルコール性・心筋・筋由来を疑う材料になる</v>
       </c>
-      <c r="K14" t="str">
+      <c r="L14" t="str">
         <v>肝機能,糖尿病,てんかん,精神疾患（非定型抗精神病薬）</v>
       </c>
-      <c r="L14" t="str">
+      <c r="M14" t="str">
         <v>AST,GOT,肝機能,肝障害</v>
       </c>
-      <c r="M14" t="str">
+      <c r="N14" t="str">
         <v/>
       </c>
     </row>
@@ -1017,21 +1060,24 @@
         <v>体重管理と脂質の摂りすぎに注意する（脂肪肝が疑われる場合）。新規薬剤の開始時期と重なっていないか確認する</v>
       </c>
       <c r="H15" t="str">
+        <v>アセトアミノフェン(過量)、スタチン系、抗結核薬(イソニアジド・リファンピシン)、バルプロ酸、NSAIDs、メトトレキサート</v>
+      </c>
+      <c r="I15" t="str">
         <v>臨床的に問題になることは少ない</v>
       </c>
-      <c r="I15" t="str">
-        <v/>
-      </c>
       <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
         <v>新規薬剤開始後の肝障害の指標として重要。健診でALTのみ軽度上昇していることが多く、その場合は脂肪肝（NAFLD）の頻度が高い</v>
       </c>
-      <c r="K15" t="str">
+      <c r="L15" t="str">
         <v>肝機能,糖尿病,てんかん,精神疾患（非定型抗精神病薬）</v>
       </c>
-      <c r="L15" t="str">
+      <c r="M15" t="str">
         <v>ALT,GPT,肝機能,肝障害,脂肪肝</v>
       </c>
-      <c r="M15" t="str">
+      <c r="N15" t="str">
         <v/>
       </c>
     </row>
@@ -1064,15 +1110,18 @@
         <v/>
       </c>
       <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
         <v>臓器特異性が低いため単独では原因を特定しにくい。AST/ALT(肝)、CK(筋)、ビリルビン・ハプトグロビン(溶血)など他の検査値と組み合わせて原因臓器を推定する</v>
       </c>
-      <c r="K16" t="str">
-        <v/>
-      </c>
       <c r="L16" t="str">
+        <v/>
+      </c>
+      <c r="M16" t="str">
         <v>LDH,乳酸脱水素酵素,溶血,心筋梗塞,悪性腫瘍</v>
       </c>
-      <c r="M16" t="str">
+      <c r="N16" t="str">
         <v/>
       </c>
     </row>
@@ -1099,27 +1148,30 @@
         <v>脂肪肝が疑われる場合は食事・運動習慣の見直しを勧める</v>
       </c>
       <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
         <v>肝硬変など肝臓の合成能低下、低栄養、有機リン中毒（農薬など）</v>
       </c>
-      <c r="I17" t="str">
-        <v/>
-      </c>
       <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
         <v>アルブミンと同様に肝臓の「合成能」を見る指標。低栄養か肝硬変かは、アルブミンや血小板数（肝硬変で低下しやすい）と合わせて判断する</v>
       </c>
-      <c r="K17" t="str">
+      <c r="L17" t="str">
         <v>肝機能</v>
       </c>
-      <c r="L17" t="str">
+      <c r="M17" t="str">
         <v>コリンエステラーゼ,ChE,肝合成能,脂肪肝,肝硬変</v>
       </c>
-      <c r="M17" t="str">
+      <c r="N17" t="str">
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>アルカリホスファターゼ（ALP）</v>
+        <v>アルカリフォスファターゼ（ALP）</v>
       </c>
       <c r="B18" t="str">
         <v>ALP</v>
@@ -1140,21 +1192,24 @@
         <v/>
       </c>
       <c r="H18" t="str">
-        <v/>
+        <v>抗てんかん薬(フェニトイン等)、胆汁うっ滞型の薬剤性肝障害を起こしうる抗菌薬・NSAIDs</v>
       </c>
       <c r="I18" t="str">
         <v/>
       </c>
       <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
         <v>骨由来か肝由来かの区別には骨型ALPアイソザイムやγ-GTPとの組み合わせで判断する</v>
       </c>
-      <c r="K18" t="str">
+      <c r="L18" t="str">
         <v>骨粗鬆症,肝機能</v>
       </c>
-      <c r="L18" t="str">
-        <v>ALP,アルカリホスファターゼ,骨代謝,肝機能</v>
-      </c>
       <c r="M18" t="str">
+        <v>ALP,アルカリフォスファターゼ,骨代謝,肝機能</v>
+      </c>
+      <c r="N18" t="str">
         <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
@@ -1182,21 +1237,24 @@
         <v>飲酒量を控える、休肝日をつくるよう伝える</v>
       </c>
       <c r="H19" t="str">
+        <v>アルコール、フェニトイン、バルビツール酸系など肝薬物代謝酵素誘導作用のある薬剤</v>
+      </c>
+      <c r="I19" t="str">
         <v>臨床的に問題になることは少ない</v>
       </c>
-      <c r="I19" t="str">
-        <v/>
-      </c>
       <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
         <v>飲酒歴の確認に使いやすい数値。断酒・節酒で比較的早く改善するため、生活指導の効果を示す指標としても使える</v>
       </c>
-      <c r="K19" t="str">
+      <c r="L19" t="str">
         <v>肝機能</v>
       </c>
-      <c r="L19" t="str">
+      <c r="M19" t="str">
         <v>ガンマGTP,γ-GTP,GGT,肝機能,飲酒,アルコール</v>
       </c>
-      <c r="M19" t="str">
+      <c r="N19" t="str">
         <v/>
       </c>
     </row>
@@ -1223,21 +1281,24 @@
         <v>皮膚や白目の黄染、尿の色が濃くなっていないか確認する</v>
       </c>
       <c r="H20" t="str">
-        <v/>
+        <v>肝毒性のある薬剤全般に加え、シクロスポリン・リファンピシン(トランスポーター阻害による上昇)</v>
       </c>
       <c r="I20" t="str">
         <v/>
       </c>
       <c r="J20" t="str">
+        <v/>
+      </c>
+      <c r="K20" t="str">
         <v>直接ビリルビン・間接ビリルビンの内訳で原因を推測できる（直接優位は胆道系、間接優位は溶血・体質性）。AST/ALT/γ-GTPと合わせて評価する</v>
       </c>
-      <c r="K20" t="str">
+      <c r="L20" t="str">
         <v>肝機能</v>
       </c>
-      <c r="L20" t="str">
+      <c r="M20" t="str">
         <v>総ビリルビン,T-Bil,黄疸,ビリルビン,ジルベール症候群</v>
       </c>
-      <c r="M20" t="str">
+      <c r="N20" t="str">
         <v/>
       </c>
     </row>
@@ -1264,21 +1325,24 @@
         <v/>
       </c>
       <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
         <v>低栄養、肝機能低下（アルブミン産生低下）、ネフローゼ症候群、消化管からのたんぱく漏出</v>
       </c>
-      <c r="I21" t="str">
+      <c r="J21" t="str">
         <v>食事摂取量（特にたんぱく質）を確認する</v>
       </c>
-      <c r="J21" t="str">
+      <c r="K21" t="str">
         <v>アルブミンとグロブリンの内訳（A/G比）も合わせて確認すると原因の絞り込みに役立つ。低栄養か肝機能低下かはアルブミンの値と合わせて判断する</v>
       </c>
-      <c r="K21" t="str">
+      <c r="L21" t="str">
         <v>肝機能</v>
       </c>
-      <c r="L21" t="str">
+      <c r="M21" t="str">
         <v>総タンパク,TP,総蛋白,栄養状態,A/G比</v>
       </c>
-      <c r="M21" t="str">
+      <c r="N21" t="str">
         <v>食事と栄養 p.23（たんぱく質）</v>
       </c>
     </row>
@@ -1305,21 +1369,24 @@
         <v/>
       </c>
       <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
         <v>低栄養／肝機能低下／ネフローゼ症候群／クローン病</v>
       </c>
-      <c r="I22" t="str">
+      <c r="J22" t="str">
         <v>主食に偏らず、肉・魚・卵・大豆製品などたんぱく質をしっかり摂るよう伝える。食欲が落ちている場合は少量頻回の食事も提案する</v>
       </c>
-      <c r="J22" t="str">
+      <c r="K22" t="str">
         <v>3前半は注意ライン。食事摂取量を必ず確認</v>
       </c>
-      <c r="K22" t="str">
+      <c r="L22" t="str">
         <v>肝機能,栄養,腎機能</v>
       </c>
-      <c r="L22" t="str">
+      <c r="M22" t="str">
         <v>アルブミン,Alb,むくみ,浮腫,栄養状態</v>
       </c>
-      <c r="M22" t="str">
+      <c r="N22" t="str">
         <v>食事と栄養 p.23（たんぱく質）／p.242（フレイルQ110 アルブミン値を上げる食事指導）</v>
       </c>
     </row>
@@ -1346,21 +1413,24 @@
         <v>便秘の解消（排便コントロール）を心がける。ラクツロースやリファキシミンなど肝性脳症治療薬の服薬状況を確認する</v>
       </c>
       <c r="H23" t="str">
+        <v>バルプロ酸(デパケン等)</v>
+      </c>
+      <c r="I23" t="str">
         <v>通常、臨床的意義は乏しい</v>
       </c>
-      <c r="I23" t="str">
-        <v/>
-      </c>
       <c r="J23" t="str">
+        <v/>
+      </c>
+      <c r="K23" t="str">
         <v>バルプロ酸(デパケン等)は肝疾患の既往がなくても高アンモニア血症を起こすことがあり、意識障害・傾眠が出現した場合は薬剤性を疑ってアンモニア値を確認する。採血後は室温放置で見かけ上上昇するため測定条件にも注意。ラクツロース・リファキシミンは腸管内でのアンモニア産生・吸収を抑える目的で使用される</v>
       </c>
-      <c r="K23" t="str">
+      <c r="L23" t="str">
         <v>肝機能</v>
       </c>
-      <c r="L23" t="str">
+      <c r="M23" t="str">
         <v>アンモニア,NH3,肝性脳症,バルプロ酸,門脈シャント</v>
       </c>
-      <c r="M23" t="str">
+      <c r="N23" t="str">
         <v/>
       </c>
     </row>
@@ -1387,21 +1457,24 @@
         <v>糖質・アルコールの摂りすぎに注意し、有酸素運動を勧める</v>
       </c>
       <c r="H24" t="str">
+        <v>非定型抗精神病薬(オランザピン・クエチアピン)、ステロイド、エストロゲン製剤、非選択的β遮断薬、サイアザイド系利尿薬、タモキシフェン</v>
+      </c>
+      <c r="I24" t="str">
         <v>低栄養、甲状腺機能亢進症</v>
       </c>
-      <c r="I24" t="str">
-        <v/>
-      </c>
       <c r="J24" t="str">
+        <v/>
+      </c>
+      <c r="K24" t="str">
         <v>採血が食後か空腹時かで数値が大きく変わるため必ず確認する。500 mg/dL以上では急性膵炎のリスクが高まるため注意。フィブラート系・EPA製剤などの効果判定に使う</v>
       </c>
-      <c r="K24" t="str">
+      <c r="L24" t="str">
         <v>脂質異常症</v>
       </c>
-      <c r="L24" t="str">
+      <c r="M24" t="str">
         <v>中性脂肪,トリグリセリド,TG,脂質異常症</v>
       </c>
-      <c r="M24" t="str">
+      <c r="N24" t="str">
         <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
       </c>
     </row>
@@ -1428,21 +1501,24 @@
         <v>動物性脂肪を控え、食物繊維を増やすよう伝える</v>
       </c>
       <c r="H25" t="str">
+        <v>非定型抗精神病薬、ステロイド、サイアザイド系利尿薬、非選択的β遮断薬</v>
+      </c>
+      <c r="I25" t="str">
         <v>低栄養、肝機能低下、甲状腺機能亢進症</v>
       </c>
-      <c r="I25" t="str">
-        <v/>
-      </c>
       <c r="J25" t="str">
+        <v/>
+      </c>
+      <c r="K25" t="str">
         <v>現在はLDLコレステロールでの評価が主流。総コレステロールだけでは悪玉・善玉の内訳が分からないため、LDL・HDL・中性脂肪と合わせて評価する</v>
       </c>
-      <c r="K25" t="str">
+      <c r="L25" t="str">
         <v>脂質異常症</v>
       </c>
-      <c r="L25" t="str">
+      <c r="M25" t="str">
         <v>総コレステロール,TC,コレステロール,脂質異常症</v>
       </c>
-      <c r="M25" t="str">
+      <c r="N25" t="str">
         <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
       </c>
     </row>
@@ -1470,21 +1546,24 @@
         <v>動物性脂肪や揚げ物を控え、青魚や食物繊維（野菜・海藻・きのこ）を増やすよう伝える</v>
       </c>
       <c r="H26" t="str">
+        <v>ステロイド、サイアザイド系利尿薬、非選択的β遮断薬</v>
+      </c>
+      <c r="I26" t="str">
         <v>低栄養、肝機能低下、甲状腺機能亢進症</v>
       </c>
-      <c r="I26" t="str">
-        <v/>
-      </c>
       <c r="J26" t="str">
+        <v/>
+      </c>
+      <c r="K26" t="str">
         <v>スタチン等の効果判定に使う中心的な数値。目標値は既往疾患（冠動脈疾患・糖尿病等）によって異なるため一律に判断しない</v>
       </c>
-      <c r="K26" t="str">
+      <c r="L26" t="str">
         <v>脂質異常症,精神疾患（非定型抗精神病薬）</v>
       </c>
-      <c r="L26" t="str">
+      <c r="M26" t="str">
         <v>LDL,LDLコレステロール,悪玉コレステロール,脂質異常症</v>
       </c>
-      <c r="M26" t="str">
+      <c r="N26" t="str">
         <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
       </c>
     </row>
@@ -1517,15 +1596,18 @@
         <v/>
       </c>
       <c r="J27" t="str">
+        <v/>
+      </c>
+      <c r="K27" t="str">
         <v>中性脂肪（TG）が400 mg/dL以上などLDL-Cの計算式（Friedewald式）が不正確になる場合に、LDL-Cの代わりに用いられる。目標値はLDL-Cの目標値＋30 mg/dLが目安</v>
       </c>
-      <c r="K27" t="str">
+      <c r="L27" t="str">
         <v>脂質異常症</v>
       </c>
-      <c r="L27" t="str">
+      <c r="M27" t="str">
         <v>nonHDL,non-HDLコレステロール,動脈硬化,中性脂肪,LDL計算式</v>
       </c>
-      <c r="M27" t="str">
+      <c r="N27" t="str">
         <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
       </c>
     </row>
@@ -1552,21 +1634,24 @@
         <v/>
       </c>
       <c r="H28" t="str">
+        <v/>
+      </c>
+      <c r="I28" t="str">
         <v>脂質異常症（低HDL血症）</v>
       </c>
-      <c r="I28" t="str">
+      <c r="J28" t="str">
         <v>適度な運動習慣、禁煙を勧める</v>
       </c>
-      <c r="J28" t="str">
+      <c r="K28" t="str">
         <v>喫煙、運動不足、肥満で低下しやすい。禁煙・運動習慣の改善で上昇が期待できる。低HDLは動脈硬化のリスク因子として単独でも重視される</v>
       </c>
-      <c r="K28" t="str">
+      <c r="L28" t="str">
         <v>脂質異常症</v>
       </c>
-      <c r="L28" t="str">
+      <c r="M28" t="str">
         <v>HDL,HDLコレステロール,善玉コレステロール,脂質異常症</v>
       </c>
-      <c r="M28" t="str">
+      <c r="N28" t="str">
         <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
       </c>
     </row>
@@ -1593,21 +1678,24 @@
         <v>筋肉痛・脱力感・褐色尿（横紋筋融解症の症状）がないか確認する。スタチン系薬剤服用中は特に注意する。激しい運動の直後の採血でないかも確認する</v>
       </c>
       <c r="H29" t="str">
-        <v/>
+        <v>スタチン系(特にフィブラート系との併用時)、コルヒチン</v>
       </c>
       <c r="I29" t="str">
         <v/>
       </c>
       <c r="J29" t="str">
+        <v/>
+      </c>
+      <c r="K29" t="str">
         <v>スタチン系薬剤の重大な副作用である横紋筋融解症の指標。筋肉痛・脱力感・褐色尿の有無を必ず確認し、著明高値では服薬継続の可否を医師に相談する</v>
       </c>
-      <c r="K29" t="str">
-        <v/>
-      </c>
       <c r="L29" t="str">
+        <v/>
+      </c>
+      <c r="M29" t="str">
         <v>CK,CPK,クレアチンキナーゼ,横紋筋融解症</v>
       </c>
-      <c r="M29" t="str">
+      <c r="N29" t="str">
         <v/>
       </c>
     </row>
@@ -1634,21 +1722,24 @@
         <v>脱水が疑われる場合はこまめな水分摂取を勧める。黒い便など消化管出血を示唆する症状がないか確認する</v>
       </c>
       <c r="H30" t="str">
+        <v/>
+      </c>
+      <c r="I30" t="str">
         <v>低たんぱく食、肝不全、妊娠</v>
       </c>
-      <c r="I30" t="str">
-        <v/>
-      </c>
       <c r="J30" t="str">
+        <v/>
+      </c>
+      <c r="K30" t="str">
         <v>比が高い（目安20以上）場合は脱水や消化管出血など腎前性の要因を、比が正常範囲で両方高値なら腎性の障害を疑う。BUN単独やクレアチニン単独よりも病態の絞り込みに役立つ</v>
       </c>
-      <c r="K30" t="str">
+      <c r="L30" t="str">
         <v>腎機能</v>
       </c>
-      <c r="L30" t="str">
+      <c r="M30" t="str">
         <v>BUN/CRE,BUN/Cr,尿素窒素,クレアチニン,脱水,腎前性</v>
       </c>
-      <c r="M30" t="str">
+      <c r="N30" t="str">
         <v/>
       </c>
     </row>
@@ -1681,15 +1772,18 @@
         <v/>
       </c>
       <c r="J31" t="str">
+        <v/>
+      </c>
+      <c r="K31" t="str">
         <v>ASTのみ上昇しCKが正常であれば肝臓由来を、両方上昇していれば筋肉由来を疑う手がかりになる。スタチン系薬剤による横紋筋融解症が疑われる場面での鑑別に有用</v>
       </c>
-      <c r="K31" t="str">
-        <v/>
-      </c>
       <c r="L31" t="str">
+        <v/>
+      </c>
+      <c r="M31" t="str">
         <v>CK/AST,CK,AST,横紋筋融解症,スタチン</v>
       </c>
-      <c r="M31" t="str">
+      <c r="N31" t="str">
         <v/>
       </c>
     </row>
@@ -1716,21 +1810,24 @@
         <v/>
       </c>
       <c r="H32" t="str">
+        <v/>
+      </c>
+      <c r="I32" t="str">
         <v>急性肝炎などの肝細胞障害（比が低い、つまりASTに対してLDHが相対的に低い場合は肝性が示唆される）</v>
       </c>
-      <c r="I32" t="str">
-        <v/>
-      </c>
       <c r="J32" t="str">
+        <v/>
+      </c>
+      <c r="K32" t="str">
         <v>AST・LDHが同時に上昇した際の鑑別に使う目安の一つ。単独の検査値ではなく計算上の比率であり、確定診断には他の検査（ビリルビン、CK、心筋マーカーなど）と合わせた評価が必要</v>
       </c>
-      <c r="K32" t="str">
-        <v/>
-      </c>
       <c r="L32" t="str">
+        <v/>
+      </c>
+      <c r="M32" t="str">
         <v>LDH/AST,LDH,AST,溶血,心筋梗塞,肝炎</v>
       </c>
-      <c r="M32" t="str">
+      <c r="N32" t="str">
         <v/>
       </c>
     </row>
@@ -1763,15 +1860,18 @@
         <v/>
       </c>
       <c r="J33" t="str">
+        <v/>
+      </c>
+      <c r="K33" t="str">
         <v>本来のアニオンギャップ(Na-(Cl+HCO3))の簡易代用として使われることがあるが、重炭酸(HCO3)を用いた計算の方が正確。メトホルミン使用中の乳酸アシドーシスが疑われる場面などで参考にする</v>
       </c>
-      <c r="K33" t="str">
+      <c r="L33" t="str">
         <v>電解質</v>
       </c>
-      <c r="L33" t="str">
+      <c r="M33" t="str">
         <v>Na-Cl,アニオンギャップ,AG,代謝性アシドーシス,乳酸アシドーシス</v>
       </c>
-      <c r="M33" t="str">
+      <c r="N33" t="str">
         <v/>
       </c>
     </row>
@@ -1798,27 +1898,30 @@
         <v>飲酒量や頻度を確認する</v>
       </c>
       <c r="H34" t="str">
+        <v/>
+      </c>
+      <c r="I34" t="str">
         <v>急性ウイルス性肝炎、脂肪肝（比が1未満で肝細胞の急性障害を示唆することが多い）</v>
       </c>
-      <c r="I34" t="str">
-        <v/>
-      </c>
       <c r="J34" t="str">
+        <v/>
+      </c>
+      <c r="K34" t="str">
         <v>De Ritis比とも呼ばれる。比が2以上はアルコール性肝障害や肝硬変を、1未満は急性ウイルス性肝炎や脂肪肝を示唆する目安になるが、確定診断には他の検査所見と合わせた評価が必要</v>
       </c>
-      <c r="K34" t="str">
+      <c r="L34" t="str">
         <v>肝機能</v>
       </c>
-      <c r="L34" t="str">
+      <c r="M34" t="str">
         <v>AST/ALT,De Ritis比,デリティス比,アルコール性肝障害,肝硬変</v>
       </c>
-      <c r="M34" t="str">
+      <c r="N34" t="str">
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>ALT比ALP</v>
+        <v>ALT/ALP比</v>
       </c>
       <c r="B35" t="str">
         <v>ALT比/ALP比,R比,R-factor</v>
@@ -1839,21 +1942,24 @@
         <v/>
       </c>
       <c r="H35" t="str">
+        <v/>
+      </c>
+      <c r="I35" t="str">
         <v>R値2以下：胆汁うっ滞型（閉塞性黄疸、薬剤性肝障害の胆汁うっ滞型など）</v>
       </c>
-      <c r="I35" t="str">
-        <v/>
-      </c>
       <c r="J35" t="str">
+        <v/>
+      </c>
+      <c r="K35" t="str">
         <v>R値＝(ALTの基準値上限に対する倍率)÷(ALPの基準値上限に対する倍率)で算出する。薬剤性肝障害(DILI)の病型分類(肝細胞障害型/胆汁うっ滞型/混合型)に用いられ、被疑薬の休薬・変更の判断材料になる</v>
       </c>
-      <c r="K35" t="str">
+      <c r="L35" t="str">
         <v>肝機能</v>
       </c>
-      <c r="L35" t="str">
-        <v>ALT比ALP,ALT/ALP比,R値,R-factor,DILI,薬剤性肝障害</v>
-      </c>
       <c r="M35" t="str">
+        <v>ALT/ALP比,R値,R-factor,DILI,薬剤性肝障害</v>
+      </c>
+      <c r="N35" t="str">
         <v/>
       </c>
     </row>
@@ -1886,15 +1992,18 @@
         <v/>
       </c>
       <c r="J36" t="str">
+        <v/>
+      </c>
+      <c r="K36" t="str">
         <v>アルブミン・総リンパ球数・総コレステロールの3項目それぞれに配点があり、合計点で評価する客観的栄養指標。フレイル・サルコペニアの評価やポリファーマシー対策の一環としての栄養状態把握に有用</v>
       </c>
-      <c r="K36" t="str">
-        <v/>
-      </c>
       <c r="L36" t="str">
+        <v/>
+      </c>
+      <c r="M36" t="str">
         <v>CONUT,CONUT値,栄養評価,低栄養,フレイル</v>
       </c>
-      <c r="M36" t="str">
+      <c r="N36" t="str">
         <v>食事と栄養 p.240（フレイルQ108 低栄養や食事量の評価）</v>
       </c>
     </row>
@@ -1927,15 +2036,18 @@
         <v/>
       </c>
       <c r="J37" t="str">
+        <v/>
+      </c>
+      <c r="K37" t="str">
         <v>血清の白濁により一部の検査項目（電解質など）の測定値に誤差が出ることがある（偽性低ナトリウム血症など）。中性脂肪値と合わせて評価する</v>
       </c>
-      <c r="K37" t="str">
+      <c r="L37" t="str">
         <v>脂質異常症</v>
       </c>
-      <c r="L37" t="str">
+      <c r="M37" t="str">
         <v>乳び,乳び血清,Lipemia,高中性脂肪血症</v>
       </c>
-      <c r="M37" t="str">
+      <c r="N37" t="str">
         <v/>
       </c>
     </row>
@@ -1968,15 +2080,18 @@
         <v/>
       </c>
       <c r="J38" t="str">
+        <v/>
+      </c>
+      <c r="K38" t="str">
         <v>溶血を疑う際は、間接ビリルビン上昇・LDH上昇・ハプトグロビン低下・網状赤血球増加のパターンを確認する。ヘモグロビン・MCV・MCHCの変化と合わせて総合的に判断する</v>
       </c>
-      <c r="K38" t="str">
+      <c r="L38" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
-      <c r="L38" t="str">
+      <c r="M38" t="str">
         <v>溶血,Hemolysis,溶血性貧血,G6PD,ハプトグロビン</v>
       </c>
-      <c r="M38" t="str">
+      <c r="N38" t="str">
         <v/>
       </c>
     </row>
@@ -2009,15 +2124,18 @@
         <v/>
       </c>
       <c r="J39" t="str">
+        <v/>
+      </c>
+      <c r="K39" t="str">
         <v>黄疸は検査値そのものではなく身体所見。原因を調べる際は総ビリルビン・直接ビリルビン・間接ビリルビンの内訳とAST/ALT/γ-GTPを確認する。直接優位なら胆道系、間接優位なら溶血・体質性を疑う</v>
       </c>
-      <c r="K39" t="str">
+      <c r="L39" t="str">
         <v>肝機能</v>
       </c>
-      <c r="L39" t="str">
+      <c r="M39" t="str">
         <v>黄疸,ジョンダイス,Jaundice,ビリルビン,皮膚黄染,白目</v>
       </c>
-      <c r="M39" t="str">
+      <c r="N39" t="str">
         <v/>
       </c>
     </row>
@@ -2044,21 +2162,24 @@
         <v>だるさ、むくみ、体重増加、寒がりなどの症状がないか確認する。服薬状況（飲み忘れ、他の薬との飲み合わせ）を確認する</v>
       </c>
       <c r="H40" t="str">
+        <v>アミオダロン、炭酸リチウム、インターフェロン製剤、チロシンキナーゼ阻害薬(スニチニブ等)</v>
+      </c>
+      <c r="I40" t="str">
         <v>甲状腺機能亢進症（バセドウ病など）、チラーヂンSなど甲状腺ホルモン薬の過量</v>
       </c>
-      <c r="I40" t="str">
+      <c r="J40" t="str">
         <v>動悸、体重減少、暑がり、手のふるえなどの症状がないか確認する</v>
       </c>
-      <c r="J40" t="str">
+      <c r="K40" t="str">
         <v>チラーヂンS服用中はTSHが治療目標域に収まっているかで用量調整の目安にする。メルカゾール服用中はTSH・FT4に加えて無顆粒球症の初期症状（発熱・のどの痛み）の有無や白血球数も確認する</v>
       </c>
-      <c r="K40" t="str">
+      <c r="L40" t="str">
         <v>甲状腺疾患</v>
       </c>
-      <c r="L40" t="str">
+      <c r="M40" t="str">
         <v>TSH,甲状腺刺激ホルモン,甲状腺機能,橋本病,バセドウ病,チラーヂン,メルカゾール</v>
       </c>
-      <c r="M40" t="str">
+      <c r="N40" t="str">
         <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
       </c>
     </row>
@@ -2085,21 +2206,24 @@
         <v>動悸、体重減少、暑がり、手のふるえなどの症状がないか確認する</v>
       </c>
       <c r="H41" t="str">
+        <v>レボチロキシンの過量投与、アミオダロン</v>
+      </c>
+      <c r="I41" t="str">
         <v>甲状腺機能低下症（橋本病など）</v>
       </c>
-      <c r="I41" t="str">
+      <c r="J41" t="str">
         <v>だるさ、むくみ、体重増加、寒がりなどの症状がないか確認する</v>
       </c>
-      <c r="J41" t="str">
+      <c r="K41" t="str">
         <v>TSHと逆方向に動くのが基本だが、下垂体性の異常など例外もある。TSHと合わせて評価し、片方だけで判断しない</v>
       </c>
-      <c r="K41" t="str">
+      <c r="L41" t="str">
         <v>甲状腺疾患</v>
       </c>
-      <c r="L41" t="str">
+      <c r="M41" t="str">
         <v>FT4,遊離サイロキシン,甲状腺ホルモン,甲状腺機能</v>
       </c>
-      <c r="M41" t="str">
+      <c r="N41" t="str">
         <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
       </c>
     </row>
@@ -2126,21 +2250,24 @@
         <v/>
       </c>
       <c r="H42" t="str">
-        <v/>
+        <v>NSAIDs、造影剤、アミノグリコシド系、バンコマイシン、金製剤</v>
       </c>
       <c r="I42" t="str">
         <v/>
       </c>
       <c r="J42" t="str">
+        <v/>
+      </c>
+      <c r="K42" t="str">
         <v>発熱・激しい運動・起立性蛋白尿など生理的な要因でも陽性になることがある。持続する場合に腎症の進行を疑う</v>
       </c>
-      <c r="K42" t="str">
+      <c r="L42" t="str">
         <v>糖尿病,腎機能</v>
       </c>
-      <c r="L42" t="str">
+      <c r="M42" t="str">
         <v>尿蛋白,U-pro,腎症,たんぱく尿</v>
       </c>
-      <c r="M42" t="str">
+      <c r="N42" t="str">
         <v/>
       </c>
     </row>
@@ -2167,21 +2294,24 @@
         <v/>
       </c>
       <c r="H43" t="str">
+        <v/>
+      </c>
+      <c r="I43" t="str">
         <v>尿が薄い（水分摂取が多い、腎機能低下）状態</v>
       </c>
-      <c r="I43" t="str">
-        <v/>
-      </c>
       <c r="J43" t="str">
+        <v/>
+      </c>
+      <c r="K43" t="str">
         <v>尿中アルブミン/Cr比、尿蛋白/Cr比など、他項目の補正計算に使われる。単独の高低に臨床的意味は乏しい</v>
       </c>
-      <c r="K43" t="str">
+      <c r="L43" t="str">
         <v>腎機能</v>
       </c>
-      <c r="L43" t="str">
+      <c r="M43" t="str">
         <v>尿CRE,尿クレアチニン,随時尿,補正,蛋白クレアチニン比</v>
       </c>
-      <c r="M43" t="str">
+      <c r="N43" t="str">
         <v/>
       </c>
     </row>
@@ -2208,21 +2338,24 @@
         <v>発熱や体の痛みなど感染症状がないか確認する</v>
       </c>
       <c r="H44" t="str">
+        <v>ステロイド、G-CSF製剤、炭酸リチウム</v>
+      </c>
+      <c r="I44" t="str">
         <v>抗がん剤・免疫抑制剤などによる骨髄抑制、メルカゾールなど薬剤性の無顆粒球症、再生不良性貧血、ウイルス感染</v>
       </c>
-      <c r="I44" t="str">
+      <c r="J44" t="str">
         <v>発熱、のどの痛みなど感染症状の初期サインがないか確認する。人混みを避け、手洗い・うがいを徹底するよう伝える</v>
       </c>
-      <c r="J44" t="str">
+      <c r="K44" t="str">
         <v>メルカゾール（チアマゾール）は無顆粒球症の重大な副作用があり、発熱・のどの痛みが出たらすぐ受診するよう指導する。抗がん剤・免疫抑制剤・抗てんかん薬（カルバマゼピンなど）使用中も定期的なモニタリングが必要</v>
       </c>
-      <c r="K44" t="str">
+      <c r="L44" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
-      <c r="L44" t="str">
+      <c r="M44" t="str">
         <v>白血球,WBC,好中球,感染症,白血病,無顆粒球症,骨髄抑制</v>
       </c>
-      <c r="M44" t="str">
+      <c r="N44" t="str">
         <v/>
       </c>
     </row>
@@ -2249,21 +2382,24 @@
         <v>脱水が疑われる場合はこまめな水分摂取を勧める（水分制限がある場合を除く）</v>
       </c>
       <c r="H45" t="str">
+        <v/>
+      </c>
+      <c r="I45" t="str">
         <v>貧血（鉄欠乏性貧血、腎性貧血など）、出血</v>
       </c>
-      <c r="I45" t="str">
+      <c r="J45" t="str">
         <v>ヘモグロビンと同様に、出血や食事量低下がないか確認する</v>
       </c>
-      <c r="J45" t="str">
+      <c r="K45" t="str">
         <v>ヘモグロビン・ヘマトクリットと同じ方向に動くことが多い。赤血球数だけでなくMCV・MCH・MCHCと合わせて貧血のタイプ(小球性・正球性・大球性)を判断する</v>
       </c>
-      <c r="K45" t="str">
+      <c r="L45" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
-      <c r="L45" t="str">
+      <c r="M45" t="str">
         <v>赤血球,RBC,貧血,多血症</v>
       </c>
-      <c r="M45" t="str">
+      <c r="N45" t="str">
         <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
@@ -2290,21 +2426,24 @@
         <v/>
       </c>
       <c r="H46" t="str">
+        <v/>
+      </c>
+      <c r="I46" t="str">
         <v>鉄欠乏性貧血、出血、腎性貧血、骨髄の造血機能低下</v>
       </c>
-      <c r="I46" t="str">
+      <c r="J46" t="str">
         <v>鉄分の多い食品（レバー・赤身肉・魚・ほうれん草など）を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える</v>
       </c>
-      <c r="J46" t="str">
+      <c r="K46" t="str">
         <v>原因（出血・食事量低下など）の確認が重要。腎機能低下がある場合は鉄不足以外が原因のこともある。鉄剤はヘモグロビンが正常化した後も2〜3か月程度は継続することが多い（鉄の貯蔵分を補うため。途中でやめると再び貧血になりやすい）</v>
       </c>
-      <c r="K46" t="str">
+      <c r="L46" t="str">
         <v>鉄欠乏性貧血,抗血小板療法,抗凝固療法（心房細動・血栓症）</v>
       </c>
-      <c r="L46" t="str">
+      <c r="M46" t="str">
         <v>ヘモグロビン,Hb,貧血,鉄剤,鉄欠乏性貧血</v>
       </c>
-      <c r="M46" t="str">
+      <c r="N46" t="str">
         <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
@@ -2331,21 +2470,24 @@
         <v>脱水が疑われる場合はこまめな水分摂取を勧める（水分制限がある場合を除く）</v>
       </c>
       <c r="H47" t="str">
+        <v/>
+      </c>
+      <c r="I47" t="str">
         <v>貧血（鉄欠乏性貧血、腎性貧血など）、出血</v>
       </c>
-      <c r="I47" t="str">
+      <c r="J47" t="str">
         <v>ヘモグロビンと同様に、出血や食事量低下がないか確認する</v>
       </c>
-      <c r="J47" t="str">
+      <c r="K47" t="str">
         <v>ヘモグロビン・赤血球数と合わせて評価する。3つの値は同じ方向に動くことが多く、脱水があると貧血が見かけ上隠れることがある</v>
       </c>
-      <c r="K47" t="str">
+      <c r="L47" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
-      <c r="L47" t="str">
+      <c r="M47" t="str">
         <v>ヘマトクリット,Ht,Hct,貧血,脱水,多血症</v>
       </c>
-      <c r="M47" t="str">
+      <c r="N47" t="str">
         <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
@@ -2372,21 +2514,24 @@
         <v/>
       </c>
       <c r="H48" t="str">
+        <v/>
+      </c>
+      <c r="I48" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
-      <c r="I48" t="str">
+      <c r="J48" t="str">
         <v>鉄分の多い食事を意識する（ヘモグロビンの項目を参照）</v>
       </c>
-      <c r="J48" t="str">
-        <v/>
-      </c>
       <c r="K48" t="str">
+        <v/>
+      </c>
+      <c r="L48" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
-      <c r="L48" t="str">
+      <c r="M48" t="str">
         <v>MCV,赤血球指数,貧血</v>
       </c>
-      <c r="M48" t="str">
+      <c r="N48" t="str">
         <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
@@ -2413,21 +2558,24 @@
         <v/>
       </c>
       <c r="H49" t="str">
+        <v/>
+      </c>
+      <c r="I49" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
-      <c r="I49" t="str">
+      <c r="J49" t="str">
         <v>鉄分の多い食事を意識する（ヘモグロビンの項目を参照）</v>
       </c>
-      <c r="J49" t="str">
-        <v/>
-      </c>
       <c r="K49" t="str">
+        <v/>
+      </c>
+      <c r="L49" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
-      <c r="L49" t="str">
+      <c r="M49" t="str">
         <v>MCH,赤血球指数,貧血</v>
       </c>
-      <c r="M49" t="str">
+      <c r="N49" t="str">
         <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
@@ -2454,21 +2602,24 @@
         <v/>
       </c>
       <c r="H50" t="str">
+        <v/>
+      </c>
+      <c r="I50" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
-      <c r="I50" t="str">
+      <c r="J50" t="str">
         <v>鉄分の多い食事を意識する（ヘモグロビンの項目を参照）</v>
       </c>
-      <c r="J50" t="str">
-        <v/>
-      </c>
       <c r="K50" t="str">
+        <v/>
+      </c>
+      <c r="L50" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
-      <c r="L50" t="str">
+      <c r="M50" t="str">
         <v>MCHC,赤血球指数,貧血</v>
       </c>
-      <c r="M50" t="str">
+      <c r="N50" t="str">
         <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
@@ -2495,21 +2646,24 @@
         <v/>
       </c>
       <c r="H51" t="str">
+        <v/>
+      </c>
+      <c r="I51" t="str">
         <v>抗がん剤・免疫抑制剤などによる骨髄抑制、肝硬変・脾機能亢進、再生不良性貧血、抗てんかん薬（バルプロ酸など）の副作用、ITP（特発性血小板減少性紫斑病）</v>
       </c>
-      <c r="I51" t="str">
+      <c r="J51" t="str">
         <v>あざができやすい、歯ぐきや鼻からの出血が増えていないか確認する。強い運動や転倒によるけがに注意するよう伝える</v>
       </c>
-      <c r="J51" t="str">
+      <c r="K51" t="str">
         <v>抗血小板薬・抗凝固薬使用中に血小板減少があると出血リスクがさらに高まる。抗がん剤・バルプロ酸・カルバマゼピンなど骨髄抑制のリスクがある薬剤使用中は定期採血の実施状況を確認する</v>
       </c>
-      <c r="K51" t="str">
+      <c r="L51" t="str">
         <v>てんかん,抗血小板療法</v>
       </c>
-      <c r="L51" t="str">
+      <c r="M51" t="str">
         <v>血小板,Plt,platelet,出血,あざ,紫斑,骨髄抑制</v>
       </c>
-      <c r="M51" t="str">
+      <c r="N51" t="str">
         <v/>
       </c>
     </row>
@@ -2542,15 +2696,18 @@
         <v/>
       </c>
       <c r="J52" t="str">
+        <v/>
+      </c>
+      <c r="K52" t="str">
         <v>MCVが正常範囲でもRDWが上昇している場合、鉄欠乏の初期段階を示唆することがある。MCV・MCHと合わせて評価する</v>
       </c>
-      <c r="K52" t="str">
+      <c r="L52" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
-      <c r="L52" t="str">
+      <c r="M52" t="str">
         <v>RDW-SD,赤血球分布幅,貧血,鉄欠乏</v>
       </c>
-      <c r="M52" t="str">
+      <c r="N52" t="str">
         <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
@@ -2583,15 +2740,18 @@
         <v/>
       </c>
       <c r="J53" t="str">
+        <v/>
+      </c>
+      <c r="K53" t="str">
         <v>RDW-SDと同様の意味を持つ指標。MCVが小さくRDWが高ければ鉄欠乏性貧血、MCVが大きくRDWが高ければビタミンB12・葉酸欠乏を疑う手がかりになる</v>
       </c>
-      <c r="K53" t="str">
+      <c r="L53" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
-      <c r="L53" t="str">
+      <c r="M53" t="str">
         <v>RDW-CV,赤血球分布幅,貧血,ビタミンB12,葉酸</v>
       </c>
-      <c r="M53" t="str">
+      <c r="N53" t="str">
         <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
@@ -2618,21 +2778,24 @@
         <v/>
       </c>
       <c r="H54" t="str">
+        <v/>
+      </c>
+      <c r="I54" t="str">
         <v>抗がん剤・免疫抑制剤などによる骨髄抑制、メルカゾールなど薬剤性の無顆粒球症（1,000/μL未満で好中球減少症、500/μL未満で重症感染リスクが著しく上昇）</v>
       </c>
-      <c r="I54" t="str">
+      <c r="J54" t="str">
         <v>発熱、のどの痛みなど感染症状の初期サインがないか確認する。人混みを避け、手洗い・うがいを徹底するよう伝える</v>
       </c>
-      <c r="J54" t="str">
+      <c r="K54" t="str">
         <v>抗がん剤・メルカゾール・カルバマゼピンなど骨髄抑制のリスクがある薬剤使用中は特に重視すべき数値。500/μL未満は発熱性好中球減少症のリスクが高く緊急性が高い</v>
       </c>
-      <c r="K54" t="str">
+      <c r="L54" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
-      <c r="L54" t="str">
+      <c r="M54" t="str">
         <v>好中球実数値,好中球数,ANC,無顆粒球症,発熱性好中球減少症</v>
       </c>
-      <c r="M54" t="str">
+      <c r="N54" t="str">
         <v/>
       </c>
     </row>
@@ -2659,21 +2822,24 @@
         <v>新しく始めた薬がないか確認する</v>
       </c>
       <c r="H55" t="str">
-        <v/>
+        <v>薬剤性好酸球増多(抗菌薬・NSAIDs・抗てんかん薬など)。発熱や皮疹を伴う場合はDRESS症候群にも注意</v>
       </c>
       <c r="I55" t="str">
         <v/>
       </c>
       <c r="J55" t="str">
+        <v/>
+      </c>
+      <c r="K55" t="str">
         <v>薬剤性過敏症症候群(DIHS)などでは著明な好酸球増多を認めることがあり、原因薬剤の特定に役立つ</v>
       </c>
-      <c r="K55" t="str">
+      <c r="L55" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
-      <c r="L55" t="str">
+      <c r="M55" t="str">
         <v>好酸球実数値,好酸球数,アレルギー,DIHS</v>
       </c>
-      <c r="M55" t="str">
+      <c r="N55" t="str">
         <v/>
       </c>
     </row>
@@ -2706,15 +2872,18 @@
         <v/>
       </c>
       <c r="J56" t="str">
+        <v/>
+      </c>
+      <c r="K56" t="str">
         <v>単独での臨床的意義は乏しく、他の血球指標（白血球分画全体）と合わせて評価する</v>
       </c>
-      <c r="K56" t="str">
+      <c r="L56" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
-      <c r="L56" t="str">
+      <c r="M56" t="str">
         <v>好塩基球実数値,好塩基球数</v>
       </c>
-      <c r="M56" t="str">
+      <c r="N56" t="str">
         <v/>
       </c>
     </row>
@@ -2741,21 +2910,24 @@
         <v/>
       </c>
       <c r="H57" t="str">
+        <v/>
+      </c>
+      <c r="I57" t="str">
         <v>抗がん剤・免疫抑制剤・ステロイドの使用、強いストレス、AIDSなどの免疫不全</v>
       </c>
-      <c r="I57" t="str">
+      <c r="J57" t="str">
         <v>感染予防（手洗い・うがい、人混みを避ける）を意識するよう伝える</v>
       </c>
-      <c r="J57" t="str">
+      <c r="K57" t="str">
         <v>免疫抑制剤・抗がん剤治療中のモニタリング指標としても使われる。著明な低下時は日和見感染のリスクが高まる</v>
       </c>
-      <c r="K57" t="str">
+      <c r="L57" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
-      <c r="L57" t="str">
+      <c r="M57" t="str">
         <v>リンパ球実数値,リンパ球数,ALC,免疫抑制剤,日和見感染</v>
       </c>
-      <c r="M57" t="str">
+      <c r="N57" t="str">
         <v/>
       </c>
     </row>
@@ -2788,15 +2960,18 @@
         <v/>
       </c>
       <c r="J58" t="str">
+        <v/>
+      </c>
+      <c r="K58" t="str">
         <v>単独での臨床的意義は乏しく、他の血球指標と合わせて評価する</v>
       </c>
-      <c r="K58" t="str">
+      <c r="L58" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
-      <c r="L58" t="str">
+      <c r="M58" t="str">
         <v>単球実数値,単球数</v>
       </c>
-      <c r="M58" t="str">
+      <c r="N58" t="str">
         <v/>
       </c>
     </row>
@@ -2823,21 +2998,24 @@
         <v>発熱や炎症症状がないか確認する</v>
       </c>
       <c r="H59" t="str">
+        <v/>
+      </c>
+      <c r="I59" t="str">
         <v>抗がん剤・免疫抑制剤などによる骨髄抑制、ウイルス感染、メルカゾールなど薬剤性の無顆粒球症</v>
       </c>
-      <c r="I59" t="str">
+      <c r="J59" t="str">
         <v>発熱やのどの痛みなど感染症状の初期サインがないか確認する</v>
       </c>
-      <c r="J59" t="str">
+      <c r="K59" t="str">
         <v>好中球の絶対数（好中球実数値）が500/μL未満になると重篤な感染症のリスクが高まる。割合(%)だけでなく実数値も合わせて確認する</v>
       </c>
-      <c r="K59" t="str">
+      <c r="L59" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
-      <c r="L59" t="str">
+      <c r="M59" t="str">
         <v>好中球,Neutro,Neut,感染症,無顆粒球症</v>
       </c>
-      <c r="M59" t="str">
+      <c r="N59" t="str">
         <v/>
       </c>
     </row>
@@ -2864,21 +3042,24 @@
         <v>新しく始めた薬がないか確認する。皮疹やかゆみなどアレルギー症状の有無を確認する</v>
       </c>
       <c r="H60" t="str">
-        <v/>
+        <v>薬剤性好酸球増多(抗菌薬・NSAIDs・抗てんかん薬など)。発熱や皮疹を伴う場合はDRESS症候群にも注意</v>
       </c>
       <c r="I60" t="str">
         <v/>
       </c>
       <c r="J60" t="str">
+        <v/>
+      </c>
+      <c r="K60" t="str">
         <v>薬剤性の好酸球増多は、原因薬剤の中止で改善することが多い。新規薬剤開始後の皮疹・発熱と合わせて薬剤性過敏症症候群(DIHS)を疑う材料になる</v>
       </c>
-      <c r="K60" t="str">
+      <c r="L60" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
-      <c r="L60" t="str">
+      <c r="M60" t="str">
         <v>好酸球,Eosino,Eos,アレルギー,薬疹,DIHS</v>
       </c>
-      <c r="M60" t="str">
+      <c r="N60" t="str">
         <v/>
       </c>
     </row>
@@ -2911,15 +3092,18 @@
         <v/>
       </c>
       <c r="J61" t="str">
+        <v/>
+      </c>
+      <c r="K61" t="str">
         <v>単独での臨床的意義は乏しいが、著明な増加は血液疾患（慢性骨髄性白血病等）の可能性があり他の血球指標と合わせて評価する</v>
       </c>
-      <c r="K61" t="str">
+      <c r="L61" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
-      <c r="L61" t="str">
+      <c r="M61" t="str">
         <v>好塩基球,Baso,アレルギー,白血病</v>
       </c>
-      <c r="M61" t="str">
+      <c r="N61" t="str">
         <v/>
       </c>
     </row>
@@ -2946,21 +3130,24 @@
         <v/>
       </c>
       <c r="H62" t="str">
+        <v/>
+      </c>
+      <c r="I62" t="str">
         <v>抗がん剤・免疫抑制剤・ステロイドの使用、強いストレス、AIDSなどの免疫不全</v>
       </c>
-      <c r="I62" t="str">
+      <c r="J62" t="str">
         <v>免疫が下がっている可能性があるため、感染予防（手洗い・うがい、人混みを避ける）を意識するよう伝える</v>
       </c>
-      <c r="J62" t="str">
+      <c r="K62" t="str">
         <v>ステロイド・免疫抑制剤使用中はリンパ球減少による易感染性に注意。好中球と逆方向に動くことが多い（ウイルス感染ではリンパ球優位、細菌感染では好中球優位になりやすい）</v>
       </c>
-      <c r="K62" t="str">
+      <c r="L62" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
-      <c r="L62" t="str">
+      <c r="M62" t="str">
         <v>リンパ球,Lympho,Lym,ウイルス感染,免疫抑制剤,ステロイド</v>
       </c>
-      <c r="M62" t="str">
+      <c r="N62" t="str">
         <v/>
       </c>
     </row>
@@ -2993,15 +3180,18 @@
         <v/>
       </c>
       <c r="J63" t="str">
+        <v/>
+      </c>
+      <c r="K63" t="str">
         <v>単独での臨床的意義は乏しく、他の血球指標や炎症マーカー(CRPなど)と合わせて評価する</v>
       </c>
-      <c r="K63" t="str">
+      <c r="L63" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
-      <c r="L63" t="str">
+      <c r="M63" t="str">
         <v>単球,Mono,慢性感染症,結核,炎症</v>
       </c>
-      <c r="M63" t="str">
+      <c r="N63" t="str">
         <v/>
       </c>
     </row>
@@ -3028,86 +3218,92 @@
         <v>歯ぐきや鼻からの出血、あざ、黒い便などの出血症状がないか確認する。納豆・クロレラ・青汁などビタミンKを多く含む食品の摂取状況を確認する</v>
       </c>
       <c r="H64" t="str">
+        <v>ワルファリンの過量。ワルファリン服用中はST合剤・マクロライド系・フルコナゾール等の相互作用やビタミンK摂取量の変化にも注意</v>
+      </c>
+      <c r="I64" t="str">
         <v>ワルファリンの効き不足、飲み忘れ、ビタミンK摂取量の急激な増加</v>
       </c>
-      <c r="I64" t="str">
+      <c r="J64" t="str">
         <v>服薬状況（飲み忘れ）を確認する。片側のむくみ・しびれ・胸痛など血栓症状がないか確認する</v>
       </c>
-      <c r="J64" t="str">
+      <c r="K64" t="str">
         <v>治療域は疾患・年齢によって異なる（例：非弁膜症性心房細動の高齢者では1.6〜2.6が目安になることが多い）。多くの薬剤・食品と相互作用があるため新規薬剤追加時は必ず確認する。DOAC（エリキュース、リクシアナ、プラザキサなど）ではPT-INRのモニタリングは不要</v>
       </c>
-      <c r="K64" t="str">
+      <c r="L64" t="str">
         <v>抗凝固療法（心房細動・血栓症）</v>
       </c>
-      <c r="L64" t="str">
+      <c r="M64" t="str">
         <v>PT-INR,INR,プロトロンビン時間,ワルファリン,ワーファリン,抗凝固</v>
       </c>
-      <c r="M64" t="str">
+      <c r="N64" t="str">
         <v>食事と栄養 p.221（心疾患Q93 ワルファリン服用中のビタミンK摂取）</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>C反応性蛋白（CRP）</v>
+        <v>Dダイマー</v>
       </c>
       <c r="B65" t="str">
-        <v>CRP</v>
+        <v>D-dimer</v>
       </c>
       <c r="C65" t="str">
-        <v>0.3 mg/dL未満（施設差あり）</v>
+        <v>1.0 μg/mL以下(施設・測定法により異なる)</v>
       </c>
       <c r="D65" t="str">
-        <v>体のどこかに炎症や感染が起きていないかを鋭敏に反映する数値</v>
+        <v>体の中で血栓ができて溶けた(線溶)ときにできる分解産物で、血栓症の有無をスクリーニングする指標</v>
       </c>
       <c r="E65" t="str">
-        <v>CRPは、体に炎症や感染が起きると数時間〜半日程度で急激に上昇する数値です。風邪のようなウイルス感染から細菌感染、体のどこかの炎症まで、幅広く反応するため、体調の変化を早期に捉える手がかりになります。</v>
+        <v>Dダイマーは、血管の中に血のかたまり(血栓)ができて、それが溶かされるときにできる物質です。この数値が高いと、どこかに血栓ができている可能性を考えます。ただし手術後や妊娠中、高齢の方などでも上がることがあるため、この数値だけで診断が決まるわけではありません。</v>
       </c>
       <c r="F65" t="str">
-        <v>細菌感染症、ウイルス感染症、自己免疫疾患（関節リウマチなど）、悪性腫瘍、組織の損傷（術後・心筋梗塞など）</v>
+        <v>深部静脈血栓症(DVT)・肺血栓塞栓症(PE)、播種性血管内凝固症候群(DIC)、大動脈解離、悪性腫瘍、手術後、妊娠、高齢、感染・炎症</v>
       </c>
       <c r="G65" t="str">
-        <v>発熱、痛み、腫れなど炎症症状の有無を確認する</v>
+        <v>ふくらはぎの腫れ・痛み、急な息切れ・胸痛など血栓症を疑う症状がないか確認する</v>
       </c>
       <c r="H65" t="str">
-        <v/>
+        <v>経口避妊薬・ホルモン補充療法は血栓リスクを高める。逆にワルファリン・DOAC・ヘパリンなど抗凝固薬の効果不十分で血栓が進行している可能性にも注意</v>
       </c>
       <c r="I65" t="str">
-        <v/>
+        <v>通常、臨床的意義は乏しい(基準値以下であれば血栓症の可能性は低いとする除外診断に有用)</v>
       </c>
       <c r="J65" t="str">
-        <v>白血球数と合わせて感染・炎症の程度を評価する。上昇・低下のタイミングは白血球より半日〜1日程度遅れる傾向があるため、経過を追う際は採血のタイミングに注意</v>
+        <v/>
       </c>
       <c r="K65" t="str">
-        <v/>
+        <v>陰性的中率が高く、基準値以下であれば静脈血栓塞栓症(VTE)の可能性は低いとする除外診断への活用が臨床的に重要。一方で偽陽性が多く、高値のみで血栓症と確定はできない。抗凝固療法中のモニタリングそのものには通常用いない(効果判定はPT-INR/APTT等)</v>
       </c>
       <c r="L65" t="str">
-        <v>CRP,炎症,感染</v>
+        <v>抗凝固療法（心房細動・血栓症）</v>
       </c>
       <c r="M65" t="str">
+        <v>Dダイマー,D-dimer,血栓,DVT,深部静脈血栓症,肺塞栓,DIC</v>
+      </c>
+      <c r="N65" t="str">
         <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>骨型酒石酸抵抗性フォスファターゼ（TRACP-5b）</v>
+        <v>C反応性蛋白（CRP）</v>
       </c>
       <c r="B66" t="str">
-        <v>TRACP-5b</v>
+        <v>CRP</v>
       </c>
       <c r="C66" t="str">
-        <v>120〜420 mU/dL</v>
+        <v>0.3 mg/dL未満（施設差あり）</v>
       </c>
       <c r="D66" t="str">
-        <v>骨がどれくらい壊されているかを見る検査。骨は「古い骨を壊して新しい骨を作る」入れ替えを繰り返しており、骨を壊す細胞が活発だとこの物質が血液中に増える。</v>
+        <v>体のどこかに炎症や感染が起きていないかを鋭敏に反映する数値</v>
       </c>
       <c r="E66" t="str">
-        <v>この検査は、骨がどれくらい早く減っていないかを見るものです。数値が高いと、骨が弱くなりやすい状態の目安になります。</v>
+        <v>CRPは、体に炎症や感染が起きると数時間〜半日程度で急激に上昇する数値です。風邪のようなウイルス感染から細菌感染、体のどこかの炎症まで、幅広く反応するため、体調の変化を早期に捉える手がかりになります。</v>
       </c>
       <c r="F66" t="str">
-        <v>骨粗鬆症、骨代謝回転（骨がこわれるスピード）が活発な状態</v>
+        <v>細菌感染症、ウイルス感染症、自己免疫疾患（関節リウマチなど）、悪性腫瘍、組織の損傷（術後・心筋梗塞など）</v>
       </c>
       <c r="G66" t="str">
-        <v>カルシウム・ビタミンDの摂取や、適度な荷重運動（ウォーキングなど）を意識するよう伝える</v>
+        <v>発熱、痛み、腫れなど炎症症状の有無を確認する</v>
       </c>
       <c r="H66" t="str">
         <v/>
@@ -3116,733 +3312,787 @@
         <v/>
       </c>
       <c r="J66" t="str">
-        <v>「骨を壊す側」の指標。「骨を作る側」の検査と合わせて評価する。数値だけで診断はしない</v>
+        <v/>
       </c>
       <c r="K66" t="str">
-        <v>骨粗鬆症</v>
+        <v>白血球数と合わせて感染・炎症の程度を評価する。上昇・低下のタイミングは白血球より半日〜1日程度遅れる傾向があるため、経過を追う際は採血のタイミングに注意</v>
       </c>
       <c r="L66" t="str">
-        <v>TRACP-5b,骨型酒石酸抵抗性フォスファターゼ,骨粗鬆症,骨代謝</v>
+        <v/>
       </c>
       <c r="M66" t="str">
+        <v>CRP,炎症,感染</v>
+      </c>
+      <c r="N66" t="str">
         <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>骨型アルカリフォスファターゼ</v>
+        <v>骨密度</v>
       </c>
       <c r="B67" t="str">
-        <v>BAP</v>
+        <v>BMD,骨密度</v>
       </c>
       <c r="C67" t="str">
-        <v>男性 3.7〜20.9 μg/L、女性（閉経前）2.9〜14.5 μg/L（施設差あり）</v>
+        <v>YAM(若年成人平均値)80%以上:正常、70%以上80%未満:骨量減少、70%未満:骨粗鬆症</v>
       </c>
       <c r="D67" t="str">
-        <v>ALPのうち骨に由来する成分だけを測定し、骨が作られる勢い（骨形成）を反映する</v>
+        <v>骨の中にカルシウムなどのミネラルがどれだけ詰まっているかを示す指標。20〜44歳の平均値(YAM)に対する割合(%)で評価する</v>
       </c>
       <c r="E67" t="str">
-        <v>骨型ALPは、通常のALP（アルカリホスファターゼ）の中でも、骨で作られる成分だけを選んで測定するものです。骨を新しく作る働きがどれくらい活発かを見る指標として、骨粗鬆症の治療効果判定などに使われます。</v>
+        <v>骨密度は、骨の中にカルシウムなどのミネラルがどれだけしっかり詰まっているかを表す数値です。20〜44歳の若い方の平均値を100%として、ご自身の骨密度が何%かで示されます。70%未満になると「骨粗鬆症」と診断され、骨折しやすい状態と考えられます。</v>
       </c>
       <c r="F67" t="str">
-        <v>骨代謝回転の亢進（骨粗鬆症、骨折治癒過程、骨形成促進薬による治療効果、Paget病、骨転移）</v>
+        <v>基本的に問題になることは少ない(まれに骨硬化症などの疾患)</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>骨形成の低下</v>
+        <v/>
       </c>
       <c r="I67" t="str">
-        <v/>
+        <v>骨粗鬆症、加齢による骨量減少、閉経後のエストロゲン低下、ステロイド長期使用、カルシウム・ビタミンD不足、運動不足、るいそう</v>
       </c>
       <c r="J67" t="str">
-        <v>通常のALPと異なり肝臓の影響を受けにくいため、肝機能異常がある患者でも骨代謝を評価しやすい。P1NPと同じ「骨を作る側」の指標で、骨形成促進薬（テリパラチド等）の効果判定に使われる</v>
+        <v>カルシウム・ビタミンD・ビタミンKを意識した食事、荷重運動(ウォーキング等)を勧める。ステロイド長期服用中の場合は骨粗鬆症治療薬の併用が検討されているか確認する</v>
       </c>
       <c r="K67" t="str">
+        <v>YAM70%未満、または既存の脆弱性骨折がある場合に骨粗鬆症と診断され薬物治療の対象となる(日本骨粗鬆症学会・日本骨代謝学会・厚生労働省合同「原発性骨粗鬆症の診断基準 2012年度改訂版」)。ビスホスホネート製剤は起床時空腹時に十分な水(180mL程度)で服用し、服用後30分は横にならないよう指導する。ステロイドを長期服用中の患者は骨密度によらず骨粗鬆症治療薬の併用が推奨される場合がある(グルココルチコイド誘発性骨粗鬆症: GIOP)</v>
+      </c>
+      <c r="L67" t="str">
         <v>骨粗鬆症</v>
       </c>
-      <c r="L67" t="str">
-        <v>骨型ALP,BAP,骨型アルカリフォスファターゼ,骨形成マーカー</v>
-      </c>
       <c r="M67" t="str">
+        <v>骨密度,BMD,YAM,若年成人平均値,骨粗鬆症,DXA</v>
+      </c>
+      <c r="N67" t="str">
         <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>25-ヒドロキシビタミンD</v>
+        <v>骨型酒石酸抵抗性フォスファターゼ（TRACP-5b）</v>
       </c>
       <c r="B68" t="str">
-        <v>25(OH)D</v>
+        <v>TRACP-5b</v>
       </c>
       <c r="C68" t="str">
-        <v>30 ng/mL以上：充足、20〜30 ng/mL：不足、20 ng/mL未満：欠乏（施設差あり）</v>
+        <v>120〜420 mU/dL</v>
       </c>
       <c r="D68" t="str">
-        <v>体内のビタミンDの蓄え具合を反映する指標。カルシウムの吸収や骨の健康に関わる</v>
+        <v>骨がどれくらい壊されているかを見る検査。骨は「古い骨を壊して新しい骨を作る」入れ替えを繰り返しており、骨を壊す細胞が活発だとこの物質が血液中に増える。</v>
       </c>
       <c r="E68" t="str">
-        <v>この検査は、体の中にビタミンDがどれくらい蓄えられているかを見るものです。ビタミンDは、食事から摂ったカルシウムを腸で吸収するのを助ける働きがあり、不足すると骨がもろくなりやすくなります。</v>
+        <v>この検査は、骨がどれくらい早く減っていないかを見るものです。数値が高いと、骨が弱くなりやすい状態の目安になります。</v>
       </c>
       <c r="F68" t="str">
-        <v>ビタミンD製剤の過剰摂取</v>
+        <v>骨粗鬆症、骨代謝回転（骨がこわれるスピード）が活発な状態</v>
       </c>
       <c r="G68" t="str">
-        <v>活性型ビタミンD3製剤やサプリメントの摂取量を確認する。高カルシウム血症の症状（吐き気、便秘、多尿など）がないか確認する</v>
+        <v>カルシウム・ビタミンDの摂取や、適度な荷重運動（ウォーキングなど）を意識するよう伝える</v>
       </c>
       <c r="H68" t="str">
-        <v>日光暴露不足、食事摂取不足、高齢、腸疾患による吸収不良、肝・腎機能低下（活性化障害）</v>
+        <v/>
       </c>
       <c r="I68" t="str">
-        <v>適度な日光浴、魚類・きのこ類などビタミンDを多く含む食品の摂取を意識するとよいことを伝える</v>
+        <v/>
       </c>
       <c r="J68" t="str">
-        <v>骨粗鬆症治療における活性型ビタミンD3製剤の効果判定や、投与量調整の参考に用いられる。腎機能低下患者では活性化障害により25(OH)Dが正常でも活性型が不足することがある点に注意</v>
+        <v/>
       </c>
       <c r="K68" t="str">
+        <v>「骨を壊す側」の指標。「骨を作る側」の検査と合わせて評価する。数値だけで診断はしない</v>
+      </c>
+      <c r="L68" t="str">
         <v>骨粗鬆症</v>
       </c>
-      <c r="L68" t="str">
-        <v>25(OH)D,ビタミンD,25-ヒドロキシビタミンD,ビタミンD欠乏,骨粗鬆症</v>
-      </c>
       <c r="M68" t="str">
-        <v>食事と栄養 p.38（ビタミンD）</v>
+        <v>TRACP-5b,骨型酒石酸抵抗性フォスファターゼ,骨粗鬆症,骨代謝</v>
+      </c>
+      <c r="N68" t="str">
+        <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>尿pH</v>
+        <v>骨型アルカリフォスファターゼ</v>
       </c>
       <c r="B69" t="str">
-        <v>尿pH</v>
+        <v>BAP</v>
       </c>
       <c r="C69" t="str">
-        <v>4.5〜7.5程度（弱酸性が多い）</v>
+        <v>男性 3.7〜20.9 μg/L、女性（閉経前）2.9〜14.5 μg/L（施設差あり）</v>
       </c>
       <c r="D69" t="str">
-        <v>尿の酸性・アルカリ性の度合い。食事や感染症、体の状態を反映する</v>
+        <v>ALPのうち骨に由来する成分だけを測定し、骨が作られる勢い（骨形成）を反映する</v>
       </c>
       <c r="E69" t="str">
-        <v>尿のpHは酸性・アルカリ性のバランスを表します。食事の内容や感染症、体の代謝状態によって変化します。単独で大きな問題を示すことは少ない検査です。</v>
+        <v>骨型ALPは、通常のALP（アルカリフォスファターゼ）の中でも、骨で作られる成分だけを選んで測定するものです。骨を新しく作る働きがどれくらい活発かを見る指標として、骨粗鬆症の治療効果判定などに使われます。</v>
       </c>
       <c r="F69" t="str">
-        <v>尿路感染症（尿素分解菌によるもの）、野菜中心の食事、過換気</v>
+        <v>骨代謝回転の亢進（骨粗鬆症、骨折治癒過程、骨形成促進薬による治療効果、Paget病、骨転移）</v>
       </c>
       <c r="G69" t="str">
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>高たんぱく食、糖尿病性ケトアシドーシス、痛風発作時（酸性尿は尿酸結石のリスクを高める）</v>
+        <v/>
       </c>
       <c r="I69" t="str">
-        <v>痛風・尿酸結石がある場合は、野菜など尿をアルカリ化する食品を意識するとよいことを伝える</v>
+        <v>骨形成の低下</v>
       </c>
       <c r="J69" t="str">
-        <v>高尿酸血症・尿酸結石の患者では尿pHが酸性に傾いていないか確認する。尿アルカリ化薬（ウラリットなど）の効果判定にも使う</v>
+        <v/>
       </c>
       <c r="K69" t="str">
-        <v>高尿酸血症</v>
+        <v>通常のALPと異なり肝臓の影響を受けにくいため、肝機能異常がある患者でも骨代謝を評価しやすい。P1NPと同じ「骨を作る側」の指標で、骨形成促進薬（テリパラチド等）の効果判定に使われる</v>
       </c>
       <c r="L69" t="str">
-        <v>尿pH,尿酸性度,尿アルカリ化,ウラリット</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="M69" t="str">
+        <v>骨型ALP,BAP,骨型アルカリフォスファターゼ,骨形成マーカー</v>
+      </c>
+      <c r="N69" t="str">
         <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>尿ケトン体</v>
+        <v>25-ヒドロキシビタミンD</v>
       </c>
       <c r="B70" t="str">
-        <v>尿ケトン,Ket</v>
+        <v>25(OH)D</v>
       </c>
       <c r="C70" t="str">
-        <v>陰性（－）</v>
+        <v>30 ng/mL以上：充足、20〜30 ng/mL：不足、20 ng/mL未満：欠乏（施設差あり）</v>
       </c>
       <c r="D70" t="str">
-        <v>体がブドウ糖の代わりに脂肪を分解してエネルギーを作っているサイン</v>
+        <v>体内のビタミンDの蓄え具合を反映する指標。カルシウムの吸収や骨の健康に関わる</v>
       </c>
       <c r="E70" t="str">
-        <v>この検査は、体が糖の代わりに脂肪を使ってエネルギーを作っていないかを見るものです。陽性が続くときは、食事や水分、インスリンの使い方を確認する必要があります。</v>
+        <v>この検査は、体の中にビタミンDがどれくらい蓄えられているかを見るものです。ビタミンDは、食事から摂ったカルシウムを腸で吸収するのを助ける働きがあり、不足すると骨がもろくなりやすくなります。</v>
       </c>
       <c r="F70" t="str">
-        <v>糖尿病の血糖コントロール不良（シックデイ・インスリン不足）、極端な糖質制限、絶食、嘔吐・下痢による脱水</v>
+        <v>ビタミンD製剤の過剰摂取</v>
       </c>
       <c r="G70" t="str">
-        <v/>
+        <v>活性型ビタミンD3製剤やサプリメントの摂取量を確認する。高カルシウム血症の症状（吐き気、便秘、多尿など）がないか確認する</v>
       </c>
       <c r="H70" t="str">
-        <v/>
+        <v>活性型/天然型ビタミンD製剤の過量投与</v>
       </c>
       <c r="I70" t="str">
-        <v/>
+        <v>日光暴露不足、食事摂取不足、高齢、腸疾患による吸収不良、肝・腎機能低下（活性化障害）</v>
       </c>
       <c r="J70" t="str">
-        <v>陽性かつ高血糖・全身倦怠感が強い場合は糖尿病性ケトアシドーシスの可能性があり緊急性が高い。シックデイルールの説明歴を確認する</v>
+        <v>適度な日光浴、魚類・きのこ類などビタミンDを多く含む食品の摂取を意識するとよいことを伝える</v>
       </c>
       <c r="K70" t="str">
-        <v>糖尿病</v>
+        <v>骨粗鬆症治療における活性型ビタミンD3製剤の効果判定や、投与量調整の参考に用いられる。腎機能低下患者では活性化障害により25(OH)Dが正常でも活性型が不足することがある点に注意</v>
       </c>
       <c r="L70" t="str">
-        <v>尿ケトン体,ケトン体,Ket,シックデイ,ケトアシドーシス</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="M70" t="str">
-        <v/>
+        <v>25(OH)D,ビタミンD,25-ヒドロキシビタミンD,ビタミンD欠乏,骨粗鬆症</v>
+      </c>
+      <c r="N70" t="str">
+        <v>食事と栄養 p.38（ビタミンD）</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>ウロビリノーゲン</v>
+        <v>尿pH</v>
       </c>
       <c r="B71" t="str">
-        <v>Uro</v>
+        <v>尿pH</v>
       </c>
       <c r="C71" t="str">
-        <v>正常（±）程度</v>
+        <v>4.5〜7.5程度（弱酸性が多い）</v>
       </c>
       <c r="D71" t="str">
-        <v>肝臓や胆道、赤血球の壊れ方の状態を反映する尿検査項目</v>
+        <v>尿の酸性・アルカリ性の度合い。食事や感染症、体の状態を反映する</v>
       </c>
       <c r="E71" t="str">
-        <v>ウロビリノーゲンは、赤血球やビリルビンが体の中で処理される過程でできる物質です。肝臓の働きが悪くなったり、赤血球が壊れやすくなったりすると、尿の中の量が変化します。</v>
+        <v>尿のpHは酸性・アルカリ性のバランスを表します。食事の内容や感染症、体の代謝状態によって変化します。単独で大きな問題を示すことは少ない検査です。</v>
       </c>
       <c r="F71" t="str">
-        <v>溶血性疾患（赤血球の破壊亢進）、肝機能障害</v>
+        <v>尿路感染症（尿素分解菌によるもの）、野菜中心の食事、過換気</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>胆道閉塞（胆汁が腸に流れず、ウロビリノーゲンが作られない状態）</v>
+        <v/>
       </c>
       <c r="I71" t="str">
-        <v/>
+        <v>高たんぱく食、糖尿病性ケトアシドーシス、痛風発作時（酸性尿は尿酸結石のリスクを高める）</v>
       </c>
       <c r="J71" t="str">
-        <v>完全に陰性の場合は胆道閉塞を疑う所見の一つ。肝機能（AST/ALT/ビリルビン）と合わせて評価する</v>
+        <v>痛風・尿酸結石がある場合は、野菜など尿をアルカリ化する食品を意識するとよいことを伝える</v>
       </c>
       <c r="K71" t="str">
-        <v>肝機能</v>
+        <v>高尿酸血症・尿酸結石の患者では尿pHが酸性に傾いていないか確認する。尿アルカリ化薬（ウラリットなど）の効果判定にも使う</v>
       </c>
       <c r="L71" t="str">
-        <v>ウロビリノーゲン,Uro,溶血,胆道閉塞,肝機能</v>
+        <v>高尿酸血症</v>
       </c>
       <c r="M71" t="str">
+        <v>尿pH,尿酸性度,尿アルカリ化,ウラリット</v>
+      </c>
+      <c r="N71" t="str">
         <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>尿潜血反応</v>
+        <v>尿ケトン体</v>
       </c>
       <c r="B72" t="str">
-        <v>尿潜血,U-OB</v>
+        <v>尿ケトン,Ket</v>
       </c>
       <c r="C72" t="str">
         <v>陰性（－）</v>
       </c>
       <c r="D72" t="str">
-        <v>尿に血液（赤血球）が混じっていないかを見る検査</v>
+        <v>体がブドウ糖の代わりに脂肪を分解してエネルギーを作っているサイン</v>
       </c>
       <c r="E72" t="str">
-        <v>この検査は、尿に目に見えないくらいの微量の血液が混じっていないかを調べるものです。陽性の場合、腎臓や膀胱、尿路のどこかに炎症や結石などがある可能性があります。</v>
+        <v>この検査は、体が糖の代わりに脂肪を使ってエネルギーを作っていないかを見るものです。陽性が続くときは、食事や水分、インスリンの使い方を確認する必要があります。</v>
       </c>
       <c r="F72" t="str">
-        <v>尿路結石、膀胱炎などの尿路感染症、腎炎、腫瘍、月経血の混入、激しい運動後</v>
+        <v>糖尿病の血糖コントロール不良（シックデイ・インスリン不足）、極端な糖質制限、絶食、嘔吐・下痢による脱水</v>
       </c>
       <c r="G72" t="str">
-        <v>排尿時の痛みや頻尿、目に見える血尿の有無を確認する。女性は月経の時期と重なっていないか確認する</v>
+        <v/>
       </c>
       <c r="H72" t="str">
-        <v/>
+        <v>SGLT2阻害薬(特に絶食・シックデイ時の正常血糖ケトアシドーシスに注意)</v>
       </c>
       <c r="I72" t="str">
         <v/>
       </c>
       <c r="J72" t="str">
-        <v>陽性でも尿沈渣で赤血球が確認されない場合は偽陽性（ミオグロビン尿など）のこともある。持続する場合は泌尿器科的な精査が必要</v>
+        <v/>
       </c>
       <c r="K72" t="str">
-        <v>腎機能</v>
+        <v>陽性かつ高血糖・全身倦怠感が強い場合は糖尿病性ケトアシドーシスの可能性があり緊急性が高い。シックデイルールの説明歴を確認する</v>
       </c>
       <c r="L72" t="str">
-        <v>尿潜血,潜血反応,U-OB,血尿,尿路結石,膀胱炎</v>
+        <v>糖尿病</v>
       </c>
       <c r="M72" t="str">
+        <v>尿ケトン体,ケトン体,Ket,シックデイ,ケトアシドーシス</v>
+      </c>
+      <c r="N72" t="str">
         <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>尿糖（半定量）</v>
+        <v>ウロビリノーゲン</v>
       </c>
       <c r="B73" t="str">
-        <v>尿糖,U-Glu</v>
+        <v>Uro</v>
       </c>
       <c r="C73" t="str">
-        <v>陰性（－）</v>
+        <v>正常（±）程度</v>
       </c>
       <c r="D73" t="str">
-        <v>尿に糖が漏れ出ていないかを見る検査。血糖値がかなり高いと陽性になる</v>
+        <v>肝臓や胆道、赤血球の壊れ方の状態を反映する尿検査項目</v>
       </c>
       <c r="E73" t="str">
-        <v>通常、糖は尿にはほとんど出ませんが、血糖値がかなり高くなると尿にあふれ出るようになります。血糖コントロールの目安の一つです。</v>
+        <v>ウロビリノーゲンは、赤血球やビリルビンが体の中で処理される過程でできる物質です。肝臓の働きが悪くなったり、赤血球が壊れやすくなったりすると、尿の中の量が変化します。</v>
       </c>
       <c r="F73" t="str">
-        <v>糖尿病（血糖値が腎臓で再吸収できる量を超えている状態）、腎性糖尿（血糖値が正常でも体質的に出ることがある）、SGLT2阻害薬服用中（薬の作用で意図的に糖を排泄するため陽性になるのが正常）</v>
+        <v>溶血性疾患（赤血球の破壊亢進）、肝機能障害</v>
       </c>
       <c r="G73" t="str">
-        <v>SGLT2阻害薬（フォシーガ、ジャディアンスなど）服用中は、陽性が薬の効果によるものであることを説明する。脱水や尿路感染の症状がないかも確認する</v>
+        <v/>
       </c>
       <c r="H73" t="str">
         <v/>
       </c>
       <c r="I73" t="str">
-        <v/>
+        <v>胆道閉塞（胆汁が腸に流れず、ウロビリノーゲンが作られない状態）</v>
       </c>
       <c r="J73" t="str">
-        <v>SGLT2阻害薬服用中は尿糖陽性が治療効果として想定内であることを患者に伝える。血糖値・HbA1cと合わせて評価する</v>
+        <v/>
       </c>
       <c r="K73" t="str">
-        <v>糖尿病</v>
+        <v>完全に陰性の場合は胆道閉塞を疑う所見の一つ。肝機能（AST/ALT/ビリルビン）と合わせて評価する</v>
       </c>
       <c r="L73" t="str">
-        <v>尿糖,糖半定量,U-Glu,腎性糖尿,SGLT2</v>
+        <v>肝機能</v>
       </c>
       <c r="M73" t="str">
+        <v>ウロビリノーゲン,Uro,溶血,胆道閉塞,肝機能</v>
+      </c>
+      <c r="N73" t="str">
         <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>尿蛋白定量</v>
+        <v>尿潜血反応</v>
       </c>
       <c r="B74" t="str">
-        <v>U-Pro定量,蛋白/Cr比</v>
+        <v>尿潜血,U-OB</v>
       </c>
       <c r="C74" t="str">
-        <v>0.15 g/gCr未満</v>
+        <v>陰性（－）</v>
       </c>
       <c r="D74" t="str">
-        <v>随時尿から尿蛋白の量を具体的な数値として評価する検査。ネフローゼ等の重症度判定に使う</v>
+        <v>尿に血液（赤血球）が混じっていないかを見る検査</v>
       </c>
       <c r="E74" t="str">
-        <v>これは、尿に出ているたんぱくの量を具体的な数値で見る検査です。試験紙での陽性・陰性の判定だけでなく、実際にどれくらいの量が出ているかを把握できます。</v>
+        <v>この検査は、尿に目に見えないくらいの微量の血液が混じっていないかを調べるものです。陽性の場合、腎臓や膀胱、尿路のどこかに炎症や結石などがある可能性があります。</v>
       </c>
       <c r="F74" t="str">
-        <v>腎症の進行（糖尿病性腎症、慢性腎臓病など）、ネフローゼ症候群（3.5 g/gCr以上が目安）</v>
+        <v>尿路結石、膀胱炎などの尿路感染症、腎炎、腫瘍、月経血の混入、激しい運動後</v>
       </c>
       <c r="G74" t="str">
-        <v/>
+        <v>排尿時の痛みや頻尿、目に見える血尿の有無を確認する。女性は月経の時期と重なっていないか確認する</v>
       </c>
       <c r="H74" t="str">
-        <v/>
+        <v>ワルファリン、DOAC、抗血小板薬など出血傾向を強める薬剤の服用状況を確認</v>
       </c>
       <c r="I74" t="str">
         <v/>
       </c>
       <c r="J74" t="str">
-        <v>CKD診療ガイドラインの重症度分類（尿蛋白量による区分）にも使われる定量指標。試験紙法の半定量結果より治療効果判定に適する</v>
+        <v/>
       </c>
       <c r="K74" t="str">
-        <v>腎機能,糖尿病</v>
+        <v>陽性でも尿沈渣で赤血球が確認されない場合は偽陽性（ミオグロビン尿など）のこともある。持続する場合は泌尿器科的な精査が必要</v>
       </c>
       <c r="L74" t="str">
-        <v>尿蛋白,随時尿,定量,蛋白クレアチニン比,ネフローゼ</v>
+        <v>腎機能</v>
       </c>
       <c r="M74" t="str">
+        <v>尿潜血,潜血反応,U-OB,血尿,尿路結石,膀胱炎</v>
+      </c>
+      <c r="N74" t="str">
         <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>BNP</v>
+        <v>尿糖（半定量）</v>
       </c>
       <c r="B75" t="str">
-        <v>BNP</v>
+        <v>尿糖,U-Glu</v>
       </c>
       <c r="C75" t="str">
-        <v>18.4 pg/mL以下</v>
+        <v>陰性（－）</v>
       </c>
       <c r="D75" t="str">
-        <v>心臓が無理をしているときに出る物質。心臓は血液を送るポンプだが、負担がかかると「少し助けてほしい」というサインとしてBNPを血液中に出す。</v>
+        <v>尿に糖が漏れ出ていないかを見る検査。血糖値がかなり高いと陽性になる</v>
       </c>
       <c r="E75" t="str">
-        <v>この検査は、心臓がどれくらい頑張りすぎていないかを見るものです。数値が高いと、心臓に少し負担がかかっているサインになります。</v>
+        <v>通常、糖は尿にはほとんど出ませんが、血糖値がかなり高くなると尿にあふれ出るようになります。血糖コントロールの目安の一つです。</v>
       </c>
       <c r="F75" t="str">
-        <v>心不全、心臓に負担がかかっている状態、体に水分がたまりやすいとき</v>
+        <v>糖尿病（血糖値が腎臓で再吸収できる量を超えている状態）、腎性糖尿（血糖値が正常でも体質的に出ることがある）、SGLT2阻害薬服用中（薬の作用で意図的に糖を排泄するため陽性になるのが正常）</v>
       </c>
       <c r="G75" t="str">
-        <v>塩分・水分の摂りすぎに注意し、体重の変化を毎日記録するよう伝える</v>
+        <v>SGLT2阻害薬（フォシーガ、ジャディアンスなど）服用中は、陽性が薬の効果によるものであることを説明する。脱水や尿路感染の症状がないかも確認する</v>
       </c>
       <c r="H75" t="str">
-        <v>心臓の負担は少ない状態</v>
+        <v>SGLT2阻害薬(薬理作用による陽性であれば想定内であることを説明)</v>
       </c>
       <c r="I75" t="str">
         <v/>
       </c>
       <c r="J75" t="str">
-        <v>腎機能が低いとBNPは高めに出ることがある／数値だけで判断せず、症状と合わせて評価する／息切れ、むくみ、体重増加があれば要注意</v>
+        <v/>
       </c>
       <c r="K75" t="str">
-        <v>心不全</v>
+        <v>SGLT2阻害薬服用中は尿糖陽性が治療効果として想定内であることを患者に伝える。血糖値・HbA1cと合わせて評価する</v>
       </c>
       <c r="L75" t="str">
-        <v>BNP,心不全,息切れ,むくみ</v>
+        <v>糖尿病</v>
       </c>
       <c r="M75" t="str">
-        <v>食事と栄養 p.216-222（第2部 心疾患）</v>
+        <v>尿糖,糖半定量,U-Glu,腎性糖尿,SGLT2</v>
+      </c>
+      <c r="N75" t="str">
+        <v/>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>血清CPR（Cペプチド）</v>
+        <v>尿蛋白定量</v>
       </c>
       <c r="B76" t="str">
-        <v>CPR</v>
+        <v>U-Pro定量,蛋白/Cr比</v>
       </c>
       <c r="C76" t="str">
-        <v>空腹時 0.6〜3.0 ng/mL（施設差あり）</v>
+        <v>0.15 g/gCr未満</v>
       </c>
       <c r="D76" t="str">
-        <v>自分の膵臓がどれくらいインスリンを作れているかを表す指標</v>
+        <v>随時尿から尿蛋白の量を具体的な数値として評価する検査。ネフローゼ等の重症度判定に使う</v>
       </c>
       <c r="E76" t="str">
-        <v>この検査は、ご自身の膵臓がどれくらいインスリンを作る力を持っているかを見るものです。数値が低いほど、体の中で作れるインスリンが少ないことを示します。</v>
+        <v>これは、尿に出ているたんぱくの量を具体的な数値で見る検査です。試験紙での陽性・陰性の判定だけでなく、実際にどれくらいの量が出ているかを把握できます。</v>
       </c>
       <c r="F76" t="str">
-        <v>インスリン抵抗性が強い状態（初期の2型糖尿病など）</v>
+        <v>腎症の進行（糖尿病性腎症、慢性腎臓病など）、ネフローゼ症候群（3.5 g/gCr以上が目安）</v>
       </c>
       <c r="G76" t="str">
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>膵臓のインスリン分泌能低下（1型糖尿病、糖尿病の進行）</v>
+        <v>NSAIDs、造影剤、アミノグリコシド系、バンコマイシン</v>
       </c>
       <c r="I76" t="str">
         <v/>
       </c>
       <c r="J76" t="str">
-        <v>インスリン分泌能の評価に使われる。数値が低いほどインスリン治療の必要性が高いと判断される目安になる</v>
+        <v/>
       </c>
       <c r="K76" t="str">
-        <v>糖尿病</v>
+        <v>CKD診療ガイドラインの重症度分類（尿蛋白量による区分）にも使われる定量指標。試験紙法の半定量結果より治療効果判定に適する</v>
       </c>
       <c r="L76" t="str">
-        <v>CPR,Cペプチド,インスリン分泌,血清CPR</v>
+        <v>腎機能,糖尿病</v>
       </c>
       <c r="M76" t="str">
+        <v>尿蛋白,随時尿,定量,蛋白クレアチニン比,ネフローゼ</v>
+      </c>
+      <c r="N76" t="str">
         <v/>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>尿中微量アルブミン</v>
+        <v>BNP</v>
       </c>
       <c r="B77" t="str">
-        <v>U-Alb,MAU</v>
+        <v>BNP</v>
       </c>
       <c r="C77" t="str">
-        <v>30 mg/gCr未満（尿中アルブミン/クレアチニン比）</v>
+        <v>18.4 pg/mL以下</v>
       </c>
       <c r="D77" t="str">
-        <v>通常の尿蛋白検査では見つからない、ごく早期の腎症のサイン</v>
+        <v>心臓が無理をしているときに出る物質。心臓は血液を送るポンプだが、負担がかかると「少し助けてほしい」というサインとしてBNPを血液中に出す。</v>
       </c>
       <c r="E77" t="str">
-        <v>この検査は、通常の尿検査ではまだ分からないくらい早い段階の腎臓の変化を見つけるためのものです。数値が高いと、腎症の初期のサインである可能性があります。</v>
+        <v>この検査は、心臓がどれくらい頑張りすぎていないかを見るものです。数値が高いと、心臓に少し負担がかかっているサインになります。</v>
       </c>
       <c r="F77" t="str">
-        <v>糖尿病性腎症の早期段階、高血圧</v>
+        <v>心不全、心臓に負担がかかっている状態、体に水分がたまりやすいとき</v>
       </c>
       <c r="G77" t="str">
-        <v/>
+        <v>塩分・水分の摂りすぎに注意し、体重の変化を毎日記録するよう伝える</v>
       </c>
       <c r="H77" t="str">
         <v/>
       </c>
       <c r="I77" t="str">
-        <v/>
+        <v>心臓の負担は少ない状態</v>
       </c>
       <c r="J77" t="str">
-        <v>糖尿病腎症の早期発見に重要な検査。血糖・血圧コントロールで改善しうる段階なので、早期介入の意義を伝える</v>
+        <v/>
       </c>
       <c r="K77" t="str">
-        <v>糖尿病,腎機能</v>
+        <v>腎機能が低いとBNPは高めに出ることがある／数値だけで判断せず、症状と合わせて評価する／息切れ、むくみ、体重増加があれば要注意</v>
       </c>
       <c r="L77" t="str">
-        <v>微量アルブミン,U-Alb,MAU,糖尿病性腎症,早期腎症</v>
+        <v>心不全</v>
       </c>
       <c r="M77" t="str">
-        <v/>
+        <v>BNP,心不全,息切れ,むくみ</v>
+      </c>
+      <c r="N77" t="str">
+        <v>食事と栄養 p.216-222（第2部 心疾患）</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>血清鉄（Fe）</v>
+        <v>血清CPR（Cペプチド）</v>
       </c>
       <c r="B78" t="str">
-        <v>Fe</v>
+        <v>CPR</v>
       </c>
       <c r="C78" t="str">
-        <v>60〜200 μg/dL（施設差あり）</v>
+        <v>空腹時 0.6〜3.0 ng/mL（施設差あり）</v>
       </c>
       <c r="D78" t="str">
-        <v>血液中を流れている鉄の量</v>
+        <v>自分の膵臓がどれくらいインスリンを作れているかを表す指標</v>
       </c>
       <c r="E78" t="str">
-        <v>この検査は、今血液の中を流れている鉄の量を見るものです。低いと、体の中で鉄が不足している可能性があります。</v>
+        <v>この検査は、ご自身の膵臓がどれくらいインスリンを作る力を持っているかを見るものです。数値が低いほど、体の中で作れるインスリンが少ないことを示します。</v>
       </c>
       <c r="F78" t="str">
-        <v>鉄剤の過剰摂取、溶血、肝疾患</v>
+        <v>インスリン抵抗性が強い状態（初期の2型糖尿病など）</v>
       </c>
       <c r="G78" t="str">
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>鉄欠乏性貧血、慢性炎症、出血</v>
+        <v/>
       </c>
       <c r="I78" t="str">
-        <v>鉄分の多い食品（レバー・赤身肉・魚・ほうれん草など）を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える</v>
+        <v>膵臓のインスリン分泌能低下（1型糖尿病、糖尿病の進行）</v>
       </c>
       <c r="J78" t="str">
-        <v>血清鉄は日内変動が大きい。単独で判断せず総鉄結合能・フェリチンと合わせて評価する</v>
+        <v/>
       </c>
       <c r="K78" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>インスリン分泌能の評価に使われる。数値が低いほどインスリン治療の必要性が高いと判断される目安になる</v>
       </c>
       <c r="L78" t="str">
-        <v>血清鉄,Fe,鉄欠乏性貧血</v>
+        <v>糖尿病</v>
       </c>
       <c r="M78" t="str">
-        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
+        <v>CPR,Cペプチド,インスリン分泌,血清CPR</v>
+      </c>
+      <c r="N78" t="str">
+        <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>総鉄結合能（TIBC）</v>
+        <v>尿中微量アルブミン</v>
       </c>
       <c r="B79" t="str">
-        <v>TIBC</v>
+        <v>U-Alb,MAU</v>
       </c>
       <c r="C79" t="str">
-        <v>250〜360 μg/dL（施設差あり）</v>
+        <v>30 mg/gCr未満（尿中アルブミン/クレアチニン比）</v>
       </c>
       <c r="D79" t="str">
-        <v>血液中のトランスフェリンが鉄と結合できる総量</v>
+        <v>通常の尿蛋白検査では見つからない、ごく早期の腎症のサイン</v>
       </c>
       <c r="E79" t="str">
-        <v>TIBCは、血液中でトランスフェリンという物質が鉄を運べる最大量を表します。体の中の鉄が不足すると、少しでも多く鉄を運ぼうとしてこの数値が上がる性質があります。</v>
+        <v>この検査は、通常の尿検査ではまだ分からないくらい早い段階の腎臓の変化を見つけるためのものです。数値が高いと、腎症の初期のサインである可能性があります。</v>
       </c>
       <c r="F79" t="str">
-        <v>鉄欠乏性貧血（＞360 μg/dLが目安）</v>
+        <v>糖尿病性腎症の早期段階、高血圧</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>慢性炎症、肝疾患、ネフローゼ症候群</v>
+        <v>NSAIDsなど腎機能を悪化させる薬剤。ACE阻害薬・ARB・SGLT2阻害薬は低下させる方向に働く</v>
       </c>
       <c r="I79" t="str">
         <v/>
       </c>
       <c r="J79" t="str">
-        <v>鉄が不足すると、体はより多く運ぼうとしてTIBCが上昇する。UIBC・血清鉄と併せて評価する</v>
+        <v/>
       </c>
       <c r="K79" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>糖尿病腎症の早期発見に重要な検査。血糖・血圧コントロールで改善しうる段階なので、早期介入の意義を伝える</v>
       </c>
       <c r="L79" t="str">
-        <v>TIBC,総鉄結合能,鉄欠乏性貧血</v>
+        <v>糖尿病,腎機能</v>
       </c>
       <c r="M79" t="str">
-        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
+        <v>微量アルブミン,U-Alb,MAU,糖尿病性腎症,早期腎症</v>
+      </c>
+      <c r="N79" t="str">
+        <v/>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>不飽和鉄結合能（UIBC）</v>
+        <v>血清鉄（Fe）</v>
       </c>
       <c r="B80" t="str">
-        <v>UIBC</v>
+        <v>Fe</v>
       </c>
       <c r="C80" t="str">
-        <v>170〜300 μg/dL（施設差あり）</v>
+        <v>60〜200 μg/dL（施設差あり）</v>
       </c>
       <c r="D80" t="str">
-        <v>トランスフェリンのうち、まだ鉄と結合していない余力の部分（UIBC＝TIBC－血清鉄）</v>
+        <v>血液中を流れている鉄の量</v>
       </c>
       <c r="E80" t="str">
-        <v>UIBCは、トランスフェリンのうち、まだ鉄と結合していない「空き容量」の部分を表します。鉄が不足しているときほど、この空き容量は大きくなります。</v>
+        <v>この検査は、今血液の中を流れている鉄の量を見るものです。低いと、体の中で鉄が不足している可能性があります。</v>
       </c>
       <c r="F80" t="str">
-        <v>鉄欠乏性貧血（＞300 μg/dLが目安）</v>
+        <v>鉄剤の過剰摂取、溶血、肝疾患</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>慢性炎症、鉄過剰状態</v>
+        <v>鉄剤の過量摂取(小児の誤飲を含む)</v>
       </c>
       <c r="I80" t="str">
-        <v/>
+        <v>鉄欠乏性貧血、慢性炎症、出血</v>
       </c>
       <c r="J80" t="str">
-        <v>TIBCと同じ方向に動くことが多い。血清鉄・TIBCとあわせて鉄欠乏性貧血と二次性貧血の鑑別に使う</v>
+        <v>鉄分の多い食品（レバー・赤身肉・魚・ほうれん草など）を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える</v>
       </c>
       <c r="K80" t="str">
+        <v>血清鉄は日内変動が大きい。単独で判断せず総鉄結合能・フェリチンと合わせて評価する</v>
+      </c>
+      <c r="L80" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
-      <c r="L80" t="str">
-        <v>UIBC,不飽和鉄結合能,鉄欠乏性貧血</v>
-      </c>
       <c r="M80" t="str">
+        <v>血清鉄,Fe,鉄欠乏性貧血</v>
+      </c>
+      <c r="N80" t="str">
         <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>トランスフェリン飽和度</v>
+        <v>総鉄結合能（TIBC）</v>
       </c>
       <c r="B81" t="str">
-        <v>TSAT</v>
+        <v>TIBC</v>
       </c>
       <c r="C81" t="str">
-        <v>16〜50%程度（施設差あり）</v>
+        <v>250〜360 μg/dL（施設差あり）</v>
       </c>
       <c r="D81" t="str">
-        <v>鉄を運ぶ役割のトランスフェリンのうち、実際に鉄を運んでいる割合（血清鉄÷総鉄結合能）</v>
+        <v>血液中のトランスフェリンが鉄と結合できる総量</v>
       </c>
       <c r="E81" t="str">
-        <v>トランスフェリン飽和度は、鉄を運ぶトランスフェリンのうち、実際にどれくらいが鉄を運んでいるかを割合で表したものです。鉄欠乏性貧血では低くなり、鉄が過剰にたまる病気では高くなります。</v>
+        <v>TIBCは、血液中でトランスフェリンという物質が鉄を運べる最大量を表します。体の中の鉄が不足すると、少しでも多く鉄を運ぼうとしてこの数値が上がる性質があります。</v>
       </c>
       <c r="F81" t="str">
-        <v>鉄過剰症（ヘモクロマトーシスなど）</v>
+        <v>鉄欠乏性貧血（＞360 μg/dLが目安）</v>
       </c>
       <c r="G81" t="str">
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>鉄欠乏性貧血（＜16%が目安）</v>
+        <v/>
       </c>
       <c r="I81" t="str">
-        <v/>
+        <v>慢性炎症、肝疾患、ネフローゼ症候群</v>
       </c>
       <c r="J81" t="str">
-        <v>血清鉄をTIBCで割って計算される。鉄剤補充の効果判定にも使われる</v>
+        <v/>
       </c>
       <c r="K81" t="str">
+        <v>鉄が不足すると、体はより多く運ぼうとしてTIBCが上昇する。UIBC・血清鉄と併せて評価する</v>
+      </c>
+      <c r="L81" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
-      <c r="L81" t="str">
-        <v>トランスフェリン飽和度,TSAT,鉄欠乏性貧血</v>
-      </c>
       <c r="M81" t="str">
+        <v>TIBC,総鉄結合能,鉄欠乏性貧血</v>
+      </c>
+      <c r="N81" t="str">
         <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>血清フェリチン</v>
+        <v>不飽和鉄結合能（UIBC）</v>
       </c>
       <c r="B82" t="str">
-        <v>Ferritin</v>
+        <v>UIBC</v>
       </c>
       <c r="C82" t="str">
-        <v>男性 20〜250 ng/mL、女性 10〜120 ng/mL（施設差あり）</v>
+        <v>170〜300 μg/dL（施設差あり）</v>
       </c>
       <c r="D82" t="str">
-        <v>体に貯蔵されている鉄の量を反映する指標。貧血の症状が出るより早い段階で低下する</v>
+        <v>トランスフェリンのうち、まだ鉄と結合していない余力の部分（UIBC＝TIBC－血清鉄）</v>
       </c>
       <c r="E82" t="str">
-        <v>フェリチンは、体に蓄えられている鉄の「貯金」の量を見る検査です。この数値が下がるのは、貧血の症状が出るよりも前の、とても早い段階のサインになります。</v>
+        <v>UIBCは、トランスフェリンのうち、まだ鉄と結合していない「空き容量」の部分を表します。鉄が不足しているときほど、この空き容量は大きくなります。</v>
       </c>
       <c r="F82" t="str">
-        <v>炎症性疾患、肝疾患、悪性腫瘍、鉄過剰症（フェリチンは炎症でも上昇するため、貧血の評価では注意が必要）</v>
+        <v>鉄欠乏性貧血（＞300 μg/dLが目安）</v>
       </c>
       <c r="G82" t="str">
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>鉄欠乏状態（貧血の症状が出る前の早期段階から低下する）</v>
+        <v/>
       </c>
       <c r="I82" t="str">
-        <v>鉄分の多い食品を意識するとともに、貯蔵鉄を補うため治療は数値が正常化してからも継続が必要なことを伝える</v>
+        <v>慢性炎症、鉄過剰状態</v>
       </c>
       <c r="J82" t="str">
-        <v>貯蔵鉄の指標で鉄欠乏を最も早期に反映する。ただし炎症があると鉄欠乏があっても正常〜高値に出ることがあり、CRP等の炎症所見と合わせて評価する。二次性貧血との鑑別に重要</v>
+        <v/>
       </c>
       <c r="K82" t="str">
+        <v>TIBCと同じ方向に動くことが多い。血清鉄・TIBCとあわせて鉄欠乏性貧血と二次性貧血の鑑別に使う</v>
+      </c>
+      <c r="L82" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
-      <c r="L82" t="str">
-        <v>フェリチン,Ferritin,貯蔵鉄,鉄欠乏</v>
-      </c>
       <c r="M82" t="str">
+        <v>UIBC,不飽和鉄結合能,鉄欠乏性貧血</v>
+      </c>
+      <c r="N82" t="str">
         <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>尿中尿酸/クレアチニン比（UUA/UCr）</v>
+        <v>トランスフェリン飽和度</v>
       </c>
       <c r="B83" t="str">
-        <v>UUA/UCr</v>
+        <v>TSAT</v>
       </c>
       <c r="C83" t="str">
-        <v>0.4〜0.8程度が混合型の目安</v>
+        <v>16〜50%程度（施設差あり）</v>
       </c>
       <c r="D83" t="str">
-        <v>尿酸が「作られすぎ」か「排泄できていない」かを見分ける比の値</v>
+        <v>鉄を運ぶ役割のトランスフェリンのうち、実際に鉄を運んでいる割合（血清鉄÷総鉄結合能）</v>
       </c>
       <c r="E83" t="str">
-        <v>この数値は、体の中で尿酸が「作られすぎている」のか、それとも「うまく排泄できていない」のかを見分けるために使う比の値です。高尿酸血症の治療薬を選ぶときの参考になります。</v>
+        <v>トランスフェリン飽和度は、鉄を運ぶトランスフェリンのうち、実際にどれくらいが鉄を運んでいるかを割合で表したものです。鉄欠乏性貧血では低くなり、鉄が過剰にたまる病気では高くなります。</v>
       </c>
       <c r="F83" t="str">
-        <v>尿酸産生過剰型（0.8以上が目安）</v>
+        <v>鉄過剰症（ヘモクロマトーシスなど）</v>
       </c>
       <c r="G83" t="str">
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>尿酸排泄低下型（0.4以下が目安）</v>
+        <v/>
       </c>
       <c r="I83" t="str">
-        <v/>
+        <v>鉄欠乏性貧血（＜16%が目安）</v>
       </c>
       <c r="J83" t="str">
-        <v>高尿酸血症は尿酸産生過剰型・排泄低下型・混合型に分類され、この比が目安になる。病型によって使う薬剤（尿酸生成抑制薬か尿酸排泄促進薬か）の選択が変わる</v>
+        <v/>
       </c>
       <c r="K83" t="str">
-        <v>高尿酸血症</v>
+        <v>血清鉄をTIBCで割って計算される。鉄剤補充の効果判定にも使われる</v>
       </c>
       <c r="L83" t="str">
-        <v>UUA,UCr,尿酸クリアランス,CUA,EUA,尿酸産生過剰型,尿酸排泄低下型</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="M83" t="str">
-        <v>食事と栄養 p.180-189（第2部 痛風・高尿酸血症）</v>
+        <v>トランスフェリン飽和度,TSAT,鉄欠乏性貧血</v>
+      </c>
+      <c r="N83" t="str">
+        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>ucOC（低カルボキシル化オステオカルシン）</v>
+        <v>血清フェリチン</v>
       </c>
       <c r="B84" t="str">
-        <v>ucOC</v>
+        <v>Ferritin</v>
       </c>
       <c r="C84" t="str">
-        <v>4.5 ng/mL未満（施設差あり）</v>
+        <v>男性 20〜250 ng/mL、女性 10〜120 ng/mL（施設差あり）</v>
       </c>
       <c r="D84" t="str">
-        <v>ビタミンKが不足していないかを反映する骨の指標</v>
+        <v>体に貯蔵されている鉄の量を反映する指標。貧血の症状が出るより早い段階で低下する</v>
       </c>
       <c r="E84" t="str">
-        <v>ucOCは、骨を作るために必要なビタミンKが体の中で足りているかどうかを反映する検査です。数値が高いとビタミンK不足が疑われます。</v>
+        <v>フェリチンは、体に蓄えられている鉄の「貯金」の量を見る検査です。この数値が下がるのは、貧血の症状が出るよりも前の、とても早い段階のサインになります。</v>
       </c>
       <c r="F84" t="str">
-        <v>ビタミンK不足状態</v>
+        <v>炎症性疾患、肝疾患、悪性腫瘍、鉄過剰症（フェリチンは炎症でも上昇するため、貧血の評価では注意が必要）</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3851,121 +4101,130 @@
         <v/>
       </c>
       <c r="I84" t="str">
-        <v/>
+        <v>鉄欠乏状態（貧血の症状が出る前の早期段階から低下する）</v>
       </c>
       <c r="J84" t="str">
-        <v>ビタミンK2製剤（骨粗鬆症治療薬）の適応判断や効果判定に使われる</v>
+        <v>鉄分の多い食品を意識するとともに、貯蔵鉄を補うため治療は数値が正常化してからも継続が必要なことを伝える</v>
       </c>
       <c r="K84" t="str">
-        <v>骨粗鬆症</v>
+        <v>貯蔵鉄の指標で鉄欠乏を最も早期に反映する。ただし炎症があると鉄欠乏があっても正常〜高値に出ることがあり、CRP等の炎症所見と合わせて評価する。二次性貧血との鑑別に重要</v>
       </c>
       <c r="L84" t="str">
-        <v>ucOC,オステオカルシン,ビタミンK</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="M84" t="str">
-        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
+        <v>フェリチン,Ferritin,貯蔵鉄,鉄欠乏</v>
+      </c>
+      <c r="N84" t="str">
+        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>PTH（副甲状腺ホルモン）</v>
+        <v>尿中尿酸/クレアチニン比（UUA/UCr）</v>
       </c>
       <c r="B85" t="str">
-        <v>PTH</v>
+        <v>UUA/UCr</v>
       </c>
       <c r="C85" t="str">
-        <v>10〜65 pg/mL（施設差あり）</v>
+        <v>0.4〜0.8程度が混合型の目安</v>
       </c>
       <c r="D85" t="str">
-        <v>血液中のカルシウム濃度を調節するホルモン</v>
+        <v>尿酸が「作られすぎ」か「排泄できていない」かを見分ける比の値</v>
       </c>
       <c r="E85" t="str">
-        <v>PTHは、血液中のカルシウム濃度を一定に保つために働くホルモンです。カルシウムが低くなると分泌が増え、骨からカルシウムを取り出したり、腎臓での再吸収を促したりして数値を戻そうとします。</v>
+        <v>この数値は、体の中で尿酸が「作られすぎている」のか、それとも「うまく排泄できていない」のかを見分けるために使う比の値です。高尿酸血症の治療薬を選ぶときの参考になります。</v>
       </c>
       <c r="F85" t="str">
-        <v>原発性・二次性副甲状腺機能亢進症（腎不全に伴うものなど）</v>
+        <v>尿酸産生過剰型（0.8以上が目安）</v>
       </c>
       <c r="G85" t="str">
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>副甲状腺機能低下症</v>
+        <v/>
       </c>
       <c r="I85" t="str">
-        <v/>
+        <v>尿酸排泄低下型（0.4以下が目安）</v>
       </c>
       <c r="J85" t="str">
-        <v>骨粗鬆症の二次性原因（副甲状腺機能亢進症）を除外するための検査。カルシウム・リンと合わせて評価する</v>
+        <v/>
       </c>
       <c r="K85" t="str">
-        <v>骨粗鬆症</v>
+        <v>高尿酸血症は尿酸産生過剰型・排泄低下型・混合型に分類され、この比が目安になる。病型によって使う薬剤（尿酸生成抑制薬か尿酸排泄促進薬か）の選択が変わる</v>
       </c>
       <c r="L85" t="str">
-        <v>PTH,副甲状腺ホルモン,パラトルモン</v>
+        <v>高尿酸血症</v>
       </c>
       <c r="M85" t="str">
-        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
+        <v>UUA,UCr,尿酸クリアランス,CUA,EUA,尿酸産生過剰型,尿酸排泄低下型</v>
+      </c>
+      <c r="N85" t="str">
+        <v>食事と栄養 p.180-189（第2部 痛風・高尿酸血症）</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>尿中NTX</v>
+        <v>ucOC（低カルボキシル化オステオカルシン）</v>
       </c>
       <c r="B86" t="str">
-        <v>NTX</v>
+        <v>ucOC</v>
       </c>
       <c r="C86" t="str">
-        <v>施設差が大きく一律の記載が難しい（尿中）</v>
+        <v>4.5 ng/mL未満（施設差あり）</v>
       </c>
       <c r="D86" t="str">
-        <v>骨が壊されるときに出る、骨吸収マーカーのひとつ</v>
+        <v>ビタミンKが不足していないかを反映する骨の指標</v>
       </c>
       <c r="E86" t="str">
-        <v>NTXは、骨が壊される（吸収される）ときに尿の中に出てくる物質です。骨粗鬆症の治療薬がどれくらい効いているかを確認するために使われます。</v>
+        <v>ucOCは、骨を作るために必要なビタミンKが体の中で足りているかどうかを反映する検査です。数値が高いとビタミンK不足が疑われます。</v>
       </c>
       <c r="F86" t="str">
-        <v>骨代謝回転の亢進（骨粗鬆症、閉経後など）</v>
+        <v>ビタミンK不足状態</v>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>骨吸収抑制薬（ビスホスホネート等）による治療効果</v>
+        <v/>
       </c>
       <c r="I86" t="str">
         <v/>
       </c>
       <c r="J86" t="str">
-        <v>治療開始後3〜6か月で再検し、薬の効果判定に使われる。TRACP-5bと同じ「骨を壊す側」の指標</v>
+        <v/>
       </c>
       <c r="K86" t="str">
+        <v>ビタミンK2製剤（骨粗鬆症治療薬）の適応判断や効果判定に使われる</v>
+      </c>
+      <c r="L86" t="str">
         <v>骨粗鬆症</v>
       </c>
-      <c r="L86" t="str">
-        <v>NTX,尿中NTX,骨吸収マーカー</v>
-      </c>
       <c r="M86" t="str">
+        <v>ucOC,オステオカルシン,ビタミンK</v>
+      </c>
+      <c r="N86" t="str">
         <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>カルシトニン</v>
+        <v>PTH（副甲状腺ホルモン）</v>
       </c>
       <c r="B87" t="str">
-        <v>CT</v>
+        <v>PTH</v>
       </c>
       <c r="C87" t="str">
-        <v>男性 9.52 pg/mL未満、女性 6.40 pg/mL未満（施設差あり）</v>
+        <v>10〜65 pg/mL（施設差あり）</v>
       </c>
       <c r="D87" t="str">
-        <v>血液中のカルシウムを下げる方向に働くホルモン</v>
+        <v>血液中のカルシウム濃度を調節するホルモン</v>
       </c>
       <c r="E87" t="str">
-        <v>カルシトニンは、PTHとは逆に血液中のカルシウムを下げる方向に働くホルモンです。特定の甲状腺の病気（甲状腺髄様癌）がないかを調べる際にも使われます。</v>
+        <v>PTHは、血液中のカルシウム濃度を一定に保つために働くホルモンです。カルシウムが低くなると分泌が増え、骨からカルシウムを取り出したり、腎臓での再吸収を促したりして数値を戻そうとします。</v>
       </c>
       <c r="F87" t="str">
-        <v>甲状腺髄様癌、腎不全</v>
+        <v>原発性・二次性副甲状腺機能亢進症（腎不全に伴うものなど）</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -3974,162 +4233,174 @@
         <v/>
       </c>
       <c r="I87" t="str">
-        <v/>
+        <v>副甲状腺機能低下症</v>
       </c>
       <c r="J87" t="str">
-        <v>骨粗鬆症の二次性原因の除外目的で測定されることがある検査値。同名の薬剤（カルシトニン製剤）と混同しないよう注意</v>
+        <v/>
       </c>
       <c r="K87" t="str">
+        <v>骨粗鬆症の二次性原因（副甲状腺機能亢進症）を除外するための検査。カルシウム・リンと合わせて評価する</v>
+      </c>
+      <c r="L87" t="str">
         <v>骨粗鬆症</v>
       </c>
-      <c r="L87" t="str">
-        <v>カルシトニン,CT</v>
-      </c>
       <c r="M87" t="str">
+        <v>PTH,副甲状腺ホルモン,パラトルモン</v>
+      </c>
+      <c r="N87" t="str">
         <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>DPD（デオキシピリジノリン）</v>
+        <v>尿中NTX</v>
       </c>
       <c r="B88" t="str">
-        <v>DPD</v>
+        <v>NTX</v>
       </c>
       <c r="C88" t="str">
         <v>施設差が大きく一律の記載が難しい（尿中）</v>
       </c>
       <c r="D88" t="str">
-        <v>骨のコラーゲンが壊れるときに出る、骨吸収マーカーのひとつ</v>
+        <v>骨が壊されるときに出る、骨吸収マーカーのひとつ</v>
       </c>
       <c r="E88" t="str">
-        <v>DPDも、骨が壊されるときに尿に出てくる物質の一つです。NTXと同じように、骨粗鬆症治療薬の効果を確認するために使われます。</v>
+        <v>NTXは、骨が壊される（吸収される）ときに尿の中に出てくる物質です。骨粗鬆症の治療薬がどれくらい効いているかを確認するために使われます。</v>
       </c>
       <c r="F88" t="str">
-        <v>骨代謝回転の亢進（骨粗鬆症など）</v>
+        <v>骨代謝回転の亢進（骨粗鬆症、閉経後など）</v>
       </c>
       <c r="G88" t="str">
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>骨吸収抑制薬による治療効果</v>
+        <v/>
       </c>
       <c r="I88" t="str">
-        <v/>
+        <v>骨吸収抑制薬（ビスホスホネート等）による治療効果</v>
       </c>
       <c r="J88" t="str">
-        <v>NTX・CTXと同じ「骨を壊す側」の指標。食事の影響を受けにくいとされる</v>
+        <v/>
       </c>
       <c r="K88" t="str">
+        <v>治療開始後3〜6か月で再検し、薬の効果判定に使われる。TRACP-5bと同じ「骨を壊す側」の指標</v>
+      </c>
+      <c r="L88" t="str">
         <v>骨粗鬆症</v>
       </c>
-      <c r="L88" t="str">
-        <v>DPD,デオキシピリジノリン,骨吸収マーカー</v>
-      </c>
       <c r="M88" t="str">
+        <v>NTX,尿中NTX,骨吸収マーカー</v>
+      </c>
+      <c r="N88" t="str">
         <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>CTX</v>
+        <v>カルシトニン</v>
       </c>
       <c r="B89" t="str">
-        <v>CTX</v>
+        <v>CT</v>
       </c>
       <c r="C89" t="str">
-        <v>施設差が大きく一律の記載が難しい（血清・尿中）</v>
+        <v>男性 9.52 pg/mL未満、女性 6.40 pg/mL未満（施設差あり）</v>
       </c>
       <c r="D89" t="str">
-        <v>骨のコラーゲンが壊れるときに出る、骨吸収マーカーのひとつ</v>
+        <v>血液中のカルシウムを下げる方向に働くホルモン</v>
       </c>
       <c r="E89" t="str">
-        <v>CTXも、骨が壊されるときに血液や尿に出てくる物質です。骨粗鬆症治療薬（骨を壊すのを抑える薬）の効果を確認するために使われます。</v>
+        <v>カルシトニンは、PTHとは逆に血液中のカルシウムを下げる方向に働くホルモンです。特定の甲状腺の病気（甲状腺髄様癌）がないかを調べる際にも使われます。</v>
       </c>
       <c r="F89" t="str">
-        <v>骨代謝回転の亢進（骨粗鬆症など）</v>
+        <v>甲状腺髄様癌、腎不全</v>
       </c>
       <c r="G89" t="str">
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>骨吸収抑制薬による治療効果</v>
+        <v/>
       </c>
       <c r="I89" t="str">
         <v/>
       </c>
       <c r="J89" t="str">
-        <v>NTX・DPDと同じ「骨を壊す側」の指標。血清・尿中いずれでも測定されることがある</v>
+        <v/>
       </c>
       <c r="K89" t="str">
+        <v>骨粗鬆症の二次性原因の除外目的で測定されることがある検査値。同名の薬剤（カルシトニン製剤）と混同しないよう注意</v>
+      </c>
+      <c r="L89" t="str">
         <v>骨粗鬆症</v>
       </c>
-      <c r="L89" t="str">
-        <v>CTX,骨吸収マーカー</v>
-      </c>
       <c r="M89" t="str">
+        <v>カルシトニン,CT</v>
+      </c>
+      <c r="N89" t="str">
         <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>P1NP</v>
+        <v>DPD（デオキシピリジノリン）</v>
       </c>
       <c r="B90" t="str">
-        <v>P1NP</v>
+        <v>DPD</v>
       </c>
       <c r="C90" t="str">
-        <v>施設差が大きく一律の記載が難しい（血清）</v>
+        <v>施設差が大きく一律の記載が難しい（尿中）</v>
       </c>
       <c r="D90" t="str">
-        <v>骨が新しく作られるときに出る、骨形成マーカーのひとつ</v>
+        <v>骨のコラーゲンが壊れるときに出る、骨吸収マーカーのひとつ</v>
       </c>
       <c r="E90" t="str">
-        <v>P1NPは、CTXなどとは逆に、骨が新しく作られるときに血液中に出てくる物質です。骨を作る力を高める薬（テリパラチドなど）の効果を確認するために使われます。</v>
+        <v>DPDも、骨が壊されるときに尿に出てくる物質の一つです。NTXと同じように、骨粗鬆症治療薬の効果を確認するために使われます。</v>
       </c>
       <c r="F90" t="str">
-        <v>骨代謝回転の亢進、骨形成促進薬による治療効果</v>
+        <v>骨代謝回転の亢進（骨粗鬆症など）</v>
       </c>
       <c r="G90" t="str">
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>骨形成の低下</v>
+        <v/>
       </c>
       <c r="I90" t="str">
-        <v/>
+        <v>骨吸収抑制薬による治療効果</v>
       </c>
       <c r="J90" t="str">
-        <v>TRACP-5b等「骨を壊す側」の指標とは逆の、「骨を作る側」の指標。骨形成促進薬（テリパラチド等）の効果判定に使われる</v>
+        <v/>
       </c>
       <c r="K90" t="str">
+        <v>NTX・CTXと同じ「骨を壊す側」の指標。食事の影響を受けにくいとされる</v>
+      </c>
+      <c r="L90" t="str">
         <v>骨粗鬆症</v>
       </c>
-      <c r="L90" t="str">
-        <v>P1NP,骨形成マーカー</v>
-      </c>
       <c r="M90" t="str">
+        <v>DPD,デオキシピリジノリン,骨吸収マーカー</v>
+      </c>
+      <c r="N90" t="str">
         <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>抗甲状腺マイクロゾーム抗体（抗TPO抗体）</v>
+        <v>CTX</v>
       </c>
       <c r="B91" t="str">
-        <v>TPOAb</v>
+        <v>CTX</v>
       </c>
       <c r="C91" t="str">
-        <v>陰性（16 IU/mL未満程度、施設差あり）</v>
+        <v>施設差が大きく一律の記載が難しい（血清・尿中）</v>
       </c>
       <c r="D91" t="str">
-        <v>自分の甲状腺を攻撃する抗体が出ていないかを見る検査</v>
+        <v>骨のコラーゲンが壊れるときに出る、骨吸収マーカーのひとつ</v>
       </c>
       <c r="E91" t="str">
-        <v>この検査は、体の中に自分の甲状腺を誤って攻撃してしまう抗体がないかを見るものです。陽性の場合、橋本病（慢性甲状腺炎）など甲状腺の自己免疫的な炎症が背景にある可能性があります。</v>
+        <v>CTXも、骨が壊されるときに血液や尿に出てくる物質です。骨粗鬆症治療薬（骨を壊すのを抑える薬）の効果を確認するために使われます。</v>
       </c>
       <c r="F91" t="str">
-        <v>橋本病（慢性甲状腺炎）、バセドウ病などの自己免疫性甲状腺疾患</v>
+        <v>骨代謝回転の亢進（骨粗鬆症など）</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -4138,39 +4409,42 @@
         <v/>
       </c>
       <c r="I91" t="str">
-        <v/>
+        <v>骨吸収抑制薬による治療効果</v>
       </c>
       <c r="J91" t="str">
-        <v>陽性でも必ずしも甲状腺機能異常があるとは限らない。TSH・FT4など甲状腺ホルモンの数値と合わせて評価する</v>
+        <v/>
       </c>
       <c r="K91" t="str">
-        <v>甲状腺疾患</v>
+        <v>NTX・DPDと同じ「骨を壊す側」の指標。血清・尿中いずれでも測定されることがある</v>
       </c>
       <c r="L91" t="str">
-        <v>抗TPO抗体,抗甲状腺マイクロゾーム抗体,TPOAb,橋本病</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="M91" t="str">
-        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
+        <v>CTX,骨吸収マーカー</v>
+      </c>
+      <c r="N91" t="str">
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>抗サイログロブリン抗体</v>
+        <v>P1NP</v>
       </c>
       <c r="B92" t="str">
-        <v>TgAb</v>
+        <v>P1NP</v>
       </c>
       <c r="C92" t="str">
-        <v>陰性（28 IU/mL未満程度、施設差あり）</v>
+        <v>施設差が大きく一律の記載が難しい（血清）</v>
       </c>
       <c r="D92" t="str">
-        <v>甲状腺のたんぱく質（サイログロブリン）への抗体が出ていないかを見る検査</v>
+        <v>骨が新しく作られるときに出る、骨形成マーカーのひとつ</v>
       </c>
       <c r="E92" t="str">
-        <v>この検査も、抗TPO抗体と同じく、甲状腺に対する自己免疫の有無を見るものです。あわせて調べることで橋本病などの診断の参考にします。</v>
+        <v>P1NPは、CTXなどとは逆に、骨が新しく作られるときに血液中に出てくる物質です。骨を作る力を高める薬（テリパラチドなど）の効果を確認するために使われます。</v>
       </c>
       <c r="F92" t="str">
-        <v>橋本病（慢性甲状腺炎）、バセドウ病などの自己免疫性甲状腺疾患</v>
+        <v>骨代謝回転の亢進、骨形成促進薬による治療効果</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -4179,270 +4453,379 @@
         <v/>
       </c>
       <c r="I92" t="str">
-        <v/>
+        <v>骨形成の低下</v>
       </c>
       <c r="J92" t="str">
-        <v>抗TPO抗体とあわせて測定されることが多い。単独の高値だけで治療方針が決まるわけではない</v>
+        <v/>
       </c>
       <c r="K92" t="str">
-        <v>甲状腺疾患</v>
+        <v>TRACP-5b等「骨を壊す側」の指標とは逆の、「骨を作る側」の指標。骨形成促進薬（テリパラチド等）の効果判定に使われる</v>
       </c>
       <c r="L92" t="str">
-        <v>抗サイログロブリン抗体,TgAb,橋本病</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="M92" t="str">
-        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
+        <v>P1NP,骨形成マーカー</v>
+      </c>
+      <c r="N92" t="str">
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>血中薬物濃度（TDM）</v>
+        <v>抗甲状腺マイクロゾーム抗体（抗TPO抗体）</v>
       </c>
       <c r="B93" t="str">
-        <v>TDM</v>
+        <v>TPOAb</v>
       </c>
       <c r="C93" t="str">
-        <v>薬剤ごとに有効域が異なる（例：カルバマゼピン 4〜12 μg/mL、バルプロ酸 40〜100 μg/mL、フェニトイン 10〜20 μg/mL）</v>
+        <v>陰性（16 IU/mL未満程度、施設差あり）</v>
       </c>
       <c r="D93" t="str">
-        <v>治療域が狭い薬剤で、血液中の薬の濃度が効果域・中毒域のどちらにあるかを確認する検査</v>
+        <v>自分の甲状腺を攻撃する抗体が出ていないかを見る検査</v>
       </c>
       <c r="E93" t="str">
-        <v>この薬は効く量と副作用が出る量が近いため、血液中の薬の濃度を定期的に測って、ちょうどよい範囲に入っているかを確認します。数値が低いと効果が不十分になり、高いと副作用が出やすくなります。</v>
+        <v>この検査は、体の中に自分の甲状腺を誤って攻撃してしまう抗体がないかを見るものです。陽性の場合、橋本病（慢性甲状腺炎）など甲状腺の自己免疫的な炎症が背景にある可能性があります。</v>
       </c>
       <c r="F93" t="str">
-        <v>過量投与、代謝を妨げる薬剤との併用、肝機能低下による代謝低下</v>
+        <v>橋本病（慢性甲状腺炎）、バセドウ病などの自己免疫性甲状腺疾患</v>
       </c>
       <c r="G93" t="str">
-        <v>ふらつき、眠気、めまい、物が二重に見えるなどの中毒症状がないか確認する</v>
+        <v/>
       </c>
       <c r="H93" t="str">
-        <v>飲み忘れ、自己判断による減量、代謝を促進する薬剤との併用（相互作用）</v>
+        <v/>
       </c>
       <c r="I93" t="str">
-        <v>発作やてんかん症状の再発がないか確認し、飲み忘れがないか一緒に確認する</v>
+        <v/>
       </c>
       <c r="J93" t="str">
-        <v>採血のタイミング（トラフ値かどうか）で数値の解釈が変わるため採血時点を確認する。カルバマゼピンは自己誘導により長期使用で濃度が下がることがある点にも注意</v>
+        <v/>
       </c>
       <c r="K93" t="str">
-        <v>てんかん</v>
+        <v>陽性でも必ずしも甲状腺機能異常があるとは限らない。TSH・FT4など甲状腺ホルモンの数値と合わせて評価する</v>
       </c>
       <c r="L93" t="str">
-        <v>TDM,血中薬物濃度,治療域,中毒域,カルバマゼピン,フェニトイン,バルプロ酸,抗てんかん薬</v>
+        <v>甲状腺疾患</v>
       </c>
       <c r="M93" t="str">
-        <v/>
+        <v>抗TPO抗体,抗甲状腺マイクロゾーム抗体,TPOAb,橋本病</v>
+      </c>
+      <c r="N93" t="str">
+        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>アミラーゼ（AMY）</v>
+        <v>抗サイログロブリン抗体</v>
       </c>
       <c r="B94" t="str">
-        <v>AMY</v>
+        <v>TgAb</v>
       </c>
       <c r="C94" t="str">
-        <v>44〜132 U/L（施設差あり）</v>
+        <v>陰性（28 IU/mL未満程度、施設差あり）</v>
       </c>
       <c r="D94" t="str">
-        <v>膵臓や唾液腺から出る消化酵素。膵炎などで血液中に漏れ出す</v>
+        <v>甲状腺のたんぱく質（サイログロブリン）への抗体が出ていないかを見る検査</v>
       </c>
       <c r="E94" t="str">
-        <v>アミラーゼは、でんぷんを分解する消化酵素で、主に膵臓と唾液腺から作られます。膵臓に炎症が起きると血液中に漏れ出して数値が上がるため、膵炎の診断や経過観察に使われます。</v>
+        <v>この検査も、抗TPO抗体と同じく、甲状腺に対する自己免疫の有無を見るものです。あわせて調べることで橋本病などの診断の参考にします。</v>
       </c>
       <c r="F94" t="str">
-        <v>急性膵炎、慢性膵炎の急性増悪、耳下腺炎（おたふくかぜ）、腎不全</v>
+        <v>橋本病（慢性甲状腺炎）、バセドウ病などの自己免疫性甲状腺疾患</v>
       </c>
       <c r="G94" t="str">
-        <v>飲酒を控える、脂っこい食事を避けるよう伝える</v>
+        <v/>
       </c>
       <c r="H94" t="str">
-        <v>慢性膵炎の進行期（膵臓の機能低下）</v>
+        <v/>
       </c>
       <c r="I94" t="str">
         <v/>
       </c>
       <c r="J94" t="str">
-        <v>膵臓由来か唾液腺由来かを区別するには膵型アミラーゼ(P-AMY)を確認する。急性膵炎では強い腹痛・背部痛を伴うことが多く、飲酒歴の確認も重要</v>
+        <v/>
       </c>
       <c r="K94" t="str">
-        <v/>
+        <v>抗TPO抗体とあわせて測定されることが多い。単独の高値だけで治療方針が決まるわけではない</v>
       </c>
       <c r="L94" t="str">
-        <v>アミラーゼ,AMY,膵炎,急性膵炎</v>
+        <v>甲状腺疾患</v>
       </c>
       <c r="M94" t="str">
-        <v/>
+        <v>抗サイログロブリン抗体,TgAb,橋本病</v>
+      </c>
+      <c r="N94" t="str">
+        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>間接ビリルビン</v>
+        <v>血中薬物濃度（TDM）</v>
       </c>
       <c r="B95" t="str">
-        <v>I-Bil</v>
+        <v>TDM</v>
       </c>
       <c r="C95" t="str">
-        <v>0.2〜0.8 mg/dL程度（施設差あり）</v>
+        <v>薬剤ごとに有効域が異なる（例：カルバマゼピン 4〜12 μg/mL、バルプロ酸 40〜100 μg/mL、フェニトイン 10〜20 μg/mL）</v>
       </c>
       <c r="D95" t="str">
-        <v>赤血球が壊れてできるビリルビンのうち、肝臓で処理される前の形</v>
+        <v>治療域が狭い薬剤で、血液中の薬の濃度が効果域・中毒域のどちらにあるかを確認する検査</v>
       </c>
       <c r="E95" t="str">
-        <v>間接ビリルビンは、赤血球が壊れてできたビリルビンが、まだ肝臓で処理される前の状態です。この値が高い場合、赤血球が通常より多く壊れている(溶血)か、肝臓での処理能力に生まれつきの体質差(体質性黄疸)がある可能性が考えられます。</v>
+        <v>この薬は効く量と副作用が出る量が近いため、血液中の薬の濃度を定期的に測って、ちょうどよい範囲に入っているかを確認します。数値が低いと効果が不十分になり、高いと副作用が出やすくなります。</v>
       </c>
       <c r="F95" t="str">
-        <v>溶血性疾患（自己免疫性溶血性貧血、血液型不適合輸血など）、体質性黄疸（ジルベール症候群）、新生児黄疸</v>
+        <v>過量投与、代謝を妨げる薬剤との併用、肝機能低下による代謝低下</v>
       </c>
       <c r="G95" t="str">
-        <v>皮膚や白目の黄染、尿の色の変化がないか確認する</v>
+        <v>ふらつき、眠気、めまい、物が二重に見えるなどの中毒症状がないか確認する</v>
       </c>
       <c r="H95" t="str">
         <v/>
       </c>
       <c r="I95" t="str">
-        <v/>
+        <v>飲み忘れ、自己判断による減量、代謝を促進する薬剤との併用（相互作用）</v>
       </c>
       <c r="J95" t="str">
-        <v>直接ビリルビンとの比率で原因を推測する（間接優位は溶血・体質性、直接優位は胆道系）。総ビリルビン・AST/ALTと合わせて評価する</v>
+        <v>発作やてんかん症状の再発がないか確認し、飲み忘れがないか一緒に確認する</v>
       </c>
       <c r="K95" t="str">
-        <v>肝機能</v>
+        <v>採血のタイミング（トラフ値かどうか）で数値の解釈が変わるため採血時点を確認する。カルバマゼピンは自己誘導により長期使用で濃度が下がることがある点にも注意</v>
       </c>
       <c r="L95" t="str">
-        <v>間接ビリルビン,I-Bil,溶血</v>
+        <v>てんかん</v>
       </c>
       <c r="M95" t="str">
+        <v>TDM,血中薬物濃度,治療域,中毒域,カルバマゼピン,フェニトイン,バルプロ酸,抗てんかん薬</v>
+      </c>
+      <c r="N95" t="str">
         <v/>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>直接ビリルビン</v>
+        <v>アミラーゼ（AMY）</v>
       </c>
       <c r="B96" t="str">
-        <v>D-Bil</v>
+        <v>AMY</v>
       </c>
       <c r="C96" t="str">
-        <v>0.0〜0.3 mg/dL程度（施設差あり）</v>
+        <v>44〜132 U/L（施設差あり）</v>
       </c>
       <c r="D96" t="str">
-        <v>肝臓で処理された後のビリルビン。胆道の詰まりで血液中に増える</v>
+        <v>膵臓や唾液腺から出る消化酵素。膵炎などで血液中に漏れ出す</v>
       </c>
       <c r="E96" t="str">
-        <v>直接ビリルビンは、肝臓で処理された後のビリルビンです。胆石や腫瘍などで胆汁の通り道（胆道）が詰まると、行き場を失って血液中に増え、皮膚や白目が黄色くなる黄疸として現れます。</v>
+        <v>アミラーゼは、でんぷんを分解する消化酵素で、主に膵臓と唾液腺から作られます。膵臓に炎症が起きると血液中に漏れ出して数値が上がるため、膵炎の診断や経過観察に使われます。</v>
       </c>
       <c r="F96" t="str">
-        <v>肝疾患、胆石など胆道の閉塞</v>
+        <v>急性膵炎、慢性膵炎の急性増悪、耳下腺炎（おたふくかぜ）、腎不全</v>
       </c>
       <c r="G96" t="str">
-        <v>皮膚や白目の黄染、白っぽい便、濃い茶色の尿がないか確認する</v>
+        <v>飲酒を控える、脂っこい食事を避けるよう伝える</v>
       </c>
       <c r="H96" t="str">
-        <v/>
+        <v>バルプロ酸、アザチオプリン、サイアザイド系・ループ利尿薬、ステロイドなど薬剤性膵炎の原因薬</v>
       </c>
       <c r="I96" t="str">
-        <v/>
+        <v>慢性膵炎の進行期（膵臓の機能低下）</v>
       </c>
       <c r="J96" t="str">
-        <v>直接優位の上昇は胆道系（胆石、腫瘍による閉塞）を、間接優位の上昇は溶血・体質性を疑う手がかりになる。γ-GTP・ALPと合わせて胆道系疾患を評価する</v>
+        <v/>
       </c>
       <c r="K96" t="str">
-        <v>肝機能</v>
+        <v>膵臓由来か唾液腺由来かを区別するには膵型アミラーゼ(P-AMY)を確認する。急性膵炎では強い腹痛・背部痛を伴うことが多く、飲酒歴の確認も重要</v>
       </c>
       <c r="L96" t="str">
-        <v>直接ビリルビン,D-Bil,胆石,胆道閉塞</v>
+        <v/>
       </c>
       <c r="M96" t="str">
+        <v>アミラーゼ,AMY,膵炎,急性膵炎</v>
+      </c>
+      <c r="N96" t="str">
         <v/>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>亜鉛（Zn）</v>
+        <v>間接ビリルビン</v>
       </c>
       <c r="B97" t="str">
-        <v>Zn</v>
+        <v>I-Bil</v>
       </c>
       <c r="C97" t="str">
-        <v>80〜130 μg/dL程度（施設差あり）</v>
+        <v>0.2〜0.8 mg/dL程度（施設差あり）</v>
       </c>
       <c r="D97" t="str">
-        <v>味覚や皮膚、免疫に関わる微量ミネラル。高齢者や低栄養で不足しやすい</v>
+        <v>赤血球が壊れてできるビリルビンのうち、肝臓で処理される前の形</v>
       </c>
       <c r="E97" t="str">
-        <v>亜鉛は、味を感じる働きや皮膚・粘膜の健康、免疫の働きに関わる微量ミネラルです。不足すると、味がわかりにくくなったり（味覚障害）、傷が治りにくくなったりすることがあります。</v>
+        <v>間接ビリルビンは、赤血球が壊れてできたビリルビンが、まだ肝臓で処理される前の状態です。この値が高い場合、赤血球が通常より多く壊れている(溶血)か、肝臓での処理能力に生まれつきの体質差(体質性黄疸)がある可能性が考えられます。</v>
       </c>
       <c r="F97" t="str">
-        <v/>
+        <v>溶血性疾患（自己免疫性溶血性貧血、血液型不適合輸血など）、体質性黄疸（ジルベール症候群）、新生児黄疸</v>
       </c>
       <c r="G97" t="str">
-        <v/>
+        <v>皮膚や白目の黄染、尿の色の変化がないか確認する</v>
       </c>
       <c r="H97" t="str">
-        <v>低栄養、高齢による摂取不足、消化器手術後、亜鉛の吸収を妨げる薬剤（PPI、キレート形成する薬剤など）との併用</v>
+        <v/>
       </c>
       <c r="I97" t="str">
-        <v>味覚の変化（味を感じにくい、金属味がするなど）がないか確認する。牡蠣、赤身肉、レバーなど亜鉛を多く含む食品を意識するとよいことを伝える</v>
+        <v/>
       </c>
       <c r="J97" t="str">
-        <v>薬剤性の亜鉛欠乏（PPI長期使用、D-ペニシラミン、一部の降圧薬など）に注意。亜鉛欠乏による味覚障害は原因薬剤の中止・亜鉛補充で改善することがある</v>
+        <v/>
       </c>
       <c r="K97" t="str">
-        <v/>
+        <v>直接ビリルビンとの比率で原因を推測する（間接優位は溶血・体質性、直接優位は胆道系）。総ビリルビン・AST/ALTと合わせて評価する</v>
       </c>
       <c r="L97" t="str">
-        <v>亜鉛,Zn,味覚障害,亜鉛欠乏</v>
+        <v>肝機能</v>
       </c>
       <c r="M97" t="str">
-        <v>食事と栄養 p.78（亜鉛）</v>
+        <v>間接ビリルビン,I-Bil,溶血</v>
+      </c>
+      <c r="N97" t="str">
+        <v/>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
+        <v>直接ビリルビン</v>
+      </c>
+      <c r="B98" t="str">
+        <v>D-Bil</v>
+      </c>
+      <c r="C98" t="str">
+        <v>0.0〜0.3 mg/dL程度（施設差あり）</v>
+      </c>
+      <c r="D98" t="str">
+        <v>肝臓で処理された後のビリルビン。胆道の詰まりで血液中に増える</v>
+      </c>
+      <c r="E98" t="str">
+        <v>直接ビリルビンは、肝臓で処理された後のビリルビンです。胆石や腫瘍などで胆汁の通り道（胆道）が詰まると、行き場を失って血液中に増え、皮膚や白目が黄色くなる黄疸として現れます。</v>
+      </c>
+      <c r="F98" t="str">
+        <v>肝疾患、胆石など胆道の閉塞</v>
+      </c>
+      <c r="G98" t="str">
+        <v>皮膚や白目の黄染、白っぽい便、濃い茶色の尿がないか確認する</v>
+      </c>
+      <c r="H98" t="str">
+        <v>胆汁うっ滞型の薬剤性肝障害を起こしうる抗菌薬、経口避妊薬</v>
+      </c>
+      <c r="I98" t="str">
+        <v/>
+      </c>
+      <c r="J98" t="str">
+        <v/>
+      </c>
+      <c r="K98" t="str">
+        <v>直接優位の上昇は胆道系（胆石、腫瘍による閉塞）を、間接優位の上昇は溶血・体質性を疑う手がかりになる。γ-GTP・ALPと合わせて胆道系疾患を評価する</v>
+      </c>
+      <c r="L98" t="str">
+        <v>肝機能</v>
+      </c>
+      <c r="M98" t="str">
+        <v>直接ビリルビン,D-Bil,胆石,胆道閉塞</v>
+      </c>
+      <c r="N98" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>亜鉛（Zn）</v>
+      </c>
+      <c r="B99" t="str">
+        <v>Zn</v>
+      </c>
+      <c r="C99" t="str">
+        <v>80〜130 μg/dL程度（施設差あり）</v>
+      </c>
+      <c r="D99" t="str">
+        <v>味覚や皮膚、免疫に関わる微量ミネラル。高齢者や低栄養で不足しやすい</v>
+      </c>
+      <c r="E99" t="str">
+        <v>亜鉛は、味を感じる働きや皮膚・粘膜の健康、免疫の働きに関わる微量ミネラルです。不足すると、味がわかりにくくなったり（味覚障害）、傷が治りにくくなったりすることがあります。</v>
+      </c>
+      <c r="F99" t="str">
+        <v/>
+      </c>
+      <c r="G99" t="str">
+        <v/>
+      </c>
+      <c r="H99" t="str">
+        <v/>
+      </c>
+      <c r="I99" t="str">
+        <v>低栄養、高齢による摂取不足、消化器手術後、亜鉛の吸収を妨げる薬剤（PPI、キレート形成する薬剤など）との併用</v>
+      </c>
+      <c r="J99" t="str">
+        <v>味覚の変化（味を感じにくい、金属味がするなど）がないか確認する。牡蠣、赤身肉、レバーなど亜鉛を多く含む食品を意識するとよいことを伝える</v>
+      </c>
+      <c r="K99" t="str">
+        <v>薬剤性の亜鉛欠乏（PPI長期使用、D-ペニシラミン、一部の降圧薬など）に注意。亜鉛欠乏による味覚障害は原因薬剤の中止・亜鉛補充で改善することがある</v>
+      </c>
+      <c r="L99" t="str">
+        <v/>
+      </c>
+      <c r="M99" t="str">
+        <v>亜鉛,Zn,味覚障害,亜鉛欠乏</v>
+      </c>
+      <c r="N99" t="str">
+        <v>食事と栄養 p.78（亜鉛）</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
         <v>マグネシウム（Mg）</v>
       </c>
-      <c r="B98" t="str">
+      <c r="B100" t="str">
         <v>Mg</v>
       </c>
-      <c r="C98" t="str">
+      <c r="C100" t="str">
         <v>1.8〜2.6 mg/dL程度（施設差あり）</v>
       </c>
-      <c r="D98" t="str">
+      <c r="D100" t="str">
         <v>骨や筋肉、神経の働きに関わるミネラル。低栄養や利尿薬で不足しやすい</v>
       </c>
-      <c r="E98" t="str">
+      <c r="E100" t="str">
         <v>マグネシウムは、骨や筋肉、神経の働きを支えるミネラルです。不足すると、こむら返りや不整脈、だるさなどの症状が出ることがあります。</v>
       </c>
-      <c r="F98" t="str">
+      <c r="F100" t="str">
         <v>腎不全、マグネシウム製剤（酸化マグネシウムなど）の過量投与</v>
       </c>
-      <c r="G98" t="str">
+      <c r="G100" t="str">
         <v>腎機能低下がある患者で酸化マグネシウムなどの緩下剤を使用中は、傾眠・血圧低下などの高マグネシウム血症の症状がないか確認する</v>
       </c>
-      <c r="H98" t="str">
+      <c r="H100" t="str">
+        <v>マグネシウム含有制酸薬・下剤の過量(特に腎機能低下患者)</v>
+      </c>
+      <c r="I100" t="str">
         <v>低栄養、利尿薬の使用、慢性的な下痢、アルコール多飲、PPI長期使用</v>
       </c>
-      <c r="I98" t="str">
+      <c r="J100" t="str">
         <v>こむら返りや動悸などの症状がないか確認する</v>
       </c>
-      <c r="J98" t="str">
+      <c r="K100" t="str">
         <v>腎機能低下患者への酸化マグネシウム投与は高マグネシウム血症のリスクがあるため定期的なモニタリングが必要。PPI長期使用も低マグネシウム血症のリスク因子として知られる</v>
       </c>
-      <c r="K98" t="str">
+      <c r="L100" t="str">
         <v>腎機能</v>
       </c>
-      <c r="L98" t="str">
+      <c r="M100" t="str">
         <v>マグネシウム,Mg,酸化マグネシウム,こむら返り</v>
       </c>
-      <c r="M98" t="str">
+      <c r="N100" t="str">
         <v>食事と栄養 p.84（マグネシウム）</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M98"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N100"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/検査値リファレンス初期データ.xlsx
+++ b/検査値リファレンス初期データ.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N100"/>
+  <dimension ref="A1:O100"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -410,10 +410,11 @@
     <col min="8" max="8" width="18.83203125" customWidth="1"/>
     <col min="9" max="9" width="18.83203125" customWidth="1"/>
     <col min="10" max="10" width="32.83203125" customWidth="1"/>
-    <col min="11" max="11" width="35.83203125" customWidth="1"/>
-    <col min="12" max="12" width="18.83203125" customWidth="1"/>
+    <col min="11" max="11" width="18.83203125" customWidth="1"/>
+    <col min="12" max="12" width="35.83203125" customWidth="1"/>
     <col min="13" max="13" width="18.83203125" customWidth="1"/>
-    <col min="14" max="14" width="14.83203125" customWidth="1"/>
+    <col min="14" max="14" width="18.83203125" customWidth="1"/>
+    <col min="15" max="15" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -448,15 +449,18 @@
         <v>低値の時のアドバイス</v>
       </c>
       <c r="K1" t="str">
+        <v>低値の時に注意する薬</v>
+      </c>
+      <c r="L1" t="str">
         <v>薬剤師補足</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>疾患タグ</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
         <v>検索キーワード</v>
       </c>
-      <c r="N1" t="str">
+      <c r="O1" t="str">
         <v>参考ページ</v>
       </c>
     </row>
@@ -493,15 +497,18 @@
         <v>空腹時間が長くならないよう食事を規則正しくとる。冷や汗・動悸・強い空腹感などの低血糖症状が出たらすぐに糖分を摂る</v>
       </c>
       <c r="K2" t="str">
+        <v>インスリン、SU薬(グリメピリド等)、速効型インスリン分泌促進薬(グリニド系)。β遮断薬は低血糖症状をマスクすることがあるため注意</v>
+      </c>
+      <c r="L2" t="str">
         <v>採血のタイミング（空腹時か食後か）を必ず確認する。SU薬・インスリン使用者では低血糖症状の有無も併せて聞く</v>
       </c>
-      <c r="L2" t="str">
+      <c r="M2" t="str">
         <v>糖尿病,精神疾患（非定型抗精神病薬）</v>
       </c>
-      <c r="M2" t="str">
+      <c r="N2" t="str">
         <v>血糖値,血糖,BS,Glu,グルコース,空腹時血糖,随時血糖,食後血糖</v>
       </c>
-      <c r="N2" t="str">
+      <c r="O2" t="str">
         <v>食事と栄養 p.18（炭水化物）／p.106-131（第2部 糖尿病）</v>
       </c>
     </row>
@@ -537,15 +544,18 @@
         <v>低血糖を防ぐため、食事の間隔をあけすぎないようにする。ブドウ糖など対処品の携帯を勧める</v>
       </c>
       <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
         <v>貧血・鉄剤補充・妊娠・腎不全などがあると、実際の血糖値とズレて出ることがある。直近の血糖自己測定値と合わせて確認する</v>
       </c>
-      <c r="L3" t="str">
+      <c r="M3" t="str">
         <v>糖尿病,精神疾患（非定型抗精神病薬）</v>
       </c>
-      <c r="M3" t="str">
+      <c r="N3" t="str">
         <v>HbA1c,ヘモグロビンエーワンシー,グリコヘモグロビン,血糖コントロール,NGSP</v>
       </c>
-      <c r="N3" t="str">
+      <c r="O3" t="str">
         <v>食事と栄養 p.18（炭水化物）／p.106-131（第2部 糖尿病）</v>
       </c>
     </row>
@@ -581,15 +591,18 @@
         <v/>
       </c>
       <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
         <v>クレアチニンと同時に見る。BUN/Cr比が高ければ脱水や消化管出血を、比が正常で両方高ければ腎性を疑う目安になる</v>
       </c>
-      <c r="L4" t="str">
+      <c r="M4" t="str">
         <v>腎機能,糖尿病,骨粗鬆症,抗凝固療法（心房細動・血栓症）</v>
       </c>
-      <c r="M4" t="str">
+      <c r="N4" t="str">
         <v>BUN,尿素窒素,UN,腎機能</v>
       </c>
-      <c r="N4" t="str">
+      <c r="O4" t="str">
         <v>食事と栄養 p.199-215（第2部 腎機能低下）</v>
       </c>
     </row>
@@ -625,18 +638,21 @@
       <c r="J5" t="str">
         <v/>
       </c>
-      <c r="K5" t="str" xml:space="preserve">
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str" xml:space="preserve">
         <v xml:space="preserve">筋肉量に影響されるため、るいそうの強い高齢者では腎機能を過大評価しやすい。eGFR低下時は腎排泄型薬剤の用量調整を確認する。
 CKD重症度分類（GFR区分）の目安：G1 正常または高値(90以上)／G2 正常または軽度低下(60〜89)／G3a 軽度〜中等度低下(45〜59)／G3b 中等度〜高度低下(30〜44)／G4 高度低下(15〜29)／G5 末期腎不全(15未満)。
 eGFRには体表面積1.73㎡に標準化した「標準化eGFR」（CKD病期の判定などに使用）と、実際の体表面積で補正した「個別化eGFR」（標準化eGFR×体表面積÷1.73、薬剤投与量の決定に使用）があり、体格が標準から大きく外れる患者では両者がずれるため、用量調整の場面では個別化eGFRやCCrを優先する</v>
       </c>
-      <c r="L5" t="str">
+      <c r="M5" t="str">
         <v>腎機能,糖尿病,骨粗鬆症,抗凝固療法（心房細動・血栓症）</v>
       </c>
-      <c r="M5" t="str">
+      <c r="N5" t="str">
         <v>クレアチニン,Cr,SCr,血清クレアチニン,eGFR,腎機能,GFR,推算糸球体濾過量,CKD重症度分類</v>
       </c>
-      <c r="N5" t="str">
+      <c r="O5" t="str">
         <v>食事と栄養 p.199-215（第2部 腎機能低下）／p.243（フレイルQ111 クレアチニン値が低い場合）</v>
       </c>
     </row>
@@ -671,17 +687,20 @@
       <c r="J6" t="str">
         <v>脱水を避けてこまめに水分を摂る（水分制限がある場合を除く）。腎排泄型の薬剤は減量や投与間隔の延長が必要になることがあるため、お薬手帳を最新の状態に保つ</v>
       </c>
-      <c r="K6" t="str" xml:space="preserve">
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str" xml:space="preserve">
         <v xml:space="preserve">Cockcroft-Gault式［(140−年齢)×体重(kg)÷(72×血清Cr)、女性は×0.85］で算出した推算CCrが、多くの薬剤の添付文書における腎機能別用量調整の基準に使われる。eGFRは体表面積1.73㎡で標準化した値のため、実際の体格が標準から離れる患者（高齢・るいそう・肥満など）では、添付文書のCCr基準にそのまま当てはめると過大・過小評価になりうる点に注意。
 血清Cr(mg/dL)からのおおまかな対応の目安：0.7〜1.4→CCr100±20（正常・健常）／1.4〜2.4→61〜99（日常生活に支障なし）／2.5〜4.9→24〜60（日常生活に多少の支障）／5.0〜7.9→12〜23（日常生活に支障あり）／8.0〜12.0→7〜12（日常生活の規制）／12.0超→6未満（昏睡・見当識障害）</v>
       </c>
-      <c r="L6" t="str">
+      <c r="M6" t="str">
         <v>腎機能,糖尿病,骨粗鬆症,抗凝固療法（心房細動・血栓症）</v>
       </c>
-      <c r="M6" t="str">
+      <c r="N6" t="str">
         <v>CCr,クレアチニンクリアランス,クレアチニン・クリアランス,creatinine clearance,コッククロフトゴート,Cockcroft-Gault,腎機能</v>
       </c>
-      <c r="N6" t="str">
+      <c r="O6" t="str">
         <v>食事と栄養 p.199-215（第2部 腎機能低下）</v>
       </c>
     </row>
@@ -717,15 +736,18 @@
         <v/>
       </c>
       <c r="K7" t="str">
+        <v>尿酸降下薬(フェブキソスタット、アロプリノール等)の効きすぎ</v>
+      </c>
+      <c r="L7" t="str">
         <v>利尿薬（サイアザイド系など）は尿酸を上げやすい。急激に尿酸を下げる治療の開始直後は痛風発作が誘発されることがある</v>
       </c>
-      <c r="L7" t="str">
+      <c r="M7" t="str">
         <v>高尿酸血症,糖尿病</v>
       </c>
-      <c r="M7" t="str">
+      <c r="N7" t="str">
         <v>尿酸,UA,痛風,高尿酸血症</v>
       </c>
-      <c r="N7" t="str">
+      <c r="O7" t="str">
         <v>食事と栄養 p.180-189（第2部 痛風・高尿酸血症）</v>
       </c>
     </row>
@@ -761,15 +783,18 @@
         <v>利尿薬使用中は嘔吐・下痢が続いていないか確認する。意識がぼんやりする、頭痛などの症状がないか確認する</v>
       </c>
       <c r="K8" t="str">
+        <v>サイアザイド系利尿薬、SSRI、カルバマゼピン、デスモプレシン、シクロホスファミド</v>
+      </c>
+      <c r="L8" t="str">
         <v>低ナトリウム血症は高齢者に多く、意識障害や転倒の原因になりうる。利尿薬（特にサイアザイド系）、SSRI、カルバマゼピンなどSIADHを起こしうる薬剤の使用歴を確認する</v>
       </c>
-      <c r="L8" t="str">
+      <c r="M8" t="str">
         <v>電解質</v>
       </c>
-      <c r="M8" t="str">
+      <c r="N8" t="str">
         <v>ナトリウム,Na,電解質,脱水,SIADH,低ナトリウム血症</v>
       </c>
-      <c r="N8" t="str">
+      <c r="O8" t="str">
         <v>食事と栄養 p.81（ナトリウム）</v>
       </c>
     </row>
@@ -805,15 +830,18 @@
         <v>利尿薬使用中は嘔吐・下痢が続いていないか確認する</v>
       </c>
       <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
         <v>ナトリウムと同じ方向に動くことが多いが、酸塩基平衡の異常（アシドーシス・アルカローシス）を反映して単独で動くこともある。利尿薬（特にループ利尿薬）使用中は低クロール性アルカローシスに注意</v>
       </c>
-      <c r="L9" t="str">
+      <c r="M9" t="str">
         <v>電解質,腎機能</v>
       </c>
-      <c r="M9" t="str">
+      <c r="N9" t="str">
         <v>クロール,Cl,塩素,電解質,アシドーシス,アルカローシス</v>
       </c>
-      <c r="N9" t="str">
+      <c r="O9" t="str">
         <v/>
       </c>
     </row>
@@ -849,15 +877,18 @@
         <v>利尿薬使用中は下痢・嘔吐が続いていないか確認し、必要に応じてバナナ・芋類などカリウムを含む食品を意識する</v>
       </c>
       <c r="K10" t="str">
+        <v>ループ利尿薬、サイアザイド系利尿薬、グリチルリチン製剤(甘草含有製剤)、ステロイド、インスリン、β2刺激薬</v>
+      </c>
+      <c r="L10" t="str">
         <v>高カリウム血症は不整脈・心停止のリスクがあるため脱力感・動悸の有無を確認。RAS阻害薬とカリウム保持性利尿薬の併用時は特に注意</v>
       </c>
-      <c r="L10" t="str">
+      <c r="M10" t="str">
         <v>腎機能,電解質</v>
       </c>
-      <c r="M10" t="str">
+      <c r="N10" t="str">
         <v>カリウム,K,高カリウム血症,低カリウム血症</v>
       </c>
-      <c r="N10" t="str">
+      <c r="O10" t="str">
         <v>食事と栄養 p.72（カリウム）／p.199-215（第2部 腎機能低下 Q80-82 カリウム制限）</v>
       </c>
     </row>
@@ -893,15 +924,18 @@
         <v>手足のしびれやこむら返りなど低カルシウム血症の症状がないか確認する</v>
       </c>
       <c r="K11" t="str">
+        <v>ビスホスホネート製剤、デノスマブ、ループ利尿薬、抗てんかん薬の長期使用、シナカルセト</v>
+      </c>
+      <c r="L11" t="str">
         <v>アルブミンが低いと見かけ上低く出るため、補正カルシウム値（Ca+(4-Alb)）で評価する。骨粗鬆症治療薬（活性型ビタミンD3製剤、デノスマブなど）使用中は高カルシウム血症の副作用に注意</v>
       </c>
-      <c r="L11" t="str">
+      <c r="M11" t="str">
         <v>電解質,骨粗鬆症</v>
       </c>
-      <c r="M11" t="str">
+      <c r="N11" t="str">
         <v>カルシウム,Ca,電解質</v>
       </c>
-      <c r="N11" t="str">
+      <c r="O11" t="str">
         <v>食事と栄養 p.75（カルシウム）／p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
@@ -937,15 +971,18 @@
         <v/>
       </c>
       <c r="K12" t="str">
+        <v>(実測カルシウムに準ずる)ビスホスホネート製剤、デノスマブ、ループ利尿薬</v>
+      </c>
+      <c r="L12" t="str">
         <v>補正カルシウム(mg/dL) = 実測カルシウム + (4 − アルブミン値)の式で計算する。アルブミンが4.0 g/dL未満の低栄養患者やネフローゼ症候群の患者では、実測カルシウムだけで判断すると誤りやすいため、この補正値で評価する</v>
       </c>
-      <c r="L12" t="str">
+      <c r="M12" t="str">
         <v>電解質,骨粗鬆症</v>
       </c>
-      <c r="M12" t="str">
+      <c r="N12" t="str">
         <v>補正カルシウム,Corrected Calcium,アルブミン補正,低アルブミン血症</v>
       </c>
-      <c r="N12" t="str">
+      <c r="O12" t="str">
         <v/>
       </c>
     </row>
@@ -981,15 +1018,18 @@
         <v/>
       </c>
       <c r="K13" t="str">
+        <v>リン吸着薬(セベラマー等)、アルミニウム含有制酸薬、利尿薬</v>
+      </c>
+      <c r="L13" t="str">
         <v>カルシウムと逆方向に動くことが多い（副甲状腺機能亢進症ではCa上昇・P低下）。骨粗鬆症の二次性原因の除外に用いられる</v>
       </c>
-      <c r="L13" t="str">
+      <c r="M13" t="str">
         <v>骨粗鬆症,電解質</v>
       </c>
-      <c r="M13" t="str">
+      <c r="N13" t="str">
         <v>リン,P,IP,無機リン</v>
       </c>
-      <c r="N13" t="str">
+      <c r="O13" t="str">
         <v>食事と栄養 p.165-178（第2部 骨粗鬆症）／p.199-215（第2部 腎機能低下 Q83 リン制限）</v>
       </c>
     </row>
@@ -1025,15 +1065,18 @@
         <v/>
       </c>
       <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
         <v>ALTとの比率（AST/ALT比）で肝細胞障害か他臓器由来かを推測できる。AST優位はアルコール性・心筋・筋由来を疑う材料になる</v>
       </c>
-      <c r="L14" t="str">
+      <c r="M14" t="str">
         <v>肝機能,糖尿病,てんかん,精神疾患（非定型抗精神病薬）</v>
       </c>
-      <c r="M14" t="str">
+      <c r="N14" t="str">
         <v>AST,GOT,肝機能,肝障害</v>
       </c>
-      <c r="N14" t="str">
+      <c r="O14" t="str">
         <v/>
       </c>
     </row>
@@ -1069,15 +1112,18 @@
         <v/>
       </c>
       <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
         <v>新規薬剤開始後の肝障害の指標として重要。健診でALTのみ軽度上昇していることが多く、その場合は脂肪肝（NAFLD）の頻度が高い</v>
       </c>
-      <c r="L15" t="str">
+      <c r="M15" t="str">
         <v>肝機能,糖尿病,てんかん,精神疾患（非定型抗精神病薬）</v>
       </c>
-      <c r="M15" t="str">
+      <c r="N15" t="str">
         <v>ALT,GPT,肝機能,肝障害,脂肪肝</v>
       </c>
-      <c r="N15" t="str">
+      <c r="O15" t="str">
         <v/>
       </c>
     </row>
@@ -1113,15 +1159,18 @@
         <v/>
       </c>
       <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
         <v>臓器特異性が低いため単独では原因を特定しにくい。AST/ALT(肝)、CK(筋)、ビリルビン・ハプトグロビン(溶血)など他の検査値と組み合わせて原因臓器を推定する</v>
       </c>
-      <c r="L16" t="str">
-        <v/>
-      </c>
       <c r="M16" t="str">
+        <v/>
+      </c>
+      <c r="N16" t="str">
         <v>LDH,乳酸脱水素酵素,溶血,心筋梗塞,悪性腫瘍</v>
       </c>
-      <c r="N16" t="str">
+      <c r="O16" t="str">
         <v/>
       </c>
     </row>
@@ -1157,15 +1206,18 @@
         <v/>
       </c>
       <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
         <v>アルブミンと同様に肝臓の「合成能」を見る指標。低栄養か肝硬変かは、アルブミンや血小板数（肝硬変で低下しやすい）と合わせて判断する</v>
       </c>
-      <c r="L17" t="str">
+      <c r="M17" t="str">
         <v>肝機能</v>
       </c>
-      <c r="M17" t="str">
+      <c r="N17" t="str">
         <v>コリンエステラーゼ,ChE,肝合成能,脂肪肝,肝硬変</v>
       </c>
-      <c r="N17" t="str">
+      <c r="O17" t="str">
         <v/>
       </c>
     </row>
@@ -1201,15 +1253,18 @@
         <v/>
       </c>
       <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
         <v>骨由来か肝由来かの区別には骨型ALPアイソザイムやγ-GTPとの組み合わせで判断する</v>
       </c>
-      <c r="L18" t="str">
+      <c r="M18" t="str">
         <v>骨粗鬆症,肝機能</v>
       </c>
-      <c r="M18" t="str">
+      <c r="N18" t="str">
         <v>ALP,アルカリフォスファターゼ,骨代謝,肝機能</v>
       </c>
-      <c r="N18" t="str">
+      <c r="O18" t="str">
         <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
@@ -1246,15 +1301,18 @@
         <v/>
       </c>
       <c r="K19" t="str">
+        <v/>
+      </c>
+      <c r="L19" t="str">
         <v>飲酒歴の確認に使いやすい数値。断酒・節酒で比較的早く改善するため、生活指導の効果を示す指標としても使える</v>
       </c>
-      <c r="L19" t="str">
+      <c r="M19" t="str">
         <v>肝機能</v>
       </c>
-      <c r="M19" t="str">
+      <c r="N19" t="str">
         <v>ガンマGTP,γ-GTP,GGT,肝機能,飲酒,アルコール</v>
       </c>
-      <c r="N19" t="str">
+      <c r="O19" t="str">
         <v/>
       </c>
     </row>
@@ -1290,15 +1348,18 @@
         <v/>
       </c>
       <c r="K20" t="str">
+        <v/>
+      </c>
+      <c r="L20" t="str">
         <v>直接ビリルビン・間接ビリルビンの内訳で原因を推測できる（直接優位は胆道系、間接優位は溶血・体質性）。AST/ALT/γ-GTPと合わせて評価する</v>
       </c>
-      <c r="L20" t="str">
+      <c r="M20" t="str">
         <v>肝機能</v>
       </c>
-      <c r="M20" t="str">
+      <c r="N20" t="str">
         <v>総ビリルビン,T-Bil,黄疸,ビリルビン,ジルベール症候群</v>
       </c>
-      <c r="N20" t="str">
+      <c r="O20" t="str">
         <v/>
       </c>
     </row>
@@ -1334,15 +1395,18 @@
         <v>食事摂取量（特にたんぱく質）を確認する</v>
       </c>
       <c r="K21" t="str">
+        <v/>
+      </c>
+      <c r="L21" t="str">
         <v>アルブミンとグロブリンの内訳（A/G比）も合わせて確認すると原因の絞り込みに役立つ。低栄養か肝機能低下かはアルブミンの値と合わせて判断する</v>
       </c>
-      <c r="L21" t="str">
+      <c r="M21" t="str">
         <v>肝機能</v>
       </c>
-      <c r="M21" t="str">
+      <c r="N21" t="str">
         <v>総タンパク,TP,総蛋白,栄養状態,A/G比</v>
       </c>
-      <c r="N21" t="str">
+      <c r="O21" t="str">
         <v>食事と栄養 p.23（たんぱく質）</v>
       </c>
     </row>
@@ -1378,15 +1442,18 @@
         <v>主食に偏らず、肉・魚・卵・大豆製品などたんぱく質をしっかり摂るよう伝える。食欲が落ちている場合は少量頻回の食事も提案する</v>
       </c>
       <c r="K22" t="str">
+        <v>蛋白結合率の高い薬剤(ワルファリン、フェニトイン、NSAIDs等)は遊離型濃度が上昇し、効果や副作用が増強しやすいため用量に注意</v>
+      </c>
+      <c r="L22" t="str">
         <v>3前半は注意ライン。食事摂取量を必ず確認</v>
       </c>
-      <c r="L22" t="str">
+      <c r="M22" t="str">
         <v>肝機能,栄養,腎機能</v>
       </c>
-      <c r="M22" t="str">
+      <c r="N22" t="str">
         <v>アルブミン,Alb,むくみ,浮腫,栄養状態</v>
       </c>
-      <c r="N22" t="str">
+      <c r="O22" t="str">
         <v>食事と栄養 p.23（たんぱく質）／p.242（フレイルQ110 アルブミン値を上げる食事指導）</v>
       </c>
     </row>
@@ -1422,15 +1489,18 @@
         <v/>
       </c>
       <c r="K23" t="str">
+        <v/>
+      </c>
+      <c r="L23" t="str">
         <v>バルプロ酸(デパケン等)は肝疾患の既往がなくても高アンモニア血症を起こすことがあり、意識障害・傾眠が出現した場合は薬剤性を疑ってアンモニア値を確認する。採血後は室温放置で見かけ上上昇するため測定条件にも注意。ラクツロース・リファキシミンは腸管内でのアンモニア産生・吸収を抑える目的で使用される</v>
       </c>
-      <c r="L23" t="str">
+      <c r="M23" t="str">
         <v>肝機能</v>
       </c>
-      <c r="M23" t="str">
+      <c r="N23" t="str">
         <v>アンモニア,NH3,肝性脳症,バルプロ酸,門脈シャント</v>
       </c>
-      <c r="N23" t="str">
+      <c r="O23" t="str">
         <v/>
       </c>
     </row>
@@ -1466,15 +1536,18 @@
         <v/>
       </c>
       <c r="K24" t="str">
+        <v/>
+      </c>
+      <c r="L24" t="str">
         <v>採血が食後か空腹時かで数値が大きく変わるため必ず確認する。500 mg/dL以上では急性膵炎のリスクが高まるため注意。フィブラート系・EPA製剤などの効果判定に使う</v>
       </c>
-      <c r="L24" t="str">
+      <c r="M24" t="str">
         <v>脂質異常症</v>
       </c>
-      <c r="M24" t="str">
+      <c r="N24" t="str">
         <v>中性脂肪,トリグリセリド,TG,脂質異常症</v>
       </c>
-      <c r="N24" t="str">
+      <c r="O24" t="str">
         <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
       </c>
     </row>
@@ -1510,15 +1583,18 @@
         <v/>
       </c>
       <c r="K25" t="str">
+        <v/>
+      </c>
+      <c r="L25" t="str">
         <v>現在はLDLコレステロールでの評価が主流。総コレステロールだけでは悪玉・善玉の内訳が分からないため、LDL・HDL・中性脂肪と合わせて評価する</v>
       </c>
-      <c r="L25" t="str">
+      <c r="M25" t="str">
         <v>脂質異常症</v>
       </c>
-      <c r="M25" t="str">
+      <c r="N25" t="str">
         <v>総コレステロール,TC,コレステロール,脂質異常症</v>
       </c>
-      <c r="N25" t="str">
+      <c r="O25" t="str">
         <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
       </c>
     </row>
@@ -1555,15 +1631,18 @@
         <v/>
       </c>
       <c r="K26" t="str">
+        <v/>
+      </c>
+      <c r="L26" t="str">
         <v>スタチン等の効果判定に使う中心的な数値。目標値は既往疾患（冠動脈疾患・糖尿病等）によって異なるため一律に判断しない</v>
       </c>
-      <c r="L26" t="str">
+      <c r="M26" t="str">
         <v>脂質異常症,精神疾患（非定型抗精神病薬）</v>
       </c>
-      <c r="M26" t="str">
+      <c r="N26" t="str">
         <v>LDL,LDLコレステロール,悪玉コレステロール,脂質異常症</v>
       </c>
-      <c r="N26" t="str">
+      <c r="O26" t="str">
         <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
       </c>
     </row>
@@ -1599,15 +1678,18 @@
         <v/>
       </c>
       <c r="K27" t="str">
+        <v/>
+      </c>
+      <c r="L27" t="str">
         <v>中性脂肪（TG）が400 mg/dL以上などLDL-Cの計算式（Friedewald式）が不正確になる場合に、LDL-Cの代わりに用いられる。目標値はLDL-Cの目標値＋30 mg/dLが目安</v>
       </c>
-      <c r="L27" t="str">
+      <c r="M27" t="str">
         <v>脂質異常症</v>
       </c>
-      <c r="M27" t="str">
+      <c r="N27" t="str">
         <v>nonHDL,non-HDLコレステロール,動脈硬化,中性脂肪,LDL計算式</v>
       </c>
-      <c r="N27" t="str">
+      <c r="O27" t="str">
         <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
       </c>
     </row>
@@ -1643,15 +1725,18 @@
         <v>適度な運動習慣、禁煙を勧める</v>
       </c>
       <c r="K28" t="str">
+        <v/>
+      </c>
+      <c r="L28" t="str">
         <v>喫煙、運動不足、肥満で低下しやすい。禁煙・運動習慣の改善で上昇が期待できる。低HDLは動脈硬化のリスク因子として単独でも重視される</v>
       </c>
-      <c r="L28" t="str">
+      <c r="M28" t="str">
         <v>脂質異常症</v>
       </c>
-      <c r="M28" t="str">
+      <c r="N28" t="str">
         <v>HDL,HDLコレステロール,善玉コレステロール,脂質異常症</v>
       </c>
-      <c r="N28" t="str">
+      <c r="O28" t="str">
         <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
       </c>
     </row>
@@ -1687,15 +1772,18 @@
         <v/>
       </c>
       <c r="K29" t="str">
+        <v/>
+      </c>
+      <c r="L29" t="str">
         <v>スタチン系薬剤の重大な副作用である横紋筋融解症の指標。筋肉痛・脱力感・褐色尿の有無を必ず確認し、著明高値では服薬継続の可否を医師に相談する</v>
       </c>
-      <c r="L29" t="str">
-        <v/>
-      </c>
       <c r="M29" t="str">
+        <v/>
+      </c>
+      <c r="N29" t="str">
         <v>CK,CPK,クレアチンキナーゼ,横紋筋融解症</v>
       </c>
-      <c r="N29" t="str">
+      <c r="O29" t="str">
         <v/>
       </c>
     </row>
@@ -1731,103 +1819,112 @@
         <v/>
       </c>
       <c r="K30" t="str">
+        <v/>
+      </c>
+      <c r="L30" t="str">
         <v>比が高い（目安20以上）場合は脱水や消化管出血など腎前性の要因を、比が正常範囲で両方高値なら腎性の障害を疑う。BUN単独やクレアチニン単独よりも病態の絞り込みに役立つ</v>
       </c>
-      <c r="L30" t="str">
+      <c r="M30" t="str">
         <v>腎機能</v>
       </c>
-      <c r="M30" t="str">
+      <c r="N30" t="str">
         <v>BUN/CRE,BUN/Cr,尿素窒素,クレアチニン,脱水,腎前性</v>
       </c>
-      <c r="N30" t="str">
+      <c r="O30" t="str">
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>CK/AST比</v>
+        <v>LDH/AST比</v>
       </c>
       <c r="B31" t="str">
-        <v>CK/AST</v>
+        <v>LDH/AST</v>
       </c>
       <c r="C31" t="str">
         <v>目安として使われる比率（施設差・カットオフ値の設定により異なる）</v>
       </c>
       <c r="D31" t="str">
-        <v>ASTが上昇したときに、原因が筋肉（CKも上昇）か、それ以外（肝臓など）かを見分ける目安になる比</v>
+        <v>LDHとASTの両方が上昇したときに、原因が肝臓か、それ以外（溶血・心筋・骨格筋）かを見分ける目安になる比</v>
       </c>
       <c r="E31" t="str">
-        <v>これは、筋肉の数値（CK）と肝臓の数値（AST）を比べることで、ASTの上昇が筋肉由来なのか、肝臓由来なのかを見分ける手がかりになる比率です。</v>
+        <v>これは、肝臓の数値（AST）と、全身に広く分布する酵素（LDH）の比率を見るもので、両方の数値が上がっているときに、原因が肝臓なのか、それとも血液や筋肉など他の場所なのかを見分ける手がかりになります。</v>
       </c>
       <c r="F31" t="str">
-        <v>横紋筋融解症、心筋梗塞、激しい運動など筋肉由来のAST上昇（CKも同時に高値）</v>
+        <v>溶血性疾患、心筋梗塞、骨格筋の障害（比が高いほど肝臓以外が原因の可能性）</v>
       </c>
       <c r="G31" t="str">
-        <v>筋肉痛や脱力感、褐色尿などの症状がないか確認する</v>
+        <v/>
       </c>
       <c r="H31" t="str">
         <v/>
       </c>
       <c r="I31" t="str">
-        <v/>
+        <v>急性肝炎などの肝細胞障害（比が低い、つまりASTに対してLDHが相対的に低い場合は肝性が示唆される）</v>
       </c>
       <c r="J31" t="str">
         <v/>
       </c>
       <c r="K31" t="str">
-        <v>ASTのみ上昇しCKが正常であれば肝臓由来を、両方上昇していれば筋肉由来を疑う手がかりになる。スタチン系薬剤による横紋筋融解症が疑われる場面での鑑別に有用</v>
+        <v/>
       </c>
       <c r="L31" t="str">
-        <v/>
+        <v>AST・LDHが同時に上昇した際の鑑別に使う目安の一つ。単独の検査値ではなく計算上の比率であり、確定診断には他の検査（ビリルビン、CK、心筋マーカーなど）と合わせた評価が必要</v>
       </c>
       <c r="M31" t="str">
-        <v>CK/AST,CK,AST,横紋筋融解症,スタチン</v>
+        <v/>
       </c>
       <c r="N31" t="str">
+        <v>LDH/AST,LDH,AST,溶血,心筋梗塞,肝炎</v>
+      </c>
+      <c r="O31" t="str">
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>LDH/AST比</v>
+        <v>CK/AST比</v>
       </c>
       <c r="B32" t="str">
-        <v>LDH/AST</v>
+        <v>CK/AST</v>
       </c>
       <c r="C32" t="str">
         <v>目安として使われる比率（施設差・カットオフ値の設定により異なる）</v>
       </c>
       <c r="D32" t="str">
-        <v>LDHとASTの両方が上昇したときに、原因が肝臓か、それ以外（溶血・心筋・骨格筋）かを見分ける目安になる比</v>
+        <v>ASTが上昇したときに、原因が筋肉（CKも上昇）か、それ以外（肝臓など）かを見分ける目安になる比</v>
       </c>
       <c r="E32" t="str">
-        <v>これは、肝臓の数値（AST）と、全身に広く分布する酵素（LDH）の比率を見るもので、両方の数値が上がっているときに、原因が肝臓なのか、それとも血液や筋肉など他の場所なのかを見分ける手がかりになります。</v>
+        <v>これは、筋肉の数値（CK）と肝臓の数値（AST）を比べることで、ASTの上昇が筋肉由来なのか、肝臓由来なのかを見分ける手がかりになる比率です。</v>
       </c>
       <c r="F32" t="str">
-        <v>溶血性疾患、心筋梗塞、骨格筋の障害（比が高いほど肝臓以外が原因の可能性）</v>
+        <v>横紋筋融解症、心筋梗塞、激しい運動など筋肉由来のAST上昇（CKも同時に高値）</v>
       </c>
       <c r="G32" t="str">
-        <v/>
+        <v>筋肉痛や脱力感、褐色尿などの症状がないか確認する</v>
       </c>
       <c r="H32" t="str">
         <v/>
       </c>
       <c r="I32" t="str">
-        <v>急性肝炎などの肝細胞障害（比が低い、つまりASTに対してLDHが相対的に低い場合は肝性が示唆される）</v>
+        <v/>
       </c>
       <c r="J32" t="str">
         <v/>
       </c>
       <c r="K32" t="str">
-        <v>AST・LDHが同時に上昇した際の鑑別に使う目安の一つ。単独の検査値ではなく計算上の比率であり、確定診断には他の検査（ビリルビン、CK、心筋マーカーなど）と合わせた評価が必要</v>
+        <v/>
       </c>
       <c r="L32" t="str">
-        <v/>
+        <v>ASTのみ上昇しCKが正常であれば肝臓由来を、両方上昇していれば筋肉由来を疑う手がかりになる。スタチン系薬剤による横紋筋融解症が疑われる場面での鑑別に有用</v>
       </c>
       <c r="M32" t="str">
-        <v>LDH/AST,LDH,AST,溶血,心筋梗塞,肝炎</v>
+        <v/>
       </c>
       <c r="N32" t="str">
+        <v>CK/AST,CK,AST,横紋筋融解症,スタチン</v>
+      </c>
+      <c r="O32" t="str">
         <v/>
       </c>
     </row>
@@ -1863,15 +1960,18 @@
         <v/>
       </c>
       <c r="K33" t="str">
+        <v/>
+      </c>
+      <c r="L33" t="str">
         <v>本来のアニオンギャップ(Na-(Cl+HCO3))の簡易代用として使われることがあるが、重炭酸(HCO3)を用いた計算の方が正確。メトホルミン使用中の乳酸アシドーシスが疑われる場面などで参考にする</v>
       </c>
-      <c r="L33" t="str">
+      <c r="M33" t="str">
         <v>電解質</v>
       </c>
-      <c r="M33" t="str">
+      <c r="N33" t="str">
         <v>Na-Cl,アニオンギャップ,AG,代謝性アシドーシス,乳酸アシドーシス</v>
       </c>
-      <c r="N33" t="str">
+      <c r="O33" t="str">
         <v/>
       </c>
     </row>
@@ -1907,15 +2007,18 @@
         <v/>
       </c>
       <c r="K34" t="str">
+        <v/>
+      </c>
+      <c r="L34" t="str">
         <v>De Ritis比とも呼ばれる。比が2以上はアルコール性肝障害や肝硬変を、1未満は急性ウイルス性肝炎や脂肪肝を示唆する目安になるが、確定診断には他の検査所見と合わせた評価が必要</v>
       </c>
-      <c r="L34" t="str">
+      <c r="M34" t="str">
         <v>肝機能</v>
       </c>
-      <c r="M34" t="str">
+      <c r="N34" t="str">
         <v>AST/ALT,De Ritis比,デリティス比,アルコール性肝障害,肝硬変</v>
       </c>
-      <c r="N34" t="str">
+      <c r="O34" t="str">
         <v/>
       </c>
     </row>
@@ -1951,83 +2054,89 @@
         <v/>
       </c>
       <c r="K35" t="str">
+        <v/>
+      </c>
+      <c r="L35" t="str">
         <v>R値＝(ALTの基準値上限に対する倍率)÷(ALPの基準値上限に対する倍率)で算出する。薬剤性肝障害(DILI)の病型分類(肝細胞障害型/胆汁うっ滞型/混合型)に用いられ、被疑薬の休薬・変更の判断材料になる</v>
       </c>
-      <c r="L35" t="str">
+      <c r="M35" t="str">
         <v>肝機能</v>
       </c>
-      <c r="M35" t="str">
+      <c r="N35" t="str">
         <v>ALT/ALP比,R値,R-factor,DILI,薬剤性肝障害</v>
       </c>
-      <c r="N35" t="str">
+      <c r="O35" t="str">
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>CONUT値</v>
+        <v>BNP</v>
       </c>
       <c r="B36" t="str">
-        <v>CONUT</v>
+        <v>BNP</v>
       </c>
       <c r="C36" t="str">
-        <v>0〜1点：正常、2〜4点：軽度低栄養、5〜8点：中等度低栄養、9〜12点：高度低栄養</v>
+        <v>18.4 pg/mL以下</v>
       </c>
       <c r="D36" t="str">
-        <v>アルブミン・総リンパ球数・総コレステロールの3項目から算出する栄養状態の評価スコア</v>
+        <v>心臓が無理をしているときに出る物質。心臓は血液を送るポンプだが、負担がかかると「少し助けてほしい」というサインとしてBNPを血液中に出す。</v>
       </c>
       <c r="E36" t="str">
-        <v>CONUT値は、血液検査（アルブミン、リンパ球数、コレステロール）の結果から計算される、栄養状態を数値化したスコアです。点数が高いほど低栄養の状態が疑われます。</v>
+        <v>この検査は、心臓がどれくらい頑張りすぎていないかを見るものです。数値が高いと、心臓に少し負担がかかっているサインになります。</v>
       </c>
       <c r="F36" t="str">
-        <v>低栄養状態（点数が高いほど重度）</v>
+        <v>心不全、心臓に負担がかかっている状態、体に水分がたまりやすいとき</v>
       </c>
       <c r="G36" t="str">
-        <v>食事摂取量や体重の変化を確認する。必要に応じて栄養補助食品の活用を提案する</v>
+        <v>塩分・水分の摂りすぎに注意し、体重の変化を毎日記録するよう伝える</v>
       </c>
       <c r="H36" t="str">
         <v/>
       </c>
       <c r="I36" t="str">
-        <v/>
+        <v>心臓の負担は少ない状態</v>
       </c>
       <c r="J36" t="str">
         <v/>
       </c>
       <c r="K36" t="str">
-        <v>アルブミン・総リンパ球数・総コレステロールの3項目それぞれに配点があり、合計点で評価する客観的栄養指標。フレイル・サルコペニアの評価やポリファーマシー対策の一環としての栄養状態把握に有用</v>
+        <v/>
       </c>
       <c r="L36" t="str">
-        <v/>
+        <v>腎機能が低いとBNPは高めに出ることがある／数値だけで判断せず、症状と合わせて評価する／息切れ、むくみ、体重増加があれば要注意</v>
       </c>
       <c r="M36" t="str">
-        <v>CONUT,CONUT値,栄養評価,低栄養,フレイル</v>
+        <v>心不全</v>
       </c>
       <c r="N36" t="str">
-        <v>食事と栄養 p.240（フレイルQ108 低栄養や食事量の評価）</v>
+        <v>BNP,心不全,息切れ,むくみ</v>
+      </c>
+      <c r="O36" t="str">
+        <v>食事と栄養 p.216-222（第2部 心疾患）</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>乳び</v>
+        <v>CONUT値</v>
       </c>
       <c r="B37" t="str">
-        <v>乳び,Lipemia</v>
+        <v>CONUT</v>
       </c>
       <c r="C37" t="str">
-        <v>所見なし（血清が白濁していなければ正常）</v>
+        <v>0〜1点：正常、2〜4点：軽度低栄養、5〜8点：中等度低栄養、9〜12点：高度低栄養</v>
       </c>
       <c r="D37" t="str">
-        <v>中性脂肪が非常に多いため、血清が白く濁って見える状態。検査値そのものではなく検体の外観所見</v>
+        <v>アルブミン・総リンパ球数・総コレステロールの3項目から算出する栄養状態の評価スコア</v>
       </c>
       <c r="E37" t="str">
-        <v>乳びとは、血液中の中性脂肪が非常に多いために、採血した血液（血清）が白く濁って見える状態のことです。多くの場合、食後の採血や、著しい脂質異常症が背景にあります。</v>
+        <v>CONUT値は、血液検査（アルブミン、リンパ球数、コレステロール）の結果から計算される、栄養状態を数値化したスコアです。点数が高いほど低栄養の状態が疑われます。</v>
       </c>
       <c r="F37" t="str">
-        <v>著しい高中性脂肪血症、食後採血（一時的なもの）、原発性高カイロミクロン血症などの脂質代謝異常</v>
+        <v>低栄養状態（点数が高いほど重度）</v>
       </c>
       <c r="G37" t="str">
-        <v>採血が空腹時だったかを確認する。食後採血であれば次回は空腹時の再検を提案する</v>
+        <v>食事摂取量や体重の変化を確認する。必要に応じて栄養補助食品の活用を提案する</v>
       </c>
       <c r="H37" t="str">
         <v/>
@@ -2039,39 +2148,42 @@
         <v/>
       </c>
       <c r="K37" t="str">
-        <v>血清の白濁により一部の検査項目（電解質など）の測定値に誤差が出ることがある（偽性低ナトリウム血症など）。中性脂肪値と合わせて評価する</v>
+        <v/>
       </c>
       <c r="L37" t="str">
-        <v>脂質異常症</v>
+        <v>アルブミン・総リンパ球数・総コレステロールの3項目それぞれに配点があり、合計点で評価する客観的栄養指標。フレイル・サルコペニアの評価やポリファーマシー対策の一環としての栄養状態把握に有用</v>
       </c>
       <c r="M37" t="str">
-        <v>乳び,乳び血清,Lipemia,高中性脂肪血症</v>
+        <v/>
       </c>
       <c r="N37" t="str">
-        <v/>
+        <v>CONUT,CONUT値,栄養評価,低栄養,フレイル</v>
+      </c>
+      <c r="O37" t="str">
+        <v>食事と栄養 p.240（フレイルQ108 低栄養や食事量の評価）</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>溶血</v>
+        <v>乳び</v>
       </c>
       <c r="B38" t="str">
-        <v>溶血,Hemolysis</v>
+        <v>乳び,Lipemia</v>
       </c>
       <c r="C38" t="str">
-        <v>所見なし（溶血を示唆する検査値異常がなければ正常）</v>
+        <v>所見なし（血清が白濁していなければ正常）</v>
       </c>
       <c r="D38" t="str">
-        <v>赤血球が通常より早く壊れる状態。単独の検査値ではなく、複数の検査値の組み合わせで疑う病態</v>
+        <v>中性脂肪が非常に多いため、血清が白く濁って見える状態。検査値そのものではなく検体の外観所見</v>
       </c>
       <c r="E38" t="str">
-        <v>溶血とは、赤血球が通常よりも早いペースで壊れてしまう状態のことです。壊れた赤血球からビリルビンなどが放出されるため、貧血や黄疸の原因になることがあります。</v>
+        <v>乳びとは、血液中の中性脂肪が非常に多いために、採血した血液（血清）が白く濁って見える状態のことです。多くの場合、食後の採血や、著しい脂質異常症が背景にあります。</v>
       </c>
       <c r="F38" t="str">
-        <v>自己免疫性溶血性貧血、血液型不適合輸血、G6PD欠損症などの遺伝性疾患、機械弁など人工物による物理的破壊、薬剤性溶血</v>
+        <v>著しい高中性脂肪血症、食後採血（一時的なもの）、原発性高カイロミクロン血症などの脂質代謝異常</v>
       </c>
       <c r="G38" t="str">
-        <v>倦怠感、黄疸、尿の色が濃くなるなどの症状がないか確認する</v>
+        <v>採血が空腹時だったかを確認する。食後採血であれば次回は空腹時の再検を提案する</v>
       </c>
       <c r="H38" t="str">
         <v/>
@@ -2083,39 +2195,42 @@
         <v/>
       </c>
       <c r="K38" t="str">
-        <v>溶血を疑う際は、間接ビリルビン上昇・LDH上昇・ハプトグロビン低下・網状赤血球増加のパターンを確認する。ヘモグロビン・MCV・MCHCの変化と合わせて総合的に判断する</v>
+        <v/>
       </c>
       <c r="L38" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>血清の白濁により一部の検査項目（電解質など）の測定値に誤差が出ることがある（偽性低ナトリウム血症など）。中性脂肪値と合わせて評価する</v>
       </c>
       <c r="M38" t="str">
-        <v>溶血,Hemolysis,溶血性貧血,G6PD,ハプトグロビン</v>
+        <v>脂質異常症</v>
       </c>
       <c r="N38" t="str">
+        <v>乳び,乳び血清,Lipemia,高中性脂肪血症</v>
+      </c>
+      <c r="O38" t="str">
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>黄疸</v>
+        <v>溶血</v>
       </c>
       <c r="B39" t="str">
-        <v>黄疸,Jaundice</v>
+        <v>溶血,Hemolysis</v>
       </c>
       <c r="C39" t="str">
-        <v>所見なし（皮膚・眼球結膜の黄染がなければ正常）</v>
+        <v>所見なし（溶血を示唆する検査値異常がなければ正常）</v>
       </c>
       <c r="D39" t="str">
-        <v>ビリルビンが体にたまり、皮膚や白目が黄色くなる状態。単独の検査値ではなく、ビリルビン上昇によって表れる身体所見</v>
+        <v>赤血球が通常より早く壊れる状態。単独の検査値ではなく、複数の検査値の組み合わせで疑う病態</v>
       </c>
       <c r="E39" t="str">
-        <v>黄疸は、体の中にビリルビンという黄色い色素がたまることで、皮膚や白目が黄色く見える状態です。肝臓や胆道のトラブル、赤血球が壊れやすくなる病気（溶血）などが原因となります。</v>
+        <v>溶血とは、赤血球が通常よりも早いペースで壊れてしまう状態のことです。壊れた赤血球からビリルビンなどが放出されるため、貧血や黄疸の原因になることがあります。</v>
       </c>
       <c r="F39" t="str">
-        <v>肝炎・肝硬変などの肝疾患、胆石・腫瘍による胆道閉塞、溶血性疾患、体質性黄疸（ジルベール症候群）、新生児黄疸</v>
+        <v>自己免疫性溶血性貧血、血液型不適合輸血、G6PD欠損症などの遺伝性疾患、機械弁など人工物による物理的破壊、薬剤性溶血</v>
       </c>
       <c r="G39" t="str">
-        <v>白目や皮膚の黄染に気づいたら、尿の色（濃い茶色）や便の色（白っぽい）の変化も確認し、早めの受診を勧める</v>
+        <v>倦怠感、黄疸、尿の色が濃くなるなどの症状がないか確認する</v>
       </c>
       <c r="H39" t="str">
         <v/>
@@ -2127,429 +2242,459 @@
         <v/>
       </c>
       <c r="K39" t="str">
-        <v>黄疸は検査値そのものではなく身体所見。原因を調べる際は総ビリルビン・直接ビリルビン・間接ビリルビンの内訳とAST/ALT/γ-GTPを確認する。直接優位なら胆道系、間接優位なら溶血・体質性を疑う</v>
+        <v/>
       </c>
       <c r="L39" t="str">
-        <v>肝機能</v>
+        <v>溶血を疑う際は、間接ビリルビン上昇・LDH上昇・ハプトグロビン低下・網状赤血球増加のパターンを確認する。ヘモグロビン・MCV・MCHCの変化と合わせて総合的に判断する</v>
       </c>
       <c r="M39" t="str">
-        <v>黄疸,ジョンダイス,Jaundice,ビリルビン,皮膚黄染,白目</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="N39" t="str">
+        <v>溶血,Hemolysis,溶血性貧血,G6PD,ハプトグロビン</v>
+      </c>
+      <c r="O39" t="str">
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>TSH（甲状腺刺激ホルモン）</v>
+        <v>黄疸</v>
       </c>
       <c r="B40" t="str">
-        <v>TSH</v>
+        <v>黄疸,Jaundice</v>
       </c>
       <c r="C40" t="str">
-        <v>0.5〜5.0 μIU/mL程度（施設差あり）</v>
+        <v>所見なし（皮膚・眼球結膜の黄染がなければ正常）</v>
       </c>
       <c r="D40" t="str">
-        <v>甲状腺の働きが多いか少ないかを最も敏感に反映するホルモン</v>
+        <v>ビリルビンが体にたまり、皮膚や白目が黄色くなる状態。単独の検査値ではなく、ビリルビン上昇によって表れる身体所見</v>
       </c>
       <c r="E40" t="str">
-        <v>TSHは脳の下垂体から出て、甲状腺に「もっと働いて」と指令を送るホルモンです。甲状腺の働きが弱っていると体が指令を強めるためTSHは上がり、逆に甲状腺が働きすぎているとTSHは下がります。甲状腺の状態を最初に確認する数値としてよく使われます。</v>
+        <v>黄疸は、体の中にビリルビンという黄色い色素がたまることで、皮膚や白目が黄色く見える状態です。肝臓や胆道のトラブル、赤血球が壊れやすくなる病気（溶血）などが原因となります。</v>
       </c>
       <c r="F40" t="str">
-        <v>甲状腺機能低下症（橋本病など）、チラーヂンSなど甲状腺ホルモン薬の量不足</v>
+        <v>肝炎・肝硬変などの肝疾患、胆石・腫瘍による胆道閉塞、溶血性疾患、体質性黄疸（ジルベール症候群）、新生児黄疸</v>
       </c>
       <c r="G40" t="str">
-        <v>だるさ、むくみ、体重増加、寒がりなどの症状がないか確認する。服薬状況（飲み忘れ、他の薬との飲み合わせ）を確認する</v>
+        <v>白目や皮膚の黄染に気づいたら、尿の色（濃い茶色）や便の色（白っぽい）の変化も確認し、早めの受診を勧める</v>
       </c>
       <c r="H40" t="str">
-        <v>アミオダロン、炭酸リチウム、インターフェロン製剤、チロシンキナーゼ阻害薬(スニチニブ等)</v>
+        <v/>
       </c>
       <c r="I40" t="str">
-        <v>甲状腺機能亢進症（バセドウ病など）、チラーヂンSなど甲状腺ホルモン薬の過量</v>
+        <v/>
       </c>
       <c r="J40" t="str">
-        <v>動悸、体重減少、暑がり、手のふるえなどの症状がないか確認する</v>
+        <v/>
       </c>
       <c r="K40" t="str">
-        <v>チラーヂンS服用中はTSHが治療目標域に収まっているかで用量調整の目安にする。メルカゾール服用中はTSH・FT4に加えて無顆粒球症の初期症状（発熱・のどの痛み）の有無や白血球数も確認する</v>
+        <v/>
       </c>
       <c r="L40" t="str">
-        <v>甲状腺疾患</v>
+        <v>黄疸は検査値そのものではなく身体所見。原因を調べる際は総ビリルビン・直接ビリルビン・間接ビリルビンの内訳とAST/ALT/γ-GTPを確認する。直接優位なら胆道系、間接優位なら溶血・体質性を疑う</v>
       </c>
       <c r="M40" t="str">
-        <v>TSH,甲状腺刺激ホルモン,甲状腺機能,橋本病,バセドウ病,チラーヂン,メルカゾール</v>
+        <v>肝機能</v>
       </c>
       <c r="N40" t="str">
-        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
+        <v>黄疸,ジョンダイス,Jaundice,ビリルビン,皮膚黄染,白目</v>
+      </c>
+      <c r="O40" t="str">
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>FT4（遊離サイロキシン）</v>
+        <v>TSH（甲状腺刺激ホルモン）</v>
       </c>
       <c r="B41" t="str">
-        <v>FT4</v>
+        <v>TSH</v>
       </c>
       <c r="C41" t="str">
-        <v>0.9〜1.7 ng/dL程度（施設差あり）</v>
+        <v>0.5〜5.0 μIU/mL程度（施設差あり）</v>
       </c>
       <c r="D41" t="str">
-        <v>甲状腺が実際に分泌しているホルモンの量そのものを表す数値</v>
+        <v>甲状腺の働きが多いか少ないかを最も敏感に反映するホルモン</v>
       </c>
       <c r="E41" t="str">
-        <v>FT4は甲状腺そのものが作っているホルモンの量です。TSHが「指令の強さ」だとすると、FT4は「実際に出ている量」にあたります。2つをあわせて見ることで、甲状腺の働きが今どういう状態かを詳しく判断できます。</v>
+        <v>TSHは脳の下垂体から出て、甲状腺に「もっと働いて」と指令を送るホルモンです。甲状腺の働きが弱っていると体が指令を強めるためTSHは上がり、逆に甲状腺が働きすぎているとTSHは下がります。甲状腺の状態を最初に確認する数値としてよく使われます。</v>
       </c>
       <c r="F41" t="str">
-        <v>甲状腺機能亢進症（バセドウ病など）</v>
+        <v>甲状腺機能低下症（橋本病など）、チラーヂンSなど甲状腺ホルモン薬の量不足</v>
       </c>
       <c r="G41" t="str">
+        <v>だるさ、むくみ、体重増加、寒がりなどの症状がないか確認する。服薬状況（飲み忘れ、他の薬との飲み合わせ）を確認する</v>
+      </c>
+      <c r="H41" t="str">
+        <v>アミオダロン、炭酸リチウム、インターフェロン製剤、チロシンキナーゼ阻害薬(スニチニブ等)</v>
+      </c>
+      <c r="I41" t="str">
+        <v>甲状腺機能亢進症（バセドウ病など）、チラーヂンSなど甲状腺ホルモン薬の過量</v>
+      </c>
+      <c r="J41" t="str">
         <v>動悸、体重減少、暑がり、手のふるえなどの症状がないか確認する</v>
       </c>
-      <c r="H41" t="str">
-        <v>レボチロキシンの過量投与、アミオダロン</v>
-      </c>
-      <c r="I41" t="str">
-        <v>甲状腺機能低下症（橋本病など）</v>
-      </c>
-      <c r="J41" t="str">
-        <v>だるさ、むくみ、体重増加、寒がりなどの症状がないか確認する</v>
-      </c>
       <c r="K41" t="str">
-        <v>TSHと逆方向に動くのが基本だが、下垂体性の異常など例外もある。TSHと合わせて評価し、片方だけで判断しない</v>
+        <v>レボチロキシンの過量投与</v>
       </c>
       <c r="L41" t="str">
+        <v>チラーヂンS服用中はTSHが治療目標域に収まっているかで用量調整の目安にする。メルカゾール服用中はTSH・FT4に加えて無顆粒球症の初期症状（発熱・のどの痛み）の有無や白血球数も確認する</v>
+      </c>
+      <c r="M41" t="str">
         <v>甲状腺疾患</v>
       </c>
-      <c r="M41" t="str">
-        <v>FT4,遊離サイロキシン,甲状腺ホルモン,甲状腺機能</v>
-      </c>
       <c r="N41" t="str">
+        <v>TSH,甲状腺刺激ホルモン,甲状腺機能,橋本病,バセドウ病,チラーヂン,メルカゾール</v>
+      </c>
+      <c r="O41" t="str">
         <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>尿蛋白（随時尿）</v>
+        <v>FT4（遊離サイロキシン）</v>
       </c>
       <c r="B42" t="str">
-        <v>尿蛋白,U-pro</v>
+        <v>FT4</v>
       </c>
       <c r="C42" t="str">
-        <v>陰性（－）〜弱陽性</v>
+        <v>0.9〜1.7 ng/dL程度（施設差あり）</v>
       </c>
       <c r="D42" t="str">
-        <v>腎臓から本来漏れないはずのたんぱくが尿に出ていないかを見る検査</v>
+        <v>甲状腺が実際に分泌しているホルモンの量そのものを表す数値</v>
       </c>
       <c r="E42" t="str">
-        <v>この検査は、腎臓のろ過機能に負担がかかっていないかを見るものです。本来、たんぱく質は尿にほとんど出ませんが、腎臓に負担がかかると漏れ出るようになります。</v>
+        <v>FT4は甲状腺そのものが作っているホルモンの量です。TSHが「指令の強さ」だとすると、FT4は「実際に出ている量」にあたります。2つをあわせて見ることで、甲状腺の働きが今どういう状態かを詳しく判断できます。</v>
       </c>
       <c r="F42" t="str">
-        <v>糖尿病性腎症、腎炎、高血圧性腎硬化症、発熱・運動後の一過性のもの</v>
+        <v>甲状腺機能亢進症（バセドウ病など）</v>
       </c>
       <c r="G42" t="str">
-        <v/>
+        <v>動悸、体重減少、暑がり、手のふるえなどの症状がないか確認する</v>
       </c>
       <c r="H42" t="str">
-        <v>NSAIDs、造影剤、アミノグリコシド系、バンコマイシン、金製剤</v>
+        <v>レボチロキシンの過量投与、アミオダロン</v>
       </c>
       <c r="I42" t="str">
-        <v/>
+        <v>甲状腺機能低下症（橋本病など）</v>
       </c>
       <c r="J42" t="str">
-        <v/>
+        <v>だるさ、むくみ、体重増加、寒がりなどの症状がないか確認する</v>
       </c>
       <c r="K42" t="str">
-        <v>発熱・激しい運動・起立性蛋白尿など生理的な要因でも陽性になることがある。持続する場合に腎症の進行を疑う</v>
+        <v>抗甲状腺薬(メルカゾール、プロパジール)の効きすぎ</v>
       </c>
       <c r="L42" t="str">
-        <v>糖尿病,腎機能</v>
+        <v>TSHと逆方向に動くのが基本だが、下垂体性の異常など例外もある。TSHと合わせて評価し、片方だけで判断しない</v>
       </c>
       <c r="M42" t="str">
-        <v>尿蛋白,U-pro,腎症,たんぱく尿</v>
+        <v>甲状腺疾患</v>
       </c>
       <c r="N42" t="str">
-        <v/>
+        <v>FT4,遊離サイロキシン,甲状腺ホルモン,甲状腺機能</v>
+      </c>
+      <c r="O42" t="str">
+        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>尿クレアチニン（随時尿）</v>
+        <v>尿蛋白（随時尿）</v>
       </c>
       <c r="B43" t="str">
-        <v>尿CRE</v>
+        <v>尿蛋白,U-pro</v>
       </c>
       <c r="C43" t="str">
-        <v>随時尿は主に他項目の濃度補正に利用（単独の基準値は設けにくい）</v>
+        <v>陰性（－）〜弱陽性</v>
       </c>
       <c r="D43" t="str">
-        <v>随時尿中のクレアチニン濃度。他の尿検査項目を薄まり具合で補正するための基準として使う</v>
+        <v>腎臓から本来漏れないはずのたんぱくが尿に出ていないかを見る検査</v>
       </c>
       <c r="E43" t="str">
-        <v>この数値は、尿がどれくらい薄まっているかを確認するための基準として使われます。他の尿検査の結果（蛋白やアルブミンなど）をこの値で割って補正することで、水分摂取量による影響を減らして正確に評価できます。</v>
+        <v>この検査は、腎臓のろ過機能に負担がかかっていないかを見るものです。本来、たんぱく質は尿にほとんど出ませんが、腎臓に負担がかかると漏れ出るようになります。</v>
       </c>
       <c r="F43" t="str">
-        <v/>
+        <v>糖尿病性腎症、腎炎、高血圧性腎硬化症、発熱・運動後の一過性のもの</v>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v/>
+        <v>NSAIDs、造影剤、アミノグリコシド系、バンコマイシン、金製剤</v>
       </c>
       <c r="I43" t="str">
-        <v>尿が薄い（水分摂取が多い、腎機能低下）状態</v>
+        <v/>
       </c>
       <c r="J43" t="str">
         <v/>
       </c>
       <c r="K43" t="str">
-        <v>尿中アルブミン/Cr比、尿蛋白/Cr比など、他項目の補正計算に使われる。単独の高低に臨床的意味は乏しい</v>
+        <v/>
       </c>
       <c r="L43" t="str">
-        <v>腎機能</v>
+        <v>発熱・激しい運動・起立性蛋白尿など生理的な要因でも陽性になることがある。持続する場合に腎症の進行を疑う</v>
       </c>
       <c r="M43" t="str">
-        <v>尿CRE,尿クレアチニン,随時尿,補正,蛋白クレアチニン比</v>
+        <v>糖尿病,腎機能</v>
       </c>
       <c r="N43" t="str">
+        <v>尿蛋白,U-pro,腎症,たんぱく尿</v>
+      </c>
+      <c r="O43" t="str">
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>白血球（WBC）</v>
+        <v>尿クレアチニン（随時尿）</v>
       </c>
       <c r="B44" t="str">
-        <v>WBC</v>
+        <v>尿CRE</v>
       </c>
       <c r="C44" t="str">
-        <v>3,300〜8,600 /μL程度（施設差あり）</v>
+        <v>随時尿は主に他項目の濃度補正に利用（単独の基準値は設けにくい）</v>
       </c>
       <c r="D44" t="str">
-        <v>体を細菌やウイルスから守る免疫細胞の数で、感染や炎症、薬剤の影響を反映する</v>
+        <v>随時尿中のクレアチニン濃度。他の尿検査項目を薄まり具合で補正するための基準として使う</v>
       </c>
       <c r="E44" t="str">
-        <v>白血球は体に入ってきた細菌やウイルスと戦う免疫細胞です。感染症や炎症があると増え、逆に一部のお薬の副作用や骨髄の働きが落ちると減ることがあります。</v>
+        <v>この数値は、尿がどれくらい薄まっているかを確認するための基準として使われます。他の尿検査の結果（蛋白やアルブミンなど）をこの値で割って補正することで、水分摂取量による影響を減らして正確に評価できます。</v>
       </c>
       <c r="F44" t="str">
-        <v>感染症、炎症、ステロイド使用、喫煙、白血病などの血液疾患</v>
+        <v/>
       </c>
       <c r="G44" t="str">
-        <v>発熱や体の痛みなど感染症状がないか確認する</v>
+        <v/>
       </c>
       <c r="H44" t="str">
-        <v>ステロイド、G-CSF製剤、炭酸リチウム</v>
+        <v/>
       </c>
       <c r="I44" t="str">
-        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、メルカゾールなど薬剤性の無顆粒球症、再生不良性貧血、ウイルス感染</v>
+        <v>尿が薄い（水分摂取が多い、腎機能低下）状態</v>
       </c>
       <c r="J44" t="str">
-        <v>発熱、のどの痛みなど感染症状の初期サインがないか確認する。人混みを避け、手洗い・うがいを徹底するよう伝える</v>
+        <v/>
       </c>
       <c r="K44" t="str">
-        <v>メルカゾール（チアマゾール）は無顆粒球症の重大な副作用があり、発熱・のどの痛みが出たらすぐ受診するよう指導する。抗がん剤・免疫抑制剤・抗てんかん薬（カルバマゼピンなど）使用中も定期的なモニタリングが必要</v>
+        <v/>
       </c>
       <c r="L44" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>尿中アルブミン/Cr比、尿蛋白/Cr比など、他項目の補正計算に使われる。単独の高低に臨床的意味は乏しい</v>
       </c>
       <c r="M44" t="str">
-        <v>白血球,WBC,好中球,感染症,白血病,無顆粒球症,骨髄抑制</v>
+        <v>腎機能</v>
       </c>
       <c r="N44" t="str">
+        <v>尿CRE,尿クレアチニン,随時尿,補正,蛋白クレアチニン比</v>
+      </c>
+      <c r="O44" t="str">
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>赤血球</v>
+        <v>白血球（WBC）</v>
       </c>
       <c r="B45" t="str">
-        <v>RBC</v>
+        <v>WBC</v>
       </c>
       <c r="C45" t="str">
-        <v>男性 435〜555万/μL、女性 386〜492万/μL程度（施設差あり）</v>
+        <v>3,300〜8,600 /μL程度（施設差あり）</v>
       </c>
       <c r="D45" t="str">
-        <v>血液中で酸素を運ぶ細胞の数。ヘモグロビン・ヘマトクリットと合わせて貧血・多血症を評価する</v>
+        <v>体を細菌やウイルスから守る免疫細胞の数で、感染や炎症、薬剤の影響を反映する</v>
       </c>
       <c r="E45" t="str">
-        <v>赤血球は、肺で受け取った酸素を全身に運ぶ血液の細胞です。数が少ないと貧血、多いと多血症が疑われます。ヘモグロビンやヘマトクリットと合わせて総合的に評価します。</v>
+        <v>白血球は体に入ってきた細菌やウイルスと戦う免疫細胞です。感染症や炎症があると増え、逆に一部のお薬の副作用や骨髄の働きが落ちると減ることがあります。</v>
       </c>
       <c r="F45" t="str">
-        <v>脱水、多血症（真性多血症、二次性多血症）、喫煙</v>
+        <v>感染症、炎症、ステロイド使用、喫煙、白血病などの血液疾患</v>
       </c>
       <c r="G45" t="str">
-        <v>脱水が疑われる場合はこまめな水分摂取を勧める（水分制限がある場合を除く）</v>
+        <v>発熱や体の痛みなど感染症状がないか確認する</v>
       </c>
       <c r="H45" t="str">
-        <v/>
+        <v>ステロイド、G-CSF製剤、炭酸リチウム</v>
       </c>
       <c r="I45" t="str">
-        <v>貧血（鉄欠乏性貧血、腎性貧血など）、出血</v>
+        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、メルカゾールなど薬剤性の無顆粒球症、再生不良性貧血、ウイルス感染</v>
       </c>
       <c r="J45" t="str">
-        <v>ヘモグロビンと同様に、出血や食事量低下がないか確認する</v>
+        <v>発熱、のどの痛みなど感染症状の初期サインがないか確認する。人混みを避け、手洗い・うがいを徹底するよう伝える</v>
       </c>
       <c r="K45" t="str">
-        <v>ヘモグロビン・ヘマトクリットと同じ方向に動くことが多い。赤血球数だけでなくMCV・MCH・MCHCと合わせて貧血のタイプ(小球性・正球性・大球性)を判断する</v>
+        <v>抗がん剤、メルカゾール(無顆粒球症)、クロザピン(定期的な血球モニタリング必須)、サラゾスルファピリジン</v>
       </c>
       <c r="L45" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>メルカゾール（チアマゾール）は無顆粒球症の重大な副作用があり、発熱・のどの痛みが出たらすぐ受診するよう指導する。抗がん剤・免疫抑制剤・抗てんかん薬（カルバマゼピンなど）使用中も定期的なモニタリングが必要</v>
       </c>
       <c r="M45" t="str">
-        <v>赤血球,RBC,貧血,多血症</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N45" t="str">
-        <v>食事と栄養 p.151-164（第2部 貧血）</v>
+        <v>白血球,WBC,好中球,感染症,白血病,無顆粒球症,骨髄抑制</v>
+      </c>
+      <c r="O45" t="str">
+        <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ヘモグロビン濃度</v>
+        <v>赤血球</v>
       </c>
       <c r="B46" t="str">
-        <v>Hb</v>
+        <v>RBC</v>
       </c>
       <c r="C46" t="str">
-        <v>男性 13.5〜17.5 g/dL、女性 11.5〜15.0 g/dL</v>
+        <v>男性 435〜555万/μL、女性 386〜492万/μL程度（施設差あり）</v>
       </c>
       <c r="D46" t="str">
-        <v>血液の中で酸素を運ぶ役割をしている。この値が低い状態が貧血。</v>
+        <v>血液中で酸素を運ぶ細胞の数。ヘモグロビン・ヘマトクリットと合わせて貧血・多血症を評価する</v>
       </c>
       <c r="E46" t="str">
-        <v>血の数値が良くなっても、体の中の鉄はまだ十分ではないことがあります。そのため、しばらく続けて飲むことが大切です。</v>
+        <v>赤血球は、肺で受け取った酸素を全身に運ぶ血液の細胞です。数が少ないと貧血、多いと多血症が疑われます。ヘモグロビンやヘマトクリットと合わせて総合的に評価します。</v>
       </c>
       <c r="F46" t="str">
-        <v/>
+        <v>脱水、多血症（真性多血症、二次性多血症）、喫煙</v>
       </c>
       <c r="G46" t="str">
-        <v/>
+        <v>脱水が疑われる場合はこまめな水分摂取を勧める（水分制限がある場合を除く）</v>
       </c>
       <c r="H46" t="str">
         <v/>
       </c>
       <c r="I46" t="str">
-        <v>鉄欠乏性貧血、出血、腎性貧血、骨髄の造血機能低下</v>
+        <v>貧血（鉄欠乏性貧血、腎性貧血など）、出血</v>
       </c>
       <c r="J46" t="str">
-        <v>鉄分の多い食品（レバー・赤身肉・魚・ほうれん草など）を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える</v>
+        <v>ヘモグロビンと同様に、出血や食事量低下がないか確認する</v>
       </c>
       <c r="K46" t="str">
-        <v>原因（出血・食事量低下など）の確認が重要。腎機能低下がある場合は鉄不足以外が原因のこともある。鉄剤はヘモグロビンが正常化した後も2〜3か月程度は継続することが多い（鉄の貯蔵分を補うため。途中でやめると再び貧血になりやすい）</v>
+        <v/>
       </c>
       <c r="L46" t="str">
-        <v>鉄欠乏性貧血,抗血小板療法,抗凝固療法（心房細動・血栓症）</v>
+        <v>ヘモグロビン・ヘマトクリットと同じ方向に動くことが多い。赤血球数だけでなくMCV・MCH・MCHCと合わせて貧血のタイプ(小球性・正球性・大球性)を判断する</v>
       </c>
       <c r="M46" t="str">
-        <v>ヘモグロビン,Hb,貧血,鉄剤,鉄欠乏性貧血</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="N46" t="str">
+        <v>赤血球,RBC,貧血,多血症</v>
+      </c>
+      <c r="O46" t="str">
         <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ヘマトクリット値</v>
+        <v>ヘモグロビン濃度</v>
       </c>
       <c r="B47" t="str">
-        <v>Ht,Hct</v>
+        <v>Hb</v>
       </c>
       <c r="C47" t="str">
-        <v>男性 40〜50%、女性 35〜45%</v>
+        <v>男性 13.5〜17.5 g/dL、女性 11.5〜15.0 g/dL</v>
       </c>
       <c r="D47" t="str">
-        <v>血液全体のうち赤血球が占める体積の割合。貧血・脱水の指標</v>
+        <v>血液の中で酸素を運ぶ役割をしている。この値が低い状態が貧血。</v>
       </c>
       <c r="E47" t="str">
-        <v>ヘマトクリットは、血液全体のうち赤血球が占める割合を表す数値です。この値が低いと貧血、高いと脱水や血液が濃くなっている状態が疑われます。</v>
+        <v>血の数値が良くなっても、体の中の鉄はまだ十分ではないことがあります。そのため、しばらく続けて飲むことが大切です。</v>
       </c>
       <c r="F47" t="str">
-        <v>脱水、多血症（真性多血症、二次性多血症）、喫煙</v>
+        <v/>
       </c>
       <c r="G47" t="str">
-        <v>脱水が疑われる場合はこまめな水分摂取を勧める（水分制限がある場合を除く）</v>
+        <v/>
       </c>
       <c r="H47" t="str">
         <v/>
       </c>
       <c r="I47" t="str">
-        <v>貧血（鉄欠乏性貧血、腎性貧血など）、出血</v>
+        <v>鉄欠乏性貧血、出血、腎性貧血、骨髄の造血機能低下</v>
       </c>
       <c r="J47" t="str">
-        <v>ヘモグロビンと同様に、出血や食事量低下がないか確認する</v>
+        <v>鉄分の多い食品（レバー・赤身肉・魚・ほうれん草など）を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える</v>
       </c>
       <c r="K47" t="str">
-        <v>ヘモグロビン・赤血球数と合わせて評価する。3つの値は同じ方向に動くことが多く、脱水があると貧血が見かけ上隠れることがある</v>
+        <v>NSAIDs・抗凝固薬・抗血小板薬(消化管出血のリスク)、抗がん剤、ST合剤</v>
       </c>
       <c r="L47" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>原因（出血・食事量低下など）の確認が重要。腎機能低下がある場合は鉄不足以外が原因のこともある。鉄剤はヘモグロビンが正常化した後も2〜3か月程度は継続することが多い（鉄の貯蔵分を補うため。途中でやめると再び貧血になりやすい）</v>
       </c>
       <c r="M47" t="str">
-        <v>ヘマトクリット,Ht,Hct,貧血,脱水,多血症</v>
+        <v>鉄欠乏性貧血,抗血小板療法,抗凝固療法（心房細動・血栓症）</v>
       </c>
       <c r="N47" t="str">
+        <v>ヘモグロビン,Hb,貧血,鉄剤,鉄欠乏性貧血</v>
+      </c>
+      <c r="O47" t="str">
         <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>MCV</v>
+        <v>ヘマトクリット値</v>
       </c>
       <c r="B48" t="str">
-        <v>MCV</v>
+        <v>Ht,Hct</v>
       </c>
       <c r="C48" t="str">
-        <v>79〜100 fL</v>
+        <v>男性 40〜50%、女性 35〜45%</v>
       </c>
       <c r="D48" t="str">
-        <v>赤血球1個の大きさ</v>
+        <v>血液全体のうち赤血球が占める体積の割合。貧血・脱水の指標</v>
       </c>
       <c r="E48" t="str">
-        <v>MCVは赤血球1個あたりの大きさを表す数値です。貧血があるとき、この数値で「小さい貧血」か「大きい貧血」かを見分けることができ、原因を絞り込む手がかりになります。</v>
+        <v>ヘマトクリットは、血液全体のうち赤血球が占める割合を表す数値です。この値が低いと貧血、高いと脱水や血液が濃くなっている状態が疑われます。</v>
       </c>
       <c r="F48" t="str">
-        <v/>
+        <v>脱水、多血症（真性多血症、二次性多血症）、喫煙</v>
       </c>
       <c r="G48" t="str">
-        <v/>
+        <v>脱水が疑われる場合はこまめな水分摂取を勧める（水分制限がある場合を除く）</v>
       </c>
       <c r="H48" t="str">
         <v/>
       </c>
       <c r="I48" t="str">
+        <v>貧血（鉄欠乏性貧血、腎性貧血など）、出血</v>
+      </c>
+      <c r="J48" t="str">
+        <v>ヘモグロビンと同様に、出血や食事量低下がないか確認する</v>
+      </c>
+      <c r="K48" t="str">
+        <v/>
+      </c>
+      <c r="L48" t="str">
+        <v>ヘモグロビン・赤血球数と合わせて評価する。3つの値は同じ方向に動くことが多く、脱水があると貧血が見かけ上隠れることがある</v>
+      </c>
+      <c r="M48" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
-      <c r="J48" t="str">
-        <v>鉄分の多い食事を意識する（ヘモグロビンの項目を参照）</v>
-      </c>
-      <c r="K48" t="str">
-        <v/>
-      </c>
-      <c r="L48" t="str">
-        <v>鉄欠乏性貧血</v>
-      </c>
-      <c r="M48" t="str">
-        <v>MCV,赤血球指数,貧血</v>
-      </c>
       <c r="N48" t="str">
+        <v>ヘマトクリット,Ht,Hct,貧血,脱水,多血症</v>
+      </c>
+      <c r="O48" t="str">
         <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>MCH</v>
+        <v>MCV</v>
       </c>
       <c r="B49" t="str">
-        <v>MCH</v>
+        <v>MCV</v>
       </c>
       <c r="C49" t="str">
-        <v>26.3〜34.3 pg</v>
+        <v>79〜100 fL</v>
       </c>
       <c r="D49" t="str">
-        <v>赤血球1個に含まれるヘモグロビン量</v>
+        <v>赤血球1個の大きさ</v>
       </c>
       <c r="E49" t="str">
-        <v>MCHは赤血球1個の中に含まれるヘモグロビン（酸素を運ぶ色素）の量を表す数値です。MCVと同じく、貧血の種類を見分けるのに使われます。</v>
+        <v>MCVは赤血球1個あたりの大きさを表す数値です。貧血があるとき、この数値で「小さい貧血」か「大きい貧血」かを見分けることができ、原因を絞り込む手がかりになります。</v>
       </c>
       <c r="F49" t="str">
         <v/>
@@ -2570,30 +2715,33 @@
         <v/>
       </c>
       <c r="L49" t="str">
+        <v/>
+      </c>
+      <c r="M49" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
-      <c r="M49" t="str">
-        <v>MCH,赤血球指数,貧血</v>
-      </c>
       <c r="N49" t="str">
+        <v>MCV,赤血球指数,貧血</v>
+      </c>
+      <c r="O49" t="str">
         <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>MCHC</v>
+        <v>MCH</v>
       </c>
       <c r="B50" t="str">
-        <v>MCHC</v>
+        <v>MCH</v>
       </c>
       <c r="C50" t="str">
-        <v>31.6〜36.6 %</v>
+        <v>26.3〜34.3 pg</v>
       </c>
       <c r="D50" t="str">
-        <v>単位容積あたりの赤血球に含まれるヘモグロビン濃度</v>
+        <v>赤血球1個に含まれるヘモグロビン量</v>
       </c>
       <c r="E50" t="str">
-        <v>MCHCは、赤血球の中にヘモグロビンがどれくらい濃く詰まっているかを表す数値です。鉄が不足すると、この濃度も薄くなる傾向があります。</v>
+        <v>MCHは赤血球1個の中に含まれるヘモグロビン（酸素を運ぶ色素）の量を表す数値です。MCVと同じく、貧血の種類を見分けるのに使われます。</v>
       </c>
       <c r="F50" t="str">
         <v/>
@@ -2614,33 +2762,36 @@
         <v/>
       </c>
       <c r="L50" t="str">
+        <v/>
+      </c>
+      <c r="M50" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
-      <c r="M50" t="str">
-        <v>MCHC,赤血球指数,貧血</v>
-      </c>
       <c r="N50" t="str">
+        <v>MCH,赤血球指数,貧血</v>
+      </c>
+      <c r="O50" t="str">
         <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>血小板数</v>
+        <v>MCHC</v>
       </c>
       <c r="B51" t="str">
-        <v>Plt</v>
+        <v>MCHC</v>
       </c>
       <c r="C51" t="str">
-        <v>15.0〜35.0万/μL程度（施設差あり）</v>
+        <v>31.6〜36.6 %</v>
       </c>
       <c r="D51" t="str">
-        <v>出血を止める働きをする血液成分で、少なすぎると出血しやすくなる</v>
+        <v>単位容積あたりの赤血球に含まれるヘモグロビン濃度</v>
       </c>
       <c r="E51" t="str">
-        <v>血小板は、血管が傷ついたときに集まって血を止める役割をする血液の成分です。数が少ないとあざができやすくなったり、出血が止まりにくくなったりします。抗血小板薬や抗がん剤を使っている方では、定期的にチェックすることが大切です。</v>
+        <v>MCHCは、赤血球の中にヘモグロビンがどれくらい濃く詰まっているかを表す数値です。鉄が不足すると、この濃度も薄くなる傾向があります。</v>
       </c>
       <c r="F51" t="str">
-        <v>炎症性疾患、鉄欠乏性貧血、脾摘後、骨髄増殖性疾患</v>
+        <v/>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2649,42 +2800,45 @@
         <v/>
       </c>
       <c r="I51" t="str">
-        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、肝硬変・脾機能亢進、再生不良性貧血、抗てんかん薬（バルプロ酸など）の副作用、ITP（特発性血小板減少性紫斑病）</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="J51" t="str">
-        <v>あざができやすい、歯ぐきや鼻からの出血が増えていないか確認する。強い運動や転倒によるけがに注意するよう伝える</v>
+        <v>鉄分の多い食事を意識する（ヘモグロビンの項目を参照）</v>
       </c>
       <c r="K51" t="str">
-        <v>抗血小板薬・抗凝固薬使用中に血小板減少があると出血リスクがさらに高まる。抗がん剤・バルプロ酸・カルバマゼピンなど骨髄抑制のリスクがある薬剤使用中は定期採血の実施状況を確認する</v>
+        <v/>
       </c>
       <c r="L51" t="str">
-        <v>てんかん,抗血小板療法</v>
+        <v/>
       </c>
       <c r="M51" t="str">
-        <v>血小板,Plt,platelet,出血,あざ,紫斑,骨髄抑制</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="N51" t="str">
-        <v/>
+        <v>MCHC,赤血球指数,貧血</v>
+      </c>
+      <c r="O51" t="str">
+        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>RDW-SD</v>
+        <v>血小板数</v>
       </c>
       <c r="B52" t="str">
-        <v>RDW-SD</v>
+        <v>Plt</v>
       </c>
       <c r="C52" t="str">
-        <v>39〜46 fL程度（施設差あり）</v>
+        <v>15.0〜35.0万/μL程度（施設差あり）</v>
       </c>
       <c r="D52" t="str">
-        <v>赤血球の大きさのばらつきを表す指標(絶対値)。鉄欠乏性貧血などの初期変化を捉えやすい</v>
+        <v>出血を止める働きをする血液成分で、少なすぎると出血しやすくなる</v>
       </c>
       <c r="E52" t="str">
-        <v>RDW-SDは、赤血球の大きさがどれくらいバラバラになっているかを表す数値です。貧血の原因を調べる際、鉄が足りなくなり始めた早い段階での変化を捉えるのに役立ちます。</v>
+        <v>血小板は、血管が傷ついたときに集まって血を止める役割をする血液の成分です。数が少ないとあざができやすくなったり、出血が止まりにくくなったりします。抗血小板薬や抗がん剤を使っている方では、定期的にチェックすることが大切です。</v>
       </c>
       <c r="F52" t="str">
-        <v>鉄欠乏性貧血の初期、混合性貧血（複数の原因が重なっている状態）、赤血球産生の乱れ</v>
+        <v>炎症性疾患、鉄欠乏性貧血、脾摘後、骨髄増殖性疾患</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2693,42 +2847,45 @@
         <v/>
       </c>
       <c r="I52" t="str">
-        <v/>
+        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、肝硬変・脾機能亢進、再生不良性貧血、抗てんかん薬（バルプロ酸など）の副作用、ITP（特発性血小板減少性紫斑病）</v>
       </c>
       <c r="J52" t="str">
-        <v/>
+        <v>あざができやすい、歯ぐきや鼻からの出血が増えていないか確認する。強い運動や転倒によるけがに注意するよう伝える</v>
       </c>
       <c r="K52" t="str">
-        <v>MCVが正常範囲でもRDWが上昇している場合、鉄欠乏の初期段階を示唆することがある。MCV・MCHと合わせて評価する</v>
+        <v>ヘパリン(HIT: ヘパリン起因性血小板減少症)、バルプロ酸、抗がん剤、リネゾリド</v>
       </c>
       <c r="L52" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>抗血小板薬・抗凝固薬使用中に血小板減少があると出血リスクがさらに高まる。抗がん剤・バルプロ酸・カルバマゼピンなど骨髄抑制のリスクがある薬剤使用中は定期採血の実施状況を確認する</v>
       </c>
       <c r="M52" t="str">
-        <v>RDW-SD,赤血球分布幅,貧血,鉄欠乏</v>
+        <v>てんかん,抗血小板療法</v>
       </c>
       <c r="N52" t="str">
-        <v>食事と栄養 p.151-164（第2部 貧血）</v>
+        <v>血小板,Plt,platelet,出血,あざ,紫斑,骨髄抑制</v>
+      </c>
+      <c r="O52" t="str">
+        <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>RDW-CV</v>
+        <v>RDW-SD</v>
       </c>
       <c r="B53" t="str">
-        <v>RDW-CV</v>
+        <v>RDW-SD</v>
       </c>
       <c r="C53" t="str">
-        <v>11.5〜14.5%程度（施設差あり）</v>
+        <v>39〜46 fL程度（施設差あり）</v>
       </c>
       <c r="D53" t="str">
-        <v>赤血球の大きさのばらつきを割合(%)で表した指標</v>
+        <v>赤血球の大きさのばらつきを表す指標(絶対値)。鉄欠乏性貧血などの初期変化を捉えやすい</v>
       </c>
       <c r="E53" t="str">
-        <v>RDW-CVもRDW-SDと同じく、赤血球の大きさのばらつきを表す数値ですが、こちらは割合(%)で示されます。貧血のタイプを見分ける手がかりになります。</v>
+        <v>RDW-SDは、赤血球の大きさがどれくらいバラバラになっているかを表す数値です。貧血の原因を調べる際、鉄が足りなくなり始めた早い段階での変化を捉えるのに役立ちます。</v>
       </c>
       <c r="F53" t="str">
-        <v>鉄欠乏性貧血、ビタミンB12・葉酸欠乏性貧血、混合性貧血</v>
+        <v>鉄欠乏性貧血の初期、混合性貧血（複数の原因が重なっている状態）、赤血球産生の乱れ</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2743,36 +2900,39 @@
         <v/>
       </c>
       <c r="K53" t="str">
-        <v>RDW-SDと同様の意味を持つ指標。MCVが小さくRDWが高ければ鉄欠乏性貧血、MCVが大きくRDWが高ければビタミンB12・葉酸欠乏を疑う手がかりになる</v>
+        <v/>
       </c>
       <c r="L53" t="str">
+        <v>MCVが正常範囲でもRDWが上昇している場合、鉄欠乏の初期段階を示唆することがある。MCV・MCHと合わせて評価する</v>
+      </c>
+      <c r="M53" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
-      <c r="M53" t="str">
-        <v>RDW-CV,赤血球分布幅,貧血,ビタミンB12,葉酸</v>
-      </c>
       <c r="N53" t="str">
+        <v>RDW-SD,赤血球分布幅,貧血,鉄欠乏</v>
+      </c>
+      <c r="O53" t="str">
         <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>好中球実数値</v>
+        <v>RDW-CV</v>
       </c>
       <c r="B54" t="str">
-        <v>Neutro#,ANC</v>
+        <v>RDW-CV</v>
       </c>
       <c r="C54" t="str">
-        <v>2,000〜7,500 /μL程度（施設差あり、白血球数×好中球%で算出）</v>
+        <v>11.5〜14.5%程度（施設差あり）</v>
       </c>
       <c r="D54" t="str">
-        <v>好中球の絶対数。感染症リスクを判断する上で割合(%)より重要な指標</v>
+        <v>赤血球の大きさのばらつきを割合(%)で表した指標</v>
       </c>
       <c r="E54" t="str">
-        <v>これは好中球の実際の数を表す数値です。割合(%)だけでなく、実際の数がどれくらいあるかを見ることで、感染症にかかりやすい状態かどうかをより正確に判断できます。</v>
+        <v>RDW-CVもRDW-SDと同じく、赤血球の大きさのばらつきを表す数値ですが、こちらは割合(%)で示されます。貧血のタイプを見分ける手がかりになります。</v>
       </c>
       <c r="F54" t="str">
-        <v>細菌感染症、炎症、ステロイド使用</v>
+        <v>鉄欠乏性貧血、ビタミンB12・葉酸欠乏性貧血、混合性貧血</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2781,92 +2941,98 @@
         <v/>
       </c>
       <c r="I54" t="str">
-        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、メルカゾールなど薬剤性の無顆粒球症（1,000/μL未満で好中球減少症、500/μL未満で重症感染リスクが著しく上昇）</v>
+        <v/>
       </c>
       <c r="J54" t="str">
-        <v>発熱、のどの痛みなど感染症状の初期サインがないか確認する。人混みを避け、手洗い・うがいを徹底するよう伝える</v>
+        <v/>
       </c>
       <c r="K54" t="str">
-        <v>抗がん剤・メルカゾール・カルバマゼピンなど骨髄抑制のリスクがある薬剤使用中は特に重視すべき数値。500/μL未満は発熱性好中球減少症のリスクが高く緊急性が高い</v>
+        <v/>
       </c>
       <c r="L54" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>RDW-SDと同様の意味を持つ指標。MCVが小さくRDWが高ければ鉄欠乏性貧血、MCVが大きくRDWが高ければビタミンB12・葉酸欠乏を疑う手がかりになる</v>
       </c>
       <c r="M54" t="str">
-        <v>好中球実数値,好中球数,ANC,無顆粒球症,発熱性好中球減少症</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="N54" t="str">
-        <v/>
+        <v>RDW-CV,赤血球分布幅,貧血,ビタミンB12,葉酸</v>
+      </c>
+      <c r="O54" t="str">
+        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>好酸球実数値</v>
+        <v>好中球実数値</v>
       </c>
       <c r="B55" t="str">
-        <v>Eosino#</v>
+        <v>Neutro#,ANC</v>
       </c>
       <c r="C55" t="str">
-        <v>100〜500 /μL程度（施設差あり）</v>
+        <v>2,000〜7,500 /μL程度（施設差あり、白血球数×好中球%で算出）</v>
       </c>
       <c r="D55" t="str">
-        <v>好酸球の絶対数。アレルギーや薬剤反応の程度をより正確に評価できる</v>
+        <v>好中球の絶対数。感染症リスクを判断する上で割合(%)より重要な指標</v>
       </c>
       <c r="E55" t="str">
-        <v>これは好酸球の実際の数を表す数値です。割合(%)だけでなく実数を見ることで、アレルギー反応の強さをより正確に把握できます。</v>
+        <v>これは好中球の実際の数を表す数値です。割合(%)だけでなく、実際の数がどれくらいあるかを見ることで、感染症にかかりやすい状態かどうかをより正確に判断できます。</v>
       </c>
       <c r="F55" t="str">
-        <v>アレルギー性疾患、薬剤アレルギー、寄生虫感染</v>
+        <v>細菌感染症、炎症、ステロイド使用</v>
       </c>
       <c r="G55" t="str">
-        <v>新しく始めた薬がないか確認する</v>
+        <v/>
       </c>
       <c r="H55" t="str">
-        <v>薬剤性好酸球増多(抗菌薬・NSAIDs・抗てんかん薬など)。発熱や皮疹を伴う場合はDRESS症候群にも注意</v>
+        <v/>
       </c>
       <c r="I55" t="str">
-        <v/>
+        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、メルカゾールなど薬剤性の無顆粒球症（1,000/μL未満で好中球減少症、500/μL未満で重症感染リスクが著しく上昇）</v>
       </c>
       <c r="J55" t="str">
-        <v/>
+        <v>発熱、のどの痛みなど感染症状の初期サインがないか確認する。人混みを避け、手洗い・うがいを徹底するよう伝える</v>
       </c>
       <c r="K55" t="str">
-        <v>薬剤性過敏症症候群(DIHS)などでは著明な好酸球増多を認めることがあり、原因薬剤の特定に役立つ</v>
+        <v>抗がん剤、メルカゾール(無顆粒球症)、クロザピン、サラゾスルファピリジン</v>
       </c>
       <c r="L55" t="str">
+        <v>抗がん剤・メルカゾール・カルバマゼピンなど骨髄抑制のリスクがある薬剤使用中は特に重視すべき数値。500/μL未満は発熱性好中球減少症のリスクが高く緊急性が高い</v>
+      </c>
+      <c r="M55" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
-      <c r="M55" t="str">
-        <v>好酸球実数値,好酸球数,アレルギー,DIHS</v>
-      </c>
       <c r="N55" t="str">
+        <v>好中球実数値,好中球数,ANC,無顆粒球症,発熱性好中球減少症</v>
+      </c>
+      <c r="O55" t="str">
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>好塩基球実数値</v>
+        <v>好酸球実数値</v>
       </c>
       <c r="B56" t="str">
-        <v>Baso#</v>
+        <v>Eosino#</v>
       </c>
       <c r="C56" t="str">
-        <v>0〜100 /μL程度（施設差あり）</v>
+        <v>100〜500 /μL程度（施設差あり）</v>
       </c>
       <c r="D56" t="str">
-        <v>好塩基球の絶対数</v>
+        <v>好酸球の絶対数。アレルギーや薬剤反応の程度をより正確に評価できる</v>
       </c>
       <c r="E56" t="str">
-        <v>これは好塩基球の実際の数を表す数値です。数がとても少ない種類の血球なので、通常は大きな変動を示すことは多くありません。</v>
+        <v>これは好酸球の実際の数を表す数値です。割合(%)だけでなく実数を見ることで、アレルギー反応の強さをより正確に把握できます。</v>
       </c>
       <c r="F56" t="str">
-        <v>慢性骨髄性白血病などの血液疾患、アレルギー性疾患</v>
+        <v>アレルギー性疾患、薬剤アレルギー、寄生虫感染</v>
       </c>
       <c r="G56" t="str">
-        <v/>
+        <v>新しく始めた薬がないか確認する</v>
       </c>
       <c r="H56" t="str">
-        <v/>
+        <v>薬剤性好酸球増多(抗菌薬・NSAIDs・抗てんかん薬など)。発熱や皮疹を伴う場合はDRESS症候群にも注意</v>
       </c>
       <c r="I56" t="str">
         <v/>
@@ -2875,36 +3041,39 @@
         <v/>
       </c>
       <c r="K56" t="str">
-        <v>単独での臨床的意義は乏しく、他の血球指標（白血球分画全体）と合わせて評価する</v>
+        <v/>
       </c>
       <c r="L56" t="str">
+        <v>薬剤性過敏症症候群(DIHS)などでは著明な好酸球増多を認めることがあり、原因薬剤の特定に役立つ</v>
+      </c>
+      <c r="M56" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
-      <c r="M56" t="str">
-        <v>好塩基球実数値,好塩基球数</v>
-      </c>
       <c r="N56" t="str">
+        <v>好酸球実数値,好酸球数,アレルギー,DIHS</v>
+      </c>
+      <c r="O56" t="str">
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>リンパ球実数値</v>
+        <v>好塩基球実数値</v>
       </c>
       <c r="B57" t="str">
-        <v>Lympho#,ALC</v>
+        <v>Baso#</v>
       </c>
       <c r="C57" t="str">
-        <v>1,000〜3,600 /μL程度（施設差あり）</v>
+        <v>0〜100 /μL程度（施設差あり）</v>
       </c>
       <c r="D57" t="str">
-        <v>リンパ球の絶対数。免疫力の目安として使われる</v>
+        <v>好塩基球の絶対数</v>
       </c>
       <c r="E57" t="str">
-        <v>これはリンパ球の実際の数を表す数値です。免疫力の目安の一つとして使われ、抗がん剤や免疫抑制剤の副作用モニタリングにも用いられます。</v>
+        <v>これは好塩基球の実際の数を表す数値です。数がとても少ない種類の血球なので、通常は大きな変動を示すことは多くありません。</v>
       </c>
       <c r="F57" t="str">
-        <v>ウイルス感染症、リンパ性白血病などの血液疾患</v>
+        <v>慢性骨髄性白血病などの血液疾患、アレルギー性疾患</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2913,42 +3082,45 @@
         <v/>
       </c>
       <c r="I57" t="str">
-        <v>抗がん剤・免疫抑制剤・ステロイドの使用、強いストレス、AIDSなどの免疫不全</v>
+        <v/>
       </c>
       <c r="J57" t="str">
-        <v>感染予防（手洗い・うがい、人混みを避ける）を意識するよう伝える</v>
+        <v/>
       </c>
       <c r="K57" t="str">
-        <v>免疫抑制剤・抗がん剤治療中のモニタリング指標としても使われる。著明な低下時は日和見感染のリスクが高まる</v>
+        <v/>
       </c>
       <c r="L57" t="str">
+        <v>単独での臨床的意義は乏しく、他の血球指標（白血球分画全体）と合わせて評価する</v>
+      </c>
+      <c r="M57" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
-      <c r="M57" t="str">
-        <v>リンパ球実数値,リンパ球数,ALC,免疫抑制剤,日和見感染</v>
-      </c>
       <c r="N57" t="str">
+        <v>好塩基球実数値,好塩基球数</v>
+      </c>
+      <c r="O57" t="str">
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>単球実数値</v>
+        <v>リンパ球実数値</v>
       </c>
       <c r="B58" t="str">
-        <v>Mono#</v>
+        <v>Lympho#,ALC</v>
       </c>
       <c r="C58" t="str">
-        <v>200〜600 /μL程度（施設差あり）</v>
+        <v>1,000〜3,600 /μL程度（施設差あり）</v>
       </c>
       <c r="D58" t="str">
-        <v>単球の絶対数</v>
+        <v>リンパ球の絶対数。免疫力の目安として使われる</v>
       </c>
       <c r="E58" t="str">
-        <v>これは単球の実際の数を表す数値です。慢性的な炎症や感染症の状態を把握する材料の一つになります。</v>
+        <v>これはリンパ球の実際の数を表す数値です。免疫力の目安の一つとして使われ、抗がん剤や免疫抑制剤の副作用モニタリングにも用いられます。</v>
       </c>
       <c r="F58" t="str">
-        <v>慢性感染症、炎症性疾患、血液疾患</v>
+        <v>ウイルス感染症、リンパ性白血病などの血液疾患</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2957,136 +3129,145 @@
         <v/>
       </c>
       <c r="I58" t="str">
-        <v/>
+        <v>抗がん剤・免疫抑制剤・ステロイドの使用、強いストレス、AIDSなどの免疫不全</v>
       </c>
       <c r="J58" t="str">
-        <v/>
+        <v>感染予防（手洗い・うがい、人混みを避ける）を意識するよう伝える</v>
       </c>
       <c r="K58" t="str">
-        <v>単独での臨床的意義は乏しく、他の血球指標と合わせて評価する</v>
+        <v/>
       </c>
       <c r="L58" t="str">
+        <v>免疫抑制剤・抗がん剤治療中のモニタリング指標としても使われる。著明な低下時は日和見感染のリスクが高まる</v>
+      </c>
+      <c r="M58" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
-      <c r="M58" t="str">
-        <v>単球実数値,単球数</v>
-      </c>
       <c r="N58" t="str">
+        <v>リンパ球実数値,リンパ球数,ALC,免疫抑制剤,日和見感染</v>
+      </c>
+      <c r="O58" t="str">
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>好中球</v>
+        <v>単球実数値</v>
       </c>
       <c r="B59" t="str">
-        <v>Neutro,Neut%</v>
+        <v>Mono#</v>
       </c>
       <c r="C59" t="str">
-        <v>40〜75%程度（施設差あり）</v>
+        <v>200〜600 /μL程度（施設差あり）</v>
       </c>
       <c r="D59" t="str">
-        <v>白血球の中で最も多くを占め、細菌感染と戦う主力の免疫細胞の割合</v>
+        <v>単球の絶対数</v>
       </c>
       <c r="E59" t="str">
-        <v>好中球は、白血球の中で最も数が多く、細菌が体に入ってきたときに真っ先に戦ってくれる免疫細胞です。感染症や炎症があると増え、逆に薬の副作用などで減ることがあります。</v>
+        <v>これは単球の実際の数を表す数値です。慢性的な炎症や感染症の状態を把握する材料の一つになります。</v>
       </c>
       <c r="F59" t="str">
-        <v>細菌感染症、炎症、ストレス、ステロイド使用</v>
+        <v>慢性感染症、炎症性疾患、血液疾患</v>
       </c>
       <c r="G59" t="str">
-        <v>発熱や炎症症状がないか確認する</v>
+        <v/>
       </c>
       <c r="H59" t="str">
         <v/>
       </c>
       <c r="I59" t="str">
-        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、ウイルス感染、メルカゾールなど薬剤性の無顆粒球症</v>
+        <v/>
       </c>
       <c r="J59" t="str">
-        <v>発熱やのどの痛みなど感染症状の初期サインがないか確認する</v>
+        <v/>
       </c>
       <c r="K59" t="str">
-        <v>好中球の絶対数（好中球実数値）が500/μL未満になると重篤な感染症のリスクが高まる。割合(%)だけでなく実数値も合わせて確認する</v>
+        <v/>
       </c>
       <c r="L59" t="str">
+        <v>単独での臨床的意義は乏しく、他の血球指標と合わせて評価する</v>
+      </c>
+      <c r="M59" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
-      <c r="M59" t="str">
-        <v>好中球,Neutro,Neut,感染症,無顆粒球症</v>
-      </c>
       <c r="N59" t="str">
+        <v>単球実数値,単球数</v>
+      </c>
+      <c r="O59" t="str">
         <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>好酸球</v>
+        <v>好中球</v>
       </c>
       <c r="B60" t="str">
-        <v>Eosino,Eos%</v>
+        <v>Neutro,Neut%</v>
       </c>
       <c r="C60" t="str">
-        <v>1〜5%程度（施設差あり）</v>
+        <v>40〜75%程度（施設差あり）</v>
       </c>
       <c r="D60" t="str">
-        <v>アレルギー反応や寄生虫感染に関わる白血球の一種の割合</v>
+        <v>白血球の中で最も多くを占め、細菌感染と戦う主力の免疫細胞の割合</v>
       </c>
       <c r="E60" t="str">
-        <v>好酸球は、アレルギー反応や寄生虫感染と関係が深い免疫細胞です。アレルギー性の病気や薬の副作用（薬疹など）で増えることがあります。</v>
+        <v>好中球は、白血球の中で最も数が多く、細菌が体に入ってきたときに真っ先に戦ってくれる免疫細胞です。感染症や炎症があると増え、逆に薬の副作用などで減ることがあります。</v>
       </c>
       <c r="F60" t="str">
-        <v>アレルギー性疾患（気管支喘息、アトピー性皮膚炎など）、薬剤アレルギー、寄生虫感染</v>
+        <v>細菌感染症、炎症、ストレス、ステロイド使用</v>
       </c>
       <c r="G60" t="str">
-        <v>新しく始めた薬がないか確認する。皮疹やかゆみなどアレルギー症状の有無を確認する</v>
+        <v>発熱や炎症症状がないか確認する</v>
       </c>
       <c r="H60" t="str">
-        <v>薬剤性好酸球増多(抗菌薬・NSAIDs・抗てんかん薬など)。発熱や皮疹を伴う場合はDRESS症候群にも注意</v>
+        <v/>
       </c>
       <c r="I60" t="str">
-        <v/>
+        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、ウイルス感染、メルカゾールなど薬剤性の無顆粒球症</v>
       </c>
       <c r="J60" t="str">
-        <v/>
+        <v>発熱やのどの痛みなど感染症状の初期サインがないか確認する</v>
       </c>
       <c r="K60" t="str">
-        <v>薬剤性の好酸球増多は、原因薬剤の中止で改善することが多い。新規薬剤開始後の皮疹・発熱と合わせて薬剤性過敏症症候群(DIHS)を疑う材料になる</v>
+        <v>抗がん剤、メルカゾール(無顆粒球症)、クロザピン、サラゾスルファピリジン</v>
       </c>
       <c r="L60" t="str">
+        <v>好中球の絶対数（好中球実数値）が500/μL未満になると重篤な感染症のリスクが高まる。割合(%)だけでなく実数値も合わせて確認する</v>
+      </c>
+      <c r="M60" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
-      <c r="M60" t="str">
-        <v>好酸球,Eosino,Eos,アレルギー,薬疹,DIHS</v>
-      </c>
       <c r="N60" t="str">
+        <v>好中球,Neutro,Neut,感染症,無顆粒球症</v>
+      </c>
+      <c r="O60" t="str">
         <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>好塩基球</v>
+        <v>好酸球</v>
       </c>
       <c r="B61" t="str">
-        <v>Baso,Baso%</v>
+        <v>Eosino,Eos%</v>
       </c>
       <c r="C61" t="str">
-        <v>0〜2%程度（施設差あり）</v>
+        <v>1〜5%程度（施設差あり）</v>
       </c>
       <c r="D61" t="str">
-        <v>白血球の中で最も数が少なく、アレルギー反応に関わる細胞の割合</v>
+        <v>アレルギー反応や寄生虫感染に関わる白血球の一種の割合</v>
       </c>
       <c r="E61" t="str">
-        <v>好塩基球は白血球の中で最も数が少ない種類で、アレルギー反応や炎症に関わっています。数値の変動が病気の診断に直接使われることは少ない検査です。</v>
+        <v>好酸球は、アレルギー反応や寄生虫感染と関係が深い免疫細胞です。アレルギー性の病気や薬の副作用（薬疹など）で増えることがあります。</v>
       </c>
       <c r="F61" t="str">
-        <v>慢性骨髄性白血病などの血液疾患、アレルギー性疾患、甲状腺機能低下症</v>
+        <v>アレルギー性疾患（気管支喘息、アトピー性皮膚炎など）、薬剤アレルギー、寄生虫感染</v>
       </c>
       <c r="G61" t="str">
-        <v/>
+        <v>新しく始めた薬がないか確認する。皮疹やかゆみなどアレルギー症状の有無を確認する</v>
       </c>
       <c r="H61" t="str">
-        <v/>
+        <v>薬剤性好酸球増多(抗菌薬・NSAIDs・抗てんかん薬など)。発熱や皮疹を伴う場合はDRESS症候群にも注意</v>
       </c>
       <c r="I61" t="str">
         <v/>
@@ -3095,36 +3276,39 @@
         <v/>
       </c>
       <c r="K61" t="str">
-        <v>単独での臨床的意義は乏しいが、著明な増加は血液疾患（慢性骨髄性白血病等）の可能性があり他の血球指標と合わせて評価する</v>
+        <v/>
       </c>
       <c r="L61" t="str">
+        <v>薬剤性の好酸球増多は、原因薬剤の中止で改善することが多い。新規薬剤開始後の皮疹・発熱と合わせて薬剤性過敏症症候群(DIHS)を疑う材料になる</v>
+      </c>
+      <c r="M61" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
-      <c r="M61" t="str">
-        <v>好塩基球,Baso,アレルギー,白血病</v>
-      </c>
       <c r="N61" t="str">
+        <v>好酸球,Eosino,Eos,アレルギー,薬疹,DIHS</v>
+      </c>
+      <c r="O61" t="str">
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>リンパ球</v>
+        <v>好塩基球</v>
       </c>
       <c r="B62" t="str">
-        <v>Lympho,Lym%</v>
+        <v>Baso,Baso%</v>
       </c>
       <c r="C62" t="str">
-        <v>18〜49%程度（施設差あり）</v>
+        <v>0〜2%程度（施設差あり）</v>
       </c>
       <c r="D62" t="str">
-        <v>ウイルス感染と戦い、免疫の記憶を担う白血球の割合</v>
+        <v>白血球の中で最も数が少なく、アレルギー反応に関わる細胞の割合</v>
       </c>
       <c r="E62" t="str">
-        <v>リンパ球は、ウイルスと戦ったり、一度かかった病気を記憶して免疫をつくったりする細胞です。ウイルス感染で増え、抗がん剤の副作用や強いストレスで減ることがあります。</v>
+        <v>好塩基球は白血球の中で最も数が少ない種類で、アレルギー反応や炎症に関わっています。数値の変動が病気の診断に直接使われることは少ない検査です。</v>
       </c>
       <c r="F62" t="str">
-        <v>ウイルス感染症、リンパ性白血病などの血液疾患、百日咳</v>
+        <v>慢性骨髄性白血病などの血液疾患、アレルギー性疾患、甲状腺機能低下症</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -3133,42 +3317,45 @@
         <v/>
       </c>
       <c r="I62" t="str">
-        <v>抗がん剤・免疫抑制剤・ステロイドの使用、強いストレス、AIDSなどの免疫不全</v>
+        <v/>
       </c>
       <c r="J62" t="str">
-        <v>免疫が下がっている可能性があるため、感染予防（手洗い・うがい、人混みを避ける）を意識するよう伝える</v>
+        <v/>
       </c>
       <c r="K62" t="str">
-        <v>ステロイド・免疫抑制剤使用中はリンパ球減少による易感染性に注意。好中球と逆方向に動くことが多い（ウイルス感染ではリンパ球優位、細菌感染では好中球優位になりやすい）</v>
+        <v/>
       </c>
       <c r="L62" t="str">
+        <v>単独での臨床的意義は乏しいが、著明な増加は血液疾患（慢性骨髄性白血病等）の可能性があり他の血球指標と合わせて評価する</v>
+      </c>
+      <c r="M62" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
-      <c r="M62" t="str">
-        <v>リンパ球,Lympho,Lym,ウイルス感染,免疫抑制剤,ステロイド</v>
-      </c>
       <c r="N62" t="str">
+        <v>好塩基球,Baso,アレルギー,白血病</v>
+      </c>
+      <c r="O62" t="str">
         <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>単球</v>
+        <v>リンパ球</v>
       </c>
       <c r="B63" t="str">
-        <v>Mono,Mono%</v>
+        <v>Lympho,Lym%</v>
       </c>
       <c r="C63" t="str">
-        <v>2〜10%程度（施設差あり）</v>
+        <v>18〜49%程度（施設差あり）</v>
       </c>
       <c r="D63" t="str">
-        <v>感染や炎症の後始末をする白血球の一種の割合</v>
+        <v>ウイルス感染と戦い、免疫の記憶を担う白血球の割合</v>
       </c>
       <c r="E63" t="str">
-        <v>単球は、細菌などを取り込んで処理したり、組織の修復に関わったりする免疫細胞です。慢性的な炎症や感染症の回復期に増えることがあります。</v>
+        <v>リンパ球は、ウイルスと戦ったり、一度かかった病気を記憶して免疫をつくったりする細胞です。ウイルス感染で増え、抗がん剤の副作用や強いストレスで減ることがあります。</v>
       </c>
       <c r="F63" t="str">
-        <v>慢性感染症（結核など）、炎症性疾患、血液疾患、感染症の回復期</v>
+        <v>ウイルス感染症、リンパ性白血病などの血液疾患、百日咳</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -3177,133 +3364,142 @@
         <v/>
       </c>
       <c r="I63" t="str">
-        <v/>
+        <v>抗がん剤・免疫抑制剤・ステロイドの使用、強いストレス、AIDSなどの免疫不全</v>
       </c>
       <c r="J63" t="str">
-        <v/>
+        <v>免疫が下がっている可能性があるため、感染予防（手洗い・うがい、人混みを避ける）を意識するよう伝える</v>
       </c>
       <c r="K63" t="str">
-        <v>単独での臨床的意義は乏しく、他の血球指標や炎症マーカー(CRPなど)と合わせて評価する</v>
+        <v/>
       </c>
       <c r="L63" t="str">
+        <v>ステロイド・免疫抑制剤使用中はリンパ球減少による易感染性に注意。好中球と逆方向に動くことが多い（ウイルス感染ではリンパ球優位、細菌感染では好中球優位になりやすい）</v>
+      </c>
+      <c r="M63" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
-      <c r="M63" t="str">
-        <v>単球,Mono,慢性感染症,結核,炎症</v>
-      </c>
       <c r="N63" t="str">
+        <v>リンパ球,Lympho,Lym,ウイルス感染,免疫抑制剤,ステロイド</v>
+      </c>
+      <c r="O63" t="str">
         <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>PT-INR（プロトロンビン時間国際標準比）</v>
+        <v>単球</v>
       </c>
       <c r="B64" t="str">
-        <v>PT-INR,INR</v>
+        <v>Mono,Mono%</v>
       </c>
       <c r="C64" t="str">
-        <v>治療域の目安 1.6〜3.0（ワルファリン服用時。年齢・疾患により異なる）</v>
+        <v>2〜10%程度（施設差あり）</v>
       </c>
       <c r="D64" t="str">
-        <v>血液の固まりやすさを表す数値で、ワルファリンの効き具合を確認するために使う</v>
+        <v>感染や炎症の後始末をする白血球の一種の割合</v>
       </c>
       <c r="E64" t="str">
-        <v>PT-INRは血液が固まるまでの時間をもとにした数値で、ワルファリンというお薬を飲んでいる方の効き具合を確認するために測ります。数値が高いほど血液が固まりにくく出血しやすい状態、低いほど血栓ができやすい状態を示します。</v>
+        <v>単球は、細菌などを取り込んで処理したり、組織の修復に関わったりする免疫細胞です。慢性的な炎症や感染症の回復期に増えることがあります。</v>
       </c>
       <c r="F64" t="str">
-        <v>ワルファリンの効きすぎ、肝機能低下、ビタミンK不足、納豆・青汁など摂取量の変化</v>
+        <v>慢性感染症（結核など）、炎症性疾患、血液疾患、感染症の回復期</v>
       </c>
       <c r="G64" t="str">
-        <v>歯ぐきや鼻からの出血、あざ、黒い便などの出血症状がないか確認する。納豆・クロレラ・青汁などビタミンKを多く含む食品の摂取状況を確認する</v>
+        <v/>
       </c>
       <c r="H64" t="str">
-        <v>ワルファリンの過量。ワルファリン服用中はST合剤・マクロライド系・フルコナゾール等の相互作用やビタミンK摂取量の変化にも注意</v>
+        <v/>
       </c>
       <c r="I64" t="str">
-        <v>ワルファリンの効き不足、飲み忘れ、ビタミンK摂取量の急激な増加</v>
+        <v/>
       </c>
       <c r="J64" t="str">
-        <v>服薬状況（飲み忘れ）を確認する。片側のむくみ・しびれ・胸痛など血栓症状がないか確認する</v>
+        <v/>
       </c>
       <c r="K64" t="str">
-        <v>治療域は疾患・年齢によって異なる（例：非弁膜症性心房細動の高齢者では1.6〜2.6が目安になることが多い）。多くの薬剤・食品と相互作用があるため新規薬剤追加時は必ず確認する。DOAC（エリキュース、リクシアナ、プラザキサなど）ではPT-INRのモニタリングは不要</v>
+        <v/>
       </c>
       <c r="L64" t="str">
-        <v>抗凝固療法（心房細動・血栓症）</v>
+        <v>単独での臨床的意義は乏しく、他の血球指標や炎症マーカー(CRPなど)と合わせて評価する</v>
       </c>
       <c r="M64" t="str">
-        <v>PT-INR,INR,プロトロンビン時間,ワルファリン,ワーファリン,抗凝固</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N64" t="str">
-        <v>食事と栄養 p.221（心疾患Q93 ワルファリン服用中のビタミンK摂取）</v>
+        <v>単球,Mono,慢性感染症,結核,炎症</v>
+      </c>
+      <c r="O64" t="str">
+        <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Dダイマー</v>
+        <v>C反応性蛋白（CRP）</v>
       </c>
       <c r="B65" t="str">
-        <v>D-dimer</v>
+        <v>CRP</v>
       </c>
       <c r="C65" t="str">
-        <v>1.0 μg/mL以下(施設・測定法により異なる)</v>
+        <v>0.3 mg/dL未満（施設差あり）</v>
       </c>
       <c r="D65" t="str">
-        <v>体の中で血栓ができて溶けた(線溶)ときにできる分解産物で、血栓症の有無をスクリーニングする指標</v>
+        <v>体のどこかに炎症や感染が起きていないかを鋭敏に反映する数値</v>
       </c>
       <c r="E65" t="str">
-        <v>Dダイマーは、血管の中に血のかたまり(血栓)ができて、それが溶かされるときにできる物質です。この数値が高いと、どこかに血栓ができている可能性を考えます。ただし手術後や妊娠中、高齢の方などでも上がることがあるため、この数値だけで診断が決まるわけではありません。</v>
+        <v>CRPは、体に炎症や感染が起きると数時間〜半日程度で急激に上昇する数値です。風邪のようなウイルス感染から細菌感染、体のどこかの炎症まで、幅広く反応するため、体調の変化を早期に捉える手がかりになります。</v>
       </c>
       <c r="F65" t="str">
-        <v>深部静脈血栓症(DVT)・肺血栓塞栓症(PE)、播種性血管内凝固症候群(DIC)、大動脈解離、悪性腫瘍、手術後、妊娠、高齢、感染・炎症</v>
+        <v>細菌感染症、ウイルス感染症、自己免疫疾患（関節リウマチなど）、悪性腫瘍、組織の損傷（術後・心筋梗塞など）</v>
       </c>
       <c r="G65" t="str">
-        <v>ふくらはぎの腫れ・痛み、急な息切れ・胸痛など血栓症を疑う症状がないか確認する</v>
+        <v>発熱、痛み、腫れなど炎症症状の有無を確認する</v>
       </c>
       <c r="H65" t="str">
-        <v>経口避妊薬・ホルモン補充療法は血栓リスクを高める。逆にワルファリン・DOAC・ヘパリンなど抗凝固薬の効果不十分で血栓が進行している可能性にも注意</v>
+        <v/>
       </c>
       <c r="I65" t="str">
-        <v>通常、臨床的意義は乏しい(基準値以下であれば血栓症の可能性は低いとする除外診断に有用)</v>
+        <v/>
       </c>
       <c r="J65" t="str">
         <v/>
       </c>
       <c r="K65" t="str">
-        <v>陰性的中率が高く、基準値以下であれば静脈血栓塞栓症(VTE)の可能性は低いとする除外診断への活用が臨床的に重要。一方で偽陽性が多く、高値のみで血栓症と確定はできない。抗凝固療法中のモニタリングそのものには通常用いない(効果判定はPT-INR/APTT等)</v>
+        <v/>
       </c>
       <c r="L65" t="str">
-        <v>抗凝固療法（心房細動・血栓症）</v>
+        <v>白血球数と合わせて感染・炎症の程度を評価する。上昇・低下のタイミングは白血球より半日〜1日程度遅れる傾向があるため、経過を追う際は採血のタイミングに注意</v>
       </c>
       <c r="M65" t="str">
-        <v>Dダイマー,D-dimer,血栓,DVT,深部静脈血栓症,肺塞栓,DIC</v>
+        <v/>
       </c>
       <c r="N65" t="str">
+        <v>CRP,炎症,感染</v>
+      </c>
+      <c r="O65" t="str">
         <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>C反応性蛋白（CRP）</v>
+        <v>骨型酒石酸抵抗性フォスファターゼ（TRACP-5b）</v>
       </c>
       <c r="B66" t="str">
-        <v>CRP</v>
+        <v>TRACP-5b</v>
       </c>
       <c r="C66" t="str">
-        <v>0.3 mg/dL未満（施設差あり）</v>
+        <v>120〜420 mU/dL</v>
       </c>
       <c r="D66" t="str">
-        <v>体のどこかに炎症や感染が起きていないかを鋭敏に反映する数値</v>
+        <v>骨がどれくらい壊されているかを見る検査。骨は「古い骨を壊して新しい骨を作る」入れ替えを繰り返しており、骨を壊す細胞が活発だとこの物質が血液中に増える。</v>
       </c>
       <c r="E66" t="str">
-        <v>CRPは、体に炎症や感染が起きると数時間〜半日程度で急激に上昇する数値です。風邪のようなウイルス感染から細菌感染、体のどこかの炎症まで、幅広く反応するため、体調の変化を早期に捉える手がかりになります。</v>
+        <v>この検査は、骨がどれくらい早く減っていないかを見るものです。数値が高いと、骨が弱くなりやすい状態の目安になります。</v>
       </c>
       <c r="F66" t="str">
-        <v>細菌感染症、ウイルス感染症、自己免疫疾患（関節リウマチなど）、悪性腫瘍、組織の損傷（術後・心筋梗塞など）</v>
+        <v>骨粗鬆症、骨代謝回転（骨がこわれるスピード）が活発な状態</v>
       </c>
       <c r="G66" t="str">
-        <v>発熱、痛み、腫れなど炎症症状の有無を確認する</v>
+        <v>カルシウム・ビタミンDの摂取や、適度な荷重運動（ウォーキングなど）を意識するよう伝える</v>
       </c>
       <c r="H66" t="str">
         <v/>
@@ -3315,86 +3511,92 @@
         <v/>
       </c>
       <c r="K66" t="str">
-        <v>白血球数と合わせて感染・炎症の程度を評価する。上昇・低下のタイミングは白血球より半日〜1日程度遅れる傾向があるため、経過を追う際は採血のタイミングに注意</v>
+        <v/>
       </c>
       <c r="L66" t="str">
-        <v/>
+        <v>「骨を壊す側」の指標。「骨を作る側」の検査と合わせて評価する。数値だけで診断はしない</v>
       </c>
       <c r="M66" t="str">
-        <v>CRP,炎症,感染</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="N66" t="str">
+        <v>TRACP-5b,骨型酒石酸抵抗性フォスファターゼ,骨粗鬆症,骨代謝</v>
+      </c>
+      <c r="O66" t="str">
         <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>骨密度</v>
+        <v>PT-INR（プロトロンビン時間国際標準比）</v>
       </c>
       <c r="B67" t="str">
-        <v>BMD,骨密度</v>
+        <v>PT-INR,INR</v>
       </c>
       <c r="C67" t="str">
-        <v>YAM(若年成人平均値)80%以上:正常、70%以上80%未満:骨量減少、70%未満:骨粗鬆症</v>
+        <v>治療域の目安 1.6〜3.0（ワルファリン服用時。年齢・疾患により異なる）</v>
       </c>
       <c r="D67" t="str">
-        <v>骨の中にカルシウムなどのミネラルがどれだけ詰まっているかを示す指標。20〜44歳の平均値(YAM)に対する割合(%)で評価する</v>
+        <v>血液の固まりやすさを表す数値で、ワルファリンの効き具合を確認するために使う</v>
       </c>
       <c r="E67" t="str">
-        <v>骨密度は、骨の中にカルシウムなどのミネラルがどれだけしっかり詰まっているかを表す数値です。20〜44歳の若い方の平均値を100%として、ご自身の骨密度が何%かで示されます。70%未満になると「骨粗鬆症」と診断され、骨折しやすい状態と考えられます。</v>
+        <v>PT-INRは血液が固まるまでの時間をもとにした数値で、ワルファリンというお薬を飲んでいる方の効き具合を確認するために測ります。数値が高いほど血液が固まりにくく出血しやすい状態、低いほど血栓ができやすい状態を示します。</v>
       </c>
       <c r="F67" t="str">
-        <v>基本的に問題になることは少ない(まれに骨硬化症などの疾患)</v>
+        <v>ワルファリンの効きすぎ、肝機能低下、ビタミンK不足、納豆・青汁など摂取量の変化</v>
       </c>
       <c r="G67" t="str">
-        <v/>
+        <v>歯ぐきや鼻からの出血、あざ、黒い便などの出血症状がないか確認する。納豆・クロレラ・青汁などビタミンKを多く含む食品の摂取状況を確認する</v>
       </c>
       <c r="H67" t="str">
-        <v/>
+        <v>ワルファリンの過量。ワルファリン服用中はST合剤・マクロライド系・フルコナゾール等の相互作用やビタミンK摂取量の変化にも注意</v>
       </c>
       <c r="I67" t="str">
-        <v>骨粗鬆症、加齢による骨量減少、閉経後のエストロゲン低下、ステロイド長期使用、カルシウム・ビタミンD不足、運動不足、るいそう</v>
+        <v>ワルファリンの効き不足、飲み忘れ、ビタミンK摂取量の急激な増加</v>
       </c>
       <c r="J67" t="str">
-        <v>カルシウム・ビタミンD・ビタミンKを意識した食事、荷重運動(ウォーキング等)を勧める。ステロイド長期服用中の場合は骨粗鬆症治療薬の併用が検討されているか確認する</v>
+        <v>服薬状況（飲み忘れ）を確認する。片側のむくみ・しびれ・胸痛など血栓症状がないか確認する</v>
       </c>
       <c r="K67" t="str">
-        <v>YAM70%未満、または既存の脆弱性骨折がある場合に骨粗鬆症と診断され薬物治療の対象となる(日本骨粗鬆症学会・日本骨代謝学会・厚生労働省合同「原発性骨粗鬆症の診断基準 2012年度改訂版」)。ビスホスホネート製剤は起床時空腹時に十分な水(180mL程度)で服用し、服用後30分は横にならないよう指導する。ステロイドを長期服用中の患者は骨密度によらず骨粗鬆症治療薬の併用が推奨される場合がある(グルココルチコイド誘発性骨粗鬆症: GIOP)</v>
+        <v>ワルファリン服用中で低値の場合は効果不十分の可能性。ビタミンK摂取量の変化や、リファンピシン・カルバマゼピン・バルビツール酸系など代謝を促進する薬との併用を確認</v>
       </c>
       <c r="L67" t="str">
-        <v>骨粗鬆症</v>
+        <v>治療域は疾患・年齢によって異なる（例：非弁膜症性心房細動の高齢者では1.6〜2.6が目安になることが多い）。多くの薬剤・食品と相互作用があるため新規薬剤追加時は必ず確認する。DOAC（エリキュース、リクシアナ、プラザキサなど）ではPT-INRのモニタリングは不要</v>
       </c>
       <c r="M67" t="str">
-        <v>骨密度,BMD,YAM,若年成人平均値,骨粗鬆症,DXA</v>
+        <v>抗凝固療法（心房細動・血栓症）</v>
       </c>
       <c r="N67" t="str">
-        <v/>
+        <v>PT-INR,INR,プロトロンビン時間,ワルファリン,ワーファリン,抗凝固</v>
+      </c>
+      <c r="O67" t="str">
+        <v>食事と栄養 p.221（心疾患Q93 ワルファリン服用中のビタミンK摂取）</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>骨型酒石酸抵抗性フォスファターゼ（TRACP-5b）</v>
+        <v>尿蛋白定量</v>
       </c>
       <c r="B68" t="str">
-        <v>TRACP-5b</v>
+        <v>U-Pro定量,蛋白/Cr比</v>
       </c>
       <c r="C68" t="str">
-        <v>120〜420 mU/dL</v>
+        <v>0.15 g/gCr未満</v>
       </c>
       <c r="D68" t="str">
-        <v>骨がどれくらい壊されているかを見る検査。骨は「古い骨を壊して新しい骨を作る」入れ替えを繰り返しており、骨を壊す細胞が活発だとこの物質が血液中に増える。</v>
+        <v>随時尿から尿蛋白の量を具体的な数値として評価する検査。ネフローゼ等の重症度判定に使う</v>
       </c>
       <c r="E68" t="str">
-        <v>この検査は、骨がどれくらい早く減っていないかを見るものです。数値が高いと、骨が弱くなりやすい状態の目安になります。</v>
+        <v>これは、尿に出ているたんぱくの量を具体的な数値で見る検査です。試験紙での陽性・陰性の判定だけでなく、実際にどれくらいの量が出ているかを把握できます。</v>
       </c>
       <c r="F68" t="str">
-        <v>骨粗鬆症、骨代謝回転（骨がこわれるスピード）が活発な状態</v>
+        <v>腎症の進行（糖尿病性腎症、慢性腎臓病など）、ネフローゼ症候群（3.5 g/gCr以上が目安）</v>
       </c>
       <c r="G68" t="str">
-        <v>カルシウム・ビタミンDの摂取や、適度な荷重運動（ウォーキングなど）を意識するよう伝える</v>
+        <v/>
       </c>
       <c r="H68" t="str">
-        <v/>
+        <v>NSAIDs、造影剤、アミノグリコシド系、バンコマイシン</v>
       </c>
       <c r="I68" t="str">
         <v/>
@@ -3403,15 +3605,18 @@
         <v/>
       </c>
       <c r="K68" t="str">
-        <v>「骨を壊す側」の指標。「骨を作る側」の検査と合わせて評価する。数値だけで診断はしない</v>
+        <v/>
       </c>
       <c r="L68" t="str">
-        <v>骨粗鬆症</v>
+        <v>CKD診療ガイドラインの重症度分類（尿蛋白量による区分）にも使われる定量指標。試験紙法の半定量結果より治療効果判定に適する</v>
       </c>
       <c r="M68" t="str">
-        <v>TRACP-5b,骨型酒石酸抵抗性フォスファターゼ,骨粗鬆症,骨代謝</v>
+        <v>腎機能,糖尿病</v>
       </c>
       <c r="N68" t="str">
+        <v>尿蛋白,随時尿,定量,蛋白クレアチニン比,ネフローゼ</v>
+      </c>
+      <c r="O68" t="str">
         <v/>
       </c>
     </row>
@@ -3447,15 +3652,18 @@
         <v/>
       </c>
       <c r="K69" t="str">
+        <v/>
+      </c>
+      <c r="L69" t="str">
         <v>通常のALPと異なり肝臓の影響を受けにくいため、肝機能異常がある患者でも骨代謝を評価しやすい。P1NPと同じ「骨を作る側」の指標で、骨形成促進薬（テリパラチド等）の効果判定に使われる</v>
       </c>
-      <c r="L69" t="str">
+      <c r="M69" t="str">
         <v>骨粗鬆症</v>
       </c>
-      <c r="M69" t="str">
+      <c r="N69" t="str">
         <v>骨型ALP,BAP,骨型アルカリフォスファターゼ,骨形成マーカー</v>
       </c>
-      <c r="N69" t="str">
+      <c r="O69" t="str">
         <v/>
       </c>
     </row>
@@ -3491,15 +3699,18 @@
         <v>適度な日光浴、魚類・きのこ類などビタミンDを多く含む食品の摂取を意識するとよいことを伝える</v>
       </c>
       <c r="K70" t="str">
+        <v/>
+      </c>
+      <c r="L70" t="str">
         <v>骨粗鬆症治療における活性型ビタミンD3製剤の効果判定や、投与量調整の参考に用いられる。腎機能低下患者では活性化障害により25(OH)Dが正常でも活性型が不足することがある点に注意</v>
       </c>
-      <c r="L70" t="str">
+      <c r="M70" t="str">
         <v>骨粗鬆症</v>
       </c>
-      <c r="M70" t="str">
+      <c r="N70" t="str">
         <v>25(OH)D,ビタミンD,25-ヒドロキシビタミンD,ビタミンD欠乏,骨粗鬆症</v>
       </c>
-      <c r="N70" t="str">
+      <c r="O70" t="str">
         <v>食事と栄養 p.38（ビタミンD）</v>
       </c>
     </row>
@@ -3535,15 +3746,18 @@
         <v>痛風・尿酸結石がある場合は、野菜など尿をアルカリ化する食品を意識するとよいことを伝える</v>
       </c>
       <c r="K71" t="str">
+        <v/>
+      </c>
+      <c r="L71" t="str">
         <v>高尿酸血症・尿酸結石の患者では尿pHが酸性に傾いていないか確認する。尿アルカリ化薬（ウラリットなど）の効果判定にも使う</v>
       </c>
-      <c r="L71" t="str">
+      <c r="M71" t="str">
         <v>高尿酸血症</v>
       </c>
-      <c r="M71" t="str">
+      <c r="N71" t="str">
         <v>尿pH,尿酸性度,尿アルカリ化,ウラリット</v>
       </c>
-      <c r="N71" t="str">
+      <c r="O71" t="str">
         <v/>
       </c>
     </row>
@@ -3579,15 +3793,18 @@
         <v/>
       </c>
       <c r="K72" t="str">
+        <v/>
+      </c>
+      <c r="L72" t="str">
         <v>陽性かつ高血糖・全身倦怠感が強い場合は糖尿病性ケトアシドーシスの可能性があり緊急性が高い。シックデイルールの説明歴を確認する</v>
       </c>
-      <c r="L72" t="str">
+      <c r="M72" t="str">
         <v>糖尿病</v>
       </c>
-      <c r="M72" t="str">
+      <c r="N72" t="str">
         <v>尿ケトン体,ケトン体,Ket,シックデイ,ケトアシドーシス</v>
       </c>
-      <c r="N72" t="str">
+      <c r="O72" t="str">
         <v/>
       </c>
     </row>
@@ -3623,15 +3840,18 @@
         <v/>
       </c>
       <c r="K73" t="str">
+        <v/>
+      </c>
+      <c r="L73" t="str">
         <v>完全に陰性の場合は胆道閉塞を疑う所見の一つ。肝機能（AST/ALT/ビリルビン）と合わせて評価する</v>
       </c>
-      <c r="L73" t="str">
+      <c r="M73" t="str">
         <v>肝機能</v>
       </c>
-      <c r="M73" t="str">
+      <c r="N73" t="str">
         <v>ウロビリノーゲン,Uro,溶血,胆道閉塞,肝機能</v>
       </c>
-      <c r="N73" t="str">
+      <c r="O73" t="str">
         <v/>
       </c>
     </row>
@@ -3667,15 +3887,18 @@
         <v/>
       </c>
       <c r="K74" t="str">
+        <v/>
+      </c>
+      <c r="L74" t="str">
         <v>陽性でも尿沈渣で赤血球が確認されない場合は偽陽性（ミオグロビン尿など）のこともある。持続する場合は泌尿器科的な精査が必要</v>
       </c>
-      <c r="L74" t="str">
+      <c r="M74" t="str">
         <v>腎機能</v>
       </c>
-      <c r="M74" t="str">
+      <c r="N74" t="str">
         <v>尿潜血,潜血反応,U-OB,血尿,尿路結石,膀胱炎</v>
       </c>
-      <c r="N74" t="str">
+      <c r="O74" t="str">
         <v/>
       </c>
     </row>
@@ -3711,256 +3934,274 @@
         <v/>
       </c>
       <c r="K75" t="str">
+        <v/>
+      </c>
+      <c r="L75" t="str">
         <v>SGLT2阻害薬服用中は尿糖陽性が治療効果として想定内であることを患者に伝える。血糖値・HbA1cと合わせて評価する</v>
       </c>
-      <c r="L75" t="str">
+      <c r="M75" t="str">
         <v>糖尿病</v>
       </c>
-      <c r="M75" t="str">
+      <c r="N75" t="str">
         <v>尿糖,糖半定量,U-Glu,腎性糖尿,SGLT2</v>
       </c>
-      <c r="N75" t="str">
+      <c r="O75" t="str">
         <v/>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>尿蛋白定量</v>
+        <v>血清CPR（Cペプチド）</v>
       </c>
       <c r="B76" t="str">
-        <v>U-Pro定量,蛋白/Cr比</v>
+        <v>CPR</v>
       </c>
       <c r="C76" t="str">
-        <v>0.15 g/gCr未満</v>
+        <v>空腹時 0.6〜3.0 ng/mL（施設差あり）</v>
       </c>
       <c r="D76" t="str">
-        <v>随時尿から尿蛋白の量を具体的な数値として評価する検査。ネフローゼ等の重症度判定に使う</v>
+        <v>自分の膵臓がどれくらいインスリンを作れているかを表す指標</v>
       </c>
       <c r="E76" t="str">
-        <v>これは、尿に出ているたんぱくの量を具体的な数値で見る検査です。試験紙での陽性・陰性の判定だけでなく、実際にどれくらいの量が出ているかを把握できます。</v>
+        <v>この検査は、ご自身の膵臓がどれくらいインスリンを作る力を持っているかを見るものです。数値が低いほど、体の中で作れるインスリンが少ないことを示します。</v>
       </c>
       <c r="F76" t="str">
-        <v>腎症の進行（糖尿病性腎症、慢性腎臓病など）、ネフローゼ症候群（3.5 g/gCr以上が目安）</v>
+        <v>インスリン抵抗性が強い状態（初期の2型糖尿病など）</v>
       </c>
       <c r="G76" t="str">
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>NSAIDs、造影剤、アミノグリコシド系、バンコマイシン</v>
+        <v/>
       </c>
       <c r="I76" t="str">
-        <v/>
+        <v>膵臓のインスリン分泌能低下（1型糖尿病、糖尿病の進行）</v>
       </c>
       <c r="J76" t="str">
         <v/>
       </c>
       <c r="K76" t="str">
-        <v>CKD診療ガイドラインの重症度分類（尿蛋白量による区分）にも使われる定量指標。試験紙法の半定量結果より治療効果判定に適する</v>
+        <v/>
       </c>
       <c r="L76" t="str">
-        <v>腎機能,糖尿病</v>
+        <v>インスリン分泌能の評価に使われる。数値が低いほどインスリン治療の必要性が高いと判断される目安になる</v>
       </c>
       <c r="M76" t="str">
-        <v>尿蛋白,随時尿,定量,蛋白クレアチニン比,ネフローゼ</v>
+        <v>糖尿病</v>
       </c>
       <c r="N76" t="str">
+        <v>CPR,Cペプチド,インスリン分泌,血清CPR</v>
+      </c>
+      <c r="O76" t="str">
         <v/>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>BNP</v>
+        <v>尿中微量アルブミン</v>
       </c>
       <c r="B77" t="str">
-        <v>BNP</v>
+        <v>U-Alb,MAU</v>
       </c>
       <c r="C77" t="str">
-        <v>18.4 pg/mL以下</v>
+        <v>30 mg/gCr未満（尿中アルブミン/クレアチニン比）</v>
       </c>
       <c r="D77" t="str">
-        <v>心臓が無理をしているときに出る物質。心臓は血液を送るポンプだが、負担がかかると「少し助けてほしい」というサインとしてBNPを血液中に出す。</v>
+        <v>通常の尿蛋白検査では見つからない、ごく早期の腎症のサイン</v>
       </c>
       <c r="E77" t="str">
-        <v>この検査は、心臓がどれくらい頑張りすぎていないかを見るものです。数値が高いと、心臓に少し負担がかかっているサインになります。</v>
+        <v>この検査は、通常の尿検査ではまだ分からないくらい早い段階の腎臓の変化を見つけるためのものです。数値が高いと、腎症の初期のサインである可能性があります。</v>
       </c>
       <c r="F77" t="str">
-        <v>心不全、心臓に負担がかかっている状態、体に水分がたまりやすいとき</v>
+        <v>糖尿病性腎症の早期段階、高血圧</v>
       </c>
       <c r="G77" t="str">
-        <v>塩分・水分の摂りすぎに注意し、体重の変化を毎日記録するよう伝える</v>
+        <v/>
       </c>
       <c r="H77" t="str">
-        <v/>
+        <v>NSAIDsなど腎機能を悪化させる薬剤。ACE阻害薬・ARB・SGLT2阻害薬は低下させる方向に働く</v>
       </c>
       <c r="I77" t="str">
-        <v>心臓の負担は少ない状態</v>
+        <v/>
       </c>
       <c r="J77" t="str">
         <v/>
       </c>
       <c r="K77" t="str">
-        <v>腎機能が低いとBNPは高めに出ることがある／数値だけで判断せず、症状と合わせて評価する／息切れ、むくみ、体重増加があれば要注意</v>
+        <v/>
       </c>
       <c r="L77" t="str">
-        <v>心不全</v>
+        <v>糖尿病腎症の早期発見に重要な検査。血糖・血圧コントロールで改善しうる段階なので、早期介入の意義を伝える</v>
       </c>
       <c r="M77" t="str">
-        <v>BNP,心不全,息切れ,むくみ</v>
+        <v>糖尿病,腎機能</v>
       </c>
       <c r="N77" t="str">
-        <v>食事と栄養 p.216-222（第2部 心疾患）</v>
+        <v>微量アルブミン,U-Alb,MAU,糖尿病性腎症,早期腎症</v>
+      </c>
+      <c r="O77" t="str">
+        <v/>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>血清CPR（Cペプチド）</v>
+        <v>血清鉄（Fe）</v>
       </c>
       <c r="B78" t="str">
-        <v>CPR</v>
+        <v>Fe</v>
       </c>
       <c r="C78" t="str">
-        <v>空腹時 0.6〜3.0 ng/mL（施設差あり）</v>
+        <v>60〜200 μg/dL（施設差あり）</v>
       </c>
       <c r="D78" t="str">
-        <v>自分の膵臓がどれくらいインスリンを作れているかを表す指標</v>
+        <v>血液中を流れている鉄の量</v>
       </c>
       <c r="E78" t="str">
-        <v>この検査は、ご自身の膵臓がどれくらいインスリンを作る力を持っているかを見るものです。数値が低いほど、体の中で作れるインスリンが少ないことを示します。</v>
+        <v>この検査は、今血液の中を流れている鉄の量を見るものです。低いと、体の中で鉄が不足している可能性があります。</v>
       </c>
       <c r="F78" t="str">
-        <v>インスリン抵抗性が強い状態（初期の2型糖尿病など）</v>
+        <v>鉄剤の過剰摂取、溶血、肝疾患</v>
       </c>
       <c r="G78" t="str">
         <v/>
       </c>
       <c r="H78" t="str">
-        <v/>
+        <v>鉄剤の過量摂取(小児の誤飲を含む)</v>
       </c>
       <c r="I78" t="str">
-        <v>膵臓のインスリン分泌能低下（1型糖尿病、糖尿病の進行）</v>
+        <v>鉄欠乏性貧血、慢性炎症、出血</v>
       </c>
       <c r="J78" t="str">
-        <v/>
+        <v>鉄分の多い食品（レバー・赤身肉・魚・ほうれん草など）を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える</v>
       </c>
       <c r="K78" t="str">
-        <v>インスリン分泌能の評価に使われる。数値が低いほどインスリン治療の必要性が高いと判断される目安になる</v>
+        <v>プロトンポンプ阻害薬(PPI)・H2ブロッカーは胃酸分泌抑制により鉄の吸収を低下させうる</v>
       </c>
       <c r="L78" t="str">
-        <v>糖尿病</v>
+        <v>血清鉄は日内変動が大きい。単独で判断せず総鉄結合能・フェリチンと合わせて評価する</v>
       </c>
       <c r="M78" t="str">
-        <v>CPR,Cペプチド,インスリン分泌,血清CPR</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="N78" t="str">
-        <v/>
+        <v>血清鉄,Fe,鉄欠乏性貧血</v>
+      </c>
+      <c r="O78" t="str">
+        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>尿中微量アルブミン</v>
+        <v>総鉄結合能（TIBC）</v>
       </c>
       <c r="B79" t="str">
-        <v>U-Alb,MAU</v>
+        <v>TIBC</v>
       </c>
       <c r="C79" t="str">
-        <v>30 mg/gCr未満（尿中アルブミン/クレアチニン比）</v>
+        <v>250〜360 μg/dL（施設差あり）</v>
       </c>
       <c r="D79" t="str">
-        <v>通常の尿蛋白検査では見つからない、ごく早期の腎症のサイン</v>
+        <v>血液中のトランスフェリンが鉄と結合できる総量</v>
       </c>
       <c r="E79" t="str">
-        <v>この検査は、通常の尿検査ではまだ分からないくらい早い段階の腎臓の変化を見つけるためのものです。数値が高いと、腎症の初期のサインである可能性があります。</v>
+        <v>TIBCは、血液中でトランスフェリンという物質が鉄を運べる最大量を表します。体の中の鉄が不足すると、少しでも多く鉄を運ぼうとしてこの数値が上がる性質があります。</v>
       </c>
       <c r="F79" t="str">
-        <v>糖尿病性腎症の早期段階、高血圧</v>
+        <v>鉄欠乏性貧血（＞360 μg/dLが目安）</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>NSAIDsなど腎機能を悪化させる薬剤。ACE阻害薬・ARB・SGLT2阻害薬は低下させる方向に働く</v>
+        <v/>
       </c>
       <c r="I79" t="str">
-        <v/>
+        <v>慢性炎症、肝疾患、ネフローゼ症候群</v>
       </c>
       <c r="J79" t="str">
         <v/>
       </c>
       <c r="K79" t="str">
-        <v>糖尿病腎症の早期発見に重要な検査。血糖・血圧コントロールで改善しうる段階なので、早期介入の意義を伝える</v>
+        <v/>
       </c>
       <c r="L79" t="str">
-        <v>糖尿病,腎機能</v>
+        <v>鉄が不足すると、体はより多く運ぼうとしてTIBCが上昇する。UIBC・血清鉄と併せて評価する</v>
       </c>
       <c r="M79" t="str">
-        <v>微量アルブミン,U-Alb,MAU,糖尿病性腎症,早期腎症</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="N79" t="str">
-        <v/>
+        <v>TIBC,総鉄結合能,鉄欠乏性貧血</v>
+      </c>
+      <c r="O79" t="str">
+        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>血清鉄（Fe）</v>
+        <v>不飽和鉄結合能（UIBC）</v>
       </c>
       <c r="B80" t="str">
-        <v>Fe</v>
+        <v>UIBC</v>
       </c>
       <c r="C80" t="str">
-        <v>60〜200 μg/dL（施設差あり）</v>
+        <v>170〜300 μg/dL（施設差あり）</v>
       </c>
       <c r="D80" t="str">
-        <v>血液中を流れている鉄の量</v>
+        <v>トランスフェリンのうち、まだ鉄と結合していない余力の部分（UIBC＝TIBC－血清鉄）</v>
       </c>
       <c r="E80" t="str">
-        <v>この検査は、今血液の中を流れている鉄の量を見るものです。低いと、体の中で鉄が不足している可能性があります。</v>
+        <v>UIBCは、トランスフェリンのうち、まだ鉄と結合していない「空き容量」の部分を表します。鉄が不足しているときほど、この空き容量は大きくなります。</v>
       </c>
       <c r="F80" t="str">
-        <v>鉄剤の過剰摂取、溶血、肝疾患</v>
+        <v>鉄欠乏性貧血（＞300 μg/dLが目安）</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>鉄剤の過量摂取(小児の誤飲を含む)</v>
+        <v/>
       </c>
       <c r="I80" t="str">
-        <v>鉄欠乏性貧血、慢性炎症、出血</v>
+        <v>慢性炎症、鉄過剰状態</v>
       </c>
       <c r="J80" t="str">
-        <v>鉄分の多い食品（レバー・赤身肉・魚・ほうれん草など）を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える</v>
+        <v/>
       </c>
       <c r="K80" t="str">
-        <v>血清鉄は日内変動が大きい。単独で判断せず総鉄結合能・フェリチンと合わせて評価する</v>
+        <v/>
       </c>
       <c r="L80" t="str">
+        <v>TIBCと同じ方向に動くことが多い。血清鉄・TIBCとあわせて鉄欠乏性貧血と二次性貧血の鑑別に使う</v>
+      </c>
+      <c r="M80" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
-      <c r="M80" t="str">
-        <v>血清鉄,Fe,鉄欠乏性貧血</v>
-      </c>
       <c r="N80" t="str">
+        <v>UIBC,不飽和鉄結合能,鉄欠乏性貧血</v>
+      </c>
+      <c r="O80" t="str">
         <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>総鉄結合能（TIBC）</v>
+        <v>トランスフェリン飽和度</v>
       </c>
       <c r="B81" t="str">
-        <v>TIBC</v>
+        <v>TSAT</v>
       </c>
       <c r="C81" t="str">
-        <v>250〜360 μg/dL（施設差あり）</v>
+        <v>16〜50%程度（施設差あり）</v>
       </c>
       <c r="D81" t="str">
-        <v>血液中のトランスフェリンが鉄と結合できる総量</v>
+        <v>鉄を運ぶ役割のトランスフェリンのうち、実際に鉄を運んでいる割合（血清鉄÷総鉄結合能）</v>
       </c>
       <c r="E81" t="str">
-        <v>TIBCは、血液中でトランスフェリンという物質が鉄を運べる最大量を表します。体の中の鉄が不足すると、少しでも多く鉄を運ぼうとしてこの数値が上がる性質があります。</v>
+        <v>トランスフェリン飽和度は、鉄を運ぶトランスフェリンのうち、実際にどれくらいが鉄を運んでいるかを割合で表したものです。鉄欠乏性貧血では低くなり、鉄が過剰にたまる病気では高くなります。</v>
       </c>
       <c r="F81" t="str">
-        <v>鉄欠乏性貧血（＞360 μg/dLが目安）</v>
+        <v>鉄過剰症（ヘモクロマトーシスなど）</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3969,42 +4210,45 @@
         <v/>
       </c>
       <c r="I81" t="str">
-        <v>慢性炎症、肝疾患、ネフローゼ症候群</v>
+        <v>鉄欠乏性貧血（＜16%が目安）</v>
       </c>
       <c r="J81" t="str">
         <v/>
       </c>
       <c r="K81" t="str">
-        <v>鉄が不足すると、体はより多く運ぼうとしてTIBCが上昇する。UIBC・血清鉄と併せて評価する</v>
+        <v/>
       </c>
       <c r="L81" t="str">
+        <v>血清鉄をTIBCで割って計算される。鉄剤補充の効果判定にも使われる</v>
+      </c>
+      <c r="M81" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
-      <c r="M81" t="str">
-        <v>TIBC,総鉄結合能,鉄欠乏性貧血</v>
-      </c>
       <c r="N81" t="str">
+        <v>トランスフェリン飽和度,TSAT,鉄欠乏性貧血</v>
+      </c>
+      <c r="O81" t="str">
         <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>不飽和鉄結合能（UIBC）</v>
+        <v>血清フェリチン</v>
       </c>
       <c r="B82" t="str">
-        <v>UIBC</v>
+        <v>Ferritin</v>
       </c>
       <c r="C82" t="str">
-        <v>170〜300 μg/dL（施設差あり）</v>
+        <v>男性 20〜250 ng/mL、女性 10〜120 ng/mL（施設差あり）</v>
       </c>
       <c r="D82" t="str">
-        <v>トランスフェリンのうち、まだ鉄と結合していない余力の部分（UIBC＝TIBC－血清鉄）</v>
+        <v>体に貯蔵されている鉄の量を反映する指標。貧血の症状が出るより早い段階で低下する</v>
       </c>
       <c r="E82" t="str">
-        <v>UIBCは、トランスフェリンのうち、まだ鉄と結合していない「空き容量」の部分を表します。鉄が不足しているときほど、この空き容量は大きくなります。</v>
+        <v>フェリチンは、体に蓄えられている鉄の「貯金」の量を見る検査です。この数値が下がるのは、貧血の症状が出るよりも前の、とても早い段階のサインになります。</v>
       </c>
       <c r="F82" t="str">
-        <v>鉄欠乏性貧血（＞300 μg/dLが目安）</v>
+        <v>炎症性疾患、肝疾患、悪性腫瘍、鉄過剰症（フェリチンは炎症でも上昇するため、貧血の評価では注意が必要）</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -4013,42 +4257,45 @@
         <v/>
       </c>
       <c r="I82" t="str">
-        <v>慢性炎症、鉄過剰状態</v>
+        <v>鉄欠乏状態（貧血の症状が出る前の早期段階から低下する）</v>
       </c>
       <c r="J82" t="str">
-        <v/>
+        <v>鉄分の多い食品を意識するとともに、貯蔵鉄を補うため治療は数値が正常化してからも継続が必要なことを伝える</v>
       </c>
       <c r="K82" t="str">
-        <v>TIBCと同じ方向に動くことが多い。血清鉄・TIBCとあわせて鉄欠乏性貧血と二次性貧血の鑑別に使う</v>
+        <v/>
       </c>
       <c r="L82" t="str">
+        <v>貯蔵鉄の指標で鉄欠乏を最も早期に反映する。ただし炎症があると鉄欠乏があっても正常〜高値に出ることがあり、CRP等の炎症所見と合わせて評価する。二次性貧血との鑑別に重要</v>
+      </c>
+      <c r="M82" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
-      <c r="M82" t="str">
-        <v>UIBC,不飽和鉄結合能,鉄欠乏性貧血</v>
-      </c>
       <c r="N82" t="str">
+        <v>フェリチン,Ferritin,貯蔵鉄,鉄欠乏</v>
+      </c>
+      <c r="O82" t="str">
         <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>トランスフェリン飽和度</v>
+        <v>尿中尿酸/クレアチニン比（UUA/UCr）</v>
       </c>
       <c r="B83" t="str">
-        <v>TSAT</v>
+        <v>UUA/UCr</v>
       </c>
       <c r="C83" t="str">
-        <v>16〜50%程度（施設差あり）</v>
+        <v>0.4〜0.8程度が混合型の目安</v>
       </c>
       <c r="D83" t="str">
-        <v>鉄を運ぶ役割のトランスフェリンのうち、実際に鉄を運んでいる割合（血清鉄÷総鉄結合能）</v>
+        <v>尿酸が「作られすぎ」か「排泄できていない」かを見分ける比の値</v>
       </c>
       <c r="E83" t="str">
-        <v>トランスフェリン飽和度は、鉄を運ぶトランスフェリンのうち、実際にどれくらいが鉄を運んでいるかを割合で表したものです。鉄欠乏性貧血では低くなり、鉄が過剰にたまる病気では高くなります。</v>
+        <v>この数値は、体の中で尿酸が「作られすぎている」のか、それとも「うまく排泄できていない」のかを見分けるために使う比の値です。高尿酸血症の治療薬を選ぶときの参考になります。</v>
       </c>
       <c r="F83" t="str">
-        <v>鉄過剰症（ヘモクロマトーシスなど）</v>
+        <v>尿酸産生過剰型（0.8以上が目安）</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -4057,42 +4304,45 @@
         <v/>
       </c>
       <c r="I83" t="str">
-        <v>鉄欠乏性貧血（＜16%が目安）</v>
+        <v>尿酸排泄低下型（0.4以下が目安）</v>
       </c>
       <c r="J83" t="str">
         <v/>
       </c>
       <c r="K83" t="str">
-        <v>血清鉄をTIBCで割って計算される。鉄剤補充の効果判定にも使われる</v>
+        <v/>
       </c>
       <c r="L83" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>高尿酸血症は尿酸産生過剰型・排泄低下型・混合型に分類され、この比が目安になる。病型によって使う薬剤（尿酸生成抑制薬か尿酸排泄促進薬か）の選択が変わる</v>
       </c>
       <c r="M83" t="str">
-        <v>トランスフェリン飽和度,TSAT,鉄欠乏性貧血</v>
+        <v>高尿酸血症</v>
       </c>
       <c r="N83" t="str">
-        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
+        <v>UUA,UCr,尿酸クリアランス,CUA,EUA,尿酸産生過剰型,尿酸排泄低下型</v>
+      </c>
+      <c r="O83" t="str">
+        <v>食事と栄養 p.180-189（第2部 痛風・高尿酸血症）</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>血清フェリチン</v>
+        <v>ucOC（低カルボキシル化オステオカルシン）</v>
       </c>
       <c r="B84" t="str">
-        <v>Ferritin</v>
+        <v>ucOC</v>
       </c>
       <c r="C84" t="str">
-        <v>男性 20〜250 ng/mL、女性 10〜120 ng/mL（施設差あり）</v>
+        <v>4.5 ng/mL未満（施設差あり）</v>
       </c>
       <c r="D84" t="str">
-        <v>体に貯蔵されている鉄の量を反映する指標。貧血の症状が出るより早い段階で低下する</v>
+        <v>ビタミンKが不足していないかを反映する骨の指標</v>
       </c>
       <c r="E84" t="str">
-        <v>フェリチンは、体に蓄えられている鉄の「貯金」の量を見る検査です。この数値が下がるのは、貧血の症状が出るよりも前の、とても早い段階のサインになります。</v>
+        <v>ucOCは、骨を作るために必要なビタミンKが体の中で足りているかどうかを反映する検査です。数値が高いとビタミンK不足が疑われます。</v>
       </c>
       <c r="F84" t="str">
-        <v>炎症性疾患、肝疾患、悪性腫瘍、鉄過剰症（フェリチンは炎症でも上昇するため、貧血の評価では注意が必要）</v>
+        <v>ビタミンK不足状態</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -4101,42 +4351,45 @@
         <v/>
       </c>
       <c r="I84" t="str">
-        <v>鉄欠乏状態（貧血の症状が出る前の早期段階から低下する）</v>
+        <v/>
       </c>
       <c r="J84" t="str">
-        <v>鉄分の多い食品を意識するとともに、貯蔵鉄を補うため治療は数値が正常化してからも継続が必要なことを伝える</v>
+        <v/>
       </c>
       <c r="K84" t="str">
-        <v>貯蔵鉄の指標で鉄欠乏を最も早期に反映する。ただし炎症があると鉄欠乏があっても正常〜高値に出ることがあり、CRP等の炎症所見と合わせて評価する。二次性貧血との鑑別に重要</v>
+        <v/>
       </c>
       <c r="L84" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>ビタミンK2製剤（骨粗鬆症治療薬）の適応判断や効果判定に使われる</v>
       </c>
       <c r="M84" t="str">
-        <v>フェリチン,Ferritin,貯蔵鉄,鉄欠乏</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="N84" t="str">
-        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
+        <v>ucOC,オステオカルシン,ビタミンK</v>
+      </c>
+      <c r="O84" t="str">
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>尿中尿酸/クレアチニン比（UUA/UCr）</v>
+        <v>PTH（副甲状腺ホルモン）</v>
       </c>
       <c r="B85" t="str">
-        <v>UUA/UCr</v>
+        <v>PTH</v>
       </c>
       <c r="C85" t="str">
-        <v>0.4〜0.8程度が混合型の目安</v>
+        <v>10〜65 pg/mL（施設差あり）</v>
       </c>
       <c r="D85" t="str">
-        <v>尿酸が「作られすぎ」か「排泄できていない」かを見分ける比の値</v>
+        <v>血液中のカルシウム濃度を調節するホルモン</v>
       </c>
       <c r="E85" t="str">
-        <v>この数値は、体の中で尿酸が「作られすぎている」のか、それとも「うまく排泄できていない」のかを見分けるために使う比の値です。高尿酸血症の治療薬を選ぶときの参考になります。</v>
+        <v>PTHは、血液中のカルシウム濃度を一定に保つために働くホルモンです。カルシウムが低くなると分泌が増え、骨からカルシウムを取り出したり、腎臓での再吸収を促したりして数値を戻そうとします。</v>
       </c>
       <c r="F85" t="str">
-        <v>尿酸産生過剰型（0.8以上が目安）</v>
+        <v>原発性・二次性副甲状腺機能亢進症（腎不全に伴うものなど）</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -4145,42 +4398,45 @@
         <v/>
       </c>
       <c r="I85" t="str">
-        <v>尿酸排泄低下型（0.4以下が目安）</v>
+        <v>副甲状腺機能低下症</v>
       </c>
       <c r="J85" t="str">
         <v/>
       </c>
       <c r="K85" t="str">
-        <v>高尿酸血症は尿酸産生過剰型・排泄低下型・混合型に分類され、この比が目安になる。病型によって使う薬剤（尿酸生成抑制薬か尿酸排泄促進薬か）の選択が変わる</v>
+        <v/>
       </c>
       <c r="L85" t="str">
-        <v>高尿酸血症</v>
+        <v>骨粗鬆症の二次性原因（副甲状腺機能亢進症）を除外するための検査。カルシウム・リンと合わせて評価する</v>
       </c>
       <c r="M85" t="str">
-        <v>UUA,UCr,尿酸クリアランス,CUA,EUA,尿酸産生過剰型,尿酸排泄低下型</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="N85" t="str">
-        <v>食事と栄養 p.180-189（第2部 痛風・高尿酸血症）</v>
+        <v>PTH,副甲状腺ホルモン,パラトルモン</v>
+      </c>
+      <c r="O85" t="str">
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>ucOC（低カルボキシル化オステオカルシン）</v>
+        <v>尿中NTX</v>
       </c>
       <c r="B86" t="str">
-        <v>ucOC</v>
+        <v>NTX</v>
       </c>
       <c r="C86" t="str">
-        <v>4.5 ng/mL未満（施設差あり）</v>
+        <v>施設差が大きく一律の記載が難しい（尿中）</v>
       </c>
       <c r="D86" t="str">
-        <v>ビタミンKが不足していないかを反映する骨の指標</v>
+        <v>骨が壊されるときに出る、骨吸収マーカーのひとつ</v>
       </c>
       <c r="E86" t="str">
-        <v>ucOCは、骨を作るために必要なビタミンKが体の中で足りているかどうかを反映する検査です。数値が高いとビタミンK不足が疑われます。</v>
+        <v>NTXは、骨が壊される（吸収される）ときに尿の中に出てくる物質です。骨粗鬆症の治療薬がどれくらい効いているかを確認するために使われます。</v>
       </c>
       <c r="F86" t="str">
-        <v>ビタミンK不足状態</v>
+        <v>骨代謝回転の亢進（骨粗鬆症、閉経後など）</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -4189,42 +4445,45 @@
         <v/>
       </c>
       <c r="I86" t="str">
-        <v/>
+        <v>骨吸収抑制薬（ビスホスホネート等）による治療効果</v>
       </c>
       <c r="J86" t="str">
         <v/>
       </c>
       <c r="K86" t="str">
-        <v>ビタミンK2製剤（骨粗鬆症治療薬）の適応判断や効果判定に使われる</v>
+        <v/>
       </c>
       <c r="L86" t="str">
+        <v>治療開始後3〜6か月で再検し、薬の効果判定に使われる。TRACP-5bと同じ「骨を壊す側」の指標</v>
+      </c>
+      <c r="M86" t="str">
         <v>骨粗鬆症</v>
       </c>
-      <c r="M86" t="str">
-        <v>ucOC,オステオカルシン,ビタミンK</v>
-      </c>
       <c r="N86" t="str">
+        <v>NTX,尿中NTX,骨吸収マーカー</v>
+      </c>
+      <c r="O86" t="str">
         <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>PTH（副甲状腺ホルモン）</v>
+        <v>カルシトニン</v>
       </c>
       <c r="B87" t="str">
-        <v>PTH</v>
+        <v>CT</v>
       </c>
       <c r="C87" t="str">
-        <v>10〜65 pg/mL（施設差あり）</v>
+        <v>男性 9.52 pg/mL未満、女性 6.40 pg/mL未満（施設差あり）</v>
       </c>
       <c r="D87" t="str">
-        <v>血液中のカルシウム濃度を調節するホルモン</v>
+        <v>血液中のカルシウムを下げる方向に働くホルモン</v>
       </c>
       <c r="E87" t="str">
-        <v>PTHは、血液中のカルシウム濃度を一定に保つために働くホルモンです。カルシウムが低くなると分泌が増え、骨からカルシウムを取り出したり、腎臓での再吸収を促したりして数値を戻そうとします。</v>
+        <v>カルシトニンは、PTHとは逆に血液中のカルシウムを下げる方向に働くホルモンです。特定の甲状腺の病気（甲状腺髄様癌）がないかを調べる際にも使われます。</v>
       </c>
       <c r="F87" t="str">
-        <v>原発性・二次性副甲状腺機能亢進症（腎不全に伴うものなど）</v>
+        <v>甲状腺髄様癌、腎不全</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -4233,42 +4492,45 @@
         <v/>
       </c>
       <c r="I87" t="str">
-        <v>副甲状腺機能低下症</v>
+        <v/>
       </c>
       <c r="J87" t="str">
         <v/>
       </c>
       <c r="K87" t="str">
-        <v>骨粗鬆症の二次性原因（副甲状腺機能亢進症）を除外するための検査。カルシウム・リンと合わせて評価する</v>
+        <v/>
       </c>
       <c r="L87" t="str">
+        <v>骨粗鬆症の二次性原因の除外目的で測定されることがある検査値。同名の薬剤（カルシトニン製剤）と混同しないよう注意</v>
+      </c>
+      <c r="M87" t="str">
         <v>骨粗鬆症</v>
       </c>
-      <c r="M87" t="str">
-        <v>PTH,副甲状腺ホルモン,パラトルモン</v>
-      </c>
       <c r="N87" t="str">
+        <v>カルシトニン,CT</v>
+      </c>
+      <c r="O87" t="str">
         <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>尿中NTX</v>
+        <v>DPD（デオキシピリジノリン）</v>
       </c>
       <c r="B88" t="str">
-        <v>NTX</v>
+        <v>DPD</v>
       </c>
       <c r="C88" t="str">
         <v>施設差が大きく一律の記載が難しい（尿中）</v>
       </c>
       <c r="D88" t="str">
-        <v>骨が壊されるときに出る、骨吸収マーカーのひとつ</v>
+        <v>骨のコラーゲンが壊れるときに出る、骨吸収マーカーのひとつ</v>
       </c>
       <c r="E88" t="str">
-        <v>NTXは、骨が壊される（吸収される）ときに尿の中に出てくる物質です。骨粗鬆症の治療薬がどれくらい効いているかを確認するために使われます。</v>
+        <v>DPDも、骨が壊されるときに尿に出てくる物質の一つです。NTXと同じように、骨粗鬆症治療薬の効果を確認するために使われます。</v>
       </c>
       <c r="F88" t="str">
-        <v>骨代謝回転の亢進（骨粗鬆症、閉経後など）</v>
+        <v>骨代謝回転の亢進（骨粗鬆症など）</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -4277,42 +4539,45 @@
         <v/>
       </c>
       <c r="I88" t="str">
-        <v>骨吸収抑制薬（ビスホスホネート等）による治療効果</v>
+        <v>骨吸収抑制薬による治療効果</v>
       </c>
       <c r="J88" t="str">
         <v/>
       </c>
       <c r="K88" t="str">
-        <v>治療開始後3〜6か月で再検し、薬の効果判定に使われる。TRACP-5bと同じ「骨を壊す側」の指標</v>
+        <v/>
       </c>
       <c r="L88" t="str">
+        <v>NTX・CTXと同じ「骨を壊す側」の指標。食事の影響を受けにくいとされる</v>
+      </c>
+      <c r="M88" t="str">
         <v>骨粗鬆症</v>
       </c>
-      <c r="M88" t="str">
-        <v>NTX,尿中NTX,骨吸収マーカー</v>
-      </c>
       <c r="N88" t="str">
+        <v>DPD,デオキシピリジノリン,骨吸収マーカー</v>
+      </c>
+      <c r="O88" t="str">
         <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>カルシトニン</v>
+        <v>CTX</v>
       </c>
       <c r="B89" t="str">
-        <v>CT</v>
+        <v>CTX</v>
       </c>
       <c r="C89" t="str">
-        <v>男性 9.52 pg/mL未満、女性 6.40 pg/mL未満（施設差あり）</v>
+        <v>施設差が大きく一律の記載が難しい（血清・尿中）</v>
       </c>
       <c r="D89" t="str">
-        <v>血液中のカルシウムを下げる方向に働くホルモン</v>
+        <v>骨のコラーゲンが壊れるときに出る、骨吸収マーカーのひとつ</v>
       </c>
       <c r="E89" t="str">
-        <v>カルシトニンは、PTHとは逆に血液中のカルシウムを下げる方向に働くホルモンです。特定の甲状腺の病気（甲状腺髄様癌）がないかを調べる際にも使われます。</v>
+        <v>CTXも、骨が壊されるときに血液や尿に出てくる物質です。骨粗鬆症治療薬（骨を壊すのを抑える薬）の効果を確認するために使われます。</v>
       </c>
       <c r="F89" t="str">
-        <v>甲状腺髄様癌、腎不全</v>
+        <v>骨代謝回転の亢進（骨粗鬆症など）</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -4321,42 +4586,45 @@
         <v/>
       </c>
       <c r="I89" t="str">
-        <v/>
+        <v>骨吸収抑制薬による治療効果</v>
       </c>
       <c r="J89" t="str">
         <v/>
       </c>
       <c r="K89" t="str">
-        <v>骨粗鬆症の二次性原因の除外目的で測定されることがある検査値。同名の薬剤（カルシトニン製剤）と混同しないよう注意</v>
+        <v/>
       </c>
       <c r="L89" t="str">
+        <v>NTX・DPDと同じ「骨を壊す側」の指標。血清・尿中いずれでも測定されることがある</v>
+      </c>
+      <c r="M89" t="str">
         <v>骨粗鬆症</v>
       </c>
-      <c r="M89" t="str">
-        <v>カルシトニン,CT</v>
-      </c>
       <c r="N89" t="str">
+        <v>CTX,骨吸収マーカー</v>
+      </c>
+      <c r="O89" t="str">
         <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>DPD（デオキシピリジノリン）</v>
+        <v>P1NP</v>
       </c>
       <c r="B90" t="str">
-        <v>DPD</v>
+        <v>P1NP</v>
       </c>
       <c r="C90" t="str">
-        <v>施設差が大きく一律の記載が難しい（尿中）</v>
+        <v>施設差が大きく一律の記載が難しい（血清）</v>
       </c>
       <c r="D90" t="str">
-        <v>骨のコラーゲンが壊れるときに出る、骨吸収マーカーのひとつ</v>
+        <v>骨が新しく作られるときに出る、骨形成マーカーのひとつ</v>
       </c>
       <c r="E90" t="str">
-        <v>DPDも、骨が壊されるときに尿に出てくる物質の一つです。NTXと同じように、骨粗鬆症治療薬の効果を確認するために使われます。</v>
+        <v>P1NPは、CTXなどとは逆に、骨が新しく作られるときに血液中に出てくる物質です。骨を作る力を高める薬（テリパラチドなど）の効果を確認するために使われます。</v>
       </c>
       <c r="F90" t="str">
-        <v>骨代謝回転の亢進（骨粗鬆症など）</v>
+        <v>骨代謝回転の亢進、骨形成促進薬による治療効果</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -4365,42 +4633,45 @@
         <v/>
       </c>
       <c r="I90" t="str">
-        <v>骨吸収抑制薬による治療効果</v>
+        <v>骨形成の低下</v>
       </c>
       <c r="J90" t="str">
         <v/>
       </c>
       <c r="K90" t="str">
-        <v>NTX・CTXと同じ「骨を壊す側」の指標。食事の影響を受けにくいとされる</v>
+        <v/>
       </c>
       <c r="L90" t="str">
+        <v>TRACP-5b等「骨を壊す側」の指標とは逆の、「骨を作る側」の指標。骨形成促進薬（テリパラチド等）の効果判定に使われる</v>
+      </c>
+      <c r="M90" t="str">
         <v>骨粗鬆症</v>
       </c>
-      <c r="M90" t="str">
-        <v>DPD,デオキシピリジノリン,骨吸収マーカー</v>
-      </c>
       <c r="N90" t="str">
+        <v>P1NP,骨形成マーカー</v>
+      </c>
+      <c r="O90" t="str">
         <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>CTX</v>
+        <v>抗甲状腺マイクロゾーム抗体（抗TPO抗体）</v>
       </c>
       <c r="B91" t="str">
-        <v>CTX</v>
+        <v>TPOAb</v>
       </c>
       <c r="C91" t="str">
-        <v>施設差が大きく一律の記載が難しい（血清・尿中）</v>
+        <v>陰性（16 IU/mL未満程度、施設差あり）</v>
       </c>
       <c r="D91" t="str">
-        <v>骨のコラーゲンが壊れるときに出る、骨吸収マーカーのひとつ</v>
+        <v>自分の甲状腺を攻撃する抗体が出ていないかを見る検査</v>
       </c>
       <c r="E91" t="str">
-        <v>CTXも、骨が壊されるときに血液や尿に出てくる物質です。骨粗鬆症治療薬（骨を壊すのを抑える薬）の効果を確認するために使われます。</v>
+        <v>この検査は、体の中に自分の甲状腺を誤って攻撃してしまう抗体がないかを見るものです。陽性の場合、橋本病（慢性甲状腺炎）など甲状腺の自己免疫的な炎症が背景にある可能性があります。</v>
       </c>
       <c r="F91" t="str">
-        <v>骨代謝回転の亢進（骨粗鬆症など）</v>
+        <v>橋本病（慢性甲状腺炎）、バセドウ病などの自己免疫性甲状腺疾患</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -4409,42 +4680,45 @@
         <v/>
       </c>
       <c r="I91" t="str">
-        <v>骨吸収抑制薬による治療効果</v>
+        <v/>
       </c>
       <c r="J91" t="str">
         <v/>
       </c>
       <c r="K91" t="str">
-        <v>NTX・DPDと同じ「骨を壊す側」の指標。血清・尿中いずれでも測定されることがある</v>
+        <v/>
       </c>
       <c r="L91" t="str">
-        <v>骨粗鬆症</v>
+        <v>陽性でも必ずしも甲状腺機能異常があるとは限らない。TSH・FT4など甲状腺ホルモンの数値と合わせて評価する</v>
       </c>
       <c r="M91" t="str">
-        <v>CTX,骨吸収マーカー</v>
+        <v>甲状腺疾患</v>
       </c>
       <c r="N91" t="str">
-        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
+        <v>抗TPO抗体,抗甲状腺マイクロゾーム抗体,TPOAb,橋本病</v>
+      </c>
+      <c r="O91" t="str">
+        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>P1NP</v>
+        <v>抗サイログロブリン抗体</v>
       </c>
       <c r="B92" t="str">
-        <v>P1NP</v>
+        <v>TgAb</v>
       </c>
       <c r="C92" t="str">
-        <v>施設差が大きく一律の記載が難しい（血清）</v>
+        <v>陰性（28 IU/mL未満程度、施設差あり）</v>
       </c>
       <c r="D92" t="str">
-        <v>骨が新しく作られるときに出る、骨形成マーカーのひとつ</v>
+        <v>甲状腺のたんぱく質（サイログロブリン）への抗体が出ていないかを見る検査</v>
       </c>
       <c r="E92" t="str">
-        <v>P1NPは、CTXなどとは逆に、骨が新しく作られるときに血液中に出てくる物質です。骨を作る力を高める薬（テリパラチドなど）の効果を確認するために使われます。</v>
+        <v>この検査も、抗TPO抗体と同じく、甲状腺に対する自己免疫の有無を見るものです。あわせて調べることで橋本病などの診断の参考にします。</v>
       </c>
       <c r="F92" t="str">
-        <v>骨代謝回転の亢進、骨形成促進薬による治療効果</v>
+        <v>橋本病（慢性甲状腺炎）、バセドウ病などの自己免疫性甲状腺疾患</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -4453,306 +4727,327 @@
         <v/>
       </c>
       <c r="I92" t="str">
-        <v>骨形成の低下</v>
+        <v/>
       </c>
       <c r="J92" t="str">
         <v/>
       </c>
       <c r="K92" t="str">
-        <v>TRACP-5b等「骨を壊す側」の指標とは逆の、「骨を作る側」の指標。骨形成促進薬（テリパラチド等）の効果判定に使われる</v>
+        <v/>
       </c>
       <c r="L92" t="str">
-        <v>骨粗鬆症</v>
+        <v>抗TPO抗体とあわせて測定されることが多い。単独の高値だけで治療方針が決まるわけではない</v>
       </c>
       <c r="M92" t="str">
-        <v>P1NP,骨形成マーカー</v>
+        <v>甲状腺疾患</v>
       </c>
       <c r="N92" t="str">
-        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
+        <v>抗サイログロブリン抗体,TgAb,橋本病</v>
+      </c>
+      <c r="O92" t="str">
+        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>抗甲状腺マイクロゾーム抗体（抗TPO抗体）</v>
+        <v>血中薬物濃度（TDM）</v>
       </c>
       <c r="B93" t="str">
-        <v>TPOAb</v>
+        <v>TDM</v>
       </c>
       <c r="C93" t="str">
-        <v>陰性（16 IU/mL未満程度、施設差あり）</v>
+        <v>薬剤ごとに有効域が異なる（例：カルバマゼピン 4〜12 μg/mL、バルプロ酸 40〜100 μg/mL、フェニトイン 10〜20 μg/mL）</v>
       </c>
       <c r="D93" t="str">
-        <v>自分の甲状腺を攻撃する抗体が出ていないかを見る検査</v>
+        <v>治療域が狭い薬剤で、血液中の薬の濃度が効果域・中毒域のどちらにあるかを確認する検査</v>
       </c>
       <c r="E93" t="str">
-        <v>この検査は、体の中に自分の甲状腺を誤って攻撃してしまう抗体がないかを見るものです。陽性の場合、橋本病（慢性甲状腺炎）など甲状腺の自己免疫的な炎症が背景にある可能性があります。</v>
+        <v>この薬は効く量と副作用が出る量が近いため、血液中の薬の濃度を定期的に測って、ちょうどよい範囲に入っているかを確認します。数値が低いと効果が不十分になり、高いと副作用が出やすくなります。</v>
       </c>
       <c r="F93" t="str">
-        <v>橋本病（慢性甲状腺炎）、バセドウ病などの自己免疫性甲状腺疾患</v>
+        <v>過量投与、代謝を妨げる薬剤との併用、肝機能低下による代謝低下</v>
       </c>
       <c r="G93" t="str">
-        <v/>
+        <v>ふらつき、眠気、めまい、物が二重に見えるなどの中毒症状がないか確認する</v>
       </c>
       <c r="H93" t="str">
         <v/>
       </c>
       <c r="I93" t="str">
-        <v/>
+        <v>飲み忘れ、自己判断による減量、代謝を促進する薬剤との併用（相互作用）</v>
       </c>
       <c r="J93" t="str">
-        <v/>
+        <v>発作やてんかん症状の再発がないか確認し、飲み忘れがないか一緒に確認する</v>
       </c>
       <c r="K93" t="str">
-        <v>陽性でも必ずしも甲状腺機能異常があるとは限らない。TSH・FT4など甲状腺ホルモンの数値と合わせて評価する</v>
+        <v/>
       </c>
       <c r="L93" t="str">
-        <v>甲状腺疾患</v>
+        <v>採血のタイミング（トラフ値かどうか）で数値の解釈が変わるため採血時点を確認する。カルバマゼピンは自己誘導により長期使用で濃度が下がることがある点にも注意</v>
       </c>
       <c r="M93" t="str">
-        <v>抗TPO抗体,抗甲状腺マイクロゾーム抗体,TPOAb,橋本病</v>
+        <v>てんかん</v>
       </c>
       <c r="N93" t="str">
-        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
+        <v>TDM,血中薬物濃度,治療域,中毒域,カルバマゼピン,フェニトイン,バルプロ酸,抗てんかん薬</v>
+      </c>
+      <c r="O93" t="str">
+        <v/>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>抗サイログロブリン抗体</v>
+        <v>アミラーゼ（AMY）</v>
       </c>
       <c r="B94" t="str">
-        <v>TgAb</v>
+        <v>AMY</v>
       </c>
       <c r="C94" t="str">
-        <v>陰性（28 IU/mL未満程度、施設差あり）</v>
+        <v>44〜132 U/L（施設差あり）</v>
       </c>
       <c r="D94" t="str">
-        <v>甲状腺のたんぱく質（サイログロブリン）への抗体が出ていないかを見る検査</v>
+        <v>膵臓や唾液腺から出る消化酵素。膵炎などで血液中に漏れ出す</v>
       </c>
       <c r="E94" t="str">
-        <v>この検査も、抗TPO抗体と同じく、甲状腺に対する自己免疫の有無を見るものです。あわせて調べることで橋本病などの診断の参考にします。</v>
+        <v>アミラーゼは、でんぷんを分解する消化酵素で、主に膵臓と唾液腺から作られます。膵臓に炎症が起きると血液中に漏れ出して数値が上がるため、膵炎の診断や経過観察に使われます。</v>
       </c>
       <c r="F94" t="str">
-        <v>橋本病（慢性甲状腺炎）、バセドウ病などの自己免疫性甲状腺疾患</v>
+        <v>急性膵炎、慢性膵炎の急性増悪、耳下腺炎（おたふくかぜ）、腎不全</v>
       </c>
       <c r="G94" t="str">
-        <v/>
+        <v>飲酒を控える、脂っこい食事を避けるよう伝える</v>
       </c>
       <c r="H94" t="str">
-        <v/>
+        <v>バルプロ酸、アザチオプリン、サイアザイド系・ループ利尿薬、ステロイドなど薬剤性膵炎の原因薬</v>
       </c>
       <c r="I94" t="str">
-        <v/>
+        <v>慢性膵炎の進行期（膵臓の機能低下）</v>
       </c>
       <c r="J94" t="str">
         <v/>
       </c>
       <c r="K94" t="str">
-        <v>抗TPO抗体とあわせて測定されることが多い。単独の高値だけで治療方針が決まるわけではない</v>
+        <v/>
       </c>
       <c r="L94" t="str">
-        <v>甲状腺疾患</v>
+        <v>膵臓由来か唾液腺由来かを区別するには膵型アミラーゼ(P-AMY)を確認する。急性膵炎では強い腹痛・背部痛を伴うことが多く、飲酒歴の確認も重要</v>
       </c>
       <c r="M94" t="str">
-        <v>抗サイログロブリン抗体,TgAb,橋本病</v>
+        <v/>
       </c>
       <c r="N94" t="str">
-        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
+        <v>アミラーゼ,AMY,膵炎,急性膵炎</v>
+      </c>
+      <c r="O94" t="str">
+        <v/>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>血中薬物濃度（TDM）</v>
+        <v>間接ビリルビン</v>
       </c>
       <c r="B95" t="str">
-        <v>TDM</v>
+        <v>I-Bil</v>
       </c>
       <c r="C95" t="str">
-        <v>薬剤ごとに有効域が異なる（例：カルバマゼピン 4〜12 μg/mL、バルプロ酸 40〜100 μg/mL、フェニトイン 10〜20 μg/mL）</v>
+        <v>0.2〜0.8 mg/dL程度（施設差あり）</v>
       </c>
       <c r="D95" t="str">
-        <v>治療域が狭い薬剤で、血液中の薬の濃度が効果域・中毒域のどちらにあるかを確認する検査</v>
+        <v>赤血球が壊れてできるビリルビンのうち、肝臓で処理される前の形</v>
       </c>
       <c r="E95" t="str">
-        <v>この薬は効く量と副作用が出る量が近いため、血液中の薬の濃度を定期的に測って、ちょうどよい範囲に入っているかを確認します。数値が低いと効果が不十分になり、高いと副作用が出やすくなります。</v>
+        <v>間接ビリルビンは、赤血球が壊れてできたビリルビンが、まだ肝臓で処理される前の状態です。この値が高い場合、赤血球が通常より多く壊れている(溶血)か、肝臓での処理能力に生まれつきの体質差(体質性黄疸)がある可能性が考えられます。</v>
       </c>
       <c r="F95" t="str">
-        <v>過量投与、代謝を妨げる薬剤との併用、肝機能低下による代謝低下</v>
+        <v>溶血性疾患（自己免疫性溶血性貧血、血液型不適合輸血など）、体質性黄疸（ジルベール症候群）、新生児黄疸</v>
       </c>
       <c r="G95" t="str">
-        <v>ふらつき、眠気、めまい、物が二重に見えるなどの中毒症状がないか確認する</v>
+        <v>皮膚や白目の黄染、尿の色の変化がないか確認する</v>
       </c>
       <c r="H95" t="str">
         <v/>
       </c>
       <c r="I95" t="str">
-        <v>飲み忘れ、自己判断による減量、代謝を促進する薬剤との併用（相互作用）</v>
+        <v/>
       </c>
       <c r="J95" t="str">
-        <v>発作やてんかん症状の再発がないか確認し、飲み忘れがないか一緒に確認する</v>
+        <v/>
       </c>
       <c r="K95" t="str">
-        <v>採血のタイミング（トラフ値かどうか）で数値の解釈が変わるため採血時点を確認する。カルバマゼピンは自己誘導により長期使用で濃度が下がることがある点にも注意</v>
+        <v/>
       </c>
       <c r="L95" t="str">
-        <v>てんかん</v>
+        <v>直接ビリルビンとの比率で原因を推測する（間接優位は溶血・体質性、直接優位は胆道系）。総ビリルビン・AST/ALTと合わせて評価する</v>
       </c>
       <c r="M95" t="str">
-        <v>TDM,血中薬物濃度,治療域,中毒域,カルバマゼピン,フェニトイン,バルプロ酸,抗てんかん薬</v>
+        <v>肝機能</v>
       </c>
       <c r="N95" t="str">
+        <v>間接ビリルビン,I-Bil,溶血</v>
+      </c>
+      <c r="O95" t="str">
         <v/>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>アミラーゼ（AMY）</v>
+        <v>直接ビリルビン</v>
       </c>
       <c r="B96" t="str">
-        <v>AMY</v>
+        <v>D-Bil</v>
       </c>
       <c r="C96" t="str">
-        <v>44〜132 U/L（施設差あり）</v>
+        <v>0.0〜0.3 mg/dL程度（施設差あり）</v>
       </c>
       <c r="D96" t="str">
-        <v>膵臓や唾液腺から出る消化酵素。膵炎などで血液中に漏れ出す</v>
+        <v>肝臓で処理された後のビリルビン。胆道の詰まりで血液中に増える</v>
       </c>
       <c r="E96" t="str">
-        <v>アミラーゼは、でんぷんを分解する消化酵素で、主に膵臓と唾液腺から作られます。膵臓に炎症が起きると血液中に漏れ出して数値が上がるため、膵炎の診断や経過観察に使われます。</v>
+        <v>直接ビリルビンは、肝臓で処理された後のビリルビンです。胆石や腫瘍などで胆汁の通り道（胆道）が詰まると、行き場を失って血液中に増え、皮膚や白目が黄色くなる黄疸として現れます。</v>
       </c>
       <c r="F96" t="str">
-        <v>急性膵炎、慢性膵炎の急性増悪、耳下腺炎（おたふくかぜ）、腎不全</v>
+        <v>肝疾患、胆石など胆道の閉塞</v>
       </c>
       <c r="G96" t="str">
-        <v>飲酒を控える、脂っこい食事を避けるよう伝える</v>
+        <v>皮膚や白目の黄染、白っぽい便、濃い茶色の尿がないか確認する</v>
       </c>
       <c r="H96" t="str">
-        <v>バルプロ酸、アザチオプリン、サイアザイド系・ループ利尿薬、ステロイドなど薬剤性膵炎の原因薬</v>
+        <v>胆汁うっ滞型の薬剤性肝障害を起こしうる抗菌薬、経口避妊薬</v>
       </c>
       <c r="I96" t="str">
-        <v>慢性膵炎の進行期（膵臓の機能低下）</v>
+        <v/>
       </c>
       <c r="J96" t="str">
         <v/>
       </c>
       <c r="K96" t="str">
-        <v>膵臓由来か唾液腺由来かを区別するには膵型アミラーゼ(P-AMY)を確認する。急性膵炎では強い腹痛・背部痛を伴うことが多く、飲酒歴の確認も重要</v>
+        <v/>
       </c>
       <c r="L96" t="str">
-        <v/>
+        <v>直接優位の上昇は胆道系（胆石、腫瘍による閉塞）を、間接優位の上昇は溶血・体質性を疑う手がかりになる。γ-GTP・ALPと合わせて胆道系疾患を評価する</v>
       </c>
       <c r="M96" t="str">
-        <v>アミラーゼ,AMY,膵炎,急性膵炎</v>
+        <v>肝機能</v>
       </c>
       <c r="N96" t="str">
+        <v>直接ビリルビン,D-Bil,胆石,胆道閉塞</v>
+      </c>
+      <c r="O96" t="str">
         <v/>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>間接ビリルビン</v>
+        <v>亜鉛（Zn）</v>
       </c>
       <c r="B97" t="str">
-        <v>I-Bil</v>
+        <v>Zn</v>
       </c>
       <c r="C97" t="str">
-        <v>0.2〜0.8 mg/dL程度（施設差あり）</v>
+        <v>80〜130 μg/dL程度（施設差あり）</v>
       </c>
       <c r="D97" t="str">
-        <v>赤血球が壊れてできるビリルビンのうち、肝臓で処理される前の形</v>
+        <v>味覚や皮膚、免疫に関わる微量ミネラル。高齢者や低栄養で不足しやすい</v>
       </c>
       <c r="E97" t="str">
-        <v>間接ビリルビンは、赤血球が壊れてできたビリルビンが、まだ肝臓で処理される前の状態です。この値が高い場合、赤血球が通常より多く壊れている(溶血)か、肝臓での処理能力に生まれつきの体質差(体質性黄疸)がある可能性が考えられます。</v>
+        <v>亜鉛は、味を感じる働きや皮膚・粘膜の健康、免疫の働きに関わる微量ミネラルです。不足すると、味がわかりにくくなったり（味覚障害）、傷が治りにくくなったりすることがあります。</v>
       </c>
       <c r="F97" t="str">
-        <v>溶血性疾患（自己免疫性溶血性貧血、血液型不適合輸血など）、体質性黄疸（ジルベール症候群）、新生児黄疸</v>
+        <v/>
       </c>
       <c r="G97" t="str">
-        <v>皮膚や白目の黄染、尿の色の変化がないか確認する</v>
+        <v/>
       </c>
       <c r="H97" t="str">
         <v/>
       </c>
       <c r="I97" t="str">
-        <v/>
+        <v>低栄養、高齢による摂取不足、消化器手術後、亜鉛の吸収を妨げる薬剤（PPI、キレート形成する薬剤など）との併用</v>
       </c>
       <c r="J97" t="str">
-        <v/>
+        <v>味覚の変化（味を感じにくい、金属味がするなど）がないか確認する。牡蠣、赤身肉、レバーなど亜鉛を多く含む食品を意識するとよいことを伝える</v>
       </c>
       <c r="K97" t="str">
-        <v>直接ビリルビンとの比率で原因を推測する（間接優位は溶血・体質性、直接優位は胆道系）。総ビリルビン・AST/ALTと合わせて評価する</v>
+        <v/>
       </c>
       <c r="L97" t="str">
-        <v>肝機能</v>
+        <v>薬剤性の亜鉛欠乏（PPI長期使用、D-ペニシラミン、一部の降圧薬など）に注意。亜鉛欠乏による味覚障害は原因薬剤の中止・亜鉛補充で改善することがある</v>
       </c>
       <c r="M97" t="str">
-        <v>間接ビリルビン,I-Bil,溶血</v>
+        <v/>
       </c>
       <c r="N97" t="str">
-        <v/>
+        <v>亜鉛,Zn,味覚障害,亜鉛欠乏</v>
+      </c>
+      <c r="O97" t="str">
+        <v>食事と栄養 p.78（亜鉛）</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>直接ビリルビン</v>
+        <v>マグネシウム（Mg）</v>
       </c>
       <c r="B98" t="str">
-        <v>D-Bil</v>
+        <v>Mg</v>
       </c>
       <c r="C98" t="str">
-        <v>0.0〜0.3 mg/dL程度（施設差あり）</v>
+        <v>1.8〜2.6 mg/dL程度（施設差あり）</v>
       </c>
       <c r="D98" t="str">
-        <v>肝臓で処理された後のビリルビン。胆道の詰まりで血液中に増える</v>
+        <v>骨や筋肉、神経の働きに関わるミネラル。低栄養や利尿薬で不足しやすい</v>
       </c>
       <c r="E98" t="str">
-        <v>直接ビリルビンは、肝臓で処理された後のビリルビンです。胆石や腫瘍などで胆汁の通り道（胆道）が詰まると、行き場を失って血液中に増え、皮膚や白目が黄色くなる黄疸として現れます。</v>
+        <v>マグネシウムは、骨や筋肉、神経の働きを支えるミネラルです。不足すると、こむら返りや不整脈、だるさなどの症状が出ることがあります。</v>
       </c>
       <c r="F98" t="str">
-        <v>肝疾患、胆石など胆道の閉塞</v>
+        <v>腎不全、マグネシウム製剤（酸化マグネシウムなど）の過量投与</v>
       </c>
       <c r="G98" t="str">
-        <v>皮膚や白目の黄染、白っぽい便、濃い茶色の尿がないか確認する</v>
+        <v>腎機能低下がある患者で酸化マグネシウムなどの緩下剤を使用中は、傾眠・血圧低下などの高マグネシウム血症の症状がないか確認する</v>
       </c>
       <c r="H98" t="str">
-        <v>胆汁うっ滞型の薬剤性肝障害を起こしうる抗菌薬、経口避妊薬</v>
+        <v>マグネシウム含有制酸薬・下剤の過量(特に腎機能低下患者)</v>
       </c>
       <c r="I98" t="str">
-        <v/>
+        <v>低栄養、利尿薬の使用、慢性的な下痢、アルコール多飲、PPI長期使用</v>
       </c>
       <c r="J98" t="str">
-        <v/>
+        <v>こむら返りや動悸などの症状がないか確認する</v>
       </c>
       <c r="K98" t="str">
-        <v>直接優位の上昇は胆道系（胆石、腫瘍による閉塞）を、間接優位の上昇は溶血・体質性を疑う手がかりになる。γ-GTP・ALPと合わせて胆道系疾患を評価する</v>
+        <v>プロトンポンプ阻害薬(PPI)の長期使用、ループ利尿薬、サイアザイド系利尿薬、シスプラチン、アミノグリコシド系</v>
       </c>
       <c r="L98" t="str">
-        <v>肝機能</v>
+        <v>腎機能低下患者への酸化マグネシウム投与は高マグネシウム血症のリスクがあるため定期的なモニタリングが必要。PPI長期使用も低マグネシウム血症のリスク因子として知られる</v>
       </c>
       <c r="M98" t="str">
-        <v>直接ビリルビン,D-Bil,胆石,胆道閉塞</v>
+        <v>腎機能</v>
       </c>
       <c r="N98" t="str">
-        <v/>
+        <v>マグネシウム,Mg,酸化マグネシウム,こむら返り</v>
+      </c>
+      <c r="O98" t="str">
+        <v>食事と栄養 p.84（マグネシウム）</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>亜鉛（Zn）</v>
+        <v>骨密度</v>
       </c>
       <c r="B99" t="str">
-        <v>Zn</v>
+        <v>BMD,骨密度</v>
       </c>
       <c r="C99" t="str">
-        <v>80〜130 μg/dL程度（施設差あり）</v>
+        <v>YAM(若年成人平均値)80%以上:正常、70%以上80%未満:骨量減少、70%未満:骨粗鬆症</v>
       </c>
       <c r="D99" t="str">
-        <v>味覚や皮膚、免疫に関わる微量ミネラル。高齢者や低栄養で不足しやすい</v>
+        <v>骨の中にカルシウムなどのミネラルがどれだけ詰まっているかを示す指標。20〜44歳の平均値(YAM)に対する割合(%)で評価する</v>
       </c>
       <c r="E99" t="str">
-        <v>亜鉛は、味を感じる働きや皮膚・粘膜の健康、免疫の働きに関わる微量ミネラルです。不足すると、味がわかりにくくなったり（味覚障害）、傷が治りにくくなったりすることがあります。</v>
+        <v>骨密度は、骨の中にカルシウムなどのミネラルがどれだけしっかり詰まっているかを表す数値です。20〜44歳の若い方の平均値を100%として、ご自身の骨密度が何%かで示されます。70%未満になると「骨粗鬆症」と診断され、骨折しやすい状態と考えられます。</v>
       </c>
       <c r="F99" t="str">
-        <v/>
+        <v>基本的に問題になることは少ない(まれに骨硬化症などの疾患)</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -4761,71 +5056,77 @@
         <v/>
       </c>
       <c r="I99" t="str">
-        <v>低栄養、高齢による摂取不足、消化器手術後、亜鉛の吸収を妨げる薬剤（PPI、キレート形成する薬剤など）との併用</v>
+        <v>骨粗鬆症、加齢による骨量減少、閉経後のエストロゲン低下、ステロイド長期使用、カルシウム・ビタミンD不足、運動不足、るいそう</v>
       </c>
       <c r="J99" t="str">
-        <v>味覚の変化（味を感じにくい、金属味がするなど）がないか確認する。牡蠣、赤身肉、レバーなど亜鉛を多く含む食品を意識するとよいことを伝える</v>
+        <v>カルシウム・ビタミンD・ビタミンKを意識した食事、荷重運動(ウォーキング等)を勧める。ステロイド長期服用中の場合は骨粗鬆症治療薬の併用が検討されているか確認する</v>
       </c>
       <c r="K99" t="str">
-        <v>薬剤性の亜鉛欠乏（PPI長期使用、D-ペニシラミン、一部の降圧薬など）に注意。亜鉛欠乏による味覚障害は原因薬剤の中止・亜鉛補充で改善することがある</v>
+        <v/>
       </c>
       <c r="L99" t="str">
-        <v/>
+        <v>YAM70%未満、または既存の脆弱性骨折がある場合に骨粗鬆症と診断され薬物治療の対象となる(日本骨粗鬆症学会・日本骨代謝学会・厚生労働省合同「原発性骨粗鬆症の診断基準 2012年度改訂版」)。ビスホスホネート製剤は起床時空腹時に十分な水(180mL程度)で服用し、服用後30分は横にならないよう指導する。ステロイドを長期服用中の患者は骨密度によらず骨粗鬆症治療薬の併用が推奨される場合がある(グルココルチコイド誘発性骨粗鬆症: GIOP)</v>
       </c>
       <c r="M99" t="str">
-        <v>亜鉛,Zn,味覚障害,亜鉛欠乏</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="N99" t="str">
-        <v>食事と栄養 p.78（亜鉛）</v>
+        <v>骨密度,BMD,YAM,若年成人平均値,骨粗鬆症,DXA</v>
+      </c>
+      <c r="O99" t="str">
+        <v/>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>マグネシウム（Mg）</v>
+        <v>Dダイマー</v>
       </c>
       <c r="B100" t="str">
-        <v>Mg</v>
+        <v>D-dimer</v>
       </c>
       <c r="C100" t="str">
-        <v>1.8〜2.6 mg/dL程度（施設差あり）</v>
+        <v>1.0 μg/mL以下(施設・測定法により異なる)</v>
       </c>
       <c r="D100" t="str">
-        <v>骨や筋肉、神経の働きに関わるミネラル。低栄養や利尿薬で不足しやすい</v>
+        <v>体の中で血栓ができて溶けた(線溶)ときにできる分解産物で、血栓症の有無をスクリーニングする指標</v>
       </c>
       <c r="E100" t="str">
-        <v>マグネシウムは、骨や筋肉、神経の働きを支えるミネラルです。不足すると、こむら返りや不整脈、だるさなどの症状が出ることがあります。</v>
+        <v>Dダイマーは、血管の中に血のかたまり(血栓)ができて、それが溶かされるときにできる物質です。この数値が高いと、どこかに血栓ができている可能性を考えます。ただし手術後や妊娠中、高齢の方などでも上がることがあるため、この数値だけで診断が決まるわけではありません。</v>
       </c>
       <c r="F100" t="str">
-        <v>腎不全、マグネシウム製剤（酸化マグネシウムなど）の過量投与</v>
+        <v>深部静脈血栓症(DVT)・肺血栓塞栓症(PE)、播種性血管内凝固症候群(DIC)、大動脈解離、悪性腫瘍、手術後、妊娠、高齢、感染・炎症</v>
       </c>
       <c r="G100" t="str">
-        <v>腎機能低下がある患者で酸化マグネシウムなどの緩下剤を使用中は、傾眠・血圧低下などの高マグネシウム血症の症状がないか確認する</v>
+        <v>ふくらはぎの腫れ・痛み、急な息切れ・胸痛など血栓症を疑う症状がないか確認する</v>
       </c>
       <c r="H100" t="str">
-        <v>マグネシウム含有制酸薬・下剤の過量(特に腎機能低下患者)</v>
+        <v>経口避妊薬・ホルモン補充療法は血栓リスクを高める。逆にワルファリン・DOAC・ヘパリンなど抗凝固薬の効果不十分で血栓が進行している可能性にも注意</v>
       </c>
       <c r="I100" t="str">
-        <v>低栄養、利尿薬の使用、慢性的な下痢、アルコール多飲、PPI長期使用</v>
+        <v>通常、臨床的意義は乏しい(基準値以下であれば血栓症の可能性は低いとする除外診断に有用)</v>
       </c>
       <c r="J100" t="str">
-        <v>こむら返りや動悸などの症状がないか確認する</v>
+        <v/>
       </c>
       <c r="K100" t="str">
-        <v>腎機能低下患者への酸化マグネシウム投与は高マグネシウム血症のリスクがあるため定期的なモニタリングが必要。PPI長期使用も低マグネシウム血症のリスク因子として知られる</v>
+        <v/>
       </c>
       <c r="L100" t="str">
-        <v>腎機能</v>
+        <v>陰性的中率が高く、基準値以下であれば静脈血栓塞栓症(VTE)の可能性は低いとする除外診断への活用が臨床的に重要。一方で偽陽性が多く、高値のみで血栓症と確定はできない。抗凝固療法中のモニタリングそのものには通常用いない(効果判定はPT-INR/APTT等)</v>
       </c>
       <c r="M100" t="str">
-        <v>マグネシウム,Mg,酸化マグネシウム,こむら返り</v>
+        <v>抗凝固療法（心房細動・血栓症）</v>
       </c>
       <c r="N100" t="str">
-        <v>食事と栄養 p.84（マグネシウム）</v>
+        <v>Dダイマー,D-dimer,血栓,DVT,深部静脈血栓症,肺塞栓,DIC</v>
+      </c>
+      <c r="O100" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N100"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O100"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/検査値リファレンス初期データ.xlsx
+++ b/検査値リファレンス初期データ.xlsx
@@ -485,7 +485,7 @@
         <v>糖尿病、食後高血糖、ステロイドなど薬剤性高血糖、感染・ストレスによる一時的な上昇</v>
       </c>
       <c r="G2" t="str">
-        <v>食後の血糖上昇を抑えるため、早食い・まとめ食いを避け、野菜から食べる順番を意識する</v>
+        <v>食後の血糖上昇を抑えるため、早食い・まとめ食いを避け、野菜→汁物→主菜→主食の順に食べるとよいことを伝える。間食は甘い菓子より小魚やナッツなど血糖が上がりにくいものに置き換え、食後30分以内の軽い散歩も上昇抑制に役立つ</v>
       </c>
       <c r="H2" t="str">
         <v>ステロイド、サイアザイド系利尿薬、非定型抗精神病薬(オランザピン・クエチアピン)、タクロリムス・シクロスポリン、β遮断薬、高カロリー輸液</v>
@@ -494,7 +494,7 @@
         <v>低血糖（薬剤性、食事摂取不足、シックデイ時の過量投与など）</v>
       </c>
       <c r="J2" t="str">
-        <v>空腹時間が長くならないよう食事を規則正しくとる。冷や汗・動悸・強い空腹感などの低血糖症状が出たらすぐに糖分を摂る</v>
+        <v>空腹時間が長くならないよう食事を規則正しくとる。外出時はブドウ糖やアメを携帯し、冷や汗・動悸・強い空腹感が出たらすぐ糖分を摂るよう伝える。運動量が多い日は補食を追加するなど活動量に応じた調整も説明する</v>
       </c>
       <c r="K2" t="str">
         <v>インスリン、SU薬(グリメピリド等)、速効型インスリン分泌促進薬(グリニド系)。β遮断薬は低血糖症状をマスクすることがあるため注意</v>
@@ -532,7 +532,7 @@
         <v>糖尿病、血糖コントロール不良</v>
       </c>
       <c r="G3" t="str">
-        <v>主食の量や間食の頻度を見直す、体を動かす機会を増やす。飲み忘れがあれば服薬タイミングを一緒に確認する</v>
+        <v>主食の量や間食の頻度を見直し、通勤の一駅歩きなど日常に取り入れやすい運動を増やすよう提案する。飲み忘れがあればお薬カレンダーやアラームの活用も一緒に検討する</v>
       </c>
       <c r="H3" t="str">
         <v>血糖と同様(ステロイド、非定型抗精神病薬、サイアザイド系利尿薬など)。SU薬・インスリンを使用中なら低血糖の有無も確認</v>
@@ -541,7 +541,7 @@
         <v>低血糖を繰り返している状態</v>
       </c>
       <c r="J3" t="str">
-        <v>低血糖を防ぐため、食事の間隔をあけすぎないようにする。ブドウ糖など対処品の携帯を勧める</v>
+        <v>低血糖を防ぐため、食事の間隔をあけすぎないようにする。ブドウ糖など対処品の携帯を勧め、運転前や普段と違う強度の運動をする前は血糖自己測定で確認する習慣を提案する</v>
       </c>
       <c r="K3" t="str">
         <v/>
@@ -579,7 +579,7 @@
         <v>腎機能低下・腎不全、脱水、消化管出血、高たんぱく食、ステロイド使用</v>
       </c>
       <c r="G4" t="str">
-        <v>脱水を避けてこまめに水分を摂る。極端な高たんぱく食が続いていないか確認する</v>
+        <v>脱水を避けてこまめに水分を摂る(心不全等で水分制限がある場合を除く)。極端な高たんぱく食が続いていないか確認し、黒い便など消化管出血のサインにも注意する</v>
       </c>
       <c r="H4" t="str">
         <v/>
@@ -588,7 +588,7 @@
         <v>低たんぱく食、肝不全によるたんぱく合成低下、妊娠</v>
       </c>
       <c r="J4" t="str">
-        <v/>
+        <v>食事量、特にたんぱく質(肉・魚・卵・大豆製品)の摂取量を確認する。食欲低下や極端な菜食が続いていないか、栄養状態全体もあわせて確認する</v>
       </c>
       <c r="K4" t="str">
         <v/>
@@ -627,7 +627,7 @@
         <v>クレアチニン上昇（＝eGFR低下）で考える：腎機能低下、脱水、腎不全、腎毒性のある薬剤の影響</v>
       </c>
       <c r="G5" t="str">
-        <v>脱水を避けてこまめに水分を摂る（心不全等で水分制限がある場合を除く）。塩分の摂りすぎに注意する</v>
+        <v>脱水を避けてこまめに水分を摂る(心不全等で水分制限がある場合を除く)。塩分の摂りすぎに注意し、市販の鎮痛薬(NSAIDs)を自己判断で連用していないかも確認する</v>
       </c>
       <c r="H5" t="str">
         <v>腎排泄型薬剤の減量要否を確認(ジゴキシン、NOAC、メトホルミン、アミノグリコシド系、バンコマイシン等)。悪化させうる代表薬はNSAIDs・ARB/ACE阻害薬・利尿薬・造影剤・アミノグリコシド系</v>
@@ -636,7 +636,7 @@
         <v>クレアチニンが低い場合：筋肉量の低下、高齢・るいそうで見かけ上低く出ることがある</v>
       </c>
       <c r="J5" t="str">
-        <v/>
+        <v>高齢・るいそうでは筋肉量低下により見かけ上低く出て腎機能を過大評価しやすいため注意する。筋力低下がある場合は無理のない範囲での運動やたんぱく質摂取を勧める</v>
       </c>
       <c r="K5" t="str">
         <v/>
@@ -685,7 +685,7 @@
         <v>腎機能の低下（数値が低いほどろ過機能の低下を示す）、脱水、加齢に伴う腎機能低下、糖尿病性腎症など</v>
       </c>
       <c r="J6" t="str">
-        <v>脱水を避けてこまめに水分を摂る（水分制限がある場合を除く）。腎排泄型の薬剤は減量や投与間隔の延長が必要になることがあるため、お薬手帳を最新の状態に保つ</v>
+        <v>脱水を避けてこまめに水分を摂る(水分制限がある場合を除く)。腎排泄型の薬剤は減量や投与間隔の延長が必要になることがあるため、お薬手帳を最新の状態に保ち他院受診時にも提示するよう伝える</v>
       </c>
       <c r="K6" t="str">
         <v/>
@@ -724,7 +724,7 @@
         <v>高尿酸血症、痛風、プリン体の多い食事・アルコール摂取、腎機能低下、利尿薬などの薬剤性</v>
       </c>
       <c r="G7" t="str">
-        <v>プリン体の多い食品（レバー・魚卵・干物・ビールなど）を控えめにし、水分を多めに摂る</v>
+        <v>プリン体の多い食品(レバー・魚卵・干物・ビールなど)を控えめにし、水分を多めに摂る。BMIが高い場合は減量も尿酸値の改善に有効なことを伝える</v>
       </c>
       <c r="H7" t="str">
         <v>サイアザイド系利尿薬、ループ利尿薬、少量アスピリン、ピラジナミド、シクロスポリンは上昇させうる。尿酸降下薬(アロプリノール等)服用中はコントロール状況も確認</v>
@@ -771,7 +771,7 @@
         <v>脱水、アルドステロン症、水分摂取不足、下痢・嘔吐による水分喪失</v>
       </c>
       <c r="G8" t="str">
-        <v>水分摂取状況を確認する（脱水が疑われる場合）</v>
+        <v>水分摂取状況を確認する(脱水が疑われる場合)。高齢者は口渇を感じにくいため、喉が渇く前にこまめな水分摂取を意識するよう伝える</v>
       </c>
       <c r="H8" t="str">
         <v>高張輸液、浸透圧利尿薬(グリセオール等)、抗利尿ホルモン分泌を低下させる薬(炭酸リチウム等)</v>
@@ -780,7 +780,7 @@
         <v>利尿薬（特にサイアザイド系）、SIADH（抗利尿ホルモン不適合分泌症候群）、嘔吐・下痢、心不全・肝硬変によるむくみ</v>
       </c>
       <c r="J8" t="str">
-        <v>利尿薬使用中は嘔吐・下痢が続いていないか確認する。意識がぼんやりする、頭痛などの症状がないか確認する</v>
+        <v>利尿薬使用中は嘔吐・下痢が続いていないか確認する。意識がぼんやりする、頭痛、脱力感などの症状の有無を確認し、水のみを大量に摂りすぎていないかも確認する</v>
       </c>
       <c r="K8" t="str">
         <v>サイアザイド系利尿薬、SSRI、カルバマゼピン、デスモプレシン、シクロホスファミド</v>
@@ -865,7 +865,7 @@
         <v>腎不全、アジソン病、ACE阻害薬・ARB・カリウム保持性利尿薬などの薬剤性、溶血による偽高値</v>
       </c>
       <c r="G10" t="str">
-        <v>生野菜・果物・芋類などカリウムの多い食品の摂りすぎに注意する（腎機能低下がある場合）</v>
+        <v>生野菜・果物・芋類などカリウムの多い食品の摂りすぎに注意する(腎機能低下がある場合)。茹でこぼす・水にさらすことでカリウムを減らせることもあわせて伝える</v>
       </c>
       <c r="H10" t="str">
         <v>ACE阻害薬、ARB、カリウム保持性利尿薬(スピロノラクトン等)、NSAIDs、ST合剤、ヘパリン。β遮断薬は細胞内への取り込みを阻害し上昇させうる</v>
@@ -874,7 +874,7 @@
         <v>利尿薬（特にループ・サイアザイド系）、下痢・嘔吐、インスリン投与、甘草含有製剤</v>
       </c>
       <c r="J10" t="str">
-        <v>利尿薬使用中は下痢・嘔吐が続いていないか確認し、必要に応じてバナナ・芋類などカリウムを含む食品を意識する</v>
+        <v>利尿薬使用中は下痢・嘔吐が続いていないか確認し、必要に応じてバナナ・芋類などカリウムを含む食品を意識する。脱力感・こむら返り・動悸などの症状の有無もあわせて確認する</v>
       </c>
       <c r="K10" t="str">
         <v>ループ利尿薬、サイアザイド系利尿薬、グリチルリチン製剤(甘草含有製剤)、ステロイド、インスリン、β2刺激薬</v>
@@ -912,7 +912,7 @@
         <v>副甲状腺機能亢進症、悪性腫瘍（骨転移など）、ビタミンD過剰、活性型ビタミンD3製剤の過量</v>
       </c>
       <c r="G11" t="str">
-        <v>吐き気、便秘、多尿、意識がぼんやりするなどの高カルシウム血症の症状がないか確認する。活性型ビタミンD3製剤使用中は過量になっていないか確認する</v>
+        <v>吐き気、便秘、多尿、意識がぼんやりするなどの高カルシウム血症の症状がないか確認する。活性型ビタミンD3製剤使用中は過量になっていないか、水分摂取が十分かも確認する</v>
       </c>
       <c r="H11" t="str">
         <v>活性型ビタミンD製剤、サイアザイド系利尿薬、炭酸リチウム、カルシウム含有薬(炭酸カルシウム等)</v>
@@ -921,7 +921,7 @@
         <v>副甲状腺機能低下症、ビタミンD欠乏、腎不全、低アルブミン血症（見かけ上の低下）</v>
       </c>
       <c r="J11" t="str">
-        <v>手足のしびれやこむら返りなど低カルシウム血症の症状がないか確認する</v>
+        <v>手足のしびれやこむら返りなど低カルシウム血症の症状がないか確認する。乳製品・小魚・大豆製品などカルシウムを多く含む食品と、吸収を助ける適度な日光浴を意識するよう伝える</v>
       </c>
       <c r="K11" t="str">
         <v>ビスホスホネート製剤、デノスマブ、ループ利尿薬、抗てんかん薬の長期使用、シナカルセト</v>
@@ -1006,7 +1006,7 @@
         <v>腎不全、副甲状腺機能低下症</v>
       </c>
       <c r="G13" t="str">
-        <v/>
+        <v>腎機能低下がある場合は乳製品・加工食品(リン酸塩添加物)の摂りすぎに注意する。リン吸着薬を服用中の場合は食直前・食直後など服用タイミングが守られているか確認する</v>
       </c>
       <c r="H13" t="str">
         <v>活性型ビタミンD製剤、リン含有製剤。腎機能低下患者では特に注意</v>
@@ -1015,7 +1015,7 @@
         <v>副甲状腺機能亢進症、骨軟化症、ビタミンD欠乏</v>
       </c>
       <c r="J13" t="str">
-        <v/>
+        <v>骨の痛みや筋力低下などの症状がないか確認する。極端な食事制限や食欲低下がないか、栄養状態もあわせて確認する</v>
       </c>
       <c r="K13" t="str">
         <v>リン吸着薬(セベラマー等)、アルミニウム含有制酸薬、利尿薬</v>
@@ -1053,7 +1053,7 @@
         <v>肝炎・肝硬変などの肝疾患、心筋梗塞、筋肉の障害（激しい運動・横紋筋融解症）、薬剤性肝障害</v>
       </c>
       <c r="G14" t="str">
-        <v>飲酒量を控える。激しい運動の直後の採血でないかを確認する</v>
+        <v>飲酒量を控える。激しい運動の直後の採血でないかを確認し、新規薬剤の開始時期と重なっていないかもあわせて確認する</v>
       </c>
       <c r="H14" t="str">
         <v>アセトアミノフェン(過量)、スタチン系、抗結核薬(イソニアジド・リファンピシン)、バルプロ酸、NSAIDs、メトトレキサート</v>
@@ -1100,7 +1100,7 @@
         <v>脂肪肝、肝炎（ウイルス性・アルコール性・薬剤性）、肝硬変、薬の副作用による肝機能障害</v>
       </c>
       <c r="G15" t="str">
-        <v>体重管理と脂質の摂りすぎに注意する（脂肪肝が疑われる場合）。新規薬剤の開始時期と重なっていないか確認する</v>
+        <v>体重管理と脂質の摂りすぎに注意する(脂肪肝が疑われる場合)。新規薬剤の開始時期と重なっていないか確認し、市販薬・サプリメントの使用歴も聞く</v>
       </c>
       <c r="H15" t="str">
         <v>アセトアミノフェン(過量)、スタチン系、抗結核薬(イソニアジド・リファンピシン)、バルプロ酸、NSAIDs、メトトレキサート</v>
@@ -1147,7 +1147,7 @@
         <v>肝疾患、心筋梗塞、溶血性疾患、悪性腫瘍、筋肉の障害（横紋筋融解症など）、肺疾患</v>
       </c>
       <c r="G16" t="str">
-        <v/>
+        <v>息切れ、黄疸、筋肉痛など随伴症状の有無を確認し、原因臓器を絞り込む手がかりにする</v>
       </c>
       <c r="H16" t="str">
         <v/>
@@ -1194,7 +1194,7 @@
         <v>脂肪肝、ネフローゼ症候群、肥満、甲状腺機能亢進症</v>
       </c>
       <c r="G17" t="str">
-        <v>脂肪肝が疑われる場合は食事・運動習慣の見直しを勧める</v>
+        <v>脂肪肝が疑われる場合は食事・運動習慣の見直しを勧める。急激な体重増加がないかもあわせて確認する</v>
       </c>
       <c r="H17" t="str">
         <v/>
@@ -1203,7 +1203,7 @@
         <v>肝硬変など肝臓の合成能低下、低栄養、有機リン中毒（農薬など）</v>
       </c>
       <c r="J17" t="str">
-        <v/>
+        <v>低栄養が疑われる場合は食事摂取状況を確認する。肝硬変など背景疾患がある場合は出血傾向(あざ・歯ぐきの出血)の有無もあわせて確認する</v>
       </c>
       <c r="K17" t="str">
         <v/>
@@ -1241,7 +1241,7 @@
         <v>骨代謝の亢進（骨折治癒過程、骨粗鬆症、骨転移、Paget病）、肝・胆道疾患、成長期の生理的高値</v>
       </c>
       <c r="G18" t="str">
-        <v/>
+        <v>骨折治癒過程や成長期など生理的な上昇もあるため、経過や年齢背景を確認する。肝・胆道由来が疑われる場合は黄疸や皮膚のかゆみの有無も確認する</v>
       </c>
       <c r="H18" t="str">
         <v>抗てんかん薬(フェニトイン等)、胆汁うっ滞型の薬剤性肝障害を起こしうる抗菌薬・NSAIDs</v>
@@ -1289,7 +1289,7 @@
         <v>アルコール性肝障害、脂肪肝、胆道系疾患（胆石・胆管閉塞）、薬剤性（酵素誘導）</v>
       </c>
       <c r="G19" t="str">
-        <v>飲酒量を控える、休肝日をつくるよう伝える</v>
+        <v>飲酒量を控える、休肝日をつくるよう伝える。断酒・節酒を続けると数値が比較的早く改善しやすいことを励みとして伝えるとよい</v>
       </c>
       <c r="H19" t="str">
         <v>アルコール、フェニトイン、バルビツール酸系など肝薬物代謝酵素誘導作用のある薬剤</v>
@@ -1336,7 +1336,7 @@
         <v>肝炎・肝硬変などの肝疾患、胆道閉塞（胆石・腫瘍など）、溶血性疾患（赤血球の破壊亢進）、体質性黄疸（ジルベール症候群など）</v>
       </c>
       <c r="G20" t="str">
-        <v>皮膚や白目の黄染、尿の色が濃くなっていないか確認する</v>
+        <v>皮膚や白目の黄染、尿の色が濃くなっていないか確認する。かゆみを伴う場合は胆汁うっ滞の可能性もあるため皮膚症状もあわせて聞く</v>
       </c>
       <c r="H20" t="str">
         <v>肝毒性のある薬剤全般に加え、シクロスポリン・リファンピシン(トランスポーター阻害による上昇)</v>
@@ -1392,7 +1392,7 @@
         <v>低栄養、肝機能低下（アルブミン産生低下）、ネフローゼ症候群、消化管からのたんぱく漏出</v>
       </c>
       <c r="J21" t="str">
-        <v>食事摂取量（特にたんぱく質）を確認する</v>
+        <v>食事摂取量、特にたんぱく質(肉・魚・卵・大豆製品)を確認する。むくみが出ていないかもあわせて確認する</v>
       </c>
       <c r="K21" t="str">
         <v/>
@@ -1439,7 +1439,7 @@
         <v>低栄養／肝機能低下／ネフローゼ症候群／クローン病</v>
       </c>
       <c r="J22" t="str">
-        <v>主食に偏らず、肉・魚・卵・大豆製品などたんぱく質をしっかり摂るよう伝える。食欲が落ちている場合は少量頻回の食事も提案する</v>
+        <v>主食に偏らず、肉・魚・卵・大豆製品などたんぱく質をしっかり摂るよう伝える。食欲が落ちている場合は少量頻回の食事や、間食に乳製品・卵を取り入れるなど無理のない工夫を提案し、むくみの有無もあわせて確認する</v>
       </c>
       <c r="K22" t="str">
         <v>蛋白結合率の高い薬剤(ワルファリン、フェニトイン、NSAIDs等)は遊離型濃度が上昇し、効果や副作用が増強しやすいため用量に注意</v>
@@ -1477,7 +1477,7 @@
         <v>肝硬変・肝不全（門脈-大循環シャント含む）、劇症肝炎、消化管出血、便秘、脱水、高たんぱく食、尿素サイクル異常症、一部薬剤（バルプロ酸など）</v>
       </c>
       <c r="G23" t="str">
-        <v>便秘の解消（排便コントロール）を心がける。ラクツロースやリファキシミンなど肝性脳症治療薬の服薬状況を確認する</v>
+        <v>便秘の解消(排便コントロール)を心がける。ラクツロースやリファキシミンなど肝性脳症治療薬の服薬状況を確認し、意識のもうろう感や日中の眠気の変化にも注意する</v>
       </c>
       <c r="H23" t="str">
         <v>バルプロ酸(デパケン等)</v>
@@ -1524,7 +1524,7 @@
         <v>脂質異常症、糖質・アルコールの摂りすぎ、肥満、糖尿病のコントロール不良</v>
       </c>
       <c r="G24" t="str">
-        <v>糖質・アルコールの摂りすぎに注意し、有酸素運動を勧める</v>
+        <v>糖質・アルコールの摂りすぎに注意し、ウォーキングなどの有酸素運動を週150分程度を目安に勧める。清涼飲料水や果物の摂りすぎにも注意する</v>
       </c>
       <c r="H24" t="str">
         <v>非定型抗精神病薬(オランザピン・クエチアピン)、ステロイド、エストロゲン製剤、非選択的β遮断薬、サイアザイド系利尿薬、タモキシフェン</v>
@@ -1571,7 +1571,7 @@
         <v>脂質異常症、家族性高コレステロール血症、甲状腺機能低下症</v>
       </c>
       <c r="G25" t="str">
-        <v>動物性脂肪を控え、食物繊維を増やすよう伝える</v>
+        <v>動物性脂肪を控え、食物繊維(野菜・海藻・きのこ)を増やすよう伝える。青魚に含まれる油(EPA・DHA)を意識的に摂ることも勧める</v>
       </c>
       <c r="H25" t="str">
         <v>非定型抗精神病薬、ステロイド、サイアザイド系利尿薬、非選択的β遮断薬</v>
@@ -1619,7 +1619,7 @@
         <v>脂質異常症、動脈硬化のリスク上昇、家族性高コレステロール血症、甲状腺機能低下症</v>
       </c>
       <c r="G26" t="str">
-        <v>動物性脂肪や揚げ物を控え、青魚や食物繊維（野菜・海藻・きのこ）を増やすよう伝える</v>
+        <v>動物性脂肪や揚げ物を控え、青魚や食物繊維(野菜・海藻・きのこ)を増やすよう伝える。禁煙も動脈硬化予防に重要なことを伝える</v>
       </c>
       <c r="H26" t="str">
         <v>ステロイド、サイアザイド系利尿薬、非選択的β遮断薬</v>
@@ -1722,7 +1722,7 @@
         <v>脂質異常症（低HDL血症）</v>
       </c>
       <c r="J28" t="str">
-        <v>適度な運動習慣、禁煙を勧める</v>
+        <v>適度な有酸素運動(ウォーキング等)、禁煙を勧める。適正体重の維持もHDL改善に役立つことを伝える</v>
       </c>
       <c r="K28" t="str">
         <v/>
@@ -2089,7 +2089,7 @@
         <v>心不全、心臓に負担がかかっている状態、体に水分がたまりやすいとき</v>
       </c>
       <c r="G36" t="str">
-        <v>塩分・水分の摂りすぎに注意し、体重の変化を毎日記録するよう伝える</v>
+        <v>塩分・水分の摂りすぎに注意し、体重の変化を毎日記録するよう伝える。急な体重増加(2〜3日で2kg以上)や息切れの悪化があれば早めの受診を勧める</v>
       </c>
       <c r="H36" t="str">
         <v/>
@@ -2418,7 +2418,7 @@
         <v>糖尿病性腎症、腎炎、高血圧性腎硬化症、発熱・運動後の一過性のもの</v>
       </c>
       <c r="G43" t="str">
-        <v/>
+        <v>発熱・激しい運動の直後でないか確認する(一過性のことがある)。持続する場合は塩分の摂りすぎに注意し、むくみの有無もあわせて確認する</v>
       </c>
       <c r="H43" t="str">
         <v>NSAIDs、造影剤、アミノグリコシド系、バンコマイシン、金製剤</v>
@@ -2600,7 +2600,7 @@
         <v>血液の中で酸素を運ぶ役割をしている。この値が低い状態が貧血。</v>
       </c>
       <c r="E47" t="str">
-        <v>血の数値が良くなっても、体の中の鉄はまだ十分ではないことがあります。そのため、しばらく続けて飲むことが大切です。</v>
+        <v>ヘモグロビンは、血液の中で酸素を全身に運ぶ役割をしている赤い色素です。この値が低い状態が貧血で、体がだるくなったり、階段で息切れしやすくなったりします。</v>
       </c>
       <c r="F47" t="str">
         <v/>
@@ -2615,7 +2615,7 @@
         <v>鉄欠乏性貧血、出血、腎性貧血、骨髄の造血機能低下</v>
       </c>
       <c r="J47" t="str">
-        <v>鉄分の多い食品（レバー・赤身肉・魚・ほうれん草など）を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える</v>
+        <v>鉄分の多い食品(レバー・赤身肉・魚・ほうれん草など)を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える。鉄剤は数値が正常化した後も体内に鉄を貯蔵するため2〜3か月程度は継続が必要なことを説明する</v>
       </c>
       <c r="K47" t="str">
         <v>NSAIDs・抗凝固薬・抗血小板薬(消化管出血のリスク)、抗がん剤、ST合剤</v>
@@ -2709,7 +2709,7 @@
         <v>鉄欠乏性貧血</v>
       </c>
       <c r="J49" t="str">
-        <v>鉄分の多い食事を意識する（ヘモグロビンの項目を参照）</v>
+        <v>鉄分の多い食品(レバー・赤身肉・魚・ほうれん草など)と、吸収を助けるビタミンC(柑橘類・芋類等)を一緒に摂るよう伝える</v>
       </c>
       <c r="K49" t="str">
         <v/>
@@ -2756,7 +2756,7 @@
         <v>鉄欠乏性貧血</v>
       </c>
       <c r="J50" t="str">
-        <v>鉄分の多い食事を意識する（ヘモグロビンの項目を参照）</v>
+        <v>鉄分の多い食品(レバー・赤身肉・魚・ほうれん草など)と、吸収を助けるビタミンC(柑橘類・芋類等)を一緒に摂るよう伝える</v>
       </c>
       <c r="K50" t="str">
         <v/>
@@ -2803,7 +2803,7 @@
         <v>鉄欠乏性貧血</v>
       </c>
       <c r="J51" t="str">
-        <v>鉄分の多い食事を意識する（ヘモグロビンの項目を参照）</v>
+        <v>鉄分の多い食品(レバー・赤身肉・魚・ほうれん草など)と、吸収を助けるビタミンC(柑橘類・芋類等)を一緒に摂るよう伝える</v>
       </c>
       <c r="K51" t="str">
         <v/>
@@ -2841,7 +2841,7 @@
         <v>炎症性疾患、鉄欠乏性貧血、脾摘後、骨髄増殖性疾患</v>
       </c>
       <c r="G52" t="str">
-        <v/>
+        <v>出血傾向はなく経過観察でよいことが多いが、片側の腫れ・しびれなど血栓症状がないかも念のため確認する</v>
       </c>
       <c r="H52" t="str">
         <v/>
@@ -2850,7 +2850,7 @@
         <v>抗がん剤・免疫抑制剤などによる骨髄抑制、肝硬変・脾機能亢進、再生不良性貧血、抗てんかん薬（バルプロ酸など）の副作用、ITP（特発性血小板減少性紫斑病）</v>
       </c>
       <c r="J52" t="str">
-        <v>あざができやすい、歯ぐきや鼻からの出血が増えていないか確認する。強い運動や転倒によるけがに注意するよう伝える</v>
+        <v>あざができやすい、歯ぐきや鼻からの出血が増えていないか確認する。強い運動や転倒によるけがに注意するよう伝え、歯みがきは柔らかめのブラシを勧める</v>
       </c>
       <c r="K52" t="str">
         <v>ヘパリン(HIT: ヘパリン起因性血小板減少症)、バルプロ酸、抗がん剤、リネゾリド</v>
@@ -3434,31 +3434,31 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>C反応性蛋白（CRP）</v>
+        <v>Dダイマー</v>
       </c>
       <c r="B65" t="str">
-        <v>CRP</v>
+        <v>D-dimer</v>
       </c>
       <c r="C65" t="str">
-        <v>0.3 mg/dL未満（施設差あり）</v>
+        <v>1.0 μg/mL以下(施設・測定法により異なる)</v>
       </c>
       <c r="D65" t="str">
-        <v>体のどこかに炎症や感染が起きていないかを鋭敏に反映する数値</v>
+        <v>体の中で血栓ができて溶けた(線溶)ときにできる分解産物で、血栓症の有無をスクリーニングする指標</v>
       </c>
       <c r="E65" t="str">
-        <v>CRPは、体に炎症や感染が起きると数時間〜半日程度で急激に上昇する数値です。風邪のようなウイルス感染から細菌感染、体のどこかの炎症まで、幅広く反応するため、体調の変化を早期に捉える手がかりになります。</v>
+        <v>Dダイマーは、血管の中に血のかたまり(血栓)ができて、それが溶かされるときにできる物質です。この数値が高いと、どこかに血栓ができている可能性を考えます。ただし手術後や妊娠中、高齢の方などでも上がることがあるため、この数値だけで診断が決まるわけではありません。</v>
       </c>
       <c r="F65" t="str">
-        <v>細菌感染症、ウイルス感染症、自己免疫疾患（関節リウマチなど）、悪性腫瘍、組織の損傷（術後・心筋梗塞など）</v>
+        <v>深部静脈血栓症(DVT)・肺血栓塞栓症(PE)、播種性血管内凝固症候群(DIC)、大動脈解離、悪性腫瘍、手術後、妊娠、高齢、感染・炎症</v>
       </c>
       <c r="G65" t="str">
-        <v>発熱、痛み、腫れなど炎症症状の有無を確認する</v>
+        <v>ふくらはぎの腫れ・痛み、急な息切れ・胸痛など血栓症を疑う症状がないか確認する</v>
       </c>
       <c r="H65" t="str">
-        <v/>
+        <v>経口避妊薬・ホルモン補充療法は血栓リスクを高める。逆にワルファリン・DOAC・ヘパリンなど抗凝固薬の効果不十分で血栓が進行している可能性にも注意</v>
       </c>
       <c r="I65" t="str">
-        <v/>
+        <v>通常、臨床的意義は乏しい(基準値以下であれば血栓症の可能性は低いとする除外診断に有用)</v>
       </c>
       <c r="J65" t="str">
         <v/>
@@ -3467,13 +3467,13 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>白血球数と合わせて感染・炎症の程度を評価する。上昇・低下のタイミングは白血球より半日〜1日程度遅れる傾向があるため、経過を追う際は採血のタイミングに注意</v>
+        <v>陰性的中率が高く、基準値以下であれば静脈血栓塞栓症(VTE)の可能性は低いとする除外診断への活用が臨床的に重要。一方で偽陽性が多く、高値のみで血栓症と確定はできない。抗凝固療法中のモニタリングそのものには通常用いない(効果判定はPT-INR/APTT等)</v>
       </c>
       <c r="M65" t="str">
-        <v/>
+        <v>抗凝固療法（心房細動・血栓症）</v>
       </c>
       <c r="N65" t="str">
-        <v>CRP,炎症,感染</v>
+        <v>Dダイマー,D-dimer,血栓,DVT,深部静脈血栓症,肺塞栓,DIC</v>
       </c>
       <c r="O65" t="str">
         <v/>
@@ -3481,25 +3481,25 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>骨型酒石酸抵抗性フォスファターゼ（TRACP-5b）</v>
+        <v>C反応性蛋白（CRP）</v>
       </c>
       <c r="B66" t="str">
-        <v>TRACP-5b</v>
+        <v>CRP</v>
       </c>
       <c r="C66" t="str">
-        <v>120〜420 mU/dL</v>
+        <v>0.3 mg/dL未満（施設差あり）</v>
       </c>
       <c r="D66" t="str">
-        <v>骨がどれくらい壊されているかを見る検査。骨は「古い骨を壊して新しい骨を作る」入れ替えを繰り返しており、骨を壊す細胞が活発だとこの物質が血液中に増える。</v>
+        <v>体のどこかに炎症や感染が起きていないかを鋭敏に反映する数値</v>
       </c>
       <c r="E66" t="str">
-        <v>この検査は、骨がどれくらい早く減っていないかを見るものです。数値が高いと、骨が弱くなりやすい状態の目安になります。</v>
+        <v>CRPは、体に炎症や感染が起きると数時間〜半日程度で急激に上昇する数値です。風邪のようなウイルス感染から細菌感染、体のどこかの炎症まで、幅広く反応するため、体調の変化を早期に捉える手がかりになります。</v>
       </c>
       <c r="F66" t="str">
-        <v>骨粗鬆症、骨代謝回転（骨がこわれるスピード）が活発な状態</v>
+        <v>細菌感染症、ウイルス感染症、自己免疫疾患（関節リウマチなど）、悪性腫瘍、組織の損傷（術後・心筋梗塞など）</v>
       </c>
       <c r="G66" t="str">
-        <v>カルシウム・ビタミンDの摂取や、適度な荷重運動（ウォーキングなど）を意識するよう伝える</v>
+        <v>発熱、痛み、腫れなど炎症症状の有無を確認する</v>
       </c>
       <c r="H66" t="str">
         <v/>
@@ -3514,13 +3514,13 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>「骨を壊す側」の指標。「骨を作る側」の検査と合わせて評価する。数値だけで診断はしない</v>
+        <v>白血球数と合わせて感染・炎症の程度を評価する。上昇・低下のタイミングは白血球より半日〜1日程度遅れる傾向があるため、経過を追う際は採血のタイミングに注意</v>
       </c>
       <c r="M66" t="str">
-        <v>骨粗鬆症</v>
+        <v/>
       </c>
       <c r="N66" t="str">
-        <v>TRACP-5b,骨型酒石酸抵抗性フォスファターゼ,骨粗鬆症,骨代謝</v>
+        <v>CRP,炎症,感染</v>
       </c>
       <c r="O66" t="str">
         <v/>
@@ -3528,125 +3528,125 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>PT-INR（プロトロンビン時間国際標準比）</v>
+        <v>骨型酒石酸抵抗性フォスファターゼ（TRACP-5b）</v>
       </c>
       <c r="B67" t="str">
-        <v>PT-INR,INR</v>
+        <v>TRACP-5b</v>
       </c>
       <c r="C67" t="str">
-        <v>治療域の目安 1.6〜3.0（ワルファリン服用時。年齢・疾患により異なる）</v>
+        <v>120〜420 mU/dL</v>
       </c>
       <c r="D67" t="str">
-        <v>血液の固まりやすさを表す数値で、ワルファリンの効き具合を確認するために使う</v>
+        <v>骨がどれくらい壊されているかを見る検査。骨は「古い骨を壊して新しい骨を作る」入れ替えを繰り返しており、骨を壊す細胞が活発だとこの物質が血液中に増える。</v>
       </c>
       <c r="E67" t="str">
-        <v>PT-INRは血液が固まるまでの時間をもとにした数値で、ワルファリンというお薬を飲んでいる方の効き具合を確認するために測ります。数値が高いほど血液が固まりにくく出血しやすい状態、低いほど血栓ができやすい状態を示します。</v>
+        <v>この検査は、骨がどれくらい早く減っていないかを見るものです。数値が高いと、骨が弱くなりやすい状態の目安になります。</v>
       </c>
       <c r="F67" t="str">
-        <v>ワルファリンの効きすぎ、肝機能低下、ビタミンK不足、納豆・青汁など摂取量の変化</v>
+        <v>骨粗鬆症、骨代謝回転（骨がこわれるスピード）が活発な状態</v>
       </c>
       <c r="G67" t="str">
-        <v>歯ぐきや鼻からの出血、あざ、黒い便などの出血症状がないか確認する。納豆・クロレラ・青汁などビタミンKを多く含む食品の摂取状況を確認する</v>
+        <v>カルシウム・ビタミンDの摂取や、適度な荷重運動（ウォーキングなど）を意識するよう伝える</v>
       </c>
       <c r="H67" t="str">
-        <v>ワルファリンの過量。ワルファリン服用中はST合剤・マクロライド系・フルコナゾール等の相互作用やビタミンK摂取量の変化にも注意</v>
+        <v/>
       </c>
       <c r="I67" t="str">
-        <v>ワルファリンの効き不足、飲み忘れ、ビタミンK摂取量の急激な増加</v>
+        <v/>
       </c>
       <c r="J67" t="str">
-        <v>服薬状況（飲み忘れ）を確認する。片側のむくみ・しびれ・胸痛など血栓症状がないか確認する</v>
+        <v/>
       </c>
       <c r="K67" t="str">
-        <v>ワルファリン服用中で低値の場合は効果不十分の可能性。ビタミンK摂取量の変化や、リファンピシン・カルバマゼピン・バルビツール酸系など代謝を促進する薬との併用を確認</v>
+        <v/>
       </c>
       <c r="L67" t="str">
-        <v>治療域は疾患・年齢によって異なる（例：非弁膜症性心房細動の高齢者では1.6〜2.6が目安になることが多い）。多くの薬剤・食品と相互作用があるため新規薬剤追加時は必ず確認する。DOAC（エリキュース、リクシアナ、プラザキサなど）ではPT-INRのモニタリングは不要</v>
+        <v>「骨を壊す側」の指標。「骨を作る側」の検査と合わせて評価する。数値だけで診断はしない</v>
       </c>
       <c r="M67" t="str">
-        <v>抗凝固療法（心房細動・血栓症）</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="N67" t="str">
-        <v>PT-INR,INR,プロトロンビン時間,ワルファリン,ワーファリン,抗凝固</v>
+        <v>TRACP-5b,骨型酒石酸抵抗性フォスファターゼ,骨粗鬆症,骨代謝</v>
       </c>
       <c r="O67" t="str">
-        <v>食事と栄養 p.221（心疾患Q93 ワルファリン服用中のビタミンK摂取）</v>
+        <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>尿蛋白定量</v>
+        <v>PT-INR（プロトロンビン時間国際標準比）</v>
       </c>
       <c r="B68" t="str">
-        <v>U-Pro定量,蛋白/Cr比</v>
+        <v>PT-INR,INR</v>
       </c>
       <c r="C68" t="str">
-        <v>0.15 g/gCr未満</v>
+        <v>治療域の目安 1.6〜3.0（ワルファリン服用時。年齢・疾患により異なる）</v>
       </c>
       <c r="D68" t="str">
-        <v>随時尿から尿蛋白の量を具体的な数値として評価する検査。ネフローゼ等の重症度判定に使う</v>
+        <v>血液の固まりやすさを表す数値で、ワルファリンの効き具合を確認するために使う</v>
       </c>
       <c r="E68" t="str">
-        <v>これは、尿に出ているたんぱくの量を具体的な数値で見る検査です。試験紙での陽性・陰性の判定だけでなく、実際にどれくらいの量が出ているかを把握できます。</v>
+        <v>PT-INRは血液が固まるまでの時間をもとにした数値で、ワルファリンというお薬を飲んでいる方の効き具合を確認するために測ります。数値が高いほど血液が固まりにくく出血しやすい状態、低いほど血栓ができやすい状態を示します。</v>
       </c>
       <c r="F68" t="str">
-        <v>腎症の進行（糖尿病性腎症、慢性腎臓病など）、ネフローゼ症候群（3.5 g/gCr以上が目安）</v>
+        <v>ワルファリンの効きすぎ、肝機能低下、ビタミンK不足、納豆・青汁など摂取量の変化</v>
       </c>
       <c r="G68" t="str">
-        <v/>
+        <v>歯ぐきや鼻からの出血、あざ、黒い便などの出血症状がないか確認する。納豆・クロレラ・青汁などビタミンKを多く含む食品の摂取状況を確認する</v>
       </c>
       <c r="H68" t="str">
-        <v>NSAIDs、造影剤、アミノグリコシド系、バンコマイシン</v>
+        <v>ワルファリンの過量。ワルファリン服用中はST合剤・マクロライド系・フルコナゾール等の相互作用やビタミンK摂取量の変化にも注意</v>
       </c>
       <c r="I68" t="str">
-        <v/>
+        <v>ワルファリンの効き不足、飲み忘れ、ビタミンK摂取量の急激な増加</v>
       </c>
       <c r="J68" t="str">
-        <v/>
+        <v>服薬状況（飲み忘れ）を確認する。片側のむくみ・しびれ・胸痛など血栓症状がないか確認する</v>
       </c>
       <c r="K68" t="str">
-        <v/>
+        <v>ワルファリン服用中で低値の場合は効果不十分の可能性。ビタミンK摂取量の変化や、リファンピシン・カルバマゼピン・バルビツール酸系など代謝を促進する薬との併用を確認</v>
       </c>
       <c r="L68" t="str">
-        <v>CKD診療ガイドラインの重症度分類（尿蛋白量による区分）にも使われる定量指標。試験紙法の半定量結果より治療効果判定に適する</v>
+        <v>治療域は疾患・年齢によって異なる（例：非弁膜症性心房細動の高齢者では1.6〜2.6が目安になることが多い）。多くの薬剤・食品と相互作用があるため新規薬剤追加時は必ず確認する。DOAC（エリキュース、リクシアナ、プラザキサなど）ではPT-INRのモニタリングは不要</v>
       </c>
       <c r="M68" t="str">
-        <v>腎機能,糖尿病</v>
+        <v>抗凝固療法（心房細動・血栓症）</v>
       </c>
       <c r="N68" t="str">
-        <v>尿蛋白,随時尿,定量,蛋白クレアチニン比,ネフローゼ</v>
+        <v>PT-INR,INR,プロトロンビン時間,ワルファリン,ワーファリン,抗凝固</v>
       </c>
       <c r="O68" t="str">
-        <v/>
+        <v>食事と栄養 p.221（心疾患Q93 ワルファリン服用中のビタミンK摂取）</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>骨型アルカリフォスファターゼ</v>
+        <v>尿蛋白定量</v>
       </c>
       <c r="B69" t="str">
-        <v>BAP</v>
+        <v>U-Pro定量,蛋白/Cr比</v>
       </c>
       <c r="C69" t="str">
-        <v>男性 3.7〜20.9 μg/L、女性（閉経前）2.9〜14.5 μg/L（施設差あり）</v>
+        <v>0.15 g/gCr未満</v>
       </c>
       <c r="D69" t="str">
-        <v>ALPのうち骨に由来する成分だけを測定し、骨が作られる勢い（骨形成）を反映する</v>
+        <v>随時尿から尿蛋白の量を具体的な数値として評価する検査。ネフローゼ等の重症度判定に使う</v>
       </c>
       <c r="E69" t="str">
-        <v>骨型ALPは、通常のALP（アルカリフォスファターゼ）の中でも、骨で作られる成分だけを選んで測定するものです。骨を新しく作る働きがどれくらい活発かを見る指標として、骨粗鬆症の治療効果判定などに使われます。</v>
+        <v>これは、尿に出ているたんぱくの量を具体的な数値で見る検査です。試験紙での陽性・陰性の判定だけでなく、実際にどれくらいの量が出ているかを把握できます。</v>
       </c>
       <c r="F69" t="str">
-        <v>骨代謝回転の亢進（骨粗鬆症、骨折治癒過程、骨形成促進薬による治療効果、Paget病、骨転移）</v>
+        <v>腎症の進行（糖尿病性腎症、慢性腎臓病など）、ネフローゼ症候群（3.5 g/gCr以上が目安）</v>
       </c>
       <c r="G69" t="str">
-        <v/>
+        <v>持続する場合は塩分の摂りすぎに注意し、むくみの有無も確認する。腎臓内科でのフォロー状況もあわせて確認する</v>
       </c>
       <c r="H69" t="str">
-        <v/>
+        <v>NSAIDs、造影剤、アミノグリコシド系、バンコマイシン</v>
       </c>
       <c r="I69" t="str">
-        <v>骨形成の低下</v>
+        <v/>
       </c>
       <c r="J69" t="str">
         <v/>
@@ -3655,13 +3655,13 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>通常のALPと異なり肝臓の影響を受けにくいため、肝機能異常がある患者でも骨代謝を評価しやすい。P1NPと同じ「骨を作る側」の指標で、骨形成促進薬（テリパラチド等）の効果判定に使われる</v>
+        <v>CKD診療ガイドラインの重症度分類（尿蛋白量による区分）にも使われる定量指標。試験紙法の半定量結果より治療効果判定に適する</v>
       </c>
       <c r="M69" t="str">
-        <v>骨粗鬆症</v>
+        <v>腎機能,糖尿病</v>
       </c>
       <c r="N69" t="str">
-        <v>骨型ALP,BAP,骨型アルカリフォスファターゼ,骨形成マーカー</v>
+        <v>尿蛋白,随時尿,定量,蛋白クレアチニン比,ネフローゼ</v>
       </c>
       <c r="O69" t="str">
         <v/>
@@ -3669,140 +3669,140 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>25-ヒドロキシビタミンD</v>
+        <v>骨型アルカリフォスファターゼ</v>
       </c>
       <c r="B70" t="str">
-        <v>25(OH)D</v>
+        <v>BAP</v>
       </c>
       <c r="C70" t="str">
-        <v>30 ng/mL以上：充足、20〜30 ng/mL：不足、20 ng/mL未満：欠乏（施設差あり）</v>
+        <v>男性 3.7〜20.9 μg/L、女性（閉経前）2.9〜14.5 μg/L（施設差あり）</v>
       </c>
       <c r="D70" t="str">
-        <v>体内のビタミンDの蓄え具合を反映する指標。カルシウムの吸収や骨の健康に関わる</v>
+        <v>ALPのうち骨に由来する成分だけを測定し、骨が作られる勢い（骨形成）を反映する</v>
       </c>
       <c r="E70" t="str">
-        <v>この検査は、体の中にビタミンDがどれくらい蓄えられているかを見るものです。ビタミンDは、食事から摂ったカルシウムを腸で吸収するのを助ける働きがあり、不足すると骨がもろくなりやすくなります。</v>
+        <v>骨型ALPは、通常のALP（アルカリフォスファターゼ）の中でも、骨で作られる成分だけを選んで測定するものです。骨を新しく作る働きがどれくらい活発かを見る指標として、骨粗鬆症の治療効果判定などに使われます。</v>
       </c>
       <c r="F70" t="str">
-        <v>ビタミンD製剤の過剰摂取</v>
+        <v>骨代謝回転の亢進（骨粗鬆症、骨折治癒過程、骨形成促進薬による治療効果、Paget病、骨転移）</v>
       </c>
       <c r="G70" t="str">
-        <v>活性型ビタミンD3製剤やサプリメントの摂取量を確認する。高カルシウム血症の症状（吐き気、便秘、多尿など）がないか確認する</v>
+        <v/>
       </c>
       <c r="H70" t="str">
-        <v>活性型/天然型ビタミンD製剤の過量投与</v>
+        <v/>
       </c>
       <c r="I70" t="str">
-        <v>日光暴露不足、食事摂取不足、高齢、腸疾患による吸収不良、肝・腎機能低下（活性化障害）</v>
+        <v>骨形成の低下</v>
       </c>
       <c r="J70" t="str">
-        <v>適度な日光浴、魚類・きのこ類などビタミンDを多く含む食品の摂取を意識するとよいことを伝える</v>
+        <v/>
       </c>
       <c r="K70" t="str">
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>骨粗鬆症治療における活性型ビタミンD3製剤の効果判定や、投与量調整の参考に用いられる。腎機能低下患者では活性化障害により25(OH)Dが正常でも活性型が不足することがある点に注意</v>
+        <v>通常のALPと異なり肝臓の影響を受けにくいため、肝機能異常がある患者でも骨代謝を評価しやすい。P1NPと同じ「骨を作る側」の指標で、骨形成促進薬（テリパラチド等）の効果判定に使われる</v>
       </c>
       <c r="M70" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="N70" t="str">
-        <v>25(OH)D,ビタミンD,25-ヒドロキシビタミンD,ビタミンD欠乏,骨粗鬆症</v>
+        <v>骨型ALP,BAP,骨型アルカリフォスファターゼ,骨形成マーカー</v>
       </c>
       <c r="O70" t="str">
-        <v>食事と栄養 p.38（ビタミンD）</v>
+        <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>尿pH</v>
+        <v>25-ヒドロキシビタミンD</v>
       </c>
       <c r="B71" t="str">
-        <v>尿pH</v>
+        <v>25(OH)D</v>
       </c>
       <c r="C71" t="str">
-        <v>4.5〜7.5程度（弱酸性が多い）</v>
+        <v>30 ng/mL以上：充足、20〜30 ng/mL：不足、20 ng/mL未満：欠乏（施設差あり）</v>
       </c>
       <c r="D71" t="str">
-        <v>尿の酸性・アルカリ性の度合い。食事や感染症、体の状態を反映する</v>
+        <v>体内のビタミンDの蓄え具合を反映する指標。カルシウムの吸収や骨の健康に関わる</v>
       </c>
       <c r="E71" t="str">
-        <v>尿のpHは酸性・アルカリ性のバランスを表します。食事の内容や感染症、体の代謝状態によって変化します。単独で大きな問題を示すことは少ない検査です。</v>
+        <v>この検査は、体の中にビタミンDがどれくらい蓄えられているかを見るものです。ビタミンDは、食事から摂ったカルシウムを腸で吸収するのを助ける働きがあり、不足すると骨がもろくなりやすくなります。</v>
       </c>
       <c r="F71" t="str">
-        <v>尿路感染症（尿素分解菌によるもの）、野菜中心の食事、過換気</v>
+        <v>ビタミンD製剤の過剰摂取</v>
       </c>
       <c r="G71" t="str">
-        <v/>
+        <v>活性型ビタミンD3製剤やサプリメントの摂取量を確認する。高カルシウム血症の症状（吐き気、便秘、多尿など）がないか確認する</v>
       </c>
       <c r="H71" t="str">
-        <v/>
+        <v>活性型/天然型ビタミンD製剤の過量投与</v>
       </c>
       <c r="I71" t="str">
-        <v>高たんぱく食、糖尿病性ケトアシドーシス、痛風発作時（酸性尿は尿酸結石のリスクを高める）</v>
+        <v>日光暴露不足、食事摂取不足、高齢、腸疾患による吸収不良、肝・腎機能低下（活性化障害）</v>
       </c>
       <c r="J71" t="str">
-        <v>痛風・尿酸結石がある場合は、野菜など尿をアルカリ化する食品を意識するとよいことを伝える</v>
+        <v>適度な日光浴、魚類・きのこ類などビタミンDを多く含む食品の摂取を意識するとよいことを伝える</v>
       </c>
       <c r="K71" t="str">
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>高尿酸血症・尿酸結石の患者では尿pHが酸性に傾いていないか確認する。尿アルカリ化薬（ウラリットなど）の効果判定にも使う</v>
+        <v>骨粗鬆症治療における活性型ビタミンD3製剤の効果判定や、投与量調整の参考に用いられる。腎機能低下患者では活性化障害により25(OH)Dが正常でも活性型が不足することがある点に注意</v>
       </c>
       <c r="M71" t="str">
-        <v>高尿酸血症</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="N71" t="str">
-        <v>尿pH,尿酸性度,尿アルカリ化,ウラリット</v>
+        <v>25(OH)D,ビタミンD,25-ヒドロキシビタミンD,ビタミンD欠乏,骨粗鬆症</v>
       </c>
       <c r="O71" t="str">
-        <v/>
+        <v>食事と栄養 p.38（ビタミンD）</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>尿ケトン体</v>
+        <v>尿pH</v>
       </c>
       <c r="B72" t="str">
-        <v>尿ケトン,Ket</v>
+        <v>尿pH</v>
       </c>
       <c r="C72" t="str">
-        <v>陰性（－）</v>
+        <v>4.5〜7.5程度（弱酸性が多い）</v>
       </c>
       <c r="D72" t="str">
-        <v>体がブドウ糖の代わりに脂肪を分解してエネルギーを作っているサイン</v>
+        <v>尿の酸性・アルカリ性の度合い。食事や感染症、体の状態を反映する</v>
       </c>
       <c r="E72" t="str">
-        <v>この検査は、体が糖の代わりに脂肪を使ってエネルギーを作っていないかを見るものです。陽性が続くときは、食事や水分、インスリンの使い方を確認する必要があります。</v>
+        <v>尿のpHは酸性・アルカリ性のバランスを表します。食事の内容や感染症、体の代謝状態によって変化します。単独で大きな問題を示すことは少ない検査です。</v>
       </c>
       <c r="F72" t="str">
-        <v>糖尿病の血糖コントロール不良（シックデイ・インスリン不足）、極端な糖質制限、絶食、嘔吐・下痢による脱水</v>
+        <v>尿路感染症（尿素分解菌によるもの）、野菜中心の食事、過換気</v>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>SGLT2阻害薬(特に絶食・シックデイ時の正常血糖ケトアシドーシスに注意)</v>
+        <v/>
       </c>
       <c r="I72" t="str">
-        <v/>
+        <v>高たんぱく食、糖尿病性ケトアシドーシス、痛風発作時（酸性尿は尿酸結石のリスクを高める）</v>
       </c>
       <c r="J72" t="str">
-        <v/>
+        <v>痛風・尿酸結石がある場合は、野菜など尿をアルカリ化する食品を意識するとよいことを伝える</v>
       </c>
       <c r="K72" t="str">
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>陽性かつ高血糖・全身倦怠感が強い場合は糖尿病性ケトアシドーシスの可能性があり緊急性が高い。シックデイルールの説明歴を確認する</v>
+        <v>高尿酸血症・尿酸結石の患者では尿pHが酸性に傾いていないか確認する。尿アルカリ化薬（ウラリットなど）の効果判定にも使う</v>
       </c>
       <c r="M72" t="str">
-        <v>糖尿病</v>
+        <v>高尿酸血症</v>
       </c>
       <c r="N72" t="str">
-        <v>尿ケトン体,ケトン体,Ket,シックデイ,ケトアシドーシス</v>
+        <v>尿pH,尿酸性度,尿アルカリ化,ウラリット</v>
       </c>
       <c r="O72" t="str">
         <v/>
@@ -3810,31 +3810,31 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>ウロビリノーゲン</v>
+        <v>尿ケトン体</v>
       </c>
       <c r="B73" t="str">
-        <v>Uro</v>
+        <v>尿ケトン,Ket</v>
       </c>
       <c r="C73" t="str">
-        <v>正常（±）程度</v>
+        <v>陰性（－）</v>
       </c>
       <c r="D73" t="str">
-        <v>肝臓や胆道、赤血球の壊れ方の状態を反映する尿検査項目</v>
+        <v>体がブドウ糖の代わりに脂肪を分解してエネルギーを作っているサイン</v>
       </c>
       <c r="E73" t="str">
-        <v>ウロビリノーゲンは、赤血球やビリルビンが体の中で処理される過程でできる物質です。肝臓の働きが悪くなったり、赤血球が壊れやすくなったりすると、尿の中の量が変化します。</v>
+        <v>この検査は、体が糖の代わりに脂肪を使ってエネルギーを作っていないかを見るものです。陽性が続くときは、食事や水分、インスリンの使い方を確認する必要があります。</v>
       </c>
       <c r="F73" t="str">
-        <v>溶血性疾患（赤血球の破壊亢進）、肝機能障害</v>
+        <v>糖尿病の血糖コントロール不良（シックデイ・インスリン不足）、極端な糖質制限、絶食、嘔吐・下痢による脱水</v>
       </c>
       <c r="G73" t="str">
-        <v/>
+        <v>糖尿病治療中の場合はシックデイ時の対応(インスリンを自己中断しない、水分摂取を続けるなど)を確認する。体調不良時の対応方法を事前に説明しておく</v>
       </c>
       <c r="H73" t="str">
-        <v/>
+        <v>SGLT2阻害薬(特に絶食・シックデイ時の正常血糖ケトアシドーシスに注意)</v>
       </c>
       <c r="I73" t="str">
-        <v>胆道閉塞（胆汁が腸に流れず、ウロビリノーゲンが作られない状態）</v>
+        <v/>
       </c>
       <c r="J73" t="str">
         <v/>
@@ -3843,13 +3843,13 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>完全に陰性の場合は胆道閉塞を疑う所見の一つ。肝機能（AST/ALT/ビリルビン）と合わせて評価する</v>
+        <v>陽性かつ高血糖・全身倦怠感が強い場合は糖尿病性ケトアシドーシスの可能性があり緊急性が高い。シックデイルールの説明歴を確認する</v>
       </c>
       <c r="M73" t="str">
-        <v>肝機能</v>
+        <v>糖尿病</v>
       </c>
       <c r="N73" t="str">
-        <v>ウロビリノーゲン,Uro,溶血,胆道閉塞,肝機能</v>
+        <v>尿ケトン体,ケトン体,Ket,シックデイ,ケトアシドーシス</v>
       </c>
       <c r="O73" t="str">
         <v/>
@@ -3857,31 +3857,31 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>尿潜血反応</v>
+        <v>ウロビリノーゲン</v>
       </c>
       <c r="B74" t="str">
-        <v>尿潜血,U-OB</v>
+        <v>Uro</v>
       </c>
       <c r="C74" t="str">
-        <v>陰性（－）</v>
+        <v>正常（±）程度</v>
       </c>
       <c r="D74" t="str">
-        <v>尿に血液（赤血球）が混じっていないかを見る検査</v>
+        <v>肝臓や胆道、赤血球の壊れ方の状態を反映する尿検査項目</v>
       </c>
       <c r="E74" t="str">
-        <v>この検査は、尿に目に見えないくらいの微量の血液が混じっていないかを調べるものです。陽性の場合、腎臓や膀胱、尿路のどこかに炎症や結石などがある可能性があります。</v>
+        <v>ウロビリノーゲンは、赤血球やビリルビンが体の中で処理される過程でできる物質です。肝臓の働きが悪くなったり、赤血球が壊れやすくなったりすると、尿の中の量が変化します。</v>
       </c>
       <c r="F74" t="str">
-        <v>尿路結石、膀胱炎などの尿路感染症、腎炎、腫瘍、月経血の混入、激しい運動後</v>
+        <v>溶血性疾患（赤血球の破壊亢進）、肝機能障害</v>
       </c>
       <c r="G74" t="str">
-        <v>排尿時の痛みや頻尿、目に見える血尿の有無を確認する。女性は月経の時期と重なっていないか確認する</v>
+        <v/>
       </c>
       <c r="H74" t="str">
-        <v>ワルファリン、DOAC、抗血小板薬など出血傾向を強める薬剤の服用状況を確認</v>
+        <v/>
       </c>
       <c r="I74" t="str">
-        <v/>
+        <v>胆道閉塞（胆汁が腸に流れず、ウロビリノーゲンが作られない状態）</v>
       </c>
       <c r="J74" t="str">
         <v/>
@@ -3890,13 +3890,13 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>陽性でも尿沈渣で赤血球が確認されない場合は偽陽性（ミオグロビン尿など）のこともある。持続する場合は泌尿器科的な精査が必要</v>
+        <v>完全に陰性の場合は胆道閉塞を疑う所見の一つ。肝機能（AST/ALT/ビリルビン）と合わせて評価する</v>
       </c>
       <c r="M74" t="str">
-        <v>腎機能</v>
+        <v>肝機能</v>
       </c>
       <c r="N74" t="str">
-        <v>尿潜血,潜血反応,U-OB,血尿,尿路結石,膀胱炎</v>
+        <v>ウロビリノーゲン,Uro,溶血,胆道閉塞,肝機能</v>
       </c>
       <c r="O74" t="str">
         <v/>
@@ -3904,28 +3904,28 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>尿糖（半定量）</v>
+        <v>尿潜血反応</v>
       </c>
       <c r="B75" t="str">
-        <v>尿糖,U-Glu</v>
+        <v>尿潜血,U-OB</v>
       </c>
       <c r="C75" t="str">
         <v>陰性（－）</v>
       </c>
       <c r="D75" t="str">
-        <v>尿に糖が漏れ出ていないかを見る検査。血糖値がかなり高いと陽性になる</v>
+        <v>尿に血液（赤血球）が混じっていないかを見る検査</v>
       </c>
       <c r="E75" t="str">
-        <v>通常、糖は尿にはほとんど出ませんが、血糖値がかなり高くなると尿にあふれ出るようになります。血糖コントロールの目安の一つです。</v>
+        <v>この検査は、尿に目に見えないくらいの微量の血液が混じっていないかを調べるものです。陽性の場合、腎臓や膀胱、尿路のどこかに炎症や結石などがある可能性があります。</v>
       </c>
       <c r="F75" t="str">
-        <v>糖尿病（血糖値が腎臓で再吸収できる量を超えている状態）、腎性糖尿（血糖値が正常でも体質的に出ることがある）、SGLT2阻害薬服用中（薬の作用で意図的に糖を排泄するため陽性になるのが正常）</v>
+        <v>尿路結石、膀胱炎などの尿路感染症、腎炎、腫瘍、月経血の混入、激しい運動後</v>
       </c>
       <c r="G75" t="str">
-        <v>SGLT2阻害薬（フォシーガ、ジャディアンスなど）服用中は、陽性が薬の効果によるものであることを説明する。脱水や尿路感染の症状がないかも確認する</v>
+        <v>排尿時の痛みや頻尿、目に見える血尿の有無を確認する。女性は月経の時期と重なっていないか確認する</v>
       </c>
       <c r="H75" t="str">
-        <v>SGLT2阻害薬(薬理作用による陽性であれば想定内であることを説明)</v>
+        <v>ワルファリン、DOAC、抗血小板薬など出血傾向を強める薬剤の服用状況を確認</v>
       </c>
       <c r="I75" t="str">
         <v/>
@@ -3937,13 +3937,13 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>SGLT2阻害薬服用中は尿糖陽性が治療効果として想定内であることを患者に伝える。血糖値・HbA1cと合わせて評価する</v>
+        <v>陽性でも尿沈渣で赤血球が確認されない場合は偽陽性（ミオグロビン尿など）のこともある。持続する場合は泌尿器科的な精査が必要</v>
       </c>
       <c r="M75" t="str">
-        <v>糖尿病</v>
+        <v>腎機能</v>
       </c>
       <c r="N75" t="str">
-        <v>尿糖,糖半定量,U-Glu,腎性糖尿,SGLT2</v>
+        <v>尿潜血,潜血反応,U-OB,血尿,尿路結石,膀胱炎</v>
       </c>
       <c r="O75" t="str">
         <v/>
@@ -3951,31 +3951,31 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>血清CPR（Cペプチド）</v>
+        <v>尿糖（半定量）</v>
       </c>
       <c r="B76" t="str">
-        <v>CPR</v>
+        <v>尿糖,U-Glu</v>
       </c>
       <c r="C76" t="str">
-        <v>空腹時 0.6〜3.0 ng/mL（施設差あり）</v>
+        <v>陰性（－）</v>
       </c>
       <c r="D76" t="str">
-        <v>自分の膵臓がどれくらいインスリンを作れているかを表す指標</v>
+        <v>尿に糖が漏れ出ていないかを見る検査。血糖値がかなり高いと陽性になる</v>
       </c>
       <c r="E76" t="str">
-        <v>この検査は、ご自身の膵臓がどれくらいインスリンを作る力を持っているかを見るものです。数値が低いほど、体の中で作れるインスリンが少ないことを示します。</v>
+        <v>通常、糖は尿にはほとんど出ませんが、血糖値がかなり高くなると尿にあふれ出るようになります。血糖コントロールの目安の一つです。</v>
       </c>
       <c r="F76" t="str">
-        <v>インスリン抵抗性が強い状態（初期の2型糖尿病など）</v>
+        <v>糖尿病（血糖値が腎臓で再吸収できる量を超えている状態）、腎性糖尿（血糖値が正常でも体質的に出ることがある）、SGLT2阻害薬服用中（薬の作用で意図的に糖を排泄するため陽性になるのが正常）</v>
       </c>
       <c r="G76" t="str">
-        <v/>
+        <v>SGLT2阻害薬（フォシーガ、ジャディアンスなど）服用中は、陽性が薬の効果によるものであることを説明する。脱水や尿路感染の症状がないかも確認する</v>
       </c>
       <c r="H76" t="str">
-        <v/>
+        <v>SGLT2阻害薬(薬理作用による陽性であれば想定内であることを説明)</v>
       </c>
       <c r="I76" t="str">
-        <v>膵臓のインスリン分泌能低下（1型糖尿病、糖尿病の進行）</v>
+        <v/>
       </c>
       <c r="J76" t="str">
         <v/>
@@ -3984,13 +3984,13 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>インスリン分泌能の評価に使われる。数値が低いほどインスリン治療の必要性が高いと判断される目安になる</v>
+        <v>SGLT2阻害薬服用中は尿糖陽性が治療効果として想定内であることを患者に伝える。血糖値・HbA1cと合わせて評価する</v>
       </c>
       <c r="M76" t="str">
         <v>糖尿病</v>
       </c>
       <c r="N76" t="str">
-        <v>CPR,Cペプチド,インスリン分泌,血清CPR</v>
+        <v>尿糖,糖半定量,U-Glu,腎性糖尿,SGLT2</v>
       </c>
       <c r="O76" t="str">
         <v/>
@@ -3998,31 +3998,31 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>尿中微量アルブミン</v>
+        <v>血清CPR（Cペプチド）</v>
       </c>
       <c r="B77" t="str">
-        <v>U-Alb,MAU</v>
+        <v>CPR</v>
       </c>
       <c r="C77" t="str">
-        <v>30 mg/gCr未満（尿中アルブミン/クレアチニン比）</v>
+        <v>空腹時 0.6〜3.0 ng/mL（施設差あり）</v>
       </c>
       <c r="D77" t="str">
-        <v>通常の尿蛋白検査では見つからない、ごく早期の腎症のサイン</v>
+        <v>自分の膵臓がどれくらいインスリンを作れているかを表す指標</v>
       </c>
       <c r="E77" t="str">
-        <v>この検査は、通常の尿検査ではまだ分からないくらい早い段階の腎臓の変化を見つけるためのものです。数値が高いと、腎症の初期のサインである可能性があります。</v>
+        <v>この検査は、ご自身の膵臓がどれくらいインスリンを作る力を持っているかを見るものです。数値が低いほど、体の中で作れるインスリンが少ないことを示します。</v>
       </c>
       <c r="F77" t="str">
-        <v>糖尿病性腎症の早期段階、高血圧</v>
+        <v>インスリン抵抗性が強い状態（初期の2型糖尿病など）</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>NSAIDsなど腎機能を悪化させる薬剤。ACE阻害薬・ARB・SGLT2阻害薬は低下させる方向に働く</v>
+        <v/>
       </c>
       <c r="I77" t="str">
-        <v/>
+        <v>膵臓のインスリン分泌能低下（1型糖尿病、糖尿病の進行）</v>
       </c>
       <c r="J77" t="str">
         <v/>
@@ -4031,13 +4031,13 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>糖尿病腎症の早期発見に重要な検査。血糖・血圧コントロールで改善しうる段階なので、早期介入の意義を伝える</v>
+        <v>インスリン分泌能の評価に使われる。数値が低いほどインスリン治療の必要性が高いと判断される目安になる</v>
       </c>
       <c r="M77" t="str">
-        <v>糖尿病,腎機能</v>
+        <v>糖尿病</v>
       </c>
       <c r="N77" t="str">
-        <v>微量アルブミン,U-Alb,MAU,糖尿病性腎症,早期腎症</v>
+        <v>CPR,Cペプチド,インスリン分泌,血清CPR</v>
       </c>
       <c r="O77" t="str">
         <v/>
@@ -4045,93 +4045,93 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>血清鉄（Fe）</v>
+        <v>尿中微量アルブミン</v>
       </c>
       <c r="B78" t="str">
-        <v>Fe</v>
+        <v>U-Alb,MAU</v>
       </c>
       <c r="C78" t="str">
-        <v>60〜200 μg/dL（施設差あり）</v>
+        <v>30 mg/gCr未満（尿中アルブミン/クレアチニン比）</v>
       </c>
       <c r="D78" t="str">
-        <v>血液中を流れている鉄の量</v>
+        <v>通常の尿蛋白検査では見つからない、ごく早期の腎症のサイン</v>
       </c>
       <c r="E78" t="str">
-        <v>この検査は、今血液の中を流れている鉄の量を見るものです。低いと、体の中で鉄が不足している可能性があります。</v>
+        <v>この検査は、通常の尿検査ではまだ分からないくらい早い段階の腎臓の変化を見つけるためのものです。数値が高いと、腎症の初期のサインである可能性があります。</v>
       </c>
       <c r="F78" t="str">
-        <v>鉄剤の過剰摂取、溶血、肝疾患</v>
+        <v>糖尿病性腎症の早期段階、高血圧</v>
       </c>
       <c r="G78" t="str">
-        <v/>
+        <v>血糖・血圧のコントロール状況を確認する。減塩や適正体重の維持など生活習慣の見直しも早期腎症の進行予防に役立つことを伝える</v>
       </c>
       <c r="H78" t="str">
-        <v>鉄剤の過量摂取(小児の誤飲を含む)</v>
+        <v>NSAIDsなど腎機能を悪化させる薬剤。ACE阻害薬・ARB・SGLT2阻害薬は低下させる方向に働く</v>
       </c>
       <c r="I78" t="str">
-        <v>鉄欠乏性貧血、慢性炎症、出血</v>
+        <v/>
       </c>
       <c r="J78" t="str">
-        <v>鉄分の多い食品（レバー・赤身肉・魚・ほうれん草など）を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える</v>
+        <v/>
       </c>
       <c r="K78" t="str">
-        <v>プロトンポンプ阻害薬(PPI)・H2ブロッカーは胃酸分泌抑制により鉄の吸収を低下させうる</v>
+        <v/>
       </c>
       <c r="L78" t="str">
-        <v>血清鉄は日内変動が大きい。単独で判断せず総鉄結合能・フェリチンと合わせて評価する</v>
+        <v>糖尿病腎症の早期発見に重要な検査。血糖・血圧コントロールで改善しうる段階なので、早期介入の意義を伝える</v>
       </c>
       <c r="M78" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>糖尿病,腎機能</v>
       </c>
       <c r="N78" t="str">
-        <v>血清鉄,Fe,鉄欠乏性貧血</v>
+        <v>微量アルブミン,U-Alb,MAU,糖尿病性腎症,早期腎症</v>
       </c>
       <c r="O78" t="str">
-        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
+        <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>総鉄結合能（TIBC）</v>
+        <v>血清鉄（Fe）</v>
       </c>
       <c r="B79" t="str">
-        <v>TIBC</v>
+        <v>Fe</v>
       </c>
       <c r="C79" t="str">
-        <v>250〜360 μg/dL（施設差あり）</v>
+        <v>60〜200 μg/dL（施設差あり）</v>
       </c>
       <c r="D79" t="str">
-        <v>血液中のトランスフェリンが鉄と結合できる総量</v>
+        <v>血液中を流れている鉄の量</v>
       </c>
       <c r="E79" t="str">
-        <v>TIBCは、血液中でトランスフェリンという物質が鉄を運べる最大量を表します。体の中の鉄が不足すると、少しでも多く鉄を運ぼうとしてこの数値が上がる性質があります。</v>
+        <v>この検査は、今血液の中を流れている鉄の量を見るものです。低いと、体の中で鉄が不足している可能性があります。</v>
       </c>
       <c r="F79" t="str">
-        <v>鉄欠乏性貧血（＞360 μg/dLが目安）</v>
+        <v>鉄剤の過剰摂取、溶血、肝疾患</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v/>
+        <v>鉄剤の過量摂取(小児の誤飲を含む)</v>
       </c>
       <c r="I79" t="str">
-        <v>慢性炎症、肝疾患、ネフローゼ症候群</v>
+        <v>鉄欠乏性貧血、慢性炎症、出血</v>
       </c>
       <c r="J79" t="str">
-        <v/>
+        <v>鉄分の多い食品（レバー・赤身肉・魚・ほうれん草など）を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える</v>
       </c>
       <c r="K79" t="str">
-        <v/>
+        <v>プロトンポンプ阻害薬(PPI)・H2ブロッカーは胃酸分泌抑制により鉄の吸収を低下させうる</v>
       </c>
       <c r="L79" t="str">
-        <v>鉄が不足すると、体はより多く運ぼうとしてTIBCが上昇する。UIBC・血清鉄と併せて評価する</v>
+        <v>血清鉄は日内変動が大きい。単独で判断せず総鉄結合能・フェリチンと合わせて評価する</v>
       </c>
       <c r="M79" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
       <c r="N79" t="str">
-        <v>TIBC,総鉄結合能,鉄欠乏性貧血</v>
+        <v>血清鉄,Fe,鉄欠乏性貧血</v>
       </c>
       <c r="O79" t="str">
         <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
@@ -4139,22 +4139,22 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>不飽和鉄結合能（UIBC）</v>
+        <v>総鉄結合能（TIBC）</v>
       </c>
       <c r="B80" t="str">
-        <v>UIBC</v>
+        <v>TIBC</v>
       </c>
       <c r="C80" t="str">
-        <v>170〜300 μg/dL（施設差あり）</v>
+        <v>250〜360 μg/dL（施設差あり）</v>
       </c>
       <c r="D80" t="str">
-        <v>トランスフェリンのうち、まだ鉄と結合していない余力の部分（UIBC＝TIBC－血清鉄）</v>
+        <v>血液中のトランスフェリンが鉄と結合できる総量</v>
       </c>
       <c r="E80" t="str">
-        <v>UIBCは、トランスフェリンのうち、まだ鉄と結合していない「空き容量」の部分を表します。鉄が不足しているときほど、この空き容量は大きくなります。</v>
+        <v>TIBCは、血液中でトランスフェリンという物質が鉄を運べる最大量を表します。体の中の鉄が不足すると、少しでも多く鉄を運ぼうとしてこの数値が上がる性質があります。</v>
       </c>
       <c r="F80" t="str">
-        <v>鉄欠乏性貧血（＞300 μg/dLが目安）</v>
+        <v>鉄欠乏性貧血（＞360 μg/dLが目安）</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -4163,7 +4163,7 @@
         <v/>
       </c>
       <c r="I80" t="str">
-        <v>慢性炎症、鉄過剰状態</v>
+        <v>慢性炎症、肝疾患、ネフローゼ症候群</v>
       </c>
       <c r="J80" t="str">
         <v/>
@@ -4172,13 +4172,13 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>TIBCと同じ方向に動くことが多い。血清鉄・TIBCとあわせて鉄欠乏性貧血と二次性貧血の鑑別に使う</v>
+        <v>鉄が不足すると、体はより多く運ぼうとしてTIBCが上昇する。UIBC・血清鉄と併せて評価する</v>
       </c>
       <c r="M80" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
       <c r="N80" t="str">
-        <v>UIBC,不飽和鉄結合能,鉄欠乏性貧血</v>
+        <v>TIBC,総鉄結合能,鉄欠乏性貧血</v>
       </c>
       <c r="O80" t="str">
         <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
@@ -4186,22 +4186,22 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>トランスフェリン飽和度</v>
+        <v>不飽和鉄結合能（UIBC）</v>
       </c>
       <c r="B81" t="str">
-        <v>TSAT</v>
+        <v>UIBC</v>
       </c>
       <c r="C81" t="str">
-        <v>16〜50%程度（施設差あり）</v>
+        <v>170〜300 μg/dL（施設差あり）</v>
       </c>
       <c r="D81" t="str">
-        <v>鉄を運ぶ役割のトランスフェリンのうち、実際に鉄を運んでいる割合（血清鉄÷総鉄結合能）</v>
+        <v>トランスフェリンのうち、まだ鉄と結合していない余力の部分（UIBC＝TIBC－血清鉄）</v>
       </c>
       <c r="E81" t="str">
-        <v>トランスフェリン飽和度は、鉄を運ぶトランスフェリンのうち、実際にどれくらいが鉄を運んでいるかを割合で表したものです。鉄欠乏性貧血では低くなり、鉄が過剰にたまる病気では高くなります。</v>
+        <v>UIBCは、トランスフェリンのうち、まだ鉄と結合していない「空き容量」の部分を表します。鉄が不足しているときほど、この空き容量は大きくなります。</v>
       </c>
       <c r="F81" t="str">
-        <v>鉄過剰症（ヘモクロマトーシスなど）</v>
+        <v>鉄欠乏性貧血（＞300 μg/dLが目安）</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -4210,7 +4210,7 @@
         <v/>
       </c>
       <c r="I81" t="str">
-        <v>鉄欠乏性貧血（＜16%が目安）</v>
+        <v>慢性炎症、鉄過剰状態</v>
       </c>
       <c r="J81" t="str">
         <v/>
@@ -4219,13 +4219,13 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>血清鉄をTIBCで割って計算される。鉄剤補充の効果判定にも使われる</v>
+        <v>TIBCと同じ方向に動くことが多い。血清鉄・TIBCとあわせて鉄欠乏性貧血と二次性貧血の鑑別に使う</v>
       </c>
       <c r="M81" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
       <c r="N81" t="str">
-        <v>トランスフェリン飽和度,TSAT,鉄欠乏性貧血</v>
+        <v>UIBC,不飽和鉄結合能,鉄欠乏性貧血</v>
       </c>
       <c r="O81" t="str">
         <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
@@ -4233,22 +4233,22 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>血清フェリチン</v>
+        <v>トランスフェリン飽和度</v>
       </c>
       <c r="B82" t="str">
-        <v>Ferritin</v>
+        <v>TSAT</v>
       </c>
       <c r="C82" t="str">
-        <v>男性 20〜250 ng/mL、女性 10〜120 ng/mL（施設差あり）</v>
+        <v>16〜50%程度（施設差あり）</v>
       </c>
       <c r="D82" t="str">
-        <v>体に貯蔵されている鉄の量を反映する指標。貧血の症状が出るより早い段階で低下する</v>
+        <v>鉄を運ぶ役割のトランスフェリンのうち、実際に鉄を運んでいる割合（血清鉄÷総鉄結合能）</v>
       </c>
       <c r="E82" t="str">
-        <v>フェリチンは、体に蓄えられている鉄の「貯金」の量を見る検査です。この数値が下がるのは、貧血の症状が出るよりも前の、とても早い段階のサインになります。</v>
+        <v>トランスフェリン飽和度は、鉄を運ぶトランスフェリンのうち、実際にどれくらいが鉄を運んでいるかを割合で表したものです。鉄欠乏性貧血では低くなり、鉄が過剰にたまる病気では高くなります。</v>
       </c>
       <c r="F82" t="str">
-        <v>炎症性疾患、肝疾患、悪性腫瘍、鉄過剰症（フェリチンは炎症でも上昇するため、貧血の評価では注意が必要）</v>
+        <v>鉄過剰症（ヘモクロマトーシスなど）</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -4257,22 +4257,22 @@
         <v/>
       </c>
       <c r="I82" t="str">
-        <v>鉄欠乏状態（貧血の症状が出る前の早期段階から低下する）</v>
+        <v>鉄欠乏性貧血（＜16%が目安）</v>
       </c>
       <c r="J82" t="str">
-        <v>鉄分の多い食品を意識するとともに、貯蔵鉄を補うため治療は数値が正常化してからも継続が必要なことを伝える</v>
+        <v/>
       </c>
       <c r="K82" t="str">
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>貯蔵鉄の指標で鉄欠乏を最も早期に反映する。ただし炎症があると鉄欠乏があっても正常〜高値に出ることがあり、CRP等の炎症所見と合わせて評価する。二次性貧血との鑑別に重要</v>
+        <v>血清鉄をTIBCで割って計算される。鉄剤補充の効果判定にも使われる</v>
       </c>
       <c r="M82" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
       <c r="N82" t="str">
-        <v>フェリチン,Ferritin,貯蔵鉄,鉄欠乏</v>
+        <v>トランスフェリン飽和度,TSAT,鉄欠乏性貧血</v>
       </c>
       <c r="O82" t="str">
         <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
@@ -4280,22 +4280,22 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>尿中尿酸/クレアチニン比（UUA/UCr）</v>
+        <v>血清フェリチン</v>
       </c>
       <c r="B83" t="str">
-        <v>UUA/UCr</v>
+        <v>Ferritin</v>
       </c>
       <c r="C83" t="str">
-        <v>0.4〜0.8程度が混合型の目安</v>
+        <v>男性 20〜250 ng/mL、女性 10〜120 ng/mL（施設差あり）</v>
       </c>
       <c r="D83" t="str">
-        <v>尿酸が「作られすぎ」か「排泄できていない」かを見分ける比の値</v>
+        <v>体に貯蔵されている鉄の量を反映する指標。貧血の症状が出るより早い段階で低下する</v>
       </c>
       <c r="E83" t="str">
-        <v>この数値は、体の中で尿酸が「作られすぎている」のか、それとも「うまく排泄できていない」のかを見分けるために使う比の値です。高尿酸血症の治療薬を選ぶときの参考になります。</v>
+        <v>フェリチンは、体に蓄えられている鉄の「貯金」の量を見る検査です。この数値が下がるのは、貧血の症状が出るよりも前の、とても早い段階のサインになります。</v>
       </c>
       <c r="F83" t="str">
-        <v>尿酸産生過剰型（0.8以上が目安）</v>
+        <v>炎症性疾患、肝疾患、悪性腫瘍、鉄過剰症（フェリチンは炎症でも上昇するため、貧血の評価では注意が必要）</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -4304,45 +4304,45 @@
         <v/>
       </c>
       <c r="I83" t="str">
-        <v>尿酸排泄低下型（0.4以下が目安）</v>
+        <v>鉄欠乏状態（貧血の症状が出る前の早期段階から低下する）</v>
       </c>
       <c r="J83" t="str">
-        <v/>
+        <v>鉄分の多い食品を意識するとともに、貯蔵鉄を補うため治療は数値が正常化してからも継続が必要なことを伝える</v>
       </c>
       <c r="K83" t="str">
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>高尿酸血症は尿酸産生過剰型・排泄低下型・混合型に分類され、この比が目安になる。病型によって使う薬剤（尿酸生成抑制薬か尿酸排泄促進薬か）の選択が変わる</v>
+        <v>貯蔵鉄の指標で鉄欠乏を最も早期に反映する。ただし炎症があると鉄欠乏があっても正常〜高値に出ることがあり、CRP等の炎症所見と合わせて評価する。二次性貧血との鑑別に重要</v>
       </c>
       <c r="M83" t="str">
-        <v>高尿酸血症</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="N83" t="str">
-        <v>UUA,UCr,尿酸クリアランス,CUA,EUA,尿酸産生過剰型,尿酸排泄低下型</v>
+        <v>フェリチン,Ferritin,貯蔵鉄,鉄欠乏</v>
       </c>
       <c r="O83" t="str">
-        <v>食事と栄養 p.180-189（第2部 痛風・高尿酸血症）</v>
+        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>ucOC（低カルボキシル化オステオカルシン）</v>
+        <v>尿中尿酸/クレアチニン比（UUA/UCr）</v>
       </c>
       <c r="B84" t="str">
-        <v>ucOC</v>
+        <v>UUA/UCr</v>
       </c>
       <c r="C84" t="str">
-        <v>4.5 ng/mL未満（施設差あり）</v>
+        <v>0.4〜0.8程度が混合型の目安</v>
       </c>
       <c r="D84" t="str">
-        <v>ビタミンKが不足していないかを反映する骨の指標</v>
+        <v>尿酸が「作られすぎ」か「排泄できていない」かを見分ける比の値</v>
       </c>
       <c r="E84" t="str">
-        <v>ucOCは、骨を作るために必要なビタミンKが体の中で足りているかどうかを反映する検査です。数値が高いとビタミンK不足が疑われます。</v>
+        <v>この数値は、体の中で尿酸が「作られすぎている」のか、それとも「うまく排泄できていない」のかを見分けるために使う比の値です。高尿酸血症の治療薬を選ぶときの参考になります。</v>
       </c>
       <c r="F84" t="str">
-        <v>ビタミンK不足状態</v>
+        <v>尿酸産生過剰型（0.8以上が目安）</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -4351,7 +4351,7 @@
         <v/>
       </c>
       <c r="I84" t="str">
-        <v/>
+        <v>尿酸排泄低下型（0.4以下が目安）</v>
       </c>
       <c r="J84" t="str">
         <v/>
@@ -4360,45 +4360,45 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>ビタミンK2製剤（骨粗鬆症治療薬）の適応判断や効果判定に使われる</v>
+        <v>高尿酸血症は尿酸産生過剰型・排泄低下型・混合型に分類され、この比が目安になる。病型によって使う薬剤（尿酸生成抑制薬か尿酸排泄促進薬か）の選択が変わる</v>
       </c>
       <c r="M84" t="str">
-        <v>骨粗鬆症</v>
+        <v>高尿酸血症</v>
       </c>
       <c r="N84" t="str">
-        <v>ucOC,オステオカルシン,ビタミンK</v>
+        <v>UUA,UCr,尿酸クリアランス,CUA,EUA,尿酸産生過剰型,尿酸排泄低下型</v>
       </c>
       <c r="O84" t="str">
-        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
+        <v>食事と栄養 p.180-189（第2部 痛風・高尿酸血症）</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>PTH（副甲状腺ホルモン）</v>
+        <v>ucOC（低カルボキシル化オステオカルシン）</v>
       </c>
       <c r="B85" t="str">
-        <v>PTH</v>
+        <v>ucOC</v>
       </c>
       <c r="C85" t="str">
-        <v>10〜65 pg/mL（施設差あり）</v>
+        <v>4.5 ng/mL未満（施設差あり）</v>
       </c>
       <c r="D85" t="str">
-        <v>血液中のカルシウム濃度を調節するホルモン</v>
+        <v>ビタミンKが不足していないかを反映する骨の指標</v>
       </c>
       <c r="E85" t="str">
-        <v>PTHは、血液中のカルシウム濃度を一定に保つために働くホルモンです。カルシウムが低くなると分泌が増え、骨からカルシウムを取り出したり、腎臓での再吸収を促したりして数値を戻そうとします。</v>
+        <v>ucOCは、骨を作るために必要なビタミンKが体の中で足りているかどうかを反映する検査です。数値が高いとビタミンK不足が疑われます。</v>
       </c>
       <c r="F85" t="str">
-        <v>原発性・二次性副甲状腺機能亢進症（腎不全に伴うものなど）</v>
+        <v>ビタミンK不足状態</v>
       </c>
       <c r="G85" t="str">
-        <v/>
+        <v>ビタミンK2製剤(骨粗鬆症治療薬)の適応が検討されているか確認する。ワルファリン服用中の患者では、納豆などビタミンKを多く含む食品の急な摂取量の変化を避けるよう説明する</v>
       </c>
       <c r="H85" t="str">
         <v/>
       </c>
       <c r="I85" t="str">
-        <v>副甲状腺機能低下症</v>
+        <v/>
       </c>
       <c r="J85" t="str">
         <v/>
@@ -4407,13 +4407,13 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>骨粗鬆症の二次性原因（副甲状腺機能亢進症）を除外するための検査。カルシウム・リンと合わせて評価する</v>
+        <v>ビタミンK2製剤（骨粗鬆症治療薬）の適応判断や効果判定に使われる</v>
       </c>
       <c r="M85" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="N85" t="str">
-        <v>PTH,副甲状腺ホルモン,パラトルモン</v>
+        <v>ucOC,オステオカルシン,ビタミンK</v>
       </c>
       <c r="O85" t="str">
         <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>尿中NTX</v>
+        <v>PTH（副甲状腺ホルモン）</v>
       </c>
       <c r="B86" t="str">
-        <v>NTX</v>
+        <v>PTH</v>
       </c>
       <c r="C86" t="str">
-        <v>施設差が大きく一律の記載が難しい（尿中）</v>
+        <v>10〜65 pg/mL（施設差あり）</v>
       </c>
       <c r="D86" t="str">
-        <v>骨が壊されるときに出る、骨吸収マーカーのひとつ</v>
+        <v>血液中のカルシウム濃度を調節するホルモン</v>
       </c>
       <c r="E86" t="str">
-        <v>NTXは、骨が壊される（吸収される）ときに尿の中に出てくる物質です。骨粗鬆症の治療薬がどれくらい効いているかを確認するために使われます。</v>
+        <v>PTHは、血液中のカルシウム濃度を一定に保つために働くホルモンです。カルシウムが低くなると分泌が増え、骨からカルシウムを取り出したり、腎臓での再吸収を促したりして数値を戻そうとします。</v>
       </c>
       <c r="F86" t="str">
-        <v>骨代謝回転の亢進（骨粗鬆症、閉経後など）</v>
+        <v>原発性・二次性副甲状腺機能亢進症（腎不全に伴うものなど）</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -4445,7 +4445,7 @@
         <v/>
       </c>
       <c r="I86" t="str">
-        <v>骨吸収抑制薬（ビスホスホネート等）による治療効果</v>
+        <v>副甲状腺機能低下症</v>
       </c>
       <c r="J86" t="str">
         <v/>
@@ -4454,13 +4454,13 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>治療開始後3〜6か月で再検し、薬の効果判定に使われる。TRACP-5bと同じ「骨を壊す側」の指標</v>
+        <v>骨粗鬆症の二次性原因（副甲状腺機能亢進症）を除外するための検査。カルシウム・リンと合わせて評価する</v>
       </c>
       <c r="M86" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="N86" t="str">
-        <v>NTX,尿中NTX,骨吸収マーカー</v>
+        <v>PTH,副甲状腺ホルモン,パラトルモン</v>
       </c>
       <c r="O86" t="str">
         <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
@@ -4468,22 +4468,22 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>カルシトニン</v>
+        <v>尿中NTX</v>
       </c>
       <c r="B87" t="str">
-        <v>CT</v>
+        <v>NTX</v>
       </c>
       <c r="C87" t="str">
-        <v>男性 9.52 pg/mL未満、女性 6.40 pg/mL未満（施設差あり）</v>
+        <v>施設差が大きく一律の記載が難しい（尿中）</v>
       </c>
       <c r="D87" t="str">
-        <v>血液中のカルシウムを下げる方向に働くホルモン</v>
+        <v>骨が壊されるときに出る、骨吸収マーカーのひとつ</v>
       </c>
       <c r="E87" t="str">
-        <v>カルシトニンは、PTHとは逆に血液中のカルシウムを下げる方向に働くホルモンです。特定の甲状腺の病気（甲状腺髄様癌）がないかを調べる際にも使われます。</v>
+        <v>NTXは、骨が壊される（吸収される）ときに尿の中に出てくる物質です。骨粗鬆症の治療薬がどれくらい効いているかを確認するために使われます。</v>
       </c>
       <c r="F87" t="str">
-        <v>甲状腺髄様癌、腎不全</v>
+        <v>骨代謝回転の亢進（骨粗鬆症、閉経後など）</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -4492,7 +4492,7 @@
         <v/>
       </c>
       <c r="I87" t="str">
-        <v/>
+        <v>骨吸収抑制薬（ビスホスホネート等）による治療効果</v>
       </c>
       <c r="J87" t="str">
         <v/>
@@ -4501,13 +4501,13 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>骨粗鬆症の二次性原因の除外目的で測定されることがある検査値。同名の薬剤（カルシトニン製剤）と混同しないよう注意</v>
+        <v>治療開始後3〜6か月で再検し、薬の効果判定に使われる。TRACP-5bと同じ「骨を壊す側」の指標</v>
       </c>
       <c r="M87" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="N87" t="str">
-        <v>カルシトニン,CT</v>
+        <v>NTX,尿中NTX,骨吸収マーカー</v>
       </c>
       <c r="O87" t="str">
         <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
@@ -4515,22 +4515,22 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>DPD（デオキシピリジノリン）</v>
+        <v>カルシトニン</v>
       </c>
       <c r="B88" t="str">
-        <v>DPD</v>
+        <v>CT</v>
       </c>
       <c r="C88" t="str">
-        <v>施設差が大きく一律の記載が難しい（尿中）</v>
+        <v>男性 9.52 pg/mL未満、女性 6.40 pg/mL未満（施設差あり）</v>
       </c>
       <c r="D88" t="str">
-        <v>骨のコラーゲンが壊れるときに出る、骨吸収マーカーのひとつ</v>
+        <v>血液中のカルシウムを下げる方向に働くホルモン</v>
       </c>
       <c r="E88" t="str">
-        <v>DPDも、骨が壊されるときに尿に出てくる物質の一つです。NTXと同じように、骨粗鬆症治療薬の効果を確認するために使われます。</v>
+        <v>カルシトニンは、PTHとは逆に血液中のカルシウムを下げる方向に働くホルモンです。特定の甲状腺の病気（甲状腺髄様癌）がないかを調べる際にも使われます。</v>
       </c>
       <c r="F88" t="str">
-        <v>骨代謝回転の亢進（骨粗鬆症など）</v>
+        <v>甲状腺髄様癌、腎不全</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -4539,7 +4539,7 @@
         <v/>
       </c>
       <c r="I88" t="str">
-        <v>骨吸収抑制薬による治療効果</v>
+        <v/>
       </c>
       <c r="J88" t="str">
         <v/>
@@ -4548,13 +4548,13 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>NTX・CTXと同じ「骨を壊す側」の指標。食事の影響を受けにくいとされる</v>
+        <v>骨粗鬆症の二次性原因の除外目的で測定されることがある検査値。同名の薬剤（カルシトニン製剤）と混同しないよう注意</v>
       </c>
       <c r="M88" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="N88" t="str">
-        <v>DPD,デオキシピリジノリン,骨吸収マーカー</v>
+        <v>カルシトニン,CT</v>
       </c>
       <c r="O88" t="str">
         <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
@@ -4562,19 +4562,19 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>CTX</v>
+        <v>DPD（デオキシピリジノリン）</v>
       </c>
       <c r="B89" t="str">
-        <v>CTX</v>
+        <v>DPD</v>
       </c>
       <c r="C89" t="str">
-        <v>施設差が大きく一律の記載が難しい（血清・尿中）</v>
+        <v>施設差が大きく一律の記載が難しい（尿中）</v>
       </c>
       <c r="D89" t="str">
         <v>骨のコラーゲンが壊れるときに出る、骨吸収マーカーのひとつ</v>
       </c>
       <c r="E89" t="str">
-        <v>CTXも、骨が壊されるときに血液や尿に出てくる物質です。骨粗鬆症治療薬（骨を壊すのを抑える薬）の効果を確認するために使われます。</v>
+        <v>DPDも、骨が壊されるときに尿に出てくる物質の一つです。NTXと同じように、骨粗鬆症治療薬の効果を確認するために使われます。</v>
       </c>
       <c r="F89" t="str">
         <v>骨代謝回転の亢進（骨粗鬆症など）</v>
@@ -4595,13 +4595,13 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>NTX・DPDと同じ「骨を壊す側」の指標。血清・尿中いずれでも測定されることがある</v>
+        <v>NTX・CTXと同じ「骨を壊す側」の指標。食事の影響を受けにくいとされる</v>
       </c>
       <c r="M89" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="N89" t="str">
-        <v>CTX,骨吸収マーカー</v>
+        <v>DPD,デオキシピリジノリン,骨吸収マーカー</v>
       </c>
       <c r="O89" t="str">
         <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
@@ -4609,22 +4609,22 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>P1NP</v>
+        <v>CTX</v>
       </c>
       <c r="B90" t="str">
-        <v>P1NP</v>
+        <v>CTX</v>
       </c>
       <c r="C90" t="str">
-        <v>施設差が大きく一律の記載が難しい（血清）</v>
+        <v>施設差が大きく一律の記載が難しい（血清・尿中）</v>
       </c>
       <c r="D90" t="str">
-        <v>骨が新しく作られるときに出る、骨形成マーカーのひとつ</v>
+        <v>骨のコラーゲンが壊れるときに出る、骨吸収マーカーのひとつ</v>
       </c>
       <c r="E90" t="str">
-        <v>P1NPは、CTXなどとは逆に、骨が新しく作られるときに血液中に出てくる物質です。骨を作る力を高める薬（テリパラチドなど）の効果を確認するために使われます。</v>
+        <v>CTXも、骨が壊されるときに血液や尿に出てくる物質です。骨粗鬆症治療薬（骨を壊すのを抑える薬）の効果を確認するために使われます。</v>
       </c>
       <c r="F90" t="str">
-        <v>骨代謝回転の亢進、骨形成促進薬による治療効果</v>
+        <v>骨代謝回転の亢進（骨粗鬆症など）</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -4633,7 +4633,7 @@
         <v/>
       </c>
       <c r="I90" t="str">
-        <v>骨形成の低下</v>
+        <v>骨吸収抑制薬による治療効果</v>
       </c>
       <c r="J90" t="str">
         <v/>
@@ -4642,13 +4642,13 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>TRACP-5b等「骨を壊す側」の指標とは逆の、「骨を作る側」の指標。骨形成促進薬（テリパラチド等）の効果判定に使われる</v>
+        <v>NTX・DPDと同じ「骨を壊す側」の指標。血清・尿中いずれでも測定されることがある</v>
       </c>
       <c r="M90" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="N90" t="str">
-        <v>P1NP,骨形成マーカー</v>
+        <v>CTX,骨吸収マーカー</v>
       </c>
       <c r="O90" t="str">
         <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
@@ -4656,22 +4656,22 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>抗甲状腺マイクロゾーム抗体（抗TPO抗体）</v>
+        <v>P1NP</v>
       </c>
       <c r="B91" t="str">
-        <v>TPOAb</v>
+        <v>P1NP</v>
       </c>
       <c r="C91" t="str">
-        <v>陰性（16 IU/mL未満程度、施設差あり）</v>
+        <v>施設差が大きく一律の記載が難しい（血清）</v>
       </c>
       <c r="D91" t="str">
-        <v>自分の甲状腺を攻撃する抗体が出ていないかを見る検査</v>
+        <v>骨が新しく作られるときに出る、骨形成マーカーのひとつ</v>
       </c>
       <c r="E91" t="str">
-        <v>この検査は、体の中に自分の甲状腺を誤って攻撃してしまう抗体がないかを見るものです。陽性の場合、橋本病（慢性甲状腺炎）など甲状腺の自己免疫的な炎症が背景にある可能性があります。</v>
+        <v>P1NPは、CTXなどとは逆に、骨が新しく作られるときに血液中に出てくる物質です。骨を作る力を高める薬（テリパラチドなど）の効果を確認するために使われます。</v>
       </c>
       <c r="F91" t="str">
-        <v>橋本病（慢性甲状腺炎）、バセドウ病などの自己免疫性甲状腺疾患</v>
+        <v>骨代謝回転の亢進、骨形成促進薬による治療効果</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -4680,7 +4680,7 @@
         <v/>
       </c>
       <c r="I91" t="str">
-        <v/>
+        <v>骨形成の低下</v>
       </c>
       <c r="J91" t="str">
         <v/>
@@ -4689,33 +4689,33 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>陽性でも必ずしも甲状腺機能異常があるとは限らない。TSH・FT4など甲状腺ホルモンの数値と合わせて評価する</v>
+        <v>TRACP-5b等「骨を壊す側」の指標とは逆の、「骨を作る側」の指標。骨形成促進薬（テリパラチド等）の効果判定に使われる</v>
       </c>
       <c r="M91" t="str">
-        <v>甲状腺疾患</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="N91" t="str">
-        <v>抗TPO抗体,抗甲状腺マイクロゾーム抗体,TPOAb,橋本病</v>
+        <v>P1NP,骨形成マーカー</v>
       </c>
       <c r="O91" t="str">
-        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>抗サイログロブリン抗体</v>
+        <v>抗甲状腺マイクロゾーム抗体（抗TPO抗体）</v>
       </c>
       <c r="B92" t="str">
-        <v>TgAb</v>
+        <v>TPOAb</v>
       </c>
       <c r="C92" t="str">
-        <v>陰性（28 IU/mL未満程度、施設差あり）</v>
+        <v>陰性（16 IU/mL未満程度、施設差あり）</v>
       </c>
       <c r="D92" t="str">
-        <v>甲状腺のたんぱく質（サイログロブリン）への抗体が出ていないかを見る検査</v>
+        <v>自分の甲状腺を攻撃する抗体が出ていないかを見る検査</v>
       </c>
       <c r="E92" t="str">
-        <v>この検査も、抗TPO抗体と同じく、甲状腺に対する自己免疫の有無を見るものです。あわせて調べることで橋本病などの診断の参考にします。</v>
+        <v>この検査は、体の中に自分の甲状腺を誤って攻撃してしまう抗体がないかを見るものです。陽性の場合、橋本病（慢性甲状腺炎）など甲状腺の自己免疫的な炎症が背景にある可能性があります。</v>
       </c>
       <c r="F92" t="str">
         <v>橋本病（慢性甲状腺炎）、バセドウ病などの自己免疫性甲状腺疾患</v>
@@ -4736,13 +4736,13 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>抗TPO抗体とあわせて測定されることが多い。単独の高値だけで治療方針が決まるわけではない</v>
+        <v>陽性でも必ずしも甲状腺機能異常があるとは限らない。TSH・FT4など甲状腺ホルモンの数値と合わせて評価する</v>
       </c>
       <c r="M92" t="str">
         <v>甲状腺疾患</v>
       </c>
       <c r="N92" t="str">
-        <v>抗サイログロブリン抗体,TgAb,橋本病</v>
+        <v>抗TPO抗体,抗甲状腺マイクロゾーム抗体,TPOAb,橋本病</v>
       </c>
       <c r="O92" t="str">
         <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
@@ -4750,93 +4750,93 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>血中薬物濃度（TDM）</v>
+        <v>抗サイログロブリン抗体</v>
       </c>
       <c r="B93" t="str">
-        <v>TDM</v>
+        <v>TgAb</v>
       </c>
       <c r="C93" t="str">
-        <v>薬剤ごとに有効域が異なる（例：カルバマゼピン 4〜12 μg/mL、バルプロ酸 40〜100 μg/mL、フェニトイン 10〜20 μg/mL）</v>
+        <v>陰性（28 IU/mL未満程度、施設差あり）</v>
       </c>
       <c r="D93" t="str">
-        <v>治療域が狭い薬剤で、血液中の薬の濃度が効果域・中毒域のどちらにあるかを確認する検査</v>
+        <v>甲状腺のたんぱく質（サイログロブリン）への抗体が出ていないかを見る検査</v>
       </c>
       <c r="E93" t="str">
-        <v>この薬は効く量と副作用が出る量が近いため、血液中の薬の濃度を定期的に測って、ちょうどよい範囲に入っているかを確認します。数値が低いと効果が不十分になり、高いと副作用が出やすくなります。</v>
+        <v>この検査も、抗TPO抗体と同じく、甲状腺に対する自己免疫の有無を見るものです。あわせて調べることで橋本病などの診断の参考にします。</v>
       </c>
       <c r="F93" t="str">
-        <v>過量投与、代謝を妨げる薬剤との併用、肝機能低下による代謝低下</v>
+        <v>橋本病（慢性甲状腺炎）、バセドウ病などの自己免疫性甲状腺疾患</v>
       </c>
       <c r="G93" t="str">
-        <v>ふらつき、眠気、めまい、物が二重に見えるなどの中毒症状がないか確認する</v>
+        <v/>
       </c>
       <c r="H93" t="str">
         <v/>
       </c>
       <c r="I93" t="str">
-        <v>飲み忘れ、自己判断による減量、代謝を促進する薬剤との併用（相互作用）</v>
+        <v/>
       </c>
       <c r="J93" t="str">
-        <v>発作やてんかん症状の再発がないか確認し、飲み忘れがないか一緒に確認する</v>
+        <v/>
       </c>
       <c r="K93" t="str">
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>採血のタイミング（トラフ値かどうか）で数値の解釈が変わるため採血時点を確認する。カルバマゼピンは自己誘導により長期使用で濃度が下がることがある点にも注意</v>
+        <v>抗TPO抗体とあわせて測定されることが多い。単独の高値だけで治療方針が決まるわけではない</v>
       </c>
       <c r="M93" t="str">
-        <v>てんかん</v>
+        <v>甲状腺疾患</v>
       </c>
       <c r="N93" t="str">
-        <v>TDM,血中薬物濃度,治療域,中毒域,カルバマゼピン,フェニトイン,バルプロ酸,抗てんかん薬</v>
+        <v>抗サイログロブリン抗体,TgAb,橋本病</v>
       </c>
       <c r="O93" t="str">
-        <v/>
+        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>アミラーゼ（AMY）</v>
+        <v>血中薬物濃度（TDM）</v>
       </c>
       <c r="B94" t="str">
-        <v>AMY</v>
+        <v>TDM</v>
       </c>
       <c r="C94" t="str">
-        <v>44〜132 U/L（施設差あり）</v>
+        <v>薬剤ごとに有効域が異なる（例：カルバマゼピン 4〜12 μg/mL、バルプロ酸 40〜100 μg/mL、フェニトイン 10〜20 μg/mL）</v>
       </c>
       <c r="D94" t="str">
-        <v>膵臓や唾液腺から出る消化酵素。膵炎などで血液中に漏れ出す</v>
+        <v>治療域が狭い薬剤で、血液中の薬の濃度が効果域・中毒域のどちらにあるかを確認する検査</v>
       </c>
       <c r="E94" t="str">
-        <v>アミラーゼは、でんぷんを分解する消化酵素で、主に膵臓と唾液腺から作られます。膵臓に炎症が起きると血液中に漏れ出して数値が上がるため、膵炎の診断や経過観察に使われます。</v>
+        <v>この薬は効く量と副作用が出る量が近いため、血液中の薬の濃度を定期的に測って、ちょうどよい範囲に入っているかを確認します。数値が低いと効果が不十分になり、高いと副作用が出やすくなります。</v>
       </c>
       <c r="F94" t="str">
-        <v>急性膵炎、慢性膵炎の急性増悪、耳下腺炎（おたふくかぜ）、腎不全</v>
+        <v>過量投与、代謝を妨げる薬剤との併用、肝機能低下による代謝低下</v>
       </c>
       <c r="G94" t="str">
-        <v>飲酒を控える、脂っこい食事を避けるよう伝える</v>
+        <v>ふらつき、眠気、めまい、物が二重に見えるなどの中毒症状がないか確認する</v>
       </c>
       <c r="H94" t="str">
-        <v>バルプロ酸、アザチオプリン、サイアザイド系・ループ利尿薬、ステロイドなど薬剤性膵炎の原因薬</v>
+        <v/>
       </c>
       <c r="I94" t="str">
-        <v>慢性膵炎の進行期（膵臓の機能低下）</v>
+        <v>飲み忘れ、自己判断による減量、代謝を促進する薬剤との併用（相互作用）</v>
       </c>
       <c r="J94" t="str">
-        <v/>
+        <v>発作やてんかん症状の再発がないか確認し、飲み忘れがないか一緒に確認する</v>
       </c>
       <c r="K94" t="str">
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>膵臓由来か唾液腺由来かを区別するには膵型アミラーゼ(P-AMY)を確認する。急性膵炎では強い腹痛・背部痛を伴うことが多く、飲酒歴の確認も重要</v>
+        <v>採血のタイミング（トラフ値かどうか）で数値の解釈が変わるため採血時点を確認する。カルバマゼピンは自己誘導により長期使用で濃度が下がることがある点にも注意</v>
       </c>
       <c r="M94" t="str">
-        <v/>
+        <v>てんかん</v>
       </c>
       <c r="N94" t="str">
-        <v>アミラーゼ,AMY,膵炎,急性膵炎</v>
+        <v>TDM,血中薬物濃度,治療域,中毒域,カルバマゼピン,フェニトイン,バルプロ酸,抗てんかん薬</v>
       </c>
       <c r="O94" t="str">
         <v/>
@@ -4844,31 +4844,31 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>間接ビリルビン</v>
+        <v>アミラーゼ（AMY）</v>
       </c>
       <c r="B95" t="str">
-        <v>I-Bil</v>
+        <v>AMY</v>
       </c>
       <c r="C95" t="str">
-        <v>0.2〜0.8 mg/dL程度（施設差あり）</v>
+        <v>44〜132 U/L（施設差あり）</v>
       </c>
       <c r="D95" t="str">
-        <v>赤血球が壊れてできるビリルビンのうち、肝臓で処理される前の形</v>
+        <v>膵臓や唾液腺から出る消化酵素。膵炎などで血液中に漏れ出す</v>
       </c>
       <c r="E95" t="str">
-        <v>間接ビリルビンは、赤血球が壊れてできたビリルビンが、まだ肝臓で処理される前の状態です。この値が高い場合、赤血球が通常より多く壊れている(溶血)か、肝臓での処理能力に生まれつきの体質差(体質性黄疸)がある可能性が考えられます。</v>
+        <v>アミラーゼは、でんぷんを分解する消化酵素で、主に膵臓と唾液腺から作られます。膵臓に炎症が起きると血液中に漏れ出して数値が上がるため、膵炎の診断や経過観察に使われます。</v>
       </c>
       <c r="F95" t="str">
-        <v>溶血性疾患（自己免疫性溶血性貧血、血液型不適合輸血など）、体質性黄疸（ジルベール症候群）、新生児黄疸</v>
+        <v>急性膵炎、慢性膵炎の急性増悪、耳下腺炎（おたふくかぜ）、腎不全</v>
       </c>
       <c r="G95" t="str">
-        <v>皮膚や白目の黄染、尿の色の変化がないか確認する</v>
+        <v>飲酒を控え、脂っこい食事を避けるよう伝える。強い腹痛・背部痛がある場合は急性膵炎の可能性もあるため早めの受診を勧める</v>
       </c>
       <c r="H95" t="str">
-        <v/>
+        <v>バルプロ酸、アザチオプリン、サイアザイド系・ループ利尿薬、ステロイドなど薬剤性膵炎の原因薬</v>
       </c>
       <c r="I95" t="str">
-        <v/>
+        <v>慢性膵炎の進行期（膵臓の機能低下）</v>
       </c>
       <c r="J95" t="str">
         <v/>
@@ -4877,13 +4877,13 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>直接ビリルビンとの比率で原因を推測する（間接優位は溶血・体質性、直接優位は胆道系）。総ビリルビン・AST/ALTと合わせて評価する</v>
+        <v>膵臓由来か唾液腺由来かを区別するには膵型アミラーゼ(P-AMY)を確認する。急性膵炎では強い腹痛・背部痛を伴うことが多く、飲酒歴の確認も重要</v>
       </c>
       <c r="M95" t="str">
-        <v>肝機能</v>
+        <v/>
       </c>
       <c r="N95" t="str">
-        <v>間接ビリルビン,I-Bil,溶血</v>
+        <v>アミラーゼ,AMY,膵炎,急性膵炎</v>
       </c>
       <c r="O95" t="str">
         <v/>
@@ -4891,28 +4891,28 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>直接ビリルビン</v>
+        <v>間接ビリルビン</v>
       </c>
       <c r="B96" t="str">
-        <v>D-Bil</v>
+        <v>I-Bil</v>
       </c>
       <c r="C96" t="str">
-        <v>0.0〜0.3 mg/dL程度（施設差あり）</v>
+        <v>0.2〜0.8 mg/dL程度（施設差あり）</v>
       </c>
       <c r="D96" t="str">
-        <v>肝臓で処理された後のビリルビン。胆道の詰まりで血液中に増える</v>
+        <v>赤血球が壊れてできるビリルビンのうち、肝臓で処理される前の形</v>
       </c>
       <c r="E96" t="str">
-        <v>直接ビリルビンは、肝臓で処理された後のビリルビンです。胆石や腫瘍などで胆汁の通り道（胆道）が詰まると、行き場を失って血液中に増え、皮膚や白目が黄色くなる黄疸として現れます。</v>
+        <v>間接ビリルビンは、赤血球が壊れてできたビリルビンが、まだ肝臓で処理される前の状態です。この値が高い場合、赤血球が通常より多く壊れている(溶血)か、肝臓での処理能力に生まれつきの体質差(体質性黄疸)がある可能性が考えられます。</v>
       </c>
       <c r="F96" t="str">
-        <v>肝疾患、胆石など胆道の閉塞</v>
+        <v>溶血性疾患（自己免疫性溶血性貧血、血液型不適合輸血など）、体質性黄疸（ジルベール症候群）、新生児黄疸</v>
       </c>
       <c r="G96" t="str">
-        <v>皮膚や白目の黄染、白っぽい便、濃い茶色の尿がないか確認する</v>
+        <v>皮膚や白目の黄染、尿の色の変化がないか確認する</v>
       </c>
       <c r="H96" t="str">
-        <v>胆汁うっ滞型の薬剤性肝障害を起こしうる抗菌薬、経口避妊薬</v>
+        <v/>
       </c>
       <c r="I96" t="str">
         <v/>
@@ -4924,13 +4924,13 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>直接優位の上昇は胆道系（胆石、腫瘍による閉塞）を、間接優位の上昇は溶血・体質性を疑う手がかりになる。γ-GTP・ALPと合わせて胆道系疾患を評価する</v>
+        <v>直接ビリルビンとの比率で原因を推測する（間接優位は溶血・体質性、直接優位は胆道系）。総ビリルビン・AST/ALTと合わせて評価する</v>
       </c>
       <c r="M96" t="str">
         <v>肝機能</v>
       </c>
       <c r="N96" t="str">
-        <v>直接ビリルビン,D-Bil,胆石,胆道閉塞</v>
+        <v>間接ビリルビン,I-Bil,溶血</v>
       </c>
       <c r="O96" t="str">
         <v/>
@@ -4938,187 +4938,187 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>亜鉛（Zn）</v>
+        <v>直接ビリルビン</v>
       </c>
       <c r="B97" t="str">
-        <v>Zn</v>
+        <v>D-Bil</v>
       </c>
       <c r="C97" t="str">
-        <v>80〜130 μg/dL程度（施設差あり）</v>
+        <v>0.0〜0.3 mg/dL程度（施設差あり）</v>
       </c>
       <c r="D97" t="str">
-        <v>味覚や皮膚、免疫に関わる微量ミネラル。高齢者や低栄養で不足しやすい</v>
+        <v>肝臓で処理された後のビリルビン。胆道の詰まりで血液中に増える</v>
       </c>
       <c r="E97" t="str">
-        <v>亜鉛は、味を感じる働きや皮膚・粘膜の健康、免疫の働きに関わる微量ミネラルです。不足すると、味がわかりにくくなったり（味覚障害）、傷が治りにくくなったりすることがあります。</v>
+        <v>直接ビリルビンは、肝臓で処理された後のビリルビンです。胆石や腫瘍などで胆汁の通り道（胆道）が詰まると、行き場を失って血液中に増え、皮膚や白目が黄色くなる黄疸として現れます。</v>
       </c>
       <c r="F97" t="str">
-        <v/>
+        <v>肝疾患、胆石など胆道の閉塞</v>
       </c>
       <c r="G97" t="str">
-        <v/>
+        <v>皮膚や白目の黄染、白っぽい便、濃い茶色の尿がないか確認する</v>
       </c>
       <c r="H97" t="str">
-        <v/>
+        <v>胆汁うっ滞型の薬剤性肝障害を起こしうる抗菌薬、経口避妊薬</v>
       </c>
       <c r="I97" t="str">
-        <v>低栄養、高齢による摂取不足、消化器手術後、亜鉛の吸収を妨げる薬剤（PPI、キレート形成する薬剤など）との併用</v>
+        <v/>
       </c>
       <c r="J97" t="str">
-        <v>味覚の変化（味を感じにくい、金属味がするなど）がないか確認する。牡蠣、赤身肉、レバーなど亜鉛を多く含む食品を意識するとよいことを伝える</v>
+        <v/>
       </c>
       <c r="K97" t="str">
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>薬剤性の亜鉛欠乏（PPI長期使用、D-ペニシラミン、一部の降圧薬など）に注意。亜鉛欠乏による味覚障害は原因薬剤の中止・亜鉛補充で改善することがある</v>
+        <v>直接優位の上昇は胆道系（胆石、腫瘍による閉塞）を、間接優位の上昇は溶血・体質性を疑う手がかりになる。γ-GTP・ALPと合わせて胆道系疾患を評価する</v>
       </c>
       <c r="M97" t="str">
-        <v/>
+        <v>肝機能</v>
       </c>
       <c r="N97" t="str">
-        <v>亜鉛,Zn,味覚障害,亜鉛欠乏</v>
+        <v>直接ビリルビン,D-Bil,胆石,胆道閉塞</v>
       </c>
       <c r="O97" t="str">
-        <v>食事と栄養 p.78（亜鉛）</v>
+        <v/>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>マグネシウム（Mg）</v>
+        <v>亜鉛（Zn）</v>
       </c>
       <c r="B98" t="str">
-        <v>Mg</v>
+        <v>Zn</v>
       </c>
       <c r="C98" t="str">
-        <v>1.8〜2.6 mg/dL程度（施設差あり）</v>
+        <v>80〜130 μg/dL程度（施設差あり）</v>
       </c>
       <c r="D98" t="str">
-        <v>骨や筋肉、神経の働きに関わるミネラル。低栄養や利尿薬で不足しやすい</v>
+        <v>味覚や皮膚、免疫に関わる微量ミネラル。高齢者や低栄養で不足しやすい</v>
       </c>
       <c r="E98" t="str">
-        <v>マグネシウムは、骨や筋肉、神経の働きを支えるミネラルです。不足すると、こむら返りや不整脈、だるさなどの症状が出ることがあります。</v>
+        <v>亜鉛は、味を感じる働きや皮膚・粘膜の健康、免疫の働きに関わる微量ミネラルです。不足すると、味がわかりにくくなったり（味覚障害）、傷が治りにくくなったりすることがあります。</v>
       </c>
       <c r="F98" t="str">
-        <v>腎不全、マグネシウム製剤（酸化マグネシウムなど）の過量投与</v>
+        <v/>
       </c>
       <c r="G98" t="str">
-        <v>腎機能低下がある患者で酸化マグネシウムなどの緩下剤を使用中は、傾眠・血圧低下などの高マグネシウム血症の症状がないか確認する</v>
+        <v/>
       </c>
       <c r="H98" t="str">
-        <v>マグネシウム含有制酸薬・下剤の過量(特に腎機能低下患者)</v>
+        <v/>
       </c>
       <c r="I98" t="str">
-        <v>低栄養、利尿薬の使用、慢性的な下痢、アルコール多飲、PPI長期使用</v>
+        <v>低栄養、高齢による摂取不足、消化器手術後、亜鉛の吸収を妨げる薬剤（PPI、キレート形成する薬剤など）との併用</v>
       </c>
       <c r="J98" t="str">
-        <v>こむら返りや動悸などの症状がないか確認する</v>
+        <v>味覚の変化（味を感じにくい、金属味がするなど）がないか確認する。牡蠣、赤身肉、レバーなど亜鉛を多く含む食品を意識するとよいことを伝える</v>
       </c>
       <c r="K98" t="str">
-        <v>プロトンポンプ阻害薬(PPI)の長期使用、ループ利尿薬、サイアザイド系利尿薬、シスプラチン、アミノグリコシド系</v>
+        <v/>
       </c>
       <c r="L98" t="str">
-        <v>腎機能低下患者への酸化マグネシウム投与は高マグネシウム血症のリスクがあるため定期的なモニタリングが必要。PPI長期使用も低マグネシウム血症のリスク因子として知られる</v>
+        <v>薬剤性の亜鉛欠乏（PPI長期使用、D-ペニシラミン、一部の降圧薬など）に注意。亜鉛欠乏による味覚障害は原因薬剤の中止・亜鉛補充で改善することがある</v>
       </c>
       <c r="M98" t="str">
-        <v>腎機能</v>
+        <v/>
       </c>
       <c r="N98" t="str">
-        <v>マグネシウム,Mg,酸化マグネシウム,こむら返り</v>
+        <v>亜鉛,Zn,味覚障害,亜鉛欠乏</v>
       </c>
       <c r="O98" t="str">
-        <v>食事と栄養 p.84（マグネシウム）</v>
+        <v>食事と栄養 p.78（亜鉛）</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>骨密度</v>
+        <v>マグネシウム（Mg）</v>
       </c>
       <c r="B99" t="str">
-        <v>BMD,骨密度</v>
+        <v>Mg</v>
       </c>
       <c r="C99" t="str">
-        <v>YAM(若年成人平均値)80%以上:正常、70%以上80%未満:骨量減少、70%未満:骨粗鬆症</v>
+        <v>1.8〜2.6 mg/dL程度（施設差あり）</v>
       </c>
       <c r="D99" t="str">
-        <v>骨の中にカルシウムなどのミネラルがどれだけ詰まっているかを示す指標。20〜44歳の平均値(YAM)に対する割合(%)で評価する</v>
+        <v>骨や筋肉、神経の働きに関わるミネラル。低栄養や利尿薬で不足しやすい</v>
       </c>
       <c r="E99" t="str">
-        <v>骨密度は、骨の中にカルシウムなどのミネラルがどれだけしっかり詰まっているかを表す数値です。20〜44歳の若い方の平均値を100%として、ご自身の骨密度が何%かで示されます。70%未満になると「骨粗鬆症」と診断され、骨折しやすい状態と考えられます。</v>
+        <v>マグネシウムは、骨や筋肉、神経の働きを支えるミネラルです。不足すると、こむら返りや不整脈、だるさなどの症状が出ることがあります。</v>
       </c>
       <c r="F99" t="str">
-        <v>基本的に問題になることは少ない(まれに骨硬化症などの疾患)</v>
+        <v>腎不全、マグネシウム製剤（酸化マグネシウムなど）の過量投与</v>
       </c>
       <c r="G99" t="str">
-        <v/>
+        <v>腎機能低下がある患者で酸化マグネシウムなどの緩下剤を使用中は、傾眠・血圧低下などの高マグネシウム血症の症状がないか確認する</v>
       </c>
       <c r="H99" t="str">
-        <v/>
+        <v>マグネシウム含有制酸薬・下剤の過量(特に腎機能低下患者)</v>
       </c>
       <c r="I99" t="str">
-        <v>骨粗鬆症、加齢による骨量減少、閉経後のエストロゲン低下、ステロイド長期使用、カルシウム・ビタミンD不足、運動不足、るいそう</v>
+        <v>低栄養、利尿薬の使用、慢性的な下痢、アルコール多飲、PPI長期使用</v>
       </c>
       <c r="J99" t="str">
-        <v>カルシウム・ビタミンD・ビタミンKを意識した食事、荷重運動(ウォーキング等)を勧める。ステロイド長期服用中の場合は骨粗鬆症治療薬の併用が検討されているか確認する</v>
+        <v>こむら返りや動悸などの症状がないか確認する</v>
       </c>
       <c r="K99" t="str">
-        <v/>
+        <v>プロトンポンプ阻害薬(PPI)の長期使用、ループ利尿薬、サイアザイド系利尿薬、シスプラチン、アミノグリコシド系</v>
       </c>
       <c r="L99" t="str">
-        <v>YAM70%未満、または既存の脆弱性骨折がある場合に骨粗鬆症と診断され薬物治療の対象となる(日本骨粗鬆症学会・日本骨代謝学会・厚生労働省合同「原発性骨粗鬆症の診断基準 2012年度改訂版」)。ビスホスホネート製剤は起床時空腹時に十分な水(180mL程度)で服用し、服用後30分は横にならないよう指導する。ステロイドを長期服用中の患者は骨密度によらず骨粗鬆症治療薬の併用が推奨される場合がある(グルココルチコイド誘発性骨粗鬆症: GIOP)</v>
+        <v>腎機能低下患者への酸化マグネシウム投与は高マグネシウム血症のリスクがあるため定期的なモニタリングが必要。PPI長期使用も低マグネシウム血症のリスク因子として知られる</v>
       </c>
       <c r="M99" t="str">
-        <v>骨粗鬆症</v>
+        <v>腎機能</v>
       </c>
       <c r="N99" t="str">
-        <v>骨密度,BMD,YAM,若年成人平均値,骨粗鬆症,DXA</v>
+        <v>マグネシウム,Mg,酸化マグネシウム,こむら返り</v>
       </c>
       <c r="O99" t="str">
-        <v/>
+        <v>食事と栄養 p.84（マグネシウム）</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Dダイマー</v>
+        <v>骨密度</v>
       </c>
       <c r="B100" t="str">
-        <v>D-dimer</v>
+        <v>BMD,骨密度</v>
       </c>
       <c r="C100" t="str">
-        <v>1.0 μg/mL以下(施設・測定法により異なる)</v>
+        <v>YAM(若年成人平均値)80%以上:正常、70%以上80%未満:骨量減少、70%未満:骨粗鬆症</v>
       </c>
       <c r="D100" t="str">
-        <v>体の中で血栓ができて溶けた(線溶)ときにできる分解産物で、血栓症の有無をスクリーニングする指標</v>
+        <v>骨の中にカルシウムなどのミネラルがどれだけ詰まっているかを示す指標。20〜44歳の平均値(YAM)に対する割合(%)で評価する</v>
       </c>
       <c r="E100" t="str">
-        <v>Dダイマーは、血管の中に血のかたまり(血栓)ができて、それが溶かされるときにできる物質です。この数値が高いと、どこかに血栓ができている可能性を考えます。ただし手術後や妊娠中、高齢の方などでも上がることがあるため、この数値だけで診断が決まるわけではありません。</v>
+        <v>骨密度は、骨の中にカルシウムなどのミネラルがどれだけしっかり詰まっているかを表す数値です。20〜44歳の若い方の平均値を100%として、ご自身の骨密度が何%かで示されます。70%未満になると「骨粗鬆症」と診断され、骨折しやすい状態と考えられます。</v>
       </c>
       <c r="F100" t="str">
-        <v>深部静脈血栓症(DVT)・肺血栓塞栓症(PE)、播種性血管内凝固症候群(DIC)、大動脈解離、悪性腫瘍、手術後、妊娠、高齢、感染・炎症</v>
+        <v>基本的に問題になることは少ない(まれに骨硬化症などの疾患)</v>
       </c>
       <c r="G100" t="str">
-        <v>ふくらはぎの腫れ・痛み、急な息切れ・胸痛など血栓症を疑う症状がないか確認する</v>
+        <v/>
       </c>
       <c r="H100" t="str">
-        <v>経口避妊薬・ホルモン補充療法は血栓リスクを高める。逆にワルファリン・DOAC・ヘパリンなど抗凝固薬の効果不十分で血栓が進行している可能性にも注意</v>
+        <v/>
       </c>
       <c r="I100" t="str">
-        <v>通常、臨床的意義は乏しい(基準値以下であれば血栓症の可能性は低いとする除外診断に有用)</v>
+        <v>骨粗鬆症、加齢による骨量減少、閉経後のエストロゲン低下、ステロイド長期使用、カルシウム・ビタミンD不足、運動不足、るいそう</v>
       </c>
       <c r="J100" t="str">
-        <v/>
+        <v>カルシウム・ビタミンD・ビタミンKを意識した食事、荷重運動(ウォーキング等)を勧める。ステロイド長期服用中の場合は骨粗鬆症治療薬の併用が検討されているか確認する</v>
       </c>
       <c r="K100" t="str">
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>陰性的中率が高く、基準値以下であれば静脈血栓塞栓症(VTE)の可能性は低いとする除外診断への活用が臨床的に重要。一方で偽陽性が多く、高値のみで血栓症と確定はできない。抗凝固療法中のモニタリングそのものには通常用いない(効果判定はPT-INR/APTT等)</v>
+        <v>YAM70%未満、または既存の脆弱性骨折がある場合に骨粗鬆症と診断され薬物治療の対象となる(日本骨粗鬆症学会・日本骨代謝学会・厚生労働省合同「原発性骨粗鬆症の診断基準 2012年度改訂版」)。ビスホスホネート製剤は起床時空腹時に十分な水(180mL程度)で服用し、服用後30分は横にならないよう指導する。ステロイドを長期服用中の患者は骨密度によらず骨粗鬆症治療薬の併用が推奨される場合がある(グルココルチコイド誘発性骨粗鬆症: GIOP)</v>
       </c>
       <c r="M100" t="str">
-        <v>抗凝固療法（心房細動・血栓症）</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="N100" t="str">
-        <v>Dダイマー,D-dimer,血栓,DVT,深部静脈血栓症,肺塞栓,DIC</v>
+        <v>骨密度,BMD,YAM,若年成人平均値,骨粗鬆症,DXA</v>
       </c>
       <c r="O100" t="str">
         <v/>

--- a/検査値リファレンス初期データ.xlsx
+++ b/検査値リファレンス初期データ.xlsx
@@ -1977,7 +1977,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>AST/ALT</v>
+        <v>AST/ALT比</v>
       </c>
       <c r="B34" t="str">
         <v>AST/ALT,De Ritis比</v>
@@ -2016,7 +2016,7 @@
         <v>肝機能</v>
       </c>
       <c r="N34" t="str">
-        <v>AST/ALT,De Ritis比,デリティス比,アルコール性肝障害,肝硬変</v>
+        <v>AST/ALT比,AST/ALT,De Ritis比,デリティス比,アルコール性肝障害,肝硬変</v>
       </c>
       <c r="O34" t="str">
         <v/>
@@ -2306,7 +2306,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>TSH（甲状腺刺激ホルモン）</v>
+        <v>甲状腺刺激ホルモン（TSH）</v>
       </c>
       <c r="B41" t="str">
         <v>TSH</v>

--- a/検査値リファレンス初期データ.xlsx
+++ b/検査値リファレンス初期データ.xlsx
@@ -2353,7 +2353,7 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>FT4（遊離サイロキシン）</v>
+        <v>遊離サイロキシン（FT4）</v>
       </c>
       <c r="B42" t="str">
         <v>FT4</v>

--- a/検査値リファレンス初期データ.xlsx
+++ b/検査値リファレンス初期データ.xlsx
@@ -2494,7 +2494,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>白血球（WBC）</v>
+        <v>白血球数（WBC）</v>
       </c>
       <c r="B45" t="str">
         <v>WBC</v>
@@ -2541,7 +2541,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>赤血球</v>
+        <v>赤血球数</v>
       </c>
       <c r="B46" t="str">
         <v>RBC</v>

--- a/検査値リファレンス初期データ.xlsx
+++ b/検査値リファレンス初期データ.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O100"/>
+  <dimension ref="A1:O102"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -1459,46 +1459,46 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>アンモニア</v>
+        <v>A/G</v>
       </c>
       <c r="B23" t="str">
-        <v>NH3</v>
+        <v>A/G比</v>
       </c>
       <c r="C23" t="str">
-        <v>12〜66 μg/dL（施設差あり／空腹時採血が望ましい）</v>
+        <v>1.1〜2.0程度(施設差あり)</v>
       </c>
       <c r="D23" t="str">
-        <v>肝機能低下や門脈シャントなどで代謝・排泄が低下すると上昇し、意識障害（肝性脳症）の原因となる</v>
+        <v>血液中のアルブミンとグロブリンの比率。肝機能や炎症、免疫の状態を反映する</v>
       </c>
       <c r="E23" t="str">
-        <v>アンモニアは体の中でタンパク質が分解されるときにできる老廃物で、通常は肝臓で無害な尿素に変えられて尿として排泄されます。肝臓の働きが弱っていたり血液の流れ道に変化があると、アンモニアがうまく処理されず血液中にたまり、頭がぼんやりしたり意識がもうろうとする原因になることがあります。</v>
+        <v>A/G比は、血液中のたんぱく質のうちアルブミンとグロブリンという2種類の比率を見る数値です。肝臓の働きが落ちたり、体に炎症や免疫の異常があったりすると、このバランスが崩れることがあります。</v>
       </c>
       <c r="F23" t="str">
-        <v>肝硬変・肝不全（門脈-大循環シャント含む）、劇症肝炎、消化管出血、便秘、脱水、高たんぱく食、尿素サイクル異常症、一部薬剤（バルプロ酸など）</v>
+        <v>通常、臨床的意義は乏しい(まれに無ガンマグロブリン血症など)</v>
       </c>
       <c r="G23" t="str">
-        <v>便秘の解消(排便コントロール)を心がける。ラクツロースやリファキシミンなど肝性脳症治療薬の服薬状況を確認し、意識のもうろう感や日中の眠気の変化にも注意する</v>
+        <v/>
       </c>
       <c r="H23" t="str">
-        <v>バルプロ酸(デパケン等)</v>
+        <v/>
       </c>
       <c r="I23" t="str">
-        <v>通常、臨床的意義は乏しい</v>
+        <v>肝硬変などの肝機能低下(アルブミン産生低下)、慢性炎症・感染症、多発性骨髄腫などの血液疾患(グロブリン増加)、ネフローゼ症候群</v>
       </c>
       <c r="J23" t="str">
-        <v/>
+        <v>食事摂取量やむくみの有無を確認する。慢性炎症や感染の有無もあわせて確認する</v>
       </c>
       <c r="K23" t="str">
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>バルプロ酸(デパケン等)は肝疾患の既往がなくても高アンモニア血症を起こすことがあり、意識障害・傾眠が出現した場合は薬剤性を疑ってアンモニア値を確認する。採血後は室温放置で見かけ上上昇するため測定条件にも注意。ラクツロース・リファキシミンは腸管内でのアンモニア産生・吸収を抑える目的で使用される</v>
+        <v>A/G比＝アルブミン÷(総タンパク－アルブミン)で算出する。低下はアルブミンが減った場合とグロブリンが増えた場合の両方で起こるため、総タンパク・アルブミンの実測値とあわせて原因を判断する</v>
       </c>
       <c r="M23" t="str">
         <v>肝機能</v>
       </c>
       <c r="N23" t="str">
-        <v>アンモニア,NH3,肝性脳症,バルプロ酸,門脈シャント</v>
+        <v>A/G,A/G比,アルブミングロブリン比,肝機能,多発性骨髄腫</v>
       </c>
       <c r="O23" t="str">
         <v/>
@@ -1506,31 +1506,31 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>中性脂肪（トリグリセリド）</v>
+        <v>アンモニア</v>
       </c>
       <c r="B24" t="str">
-        <v>TG</v>
+        <v>NH3</v>
       </c>
       <c r="C24" t="str">
-        <v>150 mg/dL未満（空腹時）</v>
+        <v>12〜66 μg/dL（施設差あり／空腹時採血が望ましい）</v>
       </c>
       <c r="D24" t="str">
-        <v>脂質異常症で高値になりやすい脂質で、食事の影響を強く受ける</v>
+        <v>肝機能低下や門脈シャントなどで代謝・排泄が低下すると上昇し、意識障害（肝性脳症）の原因となる</v>
       </c>
       <c r="E24" t="str">
-        <v>中性脂肪は、食事から摂った脂肪や糖質が体に蓄えられる形になったものです。食後は誰でも一時的に上がるため、正確に評価するには空腹時に採血することが大切です。高い状態が続くと動脈硬化や急性膵炎のリスクが高まります。</v>
+        <v>アンモニアは体の中でタンパク質が分解されるときにできる老廃物で、通常は肝臓で無害な尿素に変えられて尿として排泄されます。肝臓の働きが弱っていたり血液の流れ道に変化があると、アンモニアがうまく処理されず血液中にたまり、頭がぼんやりしたり意識がもうろうとする原因になることがあります。</v>
       </c>
       <c r="F24" t="str">
-        <v>脂質異常症、糖質・アルコールの摂りすぎ、肥満、糖尿病のコントロール不良</v>
+        <v>肝硬変・肝不全（門脈-大循環シャント含む）、劇症肝炎、消化管出血、便秘、脱水、高たんぱく食、尿素サイクル異常症、一部薬剤（バルプロ酸など）</v>
       </c>
       <c r="G24" t="str">
-        <v>糖質・アルコールの摂りすぎに注意し、ウォーキングなどの有酸素運動を週150分程度を目安に勧める。清涼飲料水や果物の摂りすぎにも注意する</v>
+        <v>便秘の解消(排便コントロール)を心がける。ラクツロースやリファキシミンなど肝性脳症治療薬の服薬状況を確認し、意識のもうろう感や日中の眠気の変化にも注意する</v>
       </c>
       <c r="H24" t="str">
-        <v>非定型抗精神病薬(オランザピン・クエチアピン)、ステロイド、エストロゲン製剤、非選択的β遮断薬、サイアザイド系利尿薬、タモキシフェン</v>
+        <v>バルプロ酸(デパケン等)</v>
       </c>
       <c r="I24" t="str">
-        <v>低栄養、甲状腺機能亢進症</v>
+        <v>通常、臨床的意義は乏しい</v>
       </c>
       <c r="J24" t="str">
         <v/>
@@ -1539,45 +1539,45 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>採血が食後か空腹時かで数値が大きく変わるため必ず確認する。500 mg/dL以上では急性膵炎のリスクが高まるため注意。フィブラート系・EPA製剤などの効果判定に使う</v>
+        <v>バルプロ酸(デパケン等)は肝疾患の既往がなくても高アンモニア血症を起こすことがあり、意識障害・傾眠が出現した場合は薬剤性を疑ってアンモニア値を確認する。採血後は室温放置で見かけ上上昇するため測定条件にも注意。ラクツロース・リファキシミンは腸管内でのアンモニア産生・吸収を抑える目的で使用される</v>
       </c>
       <c r="M24" t="str">
-        <v>脂質異常症</v>
+        <v>肝機能</v>
       </c>
       <c r="N24" t="str">
-        <v>中性脂肪,トリグリセリド,TG,脂質異常症</v>
+        <v>アンモニア,NH3,肝性脳症,バルプロ酸,門脈シャント</v>
       </c>
       <c r="O24" t="str">
-        <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>総コレステロール</v>
+        <v>中性脂肪（トリグリセリド）</v>
       </c>
       <c r="B25" t="str">
-        <v>TC,T-cho</v>
+        <v>TG</v>
       </c>
       <c r="C25" t="str">
-        <v>220 mg/dL未満</v>
+        <v>150 mg/dL未満（空腹時）</v>
       </c>
       <c r="D25" t="str">
-        <v>LDL・HDLなどすべてのコレステロールを合わせた総量</v>
+        <v>脂質異常症で高値になりやすい脂質で、食事の影響を強く受ける</v>
       </c>
       <c r="E25" t="str">
-        <v>総コレステロールは、体の中にあるコレステロールをすべて合わせた数値です。ただし、悪玉(LDL)が多いのか善玉(HDL)が多いのかまでは分からないため、実際の評価にはLDLコレステロールの値がより重視されます。</v>
+        <v>中性脂肪は、食事から摂った脂肪や糖質が体に蓄えられる形になったものです。食後は誰でも一時的に上がるため、正確に評価するには空腹時に採血することが大切です。高い状態が続くと動脈硬化や急性膵炎のリスクが高まります。</v>
       </c>
       <c r="F25" t="str">
-        <v>脂質異常症、家族性高コレステロール血症、甲状腺機能低下症</v>
+        <v>脂質異常症、糖質・アルコールの摂りすぎ、肥満、糖尿病のコントロール不良</v>
       </c>
       <c r="G25" t="str">
-        <v>動物性脂肪を控え、食物繊維(野菜・海藻・きのこ)を増やすよう伝える。青魚に含まれる油(EPA・DHA)を意識的に摂ることも勧める</v>
+        <v>糖質・アルコールの摂りすぎに注意し、ウォーキングなどの有酸素運動を週150分程度を目安に勧める。清涼飲料水や果物の摂りすぎにも注意する</v>
       </c>
       <c r="H25" t="str">
-        <v>非定型抗精神病薬、ステロイド、サイアザイド系利尿薬、非選択的β遮断薬</v>
+        <v>非定型抗精神病薬(オランザピン・クエチアピン)、ステロイド、エストロゲン製剤、非選択的β遮断薬、サイアザイド系利尿薬、タモキシフェン</v>
       </c>
       <c r="I25" t="str">
-        <v>低栄養、肝機能低下、甲状腺機能亢進症</v>
+        <v>低栄養、甲状腺機能亢進症</v>
       </c>
       <c r="J25" t="str">
         <v/>
@@ -1586,108 +1586,108 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>現在はLDLコレステロールでの評価が主流。総コレステロールだけでは悪玉・善玉の内訳が分からないため、LDL・HDL・中性脂肪と合わせて評価する</v>
+        <v>採血が食後か空腹時かで数値が大きく変わるため必ず確認する。500 mg/dL以上では急性膵炎のリスクが高まるため注意。フィブラート系・EPA製剤などの効果判定に使う</v>
       </c>
       <c r="M25" t="str">
         <v>脂質異常症</v>
       </c>
       <c r="N25" t="str">
-        <v>総コレステロール,TC,コレステロール,脂質異常症</v>
+        <v>中性脂肪,トリグリセリド,TG,脂質異常症</v>
       </c>
       <c r="O25" t="str">
         <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
       </c>
     </row>
-    <row r="26" xml:space="preserve">
+    <row r="26">
       <c r="A26" t="str">
+        <v>総コレステロール</v>
+      </c>
+      <c r="B26" t="str">
+        <v>TC,T-cho</v>
+      </c>
+      <c r="C26" t="str">
+        <v>220 mg/dL未満</v>
+      </c>
+      <c r="D26" t="str">
+        <v>LDL・HDLなどすべてのコレステロールを合わせた総量</v>
+      </c>
+      <c r="E26" t="str">
+        <v>総コレステロールは、体の中にあるコレステロールをすべて合わせた数値です。ただし、悪玉(LDL)が多いのか善玉(HDL)が多いのかまでは分からないため、実際の評価にはLDLコレステロールの値がより重視されます。</v>
+      </c>
+      <c r="F26" t="str">
+        <v>脂質異常症、家族性高コレステロール血症、甲状腺機能低下症</v>
+      </c>
+      <c r="G26" t="str">
+        <v>動物性脂肪を控え、食物繊維(野菜・海藻・きのこ)を増やすよう伝える。青魚に含まれる油(EPA・DHA)を意識的に摂ることも勧める</v>
+      </c>
+      <c r="H26" t="str">
+        <v>非定型抗精神病薬、ステロイド、サイアザイド系利尿薬、非選択的β遮断薬</v>
+      </c>
+      <c r="I26" t="str">
+        <v>低栄養、肝機能低下、甲状腺機能亢進症</v>
+      </c>
+      <c r="J26" t="str">
+        <v/>
+      </c>
+      <c r="K26" t="str">
+        <v/>
+      </c>
+      <c r="L26" t="str">
+        <v>現在はLDLコレステロールでの評価が主流。総コレステロールだけでは悪玉・善玉の内訳が分からないため、LDL・HDL・中性脂肪と合わせて評価する</v>
+      </c>
+      <c r="M26" t="str">
+        <v>脂質異常症</v>
+      </c>
+      <c r="N26" t="str">
+        <v>総コレステロール,TC,コレステロール,脂質異常症</v>
+      </c>
+      <c r="O26" t="str">
+        <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
+      </c>
+    </row>
+    <row r="27" xml:space="preserve">
+      <c r="A27" t="str">
         <v>LDLコレステロール</v>
       </c>
-      <c r="B26" t="str">
+      <c r="B27" t="str">
         <v>LDL-C</v>
       </c>
-      <c r="C26" t="str" xml:space="preserve">
+      <c r="C27" t="str" xml:space="preserve">
         <v xml:space="preserve">60〜139 mg/dL
 （140 mg/dL以上で高LDLコレステロール血症）</v>
       </c>
-      <c r="D26" t="str">
+      <c r="D27" t="str">
         <v>いわゆる「悪玉コレステロール」。血管の壁にたまり動脈硬化を進める</v>
       </c>
-      <c r="E26" t="str">
+      <c r="E27" t="str">
         <v>LDLコレステロールは、いわゆる悪玉コレステロールと呼ばれるものです。多いままだと血管の壁にたまって、動脈硬化や心筋梗塞・脳梗塞のリスクを高めます。数値を下げることで、将来の血管のトラブルを防ぐことが目的です。</v>
       </c>
-      <c r="F26" t="str">
+      <c r="F27" t="str">
         <v>脂質異常症、動脈硬化のリスク上昇、家族性高コレステロール血症、甲状腺機能低下症</v>
       </c>
-      <c r="G26" t="str">
+      <c r="G27" t="str">
         <v>動物性脂肪や揚げ物を控え、青魚や食物繊維(野菜・海藻・きのこ)を増やすよう伝える。禁煙も動脈硬化予防に重要なことを伝える</v>
       </c>
-      <c r="H26" t="str">
+      <c r="H27" t="str">
         <v>ステロイド、サイアザイド系利尿薬、非選択的β遮断薬</v>
       </c>
-      <c r="I26" t="str">
+      <c r="I27" t="str">
         <v>低栄養、肝機能低下、甲状腺機能亢進症</v>
       </c>
-      <c r="J26" t="str">
-        <v/>
-      </c>
-      <c r="K26" t="str">
-        <v/>
-      </c>
-      <c r="L26" t="str">
+      <c r="J27" t="str">
+        <v/>
+      </c>
+      <c r="K27" t="str">
+        <v/>
+      </c>
+      <c r="L27" t="str">
         <v>スタチン等の効果判定に使う中心的な数値。目標値は既往疾患（冠動脈疾患・糖尿病等）によって異なるため一律に判断しない</v>
       </c>
-      <c r="M26" t="str">
+      <c r="M27" t="str">
         <v>脂質異常症,精神疾患（非定型抗精神病薬）</v>
       </c>
-      <c r="N26" t="str">
+      <c r="N27" t="str">
         <v>LDL,LDLコレステロール,悪玉コレステロール,脂質異常症</v>
-      </c>
-      <c r="O26" t="str">
-        <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <v>nonHDLコレステロール</v>
-      </c>
-      <c r="B27" t="str">
-        <v>non-HDL-C</v>
-      </c>
-      <c r="C27" t="str">
-        <v>90〜149 mg/dL（150 mg/dL以上で高値）</v>
-      </c>
-      <c r="D27" t="str">
-        <v>総コレステロールからHDL（善玉）を除いた、動脈硬化を進めるすべての脂質の合計</v>
-      </c>
-      <c r="E27" t="str">
-        <v>nonHDLコレステロールは、総コレステロールから善玉のHDLを引いた数値で、LDL（悪玉）を含む、動脈硬化を進めるすべてのコレステロールの合計を表します。中性脂肪が高くLDLだけでは評価しにくい方でも、こちらで動脈硬化のリスクを評価できます。</v>
-      </c>
-      <c r="F27" t="str">
-        <v>脂質異常症、動脈硬化のリスク上昇（特に中性脂肪が高い場合にLDL-Cより実態を反映しやすい）</v>
-      </c>
-      <c r="G27" t="str">
-        <v>動物性脂肪や揚げ物を控え、青魚や食物繊維（野菜・海藻・きのこ）を増やすよう伝える</v>
-      </c>
-      <c r="H27" t="str">
-        <v/>
-      </c>
-      <c r="I27" t="str">
-        <v/>
-      </c>
-      <c r="J27" t="str">
-        <v/>
-      </c>
-      <c r="K27" t="str">
-        <v/>
-      </c>
-      <c r="L27" t="str">
-        <v>中性脂肪（TG）が400 mg/dL以上などLDL-Cの計算式（Friedewald式）が不正確になる場合に、LDL-Cの代わりに用いられる。目標値はLDL-Cの目標値＋30 mg/dLが目安</v>
-      </c>
-      <c r="M27" t="str">
-        <v>脂質異常症</v>
-      </c>
-      <c r="N27" t="str">
-        <v>nonHDL,non-HDLコレステロール,動脈硬化,中性脂肪,LDL計算式</v>
       </c>
       <c r="O27" t="str">
         <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
@@ -1695,46 +1695,46 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>HDLコレステロール</v>
+        <v>nonHDLコレステロール</v>
       </c>
       <c r="B28" t="str">
-        <v>HDL-C</v>
+        <v>non-HDL-C</v>
       </c>
       <c r="C28" t="str">
-        <v>40 mg/dL以上</v>
+        <v>90〜149 mg/dL（150 mg/dL以上で高値）</v>
       </c>
       <c r="D28" t="str">
-        <v>いわゆる「善玉コレステロール」。血管にたまった余分なコレステロールを回収する</v>
+        <v>総コレステロールからHDL（善玉）を除いた、動脈硬化を進めるすべての脂質の合計</v>
       </c>
       <c r="E28" t="str">
-        <v>HDLコレステロールは、いわゆる善玉コレステロールと呼ばれるものです。血管の壁にたまった余分なコレステロールを回収して肝臓に戻す働きがあり、数値が高いほど動脈硬化を防ぐ方向に働きます。</v>
+        <v>nonHDLコレステロールは、総コレステロールから善玉のHDLを引いた数値で、LDL（悪玉）を含む、動脈硬化を進めるすべてのコレステロールの合計を表します。中性脂肪が高くLDLだけでは評価しにくい方でも、こちらで動脈硬化のリスクを評価できます。</v>
       </c>
       <c r="F28" t="str">
-        <v/>
+        <v>脂質異常症、動脈硬化のリスク上昇（特に中性脂肪が高い場合にLDL-Cより実態を反映しやすい）</v>
       </c>
       <c r="G28" t="str">
-        <v/>
+        <v>動物性脂肪や揚げ物を控え、青魚や食物繊維（野菜・海藻・きのこ）を増やすよう伝える</v>
       </c>
       <c r="H28" t="str">
         <v/>
       </c>
       <c r="I28" t="str">
-        <v>脂質異常症（低HDL血症）</v>
+        <v/>
       </c>
       <c r="J28" t="str">
-        <v>適度な有酸素運動(ウォーキング等)、禁煙を勧める。適正体重の維持もHDL改善に役立つことを伝える</v>
+        <v/>
       </c>
       <c r="K28" t="str">
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>喫煙、運動不足、肥満で低下しやすい。禁煙・運動習慣の改善で上昇が期待できる。低HDLは動脈硬化のリスク因子として単独でも重視される</v>
+        <v>中性脂肪（TG）が400 mg/dL以上などLDL-Cの計算式（Friedewald式）が不正確になる場合に、LDL-Cの代わりに用いられる。目標値はLDL-Cの目標値＋30 mg/dLが目安</v>
       </c>
       <c r="M28" t="str">
         <v>脂質異常症</v>
       </c>
       <c r="N28" t="str">
-        <v>HDL,HDLコレステロール,善玉コレステロール,脂質異常症</v>
+        <v>nonHDL,non-HDLコレステロール,動脈硬化,中性脂肪,LDL計算式</v>
       </c>
       <c r="O28" t="str">
         <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
@@ -1742,78 +1742,78 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>CK（クレアチンフォスフォキナーゼ）</v>
+        <v>HDLコレステロール</v>
       </c>
       <c r="B29" t="str">
-        <v>CK,CPK</v>
+        <v>HDL-C</v>
       </c>
       <c r="C29" t="str">
-        <v>男性 60〜250 U/L、女性 50〜170 U/L</v>
+        <v>40 mg/dL以上</v>
       </c>
       <c r="D29" t="str">
-        <v>主に骨格筋・心筋に含まれる酵素。筋肉の損傷で血液中に漏れ出す</v>
+        <v>いわゆる「善玉コレステロール」。血管にたまった余分なコレステロールを回収する</v>
       </c>
       <c r="E29" t="str">
-        <v>CKは筋肉の中にある酵素で、激しい運動や筋肉の病気、心筋梗塞などで筋肉の細胞がダメージを受けると血液中に漏れ出して数値が上がります。スタチン系のお薬の副作用（横紋筋融解症）のチェックにも使われます。</v>
+        <v>HDLコレステロールは、いわゆる善玉コレステロールと呼ばれるものです。血管の壁にたまった余分なコレステロールを回収して肝臓に戻す働きがあり、数値が高いほど動脈硬化を防ぐ方向に働きます。</v>
       </c>
       <c r="F29" t="str">
-        <v>心筋梗塞、横紋筋融解症（スタチン系薬剤の副作用など）、激しい運動、筋肉注射直後、甲状腺機能低下症</v>
+        <v/>
       </c>
       <c r="G29" t="str">
-        <v>筋肉痛・脱力感・褐色尿（横紋筋融解症の症状）がないか確認する。スタチン系薬剤服用中は特に注意する。激しい運動の直後の採血でないかも確認する</v>
+        <v/>
       </c>
       <c r="H29" t="str">
-        <v>スタチン系(特にフィブラート系との併用時)、コルヒチン</v>
+        <v/>
       </c>
       <c r="I29" t="str">
-        <v/>
+        <v>脂質異常症（低HDL血症）</v>
       </c>
       <c r="J29" t="str">
-        <v/>
+        <v>適度な有酸素運動(ウォーキング等)、禁煙を勧める。適正体重の維持もHDL改善に役立つことを伝える</v>
       </c>
       <c r="K29" t="str">
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>スタチン系薬剤の重大な副作用である横紋筋融解症の指標。筋肉痛・脱力感・褐色尿の有無を必ず確認し、著明高値では服薬継続の可否を医師に相談する</v>
+        <v>喫煙、運動不足、肥満で低下しやすい。禁煙・運動習慣の改善で上昇が期待できる。低HDLは動脈硬化のリスク因子として単独でも重視される</v>
       </c>
       <c r="M29" t="str">
-        <v/>
+        <v>脂質異常症</v>
       </c>
       <c r="N29" t="str">
-        <v>CK,CPK,クレアチンキナーゼ,横紋筋融解症</v>
+        <v>HDL,HDLコレステロール,善玉コレステロール,脂質異常症</v>
       </c>
       <c r="O29" t="str">
-        <v/>
+        <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>BUN/CRE比</v>
+        <v>CK（クレアチンフォスフォキナーゼ）</v>
       </c>
       <c r="B30" t="str">
-        <v>BUN/Cr</v>
+        <v>CK,CPK</v>
       </c>
       <c r="C30" t="str">
-        <v>10前後が目安（施設差あり）</v>
+        <v>男性 60〜250 U/L、女性 50〜170 U/L</v>
       </c>
       <c r="D30" t="str">
-        <v>BUNとクレアチニンの比率。腎前性（脱水・出血など）か腎性かを見分ける目安になる</v>
+        <v>主に骨格筋・心筋に含まれる酵素。筋肉の損傷で血液中に漏れ出す</v>
       </c>
       <c r="E30" t="str">
-        <v>これは、BUN（尿素窒素）とクレアチニンという2つの腎機能に関わる検査値を比較したもので、腎臓そのものに問題があるのか、それとも脱水や出血など腎臓の外側に原因があるのかを見分ける手がかりになります。</v>
+        <v>CKは筋肉の中にある酵素で、激しい運動や筋肉の病気、心筋梗塞などで筋肉の細胞がダメージを受けると血液中に漏れ出して数値が上がります。スタチン系のお薬の副作用（横紋筋融解症）のチェックにも使われます。</v>
       </c>
       <c r="F30" t="str">
-        <v>脱水、消化管出血、高たんぱく食、心不全（腎臓への血流低下）</v>
+        <v>心筋梗塞、横紋筋融解症（スタチン系薬剤の副作用など）、激しい運動、筋肉注射直後、甲状腺機能低下症</v>
       </c>
       <c r="G30" t="str">
-        <v>脱水が疑われる場合はこまめな水分摂取を勧める。黒い便など消化管出血を示唆する症状がないか確認する</v>
+        <v>筋肉痛・脱力感・褐色尿（横紋筋融解症の症状）がないか確認する。スタチン系薬剤服用中は特に注意する。激しい運動の直後の採血でないかも確認する</v>
       </c>
       <c r="H30" t="str">
-        <v/>
+        <v>スタチン系(特にフィブラート系との併用時)、コルヒチン</v>
       </c>
       <c r="I30" t="str">
-        <v>低たんぱく食、肝不全、妊娠</v>
+        <v/>
       </c>
       <c r="J30" t="str">
         <v/>
@@ -1822,13 +1822,13 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>比が高い（目安20以上）場合は脱水や消化管出血など腎前性の要因を、比が正常範囲で両方高値なら腎性の障害を疑う。BUN単独やクレアチニン単独よりも病態の絞り込みに役立つ</v>
+        <v>スタチン系薬剤の重大な副作用である横紋筋融解症の指標。筋肉痛・脱力感・褐色尿の有無を必ず確認し、著明高値では服薬継続の可否を医師に相談する</v>
       </c>
       <c r="M30" t="str">
-        <v>腎機能</v>
+        <v/>
       </c>
       <c r="N30" t="str">
-        <v>BUN/CRE,BUN/Cr,尿素窒素,クレアチニン,脱水,腎前性</v>
+        <v>CK,CPK,クレアチンキナーゼ,横紋筋融解症</v>
       </c>
       <c r="O30" t="str">
         <v/>
@@ -1836,31 +1836,31 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>LDH/AST比</v>
+        <v>BUN/CRE比</v>
       </c>
       <c r="B31" t="str">
-        <v>LDH/AST</v>
+        <v>BUN/Cr</v>
       </c>
       <c r="C31" t="str">
-        <v>目安として使われる比率（施設差・カットオフ値の設定により異なる）</v>
+        <v>10前後が目安（施設差あり）</v>
       </c>
       <c r="D31" t="str">
-        <v>LDHとASTの両方が上昇したときに、原因が肝臓か、それ以外（溶血・心筋・骨格筋）かを見分ける目安になる比</v>
+        <v>BUNとクレアチニンの比率。腎前性（脱水・出血など）か腎性かを見分ける目安になる</v>
       </c>
       <c r="E31" t="str">
-        <v>これは、肝臓の数値（AST）と、全身に広く分布する酵素（LDH）の比率を見るもので、両方の数値が上がっているときに、原因が肝臓なのか、それとも血液や筋肉など他の場所なのかを見分ける手がかりになります。</v>
+        <v>これは、BUN（尿素窒素）とクレアチニンという2つの腎機能に関わる検査値を比較したもので、腎臓そのものに問題があるのか、それとも脱水や出血など腎臓の外側に原因があるのかを見分ける手がかりになります。</v>
       </c>
       <c r="F31" t="str">
-        <v>溶血性疾患、心筋梗塞、骨格筋の障害（比が高いほど肝臓以外が原因の可能性）</v>
+        <v>脱水、消化管出血、高たんぱく食、心不全（腎臓への血流低下）</v>
       </c>
       <c r="G31" t="str">
-        <v/>
+        <v>脱水が疑われる場合はこまめな水分摂取を勧める。黒い便など消化管出血を示唆する症状がないか確認する</v>
       </c>
       <c r="H31" t="str">
         <v/>
       </c>
       <c r="I31" t="str">
-        <v>急性肝炎などの肝細胞障害（比が低い、つまりASTに対してLDHが相対的に低い場合は肝性が示唆される）</v>
+        <v>低たんぱく食、肝不全、妊娠</v>
       </c>
       <c r="J31" t="str">
         <v/>
@@ -1869,13 +1869,13 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>AST・LDHが同時に上昇した際の鑑別に使う目安の一つ。単独の検査値ではなく計算上の比率であり、確定診断には他の検査（ビリルビン、CK、心筋マーカーなど）と合わせた評価が必要</v>
+        <v>比が高い（目安20以上）場合は脱水や消化管出血など腎前性の要因を、比が正常範囲で両方高値なら腎性の障害を疑う。BUN単独やクレアチニン単独よりも病態の絞り込みに役立つ</v>
       </c>
       <c r="M31" t="str">
-        <v/>
+        <v>腎機能</v>
       </c>
       <c r="N31" t="str">
-        <v>LDH/AST,LDH,AST,溶血,心筋梗塞,肝炎</v>
+        <v>BUN/CRE,BUN/Cr,尿素窒素,クレアチニン,脱水,腎前性</v>
       </c>
       <c r="O31" t="str">
         <v/>
@@ -1883,31 +1883,31 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>CK/AST比</v>
+        <v>LDH/AST比</v>
       </c>
       <c r="B32" t="str">
-        <v>CK/AST</v>
+        <v>LDH/AST</v>
       </c>
       <c r="C32" t="str">
         <v>目安として使われる比率（施設差・カットオフ値の設定により異なる）</v>
       </c>
       <c r="D32" t="str">
-        <v>ASTが上昇したときに、原因が筋肉（CKも上昇）か、それ以外（肝臓など）かを見分ける目安になる比</v>
+        <v>LDHとASTの両方が上昇したときに、原因が肝臓か、それ以外（溶血・心筋・骨格筋）かを見分ける目安になる比</v>
       </c>
       <c r="E32" t="str">
-        <v>これは、筋肉の数値（CK）と肝臓の数値（AST）を比べることで、ASTの上昇が筋肉由来なのか、肝臓由来なのかを見分ける手がかりになる比率です。</v>
+        <v>これは、肝臓の数値（AST）と、全身に広く分布する酵素（LDH）の比率を見るもので、両方の数値が上がっているときに、原因が肝臓なのか、それとも血液や筋肉など他の場所なのかを見分ける手がかりになります。</v>
       </c>
       <c r="F32" t="str">
-        <v>横紋筋融解症、心筋梗塞、激しい運動など筋肉由来のAST上昇（CKも同時に高値）</v>
+        <v>溶血性疾患、心筋梗塞、骨格筋の障害（比が高いほど肝臓以外が原因の可能性）</v>
       </c>
       <c r="G32" t="str">
-        <v>筋肉痛や脱力感、褐色尿などの症状がないか確認する</v>
+        <v/>
       </c>
       <c r="H32" t="str">
         <v/>
       </c>
       <c r="I32" t="str">
-        <v/>
+        <v>急性肝炎などの肝細胞障害（比が低い、つまりASTに対してLDHが相対的に低い場合は肝性が示唆される）</v>
       </c>
       <c r="J32" t="str">
         <v/>
@@ -1916,13 +1916,13 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>ASTのみ上昇しCKが正常であれば肝臓由来を、両方上昇していれば筋肉由来を疑う手がかりになる。スタチン系薬剤による横紋筋融解症が疑われる場面での鑑別に有用</v>
+        <v>AST・LDHが同時に上昇した際の鑑別に使う目安の一つ。単独の検査値ではなく計算上の比率であり、確定診断には他の検査（ビリルビン、CK、心筋マーカーなど）と合わせた評価が必要</v>
       </c>
       <c r="M32" t="str">
         <v/>
       </c>
       <c r="N32" t="str">
-        <v>CK/AST,CK,AST,横紋筋融解症,スタチン</v>
+        <v>LDH/AST,LDH,AST,溶血,心筋梗塞,肝炎</v>
       </c>
       <c r="O32" t="str">
         <v/>
@@ -1930,25 +1930,25 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Na-Cl（ナトリウム・クロール差）</v>
+        <v>CK/AST比</v>
       </c>
       <c r="B33" t="str">
-        <v>Na-Cl</v>
+        <v>CK/AST</v>
       </c>
       <c r="C33" t="str">
-        <v>36前後が目安（施設差あり）</v>
+        <v>目安として使われる比率（施設差・カットオフ値の設定により異なる）</v>
       </c>
       <c r="D33" t="str">
-        <v>ナトリウムからクロールを引いた値。アニオンギャップの簡易的な目安として使われる</v>
+        <v>ASTが上昇したときに、原因が筋肉（CKも上昇）か、それ以外（肝臓など）かを見分ける目安になる比</v>
       </c>
       <c r="E33" t="str">
-        <v>この数値は、ナトリウムとクロールの検査値の差から計算されるもので、体の中に通常とは違う酸（アニオン）がたまっていないかを大まかに見積もるために使われます。</v>
+        <v>これは、筋肉の数値（CK）と肝臓の数値（AST）を比べることで、ASTの上昇が筋肉由来なのか、肝臓由来なのかを見分ける手がかりになる比率です。</v>
       </c>
       <c r="F33" t="str">
-        <v>代謝性アシドーシス（乳酸アシドーシス、糖尿病性ケトアシドーシス、腎不全など、体内に有機酸がたまる病態）</v>
+        <v>横紋筋融解症、心筋梗塞、激しい運動など筋肉由来のAST上昇（CKも同時に高値）</v>
       </c>
       <c r="G33" t="str">
-        <v/>
+        <v>筋肉痛や脱力感、褐色尿などの症状がないか確認する</v>
       </c>
       <c r="H33" t="str">
         <v/>
@@ -1963,13 +1963,13 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>本来のアニオンギャップ(Na-(Cl+HCO3))の簡易代用として使われることがあるが、重炭酸(HCO3)を用いた計算の方が正確。メトホルミン使用中の乳酸アシドーシスが疑われる場面などで参考にする</v>
+        <v>ASTのみ上昇しCKが正常であれば肝臓由来を、両方上昇していれば筋肉由来を疑う手がかりになる。スタチン系薬剤による横紋筋融解症が疑われる場面での鑑別に有用</v>
       </c>
       <c r="M33" t="str">
-        <v>電解質</v>
+        <v/>
       </c>
       <c r="N33" t="str">
-        <v>Na-Cl,アニオンギャップ,AG,代謝性アシドーシス,乳酸アシドーシス</v>
+        <v>CK/AST,CK,AST,横紋筋融解症,スタチン</v>
       </c>
       <c r="O33" t="str">
         <v/>
@@ -1977,31 +1977,31 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>AST/ALT比</v>
+        <v>Na-Cl（ナトリウム・クロール差）</v>
       </c>
       <c r="B34" t="str">
-        <v>AST/ALT,De Ritis比</v>
+        <v>Na-Cl</v>
       </c>
       <c r="C34" t="str">
-        <v>1未満が目安（施設・病態により異なる）</v>
+        <v>36前後が目安（施設差あり）</v>
       </c>
       <c r="D34" t="str">
-        <v>ASTとALTの比率（De Ritis比）。肝疾患の種類を推測する手がかりになる</v>
+        <v>ナトリウムからクロールを引いた値。アニオンギャップの簡易的な目安として使われる</v>
       </c>
       <c r="E34" t="str">
-        <v>これは、肝臓に関わる2つの数値（ASTとALT）の比率を見るもので、肝臓のどのようなタイプのトラブルが起きているかを推測する手がかりになります。</v>
+        <v>この数値は、ナトリウムとクロールの検査値の差から計算されるもので、体の中に通常とは違う酸（アニオン）がたまっていないかを大まかに見積もるために使われます。</v>
       </c>
       <c r="F34" t="str">
-        <v>アルコール性肝障害、肝硬変、心筋梗塞・筋疾患の合併（比が2以上でアルコール性を強く示唆）</v>
+        <v>代謝性アシドーシス（乳酸アシドーシス、糖尿病性ケトアシドーシス、腎不全など、体内に有機酸がたまる病態）</v>
       </c>
       <c r="G34" t="str">
-        <v>飲酒量や頻度を確認する</v>
+        <v/>
       </c>
       <c r="H34" t="str">
         <v/>
       </c>
       <c r="I34" t="str">
-        <v>急性ウイルス性肝炎、脂肪肝（比が1未満で肝細胞の急性障害を示唆することが多い）</v>
+        <v/>
       </c>
       <c r="J34" t="str">
         <v/>
@@ -2010,13 +2010,13 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>De Ritis比とも呼ばれる。比が2以上はアルコール性肝障害や肝硬変を、1未満は急性ウイルス性肝炎や脂肪肝を示唆する目安になるが、確定診断には他の検査所見と合わせた評価が必要</v>
+        <v>本来のアニオンギャップ(Na-(Cl+HCO3))の簡易代用として使われることがあるが、重炭酸(HCO3)を用いた計算の方が正確。メトホルミン使用中の乳酸アシドーシスが疑われる場面などで参考にする</v>
       </c>
       <c r="M34" t="str">
-        <v>肝機能</v>
+        <v>電解質</v>
       </c>
       <c r="N34" t="str">
-        <v>AST/ALT比,AST/ALT,De Ritis比,デリティス比,アルコール性肝障害,肝硬変</v>
+        <v>Na-Cl,アニオンギャップ,AG,代謝性アシドーシス,乳酸アシドーシス</v>
       </c>
       <c r="O34" t="str">
         <v/>
@@ -2024,31 +2024,31 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>ALT/ALP比</v>
+        <v>AST/ALT比</v>
       </c>
       <c r="B35" t="str">
-        <v>ALT比/ALP比,R比,R-factor</v>
+        <v>AST/ALT,De Ritis比</v>
       </c>
       <c r="C35" t="str">
-        <v>R値 5以上：肝細胞障害型、2以下：胆汁うっ滞型、2〜5：混合型</v>
+        <v>1未満が目安（施設・病態により異なる）</v>
       </c>
       <c r="D35" t="str">
-        <v>薬剤性肝障害(DILI)などで、肝障害のパターンを「肝細胞障害型」か「胆汁うっ滞型」かに分類するための指標(R値)</v>
+        <v>ASTとALTの比率（De Ritis比）。肝疾患の種類を推測する手がかりになる</v>
       </c>
       <c r="E35" t="str">
-        <v>肝臓に関する数値はいくつかありますが、その組み合わせ方によって「肝臓の細胞自体が傷んでいるタイプ」か「胆汁の流れが悪くなっているタイプ」かをある程度見分けることができます。この指標はその判定に使われます。</v>
+        <v>これは、肝臓に関わる2つの数値（ASTとALT）の比率を見るもので、肝臓のどのようなタイプのトラブルが起きているかを推測する手がかりになります。</v>
       </c>
       <c r="F35" t="str">
-        <v>R値5以上：肝細胞障害型（ウイルス性肝炎、薬剤性肝障害の肝細胞障害型、虚血性肝障害など）</v>
+        <v>アルコール性肝障害、肝硬変、心筋梗塞・筋疾患の合併（比が2以上でアルコール性を強く示唆）</v>
       </c>
       <c r="G35" t="str">
-        <v/>
+        <v>飲酒量や頻度を確認する</v>
       </c>
       <c r="H35" t="str">
         <v/>
       </c>
       <c r="I35" t="str">
-        <v>R値2以下：胆汁うっ滞型（閉塞性黄疸、薬剤性肝障害の胆汁うっ滞型など）</v>
+        <v>急性ウイルス性肝炎、脂肪肝（比が1未満で肝細胞の急性障害を示唆することが多い）</v>
       </c>
       <c r="J35" t="str">
         <v/>
@@ -2057,13 +2057,13 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>R値＝(ALTの基準値上限に対する倍率)÷(ALPの基準値上限に対する倍率)で算出する。薬剤性肝障害(DILI)の病型分類(肝細胞障害型/胆汁うっ滞型/混合型)に用いられ、被疑薬の休薬・変更の判断材料になる</v>
+        <v>De Ritis比とも呼ばれる。比が2以上はアルコール性肝障害や肝硬変を、1未満は急性ウイルス性肝炎や脂肪肝を示唆する目安になるが、確定診断には他の検査所見と合わせた評価が必要</v>
       </c>
       <c r="M35" t="str">
         <v>肝機能</v>
       </c>
       <c r="N35" t="str">
-        <v>ALT/ALP比,R値,R-factor,DILI,薬剤性肝障害</v>
+        <v>AST/ALT比,AST/ALT,De Ritis比,デリティス比,アルコール性肝障害,肝硬変</v>
       </c>
       <c r="O35" t="str">
         <v/>
@@ -2071,31 +2071,31 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>BNP</v>
+        <v>ALT/ALP比</v>
       </c>
       <c r="B36" t="str">
-        <v>BNP</v>
+        <v>ALT比/ALP比,R比,R-factor</v>
       </c>
       <c r="C36" t="str">
-        <v>18.4 pg/mL以下</v>
+        <v>R値 5以上：肝細胞障害型、2以下：胆汁うっ滞型、2〜5：混合型</v>
       </c>
       <c r="D36" t="str">
-        <v>心臓が無理をしているときに出る物質。心臓は血液を送るポンプだが、負担がかかると「少し助けてほしい」というサインとしてBNPを血液中に出す。</v>
+        <v>薬剤性肝障害(DILI)などで、肝障害のパターンを「肝細胞障害型」か「胆汁うっ滞型」かに分類するための指標(R値)</v>
       </c>
       <c r="E36" t="str">
-        <v>この検査は、心臓がどれくらい頑張りすぎていないかを見るものです。数値が高いと、心臓に少し負担がかかっているサインになります。</v>
+        <v>肝臓に関する数値はいくつかありますが、その組み合わせ方によって「肝臓の細胞自体が傷んでいるタイプ」か「胆汁の流れが悪くなっているタイプ」かをある程度見分けることができます。この指標はその判定に使われます。</v>
       </c>
       <c r="F36" t="str">
-        <v>心不全、心臓に負担がかかっている状態、体に水分がたまりやすいとき</v>
+        <v>R値5以上：肝細胞障害型（ウイルス性肝炎、薬剤性肝障害の肝細胞障害型、虚血性肝障害など）</v>
       </c>
       <c r="G36" t="str">
-        <v>塩分・水分の摂りすぎに注意し、体重の変化を毎日記録するよう伝える。急な体重増加(2〜3日で2kg以上)や息切れの悪化があれば早めの受診を勧める</v>
+        <v/>
       </c>
       <c r="H36" t="str">
         <v/>
       </c>
       <c r="I36" t="str">
-        <v>心臓の負担は少ない状態</v>
+        <v>R値2以下：胆汁うっ滞型（閉塞性黄疸、薬剤性肝障害の胆汁うっ滞型など）</v>
       </c>
       <c r="J36" t="str">
         <v/>
@@ -2104,45 +2104,45 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>腎機能が低いとBNPは高めに出ることがある／数値だけで判断せず、症状と合わせて評価する／息切れ、むくみ、体重増加があれば要注意</v>
+        <v>R値＝(ALTの基準値上限に対する倍率)÷(ALPの基準値上限に対する倍率)で算出する。薬剤性肝障害(DILI)の病型分類(肝細胞障害型/胆汁うっ滞型/混合型)に用いられ、被疑薬の休薬・変更の判断材料になる</v>
       </c>
       <c r="M36" t="str">
-        <v>心不全</v>
+        <v>肝機能</v>
       </c>
       <c r="N36" t="str">
-        <v>BNP,心不全,息切れ,むくみ</v>
+        <v>ALT/ALP比,R値,R-factor,DILI,薬剤性肝障害</v>
       </c>
       <c r="O36" t="str">
-        <v>食事と栄養 p.216-222（第2部 心疾患）</v>
+        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>CONUT値</v>
+        <v>BNP</v>
       </c>
       <c r="B37" t="str">
-        <v>CONUT</v>
+        <v>BNP</v>
       </c>
       <c r="C37" t="str">
-        <v>0〜1点：正常、2〜4点：軽度低栄養、5〜8点：中等度低栄養、9〜12点：高度低栄養</v>
+        <v>18.4 pg/mL以下</v>
       </c>
       <c r="D37" t="str">
-        <v>アルブミン・総リンパ球数・総コレステロールの3項目から算出する栄養状態の評価スコア</v>
+        <v>心臓が無理をしているときに出る物質。心臓は血液を送るポンプだが、負担がかかると「少し助けてほしい」というサインとしてBNPを血液中に出す。</v>
       </c>
       <c r="E37" t="str">
-        <v>CONUT値は、血液検査（アルブミン、リンパ球数、コレステロール）の結果から計算される、栄養状態を数値化したスコアです。点数が高いほど低栄養の状態が疑われます。</v>
+        <v>この検査は、心臓がどれくらい頑張りすぎていないかを見るものです。数値が高いと、心臓に少し負担がかかっているサインになります。</v>
       </c>
       <c r="F37" t="str">
-        <v>低栄養状態（点数が高いほど重度）</v>
+        <v>心不全、心臓に負担がかかっている状態、体に水分がたまりやすいとき</v>
       </c>
       <c r="G37" t="str">
-        <v>食事摂取量や体重の変化を確認する。必要に応じて栄養補助食品の活用を提案する</v>
+        <v>塩分・水分の摂りすぎに注意し、体重の変化を毎日記録するよう伝える。急な体重増加(2〜3日で2kg以上)や息切れの悪化があれば早めの受診を勧める</v>
       </c>
       <c r="H37" t="str">
         <v/>
       </c>
       <c r="I37" t="str">
-        <v/>
+        <v>心臓の負担は少ない状態</v>
       </c>
       <c r="J37" t="str">
         <v/>
@@ -2151,39 +2151,39 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>アルブミン・総リンパ球数・総コレステロールの3項目それぞれに配点があり、合計点で評価する客観的栄養指標。フレイル・サルコペニアの評価やポリファーマシー対策の一環としての栄養状態把握に有用</v>
+        <v>腎機能が低いとBNPは高めに出ることがある／数値だけで判断せず、症状と合わせて評価する／息切れ、むくみ、体重増加があれば要注意</v>
       </c>
       <c r="M37" t="str">
-        <v/>
+        <v>心不全</v>
       </c>
       <c r="N37" t="str">
-        <v>CONUT,CONUT値,栄養評価,低栄養,フレイル</v>
+        <v>BNP,心不全,息切れ,むくみ</v>
       </c>
       <c r="O37" t="str">
-        <v>食事と栄養 p.240（フレイルQ108 低栄養や食事量の評価）</v>
+        <v>食事と栄養 p.216-222（第2部 心疾患）</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>乳び</v>
+        <v>CONUT値</v>
       </c>
       <c r="B38" t="str">
-        <v>乳び,Lipemia</v>
+        <v>CONUT</v>
       </c>
       <c r="C38" t="str">
-        <v>所見なし（血清が白濁していなければ正常）</v>
+        <v>0〜1点：正常、2〜4点：軽度低栄養、5〜8点：中等度低栄養、9〜12点：高度低栄養</v>
       </c>
       <c r="D38" t="str">
-        <v>中性脂肪が非常に多いため、血清が白く濁って見える状態。検査値そのものではなく検体の外観所見</v>
+        <v>アルブミン・総リンパ球数・総コレステロールの3項目から算出する栄養状態の評価スコア</v>
       </c>
       <c r="E38" t="str">
-        <v>乳びとは、血液中の中性脂肪が非常に多いために、採血した血液（血清）が白く濁って見える状態のことです。多くの場合、食後の採血や、著しい脂質異常症が背景にあります。</v>
+        <v>CONUT値は、血液検査（アルブミン、リンパ球数、コレステロール）の結果から計算される、栄養状態を数値化したスコアです。点数が高いほど低栄養の状態が疑われます。</v>
       </c>
       <c r="F38" t="str">
-        <v>著しい高中性脂肪血症、食後採血（一時的なもの）、原発性高カイロミクロン血症などの脂質代謝異常</v>
+        <v>低栄養状態（点数が高いほど重度）</v>
       </c>
       <c r="G38" t="str">
-        <v>採血が空腹時だったかを確認する。食後採血であれば次回は空腹時の再検を提案する</v>
+        <v>食事摂取量や体重の変化を確認する。必要に応じて栄養補助食品の活用を提案する</v>
       </c>
       <c r="H38" t="str">
         <v/>
@@ -2198,39 +2198,39 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>血清の白濁により一部の検査項目（電解質など）の測定値に誤差が出ることがある（偽性低ナトリウム血症など）。中性脂肪値と合わせて評価する</v>
+        <v>アルブミン・総リンパ球数・総コレステロールの3項目それぞれに配点があり、合計点で評価する客観的栄養指標。フレイル・サルコペニアの評価やポリファーマシー対策の一環としての栄養状態把握に有用</v>
       </c>
       <c r="M38" t="str">
-        <v>脂質異常症</v>
+        <v/>
       </c>
       <c r="N38" t="str">
-        <v>乳び,乳び血清,Lipemia,高中性脂肪血症</v>
+        <v>CONUT,CONUT値,栄養評価,低栄養,フレイル</v>
       </c>
       <c r="O38" t="str">
-        <v/>
+        <v>食事と栄養 p.240（フレイルQ108 低栄養や食事量の評価）</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>溶血</v>
+        <v>乳び</v>
       </c>
       <c r="B39" t="str">
-        <v>溶血,Hemolysis</v>
+        <v>乳び,Lipemia</v>
       </c>
       <c r="C39" t="str">
-        <v>所見なし（溶血を示唆する検査値異常がなければ正常）</v>
+        <v>所見なし（血清が白濁していなければ正常）</v>
       </c>
       <c r="D39" t="str">
-        <v>赤血球が通常より早く壊れる状態。単独の検査値ではなく、複数の検査値の組み合わせで疑う病態</v>
+        <v>中性脂肪が非常に多いため、血清が白く濁って見える状態。検査値そのものではなく検体の外観所見</v>
       </c>
       <c r="E39" t="str">
-        <v>溶血とは、赤血球が通常よりも早いペースで壊れてしまう状態のことです。壊れた赤血球からビリルビンなどが放出されるため、貧血や黄疸の原因になることがあります。</v>
+        <v>乳びとは、血液中の中性脂肪が非常に多いために、採血した血液（血清）が白く濁って見える状態のことです。多くの場合、食後の採血や、著しい脂質異常症が背景にあります。</v>
       </c>
       <c r="F39" t="str">
-        <v>自己免疫性溶血性貧血、血液型不適合輸血、G6PD欠損症などの遺伝性疾患、機械弁など人工物による物理的破壊、薬剤性溶血</v>
+        <v>著しい高中性脂肪血症、食後採血（一時的なもの）、原発性高カイロミクロン血症などの脂質代謝異常</v>
       </c>
       <c r="G39" t="str">
-        <v>倦怠感、黄疸、尿の色が濃くなるなどの症状がないか確認する</v>
+        <v>採血が空腹時だったかを確認する。食後採血であれば次回は空腹時の再検を提案する</v>
       </c>
       <c r="H39" t="str">
         <v/>
@@ -2245,13 +2245,13 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>溶血を疑う際は、間接ビリルビン上昇・LDH上昇・ハプトグロビン低下・網状赤血球増加のパターンを確認する。ヘモグロビン・MCV・MCHCの変化と合わせて総合的に判断する</v>
+        <v>血清の白濁により一部の検査項目（電解質など）の測定値に誤差が出ることがある（偽性低ナトリウム血症など）。中性脂肪値と合わせて評価する</v>
       </c>
       <c r="M39" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>脂質異常症</v>
       </c>
       <c r="N39" t="str">
-        <v>溶血,Hemolysis,溶血性貧血,G6PD,ハプトグロビン</v>
+        <v>乳び,乳び血清,Lipemia,高中性脂肪血症</v>
       </c>
       <c r="O39" t="str">
         <v/>
@@ -2259,25 +2259,25 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>黄疸</v>
+        <v>溶血</v>
       </c>
       <c r="B40" t="str">
-        <v>黄疸,Jaundice</v>
+        <v>溶血,Hemolysis</v>
       </c>
       <c r="C40" t="str">
-        <v>所見なし（皮膚・眼球結膜の黄染がなければ正常）</v>
+        <v>所見なし（溶血を示唆する検査値異常がなければ正常）</v>
       </c>
       <c r="D40" t="str">
-        <v>ビリルビンが体にたまり、皮膚や白目が黄色くなる状態。単独の検査値ではなく、ビリルビン上昇によって表れる身体所見</v>
+        <v>赤血球が通常より早く壊れる状態。単独の検査値ではなく、複数の検査値の組み合わせで疑う病態</v>
       </c>
       <c r="E40" t="str">
-        <v>黄疸は、体の中にビリルビンという黄色い色素がたまることで、皮膚や白目が黄色く見える状態です。肝臓や胆道のトラブル、赤血球が壊れやすくなる病気（溶血）などが原因となります。</v>
+        <v>溶血とは、赤血球が通常よりも早いペースで壊れてしまう状態のことです。壊れた赤血球からビリルビンなどが放出されるため、貧血や黄疸の原因になることがあります。</v>
       </c>
       <c r="F40" t="str">
-        <v>肝炎・肝硬変などの肝疾患、胆石・腫瘍による胆道閉塞、溶血性疾患、体質性黄疸（ジルベール症候群）、新生児黄疸</v>
+        <v>自己免疫性溶血性貧血、血液型不適合輸血、G6PD欠損症などの遺伝性疾患、機械弁など人工物による物理的破壊、薬剤性溶血</v>
       </c>
       <c r="G40" t="str">
-        <v>白目や皮膚の黄染に気づいたら、尿の色（濃い茶色）や便の色（白っぽい）の変化も確認し、早めの受診を勧める</v>
+        <v>倦怠感、黄疸、尿の色が濃くなるなどの症状がないか確認する</v>
       </c>
       <c r="H40" t="str">
         <v/>
@@ -2292,13 +2292,13 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>黄疸は検査値そのものではなく身体所見。原因を調べる際は総ビリルビン・直接ビリルビン・間接ビリルビンの内訳とAST/ALT/γ-GTPを確認する。直接優位なら胆道系、間接優位なら溶血・体質性を疑う</v>
+        <v>溶血を疑う際は、間接ビリルビン上昇・LDH上昇・ハプトグロビン低下・網状赤血球増加のパターンを確認する。ヘモグロビン・MCV・MCHCの変化と合わせて総合的に判断する</v>
       </c>
       <c r="M40" t="str">
-        <v>肝機能</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="N40" t="str">
-        <v>黄疸,ジョンダイス,Jaundice,ビリルビン,皮膚黄染,白目</v>
+        <v>溶血,Hemolysis,溶血性貧血,G6PD,ハプトグロビン</v>
       </c>
       <c r="O40" t="str">
         <v/>
@@ -2306,93 +2306,93 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>甲状腺刺激ホルモン（TSH）</v>
+        <v>黄疸</v>
       </c>
       <c r="B41" t="str">
-        <v>TSH</v>
+        <v>黄疸,Jaundice</v>
       </c>
       <c r="C41" t="str">
-        <v>0.5〜5.0 μIU/mL程度（施設差あり）</v>
+        <v>所見なし（皮膚・眼球結膜の黄染がなければ正常）</v>
       </c>
       <c r="D41" t="str">
-        <v>甲状腺の働きが多いか少ないかを最も敏感に反映するホルモン</v>
+        <v>ビリルビンが体にたまり、皮膚や白目が黄色くなる状態。単独の検査値ではなく、ビリルビン上昇によって表れる身体所見</v>
       </c>
       <c r="E41" t="str">
-        <v>TSHは脳の下垂体から出て、甲状腺に「もっと働いて」と指令を送るホルモンです。甲状腺の働きが弱っていると体が指令を強めるためTSHは上がり、逆に甲状腺が働きすぎているとTSHは下がります。甲状腺の状態を最初に確認する数値としてよく使われます。</v>
+        <v>黄疸は、体の中にビリルビンという黄色い色素がたまることで、皮膚や白目が黄色く見える状態です。肝臓や胆道のトラブル、赤血球が壊れやすくなる病気（溶血）などが原因となります。</v>
       </c>
       <c r="F41" t="str">
-        <v>甲状腺機能低下症（橋本病など）、チラーヂンSなど甲状腺ホルモン薬の量不足</v>
+        <v>肝炎・肝硬変などの肝疾患、胆石・腫瘍による胆道閉塞、溶血性疾患、体質性黄疸（ジルベール症候群）、新生児黄疸</v>
       </c>
       <c r="G41" t="str">
-        <v>だるさ、むくみ、体重増加、寒がりなどの症状がないか確認する。服薬状況（飲み忘れ、他の薬との飲み合わせ）を確認する</v>
+        <v>白目や皮膚の黄染に気づいたら、尿の色（濃い茶色）や便の色（白っぽい）の変化も確認し、早めの受診を勧める</v>
       </c>
       <c r="H41" t="str">
-        <v>アミオダロン、炭酸リチウム、インターフェロン製剤、チロシンキナーゼ阻害薬(スニチニブ等)</v>
+        <v/>
       </c>
       <c r="I41" t="str">
-        <v>甲状腺機能亢進症（バセドウ病など）、チラーヂンSなど甲状腺ホルモン薬の過量</v>
+        <v/>
       </c>
       <c r="J41" t="str">
-        <v>動悸、体重減少、暑がり、手のふるえなどの症状がないか確認する</v>
+        <v/>
       </c>
       <c r="K41" t="str">
-        <v>レボチロキシンの過量投与</v>
+        <v/>
       </c>
       <c r="L41" t="str">
-        <v>チラーヂンS服用中はTSHが治療目標域に収まっているかで用量調整の目安にする。メルカゾール服用中はTSH・FT4に加えて無顆粒球症の初期症状（発熱・のどの痛み）の有無や白血球数も確認する</v>
+        <v>黄疸は検査値そのものではなく身体所見。原因を調べる際は総ビリルビン・直接ビリルビン・間接ビリルビンの内訳とAST/ALT/γ-GTPを確認する。直接優位なら胆道系、間接優位なら溶血・体質性を疑う</v>
       </c>
       <c r="M41" t="str">
-        <v>甲状腺疾患</v>
+        <v>肝機能</v>
       </c>
       <c r="N41" t="str">
-        <v>TSH,甲状腺刺激ホルモン,甲状腺機能,橋本病,バセドウ病,チラーヂン,メルカゾール</v>
+        <v>黄疸,ジョンダイス,Jaundice,ビリルビン,皮膚黄染,白目</v>
       </c>
       <c r="O41" t="str">
-        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
+        <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>遊離サイロキシン（FT4）</v>
+        <v>甲状腺刺激ホルモン（TSH）</v>
       </c>
       <c r="B42" t="str">
-        <v>FT4</v>
+        <v>TSH</v>
       </c>
       <c r="C42" t="str">
-        <v>0.9〜1.7 ng/dL程度（施設差あり）</v>
+        <v>0.5〜5.0 μIU/mL程度（施設差あり）</v>
       </c>
       <c r="D42" t="str">
-        <v>甲状腺が実際に分泌しているホルモンの量そのものを表す数値</v>
+        <v>甲状腺の働きが多いか少ないかを最も敏感に反映するホルモン</v>
       </c>
       <c r="E42" t="str">
-        <v>FT4は甲状腺そのものが作っているホルモンの量です。TSHが「指令の強さ」だとすると、FT4は「実際に出ている量」にあたります。2つをあわせて見ることで、甲状腺の働きが今どういう状態かを詳しく判断できます。</v>
+        <v>TSHは脳の下垂体から出て、甲状腺に「もっと働いて」と指令を送るホルモンです。甲状腺の働きが弱っていると体が指令を強めるためTSHは上がり、逆に甲状腺が働きすぎているとTSHは下がります。甲状腺の状態を最初に確認する数値としてよく使われます。</v>
       </c>
       <c r="F42" t="str">
-        <v>甲状腺機能亢進症（バセドウ病など）</v>
+        <v>甲状腺機能低下症（橋本病など）、チラーヂンSなど甲状腺ホルモン薬の量不足</v>
       </c>
       <c r="G42" t="str">
+        <v>だるさ、むくみ、体重増加、寒がりなどの症状がないか確認する。服薬状況（飲み忘れ、他の薬との飲み合わせ）を確認する</v>
+      </c>
+      <c r="H42" t="str">
+        <v>アミオダロン、炭酸リチウム、インターフェロン製剤、チロシンキナーゼ阻害薬(スニチニブ等)</v>
+      </c>
+      <c r="I42" t="str">
+        <v>甲状腺機能亢進症（バセドウ病など）、チラーヂンSなど甲状腺ホルモン薬の過量</v>
+      </c>
+      <c r="J42" t="str">
         <v>動悸、体重減少、暑がり、手のふるえなどの症状がないか確認する</v>
       </c>
-      <c r="H42" t="str">
-        <v>レボチロキシンの過量投与、アミオダロン</v>
-      </c>
-      <c r="I42" t="str">
-        <v>甲状腺機能低下症（橋本病など）</v>
-      </c>
-      <c r="J42" t="str">
-        <v>だるさ、むくみ、体重増加、寒がりなどの症状がないか確認する</v>
-      </c>
       <c r="K42" t="str">
-        <v>抗甲状腺薬(メルカゾール、プロパジール)の効きすぎ</v>
+        <v>レボチロキシンの過量投与</v>
       </c>
       <c r="L42" t="str">
-        <v>TSHと逆方向に動くのが基本だが、下垂体性の異常など例外もある。TSHと合わせて評価し、片方だけで判断しない</v>
+        <v>チラーヂンS服用中はTSHが治療目標域に収まっているかで用量調整の目安にする。メルカゾール服用中はTSH・FT4に加えて無顆粒球症の初期症状（発熱・のどの痛み）の有無や白血球数も確認する</v>
       </c>
       <c r="M42" t="str">
         <v>甲状腺疾患</v>
       </c>
       <c r="N42" t="str">
-        <v>FT4,遊離サイロキシン,甲状腺ホルモン,甲状腺機能</v>
+        <v>TSH,甲状腺刺激ホルモン,甲状腺機能,橋本病,バセドウ病,チラーヂン,メルカゾール</v>
       </c>
       <c r="O42" t="str">
         <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
@@ -2400,78 +2400,78 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>尿蛋白（随時尿）</v>
+        <v>遊離サイロキシン（FT4）</v>
       </c>
       <c r="B43" t="str">
-        <v>尿蛋白,U-pro</v>
+        <v>FT4</v>
       </c>
       <c r="C43" t="str">
-        <v>陰性（－）〜弱陽性</v>
+        <v>0.9〜1.7 ng/dL程度（施設差あり）</v>
       </c>
       <c r="D43" t="str">
-        <v>腎臓から本来漏れないはずのたんぱくが尿に出ていないかを見る検査</v>
+        <v>甲状腺が実際に分泌しているホルモンの量そのものを表す数値</v>
       </c>
       <c r="E43" t="str">
-        <v>この検査は、腎臓のろ過機能に負担がかかっていないかを見るものです。本来、たんぱく質は尿にほとんど出ませんが、腎臓に負担がかかると漏れ出るようになります。</v>
+        <v>FT4は甲状腺そのものが作っているホルモンの量です。TSHが「指令の強さ」だとすると、FT4は「実際に出ている量」にあたります。2つをあわせて見ることで、甲状腺の働きが今どういう状態かを詳しく判断できます。</v>
       </c>
       <c r="F43" t="str">
-        <v>糖尿病性腎症、腎炎、高血圧性腎硬化症、発熱・運動後の一過性のもの</v>
+        <v>甲状腺機能亢進症（バセドウ病など）</v>
       </c>
       <c r="G43" t="str">
-        <v>発熱・激しい運動の直後でないか確認する(一過性のことがある)。持続する場合は塩分の摂りすぎに注意し、むくみの有無もあわせて確認する</v>
+        <v>動悸、体重減少、暑がり、手のふるえなどの症状がないか確認する</v>
       </c>
       <c r="H43" t="str">
-        <v>NSAIDs、造影剤、アミノグリコシド系、バンコマイシン、金製剤</v>
+        <v>レボチロキシンの過量投与、アミオダロン</v>
       </c>
       <c r="I43" t="str">
-        <v/>
+        <v>甲状腺機能低下症（橋本病など）</v>
       </c>
       <c r="J43" t="str">
-        <v/>
+        <v>だるさ、むくみ、体重増加、寒がりなどの症状がないか確認する</v>
       </c>
       <c r="K43" t="str">
-        <v/>
+        <v>抗甲状腺薬(メルカゾール、プロパジール)の効きすぎ</v>
       </c>
       <c r="L43" t="str">
-        <v>発熱・激しい運動・起立性蛋白尿など生理的な要因でも陽性になることがある。持続する場合に腎症の進行を疑う</v>
+        <v>TSHと逆方向に動くのが基本だが、下垂体性の異常など例外もある。TSHと合わせて評価し、片方だけで判断しない</v>
       </c>
       <c r="M43" t="str">
-        <v>糖尿病,腎機能</v>
+        <v>甲状腺疾患</v>
       </c>
       <c r="N43" t="str">
-        <v>尿蛋白,U-pro,腎症,たんぱく尿</v>
+        <v>FT4,遊離サイロキシン,甲状腺ホルモン,甲状腺機能</v>
       </c>
       <c r="O43" t="str">
-        <v/>
+        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>尿クレアチニン（随時尿）</v>
+        <v>尿蛋白（随時尿）</v>
       </c>
       <c r="B44" t="str">
-        <v>尿CRE</v>
+        <v>尿蛋白,U-pro</v>
       </c>
       <c r="C44" t="str">
-        <v>随時尿は主に他項目の濃度補正に利用（単独の基準値は設けにくい）</v>
+        <v>陰性（－）〜弱陽性</v>
       </c>
       <c r="D44" t="str">
-        <v>随時尿中のクレアチニン濃度。他の尿検査項目を薄まり具合で補正するための基準として使う</v>
+        <v>腎臓から本来漏れないはずのたんぱくが尿に出ていないかを見る検査</v>
       </c>
       <c r="E44" t="str">
-        <v>この数値は、尿がどれくらい薄まっているかを確認するための基準として使われます。他の尿検査の結果（蛋白やアルブミンなど）をこの値で割って補正することで、水分摂取量による影響を減らして正確に評価できます。</v>
+        <v>この検査は、腎臓のろ過機能に負担がかかっていないかを見るものです。本来、たんぱく質は尿にほとんど出ませんが、腎臓に負担がかかると漏れ出るようになります。</v>
       </c>
       <c r="F44" t="str">
-        <v/>
+        <v>糖尿病性腎症、腎炎、高血圧性腎硬化症、発熱・運動後の一過性のもの</v>
       </c>
       <c r="G44" t="str">
-        <v/>
+        <v>発熱・激しい運動の直後でないか確認する(一過性のことがある)。持続する場合は塩分の摂りすぎに注意し、むくみの有無もあわせて確認する</v>
       </c>
       <c r="H44" t="str">
-        <v/>
+        <v>NSAIDs、造影剤、アミノグリコシド系、バンコマイシン、金製剤</v>
       </c>
       <c r="I44" t="str">
-        <v>尿が薄い（水分摂取が多い、腎機能低下）状態</v>
+        <v/>
       </c>
       <c r="J44" t="str">
         <v/>
@@ -2480,13 +2480,13 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>尿中アルブミン/Cr比、尿蛋白/Cr比など、他項目の補正計算に使われる。単独の高低に臨床的意味は乏しい</v>
+        <v>発熱・激しい運動・起立性蛋白尿など生理的な要因でも陽性になることがある。持続する場合に腎症の進行を疑う</v>
       </c>
       <c r="M44" t="str">
-        <v>腎機能</v>
+        <v>糖尿病,腎機能</v>
       </c>
       <c r="N44" t="str">
-        <v>尿CRE,尿クレアチニン,随時尿,補正,蛋白クレアチニン比</v>
+        <v>尿蛋白,U-pro,腎症,たんぱく尿</v>
       </c>
       <c r="O44" t="str">
         <v/>
@@ -2494,46 +2494,46 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>白血球数（WBC）</v>
+        <v>尿クレアチニン（随時尿）</v>
       </c>
       <c r="B45" t="str">
-        <v>WBC</v>
+        <v>尿CRE</v>
       </c>
       <c r="C45" t="str">
-        <v>3,300〜8,600 /μL程度（施設差あり）</v>
+        <v>随時尿は主に他項目の濃度補正に利用（単独の基準値は設けにくい）</v>
       </c>
       <c r="D45" t="str">
-        <v>体を細菌やウイルスから守る免疫細胞の数で、感染や炎症、薬剤の影響を反映する</v>
+        <v>随時尿中のクレアチニン濃度。他の尿検査項目を薄まり具合で補正するための基準として使う</v>
       </c>
       <c r="E45" t="str">
-        <v>白血球は体に入ってきた細菌やウイルスと戦う免疫細胞です。感染症や炎症があると増え、逆に一部のお薬の副作用や骨髄の働きが落ちると減ることがあります。</v>
+        <v>この数値は、尿がどれくらい薄まっているかを確認するための基準として使われます。他の尿検査の結果（蛋白やアルブミンなど）をこの値で割って補正することで、水分摂取量による影響を減らして正確に評価できます。</v>
       </c>
       <c r="F45" t="str">
-        <v>感染症、炎症、ステロイド使用、喫煙、白血病などの血液疾患</v>
+        <v/>
       </c>
       <c r="G45" t="str">
-        <v>発熱や体の痛みなど感染症状がないか確認する</v>
+        <v/>
       </c>
       <c r="H45" t="str">
-        <v>ステロイド、G-CSF製剤、炭酸リチウム</v>
+        <v/>
       </c>
       <c r="I45" t="str">
-        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、メルカゾールなど薬剤性の無顆粒球症、再生不良性貧血、ウイルス感染</v>
+        <v>尿が薄い（水分摂取が多い、腎機能低下）状態</v>
       </c>
       <c r="J45" t="str">
-        <v>発熱、のどの痛みなど感染症状の初期サインがないか確認する。人混みを避け、手洗い・うがいを徹底するよう伝える</v>
+        <v/>
       </c>
       <c r="K45" t="str">
-        <v>抗がん剤、メルカゾール(無顆粒球症)、クロザピン(定期的な血球モニタリング必須)、サラゾスルファピリジン</v>
+        <v/>
       </c>
       <c r="L45" t="str">
-        <v>メルカゾール（チアマゾール）は無顆粒球症の重大な副作用があり、発熱・のどの痛みが出たらすぐ受診するよう指導する。抗がん剤・免疫抑制剤・抗てんかん薬（カルバマゼピンなど）使用中も定期的なモニタリングが必要</v>
+        <v>尿中アルブミン/Cr比、尿蛋白/Cr比など、他項目の補正計算に使われる。単独の高低に臨床的意味は乏しい</v>
       </c>
       <c r="M45" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>腎機能</v>
       </c>
       <c r="N45" t="str">
-        <v>白血球,WBC,好中球,感染症,白血病,無顆粒球症,骨髄抑制</v>
+        <v>尿CRE,尿クレアチニン,随時尿,補正,蛋白クレアチニン比</v>
       </c>
       <c r="O45" t="str">
         <v/>
@@ -2541,69 +2541,69 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>赤血球数</v>
+        <v>C－ペプチド（血中）</v>
       </c>
       <c r="B46" t="str">
-        <v>RBC</v>
+        <v>CPR</v>
       </c>
       <c r="C46" t="str">
-        <v>男性 435〜555万/μL、女性 386〜492万/μL程度（施設差あり）</v>
+        <v>空腹時 0.6〜3.0 ng/mL（施設差あり）</v>
       </c>
       <c r="D46" t="str">
-        <v>血液中で酸素を運ぶ細胞の数。ヘモグロビン・ヘマトクリットと合わせて貧血・多血症を評価する</v>
+        <v>自分の膵臓がどれくらいインスリンを作れているかを表す指標</v>
       </c>
       <c r="E46" t="str">
-        <v>赤血球は、肺で受け取った酸素を全身に運ぶ血液の細胞です。数が少ないと貧血、多いと多血症が疑われます。ヘモグロビンやヘマトクリットと合わせて総合的に評価します。</v>
+        <v>この検査は、ご自身の膵臓がどれくらいインスリンを作る力を持っているかを見るものです。数値が低いほど、体の中で作れるインスリンが少ないことを示します。</v>
       </c>
       <c r="F46" t="str">
-        <v>脱水、多血症（真性多血症、二次性多血症）、喫煙</v>
+        <v>インスリン抵抗性が強い状態（初期の2型糖尿病など）</v>
       </c>
       <c r="G46" t="str">
-        <v>脱水が疑われる場合はこまめな水分摂取を勧める（水分制限がある場合を除く）</v>
+        <v/>
       </c>
       <c r="H46" t="str">
         <v/>
       </c>
       <c r="I46" t="str">
-        <v>貧血（鉄欠乏性貧血、腎性貧血など）、出血</v>
+        <v>膵臓のインスリン分泌能低下（1型糖尿病、糖尿病の進行）</v>
       </c>
       <c r="J46" t="str">
-        <v>ヘモグロビンと同様に、出血や食事量低下がないか確認する</v>
+        <v/>
       </c>
       <c r="K46" t="str">
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>ヘモグロビン・ヘマトクリットと同じ方向に動くことが多い。赤血球数だけでなくMCV・MCH・MCHCと合わせて貧血のタイプ(小球性・正球性・大球性)を判断する</v>
+        <v>インスリン分泌能の評価に使われる。数値が低いほどインスリン治療の必要性が高いと判断される目安になる</v>
       </c>
       <c r="M46" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>糖尿病</v>
       </c>
       <c r="N46" t="str">
-        <v>赤血球,RBC,貧血,多血症</v>
+        <v>C-ペプチド,Cペプチド,CPR,C-peptide,血中CPR,インスリン分泌</v>
       </c>
       <c r="O46" t="str">
-        <v>食事と栄養 p.151-164（第2部 貧血）</v>
+        <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ヘモグロビン濃度</v>
+        <v>C－ペプチドインデックス</v>
       </c>
       <c r="B47" t="str">
-        <v>Hb</v>
+        <v>CPI</v>
       </c>
       <c r="C47" t="str">
-        <v>男性 13.5〜17.5 g/dL、女性 11.5〜15.0 g/dL</v>
+        <v>1.2以上が目安(施設・測定条件により異なる)</v>
       </c>
       <c r="D47" t="str">
-        <v>血液の中で酸素を運ぶ役割をしている。この値が低い状態が貧血。</v>
+        <v>血糖値に対してどれくらいインスリンを分泌できているかを表す指標。低いほどインスリン治療の必要性が高い</v>
       </c>
       <c r="E47" t="str">
-        <v>ヘモグロビンは、血液の中で酸素を全身に運ぶ役割をしている赤い色素です。この値が低い状態が貧血で、体がだるくなったり、階段で息切れしやすくなったりします。</v>
+        <v>これは、血糖値の高さに対して、体がどれくらいインスリンを作れているかを見る指標です。数値が低いほど、自分の膵臓だけでは血糖値に見合うインスリンを十分に作れていない可能性が高く、インスリン治療が必要かどうかの判断材料になります。</v>
       </c>
       <c r="F47" t="str">
-        <v/>
+        <v>通常、臨床的意義は乏しい</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2612,116 +2612,116 @@
         <v/>
       </c>
       <c r="I47" t="str">
-        <v>鉄欠乏性貧血、出血、腎性貧血、骨髄の造血機能低下</v>
+        <v>内因性インスリン分泌能の低下(1.2未満でインスリン治療の適応を検討する目安、0.8未満はインスリン療法が強く推奨される目安)</v>
       </c>
       <c r="J47" t="str">
-        <v>鉄分の多い食品(レバー・赤身肉・魚・ほうれん草など)を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える。鉄剤は数値が正常化した後も体内に鉄を貯蔵するため2〜3か月程度は継続が必要なことを説明する</v>
+        <v>インスリン治療の必要性について医師からどのように説明を受けているか確認する</v>
       </c>
       <c r="K47" t="str">
-        <v>NSAIDs・抗凝固薬・抗血小板薬(消化管出血のリスク)、抗がん剤、ST合剤</v>
+        <v/>
       </c>
       <c r="L47" t="str">
-        <v>原因（出血・食事量低下など）の確認が重要。腎機能低下がある場合は鉄不足以外が原因のこともある。鉄剤はヘモグロビンが正常化した後も2〜3か月程度は継続することが多い（鉄の貯蔵分を補うため。途中でやめると再び貧血になりやすい）</v>
+        <v>CPI＝血中Cペプチド(ng/mL)÷血糖値(mg/dL)×100 で算出する。空腹時に測定するのが基本で、境界値付近では食事負荷の影響を受けるため、複数回の評価や随時尿中CPRとあわせて判断することもある</v>
       </c>
       <c r="M47" t="str">
-        <v>鉄欠乏性貧血,抗血小板療法,抗凝固療法（心房細動・血栓症）</v>
+        <v>糖尿病</v>
       </c>
       <c r="N47" t="str">
-        <v>ヘモグロビン,Hb,貧血,鉄剤,鉄欠乏性貧血</v>
+        <v>CPI,Cペプチドインデックス,C-ペプチドインデックス,インスリン分泌能,インスリン治療</v>
       </c>
       <c r="O47" t="str">
-        <v>食事と栄養 p.151-164（第2部 貧血）</v>
+        <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ヘマトクリット値</v>
+        <v>白血球数（WBC）</v>
       </c>
       <c r="B48" t="str">
-        <v>Ht,Hct</v>
+        <v>WBC</v>
       </c>
       <c r="C48" t="str">
-        <v>男性 40〜50%、女性 35〜45%</v>
+        <v>3,300〜8,600 /μL程度（施設差あり）</v>
       </c>
       <c r="D48" t="str">
-        <v>血液全体のうち赤血球が占める体積の割合。貧血・脱水の指標</v>
+        <v>体を細菌やウイルスから守る免疫細胞の数で、感染や炎症、薬剤の影響を反映する</v>
       </c>
       <c r="E48" t="str">
-        <v>ヘマトクリットは、血液全体のうち赤血球が占める割合を表す数値です。この値が低いと貧血、高いと脱水や血液が濃くなっている状態が疑われます。</v>
+        <v>白血球は体に入ってきた細菌やウイルスと戦う免疫細胞です。感染症や炎症があると増え、逆に一部のお薬の副作用や骨髄の働きが落ちると減ることがあります。</v>
       </c>
       <c r="F48" t="str">
-        <v>脱水、多血症（真性多血症、二次性多血症）、喫煙</v>
+        <v>感染症、炎症、ステロイド使用、喫煙、白血病などの血液疾患</v>
       </c>
       <c r="G48" t="str">
-        <v>脱水が疑われる場合はこまめな水分摂取を勧める（水分制限がある場合を除く）</v>
+        <v>発熱や体の痛みなど感染症状がないか確認する</v>
       </c>
       <c r="H48" t="str">
-        <v/>
+        <v>ステロイド、G-CSF製剤、炭酸リチウム</v>
       </c>
       <c r="I48" t="str">
-        <v>貧血（鉄欠乏性貧血、腎性貧血など）、出血</v>
+        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、メルカゾールなど薬剤性の無顆粒球症、再生不良性貧血、ウイルス感染</v>
       </c>
       <c r="J48" t="str">
-        <v>ヘモグロビンと同様に、出血や食事量低下がないか確認する</v>
+        <v>発熱、のどの痛みなど感染症状の初期サインがないか確認する。人混みを避け、手洗い・うがいを徹底するよう伝える</v>
       </c>
       <c r="K48" t="str">
-        <v/>
+        <v>抗がん剤、メルカゾール(無顆粒球症)、クロザピン(定期的な血球モニタリング必須)、サラゾスルファピリジン</v>
       </c>
       <c r="L48" t="str">
-        <v>ヘモグロビン・赤血球数と合わせて評価する。3つの値は同じ方向に動くことが多く、脱水があると貧血が見かけ上隠れることがある</v>
+        <v>メルカゾール（チアマゾール）は無顆粒球症の重大な副作用があり、発熱・のどの痛みが出たらすぐ受診するよう指導する。抗がん剤・免疫抑制剤・抗てんかん薬（カルバマゼピンなど）使用中も定期的なモニタリングが必要</v>
       </c>
       <c r="M48" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N48" t="str">
-        <v>ヘマトクリット,Ht,Hct,貧血,脱水,多血症</v>
+        <v>白血球,WBC,好中球,感染症,白血病,無顆粒球症,骨髄抑制</v>
       </c>
       <c r="O48" t="str">
-        <v>食事と栄養 p.151-164（第2部 貧血）</v>
+        <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>MCV</v>
+        <v>赤血球数</v>
       </c>
       <c r="B49" t="str">
-        <v>MCV</v>
+        <v>RBC</v>
       </c>
       <c r="C49" t="str">
-        <v>79〜100 fL</v>
+        <v>男性 435〜555万/μL、女性 386〜492万/μL程度（施設差あり）</v>
       </c>
       <c r="D49" t="str">
-        <v>赤血球1個の大きさ</v>
+        <v>血液中で酸素を運ぶ細胞の数。ヘモグロビン・ヘマトクリットと合わせて貧血・多血症を評価する</v>
       </c>
       <c r="E49" t="str">
-        <v>MCVは赤血球1個あたりの大きさを表す数値です。貧血があるとき、この数値で「小さい貧血」か「大きい貧血」かを見分けることができ、原因を絞り込む手がかりになります。</v>
+        <v>赤血球は、肺で受け取った酸素を全身に運ぶ血液の細胞です。数が少ないと貧血、多いと多血症が疑われます。ヘモグロビンやヘマトクリットと合わせて総合的に評価します。</v>
       </c>
       <c r="F49" t="str">
-        <v/>
+        <v>脱水、多血症（真性多血症、二次性多血症）、喫煙</v>
       </c>
       <c r="G49" t="str">
-        <v/>
+        <v>脱水が疑われる場合はこまめな水分摂取を勧める（水分制限がある場合を除く）</v>
       </c>
       <c r="H49" t="str">
         <v/>
       </c>
       <c r="I49" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>貧血（鉄欠乏性貧血、腎性貧血など）、出血</v>
       </c>
       <c r="J49" t="str">
-        <v>鉄分の多い食品(レバー・赤身肉・魚・ほうれん草など)と、吸収を助けるビタミンC(柑橘類・芋類等)を一緒に摂るよう伝える</v>
+        <v>ヘモグロビンと同様に、出血や食事量低下がないか確認する</v>
       </c>
       <c r="K49" t="str">
         <v/>
       </c>
       <c r="L49" t="str">
-        <v/>
+        <v>ヘモグロビン・ヘマトクリットと同じ方向に動くことが多い。赤血球数だけでなくMCV・MCH・MCHCと合わせて貧血のタイプ(小球性・正球性・大球性)を判断する</v>
       </c>
       <c r="M49" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
       <c r="N49" t="str">
-        <v>MCV,赤血球指数,貧血</v>
+        <v>赤血球,RBC,貧血,多血症</v>
       </c>
       <c r="O49" t="str">
         <v>食事と栄養 p.151-164（第2部 貧血）</v>
@@ -2729,19 +2729,19 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>MCH</v>
+        <v>ヘモグロビン濃度</v>
       </c>
       <c r="B50" t="str">
-        <v>MCH</v>
+        <v>Hb</v>
       </c>
       <c r="C50" t="str">
-        <v>26.3〜34.3 pg</v>
+        <v>男性 13.5〜17.5 g/dL、女性 11.5〜15.0 g/dL</v>
       </c>
       <c r="D50" t="str">
-        <v>赤血球1個に含まれるヘモグロビン量</v>
+        <v>血液の中で酸素を運ぶ役割をしている。この値が低い状態が貧血。</v>
       </c>
       <c r="E50" t="str">
-        <v>MCHは赤血球1個の中に含まれるヘモグロビン（酸素を運ぶ色素）の量を表す数値です。MCVと同じく、貧血の種類を見分けるのに使われます。</v>
+        <v>ヘモグロビンは、血液の中で酸素を全身に運ぶ役割をしている赤い色素です。この値が低い状態が貧血で、体がだるくなったり、階段で息切れしやすくなったりします。</v>
       </c>
       <c r="F50" t="str">
         <v/>
@@ -2753,22 +2753,22 @@
         <v/>
       </c>
       <c r="I50" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>鉄欠乏性貧血、出血、腎性貧血、骨髄の造血機能低下</v>
       </c>
       <c r="J50" t="str">
-        <v>鉄分の多い食品(レバー・赤身肉・魚・ほうれん草など)と、吸収を助けるビタミンC(柑橘類・芋類等)を一緒に摂るよう伝える</v>
+        <v>鉄分の多い食品(レバー・赤身肉・魚・ほうれん草など)を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える。鉄剤は数値が正常化した後も体内に鉄を貯蔵するため2〜3か月程度は継続が必要なことを説明する</v>
       </c>
       <c r="K50" t="str">
-        <v/>
+        <v>NSAIDs・抗凝固薬・抗血小板薬(消化管出血のリスク)、抗がん剤、ST合剤</v>
       </c>
       <c r="L50" t="str">
-        <v/>
+        <v>原因（出血・食事量低下など）の確認が重要。腎機能低下がある場合は鉄不足以外が原因のこともある。鉄剤はヘモグロビンが正常化した後も2〜3か月程度は継続することが多い（鉄の貯蔵分を補うため。途中でやめると再び貧血になりやすい）</v>
       </c>
       <c r="M50" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>鉄欠乏性貧血,抗血小板療法,抗凝固療法（心房細動・血栓症）</v>
       </c>
       <c r="N50" t="str">
-        <v>MCH,赤血球指数,貧血</v>
+        <v>ヘモグロビン,Hb,貧血,鉄剤,鉄欠乏性貧血</v>
       </c>
       <c r="O50" t="str">
         <v>食事と栄養 p.151-164（第2部 貧血）</v>
@@ -2776,46 +2776,46 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>MCHC</v>
+        <v>ヘマトクリット値</v>
       </c>
       <c r="B51" t="str">
-        <v>MCHC</v>
+        <v>Ht,Hct</v>
       </c>
       <c r="C51" t="str">
-        <v>31.6〜36.6 %</v>
+        <v>男性 40〜50%、女性 35〜45%</v>
       </c>
       <c r="D51" t="str">
-        <v>単位容積あたりの赤血球に含まれるヘモグロビン濃度</v>
+        <v>血液全体のうち赤血球が占める体積の割合。貧血・脱水の指標</v>
       </c>
       <c r="E51" t="str">
-        <v>MCHCは、赤血球の中にヘモグロビンがどれくらい濃く詰まっているかを表す数値です。鉄が不足すると、この濃度も薄くなる傾向があります。</v>
+        <v>ヘマトクリットは、血液全体のうち赤血球が占める割合を表す数値です。この値が低いと貧血、高いと脱水や血液が濃くなっている状態が疑われます。</v>
       </c>
       <c r="F51" t="str">
-        <v/>
+        <v>脱水、多血症（真性多血症、二次性多血症）、喫煙</v>
       </c>
       <c r="G51" t="str">
-        <v/>
+        <v>脱水が疑われる場合はこまめな水分摂取を勧める（水分制限がある場合を除く）</v>
       </c>
       <c r="H51" t="str">
         <v/>
       </c>
       <c r="I51" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>貧血（鉄欠乏性貧血、腎性貧血など）、出血</v>
       </c>
       <c r="J51" t="str">
-        <v>鉄分の多い食品(レバー・赤身肉・魚・ほうれん草など)と、吸収を助けるビタミンC(柑橘類・芋類等)を一緒に摂るよう伝える</v>
+        <v>ヘモグロビンと同様に、出血や食事量低下がないか確認する</v>
       </c>
       <c r="K51" t="str">
         <v/>
       </c>
       <c r="L51" t="str">
-        <v/>
+        <v>ヘモグロビン・赤血球数と合わせて評価する。3つの値は同じ方向に動くことが多く、脱水があると貧血が見かけ上隠れることがある</v>
       </c>
       <c r="M51" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
       <c r="N51" t="str">
-        <v>MCHC,赤血球指数,貧血</v>
+        <v>ヘマトクリット,Ht,Hct,貧血,脱水,多血症</v>
       </c>
       <c r="O51" t="str">
         <v>食事と栄養 p.151-164（第2部 貧血）</v>
@@ -2823,69 +2823,69 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>血小板数</v>
+        <v>MCV</v>
       </c>
       <c r="B52" t="str">
-        <v>Plt</v>
+        <v>MCV</v>
       </c>
       <c r="C52" t="str">
-        <v>15.0〜35.0万/μL程度（施設差あり）</v>
+        <v>79〜100 fL</v>
       </c>
       <c r="D52" t="str">
-        <v>出血を止める働きをする血液成分で、少なすぎると出血しやすくなる</v>
+        <v>赤血球1個の大きさ</v>
       </c>
       <c r="E52" t="str">
-        <v>血小板は、血管が傷ついたときに集まって血を止める役割をする血液の成分です。数が少ないとあざができやすくなったり、出血が止まりにくくなったりします。抗血小板薬や抗がん剤を使っている方では、定期的にチェックすることが大切です。</v>
+        <v>MCVは赤血球1個あたりの大きさを表す数値です。貧血があるとき、この数値で「小さい貧血」か「大きい貧血」かを見分けることができ、原因を絞り込む手がかりになります。</v>
       </c>
       <c r="F52" t="str">
-        <v>炎症性疾患、鉄欠乏性貧血、脾摘後、骨髄増殖性疾患</v>
+        <v/>
       </c>
       <c r="G52" t="str">
-        <v>出血傾向はなく経過観察でよいことが多いが、片側の腫れ・しびれなど血栓症状がないかも念のため確認する</v>
+        <v/>
       </c>
       <c r="H52" t="str">
         <v/>
       </c>
       <c r="I52" t="str">
-        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、肝硬変・脾機能亢進、再生不良性貧血、抗てんかん薬（バルプロ酸など）の副作用、ITP（特発性血小板減少性紫斑病）</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="J52" t="str">
-        <v>あざができやすい、歯ぐきや鼻からの出血が増えていないか確認する。強い運動や転倒によるけがに注意するよう伝え、歯みがきは柔らかめのブラシを勧める</v>
+        <v>鉄分の多い食品(レバー・赤身肉・魚・ほうれん草など)と、吸収を助けるビタミンC(柑橘類・芋類等)を一緒に摂るよう伝える</v>
       </c>
       <c r="K52" t="str">
-        <v>ヘパリン(HIT: ヘパリン起因性血小板減少症)、バルプロ酸、抗がん剤、リネゾリド</v>
+        <v/>
       </c>
       <c r="L52" t="str">
-        <v>抗血小板薬・抗凝固薬使用中に血小板減少があると出血リスクがさらに高まる。抗がん剤・バルプロ酸・カルバマゼピンなど骨髄抑制のリスクがある薬剤使用中は定期採血の実施状況を確認する</v>
+        <v/>
       </c>
       <c r="M52" t="str">
-        <v>てんかん,抗血小板療法</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="N52" t="str">
-        <v>血小板,Plt,platelet,出血,あざ,紫斑,骨髄抑制</v>
+        <v>MCV,赤血球指数,貧血</v>
       </c>
       <c r="O52" t="str">
-        <v/>
+        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>RDW-SD</v>
+        <v>MCH</v>
       </c>
       <c r="B53" t="str">
-        <v>RDW-SD</v>
+        <v>MCH</v>
       </c>
       <c r="C53" t="str">
-        <v>39〜46 fL程度（施設差あり）</v>
+        <v>26.3〜34.3 pg</v>
       </c>
       <c r="D53" t="str">
-        <v>赤血球の大きさのばらつきを表す指標(絶対値)。鉄欠乏性貧血などの初期変化を捉えやすい</v>
+        <v>赤血球1個に含まれるヘモグロビン量</v>
       </c>
       <c r="E53" t="str">
-        <v>RDW-SDは、赤血球の大きさがどれくらいバラバラになっているかを表す数値です。貧血の原因を調べる際、鉄が足りなくなり始めた早い段階での変化を捉えるのに役立ちます。</v>
+        <v>MCHは赤血球1個の中に含まれるヘモグロビン（酸素を運ぶ色素）の量を表す数値です。MCVと同じく、貧血の種類を見分けるのに使われます。</v>
       </c>
       <c r="F53" t="str">
-        <v>鉄欠乏性貧血の初期、混合性貧血（複数の原因が重なっている状態）、赤血球産生の乱れ</v>
+        <v/>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2894,22 +2894,22 @@
         <v/>
       </c>
       <c r="I53" t="str">
-        <v/>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="J53" t="str">
-        <v/>
+        <v>鉄分の多い食品(レバー・赤身肉・魚・ほうれん草など)と、吸収を助けるビタミンC(柑橘類・芋類等)を一緒に摂るよう伝える</v>
       </c>
       <c r="K53" t="str">
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>MCVが正常範囲でもRDWが上昇している場合、鉄欠乏の初期段階を示唆することがある。MCV・MCHと合わせて評価する</v>
+        <v/>
       </c>
       <c r="M53" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
       <c r="N53" t="str">
-        <v>RDW-SD,赤血球分布幅,貧血,鉄欠乏</v>
+        <v>MCH,赤血球指数,貧血</v>
       </c>
       <c r="O53" t="str">
         <v>食事と栄養 p.151-164（第2部 貧血）</v>
@@ -2917,22 +2917,22 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>RDW-CV</v>
+        <v>MCHC</v>
       </c>
       <c r="B54" t="str">
-        <v>RDW-CV</v>
+        <v>MCHC</v>
       </c>
       <c r="C54" t="str">
-        <v>11.5〜14.5%程度（施設差あり）</v>
+        <v>31.6〜36.6 %</v>
       </c>
       <c r="D54" t="str">
-        <v>赤血球の大きさのばらつきを割合(%)で表した指標</v>
+        <v>単位容積あたりの赤血球に含まれるヘモグロビン濃度</v>
       </c>
       <c r="E54" t="str">
-        <v>RDW-CVもRDW-SDと同じく、赤血球の大きさのばらつきを表す数値ですが、こちらは割合(%)で示されます。貧血のタイプを見分ける手がかりになります。</v>
+        <v>MCHCは、赤血球の中にヘモグロビンがどれくらい濃く詰まっているかを表す数値です。鉄が不足すると、この濃度も薄くなる傾向があります。</v>
       </c>
       <c r="F54" t="str">
-        <v>鉄欠乏性貧血、ビタミンB12・葉酸欠乏性貧血、混合性貧血</v>
+        <v/>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2941,22 +2941,22 @@
         <v/>
       </c>
       <c r="I54" t="str">
-        <v/>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="J54" t="str">
-        <v/>
+        <v>鉄分の多い食品(レバー・赤身肉・魚・ほうれん草など)と、吸収を助けるビタミンC(柑橘類・芋類等)を一緒に摂るよう伝える</v>
       </c>
       <c r="K54" t="str">
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>RDW-SDと同様の意味を持つ指標。MCVが小さくRDWが高ければ鉄欠乏性貧血、MCVが大きくRDWが高ければビタミンB12・葉酸欠乏を疑う手がかりになる</v>
+        <v/>
       </c>
       <c r="M54" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
       <c r="N54" t="str">
-        <v>RDW-CV,赤血球分布幅,貧血,ビタミンB12,葉酸</v>
+        <v>MCHC,赤血球指数,貧血</v>
       </c>
       <c r="O54" t="str">
         <v>食事と栄養 p.151-164（第2部 貧血）</v>
@@ -2964,46 +2964,46 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>好中球実数値</v>
+        <v>血小板数</v>
       </c>
       <c r="B55" t="str">
-        <v>Neutro#,ANC</v>
+        <v>Plt</v>
       </c>
       <c r="C55" t="str">
-        <v>2,000〜7,500 /μL程度（施設差あり、白血球数×好中球%で算出）</v>
+        <v>15.0〜35.0万/μL程度（施設差あり）</v>
       </c>
       <c r="D55" t="str">
-        <v>好中球の絶対数。感染症リスクを判断する上で割合(%)より重要な指標</v>
+        <v>出血を止める働きをする血液成分で、少なすぎると出血しやすくなる</v>
       </c>
       <c r="E55" t="str">
-        <v>これは好中球の実際の数を表す数値です。割合(%)だけでなく、実際の数がどれくらいあるかを見ることで、感染症にかかりやすい状態かどうかをより正確に判断できます。</v>
+        <v>血小板は、血管が傷ついたときに集まって血を止める役割をする血液の成分です。数が少ないとあざができやすくなったり、出血が止まりにくくなったりします。抗血小板薬や抗がん剤を使っている方では、定期的にチェックすることが大切です。</v>
       </c>
       <c r="F55" t="str">
-        <v>細菌感染症、炎症、ステロイド使用</v>
+        <v>炎症性疾患、鉄欠乏性貧血、脾摘後、骨髄増殖性疾患</v>
       </c>
       <c r="G55" t="str">
-        <v/>
+        <v>出血傾向はなく経過観察でよいことが多いが、片側の腫れ・しびれなど血栓症状がないかも念のため確認する</v>
       </c>
       <c r="H55" t="str">
         <v/>
       </c>
       <c r="I55" t="str">
-        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、メルカゾールなど薬剤性の無顆粒球症（1,000/μL未満で好中球減少症、500/μL未満で重症感染リスクが著しく上昇）</v>
+        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、肝硬変・脾機能亢進、再生不良性貧血、抗てんかん薬（バルプロ酸など）の副作用、ITP（特発性血小板減少性紫斑病）</v>
       </c>
       <c r="J55" t="str">
-        <v>発熱、のどの痛みなど感染症状の初期サインがないか確認する。人混みを避け、手洗い・うがいを徹底するよう伝える</v>
+        <v>あざができやすい、歯ぐきや鼻からの出血が増えていないか確認する。強い運動や転倒によるけがに注意するよう伝え、歯みがきは柔らかめのブラシを勧める</v>
       </c>
       <c r="K55" t="str">
-        <v>抗がん剤、メルカゾール(無顆粒球症)、クロザピン、サラゾスルファピリジン</v>
+        <v>ヘパリン(HIT: ヘパリン起因性血小板減少症)、バルプロ酸、抗がん剤、リネゾリド</v>
       </c>
       <c r="L55" t="str">
-        <v>抗がん剤・メルカゾール・カルバマゼピンなど骨髄抑制のリスクがある薬剤使用中は特に重視すべき数値。500/μL未満は発熱性好中球減少症のリスクが高く緊急性が高い</v>
+        <v>抗血小板薬・抗凝固薬使用中に血小板減少があると出血リスクがさらに高まる。抗がん剤・バルプロ酸・カルバマゼピンなど骨髄抑制のリスクがある薬剤使用中は定期採血の実施状況を確認する</v>
       </c>
       <c r="M55" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>てんかん,抗血小板療法</v>
       </c>
       <c r="N55" t="str">
-        <v>好中球実数値,好中球数,ANC,無顆粒球症,発熱性好中球減少症</v>
+        <v>血小板,Plt,platelet,出血,あざ,紫斑,骨髄抑制</v>
       </c>
       <c r="O55" t="str">
         <v/>
@@ -3011,28 +3011,28 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>好酸球実数値</v>
+        <v>RDW-SD</v>
       </c>
       <c r="B56" t="str">
-        <v>Eosino#</v>
+        <v>RDW-SD</v>
       </c>
       <c r="C56" t="str">
-        <v>100〜500 /μL程度（施設差あり）</v>
+        <v>39〜46 fL程度（施設差あり）</v>
       </c>
       <c r="D56" t="str">
-        <v>好酸球の絶対数。アレルギーや薬剤反応の程度をより正確に評価できる</v>
+        <v>赤血球の大きさのばらつきを表す指標(絶対値)。鉄欠乏性貧血などの初期変化を捉えやすい</v>
       </c>
       <c r="E56" t="str">
-        <v>これは好酸球の実際の数を表す数値です。割合(%)だけでなく実数を見ることで、アレルギー反応の強さをより正確に把握できます。</v>
+        <v>RDW-SDは、赤血球の大きさがどれくらいバラバラになっているかを表す数値です。貧血の原因を調べる際、鉄が足りなくなり始めた早い段階での変化を捉えるのに役立ちます。</v>
       </c>
       <c r="F56" t="str">
-        <v>アレルギー性疾患、薬剤アレルギー、寄生虫感染</v>
+        <v>鉄欠乏性貧血の初期、混合性貧血（複数の原因が重なっている状態）、赤血球産生の乱れ</v>
       </c>
       <c r="G56" t="str">
-        <v>新しく始めた薬がないか確認する</v>
+        <v/>
       </c>
       <c r="H56" t="str">
-        <v>薬剤性好酸球増多(抗菌薬・NSAIDs・抗てんかん薬など)。発熱や皮疹を伴う場合はDRESS症候群にも注意</v>
+        <v/>
       </c>
       <c r="I56" t="str">
         <v/>
@@ -3044,36 +3044,36 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>薬剤性過敏症症候群(DIHS)などでは著明な好酸球増多を認めることがあり、原因薬剤の特定に役立つ</v>
+        <v>MCVが正常範囲でもRDWが上昇している場合、鉄欠乏の初期段階を示唆することがある。MCV・MCHと合わせて評価する</v>
       </c>
       <c r="M56" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="N56" t="str">
-        <v>好酸球実数値,好酸球数,アレルギー,DIHS</v>
+        <v>RDW-SD,赤血球分布幅,貧血,鉄欠乏</v>
       </c>
       <c r="O56" t="str">
-        <v/>
+        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>好塩基球実数値</v>
+        <v>RDW-CV</v>
       </c>
       <c r="B57" t="str">
-        <v>Baso#</v>
+        <v>RDW-CV</v>
       </c>
       <c r="C57" t="str">
-        <v>0〜100 /μL程度（施設差あり）</v>
+        <v>11.5〜14.5%程度（施設差あり）</v>
       </c>
       <c r="D57" t="str">
-        <v>好塩基球の絶対数</v>
+        <v>赤血球の大きさのばらつきを割合(%)で表した指標</v>
       </c>
       <c r="E57" t="str">
-        <v>これは好塩基球の実際の数を表す数値です。数がとても少ない種類の血球なので、通常は大きな変動を示すことは多くありません。</v>
+        <v>RDW-CVもRDW-SDと同じく、赤血球の大きさのばらつきを表す数値ですが、こちらは割合(%)で示されます。貧血のタイプを見分ける手がかりになります。</v>
       </c>
       <c r="F57" t="str">
-        <v>慢性骨髄性白血病などの血液疾患、アレルギー性疾患</v>
+        <v>鉄欠乏性貧血、ビタミンB12・葉酸欠乏性貧血、混合性貧血</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -3091,36 +3091,36 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>単独での臨床的意義は乏しく、他の血球指標（白血球分画全体）と合わせて評価する</v>
+        <v>RDW-SDと同様の意味を持つ指標。MCVが小さくRDWが高ければ鉄欠乏性貧血、MCVが大きくRDWが高ければビタミンB12・葉酸欠乏を疑う手がかりになる</v>
       </c>
       <c r="M57" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="N57" t="str">
-        <v>好塩基球実数値,好塩基球数</v>
+        <v>RDW-CV,赤血球分布幅,貧血,ビタミンB12,葉酸</v>
       </c>
       <c r="O57" t="str">
-        <v/>
+        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>リンパ球実数値</v>
+        <v>好中球実数値</v>
       </c>
       <c r="B58" t="str">
-        <v>Lympho#,ALC</v>
+        <v>Neutro#,ANC</v>
       </c>
       <c r="C58" t="str">
-        <v>1,000〜3,600 /μL程度（施設差あり）</v>
+        <v>2,000〜7,500 /μL程度（施設差あり、白血球数×好中球%で算出）</v>
       </c>
       <c r="D58" t="str">
-        <v>リンパ球の絶対数。免疫力の目安として使われる</v>
+        <v>好中球の絶対数。感染症リスクを判断する上で割合(%)より重要な指標</v>
       </c>
       <c r="E58" t="str">
-        <v>これはリンパ球の実際の数を表す数値です。免疫力の目安の一つとして使われ、抗がん剤や免疫抑制剤の副作用モニタリングにも用いられます。</v>
+        <v>これは好中球の実際の数を表す数値です。割合(%)だけでなく、実際の数がどれくらいあるかを見ることで、感染症にかかりやすい状態かどうかをより正確に判断できます。</v>
       </c>
       <c r="F58" t="str">
-        <v>ウイルス感染症、リンパ性白血病などの血液疾患</v>
+        <v>細菌感染症、炎症、ステロイド使用</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -3129,22 +3129,22 @@
         <v/>
       </c>
       <c r="I58" t="str">
-        <v>抗がん剤・免疫抑制剤・ステロイドの使用、強いストレス、AIDSなどの免疫不全</v>
+        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、メルカゾールなど薬剤性の無顆粒球症（1,000/μL未満で好中球減少症、500/μL未満で重症感染リスクが著しく上昇）</v>
       </c>
       <c r="J58" t="str">
-        <v>感染予防（手洗い・うがい、人混みを避ける）を意識するよう伝える</v>
+        <v>発熱、のどの痛みなど感染症状の初期サインがないか確認する。人混みを避け、手洗い・うがいを徹底するよう伝える</v>
       </c>
       <c r="K58" t="str">
-        <v/>
+        <v>抗がん剤、メルカゾール(無顆粒球症)、クロザピン、サラゾスルファピリジン</v>
       </c>
       <c r="L58" t="str">
-        <v>免疫抑制剤・抗がん剤治療中のモニタリング指標としても使われる。著明な低下時は日和見感染のリスクが高まる</v>
+        <v>抗がん剤・メルカゾール・カルバマゼピンなど骨髄抑制のリスクがある薬剤使用中は特に重視すべき数値。500/μL未満は発熱性好中球減少症のリスクが高く緊急性が高い</v>
       </c>
       <c r="M58" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N58" t="str">
-        <v>リンパ球実数値,リンパ球数,ALC,免疫抑制剤,日和見感染</v>
+        <v>好中球実数値,好中球数,ANC,無顆粒球症,発熱性好中球減少症</v>
       </c>
       <c r="O58" t="str">
         <v/>
@@ -3152,28 +3152,28 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>単球実数値</v>
+        <v>好酸球実数値</v>
       </c>
       <c r="B59" t="str">
-        <v>Mono#</v>
+        <v>Eosino#</v>
       </c>
       <c r="C59" t="str">
-        <v>200〜600 /μL程度（施設差あり）</v>
+        <v>100〜500 /μL程度（施設差あり）</v>
       </c>
       <c r="D59" t="str">
-        <v>単球の絶対数</v>
+        <v>好酸球の絶対数。アレルギーや薬剤反応の程度をより正確に評価できる</v>
       </c>
       <c r="E59" t="str">
-        <v>これは単球の実際の数を表す数値です。慢性的な炎症や感染症の状態を把握する材料の一つになります。</v>
+        <v>これは好酸球の実際の数を表す数値です。割合(%)だけでなく実数を見ることで、アレルギー反応の強さをより正確に把握できます。</v>
       </c>
       <c r="F59" t="str">
-        <v>慢性感染症、炎症性疾患、血液疾患</v>
+        <v>アレルギー性疾患、薬剤アレルギー、寄生虫感染</v>
       </c>
       <c r="G59" t="str">
-        <v/>
+        <v>新しく始めた薬がないか確認する</v>
       </c>
       <c r="H59" t="str">
-        <v/>
+        <v>薬剤性好酸球増多(抗菌薬・NSAIDs・抗てんかん薬など)。発熱や皮疹を伴う場合はDRESS症候群にも注意</v>
       </c>
       <c r="I59" t="str">
         <v/>
@@ -3185,13 +3185,13 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>単独での臨床的意義は乏しく、他の血球指標と合わせて評価する</v>
+        <v>薬剤性過敏症症候群(DIHS)などでは著明な好酸球増多を認めることがあり、原因薬剤の特定に役立つ</v>
       </c>
       <c r="M59" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N59" t="str">
-        <v>単球実数値,単球数</v>
+        <v>好酸球実数値,好酸球数,アレルギー,DIHS</v>
       </c>
       <c r="O59" t="str">
         <v/>
@@ -3199,46 +3199,46 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>好中球</v>
+        <v>好塩基球実数値</v>
       </c>
       <c r="B60" t="str">
-        <v>Neutro,Neut%</v>
+        <v>Baso#</v>
       </c>
       <c r="C60" t="str">
-        <v>40〜75%程度（施設差あり）</v>
+        <v>0〜100 /μL程度（施設差あり）</v>
       </c>
       <c r="D60" t="str">
-        <v>白血球の中で最も多くを占め、細菌感染と戦う主力の免疫細胞の割合</v>
+        <v>好塩基球の絶対数</v>
       </c>
       <c r="E60" t="str">
-        <v>好中球は、白血球の中で最も数が多く、細菌が体に入ってきたときに真っ先に戦ってくれる免疫細胞です。感染症や炎症があると増え、逆に薬の副作用などで減ることがあります。</v>
+        <v>これは好塩基球の実際の数を表す数値です。数がとても少ない種類の血球なので、通常は大きな変動を示すことは多くありません。</v>
       </c>
       <c r="F60" t="str">
-        <v>細菌感染症、炎症、ストレス、ステロイド使用</v>
+        <v>慢性骨髄性白血病などの血液疾患、アレルギー性疾患</v>
       </c>
       <c r="G60" t="str">
-        <v>発熱や炎症症状がないか確認する</v>
+        <v/>
       </c>
       <c r="H60" t="str">
         <v/>
       </c>
       <c r="I60" t="str">
-        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、ウイルス感染、メルカゾールなど薬剤性の無顆粒球症</v>
+        <v/>
       </c>
       <c r="J60" t="str">
-        <v>発熱やのどの痛みなど感染症状の初期サインがないか確認する</v>
+        <v/>
       </c>
       <c r="K60" t="str">
-        <v>抗がん剤、メルカゾール(無顆粒球症)、クロザピン、サラゾスルファピリジン</v>
+        <v/>
       </c>
       <c r="L60" t="str">
-        <v>好中球の絶対数（好中球実数値）が500/μL未満になると重篤な感染症のリスクが高まる。割合(%)だけでなく実数値も合わせて確認する</v>
+        <v>単独での臨床的意義は乏しく、他の血球指標（白血球分画全体）と合わせて評価する</v>
       </c>
       <c r="M60" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N60" t="str">
-        <v>好中球,Neutro,Neut,感染症,無顆粒球症</v>
+        <v>好塩基球実数値,好塩基球数</v>
       </c>
       <c r="O60" t="str">
         <v/>
@@ -3246,46 +3246,46 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>好酸球</v>
+        <v>リンパ球実数値</v>
       </c>
       <c r="B61" t="str">
-        <v>Eosino,Eos%</v>
+        <v>Lympho#,ALC</v>
       </c>
       <c r="C61" t="str">
-        <v>1〜5%程度（施設差あり）</v>
+        <v>1,000〜3,600 /μL程度（施設差あり）</v>
       </c>
       <c r="D61" t="str">
-        <v>アレルギー反応や寄生虫感染に関わる白血球の一種の割合</v>
+        <v>リンパ球の絶対数。免疫力の目安として使われる</v>
       </c>
       <c r="E61" t="str">
-        <v>好酸球は、アレルギー反応や寄生虫感染と関係が深い免疫細胞です。アレルギー性の病気や薬の副作用（薬疹など）で増えることがあります。</v>
+        <v>これはリンパ球の実際の数を表す数値です。免疫力の目安の一つとして使われ、抗がん剤や免疫抑制剤の副作用モニタリングにも用いられます。</v>
       </c>
       <c r="F61" t="str">
-        <v>アレルギー性疾患（気管支喘息、アトピー性皮膚炎など）、薬剤アレルギー、寄生虫感染</v>
+        <v>ウイルス感染症、リンパ性白血病などの血液疾患</v>
       </c>
       <c r="G61" t="str">
-        <v>新しく始めた薬がないか確認する。皮疹やかゆみなどアレルギー症状の有無を確認する</v>
+        <v/>
       </c>
       <c r="H61" t="str">
-        <v>薬剤性好酸球増多(抗菌薬・NSAIDs・抗てんかん薬など)。発熱や皮疹を伴う場合はDRESS症候群にも注意</v>
+        <v/>
       </c>
       <c r="I61" t="str">
-        <v/>
+        <v>抗がん剤・免疫抑制剤・ステロイドの使用、強いストレス、AIDSなどの免疫不全</v>
       </c>
       <c r="J61" t="str">
-        <v/>
+        <v>感染予防（手洗い・うがい、人混みを避ける）を意識するよう伝える</v>
       </c>
       <c r="K61" t="str">
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>薬剤性の好酸球増多は、原因薬剤の中止で改善することが多い。新規薬剤開始後の皮疹・発熱と合わせて薬剤性過敏症症候群(DIHS)を疑う材料になる</v>
+        <v>免疫抑制剤・抗がん剤治療中のモニタリング指標としても使われる。著明な低下時は日和見感染のリスクが高まる</v>
       </c>
       <c r="M61" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N61" t="str">
-        <v>好酸球,Eosino,Eos,アレルギー,薬疹,DIHS</v>
+        <v>リンパ球実数値,リンパ球数,ALC,免疫抑制剤,日和見感染</v>
       </c>
       <c r="O61" t="str">
         <v/>
@@ -3293,22 +3293,22 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>好塩基球</v>
+        <v>単球実数値</v>
       </c>
       <c r="B62" t="str">
-        <v>Baso,Baso%</v>
+        <v>Mono#</v>
       </c>
       <c r="C62" t="str">
-        <v>0〜2%程度（施設差あり）</v>
+        <v>200〜600 /μL程度（施設差あり）</v>
       </c>
       <c r="D62" t="str">
-        <v>白血球の中で最も数が少なく、アレルギー反応に関わる細胞の割合</v>
+        <v>単球の絶対数</v>
       </c>
       <c r="E62" t="str">
-        <v>好塩基球は白血球の中で最も数が少ない種類で、アレルギー反応や炎症に関わっています。数値の変動が病気の診断に直接使われることは少ない検査です。</v>
+        <v>これは単球の実際の数を表す数値です。慢性的な炎症や感染症の状態を把握する材料の一つになります。</v>
       </c>
       <c r="F62" t="str">
-        <v>慢性骨髄性白血病などの血液疾患、アレルギー性疾患、甲状腺機能低下症</v>
+        <v>慢性感染症、炎症性疾患、血液疾患</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -3326,13 +3326,13 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>単独での臨床的意義は乏しいが、著明な増加は血液疾患（慢性骨髄性白血病等）の可能性があり他の血球指標と合わせて評価する</v>
+        <v>単独での臨床的意義は乏しく、他の血球指標と合わせて評価する</v>
       </c>
       <c r="M62" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N62" t="str">
-        <v>好塩基球,Baso,アレルギー,白血病</v>
+        <v>単球実数値,単球数</v>
       </c>
       <c r="O62" t="str">
         <v/>
@@ -3340,46 +3340,46 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>リンパ球</v>
+        <v>好中球</v>
       </c>
       <c r="B63" t="str">
-        <v>Lympho,Lym%</v>
+        <v>Neutro,Neut%</v>
       </c>
       <c r="C63" t="str">
-        <v>18〜49%程度（施設差あり）</v>
+        <v>40〜75%程度（施設差あり）</v>
       </c>
       <c r="D63" t="str">
-        <v>ウイルス感染と戦い、免疫の記憶を担う白血球の割合</v>
+        <v>白血球の中で最も多くを占め、細菌感染と戦う主力の免疫細胞の割合</v>
       </c>
       <c r="E63" t="str">
-        <v>リンパ球は、ウイルスと戦ったり、一度かかった病気を記憶して免疫をつくったりする細胞です。ウイルス感染で増え、抗がん剤の副作用や強いストレスで減ることがあります。</v>
+        <v>好中球は、白血球の中で最も数が多く、細菌が体に入ってきたときに真っ先に戦ってくれる免疫細胞です。感染症や炎症があると増え、逆に薬の副作用などで減ることがあります。</v>
       </c>
       <c r="F63" t="str">
-        <v>ウイルス感染症、リンパ性白血病などの血液疾患、百日咳</v>
+        <v>細菌感染症、炎症、ストレス、ステロイド使用</v>
       </c>
       <c r="G63" t="str">
-        <v/>
+        <v>発熱や炎症症状がないか確認する</v>
       </c>
       <c r="H63" t="str">
         <v/>
       </c>
       <c r="I63" t="str">
-        <v>抗がん剤・免疫抑制剤・ステロイドの使用、強いストレス、AIDSなどの免疫不全</v>
+        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、ウイルス感染、メルカゾールなど薬剤性の無顆粒球症</v>
       </c>
       <c r="J63" t="str">
-        <v>免疫が下がっている可能性があるため、感染予防（手洗い・うがい、人混みを避ける）を意識するよう伝える</v>
+        <v>発熱やのどの痛みなど感染症状の初期サインがないか確認する</v>
       </c>
       <c r="K63" t="str">
-        <v/>
+        <v>抗がん剤、メルカゾール(無顆粒球症)、クロザピン、サラゾスルファピリジン</v>
       </c>
       <c r="L63" t="str">
-        <v>ステロイド・免疫抑制剤使用中はリンパ球減少による易感染性に注意。好中球と逆方向に動くことが多い（ウイルス感染ではリンパ球優位、細菌感染では好中球優位になりやすい）</v>
+        <v>好中球の絶対数（好中球実数値）が500/μL未満になると重篤な感染症のリスクが高まる。割合(%)だけでなく実数値も合わせて確認する</v>
       </c>
       <c r="M63" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N63" t="str">
-        <v>リンパ球,Lympho,Lym,ウイルス感染,免疫抑制剤,ステロイド</v>
+        <v>好中球,Neutro,Neut,感染症,無顆粒球症</v>
       </c>
       <c r="O63" t="str">
         <v/>
@@ -3387,28 +3387,28 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>単球</v>
+        <v>好酸球</v>
       </c>
       <c r="B64" t="str">
-        <v>Mono,Mono%</v>
+        <v>Eosino,Eos%</v>
       </c>
       <c r="C64" t="str">
-        <v>2〜10%程度（施設差あり）</v>
+        <v>1〜5%程度（施設差あり）</v>
       </c>
       <c r="D64" t="str">
-        <v>感染や炎症の後始末をする白血球の一種の割合</v>
+        <v>アレルギー反応や寄生虫感染に関わる白血球の一種の割合</v>
       </c>
       <c r="E64" t="str">
-        <v>単球は、細菌などを取り込んで処理したり、組織の修復に関わったりする免疫細胞です。慢性的な炎症や感染症の回復期に増えることがあります。</v>
+        <v>好酸球は、アレルギー反応や寄生虫感染と関係が深い免疫細胞です。アレルギー性の病気や薬の副作用（薬疹など）で増えることがあります。</v>
       </c>
       <c r="F64" t="str">
-        <v>慢性感染症（結核など）、炎症性疾患、血液疾患、感染症の回復期</v>
+        <v>アレルギー性疾患（気管支喘息、アトピー性皮膚炎など）、薬剤アレルギー、寄生虫感染</v>
       </c>
       <c r="G64" t="str">
-        <v/>
+        <v>新しく始めた薬がないか確認する。皮疹やかゆみなどアレルギー症状の有無を確認する</v>
       </c>
       <c r="H64" t="str">
-        <v/>
+        <v>薬剤性好酸球増多(抗菌薬・NSAIDs・抗てんかん薬など)。発熱や皮疹を伴う場合はDRESS症候群にも注意</v>
       </c>
       <c r="I64" t="str">
         <v/>
@@ -3420,13 +3420,13 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>単独での臨床的意義は乏しく、他の血球指標や炎症マーカー(CRPなど)と合わせて評価する</v>
+        <v>薬剤性の好酸球増多は、原因薬剤の中止で改善することが多い。新規薬剤開始後の皮疹・発熱と合わせて薬剤性過敏症症候群(DIHS)を疑う材料になる</v>
       </c>
       <c r="M64" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N64" t="str">
-        <v>単球,Mono,慢性感染症,結核,炎症</v>
+        <v>好酸球,Eosino,Eos,アレルギー,薬疹,DIHS</v>
       </c>
       <c r="O64" t="str">
         <v/>
@@ -3434,31 +3434,31 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Dダイマー</v>
+        <v>好塩基球</v>
       </c>
       <c r="B65" t="str">
-        <v>D-dimer</v>
+        <v>Baso,Baso%</v>
       </c>
       <c r="C65" t="str">
-        <v>1.0 μg/mL以下(施設・測定法により異なる)</v>
+        <v>0〜2%程度（施設差あり）</v>
       </c>
       <c r="D65" t="str">
-        <v>体の中で血栓ができて溶けた(線溶)ときにできる分解産物で、血栓症の有無をスクリーニングする指標</v>
+        <v>白血球の中で最も数が少なく、アレルギー反応に関わる細胞の割合</v>
       </c>
       <c r="E65" t="str">
-        <v>Dダイマーは、血管の中に血のかたまり(血栓)ができて、それが溶かされるときにできる物質です。この数値が高いと、どこかに血栓ができている可能性を考えます。ただし手術後や妊娠中、高齢の方などでも上がることがあるため、この数値だけで診断が決まるわけではありません。</v>
+        <v>好塩基球は白血球の中で最も数が少ない種類で、アレルギー反応や炎症に関わっています。数値の変動が病気の診断に直接使われることは少ない検査です。</v>
       </c>
       <c r="F65" t="str">
-        <v>深部静脈血栓症(DVT)・肺血栓塞栓症(PE)、播種性血管内凝固症候群(DIC)、大動脈解離、悪性腫瘍、手術後、妊娠、高齢、感染・炎症</v>
+        <v>慢性骨髄性白血病などの血液疾患、アレルギー性疾患、甲状腺機能低下症</v>
       </c>
       <c r="G65" t="str">
-        <v>ふくらはぎの腫れ・痛み、急な息切れ・胸痛など血栓症を疑う症状がないか確認する</v>
+        <v/>
       </c>
       <c r="H65" t="str">
-        <v>経口避妊薬・ホルモン補充療法は血栓リスクを高める。逆にワルファリン・DOAC・ヘパリンなど抗凝固薬の効果不十分で血栓が進行している可能性にも注意</v>
+        <v/>
       </c>
       <c r="I65" t="str">
-        <v>通常、臨床的意義は乏しい(基準値以下であれば血栓症の可能性は低いとする除外診断に有用)</v>
+        <v/>
       </c>
       <c r="J65" t="str">
         <v/>
@@ -3467,13 +3467,13 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>陰性的中率が高く、基準値以下であれば静脈血栓塞栓症(VTE)の可能性は低いとする除外診断への活用が臨床的に重要。一方で偽陽性が多く、高値のみで血栓症と確定はできない。抗凝固療法中のモニタリングそのものには通常用いない(効果判定はPT-INR/APTT等)</v>
+        <v>単独での臨床的意義は乏しいが、著明な増加は血液疾患（慢性骨髄性白血病等）の可能性があり他の血球指標と合わせて評価する</v>
       </c>
       <c r="M65" t="str">
-        <v>抗凝固療法（心房細動・血栓症）</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N65" t="str">
-        <v>Dダイマー,D-dimer,血栓,DVT,深部静脈血栓症,肺塞栓,DIC</v>
+        <v>好塩基球,Baso,アレルギー,白血病</v>
       </c>
       <c r="O65" t="str">
         <v/>
@@ -3481,46 +3481,46 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>C反応性蛋白（CRP）</v>
+        <v>リンパ球</v>
       </c>
       <c r="B66" t="str">
-        <v>CRP</v>
+        <v>Lympho,Lym%</v>
       </c>
       <c r="C66" t="str">
-        <v>0.3 mg/dL未満（施設差あり）</v>
+        <v>18〜49%程度（施設差あり）</v>
       </c>
       <c r="D66" t="str">
-        <v>体のどこかに炎症や感染が起きていないかを鋭敏に反映する数値</v>
+        <v>ウイルス感染と戦い、免疫の記憶を担う白血球の割合</v>
       </c>
       <c r="E66" t="str">
-        <v>CRPは、体に炎症や感染が起きると数時間〜半日程度で急激に上昇する数値です。風邪のようなウイルス感染から細菌感染、体のどこかの炎症まで、幅広く反応するため、体調の変化を早期に捉える手がかりになります。</v>
+        <v>リンパ球は、ウイルスと戦ったり、一度かかった病気を記憶して免疫をつくったりする細胞です。ウイルス感染で増え、抗がん剤の副作用や強いストレスで減ることがあります。</v>
       </c>
       <c r="F66" t="str">
-        <v>細菌感染症、ウイルス感染症、自己免疫疾患（関節リウマチなど）、悪性腫瘍、組織の損傷（術後・心筋梗塞など）</v>
+        <v>ウイルス感染症、リンパ性白血病などの血液疾患、百日咳</v>
       </c>
       <c r="G66" t="str">
-        <v>発熱、痛み、腫れなど炎症症状の有無を確認する</v>
+        <v/>
       </c>
       <c r="H66" t="str">
         <v/>
       </c>
       <c r="I66" t="str">
-        <v/>
+        <v>抗がん剤・免疫抑制剤・ステロイドの使用、強いストレス、AIDSなどの免疫不全</v>
       </c>
       <c r="J66" t="str">
-        <v/>
+        <v>免疫が下がっている可能性があるため、感染予防（手洗い・うがい、人混みを避ける）を意識するよう伝える</v>
       </c>
       <c r="K66" t="str">
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>白血球数と合わせて感染・炎症の程度を評価する。上昇・低下のタイミングは白血球より半日〜1日程度遅れる傾向があるため、経過を追う際は採血のタイミングに注意</v>
+        <v>ステロイド・免疫抑制剤使用中はリンパ球減少による易感染性に注意。好中球と逆方向に動くことが多い（ウイルス感染ではリンパ球優位、細菌感染では好中球優位になりやすい）</v>
       </c>
       <c r="M66" t="str">
-        <v/>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N66" t="str">
-        <v>CRP,炎症,感染</v>
+        <v>リンパ球,Lympho,Lym,ウイルス感染,免疫抑制剤,ステロイド</v>
       </c>
       <c r="O66" t="str">
         <v/>
@@ -3528,25 +3528,25 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>骨型酒石酸抵抗性フォスファターゼ（TRACP-5b）</v>
+        <v>単球</v>
       </c>
       <c r="B67" t="str">
-        <v>TRACP-5b</v>
+        <v>Mono,Mono%</v>
       </c>
       <c r="C67" t="str">
-        <v>120〜420 mU/dL</v>
+        <v>2〜10%程度（施設差あり）</v>
       </c>
       <c r="D67" t="str">
-        <v>骨がどれくらい壊されているかを見る検査。骨は「古い骨を壊して新しい骨を作る」入れ替えを繰り返しており、骨を壊す細胞が活発だとこの物質が血液中に増える。</v>
+        <v>感染や炎症の後始末をする白血球の一種の割合</v>
       </c>
       <c r="E67" t="str">
-        <v>この検査は、骨がどれくらい早く減っていないかを見るものです。数値が高いと、骨が弱くなりやすい状態の目安になります。</v>
+        <v>単球は、細菌などを取り込んで処理したり、組織の修復に関わったりする免疫細胞です。慢性的な炎症や感染症の回復期に増えることがあります。</v>
       </c>
       <c r="F67" t="str">
-        <v>骨粗鬆症、骨代謝回転（骨がこわれるスピード）が活発な状態</v>
+        <v>慢性感染症（結核など）、炎症性疾患、血液疾患、感染症の回復期</v>
       </c>
       <c r="G67" t="str">
-        <v>カルシウム・ビタミンDの摂取や、適度な荷重運動（ウォーキングなど）を意識するよう伝える</v>
+        <v/>
       </c>
       <c r="H67" t="str">
         <v/>
@@ -3561,13 +3561,13 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>「骨を壊す側」の指標。「骨を作る側」の検査と合わせて評価する。数値だけで診断はしない</v>
+        <v>単独での臨床的意義は乏しく、他の血球指標や炎症マーカー(CRPなど)と合わせて評価する</v>
       </c>
       <c r="M67" t="str">
-        <v>骨粗鬆症</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N67" t="str">
-        <v>TRACP-5b,骨型酒石酸抵抗性フォスファターゼ,骨粗鬆症,骨代謝</v>
+        <v>単球,Mono,慢性感染症,結核,炎症</v>
       </c>
       <c r="O67" t="str">
         <v/>
@@ -3575,75 +3575,75 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>PT-INR（プロトロンビン時間国際標準比）</v>
+        <v>Dダイマー</v>
       </c>
       <c r="B68" t="str">
-        <v>PT-INR,INR</v>
+        <v>D-dimer</v>
       </c>
       <c r="C68" t="str">
-        <v>治療域の目安 1.6〜3.0（ワルファリン服用時。年齢・疾患により異なる）</v>
+        <v>1.0 μg/mL以下(施設・測定法により異なる)</v>
       </c>
       <c r="D68" t="str">
-        <v>血液の固まりやすさを表す数値で、ワルファリンの効き具合を確認するために使う</v>
+        <v>体の中で血栓ができて溶けた(線溶)ときにできる分解産物で、血栓症の有無をスクリーニングする指標</v>
       </c>
       <c r="E68" t="str">
-        <v>PT-INRは血液が固まるまでの時間をもとにした数値で、ワルファリンというお薬を飲んでいる方の効き具合を確認するために測ります。数値が高いほど血液が固まりにくく出血しやすい状態、低いほど血栓ができやすい状態を示します。</v>
+        <v>Dダイマーは、血管の中に血のかたまり(血栓)ができて、それが溶かされるときにできる物質です。この数値が高いと、どこかに血栓ができている可能性を考えます。ただし手術後や妊娠中、高齢の方などでも上がることがあるため、この数値だけで診断が決まるわけではありません。</v>
       </c>
       <c r="F68" t="str">
-        <v>ワルファリンの効きすぎ、肝機能低下、ビタミンK不足、納豆・青汁など摂取量の変化</v>
+        <v>深部静脈血栓症(DVT)・肺血栓塞栓症(PE)、播種性血管内凝固症候群(DIC)、大動脈解離、悪性腫瘍、手術後、妊娠、高齢、感染・炎症</v>
       </c>
       <c r="G68" t="str">
-        <v>歯ぐきや鼻からの出血、あざ、黒い便などの出血症状がないか確認する。納豆・クロレラ・青汁などビタミンKを多く含む食品の摂取状況を確認する</v>
+        <v>ふくらはぎの腫れ・痛み、急な息切れ・胸痛など血栓症を疑う症状がないか確認する</v>
       </c>
       <c r="H68" t="str">
-        <v>ワルファリンの過量。ワルファリン服用中はST合剤・マクロライド系・フルコナゾール等の相互作用やビタミンK摂取量の変化にも注意</v>
+        <v>経口避妊薬・ホルモン補充療法は血栓リスクを高める。逆にワルファリン・DOAC・ヘパリンなど抗凝固薬の効果不十分で血栓が進行している可能性にも注意</v>
       </c>
       <c r="I68" t="str">
-        <v>ワルファリンの効き不足、飲み忘れ、ビタミンK摂取量の急激な増加</v>
+        <v>通常、臨床的意義は乏しい(基準値以下であれば血栓症の可能性は低いとする除外診断に有用)</v>
       </c>
       <c r="J68" t="str">
-        <v>服薬状況（飲み忘れ）を確認する。片側のむくみ・しびれ・胸痛など血栓症状がないか確認する</v>
+        <v/>
       </c>
       <c r="K68" t="str">
-        <v>ワルファリン服用中で低値の場合は効果不十分の可能性。ビタミンK摂取量の変化や、リファンピシン・カルバマゼピン・バルビツール酸系など代謝を促進する薬との併用を確認</v>
+        <v/>
       </c>
       <c r="L68" t="str">
-        <v>治療域は疾患・年齢によって異なる（例：非弁膜症性心房細動の高齢者では1.6〜2.6が目安になることが多い）。多くの薬剤・食品と相互作用があるため新規薬剤追加時は必ず確認する。DOAC（エリキュース、リクシアナ、プラザキサなど）ではPT-INRのモニタリングは不要</v>
+        <v>陰性的中率が高く、基準値以下であれば静脈血栓塞栓症(VTE)の可能性は低いとする除外診断への活用が臨床的に重要。一方で偽陽性が多く、高値のみで血栓症と確定はできない。抗凝固療法中のモニタリングそのものには通常用いない(効果判定はPT-INR/APTT等)</v>
       </c>
       <c r="M68" t="str">
         <v>抗凝固療法（心房細動・血栓症）</v>
       </c>
       <c r="N68" t="str">
-        <v>PT-INR,INR,プロトロンビン時間,ワルファリン,ワーファリン,抗凝固</v>
+        <v>Dダイマー,D-dimer,血栓,DVT,深部静脈血栓症,肺塞栓,DIC</v>
       </c>
       <c r="O68" t="str">
-        <v>食事と栄養 p.221（心疾患Q93 ワルファリン服用中のビタミンK摂取）</v>
+        <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>尿蛋白定量</v>
+        <v>C反応性蛋白（CRP）</v>
       </c>
       <c r="B69" t="str">
-        <v>U-Pro定量,蛋白/Cr比</v>
+        <v>CRP</v>
       </c>
       <c r="C69" t="str">
-        <v>0.15 g/gCr未満</v>
+        <v>0.3 mg/dL未満（施設差あり）</v>
       </c>
       <c r="D69" t="str">
-        <v>随時尿から尿蛋白の量を具体的な数値として評価する検査。ネフローゼ等の重症度判定に使う</v>
+        <v>体のどこかに炎症や感染が起きていないかを鋭敏に反映する数値</v>
       </c>
       <c r="E69" t="str">
-        <v>これは、尿に出ているたんぱくの量を具体的な数値で見る検査です。試験紙での陽性・陰性の判定だけでなく、実際にどれくらいの量が出ているかを把握できます。</v>
+        <v>CRPは、体に炎症や感染が起きると数時間〜半日程度で急激に上昇する数値です。風邪のようなウイルス感染から細菌感染、体のどこかの炎症まで、幅広く反応するため、体調の変化を早期に捉える手がかりになります。</v>
       </c>
       <c r="F69" t="str">
-        <v>腎症の進行（糖尿病性腎症、慢性腎臓病など）、ネフローゼ症候群（3.5 g/gCr以上が目安）</v>
+        <v>細菌感染症、ウイルス感染症、自己免疫疾患（関節リウマチなど）、悪性腫瘍、組織の損傷（術後・心筋梗塞など）</v>
       </c>
       <c r="G69" t="str">
-        <v>持続する場合は塩分の摂りすぎに注意し、むくみの有無も確認する。腎臓内科でのフォロー状況もあわせて確認する</v>
+        <v>発熱、痛み、腫れなど炎症症状の有無を確認する</v>
       </c>
       <c r="H69" t="str">
-        <v>NSAIDs、造影剤、アミノグリコシド系、バンコマイシン</v>
+        <v/>
       </c>
       <c r="I69" t="str">
         <v/>
@@ -3655,13 +3655,13 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>CKD診療ガイドラインの重症度分類（尿蛋白量による区分）にも使われる定量指標。試験紙法の半定量結果より治療効果判定に適する</v>
+        <v>白血球数と合わせて感染・炎症の程度を評価する。上昇・低下のタイミングは白血球より半日〜1日程度遅れる傾向があるため、経過を追う際は採血のタイミングに注意</v>
       </c>
       <c r="M69" t="str">
-        <v>腎機能,糖尿病</v>
+        <v/>
       </c>
       <c r="N69" t="str">
-        <v>尿蛋白,随時尿,定量,蛋白クレアチニン比,ネフローゼ</v>
+        <v>CRP,炎症,感染</v>
       </c>
       <c r="O69" t="str">
         <v/>
@@ -3669,31 +3669,31 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>骨型アルカリフォスファターゼ</v>
+        <v>骨型酒石酸抵抗性フォスファターゼ（TRACP-5b）</v>
       </c>
       <c r="B70" t="str">
-        <v>BAP</v>
+        <v>TRACP-5b</v>
       </c>
       <c r="C70" t="str">
-        <v>男性 3.7〜20.9 μg/L、女性（閉経前）2.9〜14.5 μg/L（施設差あり）</v>
+        <v>120〜420 mU/dL</v>
       </c>
       <c r="D70" t="str">
-        <v>ALPのうち骨に由来する成分だけを測定し、骨が作られる勢い（骨形成）を反映する</v>
+        <v>骨がどれくらい壊されているかを見る検査。骨は「古い骨を壊して新しい骨を作る」入れ替えを繰り返しており、骨を壊す細胞が活発だとこの物質が血液中に増える。</v>
       </c>
       <c r="E70" t="str">
-        <v>骨型ALPは、通常のALP（アルカリフォスファターゼ）の中でも、骨で作られる成分だけを選んで測定するものです。骨を新しく作る働きがどれくらい活発かを見る指標として、骨粗鬆症の治療効果判定などに使われます。</v>
+        <v>この検査は、骨がどれくらい早く減っていないかを見るものです。数値が高いと、骨が弱くなりやすい状態の目安になります。</v>
       </c>
       <c r="F70" t="str">
-        <v>骨代謝回転の亢進（骨粗鬆症、骨折治癒過程、骨形成促進薬による治療効果、Paget病、骨転移）</v>
+        <v>骨粗鬆症、骨代謝回転（骨がこわれるスピード）が活発な状態</v>
       </c>
       <c r="G70" t="str">
-        <v/>
+        <v>カルシウム・ビタミンDの摂取や、適度な荷重運動（ウォーキングなど）を意識するよう伝える</v>
       </c>
       <c r="H70" t="str">
         <v/>
       </c>
       <c r="I70" t="str">
-        <v>骨形成の低下</v>
+        <v/>
       </c>
       <c r="J70" t="str">
         <v/>
@@ -3702,13 +3702,13 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>通常のALPと異なり肝臓の影響を受けにくいため、肝機能異常がある患者でも骨代謝を評価しやすい。P1NPと同じ「骨を作る側」の指標で、骨形成促進薬（テリパラチド等）の効果判定に使われる</v>
+        <v>「骨を壊す側」の指標。「骨を作る側」の検査と合わせて評価する。数値だけで診断はしない</v>
       </c>
       <c r="M70" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="N70" t="str">
-        <v>骨型ALP,BAP,骨型アルカリフォスファターゼ,骨形成マーカー</v>
+        <v>TRACP-5b,骨型酒石酸抵抗性フォスファターゼ,骨粗鬆症,骨代謝</v>
       </c>
       <c r="O70" t="str">
         <v/>
@@ -3716,93 +3716,93 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>25-ヒドロキシビタミンD</v>
+        <v>PT-INR（プロトロンビン時間国際標準比）</v>
       </c>
       <c r="B71" t="str">
-        <v>25(OH)D</v>
+        <v>PT-INR,INR</v>
       </c>
       <c r="C71" t="str">
-        <v>30 ng/mL以上：充足、20〜30 ng/mL：不足、20 ng/mL未満：欠乏（施設差あり）</v>
+        <v>治療域の目安 1.6〜3.0（ワルファリン服用時。年齢・疾患により異なる）</v>
       </c>
       <c r="D71" t="str">
-        <v>体内のビタミンDの蓄え具合を反映する指標。カルシウムの吸収や骨の健康に関わる</v>
+        <v>血液の固まりやすさを表す数値で、ワルファリンの効き具合を確認するために使う</v>
       </c>
       <c r="E71" t="str">
-        <v>この検査は、体の中にビタミンDがどれくらい蓄えられているかを見るものです。ビタミンDは、食事から摂ったカルシウムを腸で吸収するのを助ける働きがあり、不足すると骨がもろくなりやすくなります。</v>
+        <v>PT-INRは血液が固まるまでの時間をもとにした数値で、ワルファリンというお薬を飲んでいる方の効き具合を確認するために測ります。数値が高いほど血液が固まりにくく出血しやすい状態、低いほど血栓ができやすい状態を示します。</v>
       </c>
       <c r="F71" t="str">
-        <v>ビタミンD製剤の過剰摂取</v>
+        <v>ワルファリンの効きすぎ、肝機能低下、ビタミンK不足、納豆・青汁など摂取量の変化</v>
       </c>
       <c r="G71" t="str">
-        <v>活性型ビタミンD3製剤やサプリメントの摂取量を確認する。高カルシウム血症の症状（吐き気、便秘、多尿など）がないか確認する</v>
+        <v>歯ぐきや鼻からの出血、あざ、黒い便などの出血症状がないか確認する。納豆・クロレラ・青汁などビタミンKを多く含む食品の摂取状況を確認する</v>
       </c>
       <c r="H71" t="str">
-        <v>活性型/天然型ビタミンD製剤の過量投与</v>
+        <v>ワルファリンの過量。ワルファリン服用中はST合剤・マクロライド系・フルコナゾール等の相互作用やビタミンK摂取量の変化にも注意</v>
       </c>
       <c r="I71" t="str">
-        <v>日光暴露不足、食事摂取不足、高齢、腸疾患による吸収不良、肝・腎機能低下（活性化障害）</v>
+        <v>ワルファリンの効き不足、飲み忘れ、ビタミンK摂取量の急激な増加</v>
       </c>
       <c r="J71" t="str">
-        <v>適度な日光浴、魚類・きのこ類などビタミンDを多く含む食品の摂取を意識するとよいことを伝える</v>
+        <v>服薬状況（飲み忘れ）を確認する。片側のむくみ・しびれ・胸痛など血栓症状がないか確認する</v>
       </c>
       <c r="K71" t="str">
-        <v/>
+        <v>ワルファリン服用中で低値の場合は効果不十分の可能性。ビタミンK摂取量の変化や、リファンピシン・カルバマゼピン・バルビツール酸系など代謝を促進する薬との併用を確認</v>
       </c>
       <c r="L71" t="str">
-        <v>骨粗鬆症治療における活性型ビタミンD3製剤の効果判定や、投与量調整の参考に用いられる。腎機能低下患者では活性化障害により25(OH)Dが正常でも活性型が不足することがある点に注意</v>
+        <v>治療域は疾患・年齢によって異なる（例：非弁膜症性心房細動の高齢者では1.6〜2.6が目安になることが多い）。多くの薬剤・食品と相互作用があるため新規薬剤追加時は必ず確認する。DOAC（エリキュース、リクシアナ、プラザキサなど）ではPT-INRのモニタリングは不要</v>
       </c>
       <c r="M71" t="str">
-        <v>骨粗鬆症</v>
+        <v>抗凝固療法（心房細動・血栓症）</v>
       </c>
       <c r="N71" t="str">
-        <v>25(OH)D,ビタミンD,25-ヒドロキシビタミンD,ビタミンD欠乏,骨粗鬆症</v>
+        <v>PT-INR,INR,プロトロンビン時間,ワルファリン,ワーファリン,抗凝固</v>
       </c>
       <c r="O71" t="str">
-        <v>食事と栄養 p.38（ビタミンD）</v>
+        <v>食事と栄養 p.221（心疾患Q93 ワルファリン服用中のビタミンK摂取）</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>尿pH</v>
+        <v>尿蛋白定量</v>
       </c>
       <c r="B72" t="str">
-        <v>尿pH</v>
+        <v>U-Pro定量,蛋白/Cr比</v>
       </c>
       <c r="C72" t="str">
-        <v>4.5〜7.5程度（弱酸性が多い）</v>
+        <v>0.15 g/gCr未満</v>
       </c>
       <c r="D72" t="str">
-        <v>尿の酸性・アルカリ性の度合い。食事や感染症、体の状態を反映する</v>
+        <v>随時尿から尿蛋白の量を具体的な数値として評価する検査。ネフローゼ等の重症度判定に使う</v>
       </c>
       <c r="E72" t="str">
-        <v>尿のpHは酸性・アルカリ性のバランスを表します。食事の内容や感染症、体の代謝状態によって変化します。単独で大きな問題を示すことは少ない検査です。</v>
+        <v>これは、尿に出ているたんぱくの量を具体的な数値で見る検査です。試験紙での陽性・陰性の判定だけでなく、実際にどれくらいの量が出ているかを把握できます。</v>
       </c>
       <c r="F72" t="str">
-        <v>尿路感染症（尿素分解菌によるもの）、野菜中心の食事、過換気</v>
+        <v>腎症の進行（糖尿病性腎症、慢性腎臓病など）、ネフローゼ症候群（3.5 g/gCr以上が目安）</v>
       </c>
       <c r="G72" t="str">
-        <v/>
+        <v>持続する場合は塩分の摂りすぎに注意し、むくみの有無も確認する。腎臓内科でのフォロー状況もあわせて確認する</v>
       </c>
       <c r="H72" t="str">
-        <v/>
+        <v>NSAIDs、造影剤、アミノグリコシド系、バンコマイシン</v>
       </c>
       <c r="I72" t="str">
-        <v>高たんぱく食、糖尿病性ケトアシドーシス、痛風発作時（酸性尿は尿酸結石のリスクを高める）</v>
+        <v/>
       </c>
       <c r="J72" t="str">
-        <v>痛風・尿酸結石がある場合は、野菜など尿をアルカリ化する食品を意識するとよいことを伝える</v>
+        <v/>
       </c>
       <c r="K72" t="str">
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>高尿酸血症・尿酸結石の患者では尿pHが酸性に傾いていないか確認する。尿アルカリ化薬（ウラリットなど）の効果判定にも使う</v>
+        <v>CKD診療ガイドラインの重症度分類（尿蛋白量による区分）にも使われる定量指標。試験紙法の半定量結果より治療効果判定に適する</v>
       </c>
       <c r="M72" t="str">
-        <v>高尿酸血症</v>
+        <v>腎機能,糖尿病</v>
       </c>
       <c r="N72" t="str">
-        <v>尿pH,尿酸性度,尿アルカリ化,ウラリット</v>
+        <v>尿蛋白,随時尿,定量,蛋白クレアチニン比,ネフローゼ</v>
       </c>
       <c r="O72" t="str">
         <v/>
@@ -3810,31 +3810,31 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>尿ケトン体</v>
+        <v>骨型アルカリフォスファターゼ</v>
       </c>
       <c r="B73" t="str">
-        <v>尿ケトン,Ket</v>
+        <v>BAP</v>
       </c>
       <c r="C73" t="str">
-        <v>陰性（－）</v>
+        <v>男性 3.7〜20.9 μg/L、女性（閉経前）2.9〜14.5 μg/L（施設差あり）</v>
       </c>
       <c r="D73" t="str">
-        <v>体がブドウ糖の代わりに脂肪を分解してエネルギーを作っているサイン</v>
+        <v>ALPのうち骨に由来する成分だけを測定し、骨が作られる勢い（骨形成）を反映する</v>
       </c>
       <c r="E73" t="str">
-        <v>この検査は、体が糖の代わりに脂肪を使ってエネルギーを作っていないかを見るものです。陽性が続くときは、食事や水分、インスリンの使い方を確認する必要があります。</v>
+        <v>骨型ALPは、通常のALP（アルカリフォスファターゼ）の中でも、骨で作られる成分だけを選んで測定するものです。骨を新しく作る働きがどれくらい活発かを見る指標として、骨粗鬆症の治療効果判定などに使われます。</v>
       </c>
       <c r="F73" t="str">
-        <v>糖尿病の血糖コントロール不良（シックデイ・インスリン不足）、極端な糖質制限、絶食、嘔吐・下痢による脱水</v>
+        <v>骨代謝回転の亢進（骨粗鬆症、骨折治癒過程、骨形成促進薬による治療効果、Paget病、骨転移）</v>
       </c>
       <c r="G73" t="str">
-        <v>糖尿病治療中の場合はシックデイ時の対応(インスリンを自己中断しない、水分摂取を続けるなど)を確認する。体調不良時の対応方法を事前に説明しておく</v>
+        <v/>
       </c>
       <c r="H73" t="str">
-        <v>SGLT2阻害薬(特に絶食・シックデイ時の正常血糖ケトアシドーシスに注意)</v>
+        <v/>
       </c>
       <c r="I73" t="str">
-        <v/>
+        <v>骨形成の低下</v>
       </c>
       <c r="J73" t="str">
         <v/>
@@ -3843,13 +3843,13 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>陽性かつ高血糖・全身倦怠感が強い場合は糖尿病性ケトアシドーシスの可能性があり緊急性が高い。シックデイルールの説明歴を確認する</v>
+        <v>通常のALPと異なり肝臓の影響を受けにくいため、肝機能異常がある患者でも骨代謝を評価しやすい。P1NPと同じ「骨を作る側」の指標で、骨形成促進薬（テリパラチド等）の効果判定に使われる</v>
       </c>
       <c r="M73" t="str">
-        <v>糖尿病</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="N73" t="str">
-        <v>尿ケトン体,ケトン体,Ket,シックデイ,ケトアシドーシス</v>
+        <v>骨型ALP,BAP,骨型アルカリフォスファターゼ,骨形成マーカー</v>
       </c>
       <c r="O73" t="str">
         <v/>
@@ -3857,93 +3857,93 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>ウロビリノーゲン</v>
+        <v>25-ヒドロキシビタミンD</v>
       </c>
       <c r="B74" t="str">
-        <v>Uro</v>
+        <v>25(OH)D</v>
       </c>
       <c r="C74" t="str">
-        <v>正常（±）程度</v>
+        <v>30 ng/mL以上：充足、20〜30 ng/mL：不足、20 ng/mL未満：欠乏（施設差あり）</v>
       </c>
       <c r="D74" t="str">
-        <v>肝臓や胆道、赤血球の壊れ方の状態を反映する尿検査項目</v>
+        <v>体内のビタミンDの蓄え具合を反映する指標。カルシウムの吸収や骨の健康に関わる</v>
       </c>
       <c r="E74" t="str">
-        <v>ウロビリノーゲンは、赤血球やビリルビンが体の中で処理される過程でできる物質です。肝臓の働きが悪くなったり、赤血球が壊れやすくなったりすると、尿の中の量が変化します。</v>
+        <v>この検査は、体の中にビタミンDがどれくらい蓄えられているかを見るものです。ビタミンDは、食事から摂ったカルシウムを腸で吸収するのを助ける働きがあり、不足すると骨がもろくなりやすくなります。</v>
       </c>
       <c r="F74" t="str">
-        <v>溶血性疾患（赤血球の破壊亢進）、肝機能障害</v>
+        <v>ビタミンD製剤の過剰摂取</v>
       </c>
       <c r="G74" t="str">
-        <v/>
+        <v>活性型ビタミンD3製剤やサプリメントの摂取量を確認する。高カルシウム血症の症状（吐き気、便秘、多尿など）がないか確認する</v>
       </c>
       <c r="H74" t="str">
-        <v/>
+        <v>活性型/天然型ビタミンD製剤の過量投与</v>
       </c>
       <c r="I74" t="str">
-        <v>胆道閉塞（胆汁が腸に流れず、ウロビリノーゲンが作られない状態）</v>
+        <v>日光暴露不足、食事摂取不足、高齢、腸疾患による吸収不良、肝・腎機能低下（活性化障害）</v>
       </c>
       <c r="J74" t="str">
-        <v/>
+        <v>適度な日光浴、魚類・きのこ類などビタミンDを多く含む食品の摂取を意識するとよいことを伝える</v>
       </c>
       <c r="K74" t="str">
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>完全に陰性の場合は胆道閉塞を疑う所見の一つ。肝機能（AST/ALT/ビリルビン）と合わせて評価する</v>
+        <v>骨粗鬆症治療における活性型ビタミンD3製剤の効果判定や、投与量調整の参考に用いられる。腎機能低下患者では活性化障害により25(OH)Dが正常でも活性型が不足することがある点に注意</v>
       </c>
       <c r="M74" t="str">
-        <v>肝機能</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="N74" t="str">
-        <v>ウロビリノーゲン,Uro,溶血,胆道閉塞,肝機能</v>
+        <v>25(OH)D,ビタミンD,25-ヒドロキシビタミンD,ビタミンD欠乏,骨粗鬆症</v>
       </c>
       <c r="O74" t="str">
-        <v/>
+        <v>食事と栄養 p.38（ビタミンD）</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>尿潜血反応</v>
+        <v>尿pH</v>
       </c>
       <c r="B75" t="str">
-        <v>尿潜血,U-OB</v>
+        <v>尿pH</v>
       </c>
       <c r="C75" t="str">
-        <v>陰性（－）</v>
+        <v>4.5〜7.5程度（弱酸性が多い）</v>
       </c>
       <c r="D75" t="str">
-        <v>尿に血液（赤血球）が混じっていないかを見る検査</v>
+        <v>尿の酸性・アルカリ性の度合い。食事や感染症、体の状態を反映する</v>
       </c>
       <c r="E75" t="str">
-        <v>この検査は、尿に目に見えないくらいの微量の血液が混じっていないかを調べるものです。陽性の場合、腎臓や膀胱、尿路のどこかに炎症や結石などがある可能性があります。</v>
+        <v>尿のpHは酸性・アルカリ性のバランスを表します。食事の内容や感染症、体の代謝状態によって変化します。単独で大きな問題を示すことは少ない検査です。</v>
       </c>
       <c r="F75" t="str">
-        <v>尿路結石、膀胱炎などの尿路感染症、腎炎、腫瘍、月経血の混入、激しい運動後</v>
+        <v>尿路感染症（尿素分解菌によるもの）、野菜中心の食事、過換気</v>
       </c>
       <c r="G75" t="str">
-        <v>排尿時の痛みや頻尿、目に見える血尿の有無を確認する。女性は月経の時期と重なっていないか確認する</v>
+        <v/>
       </c>
       <c r="H75" t="str">
-        <v>ワルファリン、DOAC、抗血小板薬など出血傾向を強める薬剤の服用状況を確認</v>
+        <v/>
       </c>
       <c r="I75" t="str">
-        <v/>
+        <v>高たんぱく食、糖尿病性ケトアシドーシス、痛風発作時（酸性尿は尿酸結石のリスクを高める）</v>
       </c>
       <c r="J75" t="str">
-        <v/>
+        <v>痛風・尿酸結石がある場合は、野菜など尿をアルカリ化する食品を意識するとよいことを伝える</v>
       </c>
       <c r="K75" t="str">
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>陽性でも尿沈渣で赤血球が確認されない場合は偽陽性（ミオグロビン尿など）のこともある。持続する場合は泌尿器科的な精査が必要</v>
+        <v>高尿酸血症・尿酸結石の患者では尿pHが酸性に傾いていないか確認する。尿アルカリ化薬（ウラリットなど）の効果判定にも使う</v>
       </c>
       <c r="M75" t="str">
-        <v>腎機能</v>
+        <v>高尿酸血症</v>
       </c>
       <c r="N75" t="str">
-        <v>尿潜血,潜血反応,U-OB,血尿,尿路結石,膀胱炎</v>
+        <v>尿pH,尿酸性度,尿アルカリ化,ウラリット</v>
       </c>
       <c r="O75" t="str">
         <v/>
@@ -3951,28 +3951,28 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>尿糖（半定量）</v>
+        <v>尿ケトン体</v>
       </c>
       <c r="B76" t="str">
-        <v>尿糖,U-Glu</v>
+        <v>尿ケトン,Ket</v>
       </c>
       <c r="C76" t="str">
         <v>陰性（－）</v>
       </c>
       <c r="D76" t="str">
-        <v>尿に糖が漏れ出ていないかを見る検査。血糖値がかなり高いと陽性になる</v>
+        <v>体がブドウ糖の代わりに脂肪を分解してエネルギーを作っているサイン</v>
       </c>
       <c r="E76" t="str">
-        <v>通常、糖は尿にはほとんど出ませんが、血糖値がかなり高くなると尿にあふれ出るようになります。血糖コントロールの目安の一つです。</v>
+        <v>この検査は、体が糖の代わりに脂肪を使ってエネルギーを作っていないかを見るものです。陽性が続くときは、食事や水分、インスリンの使い方を確認する必要があります。</v>
       </c>
       <c r="F76" t="str">
-        <v>糖尿病（血糖値が腎臓で再吸収できる量を超えている状態）、腎性糖尿（血糖値が正常でも体質的に出ることがある）、SGLT2阻害薬服用中（薬の作用で意図的に糖を排泄するため陽性になるのが正常）</v>
+        <v>糖尿病の血糖コントロール不良（シックデイ・インスリン不足）、極端な糖質制限、絶食、嘔吐・下痢による脱水</v>
       </c>
       <c r="G76" t="str">
-        <v>SGLT2阻害薬（フォシーガ、ジャディアンスなど）服用中は、陽性が薬の効果によるものであることを説明する。脱水や尿路感染の症状がないかも確認する</v>
+        <v>糖尿病治療中の場合はシックデイ時の対応(インスリンを自己中断しない、水分摂取を続けるなど)を確認する。体調不良時の対応方法を事前に説明しておく</v>
       </c>
       <c r="H76" t="str">
-        <v>SGLT2阻害薬(薬理作用による陽性であれば想定内であることを説明)</v>
+        <v>SGLT2阻害薬(特に絶食・シックデイ時の正常血糖ケトアシドーシスに注意)</v>
       </c>
       <c r="I76" t="str">
         <v/>
@@ -3984,13 +3984,13 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>SGLT2阻害薬服用中は尿糖陽性が治療効果として想定内であることを患者に伝える。血糖値・HbA1cと合わせて評価する</v>
+        <v>陽性かつ高血糖・全身倦怠感が強い場合は糖尿病性ケトアシドーシスの可能性があり緊急性が高い。シックデイルールの説明歴を確認する</v>
       </c>
       <c r="M76" t="str">
         <v>糖尿病</v>
       </c>
       <c r="N76" t="str">
-        <v>尿糖,糖半定量,U-Glu,腎性糖尿,SGLT2</v>
+        <v>尿ケトン体,ケトン体,Ket,シックデイ,ケトアシドーシス</v>
       </c>
       <c r="O76" t="str">
         <v/>
@@ -3998,22 +3998,22 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>血清CPR（Cペプチド）</v>
+        <v>ウロビリノーゲン</v>
       </c>
       <c r="B77" t="str">
-        <v>CPR</v>
+        <v>Uro</v>
       </c>
       <c r="C77" t="str">
-        <v>空腹時 0.6〜3.0 ng/mL（施設差あり）</v>
+        <v>正常（±）程度</v>
       </c>
       <c r="D77" t="str">
-        <v>自分の膵臓がどれくらいインスリンを作れているかを表す指標</v>
+        <v>肝臓や胆道、赤血球の壊れ方の状態を反映する尿検査項目</v>
       </c>
       <c r="E77" t="str">
-        <v>この検査は、ご自身の膵臓がどれくらいインスリンを作る力を持っているかを見るものです。数値が低いほど、体の中で作れるインスリンが少ないことを示します。</v>
+        <v>ウロビリノーゲンは、赤血球やビリルビンが体の中で処理される過程でできる物質です。肝臓の働きが悪くなったり、赤血球が壊れやすくなったりすると、尿の中の量が変化します。</v>
       </c>
       <c r="F77" t="str">
-        <v>インスリン抵抗性が強い状態（初期の2型糖尿病など）</v>
+        <v>溶血性疾患（赤血球の破壊亢進）、肝機能障害</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -4022,7 +4022,7 @@
         <v/>
       </c>
       <c r="I77" t="str">
-        <v>膵臓のインスリン分泌能低下（1型糖尿病、糖尿病の進行）</v>
+        <v>胆道閉塞（胆汁が腸に流れず、ウロビリノーゲンが作られない状態）</v>
       </c>
       <c r="J77" t="str">
         <v/>
@@ -4031,13 +4031,13 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>インスリン分泌能の評価に使われる。数値が低いほどインスリン治療の必要性が高いと判断される目安になる</v>
+        <v>完全に陰性の場合は胆道閉塞を疑う所見の一つ。肝機能（AST/ALT/ビリルビン）と合わせて評価する</v>
       </c>
       <c r="M77" t="str">
-        <v>糖尿病</v>
+        <v>肝機能</v>
       </c>
       <c r="N77" t="str">
-        <v>CPR,Cペプチド,インスリン分泌,血清CPR</v>
+        <v>ウロビリノーゲン,Uro,溶血,胆道閉塞,肝機能</v>
       </c>
       <c r="O77" t="str">
         <v/>
@@ -4045,28 +4045,28 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>尿中微量アルブミン</v>
+        <v>尿潜血反応</v>
       </c>
       <c r="B78" t="str">
-        <v>U-Alb,MAU</v>
+        <v>尿潜血,U-OB</v>
       </c>
       <c r="C78" t="str">
-        <v>30 mg/gCr未満（尿中アルブミン/クレアチニン比）</v>
+        <v>陰性（－）</v>
       </c>
       <c r="D78" t="str">
-        <v>通常の尿蛋白検査では見つからない、ごく早期の腎症のサイン</v>
+        <v>尿に血液（赤血球）が混じっていないかを見る検査</v>
       </c>
       <c r="E78" t="str">
-        <v>この検査は、通常の尿検査ではまだ分からないくらい早い段階の腎臓の変化を見つけるためのものです。数値が高いと、腎症の初期のサインである可能性があります。</v>
+        <v>この検査は、尿に目に見えないくらいの微量の血液が混じっていないかを調べるものです。陽性の場合、腎臓や膀胱、尿路のどこかに炎症や結石などがある可能性があります。</v>
       </c>
       <c r="F78" t="str">
-        <v>糖尿病性腎症の早期段階、高血圧</v>
+        <v>尿路結石、膀胱炎などの尿路感染症、腎炎、腫瘍、月経血の混入、激しい運動後</v>
       </c>
       <c r="G78" t="str">
-        <v>血糖・血圧のコントロール状況を確認する。減塩や適正体重の維持など生活習慣の見直しも早期腎症の進行予防に役立つことを伝える</v>
+        <v>排尿時の痛みや頻尿、目に見える血尿の有無を確認する。女性は月経の時期と重なっていないか確認する</v>
       </c>
       <c r="H78" t="str">
-        <v>NSAIDsなど腎機能を悪化させる薬剤。ACE阻害薬・ARB・SGLT2阻害薬は低下させる方向に働く</v>
+        <v>ワルファリン、DOAC、抗血小板薬など出血傾向を強める薬剤の服用状況を確認</v>
       </c>
       <c r="I78" t="str">
         <v/>
@@ -4078,13 +4078,13 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>糖尿病腎症の早期発見に重要な検査。血糖・血圧コントロールで改善しうる段階なので、早期介入の意義を伝える</v>
+        <v>陽性でも尿沈渣で赤血球が確認されない場合は偽陽性（ミオグロビン尿など）のこともある。持続する場合は泌尿器科的な精査が必要</v>
       </c>
       <c r="M78" t="str">
-        <v>糖尿病,腎機能</v>
+        <v>腎機能</v>
       </c>
       <c r="N78" t="str">
-        <v>微量アルブミン,U-Alb,MAU,糖尿病性腎症,早期腎症</v>
+        <v>尿潜血,潜血反応,U-OB,血尿,尿路結石,膀胱炎</v>
       </c>
       <c r="O78" t="str">
         <v/>
@@ -4092,78 +4092,78 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>血清鉄（Fe）</v>
+        <v>尿糖（半定量）</v>
       </c>
       <c r="B79" t="str">
-        <v>Fe</v>
+        <v>尿糖,U-Glu</v>
       </c>
       <c r="C79" t="str">
-        <v>60〜200 μg/dL（施設差あり）</v>
+        <v>陰性（－）</v>
       </c>
       <c r="D79" t="str">
-        <v>血液中を流れている鉄の量</v>
+        <v>尿に糖が漏れ出ていないかを見る検査。血糖値がかなり高いと陽性になる</v>
       </c>
       <c r="E79" t="str">
-        <v>この検査は、今血液の中を流れている鉄の量を見るものです。低いと、体の中で鉄が不足している可能性があります。</v>
+        <v>通常、糖は尿にはほとんど出ませんが、血糖値がかなり高くなると尿にあふれ出るようになります。血糖コントロールの目安の一つです。</v>
       </c>
       <c r="F79" t="str">
-        <v>鉄剤の過剰摂取、溶血、肝疾患</v>
+        <v>糖尿病（血糖値が腎臓で再吸収できる量を超えている状態）、腎性糖尿（血糖値が正常でも体質的に出ることがある）、SGLT2阻害薬服用中（薬の作用で意図的に糖を排泄するため陽性になるのが正常）</v>
       </c>
       <c r="G79" t="str">
-        <v/>
+        <v>SGLT2阻害薬（フォシーガ、ジャディアンスなど）服用中は、陽性が薬の効果によるものであることを説明する。脱水や尿路感染の症状がないかも確認する</v>
       </c>
       <c r="H79" t="str">
-        <v>鉄剤の過量摂取(小児の誤飲を含む)</v>
+        <v>SGLT2阻害薬(薬理作用による陽性であれば想定内であることを説明)</v>
       </c>
       <c r="I79" t="str">
-        <v>鉄欠乏性貧血、慢性炎症、出血</v>
+        <v/>
       </c>
       <c r="J79" t="str">
-        <v>鉄分の多い食品（レバー・赤身肉・魚・ほうれん草など）を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える</v>
+        <v/>
       </c>
       <c r="K79" t="str">
-        <v>プロトンポンプ阻害薬(PPI)・H2ブロッカーは胃酸分泌抑制により鉄の吸収を低下させうる</v>
+        <v/>
       </c>
       <c r="L79" t="str">
-        <v>血清鉄は日内変動が大きい。単独で判断せず総鉄結合能・フェリチンと合わせて評価する</v>
+        <v>SGLT2阻害薬服用中は尿糖陽性が治療効果として想定内であることを患者に伝える。血糖値・HbA1cと合わせて評価する</v>
       </c>
       <c r="M79" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>糖尿病</v>
       </c>
       <c r="N79" t="str">
-        <v>血清鉄,Fe,鉄欠乏性貧血</v>
+        <v>尿糖,糖半定量,U-Glu,腎性糖尿,SGLT2</v>
       </c>
       <c r="O79" t="str">
-        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
+        <v/>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>総鉄結合能（TIBC）</v>
+        <v>尿中微量アルブミン</v>
       </c>
       <c r="B80" t="str">
-        <v>TIBC</v>
+        <v>U-Alb,MAU</v>
       </c>
       <c r="C80" t="str">
-        <v>250〜360 μg/dL（施設差あり）</v>
+        <v>30 mg/gCr未満（尿中アルブミン/クレアチニン比）</v>
       </c>
       <c r="D80" t="str">
-        <v>血液中のトランスフェリンが鉄と結合できる総量</v>
+        <v>通常の尿蛋白検査では見つからない、ごく早期の腎症のサイン</v>
       </c>
       <c r="E80" t="str">
-        <v>TIBCは、血液中でトランスフェリンという物質が鉄を運べる最大量を表します。体の中の鉄が不足すると、少しでも多く鉄を運ぼうとしてこの数値が上がる性質があります。</v>
+        <v>この検査は、通常の尿検査ではまだ分からないくらい早い段階の腎臓の変化を見つけるためのものです。数値が高いと、腎症の初期のサインである可能性があります。</v>
       </c>
       <c r="F80" t="str">
-        <v>鉄欠乏性貧血（＞360 μg/dLが目安）</v>
+        <v>糖尿病性腎症の早期段階、高血圧</v>
       </c>
       <c r="G80" t="str">
-        <v/>
+        <v>血糖・血圧のコントロール状況を確認する。減塩や適正体重の維持など生活習慣の見直しも早期腎症の進行予防に役立つことを伝える</v>
       </c>
       <c r="H80" t="str">
-        <v/>
+        <v>NSAIDsなど腎機能を悪化させる薬剤。ACE阻害薬・ARB・SGLT2阻害薬は低下させる方向に働く</v>
       </c>
       <c r="I80" t="str">
-        <v>慢性炎症、肝疾患、ネフローゼ症候群</v>
+        <v/>
       </c>
       <c r="J80" t="str">
         <v/>
@@ -4172,60 +4172,60 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>鉄が不足すると、体はより多く運ぼうとしてTIBCが上昇する。UIBC・血清鉄と併せて評価する</v>
+        <v>糖尿病腎症の早期発見に重要な検査。血糖・血圧コントロールで改善しうる段階なので、早期介入の意義を伝える</v>
       </c>
       <c r="M80" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>糖尿病,腎機能</v>
       </c>
       <c r="N80" t="str">
-        <v>TIBC,総鉄結合能,鉄欠乏性貧血</v>
+        <v>微量アルブミン,U-Alb,MAU,糖尿病性腎症,早期腎症</v>
       </c>
       <c r="O80" t="str">
-        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
+        <v/>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>不飽和鉄結合能（UIBC）</v>
+        <v>血清鉄（Fe）</v>
       </c>
       <c r="B81" t="str">
-        <v>UIBC</v>
+        <v>Fe</v>
       </c>
       <c r="C81" t="str">
-        <v>170〜300 μg/dL（施設差あり）</v>
+        <v>60〜200 μg/dL（施設差あり）</v>
       </c>
       <c r="D81" t="str">
-        <v>トランスフェリンのうち、まだ鉄と結合していない余力の部分（UIBC＝TIBC－血清鉄）</v>
+        <v>血液中を流れている鉄の量</v>
       </c>
       <c r="E81" t="str">
-        <v>UIBCは、トランスフェリンのうち、まだ鉄と結合していない「空き容量」の部分を表します。鉄が不足しているときほど、この空き容量は大きくなります。</v>
+        <v>この検査は、今血液の中を流れている鉄の量を見るものです。低いと、体の中で鉄が不足している可能性があります。</v>
       </c>
       <c r="F81" t="str">
-        <v>鉄欠乏性貧血（＞300 μg/dLが目安）</v>
+        <v>鉄剤の過剰摂取、溶血、肝疾患</v>
       </c>
       <c r="G81" t="str">
         <v/>
       </c>
       <c r="H81" t="str">
-        <v/>
+        <v>鉄剤の過量摂取(小児の誤飲を含む)</v>
       </c>
       <c r="I81" t="str">
-        <v>慢性炎症、鉄過剰状態</v>
+        <v>鉄欠乏性貧血、慢性炎症、出血</v>
       </c>
       <c r="J81" t="str">
-        <v/>
+        <v>鉄分の多い食品（レバー・赤身肉・魚・ほうれん草など）を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える</v>
       </c>
       <c r="K81" t="str">
-        <v/>
+        <v>プロトンポンプ阻害薬(PPI)・H2ブロッカーは胃酸分泌抑制により鉄の吸収を低下させうる</v>
       </c>
       <c r="L81" t="str">
-        <v>TIBCと同じ方向に動くことが多い。血清鉄・TIBCとあわせて鉄欠乏性貧血と二次性貧血の鑑別に使う</v>
+        <v>血清鉄は日内変動が大きい。単独で判断せず総鉄結合能・フェリチンと合わせて評価する</v>
       </c>
       <c r="M81" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
       <c r="N81" t="str">
-        <v>UIBC,不飽和鉄結合能,鉄欠乏性貧血</v>
+        <v>血清鉄,Fe,鉄欠乏性貧血</v>
       </c>
       <c r="O81" t="str">
         <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
@@ -4233,22 +4233,22 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>トランスフェリン飽和度</v>
+        <v>総鉄結合能（TIBC）</v>
       </c>
       <c r="B82" t="str">
-        <v>TSAT</v>
+        <v>TIBC</v>
       </c>
       <c r="C82" t="str">
-        <v>16〜50%程度（施設差あり）</v>
+        <v>250〜360 μg/dL（施設差あり）</v>
       </c>
       <c r="D82" t="str">
-        <v>鉄を運ぶ役割のトランスフェリンのうち、実際に鉄を運んでいる割合（血清鉄÷総鉄結合能）</v>
+        <v>血液中のトランスフェリンが鉄と結合できる総量</v>
       </c>
       <c r="E82" t="str">
-        <v>トランスフェリン飽和度は、鉄を運ぶトランスフェリンのうち、実際にどれくらいが鉄を運んでいるかを割合で表したものです。鉄欠乏性貧血では低くなり、鉄が過剰にたまる病気では高くなります。</v>
+        <v>TIBCは、血液中でトランスフェリンという物質が鉄を運べる最大量を表します。体の中の鉄が不足すると、少しでも多く鉄を運ぼうとしてこの数値が上がる性質があります。</v>
       </c>
       <c r="F82" t="str">
-        <v>鉄過剰症（ヘモクロマトーシスなど）</v>
+        <v>鉄欠乏性貧血（＞360 μg/dLが目安）</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -4257,7 +4257,7 @@
         <v/>
       </c>
       <c r="I82" t="str">
-        <v>鉄欠乏性貧血（＜16%が目安）</v>
+        <v>慢性炎症、肝疾患、ネフローゼ症候群</v>
       </c>
       <c r="J82" t="str">
         <v/>
@@ -4266,13 +4266,13 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>血清鉄をTIBCで割って計算される。鉄剤補充の効果判定にも使われる</v>
+        <v>鉄が不足すると、体はより多く運ぼうとしてTIBCが上昇する。UIBC・血清鉄と併せて評価する</v>
       </c>
       <c r="M82" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
       <c r="N82" t="str">
-        <v>トランスフェリン飽和度,TSAT,鉄欠乏性貧血</v>
+        <v>TIBC,総鉄結合能,鉄欠乏性貧血</v>
       </c>
       <c r="O82" t="str">
         <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
@@ -4280,22 +4280,22 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>血清フェリチン</v>
+        <v>不飽和鉄結合能（UIBC）</v>
       </c>
       <c r="B83" t="str">
-        <v>Ferritin</v>
+        <v>UIBC</v>
       </c>
       <c r="C83" t="str">
-        <v>男性 20〜250 ng/mL、女性 10〜120 ng/mL（施設差あり）</v>
+        <v>170〜300 μg/dL（施設差あり）</v>
       </c>
       <c r="D83" t="str">
-        <v>体に貯蔵されている鉄の量を反映する指標。貧血の症状が出るより早い段階で低下する</v>
+        <v>トランスフェリンのうち、まだ鉄と結合していない余力の部分（UIBC＝TIBC－血清鉄）</v>
       </c>
       <c r="E83" t="str">
-        <v>フェリチンは、体に蓄えられている鉄の「貯金」の量を見る検査です。この数値が下がるのは、貧血の症状が出るよりも前の、とても早い段階のサインになります。</v>
+        <v>UIBCは、トランスフェリンのうち、まだ鉄と結合していない「空き容量」の部分を表します。鉄が不足しているときほど、この空き容量は大きくなります。</v>
       </c>
       <c r="F83" t="str">
-        <v>炎症性疾患、肝疾患、悪性腫瘍、鉄過剰症（フェリチンは炎症でも上昇するため、貧血の評価では注意が必要）</v>
+        <v>鉄欠乏性貧血（＞300 μg/dLが目安）</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -4304,22 +4304,22 @@
         <v/>
       </c>
       <c r="I83" t="str">
-        <v>鉄欠乏状態（貧血の症状が出る前の早期段階から低下する）</v>
+        <v>慢性炎症、鉄過剰状態</v>
       </c>
       <c r="J83" t="str">
-        <v>鉄分の多い食品を意識するとともに、貯蔵鉄を補うため治療は数値が正常化してからも継続が必要なことを伝える</v>
+        <v/>
       </c>
       <c r="K83" t="str">
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>貯蔵鉄の指標で鉄欠乏を最も早期に反映する。ただし炎症があると鉄欠乏があっても正常〜高値に出ることがあり、CRP等の炎症所見と合わせて評価する。二次性貧血との鑑別に重要</v>
+        <v>TIBCと同じ方向に動くことが多い。血清鉄・TIBCとあわせて鉄欠乏性貧血と二次性貧血の鑑別に使う</v>
       </c>
       <c r="M83" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
       <c r="N83" t="str">
-        <v>フェリチン,Ferritin,貯蔵鉄,鉄欠乏</v>
+        <v>UIBC,不飽和鉄結合能,鉄欠乏性貧血</v>
       </c>
       <c r="O83" t="str">
         <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
@@ -4327,22 +4327,22 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>尿中尿酸/クレアチニン比（UUA/UCr）</v>
+        <v>トランスフェリン飽和度</v>
       </c>
       <c r="B84" t="str">
-        <v>UUA/UCr</v>
+        <v>TSAT</v>
       </c>
       <c r="C84" t="str">
-        <v>0.4〜0.8程度が混合型の目安</v>
+        <v>16〜50%程度（施設差あり）</v>
       </c>
       <c r="D84" t="str">
-        <v>尿酸が「作られすぎ」か「排泄できていない」かを見分ける比の値</v>
+        <v>鉄を運ぶ役割のトランスフェリンのうち、実際に鉄を運んでいる割合（血清鉄÷総鉄結合能）</v>
       </c>
       <c r="E84" t="str">
-        <v>この数値は、体の中で尿酸が「作られすぎている」のか、それとも「うまく排泄できていない」のかを見分けるために使う比の値です。高尿酸血症の治療薬を選ぶときの参考になります。</v>
+        <v>トランスフェリン飽和度は、鉄を運ぶトランスフェリンのうち、実際にどれくらいが鉄を運んでいるかを割合で表したものです。鉄欠乏性貧血では低くなり、鉄が過剰にたまる病気では高くなります。</v>
       </c>
       <c r="F84" t="str">
-        <v>尿酸産生過剰型（0.8以上が目安）</v>
+        <v>鉄過剰症（ヘモクロマトーシスなど）</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -4351,7 +4351,7 @@
         <v/>
       </c>
       <c r="I84" t="str">
-        <v>尿酸排泄低下型（0.4以下が目安）</v>
+        <v>鉄欠乏性貧血（＜16%が目安）</v>
       </c>
       <c r="J84" t="str">
         <v/>
@@ -4360,83 +4360,83 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>高尿酸血症は尿酸産生過剰型・排泄低下型・混合型に分類され、この比が目安になる。病型によって使う薬剤（尿酸生成抑制薬か尿酸排泄促進薬か）の選択が変わる</v>
+        <v>血清鉄をTIBCで割って計算される。鉄剤補充の効果判定にも使われる</v>
       </c>
       <c r="M84" t="str">
-        <v>高尿酸血症</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="N84" t="str">
-        <v>UUA,UCr,尿酸クリアランス,CUA,EUA,尿酸産生過剰型,尿酸排泄低下型</v>
+        <v>トランスフェリン飽和度,TSAT,鉄欠乏性貧血</v>
       </c>
       <c r="O84" t="str">
-        <v>食事と栄養 p.180-189（第2部 痛風・高尿酸血症）</v>
+        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>ucOC（低カルボキシル化オステオカルシン）</v>
+        <v>血清フェリチン</v>
       </c>
       <c r="B85" t="str">
-        <v>ucOC</v>
+        <v>Ferritin</v>
       </c>
       <c r="C85" t="str">
-        <v>4.5 ng/mL未満（施設差あり）</v>
+        <v>男性 20〜250 ng/mL、女性 10〜120 ng/mL（施設差あり）</v>
       </c>
       <c r="D85" t="str">
-        <v>ビタミンKが不足していないかを反映する骨の指標</v>
+        <v>体に貯蔵されている鉄の量を反映する指標。貧血の症状が出るより早い段階で低下する</v>
       </c>
       <c r="E85" t="str">
-        <v>ucOCは、骨を作るために必要なビタミンKが体の中で足りているかどうかを反映する検査です。数値が高いとビタミンK不足が疑われます。</v>
+        <v>フェリチンは、体に蓄えられている鉄の「貯金」の量を見る検査です。この数値が下がるのは、貧血の症状が出るよりも前の、とても早い段階のサインになります。</v>
       </c>
       <c r="F85" t="str">
-        <v>ビタミンK不足状態</v>
+        <v>炎症性疾患、肝疾患、悪性腫瘍、鉄過剰症（フェリチンは炎症でも上昇するため、貧血の評価では注意が必要）</v>
       </c>
       <c r="G85" t="str">
-        <v>ビタミンK2製剤(骨粗鬆症治療薬)の適応が検討されているか確認する。ワルファリン服用中の患者では、納豆などビタミンKを多く含む食品の急な摂取量の変化を避けるよう説明する</v>
+        <v/>
       </c>
       <c r="H85" t="str">
         <v/>
       </c>
       <c r="I85" t="str">
-        <v/>
+        <v>鉄欠乏状態（貧血の症状が出る前の早期段階から低下する）</v>
       </c>
       <c r="J85" t="str">
-        <v/>
+        <v>鉄分の多い食品を意識するとともに、貯蔵鉄を補うため治療は数値が正常化してからも継続が必要なことを伝える</v>
       </c>
       <c r="K85" t="str">
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>ビタミンK2製剤（骨粗鬆症治療薬）の適応判断や効果判定に使われる</v>
+        <v>貯蔵鉄の指標で鉄欠乏を最も早期に反映する。ただし炎症があると鉄欠乏があっても正常〜高値に出ることがあり、CRP等の炎症所見と合わせて評価する。二次性貧血との鑑別に重要</v>
       </c>
       <c r="M85" t="str">
-        <v>骨粗鬆症</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="N85" t="str">
-        <v>ucOC,オステオカルシン,ビタミンK</v>
+        <v>フェリチン,Ferritin,貯蔵鉄,鉄欠乏</v>
       </c>
       <c r="O85" t="str">
-        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
+        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>PTH（副甲状腺ホルモン）</v>
+        <v>尿中尿酸/クレアチニン比（UUA/UCr）</v>
       </c>
       <c r="B86" t="str">
-        <v>PTH</v>
+        <v>UUA/UCr</v>
       </c>
       <c r="C86" t="str">
-        <v>10〜65 pg/mL（施設差あり）</v>
+        <v>0.4〜0.8程度が混合型の目安</v>
       </c>
       <c r="D86" t="str">
-        <v>血液中のカルシウム濃度を調節するホルモン</v>
+        <v>尿酸が「作られすぎ」か「排泄できていない」かを見分ける比の値</v>
       </c>
       <c r="E86" t="str">
-        <v>PTHは、血液中のカルシウム濃度を一定に保つために働くホルモンです。カルシウムが低くなると分泌が増え、骨からカルシウムを取り出したり、腎臓での再吸収を促したりして数値を戻そうとします。</v>
+        <v>この数値は、体の中で尿酸が「作られすぎている」のか、それとも「うまく排泄できていない」のかを見分けるために使う比の値です。高尿酸血症の治療薬を選ぶときの参考になります。</v>
       </c>
       <c r="F86" t="str">
-        <v>原発性・二次性副甲状腺機能亢進症（腎不全に伴うものなど）</v>
+        <v>尿酸産生過剰型（0.8以上が目安）</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -4445,7 +4445,7 @@
         <v/>
       </c>
       <c r="I86" t="str">
-        <v>副甲状腺機能低下症</v>
+        <v>尿酸排泄低下型（0.4以下が目安）</v>
       </c>
       <c r="J86" t="str">
         <v/>
@@ -4454,45 +4454,45 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>骨粗鬆症の二次性原因（副甲状腺機能亢進症）を除外するための検査。カルシウム・リンと合わせて評価する</v>
+        <v>高尿酸血症は尿酸産生過剰型・排泄低下型・混合型に分類され、この比が目安になる。病型によって使う薬剤（尿酸生成抑制薬か尿酸排泄促進薬か）の選択が変わる</v>
       </c>
       <c r="M86" t="str">
-        <v>骨粗鬆症</v>
+        <v>高尿酸血症</v>
       </c>
       <c r="N86" t="str">
-        <v>PTH,副甲状腺ホルモン,パラトルモン</v>
+        <v>UUA,UCr,尿酸クリアランス,CUA,EUA,尿酸産生過剰型,尿酸排泄低下型</v>
       </c>
       <c r="O86" t="str">
-        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
+        <v>食事と栄養 p.180-189（第2部 痛風・高尿酸血症）</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>尿中NTX</v>
+        <v>ucOC（低カルボキシル化オステオカルシン）</v>
       </c>
       <c r="B87" t="str">
-        <v>NTX</v>
+        <v>ucOC</v>
       </c>
       <c r="C87" t="str">
-        <v>施設差が大きく一律の記載が難しい（尿中）</v>
+        <v>4.5 ng/mL未満（施設差あり）</v>
       </c>
       <c r="D87" t="str">
-        <v>骨が壊されるときに出る、骨吸収マーカーのひとつ</v>
+        <v>ビタミンKが不足していないかを反映する骨の指標</v>
       </c>
       <c r="E87" t="str">
-        <v>NTXは、骨が壊される（吸収される）ときに尿の中に出てくる物質です。骨粗鬆症の治療薬がどれくらい効いているかを確認するために使われます。</v>
+        <v>ucOCは、骨を作るために必要なビタミンKが体の中で足りているかどうかを反映する検査です。数値が高いとビタミンK不足が疑われます。</v>
       </c>
       <c r="F87" t="str">
-        <v>骨代謝回転の亢進（骨粗鬆症、閉経後など）</v>
+        <v>ビタミンK不足状態</v>
       </c>
       <c r="G87" t="str">
-        <v/>
+        <v>ビタミンK2製剤(骨粗鬆症治療薬)の適応が検討されているか確認する。ワルファリン服用中の患者では、納豆などビタミンKを多く含む食品の急な摂取量の変化を避けるよう説明する</v>
       </c>
       <c r="H87" t="str">
         <v/>
       </c>
       <c r="I87" t="str">
-        <v>骨吸収抑制薬（ビスホスホネート等）による治療効果</v>
+        <v/>
       </c>
       <c r="J87" t="str">
         <v/>
@@ -4501,13 +4501,13 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>治療開始後3〜6か月で再検し、薬の効果判定に使われる。TRACP-5bと同じ「骨を壊す側」の指標</v>
+        <v>ビタミンK2製剤（骨粗鬆症治療薬）の適応判断や効果判定に使われる</v>
       </c>
       <c r="M87" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="N87" t="str">
-        <v>NTX,尿中NTX,骨吸収マーカー</v>
+        <v>ucOC,オステオカルシン,ビタミンK</v>
       </c>
       <c r="O87" t="str">
         <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
@@ -4515,22 +4515,22 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>カルシトニン</v>
+        <v>PTH（副甲状腺ホルモン）</v>
       </c>
       <c r="B88" t="str">
-        <v>CT</v>
+        <v>PTH</v>
       </c>
       <c r="C88" t="str">
-        <v>男性 9.52 pg/mL未満、女性 6.40 pg/mL未満（施設差あり）</v>
+        <v>10〜65 pg/mL（施設差あり）</v>
       </c>
       <c r="D88" t="str">
-        <v>血液中のカルシウムを下げる方向に働くホルモン</v>
+        <v>血液中のカルシウム濃度を調節するホルモン</v>
       </c>
       <c r="E88" t="str">
-        <v>カルシトニンは、PTHとは逆に血液中のカルシウムを下げる方向に働くホルモンです。特定の甲状腺の病気（甲状腺髄様癌）がないかを調べる際にも使われます。</v>
+        <v>PTHは、血液中のカルシウム濃度を一定に保つために働くホルモンです。カルシウムが低くなると分泌が増え、骨からカルシウムを取り出したり、腎臓での再吸収を促したりして数値を戻そうとします。</v>
       </c>
       <c r="F88" t="str">
-        <v>甲状腺髄様癌、腎不全</v>
+        <v>原発性・二次性副甲状腺機能亢進症（腎不全に伴うものなど）</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -4539,7 +4539,7 @@
         <v/>
       </c>
       <c r="I88" t="str">
-        <v/>
+        <v>副甲状腺機能低下症</v>
       </c>
       <c r="J88" t="str">
         <v/>
@@ -4548,13 +4548,13 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>骨粗鬆症の二次性原因の除外目的で測定されることがある検査値。同名の薬剤（カルシトニン製剤）と混同しないよう注意</v>
+        <v>骨粗鬆症の二次性原因（副甲状腺機能亢進症）を除外するための検査。カルシウム・リンと合わせて評価する</v>
       </c>
       <c r="M88" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="N88" t="str">
-        <v>カルシトニン,CT</v>
+        <v>PTH,副甲状腺ホルモン,パラトルモン</v>
       </c>
       <c r="O88" t="str">
         <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
@@ -4562,22 +4562,22 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>DPD（デオキシピリジノリン）</v>
+        <v>尿中NTX</v>
       </c>
       <c r="B89" t="str">
-        <v>DPD</v>
+        <v>NTX</v>
       </c>
       <c r="C89" t="str">
         <v>施設差が大きく一律の記載が難しい（尿中）</v>
       </c>
       <c r="D89" t="str">
-        <v>骨のコラーゲンが壊れるときに出る、骨吸収マーカーのひとつ</v>
+        <v>骨が壊されるときに出る、骨吸収マーカーのひとつ</v>
       </c>
       <c r="E89" t="str">
-        <v>DPDも、骨が壊されるときに尿に出てくる物質の一つです。NTXと同じように、骨粗鬆症治療薬の効果を確認するために使われます。</v>
+        <v>NTXは、骨が壊される（吸収される）ときに尿の中に出てくる物質です。骨粗鬆症の治療薬がどれくらい効いているかを確認するために使われます。</v>
       </c>
       <c r="F89" t="str">
-        <v>骨代謝回転の亢進（骨粗鬆症など）</v>
+        <v>骨代謝回転の亢進（骨粗鬆症、閉経後など）</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -4586,7 +4586,7 @@
         <v/>
       </c>
       <c r="I89" t="str">
-        <v>骨吸収抑制薬による治療効果</v>
+        <v>骨吸収抑制薬（ビスホスホネート等）による治療効果</v>
       </c>
       <c r="J89" t="str">
         <v/>
@@ -4595,13 +4595,13 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>NTX・CTXと同じ「骨を壊す側」の指標。食事の影響を受けにくいとされる</v>
+        <v>治療開始後3〜6か月で再検し、薬の効果判定に使われる。TRACP-5bと同じ「骨を壊す側」の指標</v>
       </c>
       <c r="M89" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="N89" t="str">
-        <v>DPD,デオキシピリジノリン,骨吸収マーカー</v>
+        <v>NTX,尿中NTX,骨吸収マーカー</v>
       </c>
       <c r="O89" t="str">
         <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
@@ -4609,22 +4609,22 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>CTX</v>
+        <v>カルシトニン</v>
       </c>
       <c r="B90" t="str">
-        <v>CTX</v>
+        <v>CT</v>
       </c>
       <c r="C90" t="str">
-        <v>施設差が大きく一律の記載が難しい（血清・尿中）</v>
+        <v>男性 9.52 pg/mL未満、女性 6.40 pg/mL未満（施設差あり）</v>
       </c>
       <c r="D90" t="str">
-        <v>骨のコラーゲンが壊れるときに出る、骨吸収マーカーのひとつ</v>
+        <v>血液中のカルシウムを下げる方向に働くホルモン</v>
       </c>
       <c r="E90" t="str">
-        <v>CTXも、骨が壊されるときに血液や尿に出てくる物質です。骨粗鬆症治療薬（骨を壊すのを抑える薬）の効果を確認するために使われます。</v>
+        <v>カルシトニンは、PTHとは逆に血液中のカルシウムを下げる方向に働くホルモンです。特定の甲状腺の病気（甲状腺髄様癌）がないかを調べる際にも使われます。</v>
       </c>
       <c r="F90" t="str">
-        <v>骨代謝回転の亢進（骨粗鬆症など）</v>
+        <v>甲状腺髄様癌、腎不全</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -4633,7 +4633,7 @@
         <v/>
       </c>
       <c r="I90" t="str">
-        <v>骨吸収抑制薬による治療効果</v>
+        <v/>
       </c>
       <c r="J90" t="str">
         <v/>
@@ -4642,13 +4642,13 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>NTX・DPDと同じ「骨を壊す側」の指標。血清・尿中いずれでも測定されることがある</v>
+        <v>骨粗鬆症の二次性原因の除外目的で測定されることがある検査値。同名の薬剤（カルシトニン製剤）と混同しないよう注意</v>
       </c>
       <c r="M90" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="N90" t="str">
-        <v>CTX,骨吸収マーカー</v>
+        <v>カルシトニン,CT</v>
       </c>
       <c r="O90" t="str">
         <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
@@ -4656,22 +4656,22 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>P1NP</v>
+        <v>DPD（デオキシピリジノリン）</v>
       </c>
       <c r="B91" t="str">
-        <v>P1NP</v>
+        <v>DPD</v>
       </c>
       <c r="C91" t="str">
-        <v>施設差が大きく一律の記載が難しい（血清）</v>
+        <v>施設差が大きく一律の記載が難しい（尿中）</v>
       </c>
       <c r="D91" t="str">
-        <v>骨が新しく作られるときに出る、骨形成マーカーのひとつ</v>
+        <v>骨のコラーゲンが壊れるときに出る、骨吸収マーカーのひとつ</v>
       </c>
       <c r="E91" t="str">
-        <v>P1NPは、CTXなどとは逆に、骨が新しく作られるときに血液中に出てくる物質です。骨を作る力を高める薬（テリパラチドなど）の効果を確認するために使われます。</v>
+        <v>DPDも、骨が壊されるときに尿に出てくる物質の一つです。NTXと同じように、骨粗鬆症治療薬の効果を確認するために使われます。</v>
       </c>
       <c r="F91" t="str">
-        <v>骨代謝回転の亢進、骨形成促進薬による治療効果</v>
+        <v>骨代謝回転の亢進（骨粗鬆症など）</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -4680,7 +4680,7 @@
         <v/>
       </c>
       <c r="I91" t="str">
-        <v>骨形成の低下</v>
+        <v>骨吸収抑制薬による治療効果</v>
       </c>
       <c r="J91" t="str">
         <v/>
@@ -4689,13 +4689,13 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>TRACP-5b等「骨を壊す側」の指標とは逆の、「骨を作る側」の指標。骨形成促進薬（テリパラチド等）の効果判定に使われる</v>
+        <v>NTX・CTXと同じ「骨を壊す側」の指標。食事の影響を受けにくいとされる</v>
       </c>
       <c r="M91" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="N91" t="str">
-        <v>P1NP,骨形成マーカー</v>
+        <v>DPD,デオキシピリジノリン,骨吸収マーカー</v>
       </c>
       <c r="O91" t="str">
         <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
@@ -4703,22 +4703,22 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>抗甲状腺マイクロゾーム抗体（抗TPO抗体）</v>
+        <v>CTX</v>
       </c>
       <c r="B92" t="str">
-        <v>TPOAb</v>
+        <v>CTX</v>
       </c>
       <c r="C92" t="str">
-        <v>陰性（16 IU/mL未満程度、施設差あり）</v>
+        <v>施設差が大きく一律の記載が難しい（血清・尿中）</v>
       </c>
       <c r="D92" t="str">
-        <v>自分の甲状腺を攻撃する抗体が出ていないかを見る検査</v>
+        <v>骨のコラーゲンが壊れるときに出る、骨吸収マーカーのひとつ</v>
       </c>
       <c r="E92" t="str">
-        <v>この検査は、体の中に自分の甲状腺を誤って攻撃してしまう抗体がないかを見るものです。陽性の場合、橋本病（慢性甲状腺炎）など甲状腺の自己免疫的な炎症が背景にある可能性があります。</v>
+        <v>CTXも、骨が壊されるときに血液や尿に出てくる物質です。骨粗鬆症治療薬（骨を壊すのを抑える薬）の効果を確認するために使われます。</v>
       </c>
       <c r="F92" t="str">
-        <v>橋本病（慢性甲状腺炎）、バセドウ病などの自己免疫性甲状腺疾患</v>
+        <v>骨代謝回転の亢進（骨粗鬆症など）</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -4727,7 +4727,7 @@
         <v/>
       </c>
       <c r="I92" t="str">
-        <v/>
+        <v>骨吸収抑制薬による治療効果</v>
       </c>
       <c r="J92" t="str">
         <v/>
@@ -4736,36 +4736,36 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>陽性でも必ずしも甲状腺機能異常があるとは限らない。TSH・FT4など甲状腺ホルモンの数値と合わせて評価する</v>
+        <v>NTX・DPDと同じ「骨を壊す側」の指標。血清・尿中いずれでも測定されることがある</v>
       </c>
       <c r="M92" t="str">
-        <v>甲状腺疾患</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="N92" t="str">
-        <v>抗TPO抗体,抗甲状腺マイクロゾーム抗体,TPOAb,橋本病</v>
+        <v>CTX,骨吸収マーカー</v>
       </c>
       <c r="O92" t="str">
-        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>抗サイログロブリン抗体</v>
+        <v>P1NP</v>
       </c>
       <c r="B93" t="str">
-        <v>TgAb</v>
+        <v>P1NP</v>
       </c>
       <c r="C93" t="str">
-        <v>陰性（28 IU/mL未満程度、施設差あり）</v>
+        <v>施設差が大きく一律の記載が難しい（血清）</v>
       </c>
       <c r="D93" t="str">
-        <v>甲状腺のたんぱく質（サイログロブリン）への抗体が出ていないかを見る検査</v>
+        <v>骨が新しく作られるときに出る、骨形成マーカーのひとつ</v>
       </c>
       <c r="E93" t="str">
-        <v>この検査も、抗TPO抗体と同じく、甲状腺に対する自己免疫の有無を見るものです。あわせて調べることで橋本病などの診断の参考にします。</v>
+        <v>P1NPは、CTXなどとは逆に、骨が新しく作られるときに血液中に出てくる物質です。骨を作る力を高める薬（テリパラチドなど）の効果を確認するために使われます。</v>
       </c>
       <c r="F93" t="str">
-        <v>橋本病（慢性甲状腺炎）、バセドウ病などの自己免疫性甲状腺疾患</v>
+        <v>骨代謝回転の亢進、骨形成促進薬による治療効果</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -4774,7 +4774,7 @@
         <v/>
       </c>
       <c r="I93" t="str">
-        <v/>
+        <v>骨形成の低下</v>
       </c>
       <c r="J93" t="str">
         <v/>
@@ -4783,92 +4783,92 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>抗TPO抗体とあわせて測定されることが多い。単独の高値だけで治療方針が決まるわけではない</v>
+        <v>TRACP-5b等「骨を壊す側」の指標とは逆の、「骨を作る側」の指標。骨形成促進薬（テリパラチド等）の効果判定に使われる</v>
       </c>
       <c r="M93" t="str">
-        <v>甲状腺疾患</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="N93" t="str">
-        <v>抗サイログロブリン抗体,TgAb,橋本病</v>
+        <v>P1NP,骨形成マーカー</v>
       </c>
       <c r="O93" t="str">
-        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>血中薬物濃度（TDM）</v>
+        <v>抗甲状腺マイクロゾーム抗体（抗TPO抗体）</v>
       </c>
       <c r="B94" t="str">
-        <v>TDM</v>
+        <v>TPOAb</v>
       </c>
       <c r="C94" t="str">
-        <v>薬剤ごとに有効域が異なる（例：カルバマゼピン 4〜12 μg/mL、バルプロ酸 40〜100 μg/mL、フェニトイン 10〜20 μg/mL）</v>
+        <v>陰性（16 IU/mL未満程度、施設差あり）</v>
       </c>
       <c r="D94" t="str">
-        <v>治療域が狭い薬剤で、血液中の薬の濃度が効果域・中毒域のどちらにあるかを確認する検査</v>
+        <v>自分の甲状腺を攻撃する抗体が出ていないかを見る検査</v>
       </c>
       <c r="E94" t="str">
-        <v>この薬は効く量と副作用が出る量が近いため、血液中の薬の濃度を定期的に測って、ちょうどよい範囲に入っているかを確認します。数値が低いと効果が不十分になり、高いと副作用が出やすくなります。</v>
+        <v>この検査は、体の中に自分の甲状腺を誤って攻撃してしまう抗体がないかを見るものです。陽性の場合、橋本病（慢性甲状腺炎）など甲状腺の自己免疫的な炎症が背景にある可能性があります。</v>
       </c>
       <c r="F94" t="str">
-        <v>過量投与、代謝を妨げる薬剤との併用、肝機能低下による代謝低下</v>
+        <v>橋本病（慢性甲状腺炎）、バセドウ病などの自己免疫性甲状腺疾患</v>
       </c>
       <c r="G94" t="str">
-        <v>ふらつき、眠気、めまい、物が二重に見えるなどの中毒症状がないか確認する</v>
+        <v/>
       </c>
       <c r="H94" t="str">
         <v/>
       </c>
       <c r="I94" t="str">
-        <v>飲み忘れ、自己判断による減量、代謝を促進する薬剤との併用（相互作用）</v>
+        <v/>
       </c>
       <c r="J94" t="str">
-        <v>発作やてんかん症状の再発がないか確認し、飲み忘れがないか一緒に確認する</v>
+        <v/>
       </c>
       <c r="K94" t="str">
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>採血のタイミング（トラフ値かどうか）で数値の解釈が変わるため採血時点を確認する。カルバマゼピンは自己誘導により長期使用で濃度が下がることがある点にも注意</v>
+        <v>陽性でも必ずしも甲状腺機能異常があるとは限らない。TSH・FT4など甲状腺ホルモンの数値と合わせて評価する</v>
       </c>
       <c r="M94" t="str">
-        <v>てんかん</v>
+        <v>甲状腺疾患</v>
       </c>
       <c r="N94" t="str">
-        <v>TDM,血中薬物濃度,治療域,中毒域,カルバマゼピン,フェニトイン,バルプロ酸,抗てんかん薬</v>
+        <v>抗TPO抗体,抗甲状腺マイクロゾーム抗体,TPOAb,橋本病</v>
       </c>
       <c r="O94" t="str">
-        <v/>
+        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>アミラーゼ（AMY）</v>
+        <v>抗サイログロブリン抗体</v>
       </c>
       <c r="B95" t="str">
-        <v>AMY</v>
+        <v>TgAb</v>
       </c>
       <c r="C95" t="str">
-        <v>44〜132 U/L（施設差あり）</v>
+        <v>陰性（28 IU/mL未満程度、施設差あり）</v>
       </c>
       <c r="D95" t="str">
-        <v>膵臓や唾液腺から出る消化酵素。膵炎などで血液中に漏れ出す</v>
+        <v>甲状腺のたんぱく質（サイログロブリン）への抗体が出ていないかを見る検査</v>
       </c>
       <c r="E95" t="str">
-        <v>アミラーゼは、でんぷんを分解する消化酵素で、主に膵臓と唾液腺から作られます。膵臓に炎症が起きると血液中に漏れ出して数値が上がるため、膵炎の診断や経過観察に使われます。</v>
+        <v>この検査も、抗TPO抗体と同じく、甲状腺に対する自己免疫の有無を見るものです。あわせて調べることで橋本病などの診断の参考にします。</v>
       </c>
       <c r="F95" t="str">
-        <v>急性膵炎、慢性膵炎の急性増悪、耳下腺炎（おたふくかぜ）、腎不全</v>
+        <v>橋本病（慢性甲状腺炎）、バセドウ病などの自己免疫性甲状腺疾患</v>
       </c>
       <c r="G95" t="str">
-        <v>飲酒を控え、脂っこい食事を避けるよう伝える。強い腹痛・背部痛がある場合は急性膵炎の可能性もあるため早めの受診を勧める</v>
+        <v/>
       </c>
       <c r="H95" t="str">
-        <v>バルプロ酸、アザチオプリン、サイアザイド系・ループ利尿薬、ステロイドなど薬剤性膵炎の原因薬</v>
+        <v/>
       </c>
       <c r="I95" t="str">
-        <v>慢性膵炎の進行期（膵臓の機能低下）</v>
+        <v/>
       </c>
       <c r="J95" t="str">
         <v/>
@@ -4877,60 +4877,60 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>膵臓由来か唾液腺由来かを区別するには膵型アミラーゼ(P-AMY)を確認する。急性膵炎では強い腹痛・背部痛を伴うことが多く、飲酒歴の確認も重要</v>
+        <v>抗TPO抗体とあわせて測定されることが多い。単独の高値だけで治療方針が決まるわけではない</v>
       </c>
       <c r="M95" t="str">
-        <v/>
+        <v>甲状腺疾患</v>
       </c>
       <c r="N95" t="str">
-        <v>アミラーゼ,AMY,膵炎,急性膵炎</v>
+        <v>抗サイログロブリン抗体,TgAb,橋本病</v>
       </c>
       <c r="O95" t="str">
-        <v/>
+        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>間接ビリルビン</v>
+        <v>血中薬物濃度（TDM）</v>
       </c>
       <c r="B96" t="str">
-        <v>I-Bil</v>
+        <v>TDM</v>
       </c>
       <c r="C96" t="str">
-        <v>0.2〜0.8 mg/dL程度（施設差あり）</v>
+        <v>薬剤ごとに有効域が異なる（例：カルバマゼピン 4〜12 μg/mL、バルプロ酸 40〜100 μg/mL、フェニトイン 10〜20 μg/mL）</v>
       </c>
       <c r="D96" t="str">
-        <v>赤血球が壊れてできるビリルビンのうち、肝臓で処理される前の形</v>
+        <v>治療域が狭い薬剤で、血液中の薬の濃度が効果域・中毒域のどちらにあるかを確認する検査</v>
       </c>
       <c r="E96" t="str">
-        <v>間接ビリルビンは、赤血球が壊れてできたビリルビンが、まだ肝臓で処理される前の状態です。この値が高い場合、赤血球が通常より多く壊れている(溶血)か、肝臓での処理能力に生まれつきの体質差(体質性黄疸)がある可能性が考えられます。</v>
+        <v>この薬は効く量と副作用が出る量が近いため、血液中の薬の濃度を定期的に測って、ちょうどよい範囲に入っているかを確認します。数値が低いと効果が不十分になり、高いと副作用が出やすくなります。</v>
       </c>
       <c r="F96" t="str">
-        <v>溶血性疾患（自己免疫性溶血性貧血、血液型不適合輸血など）、体質性黄疸（ジルベール症候群）、新生児黄疸</v>
+        <v>過量投与、代謝を妨げる薬剤との併用、肝機能低下による代謝低下</v>
       </c>
       <c r="G96" t="str">
-        <v>皮膚や白目の黄染、尿の色の変化がないか確認する</v>
+        <v>ふらつき、眠気、めまい、物が二重に見えるなどの中毒症状がないか確認する</v>
       </c>
       <c r="H96" t="str">
         <v/>
       </c>
       <c r="I96" t="str">
-        <v/>
+        <v>飲み忘れ、自己判断による減量、代謝を促進する薬剤との併用（相互作用）</v>
       </c>
       <c r="J96" t="str">
-        <v/>
+        <v>発作やてんかん症状の再発がないか確認し、飲み忘れがないか一緒に確認する</v>
       </c>
       <c r="K96" t="str">
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>直接ビリルビンとの比率で原因を推測する（間接優位は溶血・体質性、直接優位は胆道系）。総ビリルビン・AST/ALTと合わせて評価する</v>
+        <v>採血のタイミング（トラフ値かどうか）で数値の解釈が変わるため採血時点を確認する。カルバマゼピンは自己誘導により長期使用で濃度が下がることがある点にも注意</v>
       </c>
       <c r="M96" t="str">
-        <v>肝機能</v>
+        <v>てんかん</v>
       </c>
       <c r="N96" t="str">
-        <v>間接ビリルビン,I-Bil,溶血</v>
+        <v>TDM,血中薬物濃度,治療域,中毒域,カルバマゼピン,フェニトイン,バルプロ酸,抗てんかん薬</v>
       </c>
       <c r="O96" t="str">
         <v/>
@@ -4938,31 +4938,31 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>直接ビリルビン</v>
+        <v>アミラーゼ（AMY）</v>
       </c>
       <c r="B97" t="str">
-        <v>D-Bil</v>
+        <v>AMY</v>
       </c>
       <c r="C97" t="str">
-        <v>0.0〜0.3 mg/dL程度（施設差あり）</v>
+        <v>44〜132 U/L（施設差あり）</v>
       </c>
       <c r="D97" t="str">
-        <v>肝臓で処理された後のビリルビン。胆道の詰まりで血液中に増える</v>
+        <v>膵臓や唾液腺から出る消化酵素。膵炎などで血液中に漏れ出す</v>
       </c>
       <c r="E97" t="str">
-        <v>直接ビリルビンは、肝臓で処理された後のビリルビンです。胆石や腫瘍などで胆汁の通り道（胆道）が詰まると、行き場を失って血液中に増え、皮膚や白目が黄色くなる黄疸として現れます。</v>
+        <v>アミラーゼは、でんぷんを分解する消化酵素で、主に膵臓と唾液腺から作られます。膵臓に炎症が起きると血液中に漏れ出して数値が上がるため、膵炎の診断や経過観察に使われます。</v>
       </c>
       <c r="F97" t="str">
-        <v>肝疾患、胆石など胆道の閉塞</v>
+        <v>急性膵炎、慢性膵炎の急性増悪、耳下腺炎（おたふくかぜ）、腎不全</v>
       </c>
       <c r="G97" t="str">
-        <v>皮膚や白目の黄染、白っぽい便、濃い茶色の尿がないか確認する</v>
+        <v>飲酒を控え、脂っこい食事を避けるよう伝える。強い腹痛・背部痛がある場合は急性膵炎の可能性もあるため早めの受診を勧める</v>
       </c>
       <c r="H97" t="str">
-        <v>胆汁うっ滞型の薬剤性肝障害を起こしうる抗菌薬、経口避妊薬</v>
+        <v>バルプロ酸、アザチオプリン、サイアザイド系・ループ利尿薬、ステロイドなど薬剤性膵炎の原因薬</v>
       </c>
       <c r="I97" t="str">
-        <v/>
+        <v>慢性膵炎の進行期（膵臓の機能低下）</v>
       </c>
       <c r="J97" t="str">
         <v/>
@@ -4971,13 +4971,13 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>直接優位の上昇は胆道系（胆石、腫瘍による閉塞）を、間接優位の上昇は溶血・体質性を疑う手がかりになる。γ-GTP・ALPと合わせて胆道系疾患を評価する</v>
+        <v>膵臓由来か唾液腺由来かを区別するには膵型アミラーゼ(P-AMY)を確認する。急性膵炎では強い腹痛・背部痛を伴うことが多く、飲酒歴の確認も重要</v>
       </c>
       <c r="M97" t="str">
-        <v>肝機能</v>
+        <v/>
       </c>
       <c r="N97" t="str">
-        <v>直接ビリルビン,D-Bil,胆石,胆道閉塞</v>
+        <v>アミラーゼ,AMY,膵炎,急性膵炎</v>
       </c>
       <c r="O97" t="str">
         <v/>
@@ -4985,148 +4985,242 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>亜鉛（Zn）</v>
+        <v>間接ビリルビン</v>
       </c>
       <c r="B98" t="str">
-        <v>Zn</v>
+        <v>I-Bil</v>
       </c>
       <c r="C98" t="str">
-        <v>80〜130 μg/dL程度（施設差あり）</v>
+        <v>0.2〜0.8 mg/dL程度（施設差あり）</v>
       </c>
       <c r="D98" t="str">
-        <v>味覚や皮膚、免疫に関わる微量ミネラル。高齢者や低栄養で不足しやすい</v>
+        <v>赤血球が壊れてできるビリルビンのうち、肝臓で処理される前の形</v>
       </c>
       <c r="E98" t="str">
-        <v>亜鉛は、味を感じる働きや皮膚・粘膜の健康、免疫の働きに関わる微量ミネラルです。不足すると、味がわかりにくくなったり（味覚障害）、傷が治りにくくなったりすることがあります。</v>
+        <v>間接ビリルビンは、赤血球が壊れてできたビリルビンが、まだ肝臓で処理される前の状態です。この値が高い場合、赤血球が通常より多く壊れている(溶血)か、肝臓での処理能力に生まれつきの体質差(体質性黄疸)がある可能性が考えられます。</v>
       </c>
       <c r="F98" t="str">
-        <v/>
+        <v>溶血性疾患（自己免疫性溶血性貧血、血液型不適合輸血など）、体質性黄疸（ジルベール症候群）、新生児黄疸</v>
       </c>
       <c r="G98" t="str">
-        <v/>
+        <v>皮膚や白目の黄染、尿の色の変化がないか確認する</v>
       </c>
       <c r="H98" t="str">
         <v/>
       </c>
       <c r="I98" t="str">
-        <v>低栄養、高齢による摂取不足、消化器手術後、亜鉛の吸収を妨げる薬剤（PPI、キレート形成する薬剤など）との併用</v>
+        <v/>
       </c>
       <c r="J98" t="str">
-        <v>味覚の変化（味を感じにくい、金属味がするなど）がないか確認する。牡蠣、赤身肉、レバーなど亜鉛を多く含む食品を意識するとよいことを伝える</v>
+        <v/>
       </c>
       <c r="K98" t="str">
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>薬剤性の亜鉛欠乏（PPI長期使用、D-ペニシラミン、一部の降圧薬など）に注意。亜鉛欠乏による味覚障害は原因薬剤の中止・亜鉛補充で改善することがある</v>
+        <v>直接ビリルビンとの比率で原因を推測する（間接優位は溶血・体質性、直接優位は胆道系）。総ビリルビン・AST/ALTと合わせて評価する</v>
       </c>
       <c r="M98" t="str">
-        <v/>
+        <v>肝機能</v>
       </c>
       <c r="N98" t="str">
-        <v>亜鉛,Zn,味覚障害,亜鉛欠乏</v>
+        <v>間接ビリルビン,I-Bil,溶血</v>
       </c>
       <c r="O98" t="str">
-        <v>食事と栄養 p.78（亜鉛）</v>
+        <v/>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>マグネシウム（Mg）</v>
+        <v>直接ビリルビン</v>
       </c>
       <c r="B99" t="str">
-        <v>Mg</v>
+        <v>D-Bil</v>
       </c>
       <c r="C99" t="str">
-        <v>1.8〜2.6 mg/dL程度（施設差あり）</v>
+        <v>0.0〜0.3 mg/dL程度（施設差あり）</v>
       </c>
       <c r="D99" t="str">
-        <v>骨や筋肉、神経の働きに関わるミネラル。低栄養や利尿薬で不足しやすい</v>
+        <v>肝臓で処理された後のビリルビン。胆道の詰まりで血液中に増える</v>
       </c>
       <c r="E99" t="str">
-        <v>マグネシウムは、骨や筋肉、神経の働きを支えるミネラルです。不足すると、こむら返りや不整脈、だるさなどの症状が出ることがあります。</v>
+        <v>直接ビリルビンは、肝臓で処理された後のビリルビンです。胆石や腫瘍などで胆汁の通り道（胆道）が詰まると、行き場を失って血液中に増え、皮膚や白目が黄色くなる黄疸として現れます。</v>
       </c>
       <c r="F99" t="str">
-        <v>腎不全、マグネシウム製剤（酸化マグネシウムなど）の過量投与</v>
+        <v>肝疾患、胆石など胆道の閉塞</v>
       </c>
       <c r="G99" t="str">
-        <v>腎機能低下がある患者で酸化マグネシウムなどの緩下剤を使用中は、傾眠・血圧低下などの高マグネシウム血症の症状がないか確認する</v>
+        <v>皮膚や白目の黄染、白っぽい便、濃い茶色の尿がないか確認する</v>
       </c>
       <c r="H99" t="str">
-        <v>マグネシウム含有制酸薬・下剤の過量(特に腎機能低下患者)</v>
+        <v>胆汁うっ滞型の薬剤性肝障害を起こしうる抗菌薬、経口避妊薬</v>
       </c>
       <c r="I99" t="str">
-        <v>低栄養、利尿薬の使用、慢性的な下痢、アルコール多飲、PPI長期使用</v>
+        <v/>
       </c>
       <c r="J99" t="str">
-        <v>こむら返りや動悸などの症状がないか確認する</v>
+        <v/>
       </c>
       <c r="K99" t="str">
-        <v>プロトンポンプ阻害薬(PPI)の長期使用、ループ利尿薬、サイアザイド系利尿薬、シスプラチン、アミノグリコシド系</v>
+        <v/>
       </c>
       <c r="L99" t="str">
-        <v>腎機能低下患者への酸化マグネシウム投与は高マグネシウム血症のリスクがあるため定期的なモニタリングが必要。PPI長期使用も低マグネシウム血症のリスク因子として知られる</v>
+        <v>直接優位の上昇は胆道系（胆石、腫瘍による閉塞）を、間接優位の上昇は溶血・体質性を疑う手がかりになる。γ-GTP・ALPと合わせて胆道系疾患を評価する</v>
       </c>
       <c r="M99" t="str">
-        <v>腎機能</v>
+        <v>肝機能</v>
       </c>
       <c r="N99" t="str">
-        <v>マグネシウム,Mg,酸化マグネシウム,こむら返り</v>
+        <v>直接ビリルビン,D-Bil,胆石,胆道閉塞</v>
       </c>
       <c r="O99" t="str">
-        <v>食事と栄養 p.84（マグネシウム）</v>
+        <v/>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
+        <v>亜鉛（Zn）</v>
+      </c>
+      <c r="B100" t="str">
+        <v>Zn</v>
+      </c>
+      <c r="C100" t="str">
+        <v>80〜130 μg/dL程度（施設差あり）</v>
+      </c>
+      <c r="D100" t="str">
+        <v>味覚や皮膚、免疫に関わる微量ミネラル。高齢者や低栄養で不足しやすい</v>
+      </c>
+      <c r="E100" t="str">
+        <v>亜鉛は、味を感じる働きや皮膚・粘膜の健康、免疫の働きに関わる微量ミネラルです。不足すると、味がわかりにくくなったり（味覚障害）、傷が治りにくくなったりすることがあります。</v>
+      </c>
+      <c r="F100" t="str">
+        <v/>
+      </c>
+      <c r="G100" t="str">
+        <v/>
+      </c>
+      <c r="H100" t="str">
+        <v/>
+      </c>
+      <c r="I100" t="str">
+        <v>低栄養、高齢による摂取不足、消化器手術後、亜鉛の吸収を妨げる薬剤（PPI、キレート形成する薬剤など）との併用</v>
+      </c>
+      <c r="J100" t="str">
+        <v>味覚の変化（味を感じにくい、金属味がするなど）がないか確認する。牡蠣、赤身肉、レバーなど亜鉛を多く含む食品を意識するとよいことを伝える</v>
+      </c>
+      <c r="K100" t="str">
+        <v/>
+      </c>
+      <c r="L100" t="str">
+        <v>薬剤性の亜鉛欠乏（PPI長期使用、D-ペニシラミン、一部の降圧薬など）に注意。亜鉛欠乏による味覚障害は原因薬剤の中止・亜鉛補充で改善することがある</v>
+      </c>
+      <c r="M100" t="str">
+        <v/>
+      </c>
+      <c r="N100" t="str">
+        <v>亜鉛,Zn,味覚障害,亜鉛欠乏</v>
+      </c>
+      <c r="O100" t="str">
+        <v>食事と栄養 p.78（亜鉛）</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>マグネシウム（Mg）</v>
+      </c>
+      <c r="B101" t="str">
+        <v>Mg</v>
+      </c>
+      <c r="C101" t="str">
+        <v>1.8〜2.6 mg/dL程度（施設差あり）</v>
+      </c>
+      <c r="D101" t="str">
+        <v>骨や筋肉、神経の働きに関わるミネラル。低栄養や利尿薬で不足しやすい</v>
+      </c>
+      <c r="E101" t="str">
+        <v>マグネシウムは、骨や筋肉、神経の働きを支えるミネラルです。不足すると、こむら返りや不整脈、だるさなどの症状が出ることがあります。</v>
+      </c>
+      <c r="F101" t="str">
+        <v>腎不全、マグネシウム製剤（酸化マグネシウムなど）の過量投与</v>
+      </c>
+      <c r="G101" t="str">
+        <v>腎機能低下がある患者で酸化マグネシウムなどの緩下剤を使用中は、傾眠・血圧低下などの高マグネシウム血症の症状がないか確認する</v>
+      </c>
+      <c r="H101" t="str">
+        <v>マグネシウム含有制酸薬・下剤の過量(特に腎機能低下患者)</v>
+      </c>
+      <c r="I101" t="str">
+        <v>低栄養、利尿薬の使用、慢性的な下痢、アルコール多飲、PPI長期使用</v>
+      </c>
+      <c r="J101" t="str">
+        <v>こむら返りや動悸などの症状がないか確認する</v>
+      </c>
+      <c r="K101" t="str">
+        <v>プロトンポンプ阻害薬(PPI)の長期使用、ループ利尿薬、サイアザイド系利尿薬、シスプラチン、アミノグリコシド系</v>
+      </c>
+      <c r="L101" t="str">
+        <v>腎機能低下患者への酸化マグネシウム投与は高マグネシウム血症のリスクがあるため定期的なモニタリングが必要。PPI長期使用も低マグネシウム血症のリスク因子として知られる</v>
+      </c>
+      <c r="M101" t="str">
+        <v>腎機能</v>
+      </c>
+      <c r="N101" t="str">
+        <v>マグネシウム,Mg,酸化マグネシウム,こむら返り</v>
+      </c>
+      <c r="O101" t="str">
+        <v>食事と栄養 p.84（マグネシウム）</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
         <v>骨密度</v>
       </c>
-      <c r="B100" t="str">
+      <c r="B102" t="str">
         <v>BMD,骨密度</v>
       </c>
-      <c r="C100" t="str">
+      <c r="C102" t="str">
         <v>YAM(若年成人平均値)80%以上:正常、70%以上80%未満:骨量減少、70%未満:骨粗鬆症</v>
       </c>
-      <c r="D100" t="str">
+      <c r="D102" t="str">
         <v>骨の中にカルシウムなどのミネラルがどれだけ詰まっているかを示す指標。20〜44歳の平均値(YAM)に対する割合(%)で評価する</v>
       </c>
-      <c r="E100" t="str">
+      <c r="E102" t="str">
         <v>骨密度は、骨の中にカルシウムなどのミネラルがどれだけしっかり詰まっているかを表す数値です。20〜44歳の若い方の平均値を100%として、ご自身の骨密度が何%かで示されます。70%未満になると「骨粗鬆症」と診断され、骨折しやすい状態と考えられます。</v>
       </c>
-      <c r="F100" t="str">
+      <c r="F102" t="str">
         <v>基本的に問題になることは少ない(まれに骨硬化症などの疾患)</v>
       </c>
-      <c r="G100" t="str">
-        <v/>
-      </c>
-      <c r="H100" t="str">
-        <v/>
-      </c>
-      <c r="I100" t="str">
+      <c r="G102" t="str">
+        <v/>
+      </c>
+      <c r="H102" t="str">
+        <v/>
+      </c>
+      <c r="I102" t="str">
         <v>骨粗鬆症、加齢による骨量減少、閉経後のエストロゲン低下、ステロイド長期使用、カルシウム・ビタミンD不足、運動不足、るいそう</v>
       </c>
-      <c r="J100" t="str">
+      <c r="J102" t="str">
         <v>カルシウム・ビタミンD・ビタミンKを意識した食事、荷重運動(ウォーキング等)を勧める。ステロイド長期服用中の場合は骨粗鬆症治療薬の併用が検討されているか確認する</v>
       </c>
-      <c r="K100" t="str">
-        <v/>
-      </c>
-      <c r="L100" t="str">
+      <c r="K102" t="str">
+        <v/>
+      </c>
+      <c r="L102" t="str">
         <v>YAM70%未満、または既存の脆弱性骨折がある場合に骨粗鬆症と診断され薬物治療の対象となる(日本骨粗鬆症学会・日本骨代謝学会・厚生労働省合同「原発性骨粗鬆症の診断基準 2012年度改訂版」)。ビスホスホネート製剤は起床時空腹時に十分な水(180mL程度)で服用し、服用後30分は横にならないよう指導する。ステロイドを長期服用中の患者は骨密度によらず骨粗鬆症治療薬の併用が推奨される場合がある(グルココルチコイド誘発性骨粗鬆症: GIOP)</v>
       </c>
-      <c r="M100" t="str">
+      <c r="M102" t="str">
         <v>骨粗鬆症</v>
       </c>
-      <c r="N100" t="str">
+      <c r="N102" t="str">
         <v>骨密度,BMD,YAM,若年成人平均値,骨粗鬆症,DXA</v>
       </c>
-      <c r="O100" t="str">
+      <c r="O102" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O100"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O102"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/検査値リファレンス初期データ.xlsx
+++ b/検査値リファレンス初期データ.xlsx
@@ -2541,31 +2541,31 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>C－ペプチド（血中）</v>
+        <v>尿蛋白定量</v>
       </c>
       <c r="B46" t="str">
-        <v>CPR</v>
+        <v>U-Pro定量,蛋白/Cr比</v>
       </c>
       <c r="C46" t="str">
-        <v>空腹時 0.6〜3.0 ng/mL（施設差あり）</v>
+        <v>0.15 g/gCr未満</v>
       </c>
       <c r="D46" t="str">
-        <v>自分の膵臓がどれくらいインスリンを作れているかを表す指標</v>
+        <v>随時尿から尿蛋白の量を具体的な数値として評価する検査。ネフローゼ等の重症度判定に使う</v>
       </c>
       <c r="E46" t="str">
-        <v>この検査は、ご自身の膵臓がどれくらいインスリンを作る力を持っているかを見るものです。数値が低いほど、体の中で作れるインスリンが少ないことを示します。</v>
+        <v>これは、尿に出ているたんぱくの量を具体的な数値で見る検査です。試験紙での陽性・陰性の判定だけでなく、実際にどれくらいの量が出ているかを把握できます。</v>
       </c>
       <c r="F46" t="str">
-        <v>インスリン抵抗性が強い状態（初期の2型糖尿病など）</v>
+        <v>腎症の進行（糖尿病性腎症、慢性腎臓病など）、ネフローゼ症候群（3.5 g/gCr以上が目安）</v>
       </c>
       <c r="G46" t="str">
-        <v/>
+        <v>持続する場合は塩分の摂りすぎに注意し、むくみの有無も確認する。腎臓内科でのフォロー状況もあわせて確認する</v>
       </c>
       <c r="H46" t="str">
-        <v/>
+        <v>NSAIDs、造影剤、アミノグリコシド系、バンコマイシン</v>
       </c>
       <c r="I46" t="str">
-        <v>膵臓のインスリン分泌能低下（1型糖尿病、糖尿病の進行）</v>
+        <v/>
       </c>
       <c r="J46" t="str">
         <v/>
@@ -2574,13 +2574,13 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>インスリン分泌能の評価に使われる。数値が低いほどインスリン治療の必要性が高いと判断される目安になる</v>
+        <v>CKD診療ガイドラインの重症度分類（尿蛋白量による区分）にも使われる定量指標。試験紙法の半定量結果より治療効果判定に適する</v>
       </c>
       <c r="M46" t="str">
-        <v>糖尿病</v>
+        <v>腎機能,糖尿病</v>
       </c>
       <c r="N46" t="str">
-        <v>C-ペプチド,Cペプチド,CPR,C-peptide,血中CPR,インスリン分泌</v>
+        <v>尿蛋白,随時尿,定量,蛋白クレアチニン比,ネフローゼ</v>
       </c>
       <c r="O46" t="str">
         <v/>
@@ -2588,22 +2588,22 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>C－ペプチドインデックス</v>
+        <v>尿pH</v>
       </c>
       <c r="B47" t="str">
-        <v>CPI</v>
+        <v>尿pH</v>
       </c>
       <c r="C47" t="str">
-        <v>1.2以上が目安(施設・測定条件により異なる)</v>
+        <v>4.5〜7.5程度（弱酸性が多い）</v>
       </c>
       <c r="D47" t="str">
-        <v>血糖値に対してどれくらいインスリンを分泌できているかを表す指標。低いほどインスリン治療の必要性が高い</v>
+        <v>尿の酸性・アルカリ性の度合い。食事や感染症、体の状態を反映する</v>
       </c>
       <c r="E47" t="str">
-        <v>これは、血糖値の高さに対して、体がどれくらいインスリンを作れているかを見る指標です。数値が低いほど、自分の膵臓だけでは血糖値に見合うインスリンを十分に作れていない可能性が高く、インスリン治療が必要かどうかの判断材料になります。</v>
+        <v>尿のpHは酸性・アルカリ性のバランスを表します。食事の内容や感染症、体の代謝状態によって変化します。単独で大きな問題を示すことは少ない検査です。</v>
       </c>
       <c r="F47" t="str">
-        <v>通常、臨床的意義は乏しい</v>
+        <v>尿路感染症（尿素分解菌によるもの）、野菜中心の食事、過換気</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2612,22 +2612,22 @@
         <v/>
       </c>
       <c r="I47" t="str">
-        <v>内因性インスリン分泌能の低下(1.2未満でインスリン治療の適応を検討する目安、0.8未満はインスリン療法が強く推奨される目安)</v>
+        <v>高たんぱく食、糖尿病性ケトアシドーシス、痛風発作時（酸性尿は尿酸結石のリスクを高める）</v>
       </c>
       <c r="J47" t="str">
-        <v>インスリン治療の必要性について医師からどのように説明を受けているか確認する</v>
+        <v>痛風・尿酸結石がある場合は、野菜など尿をアルカリ化する食品を意識するとよいことを伝える</v>
       </c>
       <c r="K47" t="str">
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>CPI＝血中Cペプチド(ng/mL)÷血糖値(mg/dL)×100 で算出する。空腹時に測定するのが基本で、境界値付近では食事負荷の影響を受けるため、複数回の評価や随時尿中CPRとあわせて判断することもある</v>
+        <v>高尿酸血症・尿酸結石の患者では尿pHが酸性に傾いていないか確認する。尿アルカリ化薬（ウラリットなど）の効果判定にも使う</v>
       </c>
       <c r="M47" t="str">
-        <v>糖尿病</v>
+        <v>高尿酸血症</v>
       </c>
       <c r="N47" t="str">
-        <v>CPI,Cペプチドインデックス,C-ペプチドインデックス,インスリン分泌能,インスリン治療</v>
+        <v>尿pH,尿酸性度,尿アルカリ化,ウラリット</v>
       </c>
       <c r="O47" t="str">
         <v/>
@@ -2635,46 +2635,46 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>白血球数（WBC）</v>
+        <v>尿ケトン体</v>
       </c>
       <c r="B48" t="str">
-        <v>WBC</v>
+        <v>尿ケトン,Ket</v>
       </c>
       <c r="C48" t="str">
-        <v>3,300〜8,600 /μL程度（施設差あり）</v>
+        <v>陰性（－）</v>
       </c>
       <c r="D48" t="str">
-        <v>体を細菌やウイルスから守る免疫細胞の数で、感染や炎症、薬剤の影響を反映する</v>
+        <v>体がブドウ糖の代わりに脂肪を分解してエネルギーを作っているサイン</v>
       </c>
       <c r="E48" t="str">
-        <v>白血球は体に入ってきた細菌やウイルスと戦う免疫細胞です。感染症や炎症があると増え、逆に一部のお薬の副作用や骨髄の働きが落ちると減ることがあります。</v>
+        <v>この検査は、体が糖の代わりに脂肪を使ってエネルギーを作っていないかを見るものです。陽性が続くときは、食事や水分、インスリンの使い方を確認する必要があります。</v>
       </c>
       <c r="F48" t="str">
-        <v>感染症、炎症、ステロイド使用、喫煙、白血病などの血液疾患</v>
+        <v>糖尿病の血糖コントロール不良（シックデイ・インスリン不足）、極端な糖質制限、絶食、嘔吐・下痢による脱水</v>
       </c>
       <c r="G48" t="str">
-        <v>発熱や体の痛みなど感染症状がないか確認する</v>
+        <v>糖尿病治療中の場合はシックデイ時の対応(インスリンを自己中断しない、水分摂取を続けるなど)を確認する。体調不良時の対応方法を事前に説明しておく</v>
       </c>
       <c r="H48" t="str">
-        <v>ステロイド、G-CSF製剤、炭酸リチウム</v>
+        <v>SGLT2阻害薬(特に絶食・シックデイ時の正常血糖ケトアシドーシスに注意)</v>
       </c>
       <c r="I48" t="str">
-        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、メルカゾールなど薬剤性の無顆粒球症、再生不良性貧血、ウイルス感染</v>
+        <v/>
       </c>
       <c r="J48" t="str">
-        <v>発熱、のどの痛みなど感染症状の初期サインがないか確認する。人混みを避け、手洗い・うがいを徹底するよう伝える</v>
+        <v/>
       </c>
       <c r="K48" t="str">
-        <v>抗がん剤、メルカゾール(無顆粒球症)、クロザピン(定期的な血球モニタリング必須)、サラゾスルファピリジン</v>
+        <v/>
       </c>
       <c r="L48" t="str">
-        <v>メルカゾール（チアマゾール）は無顆粒球症の重大な副作用があり、発熱・のどの痛みが出たらすぐ受診するよう指導する。抗がん剤・免疫抑制剤・抗てんかん薬（カルバマゼピンなど）使用中も定期的なモニタリングが必要</v>
+        <v>陽性かつ高血糖・全身倦怠感が強い場合は糖尿病性ケトアシドーシスの可能性があり緊急性が高い。シックデイルールの説明歴を確認する</v>
       </c>
       <c r="M48" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>糖尿病</v>
       </c>
       <c r="N48" t="str">
-        <v>白血球,WBC,好中球,感染症,白血病,無顆粒球症,骨髄抑制</v>
+        <v>尿ケトン体,ケトン体,Ket,シックデイ,ケトアシドーシス</v>
       </c>
       <c r="O48" t="str">
         <v/>
@@ -2682,328 +2682,328 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>赤血球数</v>
+        <v>ウロビリノーゲン</v>
       </c>
       <c r="B49" t="str">
-        <v>RBC</v>
+        <v>Uro</v>
       </c>
       <c r="C49" t="str">
-        <v>男性 435〜555万/μL、女性 386〜492万/μL程度（施設差あり）</v>
+        <v>正常（±）程度</v>
       </c>
       <c r="D49" t="str">
-        <v>血液中で酸素を運ぶ細胞の数。ヘモグロビン・ヘマトクリットと合わせて貧血・多血症を評価する</v>
+        <v>肝臓や胆道、赤血球の壊れ方の状態を反映する尿検査項目</v>
       </c>
       <c r="E49" t="str">
-        <v>赤血球は、肺で受け取った酸素を全身に運ぶ血液の細胞です。数が少ないと貧血、多いと多血症が疑われます。ヘモグロビンやヘマトクリットと合わせて総合的に評価します。</v>
+        <v>ウロビリノーゲンは、赤血球やビリルビンが体の中で処理される過程でできる物質です。肝臓の働きが悪くなったり、赤血球が壊れやすくなったりすると、尿の中の量が変化します。</v>
       </c>
       <c r="F49" t="str">
-        <v>脱水、多血症（真性多血症、二次性多血症）、喫煙</v>
+        <v>溶血性疾患（赤血球の破壊亢進）、肝機能障害</v>
       </c>
       <c r="G49" t="str">
-        <v>脱水が疑われる場合はこまめな水分摂取を勧める（水分制限がある場合を除く）</v>
+        <v/>
       </c>
       <c r="H49" t="str">
         <v/>
       </c>
       <c r="I49" t="str">
-        <v>貧血（鉄欠乏性貧血、腎性貧血など）、出血</v>
+        <v>胆道閉塞（胆汁が腸に流れず、ウロビリノーゲンが作られない状態）</v>
       </c>
       <c r="J49" t="str">
-        <v>ヘモグロビンと同様に、出血や食事量低下がないか確認する</v>
+        <v/>
       </c>
       <c r="K49" t="str">
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>ヘモグロビン・ヘマトクリットと同じ方向に動くことが多い。赤血球数だけでなくMCV・MCH・MCHCと合わせて貧血のタイプ(小球性・正球性・大球性)を判断する</v>
+        <v>完全に陰性の場合は胆道閉塞を疑う所見の一つ。肝機能（AST/ALT/ビリルビン）と合わせて評価する</v>
       </c>
       <c r="M49" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>肝機能</v>
       </c>
       <c r="N49" t="str">
-        <v>赤血球,RBC,貧血,多血症</v>
+        <v>ウロビリノーゲン,Uro,溶血,胆道閉塞,肝機能</v>
       </c>
       <c r="O49" t="str">
-        <v>食事と栄養 p.151-164（第2部 貧血）</v>
+        <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ヘモグロビン濃度</v>
+        <v>尿潜血反応</v>
       </c>
       <c r="B50" t="str">
-        <v>Hb</v>
+        <v>尿潜血,U-OB</v>
       </c>
       <c r="C50" t="str">
-        <v>男性 13.5〜17.5 g/dL、女性 11.5〜15.0 g/dL</v>
+        <v>陰性（－）</v>
       </c>
       <c r="D50" t="str">
-        <v>血液の中で酸素を運ぶ役割をしている。この値が低い状態が貧血。</v>
+        <v>尿に血液（赤血球）が混じっていないかを見る検査</v>
       </c>
       <c r="E50" t="str">
-        <v>ヘモグロビンは、血液の中で酸素を全身に運ぶ役割をしている赤い色素です。この値が低い状態が貧血で、体がだるくなったり、階段で息切れしやすくなったりします。</v>
+        <v>この検査は、尿に目に見えないくらいの微量の血液が混じっていないかを調べるものです。陽性の場合、腎臓や膀胱、尿路のどこかに炎症や結石などがある可能性があります。</v>
       </c>
       <c r="F50" t="str">
-        <v/>
+        <v>尿路結石、膀胱炎などの尿路感染症、腎炎、腫瘍、月経血の混入、激しい運動後</v>
       </c>
       <c r="G50" t="str">
-        <v/>
+        <v>排尿時の痛みや頻尿、目に見える血尿の有無を確認する。女性は月経の時期と重なっていないか確認する</v>
       </c>
       <c r="H50" t="str">
-        <v/>
+        <v>ワルファリン、DOAC、抗血小板薬など出血傾向を強める薬剤の服用状況を確認</v>
       </c>
       <c r="I50" t="str">
-        <v>鉄欠乏性貧血、出血、腎性貧血、骨髄の造血機能低下</v>
+        <v/>
       </c>
       <c r="J50" t="str">
-        <v>鉄分の多い食品(レバー・赤身肉・魚・ほうれん草など)を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える。鉄剤は数値が正常化した後も体内に鉄を貯蔵するため2〜3か月程度は継続が必要なことを説明する</v>
+        <v/>
       </c>
       <c r="K50" t="str">
-        <v>NSAIDs・抗凝固薬・抗血小板薬(消化管出血のリスク)、抗がん剤、ST合剤</v>
+        <v/>
       </c>
       <c r="L50" t="str">
-        <v>原因（出血・食事量低下など）の確認が重要。腎機能低下がある場合は鉄不足以外が原因のこともある。鉄剤はヘモグロビンが正常化した後も2〜3か月程度は継続することが多い（鉄の貯蔵分を補うため。途中でやめると再び貧血になりやすい）</v>
+        <v>陽性でも尿沈渣で赤血球が確認されない場合は偽陽性（ミオグロビン尿など）のこともある。持続する場合は泌尿器科的な精査が必要</v>
       </c>
       <c r="M50" t="str">
-        <v>鉄欠乏性貧血,抗血小板療法,抗凝固療法（心房細動・血栓症）</v>
+        <v>腎機能</v>
       </c>
       <c r="N50" t="str">
-        <v>ヘモグロビン,Hb,貧血,鉄剤,鉄欠乏性貧血</v>
+        <v>尿潜血,潜血反応,U-OB,血尿,尿路結石,膀胱炎</v>
       </c>
       <c r="O50" t="str">
-        <v>食事と栄養 p.151-164（第2部 貧血）</v>
+        <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ヘマトクリット値</v>
+        <v>尿糖（半定量）</v>
       </c>
       <c r="B51" t="str">
-        <v>Ht,Hct</v>
+        <v>尿糖,U-Glu</v>
       </c>
       <c r="C51" t="str">
-        <v>男性 40〜50%、女性 35〜45%</v>
+        <v>陰性（－）</v>
       </c>
       <c r="D51" t="str">
-        <v>血液全体のうち赤血球が占める体積の割合。貧血・脱水の指標</v>
+        <v>尿に糖が漏れ出ていないかを見る検査。血糖値がかなり高いと陽性になる</v>
       </c>
       <c r="E51" t="str">
-        <v>ヘマトクリットは、血液全体のうち赤血球が占める割合を表す数値です。この値が低いと貧血、高いと脱水や血液が濃くなっている状態が疑われます。</v>
+        <v>通常、糖は尿にはほとんど出ませんが、血糖値がかなり高くなると尿にあふれ出るようになります。血糖コントロールの目安の一つです。</v>
       </c>
       <c r="F51" t="str">
-        <v>脱水、多血症（真性多血症、二次性多血症）、喫煙</v>
+        <v>糖尿病（血糖値が腎臓で再吸収できる量を超えている状態）、腎性糖尿（血糖値が正常でも体質的に出ることがある）、SGLT2阻害薬服用中（薬の作用で意図的に糖を排泄するため陽性になるのが正常）</v>
       </c>
       <c r="G51" t="str">
-        <v>脱水が疑われる場合はこまめな水分摂取を勧める（水分制限がある場合を除く）</v>
+        <v>SGLT2阻害薬（フォシーガ、ジャディアンスなど）服用中は、陽性が薬の効果によるものであることを説明する。脱水や尿路感染の症状がないかも確認する</v>
       </c>
       <c r="H51" t="str">
-        <v/>
+        <v>SGLT2阻害薬(薬理作用による陽性であれば想定内であることを説明)</v>
       </c>
       <c r="I51" t="str">
-        <v>貧血（鉄欠乏性貧血、腎性貧血など）、出血</v>
+        <v/>
       </c>
       <c r="J51" t="str">
-        <v>ヘモグロビンと同様に、出血や食事量低下がないか確認する</v>
+        <v/>
       </c>
       <c r="K51" t="str">
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>ヘモグロビン・赤血球数と合わせて評価する。3つの値は同じ方向に動くことが多く、脱水があると貧血が見かけ上隠れることがある</v>
+        <v>SGLT2阻害薬服用中は尿糖陽性が治療効果として想定内であることを患者に伝える。血糖値・HbA1cと合わせて評価する</v>
       </c>
       <c r="M51" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>糖尿病</v>
       </c>
       <c r="N51" t="str">
-        <v>ヘマトクリット,Ht,Hct,貧血,脱水,多血症</v>
+        <v>尿糖,糖半定量,U-Glu,腎性糖尿,SGLT2</v>
       </c>
       <c r="O51" t="str">
-        <v>食事と栄養 p.151-164（第2部 貧血）</v>
+        <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>MCV</v>
+        <v>尿中微量アルブミン</v>
       </c>
       <c r="B52" t="str">
-        <v>MCV</v>
+        <v>U-Alb,MAU</v>
       </c>
       <c r="C52" t="str">
-        <v>79〜100 fL</v>
+        <v>30 mg/gCr未満（尿中アルブミン/クレアチニン比）</v>
       </c>
       <c r="D52" t="str">
-        <v>赤血球1個の大きさ</v>
+        <v>通常の尿蛋白検査では見つからない、ごく早期の腎症のサイン</v>
       </c>
       <c r="E52" t="str">
-        <v>MCVは赤血球1個あたりの大きさを表す数値です。貧血があるとき、この数値で「小さい貧血」か「大きい貧血」かを見分けることができ、原因を絞り込む手がかりになります。</v>
+        <v>この検査は、通常の尿検査ではまだ分からないくらい早い段階の腎臓の変化を見つけるためのものです。数値が高いと、腎症の初期のサインである可能性があります。</v>
       </c>
       <c r="F52" t="str">
-        <v/>
+        <v>糖尿病性腎症の早期段階、高血圧</v>
       </c>
       <c r="G52" t="str">
-        <v/>
+        <v>血糖・血圧のコントロール状況を確認する。減塩や適正体重の維持など生活習慣の見直しも早期腎症の進行予防に役立つことを伝える</v>
       </c>
       <c r="H52" t="str">
-        <v/>
+        <v>NSAIDsなど腎機能を悪化させる薬剤。ACE阻害薬・ARB・SGLT2阻害薬は低下させる方向に働く</v>
       </c>
       <c r="I52" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v/>
       </c>
       <c r="J52" t="str">
-        <v>鉄分の多い食品(レバー・赤身肉・魚・ほうれん草など)と、吸収を助けるビタミンC(柑橘類・芋類等)を一緒に摂るよう伝える</v>
+        <v/>
       </c>
       <c r="K52" t="str">
         <v/>
       </c>
       <c r="L52" t="str">
-        <v/>
+        <v>糖尿病腎症の早期発見に重要な検査。血糖・血圧コントロールで改善しうる段階なので、早期介入の意義を伝える</v>
       </c>
       <c r="M52" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>糖尿病,腎機能</v>
       </c>
       <c r="N52" t="str">
-        <v>MCV,赤血球指数,貧血</v>
+        <v>微量アルブミン,U-Alb,MAU,糖尿病性腎症,早期腎症</v>
       </c>
       <c r="O52" t="str">
-        <v>食事と栄養 p.151-164（第2部 貧血）</v>
+        <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>MCH</v>
+        <v>C反応性蛋白（CRP）</v>
       </c>
       <c r="B53" t="str">
-        <v>MCH</v>
+        <v>CRP</v>
       </c>
       <c r="C53" t="str">
-        <v>26.3〜34.3 pg</v>
+        <v>0.3 mg/dL未満（施設差あり）</v>
       </c>
       <c r="D53" t="str">
-        <v>赤血球1個に含まれるヘモグロビン量</v>
+        <v>体のどこかに炎症や感染が起きていないかを鋭敏に反映する数値</v>
       </c>
       <c r="E53" t="str">
-        <v>MCHは赤血球1個の中に含まれるヘモグロビン（酸素を運ぶ色素）の量を表す数値です。MCVと同じく、貧血の種類を見分けるのに使われます。</v>
+        <v>CRPは、体に炎症や感染が起きると数時間〜半日程度で急激に上昇する数値です。風邪のようなウイルス感染から細菌感染、体のどこかの炎症まで、幅広く反応するため、体調の変化を早期に捉える手がかりになります。</v>
       </c>
       <c r="F53" t="str">
-        <v/>
+        <v>細菌感染症、ウイルス感染症、自己免疫疾患（関節リウマチなど）、悪性腫瘍、組織の損傷（術後・心筋梗塞など）</v>
       </c>
       <c r="G53" t="str">
-        <v/>
+        <v>発熱、痛み、腫れなど炎症症状の有無を確認する</v>
       </c>
       <c r="H53" t="str">
         <v/>
       </c>
       <c r="I53" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v/>
       </c>
       <c r="J53" t="str">
-        <v>鉄分の多い食品(レバー・赤身肉・魚・ほうれん草など)と、吸収を助けるビタミンC(柑橘類・芋類等)を一緒に摂るよう伝える</v>
+        <v/>
       </c>
       <c r="K53" t="str">
         <v/>
       </c>
       <c r="L53" t="str">
-        <v/>
+        <v>白血球数と合わせて感染・炎症の程度を評価する。上昇・低下のタイミングは白血球より半日〜1日程度遅れる傾向があるため、経過を追う際は採血のタイミングに注意</v>
       </c>
       <c r="M53" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v/>
       </c>
       <c r="N53" t="str">
-        <v>MCH,赤血球指数,貧血</v>
+        <v>CRP,炎症,感染</v>
       </c>
       <c r="O53" t="str">
-        <v>食事と栄養 p.151-164（第2部 貧血）</v>
+        <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>MCHC</v>
+        <v>PT-INR（プロトロンビン時間国際標準比）</v>
       </c>
       <c r="B54" t="str">
-        <v>MCHC</v>
+        <v>PT-INR,INR</v>
       </c>
       <c r="C54" t="str">
-        <v>31.6〜36.6 %</v>
+        <v>治療域の目安 1.6〜3.0（ワルファリン服用時。年齢・疾患により異なる）</v>
       </c>
       <c r="D54" t="str">
-        <v>単位容積あたりの赤血球に含まれるヘモグロビン濃度</v>
+        <v>血液の固まりやすさを表す数値で、ワルファリンの効き具合を確認するために使う</v>
       </c>
       <c r="E54" t="str">
-        <v>MCHCは、赤血球の中にヘモグロビンがどれくらい濃く詰まっているかを表す数値です。鉄が不足すると、この濃度も薄くなる傾向があります。</v>
+        <v>PT-INRは血液が固まるまでの時間をもとにした数値で、ワルファリンというお薬を飲んでいる方の効き具合を確認するために測ります。数値が高いほど血液が固まりにくく出血しやすい状態、低いほど血栓ができやすい状態を示します。</v>
       </c>
       <c r="F54" t="str">
-        <v/>
+        <v>ワルファリンの効きすぎ、肝機能低下、ビタミンK不足、納豆・青汁など摂取量の変化</v>
       </c>
       <c r="G54" t="str">
-        <v/>
+        <v>歯ぐきや鼻からの出血、あざ、黒い便などの出血症状がないか確認する。納豆・クロレラ・青汁などビタミンKを多く含む食品の摂取状況を確認する</v>
       </c>
       <c r="H54" t="str">
-        <v/>
+        <v>ワルファリンの過量。ワルファリン服用中はST合剤・マクロライド系・フルコナゾール等の相互作用やビタミンK摂取量の変化にも注意</v>
       </c>
       <c r="I54" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>ワルファリンの効き不足、飲み忘れ、ビタミンK摂取量の急激な増加</v>
       </c>
       <c r="J54" t="str">
-        <v>鉄分の多い食品(レバー・赤身肉・魚・ほうれん草など)と、吸収を助けるビタミンC(柑橘類・芋類等)を一緒に摂るよう伝える</v>
+        <v>服薬状況（飲み忘れ）を確認する。片側のむくみ・しびれ・胸痛など血栓症状がないか確認する</v>
       </c>
       <c r="K54" t="str">
-        <v/>
+        <v>ワルファリン服用中で低値の場合は効果不十分の可能性。ビタミンK摂取量の変化や、リファンピシン・カルバマゼピン・バルビツール酸系など代謝を促進する薬との併用を確認</v>
       </c>
       <c r="L54" t="str">
-        <v/>
+        <v>治療域は疾患・年齢によって異なる（例：非弁膜症性心房細動の高齢者では1.6〜2.6が目安になることが多い）。多くの薬剤・食品と相互作用があるため新規薬剤追加時は必ず確認する。DOAC（エリキュース、リクシアナ、プラザキサなど）ではPT-INRのモニタリングは不要</v>
       </c>
       <c r="M54" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>抗凝固療法（心房細動・血栓症）</v>
       </c>
       <c r="N54" t="str">
-        <v>MCHC,赤血球指数,貧血</v>
+        <v>PT-INR,INR,プロトロンビン時間,ワルファリン,ワーファリン,抗凝固</v>
       </c>
       <c r="O54" t="str">
-        <v>食事と栄養 p.151-164（第2部 貧血）</v>
+        <v>食事と栄養 p.221（心疾患Q93 ワルファリン服用中のビタミンK摂取）</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>血小板数</v>
+        <v>骨型酒石酸抵抗性フォスファターゼ（TRACP-5b）</v>
       </c>
       <c r="B55" t="str">
-        <v>Plt</v>
+        <v>TRACP-5b</v>
       </c>
       <c r="C55" t="str">
-        <v>15.0〜35.0万/μL程度（施設差あり）</v>
+        <v>120〜420 mU/dL</v>
       </c>
       <c r="D55" t="str">
-        <v>出血を止める働きをする血液成分で、少なすぎると出血しやすくなる</v>
+        <v>骨がどれくらい壊されているかを見る検査。骨は「古い骨を壊して新しい骨を作る」入れ替えを繰り返しており、骨を壊す細胞が活発だとこの物質が血液中に増える。</v>
       </c>
       <c r="E55" t="str">
-        <v>血小板は、血管が傷ついたときに集まって血を止める役割をする血液の成分です。数が少ないとあざができやすくなったり、出血が止まりにくくなったりします。抗血小板薬や抗がん剤を使っている方では、定期的にチェックすることが大切です。</v>
+        <v>この検査は、骨がどれくらい早く減っていないかを見るものです。数値が高いと、骨が弱くなりやすい状態の目安になります。</v>
       </c>
       <c r="F55" t="str">
-        <v>炎症性疾患、鉄欠乏性貧血、脾摘後、骨髄増殖性疾患</v>
+        <v>骨粗鬆症、骨代謝回転（骨がこわれるスピード）が活発な状態</v>
       </c>
       <c r="G55" t="str">
-        <v>出血傾向はなく経過観察でよいことが多いが、片側の腫れ・しびれなど血栓症状がないかも念のため確認する</v>
+        <v>カルシウム・ビタミンDの摂取や、適度な荷重運動（ウォーキングなど）を意識するよう伝える</v>
       </c>
       <c r="H55" t="str">
         <v/>
       </c>
       <c r="I55" t="str">
-        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、肝硬変・脾機能亢進、再生不良性貧血、抗てんかん薬（バルプロ酸など）の副作用、ITP（特発性血小板減少性紫斑病）</v>
+        <v/>
       </c>
       <c r="J55" t="str">
-        <v>あざができやすい、歯ぐきや鼻からの出血が増えていないか確認する。強い運動や転倒によるけがに注意するよう伝え、歯みがきは柔らかめのブラシを勧める</v>
+        <v/>
       </c>
       <c r="K55" t="str">
-        <v>ヘパリン(HIT: ヘパリン起因性血小板減少症)、バルプロ酸、抗がん剤、リネゾリド</v>
+        <v/>
       </c>
       <c r="L55" t="str">
-        <v>抗血小板薬・抗凝固薬使用中に血小板減少があると出血リスクがさらに高まる。抗がん剤・バルプロ酸・カルバマゼピンなど骨髄抑制のリスクがある薬剤使用中は定期採血の実施状況を確認する</v>
+        <v>「骨を壊す側」の指標。「骨を作る側」の検査と合わせて評価する。数値だけで診断はしない</v>
       </c>
       <c r="M55" t="str">
-        <v>てんかん,抗血小板療法</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="N55" t="str">
-        <v>血小板,Plt,platelet,出血,あざ,紫斑,骨髄抑制</v>
+        <v>TRACP-5b,骨型酒石酸抵抗性フォスファターゼ,骨粗鬆症,骨代謝</v>
       </c>
       <c r="O55" t="str">
         <v/>
@@ -3011,22 +3011,22 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>RDW-SD</v>
+        <v>骨型アルカリフォスファターゼ</v>
       </c>
       <c r="B56" t="str">
-        <v>RDW-SD</v>
+        <v>BAP</v>
       </c>
       <c r="C56" t="str">
-        <v>39〜46 fL程度（施設差あり）</v>
+        <v>男性 3.7〜20.9 μg/L、女性（閉経前）2.9〜14.5 μg/L（施設差あり）</v>
       </c>
       <c r="D56" t="str">
-        <v>赤血球の大きさのばらつきを表す指標(絶対値)。鉄欠乏性貧血などの初期変化を捉えやすい</v>
+        <v>ALPのうち骨に由来する成分だけを測定し、骨が作られる勢い（骨形成）を反映する</v>
       </c>
       <c r="E56" t="str">
-        <v>RDW-SDは、赤血球の大きさがどれくらいバラバラになっているかを表す数値です。貧血の原因を調べる際、鉄が足りなくなり始めた早い段階での変化を捉えるのに役立ちます。</v>
+        <v>骨型ALPは、通常のALP（アルカリフォスファターゼ）の中でも、骨で作られる成分だけを選んで測定するものです。骨を新しく作る働きがどれくらい活発かを見る指標として、骨粗鬆症の治療効果判定などに使われます。</v>
       </c>
       <c r="F56" t="str">
-        <v>鉄欠乏性貧血の初期、混合性貧血（複数の原因が重なっている状態）、赤血球産生の乱れ</v>
+        <v>骨代謝回転の亢進（骨粗鬆症、骨折治癒過程、骨形成促進薬による治療効果、Paget病、骨転移）</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="I56" t="str">
-        <v/>
+        <v>骨形成の低下</v>
       </c>
       <c r="J56" t="str">
         <v/>
@@ -3044,139 +3044,139 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>MCVが正常範囲でもRDWが上昇している場合、鉄欠乏の初期段階を示唆することがある。MCV・MCHと合わせて評価する</v>
+        <v>通常のALPと異なり肝臓の影響を受けにくいため、肝機能異常がある患者でも骨代謝を評価しやすい。P1NPと同じ「骨を作る側」の指標で、骨形成促進薬（テリパラチド等）の効果判定に使われる</v>
       </c>
       <c r="M56" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="N56" t="str">
-        <v>RDW-SD,赤血球分布幅,貧血,鉄欠乏</v>
+        <v>骨型ALP,BAP,骨型アルカリフォスファターゼ,骨形成マーカー</v>
       </c>
       <c r="O56" t="str">
-        <v>食事と栄養 p.151-164（第2部 貧血）</v>
+        <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>RDW-CV</v>
+        <v>25-ヒドロキシビタミンD</v>
       </c>
       <c r="B57" t="str">
-        <v>RDW-CV</v>
+        <v>25(OH)D</v>
       </c>
       <c r="C57" t="str">
-        <v>11.5〜14.5%程度（施設差あり）</v>
+        <v>30 ng/mL以上：充足、20〜30 ng/mL：不足、20 ng/mL未満：欠乏（施設差あり）</v>
       </c>
       <c r="D57" t="str">
-        <v>赤血球の大きさのばらつきを割合(%)で表した指標</v>
+        <v>体内のビタミンDの蓄え具合を反映する指標。カルシウムの吸収や骨の健康に関わる</v>
       </c>
       <c r="E57" t="str">
-        <v>RDW-CVもRDW-SDと同じく、赤血球の大きさのばらつきを表す数値ですが、こちらは割合(%)で示されます。貧血のタイプを見分ける手がかりになります。</v>
+        <v>この検査は、体の中にビタミンDがどれくらい蓄えられているかを見るものです。ビタミンDは、食事から摂ったカルシウムを腸で吸収するのを助ける働きがあり、不足すると骨がもろくなりやすくなります。</v>
       </c>
       <c r="F57" t="str">
-        <v>鉄欠乏性貧血、ビタミンB12・葉酸欠乏性貧血、混合性貧血</v>
+        <v>ビタミンD製剤の過剰摂取</v>
       </c>
       <c r="G57" t="str">
-        <v/>
+        <v>活性型ビタミンD3製剤やサプリメントの摂取量を確認する。高カルシウム血症の症状（吐き気、便秘、多尿など）がないか確認する</v>
       </c>
       <c r="H57" t="str">
-        <v/>
+        <v>活性型/天然型ビタミンD製剤の過量投与</v>
       </c>
       <c r="I57" t="str">
-        <v/>
+        <v>日光暴露不足、食事摂取不足、高齢、腸疾患による吸収不良、肝・腎機能低下（活性化障害）</v>
       </c>
       <c r="J57" t="str">
-        <v/>
+        <v>適度な日光浴、魚類・きのこ類などビタミンDを多く含む食品の摂取を意識するとよいことを伝える</v>
       </c>
       <c r="K57" t="str">
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>RDW-SDと同様の意味を持つ指標。MCVが小さくRDWが高ければ鉄欠乏性貧血、MCVが大きくRDWが高ければビタミンB12・葉酸欠乏を疑う手がかりになる</v>
+        <v>骨粗鬆症治療における活性型ビタミンD3製剤の効果判定や、投与量調整の参考に用いられる。腎機能低下患者では活性化障害により25(OH)Dが正常でも活性型が不足することがある点に注意</v>
       </c>
       <c r="M57" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="N57" t="str">
-        <v>RDW-CV,赤血球分布幅,貧血,ビタミンB12,葉酸</v>
+        <v>25(OH)D,ビタミンD,25-ヒドロキシビタミンD,ビタミンD欠乏,骨粗鬆症</v>
       </c>
       <c r="O57" t="str">
-        <v>食事と栄養 p.151-164（第2部 貧血）</v>
+        <v>食事と栄養 p.38（ビタミンD）</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>好中球実数値</v>
+        <v>ucOC（低カルボキシル化オステオカルシン）</v>
       </c>
       <c r="B58" t="str">
-        <v>Neutro#,ANC</v>
+        <v>ucOC</v>
       </c>
       <c r="C58" t="str">
-        <v>2,000〜7,500 /μL程度（施設差あり、白血球数×好中球%で算出）</v>
+        <v>4.5 ng/mL未満（施設差あり）</v>
       </c>
       <c r="D58" t="str">
-        <v>好中球の絶対数。感染症リスクを判断する上で割合(%)より重要な指標</v>
+        <v>ビタミンKが不足していないかを反映する骨の指標</v>
       </c>
       <c r="E58" t="str">
-        <v>これは好中球の実際の数を表す数値です。割合(%)だけでなく、実際の数がどれくらいあるかを見ることで、感染症にかかりやすい状態かどうかをより正確に判断できます。</v>
+        <v>ucOCは、骨を作るために必要なビタミンKが体の中で足りているかどうかを反映する検査です。数値が高いとビタミンK不足が疑われます。</v>
       </c>
       <c r="F58" t="str">
-        <v>細菌感染症、炎症、ステロイド使用</v>
+        <v>ビタミンK不足状態</v>
       </c>
       <c r="G58" t="str">
-        <v/>
+        <v>ビタミンK2製剤(骨粗鬆症治療薬)の適応が検討されているか確認する。ワルファリン服用中の患者では、納豆などビタミンKを多く含む食品の急な摂取量の変化を避けるよう説明する</v>
       </c>
       <c r="H58" t="str">
         <v/>
       </c>
       <c r="I58" t="str">
-        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、メルカゾールなど薬剤性の無顆粒球症（1,000/μL未満で好中球減少症、500/μL未満で重症感染リスクが著しく上昇）</v>
+        <v/>
       </c>
       <c r="J58" t="str">
-        <v>発熱、のどの痛みなど感染症状の初期サインがないか確認する。人混みを避け、手洗い・うがいを徹底するよう伝える</v>
+        <v/>
       </c>
       <c r="K58" t="str">
-        <v>抗がん剤、メルカゾール(無顆粒球症)、クロザピン、サラゾスルファピリジン</v>
+        <v/>
       </c>
       <c r="L58" t="str">
-        <v>抗がん剤・メルカゾール・カルバマゼピンなど骨髄抑制のリスクがある薬剤使用中は特に重視すべき数値。500/μL未満は発熱性好中球減少症のリスクが高く緊急性が高い</v>
+        <v>ビタミンK2製剤（骨粗鬆症治療薬）の適応判断や効果判定に使われる</v>
       </c>
       <c r="M58" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="N58" t="str">
-        <v>好中球実数値,好中球数,ANC,無顆粒球症,発熱性好中球減少症</v>
+        <v>ucOC,オステオカルシン,ビタミンK</v>
       </c>
       <c r="O58" t="str">
-        <v/>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>好酸球実数値</v>
+        <v>PTH（副甲状腺ホルモン）</v>
       </c>
       <c r="B59" t="str">
-        <v>Eosino#</v>
+        <v>PTH</v>
       </c>
       <c r="C59" t="str">
-        <v>100〜500 /μL程度（施設差あり）</v>
+        <v>10〜65 pg/mL（施設差あり）</v>
       </c>
       <c r="D59" t="str">
-        <v>好酸球の絶対数。アレルギーや薬剤反応の程度をより正確に評価できる</v>
+        <v>血液中のカルシウム濃度を調節するホルモン</v>
       </c>
       <c r="E59" t="str">
-        <v>これは好酸球の実際の数を表す数値です。割合(%)だけでなく実数を見ることで、アレルギー反応の強さをより正確に把握できます。</v>
+        <v>PTHは、血液中のカルシウム濃度を一定に保つために働くホルモンです。カルシウムが低くなると分泌が増え、骨からカルシウムを取り出したり、腎臓での再吸収を促したりして数値を戻そうとします。</v>
       </c>
       <c r="F59" t="str">
-        <v>アレルギー性疾患、薬剤アレルギー、寄生虫感染</v>
+        <v>原発性・二次性副甲状腺機能亢進症（腎不全に伴うものなど）</v>
       </c>
       <c r="G59" t="str">
-        <v>新しく始めた薬がないか確認する</v>
+        <v/>
       </c>
       <c r="H59" t="str">
-        <v>薬剤性好酸球増多(抗菌薬・NSAIDs・抗てんかん薬など)。発熱や皮疹を伴う場合はDRESS症候群にも注意</v>
+        <v/>
       </c>
       <c r="I59" t="str">
-        <v/>
+        <v>副甲状腺機能低下症</v>
       </c>
       <c r="J59" t="str">
         <v/>
@@ -3185,36 +3185,36 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>薬剤性過敏症症候群(DIHS)などでは著明な好酸球増多を認めることがあり、原因薬剤の特定に役立つ</v>
+        <v>骨粗鬆症の二次性原因（副甲状腺機能亢進症）を除外するための検査。カルシウム・リンと合わせて評価する</v>
       </c>
       <c r="M59" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="N59" t="str">
-        <v>好酸球実数値,好酸球数,アレルギー,DIHS</v>
+        <v>PTH,副甲状腺ホルモン,パラトルモン</v>
       </c>
       <c r="O59" t="str">
-        <v/>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>好塩基球実数値</v>
+        <v>尿中NTX</v>
       </c>
       <c r="B60" t="str">
-        <v>Baso#</v>
+        <v>NTX</v>
       </c>
       <c r="C60" t="str">
-        <v>0〜100 /μL程度（施設差あり）</v>
+        <v>施設差が大きく一律の記載が難しい（尿中）</v>
       </c>
       <c r="D60" t="str">
-        <v>好塩基球の絶対数</v>
+        <v>骨が壊されるときに出る、骨吸収マーカーのひとつ</v>
       </c>
       <c r="E60" t="str">
-        <v>これは好塩基球の実際の数を表す数値です。数がとても少ない種類の血球なので、通常は大きな変動を示すことは多くありません。</v>
+        <v>NTXは、骨が壊される（吸収される）ときに尿の中に出てくる物質です。骨粗鬆症の治療薬がどれくらい効いているかを確認するために使われます。</v>
       </c>
       <c r="F60" t="str">
-        <v>慢性骨髄性白血病などの血液疾患、アレルギー性疾患</v>
+        <v>骨代謝回転の亢進（骨粗鬆症、閉経後など）</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -3223,7 +3223,7 @@
         <v/>
       </c>
       <c r="I60" t="str">
-        <v/>
+        <v>骨吸収抑制薬（ビスホスホネート等）による治療効果</v>
       </c>
       <c r="J60" t="str">
         <v/>
@@ -3232,36 +3232,36 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>単独での臨床的意義は乏しく、他の血球指標（白血球分画全体）と合わせて評価する</v>
+        <v>治療開始後3〜6か月で再検し、薬の効果判定に使われる。TRACP-5bと同じ「骨を壊す側」の指標</v>
       </c>
       <c r="M60" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="N60" t="str">
-        <v>好塩基球実数値,好塩基球数</v>
+        <v>NTX,尿中NTX,骨吸収マーカー</v>
       </c>
       <c r="O60" t="str">
-        <v/>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>リンパ球実数値</v>
+        <v>カルシトニン</v>
       </c>
       <c r="B61" t="str">
-        <v>Lympho#,ALC</v>
+        <v>CT</v>
       </c>
       <c r="C61" t="str">
-        <v>1,000〜3,600 /μL程度（施設差あり）</v>
+        <v>男性 9.52 pg/mL未満、女性 6.40 pg/mL未満（施設差あり）</v>
       </c>
       <c r="D61" t="str">
-        <v>リンパ球の絶対数。免疫力の目安として使われる</v>
+        <v>血液中のカルシウムを下げる方向に働くホルモン</v>
       </c>
       <c r="E61" t="str">
-        <v>これはリンパ球の実際の数を表す数値です。免疫力の目安の一つとして使われ、抗がん剤や免疫抑制剤の副作用モニタリングにも用いられます。</v>
+        <v>カルシトニンは、PTHとは逆に血液中のカルシウムを下げる方向に働くホルモンです。特定の甲状腺の病気（甲状腺髄様癌）がないかを調べる際にも使われます。</v>
       </c>
       <c r="F61" t="str">
-        <v>ウイルス感染症、リンパ性白血病などの血液疾患</v>
+        <v>甲状腺髄様癌、腎不全</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -3270,45 +3270,45 @@
         <v/>
       </c>
       <c r="I61" t="str">
-        <v>抗がん剤・免疫抑制剤・ステロイドの使用、強いストレス、AIDSなどの免疫不全</v>
+        <v/>
       </c>
       <c r="J61" t="str">
-        <v>感染予防（手洗い・うがい、人混みを避ける）を意識するよう伝える</v>
+        <v/>
       </c>
       <c r="K61" t="str">
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>免疫抑制剤・抗がん剤治療中のモニタリング指標としても使われる。著明な低下時は日和見感染のリスクが高まる</v>
+        <v>骨粗鬆症の二次性原因の除外目的で測定されることがある検査値。同名の薬剤（カルシトニン製剤）と混同しないよう注意</v>
       </c>
       <c r="M61" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="N61" t="str">
-        <v>リンパ球実数値,リンパ球数,ALC,免疫抑制剤,日和見感染</v>
+        <v>カルシトニン,CT</v>
       </c>
       <c r="O61" t="str">
-        <v/>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>単球実数値</v>
+        <v>DPD（デオキシピリジノリン）</v>
       </c>
       <c r="B62" t="str">
-        <v>Mono#</v>
+        <v>DPD</v>
       </c>
       <c r="C62" t="str">
-        <v>200〜600 /μL程度（施設差あり）</v>
+        <v>施設差が大きく一律の記載が難しい（尿中）</v>
       </c>
       <c r="D62" t="str">
-        <v>単球の絶対数</v>
+        <v>骨のコラーゲンが壊れるときに出る、骨吸収マーカーのひとつ</v>
       </c>
       <c r="E62" t="str">
-        <v>これは単球の実際の数を表す数値です。慢性的な炎症や感染症の状態を把握する材料の一つになります。</v>
+        <v>DPDも、骨が壊されるときに尿に出てくる物質の一つです。NTXと同じように、骨粗鬆症治療薬の効果を確認するために使われます。</v>
       </c>
       <c r="F62" t="str">
-        <v>慢性感染症、炎症性疾患、血液疾患</v>
+        <v>骨代謝回転の亢進（骨粗鬆症など）</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -3317,7 +3317,7 @@
         <v/>
       </c>
       <c r="I62" t="str">
-        <v/>
+        <v>骨吸収抑制薬による治療効果</v>
       </c>
       <c r="J62" t="str">
         <v/>
@@ -3326,92 +3326,92 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>単独での臨床的意義は乏しく、他の血球指標と合わせて評価する</v>
+        <v>NTX・CTXと同じ「骨を壊す側」の指標。食事の影響を受けにくいとされる</v>
       </c>
       <c r="M62" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="N62" t="str">
-        <v>単球実数値,単球数</v>
+        <v>DPD,デオキシピリジノリン,骨吸収マーカー</v>
       </c>
       <c r="O62" t="str">
-        <v/>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>好中球</v>
+        <v>CTX</v>
       </c>
       <c r="B63" t="str">
-        <v>Neutro,Neut%</v>
+        <v>CTX</v>
       </c>
       <c r="C63" t="str">
-        <v>40〜75%程度（施設差あり）</v>
+        <v>施設差が大きく一律の記載が難しい（血清・尿中）</v>
       </c>
       <c r="D63" t="str">
-        <v>白血球の中で最も多くを占め、細菌感染と戦う主力の免疫細胞の割合</v>
+        <v>骨のコラーゲンが壊れるときに出る、骨吸収マーカーのひとつ</v>
       </c>
       <c r="E63" t="str">
-        <v>好中球は、白血球の中で最も数が多く、細菌が体に入ってきたときに真っ先に戦ってくれる免疫細胞です。感染症や炎症があると増え、逆に薬の副作用などで減ることがあります。</v>
+        <v>CTXも、骨が壊されるときに血液や尿に出てくる物質です。骨粗鬆症治療薬（骨を壊すのを抑える薬）の効果を確認するために使われます。</v>
       </c>
       <c r="F63" t="str">
-        <v>細菌感染症、炎症、ストレス、ステロイド使用</v>
+        <v>骨代謝回転の亢進（骨粗鬆症など）</v>
       </c>
       <c r="G63" t="str">
-        <v>発熱や炎症症状がないか確認する</v>
+        <v/>
       </c>
       <c r="H63" t="str">
         <v/>
       </c>
       <c r="I63" t="str">
-        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、ウイルス感染、メルカゾールなど薬剤性の無顆粒球症</v>
+        <v>骨吸収抑制薬による治療効果</v>
       </c>
       <c r="J63" t="str">
-        <v>発熱やのどの痛みなど感染症状の初期サインがないか確認する</v>
+        <v/>
       </c>
       <c r="K63" t="str">
-        <v>抗がん剤、メルカゾール(無顆粒球症)、クロザピン、サラゾスルファピリジン</v>
+        <v/>
       </c>
       <c r="L63" t="str">
-        <v>好中球の絶対数（好中球実数値）が500/μL未満になると重篤な感染症のリスクが高まる。割合(%)だけでなく実数値も合わせて確認する</v>
+        <v>NTX・DPDと同じ「骨を壊す側」の指標。血清・尿中いずれでも測定されることがある</v>
       </c>
       <c r="M63" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="N63" t="str">
-        <v>好中球,Neutro,Neut,感染症,無顆粒球症</v>
+        <v>CTX,骨吸収マーカー</v>
       </c>
       <c r="O63" t="str">
-        <v/>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>好酸球</v>
+        <v>P1NP</v>
       </c>
       <c r="B64" t="str">
-        <v>Eosino,Eos%</v>
+        <v>P1NP</v>
       </c>
       <c r="C64" t="str">
-        <v>1〜5%程度（施設差あり）</v>
+        <v>施設差が大きく一律の記載が難しい（血清）</v>
       </c>
       <c r="D64" t="str">
-        <v>アレルギー反応や寄生虫感染に関わる白血球の一種の割合</v>
+        <v>骨が新しく作られるときに出る、骨形成マーカーのひとつ</v>
       </c>
       <c r="E64" t="str">
-        <v>好酸球は、アレルギー反応や寄生虫感染と関係が深い免疫細胞です。アレルギー性の病気や薬の副作用（薬疹など）で増えることがあります。</v>
+        <v>P1NPは、CTXなどとは逆に、骨が新しく作られるときに血液中に出てくる物質です。骨を作る力を高める薬（テリパラチドなど）の効果を確認するために使われます。</v>
       </c>
       <c r="F64" t="str">
-        <v>アレルギー性疾患（気管支喘息、アトピー性皮膚炎など）、薬剤アレルギー、寄生虫感染</v>
+        <v>骨代謝回転の亢進、骨形成促進薬による治療効果</v>
       </c>
       <c r="G64" t="str">
-        <v>新しく始めた薬がないか確認する。皮疹やかゆみなどアレルギー症状の有無を確認する</v>
+        <v/>
       </c>
       <c r="H64" t="str">
-        <v>薬剤性好酸球増多(抗菌薬・NSAIDs・抗てんかん薬など)。発熱や皮疹を伴う場合はDRESS症候群にも注意</v>
+        <v/>
       </c>
       <c r="I64" t="str">
-        <v/>
+        <v>骨形成の低下</v>
       </c>
       <c r="J64" t="str">
         <v/>
@@ -3420,83 +3420,83 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>薬剤性の好酸球増多は、原因薬剤の中止で改善することが多い。新規薬剤開始後の皮疹・発熱と合わせて薬剤性過敏症症候群(DIHS)を疑う材料になる</v>
+        <v>TRACP-5b等「骨を壊す側」の指標とは逆の、「骨を作る側」の指標。骨形成促進薬（テリパラチド等）の効果判定に使われる</v>
       </c>
       <c r="M64" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="N64" t="str">
-        <v>好酸球,Eosino,Eos,アレルギー,薬疹,DIHS</v>
+        <v>P1NP,骨形成マーカー</v>
       </c>
       <c r="O64" t="str">
-        <v/>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>好塩基球</v>
+        <v>血清鉄（Fe）</v>
       </c>
       <c r="B65" t="str">
-        <v>Baso,Baso%</v>
+        <v>Fe</v>
       </c>
       <c r="C65" t="str">
-        <v>0〜2%程度（施設差あり）</v>
+        <v>60〜200 μg/dL（施設差あり）</v>
       </c>
       <c r="D65" t="str">
-        <v>白血球の中で最も数が少なく、アレルギー反応に関わる細胞の割合</v>
+        <v>血液中を流れている鉄の量</v>
       </c>
       <c r="E65" t="str">
-        <v>好塩基球は白血球の中で最も数が少ない種類で、アレルギー反応や炎症に関わっています。数値の変動が病気の診断に直接使われることは少ない検査です。</v>
+        <v>この検査は、今血液の中を流れている鉄の量を見るものです。低いと、体の中で鉄が不足している可能性があります。</v>
       </c>
       <c r="F65" t="str">
-        <v>慢性骨髄性白血病などの血液疾患、アレルギー性疾患、甲状腺機能低下症</v>
+        <v>鉄剤の過剰摂取、溶血、肝疾患</v>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v/>
+        <v>鉄剤の過量摂取(小児の誤飲を含む)</v>
       </c>
       <c r="I65" t="str">
-        <v/>
+        <v>鉄欠乏性貧血、慢性炎症、出血</v>
       </c>
       <c r="J65" t="str">
-        <v/>
+        <v>鉄分の多い食品（レバー・赤身肉・魚・ほうれん草など）を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える</v>
       </c>
       <c r="K65" t="str">
-        <v/>
+        <v>プロトンポンプ阻害薬(PPI)・H2ブロッカーは胃酸分泌抑制により鉄の吸収を低下させうる</v>
       </c>
       <c r="L65" t="str">
-        <v>単独での臨床的意義は乏しいが、著明な増加は血液疾患（慢性骨髄性白血病等）の可能性があり他の血球指標と合わせて評価する</v>
+        <v>血清鉄は日内変動が大きい。単独で判断せず総鉄結合能・フェリチンと合わせて評価する</v>
       </c>
       <c r="M65" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="N65" t="str">
-        <v>好塩基球,Baso,アレルギー,白血病</v>
+        <v>血清鉄,Fe,鉄欠乏性貧血</v>
       </c>
       <c r="O65" t="str">
-        <v/>
+        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>リンパ球</v>
+        <v>総鉄結合能（TIBC）</v>
       </c>
       <c r="B66" t="str">
-        <v>Lympho,Lym%</v>
+        <v>TIBC</v>
       </c>
       <c r="C66" t="str">
-        <v>18〜49%程度（施設差あり）</v>
+        <v>250〜360 μg/dL（施設差あり）</v>
       </c>
       <c r="D66" t="str">
-        <v>ウイルス感染と戦い、免疫の記憶を担う白血球の割合</v>
+        <v>血液中のトランスフェリンが鉄と結合できる総量</v>
       </c>
       <c r="E66" t="str">
-        <v>リンパ球は、ウイルスと戦ったり、一度かかった病気を記憶して免疫をつくったりする細胞です。ウイルス感染で増え、抗がん剤の副作用や強いストレスで減ることがあります。</v>
+        <v>TIBCは、血液中でトランスフェリンという物質が鉄を運べる最大量を表します。体の中の鉄が不足すると、少しでも多く鉄を運ぼうとしてこの数値が上がる性質があります。</v>
       </c>
       <c r="F66" t="str">
-        <v>ウイルス感染症、リンパ性白血病などの血液疾患、百日咳</v>
+        <v>鉄欠乏性貧血（＞360 μg/dLが目安）</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -3505,45 +3505,45 @@
         <v/>
       </c>
       <c r="I66" t="str">
-        <v>抗がん剤・免疫抑制剤・ステロイドの使用、強いストレス、AIDSなどの免疫不全</v>
+        <v>慢性炎症、肝疾患、ネフローゼ症候群</v>
       </c>
       <c r="J66" t="str">
-        <v>免疫が下がっている可能性があるため、感染予防（手洗い・うがい、人混みを避ける）を意識するよう伝える</v>
+        <v/>
       </c>
       <c r="K66" t="str">
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>ステロイド・免疫抑制剤使用中はリンパ球減少による易感染性に注意。好中球と逆方向に動くことが多い（ウイルス感染ではリンパ球優位、細菌感染では好中球優位になりやすい）</v>
+        <v>鉄が不足すると、体はより多く運ぼうとしてTIBCが上昇する。UIBC・血清鉄と併せて評価する</v>
       </c>
       <c r="M66" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="N66" t="str">
-        <v>リンパ球,Lympho,Lym,ウイルス感染,免疫抑制剤,ステロイド</v>
+        <v>TIBC,総鉄結合能,鉄欠乏性貧血</v>
       </c>
       <c r="O66" t="str">
-        <v/>
+        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>単球</v>
+        <v>不飽和鉄結合能（UIBC）</v>
       </c>
       <c r="B67" t="str">
-        <v>Mono,Mono%</v>
+        <v>UIBC</v>
       </c>
       <c r="C67" t="str">
-        <v>2〜10%程度（施設差あり）</v>
+        <v>170〜300 μg/dL（施設差あり）</v>
       </c>
       <c r="D67" t="str">
-        <v>感染や炎症の後始末をする白血球の一種の割合</v>
+        <v>トランスフェリンのうち、まだ鉄と結合していない余力の部分（UIBC＝TIBC－血清鉄）</v>
       </c>
       <c r="E67" t="str">
-        <v>単球は、細菌などを取り込んで処理したり、組織の修復に関わったりする免疫細胞です。慢性的な炎症や感染症の回復期に増えることがあります。</v>
+        <v>UIBCは、トランスフェリンのうち、まだ鉄と結合していない「空き容量」の部分を表します。鉄が不足しているときほど、この空き容量は大きくなります。</v>
       </c>
       <c r="F67" t="str">
-        <v>慢性感染症（結核など）、炎症性疾患、血液疾患、感染症の回復期</v>
+        <v>鉄欠乏性貧血（＞300 μg/dLが目安）</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -3552,7 +3552,7 @@
         <v/>
       </c>
       <c r="I67" t="str">
-        <v/>
+        <v>慢性炎症、鉄過剰状態</v>
       </c>
       <c r="J67" t="str">
         <v/>
@@ -3561,45 +3561,45 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>単独での臨床的意義は乏しく、他の血球指標や炎症マーカー(CRPなど)と合わせて評価する</v>
+        <v>TIBCと同じ方向に動くことが多い。血清鉄・TIBCとあわせて鉄欠乏性貧血と二次性貧血の鑑別に使う</v>
       </c>
       <c r="M67" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="N67" t="str">
-        <v>単球,Mono,慢性感染症,結核,炎症</v>
+        <v>UIBC,不飽和鉄結合能,鉄欠乏性貧血</v>
       </c>
       <c r="O67" t="str">
-        <v/>
+        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Dダイマー</v>
+        <v>トランスフェリン飽和度</v>
       </c>
       <c r="B68" t="str">
-        <v>D-dimer</v>
+        <v>TSAT</v>
       </c>
       <c r="C68" t="str">
-        <v>1.0 μg/mL以下(施設・測定法により異なる)</v>
+        <v>16〜50%程度（施設差あり）</v>
       </c>
       <c r="D68" t="str">
-        <v>体の中で血栓ができて溶けた(線溶)ときにできる分解産物で、血栓症の有無をスクリーニングする指標</v>
+        <v>鉄を運ぶ役割のトランスフェリンのうち、実際に鉄を運んでいる割合（血清鉄÷総鉄結合能）</v>
       </c>
       <c r="E68" t="str">
-        <v>Dダイマーは、血管の中に血のかたまり(血栓)ができて、それが溶かされるときにできる物質です。この数値が高いと、どこかに血栓ができている可能性を考えます。ただし手術後や妊娠中、高齢の方などでも上がることがあるため、この数値だけで診断が決まるわけではありません。</v>
+        <v>トランスフェリン飽和度は、鉄を運ぶトランスフェリンのうち、実際にどれくらいが鉄を運んでいるかを割合で表したものです。鉄欠乏性貧血では低くなり、鉄が過剰にたまる病気では高くなります。</v>
       </c>
       <c r="F68" t="str">
-        <v>深部静脈血栓症(DVT)・肺血栓塞栓症(PE)、播種性血管内凝固症候群(DIC)、大動脈解離、悪性腫瘍、手術後、妊娠、高齢、感染・炎症</v>
+        <v>鉄過剰症（ヘモクロマトーシスなど）</v>
       </c>
       <c r="G68" t="str">
-        <v>ふくらはぎの腫れ・痛み、急な息切れ・胸痛など血栓症を疑う症状がないか確認する</v>
+        <v/>
       </c>
       <c r="H68" t="str">
-        <v>経口避妊薬・ホルモン補充療法は血栓リスクを高める。逆にワルファリン・DOAC・ヘパリンなど抗凝固薬の効果不十分で血栓が進行している可能性にも注意</v>
+        <v/>
       </c>
       <c r="I68" t="str">
-        <v>通常、臨床的意義は乏しい(基準値以下であれば血栓症の可能性は低いとする除外診断に有用)</v>
+        <v>鉄欠乏性貧血（＜16%が目安）</v>
       </c>
       <c r="J68" t="str">
         <v/>
@@ -3608,92 +3608,92 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>陰性的中率が高く、基準値以下であれば静脈血栓塞栓症(VTE)の可能性は低いとする除外診断への活用が臨床的に重要。一方で偽陽性が多く、高値のみで血栓症と確定はできない。抗凝固療法中のモニタリングそのものには通常用いない(効果判定はPT-INR/APTT等)</v>
+        <v>血清鉄をTIBCで割って計算される。鉄剤補充の効果判定にも使われる</v>
       </c>
       <c r="M68" t="str">
-        <v>抗凝固療法（心房細動・血栓症）</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="N68" t="str">
-        <v>Dダイマー,D-dimer,血栓,DVT,深部静脈血栓症,肺塞栓,DIC</v>
+        <v>トランスフェリン飽和度,TSAT,鉄欠乏性貧血</v>
       </c>
       <c r="O68" t="str">
-        <v/>
+        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>C反応性蛋白（CRP）</v>
+        <v>血清フェリチン</v>
       </c>
       <c r="B69" t="str">
-        <v>CRP</v>
+        <v>Ferritin</v>
       </c>
       <c r="C69" t="str">
-        <v>0.3 mg/dL未満（施設差あり）</v>
+        <v>男性 20〜250 ng/mL、女性 10〜120 ng/mL（施設差あり）</v>
       </c>
       <c r="D69" t="str">
-        <v>体のどこかに炎症や感染が起きていないかを鋭敏に反映する数値</v>
+        <v>体に貯蔵されている鉄の量を反映する指標。貧血の症状が出るより早い段階で低下する</v>
       </c>
       <c r="E69" t="str">
-        <v>CRPは、体に炎症や感染が起きると数時間〜半日程度で急激に上昇する数値です。風邪のようなウイルス感染から細菌感染、体のどこかの炎症まで、幅広く反応するため、体調の変化を早期に捉える手がかりになります。</v>
+        <v>フェリチンは、体に蓄えられている鉄の「貯金」の量を見る検査です。この数値が下がるのは、貧血の症状が出るよりも前の、とても早い段階のサインになります。</v>
       </c>
       <c r="F69" t="str">
-        <v>細菌感染症、ウイルス感染症、自己免疫疾患（関節リウマチなど）、悪性腫瘍、組織の損傷（術後・心筋梗塞など）</v>
+        <v>炎症性疾患、肝疾患、悪性腫瘍、鉄過剰症（フェリチンは炎症でも上昇するため、貧血の評価では注意が必要）</v>
       </c>
       <c r="G69" t="str">
-        <v>発熱、痛み、腫れなど炎症症状の有無を確認する</v>
+        <v/>
       </c>
       <c r="H69" t="str">
         <v/>
       </c>
       <c r="I69" t="str">
-        <v/>
+        <v>鉄欠乏状態（貧血の症状が出る前の早期段階から低下する）</v>
       </c>
       <c r="J69" t="str">
-        <v/>
+        <v>鉄分の多い食品を意識するとともに、貯蔵鉄を補うため治療は数値が正常化してからも継続が必要なことを伝える</v>
       </c>
       <c r="K69" t="str">
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>白血球数と合わせて感染・炎症の程度を評価する。上昇・低下のタイミングは白血球より半日〜1日程度遅れる傾向があるため、経過を追う際は採血のタイミングに注意</v>
+        <v>貯蔵鉄の指標で鉄欠乏を最も早期に反映する。ただし炎症があると鉄欠乏があっても正常〜高値に出ることがあり、CRP等の炎症所見と合わせて評価する。二次性貧血との鑑別に重要</v>
       </c>
       <c r="M69" t="str">
-        <v/>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="N69" t="str">
-        <v>CRP,炎症,感染</v>
+        <v>フェリチン,Ferritin,貯蔵鉄,鉄欠乏</v>
       </c>
       <c r="O69" t="str">
-        <v/>
+        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>骨型酒石酸抵抗性フォスファターゼ（TRACP-5b）</v>
+        <v>尿中尿酸/クレアチニン比（UUA/UCr）</v>
       </c>
       <c r="B70" t="str">
-        <v>TRACP-5b</v>
+        <v>UUA/UCr</v>
       </c>
       <c r="C70" t="str">
-        <v>120〜420 mU/dL</v>
+        <v>0.4〜0.8程度が混合型の目安</v>
       </c>
       <c r="D70" t="str">
-        <v>骨がどれくらい壊されているかを見る検査。骨は「古い骨を壊して新しい骨を作る」入れ替えを繰り返しており、骨を壊す細胞が活発だとこの物質が血液中に増える。</v>
+        <v>尿酸が「作られすぎ」か「排泄できていない」かを見分ける比の値</v>
       </c>
       <c r="E70" t="str">
-        <v>この検査は、骨がどれくらい早く減っていないかを見るものです。数値が高いと、骨が弱くなりやすい状態の目安になります。</v>
+        <v>この数値は、体の中で尿酸が「作られすぎている」のか、それとも「うまく排泄できていない」のかを見分けるために使う比の値です。高尿酸血症の治療薬を選ぶときの参考になります。</v>
       </c>
       <c r="F70" t="str">
-        <v>骨粗鬆症、骨代謝回転（骨がこわれるスピード）が活発な状態</v>
+        <v>尿酸産生過剰型（0.8以上が目安）</v>
       </c>
       <c r="G70" t="str">
-        <v>カルシウム・ビタミンDの摂取や、適度な荷重運動（ウォーキングなど）を意識するよう伝える</v>
+        <v/>
       </c>
       <c r="H70" t="str">
         <v/>
       </c>
       <c r="I70" t="str">
-        <v/>
+        <v>尿酸排泄低下型（0.4以下が目安）</v>
       </c>
       <c r="J70" t="str">
         <v/>
@@ -3702,89 +3702,89 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>「骨を壊す側」の指標。「骨を作る側」の検査と合わせて評価する。数値だけで診断はしない</v>
+        <v>高尿酸血症は尿酸産生過剰型・排泄低下型・混合型に分類され、この比が目安になる。病型によって使う薬剤（尿酸生成抑制薬か尿酸排泄促進薬か）の選択が変わる</v>
       </c>
       <c r="M70" t="str">
-        <v>骨粗鬆症</v>
+        <v>高尿酸血症</v>
       </c>
       <c r="N70" t="str">
-        <v>TRACP-5b,骨型酒石酸抵抗性フォスファターゼ,骨粗鬆症,骨代謝</v>
+        <v>UUA,UCr,尿酸クリアランス,CUA,EUA,尿酸産生過剰型,尿酸排泄低下型</v>
       </c>
       <c r="O70" t="str">
-        <v/>
+        <v>食事と栄養 p.180-189（第2部 痛風・高尿酸血症）</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>PT-INR（プロトロンビン時間国際標準比）</v>
+        <v>抗甲状腺マイクロゾーム抗体（抗TPO抗体）</v>
       </c>
       <c r="B71" t="str">
-        <v>PT-INR,INR</v>
+        <v>TPOAb</v>
       </c>
       <c r="C71" t="str">
-        <v>治療域の目安 1.6〜3.0（ワルファリン服用時。年齢・疾患により異なる）</v>
+        <v>陰性（16 IU/mL未満程度、施設差あり）</v>
       </c>
       <c r="D71" t="str">
-        <v>血液の固まりやすさを表す数値で、ワルファリンの効き具合を確認するために使う</v>
+        <v>自分の甲状腺を攻撃する抗体が出ていないかを見る検査</v>
       </c>
       <c r="E71" t="str">
-        <v>PT-INRは血液が固まるまでの時間をもとにした数値で、ワルファリンというお薬を飲んでいる方の効き具合を確認するために測ります。数値が高いほど血液が固まりにくく出血しやすい状態、低いほど血栓ができやすい状態を示します。</v>
+        <v>この検査は、体の中に自分の甲状腺を誤って攻撃してしまう抗体がないかを見るものです。陽性の場合、橋本病（慢性甲状腺炎）など甲状腺の自己免疫的な炎症が背景にある可能性があります。</v>
       </c>
       <c r="F71" t="str">
-        <v>ワルファリンの効きすぎ、肝機能低下、ビタミンK不足、納豆・青汁など摂取量の変化</v>
+        <v>橋本病（慢性甲状腺炎）、バセドウ病などの自己免疫性甲状腺疾患</v>
       </c>
       <c r="G71" t="str">
-        <v>歯ぐきや鼻からの出血、あざ、黒い便などの出血症状がないか確認する。納豆・クロレラ・青汁などビタミンKを多く含む食品の摂取状況を確認する</v>
+        <v/>
       </c>
       <c r="H71" t="str">
-        <v>ワルファリンの過量。ワルファリン服用中はST合剤・マクロライド系・フルコナゾール等の相互作用やビタミンK摂取量の変化にも注意</v>
+        <v/>
       </c>
       <c r="I71" t="str">
-        <v>ワルファリンの効き不足、飲み忘れ、ビタミンK摂取量の急激な増加</v>
+        <v/>
       </c>
       <c r="J71" t="str">
-        <v>服薬状況（飲み忘れ）を確認する。片側のむくみ・しびれ・胸痛など血栓症状がないか確認する</v>
+        <v/>
       </c>
       <c r="K71" t="str">
-        <v>ワルファリン服用中で低値の場合は効果不十分の可能性。ビタミンK摂取量の変化や、リファンピシン・カルバマゼピン・バルビツール酸系など代謝を促進する薬との併用を確認</v>
+        <v/>
       </c>
       <c r="L71" t="str">
-        <v>治療域は疾患・年齢によって異なる（例：非弁膜症性心房細動の高齢者では1.6〜2.6が目安になることが多い）。多くの薬剤・食品と相互作用があるため新規薬剤追加時は必ず確認する。DOAC（エリキュース、リクシアナ、プラザキサなど）ではPT-INRのモニタリングは不要</v>
+        <v>陽性でも必ずしも甲状腺機能異常があるとは限らない。TSH・FT4など甲状腺ホルモンの数値と合わせて評価する</v>
       </c>
       <c r="M71" t="str">
-        <v>抗凝固療法（心房細動・血栓症）</v>
+        <v>甲状腺疾患</v>
       </c>
       <c r="N71" t="str">
-        <v>PT-INR,INR,プロトロンビン時間,ワルファリン,ワーファリン,抗凝固</v>
+        <v>抗TPO抗体,抗甲状腺マイクロゾーム抗体,TPOAb,橋本病</v>
       </c>
       <c r="O71" t="str">
-        <v>食事と栄養 p.221（心疾患Q93 ワルファリン服用中のビタミンK摂取）</v>
+        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>尿蛋白定量</v>
+        <v>抗サイログロブリン抗体</v>
       </c>
       <c r="B72" t="str">
-        <v>U-Pro定量,蛋白/Cr比</v>
+        <v>TgAb</v>
       </c>
       <c r="C72" t="str">
-        <v>0.15 g/gCr未満</v>
+        <v>陰性（28 IU/mL未満程度、施設差あり）</v>
       </c>
       <c r="D72" t="str">
-        <v>随時尿から尿蛋白の量を具体的な数値として評価する検査。ネフローゼ等の重症度判定に使う</v>
+        <v>甲状腺のたんぱく質（サイログロブリン）への抗体が出ていないかを見る検査</v>
       </c>
       <c r="E72" t="str">
-        <v>これは、尿に出ているたんぱくの量を具体的な数値で見る検査です。試験紙での陽性・陰性の判定だけでなく、実際にどれくらいの量が出ているかを把握できます。</v>
+        <v>この検査も、抗TPO抗体と同じく、甲状腺に対する自己免疫の有無を見るものです。あわせて調べることで橋本病などの診断の参考にします。</v>
       </c>
       <c r="F72" t="str">
-        <v>腎症の進行（糖尿病性腎症、慢性腎臓病など）、ネフローゼ症候群（3.5 g/gCr以上が目安）</v>
+        <v>橋本病（慢性甲状腺炎）、バセドウ病などの自己免疫性甲状腺疾患</v>
       </c>
       <c r="G72" t="str">
-        <v>持続する場合は塩分の摂りすぎに注意し、むくみの有無も確認する。腎臓内科でのフォロー状況もあわせて確認する</v>
+        <v/>
       </c>
       <c r="H72" t="str">
-        <v>NSAIDs、造影剤、アミノグリコシド系、バンコマイシン</v>
+        <v/>
       </c>
       <c r="I72" t="str">
         <v/>
@@ -3796,60 +3796,60 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>CKD診療ガイドラインの重症度分類（尿蛋白量による区分）にも使われる定量指標。試験紙法の半定量結果より治療効果判定に適する</v>
+        <v>抗TPO抗体とあわせて測定されることが多い。単独の高値だけで治療方針が決まるわけではない</v>
       </c>
       <c r="M72" t="str">
-        <v>腎機能,糖尿病</v>
+        <v>甲状腺疾患</v>
       </c>
       <c r="N72" t="str">
-        <v>尿蛋白,随時尿,定量,蛋白クレアチニン比,ネフローゼ</v>
+        <v>抗サイログロブリン抗体,TgAb,橋本病</v>
       </c>
       <c r="O72" t="str">
-        <v/>
+        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>骨型アルカリフォスファターゼ</v>
+        <v>血中薬物濃度（TDM）</v>
       </c>
       <c r="B73" t="str">
-        <v>BAP</v>
+        <v>TDM</v>
       </c>
       <c r="C73" t="str">
-        <v>男性 3.7〜20.9 μg/L、女性（閉経前）2.9〜14.5 μg/L（施設差あり）</v>
+        <v>薬剤ごとに有効域が異なる（例：カルバマゼピン 4〜12 μg/mL、バルプロ酸 40〜100 μg/mL、フェニトイン 10〜20 μg/mL）</v>
       </c>
       <c r="D73" t="str">
-        <v>ALPのうち骨に由来する成分だけを測定し、骨が作られる勢い（骨形成）を反映する</v>
+        <v>治療域が狭い薬剤で、血液中の薬の濃度が効果域・中毒域のどちらにあるかを確認する検査</v>
       </c>
       <c r="E73" t="str">
-        <v>骨型ALPは、通常のALP（アルカリフォスファターゼ）の中でも、骨で作られる成分だけを選んで測定するものです。骨を新しく作る働きがどれくらい活発かを見る指標として、骨粗鬆症の治療効果判定などに使われます。</v>
+        <v>この薬は効く量と副作用が出る量が近いため、血液中の薬の濃度を定期的に測って、ちょうどよい範囲に入っているかを確認します。数値が低いと効果が不十分になり、高いと副作用が出やすくなります。</v>
       </c>
       <c r="F73" t="str">
-        <v>骨代謝回転の亢進（骨粗鬆症、骨折治癒過程、骨形成促進薬による治療効果、Paget病、骨転移）</v>
+        <v>過量投与、代謝を妨げる薬剤との併用、肝機能低下による代謝低下</v>
       </c>
       <c r="G73" t="str">
-        <v/>
+        <v>ふらつき、眠気、めまい、物が二重に見えるなどの中毒症状がないか確認する</v>
       </c>
       <c r="H73" t="str">
         <v/>
       </c>
       <c r="I73" t="str">
-        <v>骨形成の低下</v>
+        <v>飲み忘れ、自己判断による減量、代謝を促進する薬剤との併用（相互作用）</v>
       </c>
       <c r="J73" t="str">
-        <v/>
+        <v>発作やてんかん症状の再発がないか確認し、飲み忘れがないか一緒に確認する</v>
       </c>
       <c r="K73" t="str">
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>通常のALPと異なり肝臓の影響を受けにくいため、肝機能異常がある患者でも骨代謝を評価しやすい。P1NPと同じ「骨を作る側」の指標で、骨形成促進薬（テリパラチド等）の効果判定に使われる</v>
+        <v>採血のタイミング（トラフ値かどうか）で数値の解釈が変わるため採血時点を確認する。カルバマゼピンは自己誘導により長期使用で濃度が下がることがある点にも注意</v>
       </c>
       <c r="M73" t="str">
-        <v>骨粗鬆症</v>
+        <v>てんかん</v>
       </c>
       <c r="N73" t="str">
-        <v>骨型ALP,BAP,骨型アルカリフォスファターゼ,骨形成マーカー</v>
+        <v>TDM,血中薬物濃度,治療域,中毒域,カルバマゼピン,フェニトイン,バルプロ酸,抗てんかん薬</v>
       </c>
       <c r="O73" t="str">
         <v/>
@@ -3857,93 +3857,93 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>25-ヒドロキシビタミンD</v>
+        <v>アミラーゼ（AMY）</v>
       </c>
       <c r="B74" t="str">
-        <v>25(OH)D</v>
+        <v>AMY</v>
       </c>
       <c r="C74" t="str">
-        <v>30 ng/mL以上：充足、20〜30 ng/mL：不足、20 ng/mL未満：欠乏（施設差あり）</v>
+        <v>44〜132 U/L（施設差あり）</v>
       </c>
       <c r="D74" t="str">
-        <v>体内のビタミンDの蓄え具合を反映する指標。カルシウムの吸収や骨の健康に関わる</v>
+        <v>膵臓や唾液腺から出る消化酵素。膵炎などで血液中に漏れ出す</v>
       </c>
       <c r="E74" t="str">
-        <v>この検査は、体の中にビタミンDがどれくらい蓄えられているかを見るものです。ビタミンDは、食事から摂ったカルシウムを腸で吸収するのを助ける働きがあり、不足すると骨がもろくなりやすくなります。</v>
+        <v>アミラーゼは、でんぷんを分解する消化酵素で、主に膵臓と唾液腺から作られます。膵臓に炎症が起きると血液中に漏れ出して数値が上がるため、膵炎の診断や経過観察に使われます。</v>
       </c>
       <c r="F74" t="str">
-        <v>ビタミンD製剤の過剰摂取</v>
+        <v>急性膵炎、慢性膵炎の急性増悪、耳下腺炎（おたふくかぜ）、腎不全</v>
       </c>
       <c r="G74" t="str">
-        <v>活性型ビタミンD3製剤やサプリメントの摂取量を確認する。高カルシウム血症の症状（吐き気、便秘、多尿など）がないか確認する</v>
+        <v>飲酒を控え、脂っこい食事を避けるよう伝える。強い腹痛・背部痛がある場合は急性膵炎の可能性もあるため早めの受診を勧める</v>
       </c>
       <c r="H74" t="str">
-        <v>活性型/天然型ビタミンD製剤の過量投与</v>
+        <v>バルプロ酸、アザチオプリン、サイアザイド系・ループ利尿薬、ステロイドなど薬剤性膵炎の原因薬</v>
       </c>
       <c r="I74" t="str">
-        <v>日光暴露不足、食事摂取不足、高齢、腸疾患による吸収不良、肝・腎機能低下（活性化障害）</v>
+        <v>慢性膵炎の進行期（膵臓の機能低下）</v>
       </c>
       <c r="J74" t="str">
-        <v>適度な日光浴、魚類・きのこ類などビタミンDを多く含む食品の摂取を意識するとよいことを伝える</v>
+        <v/>
       </c>
       <c r="K74" t="str">
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>骨粗鬆症治療における活性型ビタミンD3製剤の効果判定や、投与量調整の参考に用いられる。腎機能低下患者では活性化障害により25(OH)Dが正常でも活性型が不足することがある点に注意</v>
+        <v>膵臓由来か唾液腺由来かを区別するには膵型アミラーゼ(P-AMY)を確認する。急性膵炎では強い腹痛・背部痛を伴うことが多く、飲酒歴の確認も重要</v>
       </c>
       <c r="M74" t="str">
-        <v>骨粗鬆症</v>
+        <v/>
       </c>
       <c r="N74" t="str">
-        <v>25(OH)D,ビタミンD,25-ヒドロキシビタミンD,ビタミンD欠乏,骨粗鬆症</v>
+        <v>アミラーゼ,AMY,膵炎,急性膵炎</v>
       </c>
       <c r="O74" t="str">
-        <v>食事と栄養 p.38（ビタミンD）</v>
+        <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>尿pH</v>
+        <v>間接ビリルビン</v>
       </c>
       <c r="B75" t="str">
-        <v>尿pH</v>
+        <v>I-Bil</v>
       </c>
       <c r="C75" t="str">
-        <v>4.5〜7.5程度（弱酸性が多い）</v>
+        <v>0.2〜0.8 mg/dL程度（施設差あり）</v>
       </c>
       <c r="D75" t="str">
-        <v>尿の酸性・アルカリ性の度合い。食事や感染症、体の状態を反映する</v>
+        <v>赤血球が壊れてできるビリルビンのうち、肝臓で処理される前の形</v>
       </c>
       <c r="E75" t="str">
-        <v>尿のpHは酸性・アルカリ性のバランスを表します。食事の内容や感染症、体の代謝状態によって変化します。単独で大きな問題を示すことは少ない検査です。</v>
+        <v>間接ビリルビンは、赤血球が壊れてできたビリルビンが、まだ肝臓で処理される前の状態です。この値が高い場合、赤血球が通常より多く壊れている(溶血)か、肝臓での処理能力に生まれつきの体質差(体質性黄疸)がある可能性が考えられます。</v>
       </c>
       <c r="F75" t="str">
-        <v>尿路感染症（尿素分解菌によるもの）、野菜中心の食事、過換気</v>
+        <v>溶血性疾患（自己免疫性溶血性貧血、血液型不適合輸血など）、体質性黄疸（ジルベール症候群）、新生児黄疸</v>
       </c>
       <c r="G75" t="str">
-        <v/>
+        <v>皮膚や白目の黄染、尿の色の変化がないか確認する</v>
       </c>
       <c r="H75" t="str">
         <v/>
       </c>
       <c r="I75" t="str">
-        <v>高たんぱく食、糖尿病性ケトアシドーシス、痛風発作時（酸性尿は尿酸結石のリスクを高める）</v>
+        <v/>
       </c>
       <c r="J75" t="str">
-        <v>痛風・尿酸結石がある場合は、野菜など尿をアルカリ化する食品を意識するとよいことを伝える</v>
+        <v/>
       </c>
       <c r="K75" t="str">
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>高尿酸血症・尿酸結石の患者では尿pHが酸性に傾いていないか確認する。尿アルカリ化薬（ウラリットなど）の効果判定にも使う</v>
+        <v>直接ビリルビンとの比率で原因を推測する（間接優位は溶血・体質性、直接優位は胆道系）。総ビリルビン・AST/ALTと合わせて評価する</v>
       </c>
       <c r="M75" t="str">
-        <v>高尿酸血症</v>
+        <v>肝機能</v>
       </c>
       <c r="N75" t="str">
-        <v>尿pH,尿酸性度,尿アルカリ化,ウラリット</v>
+        <v>間接ビリルビン,I-Bil,溶血</v>
       </c>
       <c r="O75" t="str">
         <v/>
@@ -3951,28 +3951,28 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>尿ケトン体</v>
+        <v>直接ビリルビン</v>
       </c>
       <c r="B76" t="str">
-        <v>尿ケトン,Ket</v>
+        <v>D-Bil</v>
       </c>
       <c r="C76" t="str">
-        <v>陰性（－）</v>
+        <v>0.0〜0.3 mg/dL程度（施設差あり）</v>
       </c>
       <c r="D76" t="str">
-        <v>体がブドウ糖の代わりに脂肪を分解してエネルギーを作っているサイン</v>
+        <v>肝臓で処理された後のビリルビン。胆道の詰まりで血液中に増える</v>
       </c>
       <c r="E76" t="str">
-        <v>この検査は、体が糖の代わりに脂肪を使ってエネルギーを作っていないかを見るものです。陽性が続くときは、食事や水分、インスリンの使い方を確認する必要があります。</v>
+        <v>直接ビリルビンは、肝臓で処理された後のビリルビンです。胆石や腫瘍などで胆汁の通り道（胆道）が詰まると、行き場を失って血液中に増え、皮膚や白目が黄色くなる黄疸として現れます。</v>
       </c>
       <c r="F76" t="str">
-        <v>糖尿病の血糖コントロール不良（シックデイ・インスリン不足）、極端な糖質制限、絶食、嘔吐・下痢による脱水</v>
+        <v>肝疾患、胆石など胆道の閉塞</v>
       </c>
       <c r="G76" t="str">
-        <v>糖尿病治療中の場合はシックデイ時の対応(インスリンを自己中断しない、水分摂取を続けるなど)を確認する。体調不良時の対応方法を事前に説明しておく</v>
+        <v>皮膚や白目の黄染、白っぽい便、濃い茶色の尿がないか確認する</v>
       </c>
       <c r="H76" t="str">
-        <v>SGLT2阻害薬(特に絶食・シックデイ時の正常血糖ケトアシドーシスに注意)</v>
+        <v>胆汁うっ滞型の薬剤性肝障害を起こしうる抗菌薬、経口避妊薬</v>
       </c>
       <c r="I76" t="str">
         <v/>
@@ -3984,13 +3984,13 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>陽性かつ高血糖・全身倦怠感が強い場合は糖尿病性ケトアシドーシスの可能性があり緊急性が高い。シックデイルールの説明歴を確認する</v>
+        <v>直接優位の上昇は胆道系（胆石、腫瘍による閉塞）を、間接優位の上昇は溶血・体質性を疑う手がかりになる。γ-GTP・ALPと合わせて胆道系疾患を評価する</v>
       </c>
       <c r="M76" t="str">
-        <v>糖尿病</v>
+        <v>肝機能</v>
       </c>
       <c r="N76" t="str">
-        <v>尿ケトン体,ケトン体,Ket,シックデイ,ケトアシドーシス</v>
+        <v>直接ビリルビン,D-Bil,胆石,胆道閉塞</v>
       </c>
       <c r="O76" t="str">
         <v/>
@@ -3998,22 +3998,22 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>ウロビリノーゲン</v>
+        <v>亜鉛（Zn）</v>
       </c>
       <c r="B77" t="str">
-        <v>Uro</v>
+        <v>Zn</v>
       </c>
       <c r="C77" t="str">
-        <v>正常（±）程度</v>
+        <v>80〜130 μg/dL程度（施設差あり）</v>
       </c>
       <c r="D77" t="str">
-        <v>肝臓や胆道、赤血球の壊れ方の状態を反映する尿検査項目</v>
+        <v>味覚や皮膚、免疫に関わる微量ミネラル。高齢者や低栄養で不足しやすい</v>
       </c>
       <c r="E77" t="str">
-        <v>ウロビリノーゲンは、赤血球やビリルビンが体の中で処理される過程でできる物質です。肝臓の働きが悪くなったり、赤血球が壊れやすくなったりすると、尿の中の量が変化します。</v>
+        <v>亜鉛は、味を感じる働きや皮膚・粘膜の健康、免疫の働きに関わる微量ミネラルです。不足すると、味がわかりにくくなったり（味覚障害）、傷が治りにくくなったりすることがあります。</v>
       </c>
       <c r="F77" t="str">
-        <v>溶血性疾患（赤血球の破壊亢進）、肝機能障害</v>
+        <v/>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -4022,101 +4022,101 @@
         <v/>
       </c>
       <c r="I77" t="str">
-        <v>胆道閉塞（胆汁が腸に流れず、ウロビリノーゲンが作られない状態）</v>
+        <v>低栄養、高齢による摂取不足、消化器手術後、亜鉛の吸収を妨げる薬剤（PPI、キレート形成する薬剤など）との併用</v>
       </c>
       <c r="J77" t="str">
-        <v/>
+        <v>味覚の変化（味を感じにくい、金属味がするなど）がないか確認する。牡蠣、赤身肉、レバーなど亜鉛を多く含む食品を意識するとよいことを伝える</v>
       </c>
       <c r="K77" t="str">
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>完全に陰性の場合は胆道閉塞を疑う所見の一つ。肝機能（AST/ALT/ビリルビン）と合わせて評価する</v>
+        <v>薬剤性の亜鉛欠乏（PPI長期使用、D-ペニシラミン、一部の降圧薬など）に注意。亜鉛欠乏による味覚障害は原因薬剤の中止・亜鉛補充で改善することがある</v>
       </c>
       <c r="M77" t="str">
-        <v>肝機能</v>
+        <v/>
       </c>
       <c r="N77" t="str">
-        <v>ウロビリノーゲン,Uro,溶血,胆道閉塞,肝機能</v>
+        <v>亜鉛,Zn,味覚障害,亜鉛欠乏</v>
       </c>
       <c r="O77" t="str">
-        <v/>
+        <v>食事と栄養 p.78（亜鉛）</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>尿潜血反応</v>
+        <v>マグネシウム（Mg）</v>
       </c>
       <c r="B78" t="str">
-        <v>尿潜血,U-OB</v>
+        <v>Mg</v>
       </c>
       <c r="C78" t="str">
-        <v>陰性（－）</v>
+        <v>1.8〜2.6 mg/dL程度（施設差あり）</v>
       </c>
       <c r="D78" t="str">
-        <v>尿に血液（赤血球）が混じっていないかを見る検査</v>
+        <v>骨や筋肉、神経の働きに関わるミネラル。低栄養や利尿薬で不足しやすい</v>
       </c>
       <c r="E78" t="str">
-        <v>この検査は、尿に目に見えないくらいの微量の血液が混じっていないかを調べるものです。陽性の場合、腎臓や膀胱、尿路のどこかに炎症や結石などがある可能性があります。</v>
+        <v>マグネシウムは、骨や筋肉、神経の働きを支えるミネラルです。不足すると、こむら返りや不整脈、だるさなどの症状が出ることがあります。</v>
       </c>
       <c r="F78" t="str">
-        <v>尿路結石、膀胱炎などの尿路感染症、腎炎、腫瘍、月経血の混入、激しい運動後</v>
+        <v>腎不全、マグネシウム製剤（酸化マグネシウムなど）の過量投与</v>
       </c>
       <c r="G78" t="str">
-        <v>排尿時の痛みや頻尿、目に見える血尿の有無を確認する。女性は月経の時期と重なっていないか確認する</v>
+        <v>腎機能低下がある患者で酸化マグネシウムなどの緩下剤を使用中は、傾眠・血圧低下などの高マグネシウム血症の症状がないか確認する</v>
       </c>
       <c r="H78" t="str">
-        <v>ワルファリン、DOAC、抗血小板薬など出血傾向を強める薬剤の服用状況を確認</v>
+        <v>マグネシウム含有制酸薬・下剤の過量(特に腎機能低下患者)</v>
       </c>
       <c r="I78" t="str">
-        <v/>
+        <v>低栄養、利尿薬の使用、慢性的な下痢、アルコール多飲、PPI長期使用</v>
       </c>
       <c r="J78" t="str">
-        <v/>
+        <v>こむら返りや動悸などの症状がないか確認する</v>
       </c>
       <c r="K78" t="str">
-        <v/>
+        <v>プロトンポンプ阻害薬(PPI)の長期使用、ループ利尿薬、サイアザイド系利尿薬、シスプラチン、アミノグリコシド系</v>
       </c>
       <c r="L78" t="str">
-        <v>陽性でも尿沈渣で赤血球が確認されない場合は偽陽性（ミオグロビン尿など）のこともある。持続する場合は泌尿器科的な精査が必要</v>
+        <v>腎機能低下患者への酸化マグネシウム投与は高マグネシウム血症のリスクがあるため定期的なモニタリングが必要。PPI長期使用も低マグネシウム血症のリスク因子として知られる</v>
       </c>
       <c r="M78" t="str">
         <v>腎機能</v>
       </c>
       <c r="N78" t="str">
-        <v>尿潜血,潜血反応,U-OB,血尿,尿路結石,膀胱炎</v>
+        <v>マグネシウム,Mg,酸化マグネシウム,こむら返り</v>
       </c>
       <c r="O78" t="str">
-        <v/>
+        <v>食事と栄養 p.84（マグネシウム）</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>尿糖（半定量）</v>
+        <v>C－ペプチド（血中）</v>
       </c>
       <c r="B79" t="str">
-        <v>尿糖,U-Glu</v>
+        <v>CPR</v>
       </c>
       <c r="C79" t="str">
-        <v>陰性（－）</v>
+        <v>空腹時 0.6〜3.0 ng/mL（施設差あり）</v>
       </c>
       <c r="D79" t="str">
-        <v>尿に糖が漏れ出ていないかを見る検査。血糖値がかなり高いと陽性になる</v>
+        <v>自分の膵臓がどれくらいインスリンを作れているかを表す指標</v>
       </c>
       <c r="E79" t="str">
-        <v>通常、糖は尿にはほとんど出ませんが、血糖値がかなり高くなると尿にあふれ出るようになります。血糖コントロールの目安の一つです。</v>
+        <v>この検査は、ご自身の膵臓がどれくらいインスリンを作る力を持っているかを見るものです。数値が低いほど、体の中で作れるインスリンが少ないことを示します。</v>
       </c>
       <c r="F79" t="str">
-        <v>糖尿病（血糖値が腎臓で再吸収できる量を超えている状態）、腎性糖尿（血糖値が正常でも体質的に出ることがある）、SGLT2阻害薬服用中（薬の作用で意図的に糖を排泄するため陽性になるのが正常）</v>
+        <v>インスリン抵抗性が強い状態（初期の2型糖尿病など）</v>
       </c>
       <c r="G79" t="str">
-        <v>SGLT2阻害薬（フォシーガ、ジャディアンスなど）服用中は、陽性が薬の効果によるものであることを説明する。脱水や尿路感染の症状がないかも確認する</v>
+        <v/>
       </c>
       <c r="H79" t="str">
-        <v>SGLT2阻害薬(薬理作用による陽性であれば想定内であることを説明)</v>
+        <v/>
       </c>
       <c r="I79" t="str">
-        <v/>
+        <v>膵臓のインスリン分泌能低下（1型糖尿病、糖尿病の進行）</v>
       </c>
       <c r="J79" t="str">
         <v/>
@@ -4125,13 +4125,13 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>SGLT2阻害薬服用中は尿糖陽性が治療効果として想定内であることを患者に伝える。血糖値・HbA1cと合わせて評価する</v>
+        <v>インスリン分泌能の評価に使われる。数値が低いほどインスリン治療の必要性が高いと判断される目安になる</v>
       </c>
       <c r="M79" t="str">
         <v>糖尿病</v>
       </c>
       <c r="N79" t="str">
-        <v>尿糖,糖半定量,U-Glu,腎性糖尿,SGLT2</v>
+        <v>C-ペプチド,Cペプチド,CPR,C-peptide,血中CPR,インスリン分泌</v>
       </c>
       <c r="O79" t="str">
         <v/>
@@ -4139,46 +4139,46 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>尿中微量アルブミン</v>
+        <v>C－ペプチドインデックス</v>
       </c>
       <c r="B80" t="str">
-        <v>U-Alb,MAU</v>
+        <v>CPI</v>
       </c>
       <c r="C80" t="str">
-        <v>30 mg/gCr未満（尿中アルブミン/クレアチニン比）</v>
+        <v>1.2以上が目安(施設・測定条件により異なる)</v>
       </c>
       <c r="D80" t="str">
-        <v>通常の尿蛋白検査では見つからない、ごく早期の腎症のサイン</v>
+        <v>血糖値に対してどれくらいインスリンを分泌できているかを表す指標。低いほどインスリン治療の必要性が高い</v>
       </c>
       <c r="E80" t="str">
-        <v>この検査は、通常の尿検査ではまだ分からないくらい早い段階の腎臓の変化を見つけるためのものです。数値が高いと、腎症の初期のサインである可能性があります。</v>
+        <v>これは、血糖値の高さに対して、体がどれくらいインスリンを作れているかを見る指標です。数値が低いほど、自分の膵臓だけでは血糖値に見合うインスリンを十分に作れていない可能性が高く、インスリン治療が必要かどうかの判断材料になります。</v>
       </c>
       <c r="F80" t="str">
-        <v>糖尿病性腎症の早期段階、高血圧</v>
+        <v>通常、臨床的意義は乏しい</v>
       </c>
       <c r="G80" t="str">
-        <v>血糖・血圧のコントロール状況を確認する。減塩や適正体重の維持など生活習慣の見直しも早期腎症の進行予防に役立つことを伝える</v>
+        <v/>
       </c>
       <c r="H80" t="str">
-        <v>NSAIDsなど腎機能を悪化させる薬剤。ACE阻害薬・ARB・SGLT2阻害薬は低下させる方向に働く</v>
+        <v/>
       </c>
       <c r="I80" t="str">
-        <v/>
+        <v>内因性インスリン分泌能の低下(1.2未満でインスリン治療の適応を検討する目安、0.8未満はインスリン療法が強く推奨される目安)</v>
       </c>
       <c r="J80" t="str">
-        <v/>
+        <v>インスリン治療の必要性について医師からどのように説明を受けているか確認する</v>
       </c>
       <c r="K80" t="str">
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>糖尿病腎症の早期発見に重要な検査。血糖・血圧コントロールで改善しうる段階なので、早期介入の意義を伝える</v>
+        <v>CPI＝血中Cペプチド(ng/mL)÷血糖値(mg/dL)×100 で算出する。空腹時に測定するのが基本で、境界値付近では食事負荷の影響を受けるため、複数回の評価や随時尿中CPRとあわせて判断することもある</v>
       </c>
       <c r="M80" t="str">
-        <v>糖尿病,腎機能</v>
+        <v>糖尿病</v>
       </c>
       <c r="N80" t="str">
-        <v>微量アルブミン,U-Alb,MAU,糖尿病性腎症,早期腎症</v>
+        <v>CPI,Cペプチドインデックス,C-ペプチドインデックス,インスリン分泌能,インスリン治療</v>
       </c>
       <c r="O80" t="str">
         <v/>
@@ -4186,116 +4186,116 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>血清鉄（Fe）</v>
+        <v>白血球数（WBC）</v>
       </c>
       <c r="B81" t="str">
-        <v>Fe</v>
+        <v>WBC</v>
       </c>
       <c r="C81" t="str">
-        <v>60〜200 μg/dL（施設差あり）</v>
+        <v>3,300〜8,600 /μL程度（施設差あり）</v>
       </c>
       <c r="D81" t="str">
-        <v>血液中を流れている鉄の量</v>
+        <v>体を細菌やウイルスから守る免疫細胞の数で、感染や炎症、薬剤の影響を反映する</v>
       </c>
       <c r="E81" t="str">
-        <v>この検査は、今血液の中を流れている鉄の量を見るものです。低いと、体の中で鉄が不足している可能性があります。</v>
+        <v>白血球は体に入ってきた細菌やウイルスと戦う免疫細胞です。感染症や炎症があると増え、逆に一部のお薬の副作用や骨髄の働きが落ちると減ることがあります。</v>
       </c>
       <c r="F81" t="str">
-        <v>鉄剤の過剰摂取、溶血、肝疾患</v>
+        <v>感染症、炎症、ステロイド使用、喫煙、白血病などの血液疾患</v>
       </c>
       <c r="G81" t="str">
-        <v/>
+        <v>発熱や体の痛みなど感染症状がないか確認する</v>
       </c>
       <c r="H81" t="str">
-        <v>鉄剤の過量摂取(小児の誤飲を含む)</v>
+        <v>ステロイド、G-CSF製剤、炭酸リチウム</v>
       </c>
       <c r="I81" t="str">
-        <v>鉄欠乏性貧血、慢性炎症、出血</v>
+        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、メルカゾールなど薬剤性の無顆粒球症、再生不良性貧血、ウイルス感染</v>
       </c>
       <c r="J81" t="str">
-        <v>鉄分の多い食品（レバー・赤身肉・魚・ほうれん草など）を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える</v>
+        <v>発熱、のどの痛みなど感染症状の初期サインがないか確認する。人混みを避け、手洗い・うがいを徹底するよう伝える</v>
       </c>
       <c r="K81" t="str">
-        <v>プロトンポンプ阻害薬(PPI)・H2ブロッカーは胃酸分泌抑制により鉄の吸収を低下させうる</v>
+        <v>抗がん剤、メルカゾール(無顆粒球症)、クロザピン(定期的な血球モニタリング必須)、サラゾスルファピリジン</v>
       </c>
       <c r="L81" t="str">
-        <v>血清鉄は日内変動が大きい。単独で判断せず総鉄結合能・フェリチンと合わせて評価する</v>
+        <v>メルカゾール（チアマゾール）は無顆粒球症の重大な副作用があり、発熱・のどの痛みが出たらすぐ受診するよう指導する。抗がん剤・免疫抑制剤・抗てんかん薬（カルバマゼピンなど）使用中も定期的なモニタリングが必要</v>
       </c>
       <c r="M81" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N81" t="str">
-        <v>血清鉄,Fe,鉄欠乏性貧血</v>
+        <v>白血球,WBC,好中球,感染症,白血病,無顆粒球症,骨髄抑制</v>
       </c>
       <c r="O81" t="str">
-        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
+        <v/>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>総鉄結合能（TIBC）</v>
+        <v>赤血球数</v>
       </c>
       <c r="B82" t="str">
-        <v>TIBC</v>
+        <v>RBC</v>
       </c>
       <c r="C82" t="str">
-        <v>250〜360 μg/dL（施設差あり）</v>
+        <v>男性 435〜555万/μL、女性 386〜492万/μL程度（施設差あり）</v>
       </c>
       <c r="D82" t="str">
-        <v>血液中のトランスフェリンが鉄と結合できる総量</v>
+        <v>血液中で酸素を運ぶ細胞の数。ヘモグロビン・ヘマトクリットと合わせて貧血・多血症を評価する</v>
       </c>
       <c r="E82" t="str">
-        <v>TIBCは、血液中でトランスフェリンという物質が鉄を運べる最大量を表します。体の中の鉄が不足すると、少しでも多く鉄を運ぼうとしてこの数値が上がる性質があります。</v>
+        <v>赤血球は、肺で受け取った酸素を全身に運ぶ血液の細胞です。数が少ないと貧血、多いと多血症が疑われます。ヘモグロビンやヘマトクリットと合わせて総合的に評価します。</v>
       </c>
       <c r="F82" t="str">
-        <v>鉄欠乏性貧血（＞360 μg/dLが目安）</v>
+        <v>脱水、多血症（真性多血症、二次性多血症）、喫煙</v>
       </c>
       <c r="G82" t="str">
-        <v/>
+        <v>脱水が疑われる場合はこまめな水分摂取を勧める（水分制限がある場合を除く）</v>
       </c>
       <c r="H82" t="str">
         <v/>
       </c>
       <c r="I82" t="str">
-        <v>慢性炎症、肝疾患、ネフローゼ症候群</v>
+        <v>貧血（鉄欠乏性貧血、腎性貧血など）、出血</v>
       </c>
       <c r="J82" t="str">
-        <v/>
+        <v>ヘモグロビンと同様に、出血や食事量低下がないか確認する</v>
       </c>
       <c r="K82" t="str">
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>鉄が不足すると、体はより多く運ぼうとしてTIBCが上昇する。UIBC・血清鉄と併せて評価する</v>
+        <v>ヘモグロビン・ヘマトクリットと同じ方向に動くことが多い。赤血球数だけでなくMCV・MCH・MCHCと合わせて貧血のタイプ(小球性・正球性・大球性)を判断する</v>
       </c>
       <c r="M82" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
       <c r="N82" t="str">
-        <v>TIBC,総鉄結合能,鉄欠乏性貧血</v>
+        <v>赤血球,RBC,貧血,多血症</v>
       </c>
       <c r="O82" t="str">
-        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
+        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>不飽和鉄結合能（UIBC）</v>
+        <v>ヘモグロビン濃度</v>
       </c>
       <c r="B83" t="str">
-        <v>UIBC</v>
+        <v>Hb</v>
       </c>
       <c r="C83" t="str">
-        <v>170〜300 μg/dL（施設差あり）</v>
+        <v>男性 13.5〜17.5 g/dL、女性 11.5〜15.0 g/dL</v>
       </c>
       <c r="D83" t="str">
-        <v>トランスフェリンのうち、まだ鉄と結合していない余力の部分（UIBC＝TIBC－血清鉄）</v>
+        <v>血液の中で酸素を運ぶ役割をしている。この値が低い状態が貧血。</v>
       </c>
       <c r="E83" t="str">
-        <v>UIBCは、トランスフェリンのうち、まだ鉄と結合していない「空き容量」の部分を表します。鉄が不足しているときほど、この空き容量は大きくなります。</v>
+        <v>ヘモグロビンは、血液の中で酸素を全身に運ぶ役割をしている赤い色素です。この値が低い状態が貧血で、体がだるくなったり、階段で息切れしやすくなったりします。</v>
       </c>
       <c r="F83" t="str">
-        <v>鉄欠乏性貧血（＞300 μg/dLが目安）</v>
+        <v/>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -4304,92 +4304,92 @@
         <v/>
       </c>
       <c r="I83" t="str">
-        <v>慢性炎症、鉄過剰状態</v>
+        <v>鉄欠乏性貧血、出血、腎性貧血、骨髄の造血機能低下</v>
       </c>
       <c r="J83" t="str">
-        <v/>
+        <v>鉄分の多い食品(レバー・赤身肉・魚・ほうれん草など)を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える。鉄剤は数値が正常化した後も体内に鉄を貯蔵するため2〜3か月程度は継続が必要なことを説明する</v>
       </c>
       <c r="K83" t="str">
-        <v/>
+        <v>NSAIDs・抗凝固薬・抗血小板薬(消化管出血のリスク)、抗がん剤、ST合剤</v>
       </c>
       <c r="L83" t="str">
-        <v>TIBCと同じ方向に動くことが多い。血清鉄・TIBCとあわせて鉄欠乏性貧血と二次性貧血の鑑別に使う</v>
+        <v>原因（出血・食事量低下など）の確認が重要。腎機能低下がある場合は鉄不足以外が原因のこともある。鉄剤はヘモグロビンが正常化した後も2〜3か月程度は継続することが多い（鉄の貯蔵分を補うため。途中でやめると再び貧血になりやすい）</v>
       </c>
       <c r="M83" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>鉄欠乏性貧血,抗血小板療法,抗凝固療法（心房細動・血栓症）</v>
       </c>
       <c r="N83" t="str">
-        <v>UIBC,不飽和鉄結合能,鉄欠乏性貧血</v>
+        <v>ヘモグロビン,Hb,貧血,鉄剤,鉄欠乏性貧血</v>
       </c>
       <c r="O83" t="str">
-        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
+        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>トランスフェリン飽和度</v>
+        <v>ヘマトクリット値</v>
       </c>
       <c r="B84" t="str">
-        <v>TSAT</v>
+        <v>Ht,Hct</v>
       </c>
       <c r="C84" t="str">
-        <v>16〜50%程度（施設差あり）</v>
+        <v>男性 40〜50%、女性 35〜45%</v>
       </c>
       <c r="D84" t="str">
-        <v>鉄を運ぶ役割のトランスフェリンのうち、実際に鉄を運んでいる割合（血清鉄÷総鉄結合能）</v>
+        <v>血液全体のうち赤血球が占める体積の割合。貧血・脱水の指標</v>
       </c>
       <c r="E84" t="str">
-        <v>トランスフェリン飽和度は、鉄を運ぶトランスフェリンのうち、実際にどれくらいが鉄を運んでいるかを割合で表したものです。鉄欠乏性貧血では低くなり、鉄が過剰にたまる病気では高くなります。</v>
+        <v>ヘマトクリットは、血液全体のうち赤血球が占める割合を表す数値です。この値が低いと貧血、高いと脱水や血液が濃くなっている状態が疑われます。</v>
       </c>
       <c r="F84" t="str">
-        <v>鉄過剰症（ヘモクロマトーシスなど）</v>
+        <v>脱水、多血症（真性多血症、二次性多血症）、喫煙</v>
       </c>
       <c r="G84" t="str">
-        <v/>
+        <v>脱水が疑われる場合はこまめな水分摂取を勧める（水分制限がある場合を除く）</v>
       </c>
       <c r="H84" t="str">
         <v/>
       </c>
       <c r="I84" t="str">
-        <v>鉄欠乏性貧血（＜16%が目安）</v>
+        <v>貧血（鉄欠乏性貧血、腎性貧血など）、出血</v>
       </c>
       <c r="J84" t="str">
-        <v/>
+        <v>ヘモグロビンと同様に、出血や食事量低下がないか確認する</v>
       </c>
       <c r="K84" t="str">
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>血清鉄をTIBCで割って計算される。鉄剤補充の効果判定にも使われる</v>
+        <v>ヘモグロビン・赤血球数と合わせて評価する。3つの値は同じ方向に動くことが多く、脱水があると貧血が見かけ上隠れることがある</v>
       </c>
       <c r="M84" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
       <c r="N84" t="str">
-        <v>トランスフェリン飽和度,TSAT,鉄欠乏性貧血</v>
+        <v>ヘマトクリット,Ht,Hct,貧血,脱水,多血症</v>
       </c>
       <c r="O84" t="str">
-        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
+        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>血清フェリチン</v>
+        <v>MCV</v>
       </c>
       <c r="B85" t="str">
-        <v>Ferritin</v>
+        <v>MCV</v>
       </c>
       <c r="C85" t="str">
-        <v>男性 20〜250 ng/mL、女性 10〜120 ng/mL（施設差あり）</v>
+        <v>79〜100 fL</v>
       </c>
       <c r="D85" t="str">
-        <v>体に貯蔵されている鉄の量を反映する指標。貧血の症状が出るより早い段階で低下する</v>
+        <v>赤血球1個の大きさ</v>
       </c>
       <c r="E85" t="str">
-        <v>フェリチンは、体に蓄えられている鉄の「貯金」の量を見る検査です。この数値が下がるのは、貧血の症状が出るよりも前の、とても早い段階のサインになります。</v>
+        <v>MCVは赤血球1個あたりの大きさを表す数値です。貧血があるとき、この数値で「小さい貧血」か「大きい貧血」かを見分けることができ、原因を絞り込む手がかりになります。</v>
       </c>
       <c r="F85" t="str">
-        <v>炎症性疾患、肝疾患、悪性腫瘍、鉄過剰症（フェリチンは炎症でも上昇するため、貧血の評価では注意が必要）</v>
+        <v/>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -4398,45 +4398,45 @@
         <v/>
       </c>
       <c r="I85" t="str">
-        <v>鉄欠乏状態（貧血の症状が出る前の早期段階から低下する）</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="J85" t="str">
-        <v>鉄分の多い食品を意識するとともに、貯蔵鉄を補うため治療は数値が正常化してからも継続が必要なことを伝える</v>
+        <v>鉄分の多い食品(レバー・赤身肉・魚・ほうれん草など)と、吸収を助けるビタミンC(柑橘類・芋類等)を一緒に摂るよう伝える</v>
       </c>
       <c r="K85" t="str">
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>貯蔵鉄の指標で鉄欠乏を最も早期に反映する。ただし炎症があると鉄欠乏があっても正常〜高値に出ることがあり、CRP等の炎症所見と合わせて評価する。二次性貧血との鑑別に重要</v>
+        <v/>
       </c>
       <c r="M85" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
       <c r="N85" t="str">
-        <v>フェリチン,Ferritin,貯蔵鉄,鉄欠乏</v>
+        <v>MCV,赤血球指数,貧血</v>
       </c>
       <c r="O85" t="str">
-        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
+        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>尿中尿酸/クレアチニン比（UUA/UCr）</v>
+        <v>MCH</v>
       </c>
       <c r="B86" t="str">
-        <v>UUA/UCr</v>
+        <v>MCH</v>
       </c>
       <c r="C86" t="str">
-        <v>0.4〜0.8程度が混合型の目安</v>
+        <v>26.3〜34.3 pg</v>
       </c>
       <c r="D86" t="str">
-        <v>尿酸が「作られすぎ」か「排泄できていない」かを見分ける比の値</v>
+        <v>赤血球1個に含まれるヘモグロビン量</v>
       </c>
       <c r="E86" t="str">
-        <v>この数値は、体の中で尿酸が「作られすぎている」のか、それとも「うまく排泄できていない」のかを見分けるために使う比の値です。高尿酸血症の治療薬を選ぶときの参考になります。</v>
+        <v>MCHは赤血球1個の中に含まれるヘモグロビン（酸素を運ぶ色素）の量を表す数値です。MCVと同じく、貧血の種類を見分けるのに使われます。</v>
       </c>
       <c r="F86" t="str">
-        <v>尿酸産生過剰型（0.8以上が目安）</v>
+        <v/>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -4445,139 +4445,139 @@
         <v/>
       </c>
       <c r="I86" t="str">
-        <v>尿酸排泄低下型（0.4以下が目安）</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="J86" t="str">
-        <v/>
+        <v>鉄分の多い食品(レバー・赤身肉・魚・ほうれん草など)と、吸収を助けるビタミンC(柑橘類・芋類等)を一緒に摂るよう伝える</v>
       </c>
       <c r="K86" t="str">
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>高尿酸血症は尿酸産生過剰型・排泄低下型・混合型に分類され、この比が目安になる。病型によって使う薬剤（尿酸生成抑制薬か尿酸排泄促進薬か）の選択が変わる</v>
+        <v/>
       </c>
       <c r="M86" t="str">
-        <v>高尿酸血症</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="N86" t="str">
-        <v>UUA,UCr,尿酸クリアランス,CUA,EUA,尿酸産生過剰型,尿酸排泄低下型</v>
+        <v>MCH,赤血球指数,貧血</v>
       </c>
       <c r="O86" t="str">
-        <v>食事と栄養 p.180-189（第2部 痛風・高尿酸血症）</v>
+        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>ucOC（低カルボキシル化オステオカルシン）</v>
+        <v>MCHC</v>
       </c>
       <c r="B87" t="str">
-        <v>ucOC</v>
+        <v>MCHC</v>
       </c>
       <c r="C87" t="str">
-        <v>4.5 ng/mL未満（施設差あり）</v>
+        <v>31.6〜36.6 %</v>
       </c>
       <c r="D87" t="str">
-        <v>ビタミンKが不足していないかを反映する骨の指標</v>
+        <v>単位容積あたりの赤血球に含まれるヘモグロビン濃度</v>
       </c>
       <c r="E87" t="str">
-        <v>ucOCは、骨を作るために必要なビタミンKが体の中で足りているかどうかを反映する検査です。数値が高いとビタミンK不足が疑われます。</v>
+        <v>MCHCは、赤血球の中にヘモグロビンがどれくらい濃く詰まっているかを表す数値です。鉄が不足すると、この濃度も薄くなる傾向があります。</v>
       </c>
       <c r="F87" t="str">
-        <v>ビタミンK不足状態</v>
+        <v/>
       </c>
       <c r="G87" t="str">
-        <v>ビタミンK2製剤(骨粗鬆症治療薬)の適応が検討されているか確認する。ワルファリン服用中の患者では、納豆などビタミンKを多く含む食品の急な摂取量の変化を避けるよう説明する</v>
+        <v/>
       </c>
       <c r="H87" t="str">
         <v/>
       </c>
       <c r="I87" t="str">
-        <v/>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="J87" t="str">
-        <v/>
+        <v>鉄分の多い食品(レバー・赤身肉・魚・ほうれん草など)と、吸収を助けるビタミンC(柑橘類・芋類等)を一緒に摂るよう伝える</v>
       </c>
       <c r="K87" t="str">
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>ビタミンK2製剤（骨粗鬆症治療薬）の適応判断や効果判定に使われる</v>
+        <v/>
       </c>
       <c r="M87" t="str">
-        <v>骨粗鬆症</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="N87" t="str">
-        <v>ucOC,オステオカルシン,ビタミンK</v>
+        <v>MCHC,赤血球指数,貧血</v>
       </c>
       <c r="O87" t="str">
-        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
+        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>PTH（副甲状腺ホルモン）</v>
+        <v>血小板数</v>
       </c>
       <c r="B88" t="str">
-        <v>PTH</v>
+        <v>Plt</v>
       </c>
       <c r="C88" t="str">
-        <v>10〜65 pg/mL（施設差あり）</v>
+        <v>15.0〜35.0万/μL程度（施設差あり）</v>
       </c>
       <c r="D88" t="str">
-        <v>血液中のカルシウム濃度を調節するホルモン</v>
+        <v>出血を止める働きをする血液成分で、少なすぎると出血しやすくなる</v>
       </c>
       <c r="E88" t="str">
-        <v>PTHは、血液中のカルシウム濃度を一定に保つために働くホルモンです。カルシウムが低くなると分泌が増え、骨からカルシウムを取り出したり、腎臓での再吸収を促したりして数値を戻そうとします。</v>
+        <v>血小板は、血管が傷ついたときに集まって血を止める役割をする血液の成分です。数が少ないとあざができやすくなったり、出血が止まりにくくなったりします。抗血小板薬や抗がん剤を使っている方では、定期的にチェックすることが大切です。</v>
       </c>
       <c r="F88" t="str">
-        <v>原発性・二次性副甲状腺機能亢進症（腎不全に伴うものなど）</v>
+        <v>炎症性疾患、鉄欠乏性貧血、脾摘後、骨髄増殖性疾患</v>
       </c>
       <c r="G88" t="str">
-        <v/>
+        <v>出血傾向はなく経過観察でよいことが多いが、片側の腫れ・しびれなど血栓症状がないかも念のため確認する</v>
       </c>
       <c r="H88" t="str">
         <v/>
       </c>
       <c r="I88" t="str">
-        <v>副甲状腺機能低下症</v>
+        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、肝硬変・脾機能亢進、再生不良性貧血、抗てんかん薬（バルプロ酸など）の副作用、ITP（特発性血小板減少性紫斑病）</v>
       </c>
       <c r="J88" t="str">
-        <v/>
+        <v>あざができやすい、歯ぐきや鼻からの出血が増えていないか確認する。強い運動や転倒によるけがに注意するよう伝え、歯みがきは柔らかめのブラシを勧める</v>
       </c>
       <c r="K88" t="str">
-        <v/>
+        <v>ヘパリン(HIT: ヘパリン起因性血小板減少症)、バルプロ酸、抗がん剤、リネゾリド</v>
       </c>
       <c r="L88" t="str">
-        <v>骨粗鬆症の二次性原因（副甲状腺機能亢進症）を除外するための検査。カルシウム・リンと合わせて評価する</v>
+        <v>抗血小板薬・抗凝固薬使用中に血小板減少があると出血リスクがさらに高まる。抗がん剤・バルプロ酸・カルバマゼピンなど骨髄抑制のリスクがある薬剤使用中は定期採血の実施状況を確認する</v>
       </c>
       <c r="M88" t="str">
-        <v>骨粗鬆症</v>
+        <v>てんかん,抗血小板療法</v>
       </c>
       <c r="N88" t="str">
-        <v>PTH,副甲状腺ホルモン,パラトルモン</v>
+        <v>血小板,Plt,platelet,出血,あざ,紫斑,骨髄抑制</v>
       </c>
       <c r="O88" t="str">
-        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
+        <v/>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>尿中NTX</v>
+        <v>RDW-SD</v>
       </c>
       <c r="B89" t="str">
-        <v>NTX</v>
+        <v>RDW-SD</v>
       </c>
       <c r="C89" t="str">
-        <v>施設差が大きく一律の記載が難しい（尿中）</v>
+        <v>39〜46 fL程度（施設差あり）</v>
       </c>
       <c r="D89" t="str">
-        <v>骨が壊されるときに出る、骨吸収マーカーのひとつ</v>
+        <v>赤血球の大きさのばらつきを表す指標(絶対値)。鉄欠乏性貧血などの初期変化を捉えやすい</v>
       </c>
       <c r="E89" t="str">
-        <v>NTXは、骨が壊される（吸収される）ときに尿の中に出てくる物質です。骨粗鬆症の治療薬がどれくらい効いているかを確認するために使われます。</v>
+        <v>RDW-SDは、赤血球の大きさがどれくらいバラバラになっているかを表す数値です。貧血の原因を調べる際、鉄が足りなくなり始めた早い段階での変化を捉えるのに役立ちます。</v>
       </c>
       <c r="F89" t="str">
-        <v>骨代謝回転の亢進（骨粗鬆症、閉経後など）</v>
+        <v>鉄欠乏性貧血の初期、混合性貧血（複数の原因が重なっている状態）、赤血球産生の乱れ</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -4586,7 +4586,7 @@
         <v/>
       </c>
       <c r="I89" t="str">
-        <v>骨吸収抑制薬（ビスホスホネート等）による治療効果</v>
+        <v/>
       </c>
       <c r="J89" t="str">
         <v/>
@@ -4595,36 +4595,36 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>治療開始後3〜6か月で再検し、薬の効果判定に使われる。TRACP-5bと同じ「骨を壊す側」の指標</v>
+        <v>MCVが正常範囲でもRDWが上昇している場合、鉄欠乏の初期段階を示唆することがある。MCV・MCHと合わせて評価する</v>
       </c>
       <c r="M89" t="str">
-        <v>骨粗鬆症</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="N89" t="str">
-        <v>NTX,尿中NTX,骨吸収マーカー</v>
+        <v>RDW-SD,赤血球分布幅,貧血,鉄欠乏</v>
       </c>
       <c r="O89" t="str">
-        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
+        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>カルシトニン</v>
+        <v>RDW-CV</v>
       </c>
       <c r="B90" t="str">
-        <v>CT</v>
+        <v>RDW-CV</v>
       </c>
       <c r="C90" t="str">
-        <v>男性 9.52 pg/mL未満、女性 6.40 pg/mL未満（施設差あり）</v>
+        <v>11.5〜14.5%程度（施設差あり）</v>
       </c>
       <c r="D90" t="str">
-        <v>血液中のカルシウムを下げる方向に働くホルモン</v>
+        <v>赤血球の大きさのばらつきを割合(%)で表した指標</v>
       </c>
       <c r="E90" t="str">
-        <v>カルシトニンは、PTHとは逆に血液中のカルシウムを下げる方向に働くホルモンです。特定の甲状腺の病気（甲状腺髄様癌）がないかを調べる際にも使われます。</v>
+        <v>RDW-CVもRDW-SDと同じく、赤血球の大きさのばらつきを表す数値ですが、こちらは割合(%)で示されます。貧血のタイプを見分ける手がかりになります。</v>
       </c>
       <c r="F90" t="str">
-        <v>甲状腺髄様癌、腎不全</v>
+        <v>鉄欠乏性貧血、ビタミンB12・葉酸欠乏性貧血、混合性貧血</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -4642,36 +4642,36 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>骨粗鬆症の二次性原因の除外目的で測定されることがある検査値。同名の薬剤（カルシトニン製剤）と混同しないよう注意</v>
+        <v>RDW-SDと同様の意味を持つ指標。MCVが小さくRDWが高ければ鉄欠乏性貧血、MCVが大きくRDWが高ければビタミンB12・葉酸欠乏を疑う手がかりになる</v>
       </c>
       <c r="M90" t="str">
-        <v>骨粗鬆症</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="N90" t="str">
-        <v>カルシトニン,CT</v>
+        <v>RDW-CV,赤血球分布幅,貧血,ビタミンB12,葉酸</v>
       </c>
       <c r="O90" t="str">
-        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
+        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>DPD（デオキシピリジノリン）</v>
+        <v>好中球実数値</v>
       </c>
       <c r="B91" t="str">
-        <v>DPD</v>
+        <v>Neutro#,ANC</v>
       </c>
       <c r="C91" t="str">
-        <v>施設差が大きく一律の記載が難しい（尿中）</v>
+        <v>2,000〜7,500 /μL程度（施設差あり、白血球数×好中球%で算出）</v>
       </c>
       <c r="D91" t="str">
-        <v>骨のコラーゲンが壊れるときに出る、骨吸収マーカーのひとつ</v>
+        <v>好中球の絶対数。感染症リスクを判断する上で割合(%)より重要な指標</v>
       </c>
       <c r="E91" t="str">
-        <v>DPDも、骨が壊されるときに尿に出てくる物質の一つです。NTXと同じように、骨粗鬆症治療薬の効果を確認するために使われます。</v>
+        <v>これは好中球の実際の数を表す数値です。割合(%)だけでなく、実際の数がどれくらいあるかを見ることで、感染症にかかりやすい状態かどうかをより正確に判断できます。</v>
       </c>
       <c r="F91" t="str">
-        <v>骨代謝回転の亢進（骨粗鬆症など）</v>
+        <v>細菌感染症、炎症、ステロイド使用</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -4680,54 +4680,54 @@
         <v/>
       </c>
       <c r="I91" t="str">
-        <v>骨吸収抑制薬による治療効果</v>
+        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、メルカゾールなど薬剤性の無顆粒球症（1,000/μL未満で好中球減少症、500/μL未満で重症感染リスクが著しく上昇）</v>
       </c>
       <c r="J91" t="str">
-        <v/>
+        <v>発熱、のどの痛みなど感染症状の初期サインがないか確認する。人混みを避け、手洗い・うがいを徹底するよう伝える</v>
       </c>
       <c r="K91" t="str">
-        <v/>
+        <v>抗がん剤、メルカゾール(無顆粒球症)、クロザピン、サラゾスルファピリジン</v>
       </c>
       <c r="L91" t="str">
-        <v>NTX・CTXと同じ「骨を壊す側」の指標。食事の影響を受けにくいとされる</v>
+        <v>抗がん剤・メルカゾール・カルバマゼピンなど骨髄抑制のリスクがある薬剤使用中は特に重視すべき数値。500/μL未満は発熱性好中球減少症のリスクが高く緊急性が高い</v>
       </c>
       <c r="M91" t="str">
-        <v>骨粗鬆症</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N91" t="str">
-        <v>DPD,デオキシピリジノリン,骨吸収マーカー</v>
+        <v>好中球実数値,好中球数,ANC,無顆粒球症,発熱性好中球減少症</v>
       </c>
       <c r="O91" t="str">
-        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
+        <v/>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>CTX</v>
+        <v>好酸球実数値</v>
       </c>
       <c r="B92" t="str">
-        <v>CTX</v>
+        <v>Eosino#</v>
       </c>
       <c r="C92" t="str">
-        <v>施設差が大きく一律の記載が難しい（血清・尿中）</v>
+        <v>100〜500 /μL程度（施設差あり）</v>
       </c>
       <c r="D92" t="str">
-        <v>骨のコラーゲンが壊れるときに出る、骨吸収マーカーのひとつ</v>
+        <v>好酸球の絶対数。アレルギーや薬剤反応の程度をより正確に評価できる</v>
       </c>
       <c r="E92" t="str">
-        <v>CTXも、骨が壊されるときに血液や尿に出てくる物質です。骨粗鬆症治療薬（骨を壊すのを抑える薬）の効果を確認するために使われます。</v>
+        <v>これは好酸球の実際の数を表す数値です。割合(%)だけでなく実数を見ることで、アレルギー反応の強さをより正確に把握できます。</v>
       </c>
       <c r="F92" t="str">
-        <v>骨代謝回転の亢進（骨粗鬆症など）</v>
+        <v>アレルギー性疾患、薬剤アレルギー、寄生虫感染</v>
       </c>
       <c r="G92" t="str">
-        <v/>
+        <v>新しく始めた薬がないか確認する</v>
       </c>
       <c r="H92" t="str">
-        <v/>
+        <v>薬剤性好酸球増多(抗菌薬・NSAIDs・抗てんかん薬など)。発熱や皮疹を伴う場合はDRESS症候群にも注意</v>
       </c>
       <c r="I92" t="str">
-        <v>骨吸収抑制薬による治療効果</v>
+        <v/>
       </c>
       <c r="J92" t="str">
         <v/>
@@ -4736,36 +4736,36 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>NTX・DPDと同じ「骨を壊す側」の指標。血清・尿中いずれでも測定されることがある</v>
+        <v>薬剤性過敏症症候群(DIHS)などでは著明な好酸球増多を認めることがあり、原因薬剤の特定に役立つ</v>
       </c>
       <c r="M92" t="str">
-        <v>骨粗鬆症</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N92" t="str">
-        <v>CTX,骨吸収マーカー</v>
+        <v>好酸球実数値,好酸球数,アレルギー,DIHS</v>
       </c>
       <c r="O92" t="str">
-        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
+        <v/>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>P1NP</v>
+        <v>好塩基球実数値</v>
       </c>
       <c r="B93" t="str">
-        <v>P1NP</v>
+        <v>Baso#</v>
       </c>
       <c r="C93" t="str">
-        <v>施設差が大きく一律の記載が難しい（血清）</v>
+        <v>0〜100 /μL程度（施設差あり）</v>
       </c>
       <c r="D93" t="str">
-        <v>骨が新しく作られるときに出る、骨形成マーカーのひとつ</v>
+        <v>好塩基球の絶対数</v>
       </c>
       <c r="E93" t="str">
-        <v>P1NPは、CTXなどとは逆に、骨が新しく作られるときに血液中に出てくる物質です。骨を作る力を高める薬（テリパラチドなど）の効果を確認するために使われます。</v>
+        <v>これは好塩基球の実際の数を表す数値です。数がとても少ない種類の血球なので、通常は大きな変動を示すことは多くありません。</v>
       </c>
       <c r="F93" t="str">
-        <v>骨代謝回転の亢進、骨形成促進薬による治療効果</v>
+        <v>慢性骨髄性白血病などの血液疾患、アレルギー性疾患</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -4774,7 +4774,7 @@
         <v/>
       </c>
       <c r="I93" t="str">
-        <v>骨形成の低下</v>
+        <v/>
       </c>
       <c r="J93" t="str">
         <v/>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>TRACP-5b等「骨を壊す側」の指標とは逆の、「骨を作る側」の指標。骨形成促進薬（テリパラチド等）の効果判定に使われる</v>
+        <v>単独での臨床的意義は乏しく、他の血球指標（白血球分画全体）と合わせて評価する</v>
       </c>
       <c r="M93" t="str">
-        <v>骨粗鬆症</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N93" t="str">
-        <v>P1NP,骨形成マーカー</v>
+        <v>好塩基球実数値,好塩基球数</v>
       </c>
       <c r="O93" t="str">
-        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
+        <v/>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>抗甲状腺マイクロゾーム抗体（抗TPO抗体）</v>
+        <v>リンパ球実数値</v>
       </c>
       <c r="B94" t="str">
-        <v>TPOAb</v>
+        <v>Lympho#,ALC</v>
       </c>
       <c r="C94" t="str">
-        <v>陰性（16 IU/mL未満程度、施設差あり）</v>
+        <v>1,000〜3,600 /μL程度（施設差あり）</v>
       </c>
       <c r="D94" t="str">
-        <v>自分の甲状腺を攻撃する抗体が出ていないかを見る検査</v>
+        <v>リンパ球の絶対数。免疫力の目安として使われる</v>
       </c>
       <c r="E94" t="str">
-        <v>この検査は、体の中に自分の甲状腺を誤って攻撃してしまう抗体がないかを見るものです。陽性の場合、橋本病（慢性甲状腺炎）など甲状腺の自己免疫的な炎症が背景にある可能性があります。</v>
+        <v>これはリンパ球の実際の数を表す数値です。免疫力の目安の一つとして使われ、抗がん剤や免疫抑制剤の副作用モニタリングにも用いられます。</v>
       </c>
       <c r="F94" t="str">
-        <v>橋本病（慢性甲状腺炎）、バセドウ病などの自己免疫性甲状腺疾患</v>
+        <v>ウイルス感染症、リンパ性白血病などの血液疾患</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -4821,45 +4821,45 @@
         <v/>
       </c>
       <c r="I94" t="str">
-        <v/>
+        <v>抗がん剤・免疫抑制剤・ステロイドの使用、強いストレス、AIDSなどの免疫不全</v>
       </c>
       <c r="J94" t="str">
-        <v/>
+        <v>感染予防（手洗い・うがい、人混みを避ける）を意識するよう伝える</v>
       </c>
       <c r="K94" t="str">
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>陽性でも必ずしも甲状腺機能異常があるとは限らない。TSH・FT4など甲状腺ホルモンの数値と合わせて評価する</v>
+        <v>免疫抑制剤・抗がん剤治療中のモニタリング指標としても使われる。著明な低下時は日和見感染のリスクが高まる</v>
       </c>
       <c r="M94" t="str">
-        <v>甲状腺疾患</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N94" t="str">
-        <v>抗TPO抗体,抗甲状腺マイクロゾーム抗体,TPOAb,橋本病</v>
+        <v>リンパ球実数値,リンパ球数,ALC,免疫抑制剤,日和見感染</v>
       </c>
       <c r="O94" t="str">
-        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
+        <v/>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>抗サイログロブリン抗体</v>
+        <v>単球実数値</v>
       </c>
       <c r="B95" t="str">
-        <v>TgAb</v>
+        <v>Mono#</v>
       </c>
       <c r="C95" t="str">
-        <v>陰性（28 IU/mL未満程度、施設差あり）</v>
+        <v>200〜600 /μL程度（施設差あり）</v>
       </c>
       <c r="D95" t="str">
-        <v>甲状腺のたんぱく質（サイログロブリン）への抗体が出ていないかを見る検査</v>
+        <v>単球の絶対数</v>
       </c>
       <c r="E95" t="str">
-        <v>この検査も、抗TPO抗体と同じく、甲状腺に対する自己免疫の有無を見るものです。あわせて調べることで橋本病などの診断の参考にします。</v>
+        <v>これは単球の実際の数を表す数値です。慢性的な炎症や感染症の状態を把握する材料の一つになります。</v>
       </c>
       <c r="F95" t="str">
-        <v>橋本病（慢性甲状腺炎）、バセドウ病などの自己免疫性甲状腺疾患</v>
+        <v>慢性感染症、炎症性疾患、血液疾患</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -4877,60 +4877,60 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>抗TPO抗体とあわせて測定されることが多い。単独の高値だけで治療方針が決まるわけではない</v>
+        <v>単独での臨床的意義は乏しく、他の血球指標と合わせて評価する</v>
       </c>
       <c r="M95" t="str">
-        <v>甲状腺疾患</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N95" t="str">
-        <v>抗サイログロブリン抗体,TgAb,橋本病</v>
+        <v>単球実数値,単球数</v>
       </c>
       <c r="O95" t="str">
-        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
+        <v/>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>血中薬物濃度（TDM）</v>
+        <v>好中球</v>
       </c>
       <c r="B96" t="str">
-        <v>TDM</v>
+        <v>Neutro,Neut%</v>
       </c>
       <c r="C96" t="str">
-        <v>薬剤ごとに有効域が異なる（例：カルバマゼピン 4〜12 μg/mL、バルプロ酸 40〜100 μg/mL、フェニトイン 10〜20 μg/mL）</v>
+        <v>40〜75%程度（施設差あり）</v>
       </c>
       <c r="D96" t="str">
-        <v>治療域が狭い薬剤で、血液中の薬の濃度が効果域・中毒域のどちらにあるかを確認する検査</v>
+        <v>白血球の中で最も多くを占め、細菌感染と戦う主力の免疫細胞の割合</v>
       </c>
       <c r="E96" t="str">
-        <v>この薬は効く量と副作用が出る量が近いため、血液中の薬の濃度を定期的に測って、ちょうどよい範囲に入っているかを確認します。数値が低いと効果が不十分になり、高いと副作用が出やすくなります。</v>
+        <v>好中球は、白血球の中で最も数が多く、細菌が体に入ってきたときに真っ先に戦ってくれる免疫細胞です。感染症や炎症があると増え、逆に薬の副作用などで減ることがあります。</v>
       </c>
       <c r="F96" t="str">
-        <v>過量投与、代謝を妨げる薬剤との併用、肝機能低下による代謝低下</v>
+        <v>細菌感染症、炎症、ストレス、ステロイド使用</v>
       </c>
       <c r="G96" t="str">
-        <v>ふらつき、眠気、めまい、物が二重に見えるなどの中毒症状がないか確認する</v>
+        <v>発熱や炎症症状がないか確認する</v>
       </c>
       <c r="H96" t="str">
         <v/>
       </c>
       <c r="I96" t="str">
-        <v>飲み忘れ、自己判断による減量、代謝を促進する薬剤との併用（相互作用）</v>
+        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、ウイルス感染、メルカゾールなど薬剤性の無顆粒球症</v>
       </c>
       <c r="J96" t="str">
-        <v>発作やてんかん症状の再発がないか確認し、飲み忘れがないか一緒に確認する</v>
+        <v>発熱やのどの痛みなど感染症状の初期サインがないか確認する</v>
       </c>
       <c r="K96" t="str">
-        <v/>
+        <v>抗がん剤、メルカゾール(無顆粒球症)、クロザピン、サラゾスルファピリジン</v>
       </c>
       <c r="L96" t="str">
-        <v>採血のタイミング（トラフ値かどうか）で数値の解釈が変わるため採血時点を確認する。カルバマゼピンは自己誘導により長期使用で濃度が下がることがある点にも注意</v>
+        <v>好中球の絶対数（好中球実数値）が500/μL未満になると重篤な感染症のリスクが高まる。割合(%)だけでなく実数値も合わせて確認する</v>
       </c>
       <c r="M96" t="str">
-        <v>てんかん</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N96" t="str">
-        <v>TDM,血中薬物濃度,治療域,中毒域,カルバマゼピン,フェニトイン,バルプロ酸,抗てんかん薬</v>
+        <v>好中球,Neutro,Neut,感染症,無顆粒球症</v>
       </c>
       <c r="O96" t="str">
         <v/>
@@ -4938,31 +4938,31 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>アミラーゼ（AMY）</v>
+        <v>好酸球</v>
       </c>
       <c r="B97" t="str">
-        <v>AMY</v>
+        <v>Eosino,Eos%</v>
       </c>
       <c r="C97" t="str">
-        <v>44〜132 U/L（施設差あり）</v>
+        <v>1〜5%程度（施設差あり）</v>
       </c>
       <c r="D97" t="str">
-        <v>膵臓や唾液腺から出る消化酵素。膵炎などで血液中に漏れ出す</v>
+        <v>アレルギー反応や寄生虫感染に関わる白血球の一種の割合</v>
       </c>
       <c r="E97" t="str">
-        <v>アミラーゼは、でんぷんを分解する消化酵素で、主に膵臓と唾液腺から作られます。膵臓に炎症が起きると血液中に漏れ出して数値が上がるため、膵炎の診断や経過観察に使われます。</v>
+        <v>好酸球は、アレルギー反応や寄生虫感染と関係が深い免疫細胞です。アレルギー性の病気や薬の副作用（薬疹など）で増えることがあります。</v>
       </c>
       <c r="F97" t="str">
-        <v>急性膵炎、慢性膵炎の急性増悪、耳下腺炎（おたふくかぜ）、腎不全</v>
+        <v>アレルギー性疾患（気管支喘息、アトピー性皮膚炎など）、薬剤アレルギー、寄生虫感染</v>
       </c>
       <c r="G97" t="str">
-        <v>飲酒を控え、脂っこい食事を避けるよう伝える。強い腹痛・背部痛がある場合は急性膵炎の可能性もあるため早めの受診を勧める</v>
+        <v>新しく始めた薬がないか確認する。皮疹やかゆみなどアレルギー症状の有無を確認する</v>
       </c>
       <c r="H97" t="str">
-        <v>バルプロ酸、アザチオプリン、サイアザイド系・ループ利尿薬、ステロイドなど薬剤性膵炎の原因薬</v>
+        <v>薬剤性好酸球増多(抗菌薬・NSAIDs・抗てんかん薬など)。発熱や皮疹を伴う場合はDRESS症候群にも注意</v>
       </c>
       <c r="I97" t="str">
-        <v>慢性膵炎の進行期（膵臓の機能低下）</v>
+        <v/>
       </c>
       <c r="J97" t="str">
         <v/>
@@ -4971,13 +4971,13 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>膵臓由来か唾液腺由来かを区別するには膵型アミラーゼ(P-AMY)を確認する。急性膵炎では強い腹痛・背部痛を伴うことが多く、飲酒歴の確認も重要</v>
+        <v>薬剤性の好酸球増多は、原因薬剤の中止で改善することが多い。新規薬剤開始後の皮疹・発熱と合わせて薬剤性過敏症症候群(DIHS)を疑う材料になる</v>
       </c>
       <c r="M97" t="str">
-        <v/>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N97" t="str">
-        <v>アミラーゼ,AMY,膵炎,急性膵炎</v>
+        <v>好酸球,Eosino,Eos,アレルギー,薬疹,DIHS</v>
       </c>
       <c r="O97" t="str">
         <v/>
@@ -4985,25 +4985,25 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>間接ビリルビン</v>
+        <v>好塩基球</v>
       </c>
       <c r="B98" t="str">
-        <v>I-Bil</v>
+        <v>Baso,Baso%</v>
       </c>
       <c r="C98" t="str">
-        <v>0.2〜0.8 mg/dL程度（施設差あり）</v>
+        <v>0〜2%程度（施設差あり）</v>
       </c>
       <c r="D98" t="str">
-        <v>赤血球が壊れてできるビリルビンのうち、肝臓で処理される前の形</v>
+        <v>白血球の中で最も数が少なく、アレルギー反応に関わる細胞の割合</v>
       </c>
       <c r="E98" t="str">
-        <v>間接ビリルビンは、赤血球が壊れてできたビリルビンが、まだ肝臓で処理される前の状態です。この値が高い場合、赤血球が通常より多く壊れている(溶血)か、肝臓での処理能力に生まれつきの体質差(体質性黄疸)がある可能性が考えられます。</v>
+        <v>好塩基球は白血球の中で最も数が少ない種類で、アレルギー反応や炎症に関わっています。数値の変動が病気の診断に直接使われることは少ない検査です。</v>
       </c>
       <c r="F98" t="str">
-        <v>溶血性疾患（自己免疫性溶血性貧血、血液型不適合輸血など）、体質性黄疸（ジルベール症候群）、新生児黄疸</v>
+        <v>慢性骨髄性白血病などの血液疾患、アレルギー性疾患、甲状腺機能低下症</v>
       </c>
       <c r="G98" t="str">
-        <v>皮膚や白目の黄染、尿の色の変化がないか確認する</v>
+        <v/>
       </c>
       <c r="H98" t="str">
         <v/>
@@ -5018,13 +5018,13 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>直接ビリルビンとの比率で原因を推測する（間接優位は溶血・体質性、直接優位は胆道系）。総ビリルビン・AST/ALTと合わせて評価する</v>
+        <v>単独での臨床的意義は乏しいが、著明な増加は血液疾患（慢性骨髄性白血病等）の可能性があり他の血球指標と合わせて評価する</v>
       </c>
       <c r="M98" t="str">
-        <v>肝機能</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N98" t="str">
-        <v>間接ビリルビン,I-Bil,溶血</v>
+        <v>好塩基球,Baso,アレルギー,白血病</v>
       </c>
       <c r="O98" t="str">
         <v/>
@@ -5032,46 +5032,46 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>直接ビリルビン</v>
+        <v>リンパ球</v>
       </c>
       <c r="B99" t="str">
-        <v>D-Bil</v>
+        <v>Lympho,Lym%</v>
       </c>
       <c r="C99" t="str">
-        <v>0.0〜0.3 mg/dL程度（施設差あり）</v>
+        <v>18〜49%程度（施設差あり）</v>
       </c>
       <c r="D99" t="str">
-        <v>肝臓で処理された後のビリルビン。胆道の詰まりで血液中に増える</v>
+        <v>ウイルス感染と戦い、免疫の記憶を担う白血球の割合</v>
       </c>
       <c r="E99" t="str">
-        <v>直接ビリルビンは、肝臓で処理された後のビリルビンです。胆石や腫瘍などで胆汁の通り道（胆道）が詰まると、行き場を失って血液中に増え、皮膚や白目が黄色くなる黄疸として現れます。</v>
+        <v>リンパ球は、ウイルスと戦ったり、一度かかった病気を記憶して免疫をつくったりする細胞です。ウイルス感染で増え、抗がん剤の副作用や強いストレスで減ることがあります。</v>
       </c>
       <c r="F99" t="str">
-        <v>肝疾患、胆石など胆道の閉塞</v>
+        <v>ウイルス感染症、リンパ性白血病などの血液疾患、百日咳</v>
       </c>
       <c r="G99" t="str">
-        <v>皮膚や白目の黄染、白っぽい便、濃い茶色の尿がないか確認する</v>
+        <v/>
       </c>
       <c r="H99" t="str">
-        <v>胆汁うっ滞型の薬剤性肝障害を起こしうる抗菌薬、経口避妊薬</v>
+        <v/>
       </c>
       <c r="I99" t="str">
-        <v/>
+        <v>抗がん剤・免疫抑制剤・ステロイドの使用、強いストレス、AIDSなどの免疫不全</v>
       </c>
       <c r="J99" t="str">
-        <v/>
+        <v>免疫が下がっている可能性があるため、感染予防（手洗い・うがい、人混みを避ける）を意識するよう伝える</v>
       </c>
       <c r="K99" t="str">
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>直接優位の上昇は胆道系（胆石、腫瘍による閉塞）を、間接優位の上昇は溶血・体質性を疑う手がかりになる。γ-GTP・ALPと合わせて胆道系疾患を評価する</v>
+        <v>ステロイド・免疫抑制剤使用中はリンパ球減少による易感染性に注意。好中球と逆方向に動くことが多い（ウイルス感染ではリンパ球優位、細菌感染では好中球優位になりやすい）</v>
       </c>
       <c r="M99" t="str">
-        <v>肝機能</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N99" t="str">
-        <v>直接ビリルビン,D-Bil,胆石,胆道閉塞</v>
+        <v>リンパ球,Lympho,Lym,ウイルス感染,免疫抑制剤,ステロイド</v>
       </c>
       <c r="O99" t="str">
         <v/>
@@ -5079,22 +5079,22 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>亜鉛（Zn）</v>
+        <v>単球</v>
       </c>
       <c r="B100" t="str">
-        <v>Zn</v>
+        <v>Mono,Mono%</v>
       </c>
       <c r="C100" t="str">
-        <v>80〜130 μg/dL程度（施設差あり）</v>
+        <v>2〜10%程度（施設差あり）</v>
       </c>
       <c r="D100" t="str">
-        <v>味覚や皮膚、免疫に関わる微量ミネラル。高齢者や低栄養で不足しやすい</v>
+        <v>感染や炎症の後始末をする白血球の一種の割合</v>
       </c>
       <c r="E100" t="str">
-        <v>亜鉛は、味を感じる働きや皮膚・粘膜の健康、免疫の働きに関わる微量ミネラルです。不足すると、味がわかりにくくなったり（味覚障害）、傷が治りにくくなったりすることがあります。</v>
+        <v>単球は、細菌などを取り込んで処理したり、組織の修復に関わったりする免疫細胞です。慢性的な炎症や感染症の回復期に増えることがあります。</v>
       </c>
       <c r="F100" t="str">
-        <v/>
+        <v>慢性感染症（結核など）、炎症性疾患、血液疾患、感染症の回復期</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -5103,72 +5103,72 @@
         <v/>
       </c>
       <c r="I100" t="str">
-        <v>低栄養、高齢による摂取不足、消化器手術後、亜鉛の吸収を妨げる薬剤（PPI、キレート形成する薬剤など）との併用</v>
+        <v/>
       </c>
       <c r="J100" t="str">
-        <v>味覚の変化（味を感じにくい、金属味がするなど）がないか確認する。牡蠣、赤身肉、レバーなど亜鉛を多く含む食品を意識するとよいことを伝える</v>
+        <v/>
       </c>
       <c r="K100" t="str">
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>薬剤性の亜鉛欠乏（PPI長期使用、D-ペニシラミン、一部の降圧薬など）に注意。亜鉛欠乏による味覚障害は原因薬剤の中止・亜鉛補充で改善することがある</v>
+        <v>単独での臨床的意義は乏しく、他の血球指標や炎症マーカー(CRPなど)と合わせて評価する</v>
       </c>
       <c r="M100" t="str">
-        <v/>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N100" t="str">
-        <v>亜鉛,Zn,味覚障害,亜鉛欠乏</v>
+        <v>単球,Mono,慢性感染症,結核,炎症</v>
       </c>
       <c r="O100" t="str">
-        <v>食事と栄養 p.78（亜鉛）</v>
+        <v/>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>マグネシウム（Mg）</v>
+        <v>Dダイマー</v>
       </c>
       <c r="B101" t="str">
-        <v>Mg</v>
+        <v>D-dimer</v>
       </c>
       <c r="C101" t="str">
-        <v>1.8〜2.6 mg/dL程度（施設差あり）</v>
+        <v>1.0 μg/mL以下(施設・測定法により異なる)</v>
       </c>
       <c r="D101" t="str">
-        <v>骨や筋肉、神経の働きに関わるミネラル。低栄養や利尿薬で不足しやすい</v>
+        <v>体の中で血栓ができて溶けた(線溶)ときにできる分解産物で、血栓症の有無をスクリーニングする指標</v>
       </c>
       <c r="E101" t="str">
-        <v>マグネシウムは、骨や筋肉、神経の働きを支えるミネラルです。不足すると、こむら返りや不整脈、だるさなどの症状が出ることがあります。</v>
+        <v>Dダイマーは、血管の中に血のかたまり(血栓)ができて、それが溶かされるときにできる物質です。この数値が高いと、どこかに血栓ができている可能性を考えます。ただし手術後や妊娠中、高齢の方などでも上がることがあるため、この数値だけで診断が決まるわけではありません。</v>
       </c>
       <c r="F101" t="str">
-        <v>腎不全、マグネシウム製剤（酸化マグネシウムなど）の過量投与</v>
+        <v>深部静脈血栓症(DVT)・肺血栓塞栓症(PE)、播種性血管内凝固症候群(DIC)、大動脈解離、悪性腫瘍、手術後、妊娠、高齢、感染・炎症</v>
       </c>
       <c r="G101" t="str">
-        <v>腎機能低下がある患者で酸化マグネシウムなどの緩下剤を使用中は、傾眠・血圧低下などの高マグネシウム血症の症状がないか確認する</v>
+        <v>ふくらはぎの腫れ・痛み、急な息切れ・胸痛など血栓症を疑う症状がないか確認する</v>
       </c>
       <c r="H101" t="str">
-        <v>マグネシウム含有制酸薬・下剤の過量(特に腎機能低下患者)</v>
+        <v>経口避妊薬・ホルモン補充療法は血栓リスクを高める。逆にワルファリン・DOAC・ヘパリンなど抗凝固薬の効果不十分で血栓が進行している可能性にも注意</v>
       </c>
       <c r="I101" t="str">
-        <v>低栄養、利尿薬の使用、慢性的な下痢、アルコール多飲、PPI長期使用</v>
+        <v>通常、臨床的意義は乏しい(基準値以下であれば血栓症の可能性は低いとする除外診断に有用)</v>
       </c>
       <c r="J101" t="str">
-        <v>こむら返りや動悸などの症状がないか確認する</v>
+        <v/>
       </c>
       <c r="K101" t="str">
-        <v>プロトンポンプ阻害薬(PPI)の長期使用、ループ利尿薬、サイアザイド系利尿薬、シスプラチン、アミノグリコシド系</v>
+        <v/>
       </c>
       <c r="L101" t="str">
-        <v>腎機能低下患者への酸化マグネシウム投与は高マグネシウム血症のリスクがあるため定期的なモニタリングが必要。PPI長期使用も低マグネシウム血症のリスク因子として知られる</v>
+        <v>陰性的中率が高く、基準値以下であれば静脈血栓塞栓症(VTE)の可能性は低いとする除外診断への活用が臨床的に重要。一方で偽陽性が多く、高値のみで血栓症と確定はできない。抗凝固療法中のモニタリングそのものには通常用いない(効果判定はPT-INR/APTT等)</v>
       </c>
       <c r="M101" t="str">
-        <v>腎機能</v>
+        <v>抗凝固療法（心房細動・血栓症）</v>
       </c>
       <c r="N101" t="str">
-        <v>マグネシウム,Mg,酸化マグネシウム,こむら返り</v>
+        <v>Dダイマー,D-dimer,血栓,DVT,深部静脈血栓症,肺塞栓,DIC</v>
       </c>
       <c r="O101" t="str">
-        <v>食事と栄養 p.84（マグネシウム）</v>
+        <v/>
       </c>
     </row>
     <row r="102">

--- a/検査値リファレンス初期データ.xlsx
+++ b/検査値リファレンス初期データ.xlsx
@@ -2165,31 +2165,31 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>CONUT値</v>
+        <v>C－ペプチド（血中）</v>
       </c>
       <c r="B38" t="str">
-        <v>CONUT</v>
+        <v>CPR</v>
       </c>
       <c r="C38" t="str">
-        <v>0〜1点：正常、2〜4点：軽度低栄養、5〜8点：中等度低栄養、9〜12点：高度低栄養</v>
+        <v>空腹時 0.6〜3.0 ng/mL（施設差あり）</v>
       </c>
       <c r="D38" t="str">
-        <v>アルブミン・総リンパ球数・総コレステロールの3項目から算出する栄養状態の評価スコア</v>
+        <v>自分の膵臓がどれくらいインスリンを作れているかを表す指標</v>
       </c>
       <c r="E38" t="str">
-        <v>CONUT値は、血液検査（アルブミン、リンパ球数、コレステロール）の結果から計算される、栄養状態を数値化したスコアです。点数が高いほど低栄養の状態が疑われます。</v>
+        <v>この検査は、ご自身の膵臓がどれくらいインスリンを作る力を持っているかを見るものです。数値が低いほど、体の中で作れるインスリンが少ないことを示します。</v>
       </c>
       <c r="F38" t="str">
-        <v>低栄養状態（点数が高いほど重度）</v>
+        <v>インスリン抵抗性が強い状態（初期の2型糖尿病など）</v>
       </c>
       <c r="G38" t="str">
-        <v>食事摂取量や体重の変化を確認する。必要に応じて栄養補助食品の活用を提案する</v>
+        <v/>
       </c>
       <c r="H38" t="str">
         <v/>
       </c>
       <c r="I38" t="str">
-        <v/>
+        <v>膵臓のインスリン分泌能低下（1型糖尿病、糖尿病の進行）</v>
       </c>
       <c r="J38" t="str">
         <v/>
@@ -2198,60 +2198,60 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>アルブミン・総リンパ球数・総コレステロールの3項目それぞれに配点があり、合計点で評価する客観的栄養指標。フレイル・サルコペニアの評価やポリファーマシー対策の一環としての栄養状態把握に有用</v>
+        <v>インスリン分泌能の評価に使われる。数値が低いほどインスリン治療の必要性が高いと判断される目安になる</v>
       </c>
       <c r="M38" t="str">
-        <v/>
+        <v>糖尿病</v>
       </c>
       <c r="N38" t="str">
-        <v>CONUT,CONUT値,栄養評価,低栄養,フレイル</v>
+        <v>C-ペプチド,Cペプチド,CPR,C-peptide,血中CPR,インスリン分泌</v>
       </c>
       <c r="O38" t="str">
-        <v>食事と栄養 p.240（フレイルQ108 低栄養や食事量の評価）</v>
+        <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>乳び</v>
+        <v>C－ペプチドインデックス</v>
       </c>
       <c r="B39" t="str">
-        <v>乳び,Lipemia</v>
+        <v>CPI</v>
       </c>
       <c r="C39" t="str">
-        <v>所見なし（血清が白濁していなければ正常）</v>
+        <v>1.2以上が目安(施設・測定条件により異なる)</v>
       </c>
       <c r="D39" t="str">
-        <v>中性脂肪が非常に多いため、血清が白く濁って見える状態。検査値そのものではなく検体の外観所見</v>
+        <v>血糖値に対してどれくらいインスリンを分泌できているかを表す指標。低いほどインスリン治療の必要性が高い</v>
       </c>
       <c r="E39" t="str">
-        <v>乳びとは、血液中の中性脂肪が非常に多いために、採血した血液（血清）が白く濁って見える状態のことです。多くの場合、食後の採血や、著しい脂質異常症が背景にあります。</v>
+        <v>これは、血糖値の高さに対して、体がどれくらいインスリンを作れているかを見る指標です。数値が低いほど、自分の膵臓だけでは血糖値に見合うインスリンを十分に作れていない可能性が高く、インスリン治療が必要かどうかの判断材料になります。</v>
       </c>
       <c r="F39" t="str">
-        <v>著しい高中性脂肪血症、食後採血（一時的なもの）、原発性高カイロミクロン血症などの脂質代謝異常</v>
+        <v>通常、臨床的意義は乏しい</v>
       </c>
       <c r="G39" t="str">
-        <v>採血が空腹時だったかを確認する。食後採血であれば次回は空腹時の再検を提案する</v>
+        <v/>
       </c>
       <c r="H39" t="str">
         <v/>
       </c>
       <c r="I39" t="str">
-        <v/>
+        <v>内因性インスリン分泌能の低下(1.2未満でインスリン治療の適応を検討する目安、0.8未満はインスリン療法が強く推奨される目安)</v>
       </c>
       <c r="J39" t="str">
-        <v/>
+        <v>インスリン治療の必要性について医師からどのように説明を受けているか確認する</v>
       </c>
       <c r="K39" t="str">
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>血清の白濁により一部の検査項目（電解質など）の測定値に誤差が出ることがある（偽性低ナトリウム血症など）。中性脂肪値と合わせて評価する</v>
+        <v>CPI＝血中Cペプチド(ng/mL)÷血糖値(mg/dL)×100 で算出する。空腹時に測定するのが基本で、境界値付近では食事負荷の影響を受けるため、複数回の評価や随時尿中CPRとあわせて判断することもある</v>
       </c>
       <c r="M39" t="str">
-        <v>脂質異常症</v>
+        <v>糖尿病</v>
       </c>
       <c r="N39" t="str">
-        <v>乳び,乳び血清,Lipemia,高中性脂肪血症</v>
+        <v>CPI,Cペプチドインデックス,C-ペプチドインデックス,インスリン分泌能,インスリン治療</v>
       </c>
       <c r="O39" t="str">
         <v/>
@@ -2259,25 +2259,25 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>溶血</v>
+        <v>CONUT値</v>
       </c>
       <c r="B40" t="str">
-        <v>溶血,Hemolysis</v>
+        <v>CONUT</v>
       </c>
       <c r="C40" t="str">
-        <v>所見なし（溶血を示唆する検査値異常がなければ正常）</v>
+        <v>0〜1点：正常、2〜4点：軽度低栄養、5〜8点：中等度低栄養、9〜12点：高度低栄養</v>
       </c>
       <c r="D40" t="str">
-        <v>赤血球が通常より早く壊れる状態。単独の検査値ではなく、複数の検査値の組み合わせで疑う病態</v>
+        <v>アルブミン・総リンパ球数・総コレステロールの3項目から算出する栄養状態の評価スコア</v>
       </c>
       <c r="E40" t="str">
-        <v>溶血とは、赤血球が通常よりも早いペースで壊れてしまう状態のことです。壊れた赤血球からビリルビンなどが放出されるため、貧血や黄疸の原因になることがあります。</v>
+        <v>CONUT値は、血液検査（アルブミン、リンパ球数、コレステロール）の結果から計算される、栄養状態を数値化したスコアです。点数が高いほど低栄養の状態が疑われます。</v>
       </c>
       <c r="F40" t="str">
-        <v>自己免疫性溶血性貧血、血液型不適合輸血、G6PD欠損症などの遺伝性疾患、機械弁など人工物による物理的破壊、薬剤性溶血</v>
+        <v>低栄養状態（点数が高いほど重度）</v>
       </c>
       <c r="G40" t="str">
-        <v>倦怠感、黄疸、尿の色が濃くなるなどの症状がないか確認する</v>
+        <v>食事摂取量や体重の変化を確認する。必要に応じて栄養補助食品の活用を提案する</v>
       </c>
       <c r="H40" t="str">
         <v/>
@@ -2292,39 +2292,39 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>溶血を疑う際は、間接ビリルビン上昇・LDH上昇・ハプトグロビン低下・網状赤血球増加のパターンを確認する。ヘモグロビン・MCV・MCHCの変化と合わせて総合的に判断する</v>
+        <v>アルブミン・総リンパ球数・総コレステロールの3項目それぞれに配点があり、合計点で評価する客観的栄養指標。フレイル・サルコペニアの評価やポリファーマシー対策の一環としての栄養状態把握に有用</v>
       </c>
       <c r="M40" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v/>
       </c>
       <c r="N40" t="str">
-        <v>溶血,Hemolysis,溶血性貧血,G6PD,ハプトグロビン</v>
+        <v>CONUT,CONUT値,栄養評価,低栄養,フレイル</v>
       </c>
       <c r="O40" t="str">
-        <v/>
+        <v>食事と栄養 p.240（フレイルQ108 低栄養や食事量の評価）</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>黄疸</v>
+        <v>乳び</v>
       </c>
       <c r="B41" t="str">
-        <v>黄疸,Jaundice</v>
+        <v>乳び,Lipemia</v>
       </c>
       <c r="C41" t="str">
-        <v>所見なし（皮膚・眼球結膜の黄染がなければ正常）</v>
+        <v>所見なし（血清が白濁していなければ正常）</v>
       </c>
       <c r="D41" t="str">
-        <v>ビリルビンが体にたまり、皮膚や白目が黄色くなる状態。単独の検査値ではなく、ビリルビン上昇によって表れる身体所見</v>
+        <v>中性脂肪が非常に多いため、血清が白く濁って見える状態。検査値そのものではなく検体の外観所見</v>
       </c>
       <c r="E41" t="str">
-        <v>黄疸は、体の中にビリルビンという黄色い色素がたまることで、皮膚や白目が黄色く見える状態です。肝臓や胆道のトラブル、赤血球が壊れやすくなる病気（溶血）などが原因となります。</v>
+        <v>乳びとは、血液中の中性脂肪が非常に多いために、採血した血液（血清）が白く濁って見える状態のことです。多くの場合、食後の採血や、著しい脂質異常症が背景にあります。</v>
       </c>
       <c r="F41" t="str">
-        <v>肝炎・肝硬変などの肝疾患、胆石・腫瘍による胆道閉塞、溶血性疾患、体質性黄疸（ジルベール症候群）、新生児黄疸</v>
+        <v>著しい高中性脂肪血症、食後採血（一時的なもの）、原発性高カイロミクロン血症などの脂質代謝異常</v>
       </c>
       <c r="G41" t="str">
-        <v>白目や皮膚の黄染に気づいたら、尿の色（濃い茶色）や便の色（白っぽい）の変化も確認し、早めの受診を勧める</v>
+        <v>採血が空腹時だったかを確認する。食後採血であれば次回は空腹時の再検を提案する</v>
       </c>
       <c r="H41" t="str">
         <v/>
@@ -2339,13 +2339,13 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>黄疸は検査値そのものではなく身体所見。原因を調べる際は総ビリルビン・直接ビリルビン・間接ビリルビンの内訳とAST/ALT/γ-GTPを確認する。直接優位なら胆道系、間接優位なら溶血・体質性を疑う</v>
+        <v>血清の白濁により一部の検査項目（電解質など）の測定値に誤差が出ることがある（偽性低ナトリウム血症など）。中性脂肪値と合わせて評価する</v>
       </c>
       <c r="M41" t="str">
-        <v>肝機能</v>
+        <v>脂質異常症</v>
       </c>
       <c r="N41" t="str">
-        <v>黄疸,ジョンダイス,Jaundice,ビリルビン,皮膚黄染,白目</v>
+        <v>乳び,乳び血清,Lipemia,高中性脂肪血症</v>
       </c>
       <c r="O41" t="str">
         <v/>
@@ -2353,216 +2353,216 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>甲状腺刺激ホルモン（TSH）</v>
+        <v>溶血</v>
       </c>
       <c r="B42" t="str">
-        <v>TSH</v>
+        <v>溶血,Hemolysis</v>
       </c>
       <c r="C42" t="str">
-        <v>0.5〜5.0 μIU/mL程度（施設差あり）</v>
+        <v>所見なし（溶血を示唆する検査値異常がなければ正常）</v>
       </c>
       <c r="D42" t="str">
-        <v>甲状腺の働きが多いか少ないかを最も敏感に反映するホルモン</v>
+        <v>赤血球が通常より早く壊れる状態。単独の検査値ではなく、複数の検査値の組み合わせで疑う病態</v>
       </c>
       <c r="E42" t="str">
-        <v>TSHは脳の下垂体から出て、甲状腺に「もっと働いて」と指令を送るホルモンです。甲状腺の働きが弱っていると体が指令を強めるためTSHは上がり、逆に甲状腺が働きすぎているとTSHは下がります。甲状腺の状態を最初に確認する数値としてよく使われます。</v>
+        <v>溶血とは、赤血球が通常よりも早いペースで壊れてしまう状態のことです。壊れた赤血球からビリルビンなどが放出されるため、貧血や黄疸の原因になることがあります。</v>
       </c>
       <c r="F42" t="str">
-        <v>甲状腺機能低下症（橋本病など）、チラーヂンSなど甲状腺ホルモン薬の量不足</v>
+        <v>自己免疫性溶血性貧血、血液型不適合輸血、G6PD欠損症などの遺伝性疾患、機械弁など人工物による物理的破壊、薬剤性溶血</v>
       </c>
       <c r="G42" t="str">
-        <v>だるさ、むくみ、体重増加、寒がりなどの症状がないか確認する。服薬状況（飲み忘れ、他の薬との飲み合わせ）を確認する</v>
+        <v>倦怠感、黄疸、尿の色が濃くなるなどの症状がないか確認する</v>
       </c>
       <c r="H42" t="str">
-        <v>アミオダロン、炭酸リチウム、インターフェロン製剤、チロシンキナーゼ阻害薬(スニチニブ等)</v>
+        <v/>
       </c>
       <c r="I42" t="str">
-        <v>甲状腺機能亢進症（バセドウ病など）、チラーヂンSなど甲状腺ホルモン薬の過量</v>
+        <v/>
       </c>
       <c r="J42" t="str">
-        <v>動悸、体重減少、暑がり、手のふるえなどの症状がないか確認する</v>
+        <v/>
       </c>
       <c r="K42" t="str">
-        <v>レボチロキシンの過量投与</v>
+        <v/>
       </c>
       <c r="L42" t="str">
-        <v>チラーヂンS服用中はTSHが治療目標域に収まっているかで用量調整の目安にする。メルカゾール服用中はTSH・FT4に加えて無顆粒球症の初期症状（発熱・のどの痛み）の有無や白血球数も確認する</v>
+        <v>溶血を疑う際は、間接ビリルビン上昇・LDH上昇・ハプトグロビン低下・網状赤血球増加のパターンを確認する。ヘモグロビン・MCV・MCHCの変化と合わせて総合的に判断する</v>
       </c>
       <c r="M42" t="str">
-        <v>甲状腺疾患</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="N42" t="str">
-        <v>TSH,甲状腺刺激ホルモン,甲状腺機能,橋本病,バセドウ病,チラーヂン,メルカゾール</v>
+        <v>溶血,Hemolysis,溶血性貧血,G6PD,ハプトグロビン</v>
       </c>
       <c r="O42" t="str">
-        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
+        <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>遊離サイロキシン（FT4）</v>
+        <v>黄疸</v>
       </c>
       <c r="B43" t="str">
-        <v>FT4</v>
+        <v>黄疸,Jaundice</v>
       </c>
       <c r="C43" t="str">
-        <v>0.9〜1.7 ng/dL程度（施設差あり）</v>
+        <v>所見なし（皮膚・眼球結膜の黄染がなければ正常）</v>
       </c>
       <c r="D43" t="str">
-        <v>甲状腺が実際に分泌しているホルモンの量そのものを表す数値</v>
+        <v>ビリルビンが体にたまり、皮膚や白目が黄色くなる状態。単独の検査値ではなく、ビリルビン上昇によって表れる身体所見</v>
       </c>
       <c r="E43" t="str">
-        <v>FT4は甲状腺そのものが作っているホルモンの量です。TSHが「指令の強さ」だとすると、FT4は「実際に出ている量」にあたります。2つをあわせて見ることで、甲状腺の働きが今どういう状態かを詳しく判断できます。</v>
+        <v>黄疸は、体の中にビリルビンという黄色い色素がたまることで、皮膚や白目が黄色く見える状態です。肝臓や胆道のトラブル、赤血球が壊れやすくなる病気（溶血）などが原因となります。</v>
       </c>
       <c r="F43" t="str">
-        <v>甲状腺機能亢進症（バセドウ病など）</v>
+        <v>肝炎・肝硬変などの肝疾患、胆石・腫瘍による胆道閉塞、溶血性疾患、体質性黄疸（ジルベール症候群）、新生児黄疸</v>
       </c>
       <c r="G43" t="str">
-        <v>動悸、体重減少、暑がり、手のふるえなどの症状がないか確認する</v>
+        <v>白目や皮膚の黄染に気づいたら、尿の色（濃い茶色）や便の色（白っぽい）の変化も確認し、早めの受診を勧める</v>
       </c>
       <c r="H43" t="str">
-        <v>レボチロキシンの過量投与、アミオダロン</v>
+        <v/>
       </c>
       <c r="I43" t="str">
-        <v>甲状腺機能低下症（橋本病など）</v>
+        <v/>
       </c>
       <c r="J43" t="str">
-        <v>だるさ、むくみ、体重増加、寒がりなどの症状がないか確認する</v>
+        <v/>
       </c>
       <c r="K43" t="str">
-        <v>抗甲状腺薬(メルカゾール、プロパジール)の効きすぎ</v>
+        <v/>
       </c>
       <c r="L43" t="str">
-        <v>TSHと逆方向に動くのが基本だが、下垂体性の異常など例外もある。TSHと合わせて評価し、片方だけで判断しない</v>
+        <v>黄疸は検査値そのものではなく身体所見。原因を調べる際は総ビリルビン・直接ビリルビン・間接ビリルビンの内訳とAST/ALT/γ-GTPを確認する。直接優位なら胆道系、間接優位なら溶血・体質性を疑う</v>
       </c>
       <c r="M43" t="str">
-        <v>甲状腺疾患</v>
+        <v>肝機能</v>
       </c>
       <c r="N43" t="str">
-        <v>FT4,遊離サイロキシン,甲状腺ホルモン,甲状腺機能</v>
+        <v>黄疸,ジョンダイス,Jaundice,ビリルビン,皮膚黄染,白目</v>
       </c>
       <c r="O43" t="str">
-        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
+        <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>尿蛋白（随時尿）</v>
+        <v>甲状腺刺激ホルモン（TSH）</v>
       </c>
       <c r="B44" t="str">
-        <v>尿蛋白,U-pro</v>
+        <v>TSH</v>
       </c>
       <c r="C44" t="str">
-        <v>陰性（－）〜弱陽性</v>
+        <v>0.5〜5.0 μIU/mL程度（施設差あり）</v>
       </c>
       <c r="D44" t="str">
-        <v>腎臓から本来漏れないはずのたんぱくが尿に出ていないかを見る検査</v>
+        <v>甲状腺の働きが多いか少ないかを最も敏感に反映するホルモン</v>
       </c>
       <c r="E44" t="str">
-        <v>この検査は、腎臓のろ過機能に負担がかかっていないかを見るものです。本来、たんぱく質は尿にほとんど出ませんが、腎臓に負担がかかると漏れ出るようになります。</v>
+        <v>TSHは脳の下垂体から出て、甲状腺に「もっと働いて」と指令を送るホルモンです。甲状腺の働きが弱っていると体が指令を強めるためTSHは上がり、逆に甲状腺が働きすぎているとTSHは下がります。甲状腺の状態を最初に確認する数値としてよく使われます。</v>
       </c>
       <c r="F44" t="str">
-        <v>糖尿病性腎症、腎炎、高血圧性腎硬化症、発熱・運動後の一過性のもの</v>
+        <v>甲状腺機能低下症（橋本病など）、チラーヂンSなど甲状腺ホルモン薬の量不足</v>
       </c>
       <c r="G44" t="str">
-        <v>発熱・激しい運動の直後でないか確認する(一過性のことがある)。持続する場合は塩分の摂りすぎに注意し、むくみの有無もあわせて確認する</v>
+        <v>だるさ、むくみ、体重増加、寒がりなどの症状がないか確認する。服薬状況（飲み忘れ、他の薬との飲み合わせ）を確認する</v>
       </c>
       <c r="H44" t="str">
-        <v>NSAIDs、造影剤、アミノグリコシド系、バンコマイシン、金製剤</v>
+        <v>アミオダロン、炭酸リチウム、インターフェロン製剤、チロシンキナーゼ阻害薬(スニチニブ等)</v>
       </c>
       <c r="I44" t="str">
-        <v/>
+        <v>甲状腺機能亢進症（バセドウ病など）、チラーヂンSなど甲状腺ホルモン薬の過量</v>
       </c>
       <c r="J44" t="str">
-        <v/>
+        <v>動悸、体重減少、暑がり、手のふるえなどの症状がないか確認する</v>
       </c>
       <c r="K44" t="str">
-        <v/>
+        <v>レボチロキシンの過量投与</v>
       </c>
       <c r="L44" t="str">
-        <v>発熱・激しい運動・起立性蛋白尿など生理的な要因でも陽性になることがある。持続する場合に腎症の進行を疑う</v>
+        <v>チラーヂンS服用中はTSHが治療目標域に収まっているかで用量調整の目安にする。メルカゾール服用中はTSH・FT4に加えて無顆粒球症の初期症状（発熱・のどの痛み）の有無や白血球数も確認する</v>
       </c>
       <c r="M44" t="str">
-        <v>糖尿病,腎機能</v>
+        <v>甲状腺疾患</v>
       </c>
       <c r="N44" t="str">
-        <v>尿蛋白,U-pro,腎症,たんぱく尿</v>
+        <v>TSH,甲状腺刺激ホルモン,甲状腺機能,橋本病,バセドウ病,チラーヂン,メルカゾール</v>
       </c>
       <c r="O44" t="str">
-        <v/>
+        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>尿クレアチニン（随時尿）</v>
+        <v>遊離サイロキシン（FT4）</v>
       </c>
       <c r="B45" t="str">
-        <v>尿CRE</v>
+        <v>FT4</v>
       </c>
       <c r="C45" t="str">
-        <v>随時尿は主に他項目の濃度補正に利用（単独の基準値は設けにくい）</v>
+        <v>0.9〜1.7 ng/dL程度（施設差あり）</v>
       </c>
       <c r="D45" t="str">
-        <v>随時尿中のクレアチニン濃度。他の尿検査項目を薄まり具合で補正するための基準として使う</v>
+        <v>甲状腺が実際に分泌しているホルモンの量そのものを表す数値</v>
       </c>
       <c r="E45" t="str">
-        <v>この数値は、尿がどれくらい薄まっているかを確認するための基準として使われます。他の尿検査の結果（蛋白やアルブミンなど）をこの値で割って補正することで、水分摂取量による影響を減らして正確に評価できます。</v>
+        <v>FT4は甲状腺そのものが作っているホルモンの量です。TSHが「指令の強さ」だとすると、FT4は「実際に出ている量」にあたります。2つをあわせて見ることで、甲状腺の働きが今どういう状態かを詳しく判断できます。</v>
       </c>
       <c r="F45" t="str">
-        <v/>
+        <v>甲状腺機能亢進症（バセドウ病など）</v>
       </c>
       <c r="G45" t="str">
-        <v/>
+        <v>動悸、体重減少、暑がり、手のふるえなどの症状がないか確認する</v>
       </c>
       <c r="H45" t="str">
-        <v/>
+        <v>レボチロキシンの過量投与、アミオダロン</v>
       </c>
       <c r="I45" t="str">
-        <v>尿が薄い（水分摂取が多い、腎機能低下）状態</v>
+        <v>甲状腺機能低下症（橋本病など）</v>
       </c>
       <c r="J45" t="str">
-        <v/>
+        <v>だるさ、むくみ、体重増加、寒がりなどの症状がないか確認する</v>
       </c>
       <c r="K45" t="str">
-        <v/>
+        <v>抗甲状腺薬(メルカゾール、プロパジール)の効きすぎ</v>
       </c>
       <c r="L45" t="str">
-        <v>尿中アルブミン/Cr比、尿蛋白/Cr比など、他項目の補正計算に使われる。単独の高低に臨床的意味は乏しい</v>
+        <v>TSHと逆方向に動くのが基本だが、下垂体性の異常など例外もある。TSHと合わせて評価し、片方だけで判断しない</v>
       </c>
       <c r="M45" t="str">
-        <v>腎機能</v>
+        <v>甲状腺疾患</v>
       </c>
       <c r="N45" t="str">
-        <v>尿CRE,尿クレアチニン,随時尿,補正,蛋白クレアチニン比</v>
+        <v>FT4,遊離サイロキシン,甲状腺ホルモン,甲状腺機能</v>
       </c>
       <c r="O45" t="str">
-        <v/>
+        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>尿蛋白定量</v>
+        <v>尿蛋白（随時尿）</v>
       </c>
       <c r="B46" t="str">
-        <v>U-Pro定量,蛋白/Cr比</v>
+        <v>尿蛋白,U-pro</v>
       </c>
       <c r="C46" t="str">
-        <v>0.15 g/gCr未満</v>
+        <v>陰性（－）〜弱陽性</v>
       </c>
       <c r="D46" t="str">
-        <v>随時尿から尿蛋白の量を具体的な数値として評価する検査。ネフローゼ等の重症度判定に使う</v>
+        <v>腎臓から本来漏れないはずのたんぱくが尿に出ていないかを見る検査</v>
       </c>
       <c r="E46" t="str">
-        <v>これは、尿に出ているたんぱくの量を具体的な数値で見る検査です。試験紙での陽性・陰性の判定だけでなく、実際にどれくらいの量が出ているかを把握できます。</v>
+        <v>この検査は、腎臓のろ過機能に負担がかかっていないかを見るものです。本来、たんぱく質は尿にほとんど出ませんが、腎臓に負担がかかると漏れ出るようになります。</v>
       </c>
       <c r="F46" t="str">
-        <v>腎症の進行（糖尿病性腎症、慢性腎臓病など）、ネフローゼ症候群（3.5 g/gCr以上が目安）</v>
+        <v>糖尿病性腎症、腎炎、高血圧性腎硬化症、発熱・運動後の一過性のもの</v>
       </c>
       <c r="G46" t="str">
-        <v>持続する場合は塩分の摂りすぎに注意し、むくみの有無も確認する。腎臓内科でのフォロー状況もあわせて確認する</v>
+        <v>発熱・激しい運動の直後でないか確認する(一過性のことがある)。持続する場合は塩分の摂りすぎに注意し、むくみの有無もあわせて確認する</v>
       </c>
       <c r="H46" t="str">
-        <v>NSAIDs、造影剤、アミノグリコシド系、バンコマイシン</v>
+        <v>NSAIDs、造影剤、アミノグリコシド系、バンコマイシン、金製剤</v>
       </c>
       <c r="I46" t="str">
         <v/>
@@ -2574,13 +2574,13 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>CKD診療ガイドラインの重症度分類（尿蛋白量による区分）にも使われる定量指標。試験紙法の半定量結果より治療効果判定に適する</v>
+        <v>発熱・激しい運動・起立性蛋白尿など生理的な要因でも陽性になることがある。持続する場合に腎症の進行を疑う</v>
       </c>
       <c r="M46" t="str">
-        <v>腎機能,糖尿病</v>
+        <v>糖尿病,腎機能</v>
       </c>
       <c r="N46" t="str">
-        <v>尿蛋白,随時尿,定量,蛋白クレアチニン比,ネフローゼ</v>
+        <v>尿蛋白,U-pro,腎症,たんぱく尿</v>
       </c>
       <c r="O46" t="str">
         <v/>
@@ -2588,22 +2588,22 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>尿pH</v>
+        <v>尿クレアチニン（随時尿）</v>
       </c>
       <c r="B47" t="str">
-        <v>尿pH</v>
+        <v>尿CRE</v>
       </c>
       <c r="C47" t="str">
-        <v>4.5〜7.5程度（弱酸性が多い）</v>
+        <v>随時尿は主に他項目の濃度補正に利用（単独の基準値は設けにくい）</v>
       </c>
       <c r="D47" t="str">
-        <v>尿の酸性・アルカリ性の度合い。食事や感染症、体の状態を反映する</v>
+        <v>随時尿中のクレアチニン濃度。他の尿検査項目を薄まり具合で補正するための基準として使う</v>
       </c>
       <c r="E47" t="str">
-        <v>尿のpHは酸性・アルカリ性のバランスを表します。食事の内容や感染症、体の代謝状態によって変化します。単独で大きな問題を示すことは少ない検査です。</v>
+        <v>この数値は、尿がどれくらい薄まっているかを確認するための基準として使われます。他の尿検査の結果（蛋白やアルブミンなど）をこの値で割って補正することで、水分摂取量による影響を減らして正確に評価できます。</v>
       </c>
       <c r="F47" t="str">
-        <v>尿路感染症（尿素分解菌によるもの）、野菜中心の食事、過換気</v>
+        <v/>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2612,22 +2612,22 @@
         <v/>
       </c>
       <c r="I47" t="str">
-        <v>高たんぱく食、糖尿病性ケトアシドーシス、痛風発作時（酸性尿は尿酸結石のリスクを高める）</v>
+        <v>尿が薄い（水分摂取が多い、腎機能低下）状態</v>
       </c>
       <c r="J47" t="str">
-        <v>痛風・尿酸結石がある場合は、野菜など尿をアルカリ化する食品を意識するとよいことを伝える</v>
+        <v/>
       </c>
       <c r="K47" t="str">
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>高尿酸血症・尿酸結石の患者では尿pHが酸性に傾いていないか確認する。尿アルカリ化薬（ウラリットなど）の効果判定にも使う</v>
+        <v>尿中アルブミン/Cr比、尿蛋白/Cr比など、他項目の補正計算に使われる。単独の高低に臨床的意味は乏しい</v>
       </c>
       <c r="M47" t="str">
-        <v>高尿酸血症</v>
+        <v>腎機能</v>
       </c>
       <c r="N47" t="str">
-        <v>尿pH,尿酸性度,尿アルカリ化,ウラリット</v>
+        <v>尿CRE,尿クレアチニン,随時尿,補正,蛋白クレアチニン比</v>
       </c>
       <c r="O47" t="str">
         <v/>
@@ -2635,28 +2635,28 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>尿ケトン体</v>
+        <v>尿蛋白定量</v>
       </c>
       <c r="B48" t="str">
-        <v>尿ケトン,Ket</v>
+        <v>U-Pro定量,蛋白/Cr比</v>
       </c>
       <c r="C48" t="str">
-        <v>陰性（－）</v>
+        <v>0.15 g/gCr未満</v>
       </c>
       <c r="D48" t="str">
-        <v>体がブドウ糖の代わりに脂肪を分解してエネルギーを作っているサイン</v>
+        <v>随時尿から尿蛋白の量を具体的な数値として評価する検査。ネフローゼ等の重症度判定に使う</v>
       </c>
       <c r="E48" t="str">
-        <v>この検査は、体が糖の代わりに脂肪を使ってエネルギーを作っていないかを見るものです。陽性が続くときは、食事や水分、インスリンの使い方を確認する必要があります。</v>
+        <v>これは、尿に出ているたんぱくの量を具体的な数値で見る検査です。試験紙での陽性・陰性の判定だけでなく、実際にどれくらいの量が出ているかを把握できます。</v>
       </c>
       <c r="F48" t="str">
-        <v>糖尿病の血糖コントロール不良（シックデイ・インスリン不足）、極端な糖質制限、絶食、嘔吐・下痢による脱水</v>
+        <v>腎症の進行（糖尿病性腎症、慢性腎臓病など）、ネフローゼ症候群（3.5 g/gCr以上が目安）</v>
       </c>
       <c r="G48" t="str">
-        <v>糖尿病治療中の場合はシックデイ時の対応(インスリンを自己中断しない、水分摂取を続けるなど)を確認する。体調不良時の対応方法を事前に説明しておく</v>
+        <v>持続する場合は塩分の摂りすぎに注意し、むくみの有無も確認する。腎臓内科でのフォロー状況もあわせて確認する</v>
       </c>
       <c r="H48" t="str">
-        <v>SGLT2阻害薬(特に絶食・シックデイ時の正常血糖ケトアシドーシスに注意)</v>
+        <v>NSAIDs、造影剤、アミノグリコシド系、バンコマイシン</v>
       </c>
       <c r="I48" t="str">
         <v/>
@@ -2668,13 +2668,13 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>陽性かつ高血糖・全身倦怠感が強い場合は糖尿病性ケトアシドーシスの可能性があり緊急性が高い。シックデイルールの説明歴を確認する</v>
+        <v>CKD診療ガイドラインの重症度分類（尿蛋白量による区分）にも使われる定量指標。試験紙法の半定量結果より治療効果判定に適する</v>
       </c>
       <c r="M48" t="str">
-        <v>糖尿病</v>
+        <v>腎機能,糖尿病</v>
       </c>
       <c r="N48" t="str">
-        <v>尿ケトン体,ケトン体,Ket,シックデイ,ケトアシドーシス</v>
+        <v>尿蛋白,随時尿,定量,蛋白クレアチニン比,ネフローゼ</v>
       </c>
       <c r="O48" t="str">
         <v/>
@@ -2682,22 +2682,22 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ウロビリノーゲン</v>
+        <v>尿pH</v>
       </c>
       <c r="B49" t="str">
-        <v>Uro</v>
+        <v>尿pH</v>
       </c>
       <c r="C49" t="str">
-        <v>正常（±）程度</v>
+        <v>4.5〜7.5程度（弱酸性が多い）</v>
       </c>
       <c r="D49" t="str">
-        <v>肝臓や胆道、赤血球の壊れ方の状態を反映する尿検査項目</v>
+        <v>尿の酸性・アルカリ性の度合い。食事や感染症、体の状態を反映する</v>
       </c>
       <c r="E49" t="str">
-        <v>ウロビリノーゲンは、赤血球やビリルビンが体の中で処理される過程でできる物質です。肝臓の働きが悪くなったり、赤血球が壊れやすくなったりすると、尿の中の量が変化します。</v>
+        <v>尿のpHは酸性・アルカリ性のバランスを表します。食事の内容や感染症、体の代謝状態によって変化します。単独で大きな問題を示すことは少ない検査です。</v>
       </c>
       <c r="F49" t="str">
-        <v>溶血性疾患（赤血球の破壊亢進）、肝機能障害</v>
+        <v>尿路感染症（尿素分解菌によるもの）、野菜中心の食事、過換気</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2706,22 +2706,22 @@
         <v/>
       </c>
       <c r="I49" t="str">
-        <v>胆道閉塞（胆汁が腸に流れず、ウロビリノーゲンが作られない状態）</v>
+        <v>高たんぱく食、糖尿病性ケトアシドーシス、痛風発作時（酸性尿は尿酸結石のリスクを高める）</v>
       </c>
       <c r="J49" t="str">
-        <v/>
+        <v>痛風・尿酸結石がある場合は、野菜など尿をアルカリ化する食品を意識するとよいことを伝える</v>
       </c>
       <c r="K49" t="str">
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>完全に陰性の場合は胆道閉塞を疑う所見の一つ。肝機能（AST/ALT/ビリルビン）と合わせて評価する</v>
+        <v>高尿酸血症・尿酸結石の患者では尿pHが酸性に傾いていないか確認する。尿アルカリ化薬（ウラリットなど）の効果判定にも使う</v>
       </c>
       <c r="M49" t="str">
-        <v>肝機能</v>
+        <v>高尿酸血症</v>
       </c>
       <c r="N49" t="str">
-        <v>ウロビリノーゲン,Uro,溶血,胆道閉塞,肝機能</v>
+        <v>尿pH,尿酸性度,尿アルカリ化,ウラリット</v>
       </c>
       <c r="O49" t="str">
         <v/>
@@ -2729,28 +2729,28 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>尿潜血反応</v>
+        <v>尿ケトン体</v>
       </c>
       <c r="B50" t="str">
-        <v>尿潜血,U-OB</v>
+        <v>尿ケトン,Ket</v>
       </c>
       <c r="C50" t="str">
         <v>陰性（－）</v>
       </c>
       <c r="D50" t="str">
-        <v>尿に血液（赤血球）が混じっていないかを見る検査</v>
+        <v>体がブドウ糖の代わりに脂肪を分解してエネルギーを作っているサイン</v>
       </c>
       <c r="E50" t="str">
-        <v>この検査は、尿に目に見えないくらいの微量の血液が混じっていないかを調べるものです。陽性の場合、腎臓や膀胱、尿路のどこかに炎症や結石などがある可能性があります。</v>
+        <v>この検査は、体が糖の代わりに脂肪を使ってエネルギーを作っていないかを見るものです。陽性が続くときは、食事や水分、インスリンの使い方を確認する必要があります。</v>
       </c>
       <c r="F50" t="str">
-        <v>尿路結石、膀胱炎などの尿路感染症、腎炎、腫瘍、月経血の混入、激しい運動後</v>
+        <v>糖尿病の血糖コントロール不良（シックデイ・インスリン不足）、極端な糖質制限、絶食、嘔吐・下痢による脱水</v>
       </c>
       <c r="G50" t="str">
-        <v>排尿時の痛みや頻尿、目に見える血尿の有無を確認する。女性は月経の時期と重なっていないか確認する</v>
+        <v>糖尿病治療中の場合はシックデイ時の対応(インスリンを自己中断しない、水分摂取を続けるなど)を確認する。体調不良時の対応方法を事前に説明しておく</v>
       </c>
       <c r="H50" t="str">
-        <v>ワルファリン、DOAC、抗血小板薬など出血傾向を強める薬剤の服用状況を確認</v>
+        <v>SGLT2阻害薬(特に絶食・シックデイ時の正常血糖ケトアシドーシスに注意)</v>
       </c>
       <c r="I50" t="str">
         <v/>
@@ -2762,13 +2762,13 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>陽性でも尿沈渣で赤血球が確認されない場合は偽陽性（ミオグロビン尿など）のこともある。持続する場合は泌尿器科的な精査が必要</v>
+        <v>陽性かつ高血糖・全身倦怠感が強い場合は糖尿病性ケトアシドーシスの可能性があり緊急性が高い。シックデイルールの説明歴を確認する</v>
       </c>
       <c r="M50" t="str">
-        <v>腎機能</v>
+        <v>糖尿病</v>
       </c>
       <c r="N50" t="str">
-        <v>尿潜血,潜血反応,U-OB,血尿,尿路結石,膀胱炎</v>
+        <v>尿ケトン体,ケトン体,Ket,シックデイ,ケトアシドーシス</v>
       </c>
       <c r="O50" t="str">
         <v/>
@@ -2776,31 +2776,31 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>尿糖（半定量）</v>
+        <v>ウロビリノーゲン</v>
       </c>
       <c r="B51" t="str">
-        <v>尿糖,U-Glu</v>
+        <v>Uro</v>
       </c>
       <c r="C51" t="str">
-        <v>陰性（－）</v>
+        <v>正常（±）程度</v>
       </c>
       <c r="D51" t="str">
-        <v>尿に糖が漏れ出ていないかを見る検査。血糖値がかなり高いと陽性になる</v>
+        <v>肝臓や胆道、赤血球の壊れ方の状態を反映する尿検査項目</v>
       </c>
       <c r="E51" t="str">
-        <v>通常、糖は尿にはほとんど出ませんが、血糖値がかなり高くなると尿にあふれ出るようになります。血糖コントロールの目安の一つです。</v>
+        <v>ウロビリノーゲンは、赤血球やビリルビンが体の中で処理される過程でできる物質です。肝臓の働きが悪くなったり、赤血球が壊れやすくなったりすると、尿の中の量が変化します。</v>
       </c>
       <c r="F51" t="str">
-        <v>糖尿病（血糖値が腎臓で再吸収できる量を超えている状態）、腎性糖尿（血糖値が正常でも体質的に出ることがある）、SGLT2阻害薬服用中（薬の作用で意図的に糖を排泄するため陽性になるのが正常）</v>
+        <v>溶血性疾患（赤血球の破壊亢進）、肝機能障害</v>
       </c>
       <c r="G51" t="str">
-        <v>SGLT2阻害薬（フォシーガ、ジャディアンスなど）服用中は、陽性が薬の効果によるものであることを説明する。脱水や尿路感染の症状がないかも確認する</v>
+        <v/>
       </c>
       <c r="H51" t="str">
-        <v>SGLT2阻害薬(薬理作用による陽性であれば想定内であることを説明)</v>
+        <v/>
       </c>
       <c r="I51" t="str">
-        <v/>
+        <v>胆道閉塞（胆汁が腸に流れず、ウロビリノーゲンが作られない状態）</v>
       </c>
       <c r="J51" t="str">
         <v/>
@@ -2809,13 +2809,13 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>SGLT2阻害薬服用中は尿糖陽性が治療効果として想定内であることを患者に伝える。血糖値・HbA1cと合わせて評価する</v>
+        <v>完全に陰性の場合は胆道閉塞を疑う所見の一つ。肝機能（AST/ALT/ビリルビン）と合わせて評価する</v>
       </c>
       <c r="M51" t="str">
-        <v>糖尿病</v>
+        <v>肝機能</v>
       </c>
       <c r="N51" t="str">
-        <v>尿糖,糖半定量,U-Glu,腎性糖尿,SGLT2</v>
+        <v>ウロビリノーゲン,Uro,溶血,胆道閉塞,肝機能</v>
       </c>
       <c r="O51" t="str">
         <v/>
@@ -2823,28 +2823,28 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>尿中微量アルブミン</v>
+        <v>尿潜血反応</v>
       </c>
       <c r="B52" t="str">
-        <v>U-Alb,MAU</v>
+        <v>尿潜血,U-OB</v>
       </c>
       <c r="C52" t="str">
-        <v>30 mg/gCr未満（尿中アルブミン/クレアチニン比）</v>
+        <v>陰性（－）</v>
       </c>
       <c r="D52" t="str">
-        <v>通常の尿蛋白検査では見つからない、ごく早期の腎症のサイン</v>
+        <v>尿に血液（赤血球）が混じっていないかを見る検査</v>
       </c>
       <c r="E52" t="str">
-        <v>この検査は、通常の尿検査ではまだ分からないくらい早い段階の腎臓の変化を見つけるためのものです。数値が高いと、腎症の初期のサインである可能性があります。</v>
+        <v>この検査は、尿に目に見えないくらいの微量の血液が混じっていないかを調べるものです。陽性の場合、腎臓や膀胱、尿路のどこかに炎症や結石などがある可能性があります。</v>
       </c>
       <c r="F52" t="str">
-        <v>糖尿病性腎症の早期段階、高血圧</v>
+        <v>尿路結石、膀胱炎などの尿路感染症、腎炎、腫瘍、月経血の混入、激しい運動後</v>
       </c>
       <c r="G52" t="str">
-        <v>血糖・血圧のコントロール状況を確認する。減塩や適正体重の維持など生活習慣の見直しも早期腎症の進行予防に役立つことを伝える</v>
+        <v>排尿時の痛みや頻尿、目に見える血尿の有無を確認する。女性は月経の時期と重なっていないか確認する</v>
       </c>
       <c r="H52" t="str">
-        <v>NSAIDsなど腎機能を悪化させる薬剤。ACE阻害薬・ARB・SGLT2阻害薬は低下させる方向に働く</v>
+        <v>ワルファリン、DOAC、抗血小板薬など出血傾向を強める薬剤の服用状況を確認</v>
       </c>
       <c r="I52" t="str">
         <v/>
@@ -2856,13 +2856,13 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>糖尿病腎症の早期発見に重要な検査。血糖・血圧コントロールで改善しうる段階なので、早期介入の意義を伝える</v>
+        <v>陽性でも尿沈渣で赤血球が確認されない場合は偽陽性（ミオグロビン尿など）のこともある。持続する場合は泌尿器科的な精査が必要</v>
       </c>
       <c r="M52" t="str">
-        <v>糖尿病,腎機能</v>
+        <v>腎機能</v>
       </c>
       <c r="N52" t="str">
-        <v>微量アルブミン,U-Alb,MAU,糖尿病性腎症,早期腎症</v>
+        <v>尿潜血,潜血反応,U-OB,血尿,尿路結石,膀胱炎</v>
       </c>
       <c r="O52" t="str">
         <v/>
@@ -2870,28 +2870,28 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>C反応性蛋白（CRP）</v>
+        <v>尿糖（半定量）</v>
       </c>
       <c r="B53" t="str">
-        <v>CRP</v>
+        <v>尿糖,U-Glu</v>
       </c>
       <c r="C53" t="str">
-        <v>0.3 mg/dL未満（施設差あり）</v>
+        <v>陰性（－）</v>
       </c>
       <c r="D53" t="str">
-        <v>体のどこかに炎症や感染が起きていないかを鋭敏に反映する数値</v>
+        <v>尿に糖が漏れ出ていないかを見る検査。血糖値がかなり高いと陽性になる</v>
       </c>
       <c r="E53" t="str">
-        <v>CRPは、体に炎症や感染が起きると数時間〜半日程度で急激に上昇する数値です。風邪のようなウイルス感染から細菌感染、体のどこかの炎症まで、幅広く反応するため、体調の変化を早期に捉える手がかりになります。</v>
+        <v>通常、糖は尿にはほとんど出ませんが、血糖値がかなり高くなると尿にあふれ出るようになります。血糖コントロールの目安の一つです。</v>
       </c>
       <c r="F53" t="str">
-        <v>細菌感染症、ウイルス感染症、自己免疫疾患（関節リウマチなど）、悪性腫瘍、組織の損傷（術後・心筋梗塞など）</v>
+        <v>糖尿病（血糖値が腎臓で再吸収できる量を超えている状態）、腎性糖尿（血糖値が正常でも体質的に出ることがある）、SGLT2阻害薬服用中（薬の作用で意図的に糖を排泄するため陽性になるのが正常）</v>
       </c>
       <c r="G53" t="str">
-        <v>発熱、痛み、腫れなど炎症症状の有無を確認する</v>
+        <v>SGLT2阻害薬（フォシーガ、ジャディアンスなど）服用中は、陽性が薬の効果によるものであることを説明する。脱水や尿路感染の症状がないかも確認する</v>
       </c>
       <c r="H53" t="str">
-        <v/>
+        <v>SGLT2阻害薬(薬理作用による陽性であれば想定内であることを説明)</v>
       </c>
       <c r="I53" t="str">
         <v/>
@@ -2903,13 +2903,13 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>白血球数と合わせて感染・炎症の程度を評価する。上昇・低下のタイミングは白血球より半日〜1日程度遅れる傾向があるため、経過を追う際は採血のタイミングに注意</v>
+        <v>SGLT2阻害薬服用中は尿糖陽性が治療効果として想定内であることを患者に伝える。血糖値・HbA1cと合わせて評価する</v>
       </c>
       <c r="M53" t="str">
-        <v/>
+        <v>糖尿病</v>
       </c>
       <c r="N53" t="str">
-        <v>CRP,炎症,感染</v>
+        <v>尿糖,糖半定量,U-Glu,腎性糖尿,SGLT2</v>
       </c>
       <c r="O53" t="str">
         <v/>
@@ -2917,72 +2917,72 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>PT-INR（プロトロンビン時間国際標準比）</v>
+        <v>尿中微量アルブミン</v>
       </c>
       <c r="B54" t="str">
-        <v>PT-INR,INR</v>
+        <v>U-Alb,MAU</v>
       </c>
       <c r="C54" t="str">
-        <v>治療域の目安 1.6〜3.0（ワルファリン服用時。年齢・疾患により異なる）</v>
+        <v>30 mg/gCr未満（尿中アルブミン/クレアチニン比）</v>
       </c>
       <c r="D54" t="str">
-        <v>血液の固まりやすさを表す数値で、ワルファリンの効き具合を確認するために使う</v>
+        <v>通常の尿蛋白検査では見つからない、ごく早期の腎症のサイン</v>
       </c>
       <c r="E54" t="str">
-        <v>PT-INRは血液が固まるまでの時間をもとにした数値で、ワルファリンというお薬を飲んでいる方の効き具合を確認するために測ります。数値が高いほど血液が固まりにくく出血しやすい状態、低いほど血栓ができやすい状態を示します。</v>
+        <v>この検査は、通常の尿検査ではまだ分からないくらい早い段階の腎臓の変化を見つけるためのものです。数値が高いと、腎症の初期のサインである可能性があります。</v>
       </c>
       <c r="F54" t="str">
-        <v>ワルファリンの効きすぎ、肝機能低下、ビタミンK不足、納豆・青汁など摂取量の変化</v>
+        <v>糖尿病性腎症の早期段階、高血圧</v>
       </c>
       <c r="G54" t="str">
-        <v>歯ぐきや鼻からの出血、あざ、黒い便などの出血症状がないか確認する。納豆・クロレラ・青汁などビタミンKを多く含む食品の摂取状況を確認する</v>
+        <v>血糖・血圧のコントロール状況を確認する。減塩や適正体重の維持など生活習慣の見直しも早期腎症の進行予防に役立つことを伝える</v>
       </c>
       <c r="H54" t="str">
-        <v>ワルファリンの過量。ワルファリン服用中はST合剤・マクロライド系・フルコナゾール等の相互作用やビタミンK摂取量の変化にも注意</v>
+        <v>NSAIDsなど腎機能を悪化させる薬剤。ACE阻害薬・ARB・SGLT2阻害薬は低下させる方向に働く</v>
       </c>
       <c r="I54" t="str">
-        <v>ワルファリンの効き不足、飲み忘れ、ビタミンK摂取量の急激な増加</v>
+        <v/>
       </c>
       <c r="J54" t="str">
-        <v>服薬状況（飲み忘れ）を確認する。片側のむくみ・しびれ・胸痛など血栓症状がないか確認する</v>
+        <v/>
       </c>
       <c r="K54" t="str">
-        <v>ワルファリン服用中で低値の場合は効果不十分の可能性。ビタミンK摂取量の変化や、リファンピシン・カルバマゼピン・バルビツール酸系など代謝を促進する薬との併用を確認</v>
+        <v/>
       </c>
       <c r="L54" t="str">
-        <v>治療域は疾患・年齢によって異なる（例：非弁膜症性心房細動の高齢者では1.6〜2.6が目安になることが多い）。多くの薬剤・食品と相互作用があるため新規薬剤追加時は必ず確認する。DOAC（エリキュース、リクシアナ、プラザキサなど）ではPT-INRのモニタリングは不要</v>
+        <v>糖尿病腎症の早期発見に重要な検査。血糖・血圧コントロールで改善しうる段階なので、早期介入の意義を伝える</v>
       </c>
       <c r="M54" t="str">
-        <v>抗凝固療法（心房細動・血栓症）</v>
+        <v>糖尿病,腎機能</v>
       </c>
       <c r="N54" t="str">
-        <v>PT-INR,INR,プロトロンビン時間,ワルファリン,ワーファリン,抗凝固</v>
+        <v>微量アルブミン,U-Alb,MAU,糖尿病性腎症,早期腎症</v>
       </c>
       <c r="O54" t="str">
-        <v>食事と栄養 p.221（心疾患Q93 ワルファリン服用中のビタミンK摂取）</v>
+        <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>骨型酒石酸抵抗性フォスファターゼ（TRACP-5b）</v>
+        <v>C反応性蛋白（CRP）</v>
       </c>
       <c r="B55" t="str">
-        <v>TRACP-5b</v>
+        <v>CRP</v>
       </c>
       <c r="C55" t="str">
-        <v>120〜420 mU/dL</v>
+        <v>0.3 mg/dL未満（施設差あり）</v>
       </c>
       <c r="D55" t="str">
-        <v>骨がどれくらい壊されているかを見る検査。骨は「古い骨を壊して新しい骨を作る」入れ替えを繰り返しており、骨を壊す細胞が活発だとこの物質が血液中に増える。</v>
+        <v>体のどこかに炎症や感染が起きていないかを鋭敏に反映する数値</v>
       </c>
       <c r="E55" t="str">
-        <v>この検査は、骨がどれくらい早く減っていないかを見るものです。数値が高いと、骨が弱くなりやすい状態の目安になります。</v>
+        <v>CRPは、体に炎症や感染が起きると数時間〜半日程度で急激に上昇する数値です。風邪のようなウイルス感染から細菌感染、体のどこかの炎症まで、幅広く反応するため、体調の変化を早期に捉える手がかりになります。</v>
       </c>
       <c r="F55" t="str">
-        <v>骨粗鬆症、骨代謝回転（骨がこわれるスピード）が活発な状態</v>
+        <v>細菌感染症、ウイルス感染症、自己免疫疾患（関節リウマチなど）、悪性腫瘍、組織の損傷（術後・心筋梗塞など）</v>
       </c>
       <c r="G55" t="str">
-        <v>カルシウム・ビタミンDの摂取や、適度な荷重運動（ウォーキングなど）を意識するよう伝える</v>
+        <v>発熱、痛み、腫れなど炎症症状の有無を確認する</v>
       </c>
       <c r="H55" t="str">
         <v/>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>「骨を壊す側」の指標。「骨を作る側」の検査と合わせて評価する。数値だけで診断はしない</v>
+        <v>白血球数と合わせて感染・炎症の程度を評価する。上昇・低下のタイミングは白血球より半日〜1日程度遅れる傾向があるため、経過を追う際は採血のタイミングに注意</v>
       </c>
       <c r="M55" t="str">
-        <v>骨粗鬆症</v>
+        <v/>
       </c>
       <c r="N55" t="str">
-        <v>TRACP-5b,骨型酒石酸抵抗性フォスファターゼ,骨粗鬆症,骨代謝</v>
+        <v>CRP,炎症,感染</v>
       </c>
       <c r="O55" t="str">
         <v/>
@@ -3011,125 +3011,125 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>骨型アルカリフォスファターゼ</v>
+        <v>PT-INR（プロトロンビン時間国際標準比）</v>
       </c>
       <c r="B56" t="str">
-        <v>BAP</v>
+        <v>PT-INR,INR</v>
       </c>
       <c r="C56" t="str">
-        <v>男性 3.7〜20.9 μg/L、女性（閉経前）2.9〜14.5 μg/L（施設差あり）</v>
+        <v>治療域の目安 1.6〜3.0（ワルファリン服用時。年齢・疾患により異なる）</v>
       </c>
       <c r="D56" t="str">
-        <v>ALPのうち骨に由来する成分だけを測定し、骨が作られる勢い（骨形成）を反映する</v>
+        <v>血液の固まりやすさを表す数値で、ワルファリンの効き具合を確認するために使う</v>
       </c>
       <c r="E56" t="str">
-        <v>骨型ALPは、通常のALP（アルカリフォスファターゼ）の中でも、骨で作られる成分だけを選んで測定するものです。骨を新しく作る働きがどれくらい活発かを見る指標として、骨粗鬆症の治療効果判定などに使われます。</v>
+        <v>PT-INRは血液が固まるまでの時間をもとにした数値で、ワルファリンというお薬を飲んでいる方の効き具合を確認するために測ります。数値が高いほど血液が固まりにくく出血しやすい状態、低いほど血栓ができやすい状態を示します。</v>
       </c>
       <c r="F56" t="str">
-        <v>骨代謝回転の亢進（骨粗鬆症、骨折治癒過程、骨形成促進薬による治療効果、Paget病、骨転移）</v>
+        <v>ワルファリンの効きすぎ、肝機能低下、ビタミンK不足、納豆・青汁など摂取量の変化</v>
       </c>
       <c r="G56" t="str">
-        <v/>
+        <v>歯ぐきや鼻からの出血、あざ、黒い便などの出血症状がないか確認する。納豆・クロレラ・青汁などビタミンKを多く含む食品の摂取状況を確認する</v>
       </c>
       <c r="H56" t="str">
-        <v/>
+        <v>ワルファリンの過量。ワルファリン服用中はST合剤・マクロライド系・フルコナゾール等の相互作用やビタミンK摂取量の変化にも注意</v>
       </c>
       <c r="I56" t="str">
-        <v>骨形成の低下</v>
+        <v>ワルファリンの効き不足、飲み忘れ、ビタミンK摂取量の急激な増加</v>
       </c>
       <c r="J56" t="str">
-        <v/>
+        <v>服薬状況（飲み忘れ）を確認する。片側のむくみ・しびれ・胸痛など血栓症状がないか確認する</v>
       </c>
       <c r="K56" t="str">
-        <v/>
+        <v>ワルファリン服用中で低値の場合は効果不十分の可能性。ビタミンK摂取量の変化や、リファンピシン・カルバマゼピン・バルビツール酸系など代謝を促進する薬との併用を確認</v>
       </c>
       <c r="L56" t="str">
-        <v>通常のALPと異なり肝臓の影響を受けにくいため、肝機能異常がある患者でも骨代謝を評価しやすい。P1NPと同じ「骨を作る側」の指標で、骨形成促進薬（テリパラチド等）の効果判定に使われる</v>
+        <v>治療域は疾患・年齢によって異なる（例：非弁膜症性心房細動の高齢者では1.6〜2.6が目安になることが多い）。多くの薬剤・食品と相互作用があるため新規薬剤追加時は必ず確認する。DOAC（エリキュース、リクシアナ、プラザキサなど）ではPT-INRのモニタリングは不要</v>
       </c>
       <c r="M56" t="str">
-        <v>骨粗鬆症</v>
+        <v>抗凝固療法（心房細動・血栓症）</v>
       </c>
       <c r="N56" t="str">
-        <v>骨型ALP,BAP,骨型アルカリフォスファターゼ,骨形成マーカー</v>
+        <v>PT-INR,INR,プロトロンビン時間,ワルファリン,ワーファリン,抗凝固</v>
       </c>
       <c r="O56" t="str">
-        <v/>
+        <v>食事と栄養 p.221（心疾患Q93 ワルファリン服用中のビタミンK摂取）</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>25-ヒドロキシビタミンD</v>
+        <v>骨型酒石酸抵抗性フォスファターゼ（TRACP-5b）</v>
       </c>
       <c r="B57" t="str">
-        <v>25(OH)D</v>
+        <v>TRACP-5b</v>
       </c>
       <c r="C57" t="str">
-        <v>30 ng/mL以上：充足、20〜30 ng/mL：不足、20 ng/mL未満：欠乏（施設差あり）</v>
+        <v>120〜420 mU/dL</v>
       </c>
       <c r="D57" t="str">
-        <v>体内のビタミンDの蓄え具合を反映する指標。カルシウムの吸収や骨の健康に関わる</v>
+        <v>骨がどれくらい壊されているかを見る検査。骨は「古い骨を壊して新しい骨を作る」入れ替えを繰り返しており、骨を壊す細胞が活発だとこの物質が血液中に増える。</v>
       </c>
       <c r="E57" t="str">
-        <v>この検査は、体の中にビタミンDがどれくらい蓄えられているかを見るものです。ビタミンDは、食事から摂ったカルシウムを腸で吸収するのを助ける働きがあり、不足すると骨がもろくなりやすくなります。</v>
+        <v>この検査は、骨がどれくらい早く減っていないかを見るものです。数値が高いと、骨が弱くなりやすい状態の目安になります。</v>
       </c>
       <c r="F57" t="str">
-        <v>ビタミンD製剤の過剰摂取</v>
+        <v>骨粗鬆症、骨代謝回転（骨がこわれるスピード）が活発な状態</v>
       </c>
       <c r="G57" t="str">
-        <v>活性型ビタミンD3製剤やサプリメントの摂取量を確認する。高カルシウム血症の症状（吐き気、便秘、多尿など）がないか確認する</v>
+        <v>カルシウム・ビタミンDの摂取や、適度な荷重運動（ウォーキングなど）を意識するよう伝える</v>
       </c>
       <c r="H57" t="str">
-        <v>活性型/天然型ビタミンD製剤の過量投与</v>
+        <v/>
       </c>
       <c r="I57" t="str">
-        <v>日光暴露不足、食事摂取不足、高齢、腸疾患による吸収不良、肝・腎機能低下（活性化障害）</v>
+        <v/>
       </c>
       <c r="J57" t="str">
-        <v>適度な日光浴、魚類・きのこ類などビタミンDを多く含む食品の摂取を意識するとよいことを伝える</v>
+        <v/>
       </c>
       <c r="K57" t="str">
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>骨粗鬆症治療における活性型ビタミンD3製剤の効果判定や、投与量調整の参考に用いられる。腎機能低下患者では活性化障害により25(OH)Dが正常でも活性型が不足することがある点に注意</v>
+        <v>「骨を壊す側」の指標。「骨を作る側」の検査と合わせて評価する。数値だけで診断はしない</v>
       </c>
       <c r="M57" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="N57" t="str">
-        <v>25(OH)D,ビタミンD,25-ヒドロキシビタミンD,ビタミンD欠乏,骨粗鬆症</v>
+        <v>TRACP-5b,骨型酒石酸抵抗性フォスファターゼ,骨粗鬆症,骨代謝</v>
       </c>
       <c r="O57" t="str">
-        <v>食事と栄養 p.38（ビタミンD）</v>
+        <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ucOC（低カルボキシル化オステオカルシン）</v>
+        <v>骨型アルカリフォスファターゼ</v>
       </c>
       <c r="B58" t="str">
-        <v>ucOC</v>
+        <v>BAP</v>
       </c>
       <c r="C58" t="str">
-        <v>4.5 ng/mL未満（施設差あり）</v>
+        <v>男性 3.7〜20.9 μg/L、女性（閉経前）2.9〜14.5 μg/L（施設差あり）</v>
       </c>
       <c r="D58" t="str">
-        <v>ビタミンKが不足していないかを反映する骨の指標</v>
+        <v>ALPのうち骨に由来する成分だけを測定し、骨が作られる勢い（骨形成）を反映する</v>
       </c>
       <c r="E58" t="str">
-        <v>ucOCは、骨を作るために必要なビタミンKが体の中で足りているかどうかを反映する検査です。数値が高いとビタミンK不足が疑われます。</v>
+        <v>骨型ALPは、通常のALP（アルカリフォスファターゼ）の中でも、骨で作られる成分だけを選んで測定するものです。骨を新しく作る働きがどれくらい活発かを見る指標として、骨粗鬆症の治療効果判定などに使われます。</v>
       </c>
       <c r="F58" t="str">
-        <v>ビタミンK不足状態</v>
+        <v>骨代謝回転の亢進（骨粗鬆症、骨折治癒過程、骨形成促進薬による治療効果、Paget病、骨転移）</v>
       </c>
       <c r="G58" t="str">
-        <v>ビタミンK2製剤(骨粗鬆症治療薬)の適応が検討されているか確認する。ワルファリン服用中の患者では、納豆などビタミンKを多く含む食品の急な摂取量の変化を避けるよう説明する</v>
+        <v/>
       </c>
       <c r="H58" t="str">
         <v/>
       </c>
       <c r="I58" t="str">
-        <v/>
+        <v>骨形成の低下</v>
       </c>
       <c r="J58" t="str">
         <v/>
@@ -3138,92 +3138,92 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>ビタミンK2製剤（骨粗鬆症治療薬）の適応判断や効果判定に使われる</v>
+        <v>通常のALPと異なり肝臓の影響を受けにくいため、肝機能異常がある患者でも骨代謝を評価しやすい。P1NPと同じ「骨を作る側」の指標で、骨形成促進薬（テリパラチド等）の効果判定に使われる</v>
       </c>
       <c r="M58" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="N58" t="str">
-        <v>ucOC,オステオカルシン,ビタミンK</v>
+        <v>骨型ALP,BAP,骨型アルカリフォスファターゼ,骨形成マーカー</v>
       </c>
       <c r="O58" t="str">
-        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>PTH（副甲状腺ホルモン）</v>
+        <v>25-ヒドロキシビタミンD</v>
       </c>
       <c r="B59" t="str">
-        <v>PTH</v>
+        <v>25(OH)D</v>
       </c>
       <c r="C59" t="str">
-        <v>10〜65 pg/mL（施設差あり）</v>
+        <v>30 ng/mL以上：充足、20〜30 ng/mL：不足、20 ng/mL未満：欠乏（施設差あり）</v>
       </c>
       <c r="D59" t="str">
-        <v>血液中のカルシウム濃度を調節するホルモン</v>
+        <v>体内のビタミンDの蓄え具合を反映する指標。カルシウムの吸収や骨の健康に関わる</v>
       </c>
       <c r="E59" t="str">
-        <v>PTHは、血液中のカルシウム濃度を一定に保つために働くホルモンです。カルシウムが低くなると分泌が増え、骨からカルシウムを取り出したり、腎臓での再吸収を促したりして数値を戻そうとします。</v>
+        <v>この検査は、体の中にビタミンDがどれくらい蓄えられているかを見るものです。ビタミンDは、食事から摂ったカルシウムを腸で吸収するのを助ける働きがあり、不足すると骨がもろくなりやすくなります。</v>
       </c>
       <c r="F59" t="str">
-        <v>原発性・二次性副甲状腺機能亢進症（腎不全に伴うものなど）</v>
+        <v>ビタミンD製剤の過剰摂取</v>
       </c>
       <c r="G59" t="str">
-        <v/>
+        <v>活性型ビタミンD3製剤やサプリメントの摂取量を確認する。高カルシウム血症の症状（吐き気、便秘、多尿など）がないか確認する</v>
       </c>
       <c r="H59" t="str">
-        <v/>
+        <v>活性型/天然型ビタミンD製剤の過量投与</v>
       </c>
       <c r="I59" t="str">
-        <v>副甲状腺機能低下症</v>
+        <v>日光暴露不足、食事摂取不足、高齢、腸疾患による吸収不良、肝・腎機能低下（活性化障害）</v>
       </c>
       <c r="J59" t="str">
-        <v/>
+        <v>適度な日光浴、魚類・きのこ類などビタミンDを多く含む食品の摂取を意識するとよいことを伝える</v>
       </c>
       <c r="K59" t="str">
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>骨粗鬆症の二次性原因（副甲状腺機能亢進症）を除外するための検査。カルシウム・リンと合わせて評価する</v>
+        <v>骨粗鬆症治療における活性型ビタミンD3製剤の効果判定や、投与量調整の参考に用いられる。腎機能低下患者では活性化障害により25(OH)Dが正常でも活性型が不足することがある点に注意</v>
       </c>
       <c r="M59" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="N59" t="str">
-        <v>PTH,副甲状腺ホルモン,パラトルモン</v>
+        <v>25(OH)D,ビタミンD,25-ヒドロキシビタミンD,ビタミンD欠乏,骨粗鬆症</v>
       </c>
       <c r="O59" t="str">
-        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
+        <v>食事と栄養 p.38（ビタミンD）</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>尿中NTX</v>
+        <v>ucOC（低カルボキシル化オステオカルシン）</v>
       </c>
       <c r="B60" t="str">
-        <v>NTX</v>
+        <v>ucOC</v>
       </c>
       <c r="C60" t="str">
-        <v>施設差が大きく一律の記載が難しい（尿中）</v>
+        <v>4.5 ng/mL未満（施設差あり）</v>
       </c>
       <c r="D60" t="str">
-        <v>骨が壊されるときに出る、骨吸収マーカーのひとつ</v>
+        <v>ビタミンKが不足していないかを反映する骨の指標</v>
       </c>
       <c r="E60" t="str">
-        <v>NTXは、骨が壊される（吸収される）ときに尿の中に出てくる物質です。骨粗鬆症の治療薬がどれくらい効いているかを確認するために使われます。</v>
+        <v>ucOCは、骨を作るために必要なビタミンKが体の中で足りているかどうかを反映する検査です。数値が高いとビタミンK不足が疑われます。</v>
       </c>
       <c r="F60" t="str">
-        <v>骨代謝回転の亢進（骨粗鬆症、閉経後など）</v>
+        <v>ビタミンK不足状態</v>
       </c>
       <c r="G60" t="str">
-        <v/>
+        <v>ビタミンK2製剤(骨粗鬆症治療薬)の適応が検討されているか確認する。ワルファリン服用中の患者では、納豆などビタミンKを多く含む食品の急な摂取量の変化を避けるよう説明する</v>
       </c>
       <c r="H60" t="str">
         <v/>
       </c>
       <c r="I60" t="str">
-        <v>骨吸収抑制薬（ビスホスホネート等）による治療効果</v>
+        <v/>
       </c>
       <c r="J60" t="str">
         <v/>
@@ -3232,13 +3232,13 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>治療開始後3〜6か月で再検し、薬の効果判定に使われる。TRACP-5bと同じ「骨を壊す側」の指標</v>
+        <v>ビタミンK2製剤（骨粗鬆症治療薬）の適応判断や効果判定に使われる</v>
       </c>
       <c r="M60" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="N60" t="str">
-        <v>NTX,尿中NTX,骨吸収マーカー</v>
+        <v>ucOC,オステオカルシン,ビタミンK</v>
       </c>
       <c r="O60" t="str">
         <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
@@ -3246,22 +3246,22 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>カルシトニン</v>
+        <v>PTH（副甲状腺ホルモン）</v>
       </c>
       <c r="B61" t="str">
-        <v>CT</v>
+        <v>PTH</v>
       </c>
       <c r="C61" t="str">
-        <v>男性 9.52 pg/mL未満、女性 6.40 pg/mL未満（施設差あり）</v>
+        <v>10〜65 pg/mL（施設差あり）</v>
       </c>
       <c r="D61" t="str">
-        <v>血液中のカルシウムを下げる方向に働くホルモン</v>
+        <v>血液中のカルシウム濃度を調節するホルモン</v>
       </c>
       <c r="E61" t="str">
-        <v>カルシトニンは、PTHとは逆に血液中のカルシウムを下げる方向に働くホルモンです。特定の甲状腺の病気（甲状腺髄様癌）がないかを調べる際にも使われます。</v>
+        <v>PTHは、血液中のカルシウム濃度を一定に保つために働くホルモンです。カルシウムが低くなると分泌が増え、骨からカルシウムを取り出したり、腎臓での再吸収を促したりして数値を戻そうとします。</v>
       </c>
       <c r="F61" t="str">
-        <v>甲状腺髄様癌、腎不全</v>
+        <v>原発性・二次性副甲状腺機能亢進症（腎不全に伴うものなど）</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -3270,7 +3270,7 @@
         <v/>
       </c>
       <c r="I61" t="str">
-        <v/>
+        <v>副甲状腺機能低下症</v>
       </c>
       <c r="J61" t="str">
         <v/>
@@ -3279,13 +3279,13 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>骨粗鬆症の二次性原因の除外目的で測定されることがある検査値。同名の薬剤（カルシトニン製剤）と混同しないよう注意</v>
+        <v>骨粗鬆症の二次性原因（副甲状腺機能亢進症）を除外するための検査。カルシウム・リンと合わせて評価する</v>
       </c>
       <c r="M61" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="N61" t="str">
-        <v>カルシトニン,CT</v>
+        <v>PTH,副甲状腺ホルモン,パラトルモン</v>
       </c>
       <c r="O61" t="str">
         <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
@@ -3293,22 +3293,22 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>DPD（デオキシピリジノリン）</v>
+        <v>尿中NTX</v>
       </c>
       <c r="B62" t="str">
-        <v>DPD</v>
+        <v>NTX</v>
       </c>
       <c r="C62" t="str">
         <v>施設差が大きく一律の記載が難しい（尿中）</v>
       </c>
       <c r="D62" t="str">
-        <v>骨のコラーゲンが壊れるときに出る、骨吸収マーカーのひとつ</v>
+        <v>骨が壊されるときに出る、骨吸収マーカーのひとつ</v>
       </c>
       <c r="E62" t="str">
-        <v>DPDも、骨が壊されるときに尿に出てくる物質の一つです。NTXと同じように、骨粗鬆症治療薬の効果を確認するために使われます。</v>
+        <v>NTXは、骨が壊される（吸収される）ときに尿の中に出てくる物質です。骨粗鬆症の治療薬がどれくらい効いているかを確認するために使われます。</v>
       </c>
       <c r="F62" t="str">
-        <v>骨代謝回転の亢進（骨粗鬆症など）</v>
+        <v>骨代謝回転の亢進（骨粗鬆症、閉経後など）</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -3317,7 +3317,7 @@
         <v/>
       </c>
       <c r="I62" t="str">
-        <v>骨吸収抑制薬による治療効果</v>
+        <v>骨吸収抑制薬（ビスホスホネート等）による治療効果</v>
       </c>
       <c r="J62" t="str">
         <v/>
@@ -3326,13 +3326,13 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>NTX・CTXと同じ「骨を壊す側」の指標。食事の影響を受けにくいとされる</v>
+        <v>治療開始後3〜6か月で再検し、薬の効果判定に使われる。TRACP-5bと同じ「骨を壊す側」の指標</v>
       </c>
       <c r="M62" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="N62" t="str">
-        <v>DPD,デオキシピリジノリン,骨吸収マーカー</v>
+        <v>NTX,尿中NTX,骨吸収マーカー</v>
       </c>
       <c r="O62" t="str">
         <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
@@ -3340,22 +3340,22 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>CTX</v>
+        <v>カルシトニン</v>
       </c>
       <c r="B63" t="str">
-        <v>CTX</v>
+        <v>CT</v>
       </c>
       <c r="C63" t="str">
-        <v>施設差が大きく一律の記載が難しい（血清・尿中）</v>
+        <v>男性 9.52 pg/mL未満、女性 6.40 pg/mL未満（施設差あり）</v>
       </c>
       <c r="D63" t="str">
-        <v>骨のコラーゲンが壊れるときに出る、骨吸収マーカーのひとつ</v>
+        <v>血液中のカルシウムを下げる方向に働くホルモン</v>
       </c>
       <c r="E63" t="str">
-        <v>CTXも、骨が壊されるときに血液や尿に出てくる物質です。骨粗鬆症治療薬（骨を壊すのを抑える薬）の効果を確認するために使われます。</v>
+        <v>カルシトニンは、PTHとは逆に血液中のカルシウムを下げる方向に働くホルモンです。特定の甲状腺の病気（甲状腺髄様癌）がないかを調べる際にも使われます。</v>
       </c>
       <c r="F63" t="str">
-        <v>骨代謝回転の亢進（骨粗鬆症など）</v>
+        <v>甲状腺髄様癌、腎不全</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -3364,7 +3364,7 @@
         <v/>
       </c>
       <c r="I63" t="str">
-        <v>骨吸収抑制薬による治療効果</v>
+        <v/>
       </c>
       <c r="J63" t="str">
         <v/>
@@ -3373,13 +3373,13 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>NTX・DPDと同じ「骨を壊す側」の指標。血清・尿中いずれでも測定されることがある</v>
+        <v>骨粗鬆症の二次性原因の除外目的で測定されることがある検査値。同名の薬剤（カルシトニン製剤）と混同しないよう注意</v>
       </c>
       <c r="M63" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="N63" t="str">
-        <v>CTX,骨吸収マーカー</v>
+        <v>カルシトニン,CT</v>
       </c>
       <c r="O63" t="str">
         <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
@@ -3387,22 +3387,22 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>P1NP</v>
+        <v>DPD（デオキシピリジノリン）</v>
       </c>
       <c r="B64" t="str">
-        <v>P1NP</v>
+        <v>DPD</v>
       </c>
       <c r="C64" t="str">
-        <v>施設差が大きく一律の記載が難しい（血清）</v>
+        <v>施設差が大きく一律の記載が難しい（尿中）</v>
       </c>
       <c r="D64" t="str">
-        <v>骨が新しく作られるときに出る、骨形成マーカーのひとつ</v>
+        <v>骨のコラーゲンが壊れるときに出る、骨吸収マーカーのひとつ</v>
       </c>
       <c r="E64" t="str">
-        <v>P1NPは、CTXなどとは逆に、骨が新しく作られるときに血液中に出てくる物質です。骨を作る力を高める薬（テリパラチドなど）の効果を確認するために使われます。</v>
+        <v>DPDも、骨が壊されるときに尿に出てくる物質の一つです。NTXと同じように、骨粗鬆症治療薬の効果を確認するために使われます。</v>
       </c>
       <c r="F64" t="str">
-        <v>骨代謝回転の亢進、骨形成促進薬による治療効果</v>
+        <v>骨代謝回転の亢進（骨粗鬆症など）</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -3411,7 +3411,7 @@
         <v/>
       </c>
       <c r="I64" t="str">
-        <v>骨形成の低下</v>
+        <v>骨吸収抑制薬による治療効果</v>
       </c>
       <c r="J64" t="str">
         <v/>
@@ -3420,13 +3420,13 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>TRACP-5b等「骨を壊す側」の指標とは逆の、「骨を作る側」の指標。骨形成促進薬（テリパラチド等）の効果判定に使われる</v>
+        <v>NTX・CTXと同じ「骨を壊す側」の指標。食事の影響を受けにくいとされる</v>
       </c>
       <c r="M64" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="N64" t="str">
-        <v>P1NP,骨形成マーカー</v>
+        <v>DPD,デオキシピリジノリン,骨吸収マーカー</v>
       </c>
       <c r="O64" t="str">
         <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
@@ -3434,69 +3434,69 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>血清鉄（Fe）</v>
+        <v>CTX</v>
       </c>
       <c r="B65" t="str">
-        <v>Fe</v>
+        <v>CTX</v>
       </c>
       <c r="C65" t="str">
-        <v>60〜200 μg/dL（施設差あり）</v>
+        <v>施設差が大きく一律の記載が難しい（血清・尿中）</v>
       </c>
       <c r="D65" t="str">
-        <v>血液中を流れている鉄の量</v>
+        <v>骨のコラーゲンが壊れるときに出る、骨吸収マーカーのひとつ</v>
       </c>
       <c r="E65" t="str">
-        <v>この検査は、今血液の中を流れている鉄の量を見るものです。低いと、体の中で鉄が不足している可能性があります。</v>
+        <v>CTXも、骨が壊されるときに血液や尿に出てくる物質です。骨粗鬆症治療薬（骨を壊すのを抑える薬）の効果を確認するために使われます。</v>
       </c>
       <c r="F65" t="str">
-        <v>鉄剤の過剰摂取、溶血、肝疾患</v>
+        <v>骨代謝回転の亢進（骨粗鬆症など）</v>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>鉄剤の過量摂取(小児の誤飲を含む)</v>
+        <v/>
       </c>
       <c r="I65" t="str">
-        <v>鉄欠乏性貧血、慢性炎症、出血</v>
+        <v>骨吸収抑制薬による治療効果</v>
       </c>
       <c r="J65" t="str">
-        <v>鉄分の多い食品（レバー・赤身肉・魚・ほうれん草など）を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える</v>
+        <v/>
       </c>
       <c r="K65" t="str">
-        <v>プロトンポンプ阻害薬(PPI)・H2ブロッカーは胃酸分泌抑制により鉄の吸収を低下させうる</v>
+        <v/>
       </c>
       <c r="L65" t="str">
-        <v>血清鉄は日内変動が大きい。単独で判断せず総鉄結合能・フェリチンと合わせて評価する</v>
+        <v>NTX・DPDと同じ「骨を壊す側」の指標。血清・尿中いずれでも測定されることがある</v>
       </c>
       <c r="M65" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="N65" t="str">
-        <v>血清鉄,Fe,鉄欠乏性貧血</v>
+        <v>CTX,骨吸収マーカー</v>
       </c>
       <c r="O65" t="str">
-        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>総鉄結合能（TIBC）</v>
+        <v>P1NP</v>
       </c>
       <c r="B66" t="str">
-        <v>TIBC</v>
+        <v>P1NP</v>
       </c>
       <c r="C66" t="str">
-        <v>250〜360 μg/dL（施設差あり）</v>
+        <v>施設差が大きく一律の記載が難しい（血清）</v>
       </c>
       <c r="D66" t="str">
-        <v>血液中のトランスフェリンが鉄と結合できる総量</v>
+        <v>骨が新しく作られるときに出る、骨形成マーカーのひとつ</v>
       </c>
       <c r="E66" t="str">
-        <v>TIBCは、血液中でトランスフェリンという物質が鉄を運べる最大量を表します。体の中の鉄が不足すると、少しでも多く鉄を運ぼうとしてこの数値が上がる性質があります。</v>
+        <v>P1NPは、CTXなどとは逆に、骨が新しく作られるときに血液中に出てくる物質です。骨を作る力を高める薬（テリパラチドなど）の効果を確認するために使われます。</v>
       </c>
       <c r="F66" t="str">
-        <v>鉄欠乏性貧血（＞360 μg/dLが目安）</v>
+        <v>骨代謝回転の亢進、骨形成促進薬による治療効果</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -3505,7 +3505,7 @@
         <v/>
       </c>
       <c r="I66" t="str">
-        <v>慢性炎症、肝疾患、ネフローゼ症候群</v>
+        <v>骨形成の低下</v>
       </c>
       <c r="J66" t="str">
         <v/>
@@ -3514,60 +3514,60 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>鉄が不足すると、体はより多く運ぼうとしてTIBCが上昇する。UIBC・血清鉄と併せて評価する</v>
+        <v>TRACP-5b等「骨を壊す側」の指標とは逆の、「骨を作る側」の指標。骨形成促進薬（テリパラチド等）の効果判定に使われる</v>
       </c>
       <c r="M66" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="N66" t="str">
-        <v>TIBC,総鉄結合能,鉄欠乏性貧血</v>
+        <v>P1NP,骨形成マーカー</v>
       </c>
       <c r="O66" t="str">
-        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>不飽和鉄結合能（UIBC）</v>
+        <v>血清鉄（Fe）</v>
       </c>
       <c r="B67" t="str">
-        <v>UIBC</v>
+        <v>Fe</v>
       </c>
       <c r="C67" t="str">
-        <v>170〜300 μg/dL（施設差あり）</v>
+        <v>60〜200 μg/dL（施設差あり）</v>
       </c>
       <c r="D67" t="str">
-        <v>トランスフェリンのうち、まだ鉄と結合していない余力の部分（UIBC＝TIBC－血清鉄）</v>
+        <v>血液中を流れている鉄の量</v>
       </c>
       <c r="E67" t="str">
-        <v>UIBCは、トランスフェリンのうち、まだ鉄と結合していない「空き容量」の部分を表します。鉄が不足しているときほど、この空き容量は大きくなります。</v>
+        <v>この検査は、今血液の中を流れている鉄の量を見るものです。低いと、体の中で鉄が不足している可能性があります。</v>
       </c>
       <c r="F67" t="str">
-        <v>鉄欠乏性貧血（＞300 μg/dLが目安）</v>
+        <v>鉄剤の過剰摂取、溶血、肝疾患</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v/>
+        <v>鉄剤の過量摂取(小児の誤飲を含む)</v>
       </c>
       <c r="I67" t="str">
-        <v>慢性炎症、鉄過剰状態</v>
+        <v>鉄欠乏性貧血、慢性炎症、出血</v>
       </c>
       <c r="J67" t="str">
-        <v/>
+        <v>鉄分の多い食品（レバー・赤身肉・魚・ほうれん草など）を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える</v>
       </c>
       <c r="K67" t="str">
-        <v/>
+        <v>プロトンポンプ阻害薬(PPI)・H2ブロッカーは胃酸分泌抑制により鉄の吸収を低下させうる</v>
       </c>
       <c r="L67" t="str">
-        <v>TIBCと同じ方向に動くことが多い。血清鉄・TIBCとあわせて鉄欠乏性貧血と二次性貧血の鑑別に使う</v>
+        <v>血清鉄は日内変動が大きい。単独で判断せず総鉄結合能・フェリチンと合わせて評価する</v>
       </c>
       <c r="M67" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
       <c r="N67" t="str">
-        <v>UIBC,不飽和鉄結合能,鉄欠乏性貧血</v>
+        <v>血清鉄,Fe,鉄欠乏性貧血</v>
       </c>
       <c r="O67" t="str">
         <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
@@ -3575,22 +3575,22 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>トランスフェリン飽和度</v>
+        <v>総鉄結合能（TIBC）</v>
       </c>
       <c r="B68" t="str">
-        <v>TSAT</v>
+        <v>TIBC</v>
       </c>
       <c r="C68" t="str">
-        <v>16〜50%程度（施設差あり）</v>
+        <v>250〜360 μg/dL（施設差あり）</v>
       </c>
       <c r="D68" t="str">
-        <v>鉄を運ぶ役割のトランスフェリンのうち、実際に鉄を運んでいる割合（血清鉄÷総鉄結合能）</v>
+        <v>血液中のトランスフェリンが鉄と結合できる総量</v>
       </c>
       <c r="E68" t="str">
-        <v>トランスフェリン飽和度は、鉄を運ぶトランスフェリンのうち、実際にどれくらいが鉄を運んでいるかを割合で表したものです。鉄欠乏性貧血では低くなり、鉄が過剰にたまる病気では高くなります。</v>
+        <v>TIBCは、血液中でトランスフェリンという物質が鉄を運べる最大量を表します。体の中の鉄が不足すると、少しでも多く鉄を運ぼうとしてこの数値が上がる性質があります。</v>
       </c>
       <c r="F68" t="str">
-        <v>鉄過剰症（ヘモクロマトーシスなど）</v>
+        <v>鉄欠乏性貧血（＞360 μg/dLが目安）</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v/>
       </c>
       <c r="I68" t="str">
-        <v>鉄欠乏性貧血（＜16%が目安）</v>
+        <v>慢性炎症、肝疾患、ネフローゼ症候群</v>
       </c>
       <c r="J68" t="str">
         <v/>
@@ -3608,13 +3608,13 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>血清鉄をTIBCで割って計算される。鉄剤補充の効果判定にも使われる</v>
+        <v>鉄が不足すると、体はより多く運ぼうとしてTIBCが上昇する。UIBC・血清鉄と併せて評価する</v>
       </c>
       <c r="M68" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
       <c r="N68" t="str">
-        <v>トランスフェリン飽和度,TSAT,鉄欠乏性貧血</v>
+        <v>TIBC,総鉄結合能,鉄欠乏性貧血</v>
       </c>
       <c r="O68" t="str">
         <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
@@ -3622,22 +3622,22 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>血清フェリチン</v>
+        <v>不飽和鉄結合能（UIBC）</v>
       </c>
       <c r="B69" t="str">
-        <v>Ferritin</v>
+        <v>UIBC</v>
       </c>
       <c r="C69" t="str">
-        <v>男性 20〜250 ng/mL、女性 10〜120 ng/mL（施設差あり）</v>
+        <v>170〜300 μg/dL（施設差あり）</v>
       </c>
       <c r="D69" t="str">
-        <v>体に貯蔵されている鉄の量を反映する指標。貧血の症状が出るより早い段階で低下する</v>
+        <v>トランスフェリンのうち、まだ鉄と結合していない余力の部分（UIBC＝TIBC－血清鉄）</v>
       </c>
       <c r="E69" t="str">
-        <v>フェリチンは、体に蓄えられている鉄の「貯金」の量を見る検査です。この数値が下がるのは、貧血の症状が出るよりも前の、とても早い段階のサインになります。</v>
+        <v>UIBCは、トランスフェリンのうち、まだ鉄と結合していない「空き容量」の部分を表します。鉄が不足しているときほど、この空き容量は大きくなります。</v>
       </c>
       <c r="F69" t="str">
-        <v>炎症性疾患、肝疾患、悪性腫瘍、鉄過剰症（フェリチンは炎症でも上昇するため、貧血の評価では注意が必要）</v>
+        <v>鉄欠乏性貧血（＞300 μg/dLが目安）</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3646,22 +3646,22 @@
         <v/>
       </c>
       <c r="I69" t="str">
-        <v>鉄欠乏状態（貧血の症状が出る前の早期段階から低下する）</v>
+        <v>慢性炎症、鉄過剰状態</v>
       </c>
       <c r="J69" t="str">
-        <v>鉄分の多い食品を意識するとともに、貯蔵鉄を補うため治療は数値が正常化してからも継続が必要なことを伝える</v>
+        <v/>
       </c>
       <c r="K69" t="str">
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>貯蔵鉄の指標で鉄欠乏を最も早期に反映する。ただし炎症があると鉄欠乏があっても正常〜高値に出ることがあり、CRP等の炎症所見と合わせて評価する。二次性貧血との鑑別に重要</v>
+        <v>TIBCと同じ方向に動くことが多い。血清鉄・TIBCとあわせて鉄欠乏性貧血と二次性貧血の鑑別に使う</v>
       </c>
       <c r="M69" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
       <c r="N69" t="str">
-        <v>フェリチン,Ferritin,貯蔵鉄,鉄欠乏</v>
+        <v>UIBC,不飽和鉄結合能,鉄欠乏性貧血</v>
       </c>
       <c r="O69" t="str">
         <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
@@ -3669,22 +3669,22 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>尿中尿酸/クレアチニン比（UUA/UCr）</v>
+        <v>トランスフェリン飽和度</v>
       </c>
       <c r="B70" t="str">
-        <v>UUA/UCr</v>
+        <v>TSAT</v>
       </c>
       <c r="C70" t="str">
-        <v>0.4〜0.8程度が混合型の目安</v>
+        <v>16〜50%程度（施設差あり）</v>
       </c>
       <c r="D70" t="str">
-        <v>尿酸が「作られすぎ」か「排泄できていない」かを見分ける比の値</v>
+        <v>鉄を運ぶ役割のトランスフェリンのうち、実際に鉄を運んでいる割合（血清鉄÷総鉄結合能）</v>
       </c>
       <c r="E70" t="str">
-        <v>この数値は、体の中で尿酸が「作られすぎている」のか、それとも「うまく排泄できていない」のかを見分けるために使う比の値です。高尿酸血症の治療薬を選ぶときの参考になります。</v>
+        <v>トランスフェリン飽和度は、鉄を運ぶトランスフェリンのうち、実際にどれくらいが鉄を運んでいるかを割合で表したものです。鉄欠乏性貧血では低くなり、鉄が過剰にたまる病気では高くなります。</v>
       </c>
       <c r="F70" t="str">
-        <v>尿酸産生過剰型（0.8以上が目安）</v>
+        <v>鉄過剰症（ヘモクロマトーシスなど）</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3693,7 +3693,7 @@
         <v/>
       </c>
       <c r="I70" t="str">
-        <v>尿酸排泄低下型（0.4以下が目安）</v>
+        <v>鉄欠乏性貧血（＜16%が目安）</v>
       </c>
       <c r="J70" t="str">
         <v/>
@@ -3702,36 +3702,36 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>高尿酸血症は尿酸産生過剰型・排泄低下型・混合型に分類され、この比が目安になる。病型によって使う薬剤（尿酸生成抑制薬か尿酸排泄促進薬か）の選択が変わる</v>
+        <v>血清鉄をTIBCで割って計算される。鉄剤補充の効果判定にも使われる</v>
       </c>
       <c r="M70" t="str">
-        <v>高尿酸血症</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="N70" t="str">
-        <v>UUA,UCr,尿酸クリアランス,CUA,EUA,尿酸産生過剰型,尿酸排泄低下型</v>
+        <v>トランスフェリン飽和度,TSAT,鉄欠乏性貧血</v>
       </c>
       <c r="O70" t="str">
-        <v>食事と栄養 p.180-189（第2部 痛風・高尿酸血症）</v>
+        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>抗甲状腺マイクロゾーム抗体（抗TPO抗体）</v>
+        <v>血清フェリチン</v>
       </c>
       <c r="B71" t="str">
-        <v>TPOAb</v>
+        <v>Ferritin</v>
       </c>
       <c r="C71" t="str">
-        <v>陰性（16 IU/mL未満程度、施設差あり）</v>
+        <v>男性 20〜250 ng/mL、女性 10〜120 ng/mL（施設差あり）</v>
       </c>
       <c r="D71" t="str">
-        <v>自分の甲状腺を攻撃する抗体が出ていないかを見る検査</v>
+        <v>体に貯蔵されている鉄の量を反映する指標。貧血の症状が出るより早い段階で低下する</v>
       </c>
       <c r="E71" t="str">
-        <v>この検査は、体の中に自分の甲状腺を誤って攻撃してしまう抗体がないかを見るものです。陽性の場合、橋本病（慢性甲状腺炎）など甲状腺の自己免疫的な炎症が背景にある可能性があります。</v>
+        <v>フェリチンは、体に蓄えられている鉄の「貯金」の量を見る検査です。この数値が下がるのは、貧血の症状が出るよりも前の、とても早い段階のサインになります。</v>
       </c>
       <c r="F71" t="str">
-        <v>橋本病（慢性甲状腺炎）、バセドウ病などの自己免疫性甲状腺疾患</v>
+        <v>炎症性疾患、肝疾患、悪性腫瘍、鉄過剰症（フェリチンは炎症でも上昇するため、貧血の評価では注意が必要）</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3740,45 +3740,45 @@
         <v/>
       </c>
       <c r="I71" t="str">
-        <v/>
+        <v>鉄欠乏状態（貧血の症状が出る前の早期段階から低下する）</v>
       </c>
       <c r="J71" t="str">
-        <v/>
+        <v>鉄分の多い食品を意識するとともに、貯蔵鉄を補うため治療は数値が正常化してからも継続が必要なことを伝える</v>
       </c>
       <c r="K71" t="str">
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>陽性でも必ずしも甲状腺機能異常があるとは限らない。TSH・FT4など甲状腺ホルモンの数値と合わせて評価する</v>
+        <v>貯蔵鉄の指標で鉄欠乏を最も早期に反映する。ただし炎症があると鉄欠乏があっても正常〜高値に出ることがあり、CRP等の炎症所見と合わせて評価する。二次性貧血との鑑別に重要</v>
       </c>
       <c r="M71" t="str">
-        <v>甲状腺疾患</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="N71" t="str">
-        <v>抗TPO抗体,抗甲状腺マイクロゾーム抗体,TPOAb,橋本病</v>
+        <v>フェリチン,Ferritin,貯蔵鉄,鉄欠乏</v>
       </c>
       <c r="O71" t="str">
-        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
+        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>抗サイログロブリン抗体</v>
+        <v>尿中尿酸/クレアチニン比（UUA/UCr）</v>
       </c>
       <c r="B72" t="str">
-        <v>TgAb</v>
+        <v>UUA/UCr</v>
       </c>
       <c r="C72" t="str">
-        <v>陰性（28 IU/mL未満程度、施設差あり）</v>
+        <v>0.4〜0.8程度が混合型の目安</v>
       </c>
       <c r="D72" t="str">
-        <v>甲状腺のたんぱく質（サイログロブリン）への抗体が出ていないかを見る検査</v>
+        <v>尿酸が「作られすぎ」か「排泄できていない」かを見分ける比の値</v>
       </c>
       <c r="E72" t="str">
-        <v>この検査も、抗TPO抗体と同じく、甲状腺に対する自己免疫の有無を見るものです。あわせて調べることで橋本病などの診断の参考にします。</v>
+        <v>この数値は、体の中で尿酸が「作られすぎている」のか、それとも「うまく排泄できていない」のかを見分けるために使う比の値です。高尿酸血症の治療薬を選ぶときの参考になります。</v>
       </c>
       <c r="F72" t="str">
-        <v>橋本病（慢性甲状腺炎）、バセドウ病などの自己免疫性甲状腺疾患</v>
+        <v>尿酸産生過剰型（0.8以上が目安）</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3787,7 +3787,7 @@
         <v/>
       </c>
       <c r="I72" t="str">
-        <v/>
+        <v>尿酸排泄低下型（0.4以下が目安）</v>
       </c>
       <c r="J72" t="str">
         <v/>
@@ -3796,92 +3796,92 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>抗TPO抗体とあわせて測定されることが多い。単独の高値だけで治療方針が決まるわけではない</v>
+        <v>高尿酸血症は尿酸産生過剰型・排泄低下型・混合型に分類され、この比が目安になる。病型によって使う薬剤（尿酸生成抑制薬か尿酸排泄促進薬か）の選択が変わる</v>
       </c>
       <c r="M72" t="str">
-        <v>甲状腺疾患</v>
+        <v>高尿酸血症</v>
       </c>
       <c r="N72" t="str">
-        <v>抗サイログロブリン抗体,TgAb,橋本病</v>
+        <v>UUA,UCr,尿酸クリアランス,CUA,EUA,尿酸産生過剰型,尿酸排泄低下型</v>
       </c>
       <c r="O72" t="str">
-        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
+        <v>食事と栄養 p.180-189（第2部 痛風・高尿酸血症）</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>血中薬物濃度（TDM）</v>
+        <v>抗甲状腺マイクロゾーム抗体（抗TPO抗体）</v>
       </c>
       <c r="B73" t="str">
-        <v>TDM</v>
+        <v>TPOAb</v>
       </c>
       <c r="C73" t="str">
-        <v>薬剤ごとに有効域が異なる（例：カルバマゼピン 4〜12 μg/mL、バルプロ酸 40〜100 μg/mL、フェニトイン 10〜20 μg/mL）</v>
+        <v>陰性（16 IU/mL未満程度、施設差あり）</v>
       </c>
       <c r="D73" t="str">
-        <v>治療域が狭い薬剤で、血液中の薬の濃度が効果域・中毒域のどちらにあるかを確認する検査</v>
+        <v>自分の甲状腺を攻撃する抗体が出ていないかを見る検査</v>
       </c>
       <c r="E73" t="str">
-        <v>この薬は効く量と副作用が出る量が近いため、血液中の薬の濃度を定期的に測って、ちょうどよい範囲に入っているかを確認します。数値が低いと効果が不十分になり、高いと副作用が出やすくなります。</v>
+        <v>この検査は、体の中に自分の甲状腺を誤って攻撃してしまう抗体がないかを見るものです。陽性の場合、橋本病（慢性甲状腺炎）など甲状腺の自己免疫的な炎症が背景にある可能性があります。</v>
       </c>
       <c r="F73" t="str">
-        <v>過量投与、代謝を妨げる薬剤との併用、肝機能低下による代謝低下</v>
+        <v>橋本病（慢性甲状腺炎）、バセドウ病などの自己免疫性甲状腺疾患</v>
       </c>
       <c r="G73" t="str">
-        <v>ふらつき、眠気、めまい、物が二重に見えるなどの中毒症状がないか確認する</v>
+        <v/>
       </c>
       <c r="H73" t="str">
         <v/>
       </c>
       <c r="I73" t="str">
-        <v>飲み忘れ、自己判断による減量、代謝を促進する薬剤との併用（相互作用）</v>
+        <v/>
       </c>
       <c r="J73" t="str">
-        <v>発作やてんかん症状の再発がないか確認し、飲み忘れがないか一緒に確認する</v>
+        <v/>
       </c>
       <c r="K73" t="str">
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>採血のタイミング（トラフ値かどうか）で数値の解釈が変わるため採血時点を確認する。カルバマゼピンは自己誘導により長期使用で濃度が下がることがある点にも注意</v>
+        <v>陽性でも必ずしも甲状腺機能異常があるとは限らない。TSH・FT4など甲状腺ホルモンの数値と合わせて評価する</v>
       </c>
       <c r="M73" t="str">
-        <v>てんかん</v>
+        <v>甲状腺疾患</v>
       </c>
       <c r="N73" t="str">
-        <v>TDM,血中薬物濃度,治療域,中毒域,カルバマゼピン,フェニトイン,バルプロ酸,抗てんかん薬</v>
+        <v>抗TPO抗体,抗甲状腺マイクロゾーム抗体,TPOAb,橋本病</v>
       </c>
       <c r="O73" t="str">
-        <v/>
+        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>アミラーゼ（AMY）</v>
+        <v>抗サイログロブリン抗体</v>
       </c>
       <c r="B74" t="str">
-        <v>AMY</v>
+        <v>TgAb</v>
       </c>
       <c r="C74" t="str">
-        <v>44〜132 U/L（施設差あり）</v>
+        <v>陰性（28 IU/mL未満程度、施設差あり）</v>
       </c>
       <c r="D74" t="str">
-        <v>膵臓や唾液腺から出る消化酵素。膵炎などで血液中に漏れ出す</v>
+        <v>甲状腺のたんぱく質（サイログロブリン）への抗体が出ていないかを見る検査</v>
       </c>
       <c r="E74" t="str">
-        <v>アミラーゼは、でんぷんを分解する消化酵素で、主に膵臓と唾液腺から作られます。膵臓に炎症が起きると血液中に漏れ出して数値が上がるため、膵炎の診断や経過観察に使われます。</v>
+        <v>この検査も、抗TPO抗体と同じく、甲状腺に対する自己免疫の有無を見るものです。あわせて調べることで橋本病などの診断の参考にします。</v>
       </c>
       <c r="F74" t="str">
-        <v>急性膵炎、慢性膵炎の急性増悪、耳下腺炎（おたふくかぜ）、腎不全</v>
+        <v>橋本病（慢性甲状腺炎）、バセドウ病などの自己免疫性甲状腺疾患</v>
       </c>
       <c r="G74" t="str">
-        <v>飲酒を控え、脂っこい食事を避けるよう伝える。強い腹痛・背部痛がある場合は急性膵炎の可能性もあるため早めの受診を勧める</v>
+        <v/>
       </c>
       <c r="H74" t="str">
-        <v>バルプロ酸、アザチオプリン、サイアザイド系・ループ利尿薬、ステロイドなど薬剤性膵炎の原因薬</v>
+        <v/>
       </c>
       <c r="I74" t="str">
-        <v>慢性膵炎の進行期（膵臓の機能低下）</v>
+        <v/>
       </c>
       <c r="J74" t="str">
         <v/>
@@ -3890,60 +3890,60 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>膵臓由来か唾液腺由来かを区別するには膵型アミラーゼ(P-AMY)を確認する。急性膵炎では強い腹痛・背部痛を伴うことが多く、飲酒歴の確認も重要</v>
+        <v>抗TPO抗体とあわせて測定されることが多い。単独の高値だけで治療方針が決まるわけではない</v>
       </c>
       <c r="M74" t="str">
-        <v/>
+        <v>甲状腺疾患</v>
       </c>
       <c r="N74" t="str">
-        <v>アミラーゼ,AMY,膵炎,急性膵炎</v>
+        <v>抗サイログロブリン抗体,TgAb,橋本病</v>
       </c>
       <c r="O74" t="str">
-        <v/>
+        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>間接ビリルビン</v>
+        <v>血中薬物濃度（TDM）</v>
       </c>
       <c r="B75" t="str">
-        <v>I-Bil</v>
+        <v>TDM</v>
       </c>
       <c r="C75" t="str">
-        <v>0.2〜0.8 mg/dL程度（施設差あり）</v>
+        <v>薬剤ごとに有効域が異なる（例：カルバマゼピン 4〜12 μg/mL、バルプロ酸 40〜100 μg/mL、フェニトイン 10〜20 μg/mL）</v>
       </c>
       <c r="D75" t="str">
-        <v>赤血球が壊れてできるビリルビンのうち、肝臓で処理される前の形</v>
+        <v>治療域が狭い薬剤で、血液中の薬の濃度が効果域・中毒域のどちらにあるかを確認する検査</v>
       </c>
       <c r="E75" t="str">
-        <v>間接ビリルビンは、赤血球が壊れてできたビリルビンが、まだ肝臓で処理される前の状態です。この値が高い場合、赤血球が通常より多く壊れている(溶血)か、肝臓での処理能力に生まれつきの体質差(体質性黄疸)がある可能性が考えられます。</v>
+        <v>この薬は効く量と副作用が出る量が近いため、血液中の薬の濃度を定期的に測って、ちょうどよい範囲に入っているかを確認します。数値が低いと効果が不十分になり、高いと副作用が出やすくなります。</v>
       </c>
       <c r="F75" t="str">
-        <v>溶血性疾患（自己免疫性溶血性貧血、血液型不適合輸血など）、体質性黄疸（ジルベール症候群）、新生児黄疸</v>
+        <v>過量投与、代謝を妨げる薬剤との併用、肝機能低下による代謝低下</v>
       </c>
       <c r="G75" t="str">
-        <v>皮膚や白目の黄染、尿の色の変化がないか確認する</v>
+        <v>ふらつき、眠気、めまい、物が二重に見えるなどの中毒症状がないか確認する</v>
       </c>
       <c r="H75" t="str">
         <v/>
       </c>
       <c r="I75" t="str">
-        <v/>
+        <v>飲み忘れ、自己判断による減量、代謝を促進する薬剤との併用（相互作用）</v>
       </c>
       <c r="J75" t="str">
-        <v/>
+        <v>発作やてんかん症状の再発がないか確認し、飲み忘れがないか一緒に確認する</v>
       </c>
       <c r="K75" t="str">
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>直接ビリルビンとの比率で原因を推測する（間接優位は溶血・体質性、直接優位は胆道系）。総ビリルビン・AST/ALTと合わせて評価する</v>
+        <v>採血のタイミング（トラフ値かどうか）で数値の解釈が変わるため採血時点を確認する。カルバマゼピンは自己誘導により長期使用で濃度が下がることがある点にも注意</v>
       </c>
       <c r="M75" t="str">
-        <v>肝機能</v>
+        <v>てんかん</v>
       </c>
       <c r="N75" t="str">
-        <v>間接ビリルビン,I-Bil,溶血</v>
+        <v>TDM,血中薬物濃度,治療域,中毒域,カルバマゼピン,フェニトイン,バルプロ酸,抗てんかん薬</v>
       </c>
       <c r="O75" t="str">
         <v/>
@@ -3951,31 +3951,31 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>直接ビリルビン</v>
+        <v>アミラーゼ（AMY）</v>
       </c>
       <c r="B76" t="str">
-        <v>D-Bil</v>
+        <v>AMY</v>
       </c>
       <c r="C76" t="str">
-        <v>0.0〜0.3 mg/dL程度（施設差あり）</v>
+        <v>44〜132 U/L（施設差あり）</v>
       </c>
       <c r="D76" t="str">
-        <v>肝臓で処理された後のビリルビン。胆道の詰まりで血液中に増える</v>
+        <v>膵臓や唾液腺から出る消化酵素。膵炎などで血液中に漏れ出す</v>
       </c>
       <c r="E76" t="str">
-        <v>直接ビリルビンは、肝臓で処理された後のビリルビンです。胆石や腫瘍などで胆汁の通り道（胆道）が詰まると、行き場を失って血液中に増え、皮膚や白目が黄色くなる黄疸として現れます。</v>
+        <v>アミラーゼは、でんぷんを分解する消化酵素で、主に膵臓と唾液腺から作られます。膵臓に炎症が起きると血液中に漏れ出して数値が上がるため、膵炎の診断や経過観察に使われます。</v>
       </c>
       <c r="F76" t="str">
-        <v>肝疾患、胆石など胆道の閉塞</v>
+        <v>急性膵炎、慢性膵炎の急性増悪、耳下腺炎（おたふくかぜ）、腎不全</v>
       </c>
       <c r="G76" t="str">
-        <v>皮膚や白目の黄染、白っぽい便、濃い茶色の尿がないか確認する</v>
+        <v>飲酒を控え、脂っこい食事を避けるよう伝える。強い腹痛・背部痛がある場合は急性膵炎の可能性もあるため早めの受診を勧める</v>
       </c>
       <c r="H76" t="str">
-        <v>胆汁うっ滞型の薬剤性肝障害を起こしうる抗菌薬、経口避妊薬</v>
+        <v>バルプロ酸、アザチオプリン、サイアザイド系・ループ利尿薬、ステロイドなど薬剤性膵炎の原因薬</v>
       </c>
       <c r="I76" t="str">
-        <v/>
+        <v>慢性膵炎の進行期（膵臓の機能低下）</v>
       </c>
       <c r="J76" t="str">
         <v/>
@@ -3984,13 +3984,13 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>直接優位の上昇は胆道系（胆石、腫瘍による閉塞）を、間接優位の上昇は溶血・体質性を疑う手がかりになる。γ-GTP・ALPと合わせて胆道系疾患を評価する</v>
+        <v>膵臓由来か唾液腺由来かを区別するには膵型アミラーゼ(P-AMY)を確認する。急性膵炎では強い腹痛・背部痛を伴うことが多く、飲酒歴の確認も重要</v>
       </c>
       <c r="M76" t="str">
-        <v>肝機能</v>
+        <v/>
       </c>
       <c r="N76" t="str">
-        <v>直接ビリルビン,D-Bil,胆石,胆道閉塞</v>
+        <v>アミラーゼ,AMY,膵炎,急性膵炎</v>
       </c>
       <c r="O76" t="str">
         <v/>
@@ -3998,116 +3998,116 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>亜鉛（Zn）</v>
+        <v>間接ビリルビン</v>
       </c>
       <c r="B77" t="str">
-        <v>Zn</v>
+        <v>I-Bil</v>
       </c>
       <c r="C77" t="str">
-        <v>80〜130 μg/dL程度（施設差あり）</v>
+        <v>0.2〜0.8 mg/dL程度（施設差あり）</v>
       </c>
       <c r="D77" t="str">
-        <v>味覚や皮膚、免疫に関わる微量ミネラル。高齢者や低栄養で不足しやすい</v>
+        <v>赤血球が壊れてできるビリルビンのうち、肝臓で処理される前の形</v>
       </c>
       <c r="E77" t="str">
-        <v>亜鉛は、味を感じる働きや皮膚・粘膜の健康、免疫の働きに関わる微量ミネラルです。不足すると、味がわかりにくくなったり（味覚障害）、傷が治りにくくなったりすることがあります。</v>
+        <v>間接ビリルビンは、赤血球が壊れてできたビリルビンが、まだ肝臓で処理される前の状態です。この値が高い場合、赤血球が通常より多く壊れている(溶血)か、肝臓での処理能力に生まれつきの体質差(体質性黄疸)がある可能性が考えられます。</v>
       </c>
       <c r="F77" t="str">
-        <v/>
+        <v>溶血性疾患（自己免疫性溶血性貧血、血液型不適合輸血など）、体質性黄疸（ジルベール症候群）、新生児黄疸</v>
       </c>
       <c r="G77" t="str">
-        <v/>
+        <v>皮膚や白目の黄染、尿の色の変化がないか確認する</v>
       </c>
       <c r="H77" t="str">
         <v/>
       </c>
       <c r="I77" t="str">
-        <v>低栄養、高齢による摂取不足、消化器手術後、亜鉛の吸収を妨げる薬剤（PPI、キレート形成する薬剤など）との併用</v>
+        <v/>
       </c>
       <c r="J77" t="str">
-        <v>味覚の変化（味を感じにくい、金属味がするなど）がないか確認する。牡蠣、赤身肉、レバーなど亜鉛を多く含む食品を意識するとよいことを伝える</v>
+        <v/>
       </c>
       <c r="K77" t="str">
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>薬剤性の亜鉛欠乏（PPI長期使用、D-ペニシラミン、一部の降圧薬など）に注意。亜鉛欠乏による味覚障害は原因薬剤の中止・亜鉛補充で改善することがある</v>
+        <v>直接ビリルビンとの比率で原因を推測する（間接優位は溶血・体質性、直接優位は胆道系）。総ビリルビン・AST/ALTと合わせて評価する</v>
       </c>
       <c r="M77" t="str">
-        <v/>
+        <v>肝機能</v>
       </c>
       <c r="N77" t="str">
-        <v>亜鉛,Zn,味覚障害,亜鉛欠乏</v>
+        <v>間接ビリルビン,I-Bil,溶血</v>
       </c>
       <c r="O77" t="str">
-        <v>食事と栄養 p.78（亜鉛）</v>
+        <v/>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>マグネシウム（Mg）</v>
+        <v>直接ビリルビン</v>
       </c>
       <c r="B78" t="str">
-        <v>Mg</v>
+        <v>D-Bil</v>
       </c>
       <c r="C78" t="str">
-        <v>1.8〜2.6 mg/dL程度（施設差あり）</v>
+        <v>0.0〜0.3 mg/dL程度（施設差あり）</v>
       </c>
       <c r="D78" t="str">
-        <v>骨や筋肉、神経の働きに関わるミネラル。低栄養や利尿薬で不足しやすい</v>
+        <v>肝臓で処理された後のビリルビン。胆道の詰まりで血液中に増える</v>
       </c>
       <c r="E78" t="str">
-        <v>マグネシウムは、骨や筋肉、神経の働きを支えるミネラルです。不足すると、こむら返りや不整脈、だるさなどの症状が出ることがあります。</v>
+        <v>直接ビリルビンは、肝臓で処理された後のビリルビンです。胆石や腫瘍などで胆汁の通り道（胆道）が詰まると、行き場を失って血液中に増え、皮膚や白目が黄色くなる黄疸として現れます。</v>
       </c>
       <c r="F78" t="str">
-        <v>腎不全、マグネシウム製剤（酸化マグネシウムなど）の過量投与</v>
+        <v>肝疾患、胆石など胆道の閉塞</v>
       </c>
       <c r="G78" t="str">
-        <v>腎機能低下がある患者で酸化マグネシウムなどの緩下剤を使用中は、傾眠・血圧低下などの高マグネシウム血症の症状がないか確認する</v>
+        <v>皮膚や白目の黄染、白っぽい便、濃い茶色の尿がないか確認する</v>
       </c>
       <c r="H78" t="str">
-        <v>マグネシウム含有制酸薬・下剤の過量(特に腎機能低下患者)</v>
+        <v>胆汁うっ滞型の薬剤性肝障害を起こしうる抗菌薬、経口避妊薬</v>
       </c>
       <c r="I78" t="str">
-        <v>低栄養、利尿薬の使用、慢性的な下痢、アルコール多飲、PPI長期使用</v>
+        <v/>
       </c>
       <c r="J78" t="str">
-        <v>こむら返りや動悸などの症状がないか確認する</v>
+        <v/>
       </c>
       <c r="K78" t="str">
-        <v>プロトンポンプ阻害薬(PPI)の長期使用、ループ利尿薬、サイアザイド系利尿薬、シスプラチン、アミノグリコシド系</v>
+        <v/>
       </c>
       <c r="L78" t="str">
-        <v>腎機能低下患者への酸化マグネシウム投与は高マグネシウム血症のリスクがあるため定期的なモニタリングが必要。PPI長期使用も低マグネシウム血症のリスク因子として知られる</v>
+        <v>直接優位の上昇は胆道系（胆石、腫瘍による閉塞）を、間接優位の上昇は溶血・体質性を疑う手がかりになる。γ-GTP・ALPと合わせて胆道系疾患を評価する</v>
       </c>
       <c r="M78" t="str">
-        <v>腎機能</v>
+        <v>肝機能</v>
       </c>
       <c r="N78" t="str">
-        <v>マグネシウム,Mg,酸化マグネシウム,こむら返り</v>
+        <v>直接ビリルビン,D-Bil,胆石,胆道閉塞</v>
       </c>
       <c r="O78" t="str">
-        <v>食事と栄養 p.84（マグネシウム）</v>
+        <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>C－ペプチド（血中）</v>
+        <v>亜鉛（Zn）</v>
       </c>
       <c r="B79" t="str">
-        <v>CPR</v>
+        <v>Zn</v>
       </c>
       <c r="C79" t="str">
-        <v>空腹時 0.6〜3.0 ng/mL（施設差あり）</v>
+        <v>80〜130 μg/dL程度（施設差あり）</v>
       </c>
       <c r="D79" t="str">
-        <v>自分の膵臓がどれくらいインスリンを作れているかを表す指標</v>
+        <v>味覚や皮膚、免疫に関わる微量ミネラル。高齢者や低栄養で不足しやすい</v>
       </c>
       <c r="E79" t="str">
-        <v>この検査は、ご自身の膵臓がどれくらいインスリンを作る力を持っているかを見るものです。数値が低いほど、体の中で作れるインスリンが少ないことを示します。</v>
+        <v>亜鉛は、味を感じる働きや皮膚・粘膜の健康、免疫の働きに関わる微量ミネラルです。不足すると、味がわかりにくくなったり（味覚障害）、傷が治りにくくなったりすることがあります。</v>
       </c>
       <c r="F79" t="str">
-        <v>インスリン抵抗性が強い状態（初期の2型糖尿病など）</v>
+        <v/>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -4116,72 +4116,72 @@
         <v/>
       </c>
       <c r="I79" t="str">
-        <v>膵臓のインスリン分泌能低下（1型糖尿病、糖尿病の進行）</v>
+        <v>低栄養、高齢による摂取不足、消化器手術後、亜鉛の吸収を妨げる薬剤（PPI、キレート形成する薬剤など）との併用</v>
       </c>
       <c r="J79" t="str">
-        <v/>
+        <v>味覚の変化（味を感じにくい、金属味がするなど）がないか確認する。牡蠣、赤身肉、レバーなど亜鉛を多く含む食品を意識するとよいことを伝える</v>
       </c>
       <c r="K79" t="str">
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>インスリン分泌能の評価に使われる。数値が低いほどインスリン治療の必要性が高いと判断される目安になる</v>
+        <v>薬剤性の亜鉛欠乏（PPI長期使用、D-ペニシラミン、一部の降圧薬など）に注意。亜鉛欠乏による味覚障害は原因薬剤の中止・亜鉛補充で改善することがある</v>
       </c>
       <c r="M79" t="str">
-        <v>糖尿病</v>
+        <v/>
       </c>
       <c r="N79" t="str">
-        <v>C-ペプチド,Cペプチド,CPR,C-peptide,血中CPR,インスリン分泌</v>
+        <v>亜鉛,Zn,味覚障害,亜鉛欠乏</v>
       </c>
       <c r="O79" t="str">
-        <v/>
+        <v>食事と栄養 p.78（亜鉛）</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>C－ペプチドインデックス</v>
+        <v>マグネシウム（Mg）</v>
       </c>
       <c r="B80" t="str">
-        <v>CPI</v>
+        <v>Mg</v>
       </c>
       <c r="C80" t="str">
-        <v>1.2以上が目安(施設・測定条件により異なる)</v>
+        <v>1.8〜2.6 mg/dL程度（施設差あり）</v>
       </c>
       <c r="D80" t="str">
-        <v>血糖値に対してどれくらいインスリンを分泌できているかを表す指標。低いほどインスリン治療の必要性が高い</v>
+        <v>骨や筋肉、神経の働きに関わるミネラル。低栄養や利尿薬で不足しやすい</v>
       </c>
       <c r="E80" t="str">
-        <v>これは、血糖値の高さに対して、体がどれくらいインスリンを作れているかを見る指標です。数値が低いほど、自分の膵臓だけでは血糖値に見合うインスリンを十分に作れていない可能性が高く、インスリン治療が必要かどうかの判断材料になります。</v>
+        <v>マグネシウムは、骨や筋肉、神経の働きを支えるミネラルです。不足すると、こむら返りや不整脈、だるさなどの症状が出ることがあります。</v>
       </c>
       <c r="F80" t="str">
-        <v>通常、臨床的意義は乏しい</v>
+        <v>腎不全、マグネシウム製剤（酸化マグネシウムなど）の過量投与</v>
       </c>
       <c r="G80" t="str">
-        <v/>
+        <v>腎機能低下がある患者で酸化マグネシウムなどの緩下剤を使用中は、傾眠・血圧低下などの高マグネシウム血症の症状がないか確認する</v>
       </c>
       <c r="H80" t="str">
-        <v/>
+        <v>マグネシウム含有制酸薬・下剤の過量(特に腎機能低下患者)</v>
       </c>
       <c r="I80" t="str">
-        <v>内因性インスリン分泌能の低下(1.2未満でインスリン治療の適応を検討する目安、0.8未満はインスリン療法が強く推奨される目安)</v>
+        <v>低栄養、利尿薬の使用、慢性的な下痢、アルコール多飲、PPI長期使用</v>
       </c>
       <c r="J80" t="str">
-        <v>インスリン治療の必要性について医師からどのように説明を受けているか確認する</v>
+        <v>こむら返りや動悸などの症状がないか確認する</v>
       </c>
       <c r="K80" t="str">
-        <v/>
+        <v>プロトンポンプ阻害薬(PPI)の長期使用、ループ利尿薬、サイアザイド系利尿薬、シスプラチン、アミノグリコシド系</v>
       </c>
       <c r="L80" t="str">
-        <v>CPI＝血中Cペプチド(ng/mL)÷血糖値(mg/dL)×100 で算出する。空腹時に測定するのが基本で、境界値付近では食事負荷の影響を受けるため、複数回の評価や随時尿中CPRとあわせて判断することもある</v>
+        <v>腎機能低下患者への酸化マグネシウム投与は高マグネシウム血症のリスクがあるため定期的なモニタリングが必要。PPI長期使用も低マグネシウム血症のリスク因子として知られる</v>
       </c>
       <c r="M80" t="str">
-        <v>糖尿病</v>
+        <v>腎機能</v>
       </c>
       <c r="N80" t="str">
-        <v>CPI,Cペプチドインデックス,C-ペプチドインデックス,インスリン分泌能,インスリン治療</v>
+        <v>マグネシウム,Mg,酸化マグネシウム,こむら返り</v>
       </c>
       <c r="O80" t="str">
-        <v/>
+        <v>食事と栄養 p.84（マグネシウム）</v>
       </c>
     </row>
     <row r="81">

--- a/検査値リファレンス初期データ.xlsx
+++ b/検査値リファレンス初期データ.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O102"/>
+  <dimension ref="A1:O106"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -464,711 +464,711 @@
         <v>参考ページ</v>
       </c>
     </row>
-    <row r="2" xml:space="preserve">
+    <row r="2">
       <c r="A2" t="str">
+        <v>収縮期血圧</v>
+      </c>
+      <c r="B2" t="str">
+        <v>SBP,収縮期血圧</v>
+      </c>
+      <c r="C2" t="str">
+        <v>診察室血圧 120mmHg未満が正常域、140mmHg以上で高血圧(家庭血圧はそれぞれ5mmHg低い値が基準)</v>
+      </c>
+      <c r="D2" t="str">
+        <v>心臓が収縮して血液を送り出すときの血圧の最高値、いわゆる「上の血圧」</v>
+      </c>
+      <c r="E2" t="str">
+        <v>収縮期血圧は、心臓がギュッと縮んで血液を送り出す瞬間の血圧で、いわゆる「上の血圧」です。血管にかかる圧力の中で最も高い値になります。</v>
+      </c>
+      <c r="F2" t="str">
+        <v>本態性高血圧、二次性高血圧(腎性・内分泌性など)、動脈硬化(高齢者で収縮期のみ上昇しやすい)、白衣高血圧、痛みやストレスによる一時的な上昇</v>
+      </c>
+      <c r="G2" t="str">
+        <v>減塩(1日6g未満が目安)を心がけ、野菜・果物を積極的に摂るよう伝える。適度な運動・禁煙・節酒も血圧改善に役立つことを伝え、家庭血圧の記録習慣も勧める</v>
+      </c>
+      <c r="H2" t="str">
+        <v>NSAIDs、ステロイド、経口避妊薬、甘草含有製剤(グリチルリチン)、一部の抗うつ薬・血管新生阻害薬は血圧を上げうる</v>
+      </c>
+      <c r="I2" t="str">
+        <v>起立性低血圧、脱水、降圧薬の効きすぎ、心不全の増悪、出血・ショック</v>
+      </c>
+      <c r="J2" t="str">
+        <v>めまい・立ちくらみの有無を確認する。急に立ち上がらずゆっくり動作するよう伝え、脱水が疑われる場合はこまめな水分摂取を勧める</v>
+      </c>
+      <c r="K2" t="str">
+        <v>降圧薬(特に利尿薬・α遮断薬)の効きすぎ、抗うつ薬・抗パーキンソン病薬などによる起立性低血圧</v>
+      </c>
+      <c r="L2" t="str">
+        <v>診察室血圧と家庭血圧で基準値が異なる(家庭血圧のほうが5mmHg低い基準)。高齢者では収縮期血圧のみが高くなる収縮期高血圧が多く、動脈硬化を反映する。降圧薬開始・増量後はふらつき・立ちくらみの有無を確認する</v>
+      </c>
+      <c r="M2" t="str">
+        <v>心不全</v>
+      </c>
+      <c r="N2" t="str">
+        <v>血圧,収縮期血圧,SBP,上の血圧,高血圧</v>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>拡張期血圧</v>
+      </c>
+      <c r="B3" t="str">
+        <v>DBP,拡張期血圧</v>
+      </c>
+      <c r="C3" t="str">
+        <v>診察室血圧 80mmHg未満が正常域、90mmHg以上で高血圧(家庭血圧はそれぞれ5mmHg低い値が基準)</v>
+      </c>
+      <c r="D3" t="str">
+        <v>心臓が拡張して血液をため込むときの血圧の最低値、いわゆる「下の血圧」</v>
+      </c>
+      <c r="E3" t="str">
+        <v>拡張期血圧は、心臓が広がって次の収縮に備えて血液をためている瞬間の血圧で、いわゆる「下の血圧」です。</v>
+      </c>
+      <c r="F3" t="str">
+        <v>本態性高血圧、二次性高血圧、若年〜中年での血管抵抗上昇が主体の高血圧</v>
+      </c>
+      <c r="G3" t="str">
+        <v>収縮期血圧と同様、減塩・適度な運動・禁煙・節酒を心がけるよう伝える</v>
+      </c>
+      <c r="H3" t="str">
+        <v>NSAIDs、ステロイド、経口避妊薬、甘草含有製剤(グリチルリチン)</v>
+      </c>
+      <c r="I3" t="str">
+        <v>大動脈弁閉鎖不全症、甲状腺機能亢進症、動脈硬化の進行(脈圧が開大)</v>
+      </c>
+      <c r="J3" t="str">
+        <v>めまいなどの症状がないか確認する</v>
+      </c>
+      <c r="K3" t="str">
+        <v>降圧薬(特に血管拡張作用の強いCa拮抗薬)の効きすぎ</v>
+      </c>
+      <c r="L3" t="str">
+        <v>加齢とともに動脈硬化が進むと拡張期血圧は低下し、収縮期血圧との差(脈圧)が開大する。脈圧の開大は動脈硬化の進行を示唆する所見として重視される</v>
+      </c>
+      <c r="M3" t="str">
+        <v>心不全</v>
+      </c>
+      <c r="N3" t="str">
+        <v>血圧,拡張期血圧,DBP,下の血圧,高血圧,脈圧</v>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>脈拍</v>
+      </c>
+      <c r="B4" t="str">
+        <v>HR,脈拍</v>
+      </c>
+      <c r="C4" t="str">
+        <v>60〜100回/分</v>
+      </c>
+      <c r="D4" t="str">
+        <v>心臓が1分間に拍動する回数。心臓のリズムや働き具合の目安になる</v>
+      </c>
+      <c r="E4" t="str">
+        <v>脈拍は心臓が1分間に何回打っているかを表す数値です。運動や緊張で一時的に増えたり、リラックスしていると減ったりします。極端に速い・遅い状態が続く場合は、心臓の病気やお薬の影響が考えられます。</v>
+      </c>
+      <c r="F4" t="str">
+        <v>頻脈性不整脈(心房細動等)、発熱、脱水、甲状腺機能亢進症、貧血、痛み・不安・カフェイン摂取、薬剤性(β刺激薬など)</v>
+      </c>
+      <c r="G4" t="str">
+        <v>動悸・息切れなどの症状がないか確認する。カフェインの摂りすぎがないかもあわせて確認する</v>
+      </c>
+      <c r="H4" t="str">
+        <v>β刺激薬(気管支拡張薬)、甲状腺ホルモン薬の過量、一部の抗コリン薬</v>
+      </c>
+      <c r="I4" t="str">
+        <v>徐脈性不整脈(洞不全症候群、房室ブロック等)、甲状腺機能低下症、薬剤性(β遮断薬・ジゴキシン等)、アスリート心</v>
+      </c>
+      <c r="J4" t="str">
+        <v>めまい・失神・強い倦怠感がないか確認する。特にβ遮断薬服用中は自己判断で中断せず、症状があれば医師に相談するよう伝える</v>
+      </c>
+      <c r="K4" t="str">
+        <v>β遮断薬、非ジヒドロピリジン系Ca拮抗薬(ベラパミル・ジルチアゼム)、ジゴキシン、一部の抗不整脈薬</v>
+      </c>
+      <c r="L4" t="str">
+        <v>β遮断薬・ジゴキシン服用中は徐脈の指標として重要。心房細動患者では脈拍数と実際の心拍数(心電図)にずれ(脈拍欠損)が生じることがある点にも留意する</v>
+      </c>
+      <c r="M4" t="str">
+        <v>抗凝固療法（心房細動・血栓症）,心不全</v>
+      </c>
+      <c r="N4" t="str">
+        <v>脈拍,心拍数,HR,頻脈,徐脈,不整脈</v>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>眼圧</v>
+      </c>
+      <c r="B5" t="str">
+        <v>IOP,眼圧</v>
+      </c>
+      <c r="C5" t="str">
+        <v>10〜21 mmHg</v>
+      </c>
+      <c r="D5" t="str">
+        <v>眼球内の圧力。高い状態が続くと視神経が障害され緑内障の原因になる</v>
+      </c>
+      <c r="E5" t="str">
+        <v>眼圧は、目の中を満たしている水(房水)の圧力です。この圧力が高い状態が続くと、視神経が徐々に傷んで視野が欠けていく緑内障の原因になることがあります。</v>
+      </c>
+      <c r="F5" t="str">
+        <v>緑内障(開放隅角緑内障・閉塞隅角緑内障)、ステロイド点眼・全身投与による眼圧上昇(ステロイド緑内障)、ぶどう膜炎</v>
+      </c>
+      <c r="G5" t="str">
+        <v>目のかすみ、頭痛、吐き気、視野が欠ける感じがないか確認する。ステロイド点眼を使用中の場合は自己判断で中止せず定期受診を続けるよう伝える</v>
+      </c>
+      <c r="H5" t="str">
+        <v>ステロイド(点眼・内服・吸入)、抗コリン薬(閉塞隅角緑内障がある場合は禁忌〜慎重投与)、一部の抗うつ薬・抗ヒスタミン薬(抗コリン作用)</v>
+      </c>
+      <c r="I5" t="str">
+        <v>低眼圧症(眼科手術後、外傷、ぶどう膜炎による房水産生低下など)</v>
+      </c>
+      <c r="J5" t="str">
+        <v>眼科手術後などで急激な視力低下がある場合は早めの受診を勧める</v>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>緑内障治療薬(点眼)は種類が多く複数併用することが多いため、点眼順序(5分以上あける)や防腐剤による角膜障害にも注意する。閉塞隅角緑内障の患者には抗コリン作用のある薬剤(一部の感冒薬・抗うつ薬・過活動膀胱治療薬等)が禁忌〜慎重投与となる場合がある</v>
+      </c>
+      <c r="M5" t="str">
+        <v/>
+      </c>
+      <c r="N5" t="str">
+        <v>眼圧,IOP,緑内障,ステロイド緑内障</v>
+      </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6" xml:space="preserve">
+      <c r="A6" t="str">
         <v>血糖（空腹時・随時）</v>
       </c>
-      <c r="B2" t="str">
+      <c r="B6" t="str">
         <v>BS,Glu</v>
       </c>
-      <c r="C2" t="str" xml:space="preserve">
+      <c r="C6" t="str" xml:space="preserve">
         <v xml:space="preserve">空腹時 70〜109 mg/dL
 （随時血糖は食後に上がるため単独では判断しにくい）</v>
       </c>
-      <c r="D2" t="str">
+      <c r="D6" t="str">
         <v>採血したその瞬間の血液中のブドウ糖の濃度</v>
       </c>
-      <c r="E2" t="str">
+      <c r="E6" t="str">
         <v>この数値は採血したその瞬間の血糖値です。食事の前後で大きく変わるので、いつ測ったかによって見方が変わります。空腹時に高い場合や、食後を含めた随時血糖で200を超える場合は、糖尿病を疑う目安になります。</v>
       </c>
-      <c r="F2" t="str">
+      <c r="F6" t="str">
         <v>糖尿病、食後高血糖、ステロイドなど薬剤性高血糖、感染・ストレスによる一時的な上昇</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G6" t="str">
         <v>食後の血糖上昇を抑えるため、早食い・まとめ食いを避け、野菜→汁物→主菜→主食の順に食べるとよいことを伝える。間食は甘い菓子より小魚やナッツなど血糖が上がりにくいものに置き換え、食後30分以内の軽い散歩も上昇抑制に役立つ</v>
       </c>
-      <c r="H2" t="str">
+      <c r="H6" t="str">
         <v>ステロイド、サイアザイド系利尿薬、非定型抗精神病薬(オランザピン・クエチアピン)、タクロリムス・シクロスポリン、β遮断薬、高カロリー輸液</v>
       </c>
-      <c r="I2" t="str">
+      <c r="I6" t="str">
         <v>低血糖（薬剤性、食事摂取不足、シックデイ時の過量投与など）</v>
       </c>
-      <c r="J2" t="str">
+      <c r="J6" t="str">
         <v>空腹時間が長くならないよう食事を規則正しくとる。外出時はブドウ糖やアメを携帯し、冷や汗・動悸・強い空腹感が出たらすぐ糖分を摂るよう伝える。運動量が多い日は補食を追加するなど活動量に応じた調整も説明する</v>
       </c>
-      <c r="K2" t="str">
+      <c r="K6" t="str">
         <v>インスリン、SU薬(グリメピリド等)、速効型インスリン分泌促進薬(グリニド系)。β遮断薬は低血糖症状をマスクすることがあるため注意</v>
       </c>
-      <c r="L2" t="str">
+      <c r="L6" t="str">
         <v>採血のタイミング（空腹時か食後か）を必ず確認する。SU薬・インスリン使用者では低血糖症状の有無も併せて聞く</v>
       </c>
-      <c r="M2" t="str">
+      <c r="M6" t="str">
         <v>糖尿病,精神疾患（非定型抗精神病薬）</v>
       </c>
-      <c r="N2" t="str">
+      <c r="N6" t="str">
         <v>血糖値,血糖,BS,Glu,グルコース,空腹時血糖,随時血糖,食後血糖</v>
       </c>
-      <c r="O2" t="str">
+      <c r="O6" t="str">
         <v>食事と栄養 p.18（炭水化物）／p.106-131（第2部 糖尿病）</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
+    <row r="7">
+      <c r="A7" t="str">
         <v>HbA1c</v>
       </c>
-      <c r="B3" t="str">
+      <c r="B7" t="str">
         <v>HbA1c</v>
       </c>
-      <c r="C3" t="str">
+      <c r="C7" t="str">
         <v>6.5%未満（NGSP値）</v>
       </c>
-      <c r="D3" t="str">
+      <c r="D7" t="str">
         <v>過去1〜2か月の平均的な血糖の高さを表す数値</v>
       </c>
-      <c r="E3" t="str">
+      <c r="E7" t="str">
         <v>HbA1cは、この1〜2か月の血糖値の平均を表す数値です。その日の食事や体調に左右されにくいので、普段の血糖コントロールがどれくらいできているかを見るのに使います。数値が高いほど、平均して血糖値が高めだったことを示します。</v>
       </c>
-      <c r="F3" t="str">
+      <c r="F7" t="str">
         <v>糖尿病、血糖コントロール不良</v>
       </c>
-      <c r="G3" t="str">
+      <c r="G7" t="str">
         <v>主食の量や間食の頻度を見直し、通勤の一駅歩きなど日常に取り入れやすい運動を増やすよう提案する。飲み忘れがあればお薬カレンダーやアラームの活用も一緒に検討する</v>
       </c>
-      <c r="H3" t="str">
+      <c r="H7" t="str">
         <v>血糖と同様(ステロイド、非定型抗精神病薬、サイアザイド系利尿薬など)。SU薬・インスリンを使用中なら低血糖の有無も確認</v>
       </c>
-      <c r="I3" t="str">
+      <c r="I7" t="str">
         <v>低血糖を繰り返している状態</v>
       </c>
-      <c r="J3" t="str">
+      <c r="J7" t="str">
         <v>低血糖を防ぐため、食事の間隔をあけすぎないようにする。ブドウ糖など対処品の携帯を勧め、運転前や普段と違う強度の運動をする前は血糖自己測定で確認する習慣を提案する</v>
       </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
         <v>貧血・鉄剤補充・妊娠・腎不全などがあると、実際の血糖値とズレて出ることがある。直近の血糖自己測定値と合わせて確認する</v>
       </c>
-      <c r="M3" t="str">
+      <c r="M7" t="str">
         <v>糖尿病,精神疾患（非定型抗精神病薬）</v>
       </c>
-      <c r="N3" t="str">
+      <c r="N7" t="str">
         <v>HbA1c,ヘモグロビンエーワンシー,グリコヘモグロビン,血糖コントロール,NGSP</v>
       </c>
-      <c r="O3" t="str">
+      <c r="O7" t="str">
         <v>食事と栄養 p.18（炭水化物）／p.106-131（第2部 糖尿病）</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="str">
+    <row r="8">
+      <c r="A8" t="str">
         <v>尿素窒素（BUN）</v>
       </c>
-      <c r="B4" t="str">
+      <c r="B8" t="str">
         <v>BUN,UN</v>
       </c>
-      <c r="C4" t="str">
+      <c r="C8" t="str">
         <v>8〜20 mg/dL</v>
       </c>
-      <c r="D4" t="str">
+      <c r="D8" t="str">
         <v>たんぱく質が分解されてできる老廃物で、腎機能や体の状態を反映する</v>
       </c>
-      <c r="E4" t="str">
+      <c r="E8" t="str">
         <v>BUNはたんぱく質が体の中で使われたあとにできる老廃物のひとつです。腎臓の働きが落ちると排泄されにくくなって数値が上がりますが、脱水や消化管出血、たんぱく質の摂りすぎでも上がることがあります。</v>
       </c>
-      <c r="F4" t="str">
+      <c r="F8" t="str">
         <v>腎機能低下・腎不全、脱水、消化管出血、高たんぱく食、ステロイド使用</v>
       </c>
-      <c r="G4" t="str">
+      <c r="G8" t="str">
         <v>脱水を避けてこまめに水分を摂る(心不全等で水分制限がある場合を除く)。極端な高たんぱく食が続いていないか確認し、黒い便など消化管出血のサインにも注意する</v>
       </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
         <v>低たんぱく食、肝不全によるたんぱく合成低下、妊娠</v>
       </c>
-      <c r="J4" t="str">
+      <c r="J8" t="str">
         <v>食事量、特にたんぱく質(肉・魚・卵・大豆製品)の摂取量を確認する。食欲低下や極端な菜食が続いていないか、栄養状態全体もあわせて確認する</v>
       </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
         <v>クレアチニンと同時に見る。BUN/Cr比が高ければ脱水や消化管出血を、比が正常で両方高ければ腎性を疑う目安になる</v>
       </c>
-      <c r="M4" t="str">
+      <c r="M8" t="str">
         <v>腎機能,糖尿病,骨粗鬆症,抗凝固療法（心房細動・血栓症）</v>
       </c>
-      <c r="N4" t="str">
+      <c r="N8" t="str">
         <v>BUN,尿素窒素,UN,腎機能</v>
       </c>
-      <c r="O4" t="str">
+      <c r="O8" t="str">
         <v>食事と栄養 p.199-215（第2部 腎機能低下）</v>
       </c>
     </row>
-    <row r="5" xml:space="preserve">
-      <c r="A5" t="str">
+    <row r="9" xml:space="preserve">
+      <c r="A9" t="str">
         <v>クレアチニン・eGFR</v>
       </c>
-      <c r="B5" t="str">
+      <c r="B9" t="str">
         <v>Cr,eGFR</v>
       </c>
-      <c r="C5" t="str" xml:space="preserve">
+      <c r="C9" t="str" xml:space="preserve">
         <v xml:space="preserve">クレアチニン 男性0.6〜1.1 mg/dL、女性0.4〜0.8 mg/dL
 eGFR 60 mL/分/1.73㎡以上</v>
       </c>
-      <c r="D5" t="str">
+      <c r="D9" t="str">
         <v>腎臓がどれくらい老廃物をろ過できているかを表す指標</v>
       </c>
-      <c r="E5" t="str">
+      <c r="E9" t="str">
         <v>クレアチニンは筋肉から出る老廃物で、腎臓のろ過機能が落ちると血液の中に増えていきます。eGFRはそのクレアチニンの値や年齢から計算した「腎臓の働きの点数」のようなもので、100に近いほど良く、数字が下がるほど腎臓の働きが落ちていることを表します。</v>
       </c>
-      <c r="F5" t="str">
+      <c r="F9" t="str">
         <v>クレアチニン上昇（＝eGFR低下）で考える：腎機能低下、脱水、腎不全、腎毒性のある薬剤の影響</v>
       </c>
-      <c r="G5" t="str">
+      <c r="G9" t="str">
         <v>脱水を避けてこまめに水分を摂る(心不全等で水分制限がある場合を除く)。塩分の摂りすぎに注意し、市販の鎮痛薬(NSAIDs)を自己判断で連用していないかも確認する</v>
       </c>
-      <c r="H5" t="str">
+      <c r="H9" t="str">
         <v>腎排泄型薬剤の減量要否を確認(ジゴキシン、NOAC、メトホルミン、アミノグリコシド系、バンコマイシン等)。悪化させうる代表薬はNSAIDs・ARB/ACE阻害薬・利尿薬・造影剤・アミノグリコシド系</v>
       </c>
-      <c r="I5" t="str">
+      <c r="I9" t="str">
         <v>クレアチニンが低い場合：筋肉量の低下、高齢・るいそうで見かけ上低く出ることがある</v>
       </c>
-      <c r="J5" t="str">
+      <c r="J9" t="str">
         <v>高齢・るいそうでは筋肉量低下により見かけ上低く出て腎機能を過大評価しやすいため注意する。筋力低下がある場合は無理のない範囲での運動やたんぱく質摂取を勧める</v>
       </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str" xml:space="preserve">
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str" xml:space="preserve">
         <v xml:space="preserve">筋肉量に影響されるため、るいそうの強い高齢者では腎機能を過大評価しやすい。eGFR低下時は腎排泄型薬剤の用量調整を確認する。
 CKD重症度分類（GFR区分）の目安：G1 正常または高値(90以上)／G2 正常または軽度低下(60〜89)／G3a 軽度〜中等度低下(45〜59)／G3b 中等度〜高度低下(30〜44)／G4 高度低下(15〜29)／G5 末期腎不全(15未満)。
 eGFRには体表面積1.73㎡に標準化した「標準化eGFR」（CKD病期の判定などに使用）と、実際の体表面積で補正した「個別化eGFR」（標準化eGFR×体表面積÷1.73、薬剤投与量の決定に使用）があり、体格が標準から大きく外れる患者では両者がずれるため、用量調整の場面では個別化eGFRやCCrを優先する</v>
       </c>
-      <c r="M5" t="str">
+      <c r="M9" t="str">
         <v>腎機能,糖尿病,骨粗鬆症,抗凝固療法（心房細動・血栓症）</v>
       </c>
-      <c r="N5" t="str">
+      <c r="N9" t="str">
         <v>クレアチニン,Cr,SCr,血清クレアチニン,eGFR,腎機能,GFR,推算糸球体濾過量,CKD重症度分類</v>
       </c>
-      <c r="O5" t="str">
+      <c r="O9" t="str">
         <v>食事と栄養 p.199-215（第2部 腎機能低下）／p.243（フレイルQ111 クレアチニン値が低い場合）</v>
       </c>
     </row>
-    <row r="6" xml:space="preserve">
-      <c r="A6" t="str">
+    <row r="10" xml:space="preserve">
+      <c r="A10" t="str">
         <v>CCr（クレアチニンクリアランス）</v>
       </c>
-      <c r="B6" t="str">
+      <c r="B10" t="str">
         <v>CCr</v>
       </c>
-      <c r="C6" t="str">
+      <c r="C10" t="str">
         <v>目安 91〜130 mL/分（Cockcroft-Gault式で算出。年齢・体重・性別で変動）</v>
       </c>
-      <c r="D6" t="str">
+      <c r="D10" t="str">
         <v>腎臓が実際にどれくらい血液をろ過・排泄できているかを、より直接的に表す指標</v>
       </c>
-      <c r="E6" t="str">
+      <c r="E10" t="str">
         <v>CCrは、腎臓が1分間にどれくらいの血液をきれいにできているかを表す数値です。クレアチニンという体の老廃物が尿にどれくらい出ているかをもとに計算します。お薬の量を腎臓の働きに合わせて調整するときによく使われる指標です。</v>
       </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
         <v>添付文書のCCr基準で減量が必要な薬剤(NOAC、ST合剤、アシクロビル等)の用量を確認</v>
       </c>
-      <c r="I6" t="str">
+      <c r="I10" t="str">
         <v>腎機能の低下（数値が低いほどろ過機能の低下を示す）、脱水、加齢に伴う腎機能低下、糖尿病性腎症など</v>
       </c>
-      <c r="J6" t="str">
+      <c r="J10" t="str">
         <v>脱水を避けてこまめに水分を摂る(水分制限がある場合を除く)。腎排泄型の薬剤は減量や投与間隔の延長が必要になることがあるため、お薬手帳を最新の状態に保ち他院受診時にも提示するよう伝える</v>
       </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str" xml:space="preserve">
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str" xml:space="preserve">
         <v xml:space="preserve">Cockcroft-Gault式［(140−年齢)×体重(kg)÷(72×血清Cr)、女性は×0.85］で算出した推算CCrが、多くの薬剤の添付文書における腎機能別用量調整の基準に使われる。eGFRは体表面積1.73㎡で標準化した値のため、実際の体格が標準から離れる患者（高齢・るいそう・肥満など）では、添付文書のCCr基準にそのまま当てはめると過大・過小評価になりうる点に注意。
 血清Cr(mg/dL)からのおおまかな対応の目安：0.7〜1.4→CCr100±20（正常・健常）／1.4〜2.4→61〜99（日常生活に支障なし）／2.5〜4.9→24〜60（日常生活に多少の支障）／5.0〜7.9→12〜23（日常生活に支障あり）／8.0〜12.0→7〜12（日常生活の規制）／12.0超→6未満（昏睡・見当識障害）</v>
       </c>
-      <c r="M6" t="str">
+      <c r="M10" t="str">
         <v>腎機能,糖尿病,骨粗鬆症,抗凝固療法（心房細動・血栓症）</v>
       </c>
-      <c r="N6" t="str">
+      <c r="N10" t="str">
         <v>CCr,クレアチニンクリアランス,クレアチニン・クリアランス,creatinine clearance,コッククロフトゴート,Cockcroft-Gault,腎機能</v>
       </c>
-      <c r="O6" t="str">
+      <c r="O10" t="str">
         <v>食事と栄養 p.199-215（第2部 腎機能低下）</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>尿酸</v>
-      </c>
-      <c r="B7" t="str">
-        <v>UA</v>
-      </c>
-      <c r="C7" t="str">
-        <v>2.0〜7.0 mg/dL</v>
-      </c>
-      <c r="D7" t="str">
-        <v>プリン体が分解されてできる老廃物で、高いと痛風や尿路結石のリスクになる</v>
-      </c>
-      <c r="E7" t="str">
-        <v>尿酸はプリン体という物質が体の中で分解されてできる老廃物です。7.0を超えた状態が続くと、関節に結晶がたまって痛風発作を起こしたり、尿路結石ができやすくなったりします。</v>
-      </c>
-      <c r="F7" t="str">
-        <v>高尿酸血症、痛風、プリン体の多い食事・アルコール摂取、腎機能低下、利尿薬などの薬剤性</v>
-      </c>
-      <c r="G7" t="str">
-        <v>プリン体の多い食品(レバー・魚卵・干物・ビールなど)を控えめにし、水分を多めに摂る。BMIが高い場合は減量も尿酸値の改善に有効なことを伝える</v>
-      </c>
-      <c r="H7" t="str">
-        <v>サイアザイド系利尿薬、ループ利尿薬、少量アスピリン、ピラジナミド、シクロスポリンは上昇させうる。尿酸降下薬(アロプリノール等)服用中はコントロール状況も確認</v>
-      </c>
-      <c r="I7" t="str">
-        <v>尿酸排泄促進薬の効果、まれに特発性腎性低尿酸血症</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v>尿酸降下薬(フェブキソスタット、アロプリノール等)の効きすぎ</v>
-      </c>
-      <c r="L7" t="str">
-        <v>利尿薬（サイアザイド系など）は尿酸を上げやすい。急激に尿酸を下げる治療の開始直後は痛風発作が誘発されることがある</v>
-      </c>
-      <c r="M7" t="str">
-        <v>高尿酸血症,糖尿病</v>
-      </c>
-      <c r="N7" t="str">
-        <v>尿酸,UA,痛風,高尿酸血症</v>
-      </c>
-      <c r="O7" t="str">
-        <v>食事と栄養 p.180-189（第2部 痛風・高尿酸血症）</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>ナトリウム（Na）</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Na</v>
-      </c>
-      <c r="C8" t="str">
-        <v>135〜145 mEq/L</v>
-      </c>
-      <c r="D8" t="str">
-        <v>体内の水分バランスや神経・筋肉の働きに関わる、血液中に最も多い電解質</v>
-      </c>
-      <c r="E8" t="str">
-        <v>ナトリウムは、体の中の水分バランスを保ったり、神経や筋肉が正しく働くために欠かせないミネラルです。多すぎても少なすぎても、意識障害やけいれんなど重い症状につながることがあります。</v>
-      </c>
-      <c r="F8" t="str">
-        <v>脱水、アルドステロン症、水分摂取不足、下痢・嘔吐による水分喪失</v>
-      </c>
-      <c r="G8" t="str">
-        <v>水分摂取状況を確認する(脱水が疑われる場合)。高齢者は口渇を感じにくいため、喉が渇く前にこまめな水分摂取を意識するよう伝える</v>
-      </c>
-      <c r="H8" t="str">
-        <v>高張輸液、浸透圧利尿薬(グリセオール等)、抗利尿ホルモン分泌を低下させる薬(炭酸リチウム等)</v>
-      </c>
-      <c r="I8" t="str">
-        <v>利尿薬（特にサイアザイド系）、SIADH（抗利尿ホルモン不適合分泌症候群）、嘔吐・下痢、心不全・肝硬変によるむくみ</v>
-      </c>
-      <c r="J8" t="str">
-        <v>利尿薬使用中は嘔吐・下痢が続いていないか確認する。意識がぼんやりする、頭痛、脱力感などの症状の有無を確認し、水のみを大量に摂りすぎていないかも確認する</v>
-      </c>
-      <c r="K8" t="str">
-        <v>サイアザイド系利尿薬、SSRI、カルバマゼピン、デスモプレシン、シクロホスファミド</v>
-      </c>
-      <c r="L8" t="str">
-        <v>低ナトリウム血症は高齢者に多く、意識障害や転倒の原因になりうる。利尿薬（特にサイアザイド系）、SSRI、カルバマゼピンなどSIADHを起こしうる薬剤の使用歴を確認する</v>
-      </c>
-      <c r="M8" t="str">
-        <v>電解質</v>
-      </c>
-      <c r="N8" t="str">
-        <v>ナトリウム,Na,電解質,脱水,SIADH,低ナトリウム血症</v>
-      </c>
-      <c r="O8" t="str">
-        <v>食事と栄養 p.81（ナトリウム）</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>クロール</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Cl</v>
-      </c>
-      <c r="C9" t="str">
-        <v>98〜108 mEq/L</v>
-      </c>
-      <c r="D9" t="str">
-        <v>ナトリウムと共に体の水分・酸塩基バランスに関わる電解質</v>
-      </c>
-      <c r="E9" t="str">
-        <v>クロールは、ナトリウムと一緒に体の水分バランスや、体液の性質（酸性・アルカリ性）を保つ働きをしているミネラルです。多くの場合、ナトリウムと同じように変動します。</v>
-      </c>
-      <c r="F9" t="str">
-        <v>脱水、腎不全、代謝性アシドーシス、高ナトリウム血症に伴うもの</v>
-      </c>
-      <c r="G9" t="str">
-        <v>脱水が疑われる場合はこまめな水分摂取を勧める（水分制限がある場合を除く）</v>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>嘔吐・下痢、利尿薬使用、代謝性アルカローシス</v>
-      </c>
-      <c r="J9" t="str">
-        <v>利尿薬使用中は嘔吐・下痢が続いていないか確認する</v>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>ナトリウムと同じ方向に動くことが多いが、酸塩基平衡の異常（アシドーシス・アルカローシス）を反映して単独で動くこともある。利尿薬（特にループ利尿薬）使用中は低クロール性アルカローシスに注意</v>
-      </c>
-      <c r="M9" t="str">
-        <v>電解質,腎機能</v>
-      </c>
-      <c r="N9" t="str">
-        <v>クロール,Cl,塩素,電解質,アシドーシス,アルカローシス</v>
-      </c>
-      <c r="O9" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>カリウム（K）</v>
-      </c>
-      <c r="B10" t="str">
-        <v>K</v>
-      </c>
-      <c r="C10" t="str">
-        <v>3.5〜5.0 mEq/L（5.5 mEq/L以上で高カリウム血症と診断）</v>
-      </c>
-      <c r="D10" t="str">
-        <v>心臓や筋肉の働きに関わる電解質で、高すぎても低すぎても不整脈につながる</v>
-      </c>
-      <c r="E10" t="str">
-        <v>カリウムは心臓や筋肉が正しく動くために必要なミネラルです。多すぎても少なすぎても脈の乱れにつながることがあるため、腎臓のお薬やお通じのお薬を使っている方は定期的にチェックすることが大切です。</v>
-      </c>
-      <c r="F10" t="str">
-        <v>腎不全、アジソン病、ACE阻害薬・ARB・カリウム保持性利尿薬などの薬剤性、溶血による偽高値</v>
-      </c>
-      <c r="G10" t="str">
-        <v>生野菜・果物・芋類などカリウムの多い食品の摂りすぎに注意する(腎機能低下がある場合)。茹でこぼす・水にさらすことでカリウムを減らせることもあわせて伝える</v>
-      </c>
-      <c r="H10" t="str">
-        <v>ACE阻害薬、ARB、カリウム保持性利尿薬(スピロノラクトン等)、NSAIDs、ST合剤、ヘパリン。β遮断薬は細胞内への取り込みを阻害し上昇させうる</v>
-      </c>
-      <c r="I10" t="str">
-        <v>利尿薬（特にループ・サイアザイド系）、下痢・嘔吐、インスリン投与、甘草含有製剤</v>
-      </c>
-      <c r="J10" t="str">
-        <v>利尿薬使用中は下痢・嘔吐が続いていないか確認し、必要に応じてバナナ・芋類などカリウムを含む食品を意識する。脱力感・こむら返り・動悸などの症状の有無もあわせて確認する</v>
-      </c>
-      <c r="K10" t="str">
-        <v>ループ利尿薬、サイアザイド系利尿薬、グリチルリチン製剤(甘草含有製剤)、ステロイド、インスリン、β2刺激薬</v>
-      </c>
-      <c r="L10" t="str">
-        <v>高カリウム血症は不整脈・心停止のリスクがあるため脱力感・動悸の有無を確認。RAS阻害薬とカリウム保持性利尿薬の併用時は特に注意</v>
-      </c>
-      <c r="M10" t="str">
-        <v>腎機能,電解質</v>
-      </c>
-      <c r="N10" t="str">
-        <v>カリウム,K,高カリウム血症,低カリウム血症</v>
-      </c>
-      <c r="O10" t="str">
-        <v>食事と栄養 p.72（カリウム）／p.199-215（第2部 腎機能低下 Q80-82 カリウム制限）</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>カルシウム（Ca）</v>
+        <v>尿酸</v>
       </c>
       <c r="B11" t="str">
-        <v>Ca</v>
+        <v>UA</v>
       </c>
       <c r="C11" t="str">
-        <v>8.5〜10.0 mg/dL</v>
+        <v>2.0〜7.0 mg/dL</v>
       </c>
       <c r="D11" t="str">
-        <v>骨や歯の材料であると同時に、神経・筋肉・血液凝固にも関わるミネラル</v>
+        <v>プリン体が分解されてできる老廃物で、高いと痛風や尿路結石のリスクになる</v>
       </c>
       <c r="E11" t="str">
-        <v>カルシウムは骨や歯の材料になるだけでなく、神経の伝達や筋肉の収縮、血液を固める働きにも関わっている重要なミネラルです。副甲状腺ホルモンやビタミンDによって血液中の濃度が細かく調整されています。</v>
+        <v>尿酸はプリン体という物質が体の中で分解されてできる老廃物です。7.0を超えた状態が続くと、関節に結晶がたまって痛風発作を起こしたり、尿路結石ができやすくなったりします。</v>
       </c>
       <c r="F11" t="str">
-        <v>副甲状腺機能亢進症、悪性腫瘍（骨転移など）、ビタミンD過剰、活性型ビタミンD3製剤の過量</v>
+        <v>高尿酸血症、痛風、プリン体の多い食事・アルコール摂取、腎機能低下、利尿薬などの薬剤性</v>
       </c>
       <c r="G11" t="str">
-        <v>吐き気、便秘、多尿、意識がぼんやりするなどの高カルシウム血症の症状がないか確認する。活性型ビタミンD3製剤使用中は過量になっていないか、水分摂取が十分かも確認する</v>
+        <v>プリン体の多い食品(レバー・魚卵・干物・ビールなど)を控えめにし、水分を多めに摂る。BMIが高い場合は減量も尿酸値の改善に有効なことを伝える</v>
       </c>
       <c r="H11" t="str">
-        <v>活性型ビタミンD製剤、サイアザイド系利尿薬、炭酸リチウム、カルシウム含有薬(炭酸カルシウム等)</v>
+        <v>サイアザイド系利尿薬、ループ利尿薬、少量アスピリン、ピラジナミド、シクロスポリンは上昇させうる。尿酸降下薬(アロプリノール等)服用中はコントロール状況も確認</v>
       </c>
       <c r="I11" t="str">
-        <v>副甲状腺機能低下症、ビタミンD欠乏、腎不全、低アルブミン血症（見かけ上の低下）</v>
+        <v>尿酸排泄促進薬の効果、まれに特発性腎性低尿酸血症</v>
       </c>
       <c r="J11" t="str">
-        <v>手足のしびれやこむら返りなど低カルシウム血症の症状がないか確認する。乳製品・小魚・大豆製品などカルシウムを多く含む食品と、吸収を助ける適度な日光浴を意識するよう伝える</v>
+        <v/>
       </c>
       <c r="K11" t="str">
-        <v>ビスホスホネート製剤、デノスマブ、ループ利尿薬、抗てんかん薬の長期使用、シナカルセト</v>
+        <v>尿酸降下薬(フェブキソスタット、アロプリノール等)の効きすぎ</v>
       </c>
       <c r="L11" t="str">
-        <v>アルブミンが低いと見かけ上低く出るため、補正カルシウム値（Ca+(4-Alb)）で評価する。骨粗鬆症治療薬（活性型ビタミンD3製剤、デノスマブなど）使用中は高カルシウム血症の副作用に注意</v>
+        <v>利尿薬（サイアザイド系など）は尿酸を上げやすい。急激に尿酸を下げる治療の開始直後は痛風発作が誘発されることがある</v>
       </c>
       <c r="M11" t="str">
-        <v>電解質,骨粗鬆症</v>
+        <v>高尿酸血症,糖尿病</v>
       </c>
       <c r="N11" t="str">
-        <v>カルシウム,Ca,電解質</v>
+        <v>尿酸,UA,痛風,高尿酸血症</v>
       </c>
       <c r="O11" t="str">
-        <v>食事と栄養 p.75（カルシウム）／p.165-178（第2部 骨粗鬆症）</v>
+        <v>食事と栄養 p.180-189（第2部 痛風・高尿酸血症）</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>補正カルシウム（参考値）</v>
+        <v>ナトリウム（Na）</v>
       </c>
       <c r="B12" t="str">
-        <v>Corrected Ca,補正Ca</v>
+        <v>Na</v>
       </c>
       <c r="C12" t="str">
-        <v>実測カルシウム値と同じ基準値を用いる（8.5〜10.0 mg/dL）</v>
+        <v>135〜145 mEq/L</v>
       </c>
       <c r="D12" t="str">
-        <v>アルブミンが低い患者で、見かけ上のカルシウム値を実際の値に近づけるための補正値</v>
+        <v>体内の水分バランスや神経・筋肉の働きに関わる、血液中に最も多い電解質</v>
       </c>
       <c r="E12" t="str">
-        <v>血液中のカルシウムの多くはアルブミンというたんぱく質にくっついて存在しています。アルブミンが少ないと、実際のカルシウムの量が変わらなくても検査値上は低く出てしまうことがあるため、その影響を補正した数値がこの「補正カルシウム」です。</v>
+        <v>ナトリウムは、体の中の水分バランスを保ったり、神経や筋肉が正しく働くために欠かせないミネラルです。多すぎても少なすぎても、意識障害やけいれんなど重い症状につながることがあります。</v>
       </c>
       <c r="F12" t="str">
-        <v>（実測カルシウムの高値と同様）副甲状腺機能亢進症、悪性腫瘍（骨転移など）、ビタミンD過剰</v>
+        <v>脱水、アルドステロン症、水分摂取不足、下痢・嘔吐による水分喪失</v>
       </c>
       <c r="G12" t="str">
-        <v/>
+        <v>水分摂取状況を確認する(脱水が疑われる場合)。高齢者は口渇を感じにくいため、喉が渇く前にこまめな水分摂取を意識するよう伝える</v>
       </c>
       <c r="H12" t="str">
-        <v>(実測カルシウムに準ずる)活性型ビタミンD製剤、サイアザイド系利尿薬、炭酸リチウム</v>
+        <v>高張輸液、浸透圧利尿薬(グリセオール等)、抗利尿ホルモン分泌を低下させる薬(炭酸リチウム等)</v>
       </c>
       <c r="I12" t="str">
-        <v>（実測カルシウムの低値と同様）副甲状腺機能低下症、ビタミンD欠乏、腎不全</v>
+        <v>利尿薬（特にサイアザイド系）、SIADH（抗利尿ホルモン不適合分泌症候群）、嘔吐・下痢、心不全・肝硬変によるむくみ</v>
       </c>
       <c r="J12" t="str">
-        <v/>
+        <v>利尿薬使用中は嘔吐・下痢が続いていないか確認する。意識がぼんやりする、頭痛、脱力感などの症状の有無を確認し、水のみを大量に摂りすぎていないかも確認する</v>
       </c>
       <c r="K12" t="str">
-        <v>(実測カルシウムに準ずる)ビスホスホネート製剤、デノスマブ、ループ利尿薬</v>
+        <v>サイアザイド系利尿薬、SSRI、カルバマゼピン、デスモプレシン、シクロホスファミド</v>
       </c>
       <c r="L12" t="str">
-        <v>補正カルシウム(mg/dL) = 実測カルシウム + (4 − アルブミン値)の式で計算する。アルブミンが4.0 g/dL未満の低栄養患者やネフローゼ症候群の患者では、実測カルシウムだけで判断すると誤りやすいため、この補正値で評価する</v>
+        <v>低ナトリウム血症は高齢者に多く、意識障害や転倒の原因になりうる。利尿薬（特にサイアザイド系）、SSRI、カルバマゼピンなどSIADHを起こしうる薬剤の使用歴を確認する</v>
       </c>
       <c r="M12" t="str">
-        <v>電解質,骨粗鬆症</v>
+        <v>電解質</v>
       </c>
       <c r="N12" t="str">
-        <v>補正カルシウム,Corrected Calcium,アルブミン補正,低アルブミン血症</v>
+        <v>ナトリウム,Na,電解質,脱水,SIADH,低ナトリウム血症</v>
       </c>
       <c r="O12" t="str">
-        <v/>
+        <v>食事と栄養 p.81（ナトリウム）</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>リン（P）</v>
+        <v>クロール</v>
       </c>
       <c r="B13" t="str">
-        <v>P,IP</v>
+        <v>Cl</v>
       </c>
       <c r="C13" t="str">
-        <v>2.5〜4.5 mg/dL</v>
+        <v>98〜108 mEq/L</v>
       </c>
       <c r="D13" t="str">
-        <v>カルシウムとともに骨を作る主要なミネラル</v>
+        <v>ナトリウムと共に体の水分・酸塩基バランスに関わる電解質</v>
       </c>
       <c r="E13" t="str">
-        <v>リンはカルシウムと一緒に骨や歯を作る材料になるミネラルです。カルシウムと逆方向に動くことが多く、腎臓の働きやホルモンのバランスによっても変動します。</v>
+        <v>クロールは、ナトリウムと一緒に体の水分バランスや、体液の性質（酸性・アルカリ性）を保つ働きをしているミネラルです。多くの場合、ナトリウムと同じように変動します。</v>
       </c>
       <c r="F13" t="str">
-        <v>腎不全、副甲状腺機能低下症</v>
+        <v>脱水、腎不全、代謝性アシドーシス、高ナトリウム血症に伴うもの</v>
       </c>
       <c r="G13" t="str">
-        <v>腎機能低下がある場合は乳製品・加工食品(リン酸塩添加物)の摂りすぎに注意する。リン吸着薬を服用中の場合は食直前・食直後など服用タイミングが守られているか確認する</v>
+        <v>脱水が疑われる場合はこまめな水分摂取を勧める（水分制限がある場合を除く）</v>
       </c>
       <c r="H13" t="str">
-        <v>活性型ビタミンD製剤、リン含有製剤。腎機能低下患者では特に注意</v>
+        <v/>
       </c>
       <c r="I13" t="str">
-        <v>副甲状腺機能亢進症、骨軟化症、ビタミンD欠乏</v>
+        <v>嘔吐・下痢、利尿薬使用、代謝性アルカローシス</v>
       </c>
       <c r="J13" t="str">
-        <v>骨の痛みや筋力低下などの症状がないか確認する。極端な食事制限や食欲低下がないか、栄養状態もあわせて確認する</v>
+        <v>利尿薬使用中は嘔吐・下痢が続いていないか確認する</v>
       </c>
       <c r="K13" t="str">
-        <v>リン吸着薬(セベラマー等)、アルミニウム含有制酸薬、利尿薬</v>
+        <v/>
       </c>
       <c r="L13" t="str">
-        <v>カルシウムと逆方向に動くことが多い（副甲状腺機能亢進症ではCa上昇・P低下）。骨粗鬆症の二次性原因の除外に用いられる</v>
+        <v>ナトリウムと同じ方向に動くことが多いが、酸塩基平衡の異常（アシドーシス・アルカローシス）を反映して単独で動くこともある。利尿薬（特にループ利尿薬）使用中は低クロール性アルカローシスに注意</v>
       </c>
       <c r="M13" t="str">
-        <v>骨粗鬆症,電解質</v>
+        <v>電解質,腎機能</v>
       </c>
       <c r="N13" t="str">
-        <v>リン,P,IP,無機リン</v>
+        <v>クロール,Cl,塩素,電解質,アシドーシス,アルカローシス</v>
       </c>
       <c r="O13" t="str">
-        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）／p.199-215（第2部 腎機能低下 Q83 リン制限）</v>
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>AST（GOT）</v>
+        <v>カリウム（K）</v>
       </c>
       <c r="B14" t="str">
-        <v>AST,GOT</v>
+        <v>K</v>
       </c>
       <c r="C14" t="str">
-        <v>10〜40 U/L</v>
+        <v>3.5〜5.0 mEq/L（5.5 mEq/L以上で高カリウム血症と診断）</v>
       </c>
       <c r="D14" t="str">
-        <v>肝臓や心臓・筋肉の細胞が壊れると血液中に漏れ出す酵素</v>
+        <v>心臓や筋肉の働きに関わる電解質で、高すぎても低すぎても不整脈につながる</v>
       </c>
       <c r="E14" t="str">
-        <v>ASTは肝臓や心臓、筋肉の細胞の中にある酵素です。これらの細胞がダメージを受けたり壊れたりすると血液中に漏れ出して数値が上がります。肝臓の状態を見るときはALTと一緒に確認します。</v>
+        <v>カリウムは心臓や筋肉が正しく動くために必要なミネラルです。多すぎても少なすぎても脈の乱れにつながることがあるため、腎臓のお薬やお通じのお薬を使っている方は定期的にチェックすることが大切です。</v>
       </c>
       <c r="F14" t="str">
-        <v>肝炎・肝硬変などの肝疾患、心筋梗塞、筋肉の障害（激しい運動・横紋筋融解症）、薬剤性肝障害</v>
+        <v>腎不全、アジソン病、ACE阻害薬・ARB・カリウム保持性利尿薬などの薬剤性、溶血による偽高値</v>
       </c>
       <c r="G14" t="str">
-        <v>飲酒量を控える。激しい運動の直後の採血でないかを確認し、新規薬剤の開始時期と重なっていないかもあわせて確認する</v>
+        <v>生野菜・果物・芋類などカリウムの多い食品の摂りすぎに注意する(腎機能低下がある場合)。茹でこぼす・水にさらすことでカリウムを減らせることもあわせて伝える</v>
       </c>
       <c r="H14" t="str">
-        <v>アセトアミノフェン(過量)、スタチン系、抗結核薬(イソニアジド・リファンピシン)、バルプロ酸、NSAIDs、メトトレキサート</v>
+        <v>ACE阻害薬、ARB、カリウム保持性利尿薬(スピロノラクトン等)、NSAIDs、ST合剤、ヘパリン。β遮断薬は細胞内への取り込みを阻害し上昇させうる</v>
       </c>
       <c r="I14" t="str">
-        <v>臨床的に問題になることは少ない</v>
+        <v>利尿薬（特にループ・サイアザイド系）、下痢・嘔吐、インスリン投与、甘草含有製剤</v>
       </c>
       <c r="J14" t="str">
-        <v/>
+        <v>利尿薬使用中は下痢・嘔吐が続いていないか確認し、必要に応じてバナナ・芋類などカリウムを含む食品を意識する。脱力感・こむら返り・動悸などの症状の有無もあわせて確認する</v>
       </c>
       <c r="K14" t="str">
-        <v/>
+        <v>ループ利尿薬、サイアザイド系利尿薬、グリチルリチン製剤(甘草含有製剤)、ステロイド、インスリン、β2刺激薬</v>
       </c>
       <c r="L14" t="str">
-        <v>ALTとの比率（AST/ALT比）で肝細胞障害か他臓器由来かを推測できる。AST優位はアルコール性・心筋・筋由来を疑う材料になる</v>
+        <v>高カリウム血症は不整脈・心停止のリスクがあるため脱力感・動悸の有無を確認。RAS阻害薬とカリウム保持性利尿薬の併用時は特に注意</v>
       </c>
       <c r="M14" t="str">
-        <v>肝機能,糖尿病,てんかん,精神疾患（非定型抗精神病薬）</v>
+        <v>腎機能,電解質</v>
       </c>
       <c r="N14" t="str">
-        <v>AST,GOT,肝機能,肝障害</v>
+        <v>カリウム,K,高カリウム血症,低カリウム血症</v>
       </c>
       <c r="O14" t="str">
-        <v/>
+        <v>食事と栄養 p.72（カリウム）／p.199-215（第2部 腎機能低下 Q80-82 カリウム制限）</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ALT（GPT）</v>
+        <v>カルシウム（Ca）</v>
       </c>
       <c r="B15" t="str">
-        <v>ALT,GPT</v>
+        <v>Ca</v>
       </c>
       <c r="C15" t="str">
-        <v>5〜40 U/L</v>
+        <v>8.5〜10.0 mg/dL</v>
       </c>
       <c r="D15" t="str">
-        <v>主に肝臓の細胞に含まれる酵素で、肝障害の指標として最もよく使われる</v>
+        <v>骨や歯の材料であると同時に、神経・筋肉・血液凝固にも関わるミネラル</v>
       </c>
       <c r="E15" t="str">
-        <v>ALTは主に肝臓の細胞の中にある酵素です。肝臓の細胞がダメージを受けると血液中に漏れ出して数値が上がります。ASTよりも肝臓に特異的な数値なので、肝臓の状態を見るときによく使われます。</v>
+        <v>カルシウムは骨や歯の材料になるだけでなく、神経の伝達や筋肉の収縮、血液を固める働きにも関わっている重要なミネラルです。副甲状腺ホルモンやビタミンDによって血液中の濃度が細かく調整されています。</v>
       </c>
       <c r="F15" t="str">
-        <v>脂肪肝、肝炎（ウイルス性・アルコール性・薬剤性）、肝硬変、薬の副作用による肝機能障害</v>
+        <v>副甲状腺機能亢進症、悪性腫瘍（骨転移など）、ビタミンD過剰、活性型ビタミンD3製剤の過量</v>
       </c>
       <c r="G15" t="str">
-        <v>体重管理と脂質の摂りすぎに注意する(脂肪肝が疑われる場合)。新規薬剤の開始時期と重なっていないか確認し、市販薬・サプリメントの使用歴も聞く</v>
+        <v>吐き気、便秘、多尿、意識がぼんやりするなどの高カルシウム血症の症状がないか確認する。活性型ビタミンD3製剤使用中は過量になっていないか、水分摂取が十分かも確認する</v>
       </c>
       <c r="H15" t="str">
-        <v>アセトアミノフェン(過量)、スタチン系、抗結核薬(イソニアジド・リファンピシン)、バルプロ酸、NSAIDs、メトトレキサート</v>
+        <v>活性型ビタミンD製剤、サイアザイド系利尿薬、炭酸リチウム、カルシウム含有薬(炭酸カルシウム等)</v>
       </c>
       <c r="I15" t="str">
-        <v>臨床的に問題になることは少ない</v>
+        <v>副甲状腺機能低下症、ビタミンD欠乏、腎不全、低アルブミン血症（見かけ上の低下）</v>
       </c>
       <c r="J15" t="str">
-        <v/>
+        <v>手足のしびれやこむら返りなど低カルシウム血症の症状がないか確認する。乳製品・小魚・大豆製品などカルシウムを多く含む食品と、吸収を助ける適度な日光浴を意識するよう伝える</v>
       </c>
       <c r="K15" t="str">
-        <v/>
+        <v>ビスホスホネート製剤、デノスマブ、ループ利尿薬、抗てんかん薬の長期使用、シナカルセト</v>
       </c>
       <c r="L15" t="str">
-        <v>新規薬剤開始後の肝障害の指標として重要。健診でALTのみ軽度上昇していることが多く、その場合は脂肪肝（NAFLD）の頻度が高い</v>
+        <v>アルブミンが低いと見かけ上低く出るため、補正カルシウム値（Ca+(4-Alb)）で評価する。骨粗鬆症治療薬（活性型ビタミンD3製剤、デノスマブなど）使用中は高カルシウム血症の副作用に注意</v>
       </c>
       <c r="M15" t="str">
-        <v>肝機能,糖尿病,てんかん,精神疾患（非定型抗精神病薬）</v>
+        <v>電解質,骨粗鬆症</v>
       </c>
       <c r="N15" t="str">
-        <v>ALT,GPT,肝機能,肝障害,脂肪肝</v>
+        <v>カルシウム,Ca,電解質</v>
       </c>
       <c r="O15" t="str">
-        <v/>
+        <v>食事と栄養 p.75（カルシウム）／p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>乳酸脱水素酵素（LDH）</v>
+        <v>補正カルシウム（参考値）</v>
       </c>
       <c r="B16" t="str">
-        <v>LDH</v>
+        <v>Corrected Ca,補正Ca</v>
       </c>
       <c r="C16" t="str">
-        <v>120〜245 U/L程度（施設差あり）</v>
+        <v>実測カルシウム値と同じ基準値を用いる（8.5〜10.0 mg/dL）</v>
       </c>
       <c r="D16" t="str">
-        <v>全身のさまざまな組織に含まれる酵素で、細胞が壊れると幅広く上昇する</v>
+        <v>アルブミンが低い患者で、見かけ上のカルシウム値を実際の値に近づけるための補正値</v>
       </c>
       <c r="E16" t="str">
-        <v>LDHは全身の細胞の中にある酵素で、肝臓、心臓、筋肉、血液など、いろいろな組織の細胞がダメージを受けると血液中に漏れ出します。どの臓器が原因かを絞り込むには、他の検査値と組み合わせて評価します。</v>
+        <v>血液中のカルシウムの多くはアルブミンというたんぱく質にくっついて存在しています。アルブミンが少ないと、実際のカルシウムの量が変わらなくても検査値上は低く出てしまうことがあるため、その影響を補正した数値がこの「補正カルシウム」です。</v>
       </c>
       <c r="F16" t="str">
-        <v>肝疾患、心筋梗塞、溶血性疾患、悪性腫瘍、筋肉の障害（横紋筋融解症など）、肺疾患</v>
+        <v>（実測カルシウムの高値と同様）副甲状腺機能亢進症、悪性腫瘍（骨転移など）、ビタミンD過剰</v>
       </c>
       <c r="G16" t="str">
-        <v>息切れ、黄疸、筋肉痛など随伴症状の有無を確認し、原因臓器を絞り込む手がかりにする</v>
+        <v/>
       </c>
       <c r="H16" t="str">
-        <v/>
+        <v>(実測カルシウムに準ずる)活性型ビタミンD製剤、サイアザイド系利尿薬、炭酸リチウム</v>
       </c>
       <c r="I16" t="str">
-        <v/>
+        <v>（実測カルシウムの低値と同様）副甲状腺機能低下症、ビタミンD欠乏、腎不全</v>
       </c>
       <c r="J16" t="str">
         <v/>
       </c>
       <c r="K16" t="str">
-        <v/>
+        <v>(実測カルシウムに準ずる)ビスホスホネート製剤、デノスマブ、ループ利尿薬</v>
       </c>
       <c r="L16" t="str">
-        <v>臓器特異性が低いため単独では原因を特定しにくい。AST/ALT(肝)、CK(筋)、ビリルビン・ハプトグロビン(溶血)など他の検査値と組み合わせて原因臓器を推定する</v>
+        <v>補正カルシウム(mg/dL) = 実測カルシウム + (4 − アルブミン値)の式で計算する。アルブミンが4.0 g/dL未満の低栄養患者やネフローゼ症候群の患者では、実測カルシウムだけで判断すると誤りやすいため、この補正値で評価する</v>
       </c>
       <c r="M16" t="str">
-        <v/>
+        <v>電解質,骨粗鬆症</v>
       </c>
       <c r="N16" t="str">
-        <v>LDH,乳酸脱水素酵素,溶血,心筋梗塞,悪性腫瘍</v>
+        <v>補正カルシウム,Corrected Calcium,アルブミン補正,低アルブミン血症</v>
       </c>
       <c r="O16" t="str">
         <v/>
@@ -1176,329 +1176,329 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>コリンエステラーゼ</v>
+        <v>リン（P）</v>
       </c>
       <c r="B17" t="str">
-        <v>ChE</v>
+        <v>P,IP</v>
       </c>
       <c r="C17" t="str">
-        <v>男性 240〜486 U/L、女性 201〜421 U/L（施設差あり）</v>
+        <v>2.5〜4.5 mg/dL</v>
       </c>
       <c r="D17" t="str">
-        <v>主に肝臓で作られる酵素。肝臓のたんぱく質を作る力（合成能）を反映する</v>
+        <v>カルシウムとともに骨を作る主要なミネラル</v>
       </c>
       <c r="E17" t="str">
-        <v>コリンエステラーゼは肝臓で作られる酵素です。肝臓がたんぱく質を作る力が落ちると数値が下がり、逆に脂肪肝や栄養状態が良すぎる場合は上がることがあります。</v>
+        <v>リンはカルシウムと一緒に骨や歯を作る材料になるミネラルです。カルシウムと逆方向に動くことが多く、腎臓の働きやホルモンのバランスによっても変動します。</v>
       </c>
       <c r="F17" t="str">
-        <v>脂肪肝、ネフローゼ症候群、肥満、甲状腺機能亢進症</v>
+        <v>腎不全、副甲状腺機能低下症</v>
       </c>
       <c r="G17" t="str">
-        <v>脂肪肝が疑われる場合は食事・運動習慣の見直しを勧める。急激な体重増加がないかもあわせて確認する</v>
+        <v>腎機能低下がある場合は乳製品・加工食品(リン酸塩添加物)の摂りすぎに注意する。リン吸着薬を服用中の場合は食直前・食直後など服用タイミングが守られているか確認する</v>
       </c>
       <c r="H17" t="str">
-        <v/>
+        <v>活性型ビタミンD製剤、リン含有製剤。腎機能低下患者では特に注意</v>
       </c>
       <c r="I17" t="str">
-        <v>肝硬変など肝臓の合成能低下、低栄養、有機リン中毒（農薬など）</v>
+        <v>副甲状腺機能亢進症、骨軟化症、ビタミンD欠乏</v>
       </c>
       <c r="J17" t="str">
-        <v>低栄養が疑われる場合は食事摂取状況を確認する。肝硬変など背景疾患がある場合は出血傾向(あざ・歯ぐきの出血)の有無もあわせて確認する</v>
+        <v>骨の痛みや筋力低下などの症状がないか確認する。極端な食事制限や食欲低下がないか、栄養状態もあわせて確認する</v>
       </c>
       <c r="K17" t="str">
-        <v/>
+        <v>リン吸着薬(セベラマー等)、アルミニウム含有制酸薬、利尿薬</v>
       </c>
       <c r="L17" t="str">
-        <v>アルブミンと同様に肝臓の「合成能」を見る指標。低栄養か肝硬変かは、アルブミンや血小板数（肝硬変で低下しやすい）と合わせて判断する</v>
+        <v>カルシウムと逆方向に動くことが多い（副甲状腺機能亢進症ではCa上昇・P低下）。骨粗鬆症の二次性原因の除外に用いられる</v>
       </c>
       <c r="M17" t="str">
-        <v>肝機能</v>
+        <v>骨粗鬆症,電解質</v>
       </c>
       <c r="N17" t="str">
-        <v>コリンエステラーゼ,ChE,肝合成能,脂肪肝,肝硬変</v>
+        <v>リン,P,IP,無機リン</v>
       </c>
       <c r="O17" t="str">
-        <v/>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）／p.199-215（第2部 腎機能低下 Q83 リン制限）</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
+        <v>AST（GOT）</v>
+      </c>
+      <c r="B18" t="str">
+        <v>AST,GOT</v>
+      </c>
+      <c r="C18" t="str">
+        <v>10〜40 U/L</v>
+      </c>
+      <c r="D18" t="str">
+        <v>肝臓や心臓・筋肉の細胞が壊れると血液中に漏れ出す酵素</v>
+      </c>
+      <c r="E18" t="str">
+        <v>ASTは肝臓や心臓、筋肉の細胞の中にある酵素です。これらの細胞がダメージを受けたり壊れたりすると血液中に漏れ出して数値が上がります。肝臓の状態を見るときはALTと一緒に確認します。</v>
+      </c>
+      <c r="F18" t="str">
+        <v>肝炎・肝硬変などの肝疾患、心筋梗塞、筋肉の障害（激しい運動・横紋筋融解症）、薬剤性肝障害</v>
+      </c>
+      <c r="G18" t="str">
+        <v>飲酒量を控える。激しい運動の直後の採血でないかを確認し、新規薬剤の開始時期と重なっていないかもあわせて確認する</v>
+      </c>
+      <c r="H18" t="str">
+        <v>アセトアミノフェン(過量)、スタチン系、抗結核薬(イソニアジド・リファンピシン)、バルプロ酸、NSAIDs、メトトレキサート</v>
+      </c>
+      <c r="I18" t="str">
+        <v>臨床的に問題になることは少ない</v>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
+        <v>ALTとの比率（AST/ALT比）で肝細胞障害か他臓器由来かを推測できる。AST優位はアルコール性・心筋・筋由来を疑う材料になる</v>
+      </c>
+      <c r="M18" t="str">
+        <v>肝機能,糖尿病,てんかん,精神疾患（非定型抗精神病薬）</v>
+      </c>
+      <c r="N18" t="str">
+        <v>AST,GOT,肝機能,肝障害</v>
+      </c>
+      <c r="O18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>ALT（GPT）</v>
+      </c>
+      <c r="B19" t="str">
+        <v>ALT,GPT</v>
+      </c>
+      <c r="C19" t="str">
+        <v>5〜40 U/L</v>
+      </c>
+      <c r="D19" t="str">
+        <v>主に肝臓の細胞に含まれる酵素で、肝障害の指標として最もよく使われる</v>
+      </c>
+      <c r="E19" t="str">
+        <v>ALTは主に肝臓の細胞の中にある酵素です。肝臓の細胞がダメージを受けると血液中に漏れ出して数値が上がります。ASTよりも肝臓に特異的な数値なので、肝臓の状態を見るときによく使われます。</v>
+      </c>
+      <c r="F19" t="str">
+        <v>脂肪肝、肝炎（ウイルス性・アルコール性・薬剤性）、肝硬変、薬の副作用による肝機能障害</v>
+      </c>
+      <c r="G19" t="str">
+        <v>体重管理と脂質の摂りすぎに注意する(脂肪肝が疑われる場合)。新規薬剤の開始時期と重なっていないか確認し、市販薬・サプリメントの使用歴も聞く</v>
+      </c>
+      <c r="H19" t="str">
+        <v>アセトアミノフェン(過量)、スタチン系、抗結核薬(イソニアジド・リファンピシン)、バルプロ酸、NSAIDs、メトトレキサート</v>
+      </c>
+      <c r="I19" t="str">
+        <v>臨床的に問題になることは少ない</v>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
+        <v/>
+      </c>
+      <c r="L19" t="str">
+        <v>新規薬剤開始後の肝障害の指標として重要。健診でALTのみ軽度上昇していることが多く、その場合は脂肪肝（NAFLD）の頻度が高い</v>
+      </c>
+      <c r="M19" t="str">
+        <v>肝機能,糖尿病,てんかん,精神疾患（非定型抗精神病薬）</v>
+      </c>
+      <c r="N19" t="str">
+        <v>ALT,GPT,肝機能,肝障害,脂肪肝</v>
+      </c>
+      <c r="O19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>乳酸脱水素酵素（LDH）</v>
+      </c>
+      <c r="B20" t="str">
+        <v>LDH</v>
+      </c>
+      <c r="C20" t="str">
+        <v>120〜245 U/L程度（施設差あり）</v>
+      </c>
+      <c r="D20" t="str">
+        <v>全身のさまざまな組織に含まれる酵素で、細胞が壊れると幅広く上昇する</v>
+      </c>
+      <c r="E20" t="str">
+        <v>LDHは全身の細胞の中にある酵素で、肝臓、心臓、筋肉、血液など、いろいろな組織の細胞がダメージを受けると血液中に漏れ出します。どの臓器が原因かを絞り込むには、他の検査値と組み合わせて評価します。</v>
+      </c>
+      <c r="F20" t="str">
+        <v>肝疾患、心筋梗塞、溶血性疾患、悪性腫瘍、筋肉の障害（横紋筋融解症など）、肺疾患</v>
+      </c>
+      <c r="G20" t="str">
+        <v>息切れ、黄疸、筋肉痛など随伴症状の有無を確認し、原因臓器を絞り込む手がかりにする</v>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v/>
+      </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
+      <c r="K20" t="str">
+        <v/>
+      </c>
+      <c r="L20" t="str">
+        <v>臓器特異性が低いため単独では原因を特定しにくい。AST/ALT(肝)、CK(筋)、ビリルビン・ハプトグロビン(溶血)など他の検査値と組み合わせて原因臓器を推定する</v>
+      </c>
+      <c r="M20" t="str">
+        <v/>
+      </c>
+      <c r="N20" t="str">
+        <v>LDH,乳酸脱水素酵素,溶血,心筋梗塞,悪性腫瘍</v>
+      </c>
+      <c r="O20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>コリンエステラーゼ</v>
+      </c>
+      <c r="B21" t="str">
+        <v>ChE</v>
+      </c>
+      <c r="C21" t="str">
+        <v>男性 240〜486 U/L、女性 201〜421 U/L（施設差あり）</v>
+      </c>
+      <c r="D21" t="str">
+        <v>主に肝臓で作られる酵素。肝臓のたんぱく質を作る力（合成能）を反映する</v>
+      </c>
+      <c r="E21" t="str">
+        <v>コリンエステラーゼは肝臓で作られる酵素です。肝臓がたんぱく質を作る力が落ちると数値が下がり、逆に脂肪肝や栄養状態が良すぎる場合は上がることがあります。</v>
+      </c>
+      <c r="F21" t="str">
+        <v>脂肪肝、ネフローゼ症候群、肥満、甲状腺機能亢進症</v>
+      </c>
+      <c r="G21" t="str">
+        <v>脂肪肝が疑われる場合は食事・運動習慣の見直しを勧める。急激な体重増加がないかもあわせて確認する</v>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v>肝硬変など肝臓の合成能低下、低栄養、有機リン中毒（農薬など）</v>
+      </c>
+      <c r="J21" t="str">
+        <v>低栄養が疑われる場合は食事摂取状況を確認する。肝硬変など背景疾患がある場合は出血傾向(あざ・歯ぐきの出血)の有無もあわせて確認する</v>
+      </c>
+      <c r="K21" t="str">
+        <v/>
+      </c>
+      <c r="L21" t="str">
+        <v>アルブミンと同様に肝臓の「合成能」を見る指標。低栄養か肝硬変かは、アルブミンや血小板数（肝硬変で低下しやすい）と合わせて判断する</v>
+      </c>
+      <c r="M21" t="str">
+        <v>肝機能</v>
+      </c>
+      <c r="N21" t="str">
+        <v>コリンエステラーゼ,ChE,肝合成能,脂肪肝,肝硬変</v>
+      </c>
+      <c r="O21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
         <v>アルカリフォスファターゼ（ALP）</v>
       </c>
-      <c r="B18" t="str">
+      <c r="B22" t="str">
         <v>ALP</v>
       </c>
-      <c r="C18" t="str">
+      <c r="C22" t="str">
         <v>38〜113 U/L（施設・測定法により大きく異なる）</v>
       </c>
-      <c r="D18" t="str">
+      <c r="D22" t="str">
         <v>骨や肝臓・胆道に多く含まれる酵素で、骨を作る働きの指標にもなる</v>
       </c>
-      <c r="E18" t="str">
+      <c r="E22" t="str">
         <v>ALPは骨や肝臓、胆道に多く含まれる酵素です。骨を作る働きが活発なとき（骨の成長期や骨折の治癒過程など）や、肝臓・胆道にトラブルがあるときに数値が上がります。</v>
       </c>
-      <c r="F18" t="str">
+      <c r="F22" t="str">
         <v>骨代謝の亢進（骨折治癒過程、骨粗鬆症、骨転移、Paget病）、肝・胆道疾患、成長期の生理的高値</v>
       </c>
-      <c r="G18" t="str">
+      <c r="G22" t="str">
         <v>骨折治癒過程や成長期など生理的な上昇もあるため、経過や年齢背景を確認する。肝・胆道由来が疑われる場合は黄疸や皮膚のかゆみの有無も確認する</v>
       </c>
-      <c r="H18" t="str">
+      <c r="H22" t="str">
         <v>抗てんかん薬(フェニトイン等)、胆汁うっ滞型の薬剤性肝障害を起こしうる抗菌薬・NSAIDs</v>
       </c>
-      <c r="I18" t="str">
-        <v/>
-      </c>
-      <c r="J18" t="str">
-        <v/>
-      </c>
-      <c r="K18" t="str">
-        <v/>
-      </c>
-      <c r="L18" t="str">
+      <c r="I22" t="str">
+        <v/>
+      </c>
+      <c r="J22" t="str">
+        <v/>
+      </c>
+      <c r="K22" t="str">
+        <v/>
+      </c>
+      <c r="L22" t="str">
         <v>骨由来か肝由来かの区別には骨型ALPアイソザイムやγ-GTPとの組み合わせで判断する</v>
       </c>
-      <c r="M18" t="str">
+      <c r="M22" t="str">
         <v>骨粗鬆症,肝機能</v>
       </c>
-      <c r="N18" t="str">
+      <c r="N22" t="str">
         <v>ALP,アルカリフォスファターゼ,骨代謝,肝機能</v>
       </c>
-      <c r="O18" t="str">
+      <c r="O22" t="str">
         <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
-    <row r="19" xml:space="preserve">
-      <c r="A19" t="str">
+    <row r="23" xml:space="preserve">
+      <c r="A23" t="str">
         <v>γ-GTP</v>
       </c>
-      <c r="B19" t="str">
+      <c r="B23" t="str">
         <v>γ-GTP,GGT</v>
       </c>
-      <c r="C19" t="str" xml:space="preserve">
+      <c r="C23" t="str" xml:space="preserve">
         <v xml:space="preserve">男性 〜50 U/L、女性 〜30 U/L
 （施設差が大きい）</v>
       </c>
-      <c r="D19" t="str">
+      <c r="D23" t="str">
         <v>アルコールや胆道のトラブルに反応しやすい肝臓の酵素</v>
       </c>
-      <c r="E19" t="str">
+      <c r="E23" t="str">
         <v>γ-GTPは肝臓や胆道の細胞にある酵素で、特にお酒の影響を受けやすいことが知られています。数値が高いときは、アルコールの摂取量や胆道（胆汁の通り道）の状態を確認する目安になります。</v>
       </c>
-      <c r="F19" t="str">
+      <c r="F23" t="str">
         <v>アルコール性肝障害、脂肪肝、胆道系疾患（胆石・胆管閉塞）、薬剤性（酵素誘導）</v>
       </c>
-      <c r="G19" t="str">
+      <c r="G23" t="str">
         <v>飲酒量を控える、休肝日をつくるよう伝える。断酒・節酒を続けると数値が比較的早く改善しやすいことを励みとして伝えるとよい</v>
       </c>
-      <c r="H19" t="str">
+      <c r="H23" t="str">
         <v>アルコール、フェニトイン、バルビツール酸系など肝薬物代謝酵素誘導作用のある薬剤</v>
       </c>
-      <c r="I19" t="str">
+      <c r="I23" t="str">
         <v>臨床的に問題になることは少ない</v>
       </c>
-      <c r="J19" t="str">
-        <v/>
-      </c>
-      <c r="K19" t="str">
-        <v/>
-      </c>
-      <c r="L19" t="str">
+      <c r="J23" t="str">
+        <v/>
+      </c>
+      <c r="K23" t="str">
+        <v/>
+      </c>
+      <c r="L23" t="str">
         <v>飲酒歴の確認に使いやすい数値。断酒・節酒で比較的早く改善するため、生活指導の効果を示す指標としても使える</v>
-      </c>
-      <c r="M19" t="str">
-        <v>肝機能</v>
-      </c>
-      <c r="N19" t="str">
-        <v>ガンマGTP,γ-GTP,GGT,肝機能,飲酒,アルコール</v>
-      </c>
-      <c r="O19" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>総ビリルビン</v>
-      </c>
-      <c r="B20" t="str">
-        <v>T-Bil</v>
-      </c>
-      <c r="C20" t="str">
-        <v>0.2〜1.2 mg/dL</v>
-      </c>
-      <c r="D20" t="str">
-        <v>赤血球が壊れてできる黄色い色素の総量。肝臓・胆道の状態や黄疸の指標</v>
-      </c>
-      <c r="E20" t="str">
-        <v>ビリルビンは赤血球が寿命を迎えて壊れるときにできる黄色い色素です。肝臓で処理されて排泄されますが、肝臓や胆道にトラブルがあると血液中に増え、皮膚や白目が黄色くなる黄疸として現れます。</v>
-      </c>
-      <c r="F20" t="str">
-        <v>肝炎・肝硬変などの肝疾患、胆道閉塞（胆石・腫瘍など）、溶血性疾患（赤血球の破壊亢進）、体質性黄疸（ジルベール症候群など）</v>
-      </c>
-      <c r="G20" t="str">
-        <v>皮膚や白目の黄染、尿の色が濃くなっていないか確認する。かゆみを伴う場合は胆汁うっ滞の可能性もあるため皮膚症状もあわせて聞く</v>
-      </c>
-      <c r="H20" t="str">
-        <v>肝毒性のある薬剤全般に加え、シクロスポリン・リファンピシン(トランスポーター阻害による上昇)</v>
-      </c>
-      <c r="I20" t="str">
-        <v/>
-      </c>
-      <c r="J20" t="str">
-        <v/>
-      </c>
-      <c r="K20" t="str">
-        <v/>
-      </c>
-      <c r="L20" t="str">
-        <v>直接ビリルビン・間接ビリルビンの内訳で原因を推測できる（直接優位は胆道系、間接優位は溶血・体質性）。AST/ALT/γ-GTPと合わせて評価する</v>
-      </c>
-      <c r="M20" t="str">
-        <v>肝機能</v>
-      </c>
-      <c r="N20" t="str">
-        <v>総ビリルビン,T-Bil,黄疸,ビリルビン,ジルベール症候群</v>
-      </c>
-      <c r="O20" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>総タンパク</v>
-      </c>
-      <c r="B21" t="str">
-        <v>TP</v>
-      </c>
-      <c r="C21" t="str">
-        <v>6.6〜8.1 g/dL</v>
-      </c>
-      <c r="D21" t="str">
-        <v>血液中のたんぱく質（アルブミン＋グロブリン）の総量。栄養状態や肝機能、炎症の目安</v>
-      </c>
-      <c r="E21" t="str">
-        <v>総タンパクは、血液中のたんぱく質の合計量です。栄養状態や肝臓の働き、体の炎症の有無などを反映します。</v>
-      </c>
-      <c r="F21" t="str">
-        <v>脱水、多発性骨髄腫など（グロブリン増加）、慢性炎症</v>
-      </c>
-      <c r="G21" t="str">
-        <v/>
-      </c>
-      <c r="H21" t="str">
-        <v/>
-      </c>
-      <c r="I21" t="str">
-        <v>低栄養、肝機能低下（アルブミン産生低下）、ネフローゼ症候群、消化管からのたんぱく漏出</v>
-      </c>
-      <c r="J21" t="str">
-        <v>食事摂取量、特にたんぱく質(肉・魚・卵・大豆製品)を確認する。むくみが出ていないかもあわせて確認する</v>
-      </c>
-      <c r="K21" t="str">
-        <v/>
-      </c>
-      <c r="L21" t="str">
-        <v>アルブミンとグロブリンの内訳（A/G比）も合わせて確認すると原因の絞り込みに役立つ。低栄養か肝機能低下かはアルブミンの値と合わせて判断する</v>
-      </c>
-      <c r="M21" t="str">
-        <v>肝機能</v>
-      </c>
-      <c r="N21" t="str">
-        <v>総タンパク,TP,総蛋白,栄養状態,A/G比</v>
-      </c>
-      <c r="O21" t="str">
-        <v>食事と栄養 p.23（たんぱく質）</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>アルブミン</v>
-      </c>
-      <c r="B22" t="str">
-        <v>Alb</v>
-      </c>
-      <c r="C22" t="str">
-        <v>3.8〜5.2 g/dL</v>
-      </c>
-      <c r="D22" t="str">
-        <v>体の栄養状態を見る目安になるたんぱく質。血液の中で栄養を運ぶ、水分を血管の中に保つという働きをしている。</v>
-      </c>
-      <c r="E22" t="str">
-        <v>アルブミンは栄養の状態を見る数値です。食事量が少なかったり、肝臓や腎臓、腸の働きが弱ると下がることがあります。数値が低いと、むくみが出やすくなります。</v>
-      </c>
-      <c r="F22" t="str">
-        <v>脱水（見かけ上の上昇）</v>
-      </c>
-      <c r="G22" t="str">
-        <v/>
-      </c>
-      <c r="H22" t="str">
-        <v/>
-      </c>
-      <c r="I22" t="str">
-        <v>低栄養／肝機能低下／ネフローゼ症候群／クローン病</v>
-      </c>
-      <c r="J22" t="str">
-        <v>主食に偏らず、肉・魚・卵・大豆製品などたんぱく質をしっかり摂るよう伝える。食欲が落ちている場合は少量頻回の食事や、間食に乳製品・卵を取り入れるなど無理のない工夫を提案し、むくみの有無もあわせて確認する</v>
-      </c>
-      <c r="K22" t="str">
-        <v>蛋白結合率の高い薬剤(ワルファリン、フェニトイン、NSAIDs等)は遊離型濃度が上昇し、効果や副作用が増強しやすいため用量に注意</v>
-      </c>
-      <c r="L22" t="str">
-        <v>3前半は注意ライン。食事摂取量を必ず確認</v>
-      </c>
-      <c r="M22" t="str">
-        <v>肝機能,栄養,腎機能</v>
-      </c>
-      <c r="N22" t="str">
-        <v>アルブミン,Alb,むくみ,浮腫,栄養状態</v>
-      </c>
-      <c r="O22" t="str">
-        <v>食事と栄養 p.23（たんぱく質）／p.242（フレイルQ110 アルブミン値を上げる食事指導）</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>A/G</v>
-      </c>
-      <c r="B23" t="str">
-        <v>A/G比</v>
-      </c>
-      <c r="C23" t="str">
-        <v>1.1〜2.0程度(施設差あり)</v>
-      </c>
-      <c r="D23" t="str">
-        <v>血液中のアルブミンとグロブリンの比率。肝機能や炎症、免疫の状態を反映する</v>
-      </c>
-      <c r="E23" t="str">
-        <v>A/G比は、血液中のたんぱく質のうちアルブミンとグロブリンという2種類の比率を見る数値です。肝臓の働きが落ちたり、体に炎症や免疫の異常があったりすると、このバランスが崩れることがあります。</v>
-      </c>
-      <c r="F23" t="str">
-        <v>通常、臨床的意義は乏しい(まれに無ガンマグロブリン血症など)</v>
-      </c>
-      <c r="G23" t="str">
-        <v/>
-      </c>
-      <c r="H23" t="str">
-        <v/>
-      </c>
-      <c r="I23" t="str">
-        <v>肝硬変などの肝機能低下(アルブミン産生低下)、慢性炎症・感染症、多発性骨髄腫などの血液疾患(グロブリン増加)、ネフローゼ症候群</v>
-      </c>
-      <c r="J23" t="str">
-        <v>食事摂取量やむくみの有無を確認する。慢性炎症や感染の有無もあわせて確認する</v>
-      </c>
-      <c r="K23" t="str">
-        <v/>
-      </c>
-      <c r="L23" t="str">
-        <v>A/G比＝アルブミン÷(総タンパク－アルブミン)で算出する。低下はアルブミンが減った場合とグロブリンが増えた場合の両方で起こるため、総タンパク・アルブミンの実測値とあわせて原因を判断する</v>
       </c>
       <c r="M23" t="str">
         <v>肝機能</v>
       </c>
       <c r="N23" t="str">
-        <v>A/G,A/G比,アルブミングロブリン比,肝機能,多発性骨髄腫</v>
+        <v>ガンマGTP,γ-GTP,GGT,肝機能,飲酒,アルコール</v>
       </c>
       <c r="O23" t="str">
         <v/>
@@ -1506,31 +1506,31 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>アンモニア</v>
+        <v>総ビリルビン</v>
       </c>
       <c r="B24" t="str">
-        <v>NH3</v>
+        <v>T-Bil</v>
       </c>
       <c r="C24" t="str">
-        <v>12〜66 μg/dL（施設差あり／空腹時採血が望ましい）</v>
+        <v>0.2〜1.2 mg/dL</v>
       </c>
       <c r="D24" t="str">
-        <v>肝機能低下や門脈シャントなどで代謝・排泄が低下すると上昇し、意識障害（肝性脳症）の原因となる</v>
+        <v>赤血球が壊れてできる黄色い色素の総量。肝臓・胆道の状態や黄疸の指標</v>
       </c>
       <c r="E24" t="str">
-        <v>アンモニアは体の中でタンパク質が分解されるときにできる老廃物で、通常は肝臓で無害な尿素に変えられて尿として排泄されます。肝臓の働きが弱っていたり血液の流れ道に変化があると、アンモニアがうまく処理されず血液中にたまり、頭がぼんやりしたり意識がもうろうとする原因になることがあります。</v>
+        <v>ビリルビンは赤血球が寿命を迎えて壊れるときにできる黄色い色素です。肝臓で処理されて排泄されますが、肝臓や胆道にトラブルがあると血液中に増え、皮膚や白目が黄色くなる黄疸として現れます。</v>
       </c>
       <c r="F24" t="str">
-        <v>肝硬変・肝不全（門脈-大循環シャント含む）、劇症肝炎、消化管出血、便秘、脱水、高たんぱく食、尿素サイクル異常症、一部薬剤（バルプロ酸など）</v>
+        <v>肝炎・肝硬変などの肝疾患、胆道閉塞（胆石・腫瘍など）、溶血性疾患（赤血球の破壊亢進）、体質性黄疸（ジルベール症候群など）</v>
       </c>
       <c r="G24" t="str">
-        <v>便秘の解消(排便コントロール)を心がける。ラクツロースやリファキシミンなど肝性脳症治療薬の服薬状況を確認し、意識のもうろう感や日中の眠気の変化にも注意する</v>
+        <v>皮膚や白目の黄染、尿の色が濃くなっていないか確認する。かゆみを伴う場合は胆汁うっ滞の可能性もあるため皮膚症状もあわせて聞く</v>
       </c>
       <c r="H24" t="str">
-        <v>バルプロ酸(デパケン等)</v>
+        <v>肝毒性のある薬剤全般に加え、シクロスポリン・リファンピシン(トランスポーター阻害による上昇)</v>
       </c>
       <c r="I24" t="str">
-        <v>通常、臨床的意義は乏しい</v>
+        <v/>
       </c>
       <c r="J24" t="str">
         <v/>
@@ -1539,13 +1539,13 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>バルプロ酸(デパケン等)は肝疾患の既往がなくても高アンモニア血症を起こすことがあり、意識障害・傾眠が出現した場合は薬剤性を疑ってアンモニア値を確認する。採血後は室温放置で見かけ上上昇するため測定条件にも注意。ラクツロース・リファキシミンは腸管内でのアンモニア産生・吸収を抑える目的で使用される</v>
+        <v>直接ビリルビン・間接ビリルビンの内訳で原因を推測できる（直接優位は胆道系、間接優位は溶血・体質性）。AST/ALT/γ-GTPと合わせて評価する</v>
       </c>
       <c r="M24" t="str">
         <v>肝機能</v>
       </c>
       <c r="N24" t="str">
-        <v>アンモニア,NH3,肝性脳症,バルプロ酸,門脈シャント</v>
+        <v>総ビリルビン,T-Bil,黄疸,ビリルビン,ジルベール症候群</v>
       </c>
       <c r="O24" t="str">
         <v/>
@@ -1553,361 +1553,361 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>中性脂肪（トリグリセリド）</v>
+        <v>総タンパク</v>
       </c>
       <c r="B25" t="str">
-        <v>TG</v>
+        <v>TP</v>
       </c>
       <c r="C25" t="str">
-        <v>150 mg/dL未満（空腹時）</v>
+        <v>6.6〜8.1 g/dL</v>
       </c>
       <c r="D25" t="str">
-        <v>脂質異常症で高値になりやすい脂質で、食事の影響を強く受ける</v>
+        <v>血液中のたんぱく質（アルブミン＋グロブリン）の総量。栄養状態や肝機能、炎症の目安</v>
       </c>
       <c r="E25" t="str">
-        <v>中性脂肪は、食事から摂った脂肪や糖質が体に蓄えられる形になったものです。食後は誰でも一時的に上がるため、正確に評価するには空腹時に採血することが大切です。高い状態が続くと動脈硬化や急性膵炎のリスクが高まります。</v>
+        <v>総タンパクは、血液中のたんぱく質の合計量です。栄養状態や肝臓の働き、体の炎症の有無などを反映します。</v>
       </c>
       <c r="F25" t="str">
-        <v>脂質異常症、糖質・アルコールの摂りすぎ、肥満、糖尿病のコントロール不良</v>
+        <v>脱水、多発性骨髄腫など（グロブリン増加）、慢性炎症</v>
       </c>
       <c r="G25" t="str">
-        <v>糖質・アルコールの摂りすぎに注意し、ウォーキングなどの有酸素運動を週150分程度を目安に勧める。清涼飲料水や果物の摂りすぎにも注意する</v>
+        <v/>
       </c>
       <c r="H25" t="str">
-        <v>非定型抗精神病薬(オランザピン・クエチアピン)、ステロイド、エストロゲン製剤、非選択的β遮断薬、サイアザイド系利尿薬、タモキシフェン</v>
+        <v/>
       </c>
       <c r="I25" t="str">
-        <v>低栄養、甲状腺機能亢進症</v>
+        <v>低栄養、肝機能低下（アルブミン産生低下）、ネフローゼ症候群、消化管からのたんぱく漏出</v>
       </c>
       <c r="J25" t="str">
-        <v/>
+        <v>食事摂取量、特にたんぱく質(肉・魚・卵・大豆製品)を確認する。むくみが出ていないかもあわせて確認する</v>
       </c>
       <c r="K25" t="str">
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>採血が食後か空腹時かで数値が大きく変わるため必ず確認する。500 mg/dL以上では急性膵炎のリスクが高まるため注意。フィブラート系・EPA製剤などの効果判定に使う</v>
+        <v>アルブミンとグロブリンの内訳（A/G比）も合わせて確認すると原因の絞り込みに役立つ。低栄養か肝機能低下かはアルブミンの値と合わせて判断する</v>
       </c>
       <c r="M25" t="str">
-        <v>脂質異常症</v>
+        <v>肝機能</v>
       </c>
       <c r="N25" t="str">
-        <v>中性脂肪,トリグリセリド,TG,脂質異常症</v>
+        <v>総タンパク,TP,総蛋白,栄養状態,A/G比</v>
       </c>
       <c r="O25" t="str">
-        <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
+        <v>食事と栄養 p.23（たんぱく質）</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
+        <v>アルブミン</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Alb</v>
+      </c>
+      <c r="C26" t="str">
+        <v>3.8〜5.2 g/dL</v>
+      </c>
+      <c r="D26" t="str">
+        <v>体の栄養状態を見る目安になるたんぱく質。血液の中で栄養を運ぶ、水分を血管の中に保つという働きをしている。</v>
+      </c>
+      <c r="E26" t="str">
+        <v>アルブミンは栄養の状態を見る数値です。食事量が少なかったり、肝臓や腎臓、腸の働きが弱ると下がることがあります。数値が低いと、むくみが出やすくなります。</v>
+      </c>
+      <c r="F26" t="str">
+        <v>脱水（見かけ上の上昇）</v>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
+      <c r="I26" t="str">
+        <v>低栄養／肝機能低下／ネフローゼ症候群／クローン病</v>
+      </c>
+      <c r="J26" t="str">
+        <v>主食に偏らず、肉・魚・卵・大豆製品などたんぱく質をしっかり摂るよう伝える。食欲が落ちている場合は少量頻回の食事や、間食に乳製品・卵を取り入れるなど無理のない工夫を提案し、むくみの有無もあわせて確認する</v>
+      </c>
+      <c r="K26" t="str">
+        <v>蛋白結合率の高い薬剤(ワルファリン、フェニトイン、NSAIDs等)は遊離型濃度が上昇し、効果や副作用が増強しやすいため用量に注意</v>
+      </c>
+      <c r="L26" t="str">
+        <v>3前半は注意ライン。食事摂取量を必ず確認</v>
+      </c>
+      <c r="M26" t="str">
+        <v>肝機能,栄養,腎機能</v>
+      </c>
+      <c r="N26" t="str">
+        <v>アルブミン,Alb,むくみ,浮腫,栄養状態</v>
+      </c>
+      <c r="O26" t="str">
+        <v>食事と栄養 p.23（たんぱく質）／p.242（フレイルQ110 アルブミン値を上げる食事指導）</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>A/G</v>
+      </c>
+      <c r="B27" t="str">
+        <v>A/G比</v>
+      </c>
+      <c r="C27" t="str">
+        <v>1.1〜2.0程度(施設差あり)</v>
+      </c>
+      <c r="D27" t="str">
+        <v>血液中のアルブミンとグロブリンの比率。肝機能や炎症、免疫の状態を反映する</v>
+      </c>
+      <c r="E27" t="str">
+        <v>A/G比は、血液中のたんぱく質のうちアルブミンとグロブリンという2種類の比率を見る数値です。肝臓の働きが落ちたり、体に炎症や免疫の異常があったりすると、このバランスが崩れることがあります。</v>
+      </c>
+      <c r="F27" t="str">
+        <v>通常、臨床的意義は乏しい(まれに無ガンマグロブリン血症など)</v>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
+      <c r="H27" t="str">
+        <v/>
+      </c>
+      <c r="I27" t="str">
+        <v>肝硬変などの肝機能低下(アルブミン産生低下)、慢性炎症・感染症、多発性骨髄腫などの血液疾患(グロブリン増加)、ネフローゼ症候群</v>
+      </c>
+      <c r="J27" t="str">
+        <v>食事摂取量やむくみの有無を確認する。慢性炎症や感染の有無もあわせて確認する</v>
+      </c>
+      <c r="K27" t="str">
+        <v/>
+      </c>
+      <c r="L27" t="str">
+        <v>A/G比＝アルブミン÷(総タンパク－アルブミン)で算出する。低下はアルブミンが減った場合とグロブリンが増えた場合の両方で起こるため、総タンパク・アルブミンの実測値とあわせて原因を判断する</v>
+      </c>
+      <c r="M27" t="str">
+        <v>肝機能</v>
+      </c>
+      <c r="N27" t="str">
+        <v>A/G,A/G比,アルブミングロブリン比,肝機能,多発性骨髄腫</v>
+      </c>
+      <c r="O27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>アンモニア</v>
+      </c>
+      <c r="B28" t="str">
+        <v>NH3</v>
+      </c>
+      <c r="C28" t="str">
+        <v>12〜66 μg/dL（施設差あり／空腹時採血が望ましい）</v>
+      </c>
+      <c r="D28" t="str">
+        <v>肝機能低下や門脈シャントなどで代謝・排泄が低下すると上昇し、意識障害（肝性脳症）の原因となる</v>
+      </c>
+      <c r="E28" t="str">
+        <v>アンモニアは体の中でタンパク質が分解されるときにできる老廃物で、通常は肝臓で無害な尿素に変えられて尿として排泄されます。肝臓の働きが弱っていたり血液の流れ道に変化があると、アンモニアがうまく処理されず血液中にたまり、頭がぼんやりしたり意識がもうろうとする原因になることがあります。</v>
+      </c>
+      <c r="F28" t="str">
+        <v>肝硬変・肝不全（門脈-大循環シャント含む）、劇症肝炎、消化管出血、便秘、脱水、高たんぱく食、尿素サイクル異常症、一部薬剤（バルプロ酸など）</v>
+      </c>
+      <c r="G28" t="str">
+        <v>便秘の解消(排便コントロール)を心がける。ラクツロースやリファキシミンなど肝性脳症治療薬の服薬状況を確認し、意識のもうろう感や日中の眠気の変化にも注意する</v>
+      </c>
+      <c r="H28" t="str">
+        <v>バルプロ酸(デパケン等)</v>
+      </c>
+      <c r="I28" t="str">
+        <v>通常、臨床的意義は乏しい</v>
+      </c>
+      <c r="J28" t="str">
+        <v/>
+      </c>
+      <c r="K28" t="str">
+        <v/>
+      </c>
+      <c r="L28" t="str">
+        <v>バルプロ酸(デパケン等)は肝疾患の既往がなくても高アンモニア血症を起こすことがあり、意識障害・傾眠が出現した場合は薬剤性を疑ってアンモニア値を確認する。採血後は室温放置で見かけ上上昇するため測定条件にも注意。ラクツロース・リファキシミンは腸管内でのアンモニア産生・吸収を抑える目的で使用される</v>
+      </c>
+      <c r="M28" t="str">
+        <v>肝機能</v>
+      </c>
+      <c r="N28" t="str">
+        <v>アンモニア,NH3,肝性脳症,バルプロ酸,門脈シャント</v>
+      </c>
+      <c r="O28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>中性脂肪（トリグリセリド）</v>
+      </c>
+      <c r="B29" t="str">
+        <v>TG</v>
+      </c>
+      <c r="C29" t="str">
+        <v>150 mg/dL未満（空腹時）</v>
+      </c>
+      <c r="D29" t="str">
+        <v>脂質異常症で高値になりやすい脂質で、食事の影響を強く受ける</v>
+      </c>
+      <c r="E29" t="str">
+        <v>中性脂肪は、食事から摂った脂肪や糖質が体に蓄えられる形になったものです。食後は誰でも一時的に上がるため、正確に評価するには空腹時に採血することが大切です。高い状態が続くと動脈硬化や急性膵炎のリスクが高まります。</v>
+      </c>
+      <c r="F29" t="str">
+        <v>脂質異常症、糖質・アルコールの摂りすぎ、肥満、糖尿病のコントロール不良</v>
+      </c>
+      <c r="G29" t="str">
+        <v>糖質・アルコールの摂りすぎに注意し、ウォーキングなどの有酸素運動を週150分程度を目安に勧める。清涼飲料水や果物の摂りすぎにも注意する</v>
+      </c>
+      <c r="H29" t="str">
+        <v>非定型抗精神病薬(オランザピン・クエチアピン)、ステロイド、エストロゲン製剤、非選択的β遮断薬、サイアザイド系利尿薬、タモキシフェン</v>
+      </c>
+      <c r="I29" t="str">
+        <v>低栄養、甲状腺機能亢進症</v>
+      </c>
+      <c r="J29" t="str">
+        <v/>
+      </c>
+      <c r="K29" t="str">
+        <v/>
+      </c>
+      <c r="L29" t="str">
+        <v>採血が食後か空腹時かで数値が大きく変わるため必ず確認する。500 mg/dL以上では急性膵炎のリスクが高まるため注意。フィブラート系・EPA製剤などの効果判定に使う</v>
+      </c>
+      <c r="M29" t="str">
+        <v>脂質異常症</v>
+      </c>
+      <c r="N29" t="str">
+        <v>中性脂肪,トリグリセリド,TG,脂質異常症</v>
+      </c>
+      <c r="O29" t="str">
+        <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
         <v>総コレステロール</v>
       </c>
-      <c r="B26" t="str">
+      <c r="B30" t="str">
         <v>TC,T-cho</v>
       </c>
-      <c r="C26" t="str">
+      <c r="C30" t="str">
         <v>220 mg/dL未満</v>
       </c>
-      <c r="D26" t="str">
+      <c r="D30" t="str">
         <v>LDL・HDLなどすべてのコレステロールを合わせた総量</v>
       </c>
-      <c r="E26" t="str">
+      <c r="E30" t="str">
         <v>総コレステロールは、体の中にあるコレステロールをすべて合わせた数値です。ただし、悪玉(LDL)が多いのか善玉(HDL)が多いのかまでは分からないため、実際の評価にはLDLコレステロールの値がより重視されます。</v>
       </c>
-      <c r="F26" t="str">
+      <c r="F30" t="str">
         <v>脂質異常症、家族性高コレステロール血症、甲状腺機能低下症</v>
       </c>
-      <c r="G26" t="str">
+      <c r="G30" t="str">
         <v>動物性脂肪を控え、食物繊維(野菜・海藻・きのこ)を増やすよう伝える。青魚に含まれる油(EPA・DHA)を意識的に摂ることも勧める</v>
       </c>
-      <c r="H26" t="str">
+      <c r="H30" t="str">
         <v>非定型抗精神病薬、ステロイド、サイアザイド系利尿薬、非選択的β遮断薬</v>
       </c>
-      <c r="I26" t="str">
+      <c r="I30" t="str">
         <v>低栄養、肝機能低下、甲状腺機能亢進症</v>
       </c>
-      <c r="J26" t="str">
-        <v/>
-      </c>
-      <c r="K26" t="str">
-        <v/>
-      </c>
-      <c r="L26" t="str">
+      <c r="J30" t="str">
+        <v/>
+      </c>
+      <c r="K30" t="str">
+        <v/>
+      </c>
+      <c r="L30" t="str">
         <v>現在はLDLコレステロールでの評価が主流。総コレステロールだけでは悪玉・善玉の内訳が分からないため、LDL・HDL・中性脂肪と合わせて評価する</v>
       </c>
-      <c r="M26" t="str">
+      <c r="M30" t="str">
         <v>脂質異常症</v>
       </c>
-      <c r="N26" t="str">
+      <c r="N30" t="str">
         <v>総コレステロール,TC,コレステロール,脂質異常症</v>
       </c>
-      <c r="O26" t="str">
+      <c r="O30" t="str">
         <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
       </c>
     </row>
-    <row r="27" xml:space="preserve">
-      <c r="A27" t="str">
+    <row r="31" xml:space="preserve">
+      <c r="A31" t="str">
         <v>LDLコレステロール</v>
       </c>
-      <c r="B27" t="str">
+      <c r="B31" t="str">
         <v>LDL-C</v>
       </c>
-      <c r="C27" t="str" xml:space="preserve">
+      <c r="C31" t="str" xml:space="preserve">
         <v xml:space="preserve">60〜139 mg/dL
 （140 mg/dL以上で高LDLコレステロール血症）</v>
       </c>
-      <c r="D27" t="str">
+      <c r="D31" t="str">
         <v>いわゆる「悪玉コレステロール」。血管の壁にたまり動脈硬化を進める</v>
       </c>
-      <c r="E27" t="str">
+      <c r="E31" t="str">
         <v>LDLコレステロールは、いわゆる悪玉コレステロールと呼ばれるものです。多いままだと血管の壁にたまって、動脈硬化や心筋梗塞・脳梗塞のリスクを高めます。数値を下げることで、将来の血管のトラブルを防ぐことが目的です。</v>
       </c>
-      <c r="F27" t="str">
+      <c r="F31" t="str">
         <v>脂質異常症、動脈硬化のリスク上昇、家族性高コレステロール血症、甲状腺機能低下症</v>
       </c>
-      <c r="G27" t="str">
+      <c r="G31" t="str">
         <v>動物性脂肪や揚げ物を控え、青魚や食物繊維(野菜・海藻・きのこ)を増やすよう伝える。禁煙も動脈硬化予防に重要なことを伝える</v>
       </c>
-      <c r="H27" t="str">
+      <c r="H31" t="str">
         <v>ステロイド、サイアザイド系利尿薬、非選択的β遮断薬</v>
       </c>
-      <c r="I27" t="str">
+      <c r="I31" t="str">
         <v>低栄養、肝機能低下、甲状腺機能亢進症</v>
       </c>
-      <c r="J27" t="str">
-        <v/>
-      </c>
-      <c r="K27" t="str">
-        <v/>
-      </c>
-      <c r="L27" t="str">
+      <c r="J31" t="str">
+        <v/>
+      </c>
+      <c r="K31" t="str">
+        <v/>
+      </c>
+      <c r="L31" t="str">
         <v>スタチン等の効果判定に使う中心的な数値。目標値は既往疾患（冠動脈疾患・糖尿病等）によって異なるため一律に判断しない</v>
       </c>
-      <c r="M27" t="str">
+      <c r="M31" t="str">
         <v>脂質異常症,精神疾患（非定型抗精神病薬）</v>
       </c>
-      <c r="N27" t="str">
+      <c r="N31" t="str">
         <v>LDL,LDLコレステロール,悪玉コレステロール,脂質異常症</v>
       </c>
-      <c r="O27" t="str">
+      <c r="O31" t="str">
         <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v>nonHDLコレステロール</v>
-      </c>
-      <c r="B28" t="str">
-        <v>non-HDL-C</v>
-      </c>
-      <c r="C28" t="str">
-        <v>90〜149 mg/dL（150 mg/dL以上で高値）</v>
-      </c>
-      <c r="D28" t="str">
-        <v>総コレステロールからHDL（善玉）を除いた、動脈硬化を進めるすべての脂質の合計</v>
-      </c>
-      <c r="E28" t="str">
-        <v>nonHDLコレステロールは、総コレステロールから善玉のHDLを引いた数値で、LDL（悪玉）を含む、動脈硬化を進めるすべてのコレステロールの合計を表します。中性脂肪が高くLDLだけでは評価しにくい方でも、こちらで動脈硬化のリスクを評価できます。</v>
-      </c>
-      <c r="F28" t="str">
-        <v>脂質異常症、動脈硬化のリスク上昇（特に中性脂肪が高い場合にLDL-Cより実態を反映しやすい）</v>
-      </c>
-      <c r="G28" t="str">
-        <v>動物性脂肪や揚げ物を控え、青魚や食物繊維（野菜・海藻・きのこ）を増やすよう伝える</v>
-      </c>
-      <c r="H28" t="str">
-        <v/>
-      </c>
-      <c r="I28" t="str">
-        <v/>
-      </c>
-      <c r="J28" t="str">
-        <v/>
-      </c>
-      <c r="K28" t="str">
-        <v/>
-      </c>
-      <c r="L28" t="str">
-        <v>中性脂肪（TG）が400 mg/dL以上などLDL-Cの計算式（Friedewald式）が不正確になる場合に、LDL-Cの代わりに用いられる。目標値はLDL-Cの目標値＋30 mg/dLが目安</v>
-      </c>
-      <c r="M28" t="str">
-        <v>脂質異常症</v>
-      </c>
-      <c r="N28" t="str">
-        <v>nonHDL,non-HDLコレステロール,動脈硬化,中性脂肪,LDL計算式</v>
-      </c>
-      <c r="O28" t="str">
-        <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="str">
-        <v>HDLコレステロール</v>
-      </c>
-      <c r="B29" t="str">
-        <v>HDL-C</v>
-      </c>
-      <c r="C29" t="str">
-        <v>40 mg/dL以上</v>
-      </c>
-      <c r="D29" t="str">
-        <v>いわゆる「善玉コレステロール」。血管にたまった余分なコレステロールを回収する</v>
-      </c>
-      <c r="E29" t="str">
-        <v>HDLコレステロールは、いわゆる善玉コレステロールと呼ばれるものです。血管の壁にたまった余分なコレステロールを回収して肝臓に戻す働きがあり、数値が高いほど動脈硬化を防ぐ方向に働きます。</v>
-      </c>
-      <c r="F29" t="str">
-        <v/>
-      </c>
-      <c r="G29" t="str">
-        <v/>
-      </c>
-      <c r="H29" t="str">
-        <v/>
-      </c>
-      <c r="I29" t="str">
-        <v>脂質異常症（低HDL血症）</v>
-      </c>
-      <c r="J29" t="str">
-        <v>適度な有酸素運動(ウォーキング等)、禁煙を勧める。適正体重の維持もHDL改善に役立つことを伝える</v>
-      </c>
-      <c r="K29" t="str">
-        <v/>
-      </c>
-      <c r="L29" t="str">
-        <v>喫煙、運動不足、肥満で低下しやすい。禁煙・運動習慣の改善で上昇が期待できる。低HDLは動脈硬化のリスク因子として単独でも重視される</v>
-      </c>
-      <c r="M29" t="str">
-        <v>脂質異常症</v>
-      </c>
-      <c r="N29" t="str">
-        <v>HDL,HDLコレステロール,善玉コレステロール,脂質異常症</v>
-      </c>
-      <c r="O29" t="str">
-        <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="str">
-        <v>CK（クレアチンフォスフォキナーゼ）</v>
-      </c>
-      <c r="B30" t="str">
-        <v>CK,CPK</v>
-      </c>
-      <c r="C30" t="str">
-        <v>男性 60〜250 U/L、女性 50〜170 U/L</v>
-      </c>
-      <c r="D30" t="str">
-        <v>主に骨格筋・心筋に含まれる酵素。筋肉の損傷で血液中に漏れ出す</v>
-      </c>
-      <c r="E30" t="str">
-        <v>CKは筋肉の中にある酵素で、激しい運動や筋肉の病気、心筋梗塞などで筋肉の細胞がダメージを受けると血液中に漏れ出して数値が上がります。スタチン系のお薬の副作用（横紋筋融解症）のチェックにも使われます。</v>
-      </c>
-      <c r="F30" t="str">
-        <v>心筋梗塞、横紋筋融解症（スタチン系薬剤の副作用など）、激しい運動、筋肉注射直後、甲状腺機能低下症</v>
-      </c>
-      <c r="G30" t="str">
-        <v>筋肉痛・脱力感・褐色尿（横紋筋融解症の症状）がないか確認する。スタチン系薬剤服用中は特に注意する。激しい運動の直後の採血でないかも確認する</v>
-      </c>
-      <c r="H30" t="str">
-        <v>スタチン系(特にフィブラート系との併用時)、コルヒチン</v>
-      </c>
-      <c r="I30" t="str">
-        <v/>
-      </c>
-      <c r="J30" t="str">
-        <v/>
-      </c>
-      <c r="K30" t="str">
-        <v/>
-      </c>
-      <c r="L30" t="str">
-        <v>スタチン系薬剤の重大な副作用である横紋筋融解症の指標。筋肉痛・脱力感・褐色尿の有無を必ず確認し、著明高値では服薬継続の可否を医師に相談する</v>
-      </c>
-      <c r="M30" t="str">
-        <v/>
-      </c>
-      <c r="N30" t="str">
-        <v>CK,CPK,クレアチンキナーゼ,横紋筋融解症</v>
-      </c>
-      <c r="O30" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="str">
-        <v>BUN/CRE比</v>
-      </c>
-      <c r="B31" t="str">
-        <v>BUN/Cr</v>
-      </c>
-      <c r="C31" t="str">
-        <v>10前後が目安（施設差あり）</v>
-      </c>
-      <c r="D31" t="str">
-        <v>BUNとクレアチニンの比率。腎前性（脱水・出血など）か腎性かを見分ける目安になる</v>
-      </c>
-      <c r="E31" t="str">
-        <v>これは、BUN（尿素窒素）とクレアチニンという2つの腎機能に関わる検査値を比較したもので、腎臓そのものに問題があるのか、それとも脱水や出血など腎臓の外側に原因があるのかを見分ける手がかりになります。</v>
-      </c>
-      <c r="F31" t="str">
-        <v>脱水、消化管出血、高たんぱく食、心不全（腎臓への血流低下）</v>
-      </c>
-      <c r="G31" t="str">
-        <v>脱水が疑われる場合はこまめな水分摂取を勧める。黒い便など消化管出血を示唆する症状がないか確認する</v>
-      </c>
-      <c r="H31" t="str">
-        <v/>
-      </c>
-      <c r="I31" t="str">
-        <v>低たんぱく食、肝不全、妊娠</v>
-      </c>
-      <c r="J31" t="str">
-        <v/>
-      </c>
-      <c r="K31" t="str">
-        <v/>
-      </c>
-      <c r="L31" t="str">
-        <v>比が高い（目安20以上）場合は脱水や消化管出血など腎前性の要因を、比が正常範囲で両方高値なら腎性の障害を疑う。BUN単独やクレアチニン単独よりも病態の絞り込みに役立つ</v>
-      </c>
-      <c r="M31" t="str">
-        <v>腎機能</v>
-      </c>
-      <c r="N31" t="str">
-        <v>BUN/CRE,BUN/Cr,尿素窒素,クレアチニン,脱水,腎前性</v>
-      </c>
-      <c r="O31" t="str">
-        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>LDH/AST比</v>
+        <v>nonHDLコレステロール</v>
       </c>
       <c r="B32" t="str">
-        <v>LDH/AST</v>
+        <v>non-HDL-C</v>
       </c>
       <c r="C32" t="str">
-        <v>目安として使われる比率（施設差・カットオフ値の設定により異なる）</v>
+        <v>90〜149 mg/dL（150 mg/dL以上で高値）</v>
       </c>
       <c r="D32" t="str">
-        <v>LDHとASTの両方が上昇したときに、原因が肝臓か、それ以外（溶血・心筋・骨格筋）かを見分ける目安になる比</v>
+        <v>総コレステロールからHDL（善玉）を除いた、動脈硬化を進めるすべての脂質の合計</v>
       </c>
       <c r="E32" t="str">
-        <v>これは、肝臓の数値（AST）と、全身に広く分布する酵素（LDH）の比率を見るもので、両方の数値が上がっているときに、原因が肝臓なのか、それとも血液や筋肉など他の場所なのかを見分ける手がかりになります。</v>
+        <v>nonHDLコレステロールは、総コレステロールから善玉のHDLを引いた数値で、LDL（悪玉）を含む、動脈硬化を進めるすべてのコレステロールの合計を表します。中性脂肪が高くLDLだけでは評価しにくい方でも、こちらで動脈硬化のリスクを評価できます。</v>
       </c>
       <c r="F32" t="str">
-        <v>溶血性疾患、心筋梗塞、骨格筋の障害（比が高いほど肝臓以外が原因の可能性）</v>
+        <v>脂質異常症、動脈硬化のリスク上昇（特に中性脂肪が高い場合にLDL-Cより実態を反映しやすい）</v>
       </c>
       <c r="G32" t="str">
-        <v/>
+        <v>動物性脂肪や揚げ物を控え、青魚や食物繊維（野菜・海藻・きのこ）を増やすよう伝える</v>
       </c>
       <c r="H32" t="str">
         <v/>
       </c>
       <c r="I32" t="str">
-        <v>急性肝炎などの肝細胞障害（比が低い、つまりASTに対してLDHが相対的に低い場合は肝性が示唆される）</v>
+        <v/>
       </c>
       <c r="J32" t="str">
         <v/>
@@ -1916,89 +1916,89 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>AST・LDHが同時に上昇した際の鑑別に使う目安の一つ。単独の検査値ではなく計算上の比率であり、確定診断には他の検査（ビリルビン、CK、心筋マーカーなど）と合わせた評価が必要</v>
+        <v>中性脂肪（TG）が400 mg/dL以上などLDL-Cの計算式（Friedewald式）が不正確になる場合に、LDL-Cの代わりに用いられる。目標値はLDL-Cの目標値＋30 mg/dLが目安</v>
       </c>
       <c r="M32" t="str">
-        <v/>
+        <v>脂質異常症</v>
       </c>
       <c r="N32" t="str">
-        <v>LDH/AST,LDH,AST,溶血,心筋梗塞,肝炎</v>
+        <v>nonHDL,non-HDLコレステロール,動脈硬化,中性脂肪,LDL計算式</v>
       </c>
       <c r="O32" t="str">
-        <v/>
+        <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>CK/AST比</v>
+        <v>HDLコレステロール</v>
       </c>
       <c r="B33" t="str">
-        <v>CK/AST</v>
+        <v>HDL-C</v>
       </c>
       <c r="C33" t="str">
-        <v>目安として使われる比率（施設差・カットオフ値の設定により異なる）</v>
+        <v>40 mg/dL以上</v>
       </c>
       <c r="D33" t="str">
-        <v>ASTが上昇したときに、原因が筋肉（CKも上昇）か、それ以外（肝臓など）かを見分ける目安になる比</v>
+        <v>いわゆる「善玉コレステロール」。血管にたまった余分なコレステロールを回収する</v>
       </c>
       <c r="E33" t="str">
-        <v>これは、筋肉の数値（CK）と肝臓の数値（AST）を比べることで、ASTの上昇が筋肉由来なのか、肝臓由来なのかを見分ける手がかりになる比率です。</v>
+        <v>HDLコレステロールは、いわゆる善玉コレステロールと呼ばれるものです。血管の壁にたまった余分なコレステロールを回収して肝臓に戻す働きがあり、数値が高いほど動脈硬化を防ぐ方向に働きます。</v>
       </c>
       <c r="F33" t="str">
-        <v>横紋筋融解症、心筋梗塞、激しい運動など筋肉由来のAST上昇（CKも同時に高値）</v>
+        <v/>
       </c>
       <c r="G33" t="str">
-        <v>筋肉痛や脱力感、褐色尿などの症状がないか確認する</v>
+        <v/>
       </c>
       <c r="H33" t="str">
         <v/>
       </c>
       <c r="I33" t="str">
-        <v/>
+        <v>脂質異常症（低HDL血症）</v>
       </c>
       <c r="J33" t="str">
-        <v/>
+        <v>適度な有酸素運動(ウォーキング等)、禁煙を勧める。適正体重の維持もHDL改善に役立つことを伝える</v>
       </c>
       <c r="K33" t="str">
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>ASTのみ上昇しCKが正常であれば肝臓由来を、両方上昇していれば筋肉由来を疑う手がかりになる。スタチン系薬剤による横紋筋融解症が疑われる場面での鑑別に有用</v>
+        <v>喫煙、運動不足、肥満で低下しやすい。禁煙・運動習慣の改善で上昇が期待できる。低HDLは動脈硬化のリスク因子として単独でも重視される</v>
       </c>
       <c r="M33" t="str">
-        <v/>
+        <v>脂質異常症</v>
       </c>
       <c r="N33" t="str">
-        <v>CK/AST,CK,AST,横紋筋融解症,スタチン</v>
+        <v>HDL,HDLコレステロール,善玉コレステロール,脂質異常症</v>
       </c>
       <c r="O33" t="str">
-        <v/>
+        <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Na-Cl（ナトリウム・クロール差）</v>
+        <v>CK（クレアチンフォスフォキナーゼ）</v>
       </c>
       <c r="B34" t="str">
-        <v>Na-Cl</v>
+        <v>CK,CPK</v>
       </c>
       <c r="C34" t="str">
-        <v>36前後が目安（施設差あり）</v>
+        <v>男性 60〜250 U/L、女性 50〜170 U/L</v>
       </c>
       <c r="D34" t="str">
-        <v>ナトリウムからクロールを引いた値。アニオンギャップの簡易的な目安として使われる</v>
+        <v>主に骨格筋・心筋に含まれる酵素。筋肉の損傷で血液中に漏れ出す</v>
       </c>
       <c r="E34" t="str">
-        <v>この数値は、ナトリウムとクロールの検査値の差から計算されるもので、体の中に通常とは違う酸（アニオン）がたまっていないかを大まかに見積もるために使われます。</v>
+        <v>CKは筋肉の中にある酵素で、激しい運動や筋肉の病気、心筋梗塞などで筋肉の細胞がダメージを受けると血液中に漏れ出して数値が上がります。スタチン系のお薬の副作用（横紋筋融解症）のチェックにも使われます。</v>
       </c>
       <c r="F34" t="str">
-        <v>代謝性アシドーシス（乳酸アシドーシス、糖尿病性ケトアシドーシス、腎不全など、体内に有機酸がたまる病態）</v>
+        <v>心筋梗塞、横紋筋融解症（スタチン系薬剤の副作用など）、激しい運動、筋肉注射直後、甲状腺機能低下症</v>
       </c>
       <c r="G34" t="str">
-        <v/>
+        <v>筋肉痛・脱力感・褐色尿（横紋筋融解症の症状）がないか確認する。スタチン系薬剤服用中は特に注意する。激しい運動の直後の採血でないかも確認する</v>
       </c>
       <c r="H34" t="str">
-        <v/>
+        <v>スタチン系(特にフィブラート系との併用時)、コルヒチン</v>
       </c>
       <c r="I34" t="str">
         <v/>
@@ -2010,13 +2010,13 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>本来のアニオンギャップ(Na-(Cl+HCO3))の簡易代用として使われることがあるが、重炭酸(HCO3)を用いた計算の方が正確。メトホルミン使用中の乳酸アシドーシスが疑われる場面などで参考にする</v>
+        <v>スタチン系薬剤の重大な副作用である横紋筋融解症の指標。筋肉痛・脱力感・褐色尿の有無を必ず確認し、著明高値では服薬継続の可否を医師に相談する</v>
       </c>
       <c r="M34" t="str">
-        <v>電解質</v>
+        <v/>
       </c>
       <c r="N34" t="str">
-        <v>Na-Cl,アニオンギャップ,AG,代謝性アシドーシス,乳酸アシドーシス</v>
+        <v>CK,CPK,クレアチンキナーゼ,横紋筋融解症</v>
       </c>
       <c r="O34" t="str">
         <v/>
@@ -2024,31 +2024,31 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>AST/ALT比</v>
+        <v>BUN/CRE比</v>
       </c>
       <c r="B35" t="str">
-        <v>AST/ALT,De Ritis比</v>
+        <v>BUN/Cr</v>
       </c>
       <c r="C35" t="str">
-        <v>1未満が目安（施設・病態により異なる）</v>
+        <v>10前後が目安（施設差あり）</v>
       </c>
       <c r="D35" t="str">
-        <v>ASTとALTの比率（De Ritis比）。肝疾患の種類を推測する手がかりになる</v>
+        <v>BUNとクレアチニンの比率。腎前性（脱水・出血など）か腎性かを見分ける目安になる</v>
       </c>
       <c r="E35" t="str">
-        <v>これは、肝臓に関わる2つの数値（ASTとALT）の比率を見るもので、肝臓のどのようなタイプのトラブルが起きているかを推測する手がかりになります。</v>
+        <v>これは、BUN（尿素窒素）とクレアチニンという2つの腎機能に関わる検査値を比較したもので、腎臓そのものに問題があるのか、それとも脱水や出血など腎臓の外側に原因があるのかを見分ける手がかりになります。</v>
       </c>
       <c r="F35" t="str">
-        <v>アルコール性肝障害、肝硬変、心筋梗塞・筋疾患の合併（比が2以上でアルコール性を強く示唆）</v>
+        <v>脱水、消化管出血、高たんぱく食、心不全（腎臓への血流低下）</v>
       </c>
       <c r="G35" t="str">
-        <v>飲酒量や頻度を確認する</v>
+        <v>脱水が疑われる場合はこまめな水分摂取を勧める。黒い便など消化管出血を示唆する症状がないか確認する</v>
       </c>
       <c r="H35" t="str">
         <v/>
       </c>
       <c r="I35" t="str">
-        <v>急性ウイルス性肝炎、脂肪肝（比が1未満で肝細胞の急性障害を示唆することが多い）</v>
+        <v>低たんぱく食、肝不全、妊娠</v>
       </c>
       <c r="J35" t="str">
         <v/>
@@ -2057,13 +2057,13 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>De Ritis比とも呼ばれる。比が2以上はアルコール性肝障害や肝硬変を、1未満は急性ウイルス性肝炎や脂肪肝を示唆する目安になるが、確定診断には他の検査所見と合わせた評価が必要</v>
+        <v>比が高い（目安20以上）場合は脱水や消化管出血など腎前性の要因を、比が正常範囲で両方高値なら腎性の障害を疑う。BUN単独やクレアチニン単独よりも病態の絞り込みに役立つ</v>
       </c>
       <c r="M35" t="str">
-        <v>肝機能</v>
+        <v>腎機能</v>
       </c>
       <c r="N35" t="str">
-        <v>AST/ALT比,AST/ALT,De Ritis比,デリティス比,アルコール性肝障害,肝硬変</v>
+        <v>BUN/CRE,BUN/Cr,尿素窒素,クレアチニン,脱水,腎前性</v>
       </c>
       <c r="O35" t="str">
         <v/>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>ALT/ALP比</v>
+        <v>LDH/AST比</v>
       </c>
       <c r="B36" t="str">
-        <v>ALT比/ALP比,R比,R-factor</v>
+        <v>LDH/AST</v>
       </c>
       <c r="C36" t="str">
-        <v>R値 5以上：肝細胞障害型、2以下：胆汁うっ滞型、2〜5：混合型</v>
+        <v>目安として使われる比率（施設差・カットオフ値の設定により異なる）</v>
       </c>
       <c r="D36" t="str">
-        <v>薬剤性肝障害(DILI)などで、肝障害のパターンを「肝細胞障害型」か「胆汁うっ滞型」かに分類するための指標(R値)</v>
+        <v>LDHとASTの両方が上昇したときに、原因が肝臓か、それ以外（溶血・心筋・骨格筋）かを見分ける目安になる比</v>
       </c>
       <c r="E36" t="str">
-        <v>肝臓に関する数値はいくつかありますが、その組み合わせ方によって「肝臓の細胞自体が傷んでいるタイプ」か「胆汁の流れが悪くなっているタイプ」かをある程度見分けることができます。この指標はその判定に使われます。</v>
+        <v>これは、肝臓の数値（AST）と、全身に広く分布する酵素（LDH）の比率を見るもので、両方の数値が上がっているときに、原因が肝臓なのか、それとも血液や筋肉など他の場所なのかを見分ける手がかりになります。</v>
       </c>
       <c r="F36" t="str">
-        <v>R値5以上：肝細胞障害型（ウイルス性肝炎、薬剤性肝障害の肝細胞障害型、虚血性肝障害など）</v>
+        <v>溶血性疾患、心筋梗塞、骨格筋の障害（比が高いほど肝臓以外が原因の可能性）</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -2095,7 +2095,7 @@
         <v/>
       </c>
       <c r="I36" t="str">
-        <v>R値2以下：胆汁うっ滞型（閉塞性黄疸、薬剤性肝障害の胆汁うっ滞型など）</v>
+        <v>急性肝炎などの肝細胞障害（比が低い、つまりASTに対してLDHが相対的に低い場合は肝性が示唆される）</v>
       </c>
       <c r="J36" t="str">
         <v/>
@@ -2104,13 +2104,13 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>R値＝(ALTの基準値上限に対する倍率)÷(ALPの基準値上限に対する倍率)で算出する。薬剤性肝障害(DILI)の病型分類(肝細胞障害型/胆汁うっ滞型/混合型)に用いられ、被疑薬の休薬・変更の判断材料になる</v>
+        <v>AST・LDHが同時に上昇した際の鑑別に使う目安の一つ。単独の検査値ではなく計算上の比率であり、確定診断には他の検査（ビリルビン、CK、心筋マーカーなど）と合わせた評価が必要</v>
       </c>
       <c r="M36" t="str">
-        <v>肝機能</v>
+        <v/>
       </c>
       <c r="N36" t="str">
-        <v>ALT/ALP比,R値,R-factor,DILI,薬剤性肝障害</v>
+        <v>LDH/AST,LDH,AST,溶血,心筋梗塞,肝炎</v>
       </c>
       <c r="O36" t="str">
         <v/>
@@ -2118,31 +2118,31 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>BNP</v>
+        <v>CK/AST比</v>
       </c>
       <c r="B37" t="str">
-        <v>BNP</v>
+        <v>CK/AST</v>
       </c>
       <c r="C37" t="str">
-        <v>18.4 pg/mL以下</v>
+        <v>目安として使われる比率（施設差・カットオフ値の設定により異なる）</v>
       </c>
       <c r="D37" t="str">
-        <v>心臓が無理をしているときに出る物質。心臓は血液を送るポンプだが、負担がかかると「少し助けてほしい」というサインとしてBNPを血液中に出す。</v>
+        <v>ASTが上昇したときに、原因が筋肉（CKも上昇）か、それ以外（肝臓など）かを見分ける目安になる比</v>
       </c>
       <c r="E37" t="str">
-        <v>この検査は、心臓がどれくらい頑張りすぎていないかを見るものです。数値が高いと、心臓に少し負担がかかっているサインになります。</v>
+        <v>これは、筋肉の数値（CK）と肝臓の数値（AST）を比べることで、ASTの上昇が筋肉由来なのか、肝臓由来なのかを見分ける手がかりになる比率です。</v>
       </c>
       <c r="F37" t="str">
-        <v>心不全、心臓に負担がかかっている状態、体に水分がたまりやすいとき</v>
+        <v>横紋筋融解症、心筋梗塞、激しい運動など筋肉由来のAST上昇（CKも同時に高値）</v>
       </c>
       <c r="G37" t="str">
-        <v>塩分・水分の摂りすぎに注意し、体重の変化を毎日記録するよう伝える。急な体重増加(2〜3日で2kg以上)や息切れの悪化があれば早めの受診を勧める</v>
+        <v>筋肉痛や脱力感、褐色尿などの症状がないか確認する</v>
       </c>
       <c r="H37" t="str">
         <v/>
       </c>
       <c r="I37" t="str">
-        <v>心臓の負担は少ない状態</v>
+        <v/>
       </c>
       <c r="J37" t="str">
         <v/>
@@ -2151,36 +2151,36 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>腎機能が低いとBNPは高めに出ることがある／数値だけで判断せず、症状と合わせて評価する／息切れ、むくみ、体重増加があれば要注意</v>
+        <v>ASTのみ上昇しCKが正常であれば肝臓由来を、両方上昇していれば筋肉由来を疑う手がかりになる。スタチン系薬剤による横紋筋融解症が疑われる場面での鑑別に有用</v>
       </c>
       <c r="M37" t="str">
-        <v>心不全</v>
+        <v/>
       </c>
       <c r="N37" t="str">
-        <v>BNP,心不全,息切れ,むくみ</v>
+        <v>CK/AST,CK,AST,横紋筋融解症,スタチン</v>
       </c>
       <c r="O37" t="str">
-        <v>食事と栄養 p.216-222（第2部 心疾患）</v>
+        <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>C－ペプチド（血中）</v>
+        <v>Na-Cl（ナトリウム・クロール差）</v>
       </c>
       <c r="B38" t="str">
-        <v>CPR</v>
+        <v>Na-Cl</v>
       </c>
       <c r="C38" t="str">
-        <v>空腹時 0.6〜3.0 ng/mL（施設差あり）</v>
+        <v>36前後が目安（施設差あり）</v>
       </c>
       <c r="D38" t="str">
-        <v>自分の膵臓がどれくらいインスリンを作れているかを表す指標</v>
+        <v>ナトリウムからクロールを引いた値。アニオンギャップの簡易的な目安として使われる</v>
       </c>
       <c r="E38" t="str">
-        <v>この検査は、ご自身の膵臓がどれくらいインスリンを作る力を持っているかを見るものです。数値が低いほど、体の中で作れるインスリンが少ないことを示します。</v>
+        <v>この数値は、ナトリウムとクロールの検査値の差から計算されるもので、体の中に通常とは違う酸（アニオン）がたまっていないかを大まかに見積もるために使われます。</v>
       </c>
       <c r="F38" t="str">
-        <v>インスリン抵抗性が強い状態（初期の2型糖尿病など）</v>
+        <v>代謝性アシドーシス（乳酸アシドーシス、糖尿病性ケトアシドーシス、腎不全など、体内に有機酸がたまる病態）</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -2189,7 +2189,7 @@
         <v/>
       </c>
       <c r="I38" t="str">
-        <v>膵臓のインスリン分泌能低下（1型糖尿病、糖尿病の進行）</v>
+        <v/>
       </c>
       <c r="J38" t="str">
         <v/>
@@ -2198,13 +2198,13 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>インスリン分泌能の評価に使われる。数値が低いほどインスリン治療の必要性が高いと判断される目安になる</v>
+        <v>本来のアニオンギャップ(Na-(Cl+HCO3))の簡易代用として使われることがあるが、重炭酸(HCO3)を用いた計算の方が正確。メトホルミン使用中の乳酸アシドーシスが疑われる場面などで参考にする</v>
       </c>
       <c r="M38" t="str">
-        <v>糖尿病</v>
+        <v>電解質</v>
       </c>
       <c r="N38" t="str">
-        <v>C-ペプチド,Cペプチド,CPR,C-peptide,血中CPR,インスリン分泌</v>
+        <v>Na-Cl,アニオンギャップ,AG,代謝性アシドーシス,乳酸アシドーシス</v>
       </c>
       <c r="O38" t="str">
         <v/>
@@ -2212,46 +2212,46 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>C－ペプチドインデックス</v>
+        <v>AST/ALT比</v>
       </c>
       <c r="B39" t="str">
-        <v>CPI</v>
+        <v>AST/ALT,De Ritis比</v>
       </c>
       <c r="C39" t="str">
-        <v>1.2以上が目安(施設・測定条件により異なる)</v>
+        <v>1未満が目安（施設・病態により異なる）</v>
       </c>
       <c r="D39" t="str">
-        <v>血糖値に対してどれくらいインスリンを分泌できているかを表す指標。低いほどインスリン治療の必要性が高い</v>
+        <v>ASTとALTの比率（De Ritis比）。肝疾患の種類を推測する手がかりになる</v>
       </c>
       <c r="E39" t="str">
-        <v>これは、血糖値の高さに対して、体がどれくらいインスリンを作れているかを見る指標です。数値が低いほど、自分の膵臓だけでは血糖値に見合うインスリンを十分に作れていない可能性が高く、インスリン治療が必要かどうかの判断材料になります。</v>
+        <v>これは、肝臓に関わる2つの数値（ASTとALT）の比率を見るもので、肝臓のどのようなタイプのトラブルが起きているかを推測する手がかりになります。</v>
       </c>
       <c r="F39" t="str">
-        <v>通常、臨床的意義は乏しい</v>
+        <v>アルコール性肝障害、肝硬変、心筋梗塞・筋疾患の合併（比が2以上でアルコール性を強く示唆）</v>
       </c>
       <c r="G39" t="str">
-        <v/>
+        <v>飲酒量や頻度を確認する</v>
       </c>
       <c r="H39" t="str">
         <v/>
       </c>
       <c r="I39" t="str">
-        <v>内因性インスリン分泌能の低下(1.2未満でインスリン治療の適応を検討する目安、0.8未満はインスリン療法が強く推奨される目安)</v>
+        <v>急性ウイルス性肝炎、脂肪肝（比が1未満で肝細胞の急性障害を示唆することが多い）</v>
       </c>
       <c r="J39" t="str">
-        <v>インスリン治療の必要性について医師からどのように説明を受けているか確認する</v>
+        <v/>
       </c>
       <c r="K39" t="str">
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>CPI＝血中Cペプチド(ng/mL)÷血糖値(mg/dL)×100 で算出する。空腹時に測定するのが基本で、境界値付近では食事負荷の影響を受けるため、複数回の評価や随時尿中CPRとあわせて判断することもある</v>
+        <v>De Ritis比とも呼ばれる。比が2以上はアルコール性肝障害や肝硬変を、1未満は急性ウイルス性肝炎や脂肪肝を示唆する目安になるが、確定診断には他の検査所見と合わせた評価が必要</v>
       </c>
       <c r="M39" t="str">
-        <v>糖尿病</v>
+        <v>肝機能</v>
       </c>
       <c r="N39" t="str">
-        <v>CPI,Cペプチドインデックス,C-ペプチドインデックス,インスリン分泌能,インスリン治療</v>
+        <v>AST/ALT比,AST/ALT,De Ritis比,デリティス比,アルコール性肝障害,肝硬変</v>
       </c>
       <c r="O39" t="str">
         <v/>
@@ -2259,31 +2259,31 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>CONUT値</v>
+        <v>ALT/ALP比</v>
       </c>
       <c r="B40" t="str">
-        <v>CONUT</v>
+        <v>ALT比/ALP比,R比,R-factor</v>
       </c>
       <c r="C40" t="str">
-        <v>0〜1点：正常、2〜4点：軽度低栄養、5〜8点：中等度低栄養、9〜12点：高度低栄養</v>
+        <v>R値 5以上：肝細胞障害型、2以下：胆汁うっ滞型、2〜5：混合型</v>
       </c>
       <c r="D40" t="str">
-        <v>アルブミン・総リンパ球数・総コレステロールの3項目から算出する栄養状態の評価スコア</v>
+        <v>薬剤性肝障害(DILI)などで、肝障害のパターンを「肝細胞障害型」か「胆汁うっ滞型」かに分類するための指標(R値)</v>
       </c>
       <c r="E40" t="str">
-        <v>CONUT値は、血液検査（アルブミン、リンパ球数、コレステロール）の結果から計算される、栄養状態を数値化したスコアです。点数が高いほど低栄養の状態が疑われます。</v>
+        <v>肝臓に関する数値はいくつかありますが、その組み合わせ方によって「肝臓の細胞自体が傷んでいるタイプ」か「胆汁の流れが悪くなっているタイプ」かをある程度見分けることができます。この指標はその判定に使われます。</v>
       </c>
       <c r="F40" t="str">
-        <v>低栄養状態（点数が高いほど重度）</v>
+        <v>R値5以上：肝細胞障害型（ウイルス性肝炎、薬剤性肝障害の肝細胞障害型、虚血性肝障害など）</v>
       </c>
       <c r="G40" t="str">
-        <v>食事摂取量や体重の変化を確認する。必要に応じて栄養補助食品の活用を提案する</v>
+        <v/>
       </c>
       <c r="H40" t="str">
         <v/>
       </c>
       <c r="I40" t="str">
-        <v/>
+        <v>R値2以下：胆汁うっ滞型（閉塞性黄疸、薬剤性肝障害の胆汁うっ滞型など）</v>
       </c>
       <c r="J40" t="str">
         <v/>
@@ -2292,45 +2292,45 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>アルブミン・総リンパ球数・総コレステロールの3項目それぞれに配点があり、合計点で評価する客観的栄養指標。フレイル・サルコペニアの評価やポリファーマシー対策の一環としての栄養状態把握に有用</v>
+        <v>R値＝(ALTの基準値上限に対する倍率)÷(ALPの基準値上限に対する倍率)で算出する。薬剤性肝障害(DILI)の病型分類(肝細胞障害型/胆汁うっ滞型/混合型)に用いられ、被疑薬の休薬・変更の判断材料になる</v>
       </c>
       <c r="M40" t="str">
-        <v/>
+        <v>肝機能</v>
       </c>
       <c r="N40" t="str">
-        <v>CONUT,CONUT値,栄養評価,低栄養,フレイル</v>
+        <v>ALT/ALP比,R値,R-factor,DILI,薬剤性肝障害</v>
       </c>
       <c r="O40" t="str">
-        <v>食事と栄養 p.240（フレイルQ108 低栄養や食事量の評価）</v>
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>乳び</v>
+        <v>BNP</v>
       </c>
       <c r="B41" t="str">
-        <v>乳び,Lipemia</v>
+        <v>BNP</v>
       </c>
       <c r="C41" t="str">
-        <v>所見なし（血清が白濁していなければ正常）</v>
+        <v>18.4 pg/mL以下</v>
       </c>
       <c r="D41" t="str">
-        <v>中性脂肪が非常に多いため、血清が白く濁って見える状態。検査値そのものではなく検体の外観所見</v>
+        <v>心臓が無理をしているときに出る物質。心臓は血液を送るポンプだが、負担がかかると「少し助けてほしい」というサインとしてBNPを血液中に出す。</v>
       </c>
       <c r="E41" t="str">
-        <v>乳びとは、血液中の中性脂肪が非常に多いために、採血した血液（血清）が白く濁って見える状態のことです。多くの場合、食後の採血や、著しい脂質異常症が背景にあります。</v>
+        <v>この検査は、心臓がどれくらい頑張りすぎていないかを見るものです。数値が高いと、心臓に少し負担がかかっているサインになります。</v>
       </c>
       <c r="F41" t="str">
-        <v>著しい高中性脂肪血症、食後採血（一時的なもの）、原発性高カイロミクロン血症などの脂質代謝異常</v>
+        <v>心不全、心臓に負担がかかっている状態、体に水分がたまりやすいとき</v>
       </c>
       <c r="G41" t="str">
-        <v>採血が空腹時だったかを確認する。食後採血であれば次回は空腹時の再検を提案する</v>
+        <v>塩分・水分の摂りすぎに注意し、体重の変化を毎日記録するよう伝える。急な体重増加(2〜3日で2kg以上)や息切れの悪化があれば早めの受診を勧める</v>
       </c>
       <c r="H41" t="str">
         <v/>
       </c>
       <c r="I41" t="str">
-        <v/>
+        <v>心臓の負担は少ない状態</v>
       </c>
       <c r="J41" t="str">
         <v/>
@@ -2339,45 +2339,45 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>血清の白濁により一部の検査項目（電解質など）の測定値に誤差が出ることがある（偽性低ナトリウム血症など）。中性脂肪値と合わせて評価する</v>
+        <v>腎機能が低いとBNPは高めに出ることがある／数値だけで判断せず、症状と合わせて評価する／息切れ、むくみ、体重増加があれば要注意</v>
       </c>
       <c r="M41" t="str">
-        <v>脂質異常症</v>
+        <v>心不全</v>
       </c>
       <c r="N41" t="str">
-        <v>乳び,乳び血清,Lipemia,高中性脂肪血症</v>
+        <v>BNP,心不全,息切れ,むくみ</v>
       </c>
       <c r="O41" t="str">
-        <v/>
+        <v>食事と栄養 p.216-222（第2部 心疾患）</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>溶血</v>
+        <v>C－ペプチド（血中）</v>
       </c>
       <c r="B42" t="str">
-        <v>溶血,Hemolysis</v>
+        <v>CPR</v>
       </c>
       <c r="C42" t="str">
-        <v>所見なし（溶血を示唆する検査値異常がなければ正常）</v>
+        <v>空腹時 0.6〜3.0 ng/mL（施設差あり）</v>
       </c>
       <c r="D42" t="str">
-        <v>赤血球が通常より早く壊れる状態。単独の検査値ではなく、複数の検査値の組み合わせで疑う病態</v>
+        <v>自分の膵臓がどれくらいインスリンを作れているかを表す指標</v>
       </c>
       <c r="E42" t="str">
-        <v>溶血とは、赤血球が通常よりも早いペースで壊れてしまう状態のことです。壊れた赤血球からビリルビンなどが放出されるため、貧血や黄疸の原因になることがあります。</v>
+        <v>この検査は、ご自身の膵臓がどれくらいインスリンを作る力を持っているかを見るものです。数値が低いほど、体の中で作れるインスリンが少ないことを示します。</v>
       </c>
       <c r="F42" t="str">
-        <v>自己免疫性溶血性貧血、血液型不適合輸血、G6PD欠損症などの遺伝性疾患、機械弁など人工物による物理的破壊、薬剤性溶血</v>
+        <v>インスリン抵抗性が強い状態（初期の2型糖尿病など）</v>
       </c>
       <c r="G42" t="str">
-        <v>倦怠感、黄疸、尿の色が濃くなるなどの症状がないか確認する</v>
+        <v/>
       </c>
       <c r="H42" t="str">
         <v/>
       </c>
       <c r="I42" t="str">
-        <v/>
+        <v>膵臓のインスリン分泌能低下（1型糖尿病、糖尿病の進行）</v>
       </c>
       <c r="J42" t="str">
         <v/>
@@ -2386,13 +2386,13 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>溶血を疑う際は、間接ビリルビン上昇・LDH上昇・ハプトグロビン低下・網状赤血球増加のパターンを確認する。ヘモグロビン・MCV・MCHCの変化と合わせて総合的に判断する</v>
+        <v>インスリン分泌能の評価に使われる。数値が低いほどインスリン治療の必要性が高いと判断される目安になる</v>
       </c>
       <c r="M42" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>糖尿病</v>
       </c>
       <c r="N42" t="str">
-        <v>溶血,Hemolysis,溶血性貧血,G6PD,ハプトグロビン</v>
+        <v>C-ペプチド,Cペプチド,CPR,C-peptide,血中CPR,インスリン分泌</v>
       </c>
       <c r="O42" t="str">
         <v/>
@@ -2400,46 +2400,46 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>黄疸</v>
+        <v>C－ペプチドインデックス</v>
       </c>
       <c r="B43" t="str">
-        <v>黄疸,Jaundice</v>
+        <v>CPI</v>
       </c>
       <c r="C43" t="str">
-        <v>所見なし（皮膚・眼球結膜の黄染がなければ正常）</v>
+        <v>1.2以上が目安(施設・測定条件により異なる)</v>
       </c>
       <c r="D43" t="str">
-        <v>ビリルビンが体にたまり、皮膚や白目が黄色くなる状態。単独の検査値ではなく、ビリルビン上昇によって表れる身体所見</v>
+        <v>血糖値に対してどれくらいインスリンを分泌できているかを表す指標。低いほどインスリン治療の必要性が高い</v>
       </c>
       <c r="E43" t="str">
-        <v>黄疸は、体の中にビリルビンという黄色い色素がたまることで、皮膚や白目が黄色く見える状態です。肝臓や胆道のトラブル、赤血球が壊れやすくなる病気（溶血）などが原因となります。</v>
+        <v>これは、血糖値の高さに対して、体がどれくらいインスリンを作れているかを見る指標です。数値が低いほど、自分の膵臓だけでは血糖値に見合うインスリンを十分に作れていない可能性が高く、インスリン治療が必要かどうかの判断材料になります。</v>
       </c>
       <c r="F43" t="str">
-        <v>肝炎・肝硬変などの肝疾患、胆石・腫瘍による胆道閉塞、溶血性疾患、体質性黄疸（ジルベール症候群）、新生児黄疸</v>
+        <v>通常、臨床的意義は乏しい</v>
       </c>
       <c r="G43" t="str">
-        <v>白目や皮膚の黄染に気づいたら、尿の色（濃い茶色）や便の色（白っぽい）の変化も確認し、早めの受診を勧める</v>
+        <v/>
       </c>
       <c r="H43" t="str">
         <v/>
       </c>
       <c r="I43" t="str">
-        <v/>
+        <v>内因性インスリン分泌能の低下(1.2未満でインスリン治療の適応を検討する目安、0.8未満はインスリン療法が強く推奨される目安)</v>
       </c>
       <c r="J43" t="str">
-        <v/>
+        <v>インスリン治療の必要性について医師からどのように説明を受けているか確認する</v>
       </c>
       <c r="K43" t="str">
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>黄疸は検査値そのものではなく身体所見。原因を調べる際は総ビリルビン・直接ビリルビン・間接ビリルビンの内訳とAST/ALT/γ-GTPを確認する。直接優位なら胆道系、間接優位なら溶血・体質性を疑う</v>
+        <v>CPI＝血中Cペプチド(ng/mL)÷血糖値(mg/dL)×100 で算出する。空腹時に測定するのが基本で、境界値付近では食事負荷の影響を受けるため、複数回の評価や随時尿中CPRとあわせて判断することもある</v>
       </c>
       <c r="M43" t="str">
-        <v>肝機能</v>
+        <v>糖尿病</v>
       </c>
       <c r="N43" t="str">
-        <v>黄疸,ジョンダイス,Jaundice,ビリルビン,皮膚黄染,白目</v>
+        <v>CPI,Cペプチドインデックス,C-ペプチドインデックス,インスリン分泌能,インスリン治療</v>
       </c>
       <c r="O43" t="str">
         <v/>
@@ -2447,122 +2447,122 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>甲状腺刺激ホルモン（TSH）</v>
+        <v>CONUT値</v>
       </c>
       <c r="B44" t="str">
-        <v>TSH</v>
+        <v>CONUT</v>
       </c>
       <c r="C44" t="str">
-        <v>0.5〜5.0 μIU/mL程度（施設差あり）</v>
+        <v>0〜1点：正常、2〜4点：軽度低栄養、5〜8点：中等度低栄養、9〜12点：高度低栄養</v>
       </c>
       <c r="D44" t="str">
-        <v>甲状腺の働きが多いか少ないかを最も敏感に反映するホルモン</v>
+        <v>アルブミン・総リンパ球数・総コレステロールの3項目から算出する栄養状態の評価スコア</v>
       </c>
       <c r="E44" t="str">
-        <v>TSHは脳の下垂体から出て、甲状腺に「もっと働いて」と指令を送るホルモンです。甲状腺の働きが弱っていると体が指令を強めるためTSHは上がり、逆に甲状腺が働きすぎているとTSHは下がります。甲状腺の状態を最初に確認する数値としてよく使われます。</v>
+        <v>CONUT値は、血液検査（アルブミン、リンパ球数、コレステロール）の結果から計算される、栄養状態を数値化したスコアです。点数が高いほど低栄養の状態が疑われます。</v>
       </c>
       <c r="F44" t="str">
-        <v>甲状腺機能低下症（橋本病など）、チラーヂンSなど甲状腺ホルモン薬の量不足</v>
+        <v>低栄養状態（点数が高いほど重度）</v>
       </c>
       <c r="G44" t="str">
-        <v>だるさ、むくみ、体重増加、寒がりなどの症状がないか確認する。服薬状況（飲み忘れ、他の薬との飲み合わせ）を確認する</v>
+        <v>食事摂取量や体重の変化を確認する。必要に応じて栄養補助食品の活用を提案する</v>
       </c>
       <c r="H44" t="str">
-        <v>アミオダロン、炭酸リチウム、インターフェロン製剤、チロシンキナーゼ阻害薬(スニチニブ等)</v>
+        <v/>
       </c>
       <c r="I44" t="str">
-        <v>甲状腺機能亢進症（バセドウ病など）、チラーヂンSなど甲状腺ホルモン薬の過量</v>
+        <v/>
       </c>
       <c r="J44" t="str">
-        <v>動悸、体重減少、暑がり、手のふるえなどの症状がないか確認する</v>
+        <v/>
       </c>
       <c r="K44" t="str">
-        <v>レボチロキシンの過量投与</v>
+        <v/>
       </c>
       <c r="L44" t="str">
-        <v>チラーヂンS服用中はTSHが治療目標域に収まっているかで用量調整の目安にする。メルカゾール服用中はTSH・FT4に加えて無顆粒球症の初期症状（発熱・のどの痛み）の有無や白血球数も確認する</v>
+        <v>アルブミン・総リンパ球数・総コレステロールの3項目それぞれに配点があり、合計点で評価する客観的栄養指標。フレイル・サルコペニアの評価やポリファーマシー対策の一環としての栄養状態把握に有用</v>
       </c>
       <c r="M44" t="str">
-        <v>甲状腺疾患</v>
+        <v/>
       </c>
       <c r="N44" t="str">
-        <v>TSH,甲状腺刺激ホルモン,甲状腺機能,橋本病,バセドウ病,チラーヂン,メルカゾール</v>
+        <v>CONUT,CONUT値,栄養評価,低栄養,フレイル</v>
       </c>
       <c r="O44" t="str">
-        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
+        <v>食事と栄養 p.240（フレイルQ108 低栄養や食事量の評価）</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>遊離サイロキシン（FT4）</v>
+        <v>乳び</v>
       </c>
       <c r="B45" t="str">
-        <v>FT4</v>
+        <v>乳び,Lipemia</v>
       </c>
       <c r="C45" t="str">
-        <v>0.9〜1.7 ng/dL程度（施設差あり）</v>
+        <v>所見なし（血清が白濁していなければ正常）</v>
       </c>
       <c r="D45" t="str">
-        <v>甲状腺が実際に分泌しているホルモンの量そのものを表す数値</v>
+        <v>中性脂肪が非常に多いため、血清が白く濁って見える状態。検査値そのものではなく検体の外観所見</v>
       </c>
       <c r="E45" t="str">
-        <v>FT4は甲状腺そのものが作っているホルモンの量です。TSHが「指令の強さ」だとすると、FT4は「実際に出ている量」にあたります。2つをあわせて見ることで、甲状腺の働きが今どういう状態かを詳しく判断できます。</v>
+        <v>乳びとは、血液中の中性脂肪が非常に多いために、採血した血液（血清）が白く濁って見える状態のことです。多くの場合、食後の採血や、著しい脂質異常症が背景にあります。</v>
       </c>
       <c r="F45" t="str">
-        <v>甲状腺機能亢進症（バセドウ病など）</v>
+        <v>著しい高中性脂肪血症、食後採血（一時的なもの）、原発性高カイロミクロン血症などの脂質代謝異常</v>
       </c>
       <c r="G45" t="str">
-        <v>動悸、体重減少、暑がり、手のふるえなどの症状がないか確認する</v>
+        <v>採血が空腹時だったかを確認する。食後採血であれば次回は空腹時の再検を提案する</v>
       </c>
       <c r="H45" t="str">
-        <v>レボチロキシンの過量投与、アミオダロン</v>
+        <v/>
       </c>
       <c r="I45" t="str">
-        <v>甲状腺機能低下症（橋本病など）</v>
+        <v/>
       </c>
       <c r="J45" t="str">
-        <v>だるさ、むくみ、体重増加、寒がりなどの症状がないか確認する</v>
+        <v/>
       </c>
       <c r="K45" t="str">
-        <v>抗甲状腺薬(メルカゾール、プロパジール)の効きすぎ</v>
+        <v/>
       </c>
       <c r="L45" t="str">
-        <v>TSHと逆方向に動くのが基本だが、下垂体性の異常など例外もある。TSHと合わせて評価し、片方だけで判断しない</v>
+        <v>血清の白濁により一部の検査項目（電解質など）の測定値に誤差が出ることがある（偽性低ナトリウム血症など）。中性脂肪値と合わせて評価する</v>
       </c>
       <c r="M45" t="str">
-        <v>甲状腺疾患</v>
+        <v>脂質異常症</v>
       </c>
       <c r="N45" t="str">
-        <v>FT4,遊離サイロキシン,甲状腺ホルモン,甲状腺機能</v>
+        <v>乳び,乳び血清,Lipemia,高中性脂肪血症</v>
       </c>
       <c r="O45" t="str">
-        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
+        <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>尿蛋白（随時尿）</v>
+        <v>溶血</v>
       </c>
       <c r="B46" t="str">
-        <v>尿蛋白,U-pro</v>
+        <v>溶血,Hemolysis</v>
       </c>
       <c r="C46" t="str">
-        <v>陰性（－）〜弱陽性</v>
+        <v>所見なし（溶血を示唆する検査値異常がなければ正常）</v>
       </c>
       <c r="D46" t="str">
-        <v>腎臓から本来漏れないはずのたんぱくが尿に出ていないかを見る検査</v>
+        <v>赤血球が通常より早く壊れる状態。単独の検査値ではなく、複数の検査値の組み合わせで疑う病態</v>
       </c>
       <c r="E46" t="str">
-        <v>この検査は、腎臓のろ過機能に負担がかかっていないかを見るものです。本来、たんぱく質は尿にほとんど出ませんが、腎臓に負担がかかると漏れ出るようになります。</v>
+        <v>溶血とは、赤血球が通常よりも早いペースで壊れてしまう状態のことです。壊れた赤血球からビリルビンなどが放出されるため、貧血や黄疸の原因になることがあります。</v>
       </c>
       <c r="F46" t="str">
-        <v>糖尿病性腎症、腎炎、高血圧性腎硬化症、発熱・運動後の一過性のもの</v>
+        <v>自己免疫性溶血性貧血、血液型不適合輸血、G6PD欠損症などの遺伝性疾患、機械弁など人工物による物理的破壊、薬剤性溶血</v>
       </c>
       <c r="G46" t="str">
-        <v>発熱・激しい運動の直後でないか確認する(一過性のことがある)。持続する場合は塩分の摂りすぎに注意し、むくみの有無もあわせて確認する</v>
+        <v>倦怠感、黄疸、尿の色が濃くなるなどの症状がないか確認する</v>
       </c>
       <c r="H46" t="str">
-        <v>NSAIDs、造影剤、アミノグリコシド系、バンコマイシン、金製剤</v>
+        <v/>
       </c>
       <c r="I46" t="str">
         <v/>
@@ -2574,13 +2574,13 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>発熱・激しい運動・起立性蛋白尿など生理的な要因でも陽性になることがある。持続する場合に腎症の進行を疑う</v>
+        <v>溶血を疑う際は、間接ビリルビン上昇・LDH上昇・ハプトグロビン低下・網状赤血球増加のパターンを確認する。ヘモグロビン・MCV・MCHCの変化と合わせて総合的に判断する</v>
       </c>
       <c r="M46" t="str">
-        <v>糖尿病,腎機能</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="N46" t="str">
-        <v>尿蛋白,U-pro,腎症,たんぱく尿</v>
+        <v>溶血,Hemolysis,溶血性貧血,G6PD,ハプトグロビン</v>
       </c>
       <c r="O46" t="str">
         <v/>
@@ -2588,31 +2588,31 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>尿クレアチニン（随時尿）</v>
+        <v>黄疸</v>
       </c>
       <c r="B47" t="str">
-        <v>尿CRE</v>
+        <v>黄疸,Jaundice</v>
       </c>
       <c r="C47" t="str">
-        <v>随時尿は主に他項目の濃度補正に利用（単独の基準値は設けにくい）</v>
+        <v>所見なし（皮膚・眼球結膜の黄染がなければ正常）</v>
       </c>
       <c r="D47" t="str">
-        <v>随時尿中のクレアチニン濃度。他の尿検査項目を薄まり具合で補正するための基準として使う</v>
+        <v>ビリルビンが体にたまり、皮膚や白目が黄色くなる状態。単独の検査値ではなく、ビリルビン上昇によって表れる身体所見</v>
       </c>
       <c r="E47" t="str">
-        <v>この数値は、尿がどれくらい薄まっているかを確認するための基準として使われます。他の尿検査の結果（蛋白やアルブミンなど）をこの値で割って補正することで、水分摂取量による影響を減らして正確に評価できます。</v>
+        <v>黄疸は、体の中にビリルビンという黄色い色素がたまることで、皮膚や白目が黄色く見える状態です。肝臓や胆道のトラブル、赤血球が壊れやすくなる病気（溶血）などが原因となります。</v>
       </c>
       <c r="F47" t="str">
-        <v/>
+        <v>肝炎・肝硬変などの肝疾患、胆石・腫瘍による胆道閉塞、溶血性疾患、体質性黄疸（ジルベール症候群）、新生児黄疸</v>
       </c>
       <c r="G47" t="str">
-        <v/>
+        <v>白目や皮膚の黄染に気づいたら、尿の色（濃い茶色）や便の色（白っぽい）の変化も確認し、早めの受診を勧める</v>
       </c>
       <c r="H47" t="str">
         <v/>
       </c>
       <c r="I47" t="str">
-        <v>尿が薄い（水分摂取が多い、腎機能低下）状態</v>
+        <v/>
       </c>
       <c r="J47" t="str">
         <v/>
@@ -2621,13 +2621,13 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>尿中アルブミン/Cr比、尿蛋白/Cr比など、他項目の補正計算に使われる。単独の高低に臨床的意味は乏しい</v>
+        <v>黄疸は検査値そのものではなく身体所見。原因を調べる際は総ビリルビン・直接ビリルビン・間接ビリルビンの内訳とAST/ALT/γ-GTPを確認する。直接優位なら胆道系、間接優位なら溶血・体質性を疑う</v>
       </c>
       <c r="M47" t="str">
-        <v>腎機能</v>
+        <v>肝機能</v>
       </c>
       <c r="N47" t="str">
-        <v>尿CRE,尿クレアチニン,随時尿,補正,蛋白クレアチニン比</v>
+        <v>黄疸,ジョンダイス,Jaundice,ビリルビン,皮膚黄染,白目</v>
       </c>
       <c r="O47" t="str">
         <v/>
@@ -2635,122 +2635,122 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>尿蛋白定量</v>
+        <v>甲状腺刺激ホルモン（TSH）</v>
       </c>
       <c r="B48" t="str">
-        <v>U-Pro定量,蛋白/Cr比</v>
+        <v>TSH</v>
       </c>
       <c r="C48" t="str">
-        <v>0.15 g/gCr未満</v>
+        <v>0.5〜5.0 μIU/mL程度（施設差あり）</v>
       </c>
       <c r="D48" t="str">
-        <v>随時尿から尿蛋白の量を具体的な数値として評価する検査。ネフローゼ等の重症度判定に使う</v>
+        <v>甲状腺の働きが多いか少ないかを最も敏感に反映するホルモン</v>
       </c>
       <c r="E48" t="str">
-        <v>これは、尿に出ているたんぱくの量を具体的な数値で見る検査です。試験紙での陽性・陰性の判定だけでなく、実際にどれくらいの量が出ているかを把握できます。</v>
+        <v>TSHは脳の下垂体から出て、甲状腺に「もっと働いて」と指令を送るホルモンです。甲状腺の働きが弱っていると体が指令を強めるためTSHは上がり、逆に甲状腺が働きすぎているとTSHは下がります。甲状腺の状態を最初に確認する数値としてよく使われます。</v>
       </c>
       <c r="F48" t="str">
-        <v>腎症の進行（糖尿病性腎症、慢性腎臓病など）、ネフローゼ症候群（3.5 g/gCr以上が目安）</v>
+        <v>甲状腺機能低下症（橋本病など）、チラーヂンSなど甲状腺ホルモン薬の量不足</v>
       </c>
       <c r="G48" t="str">
-        <v>持続する場合は塩分の摂りすぎに注意し、むくみの有無も確認する。腎臓内科でのフォロー状況もあわせて確認する</v>
+        <v>だるさ、むくみ、体重増加、寒がりなどの症状がないか確認する。服薬状況（飲み忘れ、他の薬との飲み合わせ）を確認する</v>
       </c>
       <c r="H48" t="str">
-        <v>NSAIDs、造影剤、アミノグリコシド系、バンコマイシン</v>
+        <v>アミオダロン、炭酸リチウム、インターフェロン製剤、チロシンキナーゼ阻害薬(スニチニブ等)</v>
       </c>
       <c r="I48" t="str">
-        <v/>
+        <v>甲状腺機能亢進症（バセドウ病など）、チラーヂンSなど甲状腺ホルモン薬の過量</v>
       </c>
       <c r="J48" t="str">
-        <v/>
+        <v>動悸、体重減少、暑がり、手のふるえなどの症状がないか確認する</v>
       </c>
       <c r="K48" t="str">
-        <v/>
+        <v>レボチロキシンの過量投与</v>
       </c>
       <c r="L48" t="str">
-        <v>CKD診療ガイドラインの重症度分類（尿蛋白量による区分）にも使われる定量指標。試験紙法の半定量結果より治療効果判定に適する</v>
+        <v>チラーヂンS服用中はTSHが治療目標域に収まっているかで用量調整の目安にする。メルカゾール服用中はTSH・FT4に加えて無顆粒球症の初期症状（発熱・のどの痛み）の有無や白血球数も確認する</v>
       </c>
       <c r="M48" t="str">
-        <v>腎機能,糖尿病</v>
+        <v>甲状腺疾患</v>
       </c>
       <c r="N48" t="str">
-        <v>尿蛋白,随時尿,定量,蛋白クレアチニン比,ネフローゼ</v>
+        <v>TSH,甲状腺刺激ホルモン,甲状腺機能,橋本病,バセドウ病,チラーヂン,メルカゾール</v>
       </c>
       <c r="O48" t="str">
-        <v/>
+        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>尿pH</v>
+        <v>遊離サイロキシン（FT4）</v>
       </c>
       <c r="B49" t="str">
-        <v>尿pH</v>
+        <v>FT4</v>
       </c>
       <c r="C49" t="str">
-        <v>4.5〜7.5程度（弱酸性が多い）</v>
+        <v>0.9〜1.7 ng/dL程度（施設差あり）</v>
       </c>
       <c r="D49" t="str">
-        <v>尿の酸性・アルカリ性の度合い。食事や感染症、体の状態を反映する</v>
+        <v>甲状腺が実際に分泌しているホルモンの量そのものを表す数値</v>
       </c>
       <c r="E49" t="str">
-        <v>尿のpHは酸性・アルカリ性のバランスを表します。食事の内容や感染症、体の代謝状態によって変化します。単独で大きな問題を示すことは少ない検査です。</v>
+        <v>FT4は甲状腺そのものが作っているホルモンの量です。TSHが「指令の強さ」だとすると、FT4は「実際に出ている量」にあたります。2つをあわせて見ることで、甲状腺の働きが今どういう状態かを詳しく判断できます。</v>
       </c>
       <c r="F49" t="str">
-        <v>尿路感染症（尿素分解菌によるもの）、野菜中心の食事、過換気</v>
+        <v>甲状腺機能亢進症（バセドウ病など）</v>
       </c>
       <c r="G49" t="str">
-        <v/>
+        <v>動悸、体重減少、暑がり、手のふるえなどの症状がないか確認する</v>
       </c>
       <c r="H49" t="str">
-        <v/>
+        <v>レボチロキシンの過量投与、アミオダロン</v>
       </c>
       <c r="I49" t="str">
-        <v>高たんぱく食、糖尿病性ケトアシドーシス、痛風発作時（酸性尿は尿酸結石のリスクを高める）</v>
+        <v>甲状腺機能低下症（橋本病など）</v>
       </c>
       <c r="J49" t="str">
-        <v>痛風・尿酸結石がある場合は、野菜など尿をアルカリ化する食品を意識するとよいことを伝える</v>
+        <v>だるさ、むくみ、体重増加、寒がりなどの症状がないか確認する</v>
       </c>
       <c r="K49" t="str">
-        <v/>
+        <v>抗甲状腺薬(メルカゾール、プロパジール)の効きすぎ</v>
       </c>
       <c r="L49" t="str">
-        <v>高尿酸血症・尿酸結石の患者では尿pHが酸性に傾いていないか確認する。尿アルカリ化薬（ウラリットなど）の効果判定にも使う</v>
+        <v>TSHと逆方向に動くのが基本だが、下垂体性の異常など例外もある。TSHと合わせて評価し、片方だけで判断しない</v>
       </c>
       <c r="M49" t="str">
-        <v>高尿酸血症</v>
+        <v>甲状腺疾患</v>
       </c>
       <c r="N49" t="str">
-        <v>尿pH,尿酸性度,尿アルカリ化,ウラリット</v>
+        <v>FT4,遊離サイロキシン,甲状腺ホルモン,甲状腺機能</v>
       </c>
       <c r="O49" t="str">
-        <v/>
+        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>尿ケトン体</v>
+        <v>尿蛋白（随時尿）</v>
       </c>
       <c r="B50" t="str">
-        <v>尿ケトン,Ket</v>
+        <v>尿蛋白,U-pro</v>
       </c>
       <c r="C50" t="str">
-        <v>陰性（－）</v>
+        <v>陰性（－）〜弱陽性</v>
       </c>
       <c r="D50" t="str">
-        <v>体がブドウ糖の代わりに脂肪を分解してエネルギーを作っているサイン</v>
+        <v>腎臓から本来漏れないはずのたんぱくが尿に出ていないかを見る検査</v>
       </c>
       <c r="E50" t="str">
-        <v>この検査は、体が糖の代わりに脂肪を使ってエネルギーを作っていないかを見るものです。陽性が続くときは、食事や水分、インスリンの使い方を確認する必要があります。</v>
+        <v>この検査は、腎臓のろ過機能に負担がかかっていないかを見るものです。本来、たんぱく質は尿にほとんど出ませんが、腎臓に負担がかかると漏れ出るようになります。</v>
       </c>
       <c r="F50" t="str">
-        <v>糖尿病の血糖コントロール不良（シックデイ・インスリン不足）、極端な糖質制限、絶食、嘔吐・下痢による脱水</v>
+        <v>糖尿病性腎症、腎炎、高血圧性腎硬化症、発熱・運動後の一過性のもの</v>
       </c>
       <c r="G50" t="str">
-        <v>糖尿病治療中の場合はシックデイ時の対応(インスリンを自己中断しない、水分摂取を続けるなど)を確認する。体調不良時の対応方法を事前に説明しておく</v>
+        <v>発熱・激しい運動の直後でないか確認する(一過性のことがある)。持続する場合は塩分の摂りすぎに注意し、むくみの有無もあわせて確認する</v>
       </c>
       <c r="H50" t="str">
-        <v>SGLT2阻害薬(特に絶食・シックデイ時の正常血糖ケトアシドーシスに注意)</v>
+        <v>NSAIDs、造影剤、アミノグリコシド系、バンコマイシン、金製剤</v>
       </c>
       <c r="I50" t="str">
         <v/>
@@ -2762,13 +2762,13 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>陽性かつ高血糖・全身倦怠感が強い場合は糖尿病性ケトアシドーシスの可能性があり緊急性が高い。シックデイルールの説明歴を確認する</v>
+        <v>発熱・激しい運動・起立性蛋白尿など生理的な要因でも陽性になることがある。持続する場合に腎症の進行を疑う</v>
       </c>
       <c r="M50" t="str">
-        <v>糖尿病</v>
+        <v>糖尿病,腎機能</v>
       </c>
       <c r="N50" t="str">
-        <v>尿ケトン体,ケトン体,Ket,シックデイ,ケトアシドーシス</v>
+        <v>尿蛋白,U-pro,腎症,たんぱく尿</v>
       </c>
       <c r="O50" t="str">
         <v/>
@@ -2776,22 +2776,22 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ウロビリノーゲン</v>
+        <v>尿クレアチニン（随時尿）</v>
       </c>
       <c r="B51" t="str">
-        <v>Uro</v>
+        <v>尿CRE</v>
       </c>
       <c r="C51" t="str">
-        <v>正常（±）程度</v>
+        <v>随時尿は主に他項目の濃度補正に利用（単独の基準値は設けにくい）</v>
       </c>
       <c r="D51" t="str">
-        <v>肝臓や胆道、赤血球の壊れ方の状態を反映する尿検査項目</v>
+        <v>随時尿中のクレアチニン濃度。他の尿検査項目を薄まり具合で補正するための基準として使う</v>
       </c>
       <c r="E51" t="str">
-        <v>ウロビリノーゲンは、赤血球やビリルビンが体の中で処理される過程でできる物質です。肝臓の働きが悪くなったり、赤血球が壊れやすくなったりすると、尿の中の量が変化します。</v>
+        <v>この数値は、尿がどれくらい薄まっているかを確認するための基準として使われます。他の尿検査の結果（蛋白やアルブミンなど）をこの値で割って補正することで、水分摂取量による影響を減らして正確に評価できます。</v>
       </c>
       <c r="F51" t="str">
-        <v>溶血性疾患（赤血球の破壊亢進）、肝機能障害</v>
+        <v/>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2800,7 +2800,7 @@
         <v/>
       </c>
       <c r="I51" t="str">
-        <v>胆道閉塞（胆汁が腸に流れず、ウロビリノーゲンが作られない状態）</v>
+        <v>尿が薄い（水分摂取が多い、腎機能低下）状態</v>
       </c>
       <c r="J51" t="str">
         <v/>
@@ -2809,13 +2809,13 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>完全に陰性の場合は胆道閉塞を疑う所見の一つ。肝機能（AST/ALT/ビリルビン）と合わせて評価する</v>
+        <v>尿中アルブミン/Cr比、尿蛋白/Cr比など、他項目の補正計算に使われる。単独の高低に臨床的意味は乏しい</v>
       </c>
       <c r="M51" t="str">
-        <v>肝機能</v>
+        <v>腎機能</v>
       </c>
       <c r="N51" t="str">
-        <v>ウロビリノーゲン,Uro,溶血,胆道閉塞,肝機能</v>
+        <v>尿CRE,尿クレアチニン,随時尿,補正,蛋白クレアチニン比</v>
       </c>
       <c r="O51" t="str">
         <v/>
@@ -2823,28 +2823,28 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>尿潜血反応</v>
+        <v>尿蛋白定量</v>
       </c>
       <c r="B52" t="str">
-        <v>尿潜血,U-OB</v>
+        <v>U-Pro定量,蛋白/Cr比</v>
       </c>
       <c r="C52" t="str">
-        <v>陰性（－）</v>
+        <v>0.15 g/gCr未満</v>
       </c>
       <c r="D52" t="str">
-        <v>尿に血液（赤血球）が混じっていないかを見る検査</v>
+        <v>随時尿から尿蛋白の量を具体的な数値として評価する検査。ネフローゼ等の重症度判定に使う</v>
       </c>
       <c r="E52" t="str">
-        <v>この検査は、尿に目に見えないくらいの微量の血液が混じっていないかを調べるものです。陽性の場合、腎臓や膀胱、尿路のどこかに炎症や結石などがある可能性があります。</v>
+        <v>これは、尿に出ているたんぱくの量を具体的な数値で見る検査です。試験紙での陽性・陰性の判定だけでなく、実際にどれくらいの量が出ているかを把握できます。</v>
       </c>
       <c r="F52" t="str">
-        <v>尿路結石、膀胱炎などの尿路感染症、腎炎、腫瘍、月経血の混入、激しい運動後</v>
+        <v>腎症の進行（糖尿病性腎症、慢性腎臓病など）、ネフローゼ症候群（3.5 g/gCr以上が目安）</v>
       </c>
       <c r="G52" t="str">
-        <v>排尿時の痛みや頻尿、目に見える血尿の有無を確認する。女性は月経の時期と重なっていないか確認する</v>
+        <v>持続する場合は塩分の摂りすぎに注意し、むくみの有無も確認する。腎臓内科でのフォロー状況もあわせて確認する</v>
       </c>
       <c r="H52" t="str">
-        <v>ワルファリン、DOAC、抗血小板薬など出血傾向を強める薬剤の服用状況を確認</v>
+        <v>NSAIDs、造影剤、アミノグリコシド系、バンコマイシン</v>
       </c>
       <c r="I52" t="str">
         <v/>
@@ -2856,13 +2856,13 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>陽性でも尿沈渣で赤血球が確認されない場合は偽陽性（ミオグロビン尿など）のこともある。持続する場合は泌尿器科的な精査が必要</v>
+        <v>CKD診療ガイドラインの重症度分類（尿蛋白量による区分）にも使われる定量指標。試験紙法の半定量結果より治療効果判定に適する</v>
       </c>
       <c r="M52" t="str">
-        <v>腎機能</v>
+        <v>腎機能,糖尿病</v>
       </c>
       <c r="N52" t="str">
-        <v>尿潜血,潜血反応,U-OB,血尿,尿路結石,膀胱炎</v>
+        <v>尿蛋白,随時尿,定量,蛋白クレアチニン比,ネフローゼ</v>
       </c>
       <c r="O52" t="str">
         <v/>
@@ -2870,46 +2870,46 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>尿糖（半定量）</v>
+        <v>尿pH</v>
       </c>
       <c r="B53" t="str">
-        <v>尿糖,U-Glu</v>
+        <v>尿pH</v>
       </c>
       <c r="C53" t="str">
-        <v>陰性（－）</v>
+        <v>4.5〜7.5程度（弱酸性が多い）</v>
       </c>
       <c r="D53" t="str">
-        <v>尿に糖が漏れ出ていないかを見る検査。血糖値がかなり高いと陽性になる</v>
+        <v>尿の酸性・アルカリ性の度合い。食事や感染症、体の状態を反映する</v>
       </c>
       <c r="E53" t="str">
-        <v>通常、糖は尿にはほとんど出ませんが、血糖値がかなり高くなると尿にあふれ出るようになります。血糖コントロールの目安の一つです。</v>
+        <v>尿のpHは酸性・アルカリ性のバランスを表します。食事の内容や感染症、体の代謝状態によって変化します。単独で大きな問題を示すことは少ない検査です。</v>
       </c>
       <c r="F53" t="str">
-        <v>糖尿病（血糖値が腎臓で再吸収できる量を超えている状態）、腎性糖尿（血糖値が正常でも体質的に出ることがある）、SGLT2阻害薬服用中（薬の作用で意図的に糖を排泄するため陽性になるのが正常）</v>
+        <v>尿路感染症（尿素分解菌によるもの）、野菜中心の食事、過換気</v>
       </c>
       <c r="G53" t="str">
-        <v>SGLT2阻害薬（フォシーガ、ジャディアンスなど）服用中は、陽性が薬の効果によるものであることを説明する。脱水や尿路感染の症状がないかも確認する</v>
+        <v/>
       </c>
       <c r="H53" t="str">
-        <v>SGLT2阻害薬(薬理作用による陽性であれば想定内であることを説明)</v>
+        <v/>
       </c>
       <c r="I53" t="str">
-        <v/>
+        <v>高たんぱく食、糖尿病性ケトアシドーシス、痛風発作時（酸性尿は尿酸結石のリスクを高める）</v>
       </c>
       <c r="J53" t="str">
-        <v/>
+        <v>痛風・尿酸結石がある場合は、野菜など尿をアルカリ化する食品を意識するとよいことを伝える</v>
       </c>
       <c r="K53" t="str">
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>SGLT2阻害薬服用中は尿糖陽性が治療効果として想定内であることを患者に伝える。血糖値・HbA1cと合わせて評価する</v>
+        <v>高尿酸血症・尿酸結石の患者では尿pHが酸性に傾いていないか確認する。尿アルカリ化薬（ウラリットなど）の効果判定にも使う</v>
       </c>
       <c r="M53" t="str">
-        <v>糖尿病</v>
+        <v>高尿酸血症</v>
       </c>
       <c r="N53" t="str">
-        <v>尿糖,糖半定量,U-Glu,腎性糖尿,SGLT2</v>
+        <v>尿pH,尿酸性度,尿アルカリ化,ウラリット</v>
       </c>
       <c r="O53" t="str">
         <v/>
@@ -2917,28 +2917,28 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>尿中微量アルブミン</v>
+        <v>尿ケトン体</v>
       </c>
       <c r="B54" t="str">
-        <v>U-Alb,MAU</v>
+        <v>尿ケトン,Ket</v>
       </c>
       <c r="C54" t="str">
-        <v>30 mg/gCr未満（尿中アルブミン/クレアチニン比）</v>
+        <v>陰性（－）</v>
       </c>
       <c r="D54" t="str">
-        <v>通常の尿蛋白検査では見つからない、ごく早期の腎症のサイン</v>
+        <v>体がブドウ糖の代わりに脂肪を分解してエネルギーを作っているサイン</v>
       </c>
       <c r="E54" t="str">
-        <v>この検査は、通常の尿検査ではまだ分からないくらい早い段階の腎臓の変化を見つけるためのものです。数値が高いと、腎症の初期のサインである可能性があります。</v>
+        <v>この検査は、体が糖の代わりに脂肪を使ってエネルギーを作っていないかを見るものです。陽性が続くときは、食事や水分、インスリンの使い方を確認する必要があります。</v>
       </c>
       <c r="F54" t="str">
-        <v>糖尿病性腎症の早期段階、高血圧</v>
+        <v>糖尿病の血糖コントロール不良（シックデイ・インスリン不足）、極端な糖質制限、絶食、嘔吐・下痢による脱水</v>
       </c>
       <c r="G54" t="str">
-        <v>血糖・血圧のコントロール状況を確認する。減塩や適正体重の維持など生活習慣の見直しも早期腎症の進行予防に役立つことを伝える</v>
+        <v>糖尿病治療中の場合はシックデイ時の対応(インスリンを自己中断しない、水分摂取を続けるなど)を確認する。体調不良時の対応方法を事前に説明しておく</v>
       </c>
       <c r="H54" t="str">
-        <v>NSAIDsなど腎機能を悪化させる薬剤。ACE阻害薬・ARB・SGLT2阻害薬は低下させる方向に働く</v>
+        <v>SGLT2阻害薬(特に絶食・シックデイ時の正常血糖ケトアシドーシスに注意)</v>
       </c>
       <c r="I54" t="str">
         <v/>
@@ -2950,13 +2950,13 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>糖尿病腎症の早期発見に重要な検査。血糖・血圧コントロールで改善しうる段階なので、早期介入の意義を伝える</v>
+        <v>陽性かつ高血糖・全身倦怠感が強い場合は糖尿病性ケトアシドーシスの可能性があり緊急性が高い。シックデイルールの説明歴を確認する</v>
       </c>
       <c r="M54" t="str">
-        <v>糖尿病,腎機能</v>
+        <v>糖尿病</v>
       </c>
       <c r="N54" t="str">
-        <v>微量アルブミン,U-Alb,MAU,糖尿病性腎症,早期腎症</v>
+        <v>尿ケトン体,ケトン体,Ket,シックデイ,ケトアシドーシス</v>
       </c>
       <c r="O54" t="str">
         <v/>
@@ -2964,31 +2964,31 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>C反応性蛋白（CRP）</v>
+        <v>ウロビリノーゲン</v>
       </c>
       <c r="B55" t="str">
-        <v>CRP</v>
+        <v>Uro</v>
       </c>
       <c r="C55" t="str">
-        <v>0.3 mg/dL未満（施設差あり）</v>
+        <v>正常（±）程度</v>
       </c>
       <c r="D55" t="str">
-        <v>体のどこかに炎症や感染が起きていないかを鋭敏に反映する数値</v>
+        <v>肝臓や胆道、赤血球の壊れ方の状態を反映する尿検査項目</v>
       </c>
       <c r="E55" t="str">
-        <v>CRPは、体に炎症や感染が起きると数時間〜半日程度で急激に上昇する数値です。風邪のようなウイルス感染から細菌感染、体のどこかの炎症まで、幅広く反応するため、体調の変化を早期に捉える手がかりになります。</v>
+        <v>ウロビリノーゲンは、赤血球やビリルビンが体の中で処理される過程でできる物質です。肝臓の働きが悪くなったり、赤血球が壊れやすくなったりすると、尿の中の量が変化します。</v>
       </c>
       <c r="F55" t="str">
-        <v>細菌感染症、ウイルス感染症、自己免疫疾患（関節リウマチなど）、悪性腫瘍、組織の損傷（術後・心筋梗塞など）</v>
+        <v>溶血性疾患（赤血球の破壊亢進）、肝機能障害</v>
       </c>
       <c r="G55" t="str">
-        <v>発熱、痛み、腫れなど炎症症状の有無を確認する</v>
+        <v/>
       </c>
       <c r="H55" t="str">
         <v/>
       </c>
       <c r="I55" t="str">
-        <v/>
+        <v>胆道閉塞（胆汁が腸に流れず、ウロビリノーゲンが作られない状態）</v>
       </c>
       <c r="J55" t="str">
         <v/>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>白血球数と合わせて感染・炎症の程度を評価する。上昇・低下のタイミングは白血球より半日〜1日程度遅れる傾向があるため、経過を追う際は採血のタイミングに注意</v>
+        <v>完全に陰性の場合は胆道閉塞を疑う所見の一つ。肝機能（AST/ALT/ビリルビン）と合わせて評価する</v>
       </c>
       <c r="M55" t="str">
-        <v/>
+        <v>肝機能</v>
       </c>
       <c r="N55" t="str">
-        <v>CRP,炎症,感染</v>
+        <v>ウロビリノーゲン,Uro,溶血,胆道閉塞,肝機能</v>
       </c>
       <c r="O55" t="str">
         <v/>
@@ -3011,75 +3011,75 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>PT-INR（プロトロンビン時間国際標準比）</v>
+        <v>尿潜血反応</v>
       </c>
       <c r="B56" t="str">
-        <v>PT-INR,INR</v>
+        <v>尿潜血,U-OB</v>
       </c>
       <c r="C56" t="str">
-        <v>治療域の目安 1.6〜3.0（ワルファリン服用時。年齢・疾患により異なる）</v>
+        <v>陰性（－）</v>
       </c>
       <c r="D56" t="str">
-        <v>血液の固まりやすさを表す数値で、ワルファリンの効き具合を確認するために使う</v>
+        <v>尿に血液（赤血球）が混じっていないかを見る検査</v>
       </c>
       <c r="E56" t="str">
-        <v>PT-INRは血液が固まるまでの時間をもとにした数値で、ワルファリンというお薬を飲んでいる方の効き具合を確認するために測ります。数値が高いほど血液が固まりにくく出血しやすい状態、低いほど血栓ができやすい状態を示します。</v>
+        <v>この検査は、尿に目に見えないくらいの微量の血液が混じっていないかを調べるものです。陽性の場合、腎臓や膀胱、尿路のどこかに炎症や結石などがある可能性があります。</v>
       </c>
       <c r="F56" t="str">
-        <v>ワルファリンの効きすぎ、肝機能低下、ビタミンK不足、納豆・青汁など摂取量の変化</v>
+        <v>尿路結石、膀胱炎などの尿路感染症、腎炎、腫瘍、月経血の混入、激しい運動後</v>
       </c>
       <c r="G56" t="str">
-        <v>歯ぐきや鼻からの出血、あざ、黒い便などの出血症状がないか確認する。納豆・クロレラ・青汁などビタミンKを多く含む食品の摂取状況を確認する</v>
+        <v>排尿時の痛みや頻尿、目に見える血尿の有無を確認する。女性は月経の時期と重なっていないか確認する</v>
       </c>
       <c r="H56" t="str">
-        <v>ワルファリンの過量。ワルファリン服用中はST合剤・マクロライド系・フルコナゾール等の相互作用やビタミンK摂取量の変化にも注意</v>
+        <v>ワルファリン、DOAC、抗血小板薬など出血傾向を強める薬剤の服用状況を確認</v>
       </c>
       <c r="I56" t="str">
-        <v>ワルファリンの効き不足、飲み忘れ、ビタミンK摂取量の急激な増加</v>
+        <v/>
       </c>
       <c r="J56" t="str">
-        <v>服薬状況（飲み忘れ）を確認する。片側のむくみ・しびれ・胸痛など血栓症状がないか確認する</v>
+        <v/>
       </c>
       <c r="K56" t="str">
-        <v>ワルファリン服用中で低値の場合は効果不十分の可能性。ビタミンK摂取量の変化や、リファンピシン・カルバマゼピン・バルビツール酸系など代謝を促進する薬との併用を確認</v>
+        <v/>
       </c>
       <c r="L56" t="str">
-        <v>治療域は疾患・年齢によって異なる（例：非弁膜症性心房細動の高齢者では1.6〜2.6が目安になることが多い）。多くの薬剤・食品と相互作用があるため新規薬剤追加時は必ず確認する。DOAC（エリキュース、リクシアナ、プラザキサなど）ではPT-INRのモニタリングは不要</v>
+        <v>陽性でも尿沈渣で赤血球が確認されない場合は偽陽性（ミオグロビン尿など）のこともある。持続する場合は泌尿器科的な精査が必要</v>
       </c>
       <c r="M56" t="str">
-        <v>抗凝固療法（心房細動・血栓症）</v>
+        <v>腎機能</v>
       </c>
       <c r="N56" t="str">
-        <v>PT-INR,INR,プロトロンビン時間,ワルファリン,ワーファリン,抗凝固</v>
+        <v>尿潜血,潜血反応,U-OB,血尿,尿路結石,膀胱炎</v>
       </c>
       <c r="O56" t="str">
-        <v>食事と栄養 p.221（心疾患Q93 ワルファリン服用中のビタミンK摂取）</v>
+        <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>骨型酒石酸抵抗性フォスファターゼ（TRACP-5b）</v>
+        <v>尿糖（半定量）</v>
       </c>
       <c r="B57" t="str">
-        <v>TRACP-5b</v>
+        <v>尿糖,U-Glu</v>
       </c>
       <c r="C57" t="str">
-        <v>120〜420 mU/dL</v>
+        <v>陰性（－）</v>
       </c>
       <c r="D57" t="str">
-        <v>骨がどれくらい壊されているかを見る検査。骨は「古い骨を壊して新しい骨を作る」入れ替えを繰り返しており、骨を壊す細胞が活発だとこの物質が血液中に増える。</v>
+        <v>尿に糖が漏れ出ていないかを見る検査。血糖値がかなり高いと陽性になる</v>
       </c>
       <c r="E57" t="str">
-        <v>この検査は、骨がどれくらい早く減っていないかを見るものです。数値が高いと、骨が弱くなりやすい状態の目安になります。</v>
+        <v>通常、糖は尿にはほとんど出ませんが、血糖値がかなり高くなると尿にあふれ出るようになります。血糖コントロールの目安の一つです。</v>
       </c>
       <c r="F57" t="str">
-        <v>骨粗鬆症、骨代謝回転（骨がこわれるスピード）が活発な状態</v>
+        <v>糖尿病（血糖値が腎臓で再吸収できる量を超えている状態）、腎性糖尿（血糖値が正常でも体質的に出ることがある）、SGLT2阻害薬服用中（薬の作用で意図的に糖を排泄するため陽性になるのが正常）</v>
       </c>
       <c r="G57" t="str">
-        <v>カルシウム・ビタミンDの摂取や、適度な荷重運動（ウォーキングなど）を意識するよう伝える</v>
+        <v>SGLT2阻害薬（フォシーガ、ジャディアンスなど）服用中は、陽性が薬の効果によるものであることを説明する。脱水や尿路感染の症状がないかも確認する</v>
       </c>
       <c r="H57" t="str">
-        <v/>
+        <v>SGLT2阻害薬(薬理作用による陽性であれば想定内であることを説明)</v>
       </c>
       <c r="I57" t="str">
         <v/>
@@ -3091,13 +3091,13 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>「骨を壊す側」の指標。「骨を作る側」の検査と合わせて評価する。数値だけで診断はしない</v>
+        <v>SGLT2阻害薬服用中は尿糖陽性が治療効果として想定内であることを患者に伝える。血糖値・HbA1cと合わせて評価する</v>
       </c>
       <c r="M57" t="str">
-        <v>骨粗鬆症</v>
+        <v>糖尿病</v>
       </c>
       <c r="N57" t="str">
-        <v>TRACP-5b,骨型酒石酸抵抗性フォスファターゼ,骨粗鬆症,骨代謝</v>
+        <v>尿糖,糖半定量,U-Glu,腎性糖尿,SGLT2</v>
       </c>
       <c r="O57" t="str">
         <v/>
@@ -3105,31 +3105,31 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>骨型アルカリフォスファターゼ</v>
+        <v>尿中微量アルブミン</v>
       </c>
       <c r="B58" t="str">
-        <v>BAP</v>
+        <v>U-Alb,MAU</v>
       </c>
       <c r="C58" t="str">
-        <v>男性 3.7〜20.9 μg/L、女性（閉経前）2.9〜14.5 μg/L（施設差あり）</v>
+        <v>30 mg/gCr未満（尿中アルブミン/クレアチニン比）</v>
       </c>
       <c r="D58" t="str">
-        <v>ALPのうち骨に由来する成分だけを測定し、骨が作られる勢い（骨形成）を反映する</v>
+        <v>通常の尿蛋白検査では見つからない、ごく早期の腎症のサイン</v>
       </c>
       <c r="E58" t="str">
-        <v>骨型ALPは、通常のALP（アルカリフォスファターゼ）の中でも、骨で作られる成分だけを選んで測定するものです。骨を新しく作る働きがどれくらい活発かを見る指標として、骨粗鬆症の治療効果判定などに使われます。</v>
+        <v>この検査は、通常の尿検査ではまだ分からないくらい早い段階の腎臓の変化を見つけるためのものです。数値が高いと、腎症の初期のサインである可能性があります。</v>
       </c>
       <c r="F58" t="str">
-        <v>骨代謝回転の亢進（骨粗鬆症、骨折治癒過程、骨形成促進薬による治療効果、Paget病、骨転移）</v>
+        <v>糖尿病性腎症の早期段階、高血圧</v>
       </c>
       <c r="G58" t="str">
-        <v/>
+        <v>血糖・血圧のコントロール状況を確認する。減塩や適正体重の維持など生活習慣の見直しも早期腎症の進行予防に役立つことを伝える</v>
       </c>
       <c r="H58" t="str">
-        <v/>
+        <v>NSAIDsなど腎機能を悪化させる薬剤。ACE阻害薬・ARB・SGLT2阻害薬は低下させる方向に働く</v>
       </c>
       <c r="I58" t="str">
-        <v>骨形成の低下</v>
+        <v/>
       </c>
       <c r="J58" t="str">
         <v/>
@@ -3138,13 +3138,13 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>通常のALPと異なり肝臓の影響を受けにくいため、肝機能異常がある患者でも骨代謝を評価しやすい。P1NPと同じ「骨を作る側」の指標で、骨形成促進薬（テリパラチド等）の効果判定に使われる</v>
+        <v>糖尿病腎症の早期発見に重要な検査。血糖・血圧コントロールで改善しうる段階なので、早期介入の意義を伝える</v>
       </c>
       <c r="M58" t="str">
-        <v>骨粗鬆症</v>
+        <v>糖尿病,腎機能</v>
       </c>
       <c r="N58" t="str">
-        <v>骨型ALP,BAP,骨型アルカリフォスファターゼ,骨形成マーカー</v>
+        <v>微量アルブミン,U-Alb,MAU,糖尿病性腎症,早期腎症</v>
       </c>
       <c r="O58" t="str">
         <v/>
@@ -3152,125 +3152,125 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>25-ヒドロキシビタミンD</v>
+        <v>C反応性蛋白（CRP）</v>
       </c>
       <c r="B59" t="str">
-        <v>25(OH)D</v>
+        <v>CRP</v>
       </c>
       <c r="C59" t="str">
-        <v>30 ng/mL以上：充足、20〜30 ng/mL：不足、20 ng/mL未満：欠乏（施設差あり）</v>
+        <v>0.3 mg/dL未満（施設差あり）</v>
       </c>
       <c r="D59" t="str">
-        <v>体内のビタミンDの蓄え具合を反映する指標。カルシウムの吸収や骨の健康に関わる</v>
+        <v>体のどこかに炎症や感染が起きていないかを鋭敏に反映する数値</v>
       </c>
       <c r="E59" t="str">
-        <v>この検査は、体の中にビタミンDがどれくらい蓄えられているかを見るものです。ビタミンDは、食事から摂ったカルシウムを腸で吸収するのを助ける働きがあり、不足すると骨がもろくなりやすくなります。</v>
+        <v>CRPは、体に炎症や感染が起きると数時間〜半日程度で急激に上昇する数値です。風邪のようなウイルス感染から細菌感染、体のどこかの炎症まで、幅広く反応するため、体調の変化を早期に捉える手がかりになります。</v>
       </c>
       <c r="F59" t="str">
-        <v>ビタミンD製剤の過剰摂取</v>
+        <v>細菌感染症、ウイルス感染症、自己免疫疾患（関節リウマチなど）、悪性腫瘍、組織の損傷（術後・心筋梗塞など）</v>
       </c>
       <c r="G59" t="str">
-        <v>活性型ビタミンD3製剤やサプリメントの摂取量を確認する。高カルシウム血症の症状（吐き気、便秘、多尿など）がないか確認する</v>
+        <v>発熱、痛み、腫れなど炎症症状の有無を確認する</v>
       </c>
       <c r="H59" t="str">
-        <v>活性型/天然型ビタミンD製剤の過量投与</v>
+        <v/>
       </c>
       <c r="I59" t="str">
-        <v>日光暴露不足、食事摂取不足、高齢、腸疾患による吸収不良、肝・腎機能低下（活性化障害）</v>
+        <v/>
       </c>
       <c r="J59" t="str">
-        <v>適度な日光浴、魚類・きのこ類などビタミンDを多く含む食品の摂取を意識するとよいことを伝える</v>
+        <v/>
       </c>
       <c r="K59" t="str">
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>骨粗鬆症治療における活性型ビタミンD3製剤の効果判定や、投与量調整の参考に用いられる。腎機能低下患者では活性化障害により25(OH)Dが正常でも活性型が不足することがある点に注意</v>
+        <v>白血球数と合わせて感染・炎症の程度を評価する。上昇・低下のタイミングは白血球より半日〜1日程度遅れる傾向があるため、経過を追う際は採血のタイミングに注意</v>
       </c>
       <c r="M59" t="str">
-        <v>骨粗鬆症</v>
+        <v/>
       </c>
       <c r="N59" t="str">
-        <v>25(OH)D,ビタミンD,25-ヒドロキシビタミンD,ビタミンD欠乏,骨粗鬆症</v>
+        <v>CRP,炎症,感染</v>
       </c>
       <c r="O59" t="str">
-        <v>食事と栄養 p.38（ビタミンD）</v>
+        <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ucOC（低カルボキシル化オステオカルシン）</v>
+        <v>PT-INR（プロトロンビン時間国際標準比）</v>
       </c>
       <c r="B60" t="str">
-        <v>ucOC</v>
+        <v>PT-INR,INR</v>
       </c>
       <c r="C60" t="str">
-        <v>4.5 ng/mL未満（施設差あり）</v>
+        <v>治療域の目安 1.6〜3.0（ワルファリン服用時。年齢・疾患により異なる）</v>
       </c>
       <c r="D60" t="str">
-        <v>ビタミンKが不足していないかを反映する骨の指標</v>
+        <v>血液の固まりやすさを表す数値で、ワルファリンの効き具合を確認するために使う</v>
       </c>
       <c r="E60" t="str">
-        <v>ucOCは、骨を作るために必要なビタミンKが体の中で足りているかどうかを反映する検査です。数値が高いとビタミンK不足が疑われます。</v>
+        <v>PT-INRは血液が固まるまでの時間をもとにした数値で、ワルファリンというお薬を飲んでいる方の効き具合を確認するために測ります。数値が高いほど血液が固まりにくく出血しやすい状態、低いほど血栓ができやすい状態を示します。</v>
       </c>
       <c r="F60" t="str">
-        <v>ビタミンK不足状態</v>
+        <v>ワルファリンの効きすぎ、肝機能低下、ビタミンK不足、納豆・青汁など摂取量の変化</v>
       </c>
       <c r="G60" t="str">
-        <v>ビタミンK2製剤(骨粗鬆症治療薬)の適応が検討されているか確認する。ワルファリン服用中の患者では、納豆などビタミンKを多く含む食品の急な摂取量の変化を避けるよう説明する</v>
+        <v>歯ぐきや鼻からの出血、あざ、黒い便などの出血症状がないか確認する。納豆・クロレラ・青汁などビタミンKを多く含む食品の摂取状況を確認する</v>
       </c>
       <c r="H60" t="str">
-        <v/>
+        <v>ワルファリンの過量。ワルファリン服用中はST合剤・マクロライド系・フルコナゾール等の相互作用やビタミンK摂取量の変化にも注意</v>
       </c>
       <c r="I60" t="str">
-        <v/>
+        <v>ワルファリンの効き不足、飲み忘れ、ビタミンK摂取量の急激な増加</v>
       </c>
       <c r="J60" t="str">
-        <v/>
+        <v>服薬状況（飲み忘れ）を確認する。片側のむくみ・しびれ・胸痛など血栓症状がないか確認する</v>
       </c>
       <c r="K60" t="str">
-        <v/>
+        <v>ワルファリン服用中で低値の場合は効果不十分の可能性。ビタミンK摂取量の変化や、リファンピシン・カルバマゼピン・バルビツール酸系など代謝を促進する薬との併用を確認</v>
       </c>
       <c r="L60" t="str">
-        <v>ビタミンK2製剤（骨粗鬆症治療薬）の適応判断や効果判定に使われる</v>
+        <v>治療域は疾患・年齢によって異なる（例：非弁膜症性心房細動の高齢者では1.6〜2.6が目安になることが多い）。多くの薬剤・食品と相互作用があるため新規薬剤追加時は必ず確認する。DOAC（エリキュース、リクシアナ、プラザキサなど）ではPT-INRのモニタリングは不要</v>
       </c>
       <c r="M60" t="str">
-        <v>骨粗鬆症</v>
+        <v>抗凝固療法（心房細動・血栓症）</v>
       </c>
       <c r="N60" t="str">
-        <v>ucOC,オステオカルシン,ビタミンK</v>
+        <v>PT-INR,INR,プロトロンビン時間,ワルファリン,ワーファリン,抗凝固</v>
       </c>
       <c r="O60" t="str">
-        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
+        <v>食事と栄養 p.221（心疾患Q93 ワルファリン服用中のビタミンK摂取）</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>PTH（副甲状腺ホルモン）</v>
+        <v>骨型酒石酸抵抗性フォスファターゼ（TRACP-5b）</v>
       </c>
       <c r="B61" t="str">
-        <v>PTH</v>
+        <v>TRACP-5b</v>
       </c>
       <c r="C61" t="str">
-        <v>10〜65 pg/mL（施設差あり）</v>
+        <v>120〜420 mU/dL</v>
       </c>
       <c r="D61" t="str">
-        <v>血液中のカルシウム濃度を調節するホルモン</v>
+        <v>骨がどれくらい壊されているかを見る検査。骨は「古い骨を壊して新しい骨を作る」入れ替えを繰り返しており、骨を壊す細胞が活発だとこの物質が血液中に増える。</v>
       </c>
       <c r="E61" t="str">
-        <v>PTHは、血液中のカルシウム濃度を一定に保つために働くホルモンです。カルシウムが低くなると分泌が増え、骨からカルシウムを取り出したり、腎臓での再吸収を促したりして数値を戻そうとします。</v>
+        <v>この検査は、骨がどれくらい早く減っていないかを見るものです。数値が高いと、骨が弱くなりやすい状態の目安になります。</v>
       </c>
       <c r="F61" t="str">
-        <v>原発性・二次性副甲状腺機能亢進症（腎不全に伴うものなど）</v>
+        <v>骨粗鬆症、骨代謝回転（骨がこわれるスピード）が活発な状態</v>
       </c>
       <c r="G61" t="str">
-        <v/>
+        <v>カルシウム・ビタミンDの摂取や、適度な荷重運動（ウォーキングなど）を意識するよう伝える</v>
       </c>
       <c r="H61" t="str">
         <v/>
       </c>
       <c r="I61" t="str">
-        <v>副甲状腺機能低下症</v>
+        <v/>
       </c>
       <c r="J61" t="str">
         <v/>
@@ -3279,36 +3279,36 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>骨粗鬆症の二次性原因（副甲状腺機能亢進症）を除外するための検査。カルシウム・リンと合わせて評価する</v>
+        <v>「骨を壊す側」の指標。「骨を作る側」の検査と合わせて評価する。数値だけで診断はしない</v>
       </c>
       <c r="M61" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="N61" t="str">
-        <v>PTH,副甲状腺ホルモン,パラトルモン</v>
+        <v>TRACP-5b,骨型酒石酸抵抗性フォスファターゼ,骨粗鬆症,骨代謝</v>
       </c>
       <c r="O61" t="str">
-        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
+        <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>尿中NTX</v>
+        <v>骨型アルカリフォスファターゼ</v>
       </c>
       <c r="B62" t="str">
-        <v>NTX</v>
+        <v>BAP</v>
       </c>
       <c r="C62" t="str">
-        <v>施設差が大きく一律の記載が難しい（尿中）</v>
+        <v>男性 3.7〜20.9 μg/L、女性（閉経前）2.9〜14.5 μg/L（施設差あり）</v>
       </c>
       <c r="D62" t="str">
-        <v>骨が壊されるときに出る、骨吸収マーカーのひとつ</v>
+        <v>ALPのうち骨に由来する成分だけを測定し、骨が作られる勢い（骨形成）を反映する</v>
       </c>
       <c r="E62" t="str">
-        <v>NTXは、骨が壊される（吸収される）ときに尿の中に出てくる物質です。骨粗鬆症の治療薬がどれくらい効いているかを確認するために使われます。</v>
+        <v>骨型ALPは、通常のALP（アルカリフォスファターゼ）の中でも、骨で作られる成分だけを選んで測定するものです。骨を新しく作る働きがどれくらい活発かを見る指標として、骨粗鬆症の治療効果判定などに使われます。</v>
       </c>
       <c r="F62" t="str">
-        <v>骨代謝回転の亢進（骨粗鬆症、閉経後など）</v>
+        <v>骨代謝回転の亢進（骨粗鬆症、骨折治癒過程、骨形成促進薬による治療効果、Paget病、骨転移）</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -3317,7 +3317,7 @@
         <v/>
       </c>
       <c r="I62" t="str">
-        <v>骨吸収抑制薬（ビスホスホネート等）による治療効果</v>
+        <v>骨形成の低下</v>
       </c>
       <c r="J62" t="str">
         <v/>
@@ -3326,92 +3326,92 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>治療開始後3〜6か月で再検し、薬の効果判定に使われる。TRACP-5bと同じ「骨を壊す側」の指標</v>
+        <v>通常のALPと異なり肝臓の影響を受けにくいため、肝機能異常がある患者でも骨代謝を評価しやすい。P1NPと同じ「骨を作る側」の指標で、骨形成促進薬（テリパラチド等）の効果判定に使われる</v>
       </c>
       <c r="M62" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="N62" t="str">
-        <v>NTX,尿中NTX,骨吸収マーカー</v>
+        <v>骨型ALP,BAP,骨型アルカリフォスファターゼ,骨形成マーカー</v>
       </c>
       <c r="O62" t="str">
-        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
+        <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>カルシトニン</v>
+        <v>25-ヒドロキシビタミンD</v>
       </c>
       <c r="B63" t="str">
-        <v>CT</v>
+        <v>25(OH)D</v>
       </c>
       <c r="C63" t="str">
-        <v>男性 9.52 pg/mL未満、女性 6.40 pg/mL未満（施設差あり）</v>
+        <v>30 ng/mL以上：充足、20〜30 ng/mL：不足、20 ng/mL未満：欠乏（施設差あり）</v>
       </c>
       <c r="D63" t="str">
-        <v>血液中のカルシウムを下げる方向に働くホルモン</v>
+        <v>体内のビタミンDの蓄え具合を反映する指標。カルシウムの吸収や骨の健康に関わる</v>
       </c>
       <c r="E63" t="str">
-        <v>カルシトニンは、PTHとは逆に血液中のカルシウムを下げる方向に働くホルモンです。特定の甲状腺の病気（甲状腺髄様癌）がないかを調べる際にも使われます。</v>
+        <v>この検査は、体の中にビタミンDがどれくらい蓄えられているかを見るものです。ビタミンDは、食事から摂ったカルシウムを腸で吸収するのを助ける働きがあり、不足すると骨がもろくなりやすくなります。</v>
       </c>
       <c r="F63" t="str">
-        <v>甲状腺髄様癌、腎不全</v>
+        <v>ビタミンD製剤の過剰摂取</v>
       </c>
       <c r="G63" t="str">
-        <v/>
+        <v>活性型ビタミンD3製剤やサプリメントの摂取量を確認する。高カルシウム血症の症状（吐き気、便秘、多尿など）がないか確認する</v>
       </c>
       <c r="H63" t="str">
-        <v/>
+        <v>活性型/天然型ビタミンD製剤の過量投与</v>
       </c>
       <c r="I63" t="str">
-        <v/>
+        <v>日光暴露不足、食事摂取不足、高齢、腸疾患による吸収不良、肝・腎機能低下（活性化障害）</v>
       </c>
       <c r="J63" t="str">
-        <v/>
+        <v>適度な日光浴、魚類・きのこ類などビタミンDを多く含む食品の摂取を意識するとよいことを伝える</v>
       </c>
       <c r="K63" t="str">
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>骨粗鬆症の二次性原因の除外目的で測定されることがある検査値。同名の薬剤（カルシトニン製剤）と混同しないよう注意</v>
+        <v>骨粗鬆症治療における活性型ビタミンD3製剤の効果判定や、投与量調整の参考に用いられる。腎機能低下患者では活性化障害により25(OH)Dが正常でも活性型が不足することがある点に注意</v>
       </c>
       <c r="M63" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="N63" t="str">
-        <v>カルシトニン,CT</v>
+        <v>25(OH)D,ビタミンD,25-ヒドロキシビタミンD,ビタミンD欠乏,骨粗鬆症</v>
       </c>
       <c r="O63" t="str">
-        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
+        <v>食事と栄養 p.38（ビタミンD）</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>DPD（デオキシピリジノリン）</v>
+        <v>ucOC（低カルボキシル化オステオカルシン）</v>
       </c>
       <c r="B64" t="str">
-        <v>DPD</v>
+        <v>ucOC</v>
       </c>
       <c r="C64" t="str">
-        <v>施設差が大きく一律の記載が難しい（尿中）</v>
+        <v>4.5 ng/mL未満（施設差あり）</v>
       </c>
       <c r="D64" t="str">
-        <v>骨のコラーゲンが壊れるときに出る、骨吸収マーカーのひとつ</v>
+        <v>ビタミンKが不足していないかを反映する骨の指標</v>
       </c>
       <c r="E64" t="str">
-        <v>DPDも、骨が壊されるときに尿に出てくる物質の一つです。NTXと同じように、骨粗鬆症治療薬の効果を確認するために使われます。</v>
+        <v>ucOCは、骨を作るために必要なビタミンKが体の中で足りているかどうかを反映する検査です。数値が高いとビタミンK不足が疑われます。</v>
       </c>
       <c r="F64" t="str">
-        <v>骨代謝回転の亢進（骨粗鬆症など）</v>
+        <v>ビタミンK不足状態</v>
       </c>
       <c r="G64" t="str">
-        <v/>
+        <v>ビタミンK2製剤(骨粗鬆症治療薬)の適応が検討されているか確認する。ワルファリン服用中の患者では、納豆などビタミンKを多く含む食品の急な摂取量の変化を避けるよう説明する</v>
       </c>
       <c r="H64" t="str">
         <v/>
       </c>
       <c r="I64" t="str">
-        <v>骨吸収抑制薬による治療効果</v>
+        <v/>
       </c>
       <c r="J64" t="str">
         <v/>
@@ -3420,13 +3420,13 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>NTX・CTXと同じ「骨を壊す側」の指標。食事の影響を受けにくいとされる</v>
+        <v>ビタミンK2製剤（骨粗鬆症治療薬）の適応判断や効果判定に使われる</v>
       </c>
       <c r="M64" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="N64" t="str">
-        <v>DPD,デオキシピリジノリン,骨吸収マーカー</v>
+        <v>ucOC,オステオカルシン,ビタミンK</v>
       </c>
       <c r="O64" t="str">
         <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
@@ -3434,22 +3434,22 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>CTX</v>
+        <v>PTH（副甲状腺ホルモン）</v>
       </c>
       <c r="B65" t="str">
-        <v>CTX</v>
+        <v>PTH</v>
       </c>
       <c r="C65" t="str">
-        <v>施設差が大きく一律の記載が難しい（血清・尿中）</v>
+        <v>10〜65 pg/mL（施設差あり）</v>
       </c>
       <c r="D65" t="str">
-        <v>骨のコラーゲンが壊れるときに出る、骨吸収マーカーのひとつ</v>
+        <v>血液中のカルシウム濃度を調節するホルモン</v>
       </c>
       <c r="E65" t="str">
-        <v>CTXも、骨が壊されるときに血液や尿に出てくる物質です。骨粗鬆症治療薬（骨を壊すのを抑える薬）の効果を確認するために使われます。</v>
+        <v>PTHは、血液中のカルシウム濃度を一定に保つために働くホルモンです。カルシウムが低くなると分泌が増え、骨からカルシウムを取り出したり、腎臓での再吸収を促したりして数値を戻そうとします。</v>
       </c>
       <c r="F65" t="str">
-        <v>骨代謝回転の亢進（骨粗鬆症など）</v>
+        <v>原発性・二次性副甲状腺機能亢進症（腎不全に伴うものなど）</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -3458,7 +3458,7 @@
         <v/>
       </c>
       <c r="I65" t="str">
-        <v>骨吸収抑制薬による治療効果</v>
+        <v>副甲状腺機能低下症</v>
       </c>
       <c r="J65" t="str">
         <v/>
@@ -3467,13 +3467,13 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>NTX・DPDと同じ「骨を壊す側」の指標。血清・尿中いずれでも測定されることがある</v>
+        <v>骨粗鬆症の二次性原因（副甲状腺機能亢進症）を除外するための検査。カルシウム・リンと合わせて評価する</v>
       </c>
       <c r="M65" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="N65" t="str">
-        <v>CTX,骨吸収マーカー</v>
+        <v>PTH,副甲状腺ホルモン,パラトルモン</v>
       </c>
       <c r="O65" t="str">
         <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
@@ -3481,22 +3481,22 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>P1NP</v>
+        <v>尿中NTX</v>
       </c>
       <c r="B66" t="str">
-        <v>P1NP</v>
+        <v>NTX</v>
       </c>
       <c r="C66" t="str">
-        <v>施設差が大きく一律の記載が難しい（血清）</v>
+        <v>施設差が大きく一律の記載が難しい（尿中）</v>
       </c>
       <c r="D66" t="str">
-        <v>骨が新しく作られるときに出る、骨形成マーカーのひとつ</v>
+        <v>骨が壊されるときに出る、骨吸収マーカーのひとつ</v>
       </c>
       <c r="E66" t="str">
-        <v>P1NPは、CTXなどとは逆に、骨が新しく作られるときに血液中に出てくる物質です。骨を作る力を高める薬（テリパラチドなど）の効果を確認するために使われます。</v>
+        <v>NTXは、骨が壊される（吸収される）ときに尿の中に出てくる物質です。骨粗鬆症の治療薬がどれくらい効いているかを確認するために使われます。</v>
       </c>
       <c r="F66" t="str">
-        <v>骨代謝回転の亢進、骨形成促進薬による治療効果</v>
+        <v>骨代謝回転の亢進（骨粗鬆症、閉経後など）</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -3505,7 +3505,7 @@
         <v/>
       </c>
       <c r="I66" t="str">
-        <v>骨形成の低下</v>
+        <v>骨吸収抑制薬（ビスホスホネート等）による治療効果</v>
       </c>
       <c r="J66" t="str">
         <v/>
@@ -3514,13 +3514,13 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>TRACP-5b等「骨を壊す側」の指標とは逆の、「骨を作る側」の指標。骨形成促進薬（テリパラチド等）の効果判定に使われる</v>
+        <v>治療開始後3〜6か月で再検し、薬の効果判定に使われる。TRACP-5bと同じ「骨を壊す側」の指標</v>
       </c>
       <c r="M66" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="N66" t="str">
-        <v>P1NP,骨形成マーカー</v>
+        <v>NTX,尿中NTX,骨吸収マーカー</v>
       </c>
       <c r="O66" t="str">
         <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
@@ -3528,69 +3528,69 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>血清鉄（Fe）</v>
+        <v>カルシトニン</v>
       </c>
       <c r="B67" t="str">
-        <v>Fe</v>
+        <v>CT</v>
       </c>
       <c r="C67" t="str">
-        <v>60〜200 μg/dL（施設差あり）</v>
+        <v>男性 9.52 pg/mL未満、女性 6.40 pg/mL未満（施設差あり）</v>
       </c>
       <c r="D67" t="str">
-        <v>血液中を流れている鉄の量</v>
+        <v>血液中のカルシウムを下げる方向に働くホルモン</v>
       </c>
       <c r="E67" t="str">
-        <v>この検査は、今血液の中を流れている鉄の量を見るものです。低いと、体の中で鉄が不足している可能性があります。</v>
+        <v>カルシトニンは、PTHとは逆に血液中のカルシウムを下げる方向に働くホルモンです。特定の甲状腺の病気（甲状腺髄様癌）がないかを調べる際にも使われます。</v>
       </c>
       <c r="F67" t="str">
-        <v>鉄剤の過剰摂取、溶血、肝疾患</v>
+        <v>甲状腺髄様癌、腎不全</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>鉄剤の過量摂取(小児の誤飲を含む)</v>
+        <v/>
       </c>
       <c r="I67" t="str">
-        <v>鉄欠乏性貧血、慢性炎症、出血</v>
+        <v/>
       </c>
       <c r="J67" t="str">
-        <v>鉄分の多い食品（レバー・赤身肉・魚・ほうれん草など）を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える</v>
+        <v/>
       </c>
       <c r="K67" t="str">
-        <v>プロトンポンプ阻害薬(PPI)・H2ブロッカーは胃酸分泌抑制により鉄の吸収を低下させうる</v>
+        <v/>
       </c>
       <c r="L67" t="str">
-        <v>血清鉄は日内変動が大きい。単独で判断せず総鉄結合能・フェリチンと合わせて評価する</v>
+        <v>骨粗鬆症の二次性原因の除外目的で測定されることがある検査値。同名の薬剤（カルシトニン製剤）と混同しないよう注意</v>
       </c>
       <c r="M67" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="N67" t="str">
-        <v>血清鉄,Fe,鉄欠乏性貧血</v>
+        <v>カルシトニン,CT</v>
       </c>
       <c r="O67" t="str">
-        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>総鉄結合能（TIBC）</v>
+        <v>DPD（デオキシピリジノリン）</v>
       </c>
       <c r="B68" t="str">
-        <v>TIBC</v>
+        <v>DPD</v>
       </c>
       <c r="C68" t="str">
-        <v>250〜360 μg/dL（施設差あり）</v>
+        <v>施設差が大きく一律の記載が難しい（尿中）</v>
       </c>
       <c r="D68" t="str">
-        <v>血液中のトランスフェリンが鉄と結合できる総量</v>
+        <v>骨のコラーゲンが壊れるときに出る、骨吸収マーカーのひとつ</v>
       </c>
       <c r="E68" t="str">
-        <v>TIBCは、血液中でトランスフェリンという物質が鉄を運べる最大量を表します。体の中の鉄が不足すると、少しでも多く鉄を運ぼうとしてこの数値が上がる性質があります。</v>
+        <v>DPDも、骨が壊されるときに尿に出てくる物質の一つです。NTXと同じように、骨粗鬆症治療薬の効果を確認するために使われます。</v>
       </c>
       <c r="F68" t="str">
-        <v>鉄欠乏性貧血（＞360 μg/dLが目安）</v>
+        <v>骨代謝回転の亢進（骨粗鬆症など）</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v/>
       </c>
       <c r="I68" t="str">
-        <v>慢性炎症、肝疾患、ネフローゼ症候群</v>
+        <v>骨吸収抑制薬による治療効果</v>
       </c>
       <c r="J68" t="str">
         <v/>
@@ -3608,36 +3608,36 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>鉄が不足すると、体はより多く運ぼうとしてTIBCが上昇する。UIBC・血清鉄と併せて評価する</v>
+        <v>NTX・CTXと同じ「骨を壊す側」の指標。食事の影響を受けにくいとされる</v>
       </c>
       <c r="M68" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="N68" t="str">
-        <v>TIBC,総鉄結合能,鉄欠乏性貧血</v>
+        <v>DPD,デオキシピリジノリン,骨吸収マーカー</v>
       </c>
       <c r="O68" t="str">
-        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>不飽和鉄結合能（UIBC）</v>
+        <v>CTX</v>
       </c>
       <c r="B69" t="str">
-        <v>UIBC</v>
+        <v>CTX</v>
       </c>
       <c r="C69" t="str">
-        <v>170〜300 μg/dL（施設差あり）</v>
+        <v>施設差が大きく一律の記載が難しい（血清・尿中）</v>
       </c>
       <c r="D69" t="str">
-        <v>トランスフェリンのうち、まだ鉄と結合していない余力の部分（UIBC＝TIBC－血清鉄）</v>
+        <v>骨のコラーゲンが壊れるときに出る、骨吸収マーカーのひとつ</v>
       </c>
       <c r="E69" t="str">
-        <v>UIBCは、トランスフェリンのうち、まだ鉄と結合していない「空き容量」の部分を表します。鉄が不足しているときほど、この空き容量は大きくなります。</v>
+        <v>CTXも、骨が壊されるときに血液や尿に出てくる物質です。骨粗鬆症治療薬（骨を壊すのを抑える薬）の効果を確認するために使われます。</v>
       </c>
       <c r="F69" t="str">
-        <v>鉄欠乏性貧血（＞300 μg/dLが目安）</v>
+        <v>骨代謝回転の亢進（骨粗鬆症など）</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3646,7 +3646,7 @@
         <v/>
       </c>
       <c r="I69" t="str">
-        <v>慢性炎症、鉄過剰状態</v>
+        <v>骨吸収抑制薬による治療効果</v>
       </c>
       <c r="J69" t="str">
         <v/>
@@ -3655,36 +3655,36 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>TIBCと同じ方向に動くことが多い。血清鉄・TIBCとあわせて鉄欠乏性貧血と二次性貧血の鑑別に使う</v>
+        <v>NTX・DPDと同じ「骨を壊す側」の指標。血清・尿中いずれでも測定されることがある</v>
       </c>
       <c r="M69" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="N69" t="str">
-        <v>UIBC,不飽和鉄結合能,鉄欠乏性貧血</v>
+        <v>CTX,骨吸収マーカー</v>
       </c>
       <c r="O69" t="str">
-        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>トランスフェリン飽和度</v>
+        <v>P1NP</v>
       </c>
       <c r="B70" t="str">
-        <v>TSAT</v>
+        <v>P1NP</v>
       </c>
       <c r="C70" t="str">
-        <v>16〜50%程度（施設差あり）</v>
+        <v>施設差が大きく一律の記載が難しい（血清）</v>
       </c>
       <c r="D70" t="str">
-        <v>鉄を運ぶ役割のトランスフェリンのうち、実際に鉄を運んでいる割合（血清鉄÷総鉄結合能）</v>
+        <v>骨が新しく作られるときに出る、骨形成マーカーのひとつ</v>
       </c>
       <c r="E70" t="str">
-        <v>トランスフェリン飽和度は、鉄を運ぶトランスフェリンのうち、実際にどれくらいが鉄を運んでいるかを割合で表したものです。鉄欠乏性貧血では低くなり、鉄が過剰にたまる病気では高くなります。</v>
+        <v>P1NPは、CTXなどとは逆に、骨が新しく作られるときに血液中に出てくる物質です。骨を作る力を高める薬（テリパラチドなど）の効果を確認するために使われます。</v>
       </c>
       <c r="F70" t="str">
-        <v>鉄過剰症（ヘモクロマトーシスなど）</v>
+        <v>骨代謝回転の亢進、骨形成促進薬による治療効果</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3693,7 +3693,7 @@
         <v/>
       </c>
       <c r="I70" t="str">
-        <v>鉄欠乏性貧血（＜16%が目安）</v>
+        <v>骨形成の低下</v>
       </c>
       <c r="J70" t="str">
         <v/>
@@ -3702,60 +3702,60 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>血清鉄をTIBCで割って計算される。鉄剤補充の効果判定にも使われる</v>
+        <v>TRACP-5b等「骨を壊す側」の指標とは逆の、「骨を作る側」の指標。骨形成促進薬（テリパラチド等）の効果判定に使われる</v>
       </c>
       <c r="M70" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="N70" t="str">
-        <v>トランスフェリン飽和度,TSAT,鉄欠乏性貧血</v>
+        <v>P1NP,骨形成マーカー</v>
       </c>
       <c r="O70" t="str">
-        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>血清フェリチン</v>
+        <v>血清鉄（Fe）</v>
       </c>
       <c r="B71" t="str">
-        <v>Ferritin</v>
+        <v>Fe</v>
       </c>
       <c r="C71" t="str">
-        <v>男性 20〜250 ng/mL、女性 10〜120 ng/mL（施設差あり）</v>
+        <v>60〜200 μg/dL（施設差あり）</v>
       </c>
       <c r="D71" t="str">
-        <v>体に貯蔵されている鉄の量を反映する指標。貧血の症状が出るより早い段階で低下する</v>
+        <v>血液中を流れている鉄の量</v>
       </c>
       <c r="E71" t="str">
-        <v>フェリチンは、体に蓄えられている鉄の「貯金」の量を見る検査です。この数値が下がるのは、貧血の症状が出るよりも前の、とても早い段階のサインになります。</v>
+        <v>この検査は、今血液の中を流れている鉄の量を見るものです。低いと、体の中で鉄が不足している可能性があります。</v>
       </c>
       <c r="F71" t="str">
-        <v>炎症性疾患、肝疾患、悪性腫瘍、鉄過剰症（フェリチンは炎症でも上昇するため、貧血の評価では注意が必要）</v>
+        <v>鉄剤の過剰摂取、溶血、肝疾患</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v/>
+        <v>鉄剤の過量摂取(小児の誤飲を含む)</v>
       </c>
       <c r="I71" t="str">
-        <v>鉄欠乏状態（貧血の症状が出る前の早期段階から低下する）</v>
+        <v>鉄欠乏性貧血、慢性炎症、出血</v>
       </c>
       <c r="J71" t="str">
-        <v>鉄分の多い食品を意識するとともに、貯蔵鉄を補うため治療は数値が正常化してからも継続が必要なことを伝える</v>
+        <v>鉄分の多い食品（レバー・赤身肉・魚・ほうれん草など）を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える</v>
       </c>
       <c r="K71" t="str">
-        <v/>
+        <v>プロトンポンプ阻害薬(PPI)・H2ブロッカーは胃酸分泌抑制により鉄の吸収を低下させうる</v>
       </c>
       <c r="L71" t="str">
-        <v>貯蔵鉄の指標で鉄欠乏を最も早期に反映する。ただし炎症があると鉄欠乏があっても正常〜高値に出ることがあり、CRP等の炎症所見と合わせて評価する。二次性貧血との鑑別に重要</v>
+        <v>血清鉄は日内変動が大きい。単独で判断せず総鉄結合能・フェリチンと合わせて評価する</v>
       </c>
       <c r="M71" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
       <c r="N71" t="str">
-        <v>フェリチン,Ferritin,貯蔵鉄,鉄欠乏</v>
+        <v>血清鉄,Fe,鉄欠乏性貧血</v>
       </c>
       <c r="O71" t="str">
         <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
@@ -3763,22 +3763,22 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>尿中尿酸/クレアチニン比（UUA/UCr）</v>
+        <v>総鉄結合能（TIBC）</v>
       </c>
       <c r="B72" t="str">
-        <v>UUA/UCr</v>
+        <v>TIBC</v>
       </c>
       <c r="C72" t="str">
-        <v>0.4〜0.8程度が混合型の目安</v>
+        <v>250〜360 μg/dL（施設差あり）</v>
       </c>
       <c r="D72" t="str">
-        <v>尿酸が「作られすぎ」か「排泄できていない」かを見分ける比の値</v>
+        <v>血液中のトランスフェリンが鉄と結合できる総量</v>
       </c>
       <c r="E72" t="str">
-        <v>この数値は、体の中で尿酸が「作られすぎている」のか、それとも「うまく排泄できていない」のかを見分けるために使う比の値です。高尿酸血症の治療薬を選ぶときの参考になります。</v>
+        <v>TIBCは、血液中でトランスフェリンという物質が鉄を運べる最大量を表します。体の中の鉄が不足すると、少しでも多く鉄を運ぼうとしてこの数値が上がる性質があります。</v>
       </c>
       <c r="F72" t="str">
-        <v>尿酸産生過剰型（0.8以上が目安）</v>
+        <v>鉄欠乏性貧血（＞360 μg/dLが目安）</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3787,7 +3787,7 @@
         <v/>
       </c>
       <c r="I72" t="str">
-        <v>尿酸排泄低下型（0.4以下が目安）</v>
+        <v>慢性炎症、肝疾患、ネフローゼ症候群</v>
       </c>
       <c r="J72" t="str">
         <v/>
@@ -3796,36 +3796,36 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>高尿酸血症は尿酸産生過剰型・排泄低下型・混合型に分類され、この比が目安になる。病型によって使う薬剤（尿酸生成抑制薬か尿酸排泄促進薬か）の選択が変わる</v>
+        <v>鉄が不足すると、体はより多く運ぼうとしてTIBCが上昇する。UIBC・血清鉄と併せて評価する</v>
       </c>
       <c r="M72" t="str">
-        <v>高尿酸血症</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="N72" t="str">
-        <v>UUA,UCr,尿酸クリアランス,CUA,EUA,尿酸産生過剰型,尿酸排泄低下型</v>
+        <v>TIBC,総鉄結合能,鉄欠乏性貧血</v>
       </c>
       <c r="O72" t="str">
-        <v>食事と栄養 p.180-189（第2部 痛風・高尿酸血症）</v>
+        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>抗甲状腺マイクロゾーム抗体（抗TPO抗体）</v>
+        <v>不飽和鉄結合能（UIBC）</v>
       </c>
       <c r="B73" t="str">
-        <v>TPOAb</v>
+        <v>UIBC</v>
       </c>
       <c r="C73" t="str">
-        <v>陰性（16 IU/mL未満程度、施設差あり）</v>
+        <v>170〜300 μg/dL（施設差あり）</v>
       </c>
       <c r="D73" t="str">
-        <v>自分の甲状腺を攻撃する抗体が出ていないかを見る検査</v>
+        <v>トランスフェリンのうち、まだ鉄と結合していない余力の部分（UIBC＝TIBC－血清鉄）</v>
       </c>
       <c r="E73" t="str">
-        <v>この検査は、体の中に自分の甲状腺を誤って攻撃してしまう抗体がないかを見るものです。陽性の場合、橋本病（慢性甲状腺炎）など甲状腺の自己免疫的な炎症が背景にある可能性があります。</v>
+        <v>UIBCは、トランスフェリンのうち、まだ鉄と結合していない「空き容量」の部分を表します。鉄が不足しているときほど、この空き容量は大きくなります。</v>
       </c>
       <c r="F73" t="str">
-        <v>橋本病（慢性甲状腺炎）、バセドウ病などの自己免疫性甲状腺疾患</v>
+        <v>鉄欠乏性貧血（＞300 μg/dLが目安）</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3834,7 +3834,7 @@
         <v/>
       </c>
       <c r="I73" t="str">
-        <v/>
+        <v>慢性炎症、鉄過剰状態</v>
       </c>
       <c r="J73" t="str">
         <v/>
@@ -3843,36 +3843,36 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>陽性でも必ずしも甲状腺機能異常があるとは限らない。TSH・FT4など甲状腺ホルモンの数値と合わせて評価する</v>
+        <v>TIBCと同じ方向に動くことが多い。血清鉄・TIBCとあわせて鉄欠乏性貧血と二次性貧血の鑑別に使う</v>
       </c>
       <c r="M73" t="str">
-        <v>甲状腺疾患</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="N73" t="str">
-        <v>抗TPO抗体,抗甲状腺マイクロゾーム抗体,TPOAb,橋本病</v>
+        <v>UIBC,不飽和鉄結合能,鉄欠乏性貧血</v>
       </c>
       <c r="O73" t="str">
-        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
+        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>抗サイログロブリン抗体</v>
+        <v>トランスフェリン飽和度</v>
       </c>
       <c r="B74" t="str">
-        <v>TgAb</v>
+        <v>TSAT</v>
       </c>
       <c r="C74" t="str">
-        <v>陰性（28 IU/mL未満程度、施設差あり）</v>
+        <v>16〜50%程度（施設差あり）</v>
       </c>
       <c r="D74" t="str">
-        <v>甲状腺のたんぱく質（サイログロブリン）への抗体が出ていないかを見る検査</v>
+        <v>鉄を運ぶ役割のトランスフェリンのうち、実際に鉄を運んでいる割合（血清鉄÷総鉄結合能）</v>
       </c>
       <c r="E74" t="str">
-        <v>この検査も、抗TPO抗体と同じく、甲状腺に対する自己免疫の有無を見るものです。あわせて調べることで橋本病などの診断の参考にします。</v>
+        <v>トランスフェリン飽和度は、鉄を運ぶトランスフェリンのうち、実際にどれくらいが鉄を運んでいるかを割合で表したものです。鉄欠乏性貧血では低くなり、鉄が過剰にたまる病気では高くなります。</v>
       </c>
       <c r="F74" t="str">
-        <v>橋本病（慢性甲状腺炎）、バセドウ病などの自己免疫性甲状腺疾患</v>
+        <v>鉄過剰症（ヘモクロマトーシスなど）</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3881,7 +3881,7 @@
         <v/>
       </c>
       <c r="I74" t="str">
-        <v/>
+        <v>鉄欠乏性貧血（＜16%が目安）</v>
       </c>
       <c r="J74" t="str">
         <v/>
@@ -3890,92 +3890,92 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>抗TPO抗体とあわせて測定されることが多い。単独の高値だけで治療方針が決まるわけではない</v>
+        <v>血清鉄をTIBCで割って計算される。鉄剤補充の効果判定にも使われる</v>
       </c>
       <c r="M74" t="str">
-        <v>甲状腺疾患</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="N74" t="str">
-        <v>抗サイログロブリン抗体,TgAb,橋本病</v>
+        <v>トランスフェリン飽和度,TSAT,鉄欠乏性貧血</v>
       </c>
       <c r="O74" t="str">
-        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
+        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>血中薬物濃度（TDM）</v>
+        <v>血清フェリチン</v>
       </c>
       <c r="B75" t="str">
-        <v>TDM</v>
+        <v>Ferritin</v>
       </c>
       <c r="C75" t="str">
-        <v>薬剤ごとに有効域が異なる（例：カルバマゼピン 4〜12 μg/mL、バルプロ酸 40〜100 μg/mL、フェニトイン 10〜20 μg/mL）</v>
+        <v>男性 20〜250 ng/mL、女性 10〜120 ng/mL（施設差あり）</v>
       </c>
       <c r="D75" t="str">
-        <v>治療域が狭い薬剤で、血液中の薬の濃度が効果域・中毒域のどちらにあるかを確認する検査</v>
+        <v>体に貯蔵されている鉄の量を反映する指標。貧血の症状が出るより早い段階で低下する</v>
       </c>
       <c r="E75" t="str">
-        <v>この薬は効く量と副作用が出る量が近いため、血液中の薬の濃度を定期的に測って、ちょうどよい範囲に入っているかを確認します。数値が低いと効果が不十分になり、高いと副作用が出やすくなります。</v>
+        <v>フェリチンは、体に蓄えられている鉄の「貯金」の量を見る検査です。この数値が下がるのは、貧血の症状が出るよりも前の、とても早い段階のサインになります。</v>
       </c>
       <c r="F75" t="str">
-        <v>過量投与、代謝を妨げる薬剤との併用、肝機能低下による代謝低下</v>
+        <v>炎症性疾患、肝疾患、悪性腫瘍、鉄過剰症（フェリチンは炎症でも上昇するため、貧血の評価では注意が必要）</v>
       </c>
       <c r="G75" t="str">
-        <v>ふらつき、眠気、めまい、物が二重に見えるなどの中毒症状がないか確認する</v>
+        <v/>
       </c>
       <c r="H75" t="str">
         <v/>
       </c>
       <c r="I75" t="str">
-        <v>飲み忘れ、自己判断による減量、代謝を促進する薬剤との併用（相互作用）</v>
+        <v>鉄欠乏状態（貧血の症状が出る前の早期段階から低下する）</v>
       </c>
       <c r="J75" t="str">
-        <v>発作やてんかん症状の再発がないか確認し、飲み忘れがないか一緒に確認する</v>
+        <v>鉄分の多い食品を意識するとともに、貯蔵鉄を補うため治療は数値が正常化してからも継続が必要なことを伝える</v>
       </c>
       <c r="K75" t="str">
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>採血のタイミング（トラフ値かどうか）で数値の解釈が変わるため採血時点を確認する。カルバマゼピンは自己誘導により長期使用で濃度が下がることがある点にも注意</v>
+        <v>貯蔵鉄の指標で鉄欠乏を最も早期に反映する。ただし炎症があると鉄欠乏があっても正常〜高値に出ることがあり、CRP等の炎症所見と合わせて評価する。二次性貧血との鑑別に重要</v>
       </c>
       <c r="M75" t="str">
-        <v>てんかん</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="N75" t="str">
-        <v>TDM,血中薬物濃度,治療域,中毒域,カルバマゼピン,フェニトイン,バルプロ酸,抗てんかん薬</v>
+        <v>フェリチン,Ferritin,貯蔵鉄,鉄欠乏</v>
       </c>
       <c r="O75" t="str">
-        <v/>
+        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>アミラーゼ（AMY）</v>
+        <v>尿中尿酸/クレアチニン比（UUA/UCr）</v>
       </c>
       <c r="B76" t="str">
-        <v>AMY</v>
+        <v>UUA/UCr</v>
       </c>
       <c r="C76" t="str">
-        <v>44〜132 U/L（施設差あり）</v>
+        <v>0.4〜0.8程度が混合型の目安</v>
       </c>
       <c r="D76" t="str">
-        <v>膵臓や唾液腺から出る消化酵素。膵炎などで血液中に漏れ出す</v>
+        <v>尿酸が「作られすぎ」か「排泄できていない」かを見分ける比の値</v>
       </c>
       <c r="E76" t="str">
-        <v>アミラーゼは、でんぷんを分解する消化酵素で、主に膵臓と唾液腺から作られます。膵臓に炎症が起きると血液中に漏れ出して数値が上がるため、膵炎の診断や経過観察に使われます。</v>
+        <v>この数値は、体の中で尿酸が「作られすぎている」のか、それとも「うまく排泄できていない」のかを見分けるために使う比の値です。高尿酸血症の治療薬を選ぶときの参考になります。</v>
       </c>
       <c r="F76" t="str">
-        <v>急性膵炎、慢性膵炎の急性増悪、耳下腺炎（おたふくかぜ）、腎不全</v>
+        <v>尿酸産生過剰型（0.8以上が目安）</v>
       </c>
       <c r="G76" t="str">
-        <v>飲酒を控え、脂っこい食事を避けるよう伝える。強い腹痛・背部痛がある場合は急性膵炎の可能性もあるため早めの受診を勧める</v>
+        <v/>
       </c>
       <c r="H76" t="str">
-        <v>バルプロ酸、アザチオプリン、サイアザイド系・ループ利尿薬、ステロイドなど薬剤性膵炎の原因薬</v>
+        <v/>
       </c>
       <c r="I76" t="str">
-        <v>慢性膵炎の進行期（膵臓の機能低下）</v>
+        <v>尿酸排泄低下型（0.4以下が目安）</v>
       </c>
       <c r="J76" t="str">
         <v/>
@@ -3984,39 +3984,39 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>膵臓由来か唾液腺由来かを区別するには膵型アミラーゼ(P-AMY)を確認する。急性膵炎では強い腹痛・背部痛を伴うことが多く、飲酒歴の確認も重要</v>
+        <v>高尿酸血症は尿酸産生過剰型・排泄低下型・混合型に分類され、この比が目安になる。病型によって使う薬剤（尿酸生成抑制薬か尿酸排泄促進薬か）の選択が変わる</v>
       </c>
       <c r="M76" t="str">
-        <v/>
+        <v>高尿酸血症</v>
       </c>
       <c r="N76" t="str">
-        <v>アミラーゼ,AMY,膵炎,急性膵炎</v>
+        <v>UUA,UCr,尿酸クリアランス,CUA,EUA,尿酸産生過剰型,尿酸排泄低下型</v>
       </c>
       <c r="O76" t="str">
-        <v/>
+        <v>食事と栄養 p.180-189（第2部 痛風・高尿酸血症）</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>間接ビリルビン</v>
+        <v>抗甲状腺マイクロゾーム抗体（抗TPO抗体）</v>
       </c>
       <c r="B77" t="str">
-        <v>I-Bil</v>
+        <v>TPOAb</v>
       </c>
       <c r="C77" t="str">
-        <v>0.2〜0.8 mg/dL程度（施設差あり）</v>
+        <v>陰性（16 IU/mL未満程度、施設差あり）</v>
       </c>
       <c r="D77" t="str">
-        <v>赤血球が壊れてできるビリルビンのうち、肝臓で処理される前の形</v>
+        <v>自分の甲状腺を攻撃する抗体が出ていないかを見る検査</v>
       </c>
       <c r="E77" t="str">
-        <v>間接ビリルビンは、赤血球が壊れてできたビリルビンが、まだ肝臓で処理される前の状態です。この値が高い場合、赤血球が通常より多く壊れている(溶血)か、肝臓での処理能力に生まれつきの体質差(体質性黄疸)がある可能性が考えられます。</v>
+        <v>この検査は、体の中に自分の甲状腺を誤って攻撃してしまう抗体がないかを見るものです。陽性の場合、橋本病（慢性甲状腺炎）など甲状腺の自己免疫的な炎症が背景にある可能性があります。</v>
       </c>
       <c r="F77" t="str">
-        <v>溶血性疾患（自己免疫性溶血性貧血、血液型不適合輸血など）、体質性黄疸（ジルベール症候群）、新生児黄疸</v>
+        <v>橋本病（慢性甲状腺炎）、バセドウ病などの自己免疫性甲状腺疾患</v>
       </c>
       <c r="G77" t="str">
-        <v>皮膚や白目の黄染、尿の色の変化がないか確認する</v>
+        <v/>
       </c>
       <c r="H77" t="str">
         <v/>
@@ -4031,42 +4031,42 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>直接ビリルビンとの比率で原因を推測する（間接優位は溶血・体質性、直接優位は胆道系）。総ビリルビン・AST/ALTと合わせて評価する</v>
+        <v>陽性でも必ずしも甲状腺機能異常があるとは限らない。TSH・FT4など甲状腺ホルモンの数値と合わせて評価する</v>
       </c>
       <c r="M77" t="str">
-        <v>肝機能</v>
+        <v>甲状腺疾患</v>
       </c>
       <c r="N77" t="str">
-        <v>間接ビリルビン,I-Bil,溶血</v>
+        <v>抗TPO抗体,抗甲状腺マイクロゾーム抗体,TPOAb,橋本病</v>
       </c>
       <c r="O77" t="str">
-        <v/>
+        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>直接ビリルビン</v>
+        <v>抗サイログロブリン抗体</v>
       </c>
       <c r="B78" t="str">
-        <v>D-Bil</v>
+        <v>TgAb</v>
       </c>
       <c r="C78" t="str">
-        <v>0.0〜0.3 mg/dL程度（施設差あり）</v>
+        <v>陰性（28 IU/mL未満程度、施設差あり）</v>
       </c>
       <c r="D78" t="str">
-        <v>肝臓で処理された後のビリルビン。胆道の詰まりで血液中に増える</v>
+        <v>甲状腺のたんぱく質（サイログロブリン）への抗体が出ていないかを見る検査</v>
       </c>
       <c r="E78" t="str">
-        <v>直接ビリルビンは、肝臓で処理された後のビリルビンです。胆石や腫瘍などで胆汁の通り道（胆道）が詰まると、行き場を失って血液中に増え、皮膚や白目が黄色くなる黄疸として現れます。</v>
+        <v>この検査も、抗TPO抗体と同じく、甲状腺に対する自己免疫の有無を見るものです。あわせて調べることで橋本病などの診断の参考にします。</v>
       </c>
       <c r="F78" t="str">
-        <v>肝疾患、胆石など胆道の閉塞</v>
+        <v>橋本病（慢性甲状腺炎）、バセドウ病などの自己免疫性甲状腺疾患</v>
       </c>
       <c r="G78" t="str">
-        <v>皮膚や白目の黄染、白っぽい便、濃い茶色の尿がないか確認する</v>
+        <v/>
       </c>
       <c r="H78" t="str">
-        <v>胆汁うっ滞型の薬剤性肝障害を起こしうる抗菌薬、経口避妊薬</v>
+        <v/>
       </c>
       <c r="I78" t="str">
         <v/>
@@ -4078,154 +4078,154 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>直接優位の上昇は胆道系（胆石、腫瘍による閉塞）を、間接優位の上昇は溶血・体質性を疑う手がかりになる。γ-GTP・ALPと合わせて胆道系疾患を評価する</v>
+        <v>抗TPO抗体とあわせて測定されることが多い。単独の高値だけで治療方針が決まるわけではない</v>
       </c>
       <c r="M78" t="str">
-        <v>肝機能</v>
+        <v>甲状腺疾患</v>
       </c>
       <c r="N78" t="str">
-        <v>直接ビリルビン,D-Bil,胆石,胆道閉塞</v>
+        <v>抗サイログロブリン抗体,TgAb,橋本病</v>
       </c>
       <c r="O78" t="str">
-        <v/>
+        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>亜鉛（Zn）</v>
+        <v>血中薬物濃度（TDM）</v>
       </c>
       <c r="B79" t="str">
-        <v>Zn</v>
+        <v>TDM</v>
       </c>
       <c r="C79" t="str">
-        <v>80〜130 μg/dL程度（施設差あり）</v>
+        <v>薬剤ごとに有効域が異なる（例：フェニトイン 10〜20 μg/mL、ゾニサミド 10〜40 μg/mL、カルバマゼピン 4〜12 μg/mL、バルプロ酸ナトリウム 40〜120 μg/mL、ラモトリギン 1〜10 μg/mL(併用薬により変動)）</v>
       </c>
       <c r="D79" t="str">
-        <v>味覚や皮膚、免疫に関わる微量ミネラル。高齢者や低栄養で不足しやすい</v>
+        <v>治療域が狭い薬剤で、血液中の薬の濃度が効果域・中毒域のどちらにあるかを確認する検査</v>
       </c>
       <c r="E79" t="str">
-        <v>亜鉛は、味を感じる働きや皮膚・粘膜の健康、免疫の働きに関わる微量ミネラルです。不足すると、味がわかりにくくなったり（味覚障害）、傷が治りにくくなったりすることがあります。</v>
+        <v>この薬は効く量と副作用が出る量が近いため、血液中の薬の濃度を定期的に測って、ちょうどよい範囲に入っているかを確認します。数値が低いと効果が不十分になり、高いと副作用が出やすくなります。</v>
       </c>
       <c r="F79" t="str">
-        <v/>
+        <v>過量投与、代謝を妨げる薬剤との併用、肝機能低下による代謝低下</v>
       </c>
       <c r="G79" t="str">
-        <v/>
+        <v>ふらつき、眠気、めまい、物が二重に見えるなどの中毒症状がないか確認する</v>
       </c>
       <c r="H79" t="str">
         <v/>
       </c>
       <c r="I79" t="str">
-        <v>低栄養、高齢による摂取不足、消化器手術後、亜鉛の吸収を妨げる薬剤（PPI、キレート形成する薬剤など）との併用</v>
+        <v>飲み忘れ、自己判断による減量、代謝を促進する薬剤との併用（相互作用）</v>
       </c>
       <c r="J79" t="str">
-        <v>味覚の変化（味を感じにくい、金属味がするなど）がないか確認する。牡蠣、赤身肉、レバーなど亜鉛を多く含む食品を意識するとよいことを伝える</v>
+        <v>発作やてんかん症状の再発がないか確認し、飲み忘れがないか一緒に確認する</v>
       </c>
       <c r="K79" t="str">
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>薬剤性の亜鉛欠乏（PPI長期使用、D-ペニシラミン、一部の降圧薬など）に注意。亜鉛欠乏による味覚障害は原因薬剤の中止・亜鉛補充で改善することがある</v>
+        <v>採血のタイミング（トラフ値かどうか）で数値の解釈が変わるため採血時点を確認する。カルバマゼピンは自己誘導により長期使用で濃度が下がることがある点にも注意</v>
       </c>
       <c r="M79" t="str">
-        <v/>
+        <v>てんかん</v>
       </c>
       <c r="N79" t="str">
-        <v>亜鉛,Zn,味覚障害,亜鉛欠乏</v>
+        <v>TDM,血中薬物濃度,治療域,中毒域,カルバマゼピン,フェニトイン,バルプロ酸,抗てんかん薬,ゾニサミド,ラモトリギン</v>
       </c>
       <c r="O79" t="str">
-        <v>食事と栄養 p.78（亜鉛）</v>
+        <v/>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>マグネシウム（Mg）</v>
+        <v>アミラーゼ（AMY）</v>
       </c>
       <c r="B80" t="str">
-        <v>Mg</v>
+        <v>AMY</v>
       </c>
       <c r="C80" t="str">
-        <v>1.8〜2.6 mg/dL程度（施設差あり）</v>
+        <v>44〜132 U/L（施設差あり）</v>
       </c>
       <c r="D80" t="str">
-        <v>骨や筋肉、神経の働きに関わるミネラル。低栄養や利尿薬で不足しやすい</v>
+        <v>膵臓や唾液腺から出る消化酵素。膵炎などで血液中に漏れ出す</v>
       </c>
       <c r="E80" t="str">
-        <v>マグネシウムは、骨や筋肉、神経の働きを支えるミネラルです。不足すると、こむら返りや不整脈、だるさなどの症状が出ることがあります。</v>
+        <v>アミラーゼは、でんぷんを分解する消化酵素で、主に膵臓と唾液腺から作られます。膵臓に炎症が起きると血液中に漏れ出して数値が上がるため、膵炎の診断や経過観察に使われます。</v>
       </c>
       <c r="F80" t="str">
-        <v>腎不全、マグネシウム製剤（酸化マグネシウムなど）の過量投与</v>
+        <v>急性膵炎、慢性膵炎の急性増悪、耳下腺炎（おたふくかぜ）、腎不全</v>
       </c>
       <c r="G80" t="str">
-        <v>腎機能低下がある患者で酸化マグネシウムなどの緩下剤を使用中は、傾眠・血圧低下などの高マグネシウム血症の症状がないか確認する</v>
+        <v>飲酒を控え、脂っこい食事を避けるよう伝える。強い腹痛・背部痛がある場合は急性膵炎の可能性もあるため早めの受診を勧める</v>
       </c>
       <c r="H80" t="str">
-        <v>マグネシウム含有制酸薬・下剤の過量(特に腎機能低下患者)</v>
+        <v>バルプロ酸、アザチオプリン、サイアザイド系・ループ利尿薬、ステロイドなど薬剤性膵炎の原因薬</v>
       </c>
       <c r="I80" t="str">
-        <v>低栄養、利尿薬の使用、慢性的な下痢、アルコール多飲、PPI長期使用</v>
+        <v>慢性膵炎の進行期（膵臓の機能低下）</v>
       </c>
       <c r="J80" t="str">
-        <v>こむら返りや動悸などの症状がないか確認する</v>
+        <v/>
       </c>
       <c r="K80" t="str">
-        <v>プロトンポンプ阻害薬(PPI)の長期使用、ループ利尿薬、サイアザイド系利尿薬、シスプラチン、アミノグリコシド系</v>
+        <v/>
       </c>
       <c r="L80" t="str">
-        <v>腎機能低下患者への酸化マグネシウム投与は高マグネシウム血症のリスクがあるため定期的なモニタリングが必要。PPI長期使用も低マグネシウム血症のリスク因子として知られる</v>
+        <v>膵臓由来か唾液腺由来かを区別するには膵型アミラーゼ(P-AMY)を確認する。急性膵炎では強い腹痛・背部痛を伴うことが多く、飲酒歴の確認も重要</v>
       </c>
       <c r="M80" t="str">
-        <v>腎機能</v>
+        <v/>
       </c>
       <c r="N80" t="str">
-        <v>マグネシウム,Mg,酸化マグネシウム,こむら返り</v>
+        <v>アミラーゼ,AMY,膵炎,急性膵炎</v>
       </c>
       <c r="O80" t="str">
-        <v>食事と栄養 p.84（マグネシウム）</v>
+        <v/>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>白血球数（WBC）</v>
+        <v>間接ビリルビン</v>
       </c>
       <c r="B81" t="str">
-        <v>WBC</v>
+        <v>I-Bil</v>
       </c>
       <c r="C81" t="str">
-        <v>3,300〜8,600 /μL程度（施設差あり）</v>
+        <v>0.2〜0.8 mg/dL程度（施設差あり）</v>
       </c>
       <c r="D81" t="str">
-        <v>体を細菌やウイルスから守る免疫細胞の数で、感染や炎症、薬剤の影響を反映する</v>
+        <v>赤血球が壊れてできるビリルビンのうち、肝臓で処理される前の形</v>
       </c>
       <c r="E81" t="str">
-        <v>白血球は体に入ってきた細菌やウイルスと戦う免疫細胞です。感染症や炎症があると増え、逆に一部のお薬の副作用や骨髄の働きが落ちると減ることがあります。</v>
+        <v>間接ビリルビンは、赤血球が壊れてできたビリルビンが、まだ肝臓で処理される前の状態です。この値が高い場合、赤血球が通常より多く壊れている(溶血)か、肝臓での処理能力に生まれつきの体質差(体質性黄疸)がある可能性が考えられます。</v>
       </c>
       <c r="F81" t="str">
-        <v>感染症、炎症、ステロイド使用、喫煙、白血病などの血液疾患</v>
+        <v>溶血性疾患（自己免疫性溶血性貧血、血液型不適合輸血など）、体質性黄疸（ジルベール症候群）、新生児黄疸</v>
       </c>
       <c r="G81" t="str">
-        <v>発熱や体の痛みなど感染症状がないか確認する</v>
+        <v>皮膚や白目の黄染、尿の色の変化がないか確認する</v>
       </c>
       <c r="H81" t="str">
-        <v>ステロイド、G-CSF製剤、炭酸リチウム</v>
+        <v/>
       </c>
       <c r="I81" t="str">
-        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、メルカゾールなど薬剤性の無顆粒球症、再生不良性貧血、ウイルス感染</v>
+        <v/>
       </c>
       <c r="J81" t="str">
-        <v>発熱、のどの痛みなど感染症状の初期サインがないか確認する。人混みを避け、手洗い・うがいを徹底するよう伝える</v>
+        <v/>
       </c>
       <c r="K81" t="str">
-        <v>抗がん剤、メルカゾール(無顆粒球症)、クロザピン(定期的な血球モニタリング必須)、サラゾスルファピリジン</v>
+        <v/>
       </c>
       <c r="L81" t="str">
-        <v>メルカゾール（チアマゾール）は無顆粒球症の重大な副作用があり、発熱・のどの痛みが出たらすぐ受診するよう指導する。抗がん剤・免疫抑制剤・抗てんかん薬（カルバマゼピンなど）使用中も定期的なモニタリングが必要</v>
+        <v>直接ビリルビンとの比率で原因を推測する（間接優位は溶血・体質性、直接優位は胆道系）。総ビリルビン・AST/ALTと合わせて評価する</v>
       </c>
       <c r="M81" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>肝機能</v>
       </c>
       <c r="N81" t="str">
-        <v>白血球,WBC,好中球,感染症,白血病,無顆粒球症,骨髄抑制</v>
+        <v>間接ビリルビン,I-Bil,溶血</v>
       </c>
       <c r="O81" t="str">
         <v/>
@@ -4233,66 +4233,66 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>赤血球数</v>
+        <v>直接ビリルビン</v>
       </c>
       <c r="B82" t="str">
-        <v>RBC</v>
+        <v>D-Bil</v>
       </c>
       <c r="C82" t="str">
-        <v>男性 435〜555万/μL、女性 386〜492万/μL程度（施設差あり）</v>
+        <v>0.0〜0.3 mg/dL程度（施設差あり）</v>
       </c>
       <c r="D82" t="str">
-        <v>血液中で酸素を運ぶ細胞の数。ヘモグロビン・ヘマトクリットと合わせて貧血・多血症を評価する</v>
+        <v>肝臓で処理された後のビリルビン。胆道の詰まりで血液中に増える</v>
       </c>
       <c r="E82" t="str">
-        <v>赤血球は、肺で受け取った酸素を全身に運ぶ血液の細胞です。数が少ないと貧血、多いと多血症が疑われます。ヘモグロビンやヘマトクリットと合わせて総合的に評価します。</v>
+        <v>直接ビリルビンは、肝臓で処理された後のビリルビンです。胆石や腫瘍などで胆汁の通り道（胆道）が詰まると、行き場を失って血液中に増え、皮膚や白目が黄色くなる黄疸として現れます。</v>
       </c>
       <c r="F82" t="str">
-        <v>脱水、多血症（真性多血症、二次性多血症）、喫煙</v>
+        <v>肝疾患、胆石など胆道の閉塞</v>
       </c>
       <c r="G82" t="str">
-        <v>脱水が疑われる場合はこまめな水分摂取を勧める（水分制限がある場合を除く）</v>
+        <v>皮膚や白目の黄染、白っぽい便、濃い茶色の尿がないか確認する</v>
       </c>
       <c r="H82" t="str">
-        <v/>
+        <v>胆汁うっ滞型の薬剤性肝障害を起こしうる抗菌薬、経口避妊薬</v>
       </c>
       <c r="I82" t="str">
-        <v>貧血（鉄欠乏性貧血、腎性貧血など）、出血</v>
+        <v/>
       </c>
       <c r="J82" t="str">
-        <v>ヘモグロビンと同様に、出血や食事量低下がないか確認する</v>
+        <v/>
       </c>
       <c r="K82" t="str">
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>ヘモグロビン・ヘマトクリットと同じ方向に動くことが多い。赤血球数だけでなくMCV・MCH・MCHCと合わせて貧血のタイプ(小球性・正球性・大球性)を判断する</v>
+        <v>直接優位の上昇は胆道系（胆石、腫瘍による閉塞）を、間接優位の上昇は溶血・体質性を疑う手がかりになる。γ-GTP・ALPと合わせて胆道系疾患を評価する</v>
       </c>
       <c r="M82" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>肝機能</v>
       </c>
       <c r="N82" t="str">
-        <v>赤血球,RBC,貧血,多血症</v>
+        <v>直接ビリルビン,D-Bil,胆石,胆道閉塞</v>
       </c>
       <c r="O82" t="str">
-        <v>食事と栄養 p.151-164（第2部 貧血）</v>
+        <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>ヘモグロビン濃度</v>
+        <v>亜鉛（Zn）</v>
       </c>
       <c r="B83" t="str">
-        <v>Hb</v>
+        <v>Zn</v>
       </c>
       <c r="C83" t="str">
-        <v>男性 13.5〜17.5 g/dL、女性 11.5〜15.0 g/dL</v>
+        <v>80〜130 μg/dL程度（施設差あり）</v>
       </c>
       <c r="D83" t="str">
-        <v>血液の中で酸素を運ぶ役割をしている。この値が低い状態が貧血。</v>
+        <v>味覚や皮膚、免疫に関わる微量ミネラル。高齢者や低栄養で不足しやすい</v>
       </c>
       <c r="E83" t="str">
-        <v>ヘモグロビンは、血液の中で酸素を全身に運ぶ役割をしている赤い色素です。この値が低い状態が貧血で、体がだるくなったり、階段で息切れしやすくなったりします。</v>
+        <v>亜鉛は、味を感じる働きや皮膚・粘膜の健康、免疫の働きに関わる微量ミネラルです。不足すると、味がわかりにくくなったり（味覚障害）、傷が治りにくくなったりすることがあります。</v>
       </c>
       <c r="F83" t="str">
         <v/>
@@ -4304,163 +4304,163 @@
         <v/>
       </c>
       <c r="I83" t="str">
-        <v>鉄欠乏性貧血、出血、腎性貧血、骨髄の造血機能低下</v>
+        <v>低栄養、高齢による摂取不足、消化器手術後、亜鉛の吸収を妨げる薬剤（PPI、キレート形成する薬剤など）との併用</v>
       </c>
       <c r="J83" t="str">
-        <v>鉄分の多い食品(レバー・赤身肉・魚・ほうれん草など)を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える。鉄剤は数値が正常化した後も体内に鉄を貯蔵するため2〜3か月程度は継続が必要なことを説明する</v>
+        <v>味覚の変化（味を感じにくい、金属味がするなど）がないか確認する。牡蠣、赤身肉、レバーなど亜鉛を多く含む食品を意識するとよいことを伝える</v>
       </c>
       <c r="K83" t="str">
-        <v>NSAIDs・抗凝固薬・抗血小板薬(消化管出血のリスク)、抗がん剤、ST合剤</v>
+        <v/>
       </c>
       <c r="L83" t="str">
-        <v>原因（出血・食事量低下など）の確認が重要。腎機能低下がある場合は鉄不足以外が原因のこともある。鉄剤はヘモグロビンが正常化した後も2〜3か月程度は継続することが多い（鉄の貯蔵分を補うため。途中でやめると再び貧血になりやすい）</v>
+        <v>薬剤性の亜鉛欠乏（PPI長期使用、D-ペニシラミン、一部の降圧薬など）に注意。亜鉛欠乏による味覚障害は原因薬剤の中止・亜鉛補充で改善することがある</v>
       </c>
       <c r="M83" t="str">
-        <v>鉄欠乏性貧血,抗血小板療法,抗凝固療法（心房細動・血栓症）</v>
+        <v/>
       </c>
       <c r="N83" t="str">
-        <v>ヘモグロビン,Hb,貧血,鉄剤,鉄欠乏性貧血</v>
+        <v>亜鉛,Zn,味覚障害,亜鉛欠乏</v>
       </c>
       <c r="O83" t="str">
-        <v>食事と栄養 p.151-164（第2部 貧血）</v>
+        <v>食事と栄養 p.78（亜鉛）</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>ヘマトクリット値</v>
+        <v>マグネシウム（Mg）</v>
       </c>
       <c r="B84" t="str">
-        <v>Ht,Hct</v>
+        <v>Mg</v>
       </c>
       <c r="C84" t="str">
-        <v>男性 40〜50%、女性 35〜45%</v>
+        <v>1.8〜2.6 mg/dL程度（施設差あり）</v>
       </c>
       <c r="D84" t="str">
-        <v>血液全体のうち赤血球が占める体積の割合。貧血・脱水の指標</v>
+        <v>骨や筋肉、神経の働きに関わるミネラル。低栄養や利尿薬で不足しやすい</v>
       </c>
       <c r="E84" t="str">
-        <v>ヘマトクリットは、血液全体のうち赤血球が占める割合を表す数値です。この値が低いと貧血、高いと脱水や血液が濃くなっている状態が疑われます。</v>
+        <v>マグネシウムは、骨や筋肉、神経の働きを支えるミネラルです。不足すると、こむら返りや不整脈、だるさなどの症状が出ることがあります。</v>
       </c>
       <c r="F84" t="str">
-        <v>脱水、多血症（真性多血症、二次性多血症）、喫煙</v>
+        <v>腎不全、マグネシウム製剤（酸化マグネシウムなど）の過量投与</v>
       </c>
       <c r="G84" t="str">
-        <v>脱水が疑われる場合はこまめな水分摂取を勧める（水分制限がある場合を除く）</v>
+        <v>腎機能低下がある患者で酸化マグネシウムなどの緩下剤を使用中は、傾眠・血圧低下などの高マグネシウム血症の症状がないか確認する</v>
       </c>
       <c r="H84" t="str">
-        <v/>
+        <v>マグネシウム含有制酸薬・下剤の過量(特に腎機能低下患者)</v>
       </c>
       <c r="I84" t="str">
-        <v>貧血（鉄欠乏性貧血、腎性貧血など）、出血</v>
+        <v>低栄養、利尿薬の使用、慢性的な下痢、アルコール多飲、PPI長期使用</v>
       </c>
       <c r="J84" t="str">
-        <v>ヘモグロビンと同様に、出血や食事量低下がないか確認する</v>
+        <v>こむら返りや動悸などの症状がないか確認する</v>
       </c>
       <c r="K84" t="str">
-        <v/>
+        <v>プロトンポンプ阻害薬(PPI)の長期使用、ループ利尿薬、サイアザイド系利尿薬、シスプラチン、アミノグリコシド系</v>
       </c>
       <c r="L84" t="str">
-        <v>ヘモグロビン・赤血球数と合わせて評価する。3つの値は同じ方向に動くことが多く、脱水があると貧血が見かけ上隠れることがある</v>
+        <v>腎機能低下患者への酸化マグネシウム投与は高マグネシウム血症のリスクがあるため定期的なモニタリングが必要。PPI長期使用も低マグネシウム血症のリスク因子として知られる</v>
       </c>
       <c r="M84" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>腎機能</v>
       </c>
       <c r="N84" t="str">
-        <v>ヘマトクリット,Ht,Hct,貧血,脱水,多血症</v>
+        <v>マグネシウム,Mg,酸化マグネシウム,こむら返り</v>
       </c>
       <c r="O84" t="str">
-        <v>食事と栄養 p.151-164（第2部 貧血）</v>
+        <v>食事と栄養 p.84（マグネシウム）</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>MCV</v>
+        <v>白血球数（WBC）</v>
       </c>
       <c r="B85" t="str">
-        <v>MCV</v>
+        <v>WBC</v>
       </c>
       <c r="C85" t="str">
-        <v>79〜100 fL</v>
+        <v>3,300〜8,600 /μL程度（施設差あり）</v>
       </c>
       <c r="D85" t="str">
-        <v>赤血球1個の大きさ</v>
+        <v>体を細菌やウイルスから守る免疫細胞の数で、感染や炎症、薬剤の影響を反映する</v>
       </c>
       <c r="E85" t="str">
-        <v>MCVは赤血球1個あたりの大きさを表す数値です。貧血があるとき、この数値で「小さい貧血」か「大きい貧血」かを見分けることができ、原因を絞り込む手がかりになります。</v>
+        <v>白血球は体に入ってきた細菌やウイルスと戦う免疫細胞です。感染症や炎症があると増え、逆に一部のお薬の副作用や骨髄の働きが落ちると減ることがあります。</v>
       </c>
       <c r="F85" t="str">
-        <v/>
+        <v>感染症、炎症、ステロイド使用、喫煙、白血病などの血液疾患</v>
       </c>
       <c r="G85" t="str">
-        <v/>
+        <v>発熱や体の痛みなど感染症状がないか確認する</v>
       </c>
       <c r="H85" t="str">
-        <v/>
+        <v>ステロイド、G-CSF製剤、炭酸リチウム</v>
       </c>
       <c r="I85" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、メルカゾールなど薬剤性の無顆粒球症、再生不良性貧血、ウイルス感染</v>
       </c>
       <c r="J85" t="str">
-        <v>鉄分の多い食品(レバー・赤身肉・魚・ほうれん草など)と、吸収を助けるビタミンC(柑橘類・芋類等)を一緒に摂るよう伝える</v>
+        <v>発熱、のどの痛みなど感染症状の初期サインがないか確認する。人混みを避け、手洗い・うがいを徹底するよう伝える</v>
       </c>
       <c r="K85" t="str">
-        <v/>
+        <v>抗がん剤、メルカゾール(無顆粒球症)、クロザピン(定期的な血球モニタリング必須)、サラゾスルファピリジン</v>
       </c>
       <c r="L85" t="str">
-        <v/>
+        <v>メルカゾール（チアマゾール）は無顆粒球症の重大な副作用があり、発熱・のどの痛みが出たらすぐ受診するよう指導する。抗がん剤・免疫抑制剤・抗てんかん薬（カルバマゼピンなど）使用中も定期的なモニタリングが必要</v>
       </c>
       <c r="M85" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N85" t="str">
-        <v>MCV,赤血球指数,貧血</v>
+        <v>白血球,WBC,好中球,感染症,白血病,無顆粒球症,骨髄抑制</v>
       </c>
       <c r="O85" t="str">
-        <v>食事と栄養 p.151-164（第2部 貧血）</v>
+        <v/>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>MCH</v>
+        <v>赤血球数</v>
       </c>
       <c r="B86" t="str">
-        <v>MCH</v>
+        <v>RBC</v>
       </c>
       <c r="C86" t="str">
-        <v>26.3〜34.3 pg</v>
+        <v>男性 435〜555万/μL、女性 386〜492万/μL程度（施設差あり）</v>
       </c>
       <c r="D86" t="str">
-        <v>赤血球1個に含まれるヘモグロビン量</v>
+        <v>血液中で酸素を運ぶ細胞の数。ヘモグロビン・ヘマトクリットと合わせて貧血・多血症を評価する</v>
       </c>
       <c r="E86" t="str">
-        <v>MCHは赤血球1個の中に含まれるヘモグロビン（酸素を運ぶ色素）の量を表す数値です。MCVと同じく、貧血の種類を見分けるのに使われます。</v>
+        <v>赤血球は、肺で受け取った酸素を全身に運ぶ血液の細胞です。数が少ないと貧血、多いと多血症が疑われます。ヘモグロビンやヘマトクリットと合わせて総合的に評価します。</v>
       </c>
       <c r="F86" t="str">
-        <v/>
+        <v>脱水、多血症（真性多血症、二次性多血症）、喫煙</v>
       </c>
       <c r="G86" t="str">
-        <v/>
+        <v>脱水が疑われる場合はこまめな水分摂取を勧める（水分制限がある場合を除く）</v>
       </c>
       <c r="H86" t="str">
         <v/>
       </c>
       <c r="I86" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>貧血（鉄欠乏性貧血、腎性貧血など）、出血</v>
       </c>
       <c r="J86" t="str">
-        <v>鉄分の多い食品(レバー・赤身肉・魚・ほうれん草など)と、吸収を助けるビタミンC(柑橘類・芋類等)を一緒に摂るよう伝える</v>
+        <v>ヘモグロビンと同様に、出血や食事量低下がないか確認する</v>
       </c>
       <c r="K86" t="str">
         <v/>
       </c>
       <c r="L86" t="str">
-        <v/>
+        <v>ヘモグロビン・ヘマトクリットと同じ方向に動くことが多い。赤血球数だけでなくMCV・MCH・MCHCと合わせて貧血のタイプ(小球性・正球性・大球性)を判断する</v>
       </c>
       <c r="M86" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
       <c r="N86" t="str">
-        <v>MCH,赤血球指数,貧血</v>
+        <v>赤血球,RBC,貧血,多血症</v>
       </c>
       <c r="O86" t="str">
         <v>食事と栄養 p.151-164（第2部 貧血）</v>
@@ -4468,19 +4468,19 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>MCHC</v>
+        <v>ヘモグロビン濃度</v>
       </c>
       <c r="B87" t="str">
-        <v>MCHC</v>
+        <v>Hb</v>
       </c>
       <c r="C87" t="str">
-        <v>31.6〜36.6 %</v>
+        <v>男性 13.5〜17.5 g/dL、女性 11.5〜15.0 g/dL</v>
       </c>
       <c r="D87" t="str">
-        <v>単位容積あたりの赤血球に含まれるヘモグロビン濃度</v>
+        <v>血液の中で酸素を運ぶ役割をしている。この値が低い状態が貧血。</v>
       </c>
       <c r="E87" t="str">
-        <v>MCHCは、赤血球の中にヘモグロビンがどれくらい濃く詰まっているかを表す数値です。鉄が不足すると、この濃度も薄くなる傾向があります。</v>
+        <v>ヘモグロビンは、血液の中で酸素を全身に運ぶ役割をしている赤い色素です。この値が低い状態が貧血で、体がだるくなったり、階段で息切れしやすくなったりします。</v>
       </c>
       <c r="F87" t="str">
         <v/>
@@ -4492,22 +4492,22 @@
         <v/>
       </c>
       <c r="I87" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>鉄欠乏性貧血、出血、腎性貧血、骨髄の造血機能低下</v>
       </c>
       <c r="J87" t="str">
-        <v>鉄分の多い食品(レバー・赤身肉・魚・ほうれん草など)と、吸収を助けるビタミンC(柑橘類・芋類等)を一緒に摂るよう伝える</v>
+        <v>鉄分の多い食品(レバー・赤身肉・魚・ほうれん草など)を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える。鉄剤は数値が正常化した後も体内に鉄を貯蔵するため2〜3か月程度は継続が必要なことを説明する</v>
       </c>
       <c r="K87" t="str">
-        <v/>
+        <v>NSAIDs・抗凝固薬・抗血小板薬(消化管出血のリスク)、抗がん剤、ST合剤</v>
       </c>
       <c r="L87" t="str">
-        <v/>
+        <v>原因（出血・食事量低下など）の確認が重要。腎機能低下がある場合は鉄不足以外が原因のこともある。鉄剤はヘモグロビンが正常化した後も2〜3か月程度は継続することが多い（鉄の貯蔵分を補うため。途中でやめると再び貧血になりやすい）</v>
       </c>
       <c r="M87" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>鉄欠乏性貧血,抗血小板療法,抗凝固療法（心房細動・血栓症）</v>
       </c>
       <c r="N87" t="str">
-        <v>MCHC,赤血球指数,貧血</v>
+        <v>ヘモグロビン,Hb,貧血,鉄剤,鉄欠乏性貧血</v>
       </c>
       <c r="O87" t="str">
         <v>食事と栄養 p.151-164（第2部 貧血）</v>
@@ -4515,69 +4515,69 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>血小板数</v>
+        <v>ヘマトクリット値</v>
       </c>
       <c r="B88" t="str">
-        <v>Plt</v>
+        <v>Ht,Hct</v>
       </c>
       <c r="C88" t="str">
-        <v>15.0〜35.0万/μL程度（施設差あり）</v>
+        <v>男性 40〜50%、女性 35〜45%</v>
       </c>
       <c r="D88" t="str">
-        <v>出血を止める働きをする血液成分で、少なすぎると出血しやすくなる</v>
+        <v>血液全体のうち赤血球が占める体積の割合。貧血・脱水の指標</v>
       </c>
       <c r="E88" t="str">
-        <v>血小板は、血管が傷ついたときに集まって血を止める役割をする血液の成分です。数が少ないとあざができやすくなったり、出血が止まりにくくなったりします。抗血小板薬や抗がん剤を使っている方では、定期的にチェックすることが大切です。</v>
+        <v>ヘマトクリットは、血液全体のうち赤血球が占める割合を表す数値です。この値が低いと貧血、高いと脱水や血液が濃くなっている状態が疑われます。</v>
       </c>
       <c r="F88" t="str">
-        <v>炎症性疾患、鉄欠乏性貧血、脾摘後、骨髄増殖性疾患</v>
+        <v>脱水、多血症（真性多血症、二次性多血症）、喫煙</v>
       </c>
       <c r="G88" t="str">
-        <v>出血傾向はなく経過観察でよいことが多いが、片側の腫れ・しびれなど血栓症状がないかも念のため確認する</v>
+        <v>脱水が疑われる場合はこまめな水分摂取を勧める（水分制限がある場合を除く）</v>
       </c>
       <c r="H88" t="str">
         <v/>
       </c>
       <c r="I88" t="str">
-        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、肝硬変・脾機能亢進、再生不良性貧血、抗てんかん薬（バルプロ酸など）の副作用、ITP（特発性血小板減少性紫斑病）</v>
+        <v>貧血（鉄欠乏性貧血、腎性貧血など）、出血</v>
       </c>
       <c r="J88" t="str">
-        <v>あざができやすい、歯ぐきや鼻からの出血が増えていないか確認する。強い運動や転倒によるけがに注意するよう伝え、歯みがきは柔らかめのブラシを勧める</v>
+        <v>ヘモグロビンと同様に、出血や食事量低下がないか確認する</v>
       </c>
       <c r="K88" t="str">
-        <v>ヘパリン(HIT: ヘパリン起因性血小板減少症)、バルプロ酸、抗がん剤、リネゾリド</v>
+        <v/>
       </c>
       <c r="L88" t="str">
-        <v>抗血小板薬・抗凝固薬使用中に血小板減少があると出血リスクがさらに高まる。抗がん剤・バルプロ酸・カルバマゼピンなど骨髄抑制のリスクがある薬剤使用中は定期採血の実施状況を確認する</v>
+        <v>ヘモグロビン・赤血球数と合わせて評価する。3つの値は同じ方向に動くことが多く、脱水があると貧血が見かけ上隠れることがある</v>
       </c>
       <c r="M88" t="str">
-        <v>てんかん,抗血小板療法</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="N88" t="str">
-        <v>血小板,Plt,platelet,出血,あざ,紫斑,骨髄抑制</v>
+        <v>ヘマトクリット,Ht,Hct,貧血,脱水,多血症</v>
       </c>
       <c r="O88" t="str">
-        <v/>
+        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>RDW-SD</v>
+        <v>MCV</v>
       </c>
       <c r="B89" t="str">
-        <v>RDW-SD</v>
+        <v>MCV</v>
       </c>
       <c r="C89" t="str">
-        <v>39〜46 fL程度（施設差あり）</v>
+        <v>79〜100 fL</v>
       </c>
       <c r="D89" t="str">
-        <v>赤血球の大きさのばらつきを表す指標(絶対値)。鉄欠乏性貧血などの初期変化を捉えやすい</v>
+        <v>赤血球1個の大きさ</v>
       </c>
       <c r="E89" t="str">
-        <v>RDW-SDは、赤血球の大きさがどれくらいバラバラになっているかを表す数値です。貧血の原因を調べる際、鉄が足りなくなり始めた早い段階での変化を捉えるのに役立ちます。</v>
+        <v>MCVは赤血球1個あたりの大きさを表す数値です。貧血があるとき、この数値で「小さい貧血」か「大きい貧血」かを見分けることができ、原因を絞り込む手がかりになります。</v>
       </c>
       <c r="F89" t="str">
-        <v>鉄欠乏性貧血の初期、混合性貧血（複数の原因が重なっている状態）、赤血球産生の乱れ</v>
+        <v/>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -4586,22 +4586,22 @@
         <v/>
       </c>
       <c r="I89" t="str">
-        <v/>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="J89" t="str">
-        <v/>
+        <v>鉄分の多い食品(レバー・赤身肉・魚・ほうれん草など)と、吸収を助けるビタミンC(柑橘類・芋類等)を一緒に摂るよう伝える</v>
       </c>
       <c r="K89" t="str">
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>MCVが正常範囲でもRDWが上昇している場合、鉄欠乏の初期段階を示唆することがある。MCV・MCHと合わせて評価する</v>
+        <v/>
       </c>
       <c r="M89" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
       <c r="N89" t="str">
-        <v>RDW-SD,赤血球分布幅,貧血,鉄欠乏</v>
+        <v>MCV,赤血球指数,貧血</v>
       </c>
       <c r="O89" t="str">
         <v>食事と栄養 p.151-164（第2部 貧血）</v>
@@ -4609,22 +4609,22 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>RDW-CV</v>
+        <v>MCH</v>
       </c>
       <c r="B90" t="str">
-        <v>RDW-CV</v>
+        <v>MCH</v>
       </c>
       <c r="C90" t="str">
-        <v>11.5〜14.5%程度（施設差あり）</v>
+        <v>26.3〜34.3 pg</v>
       </c>
       <c r="D90" t="str">
-        <v>赤血球の大きさのばらつきを割合(%)で表した指標</v>
+        <v>赤血球1個に含まれるヘモグロビン量</v>
       </c>
       <c r="E90" t="str">
-        <v>RDW-CVもRDW-SDと同じく、赤血球の大きさのばらつきを表す数値ですが、こちらは割合(%)で示されます。貧血のタイプを見分ける手がかりになります。</v>
+        <v>MCHは赤血球1個の中に含まれるヘモグロビン（酸素を運ぶ色素）の量を表す数値です。MCVと同じく、貧血の種類を見分けるのに使われます。</v>
       </c>
       <c r="F90" t="str">
-        <v>鉄欠乏性貧血、ビタミンB12・葉酸欠乏性貧血、混合性貧血</v>
+        <v/>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -4633,22 +4633,22 @@
         <v/>
       </c>
       <c r="I90" t="str">
-        <v/>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="J90" t="str">
-        <v/>
+        <v>鉄分の多い食品(レバー・赤身肉・魚・ほうれん草など)と、吸収を助けるビタミンC(柑橘類・芋類等)を一緒に摂るよう伝える</v>
       </c>
       <c r="K90" t="str">
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>RDW-SDと同様の意味を持つ指標。MCVが小さくRDWが高ければ鉄欠乏性貧血、MCVが大きくRDWが高ければビタミンB12・葉酸欠乏を疑う手がかりになる</v>
+        <v/>
       </c>
       <c r="M90" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
       <c r="N90" t="str">
-        <v>RDW-CV,赤血球分布幅,貧血,ビタミンB12,葉酸</v>
+        <v>MCH,赤血球指数,貧血</v>
       </c>
       <c r="O90" t="str">
         <v>食事と栄養 p.151-164（第2部 貧血）</v>
@@ -4656,22 +4656,22 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>好中球実数値</v>
+        <v>MCHC</v>
       </c>
       <c r="B91" t="str">
-        <v>Neutro#,ANC</v>
+        <v>MCHC</v>
       </c>
       <c r="C91" t="str">
-        <v>2,000〜7,500 /μL程度（施設差あり、白血球数×好中球%で算出）</v>
+        <v>31.6〜36.6 %</v>
       </c>
       <c r="D91" t="str">
-        <v>好中球の絶対数。感染症リスクを判断する上で割合(%)より重要な指標</v>
+        <v>単位容積あたりの赤血球に含まれるヘモグロビン濃度</v>
       </c>
       <c r="E91" t="str">
-        <v>これは好中球の実際の数を表す数値です。割合(%)だけでなく、実際の数がどれくらいあるかを見ることで、感染症にかかりやすい状態かどうかをより正確に判断できます。</v>
+        <v>MCHCは、赤血球の中にヘモグロビンがどれくらい濃く詰まっているかを表す数値です。鉄が不足すると、この濃度も薄くなる傾向があります。</v>
       </c>
       <c r="F91" t="str">
-        <v>細菌感染症、炎症、ステロイド使用</v>
+        <v/>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -4680,69 +4680,69 @@
         <v/>
       </c>
       <c r="I91" t="str">
-        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、メルカゾールなど薬剤性の無顆粒球症（1,000/μL未満で好中球減少症、500/μL未満で重症感染リスクが著しく上昇）</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="J91" t="str">
-        <v>発熱、のどの痛みなど感染症状の初期サインがないか確認する。人混みを避け、手洗い・うがいを徹底するよう伝える</v>
+        <v>鉄分の多い食品(レバー・赤身肉・魚・ほうれん草など)と、吸収を助けるビタミンC(柑橘類・芋類等)を一緒に摂るよう伝える</v>
       </c>
       <c r="K91" t="str">
-        <v>抗がん剤、メルカゾール(無顆粒球症)、クロザピン、サラゾスルファピリジン</v>
+        <v/>
       </c>
       <c r="L91" t="str">
-        <v>抗がん剤・メルカゾール・カルバマゼピンなど骨髄抑制のリスクがある薬剤使用中は特に重視すべき数値。500/μL未満は発熱性好中球減少症のリスクが高く緊急性が高い</v>
+        <v/>
       </c>
       <c r="M91" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="N91" t="str">
-        <v>好中球実数値,好中球数,ANC,無顆粒球症,発熱性好中球減少症</v>
+        <v>MCHC,赤血球指数,貧血</v>
       </c>
       <c r="O91" t="str">
-        <v/>
+        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>好酸球実数値</v>
+        <v>血小板数</v>
       </c>
       <c r="B92" t="str">
-        <v>Eosino#</v>
+        <v>Plt</v>
       </c>
       <c r="C92" t="str">
-        <v>100〜500 /μL程度（施設差あり）</v>
+        <v>15.0〜35.0万/μL程度（施設差あり）</v>
       </c>
       <c r="D92" t="str">
-        <v>好酸球の絶対数。アレルギーや薬剤反応の程度をより正確に評価できる</v>
+        <v>出血を止める働きをする血液成分で、少なすぎると出血しやすくなる</v>
       </c>
       <c r="E92" t="str">
-        <v>これは好酸球の実際の数を表す数値です。割合(%)だけでなく実数を見ることで、アレルギー反応の強さをより正確に把握できます。</v>
+        <v>血小板は、血管が傷ついたときに集まって血を止める役割をする血液の成分です。数が少ないとあざができやすくなったり、出血が止まりにくくなったりします。抗血小板薬や抗がん剤を使っている方では、定期的にチェックすることが大切です。</v>
       </c>
       <c r="F92" t="str">
-        <v>アレルギー性疾患、薬剤アレルギー、寄生虫感染</v>
+        <v>炎症性疾患、鉄欠乏性貧血、脾摘後、骨髄増殖性疾患</v>
       </c>
       <c r="G92" t="str">
-        <v>新しく始めた薬がないか確認する</v>
+        <v>出血傾向はなく経過観察でよいことが多いが、片側の腫れ・しびれなど血栓症状がないかも念のため確認する</v>
       </c>
       <c r="H92" t="str">
-        <v>薬剤性好酸球増多(抗菌薬・NSAIDs・抗てんかん薬など)。発熱や皮疹を伴う場合はDRESS症候群にも注意</v>
+        <v/>
       </c>
       <c r="I92" t="str">
-        <v/>
+        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、肝硬変・脾機能亢進、再生不良性貧血、抗てんかん薬（バルプロ酸など）の副作用、ITP（特発性血小板減少性紫斑病）</v>
       </c>
       <c r="J92" t="str">
-        <v/>
+        <v>あざができやすい、歯ぐきや鼻からの出血が増えていないか確認する。強い運動や転倒によるけがに注意するよう伝え、歯みがきは柔らかめのブラシを勧める</v>
       </c>
       <c r="K92" t="str">
-        <v/>
+        <v>ヘパリン(HIT: ヘパリン起因性血小板減少症)、バルプロ酸、抗がん剤、リネゾリド</v>
       </c>
       <c r="L92" t="str">
-        <v>薬剤性過敏症症候群(DIHS)などでは著明な好酸球増多を認めることがあり、原因薬剤の特定に役立つ</v>
+        <v>抗血小板薬・抗凝固薬使用中に血小板減少があると出血リスクがさらに高まる。抗がん剤・バルプロ酸・カルバマゼピンなど骨髄抑制のリスクがある薬剤使用中は定期採血の実施状況を確認する</v>
       </c>
       <c r="M92" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>てんかん,抗血小板療法</v>
       </c>
       <c r="N92" t="str">
-        <v>好酸球実数値,好酸球数,アレルギー,DIHS</v>
+        <v>血小板,Plt,platelet,出血,あざ,紫斑,骨髄抑制</v>
       </c>
       <c r="O92" t="str">
         <v/>
@@ -4750,22 +4750,22 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>好塩基球実数値</v>
+        <v>RDW-SD</v>
       </c>
       <c r="B93" t="str">
-        <v>Baso#</v>
+        <v>RDW-SD</v>
       </c>
       <c r="C93" t="str">
-        <v>0〜100 /μL程度（施設差あり）</v>
+        <v>39〜46 fL程度（施設差あり）</v>
       </c>
       <c r="D93" t="str">
-        <v>好塩基球の絶対数</v>
+        <v>赤血球の大きさのばらつきを表す指標(絶対値)。鉄欠乏性貧血などの初期変化を捉えやすい</v>
       </c>
       <c r="E93" t="str">
-        <v>これは好塩基球の実際の数を表す数値です。数がとても少ない種類の血球なので、通常は大きな変動を示すことは多くありません。</v>
+        <v>RDW-SDは、赤血球の大きさがどれくらいバラバラになっているかを表す数値です。貧血の原因を調べる際、鉄が足りなくなり始めた早い段階での変化を捉えるのに役立ちます。</v>
       </c>
       <c r="F93" t="str">
-        <v>慢性骨髄性白血病などの血液疾患、アレルギー性疾患</v>
+        <v>鉄欠乏性貧血の初期、混合性貧血（複数の原因が重なっている状態）、赤血球産生の乱れ</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>単独での臨床的意義は乏しく、他の血球指標（白血球分画全体）と合わせて評価する</v>
+        <v>MCVが正常範囲でもRDWが上昇している場合、鉄欠乏の初期段階を示唆することがある。MCV・MCHと合わせて評価する</v>
       </c>
       <c r="M93" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="N93" t="str">
-        <v>好塩基球実数値,好塩基球数</v>
+        <v>RDW-SD,赤血球分布幅,貧血,鉄欠乏</v>
       </c>
       <c r="O93" t="str">
-        <v/>
+        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>リンパ球実数値</v>
+        <v>RDW-CV</v>
       </c>
       <c r="B94" t="str">
-        <v>Lympho#,ALC</v>
+        <v>RDW-CV</v>
       </c>
       <c r="C94" t="str">
-        <v>1,000〜3,600 /μL程度（施設差あり）</v>
+        <v>11.5〜14.5%程度（施設差あり）</v>
       </c>
       <c r="D94" t="str">
-        <v>リンパ球の絶対数。免疫力の目安として使われる</v>
+        <v>赤血球の大きさのばらつきを割合(%)で表した指標</v>
       </c>
       <c r="E94" t="str">
-        <v>これはリンパ球の実際の数を表す数値です。免疫力の目安の一つとして使われ、抗がん剤や免疫抑制剤の副作用モニタリングにも用いられます。</v>
+        <v>RDW-CVもRDW-SDと同じく、赤血球の大きさのばらつきを表す数値ですが、こちらは割合(%)で示されます。貧血のタイプを見分ける手がかりになります。</v>
       </c>
       <c r="F94" t="str">
-        <v>ウイルス感染症、リンパ性白血病などの血液疾患</v>
+        <v>鉄欠乏性貧血、ビタミンB12・葉酸欠乏性貧血、混合性貧血</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -4821,45 +4821,45 @@
         <v/>
       </c>
       <c r="I94" t="str">
-        <v>抗がん剤・免疫抑制剤・ステロイドの使用、強いストレス、AIDSなどの免疫不全</v>
+        <v/>
       </c>
       <c r="J94" t="str">
-        <v>感染予防（手洗い・うがい、人混みを避ける）を意識するよう伝える</v>
+        <v/>
       </c>
       <c r="K94" t="str">
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>免疫抑制剤・抗がん剤治療中のモニタリング指標としても使われる。著明な低下時は日和見感染のリスクが高まる</v>
+        <v>RDW-SDと同様の意味を持つ指標。MCVが小さくRDWが高ければ鉄欠乏性貧血、MCVが大きくRDWが高ければビタミンB12・葉酸欠乏を疑う手がかりになる</v>
       </c>
       <c r="M94" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="N94" t="str">
-        <v>リンパ球実数値,リンパ球数,ALC,免疫抑制剤,日和見感染</v>
+        <v>RDW-CV,赤血球分布幅,貧血,ビタミンB12,葉酸</v>
       </c>
       <c r="O94" t="str">
-        <v/>
+        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>単球実数値</v>
+        <v>好中球実数値</v>
       </c>
       <c r="B95" t="str">
-        <v>Mono#</v>
+        <v>Neutro#,ANC</v>
       </c>
       <c r="C95" t="str">
-        <v>200〜600 /μL程度（施設差あり）</v>
+        <v>2,000〜7,500 /μL程度（施設差あり、白血球数×好中球%で算出）</v>
       </c>
       <c r="D95" t="str">
-        <v>単球の絶対数</v>
+        <v>好中球の絶対数。感染症リスクを判断する上で割合(%)より重要な指標</v>
       </c>
       <c r="E95" t="str">
-        <v>これは単球の実際の数を表す数値です。慢性的な炎症や感染症の状態を把握する材料の一つになります。</v>
+        <v>これは好中球の実際の数を表す数値です。割合(%)だけでなく、実際の数がどれくらいあるかを見ることで、感染症にかかりやすい状態かどうかをより正確に判断できます。</v>
       </c>
       <c r="F95" t="str">
-        <v>慢性感染症、炎症性疾患、血液疾患</v>
+        <v>細菌感染症、炎症、ステロイド使用</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -4868,22 +4868,22 @@
         <v/>
       </c>
       <c r="I95" t="str">
-        <v/>
+        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、メルカゾールなど薬剤性の無顆粒球症（1,000/μL未満で好中球減少症、500/μL未満で重症感染リスクが著しく上昇）</v>
       </c>
       <c r="J95" t="str">
-        <v/>
+        <v>発熱、のどの痛みなど感染症状の初期サインがないか確認する。人混みを避け、手洗い・うがいを徹底するよう伝える</v>
       </c>
       <c r="K95" t="str">
-        <v/>
+        <v>抗がん剤、メルカゾール(無顆粒球症)、クロザピン、サラゾスルファピリジン</v>
       </c>
       <c r="L95" t="str">
-        <v>単独での臨床的意義は乏しく、他の血球指標と合わせて評価する</v>
+        <v>抗がん剤・メルカゾール・カルバマゼピンなど骨髄抑制のリスクがある薬剤使用中は特に重視すべき数値。500/μL未満は発熱性好中球減少症のリスクが高く緊急性が高い</v>
       </c>
       <c r="M95" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N95" t="str">
-        <v>単球実数値,単球数</v>
+        <v>好中球実数値,好中球数,ANC,無顆粒球症,発熱性好中球減少症</v>
       </c>
       <c r="O95" t="str">
         <v/>
@@ -4891,46 +4891,46 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>好中球</v>
+        <v>好酸球実数値</v>
       </c>
       <c r="B96" t="str">
-        <v>Neutro,Neut%</v>
+        <v>Eosino#</v>
       </c>
       <c r="C96" t="str">
-        <v>40〜75%程度（施設差あり）</v>
+        <v>100〜500 /μL程度（施設差あり）</v>
       </c>
       <c r="D96" t="str">
-        <v>白血球の中で最も多くを占め、細菌感染と戦う主力の免疫細胞の割合</v>
+        <v>好酸球の絶対数。アレルギーや薬剤反応の程度をより正確に評価できる</v>
       </c>
       <c r="E96" t="str">
-        <v>好中球は、白血球の中で最も数が多く、細菌が体に入ってきたときに真っ先に戦ってくれる免疫細胞です。感染症や炎症があると増え、逆に薬の副作用などで減ることがあります。</v>
+        <v>これは好酸球の実際の数を表す数値です。割合(%)だけでなく実数を見ることで、アレルギー反応の強さをより正確に把握できます。</v>
       </c>
       <c r="F96" t="str">
-        <v>細菌感染症、炎症、ストレス、ステロイド使用</v>
+        <v>アレルギー性疾患、薬剤アレルギー、寄生虫感染</v>
       </c>
       <c r="G96" t="str">
-        <v>発熱や炎症症状がないか確認する</v>
+        <v>新しく始めた薬がないか確認する</v>
       </c>
       <c r="H96" t="str">
-        <v/>
+        <v>薬剤性好酸球増多(抗菌薬・NSAIDs・抗てんかん薬など)。発熱や皮疹を伴う場合はDRESS症候群にも注意</v>
       </c>
       <c r="I96" t="str">
-        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、ウイルス感染、メルカゾールなど薬剤性の無顆粒球症</v>
+        <v/>
       </c>
       <c r="J96" t="str">
-        <v>発熱やのどの痛みなど感染症状の初期サインがないか確認する</v>
+        <v/>
       </c>
       <c r="K96" t="str">
-        <v>抗がん剤、メルカゾール(無顆粒球症)、クロザピン、サラゾスルファピリジン</v>
+        <v/>
       </c>
       <c r="L96" t="str">
-        <v>好中球の絶対数（好中球実数値）が500/μL未満になると重篤な感染症のリスクが高まる。割合(%)だけでなく実数値も合わせて確認する</v>
+        <v>薬剤性過敏症症候群(DIHS)などでは著明な好酸球増多を認めることがあり、原因薬剤の特定に役立つ</v>
       </c>
       <c r="M96" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N96" t="str">
-        <v>好中球,Neutro,Neut,感染症,無顆粒球症</v>
+        <v>好酸球実数値,好酸球数,アレルギー,DIHS</v>
       </c>
       <c r="O96" t="str">
         <v/>
@@ -4938,28 +4938,28 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>好酸球</v>
+        <v>好塩基球実数値</v>
       </c>
       <c r="B97" t="str">
-        <v>Eosino,Eos%</v>
+        <v>Baso#</v>
       </c>
       <c r="C97" t="str">
-        <v>1〜5%程度（施設差あり）</v>
+        <v>0〜100 /μL程度（施設差あり）</v>
       </c>
       <c r="D97" t="str">
-        <v>アレルギー反応や寄生虫感染に関わる白血球の一種の割合</v>
+        <v>好塩基球の絶対数</v>
       </c>
       <c r="E97" t="str">
-        <v>好酸球は、アレルギー反応や寄生虫感染と関係が深い免疫細胞です。アレルギー性の病気や薬の副作用（薬疹など）で増えることがあります。</v>
+        <v>これは好塩基球の実際の数を表す数値です。数がとても少ない種類の血球なので、通常は大きな変動を示すことは多くありません。</v>
       </c>
       <c r="F97" t="str">
-        <v>アレルギー性疾患（気管支喘息、アトピー性皮膚炎など）、薬剤アレルギー、寄生虫感染</v>
+        <v>慢性骨髄性白血病などの血液疾患、アレルギー性疾患</v>
       </c>
       <c r="G97" t="str">
-        <v>新しく始めた薬がないか確認する。皮疹やかゆみなどアレルギー症状の有無を確認する</v>
+        <v/>
       </c>
       <c r="H97" t="str">
-        <v>薬剤性好酸球増多(抗菌薬・NSAIDs・抗てんかん薬など)。発熱や皮疹を伴う場合はDRESS症候群にも注意</v>
+        <v/>
       </c>
       <c r="I97" t="str">
         <v/>
@@ -4971,13 +4971,13 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>薬剤性の好酸球増多は、原因薬剤の中止で改善することが多い。新規薬剤開始後の皮疹・発熱と合わせて薬剤性過敏症症候群(DIHS)を疑う材料になる</v>
+        <v>単独での臨床的意義は乏しく、他の血球指標（白血球分画全体）と合わせて評価する</v>
       </c>
       <c r="M97" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N97" t="str">
-        <v>好酸球,Eosino,Eos,アレルギー,薬疹,DIHS</v>
+        <v>好塩基球実数値,好塩基球数</v>
       </c>
       <c r="O97" t="str">
         <v/>
@@ -4985,22 +4985,22 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>好塩基球</v>
+        <v>リンパ球実数値</v>
       </c>
       <c r="B98" t="str">
-        <v>Baso,Baso%</v>
+        <v>Lympho#,ALC</v>
       </c>
       <c r="C98" t="str">
-        <v>0〜2%程度（施設差あり）</v>
+        <v>1,000〜3,600 /μL程度（施設差あり）</v>
       </c>
       <c r="D98" t="str">
-        <v>白血球の中で最も数が少なく、アレルギー反応に関わる細胞の割合</v>
+        <v>リンパ球の絶対数。免疫力の目安として使われる</v>
       </c>
       <c r="E98" t="str">
-        <v>好塩基球は白血球の中で最も数が少ない種類で、アレルギー反応や炎症に関わっています。数値の変動が病気の診断に直接使われることは少ない検査です。</v>
+        <v>これはリンパ球の実際の数を表す数値です。免疫力の目安の一つとして使われ、抗がん剤や免疫抑制剤の副作用モニタリングにも用いられます。</v>
       </c>
       <c r="F98" t="str">
-        <v>慢性骨髄性白血病などの血液疾患、アレルギー性疾患、甲状腺機能低下症</v>
+        <v>ウイルス感染症、リンパ性白血病などの血液疾患</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -5009,22 +5009,22 @@
         <v/>
       </c>
       <c r="I98" t="str">
-        <v/>
+        <v>抗がん剤・免疫抑制剤・ステロイドの使用、強いストレス、AIDSなどの免疫不全</v>
       </c>
       <c r="J98" t="str">
-        <v/>
+        <v>感染予防（手洗い・うがい、人混みを避ける）を意識するよう伝える</v>
       </c>
       <c r="K98" t="str">
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>単独での臨床的意義は乏しいが、著明な増加は血液疾患（慢性骨髄性白血病等）の可能性があり他の血球指標と合わせて評価する</v>
+        <v>免疫抑制剤・抗がん剤治療中のモニタリング指標としても使われる。著明な低下時は日和見感染のリスクが高まる</v>
       </c>
       <c r="M98" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N98" t="str">
-        <v>好塩基球,Baso,アレルギー,白血病</v>
+        <v>リンパ球実数値,リンパ球数,ALC,免疫抑制剤,日和見感染</v>
       </c>
       <c r="O98" t="str">
         <v/>
@@ -5032,22 +5032,22 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>リンパ球</v>
+        <v>単球実数値</v>
       </c>
       <c r="B99" t="str">
-        <v>Lympho,Lym%</v>
+        <v>Mono#</v>
       </c>
       <c r="C99" t="str">
-        <v>18〜49%程度（施設差あり）</v>
+        <v>200〜600 /μL程度（施設差あり）</v>
       </c>
       <c r="D99" t="str">
-        <v>ウイルス感染と戦い、免疫の記憶を担う白血球の割合</v>
+        <v>単球の絶対数</v>
       </c>
       <c r="E99" t="str">
-        <v>リンパ球は、ウイルスと戦ったり、一度かかった病気を記憶して免疫をつくったりする細胞です。ウイルス感染で増え、抗がん剤の副作用や強いストレスで減ることがあります。</v>
+        <v>これは単球の実際の数を表す数値です。慢性的な炎症や感染症の状態を把握する材料の一つになります。</v>
       </c>
       <c r="F99" t="str">
-        <v>ウイルス感染症、リンパ性白血病などの血液疾患、百日咳</v>
+        <v>慢性感染症、炎症性疾患、血液疾患</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -5056,22 +5056,22 @@
         <v/>
       </c>
       <c r="I99" t="str">
-        <v>抗がん剤・免疫抑制剤・ステロイドの使用、強いストレス、AIDSなどの免疫不全</v>
+        <v/>
       </c>
       <c r="J99" t="str">
-        <v>免疫が下がっている可能性があるため、感染予防（手洗い・うがい、人混みを避ける）を意識するよう伝える</v>
+        <v/>
       </c>
       <c r="K99" t="str">
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>ステロイド・免疫抑制剤使用中はリンパ球減少による易感染性に注意。好中球と逆方向に動くことが多い（ウイルス感染ではリンパ球優位、細菌感染では好中球優位になりやすい）</v>
+        <v>単独での臨床的意義は乏しく、他の血球指標と合わせて評価する</v>
       </c>
       <c r="M99" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N99" t="str">
-        <v>リンパ球,Lympho,Lym,ウイルス感染,免疫抑制剤,ステロイド</v>
+        <v>単球実数値,単球数</v>
       </c>
       <c r="O99" t="str">
         <v/>
@@ -5079,46 +5079,46 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>単球</v>
+        <v>好中球</v>
       </c>
       <c r="B100" t="str">
-        <v>Mono,Mono%</v>
+        <v>Neutro,Neut%</v>
       </c>
       <c r="C100" t="str">
-        <v>2〜10%程度（施設差あり）</v>
+        <v>40〜75%程度（施設差あり）</v>
       </c>
       <c r="D100" t="str">
-        <v>感染や炎症の後始末をする白血球の一種の割合</v>
+        <v>白血球の中で最も多くを占め、細菌感染と戦う主力の免疫細胞の割合</v>
       </c>
       <c r="E100" t="str">
-        <v>単球は、細菌などを取り込んで処理したり、組織の修復に関わったりする免疫細胞です。慢性的な炎症や感染症の回復期に増えることがあります。</v>
+        <v>好中球は、白血球の中で最も数が多く、細菌が体に入ってきたときに真っ先に戦ってくれる免疫細胞です。感染症や炎症があると増え、逆に薬の副作用などで減ることがあります。</v>
       </c>
       <c r="F100" t="str">
-        <v>慢性感染症（結核など）、炎症性疾患、血液疾患、感染症の回復期</v>
+        <v>細菌感染症、炎症、ストレス、ステロイド使用</v>
       </c>
       <c r="G100" t="str">
-        <v/>
+        <v>発熱や炎症症状がないか確認する</v>
       </c>
       <c r="H100" t="str">
         <v/>
       </c>
       <c r="I100" t="str">
-        <v/>
+        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、ウイルス感染、メルカゾールなど薬剤性の無顆粒球症</v>
       </c>
       <c r="J100" t="str">
-        <v/>
+        <v>発熱やのどの痛みなど感染症状の初期サインがないか確認する</v>
       </c>
       <c r="K100" t="str">
-        <v/>
+        <v>抗がん剤、メルカゾール(無顆粒球症)、クロザピン、サラゾスルファピリジン</v>
       </c>
       <c r="L100" t="str">
-        <v>単独での臨床的意義は乏しく、他の血球指標や炎症マーカー(CRPなど)と合わせて評価する</v>
+        <v>好中球の絶対数（好中球実数値）が500/μL未満になると重篤な感染症のリスクが高まる。割合(%)だけでなく実数値も合わせて確認する</v>
       </c>
       <c r="M100" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N100" t="str">
-        <v>単球,Mono,慢性感染症,結核,炎症</v>
+        <v>好中球,Neutro,Neut,感染症,無顆粒球症</v>
       </c>
       <c r="O100" t="str">
         <v/>
@@ -5126,31 +5126,31 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Dダイマー</v>
+        <v>好酸球</v>
       </c>
       <c r="B101" t="str">
-        <v>D-dimer</v>
+        <v>Eosino,Eos%</v>
       </c>
       <c r="C101" t="str">
-        <v>1.0 μg/mL以下(施設・測定法により異なる)</v>
+        <v>1〜5%程度（施設差あり）</v>
       </c>
       <c r="D101" t="str">
-        <v>体の中で血栓ができて溶けた(線溶)ときにできる分解産物で、血栓症の有無をスクリーニングする指標</v>
+        <v>アレルギー反応や寄生虫感染に関わる白血球の一種の割合</v>
       </c>
       <c r="E101" t="str">
-        <v>Dダイマーは、血管の中に血のかたまり(血栓)ができて、それが溶かされるときにできる物質です。この数値が高いと、どこかに血栓ができている可能性を考えます。ただし手術後や妊娠中、高齢の方などでも上がることがあるため、この数値だけで診断が決まるわけではありません。</v>
+        <v>好酸球は、アレルギー反応や寄生虫感染と関係が深い免疫細胞です。アレルギー性の病気や薬の副作用（薬疹など）で増えることがあります。</v>
       </c>
       <c r="F101" t="str">
-        <v>深部静脈血栓症(DVT)・肺血栓塞栓症(PE)、播種性血管内凝固症候群(DIC)、大動脈解離、悪性腫瘍、手術後、妊娠、高齢、感染・炎症</v>
+        <v>アレルギー性疾患（気管支喘息、アトピー性皮膚炎など）、薬剤アレルギー、寄生虫感染</v>
       </c>
       <c r="G101" t="str">
-        <v>ふくらはぎの腫れ・痛み、急な息切れ・胸痛など血栓症を疑う症状がないか確認する</v>
+        <v>新しく始めた薬がないか確認する。皮疹やかゆみなどアレルギー症状の有無を確認する</v>
       </c>
       <c r="H101" t="str">
-        <v>経口避妊薬・ホルモン補充療法は血栓リスクを高める。逆にワルファリン・DOAC・ヘパリンなど抗凝固薬の効果不十分で血栓が進行している可能性にも注意</v>
+        <v>薬剤性好酸球増多(抗菌薬・NSAIDs・抗てんかん薬など)。発熱や皮疹を伴う場合はDRESS症候群にも注意</v>
       </c>
       <c r="I101" t="str">
-        <v>通常、臨床的意義は乏しい(基準値以下であれば血栓症の可能性は低いとする除外診断に有用)</v>
+        <v/>
       </c>
       <c r="J101" t="str">
         <v/>
@@ -5159,13 +5159,13 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>陰性的中率が高く、基準値以下であれば静脈血栓塞栓症(VTE)の可能性は低いとする除外診断への活用が臨床的に重要。一方で偽陽性が多く、高値のみで血栓症と確定はできない。抗凝固療法中のモニタリングそのものには通常用いない(効果判定はPT-INR/APTT等)</v>
+        <v>薬剤性の好酸球増多は、原因薬剤の中止で改善することが多い。新規薬剤開始後の皮疹・発熱と合わせて薬剤性過敏症症候群(DIHS)を疑う材料になる</v>
       </c>
       <c r="M101" t="str">
-        <v>抗凝固療法（心房細動・血栓症）</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N101" t="str">
-        <v>Dダイマー,D-dimer,血栓,DVT,深部静脈血栓症,肺塞栓,DIC</v>
+        <v>好酸球,Eosino,Eos,アレルギー,薬疹,DIHS</v>
       </c>
       <c r="O101" t="str">
         <v/>
@@ -5173,54 +5173,242 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
+        <v>好塩基球</v>
+      </c>
+      <c r="B102" t="str">
+        <v>Baso,Baso%</v>
+      </c>
+      <c r="C102" t="str">
+        <v>0〜2%程度（施設差あり）</v>
+      </c>
+      <c r="D102" t="str">
+        <v>白血球の中で最も数が少なく、アレルギー反応に関わる細胞の割合</v>
+      </c>
+      <c r="E102" t="str">
+        <v>好塩基球は白血球の中で最も数が少ない種類で、アレルギー反応や炎症に関わっています。数値の変動が病気の診断に直接使われることは少ない検査です。</v>
+      </c>
+      <c r="F102" t="str">
+        <v>慢性骨髄性白血病などの血液疾患、アレルギー性疾患、甲状腺機能低下症</v>
+      </c>
+      <c r="G102" t="str">
+        <v/>
+      </c>
+      <c r="H102" t="str">
+        <v/>
+      </c>
+      <c r="I102" t="str">
+        <v/>
+      </c>
+      <c r="J102" t="str">
+        <v/>
+      </c>
+      <c r="K102" t="str">
+        <v/>
+      </c>
+      <c r="L102" t="str">
+        <v>単独での臨床的意義は乏しいが、著明な増加は血液疾患（慢性骨髄性白血病等）の可能性があり他の血球指標と合わせて評価する</v>
+      </c>
+      <c r="M102" t="str">
+        <v>甲状腺疾患,てんかん</v>
+      </c>
+      <c r="N102" t="str">
+        <v>好塩基球,Baso,アレルギー,白血病</v>
+      </c>
+      <c r="O102" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>リンパ球</v>
+      </c>
+      <c r="B103" t="str">
+        <v>Lympho,Lym%</v>
+      </c>
+      <c r="C103" t="str">
+        <v>18〜49%程度（施設差あり）</v>
+      </c>
+      <c r="D103" t="str">
+        <v>ウイルス感染と戦い、免疫の記憶を担う白血球の割合</v>
+      </c>
+      <c r="E103" t="str">
+        <v>リンパ球は、ウイルスと戦ったり、一度かかった病気を記憶して免疫をつくったりする細胞です。ウイルス感染で増え、抗がん剤の副作用や強いストレスで減ることがあります。</v>
+      </c>
+      <c r="F103" t="str">
+        <v>ウイルス感染症、リンパ性白血病などの血液疾患、百日咳</v>
+      </c>
+      <c r="G103" t="str">
+        <v/>
+      </c>
+      <c r="H103" t="str">
+        <v/>
+      </c>
+      <c r="I103" t="str">
+        <v>抗がん剤・免疫抑制剤・ステロイドの使用、強いストレス、AIDSなどの免疫不全</v>
+      </c>
+      <c r="J103" t="str">
+        <v>免疫が下がっている可能性があるため、感染予防（手洗い・うがい、人混みを避ける）を意識するよう伝える</v>
+      </c>
+      <c r="K103" t="str">
+        <v/>
+      </c>
+      <c r="L103" t="str">
+        <v>ステロイド・免疫抑制剤使用中はリンパ球減少による易感染性に注意。好中球と逆方向に動くことが多い（ウイルス感染ではリンパ球優位、細菌感染では好中球優位になりやすい）</v>
+      </c>
+      <c r="M103" t="str">
+        <v>甲状腺疾患,てんかん</v>
+      </c>
+      <c r="N103" t="str">
+        <v>リンパ球,Lympho,Lym,ウイルス感染,免疫抑制剤,ステロイド</v>
+      </c>
+      <c r="O103" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>単球</v>
+      </c>
+      <c r="B104" t="str">
+        <v>Mono,Mono%</v>
+      </c>
+      <c r="C104" t="str">
+        <v>2〜10%程度（施設差あり）</v>
+      </c>
+      <c r="D104" t="str">
+        <v>感染や炎症の後始末をする白血球の一種の割合</v>
+      </c>
+      <c r="E104" t="str">
+        <v>単球は、細菌などを取り込んで処理したり、組織の修復に関わったりする免疫細胞です。慢性的な炎症や感染症の回復期に増えることがあります。</v>
+      </c>
+      <c r="F104" t="str">
+        <v>慢性感染症（結核など）、炎症性疾患、血液疾患、感染症の回復期</v>
+      </c>
+      <c r="G104" t="str">
+        <v/>
+      </c>
+      <c r="H104" t="str">
+        <v/>
+      </c>
+      <c r="I104" t="str">
+        <v/>
+      </c>
+      <c r="J104" t="str">
+        <v/>
+      </c>
+      <c r="K104" t="str">
+        <v/>
+      </c>
+      <c r="L104" t="str">
+        <v>単独での臨床的意義は乏しく、他の血球指標や炎症マーカー(CRPなど)と合わせて評価する</v>
+      </c>
+      <c r="M104" t="str">
+        <v>甲状腺疾患,てんかん</v>
+      </c>
+      <c r="N104" t="str">
+        <v>単球,Mono,慢性感染症,結核,炎症</v>
+      </c>
+      <c r="O104" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>Dダイマー</v>
+      </c>
+      <c r="B105" t="str">
+        <v>D-dimer</v>
+      </c>
+      <c r="C105" t="str">
+        <v>1.0 μg/mL以下(施設・測定法により異なる)</v>
+      </c>
+      <c r="D105" t="str">
+        <v>体の中で血栓ができて溶けた(線溶)ときにできる分解産物で、血栓症の有無をスクリーニングする指標</v>
+      </c>
+      <c r="E105" t="str">
+        <v>Dダイマーは、血管の中に血のかたまり(血栓)ができて、それが溶かされるときにできる物質です。この数値が高いと、どこかに血栓ができている可能性を考えます。ただし手術後や妊娠中、高齢の方などでも上がることがあるため、この数値だけで診断が決まるわけではありません。</v>
+      </c>
+      <c r="F105" t="str">
+        <v>深部静脈血栓症(DVT)・肺血栓塞栓症(PE)、播種性血管内凝固症候群(DIC)、大動脈解離、悪性腫瘍、手術後、妊娠、高齢、感染・炎症</v>
+      </c>
+      <c r="G105" t="str">
+        <v>ふくらはぎの腫れ・痛み、急な息切れ・胸痛など血栓症を疑う症状がないか確認する</v>
+      </c>
+      <c r="H105" t="str">
+        <v>経口避妊薬・ホルモン補充療法は血栓リスクを高める。逆にワルファリン・DOAC・ヘパリンなど抗凝固薬の効果不十分で血栓が進行している可能性にも注意</v>
+      </c>
+      <c r="I105" t="str">
+        <v>通常、臨床的意義は乏しい(基準値以下であれば血栓症の可能性は低いとする除外診断に有用)</v>
+      </c>
+      <c r="J105" t="str">
+        <v/>
+      </c>
+      <c r="K105" t="str">
+        <v/>
+      </c>
+      <c r="L105" t="str">
+        <v>陰性的中率が高く、基準値以下であれば静脈血栓塞栓症(VTE)の可能性は低いとする除外診断への活用が臨床的に重要。一方で偽陽性が多く、高値のみで血栓症と確定はできない。抗凝固療法中のモニタリングそのものには通常用いない(効果判定はPT-INR/APTT等)</v>
+      </c>
+      <c r="M105" t="str">
+        <v>抗凝固療法（心房細動・血栓症）</v>
+      </c>
+      <c r="N105" t="str">
+        <v>Dダイマー,D-dimer,血栓,DVT,深部静脈血栓症,肺塞栓,DIC</v>
+      </c>
+      <c r="O105" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
         <v>骨密度</v>
       </c>
-      <c r="B102" t="str">
+      <c r="B106" t="str">
         <v>BMD,骨密度</v>
       </c>
-      <c r="C102" t="str">
+      <c r="C106" t="str">
         <v>YAM(若年成人平均値)80%以上:正常、70%以上80%未満:骨量減少、70%未満:骨粗鬆症</v>
       </c>
-      <c r="D102" t="str">
+      <c r="D106" t="str">
         <v>骨の中にカルシウムなどのミネラルがどれだけ詰まっているかを示す指標。20〜44歳の平均値(YAM)に対する割合(%)で評価する</v>
       </c>
-      <c r="E102" t="str">
+      <c r="E106" t="str">
         <v>骨密度は、骨の中にカルシウムなどのミネラルがどれだけしっかり詰まっているかを表す数値です。20〜44歳の若い方の平均値を100%として、ご自身の骨密度が何%かで示されます。70%未満になると「骨粗鬆症」と診断され、骨折しやすい状態と考えられます。</v>
       </c>
-      <c r="F102" t="str">
+      <c r="F106" t="str">
         <v>基本的に問題になることは少ない(まれに骨硬化症などの疾患)</v>
       </c>
-      <c r="G102" t="str">
-        <v/>
-      </c>
-      <c r="H102" t="str">
-        <v/>
-      </c>
-      <c r="I102" t="str">
+      <c r="G106" t="str">
+        <v/>
+      </c>
+      <c r="H106" t="str">
+        <v/>
+      </c>
+      <c r="I106" t="str">
         <v>骨粗鬆症、加齢による骨量減少、閉経後のエストロゲン低下、ステロイド長期使用、カルシウム・ビタミンD不足、運動不足、るいそう</v>
       </c>
-      <c r="J102" t="str">
+      <c r="J106" t="str">
         <v>カルシウム・ビタミンD・ビタミンKを意識した食事、荷重運動(ウォーキング等)を勧める。ステロイド長期服用中の場合は骨粗鬆症治療薬の併用が検討されているか確認する</v>
       </c>
-      <c r="K102" t="str">
-        <v/>
-      </c>
-      <c r="L102" t="str">
+      <c r="K106" t="str">
+        <v/>
+      </c>
+      <c r="L106" t="str">
         <v>YAM70%未満、または既存の脆弱性骨折がある場合に骨粗鬆症と診断され薬物治療の対象となる(日本骨粗鬆症学会・日本骨代謝学会・厚生労働省合同「原発性骨粗鬆症の診断基準 2012年度改訂版」)。ビスホスホネート製剤は起床時空腹時に十分な水(180mL程度)で服用し、服用後30分は横にならないよう指導する。ステロイドを長期服用中の患者は骨密度によらず骨粗鬆症治療薬の併用が推奨される場合がある(グルココルチコイド誘発性骨粗鬆症: GIOP)</v>
       </c>
-      <c r="M102" t="str">
+      <c r="M106" t="str">
         <v>骨粗鬆症</v>
       </c>
-      <c r="N102" t="str">
+      <c r="N106" t="str">
         <v>骨密度,BMD,YAM,若年成人平均値,骨粗鬆症,DXA</v>
       </c>
-      <c r="O102" t="str">
+      <c r="O106" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O102"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O106"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/検査値リファレンス初期データ.xlsx
+++ b/検査値リファレンス初期データ.xlsx
@@ -464,711 +464,711 @@
         <v>参考ページ</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" xml:space="preserve">
       <c r="A2" t="str">
-        <v>収縮期血圧</v>
+        <v>血糖（空腹時・随時）</v>
       </c>
       <c r="B2" t="str">
-        <v>SBP,収縮期血圧</v>
-      </c>
-      <c r="C2" t="str">
-        <v>診察室血圧 120mmHg未満が正常域、140mmHg以上で高血圧(家庭血圧はそれぞれ5mmHg低い値が基準)</v>
+        <v>BS,Glu</v>
+      </c>
+      <c r="C2" t="str" xml:space="preserve">
+        <v xml:space="preserve">空腹時 70〜109 mg/dL
+（随時血糖は食後に上がるため単独では判断しにくい）</v>
       </c>
       <c r="D2" t="str">
-        <v>心臓が収縮して血液を送り出すときの血圧の最高値、いわゆる「上の血圧」</v>
+        <v>採血したその瞬間の血液中のブドウ糖の濃度</v>
       </c>
       <c r="E2" t="str">
-        <v>収縮期血圧は、心臓がギュッと縮んで血液を送り出す瞬間の血圧で、いわゆる「上の血圧」です。血管にかかる圧力の中で最も高い値になります。</v>
+        <v>この数値は採血したその瞬間の血糖値です。食事の前後で大きく変わるので、いつ測ったかによって見方が変わります。空腹時に高い場合や、食後を含めた随時血糖で200を超える場合は、糖尿病を疑う目安になります。</v>
       </c>
       <c r="F2" t="str">
-        <v>本態性高血圧、二次性高血圧(腎性・内分泌性など)、動脈硬化(高齢者で収縮期のみ上昇しやすい)、白衣高血圧、痛みやストレスによる一時的な上昇</v>
+        <v>糖尿病、食後高血糖、ステロイドなど薬剤性高血糖、感染・ストレスによる一時的な上昇</v>
       </c>
       <c r="G2" t="str">
-        <v>減塩(1日6g未満が目安)を心がけ、野菜・果物を積極的に摂るよう伝える。適度な運動・禁煙・節酒も血圧改善に役立つことを伝え、家庭血圧の記録習慣も勧める</v>
+        <v>食後の血糖上昇を抑えるため、早食い・まとめ食いを避け、野菜→汁物→主菜→主食の順に食べるとよいことを伝える。間食は甘い菓子より小魚やナッツなど血糖が上がりにくいものに置き換え、食後30分以内の軽い散歩も上昇抑制に役立つ</v>
       </c>
       <c r="H2" t="str">
-        <v>NSAIDs、ステロイド、経口避妊薬、甘草含有製剤(グリチルリチン)、一部の抗うつ薬・血管新生阻害薬は血圧を上げうる</v>
+        <v>ステロイド、サイアザイド系利尿薬、非定型抗精神病薬(オランザピン・クエチアピン)、タクロリムス・シクロスポリン、β遮断薬、高カロリー輸液</v>
       </c>
       <c r="I2" t="str">
-        <v>起立性低血圧、脱水、降圧薬の効きすぎ、心不全の増悪、出血・ショック</v>
+        <v>低血糖（薬剤性、食事摂取不足、シックデイ時の過量投与など）</v>
       </c>
       <c r="J2" t="str">
-        <v>めまい・立ちくらみの有無を確認する。急に立ち上がらずゆっくり動作するよう伝え、脱水が疑われる場合はこまめな水分摂取を勧める</v>
+        <v>空腹時間が長くならないよう食事を規則正しくとる。外出時はブドウ糖やアメを携帯し、冷や汗・動悸・強い空腹感が出たらすぐ糖分を摂るよう伝える。運動量が多い日は補食を追加するなど活動量に応じた調整も説明する</v>
       </c>
       <c r="K2" t="str">
-        <v>降圧薬(特に利尿薬・α遮断薬)の効きすぎ、抗うつ薬・抗パーキンソン病薬などによる起立性低血圧</v>
+        <v>インスリン、SU薬(グリメピリド等)、速効型インスリン分泌促進薬(グリニド系)。β遮断薬は低血糖症状をマスクすることがあるため注意</v>
       </c>
       <c r="L2" t="str">
-        <v>診察室血圧と家庭血圧で基準値が異なる(家庭血圧のほうが5mmHg低い基準)。高齢者では収縮期血圧のみが高くなる収縮期高血圧が多く、動脈硬化を反映する。降圧薬開始・増量後はふらつき・立ちくらみの有無を確認する</v>
+        <v>採血のタイミング（空腹時か食後か）を必ず確認する。SU薬・インスリン使用者では低血糖症状の有無も併せて聞く</v>
       </c>
       <c r="M2" t="str">
-        <v>心不全</v>
+        <v>糖尿病,精神疾患（非定型抗精神病薬）</v>
       </c>
       <c r="N2" t="str">
-        <v>血圧,収縮期血圧,SBP,上の血圧,高血圧</v>
+        <v>血糖値,血糖,BS,Glu,グルコース,空腹時血糖,随時血糖,食後血糖</v>
       </c>
       <c r="O2" t="str">
-        <v/>
+        <v>食事と栄養 p.18（炭水化物）／p.106-131（第2部 糖尿病）</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>拡張期血圧</v>
+        <v>HbA1c</v>
       </c>
       <c r="B3" t="str">
-        <v>DBP,拡張期血圧</v>
+        <v>HbA1c</v>
       </c>
       <c r="C3" t="str">
-        <v>診察室血圧 80mmHg未満が正常域、90mmHg以上で高血圧(家庭血圧はそれぞれ5mmHg低い値が基準)</v>
+        <v>6.5%未満（NGSP値）</v>
       </c>
       <c r="D3" t="str">
-        <v>心臓が拡張して血液をため込むときの血圧の最低値、いわゆる「下の血圧」</v>
+        <v>過去1〜2か月の平均的な血糖の高さを表す数値</v>
       </c>
       <c r="E3" t="str">
-        <v>拡張期血圧は、心臓が広がって次の収縮に備えて血液をためている瞬間の血圧で、いわゆる「下の血圧」です。</v>
+        <v>HbA1cは、この1〜2か月の血糖値の平均を表す数値です。その日の食事や体調に左右されにくいので、普段の血糖コントロールがどれくらいできているかを見るのに使います。数値が高いほど、平均して血糖値が高めだったことを示します。</v>
       </c>
       <c r="F3" t="str">
-        <v>本態性高血圧、二次性高血圧、若年〜中年での血管抵抗上昇が主体の高血圧</v>
+        <v>糖尿病、血糖コントロール不良</v>
       </c>
       <c r="G3" t="str">
-        <v>収縮期血圧と同様、減塩・適度な運動・禁煙・節酒を心がけるよう伝える</v>
+        <v>主食の量や間食の頻度を見直し、通勤の一駅歩きなど日常に取り入れやすい運動を増やすよう提案する。飲み忘れがあればお薬カレンダーやアラームの活用も一緒に検討する</v>
       </c>
       <c r="H3" t="str">
-        <v>NSAIDs、ステロイド、経口避妊薬、甘草含有製剤(グリチルリチン)</v>
+        <v>血糖と同様(ステロイド、非定型抗精神病薬、サイアザイド系利尿薬など)。SU薬・インスリンを使用中なら低血糖の有無も確認</v>
       </c>
       <c r="I3" t="str">
-        <v>大動脈弁閉鎖不全症、甲状腺機能亢進症、動脈硬化の進行(脈圧が開大)</v>
+        <v>低血糖を繰り返している状態</v>
       </c>
       <c r="J3" t="str">
-        <v>めまいなどの症状がないか確認する</v>
+        <v>低血糖を防ぐため、食事の間隔をあけすぎないようにする。ブドウ糖など対処品の携帯を勧め、運転前や普段と違う強度の運動をする前は血糖自己測定で確認する習慣を提案する</v>
       </c>
       <c r="K3" t="str">
-        <v>降圧薬(特に血管拡張作用の強いCa拮抗薬)の効きすぎ</v>
+        <v/>
       </c>
       <c r="L3" t="str">
-        <v>加齢とともに動脈硬化が進むと拡張期血圧は低下し、収縮期血圧との差(脈圧)が開大する。脈圧の開大は動脈硬化の進行を示唆する所見として重視される</v>
+        <v>貧血・鉄剤補充・妊娠・腎不全などがあると、実際の血糖値とズレて出ることがある。直近の血糖自己測定値と合わせて確認する</v>
       </c>
       <c r="M3" t="str">
-        <v>心不全</v>
+        <v>糖尿病,精神疾患（非定型抗精神病薬）</v>
       </c>
       <c r="N3" t="str">
-        <v>血圧,拡張期血圧,DBP,下の血圧,高血圧,脈圧</v>
+        <v>HbA1c,ヘモグロビンエーワンシー,グリコヘモグロビン,血糖コントロール,NGSP</v>
       </c>
       <c r="O3" t="str">
-        <v/>
+        <v>食事と栄養 p.18（炭水化物）／p.106-131（第2部 糖尿病）</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>脈拍</v>
+        <v>尿素窒素（BUN）</v>
       </c>
       <c r="B4" t="str">
-        <v>HR,脈拍</v>
+        <v>BUN,UN</v>
       </c>
       <c r="C4" t="str">
-        <v>60〜100回/分</v>
+        <v>8〜20 mg/dL</v>
       </c>
       <c r="D4" t="str">
-        <v>心臓が1分間に拍動する回数。心臓のリズムや働き具合の目安になる</v>
+        <v>たんぱく質が分解されてできる老廃物で、腎機能や体の状態を反映する</v>
       </c>
       <c r="E4" t="str">
-        <v>脈拍は心臓が1分間に何回打っているかを表す数値です。運動や緊張で一時的に増えたり、リラックスしていると減ったりします。極端に速い・遅い状態が続く場合は、心臓の病気やお薬の影響が考えられます。</v>
+        <v>BUNはたんぱく質が体の中で使われたあとにできる老廃物のひとつです。腎臓の働きが落ちると排泄されにくくなって数値が上がりますが、脱水や消化管出血、たんぱく質の摂りすぎでも上がることがあります。</v>
       </c>
       <c r="F4" t="str">
-        <v>頻脈性不整脈(心房細動等)、発熱、脱水、甲状腺機能亢進症、貧血、痛み・不安・カフェイン摂取、薬剤性(β刺激薬など)</v>
+        <v>腎機能低下・腎不全、脱水、消化管出血、高たんぱく食、ステロイド使用</v>
       </c>
       <c r="G4" t="str">
-        <v>動悸・息切れなどの症状がないか確認する。カフェインの摂りすぎがないかもあわせて確認する</v>
+        <v>脱水を避けてこまめに水分を摂る(心不全等で水分制限がある場合を除く)。極端な高たんぱく食が続いていないか確認し、黒い便など消化管出血のサインにも注意する</v>
       </c>
       <c r="H4" t="str">
-        <v>β刺激薬(気管支拡張薬)、甲状腺ホルモン薬の過量、一部の抗コリン薬</v>
+        <v/>
       </c>
       <c r="I4" t="str">
-        <v>徐脈性不整脈(洞不全症候群、房室ブロック等)、甲状腺機能低下症、薬剤性(β遮断薬・ジゴキシン等)、アスリート心</v>
+        <v>低たんぱく食、肝不全によるたんぱく合成低下、妊娠</v>
       </c>
       <c r="J4" t="str">
-        <v>めまい・失神・強い倦怠感がないか確認する。特にβ遮断薬服用中は自己判断で中断せず、症状があれば医師に相談するよう伝える</v>
+        <v>食事量、特にたんぱく質(肉・魚・卵・大豆製品)の摂取量を確認する。食欲低下や極端な菜食が続いていないか、栄養状態全体もあわせて確認する</v>
       </c>
       <c r="K4" t="str">
-        <v>β遮断薬、非ジヒドロピリジン系Ca拮抗薬(ベラパミル・ジルチアゼム)、ジゴキシン、一部の抗不整脈薬</v>
+        <v/>
       </c>
       <c r="L4" t="str">
-        <v>β遮断薬・ジゴキシン服用中は徐脈の指標として重要。心房細動患者では脈拍数と実際の心拍数(心電図)にずれ(脈拍欠損)が生じることがある点にも留意する</v>
+        <v>クレアチニンと同時に見る。BUN/Cr比が高ければ脱水や消化管出血を、比が正常で両方高ければ腎性を疑う目安になる</v>
       </c>
       <c r="M4" t="str">
-        <v>抗凝固療法（心房細動・血栓症）,心不全</v>
+        <v>腎機能,糖尿病,骨粗鬆症,抗凝固療法（心房細動・血栓症）</v>
       </c>
       <c r="N4" t="str">
-        <v>脈拍,心拍数,HR,頻脈,徐脈,不整脈</v>
+        <v>BUN,尿素窒素,UN,腎機能</v>
       </c>
       <c r="O4" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="5">
+        <v>食事と栄養 p.199-215（第2部 腎機能低下）</v>
+      </c>
+    </row>
+    <row r="5" xml:space="preserve">
       <c r="A5" t="str">
-        <v>眼圧</v>
+        <v>クレアチニン・eGFR</v>
       </c>
       <c r="B5" t="str">
-        <v>IOP,眼圧</v>
-      </c>
-      <c r="C5" t="str">
-        <v>10〜21 mmHg</v>
-      </c>
-      <c r="D5" t="str">
-        <v>眼球内の圧力。高い状態が続くと視神経が障害され緑内障の原因になる</v>
-      </c>
-      <c r="E5" t="str">
-        <v>眼圧は、目の中を満たしている水(房水)の圧力です。この圧力が高い状態が続くと、視神経が徐々に傷んで視野が欠けていく緑内障の原因になることがあります。</v>
-      </c>
-      <c r="F5" t="str">
-        <v>緑内障(開放隅角緑内障・閉塞隅角緑内障)、ステロイド点眼・全身投与による眼圧上昇(ステロイド緑内障)、ぶどう膜炎</v>
-      </c>
-      <c r="G5" t="str">
-        <v>目のかすみ、頭痛、吐き気、視野が欠ける感じがないか確認する。ステロイド点眼を使用中の場合は自己判断で中止せず定期受診を続けるよう伝える</v>
-      </c>
-      <c r="H5" t="str">
-        <v>ステロイド(点眼・内服・吸入)、抗コリン薬(閉塞隅角緑内障がある場合は禁忌〜慎重投与)、一部の抗うつ薬・抗ヒスタミン薬(抗コリン作用)</v>
-      </c>
-      <c r="I5" t="str">
-        <v>低眼圧症(眼科手術後、外傷、ぶどう膜炎による房水産生低下など)</v>
-      </c>
-      <c r="J5" t="str">
-        <v>眼科手術後などで急激な視力低下がある場合は早めの受診を勧める</v>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>緑内障治療薬(点眼)は種類が多く複数併用することが多いため、点眼順序(5分以上あける)や防腐剤による角膜障害にも注意する。閉塞隅角緑内障の患者には抗コリン作用のある薬剤(一部の感冒薬・抗うつ薬・過活動膀胱治療薬等)が禁忌〜慎重投与となる場合がある</v>
-      </c>
-      <c r="M5" t="str">
-        <v/>
-      </c>
-      <c r="N5" t="str">
-        <v>眼圧,IOP,緑内障,ステロイド緑内障</v>
-      </c>
-      <c r="O5" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="6" xml:space="preserve">
-      <c r="A6" t="str">
-        <v>血糖（空腹時・随時）</v>
-      </c>
-      <c r="B6" t="str">
-        <v>BS,Glu</v>
-      </c>
-      <c r="C6" t="str" xml:space="preserve">
-        <v xml:space="preserve">空腹時 70〜109 mg/dL
-（随時血糖は食後に上がるため単独では判断しにくい）</v>
-      </c>
-      <c r="D6" t="str">
-        <v>採血したその瞬間の血液中のブドウ糖の濃度</v>
-      </c>
-      <c r="E6" t="str">
-        <v>この数値は採血したその瞬間の血糖値です。食事の前後で大きく変わるので、いつ測ったかによって見方が変わります。空腹時に高い場合や、食後を含めた随時血糖で200を超える場合は、糖尿病を疑う目安になります。</v>
-      </c>
-      <c r="F6" t="str">
-        <v>糖尿病、食後高血糖、ステロイドなど薬剤性高血糖、感染・ストレスによる一時的な上昇</v>
-      </c>
-      <c r="G6" t="str">
-        <v>食後の血糖上昇を抑えるため、早食い・まとめ食いを避け、野菜→汁物→主菜→主食の順に食べるとよいことを伝える。間食は甘い菓子より小魚やナッツなど血糖が上がりにくいものに置き換え、食後30分以内の軽い散歩も上昇抑制に役立つ</v>
-      </c>
-      <c r="H6" t="str">
-        <v>ステロイド、サイアザイド系利尿薬、非定型抗精神病薬(オランザピン・クエチアピン)、タクロリムス・シクロスポリン、β遮断薬、高カロリー輸液</v>
-      </c>
-      <c r="I6" t="str">
-        <v>低血糖（薬剤性、食事摂取不足、シックデイ時の過量投与など）</v>
-      </c>
-      <c r="J6" t="str">
-        <v>空腹時間が長くならないよう食事を規則正しくとる。外出時はブドウ糖やアメを携帯し、冷や汗・動悸・強い空腹感が出たらすぐ糖分を摂るよう伝える。運動量が多い日は補食を追加するなど活動量に応じた調整も説明する</v>
-      </c>
-      <c r="K6" t="str">
-        <v>インスリン、SU薬(グリメピリド等)、速効型インスリン分泌促進薬(グリニド系)。β遮断薬は低血糖症状をマスクすることがあるため注意</v>
-      </c>
-      <c r="L6" t="str">
-        <v>採血のタイミング（空腹時か食後か）を必ず確認する。SU薬・インスリン使用者では低血糖症状の有無も併せて聞く</v>
-      </c>
-      <c r="M6" t="str">
-        <v>糖尿病,精神疾患（非定型抗精神病薬）</v>
-      </c>
-      <c r="N6" t="str">
-        <v>血糖値,血糖,BS,Glu,グルコース,空腹時血糖,随時血糖,食後血糖</v>
-      </c>
-      <c r="O6" t="str">
-        <v>食事と栄養 p.18（炭水化物）／p.106-131（第2部 糖尿病）</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>HbA1c</v>
-      </c>
-      <c r="B7" t="str">
-        <v>HbA1c</v>
-      </c>
-      <c r="C7" t="str">
-        <v>6.5%未満（NGSP値）</v>
-      </c>
-      <c r="D7" t="str">
-        <v>過去1〜2か月の平均的な血糖の高さを表す数値</v>
-      </c>
-      <c r="E7" t="str">
-        <v>HbA1cは、この1〜2か月の血糖値の平均を表す数値です。その日の食事や体調に左右されにくいので、普段の血糖コントロールがどれくらいできているかを見るのに使います。数値が高いほど、平均して血糖値が高めだったことを示します。</v>
-      </c>
-      <c r="F7" t="str">
-        <v>糖尿病、血糖コントロール不良</v>
-      </c>
-      <c r="G7" t="str">
-        <v>主食の量や間食の頻度を見直し、通勤の一駅歩きなど日常に取り入れやすい運動を増やすよう提案する。飲み忘れがあればお薬カレンダーやアラームの活用も一緒に検討する</v>
-      </c>
-      <c r="H7" t="str">
-        <v>血糖と同様(ステロイド、非定型抗精神病薬、サイアザイド系利尿薬など)。SU薬・インスリンを使用中なら低血糖の有無も確認</v>
-      </c>
-      <c r="I7" t="str">
-        <v>低血糖を繰り返している状態</v>
-      </c>
-      <c r="J7" t="str">
-        <v>低血糖を防ぐため、食事の間隔をあけすぎないようにする。ブドウ糖など対処品の携帯を勧め、運転前や普段と違う強度の運動をする前は血糖自己測定で確認する習慣を提案する</v>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>貧血・鉄剤補充・妊娠・腎不全などがあると、実際の血糖値とズレて出ることがある。直近の血糖自己測定値と合わせて確認する</v>
-      </c>
-      <c r="M7" t="str">
-        <v>糖尿病,精神疾患（非定型抗精神病薬）</v>
-      </c>
-      <c r="N7" t="str">
-        <v>HbA1c,ヘモグロビンエーワンシー,グリコヘモグロビン,血糖コントロール,NGSP</v>
-      </c>
-      <c r="O7" t="str">
-        <v>食事と栄養 p.18（炭水化物）／p.106-131（第2部 糖尿病）</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>尿素窒素（BUN）</v>
-      </c>
-      <c r="B8" t="str">
-        <v>BUN,UN</v>
-      </c>
-      <c r="C8" t="str">
-        <v>8〜20 mg/dL</v>
-      </c>
-      <c r="D8" t="str">
-        <v>たんぱく質が分解されてできる老廃物で、腎機能や体の状態を反映する</v>
-      </c>
-      <c r="E8" t="str">
-        <v>BUNはたんぱく質が体の中で使われたあとにできる老廃物のひとつです。腎臓の働きが落ちると排泄されにくくなって数値が上がりますが、脱水や消化管出血、たんぱく質の摂りすぎでも上がることがあります。</v>
-      </c>
-      <c r="F8" t="str">
-        <v>腎機能低下・腎不全、脱水、消化管出血、高たんぱく食、ステロイド使用</v>
-      </c>
-      <c r="G8" t="str">
-        <v>脱水を避けてこまめに水分を摂る(心不全等で水分制限がある場合を除く)。極端な高たんぱく食が続いていないか確認し、黒い便など消化管出血のサインにも注意する</v>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>低たんぱく食、肝不全によるたんぱく合成低下、妊娠</v>
-      </c>
-      <c r="J8" t="str">
-        <v>食事量、特にたんぱく質(肉・魚・卵・大豆製品)の摂取量を確認する。食欲低下や極端な菜食が続いていないか、栄養状態全体もあわせて確認する</v>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>クレアチニンと同時に見る。BUN/Cr比が高ければ脱水や消化管出血を、比が正常で両方高ければ腎性を疑う目安になる</v>
-      </c>
-      <c r="M8" t="str">
-        <v>腎機能,糖尿病,骨粗鬆症,抗凝固療法（心房細動・血栓症）</v>
-      </c>
-      <c r="N8" t="str">
-        <v>BUN,尿素窒素,UN,腎機能</v>
-      </c>
-      <c r="O8" t="str">
-        <v>食事と栄養 p.199-215（第2部 腎機能低下）</v>
-      </c>
-    </row>
-    <row r="9" xml:space="preserve">
-      <c r="A9" t="str">
-        <v>クレアチニン・eGFR</v>
-      </c>
-      <c r="B9" t="str">
         <v>Cr,eGFR</v>
       </c>
-      <c r="C9" t="str" xml:space="preserve">
+      <c r="C5" t="str" xml:space="preserve">
         <v xml:space="preserve">クレアチニン 男性0.6〜1.1 mg/dL、女性0.4〜0.8 mg/dL
 eGFR 60 mL/分/1.73㎡以上</v>
       </c>
-      <c r="D9" t="str">
+      <c r="D5" t="str">
         <v>腎臓がどれくらい老廃物をろ過できているかを表す指標</v>
       </c>
-      <c r="E9" t="str">
+      <c r="E5" t="str">
         <v>クレアチニンは筋肉から出る老廃物で、腎臓のろ過機能が落ちると血液の中に増えていきます。eGFRはそのクレアチニンの値や年齢から計算した「腎臓の働きの点数」のようなもので、100に近いほど良く、数字が下がるほど腎臓の働きが落ちていることを表します。</v>
       </c>
-      <c r="F9" t="str">
+      <c r="F5" t="str">
         <v>クレアチニン上昇（＝eGFR低下）で考える：腎機能低下、脱水、腎不全、腎毒性のある薬剤の影響</v>
       </c>
-      <c r="G9" t="str">
+      <c r="G5" t="str">
         <v>脱水を避けてこまめに水分を摂る(心不全等で水分制限がある場合を除く)。塩分の摂りすぎに注意し、市販の鎮痛薬(NSAIDs)を自己判断で連用していないかも確認する</v>
       </c>
-      <c r="H9" t="str">
+      <c r="H5" t="str">
         <v>腎排泄型薬剤の減量要否を確認(ジゴキシン、NOAC、メトホルミン、アミノグリコシド系、バンコマイシン等)。悪化させうる代表薬はNSAIDs・ARB/ACE阻害薬・利尿薬・造影剤・アミノグリコシド系</v>
       </c>
-      <c r="I9" t="str">
+      <c r="I5" t="str">
         <v>クレアチニンが低い場合：筋肉量の低下、高齢・るいそうで見かけ上低く出ることがある</v>
       </c>
-      <c r="J9" t="str">
+      <c r="J5" t="str">
         <v>高齢・るいそうでは筋肉量低下により見かけ上低く出て腎機能を過大評価しやすいため注意する。筋力低下がある場合は無理のない範囲での運動やたんぱく質摂取を勧める</v>
       </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str" xml:space="preserve">
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str" xml:space="preserve">
         <v xml:space="preserve">筋肉量に影響されるため、るいそうの強い高齢者では腎機能を過大評価しやすい。eGFR低下時は腎排泄型薬剤の用量調整を確認する。
 CKD重症度分類（GFR区分）の目安：G1 正常または高値(90以上)／G2 正常または軽度低下(60〜89)／G3a 軽度〜中等度低下(45〜59)／G3b 中等度〜高度低下(30〜44)／G4 高度低下(15〜29)／G5 末期腎不全(15未満)。
 eGFRには体表面積1.73㎡に標準化した「標準化eGFR」（CKD病期の判定などに使用）と、実際の体表面積で補正した「個別化eGFR」（標準化eGFR×体表面積÷1.73、薬剤投与量の決定に使用）があり、体格が標準から大きく外れる患者では両者がずれるため、用量調整の場面では個別化eGFRやCCrを優先する</v>
       </c>
-      <c r="M9" t="str">
+      <c r="M5" t="str">
         <v>腎機能,糖尿病,骨粗鬆症,抗凝固療法（心房細動・血栓症）</v>
       </c>
-      <c r="N9" t="str">
+      <c r="N5" t="str">
         <v>クレアチニン,Cr,SCr,血清クレアチニン,eGFR,腎機能,GFR,推算糸球体濾過量,CKD重症度分類</v>
       </c>
-      <c r="O9" t="str">
+      <c r="O5" t="str">
         <v>食事と栄養 p.199-215（第2部 腎機能低下）／p.243（フレイルQ111 クレアチニン値が低い場合）</v>
       </c>
     </row>
-    <row r="10" xml:space="preserve">
-      <c r="A10" t="str">
+    <row r="6" xml:space="preserve">
+      <c r="A6" t="str">
         <v>CCr（クレアチニンクリアランス）</v>
       </c>
-      <c r="B10" t="str">
+      <c r="B6" t="str">
         <v>CCr</v>
       </c>
-      <c r="C10" t="str">
+      <c r="C6" t="str">
         <v>目安 91〜130 mL/分（Cockcroft-Gault式で算出。年齢・体重・性別で変動）</v>
       </c>
-      <c r="D10" t="str">
+      <c r="D6" t="str">
         <v>腎臓が実際にどれくらい血液をろ過・排泄できているかを、より直接的に表す指標</v>
       </c>
-      <c r="E10" t="str">
+      <c r="E6" t="str">
         <v>CCrは、腎臓が1分間にどれくらいの血液をきれいにできているかを表す数値です。クレアチニンという体の老廃物が尿にどれくらい出ているかをもとに計算します。お薬の量を腎臓の働きに合わせて調整するときによく使われる指標です。</v>
       </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
         <v>添付文書のCCr基準で減量が必要な薬剤(NOAC、ST合剤、アシクロビル等)の用量を確認</v>
       </c>
-      <c r="I10" t="str">
+      <c r="I6" t="str">
         <v>腎機能の低下（数値が低いほどろ過機能の低下を示す）、脱水、加齢に伴う腎機能低下、糖尿病性腎症など</v>
       </c>
-      <c r="J10" t="str">
+      <c r="J6" t="str">
         <v>脱水を避けてこまめに水分を摂る(水分制限がある場合を除く)。腎排泄型の薬剤は減量や投与間隔の延長が必要になることがあるため、お薬手帳を最新の状態に保ち他院受診時にも提示するよう伝える</v>
       </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str" xml:space="preserve">
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str" xml:space="preserve">
         <v xml:space="preserve">Cockcroft-Gault式［(140−年齢)×体重(kg)÷(72×血清Cr)、女性は×0.85］で算出した推算CCrが、多くの薬剤の添付文書における腎機能別用量調整の基準に使われる。eGFRは体表面積1.73㎡で標準化した値のため、実際の体格が標準から離れる患者（高齢・るいそう・肥満など）では、添付文書のCCr基準にそのまま当てはめると過大・過小評価になりうる点に注意。
 血清Cr(mg/dL)からのおおまかな対応の目安：0.7〜1.4→CCr100±20（正常・健常）／1.4〜2.4→61〜99（日常生活に支障なし）／2.5〜4.9→24〜60（日常生活に多少の支障）／5.0〜7.9→12〜23（日常生活に支障あり）／8.0〜12.0→7〜12（日常生活の規制）／12.0超→6未満（昏睡・見当識障害）</v>
       </c>
+      <c r="M6" t="str">
+        <v>腎機能,糖尿病,骨粗鬆症,抗凝固療法（心房細動・血栓症）</v>
+      </c>
+      <c r="N6" t="str">
+        <v>CCr,クレアチニンクリアランス,クレアチニン・クリアランス,creatinine clearance,コッククロフトゴート,Cockcroft-Gault,腎機能</v>
+      </c>
+      <c r="O6" t="str">
+        <v>食事と栄養 p.199-215（第2部 腎機能低下）</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>尿酸</v>
+      </c>
+      <c r="B7" t="str">
+        <v>UA</v>
+      </c>
+      <c r="C7" t="str">
+        <v>2.0〜7.0 mg/dL</v>
+      </c>
+      <c r="D7" t="str">
+        <v>プリン体が分解されてできる老廃物で、高いと痛風や尿路結石のリスクになる</v>
+      </c>
+      <c r="E7" t="str">
+        <v>尿酸はプリン体という物質が体の中で分解されてできる老廃物です。7.0を超えた状態が続くと、関節に結晶がたまって痛風発作を起こしたり、尿路結石ができやすくなったりします。</v>
+      </c>
+      <c r="F7" t="str">
+        <v>高尿酸血症、痛風、プリン体の多い食事・アルコール摂取、腎機能低下、利尿薬などの薬剤性</v>
+      </c>
+      <c r="G7" t="str">
+        <v>プリン体の多い食品(レバー・魚卵・干物・ビールなど)を控えめにし、水分を多めに摂る。BMIが高い場合は減量も尿酸値の改善に有効なことを伝える</v>
+      </c>
+      <c r="H7" t="str">
+        <v>サイアザイド系利尿薬、ループ利尿薬、少量アスピリン、ピラジナミド、シクロスポリンは上昇させうる。尿酸降下薬(アロプリノール等)服用中はコントロール状況も確認</v>
+      </c>
+      <c r="I7" t="str">
+        <v>尿酸排泄促進薬の効果、まれに特発性腎性低尿酸血症</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v>尿酸降下薬(フェブキソスタット、アロプリノール等)の効きすぎ</v>
+      </c>
+      <c r="L7" t="str">
+        <v>利尿薬（サイアザイド系など）は尿酸を上げやすい。急激に尿酸を下げる治療の開始直後は痛風発作が誘発されることがある</v>
+      </c>
+      <c r="M7" t="str">
+        <v>高尿酸血症,糖尿病</v>
+      </c>
+      <c r="N7" t="str">
+        <v>尿酸,UA,痛風,高尿酸血症</v>
+      </c>
+      <c r="O7" t="str">
+        <v>食事と栄養 p.180-189（第2部 痛風・高尿酸血症）</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>ナトリウム（Na）</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Na</v>
+      </c>
+      <c r="C8" t="str">
+        <v>135〜145 mEq/L</v>
+      </c>
+      <c r="D8" t="str">
+        <v>体内の水分バランスや神経・筋肉の働きに関わる、血液中に最も多い電解質</v>
+      </c>
+      <c r="E8" t="str">
+        <v>ナトリウムは、体の中の水分バランスを保ったり、神経や筋肉が正しく働くために欠かせないミネラルです。多すぎても少なすぎても、意識障害やけいれんなど重い症状につながることがあります。</v>
+      </c>
+      <c r="F8" t="str">
+        <v>脱水、アルドステロン症、水分摂取不足、下痢・嘔吐による水分喪失</v>
+      </c>
+      <c r="G8" t="str">
+        <v>水分摂取状況を確認する(脱水が疑われる場合)。高齢者は口渇を感じにくいため、喉が渇く前にこまめな水分摂取を意識するよう伝える</v>
+      </c>
+      <c r="H8" t="str">
+        <v>高張輸液、浸透圧利尿薬(グリセオール等)、抗利尿ホルモン分泌を低下させる薬(炭酸リチウム等)</v>
+      </c>
+      <c r="I8" t="str">
+        <v>利尿薬（特にサイアザイド系）、SIADH（抗利尿ホルモン不適合分泌症候群）、嘔吐・下痢、心不全・肝硬変によるむくみ</v>
+      </c>
+      <c r="J8" t="str">
+        <v>利尿薬使用中は嘔吐・下痢が続いていないか確認する。意識がぼんやりする、頭痛、脱力感などの症状の有無を確認し、水のみを大量に摂りすぎていないかも確認する</v>
+      </c>
+      <c r="K8" t="str">
+        <v>サイアザイド系利尿薬、SSRI、カルバマゼピン、デスモプレシン、シクロホスファミド</v>
+      </c>
+      <c r="L8" t="str">
+        <v>低ナトリウム血症は高齢者に多く、意識障害や転倒の原因になりうる。利尿薬（特にサイアザイド系）、SSRI、カルバマゼピンなどSIADHを起こしうる薬剤の使用歴を確認する</v>
+      </c>
+      <c r="M8" t="str">
+        <v>電解質</v>
+      </c>
+      <c r="N8" t="str">
+        <v>ナトリウム,Na,電解質,脱水,SIADH,低ナトリウム血症</v>
+      </c>
+      <c r="O8" t="str">
+        <v>食事と栄養 p.81（ナトリウム）</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>クロール</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Cl</v>
+      </c>
+      <c r="C9" t="str">
+        <v>98〜108 mEq/L</v>
+      </c>
+      <c r="D9" t="str">
+        <v>ナトリウムと共に体の水分・酸塩基バランスに関わる電解質</v>
+      </c>
+      <c r="E9" t="str">
+        <v>クロールは、ナトリウムと一緒に体の水分バランスや、体液の性質（酸性・アルカリ性）を保つ働きをしているミネラルです。多くの場合、ナトリウムと同じように変動します。</v>
+      </c>
+      <c r="F9" t="str">
+        <v>脱水、腎不全、代謝性アシドーシス、高ナトリウム血症に伴うもの</v>
+      </c>
+      <c r="G9" t="str">
+        <v>脱水が疑われる場合はこまめな水分摂取を勧める（水分制限がある場合を除く）</v>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>嘔吐・下痢、利尿薬使用、代謝性アルカローシス</v>
+      </c>
+      <c r="J9" t="str">
+        <v>利尿薬使用中は嘔吐・下痢が続いていないか確認する</v>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>ナトリウムと同じ方向に動くことが多いが、酸塩基平衡の異常（アシドーシス・アルカローシス）を反映して単独で動くこともある。利尿薬（特にループ利尿薬）使用中は低クロール性アルカローシスに注意</v>
+      </c>
+      <c r="M9" t="str">
+        <v>電解質,腎機能</v>
+      </c>
+      <c r="N9" t="str">
+        <v>クロール,Cl,塩素,電解質,アシドーシス,アルカローシス</v>
+      </c>
+      <c r="O9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>カリウム（K）</v>
+      </c>
+      <c r="B10" t="str">
+        <v>K</v>
+      </c>
+      <c r="C10" t="str">
+        <v>3.5〜5.0 mEq/L（5.5 mEq/L以上で高カリウム血症と診断）</v>
+      </c>
+      <c r="D10" t="str">
+        <v>心臓や筋肉の働きに関わる電解質で、高すぎても低すぎても不整脈につながる</v>
+      </c>
+      <c r="E10" t="str">
+        <v>カリウムは心臓や筋肉が正しく動くために必要なミネラルです。多すぎても少なすぎても脈の乱れにつながることがあるため、腎臓のお薬やお通じのお薬を使っている方は定期的にチェックすることが大切です。</v>
+      </c>
+      <c r="F10" t="str">
+        <v>腎不全、アジソン病、ACE阻害薬・ARB・カリウム保持性利尿薬などの薬剤性、溶血による偽高値</v>
+      </c>
+      <c r="G10" t="str">
+        <v>生野菜・果物・芋類などカリウムの多い食品の摂りすぎに注意する(腎機能低下がある場合)。茹でこぼす・水にさらすことでカリウムを減らせることもあわせて伝える</v>
+      </c>
+      <c r="H10" t="str">
+        <v>ACE阻害薬、ARB、カリウム保持性利尿薬(スピロノラクトン等)、NSAIDs、ST合剤、ヘパリン。β遮断薬は細胞内への取り込みを阻害し上昇させうる</v>
+      </c>
+      <c r="I10" t="str">
+        <v>利尿薬（特にループ・サイアザイド系）、下痢・嘔吐、インスリン投与、甘草含有製剤</v>
+      </c>
+      <c r="J10" t="str">
+        <v>利尿薬使用中は下痢・嘔吐が続いていないか確認し、必要に応じてバナナ・芋類などカリウムを含む食品を意識する。脱力感・こむら返り・動悸などの症状の有無もあわせて確認する</v>
+      </c>
+      <c r="K10" t="str">
+        <v>ループ利尿薬、サイアザイド系利尿薬、グリチルリチン製剤(甘草含有製剤)、ステロイド、インスリン、β2刺激薬</v>
+      </c>
+      <c r="L10" t="str">
+        <v>高カリウム血症は不整脈・心停止のリスクがあるため脱力感・動悸の有無を確認。RAS阻害薬とカリウム保持性利尿薬の併用時は特に注意</v>
+      </c>
       <c r="M10" t="str">
-        <v>腎機能,糖尿病,骨粗鬆症,抗凝固療法（心房細動・血栓症）</v>
+        <v>腎機能,電解質</v>
       </c>
       <c r="N10" t="str">
-        <v>CCr,クレアチニンクリアランス,クレアチニン・クリアランス,creatinine clearance,コッククロフトゴート,Cockcroft-Gault,腎機能</v>
+        <v>カリウム,K,高カリウム血症,低カリウム血症</v>
       </c>
       <c r="O10" t="str">
-        <v>食事と栄養 p.199-215（第2部 腎機能低下）</v>
+        <v>食事と栄養 p.72（カリウム）／p.199-215（第2部 腎機能低下 Q80-82 カリウム制限）</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>尿酸</v>
+        <v>カルシウム（Ca）</v>
       </c>
       <c r="B11" t="str">
-        <v>UA</v>
+        <v>Ca</v>
       </c>
       <c r="C11" t="str">
-        <v>2.0〜7.0 mg/dL</v>
+        <v>8.5〜10.0 mg/dL</v>
       </c>
       <c r="D11" t="str">
-        <v>プリン体が分解されてできる老廃物で、高いと痛風や尿路結石のリスクになる</v>
+        <v>骨や歯の材料であると同時に、神経・筋肉・血液凝固にも関わるミネラル</v>
       </c>
       <c r="E11" t="str">
-        <v>尿酸はプリン体という物質が体の中で分解されてできる老廃物です。7.0を超えた状態が続くと、関節に結晶がたまって痛風発作を起こしたり、尿路結石ができやすくなったりします。</v>
+        <v>カルシウムは骨や歯の材料になるだけでなく、神経の伝達や筋肉の収縮、血液を固める働きにも関わっている重要なミネラルです。副甲状腺ホルモンやビタミンDによって血液中の濃度が細かく調整されています。</v>
       </c>
       <c r="F11" t="str">
-        <v>高尿酸血症、痛風、プリン体の多い食事・アルコール摂取、腎機能低下、利尿薬などの薬剤性</v>
+        <v>副甲状腺機能亢進症、悪性腫瘍（骨転移など）、ビタミンD過剰、活性型ビタミンD3製剤の過量</v>
       </c>
       <c r="G11" t="str">
-        <v>プリン体の多い食品(レバー・魚卵・干物・ビールなど)を控えめにし、水分を多めに摂る。BMIが高い場合は減量も尿酸値の改善に有効なことを伝える</v>
+        <v>吐き気、便秘、多尿、意識がぼんやりするなどの高カルシウム血症の症状がないか確認する。活性型ビタミンD3製剤使用中は過量になっていないか、水分摂取が十分かも確認する</v>
       </c>
       <c r="H11" t="str">
-        <v>サイアザイド系利尿薬、ループ利尿薬、少量アスピリン、ピラジナミド、シクロスポリンは上昇させうる。尿酸降下薬(アロプリノール等)服用中はコントロール状況も確認</v>
+        <v>活性型ビタミンD製剤、サイアザイド系利尿薬、炭酸リチウム、カルシウム含有薬(炭酸カルシウム等)</v>
       </c>
       <c r="I11" t="str">
-        <v>尿酸排泄促進薬の効果、まれに特発性腎性低尿酸血症</v>
+        <v>副甲状腺機能低下症、ビタミンD欠乏、腎不全、低アルブミン血症（見かけ上の低下）</v>
       </c>
       <c r="J11" t="str">
-        <v/>
+        <v>手足のしびれやこむら返りなど低カルシウム血症の症状がないか確認する。乳製品・小魚・大豆製品などカルシウムを多く含む食品と、吸収を助ける適度な日光浴を意識するよう伝える</v>
       </c>
       <c r="K11" t="str">
-        <v>尿酸降下薬(フェブキソスタット、アロプリノール等)の効きすぎ</v>
+        <v>ビスホスホネート製剤、デノスマブ、ループ利尿薬、抗てんかん薬の長期使用、シナカルセト</v>
       </c>
       <c r="L11" t="str">
-        <v>利尿薬（サイアザイド系など）は尿酸を上げやすい。急激に尿酸を下げる治療の開始直後は痛風発作が誘発されることがある</v>
+        <v>アルブミンが低いと見かけ上低く出るため、補正カルシウム値（Ca+(4-Alb)）で評価する。骨粗鬆症治療薬（活性型ビタミンD3製剤、デノスマブなど）使用中は高カルシウム血症の副作用に注意</v>
       </c>
       <c r="M11" t="str">
-        <v>高尿酸血症,糖尿病</v>
+        <v>電解質,骨粗鬆症</v>
       </c>
       <c r="N11" t="str">
-        <v>尿酸,UA,痛風,高尿酸血症</v>
+        <v>カルシウム,Ca,電解質</v>
       </c>
       <c r="O11" t="str">
-        <v>食事と栄養 p.180-189（第2部 痛風・高尿酸血症）</v>
+        <v>食事と栄養 p.75（カルシウム）／p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ナトリウム（Na）</v>
+        <v>補正カルシウム（参考値）</v>
       </c>
       <c r="B12" t="str">
-        <v>Na</v>
+        <v>Corrected Ca,補正Ca</v>
       </c>
       <c r="C12" t="str">
-        <v>135〜145 mEq/L</v>
+        <v>実測カルシウム値と同じ基準値を用いる（8.5〜10.0 mg/dL）</v>
       </c>
       <c r="D12" t="str">
-        <v>体内の水分バランスや神経・筋肉の働きに関わる、血液中に最も多い電解質</v>
+        <v>アルブミンが低い患者で、見かけ上のカルシウム値を実際の値に近づけるための補正値</v>
       </c>
       <c r="E12" t="str">
-        <v>ナトリウムは、体の中の水分バランスを保ったり、神経や筋肉が正しく働くために欠かせないミネラルです。多すぎても少なすぎても、意識障害やけいれんなど重い症状につながることがあります。</v>
+        <v>血液中のカルシウムの多くはアルブミンというたんぱく質にくっついて存在しています。アルブミンが少ないと、実際のカルシウムの量が変わらなくても検査値上は低く出てしまうことがあるため、その影響を補正した数値がこの「補正カルシウム」です。</v>
       </c>
       <c r="F12" t="str">
-        <v>脱水、アルドステロン症、水分摂取不足、下痢・嘔吐による水分喪失</v>
+        <v>（実測カルシウムの高値と同様）副甲状腺機能亢進症、悪性腫瘍（骨転移など）、ビタミンD過剰</v>
       </c>
       <c r="G12" t="str">
-        <v>水分摂取状況を確認する(脱水が疑われる場合)。高齢者は口渇を感じにくいため、喉が渇く前にこまめな水分摂取を意識するよう伝える</v>
+        <v/>
       </c>
       <c r="H12" t="str">
-        <v>高張輸液、浸透圧利尿薬(グリセオール等)、抗利尿ホルモン分泌を低下させる薬(炭酸リチウム等)</v>
+        <v>(実測カルシウムに準ずる)活性型ビタミンD製剤、サイアザイド系利尿薬、炭酸リチウム</v>
       </c>
       <c r="I12" t="str">
-        <v>利尿薬（特にサイアザイド系）、SIADH（抗利尿ホルモン不適合分泌症候群）、嘔吐・下痢、心不全・肝硬変によるむくみ</v>
+        <v>（実測カルシウムの低値と同様）副甲状腺機能低下症、ビタミンD欠乏、腎不全</v>
       </c>
       <c r="J12" t="str">
-        <v>利尿薬使用中は嘔吐・下痢が続いていないか確認する。意識がぼんやりする、頭痛、脱力感などの症状の有無を確認し、水のみを大量に摂りすぎていないかも確認する</v>
+        <v/>
       </c>
       <c r="K12" t="str">
-        <v>サイアザイド系利尿薬、SSRI、カルバマゼピン、デスモプレシン、シクロホスファミド</v>
+        <v>(実測カルシウムに準ずる)ビスホスホネート製剤、デノスマブ、ループ利尿薬</v>
       </c>
       <c r="L12" t="str">
-        <v>低ナトリウム血症は高齢者に多く、意識障害や転倒の原因になりうる。利尿薬（特にサイアザイド系）、SSRI、カルバマゼピンなどSIADHを起こしうる薬剤の使用歴を確認する</v>
+        <v>補正カルシウム(mg/dL) = 実測カルシウム + (4 − アルブミン値)の式で計算する。アルブミンが4.0 g/dL未満の低栄養患者やネフローゼ症候群の患者では、実測カルシウムだけで判断すると誤りやすいため、この補正値で評価する</v>
       </c>
       <c r="M12" t="str">
-        <v>電解質</v>
+        <v>電解質,骨粗鬆症</v>
       </c>
       <c r="N12" t="str">
-        <v>ナトリウム,Na,電解質,脱水,SIADH,低ナトリウム血症</v>
+        <v>補正カルシウム,Corrected Calcium,アルブミン補正,低アルブミン血症</v>
       </c>
       <c r="O12" t="str">
-        <v>食事と栄養 p.81（ナトリウム）</v>
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>クロール</v>
+        <v>リン（P）</v>
       </c>
       <c r="B13" t="str">
-        <v>Cl</v>
+        <v>P,IP</v>
       </c>
       <c r="C13" t="str">
-        <v>98〜108 mEq/L</v>
+        <v>2.5〜4.5 mg/dL</v>
       </c>
       <c r="D13" t="str">
-        <v>ナトリウムと共に体の水分・酸塩基バランスに関わる電解質</v>
+        <v>カルシウムとともに骨を作る主要なミネラル</v>
       </c>
       <c r="E13" t="str">
-        <v>クロールは、ナトリウムと一緒に体の水分バランスや、体液の性質（酸性・アルカリ性）を保つ働きをしているミネラルです。多くの場合、ナトリウムと同じように変動します。</v>
+        <v>リンはカルシウムと一緒に骨や歯を作る材料になるミネラルです。カルシウムと逆方向に動くことが多く、腎臓の働きやホルモンのバランスによっても変動します。</v>
       </c>
       <c r="F13" t="str">
-        <v>脱水、腎不全、代謝性アシドーシス、高ナトリウム血症に伴うもの</v>
+        <v>腎不全、副甲状腺機能低下症</v>
       </c>
       <c r="G13" t="str">
-        <v>脱水が疑われる場合はこまめな水分摂取を勧める（水分制限がある場合を除く）</v>
+        <v>腎機能低下がある場合は乳製品・加工食品(リン酸塩添加物)の摂りすぎに注意する。リン吸着薬を服用中の場合は食直前・食直後など服用タイミングが守られているか確認する</v>
       </c>
       <c r="H13" t="str">
-        <v/>
+        <v>活性型ビタミンD製剤、リン含有製剤。腎機能低下患者では特に注意</v>
       </c>
       <c r="I13" t="str">
-        <v>嘔吐・下痢、利尿薬使用、代謝性アルカローシス</v>
+        <v>副甲状腺機能亢進症、骨軟化症、ビタミンD欠乏</v>
       </c>
       <c r="J13" t="str">
-        <v>利尿薬使用中は嘔吐・下痢が続いていないか確認する</v>
+        <v>骨の痛みや筋力低下などの症状がないか確認する。極端な食事制限や食欲低下がないか、栄養状態もあわせて確認する</v>
       </c>
       <c r="K13" t="str">
-        <v/>
+        <v>リン吸着薬(セベラマー等)、アルミニウム含有制酸薬、利尿薬</v>
       </c>
       <c r="L13" t="str">
-        <v>ナトリウムと同じ方向に動くことが多いが、酸塩基平衡の異常（アシドーシス・アルカローシス）を反映して単独で動くこともある。利尿薬（特にループ利尿薬）使用中は低クロール性アルカローシスに注意</v>
+        <v>カルシウムと逆方向に動くことが多い（副甲状腺機能亢進症ではCa上昇・P低下）。骨粗鬆症の二次性原因の除外に用いられる</v>
       </c>
       <c r="M13" t="str">
-        <v>電解質,腎機能</v>
+        <v>骨粗鬆症,電解質</v>
       </c>
       <c r="N13" t="str">
-        <v>クロール,Cl,塩素,電解質,アシドーシス,アルカローシス</v>
+        <v>リン,P,IP,無機リン</v>
       </c>
       <c r="O13" t="str">
-        <v/>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）／p.199-215（第2部 腎機能低下 Q83 リン制限）</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>カリウム（K）</v>
+        <v>AST（GOT）</v>
       </c>
       <c r="B14" t="str">
-        <v>K</v>
+        <v>AST,GOT</v>
       </c>
       <c r="C14" t="str">
-        <v>3.5〜5.0 mEq/L（5.5 mEq/L以上で高カリウム血症と診断）</v>
+        <v>10〜40 U/L</v>
       </c>
       <c r="D14" t="str">
-        <v>心臓や筋肉の働きに関わる電解質で、高すぎても低すぎても不整脈につながる</v>
+        <v>肝臓や心臓・筋肉の細胞が壊れると血液中に漏れ出す酵素</v>
       </c>
       <c r="E14" t="str">
-        <v>カリウムは心臓や筋肉が正しく動くために必要なミネラルです。多すぎても少なすぎても脈の乱れにつながることがあるため、腎臓のお薬やお通じのお薬を使っている方は定期的にチェックすることが大切です。</v>
+        <v>ASTは肝臓や心臓、筋肉の細胞の中にある酵素です。これらの細胞がダメージを受けたり壊れたりすると血液中に漏れ出して数値が上がります。肝臓の状態を見るときはALTと一緒に確認します。</v>
       </c>
       <c r="F14" t="str">
-        <v>腎不全、アジソン病、ACE阻害薬・ARB・カリウム保持性利尿薬などの薬剤性、溶血による偽高値</v>
+        <v>肝炎・肝硬変などの肝疾患、心筋梗塞、筋肉の障害（激しい運動・横紋筋融解症）、薬剤性肝障害</v>
       </c>
       <c r="G14" t="str">
-        <v>生野菜・果物・芋類などカリウムの多い食品の摂りすぎに注意する(腎機能低下がある場合)。茹でこぼす・水にさらすことでカリウムを減らせることもあわせて伝える</v>
+        <v>飲酒量を控える。激しい運動の直後の採血でないかを確認し、新規薬剤の開始時期と重なっていないかもあわせて確認する</v>
       </c>
       <c r="H14" t="str">
-        <v>ACE阻害薬、ARB、カリウム保持性利尿薬(スピロノラクトン等)、NSAIDs、ST合剤、ヘパリン。β遮断薬は細胞内への取り込みを阻害し上昇させうる</v>
+        <v>アセトアミノフェン(過量)、スタチン系、抗結核薬(イソニアジド・リファンピシン)、バルプロ酸、NSAIDs、メトトレキサート</v>
       </c>
       <c r="I14" t="str">
-        <v>利尿薬（特にループ・サイアザイド系）、下痢・嘔吐、インスリン投与、甘草含有製剤</v>
+        <v>臨床的に問題になることは少ない</v>
       </c>
       <c r="J14" t="str">
-        <v>利尿薬使用中は下痢・嘔吐が続いていないか確認し、必要に応じてバナナ・芋類などカリウムを含む食品を意識する。脱力感・こむら返り・動悸などの症状の有無もあわせて確認する</v>
+        <v/>
       </c>
       <c r="K14" t="str">
-        <v>ループ利尿薬、サイアザイド系利尿薬、グリチルリチン製剤(甘草含有製剤)、ステロイド、インスリン、β2刺激薬</v>
+        <v/>
       </c>
       <c r="L14" t="str">
-        <v>高カリウム血症は不整脈・心停止のリスクがあるため脱力感・動悸の有無を確認。RAS阻害薬とカリウム保持性利尿薬の併用時は特に注意</v>
+        <v>ALTとの比率（AST/ALT比）で肝細胞障害か他臓器由来かを推測できる。AST優位はアルコール性・心筋・筋由来を疑う材料になる</v>
       </c>
       <c r="M14" t="str">
-        <v>腎機能,電解質</v>
+        <v>肝機能,糖尿病,てんかん,精神疾患（非定型抗精神病薬）</v>
       </c>
       <c r="N14" t="str">
-        <v>カリウム,K,高カリウム血症,低カリウム血症</v>
+        <v>AST,GOT,肝機能,肝障害</v>
       </c>
       <c r="O14" t="str">
-        <v>食事と栄養 p.72（カリウム）／p.199-215（第2部 腎機能低下 Q80-82 カリウム制限）</v>
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>カルシウム（Ca）</v>
+        <v>ALT（GPT）</v>
       </c>
       <c r="B15" t="str">
-        <v>Ca</v>
+        <v>ALT,GPT</v>
       </c>
       <c r="C15" t="str">
-        <v>8.5〜10.0 mg/dL</v>
+        <v>5〜40 U/L</v>
       </c>
       <c r="D15" t="str">
-        <v>骨や歯の材料であると同時に、神経・筋肉・血液凝固にも関わるミネラル</v>
+        <v>主に肝臓の細胞に含まれる酵素で、肝障害の指標として最もよく使われる</v>
       </c>
       <c r="E15" t="str">
-        <v>カルシウムは骨や歯の材料になるだけでなく、神経の伝達や筋肉の収縮、血液を固める働きにも関わっている重要なミネラルです。副甲状腺ホルモンやビタミンDによって血液中の濃度が細かく調整されています。</v>
+        <v>ALTは主に肝臓の細胞の中にある酵素です。肝臓の細胞がダメージを受けると血液中に漏れ出して数値が上がります。ASTよりも肝臓に特異的な数値なので、肝臓の状態を見るときによく使われます。</v>
       </c>
       <c r="F15" t="str">
-        <v>副甲状腺機能亢進症、悪性腫瘍（骨転移など）、ビタミンD過剰、活性型ビタミンD3製剤の過量</v>
+        <v>脂肪肝、肝炎（ウイルス性・アルコール性・薬剤性）、肝硬変、薬の副作用による肝機能障害</v>
       </c>
       <c r="G15" t="str">
-        <v>吐き気、便秘、多尿、意識がぼんやりするなどの高カルシウム血症の症状がないか確認する。活性型ビタミンD3製剤使用中は過量になっていないか、水分摂取が十分かも確認する</v>
+        <v>体重管理と脂質の摂りすぎに注意する(脂肪肝が疑われる場合)。新規薬剤の開始時期と重なっていないか確認し、市販薬・サプリメントの使用歴も聞く</v>
       </c>
       <c r="H15" t="str">
-        <v>活性型ビタミンD製剤、サイアザイド系利尿薬、炭酸リチウム、カルシウム含有薬(炭酸カルシウム等)</v>
+        <v>アセトアミノフェン(過量)、スタチン系、抗結核薬(イソニアジド・リファンピシン)、バルプロ酸、NSAIDs、メトトレキサート</v>
       </c>
       <c r="I15" t="str">
-        <v>副甲状腺機能低下症、ビタミンD欠乏、腎不全、低アルブミン血症（見かけ上の低下）</v>
+        <v>臨床的に問題になることは少ない</v>
       </c>
       <c r="J15" t="str">
-        <v>手足のしびれやこむら返りなど低カルシウム血症の症状がないか確認する。乳製品・小魚・大豆製品などカルシウムを多く含む食品と、吸収を助ける適度な日光浴を意識するよう伝える</v>
+        <v/>
       </c>
       <c r="K15" t="str">
-        <v>ビスホスホネート製剤、デノスマブ、ループ利尿薬、抗てんかん薬の長期使用、シナカルセト</v>
+        <v/>
       </c>
       <c r="L15" t="str">
-        <v>アルブミンが低いと見かけ上低く出るため、補正カルシウム値（Ca+(4-Alb)）で評価する。骨粗鬆症治療薬（活性型ビタミンD3製剤、デノスマブなど）使用中は高カルシウム血症の副作用に注意</v>
+        <v>新規薬剤開始後の肝障害の指標として重要。健診でALTのみ軽度上昇していることが多く、その場合は脂肪肝（NAFLD）の頻度が高い</v>
       </c>
       <c r="M15" t="str">
-        <v>電解質,骨粗鬆症</v>
+        <v>肝機能,糖尿病,てんかん,精神疾患（非定型抗精神病薬）</v>
       </c>
       <c r="N15" t="str">
-        <v>カルシウム,Ca,電解質</v>
+        <v>ALT,GPT,肝機能,肝障害,脂肪肝</v>
       </c>
       <c r="O15" t="str">
-        <v>食事と栄養 p.75（カルシウム）／p.165-178（第2部 骨粗鬆症）</v>
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>補正カルシウム（参考値）</v>
+        <v>乳酸脱水素酵素（LDH）</v>
       </c>
       <c r="B16" t="str">
-        <v>Corrected Ca,補正Ca</v>
+        <v>LDH</v>
       </c>
       <c r="C16" t="str">
-        <v>実測カルシウム値と同じ基準値を用いる（8.5〜10.0 mg/dL）</v>
+        <v>120〜245 U/L程度（施設差あり）</v>
       </c>
       <c r="D16" t="str">
-        <v>アルブミンが低い患者で、見かけ上のカルシウム値を実際の値に近づけるための補正値</v>
+        <v>全身のさまざまな組織に含まれる酵素で、細胞が壊れると幅広く上昇する</v>
       </c>
       <c r="E16" t="str">
-        <v>血液中のカルシウムの多くはアルブミンというたんぱく質にくっついて存在しています。アルブミンが少ないと、実際のカルシウムの量が変わらなくても検査値上は低く出てしまうことがあるため、その影響を補正した数値がこの「補正カルシウム」です。</v>
+        <v>LDHは全身の細胞の中にある酵素で、肝臓、心臓、筋肉、血液など、いろいろな組織の細胞がダメージを受けると血液中に漏れ出します。どの臓器が原因かを絞り込むには、他の検査値と組み合わせて評価します。</v>
       </c>
       <c r="F16" t="str">
-        <v>（実測カルシウムの高値と同様）副甲状腺機能亢進症、悪性腫瘍（骨転移など）、ビタミンD過剰</v>
+        <v>肝疾患、心筋梗塞、溶血性疾患、悪性腫瘍、筋肉の障害（横紋筋融解症など）、肺疾患</v>
       </c>
       <c r="G16" t="str">
-        <v/>
+        <v>息切れ、黄疸、筋肉痛など随伴症状の有無を確認し、原因臓器を絞り込む手がかりにする</v>
       </c>
       <c r="H16" t="str">
-        <v>(実測カルシウムに準ずる)活性型ビタミンD製剤、サイアザイド系利尿薬、炭酸リチウム</v>
+        <v/>
       </c>
       <c r="I16" t="str">
-        <v>（実測カルシウムの低値と同様）副甲状腺機能低下症、ビタミンD欠乏、腎不全</v>
+        <v/>
       </c>
       <c r="J16" t="str">
         <v/>
       </c>
       <c r="K16" t="str">
-        <v>(実測カルシウムに準ずる)ビスホスホネート製剤、デノスマブ、ループ利尿薬</v>
+        <v/>
       </c>
       <c r="L16" t="str">
-        <v>補正カルシウム(mg/dL) = 実測カルシウム + (4 − アルブミン値)の式で計算する。アルブミンが4.0 g/dL未満の低栄養患者やネフローゼ症候群の患者では、実測カルシウムだけで判断すると誤りやすいため、この補正値で評価する</v>
+        <v>臓器特異性が低いため単独では原因を特定しにくい。AST/ALT(肝)、CK(筋)、ビリルビン・ハプトグロビン(溶血)など他の検査値と組み合わせて原因臓器を推定する</v>
       </c>
       <c r="M16" t="str">
-        <v>電解質,骨粗鬆症</v>
+        <v/>
       </c>
       <c r="N16" t="str">
-        <v>補正カルシウム,Corrected Calcium,アルブミン補正,低アルブミン血症</v>
+        <v>LDH,乳酸脱水素酵素,溶血,心筋梗塞,悪性腫瘍</v>
       </c>
       <c r="O16" t="str">
         <v/>
@@ -1176,78 +1176,78 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>リン（P）</v>
+        <v>コリンエステラーゼ</v>
       </c>
       <c r="B17" t="str">
-        <v>P,IP</v>
+        <v>ChE</v>
       </c>
       <c r="C17" t="str">
-        <v>2.5〜4.5 mg/dL</v>
+        <v>男性 240〜486 U/L、女性 201〜421 U/L（施設差あり）</v>
       </c>
       <c r="D17" t="str">
-        <v>カルシウムとともに骨を作る主要なミネラル</v>
+        <v>主に肝臓で作られる酵素。肝臓のたんぱく質を作る力（合成能）を反映する</v>
       </c>
       <c r="E17" t="str">
-        <v>リンはカルシウムと一緒に骨や歯を作る材料になるミネラルです。カルシウムと逆方向に動くことが多く、腎臓の働きやホルモンのバランスによっても変動します。</v>
+        <v>コリンエステラーゼは肝臓で作られる酵素です。肝臓がたんぱく質を作る力が落ちると数値が下がり、逆に脂肪肝や栄養状態が良すぎる場合は上がることがあります。</v>
       </c>
       <c r="F17" t="str">
-        <v>腎不全、副甲状腺機能低下症</v>
+        <v>脂肪肝、ネフローゼ症候群、肥満、甲状腺機能亢進症</v>
       </c>
       <c r="G17" t="str">
-        <v>腎機能低下がある場合は乳製品・加工食品(リン酸塩添加物)の摂りすぎに注意する。リン吸着薬を服用中の場合は食直前・食直後など服用タイミングが守られているか確認する</v>
+        <v>脂肪肝が疑われる場合は食事・運動習慣の見直しを勧める。急激な体重増加がないかもあわせて確認する</v>
       </c>
       <c r="H17" t="str">
-        <v>活性型ビタミンD製剤、リン含有製剤。腎機能低下患者では特に注意</v>
+        <v/>
       </c>
       <c r="I17" t="str">
-        <v>副甲状腺機能亢進症、骨軟化症、ビタミンD欠乏</v>
+        <v>肝硬変など肝臓の合成能低下、低栄養、有機リン中毒（農薬など）</v>
       </c>
       <c r="J17" t="str">
-        <v>骨の痛みや筋力低下などの症状がないか確認する。極端な食事制限や食欲低下がないか、栄養状態もあわせて確認する</v>
+        <v>低栄養が疑われる場合は食事摂取状況を確認する。肝硬変など背景疾患がある場合は出血傾向(あざ・歯ぐきの出血)の有無もあわせて確認する</v>
       </c>
       <c r="K17" t="str">
-        <v>リン吸着薬(セベラマー等)、アルミニウム含有制酸薬、利尿薬</v>
+        <v/>
       </c>
       <c r="L17" t="str">
-        <v>カルシウムと逆方向に動くことが多い（副甲状腺機能亢進症ではCa上昇・P低下）。骨粗鬆症の二次性原因の除外に用いられる</v>
+        <v>アルブミンと同様に肝臓の「合成能」を見る指標。低栄養か肝硬変かは、アルブミンや血小板数（肝硬変で低下しやすい）と合わせて判断する</v>
       </c>
       <c r="M17" t="str">
-        <v>骨粗鬆症,電解質</v>
+        <v>肝機能</v>
       </c>
       <c r="N17" t="str">
-        <v>リン,P,IP,無機リン</v>
+        <v>コリンエステラーゼ,ChE,肝合成能,脂肪肝,肝硬変</v>
       </c>
       <c r="O17" t="str">
-        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）／p.199-215（第2部 腎機能低下 Q83 リン制限）</v>
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>AST（GOT）</v>
+        <v>アルカリフォスファターゼ（ALP）</v>
       </c>
       <c r="B18" t="str">
-        <v>AST,GOT</v>
+        <v>ALP</v>
       </c>
       <c r="C18" t="str">
-        <v>10〜40 U/L</v>
+        <v>38〜113 U/L（施設・測定法により大きく異なる）</v>
       </c>
       <c r="D18" t="str">
-        <v>肝臓や心臓・筋肉の細胞が壊れると血液中に漏れ出す酵素</v>
+        <v>骨や肝臓・胆道に多く含まれる酵素で、骨を作る働きの指標にもなる</v>
       </c>
       <c r="E18" t="str">
-        <v>ASTは肝臓や心臓、筋肉の細胞の中にある酵素です。これらの細胞がダメージを受けたり壊れたりすると血液中に漏れ出して数値が上がります。肝臓の状態を見るときはALTと一緒に確認します。</v>
+        <v>ALPは骨や肝臓、胆道に多く含まれる酵素です。骨を作る働きが活発なとき（骨の成長期や骨折の治癒過程など）や、肝臓・胆道にトラブルがあるときに数値が上がります。</v>
       </c>
       <c r="F18" t="str">
-        <v>肝炎・肝硬変などの肝疾患、心筋梗塞、筋肉の障害（激しい運動・横紋筋融解症）、薬剤性肝障害</v>
+        <v>骨代謝の亢進（骨折治癒過程、骨粗鬆症、骨転移、Paget病）、肝・胆道疾患、成長期の生理的高値</v>
       </c>
       <c r="G18" t="str">
-        <v>飲酒量を控える。激しい運動の直後の採血でないかを確認し、新規薬剤の開始時期と重なっていないかもあわせて確認する</v>
+        <v>骨折治癒過程や成長期など生理的な上昇もあるため、経過や年齢背景を確認する。肝・胆道由来が疑われる場合は黄疸や皮膚のかゆみの有無も確認する</v>
       </c>
       <c r="H18" t="str">
-        <v>アセトアミノフェン(過量)、スタチン系、抗結核薬(イソニアジド・リファンピシン)、バルプロ酸、NSAIDs、メトトレキサート</v>
+        <v>抗てんかん薬(フェニトイン等)、胆汁うっ滞型の薬剤性肝障害を起こしうる抗菌薬・NSAIDs</v>
       </c>
       <c r="I18" t="str">
-        <v>臨床的に問題になることは少ない</v>
+        <v/>
       </c>
       <c r="J18" t="str">
         <v/>
@@ -1256,42 +1256,43 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>ALTとの比率（AST/ALT比）で肝細胞障害か他臓器由来かを推測できる。AST優位はアルコール性・心筋・筋由来を疑う材料になる</v>
+        <v>骨由来か肝由来かの区別には骨型ALPアイソザイムやγ-GTPとの組み合わせで判断する</v>
       </c>
       <c r="M18" t="str">
-        <v>肝機能,糖尿病,てんかん,精神疾患（非定型抗精神病薬）</v>
+        <v>骨粗鬆症,肝機能</v>
       </c>
       <c r="N18" t="str">
-        <v>AST,GOT,肝機能,肝障害</v>
+        <v>ALP,アルカリフォスファターゼ,骨代謝,肝機能</v>
       </c>
       <c r="O18" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="19">
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
+      </c>
+    </row>
+    <row r="19" xml:space="preserve">
       <c r="A19" t="str">
-        <v>ALT（GPT）</v>
+        <v>γ-GTP</v>
       </c>
       <c r="B19" t="str">
-        <v>ALT,GPT</v>
-      </c>
-      <c r="C19" t="str">
-        <v>5〜40 U/L</v>
+        <v>γ-GTP,GGT</v>
+      </c>
+      <c r="C19" t="str" xml:space="preserve">
+        <v xml:space="preserve">男性 〜50 U/L、女性 〜30 U/L
+（施設差が大きい）</v>
       </c>
       <c r="D19" t="str">
-        <v>主に肝臓の細胞に含まれる酵素で、肝障害の指標として最もよく使われる</v>
+        <v>アルコールや胆道のトラブルに反応しやすい肝臓の酵素</v>
       </c>
       <c r="E19" t="str">
-        <v>ALTは主に肝臓の細胞の中にある酵素です。肝臓の細胞がダメージを受けると血液中に漏れ出して数値が上がります。ASTよりも肝臓に特異的な数値なので、肝臓の状態を見るときによく使われます。</v>
+        <v>γ-GTPは肝臓や胆道の細胞にある酵素で、特にお酒の影響を受けやすいことが知られています。数値が高いときは、アルコールの摂取量や胆道（胆汁の通り道）の状態を確認する目安になります。</v>
       </c>
       <c r="F19" t="str">
-        <v>脂肪肝、肝炎（ウイルス性・アルコール性・薬剤性）、肝硬変、薬の副作用による肝機能障害</v>
+        <v>アルコール性肝障害、脂肪肝、胆道系疾患（胆石・胆管閉塞）、薬剤性（酵素誘導）</v>
       </c>
       <c r="G19" t="str">
-        <v>体重管理と脂質の摂りすぎに注意する(脂肪肝が疑われる場合)。新規薬剤の開始時期と重なっていないか確認し、市販薬・サプリメントの使用歴も聞く</v>
+        <v>飲酒量を控える、休肝日をつくるよう伝える。断酒・節酒を続けると数値が比較的早く改善しやすいことを励みとして伝えるとよい</v>
       </c>
       <c r="H19" t="str">
-        <v>アセトアミノフェン(過量)、スタチン系、抗結核薬(イソニアジド・リファンピシン)、バルプロ酸、NSAIDs、メトトレキサート</v>
+        <v>アルコール、フェニトイン、バルビツール酸系など肝薬物代謝酵素誘導作用のある薬剤</v>
       </c>
       <c r="I19" t="str">
         <v>臨床的に問題になることは少ない</v>
@@ -1303,13 +1304,13 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>新規薬剤開始後の肝障害の指標として重要。健診でALTのみ軽度上昇していることが多く、その場合は脂肪肝（NAFLD）の頻度が高い</v>
+        <v>飲酒歴の確認に使いやすい数値。断酒・節酒で比較的早く改善するため、生活指導の効果を示す指標としても使える</v>
       </c>
       <c r="M19" t="str">
-        <v>肝機能,糖尿病,てんかん,精神疾患（非定型抗精神病薬）</v>
+        <v>肝機能</v>
       </c>
       <c r="N19" t="str">
-        <v>ALT,GPT,肝機能,肝障害,脂肪肝</v>
+        <v>ガンマGTP,γ-GTP,GGT,肝機能,飲酒,アルコール</v>
       </c>
       <c r="O19" t="str">
         <v/>
@@ -1317,28 +1318,28 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>乳酸脱水素酵素（LDH）</v>
+        <v>総ビリルビン</v>
       </c>
       <c r="B20" t="str">
-        <v>LDH</v>
+        <v>T-Bil</v>
       </c>
       <c r="C20" t="str">
-        <v>120〜245 U/L程度（施設差あり）</v>
+        <v>0.2〜1.2 mg/dL</v>
       </c>
       <c r="D20" t="str">
-        <v>全身のさまざまな組織に含まれる酵素で、細胞が壊れると幅広く上昇する</v>
+        <v>赤血球が壊れてできる黄色い色素の総量。肝臓・胆道の状態や黄疸の指標</v>
       </c>
       <c r="E20" t="str">
-        <v>LDHは全身の細胞の中にある酵素で、肝臓、心臓、筋肉、血液など、いろいろな組織の細胞がダメージを受けると血液中に漏れ出します。どの臓器が原因かを絞り込むには、他の検査値と組み合わせて評価します。</v>
+        <v>ビリルビンは赤血球が寿命を迎えて壊れるときにできる黄色い色素です。肝臓で処理されて排泄されますが、肝臓や胆道にトラブルがあると血液中に増え、皮膚や白目が黄色くなる黄疸として現れます。</v>
       </c>
       <c r="F20" t="str">
-        <v>肝疾患、心筋梗塞、溶血性疾患、悪性腫瘍、筋肉の障害（横紋筋融解症など）、肺疾患</v>
+        <v>肝炎・肝硬変などの肝疾患、胆道閉塞（胆石・腫瘍など）、溶血性疾患（赤血球の破壊亢進）、体質性黄疸（ジルベール症候群など）</v>
       </c>
       <c r="G20" t="str">
-        <v>息切れ、黄疸、筋肉痛など随伴症状の有無を確認し、原因臓器を絞り込む手がかりにする</v>
+        <v>皮膚や白目の黄染、尿の色が濃くなっていないか確認する。かゆみを伴う場合は胆汁うっ滞の可能性もあるため皮膚症状もあわせて聞く</v>
       </c>
       <c r="H20" t="str">
-        <v/>
+        <v>肝毒性のある薬剤全般に加え、シクロスポリン・リファンピシン(トランスポーター阻害による上昇)</v>
       </c>
       <c r="I20" t="str">
         <v/>
@@ -1350,13 +1351,13 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>臓器特異性が低いため単独では原因を特定しにくい。AST/ALT(肝)、CK(筋)、ビリルビン・ハプトグロビン(溶血)など他の検査値と組み合わせて原因臓器を推定する</v>
+        <v>直接ビリルビン・間接ビリルビンの内訳で原因を推測できる（直接優位は胆道系、間接優位は溶血・体質性）。AST/ALT/γ-GTPと合わせて評価する</v>
       </c>
       <c r="M20" t="str">
-        <v/>
+        <v>肝機能</v>
       </c>
       <c r="N20" t="str">
-        <v>LDH,乳酸脱水素酵素,溶血,心筋梗塞,悪性腫瘍</v>
+        <v>総ビリルビン,T-Bil,黄疸,ビリルビン,ジルベール症候群</v>
       </c>
       <c r="O20" t="str">
         <v/>
@@ -1364,141 +1365,140 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>コリンエステラーゼ</v>
+        <v>総タンパク</v>
       </c>
       <c r="B21" t="str">
-        <v>ChE</v>
+        <v>TP</v>
       </c>
       <c r="C21" t="str">
-        <v>男性 240〜486 U/L、女性 201〜421 U/L（施設差あり）</v>
+        <v>6.6〜8.1 g/dL</v>
       </c>
       <c r="D21" t="str">
-        <v>主に肝臓で作られる酵素。肝臓のたんぱく質を作る力（合成能）を反映する</v>
+        <v>血液中のたんぱく質（アルブミン＋グロブリン）の総量。栄養状態や肝機能、炎症の目安</v>
       </c>
       <c r="E21" t="str">
-        <v>コリンエステラーゼは肝臓で作られる酵素です。肝臓がたんぱく質を作る力が落ちると数値が下がり、逆に脂肪肝や栄養状態が良すぎる場合は上がることがあります。</v>
+        <v>総タンパクは、血液中のたんぱく質の合計量です。栄養状態や肝臓の働き、体の炎症の有無などを反映します。</v>
       </c>
       <c r="F21" t="str">
-        <v>脂肪肝、ネフローゼ症候群、肥満、甲状腺機能亢進症</v>
+        <v>脱水、多発性骨髄腫など（グロブリン増加）、慢性炎症</v>
       </c>
       <c r="G21" t="str">
-        <v>脂肪肝が疑われる場合は食事・運動習慣の見直しを勧める。急激な体重増加がないかもあわせて確認する</v>
+        <v/>
       </c>
       <c r="H21" t="str">
         <v/>
       </c>
       <c r="I21" t="str">
-        <v>肝硬変など肝臓の合成能低下、低栄養、有機リン中毒（農薬など）</v>
+        <v>低栄養、肝機能低下（アルブミン産生低下）、ネフローゼ症候群、消化管からのたんぱく漏出</v>
       </c>
       <c r="J21" t="str">
-        <v>低栄養が疑われる場合は食事摂取状況を確認する。肝硬変など背景疾患がある場合は出血傾向(あざ・歯ぐきの出血)の有無もあわせて確認する</v>
+        <v>食事摂取量、特にたんぱく質(肉・魚・卵・大豆製品)を確認する。むくみが出ていないかもあわせて確認する</v>
       </c>
       <c r="K21" t="str">
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>アルブミンと同様に肝臓の「合成能」を見る指標。低栄養か肝硬変かは、アルブミンや血小板数（肝硬変で低下しやすい）と合わせて判断する</v>
+        <v>アルブミンとグロブリンの内訳（A/G比）も合わせて確認すると原因の絞り込みに役立つ。低栄養か肝機能低下かはアルブミンの値と合わせて判断する</v>
       </c>
       <c r="M21" t="str">
         <v>肝機能</v>
       </c>
       <c r="N21" t="str">
-        <v>コリンエステラーゼ,ChE,肝合成能,脂肪肝,肝硬変</v>
+        <v>総タンパク,TP,総蛋白,栄養状態,A/G比</v>
       </c>
       <c r="O21" t="str">
-        <v/>
+        <v>食事と栄養 p.23（たんぱく質）</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>アルカリフォスファターゼ（ALP）</v>
+        <v>アルブミン</v>
       </c>
       <c r="B22" t="str">
-        <v>ALP</v>
+        <v>Alb</v>
       </c>
       <c r="C22" t="str">
-        <v>38〜113 U/L（施設・測定法により大きく異なる）</v>
+        <v>3.8〜5.2 g/dL</v>
       </c>
       <c r="D22" t="str">
-        <v>骨や肝臓・胆道に多く含まれる酵素で、骨を作る働きの指標にもなる</v>
+        <v>体の栄養状態を見る目安になるたんぱく質。血液の中で栄養を運ぶ、水分を血管の中に保つという働きをしている。</v>
       </c>
       <c r="E22" t="str">
-        <v>ALPは骨や肝臓、胆道に多く含まれる酵素です。骨を作る働きが活発なとき（骨の成長期や骨折の治癒過程など）や、肝臓・胆道にトラブルがあるときに数値が上がります。</v>
+        <v>アルブミンは栄養の状態を見る数値です。食事量が少なかったり、肝臓や腎臓、腸の働きが弱ると下がることがあります。数値が低いと、むくみが出やすくなります。</v>
       </c>
       <c r="F22" t="str">
-        <v>骨代謝の亢進（骨折治癒過程、骨粗鬆症、骨転移、Paget病）、肝・胆道疾患、成長期の生理的高値</v>
+        <v>脱水（見かけ上の上昇）</v>
       </c>
       <c r="G22" t="str">
-        <v>骨折治癒過程や成長期など生理的な上昇もあるため、経過や年齢背景を確認する。肝・胆道由来が疑われる場合は黄疸や皮膚のかゆみの有無も確認する</v>
+        <v/>
       </c>
       <c r="H22" t="str">
-        <v>抗てんかん薬(フェニトイン等)、胆汁うっ滞型の薬剤性肝障害を起こしうる抗菌薬・NSAIDs</v>
+        <v/>
       </c>
       <c r="I22" t="str">
-        <v/>
+        <v>低栄養／肝機能低下／ネフローゼ症候群／クローン病</v>
       </c>
       <c r="J22" t="str">
-        <v/>
+        <v>主食に偏らず、肉・魚・卵・大豆製品などたんぱく質をしっかり摂るよう伝える。食欲が落ちている場合は少量頻回の食事や、間食に乳製品・卵を取り入れるなど無理のない工夫を提案し、むくみの有無もあわせて確認する</v>
       </c>
       <c r="K22" t="str">
-        <v/>
+        <v>蛋白結合率の高い薬剤(ワルファリン、フェニトイン、NSAIDs等)は遊離型濃度が上昇し、効果や副作用が増強しやすいため用量に注意</v>
       </c>
       <c r="L22" t="str">
-        <v>骨由来か肝由来かの区別には骨型ALPアイソザイムやγ-GTPとの組み合わせで判断する</v>
+        <v>3前半は注意ライン。食事摂取量を必ず確認</v>
       </c>
       <c r="M22" t="str">
-        <v>骨粗鬆症,肝機能</v>
+        <v>肝機能,栄養,腎機能</v>
       </c>
       <c r="N22" t="str">
-        <v>ALP,アルカリフォスファターゼ,骨代謝,肝機能</v>
+        <v>アルブミン,Alb,むくみ,浮腫,栄養状態</v>
       </c>
       <c r="O22" t="str">
-        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
-      </c>
-    </row>
-    <row r="23" xml:space="preserve">
+        <v>食事と栄養 p.23（たんぱく質）／p.242（フレイルQ110 アルブミン値を上げる食事指導）</v>
+      </c>
+    </row>
+    <row r="23">
       <c r="A23" t="str">
-        <v>γ-GTP</v>
+        <v>A/G</v>
       </c>
       <c r="B23" t="str">
-        <v>γ-GTP,GGT</v>
-      </c>
-      <c r="C23" t="str" xml:space="preserve">
-        <v xml:space="preserve">男性 〜50 U/L、女性 〜30 U/L
-（施設差が大きい）</v>
+        <v>A/G比</v>
+      </c>
+      <c r="C23" t="str">
+        <v>1.1〜2.0程度(施設差あり)</v>
       </c>
       <c r="D23" t="str">
-        <v>アルコールや胆道のトラブルに反応しやすい肝臓の酵素</v>
+        <v>血液中のアルブミンとグロブリンの比率。肝機能や炎症、免疫の状態を反映する</v>
       </c>
       <c r="E23" t="str">
-        <v>γ-GTPは肝臓や胆道の細胞にある酵素で、特にお酒の影響を受けやすいことが知られています。数値が高いときは、アルコールの摂取量や胆道（胆汁の通り道）の状態を確認する目安になります。</v>
+        <v>A/G比は、血液中のたんぱく質のうちアルブミンとグロブリンという2種類の比率を見る数値です。肝臓の働きが落ちたり、体に炎症や免疫の異常があったりすると、このバランスが崩れることがあります。</v>
       </c>
       <c r="F23" t="str">
-        <v>アルコール性肝障害、脂肪肝、胆道系疾患（胆石・胆管閉塞）、薬剤性（酵素誘導）</v>
+        <v>通常、臨床的意義は乏しい(まれに無ガンマグロブリン血症など)</v>
       </c>
       <c r="G23" t="str">
-        <v>飲酒量を控える、休肝日をつくるよう伝える。断酒・節酒を続けると数値が比較的早く改善しやすいことを励みとして伝えるとよい</v>
+        <v/>
       </c>
       <c r="H23" t="str">
-        <v>アルコール、フェニトイン、バルビツール酸系など肝薬物代謝酵素誘導作用のある薬剤</v>
+        <v/>
       </c>
       <c r="I23" t="str">
-        <v>臨床的に問題になることは少ない</v>
+        <v>肝硬変などの肝機能低下(アルブミン産生低下)、慢性炎症・感染症、多発性骨髄腫などの血液疾患(グロブリン増加)、ネフローゼ症候群</v>
       </c>
       <c r="J23" t="str">
-        <v/>
+        <v>食事摂取量やむくみの有無を確認する。慢性炎症や感染の有無もあわせて確認する</v>
       </c>
       <c r="K23" t="str">
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>飲酒歴の確認に使いやすい数値。断酒・節酒で比較的早く改善するため、生活指導の効果を示す指標としても使える</v>
+        <v>A/G比＝アルブミン÷(総タンパク－アルブミン)で算出する。低下はアルブミンが減った場合とグロブリンが増えた場合の両方で起こるため、総タンパク・アルブミンの実測値とあわせて原因を判断する</v>
       </c>
       <c r="M23" t="str">
         <v>肝機能</v>
       </c>
       <c r="N23" t="str">
-        <v>ガンマGTP,γ-GTP,GGT,肝機能,飲酒,アルコール</v>
+        <v>A/G,A/G比,アルブミングロブリン比,肝機能,多発性骨髄腫</v>
       </c>
       <c r="O23" t="str">
         <v/>
@@ -1506,31 +1506,31 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>総ビリルビン</v>
+        <v>アンモニア</v>
       </c>
       <c r="B24" t="str">
-        <v>T-Bil</v>
+        <v>NH3</v>
       </c>
       <c r="C24" t="str">
-        <v>0.2〜1.2 mg/dL</v>
+        <v>12〜66 μg/dL（施設差あり／空腹時採血が望ましい）</v>
       </c>
       <c r="D24" t="str">
-        <v>赤血球が壊れてできる黄色い色素の総量。肝臓・胆道の状態や黄疸の指標</v>
+        <v>肝機能低下や門脈シャントなどで代謝・排泄が低下すると上昇し、意識障害（肝性脳症）の原因となる</v>
       </c>
       <c r="E24" t="str">
-        <v>ビリルビンは赤血球が寿命を迎えて壊れるときにできる黄色い色素です。肝臓で処理されて排泄されますが、肝臓や胆道にトラブルがあると血液中に増え、皮膚や白目が黄色くなる黄疸として現れます。</v>
+        <v>アンモニアは体の中でタンパク質が分解されるときにできる老廃物で、通常は肝臓で無害な尿素に変えられて尿として排泄されます。肝臓の働きが弱っていたり血液の流れ道に変化があると、アンモニアがうまく処理されず血液中にたまり、頭がぼんやりしたり意識がもうろうとする原因になることがあります。</v>
       </c>
       <c r="F24" t="str">
-        <v>肝炎・肝硬変などの肝疾患、胆道閉塞（胆石・腫瘍など）、溶血性疾患（赤血球の破壊亢進）、体質性黄疸（ジルベール症候群など）</v>
+        <v>肝硬変・肝不全（門脈-大循環シャント含む）、劇症肝炎、消化管出血、便秘、脱水、高たんぱく食、尿素サイクル異常症、一部薬剤（バルプロ酸など）</v>
       </c>
       <c r="G24" t="str">
-        <v>皮膚や白目の黄染、尿の色が濃くなっていないか確認する。かゆみを伴う場合は胆汁うっ滞の可能性もあるため皮膚症状もあわせて聞く</v>
+        <v>便秘の解消(排便コントロール)を心がける。ラクツロースやリファキシミンなど肝性脳症治療薬の服薬状況を確認し、意識のもうろう感や日中の眠気の変化にも注意する</v>
       </c>
       <c r="H24" t="str">
-        <v>肝毒性のある薬剤全般に加え、シクロスポリン・リファンピシン(トランスポーター阻害による上昇)</v>
+        <v>バルプロ酸(デパケン等)</v>
       </c>
       <c r="I24" t="str">
-        <v/>
+        <v>通常、臨床的意義は乏しい</v>
       </c>
       <c r="J24" t="str">
         <v/>
@@ -1539,13 +1539,13 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>直接ビリルビン・間接ビリルビンの内訳で原因を推測できる（直接優位は胆道系、間接優位は溶血・体質性）。AST/ALT/γ-GTPと合わせて評価する</v>
+        <v>バルプロ酸(デパケン等)は肝疾患の既往がなくても高アンモニア血症を起こすことがあり、意識障害・傾眠が出現した場合は薬剤性を疑ってアンモニア値を確認する。採血後は室温放置で見かけ上上昇するため測定条件にも注意。ラクツロース・リファキシミンは腸管内でのアンモニア産生・吸収を抑える目的で使用される</v>
       </c>
       <c r="M24" t="str">
         <v>肝機能</v>
       </c>
       <c r="N24" t="str">
-        <v>総ビリルビン,T-Bil,黄疸,ビリルビン,ジルベール症候群</v>
+        <v>アンモニア,NH3,肝性脳症,バルプロ酸,門脈シャント</v>
       </c>
       <c r="O24" t="str">
         <v/>
@@ -1553,172 +1553,173 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>総タンパク</v>
+        <v>中性脂肪（トリグリセリド）</v>
       </c>
       <c r="B25" t="str">
-        <v>TP</v>
+        <v>TG</v>
       </c>
       <c r="C25" t="str">
-        <v>6.6〜8.1 g/dL</v>
+        <v>150 mg/dL未満（空腹時）</v>
       </c>
       <c r="D25" t="str">
-        <v>血液中のたんぱく質（アルブミン＋グロブリン）の総量。栄養状態や肝機能、炎症の目安</v>
+        <v>脂質異常症で高値になりやすい脂質で、食事の影響を強く受ける</v>
       </c>
       <c r="E25" t="str">
-        <v>総タンパクは、血液中のたんぱく質の合計量です。栄養状態や肝臓の働き、体の炎症の有無などを反映します。</v>
+        <v>中性脂肪は、食事から摂った脂肪や糖質が体に蓄えられる形になったものです。食後は誰でも一時的に上がるため、正確に評価するには空腹時に採血することが大切です。高い状態が続くと動脈硬化や急性膵炎のリスクが高まります。</v>
       </c>
       <c r="F25" t="str">
-        <v>脱水、多発性骨髄腫など（グロブリン増加）、慢性炎症</v>
+        <v>脂質異常症、糖質・アルコールの摂りすぎ、肥満、糖尿病のコントロール不良</v>
       </c>
       <c r="G25" t="str">
-        <v/>
+        <v>糖質・アルコールの摂りすぎに注意し、ウォーキングなどの有酸素運動を週150分程度を目安に勧める。清涼飲料水や果物の摂りすぎにも注意する</v>
       </c>
       <c r="H25" t="str">
-        <v/>
+        <v>非定型抗精神病薬(オランザピン・クエチアピン)、ステロイド、エストロゲン製剤、非選択的β遮断薬、サイアザイド系利尿薬、タモキシフェン</v>
       </c>
       <c r="I25" t="str">
-        <v>低栄養、肝機能低下（アルブミン産生低下）、ネフローゼ症候群、消化管からのたんぱく漏出</v>
+        <v>低栄養、甲状腺機能亢進症</v>
       </c>
       <c r="J25" t="str">
-        <v>食事摂取量、特にたんぱく質(肉・魚・卵・大豆製品)を確認する。むくみが出ていないかもあわせて確認する</v>
+        <v/>
       </c>
       <c r="K25" t="str">
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>アルブミンとグロブリンの内訳（A/G比）も合わせて確認すると原因の絞り込みに役立つ。低栄養か肝機能低下かはアルブミンの値と合わせて判断する</v>
+        <v>採血が食後か空腹時かで数値が大きく変わるため必ず確認する。500 mg/dL以上では急性膵炎のリスクが高まるため注意。フィブラート系・EPA製剤などの効果判定に使う</v>
       </c>
       <c r="M25" t="str">
-        <v>肝機能</v>
+        <v>脂質異常症</v>
       </c>
       <c r="N25" t="str">
-        <v>総タンパク,TP,総蛋白,栄養状態,A/G比</v>
+        <v>中性脂肪,トリグリセリド,TG,脂質異常症</v>
       </c>
       <c r="O25" t="str">
-        <v>食事と栄養 p.23（たんぱく質）</v>
+        <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>アルブミン</v>
+        <v>総コレステロール</v>
       </c>
       <c r="B26" t="str">
-        <v>Alb</v>
+        <v>TC,T-cho</v>
       </c>
       <c r="C26" t="str">
-        <v>3.8〜5.2 g/dL</v>
+        <v>220 mg/dL未満</v>
       </c>
       <c r="D26" t="str">
-        <v>体の栄養状態を見る目安になるたんぱく質。血液の中で栄養を運ぶ、水分を血管の中に保つという働きをしている。</v>
+        <v>LDL・HDLなどすべてのコレステロールを合わせた総量</v>
       </c>
       <c r="E26" t="str">
-        <v>アルブミンは栄養の状態を見る数値です。食事量が少なかったり、肝臓や腎臓、腸の働きが弱ると下がることがあります。数値が低いと、むくみが出やすくなります。</v>
+        <v>総コレステロールは、体の中にあるコレステロールをすべて合わせた数値です。ただし、悪玉(LDL)が多いのか善玉(HDL)が多いのかまでは分からないため、実際の評価にはLDLコレステロールの値がより重視されます。</v>
       </c>
       <c r="F26" t="str">
-        <v>脱水（見かけ上の上昇）</v>
+        <v>脂質異常症、家族性高コレステロール血症、甲状腺機能低下症</v>
       </c>
       <c r="G26" t="str">
-        <v/>
+        <v>動物性脂肪を控え、食物繊維(野菜・海藻・きのこ)を増やすよう伝える。青魚に含まれる油(EPA・DHA)を意識的に摂ることも勧める</v>
       </c>
       <c r="H26" t="str">
-        <v/>
+        <v>非定型抗精神病薬、ステロイド、サイアザイド系利尿薬、非選択的β遮断薬</v>
       </c>
       <c r="I26" t="str">
-        <v>低栄養／肝機能低下／ネフローゼ症候群／クローン病</v>
+        <v>低栄養、肝機能低下、甲状腺機能亢進症</v>
       </c>
       <c r="J26" t="str">
-        <v>主食に偏らず、肉・魚・卵・大豆製品などたんぱく質をしっかり摂るよう伝える。食欲が落ちている場合は少量頻回の食事や、間食に乳製品・卵を取り入れるなど無理のない工夫を提案し、むくみの有無もあわせて確認する</v>
+        <v/>
       </c>
       <c r="K26" t="str">
-        <v>蛋白結合率の高い薬剤(ワルファリン、フェニトイン、NSAIDs等)は遊離型濃度が上昇し、効果や副作用が増強しやすいため用量に注意</v>
+        <v/>
       </c>
       <c r="L26" t="str">
-        <v>3前半は注意ライン。食事摂取量を必ず確認</v>
+        <v>現在はLDLコレステロールでの評価が主流。総コレステロールだけでは悪玉・善玉の内訳が分からないため、LDL・HDL・中性脂肪と合わせて評価する</v>
       </c>
       <c r="M26" t="str">
-        <v>肝機能,栄養,腎機能</v>
+        <v>脂質異常症</v>
       </c>
       <c r="N26" t="str">
-        <v>アルブミン,Alb,むくみ,浮腫,栄養状態</v>
+        <v>総コレステロール,TC,コレステロール,脂質異常症</v>
       </c>
       <c r="O26" t="str">
-        <v>食事と栄養 p.23（たんぱく質）／p.242（フレイルQ110 アルブミン値を上げる食事指導）</v>
-      </c>
-    </row>
-    <row r="27">
+        <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
+      </c>
+    </row>
+    <row r="27" xml:space="preserve">
       <c r="A27" t="str">
-        <v>A/G</v>
+        <v>LDLコレステロール</v>
       </c>
       <c r="B27" t="str">
-        <v>A/G比</v>
-      </c>
-      <c r="C27" t="str">
-        <v>1.1〜2.0程度(施設差あり)</v>
+        <v>LDL-C</v>
+      </c>
+      <c r="C27" t="str" xml:space="preserve">
+        <v xml:space="preserve">60〜139 mg/dL
+（140 mg/dL以上で高LDLコレステロール血症）</v>
       </c>
       <c r="D27" t="str">
-        <v>血液中のアルブミンとグロブリンの比率。肝機能や炎症、免疫の状態を反映する</v>
+        <v>いわゆる「悪玉コレステロール」。血管の壁にたまり動脈硬化を進める</v>
       </c>
       <c r="E27" t="str">
-        <v>A/G比は、血液中のたんぱく質のうちアルブミンとグロブリンという2種類の比率を見る数値です。肝臓の働きが落ちたり、体に炎症や免疫の異常があったりすると、このバランスが崩れることがあります。</v>
+        <v>LDLコレステロールは、いわゆる悪玉コレステロールと呼ばれるものです。多いままだと血管の壁にたまって、動脈硬化や心筋梗塞・脳梗塞のリスクを高めます。数値を下げることで、将来の血管のトラブルを防ぐことが目的です。</v>
       </c>
       <c r="F27" t="str">
-        <v>通常、臨床的意義は乏しい(まれに無ガンマグロブリン血症など)</v>
+        <v>脂質異常症、動脈硬化のリスク上昇、家族性高コレステロール血症、甲状腺機能低下症</v>
       </c>
       <c r="G27" t="str">
-        <v/>
+        <v>動物性脂肪や揚げ物を控え、青魚や食物繊維(野菜・海藻・きのこ)を増やすよう伝える。禁煙も動脈硬化予防に重要なことを伝える</v>
       </c>
       <c r="H27" t="str">
-        <v/>
+        <v>ステロイド、サイアザイド系利尿薬、非選択的β遮断薬</v>
       </c>
       <c r="I27" t="str">
-        <v>肝硬変などの肝機能低下(アルブミン産生低下)、慢性炎症・感染症、多発性骨髄腫などの血液疾患(グロブリン増加)、ネフローゼ症候群</v>
+        <v>低栄養、肝機能低下、甲状腺機能亢進症</v>
       </c>
       <c r="J27" t="str">
-        <v>食事摂取量やむくみの有無を確認する。慢性炎症や感染の有無もあわせて確認する</v>
+        <v/>
       </c>
       <c r="K27" t="str">
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>A/G比＝アルブミン÷(総タンパク－アルブミン)で算出する。低下はアルブミンが減った場合とグロブリンが増えた場合の両方で起こるため、総タンパク・アルブミンの実測値とあわせて原因を判断する</v>
+        <v>スタチン等の効果判定に使う中心的な数値。目標値は既往疾患（冠動脈疾患・糖尿病等）によって異なるため一律に判断しない</v>
       </c>
       <c r="M27" t="str">
-        <v>肝機能</v>
+        <v>脂質異常症,精神疾患（非定型抗精神病薬）</v>
       </c>
       <c r="N27" t="str">
-        <v>A/G,A/G比,アルブミングロブリン比,肝機能,多発性骨髄腫</v>
+        <v>LDL,LDLコレステロール,悪玉コレステロール,脂質異常症</v>
       </c>
       <c r="O27" t="str">
-        <v/>
+        <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>アンモニア</v>
+        <v>nonHDLコレステロール</v>
       </c>
       <c r="B28" t="str">
-        <v>NH3</v>
+        <v>non-HDL-C</v>
       </c>
       <c r="C28" t="str">
-        <v>12〜66 μg/dL（施設差あり／空腹時採血が望ましい）</v>
+        <v>90〜149 mg/dL（150 mg/dL以上で高値）</v>
       </c>
       <c r="D28" t="str">
-        <v>肝機能低下や門脈シャントなどで代謝・排泄が低下すると上昇し、意識障害（肝性脳症）の原因となる</v>
+        <v>総コレステロールからHDL（善玉）を除いた、動脈硬化を進めるすべての脂質の合計</v>
       </c>
       <c r="E28" t="str">
-        <v>アンモニアは体の中でタンパク質が分解されるときにできる老廃物で、通常は肝臓で無害な尿素に変えられて尿として排泄されます。肝臓の働きが弱っていたり血液の流れ道に変化があると、アンモニアがうまく処理されず血液中にたまり、頭がぼんやりしたり意識がもうろうとする原因になることがあります。</v>
+        <v>nonHDLコレステロールは、総コレステロールから善玉のHDLを引いた数値で、LDL（悪玉）を含む、動脈硬化を進めるすべてのコレステロールの合計を表します。中性脂肪が高くLDLだけでは評価しにくい方でも、こちらで動脈硬化のリスクを評価できます。</v>
       </c>
       <c r="F28" t="str">
-        <v>肝硬変・肝不全（門脈-大循環シャント含む）、劇症肝炎、消化管出血、便秘、脱水、高たんぱく食、尿素サイクル異常症、一部薬剤（バルプロ酸など）</v>
+        <v>脂質異常症、動脈硬化のリスク上昇（特に中性脂肪が高い場合にLDL-Cより実態を反映しやすい）</v>
       </c>
       <c r="G28" t="str">
-        <v>便秘の解消(排便コントロール)を心がける。ラクツロースやリファキシミンなど肝性脳症治療薬の服薬状況を確認し、意識のもうろう感や日中の眠気の変化にも注意する</v>
+        <v>動物性脂肪や揚げ物を控え、青魚や食物繊維（野菜・海藻・きのこ）を増やすよう伝える</v>
       </c>
       <c r="H28" t="str">
-        <v>バルプロ酸(デパケン等)</v>
+        <v/>
       </c>
       <c r="I28" t="str">
-        <v>通常、臨床的意義は乏しい</v>
+        <v/>
       </c>
       <c r="J28" t="str">
         <v/>
@@ -1727,60 +1728,60 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>バルプロ酸(デパケン等)は肝疾患の既往がなくても高アンモニア血症を起こすことがあり、意識障害・傾眠が出現した場合は薬剤性を疑ってアンモニア値を確認する。採血後は室温放置で見かけ上上昇するため測定条件にも注意。ラクツロース・リファキシミンは腸管内でのアンモニア産生・吸収を抑える目的で使用される</v>
+        <v>中性脂肪（TG）が400 mg/dL以上などLDL-Cの計算式（Friedewald式）が不正確になる場合に、LDL-Cの代わりに用いられる。目標値はLDL-Cの目標値＋30 mg/dLが目安</v>
       </c>
       <c r="M28" t="str">
-        <v>肝機能</v>
+        <v>脂質異常症</v>
       </c>
       <c r="N28" t="str">
-        <v>アンモニア,NH3,肝性脳症,バルプロ酸,門脈シャント</v>
+        <v>nonHDL,non-HDLコレステロール,動脈硬化,中性脂肪,LDL計算式</v>
       </c>
       <c r="O28" t="str">
-        <v/>
+        <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>中性脂肪（トリグリセリド）</v>
+        <v>HDLコレステロール</v>
       </c>
       <c r="B29" t="str">
-        <v>TG</v>
+        <v>HDL-C</v>
       </c>
       <c r="C29" t="str">
-        <v>150 mg/dL未満（空腹時）</v>
+        <v>40 mg/dL以上</v>
       </c>
       <c r="D29" t="str">
-        <v>脂質異常症で高値になりやすい脂質で、食事の影響を強く受ける</v>
+        <v>いわゆる「善玉コレステロール」。血管にたまった余分なコレステロールを回収する</v>
       </c>
       <c r="E29" t="str">
-        <v>中性脂肪は、食事から摂った脂肪や糖質が体に蓄えられる形になったものです。食後は誰でも一時的に上がるため、正確に評価するには空腹時に採血することが大切です。高い状態が続くと動脈硬化や急性膵炎のリスクが高まります。</v>
+        <v>HDLコレステロールは、いわゆる善玉コレステロールと呼ばれるものです。血管の壁にたまった余分なコレステロールを回収して肝臓に戻す働きがあり、数値が高いほど動脈硬化を防ぐ方向に働きます。</v>
       </c>
       <c r="F29" t="str">
-        <v>脂質異常症、糖質・アルコールの摂りすぎ、肥満、糖尿病のコントロール不良</v>
+        <v/>
       </c>
       <c r="G29" t="str">
-        <v>糖質・アルコールの摂りすぎに注意し、ウォーキングなどの有酸素運動を週150分程度を目安に勧める。清涼飲料水や果物の摂りすぎにも注意する</v>
+        <v/>
       </c>
       <c r="H29" t="str">
-        <v>非定型抗精神病薬(オランザピン・クエチアピン)、ステロイド、エストロゲン製剤、非選択的β遮断薬、サイアザイド系利尿薬、タモキシフェン</v>
+        <v/>
       </c>
       <c r="I29" t="str">
-        <v>低栄養、甲状腺機能亢進症</v>
+        <v>脂質異常症（低HDL血症）</v>
       </c>
       <c r="J29" t="str">
-        <v/>
+        <v>適度な有酸素運動(ウォーキング等)、禁煙を勧める。適正体重の維持もHDL改善に役立つことを伝える</v>
       </c>
       <c r="K29" t="str">
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>採血が食後か空腹時かで数値が大きく変わるため必ず確認する。500 mg/dL以上では急性膵炎のリスクが高まるため注意。フィブラート系・EPA製剤などの効果判定に使う</v>
+        <v>喫煙、運動不足、肥満で低下しやすい。禁煙・運動習慣の改善で上昇が期待できる。低HDLは動脈硬化のリスク因子として単独でも重視される</v>
       </c>
       <c r="M29" t="str">
         <v>脂質異常症</v>
       </c>
       <c r="N29" t="str">
-        <v>中性脂肪,トリグリセリド,TG,脂質異常症</v>
+        <v>HDL,HDLコレステロール,善玉コレステロール,脂質異常症</v>
       </c>
       <c r="O29" t="str">
         <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
@@ -1788,31 +1789,31 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>総コレステロール</v>
+        <v>CK（クレアチンフォスフォキナーゼ）</v>
       </c>
       <c r="B30" t="str">
-        <v>TC,T-cho</v>
+        <v>CK,CPK</v>
       </c>
       <c r="C30" t="str">
-        <v>220 mg/dL未満</v>
+        <v>男性 60〜250 U/L、女性 50〜170 U/L</v>
       </c>
       <c r="D30" t="str">
-        <v>LDL・HDLなどすべてのコレステロールを合わせた総量</v>
+        <v>主に骨格筋・心筋に含まれる酵素。筋肉の損傷で血液中に漏れ出す</v>
       </c>
       <c r="E30" t="str">
-        <v>総コレステロールは、体の中にあるコレステロールをすべて合わせた数値です。ただし、悪玉(LDL)が多いのか善玉(HDL)が多いのかまでは分からないため、実際の評価にはLDLコレステロールの値がより重視されます。</v>
+        <v>CKは筋肉の中にある酵素で、激しい運動や筋肉の病気、心筋梗塞などで筋肉の細胞がダメージを受けると血液中に漏れ出して数値が上がります。スタチン系のお薬の副作用（横紋筋融解症）のチェックにも使われます。</v>
       </c>
       <c r="F30" t="str">
-        <v>脂質異常症、家族性高コレステロール血症、甲状腺機能低下症</v>
+        <v>心筋梗塞、横紋筋融解症（スタチン系薬剤の副作用など）、激しい運動、筋肉注射直後、甲状腺機能低下症</v>
       </c>
       <c r="G30" t="str">
-        <v>動物性脂肪を控え、食物繊維(野菜・海藻・きのこ)を増やすよう伝える。青魚に含まれる油(EPA・DHA)を意識的に摂ることも勧める</v>
+        <v>筋肉痛・脱力感・褐色尿（横紋筋融解症の症状）がないか確認する。スタチン系薬剤服用中は特に注意する。激しい運動の直後の採血でないかも確認する</v>
       </c>
       <c r="H30" t="str">
-        <v>非定型抗精神病薬、ステロイド、サイアザイド系利尿薬、非選択的β遮断薬</v>
+        <v>スタチン系(特にフィブラート系との併用時)、コルヒチン</v>
       </c>
       <c r="I30" t="str">
-        <v>低栄養、肝機能低下、甲状腺機能亢進症</v>
+        <v/>
       </c>
       <c r="J30" t="str">
         <v/>
@@ -1821,46 +1822,45 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>現在はLDLコレステロールでの評価が主流。総コレステロールだけでは悪玉・善玉の内訳が分からないため、LDL・HDL・中性脂肪と合わせて評価する</v>
+        <v>スタチン系薬剤の重大な副作用である横紋筋融解症の指標。筋肉痛・脱力感・褐色尿の有無を必ず確認し、著明高値では服薬継続の可否を医師に相談する</v>
       </c>
       <c r="M30" t="str">
-        <v>脂質異常症</v>
+        <v/>
       </c>
       <c r="N30" t="str">
-        <v>総コレステロール,TC,コレステロール,脂質異常症</v>
+        <v>CK,CPK,クレアチンキナーゼ,横紋筋融解症</v>
       </c>
       <c r="O30" t="str">
-        <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
-      </c>
-    </row>
-    <row r="31" xml:space="preserve">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
       <c r="A31" t="str">
-        <v>LDLコレステロール</v>
+        <v>BUN/CRE比</v>
       </c>
       <c r="B31" t="str">
-        <v>LDL-C</v>
-      </c>
-      <c r="C31" t="str" xml:space="preserve">
-        <v xml:space="preserve">60〜139 mg/dL
-（140 mg/dL以上で高LDLコレステロール血症）</v>
+        <v>BUN/Cr</v>
+      </c>
+      <c r="C31" t="str">
+        <v>10前後が目安（施設差あり）</v>
       </c>
       <c r="D31" t="str">
-        <v>いわゆる「悪玉コレステロール」。血管の壁にたまり動脈硬化を進める</v>
+        <v>BUNとクレアチニンの比率。腎前性（脱水・出血など）か腎性かを見分ける目安になる</v>
       </c>
       <c r="E31" t="str">
-        <v>LDLコレステロールは、いわゆる悪玉コレステロールと呼ばれるものです。多いままだと血管の壁にたまって、動脈硬化や心筋梗塞・脳梗塞のリスクを高めます。数値を下げることで、将来の血管のトラブルを防ぐことが目的です。</v>
+        <v>これは、BUN（尿素窒素）とクレアチニンという2つの腎機能に関わる検査値を比較したもので、腎臓そのものに問題があるのか、それとも脱水や出血など腎臓の外側に原因があるのかを見分ける手がかりになります。</v>
       </c>
       <c r="F31" t="str">
-        <v>脂質異常症、動脈硬化のリスク上昇、家族性高コレステロール血症、甲状腺機能低下症</v>
+        <v>脱水、消化管出血、高たんぱく食、心不全（腎臓への血流低下）</v>
       </c>
       <c r="G31" t="str">
-        <v>動物性脂肪や揚げ物を控え、青魚や食物繊維(野菜・海藻・きのこ)を増やすよう伝える。禁煙も動脈硬化予防に重要なことを伝える</v>
+        <v>脱水が疑われる場合はこまめな水分摂取を勧める。黒い便など消化管出血を示唆する症状がないか確認する</v>
       </c>
       <c r="H31" t="str">
-        <v>ステロイド、サイアザイド系利尿薬、非選択的β遮断薬</v>
+        <v/>
       </c>
       <c r="I31" t="str">
-        <v>低栄養、肝機能低下、甲状腺機能亢進症</v>
+        <v>低たんぱく食、肝不全、妊娠</v>
       </c>
       <c r="J31" t="str">
         <v/>
@@ -1869,45 +1869,45 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>スタチン等の効果判定に使う中心的な数値。目標値は既往疾患（冠動脈疾患・糖尿病等）によって異なるため一律に判断しない</v>
+        <v>比が高い（目安20以上）場合は脱水や消化管出血など腎前性の要因を、比が正常範囲で両方高値なら腎性の障害を疑う。BUN単独やクレアチニン単独よりも病態の絞り込みに役立つ</v>
       </c>
       <c r="M31" t="str">
-        <v>脂質異常症,精神疾患（非定型抗精神病薬）</v>
+        <v>腎機能</v>
       </c>
       <c r="N31" t="str">
-        <v>LDL,LDLコレステロール,悪玉コレステロール,脂質異常症</v>
+        <v>BUN/CRE,BUN/Cr,尿素窒素,クレアチニン,脱水,腎前性</v>
       </c>
       <c r="O31" t="str">
-        <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>nonHDLコレステロール</v>
+        <v>LDH/AST比</v>
       </c>
       <c r="B32" t="str">
-        <v>non-HDL-C</v>
+        <v>LDH/AST</v>
       </c>
       <c r="C32" t="str">
-        <v>90〜149 mg/dL（150 mg/dL以上で高値）</v>
+        <v>目安として使われる比率（施設差・カットオフ値の設定により異なる）</v>
       </c>
       <c r="D32" t="str">
-        <v>総コレステロールからHDL（善玉）を除いた、動脈硬化を進めるすべての脂質の合計</v>
+        <v>LDHとASTの両方が上昇したときに、原因が肝臓か、それ以外（溶血・心筋・骨格筋）かを見分ける目安になる比</v>
       </c>
       <c r="E32" t="str">
-        <v>nonHDLコレステロールは、総コレステロールから善玉のHDLを引いた数値で、LDL（悪玉）を含む、動脈硬化を進めるすべてのコレステロールの合計を表します。中性脂肪が高くLDLだけでは評価しにくい方でも、こちらで動脈硬化のリスクを評価できます。</v>
+        <v>これは、肝臓の数値（AST）と、全身に広く分布する酵素（LDH）の比率を見るもので、両方の数値が上がっているときに、原因が肝臓なのか、それとも血液や筋肉など他の場所なのかを見分ける手がかりになります。</v>
       </c>
       <c r="F32" t="str">
-        <v>脂質異常症、動脈硬化のリスク上昇（特に中性脂肪が高い場合にLDL-Cより実態を反映しやすい）</v>
+        <v>溶血性疾患、心筋梗塞、骨格筋の障害（比が高いほど肝臓以外が原因の可能性）</v>
       </c>
       <c r="G32" t="str">
-        <v>動物性脂肪や揚げ物を控え、青魚や食物繊維（野菜・海藻・きのこ）を増やすよう伝える</v>
+        <v/>
       </c>
       <c r="H32" t="str">
         <v/>
       </c>
       <c r="I32" t="str">
-        <v/>
+        <v>急性肝炎などの肝細胞障害（比が低い、つまりASTに対してLDHが相対的に低い場合は肝性が示唆される）</v>
       </c>
       <c r="J32" t="str">
         <v/>
@@ -1916,89 +1916,89 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>中性脂肪（TG）が400 mg/dL以上などLDL-Cの計算式（Friedewald式）が不正確になる場合に、LDL-Cの代わりに用いられる。目標値はLDL-Cの目標値＋30 mg/dLが目安</v>
+        <v>AST・LDHが同時に上昇した際の鑑別に使う目安の一つ。単独の検査値ではなく計算上の比率であり、確定診断には他の検査（ビリルビン、CK、心筋マーカーなど）と合わせた評価が必要</v>
       </c>
       <c r="M32" t="str">
-        <v>脂質異常症</v>
+        <v/>
       </c>
       <c r="N32" t="str">
-        <v>nonHDL,non-HDLコレステロール,動脈硬化,中性脂肪,LDL計算式</v>
+        <v>LDH/AST,LDH,AST,溶血,心筋梗塞,肝炎</v>
       </c>
       <c r="O32" t="str">
-        <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>HDLコレステロール</v>
+        <v>CK/AST比</v>
       </c>
       <c r="B33" t="str">
-        <v>HDL-C</v>
+        <v>CK/AST</v>
       </c>
       <c r="C33" t="str">
-        <v>40 mg/dL以上</v>
+        <v>目安として使われる比率（施設差・カットオフ値の設定により異なる）</v>
       </c>
       <c r="D33" t="str">
-        <v>いわゆる「善玉コレステロール」。血管にたまった余分なコレステロールを回収する</v>
+        <v>ASTが上昇したときに、原因が筋肉（CKも上昇）か、それ以外（肝臓など）かを見分ける目安になる比</v>
       </c>
       <c r="E33" t="str">
-        <v>HDLコレステロールは、いわゆる善玉コレステロールと呼ばれるものです。血管の壁にたまった余分なコレステロールを回収して肝臓に戻す働きがあり、数値が高いほど動脈硬化を防ぐ方向に働きます。</v>
+        <v>これは、筋肉の数値（CK）と肝臓の数値（AST）を比べることで、ASTの上昇が筋肉由来なのか、肝臓由来なのかを見分ける手がかりになる比率です。</v>
       </c>
       <c r="F33" t="str">
-        <v/>
+        <v>横紋筋融解症、心筋梗塞、激しい運動など筋肉由来のAST上昇（CKも同時に高値）</v>
       </c>
       <c r="G33" t="str">
-        <v/>
+        <v>筋肉痛や脱力感、褐色尿などの症状がないか確認する</v>
       </c>
       <c r="H33" t="str">
         <v/>
       </c>
       <c r="I33" t="str">
-        <v>脂質異常症（低HDL血症）</v>
+        <v/>
       </c>
       <c r="J33" t="str">
-        <v>適度な有酸素運動(ウォーキング等)、禁煙を勧める。適正体重の維持もHDL改善に役立つことを伝える</v>
+        <v/>
       </c>
       <c r="K33" t="str">
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>喫煙、運動不足、肥満で低下しやすい。禁煙・運動習慣の改善で上昇が期待できる。低HDLは動脈硬化のリスク因子として単独でも重視される</v>
+        <v>ASTのみ上昇しCKが正常であれば肝臓由来を、両方上昇していれば筋肉由来を疑う手がかりになる。スタチン系薬剤による横紋筋融解症が疑われる場面での鑑別に有用</v>
       </c>
       <c r="M33" t="str">
-        <v>脂質異常症</v>
+        <v/>
       </c>
       <c r="N33" t="str">
-        <v>HDL,HDLコレステロール,善玉コレステロール,脂質異常症</v>
+        <v>CK/AST,CK,AST,横紋筋融解症,スタチン</v>
       </c>
       <c r="O33" t="str">
-        <v>食事と栄養 p.28（脂質）／p.132-150（第2部 脂質異常症）</v>
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>CK（クレアチンフォスフォキナーゼ）</v>
+        <v>Na-Cl（ナトリウム・クロール差）</v>
       </c>
       <c r="B34" t="str">
-        <v>CK,CPK</v>
+        <v>Na-Cl</v>
       </c>
       <c r="C34" t="str">
-        <v>男性 60〜250 U/L、女性 50〜170 U/L</v>
+        <v>36前後が目安（施設差あり）</v>
       </c>
       <c r="D34" t="str">
-        <v>主に骨格筋・心筋に含まれる酵素。筋肉の損傷で血液中に漏れ出す</v>
+        <v>ナトリウムからクロールを引いた値。アニオンギャップの簡易的な目安として使われる</v>
       </c>
       <c r="E34" t="str">
-        <v>CKは筋肉の中にある酵素で、激しい運動や筋肉の病気、心筋梗塞などで筋肉の細胞がダメージを受けると血液中に漏れ出して数値が上がります。スタチン系のお薬の副作用（横紋筋融解症）のチェックにも使われます。</v>
+        <v>この数値は、ナトリウムとクロールの検査値の差から計算されるもので、体の中に通常とは違う酸（アニオン）がたまっていないかを大まかに見積もるために使われます。</v>
       </c>
       <c r="F34" t="str">
-        <v>心筋梗塞、横紋筋融解症（スタチン系薬剤の副作用など）、激しい運動、筋肉注射直後、甲状腺機能低下症</v>
+        <v>代謝性アシドーシス（乳酸アシドーシス、糖尿病性ケトアシドーシス、腎不全など、体内に有機酸がたまる病態）</v>
       </c>
       <c r="G34" t="str">
-        <v>筋肉痛・脱力感・褐色尿（横紋筋融解症の症状）がないか確認する。スタチン系薬剤服用中は特に注意する。激しい運動の直後の採血でないかも確認する</v>
+        <v/>
       </c>
       <c r="H34" t="str">
-        <v>スタチン系(特にフィブラート系との併用時)、コルヒチン</v>
+        <v/>
       </c>
       <c r="I34" t="str">
         <v/>
@@ -2010,13 +2010,13 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>スタチン系薬剤の重大な副作用である横紋筋融解症の指標。筋肉痛・脱力感・褐色尿の有無を必ず確認し、著明高値では服薬継続の可否を医師に相談する</v>
+        <v>本来のアニオンギャップ(Na-(Cl+HCO3))の簡易代用として使われることがあるが、重炭酸(HCO3)を用いた計算の方が正確。メトホルミン使用中の乳酸アシドーシスが疑われる場面などで参考にする</v>
       </c>
       <c r="M34" t="str">
-        <v/>
+        <v>電解質</v>
       </c>
       <c r="N34" t="str">
-        <v>CK,CPK,クレアチンキナーゼ,横紋筋融解症</v>
+        <v>Na-Cl,アニオンギャップ,AG,代謝性アシドーシス,乳酸アシドーシス</v>
       </c>
       <c r="O34" t="str">
         <v/>
@@ -2024,31 +2024,31 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>BUN/CRE比</v>
+        <v>AST/ALT比</v>
       </c>
       <c r="B35" t="str">
-        <v>BUN/Cr</v>
+        <v>AST/ALT,De Ritis比</v>
       </c>
       <c r="C35" t="str">
-        <v>10前後が目安（施設差あり）</v>
+        <v>1未満が目安（施設・病態により異なる）</v>
       </c>
       <c r="D35" t="str">
-        <v>BUNとクレアチニンの比率。腎前性（脱水・出血など）か腎性かを見分ける目安になる</v>
+        <v>ASTとALTの比率（De Ritis比）。肝疾患の種類を推測する手がかりになる</v>
       </c>
       <c r="E35" t="str">
-        <v>これは、BUN（尿素窒素）とクレアチニンという2つの腎機能に関わる検査値を比較したもので、腎臓そのものに問題があるのか、それとも脱水や出血など腎臓の外側に原因があるのかを見分ける手がかりになります。</v>
+        <v>これは、肝臓に関わる2つの数値（ASTとALT）の比率を見るもので、肝臓のどのようなタイプのトラブルが起きているかを推測する手がかりになります。</v>
       </c>
       <c r="F35" t="str">
-        <v>脱水、消化管出血、高たんぱく食、心不全（腎臓への血流低下）</v>
+        <v>アルコール性肝障害、肝硬変、心筋梗塞・筋疾患の合併（比が2以上でアルコール性を強く示唆）</v>
       </c>
       <c r="G35" t="str">
-        <v>脱水が疑われる場合はこまめな水分摂取を勧める。黒い便など消化管出血を示唆する症状がないか確認する</v>
+        <v>飲酒量や頻度を確認する</v>
       </c>
       <c r="H35" t="str">
         <v/>
       </c>
       <c r="I35" t="str">
-        <v>低たんぱく食、肝不全、妊娠</v>
+        <v>急性ウイルス性肝炎、脂肪肝（比が1未満で肝細胞の急性障害を示唆することが多い）</v>
       </c>
       <c r="J35" t="str">
         <v/>
@@ -2057,13 +2057,13 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>比が高い（目安20以上）場合は脱水や消化管出血など腎前性の要因を、比が正常範囲で両方高値なら腎性の障害を疑う。BUN単独やクレアチニン単独よりも病態の絞り込みに役立つ</v>
+        <v>De Ritis比とも呼ばれる。比が2以上はアルコール性肝障害や肝硬変を、1未満は急性ウイルス性肝炎や脂肪肝を示唆する目安になるが、確定診断には他の検査所見と合わせた評価が必要</v>
       </c>
       <c r="M35" t="str">
-        <v>腎機能</v>
+        <v>肝機能</v>
       </c>
       <c r="N35" t="str">
-        <v>BUN/CRE,BUN/Cr,尿素窒素,クレアチニン,脱水,腎前性</v>
+        <v>AST/ALT比,AST/ALT,De Ritis比,デリティス比,アルコール性肝障害,肝硬変</v>
       </c>
       <c r="O35" t="str">
         <v/>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>LDH/AST比</v>
+        <v>ALT/ALP比</v>
       </c>
       <c r="B36" t="str">
-        <v>LDH/AST</v>
+        <v>ALT比/ALP比,R比,R-factor</v>
       </c>
       <c r="C36" t="str">
-        <v>目安として使われる比率（施設差・カットオフ値の設定により異なる）</v>
+        <v>R値 5以上：肝細胞障害型、2以下：胆汁うっ滞型、2〜5：混合型</v>
       </c>
       <c r="D36" t="str">
-        <v>LDHとASTの両方が上昇したときに、原因が肝臓か、それ以外（溶血・心筋・骨格筋）かを見分ける目安になる比</v>
+        <v>薬剤性肝障害(DILI)などで、肝障害のパターンを「肝細胞障害型」か「胆汁うっ滞型」かに分類するための指標(R値)</v>
       </c>
       <c r="E36" t="str">
-        <v>これは、肝臓の数値（AST）と、全身に広く分布する酵素（LDH）の比率を見るもので、両方の数値が上がっているときに、原因が肝臓なのか、それとも血液や筋肉など他の場所なのかを見分ける手がかりになります。</v>
+        <v>肝臓に関する数値はいくつかありますが、その組み合わせ方によって「肝臓の細胞自体が傷んでいるタイプ」か「胆汁の流れが悪くなっているタイプ」かをある程度見分けることができます。この指標はその判定に使われます。</v>
       </c>
       <c r="F36" t="str">
-        <v>溶血性疾患、心筋梗塞、骨格筋の障害（比が高いほど肝臓以外が原因の可能性）</v>
+        <v>R値5以上：肝細胞障害型（ウイルス性肝炎、薬剤性肝障害の肝細胞障害型、虚血性肝障害など）</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -2095,7 +2095,7 @@
         <v/>
       </c>
       <c r="I36" t="str">
-        <v>急性肝炎などの肝細胞障害（比が低い、つまりASTに対してLDHが相対的に低い場合は肝性が示唆される）</v>
+        <v>R値2以下：胆汁うっ滞型（閉塞性黄疸、薬剤性肝障害の胆汁うっ滞型など）</v>
       </c>
       <c r="J36" t="str">
         <v/>
@@ -2104,13 +2104,13 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>AST・LDHが同時に上昇した際の鑑別に使う目安の一つ。単独の検査値ではなく計算上の比率であり、確定診断には他の検査（ビリルビン、CK、心筋マーカーなど）と合わせた評価が必要</v>
+        <v>R値＝(ALTの基準値上限に対する倍率)÷(ALPの基準値上限に対する倍率)で算出する。薬剤性肝障害(DILI)の病型分類(肝細胞障害型/胆汁うっ滞型/混合型)に用いられ、被疑薬の休薬・変更の判断材料になる</v>
       </c>
       <c r="M36" t="str">
-        <v/>
+        <v>肝機能</v>
       </c>
       <c r="N36" t="str">
-        <v>LDH/AST,LDH,AST,溶血,心筋梗塞,肝炎</v>
+        <v>ALT/ALP比,R値,R-factor,DILI,薬剤性肝障害</v>
       </c>
       <c r="O36" t="str">
         <v/>
@@ -2118,31 +2118,31 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>CK/AST比</v>
+        <v>BNP</v>
       </c>
       <c r="B37" t="str">
-        <v>CK/AST</v>
+        <v>BNP</v>
       </c>
       <c r="C37" t="str">
-        <v>目安として使われる比率（施設差・カットオフ値の設定により異なる）</v>
+        <v>18.4 pg/mL以下</v>
       </c>
       <c r="D37" t="str">
-        <v>ASTが上昇したときに、原因が筋肉（CKも上昇）か、それ以外（肝臓など）かを見分ける目安になる比</v>
+        <v>心臓が無理をしているときに出る物質。心臓は血液を送るポンプだが、負担がかかると「少し助けてほしい」というサインとしてBNPを血液中に出す。</v>
       </c>
       <c r="E37" t="str">
-        <v>これは、筋肉の数値（CK）と肝臓の数値（AST）を比べることで、ASTの上昇が筋肉由来なのか、肝臓由来なのかを見分ける手がかりになる比率です。</v>
+        <v>この検査は、心臓がどれくらい頑張りすぎていないかを見るものです。数値が高いと、心臓に少し負担がかかっているサインになります。</v>
       </c>
       <c r="F37" t="str">
-        <v>横紋筋融解症、心筋梗塞、激しい運動など筋肉由来のAST上昇（CKも同時に高値）</v>
+        <v>心不全、心臓に負担がかかっている状態、体に水分がたまりやすいとき</v>
       </c>
       <c r="G37" t="str">
-        <v>筋肉痛や脱力感、褐色尿などの症状がないか確認する</v>
+        <v>塩分・水分の摂りすぎに注意し、体重の変化を毎日記録するよう伝える。急な体重増加(2〜3日で2kg以上)や息切れの悪化があれば早めの受診を勧める</v>
       </c>
       <c r="H37" t="str">
         <v/>
       </c>
       <c r="I37" t="str">
-        <v/>
+        <v>心臓の負担は少ない状態</v>
       </c>
       <c r="J37" t="str">
         <v/>
@@ -2151,36 +2151,36 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>ASTのみ上昇しCKが正常であれば肝臓由来を、両方上昇していれば筋肉由来を疑う手がかりになる。スタチン系薬剤による横紋筋融解症が疑われる場面での鑑別に有用</v>
+        <v>腎機能が低いとBNPは高めに出ることがある／数値だけで判断せず、症状と合わせて評価する／息切れ、むくみ、体重増加があれば要注意</v>
       </c>
       <c r="M37" t="str">
-        <v/>
+        <v>心不全</v>
       </c>
       <c r="N37" t="str">
-        <v>CK/AST,CK,AST,横紋筋融解症,スタチン</v>
+        <v>BNP,心不全,息切れ,むくみ</v>
       </c>
       <c r="O37" t="str">
-        <v/>
+        <v>食事と栄養 p.216-222（第2部 心疾患）</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Na-Cl（ナトリウム・クロール差）</v>
+        <v>C－ペプチド（血中）</v>
       </c>
       <c r="B38" t="str">
-        <v>Na-Cl</v>
+        <v>CPR</v>
       </c>
       <c r="C38" t="str">
-        <v>36前後が目安（施設差あり）</v>
+        <v>空腹時 0.6〜3.0 ng/mL（施設差あり）</v>
       </c>
       <c r="D38" t="str">
-        <v>ナトリウムからクロールを引いた値。アニオンギャップの簡易的な目安として使われる</v>
+        <v>自分の膵臓がどれくらいインスリンを作れているかを表す指標</v>
       </c>
       <c r="E38" t="str">
-        <v>この数値は、ナトリウムとクロールの検査値の差から計算されるもので、体の中に通常とは違う酸（アニオン）がたまっていないかを大まかに見積もるために使われます。</v>
+        <v>この検査は、ご自身の膵臓がどれくらいインスリンを作る力を持っているかを見るものです。数値が低いほど、体の中で作れるインスリンが少ないことを示します。</v>
       </c>
       <c r="F38" t="str">
-        <v>代謝性アシドーシス（乳酸アシドーシス、糖尿病性ケトアシドーシス、腎不全など、体内に有機酸がたまる病態）</v>
+        <v>インスリン抵抗性が強い状態（初期の2型糖尿病など）</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -2189,7 +2189,7 @@
         <v/>
       </c>
       <c r="I38" t="str">
-        <v/>
+        <v>膵臓のインスリン分泌能低下（1型糖尿病、糖尿病の進行）</v>
       </c>
       <c r="J38" t="str">
         <v/>
@@ -2198,13 +2198,13 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>本来のアニオンギャップ(Na-(Cl+HCO3))の簡易代用として使われることがあるが、重炭酸(HCO3)を用いた計算の方が正確。メトホルミン使用中の乳酸アシドーシスが疑われる場面などで参考にする</v>
+        <v>インスリン分泌能の評価に使われる。数値が低いほどインスリン治療の必要性が高いと判断される目安になる</v>
       </c>
       <c r="M38" t="str">
-        <v>電解質</v>
+        <v>糖尿病</v>
       </c>
       <c r="N38" t="str">
-        <v>Na-Cl,アニオンギャップ,AG,代謝性アシドーシス,乳酸アシドーシス</v>
+        <v>C-ペプチド,Cペプチド,CPR,C-peptide,血中CPR,インスリン分泌</v>
       </c>
       <c r="O38" t="str">
         <v/>
@@ -2212,46 +2212,46 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>AST/ALT比</v>
+        <v>C－ペプチドインデックス</v>
       </c>
       <c r="B39" t="str">
-        <v>AST/ALT,De Ritis比</v>
+        <v>CPI</v>
       </c>
       <c r="C39" t="str">
-        <v>1未満が目安（施設・病態により異なる）</v>
+        <v>1.2以上が目安(施設・測定条件により異なる)</v>
       </c>
       <c r="D39" t="str">
-        <v>ASTとALTの比率（De Ritis比）。肝疾患の種類を推測する手がかりになる</v>
+        <v>血糖値に対してどれくらいインスリンを分泌できているかを表す指標。低いほどインスリン治療の必要性が高い</v>
       </c>
       <c r="E39" t="str">
-        <v>これは、肝臓に関わる2つの数値（ASTとALT）の比率を見るもので、肝臓のどのようなタイプのトラブルが起きているかを推測する手がかりになります。</v>
+        <v>これは、血糖値の高さに対して、体がどれくらいインスリンを作れているかを見る指標です。数値が低いほど、自分の膵臓だけでは血糖値に見合うインスリンを十分に作れていない可能性が高く、インスリン治療が必要かどうかの判断材料になります。</v>
       </c>
       <c r="F39" t="str">
-        <v>アルコール性肝障害、肝硬変、心筋梗塞・筋疾患の合併（比が2以上でアルコール性を強く示唆）</v>
+        <v>通常、臨床的意義は乏しい</v>
       </c>
       <c r="G39" t="str">
-        <v>飲酒量や頻度を確認する</v>
+        <v/>
       </c>
       <c r="H39" t="str">
         <v/>
       </c>
       <c r="I39" t="str">
-        <v>急性ウイルス性肝炎、脂肪肝（比が1未満で肝細胞の急性障害を示唆することが多い）</v>
+        <v>内因性インスリン分泌能の低下(1.2未満でインスリン治療の適応を検討する目安、0.8未満はインスリン療法が強く推奨される目安)</v>
       </c>
       <c r="J39" t="str">
-        <v/>
+        <v>インスリン治療の必要性について医師からどのように説明を受けているか確認する</v>
       </c>
       <c r="K39" t="str">
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>De Ritis比とも呼ばれる。比が2以上はアルコール性肝障害や肝硬変を、1未満は急性ウイルス性肝炎や脂肪肝を示唆する目安になるが、確定診断には他の検査所見と合わせた評価が必要</v>
+        <v>CPI＝血中Cペプチド(ng/mL)÷血糖値(mg/dL)×100 で算出する。空腹時に測定するのが基本で、境界値付近では食事負荷の影響を受けるため、複数回の評価や随時尿中CPRとあわせて判断することもある</v>
       </c>
       <c r="M39" t="str">
-        <v>肝機能</v>
+        <v>糖尿病</v>
       </c>
       <c r="N39" t="str">
-        <v>AST/ALT比,AST/ALT,De Ritis比,デリティス比,アルコール性肝障害,肝硬変</v>
+        <v>CPI,Cペプチドインデックス,C-ペプチドインデックス,インスリン分泌能,インスリン治療</v>
       </c>
       <c r="O39" t="str">
         <v/>
@@ -2259,31 +2259,31 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ALT/ALP比</v>
+        <v>CONUT値</v>
       </c>
       <c r="B40" t="str">
-        <v>ALT比/ALP比,R比,R-factor</v>
+        <v>CONUT</v>
       </c>
       <c r="C40" t="str">
-        <v>R値 5以上：肝細胞障害型、2以下：胆汁うっ滞型、2〜5：混合型</v>
+        <v>0〜1点：正常、2〜4点：軽度低栄養、5〜8点：中等度低栄養、9〜12点：高度低栄養</v>
       </c>
       <c r="D40" t="str">
-        <v>薬剤性肝障害(DILI)などで、肝障害のパターンを「肝細胞障害型」か「胆汁うっ滞型」かに分類するための指標(R値)</v>
+        <v>アルブミン・総リンパ球数・総コレステロールの3項目から算出する栄養状態の評価スコア</v>
       </c>
       <c r="E40" t="str">
-        <v>肝臓に関する数値はいくつかありますが、その組み合わせ方によって「肝臓の細胞自体が傷んでいるタイプ」か「胆汁の流れが悪くなっているタイプ」かをある程度見分けることができます。この指標はその判定に使われます。</v>
+        <v>CONUT値は、血液検査（アルブミン、リンパ球数、コレステロール）の結果から計算される、栄養状態を数値化したスコアです。点数が高いほど低栄養の状態が疑われます。</v>
       </c>
       <c r="F40" t="str">
-        <v>R値5以上：肝細胞障害型（ウイルス性肝炎、薬剤性肝障害の肝細胞障害型、虚血性肝障害など）</v>
+        <v>低栄養状態（点数が高いほど重度）</v>
       </c>
       <c r="G40" t="str">
-        <v/>
+        <v>食事摂取量や体重の変化を確認する。必要に応じて栄養補助食品の活用を提案する</v>
       </c>
       <c r="H40" t="str">
         <v/>
       </c>
       <c r="I40" t="str">
-        <v>R値2以下：胆汁うっ滞型（閉塞性黄疸、薬剤性肝障害の胆汁うっ滞型など）</v>
+        <v/>
       </c>
       <c r="J40" t="str">
         <v/>
@@ -2292,45 +2292,45 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>R値＝(ALTの基準値上限に対する倍率)÷(ALPの基準値上限に対する倍率)で算出する。薬剤性肝障害(DILI)の病型分類(肝細胞障害型/胆汁うっ滞型/混合型)に用いられ、被疑薬の休薬・変更の判断材料になる</v>
+        <v>アルブミン・総リンパ球数・総コレステロールの3項目それぞれに配点があり、合計点で評価する客観的栄養指標。フレイル・サルコペニアの評価やポリファーマシー対策の一環としての栄養状態把握に有用</v>
       </c>
       <c r="M40" t="str">
-        <v>肝機能</v>
+        <v/>
       </c>
       <c r="N40" t="str">
-        <v>ALT/ALP比,R値,R-factor,DILI,薬剤性肝障害</v>
+        <v>CONUT,CONUT値,栄養評価,低栄養,フレイル</v>
       </c>
       <c r="O40" t="str">
-        <v/>
+        <v>食事と栄養 p.240（フレイルQ108 低栄養や食事量の評価）</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>BNP</v>
+        <v>乳び</v>
       </c>
       <c r="B41" t="str">
-        <v>BNP</v>
+        <v>乳び,Lipemia</v>
       </c>
       <c r="C41" t="str">
-        <v>18.4 pg/mL以下</v>
+        <v>所見なし（血清が白濁していなければ正常）</v>
       </c>
       <c r="D41" t="str">
-        <v>心臓が無理をしているときに出る物質。心臓は血液を送るポンプだが、負担がかかると「少し助けてほしい」というサインとしてBNPを血液中に出す。</v>
+        <v>中性脂肪が非常に多いため、血清が白く濁って見える状態。検査値そのものではなく検体の外観所見</v>
       </c>
       <c r="E41" t="str">
-        <v>この検査は、心臓がどれくらい頑張りすぎていないかを見るものです。数値が高いと、心臓に少し負担がかかっているサインになります。</v>
+        <v>乳びとは、血液中の中性脂肪が非常に多いために、採血した血液（血清）が白く濁って見える状態のことです。多くの場合、食後の採血や、著しい脂質異常症が背景にあります。</v>
       </c>
       <c r="F41" t="str">
-        <v>心不全、心臓に負担がかかっている状態、体に水分がたまりやすいとき</v>
+        <v>著しい高中性脂肪血症、食後採血（一時的なもの）、原発性高カイロミクロン血症などの脂質代謝異常</v>
       </c>
       <c r="G41" t="str">
-        <v>塩分・水分の摂りすぎに注意し、体重の変化を毎日記録するよう伝える。急な体重増加(2〜3日で2kg以上)や息切れの悪化があれば早めの受診を勧める</v>
+        <v>採血が空腹時だったかを確認する。食後採血であれば次回は空腹時の再検を提案する</v>
       </c>
       <c r="H41" t="str">
         <v/>
       </c>
       <c r="I41" t="str">
-        <v>心臓の負担は少ない状態</v>
+        <v/>
       </c>
       <c r="J41" t="str">
         <v/>
@@ -2339,45 +2339,45 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>腎機能が低いとBNPは高めに出ることがある／数値だけで判断せず、症状と合わせて評価する／息切れ、むくみ、体重増加があれば要注意</v>
+        <v>血清の白濁により一部の検査項目（電解質など）の測定値に誤差が出ることがある（偽性低ナトリウム血症など）。中性脂肪値と合わせて評価する</v>
       </c>
       <c r="M41" t="str">
-        <v>心不全</v>
+        <v>脂質異常症</v>
       </c>
       <c r="N41" t="str">
-        <v>BNP,心不全,息切れ,むくみ</v>
+        <v>乳び,乳び血清,Lipemia,高中性脂肪血症</v>
       </c>
       <c r="O41" t="str">
-        <v>食事と栄養 p.216-222（第2部 心疾患）</v>
+        <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>C－ペプチド（血中）</v>
+        <v>溶血</v>
       </c>
       <c r="B42" t="str">
-        <v>CPR</v>
+        <v>溶血,Hemolysis</v>
       </c>
       <c r="C42" t="str">
-        <v>空腹時 0.6〜3.0 ng/mL（施設差あり）</v>
+        <v>所見なし（溶血を示唆する検査値異常がなければ正常）</v>
       </c>
       <c r="D42" t="str">
-        <v>自分の膵臓がどれくらいインスリンを作れているかを表す指標</v>
+        <v>赤血球が通常より早く壊れる状態。単独の検査値ではなく、複数の検査値の組み合わせで疑う病態</v>
       </c>
       <c r="E42" t="str">
-        <v>この検査は、ご自身の膵臓がどれくらいインスリンを作る力を持っているかを見るものです。数値が低いほど、体の中で作れるインスリンが少ないことを示します。</v>
+        <v>溶血とは、赤血球が通常よりも早いペースで壊れてしまう状態のことです。壊れた赤血球からビリルビンなどが放出されるため、貧血や黄疸の原因になることがあります。</v>
       </c>
       <c r="F42" t="str">
-        <v>インスリン抵抗性が強い状態（初期の2型糖尿病など）</v>
+        <v>自己免疫性溶血性貧血、血液型不適合輸血、G6PD欠損症などの遺伝性疾患、機械弁など人工物による物理的破壊、薬剤性溶血</v>
       </c>
       <c r="G42" t="str">
-        <v/>
+        <v>倦怠感、黄疸、尿の色が濃くなるなどの症状がないか確認する</v>
       </c>
       <c r="H42" t="str">
         <v/>
       </c>
       <c r="I42" t="str">
-        <v>膵臓のインスリン分泌能低下（1型糖尿病、糖尿病の進行）</v>
+        <v/>
       </c>
       <c r="J42" t="str">
         <v/>
@@ -2386,13 +2386,13 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>インスリン分泌能の評価に使われる。数値が低いほどインスリン治療の必要性が高いと判断される目安になる</v>
+        <v>溶血を疑う際は、間接ビリルビン上昇・LDH上昇・ハプトグロビン低下・網状赤血球増加のパターンを確認する。ヘモグロビン・MCV・MCHCの変化と合わせて総合的に判断する</v>
       </c>
       <c r="M42" t="str">
-        <v>糖尿病</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="N42" t="str">
-        <v>C-ペプチド,Cペプチド,CPR,C-peptide,血中CPR,インスリン分泌</v>
+        <v>溶血,Hemolysis,溶血性貧血,G6PD,ハプトグロビン</v>
       </c>
       <c r="O42" t="str">
         <v/>
@@ -2400,46 +2400,46 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>C－ペプチドインデックス</v>
+        <v>黄疸</v>
       </c>
       <c r="B43" t="str">
-        <v>CPI</v>
+        <v>黄疸,Jaundice</v>
       </c>
       <c r="C43" t="str">
-        <v>1.2以上が目安(施設・測定条件により異なる)</v>
+        <v>所見なし（皮膚・眼球結膜の黄染がなければ正常）</v>
       </c>
       <c r="D43" t="str">
-        <v>血糖値に対してどれくらいインスリンを分泌できているかを表す指標。低いほどインスリン治療の必要性が高い</v>
+        <v>ビリルビンが体にたまり、皮膚や白目が黄色くなる状態。単独の検査値ではなく、ビリルビン上昇によって表れる身体所見</v>
       </c>
       <c r="E43" t="str">
-        <v>これは、血糖値の高さに対して、体がどれくらいインスリンを作れているかを見る指標です。数値が低いほど、自分の膵臓だけでは血糖値に見合うインスリンを十分に作れていない可能性が高く、インスリン治療が必要かどうかの判断材料になります。</v>
+        <v>黄疸は、体の中にビリルビンという黄色い色素がたまることで、皮膚や白目が黄色く見える状態です。肝臓や胆道のトラブル、赤血球が壊れやすくなる病気（溶血）などが原因となります。</v>
       </c>
       <c r="F43" t="str">
-        <v>通常、臨床的意義は乏しい</v>
+        <v>肝炎・肝硬変などの肝疾患、胆石・腫瘍による胆道閉塞、溶血性疾患、体質性黄疸（ジルベール症候群）、新生児黄疸</v>
       </c>
       <c r="G43" t="str">
-        <v/>
+        <v>白目や皮膚の黄染に気づいたら、尿の色（濃い茶色）や便の色（白っぽい）の変化も確認し、早めの受診を勧める</v>
       </c>
       <c r="H43" t="str">
         <v/>
       </c>
       <c r="I43" t="str">
-        <v>内因性インスリン分泌能の低下(1.2未満でインスリン治療の適応を検討する目安、0.8未満はインスリン療法が強く推奨される目安)</v>
+        <v/>
       </c>
       <c r="J43" t="str">
-        <v>インスリン治療の必要性について医師からどのように説明を受けているか確認する</v>
+        <v/>
       </c>
       <c r="K43" t="str">
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>CPI＝血中Cペプチド(ng/mL)÷血糖値(mg/dL)×100 で算出する。空腹時に測定するのが基本で、境界値付近では食事負荷の影響を受けるため、複数回の評価や随時尿中CPRとあわせて判断することもある</v>
+        <v>黄疸は検査値そのものではなく身体所見。原因を調べる際は総ビリルビン・直接ビリルビン・間接ビリルビンの内訳とAST/ALT/γ-GTPを確認する。直接優位なら胆道系、間接優位なら溶血・体質性を疑う</v>
       </c>
       <c r="M43" t="str">
-        <v>糖尿病</v>
+        <v>肝機能</v>
       </c>
       <c r="N43" t="str">
-        <v>CPI,Cペプチドインデックス,C-ペプチドインデックス,インスリン分泌能,インスリン治療</v>
+        <v>黄疸,ジョンダイス,Jaundice,ビリルビン,皮膚黄染,白目</v>
       </c>
       <c r="O43" t="str">
         <v/>
@@ -2447,122 +2447,122 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>CONUT値</v>
+        <v>甲状腺刺激ホルモン（TSH）</v>
       </c>
       <c r="B44" t="str">
-        <v>CONUT</v>
+        <v>TSH</v>
       </c>
       <c r="C44" t="str">
-        <v>0〜1点：正常、2〜4点：軽度低栄養、5〜8点：中等度低栄養、9〜12点：高度低栄養</v>
+        <v>0.5〜5.0 μIU/mL程度（施設差あり）</v>
       </c>
       <c r="D44" t="str">
-        <v>アルブミン・総リンパ球数・総コレステロールの3項目から算出する栄養状態の評価スコア</v>
+        <v>甲状腺の働きが多いか少ないかを最も敏感に反映するホルモン</v>
       </c>
       <c r="E44" t="str">
-        <v>CONUT値は、血液検査（アルブミン、リンパ球数、コレステロール）の結果から計算される、栄養状態を数値化したスコアです。点数が高いほど低栄養の状態が疑われます。</v>
+        <v>TSHは脳の下垂体から出て、甲状腺に「もっと働いて」と指令を送るホルモンです。甲状腺の働きが弱っていると体が指令を強めるためTSHは上がり、逆に甲状腺が働きすぎているとTSHは下がります。甲状腺の状態を最初に確認する数値としてよく使われます。</v>
       </c>
       <c r="F44" t="str">
-        <v>低栄養状態（点数が高いほど重度）</v>
+        <v>甲状腺機能低下症（橋本病など）、チラーヂンSなど甲状腺ホルモン薬の量不足</v>
       </c>
       <c r="G44" t="str">
-        <v>食事摂取量や体重の変化を確認する。必要に応じて栄養補助食品の活用を提案する</v>
+        <v>だるさ、むくみ、体重増加、寒がりなどの症状がないか確認する。服薬状況（飲み忘れ、他の薬との飲み合わせ）を確認する</v>
       </c>
       <c r="H44" t="str">
-        <v/>
+        <v>アミオダロン、炭酸リチウム、インターフェロン製剤、チロシンキナーゼ阻害薬(スニチニブ等)</v>
       </c>
       <c r="I44" t="str">
-        <v/>
+        <v>甲状腺機能亢進症（バセドウ病など）、チラーヂンSなど甲状腺ホルモン薬の過量</v>
       </c>
       <c r="J44" t="str">
-        <v/>
+        <v>動悸、体重減少、暑がり、手のふるえなどの症状がないか確認する</v>
       </c>
       <c r="K44" t="str">
-        <v/>
+        <v>レボチロキシンの過量投与</v>
       </c>
       <c r="L44" t="str">
-        <v>アルブミン・総リンパ球数・総コレステロールの3項目それぞれに配点があり、合計点で評価する客観的栄養指標。フレイル・サルコペニアの評価やポリファーマシー対策の一環としての栄養状態把握に有用</v>
+        <v>チラーヂンS服用中はTSHが治療目標域に収まっているかで用量調整の目安にする。メルカゾール服用中はTSH・FT4に加えて無顆粒球症の初期症状（発熱・のどの痛み）の有無や白血球数も確認する</v>
       </c>
       <c r="M44" t="str">
-        <v/>
+        <v>甲状腺疾患</v>
       </c>
       <c r="N44" t="str">
-        <v>CONUT,CONUT値,栄養評価,低栄養,フレイル</v>
+        <v>TSH,甲状腺刺激ホルモン,甲状腺機能,橋本病,バセドウ病,チラーヂン,メルカゾール</v>
       </c>
       <c r="O44" t="str">
-        <v>食事と栄養 p.240（フレイルQ108 低栄養や食事量の評価）</v>
+        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>乳び</v>
+        <v>遊離サイロキシン（FT4）</v>
       </c>
       <c r="B45" t="str">
-        <v>乳び,Lipemia</v>
+        <v>FT4</v>
       </c>
       <c r="C45" t="str">
-        <v>所見なし（血清が白濁していなければ正常）</v>
+        <v>0.9〜1.7 ng/dL程度（施設差あり）</v>
       </c>
       <c r="D45" t="str">
-        <v>中性脂肪が非常に多いため、血清が白く濁って見える状態。検査値そのものではなく検体の外観所見</v>
+        <v>甲状腺が実際に分泌しているホルモンの量そのものを表す数値</v>
       </c>
       <c r="E45" t="str">
-        <v>乳びとは、血液中の中性脂肪が非常に多いために、採血した血液（血清）が白く濁って見える状態のことです。多くの場合、食後の採血や、著しい脂質異常症が背景にあります。</v>
+        <v>FT4は甲状腺そのものが作っているホルモンの量です。TSHが「指令の強さ」だとすると、FT4は「実際に出ている量」にあたります。2つをあわせて見ることで、甲状腺の働きが今どういう状態かを詳しく判断できます。</v>
       </c>
       <c r="F45" t="str">
-        <v>著しい高中性脂肪血症、食後採血（一時的なもの）、原発性高カイロミクロン血症などの脂質代謝異常</v>
+        <v>甲状腺機能亢進症（バセドウ病など）</v>
       </c>
       <c r="G45" t="str">
-        <v>採血が空腹時だったかを確認する。食後採血であれば次回は空腹時の再検を提案する</v>
+        <v>動悸、体重減少、暑がり、手のふるえなどの症状がないか確認する</v>
       </c>
       <c r="H45" t="str">
-        <v/>
+        <v>レボチロキシンの過量投与、アミオダロン</v>
       </c>
       <c r="I45" t="str">
-        <v/>
+        <v>甲状腺機能低下症（橋本病など）</v>
       </c>
       <c r="J45" t="str">
-        <v/>
+        <v>だるさ、むくみ、体重増加、寒がりなどの症状がないか確認する</v>
       </c>
       <c r="K45" t="str">
-        <v/>
+        <v>抗甲状腺薬(メルカゾール、プロパジール)の効きすぎ</v>
       </c>
       <c r="L45" t="str">
-        <v>血清の白濁により一部の検査項目（電解質など）の測定値に誤差が出ることがある（偽性低ナトリウム血症など）。中性脂肪値と合わせて評価する</v>
+        <v>TSHと逆方向に動くのが基本だが、下垂体性の異常など例外もある。TSHと合わせて評価し、片方だけで判断しない</v>
       </c>
       <c r="M45" t="str">
-        <v>脂質異常症</v>
+        <v>甲状腺疾患</v>
       </c>
       <c r="N45" t="str">
-        <v>乳び,乳び血清,Lipemia,高中性脂肪血症</v>
+        <v>FT4,遊離サイロキシン,甲状腺ホルモン,甲状腺機能</v>
       </c>
       <c r="O45" t="str">
-        <v/>
+        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>溶血</v>
+        <v>尿蛋白（随時尿）</v>
       </c>
       <c r="B46" t="str">
-        <v>溶血,Hemolysis</v>
+        <v>尿蛋白,U-pro</v>
       </c>
       <c r="C46" t="str">
-        <v>所見なし（溶血を示唆する検査値異常がなければ正常）</v>
+        <v>陰性（－）〜弱陽性</v>
       </c>
       <c r="D46" t="str">
-        <v>赤血球が通常より早く壊れる状態。単独の検査値ではなく、複数の検査値の組み合わせで疑う病態</v>
+        <v>腎臓から本来漏れないはずのたんぱくが尿に出ていないかを見る検査</v>
       </c>
       <c r="E46" t="str">
-        <v>溶血とは、赤血球が通常よりも早いペースで壊れてしまう状態のことです。壊れた赤血球からビリルビンなどが放出されるため、貧血や黄疸の原因になることがあります。</v>
+        <v>この検査は、腎臓のろ過機能に負担がかかっていないかを見るものです。本来、たんぱく質は尿にほとんど出ませんが、腎臓に負担がかかると漏れ出るようになります。</v>
       </c>
       <c r="F46" t="str">
-        <v>自己免疫性溶血性貧血、血液型不適合輸血、G6PD欠損症などの遺伝性疾患、機械弁など人工物による物理的破壊、薬剤性溶血</v>
+        <v>糖尿病性腎症、腎炎、高血圧性腎硬化症、発熱・運動後の一過性のもの</v>
       </c>
       <c r="G46" t="str">
-        <v>倦怠感、黄疸、尿の色が濃くなるなどの症状がないか確認する</v>
+        <v>発熱・激しい運動の直後でないか確認する(一過性のことがある)。持続する場合は塩分の摂りすぎに注意し、むくみの有無もあわせて確認する</v>
       </c>
       <c r="H46" t="str">
-        <v/>
+        <v>NSAIDs、造影剤、アミノグリコシド系、バンコマイシン、金製剤</v>
       </c>
       <c r="I46" t="str">
         <v/>
@@ -2574,13 +2574,13 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>溶血を疑う際は、間接ビリルビン上昇・LDH上昇・ハプトグロビン低下・網状赤血球増加のパターンを確認する。ヘモグロビン・MCV・MCHCの変化と合わせて総合的に判断する</v>
+        <v>発熱・激しい運動・起立性蛋白尿など生理的な要因でも陽性になることがある。持続する場合に腎症の進行を疑う</v>
       </c>
       <c r="M46" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>糖尿病,腎機能</v>
       </c>
       <c r="N46" t="str">
-        <v>溶血,Hemolysis,溶血性貧血,G6PD,ハプトグロビン</v>
+        <v>尿蛋白,U-pro,腎症,たんぱく尿</v>
       </c>
       <c r="O46" t="str">
         <v/>
@@ -2588,31 +2588,31 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>黄疸</v>
+        <v>尿クレアチニン（随時尿）</v>
       </c>
       <c r="B47" t="str">
-        <v>黄疸,Jaundice</v>
+        <v>尿CRE</v>
       </c>
       <c r="C47" t="str">
-        <v>所見なし（皮膚・眼球結膜の黄染がなければ正常）</v>
+        <v>随時尿は主に他項目の濃度補正に利用（単独の基準値は設けにくい）</v>
       </c>
       <c r="D47" t="str">
-        <v>ビリルビンが体にたまり、皮膚や白目が黄色くなる状態。単独の検査値ではなく、ビリルビン上昇によって表れる身体所見</v>
+        <v>随時尿中のクレアチニン濃度。他の尿検査項目を薄まり具合で補正するための基準として使う</v>
       </c>
       <c r="E47" t="str">
-        <v>黄疸は、体の中にビリルビンという黄色い色素がたまることで、皮膚や白目が黄色く見える状態です。肝臓や胆道のトラブル、赤血球が壊れやすくなる病気（溶血）などが原因となります。</v>
+        <v>この数値は、尿がどれくらい薄まっているかを確認するための基準として使われます。他の尿検査の結果（蛋白やアルブミンなど）をこの値で割って補正することで、水分摂取量による影響を減らして正確に評価できます。</v>
       </c>
       <c r="F47" t="str">
-        <v>肝炎・肝硬変などの肝疾患、胆石・腫瘍による胆道閉塞、溶血性疾患、体質性黄疸（ジルベール症候群）、新生児黄疸</v>
+        <v/>
       </c>
       <c r="G47" t="str">
-        <v>白目や皮膚の黄染に気づいたら、尿の色（濃い茶色）や便の色（白っぽい）の変化も確認し、早めの受診を勧める</v>
+        <v/>
       </c>
       <c r="H47" t="str">
         <v/>
       </c>
       <c r="I47" t="str">
-        <v/>
+        <v>尿が薄い（水分摂取が多い、腎機能低下）状態</v>
       </c>
       <c r="J47" t="str">
         <v/>
@@ -2621,13 +2621,13 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>黄疸は検査値そのものではなく身体所見。原因を調べる際は総ビリルビン・直接ビリルビン・間接ビリルビンの内訳とAST/ALT/γ-GTPを確認する。直接優位なら胆道系、間接優位なら溶血・体質性を疑う</v>
+        <v>尿中アルブミン/Cr比、尿蛋白/Cr比など、他項目の補正計算に使われる。単独の高低に臨床的意味は乏しい</v>
       </c>
       <c r="M47" t="str">
-        <v>肝機能</v>
+        <v>腎機能</v>
       </c>
       <c r="N47" t="str">
-        <v>黄疸,ジョンダイス,Jaundice,ビリルビン,皮膚黄染,白目</v>
+        <v>尿CRE,尿クレアチニン,随時尿,補正,蛋白クレアチニン比</v>
       </c>
       <c r="O47" t="str">
         <v/>
@@ -2635,122 +2635,122 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>甲状腺刺激ホルモン（TSH）</v>
+        <v>尿蛋白定量</v>
       </c>
       <c r="B48" t="str">
-        <v>TSH</v>
+        <v>U-Pro定量,蛋白/Cr比</v>
       </c>
       <c r="C48" t="str">
-        <v>0.5〜5.0 μIU/mL程度（施設差あり）</v>
+        <v>0.15 g/gCr未満</v>
       </c>
       <c r="D48" t="str">
-        <v>甲状腺の働きが多いか少ないかを最も敏感に反映するホルモン</v>
+        <v>随時尿から尿蛋白の量を具体的な数値として評価する検査。ネフローゼ等の重症度判定に使う</v>
       </c>
       <c r="E48" t="str">
-        <v>TSHは脳の下垂体から出て、甲状腺に「もっと働いて」と指令を送るホルモンです。甲状腺の働きが弱っていると体が指令を強めるためTSHは上がり、逆に甲状腺が働きすぎているとTSHは下がります。甲状腺の状態を最初に確認する数値としてよく使われます。</v>
+        <v>これは、尿に出ているたんぱくの量を具体的な数値で見る検査です。試験紙での陽性・陰性の判定だけでなく、実際にどれくらいの量が出ているかを把握できます。</v>
       </c>
       <c r="F48" t="str">
-        <v>甲状腺機能低下症（橋本病など）、チラーヂンSなど甲状腺ホルモン薬の量不足</v>
+        <v>腎症の進行（糖尿病性腎症、慢性腎臓病など）、ネフローゼ症候群（3.5 g/gCr以上が目安）</v>
       </c>
       <c r="G48" t="str">
-        <v>だるさ、むくみ、体重増加、寒がりなどの症状がないか確認する。服薬状況（飲み忘れ、他の薬との飲み合わせ）を確認する</v>
+        <v>持続する場合は塩分の摂りすぎに注意し、むくみの有無も確認する。腎臓内科でのフォロー状況もあわせて確認する</v>
       </c>
       <c r="H48" t="str">
-        <v>アミオダロン、炭酸リチウム、インターフェロン製剤、チロシンキナーゼ阻害薬(スニチニブ等)</v>
+        <v>NSAIDs、造影剤、アミノグリコシド系、バンコマイシン</v>
       </c>
       <c r="I48" t="str">
-        <v>甲状腺機能亢進症（バセドウ病など）、チラーヂンSなど甲状腺ホルモン薬の過量</v>
+        <v/>
       </c>
       <c r="J48" t="str">
-        <v>動悸、体重減少、暑がり、手のふるえなどの症状がないか確認する</v>
+        <v/>
       </c>
       <c r="K48" t="str">
-        <v>レボチロキシンの過量投与</v>
+        <v/>
       </c>
       <c r="L48" t="str">
-        <v>チラーヂンS服用中はTSHが治療目標域に収まっているかで用量調整の目安にする。メルカゾール服用中はTSH・FT4に加えて無顆粒球症の初期症状（発熱・のどの痛み）の有無や白血球数も確認する</v>
+        <v>CKD診療ガイドラインの重症度分類（尿蛋白量による区分）にも使われる定量指標。試験紙法の半定量結果より治療効果判定に適する</v>
       </c>
       <c r="M48" t="str">
-        <v>甲状腺疾患</v>
+        <v>腎機能,糖尿病</v>
       </c>
       <c r="N48" t="str">
-        <v>TSH,甲状腺刺激ホルモン,甲状腺機能,橋本病,バセドウ病,チラーヂン,メルカゾール</v>
+        <v>尿蛋白,随時尿,定量,蛋白クレアチニン比,ネフローゼ</v>
       </c>
       <c r="O48" t="str">
-        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
+        <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>遊離サイロキシン（FT4）</v>
+        <v>尿pH</v>
       </c>
       <c r="B49" t="str">
-        <v>FT4</v>
+        <v>尿pH</v>
       </c>
       <c r="C49" t="str">
-        <v>0.9〜1.7 ng/dL程度（施設差あり）</v>
+        <v>4.5〜7.5程度（弱酸性が多い）</v>
       </c>
       <c r="D49" t="str">
-        <v>甲状腺が実際に分泌しているホルモンの量そのものを表す数値</v>
+        <v>尿の酸性・アルカリ性の度合い。食事や感染症、体の状態を反映する</v>
       </c>
       <c r="E49" t="str">
-        <v>FT4は甲状腺そのものが作っているホルモンの量です。TSHが「指令の強さ」だとすると、FT4は「実際に出ている量」にあたります。2つをあわせて見ることで、甲状腺の働きが今どういう状態かを詳しく判断できます。</v>
+        <v>尿のpHは酸性・アルカリ性のバランスを表します。食事の内容や感染症、体の代謝状態によって変化します。単独で大きな問題を示すことは少ない検査です。</v>
       </c>
       <c r="F49" t="str">
-        <v>甲状腺機能亢進症（バセドウ病など）</v>
+        <v>尿路感染症（尿素分解菌によるもの）、野菜中心の食事、過換気</v>
       </c>
       <c r="G49" t="str">
-        <v>動悸、体重減少、暑がり、手のふるえなどの症状がないか確認する</v>
+        <v/>
       </c>
       <c r="H49" t="str">
-        <v>レボチロキシンの過量投与、アミオダロン</v>
+        <v/>
       </c>
       <c r="I49" t="str">
-        <v>甲状腺機能低下症（橋本病など）</v>
+        <v>高たんぱく食、糖尿病性ケトアシドーシス、痛風発作時（酸性尿は尿酸結石のリスクを高める）</v>
       </c>
       <c r="J49" t="str">
-        <v>だるさ、むくみ、体重増加、寒がりなどの症状がないか確認する</v>
+        <v>痛風・尿酸結石がある場合は、野菜など尿をアルカリ化する食品を意識するとよいことを伝える</v>
       </c>
       <c r="K49" t="str">
-        <v>抗甲状腺薬(メルカゾール、プロパジール)の効きすぎ</v>
+        <v/>
       </c>
       <c r="L49" t="str">
-        <v>TSHと逆方向に動くのが基本だが、下垂体性の異常など例外もある。TSHと合わせて評価し、片方だけで判断しない</v>
+        <v>高尿酸血症・尿酸結石の患者では尿pHが酸性に傾いていないか確認する。尿アルカリ化薬（ウラリットなど）の効果判定にも使う</v>
       </c>
       <c r="M49" t="str">
-        <v>甲状腺疾患</v>
+        <v>高尿酸血症</v>
       </c>
       <c r="N49" t="str">
-        <v>FT4,遊離サイロキシン,甲状腺ホルモン,甲状腺機能</v>
+        <v>尿pH,尿酸性度,尿アルカリ化,ウラリット</v>
       </c>
       <c r="O49" t="str">
-        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
+        <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>尿蛋白（随時尿）</v>
+        <v>尿ケトン体</v>
       </c>
       <c r="B50" t="str">
-        <v>尿蛋白,U-pro</v>
+        <v>尿ケトン,Ket</v>
       </c>
       <c r="C50" t="str">
-        <v>陰性（－）〜弱陽性</v>
+        <v>陰性（－）</v>
       </c>
       <c r="D50" t="str">
-        <v>腎臓から本来漏れないはずのたんぱくが尿に出ていないかを見る検査</v>
+        <v>体がブドウ糖の代わりに脂肪を分解してエネルギーを作っているサイン</v>
       </c>
       <c r="E50" t="str">
-        <v>この検査は、腎臓のろ過機能に負担がかかっていないかを見るものです。本来、たんぱく質は尿にほとんど出ませんが、腎臓に負担がかかると漏れ出るようになります。</v>
+        <v>この検査は、体が糖の代わりに脂肪を使ってエネルギーを作っていないかを見るものです。陽性が続くときは、食事や水分、インスリンの使い方を確認する必要があります。</v>
       </c>
       <c r="F50" t="str">
-        <v>糖尿病性腎症、腎炎、高血圧性腎硬化症、発熱・運動後の一過性のもの</v>
+        <v>糖尿病の血糖コントロール不良（シックデイ・インスリン不足）、極端な糖質制限、絶食、嘔吐・下痢による脱水</v>
       </c>
       <c r="G50" t="str">
-        <v>発熱・激しい運動の直後でないか確認する(一過性のことがある)。持続する場合は塩分の摂りすぎに注意し、むくみの有無もあわせて確認する</v>
+        <v>糖尿病治療中の場合はシックデイ時の対応(インスリンを自己中断しない、水分摂取を続けるなど)を確認する。体調不良時の対応方法を事前に説明しておく</v>
       </c>
       <c r="H50" t="str">
-        <v>NSAIDs、造影剤、アミノグリコシド系、バンコマイシン、金製剤</v>
+        <v>SGLT2阻害薬(特に絶食・シックデイ時の正常血糖ケトアシドーシスに注意)</v>
       </c>
       <c r="I50" t="str">
         <v/>
@@ -2762,13 +2762,13 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>発熱・激しい運動・起立性蛋白尿など生理的な要因でも陽性になることがある。持続する場合に腎症の進行を疑う</v>
+        <v>陽性かつ高血糖・全身倦怠感が強い場合は糖尿病性ケトアシドーシスの可能性があり緊急性が高い。シックデイルールの説明歴を確認する</v>
       </c>
       <c r="M50" t="str">
-        <v>糖尿病,腎機能</v>
+        <v>糖尿病</v>
       </c>
       <c r="N50" t="str">
-        <v>尿蛋白,U-pro,腎症,たんぱく尿</v>
+        <v>尿ケトン体,ケトン体,Ket,シックデイ,ケトアシドーシス</v>
       </c>
       <c r="O50" t="str">
         <v/>
@@ -2776,22 +2776,22 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>尿クレアチニン（随時尿）</v>
+        <v>ウロビリノーゲン</v>
       </c>
       <c r="B51" t="str">
-        <v>尿CRE</v>
+        <v>Uro</v>
       </c>
       <c r="C51" t="str">
-        <v>随時尿は主に他項目の濃度補正に利用（単独の基準値は設けにくい）</v>
+        <v>正常（±）程度</v>
       </c>
       <c r="D51" t="str">
-        <v>随時尿中のクレアチニン濃度。他の尿検査項目を薄まり具合で補正するための基準として使う</v>
+        <v>肝臓や胆道、赤血球の壊れ方の状態を反映する尿検査項目</v>
       </c>
       <c r="E51" t="str">
-        <v>この数値は、尿がどれくらい薄まっているかを確認するための基準として使われます。他の尿検査の結果（蛋白やアルブミンなど）をこの値で割って補正することで、水分摂取量による影響を減らして正確に評価できます。</v>
+        <v>ウロビリノーゲンは、赤血球やビリルビンが体の中で処理される過程でできる物質です。肝臓の働きが悪くなったり、赤血球が壊れやすくなったりすると、尿の中の量が変化します。</v>
       </c>
       <c r="F51" t="str">
-        <v/>
+        <v>溶血性疾患（赤血球の破壊亢進）、肝機能障害</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2800,7 +2800,7 @@
         <v/>
       </c>
       <c r="I51" t="str">
-        <v>尿が薄い（水分摂取が多い、腎機能低下）状態</v>
+        <v>胆道閉塞（胆汁が腸に流れず、ウロビリノーゲンが作られない状態）</v>
       </c>
       <c r="J51" t="str">
         <v/>
@@ -2809,13 +2809,13 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>尿中アルブミン/Cr比、尿蛋白/Cr比など、他項目の補正計算に使われる。単独の高低に臨床的意味は乏しい</v>
+        <v>完全に陰性の場合は胆道閉塞を疑う所見の一つ。肝機能（AST/ALT/ビリルビン）と合わせて評価する</v>
       </c>
       <c r="M51" t="str">
-        <v>腎機能</v>
+        <v>肝機能</v>
       </c>
       <c r="N51" t="str">
-        <v>尿CRE,尿クレアチニン,随時尿,補正,蛋白クレアチニン比</v>
+        <v>ウロビリノーゲン,Uro,溶血,胆道閉塞,肝機能</v>
       </c>
       <c r="O51" t="str">
         <v/>
@@ -2823,28 +2823,28 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>尿蛋白定量</v>
+        <v>尿潜血反応</v>
       </c>
       <c r="B52" t="str">
-        <v>U-Pro定量,蛋白/Cr比</v>
+        <v>尿潜血,U-OB</v>
       </c>
       <c r="C52" t="str">
-        <v>0.15 g/gCr未満</v>
+        <v>陰性（－）</v>
       </c>
       <c r="D52" t="str">
-        <v>随時尿から尿蛋白の量を具体的な数値として評価する検査。ネフローゼ等の重症度判定に使う</v>
+        <v>尿に血液（赤血球）が混じっていないかを見る検査</v>
       </c>
       <c r="E52" t="str">
-        <v>これは、尿に出ているたんぱくの量を具体的な数値で見る検査です。試験紙での陽性・陰性の判定だけでなく、実際にどれくらいの量が出ているかを把握できます。</v>
+        <v>この検査は、尿に目に見えないくらいの微量の血液が混じっていないかを調べるものです。陽性の場合、腎臓や膀胱、尿路のどこかに炎症や結石などがある可能性があります。</v>
       </c>
       <c r="F52" t="str">
-        <v>腎症の進行（糖尿病性腎症、慢性腎臓病など）、ネフローゼ症候群（3.5 g/gCr以上が目安）</v>
+        <v>尿路結石、膀胱炎などの尿路感染症、腎炎、腫瘍、月経血の混入、激しい運動後</v>
       </c>
       <c r="G52" t="str">
-        <v>持続する場合は塩分の摂りすぎに注意し、むくみの有無も確認する。腎臓内科でのフォロー状況もあわせて確認する</v>
+        <v>排尿時の痛みや頻尿、目に見える血尿の有無を確認する。女性は月経の時期と重なっていないか確認する</v>
       </c>
       <c r="H52" t="str">
-        <v>NSAIDs、造影剤、アミノグリコシド系、バンコマイシン</v>
+        <v>ワルファリン、DOAC、抗血小板薬など出血傾向を強める薬剤の服用状況を確認</v>
       </c>
       <c r="I52" t="str">
         <v/>
@@ -2856,13 +2856,13 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>CKD診療ガイドラインの重症度分類（尿蛋白量による区分）にも使われる定量指標。試験紙法の半定量結果より治療効果判定に適する</v>
+        <v>陽性でも尿沈渣で赤血球が確認されない場合は偽陽性（ミオグロビン尿など）のこともある。持続する場合は泌尿器科的な精査が必要</v>
       </c>
       <c r="M52" t="str">
-        <v>腎機能,糖尿病</v>
+        <v>腎機能</v>
       </c>
       <c r="N52" t="str">
-        <v>尿蛋白,随時尿,定量,蛋白クレアチニン比,ネフローゼ</v>
+        <v>尿潜血,潜血反応,U-OB,血尿,尿路結石,膀胱炎</v>
       </c>
       <c r="O52" t="str">
         <v/>
@@ -2870,46 +2870,46 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>尿pH</v>
+        <v>尿糖（半定量）</v>
       </c>
       <c r="B53" t="str">
-        <v>尿pH</v>
+        <v>尿糖,U-Glu</v>
       </c>
       <c r="C53" t="str">
-        <v>4.5〜7.5程度（弱酸性が多い）</v>
+        <v>陰性（－）</v>
       </c>
       <c r="D53" t="str">
-        <v>尿の酸性・アルカリ性の度合い。食事や感染症、体の状態を反映する</v>
+        <v>尿に糖が漏れ出ていないかを見る検査。血糖値がかなり高いと陽性になる</v>
       </c>
       <c r="E53" t="str">
-        <v>尿のpHは酸性・アルカリ性のバランスを表します。食事の内容や感染症、体の代謝状態によって変化します。単独で大きな問題を示すことは少ない検査です。</v>
+        <v>通常、糖は尿にはほとんど出ませんが、血糖値がかなり高くなると尿にあふれ出るようになります。血糖コントロールの目安の一つです。</v>
       </c>
       <c r="F53" t="str">
-        <v>尿路感染症（尿素分解菌によるもの）、野菜中心の食事、過換気</v>
+        <v>糖尿病（血糖値が腎臓で再吸収できる量を超えている状態）、腎性糖尿（血糖値が正常でも体質的に出ることがある）、SGLT2阻害薬服用中（薬の作用で意図的に糖を排泄するため陽性になるのが正常）</v>
       </c>
       <c r="G53" t="str">
-        <v/>
+        <v>SGLT2阻害薬（フォシーガ、ジャディアンスなど）服用中は、陽性が薬の効果によるものであることを説明する。脱水や尿路感染の症状がないかも確認する</v>
       </c>
       <c r="H53" t="str">
-        <v/>
+        <v>SGLT2阻害薬(薬理作用による陽性であれば想定内であることを説明)</v>
       </c>
       <c r="I53" t="str">
-        <v>高たんぱく食、糖尿病性ケトアシドーシス、痛風発作時（酸性尿は尿酸結石のリスクを高める）</v>
+        <v/>
       </c>
       <c r="J53" t="str">
-        <v>痛風・尿酸結石がある場合は、野菜など尿をアルカリ化する食品を意識するとよいことを伝える</v>
+        <v/>
       </c>
       <c r="K53" t="str">
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>高尿酸血症・尿酸結石の患者では尿pHが酸性に傾いていないか確認する。尿アルカリ化薬（ウラリットなど）の効果判定にも使う</v>
+        <v>SGLT2阻害薬服用中は尿糖陽性が治療効果として想定内であることを患者に伝える。血糖値・HbA1cと合わせて評価する</v>
       </c>
       <c r="M53" t="str">
-        <v>高尿酸血症</v>
+        <v>糖尿病</v>
       </c>
       <c r="N53" t="str">
-        <v>尿pH,尿酸性度,尿アルカリ化,ウラリット</v>
+        <v>尿糖,糖半定量,U-Glu,腎性糖尿,SGLT2</v>
       </c>
       <c r="O53" t="str">
         <v/>
@@ -2917,28 +2917,28 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>尿ケトン体</v>
+        <v>尿中微量アルブミン</v>
       </c>
       <c r="B54" t="str">
-        <v>尿ケトン,Ket</v>
+        <v>U-Alb,MAU</v>
       </c>
       <c r="C54" t="str">
-        <v>陰性（－）</v>
+        <v>30 mg/gCr未満（尿中アルブミン/クレアチニン比）</v>
       </c>
       <c r="D54" t="str">
-        <v>体がブドウ糖の代わりに脂肪を分解してエネルギーを作っているサイン</v>
+        <v>通常の尿蛋白検査では見つからない、ごく早期の腎症のサイン</v>
       </c>
       <c r="E54" t="str">
-        <v>この検査は、体が糖の代わりに脂肪を使ってエネルギーを作っていないかを見るものです。陽性が続くときは、食事や水分、インスリンの使い方を確認する必要があります。</v>
+        <v>この検査は、通常の尿検査ではまだ分からないくらい早い段階の腎臓の変化を見つけるためのものです。数値が高いと、腎症の初期のサインである可能性があります。</v>
       </c>
       <c r="F54" t="str">
-        <v>糖尿病の血糖コントロール不良（シックデイ・インスリン不足）、極端な糖質制限、絶食、嘔吐・下痢による脱水</v>
+        <v>糖尿病性腎症の早期段階、高血圧</v>
       </c>
       <c r="G54" t="str">
-        <v>糖尿病治療中の場合はシックデイ時の対応(インスリンを自己中断しない、水分摂取を続けるなど)を確認する。体調不良時の対応方法を事前に説明しておく</v>
+        <v>血糖・血圧のコントロール状況を確認する。減塩や適正体重の維持など生活習慣の見直しも早期腎症の進行予防に役立つことを伝える</v>
       </c>
       <c r="H54" t="str">
-        <v>SGLT2阻害薬(特に絶食・シックデイ時の正常血糖ケトアシドーシスに注意)</v>
+        <v>NSAIDsなど腎機能を悪化させる薬剤。ACE阻害薬・ARB・SGLT2阻害薬は低下させる方向に働く</v>
       </c>
       <c r="I54" t="str">
         <v/>
@@ -2950,13 +2950,13 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>陽性かつ高血糖・全身倦怠感が強い場合は糖尿病性ケトアシドーシスの可能性があり緊急性が高い。シックデイルールの説明歴を確認する</v>
+        <v>糖尿病腎症の早期発見に重要な検査。血糖・血圧コントロールで改善しうる段階なので、早期介入の意義を伝える</v>
       </c>
       <c r="M54" t="str">
-        <v>糖尿病</v>
+        <v>糖尿病,腎機能</v>
       </c>
       <c r="N54" t="str">
-        <v>尿ケトン体,ケトン体,Ket,シックデイ,ケトアシドーシス</v>
+        <v>微量アルブミン,U-Alb,MAU,糖尿病性腎症,早期腎症</v>
       </c>
       <c r="O54" t="str">
         <v/>
@@ -2964,31 +2964,31 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ウロビリノーゲン</v>
+        <v>C反応性蛋白（CRP）</v>
       </c>
       <c r="B55" t="str">
-        <v>Uro</v>
+        <v>CRP</v>
       </c>
       <c r="C55" t="str">
-        <v>正常（±）程度</v>
+        <v>0.3 mg/dL未満（施設差あり）</v>
       </c>
       <c r="D55" t="str">
-        <v>肝臓や胆道、赤血球の壊れ方の状態を反映する尿検査項目</v>
+        <v>体のどこかに炎症や感染が起きていないかを鋭敏に反映する数値</v>
       </c>
       <c r="E55" t="str">
-        <v>ウロビリノーゲンは、赤血球やビリルビンが体の中で処理される過程でできる物質です。肝臓の働きが悪くなったり、赤血球が壊れやすくなったりすると、尿の中の量が変化します。</v>
+        <v>CRPは、体に炎症や感染が起きると数時間〜半日程度で急激に上昇する数値です。風邪のようなウイルス感染から細菌感染、体のどこかの炎症まで、幅広く反応するため、体調の変化を早期に捉える手がかりになります。</v>
       </c>
       <c r="F55" t="str">
-        <v>溶血性疾患（赤血球の破壊亢進）、肝機能障害</v>
+        <v>細菌感染症、ウイルス感染症、自己免疫疾患（関節リウマチなど）、悪性腫瘍、組織の損傷（術後・心筋梗塞など）</v>
       </c>
       <c r="G55" t="str">
-        <v/>
+        <v>発熱、痛み、腫れなど炎症症状の有無を確認する</v>
       </c>
       <c r="H55" t="str">
         <v/>
       </c>
       <c r="I55" t="str">
-        <v>胆道閉塞（胆汁が腸に流れず、ウロビリノーゲンが作られない状態）</v>
+        <v/>
       </c>
       <c r="J55" t="str">
         <v/>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>完全に陰性の場合は胆道閉塞を疑う所見の一つ。肝機能（AST/ALT/ビリルビン）と合わせて評価する</v>
+        <v>白血球数と合わせて感染・炎症の程度を評価する。上昇・低下のタイミングは白血球より半日〜1日程度遅れる傾向があるため、経過を追う際は採血のタイミングに注意</v>
       </c>
       <c r="M55" t="str">
-        <v>肝機能</v>
+        <v/>
       </c>
       <c r="N55" t="str">
-        <v>ウロビリノーゲン,Uro,溶血,胆道閉塞,肝機能</v>
+        <v>CRP,炎症,感染</v>
       </c>
       <c r="O55" t="str">
         <v/>
@@ -3011,75 +3011,75 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>尿潜血反応</v>
+        <v>PT-INR（プロトロンビン時間国際標準比）</v>
       </c>
       <c r="B56" t="str">
-        <v>尿潜血,U-OB</v>
+        <v>PT-INR,INR</v>
       </c>
       <c r="C56" t="str">
-        <v>陰性（－）</v>
+        <v>治療域の目安 1.6〜3.0（ワルファリン服用時。年齢・疾患により異なる）</v>
       </c>
       <c r="D56" t="str">
-        <v>尿に血液（赤血球）が混じっていないかを見る検査</v>
+        <v>血液の固まりやすさを表す数値で、ワルファリンの効き具合を確認するために使う</v>
       </c>
       <c r="E56" t="str">
-        <v>この検査は、尿に目に見えないくらいの微量の血液が混じっていないかを調べるものです。陽性の場合、腎臓や膀胱、尿路のどこかに炎症や結石などがある可能性があります。</v>
+        <v>PT-INRは血液が固まるまでの時間をもとにした数値で、ワルファリンというお薬を飲んでいる方の効き具合を確認するために測ります。数値が高いほど血液が固まりにくく出血しやすい状態、低いほど血栓ができやすい状態を示します。</v>
       </c>
       <c r="F56" t="str">
-        <v>尿路結石、膀胱炎などの尿路感染症、腎炎、腫瘍、月経血の混入、激しい運動後</v>
+        <v>ワルファリンの効きすぎ、肝機能低下、ビタミンK不足、納豆・青汁など摂取量の変化</v>
       </c>
       <c r="G56" t="str">
-        <v>排尿時の痛みや頻尿、目に見える血尿の有無を確認する。女性は月経の時期と重なっていないか確認する</v>
+        <v>歯ぐきや鼻からの出血、あざ、黒い便などの出血症状がないか確認する。納豆・クロレラ・青汁などビタミンKを多く含む食品の摂取状況を確認する</v>
       </c>
       <c r="H56" t="str">
-        <v>ワルファリン、DOAC、抗血小板薬など出血傾向を強める薬剤の服用状況を確認</v>
+        <v>ワルファリンの過量。ワルファリン服用中はST合剤・マクロライド系・フルコナゾール等の相互作用やビタミンK摂取量の変化にも注意</v>
       </c>
       <c r="I56" t="str">
-        <v/>
+        <v>ワルファリンの効き不足、飲み忘れ、ビタミンK摂取量の急激な増加</v>
       </c>
       <c r="J56" t="str">
-        <v/>
+        <v>服薬状況（飲み忘れ）を確認する。片側のむくみ・しびれ・胸痛など血栓症状がないか確認する</v>
       </c>
       <c r="K56" t="str">
-        <v/>
+        <v>ワルファリン服用中で低値の場合は効果不十分の可能性。ビタミンK摂取量の変化や、リファンピシン・カルバマゼピン・バルビツール酸系など代謝を促進する薬との併用を確認</v>
       </c>
       <c r="L56" t="str">
-        <v>陽性でも尿沈渣で赤血球が確認されない場合は偽陽性（ミオグロビン尿など）のこともある。持続する場合は泌尿器科的な精査が必要</v>
+        <v>治療域は疾患・年齢によって異なる（例：非弁膜症性心房細動の高齢者では1.6〜2.6が目安になることが多い）。多くの薬剤・食品と相互作用があるため新規薬剤追加時は必ず確認する。DOAC（エリキュース、リクシアナ、プラザキサなど）ではPT-INRのモニタリングは不要</v>
       </c>
       <c r="M56" t="str">
-        <v>腎機能</v>
+        <v>抗凝固療法（心房細動・血栓症）</v>
       </c>
       <c r="N56" t="str">
-        <v>尿潜血,潜血反応,U-OB,血尿,尿路結石,膀胱炎</v>
+        <v>PT-INR,INR,プロトロンビン時間,ワルファリン,ワーファリン,抗凝固</v>
       </c>
       <c r="O56" t="str">
-        <v/>
+        <v>食事と栄養 p.221（心疾患Q93 ワルファリン服用中のビタミンK摂取）</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>尿糖（半定量）</v>
+        <v>骨型酒石酸抵抗性フォスファターゼ（TRACP-5b）</v>
       </c>
       <c r="B57" t="str">
-        <v>尿糖,U-Glu</v>
+        <v>TRACP-5b</v>
       </c>
       <c r="C57" t="str">
-        <v>陰性（－）</v>
+        <v>120〜420 mU/dL</v>
       </c>
       <c r="D57" t="str">
-        <v>尿に糖が漏れ出ていないかを見る検査。血糖値がかなり高いと陽性になる</v>
+        <v>骨がどれくらい壊されているかを見る検査。骨は「古い骨を壊して新しい骨を作る」入れ替えを繰り返しており、骨を壊す細胞が活発だとこの物質が血液中に増える。</v>
       </c>
       <c r="E57" t="str">
-        <v>通常、糖は尿にはほとんど出ませんが、血糖値がかなり高くなると尿にあふれ出るようになります。血糖コントロールの目安の一つです。</v>
+        <v>この検査は、骨がどれくらい早く減っていないかを見るものです。数値が高いと、骨が弱くなりやすい状態の目安になります。</v>
       </c>
       <c r="F57" t="str">
-        <v>糖尿病（血糖値が腎臓で再吸収できる量を超えている状態）、腎性糖尿（血糖値が正常でも体質的に出ることがある）、SGLT2阻害薬服用中（薬の作用で意図的に糖を排泄するため陽性になるのが正常）</v>
+        <v>骨粗鬆症、骨代謝回転（骨がこわれるスピード）が活発な状態</v>
       </c>
       <c r="G57" t="str">
-        <v>SGLT2阻害薬（フォシーガ、ジャディアンスなど）服用中は、陽性が薬の効果によるものであることを説明する。脱水や尿路感染の症状がないかも確認する</v>
+        <v>カルシウム・ビタミンDの摂取や、適度な荷重運動（ウォーキングなど）を意識するよう伝える</v>
       </c>
       <c r="H57" t="str">
-        <v>SGLT2阻害薬(薬理作用による陽性であれば想定内であることを説明)</v>
+        <v/>
       </c>
       <c r="I57" t="str">
         <v/>
@@ -3091,13 +3091,13 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>SGLT2阻害薬服用中は尿糖陽性が治療効果として想定内であることを患者に伝える。血糖値・HbA1cと合わせて評価する</v>
+        <v>「骨を壊す側」の指標。「骨を作る側」の検査と合わせて評価する。数値だけで診断はしない</v>
       </c>
       <c r="M57" t="str">
-        <v>糖尿病</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="N57" t="str">
-        <v>尿糖,糖半定量,U-Glu,腎性糖尿,SGLT2</v>
+        <v>TRACP-5b,骨型酒石酸抵抗性フォスファターゼ,骨粗鬆症,骨代謝</v>
       </c>
       <c r="O57" t="str">
         <v/>
@@ -3105,31 +3105,31 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>尿中微量アルブミン</v>
+        <v>骨型アルカリフォスファターゼ</v>
       </c>
       <c r="B58" t="str">
-        <v>U-Alb,MAU</v>
+        <v>BAP</v>
       </c>
       <c r="C58" t="str">
-        <v>30 mg/gCr未満（尿中アルブミン/クレアチニン比）</v>
+        <v>男性 3.7〜20.9 μg/L、女性（閉経前）2.9〜14.5 μg/L（施設差あり）</v>
       </c>
       <c r="D58" t="str">
-        <v>通常の尿蛋白検査では見つからない、ごく早期の腎症のサイン</v>
+        <v>ALPのうち骨に由来する成分だけを測定し、骨が作られる勢い（骨形成）を反映する</v>
       </c>
       <c r="E58" t="str">
-        <v>この検査は、通常の尿検査ではまだ分からないくらい早い段階の腎臓の変化を見つけるためのものです。数値が高いと、腎症の初期のサインである可能性があります。</v>
+        <v>骨型ALPは、通常のALP（アルカリフォスファターゼ）の中でも、骨で作られる成分だけを選んで測定するものです。骨を新しく作る働きがどれくらい活発かを見る指標として、骨粗鬆症の治療効果判定などに使われます。</v>
       </c>
       <c r="F58" t="str">
-        <v>糖尿病性腎症の早期段階、高血圧</v>
+        <v>骨代謝回転の亢進（骨粗鬆症、骨折治癒過程、骨形成促進薬による治療効果、Paget病、骨転移）</v>
       </c>
       <c r="G58" t="str">
-        <v>血糖・血圧のコントロール状況を確認する。減塩や適正体重の維持など生活習慣の見直しも早期腎症の進行予防に役立つことを伝える</v>
+        <v/>
       </c>
       <c r="H58" t="str">
-        <v>NSAIDsなど腎機能を悪化させる薬剤。ACE阻害薬・ARB・SGLT2阻害薬は低下させる方向に働く</v>
+        <v/>
       </c>
       <c r="I58" t="str">
-        <v/>
+        <v>骨形成の低下</v>
       </c>
       <c r="J58" t="str">
         <v/>
@@ -3138,13 +3138,13 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>糖尿病腎症の早期発見に重要な検査。血糖・血圧コントロールで改善しうる段階なので、早期介入の意義を伝える</v>
+        <v>通常のALPと異なり肝臓の影響を受けにくいため、肝機能異常がある患者でも骨代謝を評価しやすい。P1NPと同じ「骨を作る側」の指標で、骨形成促進薬（テリパラチド等）の効果判定に使われる</v>
       </c>
       <c r="M58" t="str">
-        <v>糖尿病,腎機能</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="N58" t="str">
-        <v>微量アルブミン,U-Alb,MAU,糖尿病性腎症,早期腎症</v>
+        <v>骨型ALP,BAP,骨型アルカリフォスファターゼ,骨形成マーカー</v>
       </c>
       <c r="O58" t="str">
         <v/>
@@ -3152,125 +3152,125 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>C反応性蛋白（CRP）</v>
+        <v>25-ヒドロキシビタミンD</v>
       </c>
       <c r="B59" t="str">
-        <v>CRP</v>
+        <v>25(OH)D</v>
       </c>
       <c r="C59" t="str">
-        <v>0.3 mg/dL未満（施設差あり）</v>
+        <v>30 ng/mL以上：充足、20〜30 ng/mL：不足、20 ng/mL未満：欠乏（施設差あり）</v>
       </c>
       <c r="D59" t="str">
-        <v>体のどこかに炎症や感染が起きていないかを鋭敏に反映する数値</v>
+        <v>体内のビタミンDの蓄え具合を反映する指標。カルシウムの吸収や骨の健康に関わる</v>
       </c>
       <c r="E59" t="str">
-        <v>CRPは、体に炎症や感染が起きると数時間〜半日程度で急激に上昇する数値です。風邪のようなウイルス感染から細菌感染、体のどこかの炎症まで、幅広く反応するため、体調の変化を早期に捉える手がかりになります。</v>
+        <v>この検査は、体の中にビタミンDがどれくらい蓄えられているかを見るものです。ビタミンDは、食事から摂ったカルシウムを腸で吸収するのを助ける働きがあり、不足すると骨がもろくなりやすくなります。</v>
       </c>
       <c r="F59" t="str">
-        <v>細菌感染症、ウイルス感染症、自己免疫疾患（関節リウマチなど）、悪性腫瘍、組織の損傷（術後・心筋梗塞など）</v>
+        <v>ビタミンD製剤の過剰摂取</v>
       </c>
       <c r="G59" t="str">
-        <v>発熱、痛み、腫れなど炎症症状の有無を確認する</v>
+        <v>活性型ビタミンD3製剤やサプリメントの摂取量を確認する。高カルシウム血症の症状（吐き気、便秘、多尿など）がないか確認する</v>
       </c>
       <c r="H59" t="str">
-        <v/>
+        <v>活性型/天然型ビタミンD製剤の過量投与</v>
       </c>
       <c r="I59" t="str">
-        <v/>
+        <v>日光暴露不足、食事摂取不足、高齢、腸疾患による吸収不良、肝・腎機能低下（活性化障害）</v>
       </c>
       <c r="J59" t="str">
-        <v/>
+        <v>適度な日光浴、魚類・きのこ類などビタミンDを多く含む食品の摂取を意識するとよいことを伝える</v>
       </c>
       <c r="K59" t="str">
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>白血球数と合わせて感染・炎症の程度を評価する。上昇・低下のタイミングは白血球より半日〜1日程度遅れる傾向があるため、経過を追う際は採血のタイミングに注意</v>
+        <v>骨粗鬆症治療における活性型ビタミンD3製剤の効果判定や、投与量調整の参考に用いられる。腎機能低下患者では活性化障害により25(OH)Dが正常でも活性型が不足することがある点に注意</v>
       </c>
       <c r="M59" t="str">
-        <v/>
+        <v>骨粗鬆症</v>
       </c>
       <c r="N59" t="str">
-        <v>CRP,炎症,感染</v>
+        <v>25(OH)D,ビタミンD,25-ヒドロキシビタミンD,ビタミンD欠乏,骨粗鬆症</v>
       </c>
       <c r="O59" t="str">
-        <v/>
+        <v>食事と栄養 p.38（ビタミンD）</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>PT-INR（プロトロンビン時間国際標準比）</v>
+        <v>ucOC（低カルボキシル化オステオカルシン）</v>
       </c>
       <c r="B60" t="str">
-        <v>PT-INR,INR</v>
+        <v>ucOC</v>
       </c>
       <c r="C60" t="str">
-        <v>治療域の目安 1.6〜3.0（ワルファリン服用時。年齢・疾患により異なる）</v>
+        <v>4.5 ng/mL未満（施設差あり）</v>
       </c>
       <c r="D60" t="str">
-        <v>血液の固まりやすさを表す数値で、ワルファリンの効き具合を確認するために使う</v>
+        <v>ビタミンKが不足していないかを反映する骨の指標</v>
       </c>
       <c r="E60" t="str">
-        <v>PT-INRは血液が固まるまでの時間をもとにした数値で、ワルファリンというお薬を飲んでいる方の効き具合を確認するために測ります。数値が高いほど血液が固まりにくく出血しやすい状態、低いほど血栓ができやすい状態を示します。</v>
+        <v>ucOCは、骨を作るために必要なビタミンKが体の中で足りているかどうかを反映する検査です。数値が高いとビタミンK不足が疑われます。</v>
       </c>
       <c r="F60" t="str">
-        <v>ワルファリンの効きすぎ、肝機能低下、ビタミンK不足、納豆・青汁など摂取量の変化</v>
+        <v>ビタミンK不足状態</v>
       </c>
       <c r="G60" t="str">
-        <v>歯ぐきや鼻からの出血、あざ、黒い便などの出血症状がないか確認する。納豆・クロレラ・青汁などビタミンKを多く含む食品の摂取状況を確認する</v>
+        <v>ビタミンK2製剤(骨粗鬆症治療薬)の適応が検討されているか確認する。ワルファリン服用中の患者では、納豆などビタミンKを多く含む食品の急な摂取量の変化を避けるよう説明する</v>
       </c>
       <c r="H60" t="str">
-        <v>ワルファリンの過量。ワルファリン服用中はST合剤・マクロライド系・フルコナゾール等の相互作用やビタミンK摂取量の変化にも注意</v>
+        <v/>
       </c>
       <c r="I60" t="str">
-        <v>ワルファリンの効き不足、飲み忘れ、ビタミンK摂取量の急激な増加</v>
+        <v/>
       </c>
       <c r="J60" t="str">
-        <v>服薬状況（飲み忘れ）を確認する。片側のむくみ・しびれ・胸痛など血栓症状がないか確認する</v>
+        <v/>
       </c>
       <c r="K60" t="str">
-        <v>ワルファリン服用中で低値の場合は効果不十分の可能性。ビタミンK摂取量の変化や、リファンピシン・カルバマゼピン・バルビツール酸系など代謝を促進する薬との併用を確認</v>
+        <v/>
       </c>
       <c r="L60" t="str">
-        <v>治療域は疾患・年齢によって異なる（例：非弁膜症性心房細動の高齢者では1.6〜2.6が目安になることが多い）。多くの薬剤・食品と相互作用があるため新規薬剤追加時は必ず確認する。DOAC（エリキュース、リクシアナ、プラザキサなど）ではPT-INRのモニタリングは不要</v>
+        <v>ビタミンK2製剤（骨粗鬆症治療薬）の適応判断や効果判定に使われる</v>
       </c>
       <c r="M60" t="str">
-        <v>抗凝固療法（心房細動・血栓症）</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="N60" t="str">
-        <v>PT-INR,INR,プロトロンビン時間,ワルファリン,ワーファリン,抗凝固</v>
+        <v>ucOC,オステオカルシン,ビタミンK</v>
       </c>
       <c r="O60" t="str">
-        <v>食事と栄養 p.221（心疾患Q93 ワルファリン服用中のビタミンK摂取）</v>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>骨型酒石酸抵抗性フォスファターゼ（TRACP-5b）</v>
+        <v>PTH（副甲状腺ホルモン）</v>
       </c>
       <c r="B61" t="str">
-        <v>TRACP-5b</v>
+        <v>PTH</v>
       </c>
       <c r="C61" t="str">
-        <v>120〜420 mU/dL</v>
+        <v>10〜65 pg/mL（施設差あり）</v>
       </c>
       <c r="D61" t="str">
-        <v>骨がどれくらい壊されているかを見る検査。骨は「古い骨を壊して新しい骨を作る」入れ替えを繰り返しており、骨を壊す細胞が活発だとこの物質が血液中に増える。</v>
+        <v>血液中のカルシウム濃度を調節するホルモン</v>
       </c>
       <c r="E61" t="str">
-        <v>この検査は、骨がどれくらい早く減っていないかを見るものです。数値が高いと、骨が弱くなりやすい状態の目安になります。</v>
+        <v>PTHは、血液中のカルシウム濃度を一定に保つために働くホルモンです。カルシウムが低くなると分泌が増え、骨からカルシウムを取り出したり、腎臓での再吸収を促したりして数値を戻そうとします。</v>
       </c>
       <c r="F61" t="str">
-        <v>骨粗鬆症、骨代謝回転（骨がこわれるスピード）が活発な状態</v>
+        <v>原発性・二次性副甲状腺機能亢進症（腎不全に伴うものなど）</v>
       </c>
       <c r="G61" t="str">
-        <v>カルシウム・ビタミンDの摂取や、適度な荷重運動（ウォーキングなど）を意識するよう伝える</v>
+        <v/>
       </c>
       <c r="H61" t="str">
         <v/>
       </c>
       <c r="I61" t="str">
-        <v/>
+        <v>副甲状腺機能低下症</v>
       </c>
       <c r="J61" t="str">
         <v/>
@@ -3279,36 +3279,36 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>「骨を壊す側」の指標。「骨を作る側」の検査と合わせて評価する。数値だけで診断はしない</v>
+        <v>骨粗鬆症の二次性原因（副甲状腺機能亢進症）を除外するための検査。カルシウム・リンと合わせて評価する</v>
       </c>
       <c r="M61" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="N61" t="str">
-        <v>TRACP-5b,骨型酒石酸抵抗性フォスファターゼ,骨粗鬆症,骨代謝</v>
+        <v>PTH,副甲状腺ホルモン,パラトルモン</v>
       </c>
       <c r="O61" t="str">
-        <v/>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>骨型アルカリフォスファターゼ</v>
+        <v>尿中NTX</v>
       </c>
       <c r="B62" t="str">
-        <v>BAP</v>
+        <v>NTX</v>
       </c>
       <c r="C62" t="str">
-        <v>男性 3.7〜20.9 μg/L、女性（閉経前）2.9〜14.5 μg/L（施設差あり）</v>
+        <v>施設差が大きく一律の記載が難しい（尿中）</v>
       </c>
       <c r="D62" t="str">
-        <v>ALPのうち骨に由来する成分だけを測定し、骨が作られる勢い（骨形成）を反映する</v>
+        <v>骨が壊されるときに出る、骨吸収マーカーのひとつ</v>
       </c>
       <c r="E62" t="str">
-        <v>骨型ALPは、通常のALP（アルカリフォスファターゼ）の中でも、骨で作られる成分だけを選んで測定するものです。骨を新しく作る働きがどれくらい活発かを見る指標として、骨粗鬆症の治療効果判定などに使われます。</v>
+        <v>NTXは、骨が壊される（吸収される）ときに尿の中に出てくる物質です。骨粗鬆症の治療薬がどれくらい効いているかを確認するために使われます。</v>
       </c>
       <c r="F62" t="str">
-        <v>骨代謝回転の亢進（骨粗鬆症、骨折治癒過程、骨形成促進薬による治療効果、Paget病、骨転移）</v>
+        <v>骨代謝回転の亢進（骨粗鬆症、閉経後など）</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -3317,7 +3317,7 @@
         <v/>
       </c>
       <c r="I62" t="str">
-        <v>骨形成の低下</v>
+        <v>骨吸収抑制薬（ビスホスホネート等）による治療効果</v>
       </c>
       <c r="J62" t="str">
         <v/>
@@ -3326,92 +3326,92 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>通常のALPと異なり肝臓の影響を受けにくいため、肝機能異常がある患者でも骨代謝を評価しやすい。P1NPと同じ「骨を作る側」の指標で、骨形成促進薬（テリパラチド等）の効果判定に使われる</v>
+        <v>治療開始後3〜6か月で再検し、薬の効果判定に使われる。TRACP-5bと同じ「骨を壊す側」の指標</v>
       </c>
       <c r="M62" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="N62" t="str">
-        <v>骨型ALP,BAP,骨型アルカリフォスファターゼ,骨形成マーカー</v>
+        <v>NTX,尿中NTX,骨吸収マーカー</v>
       </c>
       <c r="O62" t="str">
-        <v/>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>25-ヒドロキシビタミンD</v>
+        <v>カルシトニン</v>
       </c>
       <c r="B63" t="str">
-        <v>25(OH)D</v>
+        <v>CT</v>
       </c>
       <c r="C63" t="str">
-        <v>30 ng/mL以上：充足、20〜30 ng/mL：不足、20 ng/mL未満：欠乏（施設差あり）</v>
+        <v>男性 9.52 pg/mL未満、女性 6.40 pg/mL未満（施設差あり）</v>
       </c>
       <c r="D63" t="str">
-        <v>体内のビタミンDの蓄え具合を反映する指標。カルシウムの吸収や骨の健康に関わる</v>
+        <v>血液中のカルシウムを下げる方向に働くホルモン</v>
       </c>
       <c r="E63" t="str">
-        <v>この検査は、体の中にビタミンDがどれくらい蓄えられているかを見るものです。ビタミンDは、食事から摂ったカルシウムを腸で吸収するのを助ける働きがあり、不足すると骨がもろくなりやすくなります。</v>
+        <v>カルシトニンは、PTHとは逆に血液中のカルシウムを下げる方向に働くホルモンです。特定の甲状腺の病気（甲状腺髄様癌）がないかを調べる際にも使われます。</v>
       </c>
       <c r="F63" t="str">
-        <v>ビタミンD製剤の過剰摂取</v>
+        <v>甲状腺髄様癌、腎不全</v>
       </c>
       <c r="G63" t="str">
-        <v>活性型ビタミンD3製剤やサプリメントの摂取量を確認する。高カルシウム血症の症状（吐き気、便秘、多尿など）がないか確認する</v>
+        <v/>
       </c>
       <c r="H63" t="str">
-        <v>活性型/天然型ビタミンD製剤の過量投与</v>
+        <v/>
       </c>
       <c r="I63" t="str">
-        <v>日光暴露不足、食事摂取不足、高齢、腸疾患による吸収不良、肝・腎機能低下（活性化障害）</v>
+        <v/>
       </c>
       <c r="J63" t="str">
-        <v>適度な日光浴、魚類・きのこ類などビタミンDを多く含む食品の摂取を意識するとよいことを伝える</v>
+        <v/>
       </c>
       <c r="K63" t="str">
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>骨粗鬆症治療における活性型ビタミンD3製剤の効果判定や、投与量調整の参考に用いられる。腎機能低下患者では活性化障害により25(OH)Dが正常でも活性型が不足することがある点に注意</v>
+        <v>骨粗鬆症の二次性原因の除外目的で測定されることがある検査値。同名の薬剤（カルシトニン製剤）と混同しないよう注意</v>
       </c>
       <c r="M63" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="N63" t="str">
-        <v>25(OH)D,ビタミンD,25-ヒドロキシビタミンD,ビタミンD欠乏,骨粗鬆症</v>
+        <v>カルシトニン,CT</v>
       </c>
       <c r="O63" t="str">
-        <v>食事と栄養 p.38（ビタミンD）</v>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>ucOC（低カルボキシル化オステオカルシン）</v>
+        <v>DPD（デオキシピリジノリン）</v>
       </c>
       <c r="B64" t="str">
-        <v>ucOC</v>
+        <v>DPD</v>
       </c>
       <c r="C64" t="str">
-        <v>4.5 ng/mL未満（施設差あり）</v>
+        <v>施設差が大きく一律の記載が難しい（尿中）</v>
       </c>
       <c r="D64" t="str">
-        <v>ビタミンKが不足していないかを反映する骨の指標</v>
+        <v>骨のコラーゲンが壊れるときに出る、骨吸収マーカーのひとつ</v>
       </c>
       <c r="E64" t="str">
-        <v>ucOCは、骨を作るために必要なビタミンKが体の中で足りているかどうかを反映する検査です。数値が高いとビタミンK不足が疑われます。</v>
+        <v>DPDも、骨が壊されるときに尿に出てくる物質の一つです。NTXと同じように、骨粗鬆症治療薬の効果を確認するために使われます。</v>
       </c>
       <c r="F64" t="str">
-        <v>ビタミンK不足状態</v>
+        <v>骨代謝回転の亢進（骨粗鬆症など）</v>
       </c>
       <c r="G64" t="str">
-        <v>ビタミンK2製剤(骨粗鬆症治療薬)の適応が検討されているか確認する。ワルファリン服用中の患者では、納豆などビタミンKを多く含む食品の急な摂取量の変化を避けるよう説明する</v>
+        <v/>
       </c>
       <c r="H64" t="str">
         <v/>
       </c>
       <c r="I64" t="str">
-        <v/>
+        <v>骨吸収抑制薬による治療効果</v>
       </c>
       <c r="J64" t="str">
         <v/>
@@ -3420,13 +3420,13 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>ビタミンK2製剤（骨粗鬆症治療薬）の適応判断や効果判定に使われる</v>
+        <v>NTX・CTXと同じ「骨を壊す側」の指標。食事の影響を受けにくいとされる</v>
       </c>
       <c r="M64" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="N64" t="str">
-        <v>ucOC,オステオカルシン,ビタミンK</v>
+        <v>DPD,デオキシピリジノリン,骨吸収マーカー</v>
       </c>
       <c r="O64" t="str">
         <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
@@ -3434,22 +3434,22 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>PTH（副甲状腺ホルモン）</v>
+        <v>CTX</v>
       </c>
       <c r="B65" t="str">
-        <v>PTH</v>
+        <v>CTX</v>
       </c>
       <c r="C65" t="str">
-        <v>10〜65 pg/mL（施設差あり）</v>
+        <v>施設差が大きく一律の記載が難しい（血清・尿中）</v>
       </c>
       <c r="D65" t="str">
-        <v>血液中のカルシウム濃度を調節するホルモン</v>
+        <v>骨のコラーゲンが壊れるときに出る、骨吸収マーカーのひとつ</v>
       </c>
       <c r="E65" t="str">
-        <v>PTHは、血液中のカルシウム濃度を一定に保つために働くホルモンです。カルシウムが低くなると分泌が増え、骨からカルシウムを取り出したり、腎臓での再吸収を促したりして数値を戻そうとします。</v>
+        <v>CTXも、骨が壊されるときに血液や尿に出てくる物質です。骨粗鬆症治療薬（骨を壊すのを抑える薬）の効果を確認するために使われます。</v>
       </c>
       <c r="F65" t="str">
-        <v>原発性・二次性副甲状腺機能亢進症（腎不全に伴うものなど）</v>
+        <v>骨代謝回転の亢進（骨粗鬆症など）</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -3458,7 +3458,7 @@
         <v/>
       </c>
       <c r="I65" t="str">
-        <v>副甲状腺機能低下症</v>
+        <v>骨吸収抑制薬による治療効果</v>
       </c>
       <c r="J65" t="str">
         <v/>
@@ -3467,13 +3467,13 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>骨粗鬆症の二次性原因（副甲状腺機能亢進症）を除外するための検査。カルシウム・リンと合わせて評価する</v>
+        <v>NTX・DPDと同じ「骨を壊す側」の指標。血清・尿中いずれでも測定されることがある</v>
       </c>
       <c r="M65" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="N65" t="str">
-        <v>PTH,副甲状腺ホルモン,パラトルモン</v>
+        <v>CTX,骨吸収マーカー</v>
       </c>
       <c r="O65" t="str">
         <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
@@ -3481,22 +3481,22 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>尿中NTX</v>
+        <v>P1NP</v>
       </c>
       <c r="B66" t="str">
-        <v>NTX</v>
+        <v>P1NP</v>
       </c>
       <c r="C66" t="str">
-        <v>施設差が大きく一律の記載が難しい（尿中）</v>
+        <v>施設差が大きく一律の記載が難しい（血清）</v>
       </c>
       <c r="D66" t="str">
-        <v>骨が壊されるときに出る、骨吸収マーカーのひとつ</v>
+        <v>骨が新しく作られるときに出る、骨形成マーカーのひとつ</v>
       </c>
       <c r="E66" t="str">
-        <v>NTXは、骨が壊される（吸収される）ときに尿の中に出てくる物質です。骨粗鬆症の治療薬がどれくらい効いているかを確認するために使われます。</v>
+        <v>P1NPは、CTXなどとは逆に、骨が新しく作られるときに血液中に出てくる物質です。骨を作る力を高める薬（テリパラチドなど）の効果を確認するために使われます。</v>
       </c>
       <c r="F66" t="str">
-        <v>骨代謝回転の亢進（骨粗鬆症、閉経後など）</v>
+        <v>骨代謝回転の亢進、骨形成促進薬による治療効果</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -3505,7 +3505,7 @@
         <v/>
       </c>
       <c r="I66" t="str">
-        <v>骨吸収抑制薬（ビスホスホネート等）による治療効果</v>
+        <v>骨形成の低下</v>
       </c>
       <c r="J66" t="str">
         <v/>
@@ -3514,13 +3514,13 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>治療開始後3〜6か月で再検し、薬の効果判定に使われる。TRACP-5bと同じ「骨を壊す側」の指標</v>
+        <v>TRACP-5b等「骨を壊す側」の指標とは逆の、「骨を作る側」の指標。骨形成促進薬（テリパラチド等）の効果判定に使われる</v>
       </c>
       <c r="M66" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="N66" t="str">
-        <v>NTX,尿中NTX,骨吸収マーカー</v>
+        <v>P1NP,骨形成マーカー</v>
       </c>
       <c r="O66" t="str">
         <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
@@ -3528,69 +3528,69 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>カルシトニン</v>
+        <v>血清鉄（Fe）</v>
       </c>
       <c r="B67" t="str">
-        <v>CT</v>
+        <v>Fe</v>
       </c>
       <c r="C67" t="str">
-        <v>男性 9.52 pg/mL未満、女性 6.40 pg/mL未満（施設差あり）</v>
+        <v>60〜200 μg/dL（施設差あり）</v>
       </c>
       <c r="D67" t="str">
-        <v>血液中のカルシウムを下げる方向に働くホルモン</v>
+        <v>血液中を流れている鉄の量</v>
       </c>
       <c r="E67" t="str">
-        <v>カルシトニンは、PTHとは逆に血液中のカルシウムを下げる方向に働くホルモンです。特定の甲状腺の病気（甲状腺髄様癌）がないかを調べる際にも使われます。</v>
+        <v>この検査は、今血液の中を流れている鉄の量を見るものです。低いと、体の中で鉄が不足している可能性があります。</v>
       </c>
       <c r="F67" t="str">
-        <v>甲状腺髄様癌、腎不全</v>
+        <v>鉄剤の過剰摂取、溶血、肝疾患</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v/>
+        <v>鉄剤の過量摂取(小児の誤飲を含む)</v>
       </c>
       <c r="I67" t="str">
-        <v/>
+        <v>鉄欠乏性貧血、慢性炎症、出血</v>
       </c>
       <c r="J67" t="str">
-        <v/>
+        <v>鉄分の多い食品（レバー・赤身肉・魚・ほうれん草など）を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える</v>
       </c>
       <c r="K67" t="str">
-        <v/>
+        <v>プロトンポンプ阻害薬(PPI)・H2ブロッカーは胃酸分泌抑制により鉄の吸収を低下させうる</v>
       </c>
       <c r="L67" t="str">
-        <v>骨粗鬆症の二次性原因の除外目的で測定されることがある検査値。同名の薬剤（カルシトニン製剤）と混同しないよう注意</v>
+        <v>血清鉄は日内変動が大きい。単独で判断せず総鉄結合能・フェリチンと合わせて評価する</v>
       </c>
       <c r="M67" t="str">
-        <v>骨粗鬆症</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="N67" t="str">
-        <v>カルシトニン,CT</v>
+        <v>血清鉄,Fe,鉄欠乏性貧血</v>
       </c>
       <c r="O67" t="str">
-        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
+        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>DPD（デオキシピリジノリン）</v>
+        <v>総鉄結合能（TIBC）</v>
       </c>
       <c r="B68" t="str">
-        <v>DPD</v>
+        <v>TIBC</v>
       </c>
       <c r="C68" t="str">
-        <v>施設差が大きく一律の記載が難しい（尿中）</v>
+        <v>250〜360 μg/dL（施設差あり）</v>
       </c>
       <c r="D68" t="str">
-        <v>骨のコラーゲンが壊れるときに出る、骨吸収マーカーのひとつ</v>
+        <v>血液中のトランスフェリンが鉄と結合できる総量</v>
       </c>
       <c r="E68" t="str">
-        <v>DPDも、骨が壊されるときに尿に出てくる物質の一つです。NTXと同じように、骨粗鬆症治療薬の効果を確認するために使われます。</v>
+        <v>TIBCは、血液中でトランスフェリンという物質が鉄を運べる最大量を表します。体の中の鉄が不足すると、少しでも多く鉄を運ぼうとしてこの数値が上がる性質があります。</v>
       </c>
       <c r="F68" t="str">
-        <v>骨代謝回転の亢進（骨粗鬆症など）</v>
+        <v>鉄欠乏性貧血（＞360 μg/dLが目安）</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v/>
       </c>
       <c r="I68" t="str">
-        <v>骨吸収抑制薬による治療効果</v>
+        <v>慢性炎症、肝疾患、ネフローゼ症候群</v>
       </c>
       <c r="J68" t="str">
         <v/>
@@ -3608,36 +3608,36 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>NTX・CTXと同じ「骨を壊す側」の指標。食事の影響を受けにくいとされる</v>
+        <v>鉄が不足すると、体はより多く運ぼうとしてTIBCが上昇する。UIBC・血清鉄と併せて評価する</v>
       </c>
       <c r="M68" t="str">
-        <v>骨粗鬆症</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="N68" t="str">
-        <v>DPD,デオキシピリジノリン,骨吸収マーカー</v>
+        <v>TIBC,総鉄結合能,鉄欠乏性貧血</v>
       </c>
       <c r="O68" t="str">
-        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
+        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>CTX</v>
+        <v>不飽和鉄結合能（UIBC）</v>
       </c>
       <c r="B69" t="str">
-        <v>CTX</v>
+        <v>UIBC</v>
       </c>
       <c r="C69" t="str">
-        <v>施設差が大きく一律の記載が難しい（血清・尿中）</v>
+        <v>170〜300 μg/dL（施設差あり）</v>
       </c>
       <c r="D69" t="str">
-        <v>骨のコラーゲンが壊れるときに出る、骨吸収マーカーのひとつ</v>
+        <v>トランスフェリンのうち、まだ鉄と結合していない余力の部分（UIBC＝TIBC－血清鉄）</v>
       </c>
       <c r="E69" t="str">
-        <v>CTXも、骨が壊されるときに血液や尿に出てくる物質です。骨粗鬆症治療薬（骨を壊すのを抑える薬）の効果を確認するために使われます。</v>
+        <v>UIBCは、トランスフェリンのうち、まだ鉄と結合していない「空き容量」の部分を表します。鉄が不足しているときほど、この空き容量は大きくなります。</v>
       </c>
       <c r="F69" t="str">
-        <v>骨代謝回転の亢進（骨粗鬆症など）</v>
+        <v>鉄欠乏性貧血（＞300 μg/dLが目安）</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3646,7 +3646,7 @@
         <v/>
       </c>
       <c r="I69" t="str">
-        <v>骨吸収抑制薬による治療効果</v>
+        <v>慢性炎症、鉄過剰状態</v>
       </c>
       <c r="J69" t="str">
         <v/>
@@ -3655,36 +3655,36 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>NTX・DPDと同じ「骨を壊す側」の指標。血清・尿中いずれでも測定されることがある</v>
+        <v>TIBCと同じ方向に動くことが多い。血清鉄・TIBCとあわせて鉄欠乏性貧血と二次性貧血の鑑別に使う</v>
       </c>
       <c r="M69" t="str">
-        <v>骨粗鬆症</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="N69" t="str">
-        <v>CTX,骨吸収マーカー</v>
+        <v>UIBC,不飽和鉄結合能,鉄欠乏性貧血</v>
       </c>
       <c r="O69" t="str">
-        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
+        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>P1NP</v>
+        <v>トランスフェリン飽和度</v>
       </c>
       <c r="B70" t="str">
-        <v>P1NP</v>
+        <v>TSAT</v>
       </c>
       <c r="C70" t="str">
-        <v>施設差が大きく一律の記載が難しい（血清）</v>
+        <v>16〜50%程度（施設差あり）</v>
       </c>
       <c r="D70" t="str">
-        <v>骨が新しく作られるときに出る、骨形成マーカーのひとつ</v>
+        <v>鉄を運ぶ役割のトランスフェリンのうち、実際に鉄を運んでいる割合（血清鉄÷総鉄結合能）</v>
       </c>
       <c r="E70" t="str">
-        <v>P1NPは、CTXなどとは逆に、骨が新しく作られるときに血液中に出てくる物質です。骨を作る力を高める薬（テリパラチドなど）の効果を確認するために使われます。</v>
+        <v>トランスフェリン飽和度は、鉄を運ぶトランスフェリンのうち、実際にどれくらいが鉄を運んでいるかを割合で表したものです。鉄欠乏性貧血では低くなり、鉄が過剰にたまる病気では高くなります。</v>
       </c>
       <c r="F70" t="str">
-        <v>骨代謝回転の亢進、骨形成促進薬による治療効果</v>
+        <v>鉄過剰症（ヘモクロマトーシスなど）</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3693,7 +3693,7 @@
         <v/>
       </c>
       <c r="I70" t="str">
-        <v>骨形成の低下</v>
+        <v>鉄欠乏性貧血（＜16%が目安）</v>
       </c>
       <c r="J70" t="str">
         <v/>
@@ -3702,60 +3702,60 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>TRACP-5b等「骨を壊す側」の指標とは逆の、「骨を作る側」の指標。骨形成促進薬（テリパラチド等）の効果判定に使われる</v>
+        <v>血清鉄をTIBCで割って計算される。鉄剤補充の効果判定にも使われる</v>
       </c>
       <c r="M70" t="str">
-        <v>骨粗鬆症</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="N70" t="str">
-        <v>P1NP,骨形成マーカー</v>
+        <v>トランスフェリン飽和度,TSAT,鉄欠乏性貧血</v>
       </c>
       <c r="O70" t="str">
-        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
+        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>血清鉄（Fe）</v>
+        <v>血清フェリチン</v>
       </c>
       <c r="B71" t="str">
-        <v>Fe</v>
+        <v>Ferritin</v>
       </c>
       <c r="C71" t="str">
-        <v>60〜200 μg/dL（施設差あり）</v>
+        <v>男性 20〜250 ng/mL、女性 10〜120 ng/mL（施設差あり）</v>
       </c>
       <c r="D71" t="str">
-        <v>血液中を流れている鉄の量</v>
+        <v>体に貯蔵されている鉄の量を反映する指標。貧血の症状が出るより早い段階で低下する</v>
       </c>
       <c r="E71" t="str">
-        <v>この検査は、今血液の中を流れている鉄の量を見るものです。低いと、体の中で鉄が不足している可能性があります。</v>
+        <v>フェリチンは、体に蓄えられている鉄の「貯金」の量を見る検査です。この数値が下がるのは、貧血の症状が出るよりも前の、とても早い段階のサインになります。</v>
       </c>
       <c r="F71" t="str">
-        <v>鉄剤の過剰摂取、溶血、肝疾患</v>
+        <v>炎症性疾患、肝疾患、悪性腫瘍、鉄過剰症（フェリチンは炎症でも上昇するため、貧血の評価では注意が必要）</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>鉄剤の過量摂取(小児の誤飲を含む)</v>
+        <v/>
       </c>
       <c r="I71" t="str">
-        <v>鉄欠乏性貧血、慢性炎症、出血</v>
+        <v>鉄欠乏状態（貧血の症状が出る前の早期段階から低下する）</v>
       </c>
       <c r="J71" t="str">
-        <v>鉄分の多い食品（レバー・赤身肉・魚・ほうれん草など）を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える</v>
+        <v>鉄分の多い食品を意識するとともに、貯蔵鉄を補うため治療は数値が正常化してからも継続が必要なことを伝える</v>
       </c>
       <c r="K71" t="str">
-        <v>プロトンポンプ阻害薬(PPI)・H2ブロッカーは胃酸分泌抑制により鉄の吸収を低下させうる</v>
+        <v/>
       </c>
       <c r="L71" t="str">
-        <v>血清鉄は日内変動が大きい。単独で判断せず総鉄結合能・フェリチンと合わせて評価する</v>
+        <v>貯蔵鉄の指標で鉄欠乏を最も早期に反映する。ただし炎症があると鉄欠乏があっても正常〜高値に出ることがあり、CRP等の炎症所見と合わせて評価する。二次性貧血との鑑別に重要</v>
       </c>
       <c r="M71" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
       <c r="N71" t="str">
-        <v>血清鉄,Fe,鉄欠乏性貧血</v>
+        <v>フェリチン,Ferritin,貯蔵鉄,鉄欠乏</v>
       </c>
       <c r="O71" t="str">
         <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
@@ -3763,22 +3763,22 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>総鉄結合能（TIBC）</v>
+        <v>尿中尿酸/クレアチニン比（UUA/UCr）</v>
       </c>
       <c r="B72" t="str">
-        <v>TIBC</v>
+        <v>UUA/UCr</v>
       </c>
       <c r="C72" t="str">
-        <v>250〜360 μg/dL（施設差あり）</v>
+        <v>0.4〜0.8程度が混合型の目安</v>
       </c>
       <c r="D72" t="str">
-        <v>血液中のトランスフェリンが鉄と結合できる総量</v>
+        <v>尿酸が「作られすぎ」か「排泄できていない」かを見分ける比の値</v>
       </c>
       <c r="E72" t="str">
-        <v>TIBCは、血液中でトランスフェリンという物質が鉄を運べる最大量を表します。体の中の鉄が不足すると、少しでも多く鉄を運ぼうとしてこの数値が上がる性質があります。</v>
+        <v>この数値は、体の中で尿酸が「作られすぎている」のか、それとも「うまく排泄できていない」のかを見分けるために使う比の値です。高尿酸血症の治療薬を選ぶときの参考になります。</v>
       </c>
       <c r="F72" t="str">
-        <v>鉄欠乏性貧血（＞360 μg/dLが目安）</v>
+        <v>尿酸産生過剰型（0.8以上が目安）</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3787,7 +3787,7 @@
         <v/>
       </c>
       <c r="I72" t="str">
-        <v>慢性炎症、肝疾患、ネフローゼ症候群</v>
+        <v>尿酸排泄低下型（0.4以下が目安）</v>
       </c>
       <c r="J72" t="str">
         <v/>
@@ -3796,36 +3796,36 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>鉄が不足すると、体はより多く運ぼうとしてTIBCが上昇する。UIBC・血清鉄と併せて評価する</v>
+        <v>高尿酸血症は尿酸産生過剰型・排泄低下型・混合型に分類され、この比が目安になる。病型によって使う薬剤（尿酸生成抑制薬か尿酸排泄促進薬か）の選択が変わる</v>
       </c>
       <c r="M72" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>高尿酸血症</v>
       </c>
       <c r="N72" t="str">
-        <v>TIBC,総鉄結合能,鉄欠乏性貧血</v>
+        <v>UUA,UCr,尿酸クリアランス,CUA,EUA,尿酸産生過剰型,尿酸排泄低下型</v>
       </c>
       <c r="O72" t="str">
-        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
+        <v>食事と栄養 p.180-189（第2部 痛風・高尿酸血症）</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>不飽和鉄結合能（UIBC）</v>
+        <v>抗甲状腺マイクロゾーム抗体（抗TPO抗体）</v>
       </c>
       <c r="B73" t="str">
-        <v>UIBC</v>
+        <v>TPOAb</v>
       </c>
       <c r="C73" t="str">
-        <v>170〜300 μg/dL（施設差あり）</v>
+        <v>陰性（16 IU/mL未満程度、施設差あり）</v>
       </c>
       <c r="D73" t="str">
-        <v>トランスフェリンのうち、まだ鉄と結合していない余力の部分（UIBC＝TIBC－血清鉄）</v>
+        <v>自分の甲状腺を攻撃する抗体が出ていないかを見る検査</v>
       </c>
       <c r="E73" t="str">
-        <v>UIBCは、トランスフェリンのうち、まだ鉄と結合していない「空き容量」の部分を表します。鉄が不足しているときほど、この空き容量は大きくなります。</v>
+        <v>この検査は、体の中に自分の甲状腺を誤って攻撃してしまう抗体がないかを見るものです。陽性の場合、橋本病（慢性甲状腺炎）など甲状腺の自己免疫的な炎症が背景にある可能性があります。</v>
       </c>
       <c r="F73" t="str">
-        <v>鉄欠乏性貧血（＞300 μg/dLが目安）</v>
+        <v>橋本病（慢性甲状腺炎）、バセドウ病などの自己免疫性甲状腺疾患</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3834,7 +3834,7 @@
         <v/>
       </c>
       <c r="I73" t="str">
-        <v>慢性炎症、鉄過剰状態</v>
+        <v/>
       </c>
       <c r="J73" t="str">
         <v/>
@@ -3843,36 +3843,36 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>TIBCと同じ方向に動くことが多い。血清鉄・TIBCとあわせて鉄欠乏性貧血と二次性貧血の鑑別に使う</v>
+        <v>陽性でも必ずしも甲状腺機能異常があるとは限らない。TSH・FT4など甲状腺ホルモンの数値と合わせて評価する</v>
       </c>
       <c r="M73" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>甲状腺疾患</v>
       </c>
       <c r="N73" t="str">
-        <v>UIBC,不飽和鉄結合能,鉄欠乏性貧血</v>
+        <v>抗TPO抗体,抗甲状腺マイクロゾーム抗体,TPOAb,橋本病</v>
       </c>
       <c r="O73" t="str">
-        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
+        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>トランスフェリン飽和度</v>
+        <v>抗サイログロブリン抗体</v>
       </c>
       <c r="B74" t="str">
-        <v>TSAT</v>
+        <v>TgAb</v>
       </c>
       <c r="C74" t="str">
-        <v>16〜50%程度（施設差あり）</v>
+        <v>陰性（28 IU/mL未満程度、施設差あり）</v>
       </c>
       <c r="D74" t="str">
-        <v>鉄を運ぶ役割のトランスフェリンのうち、実際に鉄を運んでいる割合（血清鉄÷総鉄結合能）</v>
+        <v>甲状腺のたんぱく質（サイログロブリン）への抗体が出ていないかを見る検査</v>
       </c>
       <c r="E74" t="str">
-        <v>トランスフェリン飽和度は、鉄を運ぶトランスフェリンのうち、実際にどれくらいが鉄を運んでいるかを割合で表したものです。鉄欠乏性貧血では低くなり、鉄が過剰にたまる病気では高くなります。</v>
+        <v>この検査も、抗TPO抗体と同じく、甲状腺に対する自己免疫の有無を見るものです。あわせて調べることで橋本病などの診断の参考にします。</v>
       </c>
       <c r="F74" t="str">
-        <v>鉄過剰症（ヘモクロマトーシスなど）</v>
+        <v>橋本病（慢性甲状腺炎）、バセドウ病などの自己免疫性甲状腺疾患</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3881,7 +3881,7 @@
         <v/>
       </c>
       <c r="I74" t="str">
-        <v>鉄欠乏性貧血（＜16%が目安）</v>
+        <v/>
       </c>
       <c r="J74" t="str">
         <v/>
@@ -3890,92 +3890,92 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>血清鉄をTIBCで割って計算される。鉄剤補充の効果判定にも使われる</v>
+        <v>抗TPO抗体とあわせて測定されることが多い。単独の高値だけで治療方針が決まるわけではない</v>
       </c>
       <c r="M74" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>甲状腺疾患</v>
       </c>
       <c r="N74" t="str">
-        <v>トランスフェリン飽和度,TSAT,鉄欠乏性貧血</v>
+        <v>抗サイログロブリン抗体,TgAb,橋本病</v>
       </c>
       <c r="O74" t="str">
-        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
+        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>血清フェリチン</v>
+        <v>血中薬物濃度（TDM）</v>
       </c>
       <c r="B75" t="str">
-        <v>Ferritin</v>
+        <v>TDM</v>
       </c>
       <c r="C75" t="str">
-        <v>男性 20〜250 ng/mL、女性 10〜120 ng/mL（施設差あり）</v>
+        <v>薬剤ごとに有効域が異なる（例：フェニトイン 10〜20 μg/mL、ゾニサミド 10〜40 μg/mL、カルバマゼピン 4〜12 μg/mL、バルプロ酸ナトリウム 40〜120 μg/mL、ラモトリギン 1〜10 μg/mL(併用薬により変動)）</v>
       </c>
       <c r="D75" t="str">
-        <v>体に貯蔵されている鉄の量を反映する指標。貧血の症状が出るより早い段階で低下する</v>
+        <v>治療域が狭い薬剤で、血液中の薬の濃度が効果域・中毒域のどちらにあるかを確認する検査</v>
       </c>
       <c r="E75" t="str">
-        <v>フェリチンは、体に蓄えられている鉄の「貯金」の量を見る検査です。この数値が下がるのは、貧血の症状が出るよりも前の、とても早い段階のサインになります。</v>
+        <v>この薬は効く量と副作用が出る量が近いため、血液中の薬の濃度を定期的に測って、ちょうどよい範囲に入っているかを確認します。数値が低いと効果が不十分になり、高いと副作用が出やすくなります。</v>
       </c>
       <c r="F75" t="str">
-        <v>炎症性疾患、肝疾患、悪性腫瘍、鉄過剰症（フェリチンは炎症でも上昇するため、貧血の評価では注意が必要）</v>
+        <v>過量投与、代謝を妨げる薬剤との併用、肝機能低下による代謝低下</v>
       </c>
       <c r="G75" t="str">
-        <v/>
+        <v>ふらつき、眠気、めまい、物が二重に見えるなどの中毒症状がないか確認する</v>
       </c>
       <c r="H75" t="str">
         <v/>
       </c>
       <c r="I75" t="str">
-        <v>鉄欠乏状態（貧血の症状が出る前の早期段階から低下する）</v>
+        <v>飲み忘れ、自己判断による減量、代謝を促進する薬剤との併用（相互作用）</v>
       </c>
       <c r="J75" t="str">
-        <v>鉄分の多い食品を意識するとともに、貯蔵鉄を補うため治療は数値が正常化してからも継続が必要なことを伝える</v>
+        <v>発作やてんかん症状の再発がないか確認し、飲み忘れがないか一緒に確認する</v>
       </c>
       <c r="K75" t="str">
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>貯蔵鉄の指標で鉄欠乏を最も早期に反映する。ただし炎症があると鉄欠乏があっても正常〜高値に出ることがあり、CRP等の炎症所見と合わせて評価する。二次性貧血との鑑別に重要</v>
+        <v>採血のタイミング（トラフ値かどうか）で数値の解釈が変わるため採血時点を確認する。カルバマゼピンは自己誘導により長期使用で濃度が下がることがある点にも注意</v>
       </c>
       <c r="M75" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>てんかん</v>
       </c>
       <c r="N75" t="str">
-        <v>フェリチン,Ferritin,貯蔵鉄,鉄欠乏</v>
+        <v>TDM,血中薬物濃度,治療域,中毒域,カルバマゼピン,フェニトイン,バルプロ酸,抗てんかん薬,ゾニサミド,ラモトリギン</v>
       </c>
       <c r="O75" t="str">
-        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
+        <v/>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>尿中尿酸/クレアチニン比（UUA/UCr）</v>
+        <v>アミラーゼ（AMY）</v>
       </c>
       <c r="B76" t="str">
-        <v>UUA/UCr</v>
+        <v>AMY</v>
       </c>
       <c r="C76" t="str">
-        <v>0.4〜0.8程度が混合型の目安</v>
+        <v>44〜132 U/L（施設差あり）</v>
       </c>
       <c r="D76" t="str">
-        <v>尿酸が「作られすぎ」か「排泄できていない」かを見分ける比の値</v>
+        <v>膵臓や唾液腺から出る消化酵素。膵炎などで血液中に漏れ出す</v>
       </c>
       <c r="E76" t="str">
-        <v>この数値は、体の中で尿酸が「作られすぎている」のか、それとも「うまく排泄できていない」のかを見分けるために使う比の値です。高尿酸血症の治療薬を選ぶときの参考になります。</v>
+        <v>アミラーゼは、でんぷんを分解する消化酵素で、主に膵臓と唾液腺から作られます。膵臓に炎症が起きると血液中に漏れ出して数値が上がるため、膵炎の診断や経過観察に使われます。</v>
       </c>
       <c r="F76" t="str">
-        <v>尿酸産生過剰型（0.8以上が目安）</v>
+        <v>急性膵炎、慢性膵炎の急性増悪、耳下腺炎（おたふくかぜ）、腎不全</v>
       </c>
       <c r="G76" t="str">
-        <v/>
+        <v>飲酒を控え、脂っこい食事を避けるよう伝える。強い腹痛・背部痛がある場合は急性膵炎の可能性もあるため早めの受診を勧める</v>
       </c>
       <c r="H76" t="str">
-        <v/>
+        <v>バルプロ酸、アザチオプリン、サイアザイド系・ループ利尿薬、ステロイドなど薬剤性膵炎の原因薬</v>
       </c>
       <c r="I76" t="str">
-        <v>尿酸排泄低下型（0.4以下が目安）</v>
+        <v>慢性膵炎の進行期（膵臓の機能低下）</v>
       </c>
       <c r="J76" t="str">
         <v/>
@@ -3984,39 +3984,39 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>高尿酸血症は尿酸産生過剰型・排泄低下型・混合型に分類され、この比が目安になる。病型によって使う薬剤（尿酸生成抑制薬か尿酸排泄促進薬か）の選択が変わる</v>
+        <v>膵臓由来か唾液腺由来かを区別するには膵型アミラーゼ(P-AMY)を確認する。急性膵炎では強い腹痛・背部痛を伴うことが多く、飲酒歴の確認も重要</v>
       </c>
       <c r="M76" t="str">
-        <v>高尿酸血症</v>
+        <v/>
       </c>
       <c r="N76" t="str">
-        <v>UUA,UCr,尿酸クリアランス,CUA,EUA,尿酸産生過剰型,尿酸排泄低下型</v>
+        <v>アミラーゼ,AMY,膵炎,急性膵炎</v>
       </c>
       <c r="O76" t="str">
-        <v>食事と栄養 p.180-189（第2部 痛風・高尿酸血症）</v>
+        <v/>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>抗甲状腺マイクロゾーム抗体（抗TPO抗体）</v>
+        <v>間接ビリルビン</v>
       </c>
       <c r="B77" t="str">
-        <v>TPOAb</v>
+        <v>I-Bil</v>
       </c>
       <c r="C77" t="str">
-        <v>陰性（16 IU/mL未満程度、施設差あり）</v>
+        <v>0.2〜0.8 mg/dL程度（施設差あり）</v>
       </c>
       <c r="D77" t="str">
-        <v>自分の甲状腺を攻撃する抗体が出ていないかを見る検査</v>
+        <v>赤血球が壊れてできるビリルビンのうち、肝臓で処理される前の形</v>
       </c>
       <c r="E77" t="str">
-        <v>この検査は、体の中に自分の甲状腺を誤って攻撃してしまう抗体がないかを見るものです。陽性の場合、橋本病（慢性甲状腺炎）など甲状腺の自己免疫的な炎症が背景にある可能性があります。</v>
+        <v>間接ビリルビンは、赤血球が壊れてできたビリルビンが、まだ肝臓で処理される前の状態です。この値が高い場合、赤血球が通常より多く壊れている(溶血)か、肝臓での処理能力に生まれつきの体質差(体質性黄疸)がある可能性が考えられます。</v>
       </c>
       <c r="F77" t="str">
-        <v>橋本病（慢性甲状腺炎）、バセドウ病などの自己免疫性甲状腺疾患</v>
+        <v>溶血性疾患（自己免疫性溶血性貧血、血液型不適合輸血など）、体質性黄疸（ジルベール症候群）、新生児黄疸</v>
       </c>
       <c r="G77" t="str">
-        <v/>
+        <v>皮膚や白目の黄染、尿の色の変化がないか確認する</v>
       </c>
       <c r="H77" t="str">
         <v/>
@@ -4031,42 +4031,42 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>陽性でも必ずしも甲状腺機能異常があるとは限らない。TSH・FT4など甲状腺ホルモンの数値と合わせて評価する</v>
+        <v>直接ビリルビンとの比率で原因を推測する（間接優位は溶血・体質性、直接優位は胆道系）。総ビリルビン・AST/ALTと合わせて評価する</v>
       </c>
       <c r="M77" t="str">
-        <v>甲状腺疾患</v>
+        <v>肝機能</v>
       </c>
       <c r="N77" t="str">
-        <v>抗TPO抗体,抗甲状腺マイクロゾーム抗体,TPOAb,橋本病</v>
+        <v>間接ビリルビン,I-Bil,溶血</v>
       </c>
       <c r="O77" t="str">
-        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
+        <v/>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>抗サイログロブリン抗体</v>
+        <v>直接ビリルビン</v>
       </c>
       <c r="B78" t="str">
-        <v>TgAb</v>
+        <v>D-Bil</v>
       </c>
       <c r="C78" t="str">
-        <v>陰性（28 IU/mL未満程度、施設差あり）</v>
+        <v>0.0〜0.3 mg/dL程度（施設差あり）</v>
       </c>
       <c r="D78" t="str">
-        <v>甲状腺のたんぱく質（サイログロブリン）への抗体が出ていないかを見る検査</v>
+        <v>肝臓で処理された後のビリルビン。胆道の詰まりで血液中に増える</v>
       </c>
       <c r="E78" t="str">
-        <v>この検査も、抗TPO抗体と同じく、甲状腺に対する自己免疫の有無を見るものです。あわせて調べることで橋本病などの診断の参考にします。</v>
+        <v>直接ビリルビンは、肝臓で処理された後のビリルビンです。胆石や腫瘍などで胆汁の通り道（胆道）が詰まると、行き場を失って血液中に増え、皮膚や白目が黄色くなる黄疸として現れます。</v>
       </c>
       <c r="F78" t="str">
-        <v>橋本病（慢性甲状腺炎）、バセドウ病などの自己免疫性甲状腺疾患</v>
+        <v>肝疾患、胆石など胆道の閉塞</v>
       </c>
       <c r="G78" t="str">
-        <v/>
+        <v>皮膚や白目の黄染、白っぽい便、濃い茶色の尿がないか確認する</v>
       </c>
       <c r="H78" t="str">
-        <v/>
+        <v>胆汁うっ滞型の薬剤性肝障害を起こしうる抗菌薬、経口避妊薬</v>
       </c>
       <c r="I78" t="str">
         <v/>
@@ -4078,154 +4078,154 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>抗TPO抗体とあわせて測定されることが多い。単独の高値だけで治療方針が決まるわけではない</v>
+        <v>直接優位の上昇は胆道系（胆石、腫瘍による閉塞）を、間接優位の上昇は溶血・体質性を疑う手がかりになる。γ-GTP・ALPと合わせて胆道系疾患を評価する</v>
       </c>
       <c r="M78" t="str">
-        <v>甲状腺疾患</v>
+        <v>肝機能</v>
       </c>
       <c r="N78" t="str">
-        <v>抗サイログロブリン抗体,TgAb,橋本病</v>
+        <v>直接ビリルビン,D-Bil,胆石,胆道閉塞</v>
       </c>
       <c r="O78" t="str">
-        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
+        <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>血中薬物濃度（TDM）</v>
+        <v>亜鉛（Zn）</v>
       </c>
       <c r="B79" t="str">
-        <v>TDM</v>
+        <v>Zn</v>
       </c>
       <c r="C79" t="str">
-        <v>薬剤ごとに有効域が異なる（例：フェニトイン 10〜20 μg/mL、ゾニサミド 10〜40 μg/mL、カルバマゼピン 4〜12 μg/mL、バルプロ酸ナトリウム 40〜120 μg/mL、ラモトリギン 1〜10 μg/mL(併用薬により変動)）</v>
+        <v>80〜130 μg/dL程度（施設差あり）</v>
       </c>
       <c r="D79" t="str">
-        <v>治療域が狭い薬剤で、血液中の薬の濃度が効果域・中毒域のどちらにあるかを確認する検査</v>
+        <v>味覚や皮膚、免疫に関わる微量ミネラル。高齢者や低栄養で不足しやすい</v>
       </c>
       <c r="E79" t="str">
-        <v>この薬は効く量と副作用が出る量が近いため、血液中の薬の濃度を定期的に測って、ちょうどよい範囲に入っているかを確認します。数値が低いと効果が不十分になり、高いと副作用が出やすくなります。</v>
+        <v>亜鉛は、味を感じる働きや皮膚・粘膜の健康、免疫の働きに関わる微量ミネラルです。不足すると、味がわかりにくくなったり（味覚障害）、傷が治りにくくなったりすることがあります。</v>
       </c>
       <c r="F79" t="str">
-        <v>過量投与、代謝を妨げる薬剤との併用、肝機能低下による代謝低下</v>
+        <v/>
       </c>
       <c r="G79" t="str">
-        <v>ふらつき、眠気、めまい、物が二重に見えるなどの中毒症状がないか確認する</v>
+        <v/>
       </c>
       <c r="H79" t="str">
         <v/>
       </c>
       <c r="I79" t="str">
-        <v>飲み忘れ、自己判断による減量、代謝を促進する薬剤との併用（相互作用）</v>
+        <v>低栄養、高齢による摂取不足、消化器手術後、亜鉛の吸収を妨げる薬剤（PPI、キレート形成する薬剤など）との併用</v>
       </c>
       <c r="J79" t="str">
-        <v>発作やてんかん症状の再発がないか確認し、飲み忘れがないか一緒に確認する</v>
+        <v>味覚の変化（味を感じにくい、金属味がするなど）がないか確認する。牡蠣、赤身肉、レバーなど亜鉛を多く含む食品を意識するとよいことを伝える</v>
       </c>
       <c r="K79" t="str">
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>採血のタイミング（トラフ値かどうか）で数値の解釈が変わるため採血時点を確認する。カルバマゼピンは自己誘導により長期使用で濃度が下がることがある点にも注意</v>
+        <v>薬剤性の亜鉛欠乏（PPI長期使用、D-ペニシラミン、一部の降圧薬など）に注意。亜鉛欠乏による味覚障害は原因薬剤の中止・亜鉛補充で改善することがある</v>
       </c>
       <c r="M79" t="str">
-        <v>てんかん</v>
+        <v/>
       </c>
       <c r="N79" t="str">
-        <v>TDM,血中薬物濃度,治療域,中毒域,カルバマゼピン,フェニトイン,バルプロ酸,抗てんかん薬,ゾニサミド,ラモトリギン</v>
+        <v>亜鉛,Zn,味覚障害,亜鉛欠乏</v>
       </c>
       <c r="O79" t="str">
-        <v/>
+        <v>食事と栄養 p.78（亜鉛）</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>アミラーゼ（AMY）</v>
+        <v>マグネシウム（Mg）</v>
       </c>
       <c r="B80" t="str">
-        <v>AMY</v>
+        <v>Mg</v>
       </c>
       <c r="C80" t="str">
-        <v>44〜132 U/L（施設差あり）</v>
+        <v>1.8〜2.6 mg/dL程度（施設差あり）</v>
       </c>
       <c r="D80" t="str">
-        <v>膵臓や唾液腺から出る消化酵素。膵炎などで血液中に漏れ出す</v>
+        <v>骨や筋肉、神経の働きに関わるミネラル。低栄養や利尿薬で不足しやすい</v>
       </c>
       <c r="E80" t="str">
-        <v>アミラーゼは、でんぷんを分解する消化酵素で、主に膵臓と唾液腺から作られます。膵臓に炎症が起きると血液中に漏れ出して数値が上がるため、膵炎の診断や経過観察に使われます。</v>
+        <v>マグネシウムは、骨や筋肉、神経の働きを支えるミネラルです。不足すると、こむら返りや不整脈、だるさなどの症状が出ることがあります。</v>
       </c>
       <c r="F80" t="str">
-        <v>急性膵炎、慢性膵炎の急性増悪、耳下腺炎（おたふくかぜ）、腎不全</v>
+        <v>腎不全、マグネシウム製剤（酸化マグネシウムなど）の過量投与</v>
       </c>
       <c r="G80" t="str">
-        <v>飲酒を控え、脂っこい食事を避けるよう伝える。強い腹痛・背部痛がある場合は急性膵炎の可能性もあるため早めの受診を勧める</v>
+        <v>腎機能低下がある患者で酸化マグネシウムなどの緩下剤を使用中は、傾眠・血圧低下などの高マグネシウム血症の症状がないか確認する</v>
       </c>
       <c r="H80" t="str">
-        <v>バルプロ酸、アザチオプリン、サイアザイド系・ループ利尿薬、ステロイドなど薬剤性膵炎の原因薬</v>
+        <v>マグネシウム含有制酸薬・下剤の過量(特に腎機能低下患者)</v>
       </c>
       <c r="I80" t="str">
-        <v>慢性膵炎の進行期（膵臓の機能低下）</v>
+        <v>低栄養、利尿薬の使用、慢性的な下痢、アルコール多飲、PPI長期使用</v>
       </c>
       <c r="J80" t="str">
-        <v/>
+        <v>こむら返りや動悸などの症状がないか確認する</v>
       </c>
       <c r="K80" t="str">
-        <v/>
+        <v>プロトンポンプ阻害薬(PPI)の長期使用、ループ利尿薬、サイアザイド系利尿薬、シスプラチン、アミノグリコシド系</v>
       </c>
       <c r="L80" t="str">
-        <v>膵臓由来か唾液腺由来かを区別するには膵型アミラーゼ(P-AMY)を確認する。急性膵炎では強い腹痛・背部痛を伴うことが多く、飲酒歴の確認も重要</v>
+        <v>腎機能低下患者への酸化マグネシウム投与は高マグネシウム血症のリスクがあるため定期的なモニタリングが必要。PPI長期使用も低マグネシウム血症のリスク因子として知られる</v>
       </c>
       <c r="M80" t="str">
-        <v/>
+        <v>腎機能</v>
       </c>
       <c r="N80" t="str">
-        <v>アミラーゼ,AMY,膵炎,急性膵炎</v>
+        <v>マグネシウム,Mg,酸化マグネシウム,こむら返り</v>
       </c>
       <c r="O80" t="str">
-        <v/>
+        <v>食事と栄養 p.84（マグネシウム）</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>間接ビリルビン</v>
+        <v>白血球数（WBC）</v>
       </c>
       <c r="B81" t="str">
-        <v>I-Bil</v>
+        <v>WBC</v>
       </c>
       <c r="C81" t="str">
-        <v>0.2〜0.8 mg/dL程度（施設差あり）</v>
+        <v>3,300〜8,600 /μL程度（施設差あり）</v>
       </c>
       <c r="D81" t="str">
-        <v>赤血球が壊れてできるビリルビンのうち、肝臓で処理される前の形</v>
+        <v>体を細菌やウイルスから守る免疫細胞の数で、感染や炎症、薬剤の影響を反映する</v>
       </c>
       <c r="E81" t="str">
-        <v>間接ビリルビンは、赤血球が壊れてできたビリルビンが、まだ肝臓で処理される前の状態です。この値が高い場合、赤血球が通常より多く壊れている(溶血)か、肝臓での処理能力に生まれつきの体質差(体質性黄疸)がある可能性が考えられます。</v>
+        <v>白血球は体に入ってきた細菌やウイルスと戦う免疫細胞です。感染症や炎症があると増え、逆に一部のお薬の副作用や骨髄の働きが落ちると減ることがあります。</v>
       </c>
       <c r="F81" t="str">
-        <v>溶血性疾患（自己免疫性溶血性貧血、血液型不適合輸血など）、体質性黄疸（ジルベール症候群）、新生児黄疸</v>
+        <v>感染症、炎症、ステロイド使用、喫煙、白血病などの血液疾患</v>
       </c>
       <c r="G81" t="str">
-        <v>皮膚や白目の黄染、尿の色の変化がないか確認する</v>
+        <v>発熱や体の痛みなど感染症状がないか確認する</v>
       </c>
       <c r="H81" t="str">
-        <v/>
+        <v>ステロイド、G-CSF製剤、炭酸リチウム</v>
       </c>
       <c r="I81" t="str">
-        <v/>
+        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、メルカゾールなど薬剤性の無顆粒球症、再生不良性貧血、ウイルス感染</v>
       </c>
       <c r="J81" t="str">
-        <v/>
+        <v>発熱、のどの痛みなど感染症状の初期サインがないか確認する。人混みを避け、手洗い・うがいを徹底するよう伝える</v>
       </c>
       <c r="K81" t="str">
-        <v/>
+        <v>抗がん剤、メルカゾール(無顆粒球症)、クロザピン(定期的な血球モニタリング必須)、サラゾスルファピリジン</v>
       </c>
       <c r="L81" t="str">
-        <v>直接ビリルビンとの比率で原因を推測する（間接優位は溶血・体質性、直接優位は胆道系）。総ビリルビン・AST/ALTと合わせて評価する</v>
+        <v>メルカゾール（チアマゾール）は無顆粒球症の重大な副作用があり、発熱・のどの痛みが出たらすぐ受診するよう指導する。抗がん剤・免疫抑制剤・抗てんかん薬（カルバマゼピンなど）使用中も定期的なモニタリングが必要</v>
       </c>
       <c r="M81" t="str">
-        <v>肝機能</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N81" t="str">
-        <v>間接ビリルビン,I-Bil,溶血</v>
+        <v>白血球,WBC,好中球,感染症,白血病,無顆粒球症,骨髄抑制</v>
       </c>
       <c r="O81" t="str">
         <v/>
@@ -4233,66 +4233,66 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>直接ビリルビン</v>
+        <v>赤血球数</v>
       </c>
       <c r="B82" t="str">
-        <v>D-Bil</v>
+        <v>RBC</v>
       </c>
       <c r="C82" t="str">
-        <v>0.0〜0.3 mg/dL程度（施設差あり）</v>
+        <v>男性 435〜555万/μL、女性 386〜492万/μL程度（施設差あり）</v>
       </c>
       <c r="D82" t="str">
-        <v>肝臓で処理された後のビリルビン。胆道の詰まりで血液中に増える</v>
+        <v>血液中で酸素を運ぶ細胞の数。ヘモグロビン・ヘマトクリットと合わせて貧血・多血症を評価する</v>
       </c>
       <c r="E82" t="str">
-        <v>直接ビリルビンは、肝臓で処理された後のビリルビンです。胆石や腫瘍などで胆汁の通り道（胆道）が詰まると、行き場を失って血液中に増え、皮膚や白目が黄色くなる黄疸として現れます。</v>
+        <v>赤血球は、肺で受け取った酸素を全身に運ぶ血液の細胞です。数が少ないと貧血、多いと多血症が疑われます。ヘモグロビンやヘマトクリットと合わせて総合的に評価します。</v>
       </c>
       <c r="F82" t="str">
-        <v>肝疾患、胆石など胆道の閉塞</v>
+        <v>脱水、多血症（真性多血症、二次性多血症）、喫煙</v>
       </c>
       <c r="G82" t="str">
-        <v>皮膚や白目の黄染、白っぽい便、濃い茶色の尿がないか確認する</v>
+        <v>脱水が疑われる場合はこまめな水分摂取を勧める（水分制限がある場合を除く）</v>
       </c>
       <c r="H82" t="str">
-        <v>胆汁うっ滞型の薬剤性肝障害を起こしうる抗菌薬、経口避妊薬</v>
+        <v/>
       </c>
       <c r="I82" t="str">
-        <v/>
+        <v>貧血（鉄欠乏性貧血、腎性貧血など）、出血</v>
       </c>
       <c r="J82" t="str">
-        <v/>
+        <v>ヘモグロビンと同様に、出血や食事量低下がないか確認する</v>
       </c>
       <c r="K82" t="str">
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>直接優位の上昇は胆道系（胆石、腫瘍による閉塞）を、間接優位の上昇は溶血・体質性を疑う手がかりになる。γ-GTP・ALPと合わせて胆道系疾患を評価する</v>
+        <v>ヘモグロビン・ヘマトクリットと同じ方向に動くことが多い。赤血球数だけでなくMCV・MCH・MCHCと合わせて貧血のタイプ(小球性・正球性・大球性)を判断する</v>
       </c>
       <c r="M82" t="str">
-        <v>肝機能</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="N82" t="str">
-        <v>直接ビリルビン,D-Bil,胆石,胆道閉塞</v>
+        <v>赤血球,RBC,貧血,多血症</v>
       </c>
       <c r="O82" t="str">
-        <v/>
+        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>亜鉛（Zn）</v>
+        <v>ヘモグロビン濃度</v>
       </c>
       <c r="B83" t="str">
-        <v>Zn</v>
+        <v>Hb</v>
       </c>
       <c r="C83" t="str">
-        <v>80〜130 μg/dL程度（施設差あり）</v>
+        <v>男性 13.5〜17.5 g/dL、女性 11.5〜15.0 g/dL</v>
       </c>
       <c r="D83" t="str">
-        <v>味覚や皮膚、免疫に関わる微量ミネラル。高齢者や低栄養で不足しやすい</v>
+        <v>血液の中で酸素を運ぶ役割をしている。この値が低い状態が貧血。</v>
       </c>
       <c r="E83" t="str">
-        <v>亜鉛は、味を感じる働きや皮膚・粘膜の健康、免疫の働きに関わる微量ミネラルです。不足すると、味がわかりにくくなったり（味覚障害）、傷が治りにくくなったりすることがあります。</v>
+        <v>ヘモグロビンは、血液の中で酸素を全身に運ぶ役割をしている赤い色素です。この値が低い状態が貧血で、体がだるくなったり、階段で息切れしやすくなったりします。</v>
       </c>
       <c r="F83" t="str">
         <v/>
@@ -4304,163 +4304,163 @@
         <v/>
       </c>
       <c r="I83" t="str">
-        <v>低栄養、高齢による摂取不足、消化器手術後、亜鉛の吸収を妨げる薬剤（PPI、キレート形成する薬剤など）との併用</v>
+        <v>鉄欠乏性貧血、出血、腎性貧血、骨髄の造血機能低下</v>
       </c>
       <c r="J83" t="str">
-        <v>味覚の変化（味を感じにくい、金属味がするなど）がないか確認する。牡蠣、赤身肉、レバーなど亜鉛を多く含む食品を意識するとよいことを伝える</v>
+        <v>鉄分の多い食品(レバー・赤身肉・魚・ほうれん草など)を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える。鉄剤は数値が正常化した後も体内に鉄を貯蔵するため2〜3か月程度は継続が必要なことを説明する</v>
       </c>
       <c r="K83" t="str">
-        <v/>
+        <v>NSAIDs・抗凝固薬・抗血小板薬(消化管出血のリスク)、抗がん剤、ST合剤</v>
       </c>
       <c r="L83" t="str">
-        <v>薬剤性の亜鉛欠乏（PPI長期使用、D-ペニシラミン、一部の降圧薬など）に注意。亜鉛欠乏による味覚障害は原因薬剤の中止・亜鉛補充で改善することがある</v>
+        <v>原因（出血・食事量低下など）の確認が重要。腎機能低下がある場合は鉄不足以外が原因のこともある。鉄剤はヘモグロビンが正常化した後も2〜3か月程度は継続することが多い（鉄の貯蔵分を補うため。途中でやめると再び貧血になりやすい）</v>
       </c>
       <c r="M83" t="str">
-        <v/>
+        <v>鉄欠乏性貧血,抗血小板療法,抗凝固療法（心房細動・血栓症）</v>
       </c>
       <c r="N83" t="str">
-        <v>亜鉛,Zn,味覚障害,亜鉛欠乏</v>
+        <v>ヘモグロビン,Hb,貧血,鉄剤,鉄欠乏性貧血</v>
       </c>
       <c r="O83" t="str">
-        <v>食事と栄養 p.78（亜鉛）</v>
+        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>マグネシウム（Mg）</v>
+        <v>ヘマトクリット値</v>
       </c>
       <c r="B84" t="str">
-        <v>Mg</v>
+        <v>Ht,Hct</v>
       </c>
       <c r="C84" t="str">
-        <v>1.8〜2.6 mg/dL程度（施設差あり）</v>
+        <v>男性 40〜50%、女性 35〜45%</v>
       </c>
       <c r="D84" t="str">
-        <v>骨や筋肉、神経の働きに関わるミネラル。低栄養や利尿薬で不足しやすい</v>
+        <v>血液全体のうち赤血球が占める体積の割合。貧血・脱水の指標</v>
       </c>
       <c r="E84" t="str">
-        <v>マグネシウムは、骨や筋肉、神経の働きを支えるミネラルです。不足すると、こむら返りや不整脈、だるさなどの症状が出ることがあります。</v>
+        <v>ヘマトクリットは、血液全体のうち赤血球が占める割合を表す数値です。この値が低いと貧血、高いと脱水や血液が濃くなっている状態が疑われます。</v>
       </c>
       <c r="F84" t="str">
-        <v>腎不全、マグネシウム製剤（酸化マグネシウムなど）の過量投与</v>
+        <v>脱水、多血症（真性多血症、二次性多血症）、喫煙</v>
       </c>
       <c r="G84" t="str">
-        <v>腎機能低下がある患者で酸化マグネシウムなどの緩下剤を使用中は、傾眠・血圧低下などの高マグネシウム血症の症状がないか確認する</v>
+        <v>脱水が疑われる場合はこまめな水分摂取を勧める（水分制限がある場合を除く）</v>
       </c>
       <c r="H84" t="str">
-        <v>マグネシウム含有制酸薬・下剤の過量(特に腎機能低下患者)</v>
+        <v/>
       </c>
       <c r="I84" t="str">
-        <v>低栄養、利尿薬の使用、慢性的な下痢、アルコール多飲、PPI長期使用</v>
+        <v>貧血（鉄欠乏性貧血、腎性貧血など）、出血</v>
       </c>
       <c r="J84" t="str">
-        <v>こむら返りや動悸などの症状がないか確認する</v>
+        <v>ヘモグロビンと同様に、出血や食事量低下がないか確認する</v>
       </c>
       <c r="K84" t="str">
-        <v>プロトンポンプ阻害薬(PPI)の長期使用、ループ利尿薬、サイアザイド系利尿薬、シスプラチン、アミノグリコシド系</v>
+        <v/>
       </c>
       <c r="L84" t="str">
-        <v>腎機能低下患者への酸化マグネシウム投与は高マグネシウム血症のリスクがあるため定期的なモニタリングが必要。PPI長期使用も低マグネシウム血症のリスク因子として知られる</v>
+        <v>ヘモグロビン・赤血球数と合わせて評価する。3つの値は同じ方向に動くことが多く、脱水があると貧血が見かけ上隠れることがある</v>
       </c>
       <c r="M84" t="str">
-        <v>腎機能</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="N84" t="str">
-        <v>マグネシウム,Mg,酸化マグネシウム,こむら返り</v>
+        <v>ヘマトクリット,Ht,Hct,貧血,脱水,多血症</v>
       </c>
       <c r="O84" t="str">
-        <v>食事と栄養 p.84（マグネシウム）</v>
+        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>白血球数（WBC）</v>
+        <v>MCV</v>
       </c>
       <c r="B85" t="str">
-        <v>WBC</v>
+        <v>MCV</v>
       </c>
       <c r="C85" t="str">
-        <v>3,300〜8,600 /μL程度（施設差あり）</v>
+        <v>79〜100 fL</v>
       </c>
       <c r="D85" t="str">
-        <v>体を細菌やウイルスから守る免疫細胞の数で、感染や炎症、薬剤の影響を反映する</v>
+        <v>赤血球1個の大きさ</v>
       </c>
       <c r="E85" t="str">
-        <v>白血球は体に入ってきた細菌やウイルスと戦う免疫細胞です。感染症や炎症があると増え、逆に一部のお薬の副作用や骨髄の働きが落ちると減ることがあります。</v>
+        <v>MCVは赤血球1個あたりの大きさを表す数値です。貧血があるとき、この数値で「小さい貧血」か「大きい貧血」かを見分けることができ、原因を絞り込む手がかりになります。</v>
       </c>
       <c r="F85" t="str">
-        <v>感染症、炎症、ステロイド使用、喫煙、白血病などの血液疾患</v>
+        <v/>
       </c>
       <c r="G85" t="str">
-        <v>発熱や体の痛みなど感染症状がないか確認する</v>
+        <v/>
       </c>
       <c r="H85" t="str">
-        <v>ステロイド、G-CSF製剤、炭酸リチウム</v>
+        <v/>
       </c>
       <c r="I85" t="str">
-        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、メルカゾールなど薬剤性の無顆粒球症、再生不良性貧血、ウイルス感染</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="J85" t="str">
-        <v>発熱、のどの痛みなど感染症状の初期サインがないか確認する。人混みを避け、手洗い・うがいを徹底するよう伝える</v>
+        <v>鉄分の多い食品(レバー・赤身肉・魚・ほうれん草など)と、吸収を助けるビタミンC(柑橘類・芋類等)を一緒に摂るよう伝える</v>
       </c>
       <c r="K85" t="str">
-        <v>抗がん剤、メルカゾール(無顆粒球症)、クロザピン(定期的な血球モニタリング必須)、サラゾスルファピリジン</v>
+        <v/>
       </c>
       <c r="L85" t="str">
-        <v>メルカゾール（チアマゾール）は無顆粒球症の重大な副作用があり、発熱・のどの痛みが出たらすぐ受診するよう指導する。抗がん剤・免疫抑制剤・抗てんかん薬（カルバマゼピンなど）使用中も定期的なモニタリングが必要</v>
+        <v/>
       </c>
       <c r="M85" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="N85" t="str">
-        <v>白血球,WBC,好中球,感染症,白血病,無顆粒球症,骨髄抑制</v>
+        <v>MCV,赤血球指数,貧血</v>
       </c>
       <c r="O85" t="str">
-        <v/>
+        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>赤血球数</v>
+        <v>MCH</v>
       </c>
       <c r="B86" t="str">
-        <v>RBC</v>
+        <v>MCH</v>
       </c>
       <c r="C86" t="str">
-        <v>男性 435〜555万/μL、女性 386〜492万/μL程度（施設差あり）</v>
+        <v>26.3〜34.3 pg</v>
       </c>
       <c r="D86" t="str">
-        <v>血液中で酸素を運ぶ細胞の数。ヘモグロビン・ヘマトクリットと合わせて貧血・多血症を評価する</v>
+        <v>赤血球1個に含まれるヘモグロビン量</v>
       </c>
       <c r="E86" t="str">
-        <v>赤血球は、肺で受け取った酸素を全身に運ぶ血液の細胞です。数が少ないと貧血、多いと多血症が疑われます。ヘモグロビンやヘマトクリットと合わせて総合的に評価します。</v>
+        <v>MCHは赤血球1個の中に含まれるヘモグロビン（酸素を運ぶ色素）の量を表す数値です。MCVと同じく、貧血の種類を見分けるのに使われます。</v>
       </c>
       <c r="F86" t="str">
-        <v>脱水、多血症（真性多血症、二次性多血症）、喫煙</v>
+        <v/>
       </c>
       <c r="G86" t="str">
-        <v>脱水が疑われる場合はこまめな水分摂取を勧める（水分制限がある場合を除く）</v>
+        <v/>
       </c>
       <c r="H86" t="str">
         <v/>
       </c>
       <c r="I86" t="str">
-        <v>貧血（鉄欠乏性貧血、腎性貧血など）、出血</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="J86" t="str">
-        <v>ヘモグロビンと同様に、出血や食事量低下がないか確認する</v>
+        <v>鉄分の多い食品(レバー・赤身肉・魚・ほうれん草など)と、吸収を助けるビタミンC(柑橘類・芋類等)を一緒に摂るよう伝える</v>
       </c>
       <c r="K86" t="str">
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>ヘモグロビン・ヘマトクリットと同じ方向に動くことが多い。赤血球数だけでなくMCV・MCH・MCHCと合わせて貧血のタイプ(小球性・正球性・大球性)を判断する</v>
+        <v/>
       </c>
       <c r="M86" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
       <c r="N86" t="str">
-        <v>赤血球,RBC,貧血,多血症</v>
+        <v>MCH,赤血球指数,貧血</v>
       </c>
       <c r="O86" t="str">
         <v>食事と栄養 p.151-164（第2部 貧血）</v>
@@ -4468,19 +4468,19 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>ヘモグロビン濃度</v>
+        <v>MCHC</v>
       </c>
       <c r="B87" t="str">
-        <v>Hb</v>
+        <v>MCHC</v>
       </c>
       <c r="C87" t="str">
-        <v>男性 13.5〜17.5 g/dL、女性 11.5〜15.0 g/dL</v>
+        <v>31.6〜36.6 %</v>
       </c>
       <c r="D87" t="str">
-        <v>血液の中で酸素を運ぶ役割をしている。この値が低い状態が貧血。</v>
+        <v>単位容積あたりの赤血球に含まれるヘモグロビン濃度</v>
       </c>
       <c r="E87" t="str">
-        <v>ヘモグロビンは、血液の中で酸素を全身に運ぶ役割をしている赤い色素です。この値が低い状態が貧血で、体がだるくなったり、階段で息切れしやすくなったりします。</v>
+        <v>MCHCは、赤血球の中にヘモグロビンがどれくらい濃く詰まっているかを表す数値です。鉄が不足すると、この濃度も薄くなる傾向があります。</v>
       </c>
       <c r="F87" t="str">
         <v/>
@@ -4492,22 +4492,22 @@
         <v/>
       </c>
       <c r="I87" t="str">
-        <v>鉄欠乏性貧血、出血、腎性貧血、骨髄の造血機能低下</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="J87" t="str">
-        <v>鉄分の多い食品(レバー・赤身肉・魚・ほうれん草など)を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える。鉄剤は数値が正常化した後も体内に鉄を貯蔵するため2〜3か月程度は継続が必要なことを説明する</v>
+        <v>鉄分の多い食品(レバー・赤身肉・魚・ほうれん草など)と、吸収を助けるビタミンC(柑橘類・芋類等)を一緒に摂るよう伝える</v>
       </c>
       <c r="K87" t="str">
-        <v>NSAIDs・抗凝固薬・抗血小板薬(消化管出血のリスク)、抗がん剤、ST合剤</v>
+        <v/>
       </c>
       <c r="L87" t="str">
-        <v>原因（出血・食事量低下など）の確認が重要。腎機能低下がある場合は鉄不足以外が原因のこともある。鉄剤はヘモグロビンが正常化した後も2〜3か月程度は継続することが多い（鉄の貯蔵分を補うため。途中でやめると再び貧血になりやすい）</v>
+        <v/>
       </c>
       <c r="M87" t="str">
-        <v>鉄欠乏性貧血,抗血小板療法,抗凝固療法（心房細動・血栓症）</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="N87" t="str">
-        <v>ヘモグロビン,Hb,貧血,鉄剤,鉄欠乏性貧血</v>
+        <v>MCHC,赤血球指数,貧血</v>
       </c>
       <c r="O87" t="str">
         <v>食事と栄養 p.151-164（第2部 貧血）</v>
@@ -4515,69 +4515,69 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>ヘマトクリット値</v>
+        <v>血小板数</v>
       </c>
       <c r="B88" t="str">
-        <v>Ht,Hct</v>
+        <v>Plt</v>
       </c>
       <c r="C88" t="str">
-        <v>男性 40〜50%、女性 35〜45%</v>
+        <v>15.0〜35.0万/μL程度（施設差あり）</v>
       </c>
       <c r="D88" t="str">
-        <v>血液全体のうち赤血球が占める体積の割合。貧血・脱水の指標</v>
+        <v>出血を止める働きをする血液成分で、少なすぎると出血しやすくなる</v>
       </c>
       <c r="E88" t="str">
-        <v>ヘマトクリットは、血液全体のうち赤血球が占める割合を表す数値です。この値が低いと貧血、高いと脱水や血液が濃くなっている状態が疑われます。</v>
+        <v>血小板は、血管が傷ついたときに集まって血を止める役割をする血液の成分です。数が少ないとあざができやすくなったり、出血が止まりにくくなったりします。抗血小板薬や抗がん剤を使っている方では、定期的にチェックすることが大切です。</v>
       </c>
       <c r="F88" t="str">
-        <v>脱水、多血症（真性多血症、二次性多血症）、喫煙</v>
+        <v>炎症性疾患、鉄欠乏性貧血、脾摘後、骨髄増殖性疾患</v>
       </c>
       <c r="G88" t="str">
-        <v>脱水が疑われる場合はこまめな水分摂取を勧める（水分制限がある場合を除く）</v>
+        <v>出血傾向はなく経過観察でよいことが多いが、片側の腫れ・しびれなど血栓症状がないかも念のため確認する</v>
       </c>
       <c r="H88" t="str">
         <v/>
       </c>
       <c r="I88" t="str">
-        <v>貧血（鉄欠乏性貧血、腎性貧血など）、出血</v>
+        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、肝硬変・脾機能亢進、再生不良性貧血、抗てんかん薬（バルプロ酸など）の副作用、ITP（特発性血小板減少性紫斑病）</v>
       </c>
       <c r="J88" t="str">
-        <v>ヘモグロビンと同様に、出血や食事量低下がないか確認する</v>
+        <v>あざができやすい、歯ぐきや鼻からの出血が増えていないか確認する。強い運動や転倒によるけがに注意するよう伝え、歯みがきは柔らかめのブラシを勧める</v>
       </c>
       <c r="K88" t="str">
-        <v/>
+        <v>ヘパリン(HIT: ヘパリン起因性血小板減少症)、バルプロ酸、抗がん剤、リネゾリド</v>
       </c>
       <c r="L88" t="str">
-        <v>ヘモグロビン・赤血球数と合わせて評価する。3つの値は同じ方向に動くことが多く、脱水があると貧血が見かけ上隠れることがある</v>
+        <v>抗血小板薬・抗凝固薬使用中に血小板減少があると出血リスクがさらに高まる。抗がん剤・バルプロ酸・カルバマゼピンなど骨髄抑制のリスクがある薬剤使用中は定期採血の実施状況を確認する</v>
       </c>
       <c r="M88" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>てんかん,抗血小板療法</v>
       </c>
       <c r="N88" t="str">
-        <v>ヘマトクリット,Ht,Hct,貧血,脱水,多血症</v>
+        <v>血小板,Plt,platelet,出血,あざ,紫斑,骨髄抑制</v>
       </c>
       <c r="O88" t="str">
-        <v>食事と栄養 p.151-164（第2部 貧血）</v>
+        <v/>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>MCV</v>
+        <v>RDW-SD</v>
       </c>
       <c r="B89" t="str">
-        <v>MCV</v>
+        <v>RDW-SD</v>
       </c>
       <c r="C89" t="str">
-        <v>79〜100 fL</v>
+        <v>39〜46 fL程度（施設差あり）</v>
       </c>
       <c r="D89" t="str">
-        <v>赤血球1個の大きさ</v>
+        <v>赤血球の大きさのばらつきを表す指標(絶対値)。鉄欠乏性貧血などの初期変化を捉えやすい</v>
       </c>
       <c r="E89" t="str">
-        <v>MCVは赤血球1個あたりの大きさを表す数値です。貧血があるとき、この数値で「小さい貧血」か「大きい貧血」かを見分けることができ、原因を絞り込む手がかりになります。</v>
+        <v>RDW-SDは、赤血球の大きさがどれくらいバラバラになっているかを表す数値です。貧血の原因を調べる際、鉄が足りなくなり始めた早い段階での変化を捉えるのに役立ちます。</v>
       </c>
       <c r="F89" t="str">
-        <v/>
+        <v>鉄欠乏性貧血の初期、混合性貧血（複数の原因が重なっている状態）、赤血球産生の乱れ</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -4586,22 +4586,22 @@
         <v/>
       </c>
       <c r="I89" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v/>
       </c>
       <c r="J89" t="str">
-        <v>鉄分の多い食品(レバー・赤身肉・魚・ほうれん草など)と、吸収を助けるビタミンC(柑橘類・芋類等)を一緒に摂るよう伝える</v>
+        <v/>
       </c>
       <c r="K89" t="str">
         <v/>
       </c>
       <c r="L89" t="str">
-        <v/>
+        <v>MCVが正常範囲でもRDWが上昇している場合、鉄欠乏の初期段階を示唆することがある。MCV・MCHと合わせて評価する</v>
       </c>
       <c r="M89" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
       <c r="N89" t="str">
-        <v>MCV,赤血球指数,貧血</v>
+        <v>RDW-SD,赤血球分布幅,貧血,鉄欠乏</v>
       </c>
       <c r="O89" t="str">
         <v>食事と栄養 p.151-164（第2部 貧血）</v>
@@ -4609,22 +4609,22 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>MCH</v>
+        <v>RDW-CV</v>
       </c>
       <c r="B90" t="str">
-        <v>MCH</v>
+        <v>RDW-CV</v>
       </c>
       <c r="C90" t="str">
-        <v>26.3〜34.3 pg</v>
+        <v>11.5〜14.5%程度（施設差あり）</v>
       </c>
       <c r="D90" t="str">
-        <v>赤血球1個に含まれるヘモグロビン量</v>
+        <v>赤血球の大きさのばらつきを割合(%)で表した指標</v>
       </c>
       <c r="E90" t="str">
-        <v>MCHは赤血球1個の中に含まれるヘモグロビン（酸素を運ぶ色素）の量を表す数値です。MCVと同じく、貧血の種類を見分けるのに使われます。</v>
+        <v>RDW-CVもRDW-SDと同じく、赤血球の大きさのばらつきを表す数値ですが、こちらは割合(%)で示されます。貧血のタイプを見分ける手がかりになります。</v>
       </c>
       <c r="F90" t="str">
-        <v/>
+        <v>鉄欠乏性貧血、ビタミンB12・葉酸欠乏性貧血、混合性貧血</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -4633,22 +4633,22 @@
         <v/>
       </c>
       <c r="I90" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v/>
       </c>
       <c r="J90" t="str">
-        <v>鉄分の多い食品(レバー・赤身肉・魚・ほうれん草など)と、吸収を助けるビタミンC(柑橘類・芋類等)を一緒に摂るよう伝える</v>
+        <v/>
       </c>
       <c r="K90" t="str">
         <v/>
       </c>
       <c r="L90" t="str">
-        <v/>
+        <v>RDW-SDと同様の意味を持つ指標。MCVが小さくRDWが高ければ鉄欠乏性貧血、MCVが大きくRDWが高ければビタミンB12・葉酸欠乏を疑う手がかりになる</v>
       </c>
       <c r="M90" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
       <c r="N90" t="str">
-        <v>MCH,赤血球指数,貧血</v>
+        <v>RDW-CV,赤血球分布幅,貧血,ビタミンB12,葉酸</v>
       </c>
       <c r="O90" t="str">
         <v>食事と栄養 p.151-164（第2部 貧血）</v>
@@ -4656,22 +4656,22 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>MCHC</v>
+        <v>好中球実数値</v>
       </c>
       <c r="B91" t="str">
-        <v>MCHC</v>
+        <v>Neutro#,ANC</v>
       </c>
       <c r="C91" t="str">
-        <v>31.6〜36.6 %</v>
+        <v>2,000〜7,500 /μL程度（施設差あり、白血球数×好中球%で算出）</v>
       </c>
       <c r="D91" t="str">
-        <v>単位容積あたりの赤血球に含まれるヘモグロビン濃度</v>
+        <v>好中球の絶対数。感染症リスクを判断する上で割合(%)より重要な指標</v>
       </c>
       <c r="E91" t="str">
-        <v>MCHCは、赤血球の中にヘモグロビンがどれくらい濃く詰まっているかを表す数値です。鉄が不足すると、この濃度も薄くなる傾向があります。</v>
+        <v>これは好中球の実際の数を表す数値です。割合(%)だけでなく、実際の数がどれくらいあるかを見ることで、感染症にかかりやすい状態かどうかをより正確に判断できます。</v>
       </c>
       <c r="F91" t="str">
-        <v/>
+        <v>細菌感染症、炎症、ステロイド使用</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -4680,69 +4680,69 @@
         <v/>
       </c>
       <c r="I91" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、メルカゾールなど薬剤性の無顆粒球症（1,000/μL未満で好中球減少症、500/μL未満で重症感染リスクが著しく上昇）</v>
       </c>
       <c r="J91" t="str">
-        <v>鉄分の多い食品(レバー・赤身肉・魚・ほうれん草など)と、吸収を助けるビタミンC(柑橘類・芋類等)を一緒に摂るよう伝える</v>
+        <v>発熱、のどの痛みなど感染症状の初期サインがないか確認する。人混みを避け、手洗い・うがいを徹底するよう伝える</v>
       </c>
       <c r="K91" t="str">
-        <v/>
+        <v>抗がん剤、メルカゾール(無顆粒球症)、クロザピン、サラゾスルファピリジン</v>
       </c>
       <c r="L91" t="str">
-        <v/>
+        <v>抗がん剤・メルカゾール・カルバマゼピンなど骨髄抑制のリスクがある薬剤使用中は特に重視すべき数値。500/μL未満は発熱性好中球減少症のリスクが高く緊急性が高い</v>
       </c>
       <c r="M91" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N91" t="str">
-        <v>MCHC,赤血球指数,貧血</v>
+        <v>好中球実数値,好中球数,ANC,無顆粒球症,発熱性好中球減少症</v>
       </c>
       <c r="O91" t="str">
-        <v>食事と栄養 p.151-164（第2部 貧血）</v>
+        <v/>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>血小板数</v>
+        <v>好酸球実数値</v>
       </c>
       <c r="B92" t="str">
-        <v>Plt</v>
+        <v>Eosino#</v>
       </c>
       <c r="C92" t="str">
-        <v>15.0〜35.0万/μL程度（施設差あり）</v>
+        <v>100〜500 /μL程度（施設差あり）</v>
       </c>
       <c r="D92" t="str">
-        <v>出血を止める働きをする血液成分で、少なすぎると出血しやすくなる</v>
+        <v>好酸球の絶対数。アレルギーや薬剤反応の程度をより正確に評価できる</v>
       </c>
       <c r="E92" t="str">
-        <v>血小板は、血管が傷ついたときに集まって血を止める役割をする血液の成分です。数が少ないとあざができやすくなったり、出血が止まりにくくなったりします。抗血小板薬や抗がん剤を使っている方では、定期的にチェックすることが大切です。</v>
+        <v>これは好酸球の実際の数を表す数値です。割合(%)だけでなく実数を見ることで、アレルギー反応の強さをより正確に把握できます。</v>
       </c>
       <c r="F92" t="str">
-        <v>炎症性疾患、鉄欠乏性貧血、脾摘後、骨髄増殖性疾患</v>
+        <v>アレルギー性疾患、薬剤アレルギー、寄生虫感染</v>
       </c>
       <c r="G92" t="str">
-        <v>出血傾向はなく経過観察でよいことが多いが、片側の腫れ・しびれなど血栓症状がないかも念のため確認する</v>
+        <v>新しく始めた薬がないか確認する</v>
       </c>
       <c r="H92" t="str">
-        <v/>
+        <v>薬剤性好酸球増多(抗菌薬・NSAIDs・抗てんかん薬など)。発熱や皮疹を伴う場合はDRESS症候群にも注意</v>
       </c>
       <c r="I92" t="str">
-        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、肝硬変・脾機能亢進、再生不良性貧血、抗てんかん薬（バルプロ酸など）の副作用、ITP（特発性血小板減少性紫斑病）</v>
+        <v/>
       </c>
       <c r="J92" t="str">
-        <v>あざができやすい、歯ぐきや鼻からの出血が増えていないか確認する。強い運動や転倒によるけがに注意するよう伝え、歯みがきは柔らかめのブラシを勧める</v>
+        <v/>
       </c>
       <c r="K92" t="str">
-        <v>ヘパリン(HIT: ヘパリン起因性血小板減少症)、バルプロ酸、抗がん剤、リネゾリド</v>
+        <v/>
       </c>
       <c r="L92" t="str">
-        <v>抗血小板薬・抗凝固薬使用中に血小板減少があると出血リスクがさらに高まる。抗がん剤・バルプロ酸・カルバマゼピンなど骨髄抑制のリスクがある薬剤使用中は定期採血の実施状況を確認する</v>
+        <v>薬剤性過敏症症候群(DIHS)などでは著明な好酸球増多を認めることがあり、原因薬剤の特定に役立つ</v>
       </c>
       <c r="M92" t="str">
-        <v>てんかん,抗血小板療法</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N92" t="str">
-        <v>血小板,Plt,platelet,出血,あざ,紫斑,骨髄抑制</v>
+        <v>好酸球実数値,好酸球数,アレルギー,DIHS</v>
       </c>
       <c r="O92" t="str">
         <v/>
@@ -4750,22 +4750,22 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>RDW-SD</v>
+        <v>好塩基球実数値</v>
       </c>
       <c r="B93" t="str">
-        <v>RDW-SD</v>
+        <v>Baso#</v>
       </c>
       <c r="C93" t="str">
-        <v>39〜46 fL程度（施設差あり）</v>
+        <v>0〜100 /μL程度（施設差あり）</v>
       </c>
       <c r="D93" t="str">
-        <v>赤血球の大きさのばらつきを表す指標(絶対値)。鉄欠乏性貧血などの初期変化を捉えやすい</v>
+        <v>好塩基球の絶対数</v>
       </c>
       <c r="E93" t="str">
-        <v>RDW-SDは、赤血球の大きさがどれくらいバラバラになっているかを表す数値です。貧血の原因を調べる際、鉄が足りなくなり始めた早い段階での変化を捉えるのに役立ちます。</v>
+        <v>これは好塩基球の実際の数を表す数値です。数がとても少ない種類の血球なので、通常は大きな変動を示すことは多くありません。</v>
       </c>
       <c r="F93" t="str">
-        <v>鉄欠乏性貧血の初期、混合性貧血（複数の原因が重なっている状態）、赤血球産生の乱れ</v>
+        <v>慢性骨髄性白血病などの血液疾患、アレルギー性疾患</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>MCVが正常範囲でもRDWが上昇している場合、鉄欠乏の初期段階を示唆することがある。MCV・MCHと合わせて評価する</v>
+        <v>単独での臨床的意義は乏しく、他の血球指標（白血球分画全体）と合わせて評価する</v>
       </c>
       <c r="M93" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N93" t="str">
-        <v>RDW-SD,赤血球分布幅,貧血,鉄欠乏</v>
+        <v>好塩基球実数値,好塩基球数</v>
       </c>
       <c r="O93" t="str">
-        <v>食事と栄養 p.151-164（第2部 貧血）</v>
+        <v/>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>RDW-CV</v>
+        <v>リンパ球実数値</v>
       </c>
       <c r="B94" t="str">
-        <v>RDW-CV</v>
+        <v>Lympho#,ALC</v>
       </c>
       <c r="C94" t="str">
-        <v>11.5〜14.5%程度（施設差あり）</v>
+        <v>1,000〜3,600 /μL程度（施設差あり）</v>
       </c>
       <c r="D94" t="str">
-        <v>赤血球の大きさのばらつきを割合(%)で表した指標</v>
+        <v>リンパ球の絶対数。免疫力の目安として使われる</v>
       </c>
       <c r="E94" t="str">
-        <v>RDW-CVもRDW-SDと同じく、赤血球の大きさのばらつきを表す数値ですが、こちらは割合(%)で示されます。貧血のタイプを見分ける手がかりになります。</v>
+        <v>これはリンパ球の実際の数を表す数値です。免疫力の目安の一つとして使われ、抗がん剤や免疫抑制剤の副作用モニタリングにも用いられます。</v>
       </c>
       <c r="F94" t="str">
-        <v>鉄欠乏性貧血、ビタミンB12・葉酸欠乏性貧血、混合性貧血</v>
+        <v>ウイルス感染症、リンパ性白血病などの血液疾患</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -4821,45 +4821,45 @@
         <v/>
       </c>
       <c r="I94" t="str">
-        <v/>
+        <v>抗がん剤・免疫抑制剤・ステロイドの使用、強いストレス、AIDSなどの免疫不全</v>
       </c>
       <c r="J94" t="str">
-        <v/>
+        <v>感染予防（手洗い・うがい、人混みを避ける）を意識するよう伝える</v>
       </c>
       <c r="K94" t="str">
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>RDW-SDと同様の意味を持つ指標。MCVが小さくRDWが高ければ鉄欠乏性貧血、MCVが大きくRDWが高ければビタミンB12・葉酸欠乏を疑う手がかりになる</v>
+        <v>免疫抑制剤・抗がん剤治療中のモニタリング指標としても使われる。著明な低下時は日和見感染のリスクが高まる</v>
       </c>
       <c r="M94" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N94" t="str">
-        <v>RDW-CV,赤血球分布幅,貧血,ビタミンB12,葉酸</v>
+        <v>リンパ球実数値,リンパ球数,ALC,免疫抑制剤,日和見感染</v>
       </c>
       <c r="O94" t="str">
-        <v>食事と栄養 p.151-164（第2部 貧血）</v>
+        <v/>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>好中球実数値</v>
+        <v>単球実数値</v>
       </c>
       <c r="B95" t="str">
-        <v>Neutro#,ANC</v>
+        <v>Mono#</v>
       </c>
       <c r="C95" t="str">
-        <v>2,000〜7,500 /μL程度（施設差あり、白血球数×好中球%で算出）</v>
+        <v>200〜600 /μL程度（施設差あり）</v>
       </c>
       <c r="D95" t="str">
-        <v>好中球の絶対数。感染症リスクを判断する上で割合(%)より重要な指標</v>
+        <v>単球の絶対数</v>
       </c>
       <c r="E95" t="str">
-        <v>これは好中球の実際の数を表す数値です。割合(%)だけでなく、実際の数がどれくらいあるかを見ることで、感染症にかかりやすい状態かどうかをより正確に判断できます。</v>
+        <v>これは単球の実際の数を表す数値です。慢性的な炎症や感染症の状態を把握する材料の一つになります。</v>
       </c>
       <c r="F95" t="str">
-        <v>細菌感染症、炎症、ステロイド使用</v>
+        <v>慢性感染症、炎症性疾患、血液疾患</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -4868,22 +4868,22 @@
         <v/>
       </c>
       <c r="I95" t="str">
-        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、メルカゾールなど薬剤性の無顆粒球症（1,000/μL未満で好中球減少症、500/μL未満で重症感染リスクが著しく上昇）</v>
+        <v/>
       </c>
       <c r="J95" t="str">
-        <v>発熱、のどの痛みなど感染症状の初期サインがないか確認する。人混みを避け、手洗い・うがいを徹底するよう伝える</v>
+        <v/>
       </c>
       <c r="K95" t="str">
-        <v>抗がん剤、メルカゾール(無顆粒球症)、クロザピン、サラゾスルファピリジン</v>
+        <v/>
       </c>
       <c r="L95" t="str">
-        <v>抗がん剤・メルカゾール・カルバマゼピンなど骨髄抑制のリスクがある薬剤使用中は特に重視すべき数値。500/μL未満は発熱性好中球減少症のリスクが高く緊急性が高い</v>
+        <v>単独での臨床的意義は乏しく、他の血球指標と合わせて評価する</v>
       </c>
       <c r="M95" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N95" t="str">
-        <v>好中球実数値,好中球数,ANC,無顆粒球症,発熱性好中球減少症</v>
+        <v>単球実数値,単球数</v>
       </c>
       <c r="O95" t="str">
         <v/>
@@ -4891,46 +4891,46 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>好酸球実数値</v>
+        <v>好中球</v>
       </c>
       <c r="B96" t="str">
-        <v>Eosino#</v>
+        <v>Neutro,Neut%</v>
       </c>
       <c r="C96" t="str">
-        <v>100〜500 /μL程度（施設差あり）</v>
+        <v>40〜75%程度（施設差あり）</v>
       </c>
       <c r="D96" t="str">
-        <v>好酸球の絶対数。アレルギーや薬剤反応の程度をより正確に評価できる</v>
+        <v>白血球の中で最も多くを占め、細菌感染と戦う主力の免疫細胞の割合</v>
       </c>
       <c r="E96" t="str">
-        <v>これは好酸球の実際の数を表す数値です。割合(%)だけでなく実数を見ることで、アレルギー反応の強さをより正確に把握できます。</v>
+        <v>好中球は、白血球の中で最も数が多く、細菌が体に入ってきたときに真っ先に戦ってくれる免疫細胞です。感染症や炎症があると増え、逆に薬の副作用などで減ることがあります。</v>
       </c>
       <c r="F96" t="str">
-        <v>アレルギー性疾患、薬剤アレルギー、寄生虫感染</v>
+        <v>細菌感染症、炎症、ストレス、ステロイド使用</v>
       </c>
       <c r="G96" t="str">
-        <v>新しく始めた薬がないか確認する</v>
+        <v>発熱や炎症症状がないか確認する</v>
       </c>
       <c r="H96" t="str">
-        <v>薬剤性好酸球増多(抗菌薬・NSAIDs・抗てんかん薬など)。発熱や皮疹を伴う場合はDRESS症候群にも注意</v>
+        <v/>
       </c>
       <c r="I96" t="str">
-        <v/>
+        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、ウイルス感染、メルカゾールなど薬剤性の無顆粒球症</v>
       </c>
       <c r="J96" t="str">
-        <v/>
+        <v>発熱やのどの痛みなど感染症状の初期サインがないか確認する</v>
       </c>
       <c r="K96" t="str">
-        <v/>
+        <v>抗がん剤、メルカゾール(無顆粒球症)、クロザピン、サラゾスルファピリジン</v>
       </c>
       <c r="L96" t="str">
-        <v>薬剤性過敏症症候群(DIHS)などでは著明な好酸球増多を認めることがあり、原因薬剤の特定に役立つ</v>
+        <v>好中球の絶対数（好中球実数値）が500/μL未満になると重篤な感染症のリスクが高まる。割合(%)だけでなく実数値も合わせて確認する</v>
       </c>
       <c r="M96" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N96" t="str">
-        <v>好酸球実数値,好酸球数,アレルギー,DIHS</v>
+        <v>好中球,Neutro,Neut,感染症,無顆粒球症</v>
       </c>
       <c r="O96" t="str">
         <v/>
@@ -4938,28 +4938,28 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>好塩基球実数値</v>
+        <v>好酸球</v>
       </c>
       <c r="B97" t="str">
-        <v>Baso#</v>
+        <v>Eosino,Eos%</v>
       </c>
       <c r="C97" t="str">
-        <v>0〜100 /μL程度（施設差あり）</v>
+        <v>1〜5%程度（施設差あり）</v>
       </c>
       <c r="D97" t="str">
-        <v>好塩基球の絶対数</v>
+        <v>アレルギー反応や寄生虫感染に関わる白血球の一種の割合</v>
       </c>
       <c r="E97" t="str">
-        <v>これは好塩基球の実際の数を表す数値です。数がとても少ない種類の血球なので、通常は大きな変動を示すことは多くありません。</v>
+        <v>好酸球は、アレルギー反応や寄生虫感染と関係が深い免疫細胞です。アレルギー性の病気や薬の副作用（薬疹など）で増えることがあります。</v>
       </c>
       <c r="F97" t="str">
-        <v>慢性骨髄性白血病などの血液疾患、アレルギー性疾患</v>
+        <v>アレルギー性疾患（気管支喘息、アトピー性皮膚炎など）、薬剤アレルギー、寄生虫感染</v>
       </c>
       <c r="G97" t="str">
-        <v/>
+        <v>新しく始めた薬がないか確認する。皮疹やかゆみなどアレルギー症状の有無を確認する</v>
       </c>
       <c r="H97" t="str">
-        <v/>
+        <v>薬剤性好酸球増多(抗菌薬・NSAIDs・抗てんかん薬など)。発熱や皮疹を伴う場合はDRESS症候群にも注意</v>
       </c>
       <c r="I97" t="str">
         <v/>
@@ -4971,13 +4971,13 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>単独での臨床的意義は乏しく、他の血球指標（白血球分画全体）と合わせて評価する</v>
+        <v>薬剤性の好酸球増多は、原因薬剤の中止で改善することが多い。新規薬剤開始後の皮疹・発熱と合わせて薬剤性過敏症症候群(DIHS)を疑う材料になる</v>
       </c>
       <c r="M97" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N97" t="str">
-        <v>好塩基球実数値,好塩基球数</v>
+        <v>好酸球,Eosino,Eos,アレルギー,薬疹,DIHS</v>
       </c>
       <c r="O97" t="str">
         <v/>
@@ -4985,22 +4985,22 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>リンパ球実数値</v>
+        <v>好塩基球</v>
       </c>
       <c r="B98" t="str">
-        <v>Lympho#,ALC</v>
+        <v>Baso,Baso%</v>
       </c>
       <c r="C98" t="str">
-        <v>1,000〜3,600 /μL程度（施設差あり）</v>
+        <v>0〜2%程度（施設差あり）</v>
       </c>
       <c r="D98" t="str">
-        <v>リンパ球の絶対数。免疫力の目安として使われる</v>
+        <v>白血球の中で最も数が少なく、アレルギー反応に関わる細胞の割合</v>
       </c>
       <c r="E98" t="str">
-        <v>これはリンパ球の実際の数を表す数値です。免疫力の目安の一つとして使われ、抗がん剤や免疫抑制剤の副作用モニタリングにも用いられます。</v>
+        <v>好塩基球は白血球の中で最も数が少ない種類で、アレルギー反応や炎症に関わっています。数値の変動が病気の診断に直接使われることは少ない検査です。</v>
       </c>
       <c r="F98" t="str">
-        <v>ウイルス感染症、リンパ性白血病などの血液疾患</v>
+        <v>慢性骨髄性白血病などの血液疾患、アレルギー性疾患、甲状腺機能低下症</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -5009,22 +5009,22 @@
         <v/>
       </c>
       <c r="I98" t="str">
-        <v>抗がん剤・免疫抑制剤・ステロイドの使用、強いストレス、AIDSなどの免疫不全</v>
+        <v/>
       </c>
       <c r="J98" t="str">
-        <v>感染予防（手洗い・うがい、人混みを避ける）を意識するよう伝える</v>
+        <v/>
       </c>
       <c r="K98" t="str">
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>免疫抑制剤・抗がん剤治療中のモニタリング指標としても使われる。著明な低下時は日和見感染のリスクが高まる</v>
+        <v>単独での臨床的意義は乏しいが、著明な増加は血液疾患（慢性骨髄性白血病等）の可能性があり他の血球指標と合わせて評価する</v>
       </c>
       <c r="M98" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N98" t="str">
-        <v>リンパ球実数値,リンパ球数,ALC,免疫抑制剤,日和見感染</v>
+        <v>好塩基球,Baso,アレルギー,白血病</v>
       </c>
       <c r="O98" t="str">
         <v/>
@@ -5032,22 +5032,22 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>単球実数値</v>
+        <v>リンパ球</v>
       </c>
       <c r="B99" t="str">
-        <v>Mono#</v>
+        <v>Lympho,Lym%</v>
       </c>
       <c r="C99" t="str">
-        <v>200〜600 /μL程度（施設差あり）</v>
+        <v>18〜49%程度（施設差あり）</v>
       </c>
       <c r="D99" t="str">
-        <v>単球の絶対数</v>
+        <v>ウイルス感染と戦い、免疫の記憶を担う白血球の割合</v>
       </c>
       <c r="E99" t="str">
-        <v>これは単球の実際の数を表す数値です。慢性的な炎症や感染症の状態を把握する材料の一つになります。</v>
+        <v>リンパ球は、ウイルスと戦ったり、一度かかった病気を記憶して免疫をつくったりする細胞です。ウイルス感染で増え、抗がん剤の副作用や強いストレスで減ることがあります。</v>
       </c>
       <c r="F99" t="str">
-        <v>慢性感染症、炎症性疾患、血液疾患</v>
+        <v>ウイルス感染症、リンパ性白血病などの血液疾患、百日咳</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -5056,22 +5056,22 @@
         <v/>
       </c>
       <c r="I99" t="str">
-        <v/>
+        <v>抗がん剤・免疫抑制剤・ステロイドの使用、強いストレス、AIDSなどの免疫不全</v>
       </c>
       <c r="J99" t="str">
-        <v/>
+        <v>免疫が下がっている可能性があるため、感染予防（手洗い・うがい、人混みを避ける）を意識するよう伝える</v>
       </c>
       <c r="K99" t="str">
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>単独での臨床的意義は乏しく、他の血球指標と合わせて評価する</v>
+        <v>ステロイド・免疫抑制剤使用中はリンパ球減少による易感染性に注意。好中球と逆方向に動くことが多い（ウイルス感染ではリンパ球優位、細菌感染では好中球優位になりやすい）</v>
       </c>
       <c r="M99" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N99" t="str">
-        <v>単球実数値,単球数</v>
+        <v>リンパ球,Lympho,Lym,ウイルス感染,免疫抑制剤,ステロイド</v>
       </c>
       <c r="O99" t="str">
         <v/>
@@ -5079,46 +5079,46 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>好中球</v>
+        <v>単球</v>
       </c>
       <c r="B100" t="str">
-        <v>Neutro,Neut%</v>
+        <v>Mono,Mono%</v>
       </c>
       <c r="C100" t="str">
-        <v>40〜75%程度（施設差あり）</v>
+        <v>2〜10%程度（施設差あり）</v>
       </c>
       <c r="D100" t="str">
-        <v>白血球の中で最も多くを占め、細菌感染と戦う主力の免疫細胞の割合</v>
+        <v>感染や炎症の後始末をする白血球の一種の割合</v>
       </c>
       <c r="E100" t="str">
-        <v>好中球は、白血球の中で最も数が多く、細菌が体に入ってきたときに真っ先に戦ってくれる免疫細胞です。感染症や炎症があると増え、逆に薬の副作用などで減ることがあります。</v>
+        <v>単球は、細菌などを取り込んで処理したり、組織の修復に関わったりする免疫細胞です。慢性的な炎症や感染症の回復期に増えることがあります。</v>
       </c>
       <c r="F100" t="str">
-        <v>細菌感染症、炎症、ストレス、ステロイド使用</v>
+        <v>慢性感染症（結核など）、炎症性疾患、血液疾患、感染症の回復期</v>
       </c>
       <c r="G100" t="str">
-        <v>発熱や炎症症状がないか確認する</v>
+        <v/>
       </c>
       <c r="H100" t="str">
         <v/>
       </c>
       <c r="I100" t="str">
-        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、ウイルス感染、メルカゾールなど薬剤性の無顆粒球症</v>
+        <v/>
       </c>
       <c r="J100" t="str">
-        <v>発熱やのどの痛みなど感染症状の初期サインがないか確認する</v>
+        <v/>
       </c>
       <c r="K100" t="str">
-        <v>抗がん剤、メルカゾール(無顆粒球症)、クロザピン、サラゾスルファピリジン</v>
+        <v/>
       </c>
       <c r="L100" t="str">
-        <v>好中球の絶対数（好中球実数値）が500/μL未満になると重篤な感染症のリスクが高まる。割合(%)だけでなく実数値も合わせて確認する</v>
+        <v>単独での臨床的意義は乏しく、他の血球指標や炎症マーカー(CRPなど)と合わせて評価する</v>
       </c>
       <c r="M100" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N100" t="str">
-        <v>好中球,Neutro,Neut,感染症,無顆粒球症</v>
+        <v>単球,Mono,慢性感染症,結核,炎症</v>
       </c>
       <c r="O100" t="str">
         <v/>
@@ -5126,31 +5126,31 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>好酸球</v>
+        <v>Dダイマー</v>
       </c>
       <c r="B101" t="str">
-        <v>Eosino,Eos%</v>
+        <v>D-dimer</v>
       </c>
       <c r="C101" t="str">
-        <v>1〜5%程度（施設差あり）</v>
+        <v>1.0 μg/mL以下(施設・測定法により異なる)</v>
       </c>
       <c r="D101" t="str">
-        <v>アレルギー反応や寄生虫感染に関わる白血球の一種の割合</v>
+        <v>体の中で血栓ができて溶けた(線溶)ときにできる分解産物で、血栓症の有無をスクリーニングする指標</v>
       </c>
       <c r="E101" t="str">
-        <v>好酸球は、アレルギー反応や寄生虫感染と関係が深い免疫細胞です。アレルギー性の病気や薬の副作用（薬疹など）で増えることがあります。</v>
+        <v>Dダイマーは、血管の中に血のかたまり(血栓)ができて、それが溶かされるときにできる物質です。この数値が高いと、どこかに血栓ができている可能性を考えます。ただし手術後や妊娠中、高齢の方などでも上がることがあるため、この数値だけで診断が決まるわけではありません。</v>
       </c>
       <c r="F101" t="str">
-        <v>アレルギー性疾患（気管支喘息、アトピー性皮膚炎など）、薬剤アレルギー、寄生虫感染</v>
+        <v>深部静脈血栓症(DVT)・肺血栓塞栓症(PE)、播種性血管内凝固症候群(DIC)、大動脈解離、悪性腫瘍、手術後、妊娠、高齢、感染・炎症</v>
       </c>
       <c r="G101" t="str">
-        <v>新しく始めた薬がないか確認する。皮疹やかゆみなどアレルギー症状の有無を確認する</v>
+        <v>ふくらはぎの腫れ・痛み、急な息切れ・胸痛など血栓症を疑う症状がないか確認する</v>
       </c>
       <c r="H101" t="str">
-        <v>薬剤性好酸球増多(抗菌薬・NSAIDs・抗てんかん薬など)。発熱や皮疹を伴う場合はDRESS症候群にも注意</v>
+        <v>経口避妊薬・ホルモン補充療法は血栓リスクを高める。逆にワルファリン・DOAC・ヘパリンなど抗凝固薬の効果不十分で血栓が進行している可能性にも注意</v>
       </c>
       <c r="I101" t="str">
-        <v/>
+        <v>通常、臨床的意義は乏しい(基準値以下であれば血栓症の可能性は低いとする除外診断に有用)</v>
       </c>
       <c r="J101" t="str">
         <v/>
@@ -5159,13 +5159,13 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>薬剤性の好酸球増多は、原因薬剤の中止で改善することが多い。新規薬剤開始後の皮疹・発熱と合わせて薬剤性過敏症症候群(DIHS)を疑う材料になる</v>
+        <v>陰性的中率が高く、基準値以下であれば静脈血栓塞栓症(VTE)の可能性は低いとする除外診断への活用が臨床的に重要。一方で偽陽性が多く、高値のみで血栓症と確定はできない。抗凝固療法中のモニタリングそのものには通常用いない(効果判定はPT-INR/APTT等)</v>
       </c>
       <c r="M101" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>抗凝固療法（心房細動・血栓症）</v>
       </c>
       <c r="N101" t="str">
-        <v>好酸球,Eosino,Eos,アレルギー,薬疹,DIHS</v>
+        <v>Dダイマー,D-dimer,血栓,DVT,深部静脈血栓症,肺塞栓,DIC</v>
       </c>
       <c r="O101" t="str">
         <v/>
@@ -5173,22 +5173,22 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>好塩基球</v>
+        <v>骨密度</v>
       </c>
       <c r="B102" t="str">
-        <v>Baso,Baso%</v>
+        <v>BMD,骨密度</v>
       </c>
       <c r="C102" t="str">
-        <v>0〜2%程度（施設差あり）</v>
+        <v>YAM(若年成人平均値)80%以上:正常、70%以上80%未満:骨量減少、70%未満:骨粗鬆症</v>
       </c>
       <c r="D102" t="str">
-        <v>白血球の中で最も数が少なく、アレルギー反応に関わる細胞の割合</v>
+        <v>骨の中にカルシウムなどのミネラルがどれだけ詰まっているかを示す指標。20〜44歳の平均値(YAM)に対する割合(%)で評価する</v>
       </c>
       <c r="E102" t="str">
-        <v>好塩基球は白血球の中で最も数が少ない種類で、アレルギー反応や炎症に関わっています。数値の変動が病気の診断に直接使われることは少ない検査です。</v>
+        <v>骨密度は、骨の中にカルシウムなどのミネラルがどれだけしっかり詰まっているかを表す数値です。20〜44歳の若い方の平均値を100%として、ご自身の骨密度が何%かで示されます。70%未満になると「骨粗鬆症」と診断され、骨折しやすい状態と考えられます。</v>
       </c>
       <c r="F102" t="str">
-        <v>慢性骨髄性白血病などの血液疾患、アレルギー性疾患、甲状腺機能低下症</v>
+        <v>基本的に問題になることは少ない(まれに骨硬化症などの疾患)</v>
       </c>
       <c r="G102" t="str">
         <v/>
@@ -5197,22 +5197,22 @@
         <v/>
       </c>
       <c r="I102" t="str">
-        <v/>
+        <v>骨粗鬆症、加齢による骨量減少、閉経後のエストロゲン低下、ステロイド長期使用、カルシウム・ビタミンD不足、運動不足、るいそう</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>カルシウム・ビタミンD・ビタミンKを意識した食事、荷重運動(ウォーキング等)を勧める。ステロイド長期服用中の場合は骨粗鬆症治療薬の併用が検討されているか確認する</v>
       </c>
       <c r="K102" t="str">
         <v/>
       </c>
       <c r="L102" t="str">
-        <v>単独での臨床的意義は乏しいが、著明な増加は血液疾患（慢性骨髄性白血病等）の可能性があり他の血球指標と合わせて評価する</v>
+        <v>YAM70%未満、または既存の脆弱性骨折がある場合に骨粗鬆症と診断され薬物治療の対象となる(日本骨粗鬆症学会・日本骨代謝学会・厚生労働省合同「原発性骨粗鬆症の診断基準 2012年度改訂版」)。ビスホスホネート製剤は起床時空腹時に十分な水(180mL程度)で服用し、服用後30分は横にならないよう指導する。ステロイドを長期服用中の患者は骨密度によらず骨粗鬆症治療薬の併用が推奨される場合がある(グルココルチコイド誘発性骨粗鬆症: GIOP)</v>
       </c>
       <c r="M102" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="N102" t="str">
-        <v>好塩基球,Baso,アレルギー,白血病</v>
+        <v>骨密度,BMD,YAM,若年成人平均値,骨粗鬆症,DXA</v>
       </c>
       <c r="O102" t="str">
         <v/>
@@ -5220,46 +5220,46 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>リンパ球</v>
+        <v>収縮期血圧</v>
       </c>
       <c r="B103" t="str">
-        <v>Lympho,Lym%</v>
+        <v>SBP,収縮期血圧</v>
       </c>
       <c r="C103" t="str">
-        <v>18〜49%程度（施設差あり）</v>
+        <v>診察室血圧 120mmHg未満が正常域、140mmHg以上で高血圧(家庭血圧はそれぞれ5mmHg低い値が基準)</v>
       </c>
       <c r="D103" t="str">
-        <v>ウイルス感染と戦い、免疫の記憶を担う白血球の割合</v>
+        <v>心臓が収縮して血液を送り出すときの血圧の最高値、いわゆる「上の血圧」</v>
       </c>
       <c r="E103" t="str">
-        <v>リンパ球は、ウイルスと戦ったり、一度かかった病気を記憶して免疫をつくったりする細胞です。ウイルス感染で増え、抗がん剤の副作用や強いストレスで減ることがあります。</v>
+        <v>収縮期血圧は、心臓がギュッと縮んで血液を送り出す瞬間の血圧で、いわゆる「上の血圧」です。血管にかかる圧力の中で最も高い値になります。</v>
       </c>
       <c r="F103" t="str">
-        <v>ウイルス感染症、リンパ性白血病などの血液疾患、百日咳</v>
+        <v>本態性高血圧、二次性高血圧(腎性・内分泌性など)、動脈硬化(高齢者で収縮期のみ上昇しやすい)、白衣高血圧、痛みやストレスによる一時的な上昇</v>
       </c>
       <c r="G103" t="str">
-        <v/>
+        <v>減塩(1日6g未満が目安)を心がけ、野菜・果物を積極的に摂るよう伝える。適度な運動・禁煙・節酒も血圧改善に役立つことを伝え、家庭血圧の記録習慣も勧める</v>
       </c>
       <c r="H103" t="str">
-        <v/>
+        <v>NSAIDs、ステロイド、経口避妊薬、甘草含有製剤(グリチルリチン)、一部の抗うつ薬・血管新生阻害薬は血圧を上げうる</v>
       </c>
       <c r="I103" t="str">
-        <v>抗がん剤・免疫抑制剤・ステロイドの使用、強いストレス、AIDSなどの免疫不全</v>
+        <v>起立性低血圧、脱水、降圧薬の効きすぎ、心不全の増悪、出血・ショック</v>
       </c>
       <c r="J103" t="str">
-        <v>免疫が下がっている可能性があるため、感染予防（手洗い・うがい、人混みを避ける）を意識するよう伝える</v>
+        <v>めまい・立ちくらみの有無を確認する。急に立ち上がらずゆっくり動作するよう伝え、脱水が疑われる場合はこまめな水分摂取を勧める</v>
       </c>
       <c r="K103" t="str">
-        <v/>
+        <v>降圧薬(特に利尿薬・α遮断薬)の効きすぎ、抗うつ薬・抗パーキンソン病薬などによる起立性低血圧</v>
       </c>
       <c r="L103" t="str">
-        <v>ステロイド・免疫抑制剤使用中はリンパ球減少による易感染性に注意。好中球と逆方向に動くことが多い（ウイルス感染ではリンパ球優位、細菌感染では好中球優位になりやすい）</v>
+        <v>診察室血圧と家庭血圧で基準値が異なる(家庭血圧のほうが5mmHg低い基準)。高齢者では収縮期血圧のみが高くなる収縮期高血圧が多く、動脈硬化を反映する。降圧薬開始・増量後はふらつき・立ちくらみの有無を確認する</v>
       </c>
       <c r="M103" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>心不全</v>
       </c>
       <c r="N103" t="str">
-        <v>リンパ球,Lympho,Lym,ウイルス感染,免疫抑制剤,ステロイド</v>
+        <v>血圧,収縮期血圧,SBP,上の血圧,高血圧</v>
       </c>
       <c r="O103" t="str">
         <v/>
@@ -5267,46 +5267,46 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>単球</v>
+        <v>拡張期血圧</v>
       </c>
       <c r="B104" t="str">
-        <v>Mono,Mono%</v>
+        <v>DBP,拡張期血圧</v>
       </c>
       <c r="C104" t="str">
-        <v>2〜10%程度（施設差あり）</v>
+        <v>診察室血圧 80mmHg未満が正常域、90mmHg以上で高血圧(家庭血圧はそれぞれ5mmHg低い値が基準)</v>
       </c>
       <c r="D104" t="str">
-        <v>感染や炎症の後始末をする白血球の一種の割合</v>
+        <v>心臓が拡張して血液をため込むときの血圧の最低値、いわゆる「下の血圧」</v>
       </c>
       <c r="E104" t="str">
-        <v>単球は、細菌などを取り込んで処理したり、組織の修復に関わったりする免疫細胞です。慢性的な炎症や感染症の回復期に増えることがあります。</v>
+        <v>拡張期血圧は、心臓が広がって次の収縮に備えて血液をためている瞬間の血圧で、いわゆる「下の血圧」です。</v>
       </c>
       <c r="F104" t="str">
-        <v>慢性感染症（結核など）、炎症性疾患、血液疾患、感染症の回復期</v>
+        <v>本態性高血圧、二次性高血圧、若年〜中年での血管抵抗上昇が主体の高血圧</v>
       </c>
       <c r="G104" t="str">
-        <v/>
+        <v>収縮期血圧と同様、減塩・適度な運動・禁煙・節酒を心がけるよう伝える</v>
       </c>
       <c r="H104" t="str">
-        <v/>
+        <v>NSAIDs、ステロイド、経口避妊薬、甘草含有製剤(グリチルリチン)</v>
       </c>
       <c r="I104" t="str">
-        <v/>
+        <v>大動脈弁閉鎖不全症、甲状腺機能亢進症、動脈硬化の進行(脈圧が開大)</v>
       </c>
       <c r="J104" t="str">
-        <v/>
+        <v>めまいなどの症状がないか確認する</v>
       </c>
       <c r="K104" t="str">
-        <v/>
+        <v>降圧薬(特に血管拡張作用の強いCa拮抗薬)の効きすぎ</v>
       </c>
       <c r="L104" t="str">
-        <v>単独での臨床的意義は乏しく、他の血球指標や炎症マーカー(CRPなど)と合わせて評価する</v>
+        <v>加齢とともに動脈硬化が進むと拡張期血圧は低下し、収縮期血圧との差(脈圧)が開大する。脈圧の開大は動脈硬化の進行を示唆する所見として重視される</v>
       </c>
       <c r="M104" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>心不全</v>
       </c>
       <c r="N104" t="str">
-        <v>単球,Mono,慢性感染症,結核,炎症</v>
+        <v>血圧,拡張期血圧,DBP,下の血圧,高血圧,脈圧</v>
       </c>
       <c r="O104" t="str">
         <v/>
@@ -5314,46 +5314,46 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Dダイマー</v>
+        <v>脈拍</v>
       </c>
       <c r="B105" t="str">
-        <v>D-dimer</v>
+        <v>HR,脈拍</v>
       </c>
       <c r="C105" t="str">
-        <v>1.0 μg/mL以下(施設・測定法により異なる)</v>
+        <v>60〜100回/分</v>
       </c>
       <c r="D105" t="str">
-        <v>体の中で血栓ができて溶けた(線溶)ときにできる分解産物で、血栓症の有無をスクリーニングする指標</v>
+        <v>心臓が1分間に拍動する回数。心臓のリズムや働き具合の目安になる</v>
       </c>
       <c r="E105" t="str">
-        <v>Dダイマーは、血管の中に血のかたまり(血栓)ができて、それが溶かされるときにできる物質です。この数値が高いと、どこかに血栓ができている可能性を考えます。ただし手術後や妊娠中、高齢の方などでも上がることがあるため、この数値だけで診断が決まるわけではありません。</v>
+        <v>脈拍は心臓が1分間に何回打っているかを表す数値です。運動や緊張で一時的に増えたり、リラックスしていると減ったりします。極端に速い・遅い状態が続く場合は、心臓の病気やお薬の影響が考えられます。</v>
       </c>
       <c r="F105" t="str">
-        <v>深部静脈血栓症(DVT)・肺血栓塞栓症(PE)、播種性血管内凝固症候群(DIC)、大動脈解離、悪性腫瘍、手術後、妊娠、高齢、感染・炎症</v>
+        <v>頻脈性不整脈(心房細動等)、発熱、脱水、甲状腺機能亢進症、貧血、痛み・不安・カフェイン摂取、薬剤性(β刺激薬など)</v>
       </c>
       <c r="G105" t="str">
-        <v>ふくらはぎの腫れ・痛み、急な息切れ・胸痛など血栓症を疑う症状がないか確認する</v>
+        <v>動悸・息切れなどの症状がないか確認する。カフェインの摂りすぎがないかもあわせて確認する</v>
       </c>
       <c r="H105" t="str">
-        <v>経口避妊薬・ホルモン補充療法は血栓リスクを高める。逆にワルファリン・DOAC・ヘパリンなど抗凝固薬の効果不十分で血栓が進行している可能性にも注意</v>
+        <v>β刺激薬(気管支拡張薬)、甲状腺ホルモン薬の過量、一部の抗コリン薬</v>
       </c>
       <c r="I105" t="str">
-        <v>通常、臨床的意義は乏しい(基準値以下であれば血栓症の可能性は低いとする除外診断に有用)</v>
+        <v>徐脈性不整脈(洞不全症候群、房室ブロック等)、甲状腺機能低下症、薬剤性(β遮断薬・ジゴキシン等)、アスリート心</v>
       </c>
       <c r="J105" t="str">
-        <v/>
+        <v>めまい・失神・強い倦怠感がないか確認する。特にβ遮断薬服用中は自己判断で中断せず、症状があれば医師に相談するよう伝える</v>
       </c>
       <c r="K105" t="str">
-        <v/>
+        <v>β遮断薬、非ジヒドロピリジン系Ca拮抗薬(ベラパミル・ジルチアゼム)、ジゴキシン、一部の抗不整脈薬</v>
       </c>
       <c r="L105" t="str">
-        <v>陰性的中率が高く、基準値以下であれば静脈血栓塞栓症(VTE)の可能性は低いとする除外診断への活用が臨床的に重要。一方で偽陽性が多く、高値のみで血栓症と確定はできない。抗凝固療法中のモニタリングそのものには通常用いない(効果判定はPT-INR/APTT等)</v>
+        <v>β遮断薬・ジゴキシン服用中は徐脈の指標として重要。心房細動患者では脈拍数と実際の心拍数(心電図)にずれ(脈拍欠損)が生じることがある点にも留意する</v>
       </c>
       <c r="M105" t="str">
-        <v>抗凝固療法（心房細動・血栓症）</v>
+        <v>抗凝固療法（心房細動・血栓症）,心不全</v>
       </c>
       <c r="N105" t="str">
-        <v>Dダイマー,D-dimer,血栓,DVT,深部静脈血栓症,肺塞栓,DIC</v>
+        <v>脈拍,心拍数,HR,頻脈,徐脈,不整脈</v>
       </c>
       <c r="O105" t="str">
         <v/>
@@ -5361,46 +5361,46 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>骨密度</v>
+        <v>眼圧</v>
       </c>
       <c r="B106" t="str">
-        <v>BMD,骨密度</v>
+        <v>IOP,眼圧</v>
       </c>
       <c r="C106" t="str">
-        <v>YAM(若年成人平均値)80%以上:正常、70%以上80%未満:骨量減少、70%未満:骨粗鬆症</v>
+        <v>10〜21 mmHg</v>
       </c>
       <c r="D106" t="str">
-        <v>骨の中にカルシウムなどのミネラルがどれだけ詰まっているかを示す指標。20〜44歳の平均値(YAM)に対する割合(%)で評価する</v>
+        <v>眼球内の圧力。高い状態が続くと視神経が障害され緑内障の原因になる</v>
       </c>
       <c r="E106" t="str">
-        <v>骨密度は、骨の中にカルシウムなどのミネラルがどれだけしっかり詰まっているかを表す数値です。20〜44歳の若い方の平均値を100%として、ご自身の骨密度が何%かで示されます。70%未満になると「骨粗鬆症」と診断され、骨折しやすい状態と考えられます。</v>
+        <v>眼圧は、目の中を満たしている水(房水)の圧力です。この圧力が高い状態が続くと、視神経が徐々に傷んで視野が欠けていく緑内障の原因になることがあります。</v>
       </c>
       <c r="F106" t="str">
-        <v>基本的に問題になることは少ない(まれに骨硬化症などの疾患)</v>
+        <v>緑内障(開放隅角緑内障・閉塞隅角緑内障)、ステロイド点眼・全身投与による眼圧上昇(ステロイド緑内障)、ぶどう膜炎</v>
       </c>
       <c r="G106" t="str">
-        <v/>
+        <v>目のかすみ、頭痛、吐き気、視野が欠ける感じがないか確認する。ステロイド点眼を使用中の場合は自己判断で中止せず定期受診を続けるよう伝える</v>
       </c>
       <c r="H106" t="str">
-        <v/>
+        <v>ステロイド(点眼・内服・吸入)、抗コリン薬(閉塞隅角緑内障がある場合は禁忌〜慎重投与)、一部の抗うつ薬・抗ヒスタミン薬(抗コリン作用)</v>
       </c>
       <c r="I106" t="str">
-        <v>骨粗鬆症、加齢による骨量減少、閉経後のエストロゲン低下、ステロイド長期使用、カルシウム・ビタミンD不足、運動不足、るいそう</v>
+        <v>低眼圧症(眼科手術後、外傷、ぶどう膜炎による房水産生低下など)</v>
       </c>
       <c r="J106" t="str">
-        <v>カルシウム・ビタミンD・ビタミンKを意識した食事、荷重運動(ウォーキング等)を勧める。ステロイド長期服用中の場合は骨粗鬆症治療薬の併用が検討されているか確認する</v>
+        <v>眼科手術後などで急激な視力低下がある場合は早めの受診を勧める</v>
       </c>
       <c r="K106" t="str">
         <v/>
       </c>
       <c r="L106" t="str">
-        <v>YAM70%未満、または既存の脆弱性骨折がある場合に骨粗鬆症と診断され薬物治療の対象となる(日本骨粗鬆症学会・日本骨代謝学会・厚生労働省合同「原発性骨粗鬆症の診断基準 2012年度改訂版」)。ビスホスホネート製剤は起床時空腹時に十分な水(180mL程度)で服用し、服用後30分は横にならないよう指導する。ステロイドを長期服用中の患者は骨密度によらず骨粗鬆症治療薬の併用が推奨される場合がある(グルココルチコイド誘発性骨粗鬆症: GIOP)</v>
+        <v>緑内障治療薬(点眼)は種類が多く複数併用することが多いため、点眼順序(5分以上あける)や防腐剤による角膜障害にも注意する。閉塞隅角緑内障の患者には抗コリン作用のある薬剤(一部の感冒薬・抗うつ薬・過活動膀胱治療薬等)が禁忌〜慎重投与となる場合がある</v>
       </c>
       <c r="M106" t="str">
-        <v>骨粗鬆症</v>
+        <v/>
       </c>
       <c r="N106" t="str">
-        <v>骨密度,BMD,YAM,若年成人平均値,骨粗鬆症,DXA</v>
+        <v>眼圧,IOP,緑内障,ステロイド緑内障</v>
       </c>
       <c r="O106" t="str">
         <v/>

--- a/検査値リファレンス初期データ.xlsx
+++ b/検査値リファレンス初期データ.xlsx
@@ -2541,46 +2541,46 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>尿蛋白（随時尿）</v>
+        <v>白血球数（WBC）</v>
       </c>
       <c r="B46" t="str">
-        <v>尿蛋白,U-pro</v>
+        <v>WBC</v>
       </c>
       <c r="C46" t="str">
-        <v>陰性（－）〜弱陽性</v>
+        <v>3,300〜8,600 /μL程度（施設差あり）</v>
       </c>
       <c r="D46" t="str">
-        <v>腎臓から本来漏れないはずのたんぱくが尿に出ていないかを見る検査</v>
+        <v>体を細菌やウイルスから守る免疫細胞の数で、感染や炎症、薬剤の影響を反映する</v>
       </c>
       <c r="E46" t="str">
-        <v>この検査は、腎臓のろ過機能に負担がかかっていないかを見るものです。本来、たんぱく質は尿にほとんど出ませんが、腎臓に負担がかかると漏れ出るようになります。</v>
+        <v>白血球は体に入ってきた細菌やウイルスと戦う免疫細胞です。感染症や炎症があると増え、逆に一部のお薬の副作用や骨髄の働きが落ちると減ることがあります。</v>
       </c>
       <c r="F46" t="str">
-        <v>糖尿病性腎症、腎炎、高血圧性腎硬化症、発熱・運動後の一過性のもの</v>
+        <v>感染症、炎症、ステロイド使用、喫煙、白血病などの血液疾患</v>
       </c>
       <c r="G46" t="str">
-        <v>発熱・激しい運動の直後でないか確認する(一過性のことがある)。持続する場合は塩分の摂りすぎに注意し、むくみの有無もあわせて確認する</v>
+        <v>発熱や体の痛みなど感染症状がないか確認する</v>
       </c>
       <c r="H46" t="str">
-        <v>NSAIDs、造影剤、アミノグリコシド系、バンコマイシン、金製剤</v>
+        <v>ステロイド、G-CSF製剤、炭酸リチウム</v>
       </c>
       <c r="I46" t="str">
-        <v/>
+        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、メルカゾールなど薬剤性の無顆粒球症、再生不良性貧血、ウイルス感染</v>
       </c>
       <c r="J46" t="str">
-        <v/>
+        <v>発熱、のどの痛みなど感染症状の初期サインがないか確認する。人混みを避け、手洗い・うがいを徹底するよう伝える</v>
       </c>
       <c r="K46" t="str">
-        <v/>
+        <v>抗がん剤、メルカゾール(無顆粒球症)、クロザピン(定期的な血球モニタリング必須)、サラゾスルファピリジン</v>
       </c>
       <c r="L46" t="str">
-        <v>発熱・激しい運動・起立性蛋白尿など生理的な要因でも陽性になることがある。持続する場合に腎症の進行を疑う</v>
+        <v>メルカゾール（チアマゾール）は無顆粒球症の重大な副作用があり、発熱・のどの痛みが出たらすぐ受診するよう指導する。抗がん剤・免疫抑制剤・抗てんかん薬（カルバマゼピンなど）使用中も定期的なモニタリングが必要</v>
       </c>
       <c r="M46" t="str">
-        <v>糖尿病,腎機能</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N46" t="str">
-        <v>尿蛋白,U-pro,腎症,たんぱく尿</v>
+        <v>白血球,WBC,好中球,感染症,白血病,無顆粒球症,骨髄抑制</v>
       </c>
       <c r="O46" t="str">
         <v/>
@@ -2588,210 +2588,210 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>尿クレアチニン（随時尿）</v>
+        <v>赤血球数</v>
       </c>
       <c r="B47" t="str">
-        <v>尿CRE</v>
+        <v>RBC</v>
       </c>
       <c r="C47" t="str">
-        <v>随時尿は主に他項目の濃度補正に利用（単独の基準値は設けにくい）</v>
+        <v>男性 435〜555万/μL、女性 386〜492万/μL程度（施設差あり）</v>
       </c>
       <c r="D47" t="str">
-        <v>随時尿中のクレアチニン濃度。他の尿検査項目を薄まり具合で補正するための基準として使う</v>
+        <v>血液中で酸素を運ぶ細胞の数。ヘモグロビン・ヘマトクリットと合わせて貧血・多血症を評価する</v>
       </c>
       <c r="E47" t="str">
-        <v>この数値は、尿がどれくらい薄まっているかを確認するための基準として使われます。他の尿検査の結果（蛋白やアルブミンなど）をこの値で割って補正することで、水分摂取量による影響を減らして正確に評価できます。</v>
+        <v>赤血球は、肺で受け取った酸素を全身に運ぶ血液の細胞です。数が少ないと貧血、多いと多血症が疑われます。ヘモグロビンやヘマトクリットと合わせて総合的に評価します。</v>
       </c>
       <c r="F47" t="str">
-        <v/>
+        <v>脱水、多血症（真性多血症、二次性多血症）、喫煙</v>
       </c>
       <c r="G47" t="str">
-        <v/>
+        <v>脱水が疑われる場合はこまめな水分摂取を勧める（水分制限がある場合を除く）</v>
       </c>
       <c r="H47" t="str">
         <v/>
       </c>
       <c r="I47" t="str">
-        <v>尿が薄い（水分摂取が多い、腎機能低下）状態</v>
+        <v>貧血（鉄欠乏性貧血、腎性貧血など）、出血</v>
       </c>
       <c r="J47" t="str">
-        <v/>
+        <v>ヘモグロビンと同様に、出血や食事量低下がないか確認する</v>
       </c>
       <c r="K47" t="str">
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>尿中アルブミン/Cr比、尿蛋白/Cr比など、他項目の補正計算に使われる。単独の高低に臨床的意味は乏しい</v>
+        <v>ヘモグロビン・ヘマトクリットと同じ方向に動くことが多い。赤血球数だけでなくMCV・MCH・MCHCと合わせて貧血のタイプ(小球性・正球性・大球性)を判断する</v>
       </c>
       <c r="M47" t="str">
-        <v>腎機能</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="N47" t="str">
-        <v>尿CRE,尿クレアチニン,随時尿,補正,蛋白クレアチニン比</v>
+        <v>赤血球,RBC,貧血,多血症</v>
       </c>
       <c r="O47" t="str">
-        <v/>
+        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>尿蛋白定量</v>
+        <v>ヘモグロビン濃度</v>
       </c>
       <c r="B48" t="str">
-        <v>U-Pro定量,蛋白/Cr比</v>
+        <v>Hb</v>
       </c>
       <c r="C48" t="str">
-        <v>0.15 g/gCr未満</v>
+        <v>男性 13.5〜17.5 g/dL、女性 11.5〜15.0 g/dL</v>
       </c>
       <c r="D48" t="str">
-        <v>随時尿から尿蛋白の量を具体的な数値として評価する検査。ネフローゼ等の重症度判定に使う</v>
+        <v>血液の中で酸素を運ぶ役割をしている。この値が低い状態が貧血。</v>
       </c>
       <c r="E48" t="str">
-        <v>これは、尿に出ているたんぱくの量を具体的な数値で見る検査です。試験紙での陽性・陰性の判定だけでなく、実際にどれくらいの量が出ているかを把握できます。</v>
+        <v>ヘモグロビンは、血液の中で酸素を全身に運ぶ役割をしている赤い色素です。この値が低い状態が貧血で、体がだるくなったり、階段で息切れしやすくなったりします。</v>
       </c>
       <c r="F48" t="str">
-        <v>腎症の進行（糖尿病性腎症、慢性腎臓病など）、ネフローゼ症候群（3.5 g/gCr以上が目安）</v>
+        <v/>
       </c>
       <c r="G48" t="str">
-        <v>持続する場合は塩分の摂りすぎに注意し、むくみの有無も確認する。腎臓内科でのフォロー状況もあわせて確認する</v>
+        <v/>
       </c>
       <c r="H48" t="str">
-        <v>NSAIDs、造影剤、アミノグリコシド系、バンコマイシン</v>
+        <v/>
       </c>
       <c r="I48" t="str">
-        <v/>
+        <v>鉄欠乏性貧血、出血、腎性貧血、骨髄の造血機能低下</v>
       </c>
       <c r="J48" t="str">
-        <v/>
+        <v>鉄分の多い食品(レバー・赤身肉・魚・ほうれん草など)を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える。鉄剤は数値が正常化した後も体内に鉄を貯蔵するため2〜3か月程度は継続が必要なことを説明する</v>
       </c>
       <c r="K48" t="str">
-        <v/>
+        <v>NSAIDs・抗凝固薬・抗血小板薬(消化管出血のリスク)、抗がん剤、ST合剤</v>
       </c>
       <c r="L48" t="str">
-        <v>CKD診療ガイドラインの重症度分類（尿蛋白量による区分）にも使われる定量指標。試験紙法の半定量結果より治療効果判定に適する</v>
+        <v>原因（出血・食事量低下など）の確認が重要。腎機能低下がある場合は鉄不足以外が原因のこともある。鉄剤はヘモグロビンが正常化した後も2〜3か月程度は継続することが多い（鉄の貯蔵分を補うため。途中でやめると再び貧血になりやすい）</v>
       </c>
       <c r="M48" t="str">
-        <v>腎機能,糖尿病</v>
+        <v>鉄欠乏性貧血,抗血小板療法,抗凝固療法（心房細動・血栓症）</v>
       </c>
       <c r="N48" t="str">
-        <v>尿蛋白,随時尿,定量,蛋白クレアチニン比,ネフローゼ</v>
+        <v>ヘモグロビン,Hb,貧血,鉄剤,鉄欠乏性貧血</v>
       </c>
       <c r="O48" t="str">
-        <v/>
+        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>尿pH</v>
+        <v>ヘマトクリット値</v>
       </c>
       <c r="B49" t="str">
-        <v>尿pH</v>
+        <v>Ht,Hct</v>
       </c>
       <c r="C49" t="str">
-        <v>4.5〜7.5程度（弱酸性が多い）</v>
+        <v>男性 40〜50%、女性 35〜45%</v>
       </c>
       <c r="D49" t="str">
-        <v>尿の酸性・アルカリ性の度合い。食事や感染症、体の状態を反映する</v>
+        <v>血液全体のうち赤血球が占める体積の割合。貧血・脱水の指標</v>
       </c>
       <c r="E49" t="str">
-        <v>尿のpHは酸性・アルカリ性のバランスを表します。食事の内容や感染症、体の代謝状態によって変化します。単独で大きな問題を示すことは少ない検査です。</v>
+        <v>ヘマトクリットは、血液全体のうち赤血球が占める割合を表す数値です。この値が低いと貧血、高いと脱水や血液が濃くなっている状態が疑われます。</v>
       </c>
       <c r="F49" t="str">
-        <v>尿路感染症（尿素分解菌によるもの）、野菜中心の食事、過換気</v>
+        <v>脱水、多血症（真性多血症、二次性多血症）、喫煙</v>
       </c>
       <c r="G49" t="str">
-        <v/>
+        <v>脱水が疑われる場合はこまめな水分摂取を勧める（水分制限がある場合を除く）</v>
       </c>
       <c r="H49" t="str">
         <v/>
       </c>
       <c r="I49" t="str">
-        <v>高たんぱく食、糖尿病性ケトアシドーシス、痛風発作時（酸性尿は尿酸結石のリスクを高める）</v>
+        <v>貧血（鉄欠乏性貧血、腎性貧血など）、出血</v>
       </c>
       <c r="J49" t="str">
-        <v>痛風・尿酸結石がある場合は、野菜など尿をアルカリ化する食品を意識するとよいことを伝える</v>
+        <v>ヘモグロビンと同様に、出血や食事量低下がないか確認する</v>
       </c>
       <c r="K49" t="str">
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>高尿酸血症・尿酸結石の患者では尿pHが酸性に傾いていないか確認する。尿アルカリ化薬（ウラリットなど）の効果判定にも使う</v>
+        <v>ヘモグロビン・赤血球数と合わせて評価する。3つの値は同じ方向に動くことが多く、脱水があると貧血が見かけ上隠れることがある</v>
       </c>
       <c r="M49" t="str">
-        <v>高尿酸血症</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="N49" t="str">
-        <v>尿pH,尿酸性度,尿アルカリ化,ウラリット</v>
+        <v>ヘマトクリット,Ht,Hct,貧血,脱水,多血症</v>
       </c>
       <c r="O49" t="str">
-        <v/>
+        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>尿ケトン体</v>
+        <v>MCV</v>
       </c>
       <c r="B50" t="str">
-        <v>尿ケトン,Ket</v>
+        <v>MCV</v>
       </c>
       <c r="C50" t="str">
-        <v>陰性（－）</v>
+        <v>79〜100 fL</v>
       </c>
       <c r="D50" t="str">
-        <v>体がブドウ糖の代わりに脂肪を分解してエネルギーを作っているサイン</v>
+        <v>赤血球1個の大きさ</v>
       </c>
       <c r="E50" t="str">
-        <v>この検査は、体が糖の代わりに脂肪を使ってエネルギーを作っていないかを見るものです。陽性が続くときは、食事や水分、インスリンの使い方を確認する必要があります。</v>
+        <v>MCVは赤血球1個あたりの大きさを表す数値です。貧血があるとき、この数値で「小さい貧血」か「大きい貧血」かを見分けることができ、原因を絞り込む手がかりになります。</v>
       </c>
       <c r="F50" t="str">
-        <v>糖尿病の血糖コントロール不良（シックデイ・インスリン不足）、極端な糖質制限、絶食、嘔吐・下痢による脱水</v>
+        <v/>
       </c>
       <c r="G50" t="str">
-        <v>糖尿病治療中の場合はシックデイ時の対応(インスリンを自己中断しない、水分摂取を続けるなど)を確認する。体調不良時の対応方法を事前に説明しておく</v>
+        <v/>
       </c>
       <c r="H50" t="str">
-        <v>SGLT2阻害薬(特に絶食・シックデイ時の正常血糖ケトアシドーシスに注意)</v>
+        <v/>
       </c>
       <c r="I50" t="str">
-        <v/>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="J50" t="str">
-        <v/>
+        <v>鉄分の多い食品(レバー・赤身肉・魚・ほうれん草など)と、吸収を助けるビタミンC(柑橘類・芋類等)を一緒に摂るよう伝える</v>
       </c>
       <c r="K50" t="str">
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>陽性かつ高血糖・全身倦怠感が強い場合は糖尿病性ケトアシドーシスの可能性があり緊急性が高い。シックデイルールの説明歴を確認する</v>
+        <v/>
       </c>
       <c r="M50" t="str">
-        <v>糖尿病</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="N50" t="str">
-        <v>尿ケトン体,ケトン体,Ket,シックデイ,ケトアシドーシス</v>
+        <v>MCV,赤血球指数,貧血</v>
       </c>
       <c r="O50" t="str">
-        <v/>
+        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ウロビリノーゲン</v>
+        <v>MCH</v>
       </c>
       <c r="B51" t="str">
-        <v>Uro</v>
+        <v>MCH</v>
       </c>
       <c r="C51" t="str">
-        <v>正常（±）程度</v>
+        <v>26.3〜34.3 pg</v>
       </c>
       <c r="D51" t="str">
-        <v>肝臓や胆道、赤血球の壊れ方の状態を反映する尿検査項目</v>
+        <v>赤血球1個に含まれるヘモグロビン量</v>
       </c>
       <c r="E51" t="str">
-        <v>ウロビリノーゲンは、赤血球やビリルビンが体の中で処理される過程でできる物質です。肝臓の働きが悪くなったり、赤血球が壊れやすくなったりすると、尿の中の量が変化します。</v>
+        <v>MCHは赤血球1個の中に含まれるヘモグロビン（酸素を運ぶ色素）の量を表す数値です。MCVと同じく、貧血の種類を見分けるのに使われます。</v>
       </c>
       <c r="F51" t="str">
-        <v>溶血性疾患（赤血球の破壊亢進）、肝機能障害</v>
+        <v/>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2800,116 +2800,116 @@
         <v/>
       </c>
       <c r="I51" t="str">
-        <v>胆道閉塞（胆汁が腸に流れず、ウロビリノーゲンが作られない状態）</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="J51" t="str">
-        <v/>
+        <v>鉄分の多い食品(レバー・赤身肉・魚・ほうれん草など)と、吸収を助けるビタミンC(柑橘類・芋類等)を一緒に摂るよう伝える</v>
       </c>
       <c r="K51" t="str">
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>完全に陰性の場合は胆道閉塞を疑う所見の一つ。肝機能（AST/ALT/ビリルビン）と合わせて評価する</v>
+        <v/>
       </c>
       <c r="M51" t="str">
-        <v>肝機能</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="N51" t="str">
-        <v>ウロビリノーゲン,Uro,溶血,胆道閉塞,肝機能</v>
+        <v>MCH,赤血球指数,貧血</v>
       </c>
       <c r="O51" t="str">
-        <v/>
+        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>尿潜血反応</v>
+        <v>MCHC</v>
       </c>
       <c r="B52" t="str">
-        <v>尿潜血,U-OB</v>
+        <v>MCHC</v>
       </c>
       <c r="C52" t="str">
-        <v>陰性（－）</v>
+        <v>31.6〜36.6 %</v>
       </c>
       <c r="D52" t="str">
-        <v>尿に血液（赤血球）が混じっていないかを見る検査</v>
+        <v>単位容積あたりの赤血球に含まれるヘモグロビン濃度</v>
       </c>
       <c r="E52" t="str">
-        <v>この検査は、尿に目に見えないくらいの微量の血液が混じっていないかを調べるものです。陽性の場合、腎臓や膀胱、尿路のどこかに炎症や結石などがある可能性があります。</v>
+        <v>MCHCは、赤血球の中にヘモグロビンがどれくらい濃く詰まっているかを表す数値です。鉄が不足すると、この濃度も薄くなる傾向があります。</v>
       </c>
       <c r="F52" t="str">
-        <v>尿路結石、膀胱炎などの尿路感染症、腎炎、腫瘍、月経血の混入、激しい運動後</v>
+        <v/>
       </c>
       <c r="G52" t="str">
-        <v>排尿時の痛みや頻尿、目に見える血尿の有無を確認する。女性は月経の時期と重なっていないか確認する</v>
+        <v/>
       </c>
       <c r="H52" t="str">
-        <v>ワルファリン、DOAC、抗血小板薬など出血傾向を強める薬剤の服用状況を確認</v>
+        <v/>
       </c>
       <c r="I52" t="str">
-        <v/>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="J52" t="str">
-        <v/>
+        <v>鉄分の多い食品(レバー・赤身肉・魚・ほうれん草など)と、吸収を助けるビタミンC(柑橘類・芋類等)を一緒に摂るよう伝える</v>
       </c>
       <c r="K52" t="str">
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>陽性でも尿沈渣で赤血球が確認されない場合は偽陽性（ミオグロビン尿など）のこともある。持続する場合は泌尿器科的な精査が必要</v>
+        <v/>
       </c>
       <c r="M52" t="str">
-        <v>腎機能</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="N52" t="str">
-        <v>尿潜血,潜血反応,U-OB,血尿,尿路結石,膀胱炎</v>
+        <v>MCHC,赤血球指数,貧血</v>
       </c>
       <c r="O52" t="str">
-        <v/>
+        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>尿糖（半定量）</v>
+        <v>血小板数</v>
       </c>
       <c r="B53" t="str">
-        <v>尿糖,U-Glu</v>
+        <v>Plt</v>
       </c>
       <c r="C53" t="str">
-        <v>陰性（－）</v>
+        <v>15.0〜35.0万/μL程度（施設差あり）</v>
       </c>
       <c r="D53" t="str">
-        <v>尿に糖が漏れ出ていないかを見る検査。血糖値がかなり高いと陽性になる</v>
+        <v>出血を止める働きをする血液成分で、少なすぎると出血しやすくなる</v>
       </c>
       <c r="E53" t="str">
-        <v>通常、糖は尿にはほとんど出ませんが、血糖値がかなり高くなると尿にあふれ出るようになります。血糖コントロールの目安の一つです。</v>
+        <v>血小板は、血管が傷ついたときに集まって血を止める役割をする血液の成分です。数が少ないとあざができやすくなったり、出血が止まりにくくなったりします。抗血小板薬や抗がん剤を使っている方では、定期的にチェックすることが大切です。</v>
       </c>
       <c r="F53" t="str">
-        <v>糖尿病（血糖値が腎臓で再吸収できる量を超えている状態）、腎性糖尿（血糖値が正常でも体質的に出ることがある）、SGLT2阻害薬服用中（薬の作用で意図的に糖を排泄するため陽性になるのが正常）</v>
+        <v>炎症性疾患、鉄欠乏性貧血、脾摘後、骨髄増殖性疾患</v>
       </c>
       <c r="G53" t="str">
-        <v>SGLT2阻害薬（フォシーガ、ジャディアンスなど）服用中は、陽性が薬の効果によるものであることを説明する。脱水や尿路感染の症状がないかも確認する</v>
+        <v>出血傾向はなく経過観察でよいことが多いが、片側の腫れ・しびれなど血栓症状がないかも念のため確認する</v>
       </c>
       <c r="H53" t="str">
-        <v>SGLT2阻害薬(薬理作用による陽性であれば想定内であることを説明)</v>
+        <v/>
       </c>
       <c r="I53" t="str">
-        <v/>
+        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、肝硬変・脾機能亢進、再生不良性貧血、抗てんかん薬（バルプロ酸など）の副作用、ITP（特発性血小板減少性紫斑病）</v>
       </c>
       <c r="J53" t="str">
-        <v/>
+        <v>あざができやすい、歯ぐきや鼻からの出血が増えていないか確認する。強い運動や転倒によるけがに注意するよう伝え、歯みがきは柔らかめのブラシを勧める</v>
       </c>
       <c r="K53" t="str">
-        <v/>
+        <v>ヘパリン(HIT: ヘパリン起因性血小板減少症)、バルプロ酸、抗がん剤、リネゾリド</v>
       </c>
       <c r="L53" t="str">
-        <v>SGLT2阻害薬服用中は尿糖陽性が治療効果として想定内であることを患者に伝える。血糖値・HbA1cと合わせて評価する</v>
+        <v>抗血小板薬・抗凝固薬使用中に血小板減少があると出血リスクがさらに高まる。抗がん剤・バルプロ酸・カルバマゼピンなど骨髄抑制のリスクがある薬剤使用中は定期採血の実施状況を確認する</v>
       </c>
       <c r="M53" t="str">
-        <v>糖尿病</v>
+        <v>てんかん,抗血小板療法</v>
       </c>
       <c r="N53" t="str">
-        <v>尿糖,糖半定量,U-Glu,腎性糖尿,SGLT2</v>
+        <v>血小板,Plt,platelet,出血,あざ,紫斑,骨髄抑制</v>
       </c>
       <c r="O53" t="str">
         <v/>
@@ -2917,28 +2917,28 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>尿中微量アルブミン</v>
+        <v>RDW-SD</v>
       </c>
       <c r="B54" t="str">
-        <v>U-Alb,MAU</v>
+        <v>RDW-SD</v>
       </c>
       <c r="C54" t="str">
-        <v>30 mg/gCr未満（尿中アルブミン/クレアチニン比）</v>
+        <v>39〜46 fL程度（施設差あり）</v>
       </c>
       <c r="D54" t="str">
-        <v>通常の尿蛋白検査では見つからない、ごく早期の腎症のサイン</v>
+        <v>赤血球の大きさのばらつきを表す指標(絶対値)。鉄欠乏性貧血などの初期変化を捉えやすい</v>
       </c>
       <c r="E54" t="str">
-        <v>この検査は、通常の尿検査ではまだ分からないくらい早い段階の腎臓の変化を見つけるためのものです。数値が高いと、腎症の初期のサインである可能性があります。</v>
+        <v>RDW-SDは、赤血球の大きさがどれくらいバラバラになっているかを表す数値です。貧血の原因を調べる際、鉄が足りなくなり始めた早い段階での変化を捉えるのに役立ちます。</v>
       </c>
       <c r="F54" t="str">
-        <v>糖尿病性腎症の早期段階、高血圧</v>
+        <v>鉄欠乏性貧血の初期、混合性貧血（複数の原因が重なっている状態）、赤血球産生の乱れ</v>
       </c>
       <c r="G54" t="str">
-        <v>血糖・血圧のコントロール状況を確認する。減塩や適正体重の維持など生活習慣の見直しも早期腎症の進行予防に役立つことを伝える</v>
+        <v/>
       </c>
       <c r="H54" t="str">
-        <v>NSAIDsなど腎機能を悪化させる薬剤。ACE阻害薬・ARB・SGLT2阻害薬は低下させる方向に働く</v>
+        <v/>
       </c>
       <c r="I54" t="str">
         <v/>
@@ -2950,39 +2950,39 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>糖尿病腎症の早期発見に重要な検査。血糖・血圧コントロールで改善しうる段階なので、早期介入の意義を伝える</v>
+        <v>MCVが正常範囲でもRDWが上昇している場合、鉄欠乏の初期段階を示唆することがある。MCV・MCHと合わせて評価する</v>
       </c>
       <c r="M54" t="str">
-        <v>糖尿病,腎機能</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="N54" t="str">
-        <v>微量アルブミン,U-Alb,MAU,糖尿病性腎症,早期腎症</v>
+        <v>RDW-SD,赤血球分布幅,貧血,鉄欠乏</v>
       </c>
       <c r="O54" t="str">
-        <v/>
+        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>C反応性蛋白（CRP）</v>
+        <v>RDW-CV</v>
       </c>
       <c r="B55" t="str">
-        <v>CRP</v>
+        <v>RDW-CV</v>
       </c>
       <c r="C55" t="str">
-        <v>0.3 mg/dL未満（施設差あり）</v>
+        <v>11.5〜14.5%程度（施設差あり）</v>
       </c>
       <c r="D55" t="str">
-        <v>体のどこかに炎症や感染が起きていないかを鋭敏に反映する数値</v>
+        <v>赤血球の大きさのばらつきを割合(%)で表した指標</v>
       </c>
       <c r="E55" t="str">
-        <v>CRPは、体に炎症や感染が起きると数時間〜半日程度で急激に上昇する数値です。風邪のようなウイルス感染から細菌感染、体のどこかの炎症まで、幅広く反応するため、体調の変化を早期に捉える手がかりになります。</v>
+        <v>RDW-CVもRDW-SDと同じく、赤血球の大きさのばらつきを表す数値ですが、こちらは割合(%)で示されます。貧血のタイプを見分ける手がかりになります。</v>
       </c>
       <c r="F55" t="str">
-        <v>細菌感染症、ウイルス感染症、自己免疫疾患（関節リウマチなど）、悪性腫瘍、組織の損傷（術後・心筋梗塞など）</v>
+        <v>鉄欠乏性貧血、ビタミンB12・葉酸欠乏性貧血、混合性貧血</v>
       </c>
       <c r="G55" t="str">
-        <v>発熱、痛み、腫れなど炎症症状の有無を確認する</v>
+        <v/>
       </c>
       <c r="H55" t="str">
         <v/>
@@ -2997,89 +2997,89 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>白血球数と合わせて感染・炎症の程度を評価する。上昇・低下のタイミングは白血球より半日〜1日程度遅れる傾向があるため、経過を追う際は採血のタイミングに注意</v>
+        <v>RDW-SDと同様の意味を持つ指標。MCVが小さくRDWが高ければ鉄欠乏性貧血、MCVが大きくRDWが高ければビタミンB12・葉酸欠乏を疑う手がかりになる</v>
       </c>
       <c r="M55" t="str">
-        <v/>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="N55" t="str">
-        <v>CRP,炎症,感染</v>
+        <v>RDW-CV,赤血球分布幅,貧血,ビタミンB12,葉酸</v>
       </c>
       <c r="O55" t="str">
-        <v/>
+        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>PT-INR（プロトロンビン時間国際標準比）</v>
+        <v>好中球実数値</v>
       </c>
       <c r="B56" t="str">
-        <v>PT-INR,INR</v>
+        <v>Neutro#,ANC</v>
       </c>
       <c r="C56" t="str">
-        <v>治療域の目安 1.6〜3.0（ワルファリン服用時。年齢・疾患により異なる）</v>
+        <v>2,000〜7,500 /μL程度（施設差あり、白血球数×好中球%で算出）</v>
       </c>
       <c r="D56" t="str">
-        <v>血液の固まりやすさを表す数値で、ワルファリンの効き具合を確認するために使う</v>
+        <v>好中球の絶対数。感染症リスクを判断する上で割合(%)より重要な指標</v>
       </c>
       <c r="E56" t="str">
-        <v>PT-INRは血液が固まるまでの時間をもとにした数値で、ワルファリンというお薬を飲んでいる方の効き具合を確認するために測ります。数値が高いほど血液が固まりにくく出血しやすい状態、低いほど血栓ができやすい状態を示します。</v>
+        <v>これは好中球の実際の数を表す数値です。割合(%)だけでなく、実際の数がどれくらいあるかを見ることで、感染症にかかりやすい状態かどうかをより正確に判断できます。</v>
       </c>
       <c r="F56" t="str">
-        <v>ワルファリンの効きすぎ、肝機能低下、ビタミンK不足、納豆・青汁など摂取量の変化</v>
+        <v>細菌感染症、炎症、ステロイド使用</v>
       </c>
       <c r="G56" t="str">
-        <v>歯ぐきや鼻からの出血、あざ、黒い便などの出血症状がないか確認する。納豆・クロレラ・青汁などビタミンKを多く含む食品の摂取状況を確認する</v>
+        <v/>
       </c>
       <c r="H56" t="str">
-        <v>ワルファリンの過量。ワルファリン服用中はST合剤・マクロライド系・フルコナゾール等の相互作用やビタミンK摂取量の変化にも注意</v>
+        <v/>
       </c>
       <c r="I56" t="str">
-        <v>ワルファリンの効き不足、飲み忘れ、ビタミンK摂取量の急激な増加</v>
+        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、メルカゾールなど薬剤性の無顆粒球症（1,000/μL未満で好中球減少症、500/μL未満で重症感染リスクが著しく上昇）</v>
       </c>
       <c r="J56" t="str">
-        <v>服薬状況（飲み忘れ）を確認する。片側のむくみ・しびれ・胸痛など血栓症状がないか確認する</v>
+        <v>発熱、のどの痛みなど感染症状の初期サインがないか確認する。人混みを避け、手洗い・うがいを徹底するよう伝える</v>
       </c>
       <c r="K56" t="str">
-        <v>ワルファリン服用中で低値の場合は効果不十分の可能性。ビタミンK摂取量の変化や、リファンピシン・カルバマゼピン・バルビツール酸系など代謝を促進する薬との併用を確認</v>
+        <v>抗がん剤、メルカゾール(無顆粒球症)、クロザピン、サラゾスルファピリジン</v>
       </c>
       <c r="L56" t="str">
-        <v>治療域は疾患・年齢によって異なる（例：非弁膜症性心房細動の高齢者では1.6〜2.6が目安になることが多い）。多くの薬剤・食品と相互作用があるため新規薬剤追加時は必ず確認する。DOAC（エリキュース、リクシアナ、プラザキサなど）ではPT-INRのモニタリングは不要</v>
+        <v>抗がん剤・メルカゾール・カルバマゼピンなど骨髄抑制のリスクがある薬剤使用中は特に重視すべき数値。500/μL未満は発熱性好中球減少症のリスクが高く緊急性が高い</v>
       </c>
       <c r="M56" t="str">
-        <v>抗凝固療法（心房細動・血栓症）</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N56" t="str">
-        <v>PT-INR,INR,プロトロンビン時間,ワルファリン,ワーファリン,抗凝固</v>
+        <v>好中球実数値,好中球数,ANC,無顆粒球症,発熱性好中球減少症</v>
       </c>
       <c r="O56" t="str">
-        <v>食事と栄養 p.221（心疾患Q93 ワルファリン服用中のビタミンK摂取）</v>
+        <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>骨型酒石酸抵抗性フォスファターゼ（TRACP-5b）</v>
+        <v>好酸球実数値</v>
       </c>
       <c r="B57" t="str">
-        <v>TRACP-5b</v>
+        <v>Eosino#</v>
       </c>
       <c r="C57" t="str">
-        <v>120〜420 mU/dL</v>
+        <v>100〜500 /μL程度（施設差あり）</v>
       </c>
       <c r="D57" t="str">
-        <v>骨がどれくらい壊されているかを見る検査。骨は「古い骨を壊して新しい骨を作る」入れ替えを繰り返しており、骨を壊す細胞が活発だとこの物質が血液中に増える。</v>
+        <v>好酸球の絶対数。アレルギーや薬剤反応の程度をより正確に評価できる</v>
       </c>
       <c r="E57" t="str">
-        <v>この検査は、骨がどれくらい早く減っていないかを見るものです。数値が高いと、骨が弱くなりやすい状態の目安になります。</v>
+        <v>これは好酸球の実際の数を表す数値です。割合(%)だけでなく実数を見ることで、アレルギー反応の強さをより正確に把握できます。</v>
       </c>
       <c r="F57" t="str">
-        <v>骨粗鬆症、骨代謝回転（骨がこわれるスピード）が活発な状態</v>
+        <v>アレルギー性疾患、薬剤アレルギー、寄生虫感染</v>
       </c>
       <c r="G57" t="str">
-        <v>カルシウム・ビタミンDの摂取や、適度な荷重運動（ウォーキングなど）を意識するよう伝える</v>
+        <v>新しく始めた薬がないか確認する</v>
       </c>
       <c r="H57" t="str">
-        <v/>
+        <v>薬剤性好酸球増多(抗菌薬・NSAIDs・抗てんかん薬など)。発熱や皮疹を伴う場合はDRESS症候群にも注意</v>
       </c>
       <c r="I57" t="str">
         <v/>
@@ -3091,13 +3091,13 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>「骨を壊す側」の指標。「骨を作る側」の検査と合わせて評価する。数値だけで診断はしない</v>
+        <v>薬剤性過敏症症候群(DIHS)などでは著明な好酸球増多を認めることがあり、原因薬剤の特定に役立つ</v>
       </c>
       <c r="M57" t="str">
-        <v>骨粗鬆症</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N57" t="str">
-        <v>TRACP-5b,骨型酒石酸抵抗性フォスファターゼ,骨粗鬆症,骨代謝</v>
+        <v>好酸球実数値,好酸球数,アレルギー,DIHS</v>
       </c>
       <c r="O57" t="str">
         <v/>
@@ -3105,22 +3105,22 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>骨型アルカリフォスファターゼ</v>
+        <v>好塩基球実数値</v>
       </c>
       <c r="B58" t="str">
-        <v>BAP</v>
+        <v>Baso#</v>
       </c>
       <c r="C58" t="str">
-        <v>男性 3.7〜20.9 μg/L、女性（閉経前）2.9〜14.5 μg/L（施設差あり）</v>
+        <v>0〜100 /μL程度（施設差あり）</v>
       </c>
       <c r="D58" t="str">
-        <v>ALPのうち骨に由来する成分だけを測定し、骨が作られる勢い（骨形成）を反映する</v>
+        <v>好塩基球の絶対数</v>
       </c>
       <c r="E58" t="str">
-        <v>骨型ALPは、通常のALP（アルカリフォスファターゼ）の中でも、骨で作られる成分だけを選んで測定するものです。骨を新しく作る働きがどれくらい活発かを見る指標として、骨粗鬆症の治療効果判定などに使われます。</v>
+        <v>これは好塩基球の実際の数を表す数値です。数がとても少ない種類の血球なので、通常は大きな変動を示すことは多くありません。</v>
       </c>
       <c r="F58" t="str">
-        <v>骨代謝回転の亢進（骨粗鬆症、骨折治癒過程、骨形成促進薬による治療効果、Paget病、骨転移）</v>
+        <v>慢性骨髄性白血病などの血液疾患、アレルギー性疾患</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -3129,7 +3129,7 @@
         <v/>
       </c>
       <c r="I58" t="str">
-        <v>骨形成の低下</v>
+        <v/>
       </c>
       <c r="J58" t="str">
         <v/>
@@ -3138,13 +3138,13 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>通常のALPと異なり肝臓の影響を受けにくいため、肝機能異常がある患者でも骨代謝を評価しやすい。P1NPと同じ「骨を作る側」の指標で、骨形成促進薬（テリパラチド等）の効果判定に使われる</v>
+        <v>単独での臨床的意義は乏しく、他の血球指標（白血球分画全体）と合わせて評価する</v>
       </c>
       <c r="M58" t="str">
-        <v>骨粗鬆症</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N58" t="str">
-        <v>骨型ALP,BAP,骨型アルカリフォスファターゼ,骨形成マーカー</v>
+        <v>好塩基球実数値,好塩基球数</v>
       </c>
       <c r="O58" t="str">
         <v/>
@@ -3152,72 +3152,72 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>25-ヒドロキシビタミンD</v>
+        <v>リンパ球実数値</v>
       </c>
       <c r="B59" t="str">
-        <v>25(OH)D</v>
+        <v>Lympho#,ALC</v>
       </c>
       <c r="C59" t="str">
-        <v>30 ng/mL以上：充足、20〜30 ng/mL：不足、20 ng/mL未満：欠乏（施設差あり）</v>
+        <v>1,000〜3,600 /μL程度（施設差あり）</v>
       </c>
       <c r="D59" t="str">
-        <v>体内のビタミンDの蓄え具合を反映する指標。カルシウムの吸収や骨の健康に関わる</v>
+        <v>リンパ球の絶対数。免疫力の目安として使われる</v>
       </c>
       <c r="E59" t="str">
-        <v>この検査は、体の中にビタミンDがどれくらい蓄えられているかを見るものです。ビタミンDは、食事から摂ったカルシウムを腸で吸収するのを助ける働きがあり、不足すると骨がもろくなりやすくなります。</v>
+        <v>これはリンパ球の実際の数を表す数値です。免疫力の目安の一つとして使われ、抗がん剤や免疫抑制剤の副作用モニタリングにも用いられます。</v>
       </c>
       <c r="F59" t="str">
-        <v>ビタミンD製剤の過剰摂取</v>
+        <v>ウイルス感染症、リンパ性白血病などの血液疾患</v>
       </c>
       <c r="G59" t="str">
-        <v>活性型ビタミンD3製剤やサプリメントの摂取量を確認する。高カルシウム血症の症状（吐き気、便秘、多尿など）がないか確認する</v>
+        <v/>
       </c>
       <c r="H59" t="str">
-        <v>活性型/天然型ビタミンD製剤の過量投与</v>
+        <v/>
       </c>
       <c r="I59" t="str">
-        <v>日光暴露不足、食事摂取不足、高齢、腸疾患による吸収不良、肝・腎機能低下（活性化障害）</v>
+        <v>抗がん剤・免疫抑制剤・ステロイドの使用、強いストレス、AIDSなどの免疫不全</v>
       </c>
       <c r="J59" t="str">
-        <v>適度な日光浴、魚類・きのこ類などビタミンDを多く含む食品の摂取を意識するとよいことを伝える</v>
+        <v>感染予防（手洗い・うがい、人混みを避ける）を意識するよう伝える</v>
       </c>
       <c r="K59" t="str">
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>骨粗鬆症治療における活性型ビタミンD3製剤の効果判定や、投与量調整の参考に用いられる。腎機能低下患者では活性化障害により25(OH)Dが正常でも活性型が不足することがある点に注意</v>
+        <v>免疫抑制剤・抗がん剤治療中のモニタリング指標としても使われる。著明な低下時は日和見感染のリスクが高まる</v>
       </c>
       <c r="M59" t="str">
-        <v>骨粗鬆症</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N59" t="str">
-        <v>25(OH)D,ビタミンD,25-ヒドロキシビタミンD,ビタミンD欠乏,骨粗鬆症</v>
+        <v>リンパ球実数値,リンパ球数,ALC,免疫抑制剤,日和見感染</v>
       </c>
       <c r="O59" t="str">
-        <v>食事と栄養 p.38（ビタミンD）</v>
+        <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ucOC（低カルボキシル化オステオカルシン）</v>
+        <v>単球実数値</v>
       </c>
       <c r="B60" t="str">
-        <v>ucOC</v>
+        <v>Mono#</v>
       </c>
       <c r="C60" t="str">
-        <v>4.5 ng/mL未満（施設差あり）</v>
+        <v>200〜600 /μL程度（施設差あり）</v>
       </c>
       <c r="D60" t="str">
-        <v>ビタミンKが不足していないかを反映する骨の指標</v>
+        <v>単球の絶対数</v>
       </c>
       <c r="E60" t="str">
-        <v>ucOCは、骨を作るために必要なビタミンKが体の中で足りているかどうかを反映する検査です。数値が高いとビタミンK不足が疑われます。</v>
+        <v>これは単球の実際の数を表す数値です。慢性的な炎症や感染症の状態を把握する材料の一つになります。</v>
       </c>
       <c r="F60" t="str">
-        <v>ビタミンK不足状態</v>
+        <v>慢性感染症、炎症性疾患、血液疾患</v>
       </c>
       <c r="G60" t="str">
-        <v>ビタミンK2製剤(骨粗鬆症治療薬)の適応が検討されているか確認する。ワルファリン服用中の患者では、納豆などビタミンKを多く含む食品の急な摂取量の変化を避けるよう説明する</v>
+        <v/>
       </c>
       <c r="H60" t="str">
         <v/>
@@ -3232,92 +3232,92 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>ビタミンK2製剤（骨粗鬆症治療薬）の適応判断や効果判定に使われる</v>
+        <v>単独での臨床的意義は乏しく、他の血球指標と合わせて評価する</v>
       </c>
       <c r="M60" t="str">
-        <v>骨粗鬆症</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N60" t="str">
-        <v>ucOC,オステオカルシン,ビタミンK</v>
+        <v>単球実数値,単球数</v>
       </c>
       <c r="O60" t="str">
-        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
+        <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>PTH（副甲状腺ホルモン）</v>
+        <v>好中球</v>
       </c>
       <c r="B61" t="str">
-        <v>PTH</v>
+        <v>Neutro,Neut%</v>
       </c>
       <c r="C61" t="str">
-        <v>10〜65 pg/mL（施設差あり）</v>
+        <v>40〜75%程度（施設差あり）</v>
       </c>
       <c r="D61" t="str">
-        <v>血液中のカルシウム濃度を調節するホルモン</v>
+        <v>白血球の中で最も多くを占め、細菌感染と戦う主力の免疫細胞の割合</v>
       </c>
       <c r="E61" t="str">
-        <v>PTHは、血液中のカルシウム濃度を一定に保つために働くホルモンです。カルシウムが低くなると分泌が増え、骨からカルシウムを取り出したり、腎臓での再吸収を促したりして数値を戻そうとします。</v>
+        <v>好中球は、白血球の中で最も数が多く、細菌が体に入ってきたときに真っ先に戦ってくれる免疫細胞です。感染症や炎症があると増え、逆に薬の副作用などで減ることがあります。</v>
       </c>
       <c r="F61" t="str">
-        <v>原発性・二次性副甲状腺機能亢進症（腎不全に伴うものなど）</v>
+        <v>細菌感染症、炎症、ストレス、ステロイド使用</v>
       </c>
       <c r="G61" t="str">
-        <v/>
+        <v>発熱や炎症症状がないか確認する</v>
       </c>
       <c r="H61" t="str">
         <v/>
       </c>
       <c r="I61" t="str">
-        <v>副甲状腺機能低下症</v>
+        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、ウイルス感染、メルカゾールなど薬剤性の無顆粒球症</v>
       </c>
       <c r="J61" t="str">
-        <v/>
+        <v>発熱やのどの痛みなど感染症状の初期サインがないか確認する</v>
       </c>
       <c r="K61" t="str">
-        <v/>
+        <v>抗がん剤、メルカゾール(無顆粒球症)、クロザピン、サラゾスルファピリジン</v>
       </c>
       <c r="L61" t="str">
-        <v>骨粗鬆症の二次性原因（副甲状腺機能亢進症）を除外するための検査。カルシウム・リンと合わせて評価する</v>
+        <v>好中球の絶対数（好中球実数値）が500/μL未満になると重篤な感染症のリスクが高まる。割合(%)だけでなく実数値も合わせて確認する</v>
       </c>
       <c r="M61" t="str">
-        <v>骨粗鬆症</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N61" t="str">
-        <v>PTH,副甲状腺ホルモン,パラトルモン</v>
+        <v>好中球,Neutro,Neut,感染症,無顆粒球症</v>
       </c>
       <c r="O61" t="str">
-        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
+        <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>尿中NTX</v>
+        <v>好酸球</v>
       </c>
       <c r="B62" t="str">
-        <v>NTX</v>
+        <v>Eosino,Eos%</v>
       </c>
       <c r="C62" t="str">
-        <v>施設差が大きく一律の記載が難しい（尿中）</v>
+        <v>1〜5%程度（施設差あり）</v>
       </c>
       <c r="D62" t="str">
-        <v>骨が壊されるときに出る、骨吸収マーカーのひとつ</v>
+        <v>アレルギー反応や寄生虫感染に関わる白血球の一種の割合</v>
       </c>
       <c r="E62" t="str">
-        <v>NTXは、骨が壊される（吸収される）ときに尿の中に出てくる物質です。骨粗鬆症の治療薬がどれくらい効いているかを確認するために使われます。</v>
+        <v>好酸球は、アレルギー反応や寄生虫感染と関係が深い免疫細胞です。アレルギー性の病気や薬の副作用（薬疹など）で増えることがあります。</v>
       </c>
       <c r="F62" t="str">
-        <v>骨代謝回転の亢進（骨粗鬆症、閉経後など）</v>
+        <v>アレルギー性疾患（気管支喘息、アトピー性皮膚炎など）、薬剤アレルギー、寄生虫感染</v>
       </c>
       <c r="G62" t="str">
-        <v/>
+        <v>新しく始めた薬がないか確認する。皮疹やかゆみなどアレルギー症状の有無を確認する</v>
       </c>
       <c r="H62" t="str">
-        <v/>
+        <v>薬剤性好酸球増多(抗菌薬・NSAIDs・抗てんかん薬など)。発熱や皮疹を伴う場合はDRESS症候群にも注意</v>
       </c>
       <c r="I62" t="str">
-        <v>骨吸収抑制薬（ビスホスホネート等）による治療効果</v>
+        <v/>
       </c>
       <c r="J62" t="str">
         <v/>
@@ -3326,36 +3326,36 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>治療開始後3〜6か月で再検し、薬の効果判定に使われる。TRACP-5bと同じ「骨を壊す側」の指標</v>
+        <v>薬剤性の好酸球増多は、原因薬剤の中止で改善することが多い。新規薬剤開始後の皮疹・発熱と合わせて薬剤性過敏症症候群(DIHS)を疑う材料になる</v>
       </c>
       <c r="M62" t="str">
-        <v>骨粗鬆症</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N62" t="str">
-        <v>NTX,尿中NTX,骨吸収マーカー</v>
+        <v>好酸球,Eosino,Eos,アレルギー,薬疹,DIHS</v>
       </c>
       <c r="O62" t="str">
-        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
+        <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>カルシトニン</v>
+        <v>好塩基球</v>
       </c>
       <c r="B63" t="str">
-        <v>CT</v>
+        <v>Baso,Baso%</v>
       </c>
       <c r="C63" t="str">
-        <v>男性 9.52 pg/mL未満、女性 6.40 pg/mL未満（施設差あり）</v>
+        <v>0〜2%程度（施設差あり）</v>
       </c>
       <c r="D63" t="str">
-        <v>血液中のカルシウムを下げる方向に働くホルモン</v>
+        <v>白血球の中で最も数が少なく、アレルギー反応に関わる細胞の割合</v>
       </c>
       <c r="E63" t="str">
-        <v>カルシトニンは、PTHとは逆に血液中のカルシウムを下げる方向に働くホルモンです。特定の甲状腺の病気（甲状腺髄様癌）がないかを調べる際にも使われます。</v>
+        <v>好塩基球は白血球の中で最も数が少ない種類で、アレルギー反応や炎症に関わっています。数値の変動が病気の診断に直接使われることは少ない検査です。</v>
       </c>
       <c r="F63" t="str">
-        <v>甲状腺髄様癌、腎不全</v>
+        <v>慢性骨髄性白血病などの血液疾患、アレルギー性疾患、甲状腺機能低下症</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -3373,36 +3373,36 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>骨粗鬆症の二次性原因の除外目的で測定されることがある検査値。同名の薬剤（カルシトニン製剤）と混同しないよう注意</v>
+        <v>単独での臨床的意義は乏しいが、著明な増加は血液疾患（慢性骨髄性白血病等）の可能性があり他の血球指標と合わせて評価する</v>
       </c>
       <c r="M63" t="str">
-        <v>骨粗鬆症</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N63" t="str">
-        <v>カルシトニン,CT</v>
+        <v>好塩基球,Baso,アレルギー,白血病</v>
       </c>
       <c r="O63" t="str">
-        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
+        <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>DPD（デオキシピリジノリン）</v>
+        <v>リンパ球</v>
       </c>
       <c r="B64" t="str">
-        <v>DPD</v>
+        <v>Lympho,Lym%</v>
       </c>
       <c r="C64" t="str">
-        <v>施設差が大きく一律の記載が難しい（尿中）</v>
+        <v>18〜49%程度（施設差あり）</v>
       </c>
       <c r="D64" t="str">
-        <v>骨のコラーゲンが壊れるときに出る、骨吸収マーカーのひとつ</v>
+        <v>ウイルス感染と戦い、免疫の記憶を担う白血球の割合</v>
       </c>
       <c r="E64" t="str">
-        <v>DPDも、骨が壊されるときに尿に出てくる物質の一つです。NTXと同じように、骨粗鬆症治療薬の効果を確認するために使われます。</v>
+        <v>リンパ球は、ウイルスと戦ったり、一度かかった病気を記憶して免疫をつくったりする細胞です。ウイルス感染で増え、抗がん剤の副作用や強いストレスで減ることがあります。</v>
       </c>
       <c r="F64" t="str">
-        <v>骨代謝回転の亢進（骨粗鬆症など）</v>
+        <v>ウイルス感染症、リンパ性白血病などの血液疾患、百日咳</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -3411,54 +3411,54 @@
         <v/>
       </c>
       <c r="I64" t="str">
-        <v>骨吸収抑制薬による治療効果</v>
+        <v>抗がん剤・免疫抑制剤・ステロイドの使用、強いストレス、AIDSなどの免疫不全</v>
       </c>
       <c r="J64" t="str">
-        <v/>
+        <v>免疫が下がっている可能性があるため、感染予防（手洗い・うがい、人混みを避ける）を意識するよう伝える</v>
       </c>
       <c r="K64" t="str">
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>NTX・CTXと同じ「骨を壊す側」の指標。食事の影響を受けにくいとされる</v>
+        <v>ステロイド・免疫抑制剤使用中はリンパ球減少による易感染性に注意。好中球と逆方向に動くことが多い（ウイルス感染ではリンパ球優位、細菌感染では好中球優位になりやすい）</v>
       </c>
       <c r="M64" t="str">
-        <v>骨粗鬆症</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N64" t="str">
-        <v>DPD,デオキシピリジノリン,骨吸収マーカー</v>
+        <v>リンパ球,Lympho,Lym,ウイルス感染,免疫抑制剤,ステロイド</v>
       </c>
       <c r="O64" t="str">
-        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
+        <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>CTX</v>
+        <v>尿蛋白（随時尿）</v>
       </c>
       <c r="B65" t="str">
-        <v>CTX</v>
+        <v>尿蛋白,U-pro</v>
       </c>
       <c r="C65" t="str">
-        <v>施設差が大きく一律の記載が難しい（血清・尿中）</v>
+        <v>陰性（－）〜弱陽性</v>
       </c>
       <c r="D65" t="str">
-        <v>骨のコラーゲンが壊れるときに出る、骨吸収マーカーのひとつ</v>
+        <v>腎臓から本来漏れないはずのたんぱくが尿に出ていないかを見る検査</v>
       </c>
       <c r="E65" t="str">
-        <v>CTXも、骨が壊されるときに血液や尿に出てくる物質です。骨粗鬆症治療薬（骨を壊すのを抑える薬）の効果を確認するために使われます。</v>
+        <v>この検査は、腎臓のろ過機能に負担がかかっていないかを見るものです。本来、たんぱく質は尿にほとんど出ませんが、腎臓に負担がかかると漏れ出るようになります。</v>
       </c>
       <c r="F65" t="str">
-        <v>骨代謝回転の亢進（骨粗鬆症など）</v>
+        <v>糖尿病性腎症、腎炎、高血圧性腎硬化症、発熱・運動後の一過性のもの</v>
       </c>
       <c r="G65" t="str">
-        <v/>
+        <v>発熱・激しい運動の直後でないか確認する(一過性のことがある)。持続する場合は塩分の摂りすぎに注意し、むくみの有無もあわせて確認する</v>
       </c>
       <c r="H65" t="str">
-        <v/>
+        <v>NSAIDs、造影剤、アミノグリコシド系、バンコマイシン、金製剤</v>
       </c>
       <c r="I65" t="str">
-        <v>骨吸収抑制薬による治療効果</v>
+        <v/>
       </c>
       <c r="J65" t="str">
         <v/>
@@ -3467,36 +3467,36 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>NTX・DPDと同じ「骨を壊す側」の指標。血清・尿中いずれでも測定されることがある</v>
+        <v>発熱・激しい運動・起立性蛋白尿など生理的な要因でも陽性になることがある。持続する場合に腎症の進行を疑う</v>
       </c>
       <c r="M65" t="str">
-        <v>骨粗鬆症</v>
+        <v>糖尿病,腎機能</v>
       </c>
       <c r="N65" t="str">
-        <v>CTX,骨吸収マーカー</v>
+        <v>尿蛋白,U-pro,腎症,たんぱく尿</v>
       </c>
       <c r="O65" t="str">
-        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
+        <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>P1NP</v>
+        <v>尿クレアチニン（随時尿）</v>
       </c>
       <c r="B66" t="str">
-        <v>P1NP</v>
+        <v>尿CRE</v>
       </c>
       <c r="C66" t="str">
-        <v>施設差が大きく一律の記載が難しい（血清）</v>
+        <v>随時尿は主に他項目の濃度補正に利用（単独の基準値は設けにくい）</v>
       </c>
       <c r="D66" t="str">
-        <v>骨が新しく作られるときに出る、骨形成マーカーのひとつ</v>
+        <v>随時尿中のクレアチニン濃度。他の尿検査項目を薄まり具合で補正するための基準として使う</v>
       </c>
       <c r="E66" t="str">
-        <v>P1NPは、CTXなどとは逆に、骨が新しく作られるときに血液中に出てくる物質です。骨を作る力を高める薬（テリパラチドなど）の効果を確認するために使われます。</v>
+        <v>この数値は、尿がどれくらい薄まっているかを確認するための基準として使われます。他の尿検査の結果（蛋白やアルブミンなど）をこの値で割って補正することで、水分摂取量による影響を減らして正確に評価できます。</v>
       </c>
       <c r="F66" t="str">
-        <v>骨代謝回転の亢進、骨形成促進薬による治療効果</v>
+        <v/>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -3505,7 +3505,7 @@
         <v/>
       </c>
       <c r="I66" t="str">
-        <v>骨形成の低下</v>
+        <v>尿が薄い（水分摂取が多い、腎機能低下）状態</v>
       </c>
       <c r="J66" t="str">
         <v/>
@@ -3514,83 +3514,83 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>TRACP-5b等「骨を壊す側」の指標とは逆の、「骨を作る側」の指標。骨形成促進薬（テリパラチド等）の効果判定に使われる</v>
+        <v>尿中アルブミン/Cr比、尿蛋白/Cr比など、他項目の補正計算に使われる。単独の高低に臨床的意味は乏しい</v>
       </c>
       <c r="M66" t="str">
-        <v>骨粗鬆症</v>
+        <v>腎機能</v>
       </c>
       <c r="N66" t="str">
-        <v>P1NP,骨形成マーカー</v>
+        <v>尿CRE,尿クレアチニン,随時尿,補正,蛋白クレアチニン比</v>
       </c>
       <c r="O66" t="str">
-        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
+        <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>血清鉄（Fe）</v>
+        <v>尿蛋白定量</v>
       </c>
       <c r="B67" t="str">
-        <v>Fe</v>
+        <v>U-Pro定量,蛋白/Cr比</v>
       </c>
       <c r="C67" t="str">
-        <v>60〜200 μg/dL（施設差あり）</v>
+        <v>0.15 g/gCr未満</v>
       </c>
       <c r="D67" t="str">
-        <v>血液中を流れている鉄の量</v>
+        <v>随時尿から尿蛋白の量を具体的な数値として評価する検査。ネフローゼ等の重症度判定に使う</v>
       </c>
       <c r="E67" t="str">
-        <v>この検査は、今血液の中を流れている鉄の量を見るものです。低いと、体の中で鉄が不足している可能性があります。</v>
+        <v>これは、尿に出ているたんぱくの量を具体的な数値で見る検査です。試験紙での陽性・陰性の判定だけでなく、実際にどれくらいの量が出ているかを把握できます。</v>
       </c>
       <c r="F67" t="str">
-        <v>鉄剤の過剰摂取、溶血、肝疾患</v>
+        <v>腎症の進行（糖尿病性腎症、慢性腎臓病など）、ネフローゼ症候群（3.5 g/gCr以上が目安）</v>
       </c>
       <c r="G67" t="str">
-        <v/>
+        <v>持続する場合は塩分の摂りすぎに注意し、むくみの有無も確認する。腎臓内科でのフォロー状況もあわせて確認する</v>
       </c>
       <c r="H67" t="str">
-        <v>鉄剤の過量摂取(小児の誤飲を含む)</v>
+        <v>NSAIDs、造影剤、アミノグリコシド系、バンコマイシン</v>
       </c>
       <c r="I67" t="str">
-        <v>鉄欠乏性貧血、慢性炎症、出血</v>
+        <v/>
       </c>
       <c r="J67" t="str">
-        <v>鉄分の多い食品（レバー・赤身肉・魚・ほうれん草など）を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える</v>
+        <v/>
       </c>
       <c r="K67" t="str">
-        <v>プロトンポンプ阻害薬(PPI)・H2ブロッカーは胃酸分泌抑制により鉄の吸収を低下させうる</v>
+        <v/>
       </c>
       <c r="L67" t="str">
-        <v>血清鉄は日内変動が大きい。単独で判断せず総鉄結合能・フェリチンと合わせて評価する</v>
+        <v>CKD診療ガイドラインの重症度分類（尿蛋白量による区分）にも使われる定量指標。試験紙法の半定量結果より治療効果判定に適する</v>
       </c>
       <c r="M67" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>腎機能,糖尿病</v>
       </c>
       <c r="N67" t="str">
-        <v>血清鉄,Fe,鉄欠乏性貧血</v>
+        <v>尿蛋白,随時尿,定量,蛋白クレアチニン比,ネフローゼ</v>
       </c>
       <c r="O67" t="str">
-        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
+        <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>総鉄結合能（TIBC）</v>
+        <v>尿pH</v>
       </c>
       <c r="B68" t="str">
-        <v>TIBC</v>
+        <v>尿pH</v>
       </c>
       <c r="C68" t="str">
-        <v>250〜360 μg/dL（施設差あり）</v>
+        <v>4.5〜7.5程度（弱酸性が多い）</v>
       </c>
       <c r="D68" t="str">
-        <v>血液中のトランスフェリンが鉄と結合できる総量</v>
+        <v>尿の酸性・アルカリ性の度合い。食事や感染症、体の状態を反映する</v>
       </c>
       <c r="E68" t="str">
-        <v>TIBCは、血液中でトランスフェリンという物質が鉄を運べる最大量を表します。体の中の鉄が不足すると、少しでも多く鉄を運ぼうとしてこの数値が上がる性質があります。</v>
+        <v>尿のpHは酸性・アルカリ性のバランスを表します。食事の内容や感染症、体の代謝状態によって変化します。単独で大きな問題を示すことは少ない検査です。</v>
       </c>
       <c r="F68" t="str">
-        <v>鉄欠乏性貧血（＞360 μg/dLが目安）</v>
+        <v>尿路感染症（尿素分解菌によるもの）、野菜中心の食事、過換気</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -3599,54 +3599,54 @@
         <v/>
       </c>
       <c r="I68" t="str">
-        <v>慢性炎症、肝疾患、ネフローゼ症候群</v>
+        <v>高たんぱく食、糖尿病性ケトアシドーシス、痛風発作時（酸性尿は尿酸結石のリスクを高める）</v>
       </c>
       <c r="J68" t="str">
-        <v/>
+        <v>痛風・尿酸結石がある場合は、野菜など尿をアルカリ化する食品を意識するとよいことを伝える</v>
       </c>
       <c r="K68" t="str">
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>鉄が不足すると、体はより多く運ぼうとしてTIBCが上昇する。UIBC・血清鉄と併せて評価する</v>
+        <v>高尿酸血症・尿酸結石の患者では尿pHが酸性に傾いていないか確認する。尿アルカリ化薬（ウラリットなど）の効果判定にも使う</v>
       </c>
       <c r="M68" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>高尿酸血症</v>
       </c>
       <c r="N68" t="str">
-        <v>TIBC,総鉄結合能,鉄欠乏性貧血</v>
+        <v>尿pH,尿酸性度,尿アルカリ化,ウラリット</v>
       </c>
       <c r="O68" t="str">
-        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
+        <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>不飽和鉄結合能（UIBC）</v>
+        <v>尿ケトン体</v>
       </c>
       <c r="B69" t="str">
-        <v>UIBC</v>
+        <v>尿ケトン,Ket</v>
       </c>
       <c r="C69" t="str">
-        <v>170〜300 μg/dL（施設差あり）</v>
+        <v>陰性（－）</v>
       </c>
       <c r="D69" t="str">
-        <v>トランスフェリンのうち、まだ鉄と結合していない余力の部分（UIBC＝TIBC－血清鉄）</v>
+        <v>体がブドウ糖の代わりに脂肪を分解してエネルギーを作っているサイン</v>
       </c>
       <c r="E69" t="str">
-        <v>UIBCは、トランスフェリンのうち、まだ鉄と結合していない「空き容量」の部分を表します。鉄が不足しているときほど、この空き容量は大きくなります。</v>
+        <v>この検査は、体が糖の代わりに脂肪を使ってエネルギーを作っていないかを見るものです。陽性が続くときは、食事や水分、インスリンの使い方を確認する必要があります。</v>
       </c>
       <c r="F69" t="str">
-        <v>鉄欠乏性貧血（＞300 μg/dLが目安）</v>
+        <v>糖尿病の血糖コントロール不良（シックデイ・インスリン不足）、極端な糖質制限、絶食、嘔吐・下痢による脱水</v>
       </c>
       <c r="G69" t="str">
-        <v/>
+        <v>糖尿病治療中の場合はシックデイ時の対応(インスリンを自己中断しない、水分摂取を続けるなど)を確認する。体調不良時の対応方法を事前に説明しておく</v>
       </c>
       <c r="H69" t="str">
-        <v/>
+        <v>SGLT2阻害薬(特に絶食・シックデイ時の正常血糖ケトアシドーシスに注意)</v>
       </c>
       <c r="I69" t="str">
-        <v>慢性炎症、鉄過剰状態</v>
+        <v/>
       </c>
       <c r="J69" t="str">
         <v/>
@@ -3655,36 +3655,36 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>TIBCと同じ方向に動くことが多い。血清鉄・TIBCとあわせて鉄欠乏性貧血と二次性貧血の鑑別に使う</v>
+        <v>陽性かつ高血糖・全身倦怠感が強い場合は糖尿病性ケトアシドーシスの可能性があり緊急性が高い。シックデイルールの説明歴を確認する</v>
       </c>
       <c r="M69" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>糖尿病</v>
       </c>
       <c r="N69" t="str">
-        <v>UIBC,不飽和鉄結合能,鉄欠乏性貧血</v>
+        <v>尿ケトン体,ケトン体,Ket,シックデイ,ケトアシドーシス</v>
       </c>
       <c r="O69" t="str">
-        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
+        <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>トランスフェリン飽和度</v>
+        <v>ウロビリノーゲン</v>
       </c>
       <c r="B70" t="str">
-        <v>TSAT</v>
+        <v>Uro</v>
       </c>
       <c r="C70" t="str">
-        <v>16〜50%程度（施設差あり）</v>
+        <v>正常（±）程度</v>
       </c>
       <c r="D70" t="str">
-        <v>鉄を運ぶ役割のトランスフェリンのうち、実際に鉄を運んでいる割合（血清鉄÷総鉄結合能）</v>
+        <v>肝臓や胆道、赤血球の壊れ方の状態を反映する尿検査項目</v>
       </c>
       <c r="E70" t="str">
-        <v>トランスフェリン飽和度は、鉄を運ぶトランスフェリンのうち、実際にどれくらいが鉄を運んでいるかを割合で表したものです。鉄欠乏性貧血では低くなり、鉄が過剰にたまる病気では高くなります。</v>
+        <v>ウロビリノーゲンは、赤血球やビリルビンが体の中で処理される過程でできる物質です。肝臓の働きが悪くなったり、赤血球が壊れやすくなったりすると、尿の中の量が変化します。</v>
       </c>
       <c r="F70" t="str">
-        <v>鉄過剰症（ヘモクロマトーシスなど）</v>
+        <v>溶血性疾患（赤血球の破壊亢進）、肝機能障害</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3693,7 +3693,7 @@
         <v/>
       </c>
       <c r="I70" t="str">
-        <v>鉄欠乏性貧血（＜16%が目安）</v>
+        <v>胆道閉塞（胆汁が腸に流れず、ウロビリノーゲンが作られない状態）</v>
       </c>
       <c r="J70" t="str">
         <v/>
@@ -3702,92 +3702,92 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>血清鉄をTIBCで割って計算される。鉄剤補充の効果判定にも使われる</v>
+        <v>完全に陰性の場合は胆道閉塞を疑う所見の一つ。肝機能（AST/ALT/ビリルビン）と合わせて評価する</v>
       </c>
       <c r="M70" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>肝機能</v>
       </c>
       <c r="N70" t="str">
-        <v>トランスフェリン飽和度,TSAT,鉄欠乏性貧血</v>
+        <v>ウロビリノーゲン,Uro,溶血,胆道閉塞,肝機能</v>
       </c>
       <c r="O70" t="str">
-        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
+        <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>血清フェリチン</v>
+        <v>尿潜血反応</v>
       </c>
       <c r="B71" t="str">
-        <v>Ferritin</v>
+        <v>尿潜血,U-OB</v>
       </c>
       <c r="C71" t="str">
-        <v>男性 20〜250 ng/mL、女性 10〜120 ng/mL（施設差あり）</v>
+        <v>陰性（－）</v>
       </c>
       <c r="D71" t="str">
-        <v>体に貯蔵されている鉄の量を反映する指標。貧血の症状が出るより早い段階で低下する</v>
+        <v>尿に血液（赤血球）が混じっていないかを見る検査</v>
       </c>
       <c r="E71" t="str">
-        <v>フェリチンは、体に蓄えられている鉄の「貯金」の量を見る検査です。この数値が下がるのは、貧血の症状が出るよりも前の、とても早い段階のサインになります。</v>
+        <v>この検査は、尿に目に見えないくらいの微量の血液が混じっていないかを調べるものです。陽性の場合、腎臓や膀胱、尿路のどこかに炎症や結石などがある可能性があります。</v>
       </c>
       <c r="F71" t="str">
-        <v>炎症性疾患、肝疾患、悪性腫瘍、鉄過剰症（フェリチンは炎症でも上昇するため、貧血の評価では注意が必要）</v>
+        <v>尿路結石、膀胱炎などの尿路感染症、腎炎、腫瘍、月経血の混入、激しい運動後</v>
       </c>
       <c r="G71" t="str">
-        <v/>
+        <v>排尿時の痛みや頻尿、目に見える血尿の有無を確認する。女性は月経の時期と重なっていないか確認する</v>
       </c>
       <c r="H71" t="str">
-        <v/>
+        <v>ワルファリン、DOAC、抗血小板薬など出血傾向を強める薬剤の服用状況を確認</v>
       </c>
       <c r="I71" t="str">
-        <v>鉄欠乏状態（貧血の症状が出る前の早期段階から低下する）</v>
+        <v/>
       </c>
       <c r="J71" t="str">
-        <v>鉄分の多い食品を意識するとともに、貯蔵鉄を補うため治療は数値が正常化してからも継続が必要なことを伝える</v>
+        <v/>
       </c>
       <c r="K71" t="str">
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>貯蔵鉄の指標で鉄欠乏を最も早期に反映する。ただし炎症があると鉄欠乏があっても正常〜高値に出ることがあり、CRP等の炎症所見と合わせて評価する。二次性貧血との鑑別に重要</v>
+        <v>陽性でも尿沈渣で赤血球が確認されない場合は偽陽性（ミオグロビン尿など）のこともある。持続する場合は泌尿器科的な精査が必要</v>
       </c>
       <c r="M71" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>腎機能</v>
       </c>
       <c r="N71" t="str">
-        <v>フェリチン,Ferritin,貯蔵鉄,鉄欠乏</v>
+        <v>尿潜血,潜血反応,U-OB,血尿,尿路結石,膀胱炎</v>
       </c>
       <c r="O71" t="str">
-        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
+        <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>尿中尿酸/クレアチニン比（UUA/UCr）</v>
+        <v>尿糖（半定量）</v>
       </c>
       <c r="B72" t="str">
-        <v>UUA/UCr</v>
+        <v>尿糖,U-Glu</v>
       </c>
       <c r="C72" t="str">
-        <v>0.4〜0.8程度が混合型の目安</v>
+        <v>陰性（－）</v>
       </c>
       <c r="D72" t="str">
-        <v>尿酸が「作られすぎ」か「排泄できていない」かを見分ける比の値</v>
+        <v>尿に糖が漏れ出ていないかを見る検査。血糖値がかなり高いと陽性になる</v>
       </c>
       <c r="E72" t="str">
-        <v>この数値は、体の中で尿酸が「作られすぎている」のか、それとも「うまく排泄できていない」のかを見分けるために使う比の値です。高尿酸血症の治療薬を選ぶときの参考になります。</v>
+        <v>通常、糖は尿にはほとんど出ませんが、血糖値がかなり高くなると尿にあふれ出るようになります。血糖コントロールの目安の一つです。</v>
       </c>
       <c r="F72" t="str">
-        <v>尿酸産生過剰型（0.8以上が目安）</v>
+        <v>糖尿病（血糖値が腎臓で再吸収できる量を超えている状態）、腎性糖尿（血糖値が正常でも体質的に出ることがある）、SGLT2阻害薬服用中（薬の作用で意図的に糖を排泄するため陽性になるのが正常）</v>
       </c>
       <c r="G72" t="str">
-        <v/>
+        <v>SGLT2阻害薬（フォシーガ、ジャディアンスなど）服用中は、陽性が薬の効果によるものであることを説明する。脱水や尿路感染の症状がないかも確認する</v>
       </c>
       <c r="H72" t="str">
-        <v/>
+        <v>SGLT2阻害薬(薬理作用による陽性であれば想定内であることを説明)</v>
       </c>
       <c r="I72" t="str">
-        <v>尿酸排泄低下型（0.4以下が目安）</v>
+        <v/>
       </c>
       <c r="J72" t="str">
         <v/>
@@ -3796,42 +3796,42 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>高尿酸血症は尿酸産生過剰型・排泄低下型・混合型に分類され、この比が目安になる。病型によって使う薬剤（尿酸生成抑制薬か尿酸排泄促進薬か）の選択が変わる</v>
+        <v>SGLT2阻害薬服用中は尿糖陽性が治療効果として想定内であることを患者に伝える。血糖値・HbA1cと合わせて評価する</v>
       </c>
       <c r="M72" t="str">
-        <v>高尿酸血症</v>
+        <v>糖尿病</v>
       </c>
       <c r="N72" t="str">
-        <v>UUA,UCr,尿酸クリアランス,CUA,EUA,尿酸産生過剰型,尿酸排泄低下型</v>
+        <v>尿糖,糖半定量,U-Glu,腎性糖尿,SGLT2</v>
       </c>
       <c r="O72" t="str">
-        <v>食事と栄養 p.180-189（第2部 痛風・高尿酸血症）</v>
+        <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>抗甲状腺マイクロゾーム抗体（抗TPO抗体）</v>
+        <v>尿中微量アルブミン</v>
       </c>
       <c r="B73" t="str">
-        <v>TPOAb</v>
+        <v>U-Alb,MAU</v>
       </c>
       <c r="C73" t="str">
-        <v>陰性（16 IU/mL未満程度、施設差あり）</v>
+        <v>30 mg/gCr未満（尿中アルブミン/クレアチニン比）</v>
       </c>
       <c r="D73" t="str">
-        <v>自分の甲状腺を攻撃する抗体が出ていないかを見る検査</v>
+        <v>通常の尿蛋白検査では見つからない、ごく早期の腎症のサイン</v>
       </c>
       <c r="E73" t="str">
-        <v>この検査は、体の中に自分の甲状腺を誤って攻撃してしまう抗体がないかを見るものです。陽性の場合、橋本病（慢性甲状腺炎）など甲状腺の自己免疫的な炎症が背景にある可能性があります。</v>
+        <v>この検査は、通常の尿検査ではまだ分からないくらい早い段階の腎臓の変化を見つけるためのものです。数値が高いと、腎症の初期のサインである可能性があります。</v>
       </c>
       <c r="F73" t="str">
-        <v>橋本病（慢性甲状腺炎）、バセドウ病などの自己免疫性甲状腺疾患</v>
+        <v>糖尿病性腎症の早期段階、高血圧</v>
       </c>
       <c r="G73" t="str">
-        <v/>
+        <v>血糖・血圧のコントロール状況を確認する。減塩や適正体重の維持など生活習慣の見直しも早期腎症の進行予防に役立つことを伝える</v>
       </c>
       <c r="H73" t="str">
-        <v/>
+        <v>NSAIDsなど腎機能を悪化させる薬剤。ACE阻害薬・ARB・SGLT2阻害薬は低下させる方向に働く</v>
       </c>
       <c r="I73" t="str">
         <v/>
@@ -3843,39 +3843,39 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>陽性でも必ずしも甲状腺機能異常があるとは限らない。TSH・FT4など甲状腺ホルモンの数値と合わせて評価する</v>
+        <v>糖尿病腎症の早期発見に重要な検査。血糖・血圧コントロールで改善しうる段階なので、早期介入の意義を伝える</v>
       </c>
       <c r="M73" t="str">
-        <v>甲状腺疾患</v>
+        <v>糖尿病,腎機能</v>
       </c>
       <c r="N73" t="str">
-        <v>抗TPO抗体,抗甲状腺マイクロゾーム抗体,TPOAb,橋本病</v>
+        <v>微量アルブミン,U-Alb,MAU,糖尿病性腎症,早期腎症</v>
       </c>
       <c r="O73" t="str">
-        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
+        <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>抗サイログロブリン抗体</v>
+        <v>C反応性蛋白（CRP）</v>
       </c>
       <c r="B74" t="str">
-        <v>TgAb</v>
+        <v>CRP</v>
       </c>
       <c r="C74" t="str">
-        <v>陰性（28 IU/mL未満程度、施設差あり）</v>
+        <v>0.3 mg/dL未満（施設差あり）</v>
       </c>
       <c r="D74" t="str">
-        <v>甲状腺のたんぱく質（サイログロブリン）への抗体が出ていないかを見る検査</v>
+        <v>体のどこかに炎症や感染が起きていないかを鋭敏に反映する数値</v>
       </c>
       <c r="E74" t="str">
-        <v>この検査も、抗TPO抗体と同じく、甲状腺に対する自己免疫の有無を見るものです。あわせて調べることで橋本病などの診断の参考にします。</v>
+        <v>CRPは、体に炎症や感染が起きると数時間〜半日程度で急激に上昇する数値です。風邪のようなウイルス感染から細菌感染、体のどこかの炎症まで、幅広く反応するため、体調の変化を早期に捉える手がかりになります。</v>
       </c>
       <c r="F74" t="str">
-        <v>橋本病（慢性甲状腺炎）、バセドウ病などの自己免疫性甲状腺疾患</v>
+        <v>細菌感染症、ウイルス感染症、自己免疫疾患（関節リウマチなど）、悪性腫瘍、組織の損傷（術後・心筋梗塞など）</v>
       </c>
       <c r="G74" t="str">
-        <v/>
+        <v>発熱、痛み、腫れなど炎症症状の有無を確認する</v>
       </c>
       <c r="H74" t="str">
         <v/>
@@ -3890,92 +3890,92 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>抗TPO抗体とあわせて測定されることが多い。単独の高値だけで治療方針が決まるわけではない</v>
+        <v>白血球数と合わせて感染・炎症の程度を評価する。上昇・低下のタイミングは白血球より半日〜1日程度遅れる傾向があるため、経過を追う際は採血のタイミングに注意</v>
       </c>
       <c r="M74" t="str">
-        <v>甲状腺疾患</v>
+        <v/>
       </c>
       <c r="N74" t="str">
-        <v>抗サイログロブリン抗体,TgAb,橋本病</v>
+        <v>CRP,炎症,感染</v>
       </c>
       <c r="O74" t="str">
-        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
+        <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>血中薬物濃度（TDM）</v>
+        <v>PT-INR（プロトロンビン時間国際標準比）</v>
       </c>
       <c r="B75" t="str">
-        <v>TDM</v>
+        <v>PT-INR,INR</v>
       </c>
       <c r="C75" t="str">
-        <v>薬剤ごとに有効域が異なる（例：フェニトイン 10〜20 μg/mL、ゾニサミド 10〜40 μg/mL、カルバマゼピン 4〜12 μg/mL、バルプロ酸ナトリウム 40〜120 μg/mL、ラモトリギン 1〜10 μg/mL(併用薬により変動)）</v>
+        <v>治療域の目安 1.6〜3.0（ワルファリン服用時。年齢・疾患により異なる）</v>
       </c>
       <c r="D75" t="str">
-        <v>治療域が狭い薬剤で、血液中の薬の濃度が効果域・中毒域のどちらにあるかを確認する検査</v>
+        <v>血液の固まりやすさを表す数値で、ワルファリンの効き具合を確認するために使う</v>
       </c>
       <c r="E75" t="str">
-        <v>この薬は効く量と副作用が出る量が近いため、血液中の薬の濃度を定期的に測って、ちょうどよい範囲に入っているかを確認します。数値が低いと効果が不十分になり、高いと副作用が出やすくなります。</v>
+        <v>PT-INRは血液が固まるまでの時間をもとにした数値で、ワルファリンというお薬を飲んでいる方の効き具合を確認するために測ります。数値が高いほど血液が固まりにくく出血しやすい状態、低いほど血栓ができやすい状態を示します。</v>
       </c>
       <c r="F75" t="str">
-        <v>過量投与、代謝を妨げる薬剤との併用、肝機能低下による代謝低下</v>
+        <v>ワルファリンの効きすぎ、肝機能低下、ビタミンK不足、納豆・青汁など摂取量の変化</v>
       </c>
       <c r="G75" t="str">
-        <v>ふらつき、眠気、めまい、物が二重に見えるなどの中毒症状がないか確認する</v>
+        <v>歯ぐきや鼻からの出血、あざ、黒い便などの出血症状がないか確認する。納豆・クロレラ・青汁などビタミンKを多く含む食品の摂取状況を確認する</v>
       </c>
       <c r="H75" t="str">
-        <v/>
+        <v>ワルファリンの過量。ワルファリン服用中はST合剤・マクロライド系・フルコナゾール等の相互作用やビタミンK摂取量の変化にも注意</v>
       </c>
       <c r="I75" t="str">
-        <v>飲み忘れ、自己判断による減量、代謝を促進する薬剤との併用（相互作用）</v>
+        <v>ワルファリンの効き不足、飲み忘れ、ビタミンK摂取量の急激な増加</v>
       </c>
       <c r="J75" t="str">
-        <v>発作やてんかん症状の再発がないか確認し、飲み忘れがないか一緒に確認する</v>
+        <v>服薬状況（飲み忘れ）を確認する。片側のむくみ・しびれ・胸痛など血栓症状がないか確認する</v>
       </c>
       <c r="K75" t="str">
-        <v/>
+        <v>ワルファリン服用中で低値の場合は効果不十分の可能性。ビタミンK摂取量の変化や、リファンピシン・カルバマゼピン・バルビツール酸系など代謝を促進する薬との併用を確認</v>
       </c>
       <c r="L75" t="str">
-        <v>採血のタイミング（トラフ値かどうか）で数値の解釈が変わるため採血時点を確認する。カルバマゼピンは自己誘導により長期使用で濃度が下がることがある点にも注意</v>
+        <v>治療域は疾患・年齢によって異なる（例：非弁膜症性心房細動の高齢者では1.6〜2.6が目安になることが多い）。多くの薬剤・食品と相互作用があるため新規薬剤追加時は必ず確認する。DOAC（エリキュース、リクシアナ、プラザキサなど）ではPT-INRのモニタリングは不要</v>
       </c>
       <c r="M75" t="str">
-        <v>てんかん</v>
+        <v>抗凝固療法（心房細動・血栓症）</v>
       </c>
       <c r="N75" t="str">
-        <v>TDM,血中薬物濃度,治療域,中毒域,カルバマゼピン,フェニトイン,バルプロ酸,抗てんかん薬,ゾニサミド,ラモトリギン</v>
+        <v>PT-INR,INR,プロトロンビン時間,ワルファリン,ワーファリン,抗凝固</v>
       </c>
       <c r="O75" t="str">
-        <v/>
+        <v>食事と栄養 p.221（心疾患Q93 ワルファリン服用中のビタミンK摂取）</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>アミラーゼ（AMY）</v>
+        <v>骨型酒石酸抵抗性フォスファターゼ（TRACP-5b）</v>
       </c>
       <c r="B76" t="str">
-        <v>AMY</v>
+        <v>TRACP-5b</v>
       </c>
       <c r="C76" t="str">
-        <v>44〜132 U/L（施設差あり）</v>
+        <v>120〜420 mU/dL</v>
       </c>
       <c r="D76" t="str">
-        <v>膵臓や唾液腺から出る消化酵素。膵炎などで血液中に漏れ出す</v>
+        <v>骨がどれくらい壊されているかを見る検査。骨は「古い骨を壊して新しい骨を作る」入れ替えを繰り返しており、骨を壊す細胞が活発だとこの物質が血液中に増える。</v>
       </c>
       <c r="E76" t="str">
-        <v>アミラーゼは、でんぷんを分解する消化酵素で、主に膵臓と唾液腺から作られます。膵臓に炎症が起きると血液中に漏れ出して数値が上がるため、膵炎の診断や経過観察に使われます。</v>
+        <v>この検査は、骨がどれくらい早く減っていないかを見るものです。数値が高いと、骨が弱くなりやすい状態の目安になります。</v>
       </c>
       <c r="F76" t="str">
-        <v>急性膵炎、慢性膵炎の急性増悪、耳下腺炎（おたふくかぜ）、腎不全</v>
+        <v>骨粗鬆症、骨代謝回転（骨がこわれるスピード）が活発な状態</v>
       </c>
       <c r="G76" t="str">
-        <v>飲酒を控え、脂っこい食事を避けるよう伝える。強い腹痛・背部痛がある場合は急性膵炎の可能性もあるため早めの受診を勧める</v>
+        <v>カルシウム・ビタミンDの摂取や、適度な荷重運動（ウォーキングなど）を意識するよう伝える</v>
       </c>
       <c r="H76" t="str">
-        <v>バルプロ酸、アザチオプリン、サイアザイド系・ループ利尿薬、ステロイドなど薬剤性膵炎の原因薬</v>
+        <v/>
       </c>
       <c r="I76" t="str">
-        <v>慢性膵炎の進行期（膵臓の機能低下）</v>
+        <v/>
       </c>
       <c r="J76" t="str">
         <v/>
@@ -3984,13 +3984,13 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>膵臓由来か唾液腺由来かを区別するには膵型アミラーゼ(P-AMY)を確認する。急性膵炎では強い腹痛・背部痛を伴うことが多く、飲酒歴の確認も重要</v>
+        <v>「骨を壊す側」の指標。「骨を作る側」の検査と合わせて評価する。数値だけで診断はしない</v>
       </c>
       <c r="M76" t="str">
-        <v/>
+        <v>骨粗鬆症</v>
       </c>
       <c r="N76" t="str">
-        <v>アミラーゼ,AMY,膵炎,急性膵炎</v>
+        <v>TRACP-5b,骨型酒石酸抵抗性フォスファターゼ,骨粗鬆症,骨代謝</v>
       </c>
       <c r="O76" t="str">
         <v/>
@@ -3998,31 +3998,31 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>間接ビリルビン</v>
+        <v>骨型アルカリフォスファターゼ</v>
       </c>
       <c r="B77" t="str">
-        <v>I-Bil</v>
+        <v>BAP</v>
       </c>
       <c r="C77" t="str">
-        <v>0.2〜0.8 mg/dL程度（施設差あり）</v>
+        <v>男性 3.7〜20.9 μg/L、女性（閉経前）2.9〜14.5 μg/L（施設差あり）</v>
       </c>
       <c r="D77" t="str">
-        <v>赤血球が壊れてできるビリルビンのうち、肝臓で処理される前の形</v>
+        <v>ALPのうち骨に由来する成分だけを測定し、骨が作られる勢い（骨形成）を反映する</v>
       </c>
       <c r="E77" t="str">
-        <v>間接ビリルビンは、赤血球が壊れてできたビリルビンが、まだ肝臓で処理される前の状態です。この値が高い場合、赤血球が通常より多く壊れている(溶血)か、肝臓での処理能力に生まれつきの体質差(体質性黄疸)がある可能性が考えられます。</v>
+        <v>骨型ALPは、通常のALP（アルカリフォスファターゼ）の中でも、骨で作られる成分だけを選んで測定するものです。骨を新しく作る働きがどれくらい活発かを見る指標として、骨粗鬆症の治療効果判定などに使われます。</v>
       </c>
       <c r="F77" t="str">
-        <v>溶血性疾患（自己免疫性溶血性貧血、血液型不適合輸血など）、体質性黄疸（ジルベール症候群）、新生児黄疸</v>
+        <v>骨代謝回転の亢進（骨粗鬆症、骨折治癒過程、骨形成促進薬による治療効果、Paget病、骨転移）</v>
       </c>
       <c r="G77" t="str">
-        <v>皮膚や白目の黄染、尿の色の変化がないか確認する</v>
+        <v/>
       </c>
       <c r="H77" t="str">
         <v/>
       </c>
       <c r="I77" t="str">
-        <v/>
+        <v>骨形成の低下</v>
       </c>
       <c r="J77" t="str">
         <v/>
@@ -4031,13 +4031,13 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>直接ビリルビンとの比率で原因を推測する（間接優位は溶血・体質性、直接優位は胆道系）。総ビリルビン・AST/ALTと合わせて評価する</v>
+        <v>通常のALPと異なり肝臓の影響を受けにくいため、肝機能異常がある患者でも骨代謝を評価しやすい。P1NPと同じ「骨を作る側」の指標で、骨形成促進薬（テリパラチド等）の効果判定に使われる</v>
       </c>
       <c r="M77" t="str">
-        <v>肝機能</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="N77" t="str">
-        <v>間接ビリルビン,I-Bil,溶血</v>
+        <v>骨型ALP,BAP,骨型アルカリフォスファターゼ,骨形成マーカー</v>
       </c>
       <c r="O77" t="str">
         <v/>
@@ -4045,257 +4045,257 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>直接ビリルビン</v>
+        <v>25-ヒドロキシビタミンD</v>
       </c>
       <c r="B78" t="str">
-        <v>D-Bil</v>
+        <v>25(OH)D</v>
       </c>
       <c r="C78" t="str">
-        <v>0.0〜0.3 mg/dL程度（施設差あり）</v>
+        <v>30 ng/mL以上：充足、20〜30 ng/mL：不足、20 ng/mL未満：欠乏（施設差あり）</v>
       </c>
       <c r="D78" t="str">
-        <v>肝臓で処理された後のビリルビン。胆道の詰まりで血液中に増える</v>
+        <v>体内のビタミンDの蓄え具合を反映する指標。カルシウムの吸収や骨の健康に関わる</v>
       </c>
       <c r="E78" t="str">
-        <v>直接ビリルビンは、肝臓で処理された後のビリルビンです。胆石や腫瘍などで胆汁の通り道（胆道）が詰まると、行き場を失って血液中に増え、皮膚や白目が黄色くなる黄疸として現れます。</v>
+        <v>この検査は、体の中にビタミンDがどれくらい蓄えられているかを見るものです。ビタミンDは、食事から摂ったカルシウムを腸で吸収するのを助ける働きがあり、不足すると骨がもろくなりやすくなります。</v>
       </c>
       <c r="F78" t="str">
-        <v>肝疾患、胆石など胆道の閉塞</v>
+        <v>ビタミンD製剤の過剰摂取</v>
       </c>
       <c r="G78" t="str">
-        <v>皮膚や白目の黄染、白っぽい便、濃い茶色の尿がないか確認する</v>
+        <v>活性型ビタミンD3製剤やサプリメントの摂取量を確認する。高カルシウム血症の症状（吐き気、便秘、多尿など）がないか確認する</v>
       </c>
       <c r="H78" t="str">
-        <v>胆汁うっ滞型の薬剤性肝障害を起こしうる抗菌薬、経口避妊薬</v>
+        <v>活性型/天然型ビタミンD製剤の過量投与</v>
       </c>
       <c r="I78" t="str">
-        <v/>
+        <v>日光暴露不足、食事摂取不足、高齢、腸疾患による吸収不良、肝・腎機能低下（活性化障害）</v>
       </c>
       <c r="J78" t="str">
-        <v/>
+        <v>適度な日光浴、魚類・きのこ類などビタミンDを多く含む食品の摂取を意識するとよいことを伝える</v>
       </c>
       <c r="K78" t="str">
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>直接優位の上昇は胆道系（胆石、腫瘍による閉塞）を、間接優位の上昇は溶血・体質性を疑う手がかりになる。γ-GTP・ALPと合わせて胆道系疾患を評価する</v>
+        <v>骨粗鬆症治療における活性型ビタミンD3製剤の効果判定や、投与量調整の参考に用いられる。腎機能低下患者では活性化障害により25(OH)Dが正常でも活性型が不足することがある点に注意</v>
       </c>
       <c r="M78" t="str">
-        <v>肝機能</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="N78" t="str">
-        <v>直接ビリルビン,D-Bil,胆石,胆道閉塞</v>
+        <v>25(OH)D,ビタミンD,25-ヒドロキシビタミンD,ビタミンD欠乏,骨粗鬆症</v>
       </c>
       <c r="O78" t="str">
-        <v/>
+        <v>食事と栄養 p.38（ビタミンD）</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>亜鉛（Zn）</v>
+        <v>ucOC（低カルボキシル化オステオカルシン）</v>
       </c>
       <c r="B79" t="str">
-        <v>Zn</v>
+        <v>ucOC</v>
       </c>
       <c r="C79" t="str">
-        <v>80〜130 μg/dL程度（施設差あり）</v>
+        <v>4.5 ng/mL未満（施設差あり）</v>
       </c>
       <c r="D79" t="str">
-        <v>味覚や皮膚、免疫に関わる微量ミネラル。高齢者や低栄養で不足しやすい</v>
+        <v>ビタミンKが不足していないかを反映する骨の指標</v>
       </c>
       <c r="E79" t="str">
-        <v>亜鉛は、味を感じる働きや皮膚・粘膜の健康、免疫の働きに関わる微量ミネラルです。不足すると、味がわかりにくくなったり（味覚障害）、傷が治りにくくなったりすることがあります。</v>
+        <v>ucOCは、骨を作るために必要なビタミンKが体の中で足りているかどうかを反映する検査です。数値が高いとビタミンK不足が疑われます。</v>
       </c>
       <c r="F79" t="str">
-        <v/>
+        <v>ビタミンK不足状態</v>
       </c>
       <c r="G79" t="str">
-        <v/>
+        <v>ビタミンK2製剤(骨粗鬆症治療薬)の適応が検討されているか確認する。ワルファリン服用中の患者では、納豆などビタミンKを多く含む食品の急な摂取量の変化を避けるよう説明する</v>
       </c>
       <c r="H79" t="str">
         <v/>
       </c>
       <c r="I79" t="str">
-        <v>低栄養、高齢による摂取不足、消化器手術後、亜鉛の吸収を妨げる薬剤（PPI、キレート形成する薬剤など）との併用</v>
+        <v/>
       </c>
       <c r="J79" t="str">
-        <v>味覚の変化（味を感じにくい、金属味がするなど）がないか確認する。牡蠣、赤身肉、レバーなど亜鉛を多く含む食品を意識するとよいことを伝える</v>
+        <v/>
       </c>
       <c r="K79" t="str">
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>薬剤性の亜鉛欠乏（PPI長期使用、D-ペニシラミン、一部の降圧薬など）に注意。亜鉛欠乏による味覚障害は原因薬剤の中止・亜鉛補充で改善することがある</v>
+        <v>ビタミンK2製剤（骨粗鬆症治療薬）の適応判断や効果判定に使われる</v>
       </c>
       <c r="M79" t="str">
-        <v/>
+        <v>骨粗鬆症</v>
       </c>
       <c r="N79" t="str">
-        <v>亜鉛,Zn,味覚障害,亜鉛欠乏</v>
+        <v>ucOC,オステオカルシン,ビタミンK</v>
       </c>
       <c r="O79" t="str">
-        <v>食事と栄養 p.78（亜鉛）</v>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>マグネシウム（Mg）</v>
+        <v>PTH（副甲状腺ホルモン）</v>
       </c>
       <c r="B80" t="str">
-        <v>Mg</v>
+        <v>PTH</v>
       </c>
       <c r="C80" t="str">
-        <v>1.8〜2.6 mg/dL程度（施設差あり）</v>
+        <v>10〜65 pg/mL（施設差あり）</v>
       </c>
       <c r="D80" t="str">
-        <v>骨や筋肉、神経の働きに関わるミネラル。低栄養や利尿薬で不足しやすい</v>
+        <v>血液中のカルシウム濃度を調節するホルモン</v>
       </c>
       <c r="E80" t="str">
-        <v>マグネシウムは、骨や筋肉、神経の働きを支えるミネラルです。不足すると、こむら返りや不整脈、だるさなどの症状が出ることがあります。</v>
+        <v>PTHは、血液中のカルシウム濃度を一定に保つために働くホルモンです。カルシウムが低くなると分泌が増え、骨からカルシウムを取り出したり、腎臓での再吸収を促したりして数値を戻そうとします。</v>
       </c>
       <c r="F80" t="str">
-        <v>腎不全、マグネシウム製剤（酸化マグネシウムなど）の過量投与</v>
+        <v>原発性・二次性副甲状腺機能亢進症（腎不全に伴うものなど）</v>
       </c>
       <c r="G80" t="str">
-        <v>腎機能低下がある患者で酸化マグネシウムなどの緩下剤を使用中は、傾眠・血圧低下などの高マグネシウム血症の症状がないか確認する</v>
+        <v/>
       </c>
       <c r="H80" t="str">
-        <v>マグネシウム含有制酸薬・下剤の過量(特に腎機能低下患者)</v>
+        <v/>
       </c>
       <c r="I80" t="str">
-        <v>低栄養、利尿薬の使用、慢性的な下痢、アルコール多飲、PPI長期使用</v>
+        <v>副甲状腺機能低下症</v>
       </c>
       <c r="J80" t="str">
-        <v>こむら返りや動悸などの症状がないか確認する</v>
+        <v/>
       </c>
       <c r="K80" t="str">
-        <v>プロトンポンプ阻害薬(PPI)の長期使用、ループ利尿薬、サイアザイド系利尿薬、シスプラチン、アミノグリコシド系</v>
+        <v/>
       </c>
       <c r="L80" t="str">
-        <v>腎機能低下患者への酸化マグネシウム投与は高マグネシウム血症のリスクがあるため定期的なモニタリングが必要。PPI長期使用も低マグネシウム血症のリスク因子として知られる</v>
+        <v>骨粗鬆症の二次性原因（副甲状腺機能亢進症）を除外するための検査。カルシウム・リンと合わせて評価する</v>
       </c>
       <c r="M80" t="str">
-        <v>腎機能</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="N80" t="str">
-        <v>マグネシウム,Mg,酸化マグネシウム,こむら返り</v>
+        <v>PTH,副甲状腺ホルモン,パラトルモン</v>
       </c>
       <c r="O80" t="str">
-        <v>食事と栄養 p.84（マグネシウム）</v>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>白血球数（WBC）</v>
+        <v>尿中NTX</v>
       </c>
       <c r="B81" t="str">
-        <v>WBC</v>
+        <v>NTX</v>
       </c>
       <c r="C81" t="str">
-        <v>3,300〜8,600 /μL程度（施設差あり）</v>
+        <v>施設差が大きく一律の記載が難しい（尿中）</v>
       </c>
       <c r="D81" t="str">
-        <v>体を細菌やウイルスから守る免疫細胞の数で、感染や炎症、薬剤の影響を反映する</v>
+        <v>骨が壊されるときに出る、骨吸収マーカーのひとつ</v>
       </c>
       <c r="E81" t="str">
-        <v>白血球は体に入ってきた細菌やウイルスと戦う免疫細胞です。感染症や炎症があると増え、逆に一部のお薬の副作用や骨髄の働きが落ちると減ることがあります。</v>
+        <v>NTXは、骨が壊される（吸収される）ときに尿の中に出てくる物質です。骨粗鬆症の治療薬がどれくらい効いているかを確認するために使われます。</v>
       </c>
       <c r="F81" t="str">
-        <v>感染症、炎症、ステロイド使用、喫煙、白血病などの血液疾患</v>
+        <v>骨代謝回転の亢進（骨粗鬆症、閉経後など）</v>
       </c>
       <c r="G81" t="str">
-        <v>発熱や体の痛みなど感染症状がないか確認する</v>
+        <v/>
       </c>
       <c r="H81" t="str">
-        <v>ステロイド、G-CSF製剤、炭酸リチウム</v>
+        <v/>
       </c>
       <c r="I81" t="str">
-        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、メルカゾールなど薬剤性の無顆粒球症、再生不良性貧血、ウイルス感染</v>
+        <v>骨吸収抑制薬（ビスホスホネート等）による治療効果</v>
       </c>
       <c r="J81" t="str">
-        <v>発熱、のどの痛みなど感染症状の初期サインがないか確認する。人混みを避け、手洗い・うがいを徹底するよう伝える</v>
+        <v/>
       </c>
       <c r="K81" t="str">
-        <v>抗がん剤、メルカゾール(無顆粒球症)、クロザピン(定期的な血球モニタリング必須)、サラゾスルファピリジン</v>
+        <v/>
       </c>
       <c r="L81" t="str">
-        <v>メルカゾール（チアマゾール）は無顆粒球症の重大な副作用があり、発熱・のどの痛みが出たらすぐ受診するよう指導する。抗がん剤・免疫抑制剤・抗てんかん薬（カルバマゼピンなど）使用中も定期的なモニタリングが必要</v>
+        <v>治療開始後3〜6か月で再検し、薬の効果判定に使われる。TRACP-5bと同じ「骨を壊す側」の指標</v>
       </c>
       <c r="M81" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="N81" t="str">
-        <v>白血球,WBC,好中球,感染症,白血病,無顆粒球症,骨髄抑制</v>
+        <v>NTX,尿中NTX,骨吸収マーカー</v>
       </c>
       <c r="O81" t="str">
-        <v/>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>赤血球数</v>
+        <v>カルシトニン</v>
       </c>
       <c r="B82" t="str">
-        <v>RBC</v>
+        <v>CT</v>
       </c>
       <c r="C82" t="str">
-        <v>男性 435〜555万/μL、女性 386〜492万/μL程度（施設差あり）</v>
+        <v>男性 9.52 pg/mL未満、女性 6.40 pg/mL未満（施設差あり）</v>
       </c>
       <c r="D82" t="str">
-        <v>血液中で酸素を運ぶ細胞の数。ヘモグロビン・ヘマトクリットと合わせて貧血・多血症を評価する</v>
+        <v>血液中のカルシウムを下げる方向に働くホルモン</v>
       </c>
       <c r="E82" t="str">
-        <v>赤血球は、肺で受け取った酸素を全身に運ぶ血液の細胞です。数が少ないと貧血、多いと多血症が疑われます。ヘモグロビンやヘマトクリットと合わせて総合的に評価します。</v>
+        <v>カルシトニンは、PTHとは逆に血液中のカルシウムを下げる方向に働くホルモンです。特定の甲状腺の病気（甲状腺髄様癌）がないかを調べる際にも使われます。</v>
       </c>
       <c r="F82" t="str">
-        <v>脱水、多血症（真性多血症、二次性多血症）、喫煙</v>
+        <v>甲状腺髄様癌、腎不全</v>
       </c>
       <c r="G82" t="str">
-        <v>脱水が疑われる場合はこまめな水分摂取を勧める（水分制限がある場合を除く）</v>
+        <v/>
       </c>
       <c r="H82" t="str">
         <v/>
       </c>
       <c r="I82" t="str">
-        <v>貧血（鉄欠乏性貧血、腎性貧血など）、出血</v>
+        <v/>
       </c>
       <c r="J82" t="str">
-        <v>ヘモグロビンと同様に、出血や食事量低下がないか確認する</v>
+        <v/>
       </c>
       <c r="K82" t="str">
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>ヘモグロビン・ヘマトクリットと同じ方向に動くことが多い。赤血球数だけでなくMCV・MCH・MCHCと合わせて貧血のタイプ(小球性・正球性・大球性)を判断する</v>
+        <v>骨粗鬆症の二次性原因の除外目的で測定されることがある検査値。同名の薬剤（カルシトニン製剤）と混同しないよう注意</v>
       </c>
       <c r="M82" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="N82" t="str">
-        <v>赤血球,RBC,貧血,多血症</v>
+        <v>カルシトニン,CT</v>
       </c>
       <c r="O82" t="str">
-        <v>食事と栄養 p.151-164（第2部 貧血）</v>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>ヘモグロビン濃度</v>
+        <v>DPD（デオキシピリジノリン）</v>
       </c>
       <c r="B83" t="str">
-        <v>Hb</v>
+        <v>DPD</v>
       </c>
       <c r="C83" t="str">
-        <v>男性 13.5〜17.5 g/dL、女性 11.5〜15.0 g/dL</v>
+        <v>施設差が大きく一律の記載が難しい（尿中）</v>
       </c>
       <c r="D83" t="str">
-        <v>血液の中で酸素を運ぶ役割をしている。この値が低い状態が貧血。</v>
+        <v>骨のコラーゲンが壊れるときに出る、骨吸収マーカーのひとつ</v>
       </c>
       <c r="E83" t="str">
-        <v>ヘモグロビンは、血液の中で酸素を全身に運ぶ役割をしている赤い色素です。この値が低い状態が貧血で、体がだるくなったり、階段で息切れしやすくなったりします。</v>
+        <v>DPDも、骨が壊されるときに尿に出てくる物質の一つです。NTXと同じように、骨粗鬆症治療薬の効果を確認するために使われます。</v>
       </c>
       <c r="F83" t="str">
-        <v/>
+        <v>骨代謝回転の亢進（骨粗鬆症など）</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -4304,92 +4304,92 @@
         <v/>
       </c>
       <c r="I83" t="str">
-        <v>鉄欠乏性貧血、出血、腎性貧血、骨髄の造血機能低下</v>
+        <v>骨吸収抑制薬による治療効果</v>
       </c>
       <c r="J83" t="str">
-        <v>鉄分の多い食品(レバー・赤身肉・魚・ほうれん草など)を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える。鉄剤は数値が正常化した後も体内に鉄を貯蔵するため2〜3か月程度は継続が必要なことを説明する</v>
+        <v/>
       </c>
       <c r="K83" t="str">
-        <v>NSAIDs・抗凝固薬・抗血小板薬(消化管出血のリスク)、抗がん剤、ST合剤</v>
+        <v/>
       </c>
       <c r="L83" t="str">
-        <v>原因（出血・食事量低下など）の確認が重要。腎機能低下がある場合は鉄不足以外が原因のこともある。鉄剤はヘモグロビンが正常化した後も2〜3か月程度は継続することが多い（鉄の貯蔵分を補うため。途中でやめると再び貧血になりやすい）</v>
+        <v>NTX・CTXと同じ「骨を壊す側」の指標。食事の影響を受けにくいとされる</v>
       </c>
       <c r="M83" t="str">
-        <v>鉄欠乏性貧血,抗血小板療法,抗凝固療法（心房細動・血栓症）</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="N83" t="str">
-        <v>ヘモグロビン,Hb,貧血,鉄剤,鉄欠乏性貧血</v>
+        <v>DPD,デオキシピリジノリン,骨吸収マーカー</v>
       </c>
       <c r="O83" t="str">
-        <v>食事と栄養 p.151-164（第2部 貧血）</v>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>ヘマトクリット値</v>
+        <v>CTX</v>
       </c>
       <c r="B84" t="str">
-        <v>Ht,Hct</v>
+        <v>CTX</v>
       </c>
       <c r="C84" t="str">
-        <v>男性 40〜50%、女性 35〜45%</v>
+        <v>施設差が大きく一律の記載が難しい（血清・尿中）</v>
       </c>
       <c r="D84" t="str">
-        <v>血液全体のうち赤血球が占める体積の割合。貧血・脱水の指標</v>
+        <v>骨のコラーゲンが壊れるときに出る、骨吸収マーカーのひとつ</v>
       </c>
       <c r="E84" t="str">
-        <v>ヘマトクリットは、血液全体のうち赤血球が占める割合を表す数値です。この値が低いと貧血、高いと脱水や血液が濃くなっている状態が疑われます。</v>
+        <v>CTXも、骨が壊されるときに血液や尿に出てくる物質です。骨粗鬆症治療薬（骨を壊すのを抑える薬）の効果を確認するために使われます。</v>
       </c>
       <c r="F84" t="str">
-        <v>脱水、多血症（真性多血症、二次性多血症）、喫煙</v>
+        <v>骨代謝回転の亢進（骨粗鬆症など）</v>
       </c>
       <c r="G84" t="str">
-        <v>脱水が疑われる場合はこまめな水分摂取を勧める（水分制限がある場合を除く）</v>
+        <v/>
       </c>
       <c r="H84" t="str">
         <v/>
       </c>
       <c r="I84" t="str">
-        <v>貧血（鉄欠乏性貧血、腎性貧血など）、出血</v>
+        <v>骨吸収抑制薬による治療効果</v>
       </c>
       <c r="J84" t="str">
-        <v>ヘモグロビンと同様に、出血や食事量低下がないか確認する</v>
+        <v/>
       </c>
       <c r="K84" t="str">
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>ヘモグロビン・赤血球数と合わせて評価する。3つの値は同じ方向に動くことが多く、脱水があると貧血が見かけ上隠れることがある</v>
+        <v>NTX・DPDと同じ「骨を壊す側」の指標。血清・尿中いずれでも測定されることがある</v>
       </c>
       <c r="M84" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="N84" t="str">
-        <v>ヘマトクリット,Ht,Hct,貧血,脱水,多血症</v>
+        <v>CTX,骨吸収マーカー</v>
       </c>
       <c r="O84" t="str">
-        <v>食事と栄養 p.151-164（第2部 貧血）</v>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>MCV</v>
+        <v>P1NP</v>
       </c>
       <c r="B85" t="str">
-        <v>MCV</v>
+        <v>P1NP</v>
       </c>
       <c r="C85" t="str">
-        <v>79〜100 fL</v>
+        <v>施設差が大きく一律の記載が難しい（血清）</v>
       </c>
       <c r="D85" t="str">
-        <v>赤血球1個の大きさ</v>
+        <v>骨が新しく作られるときに出る、骨形成マーカーのひとつ</v>
       </c>
       <c r="E85" t="str">
-        <v>MCVは赤血球1個あたりの大きさを表す数値です。貧血があるとき、この数値で「小さい貧血」か「大きい貧血」かを見分けることができ、原因を絞り込む手がかりになります。</v>
+        <v>P1NPは、CTXなどとは逆に、骨が新しく作られるときに血液中に出てくる物質です。骨を作る力を高める薬（テリパラチドなど）の効果を確認するために使われます。</v>
       </c>
       <c r="F85" t="str">
-        <v/>
+        <v>骨代謝回転の亢進、骨形成促進薬による治療効果</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -4398,92 +4398,92 @@
         <v/>
       </c>
       <c r="I85" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>骨形成の低下</v>
       </c>
       <c r="J85" t="str">
-        <v>鉄分の多い食品(レバー・赤身肉・魚・ほうれん草など)と、吸収を助けるビタミンC(柑橘類・芋類等)を一緒に摂るよう伝える</v>
+        <v/>
       </c>
       <c r="K85" t="str">
         <v/>
       </c>
       <c r="L85" t="str">
-        <v/>
+        <v>TRACP-5b等「骨を壊す側」の指標とは逆の、「骨を作る側」の指標。骨形成促進薬（テリパラチド等）の効果判定に使われる</v>
       </c>
       <c r="M85" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="N85" t="str">
-        <v>MCV,赤血球指数,貧血</v>
+        <v>P1NP,骨形成マーカー</v>
       </c>
       <c r="O85" t="str">
-        <v>食事と栄養 p.151-164（第2部 貧血）</v>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>MCH</v>
+        <v>血清鉄（Fe）</v>
       </c>
       <c r="B86" t="str">
-        <v>MCH</v>
+        <v>Fe</v>
       </c>
       <c r="C86" t="str">
-        <v>26.3〜34.3 pg</v>
+        <v>60〜200 μg/dL（施設差あり）</v>
       </c>
       <c r="D86" t="str">
-        <v>赤血球1個に含まれるヘモグロビン量</v>
+        <v>血液中を流れている鉄の量</v>
       </c>
       <c r="E86" t="str">
-        <v>MCHは赤血球1個の中に含まれるヘモグロビン（酸素を運ぶ色素）の量を表す数値です。MCVと同じく、貧血の種類を見分けるのに使われます。</v>
+        <v>この検査は、今血液の中を流れている鉄の量を見るものです。低いと、体の中で鉄が不足している可能性があります。</v>
       </c>
       <c r="F86" t="str">
-        <v/>
+        <v>鉄剤の過剰摂取、溶血、肝疾患</v>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v/>
+        <v>鉄剤の過量摂取(小児の誤飲を含む)</v>
       </c>
       <c r="I86" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>鉄欠乏性貧血、慢性炎症、出血</v>
       </c>
       <c r="J86" t="str">
-        <v>鉄分の多い食品(レバー・赤身肉・魚・ほうれん草など)と、吸収を助けるビタミンC(柑橘類・芋類等)を一緒に摂るよう伝える</v>
+        <v>鉄分の多い食品（レバー・赤身肉・魚・ほうれん草など）を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える</v>
       </c>
       <c r="K86" t="str">
-        <v/>
+        <v>プロトンポンプ阻害薬(PPI)・H2ブロッカーは胃酸分泌抑制により鉄の吸収を低下させうる</v>
       </c>
       <c r="L86" t="str">
-        <v/>
+        <v>血清鉄は日内変動が大きい。単独で判断せず総鉄結合能・フェリチンと合わせて評価する</v>
       </c>
       <c r="M86" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
       <c r="N86" t="str">
-        <v>MCH,赤血球指数,貧血</v>
+        <v>血清鉄,Fe,鉄欠乏性貧血</v>
       </c>
       <c r="O86" t="str">
-        <v>食事と栄養 p.151-164（第2部 貧血）</v>
+        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>MCHC</v>
+        <v>総鉄結合能（TIBC）</v>
       </c>
       <c r="B87" t="str">
-        <v>MCHC</v>
+        <v>TIBC</v>
       </c>
       <c r="C87" t="str">
-        <v>31.6〜36.6 %</v>
+        <v>250〜360 μg/dL（施設差あり）</v>
       </c>
       <c r="D87" t="str">
-        <v>単位容積あたりの赤血球に含まれるヘモグロビン濃度</v>
+        <v>血液中のトランスフェリンが鉄と結合できる総量</v>
       </c>
       <c r="E87" t="str">
-        <v>MCHCは、赤血球の中にヘモグロビンがどれくらい濃く詰まっているかを表す数値です。鉄が不足すると、この濃度も薄くなる傾向があります。</v>
+        <v>TIBCは、血液中でトランスフェリンという物質が鉄を運べる最大量を表します。体の中の鉄が不足すると、少しでも多く鉄を運ぼうとしてこの数値が上がる性質があります。</v>
       </c>
       <c r="F87" t="str">
-        <v/>
+        <v>鉄欠乏性貧血（＞360 μg/dLが目安）</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -4492,92 +4492,92 @@
         <v/>
       </c>
       <c r="I87" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>慢性炎症、肝疾患、ネフローゼ症候群</v>
       </c>
       <c r="J87" t="str">
-        <v>鉄分の多い食品(レバー・赤身肉・魚・ほうれん草など)と、吸収を助けるビタミンC(柑橘類・芋類等)を一緒に摂るよう伝える</v>
+        <v/>
       </c>
       <c r="K87" t="str">
         <v/>
       </c>
       <c r="L87" t="str">
-        <v/>
+        <v>鉄が不足すると、体はより多く運ぼうとしてTIBCが上昇する。UIBC・血清鉄と併せて評価する</v>
       </c>
       <c r="M87" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
       <c r="N87" t="str">
-        <v>MCHC,赤血球指数,貧血</v>
+        <v>TIBC,総鉄結合能,鉄欠乏性貧血</v>
       </c>
       <c r="O87" t="str">
-        <v>食事と栄養 p.151-164（第2部 貧血）</v>
+        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>血小板数</v>
+        <v>不飽和鉄結合能（UIBC）</v>
       </c>
       <c r="B88" t="str">
-        <v>Plt</v>
+        <v>UIBC</v>
       </c>
       <c r="C88" t="str">
-        <v>15.0〜35.0万/μL程度（施設差あり）</v>
+        <v>170〜300 μg/dL（施設差あり）</v>
       </c>
       <c r="D88" t="str">
-        <v>出血を止める働きをする血液成分で、少なすぎると出血しやすくなる</v>
+        <v>トランスフェリンのうち、まだ鉄と結合していない余力の部分（UIBC＝TIBC－血清鉄）</v>
       </c>
       <c r="E88" t="str">
-        <v>血小板は、血管が傷ついたときに集まって血を止める役割をする血液の成分です。数が少ないとあざができやすくなったり、出血が止まりにくくなったりします。抗血小板薬や抗がん剤を使っている方では、定期的にチェックすることが大切です。</v>
+        <v>UIBCは、トランスフェリンのうち、まだ鉄と結合していない「空き容量」の部分を表します。鉄が不足しているときほど、この空き容量は大きくなります。</v>
       </c>
       <c r="F88" t="str">
-        <v>炎症性疾患、鉄欠乏性貧血、脾摘後、骨髄増殖性疾患</v>
+        <v>鉄欠乏性貧血（＞300 μg/dLが目安）</v>
       </c>
       <c r="G88" t="str">
-        <v>出血傾向はなく経過観察でよいことが多いが、片側の腫れ・しびれなど血栓症状がないかも念のため確認する</v>
+        <v/>
       </c>
       <c r="H88" t="str">
         <v/>
       </c>
       <c r="I88" t="str">
-        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、肝硬変・脾機能亢進、再生不良性貧血、抗てんかん薬（バルプロ酸など）の副作用、ITP（特発性血小板減少性紫斑病）</v>
+        <v>慢性炎症、鉄過剰状態</v>
       </c>
       <c r="J88" t="str">
-        <v>あざができやすい、歯ぐきや鼻からの出血が増えていないか確認する。強い運動や転倒によるけがに注意するよう伝え、歯みがきは柔らかめのブラシを勧める</v>
+        <v/>
       </c>
       <c r="K88" t="str">
-        <v>ヘパリン(HIT: ヘパリン起因性血小板減少症)、バルプロ酸、抗がん剤、リネゾリド</v>
+        <v/>
       </c>
       <c r="L88" t="str">
-        <v>抗血小板薬・抗凝固薬使用中に血小板減少があると出血リスクがさらに高まる。抗がん剤・バルプロ酸・カルバマゼピンなど骨髄抑制のリスクがある薬剤使用中は定期採血の実施状況を確認する</v>
+        <v>TIBCと同じ方向に動くことが多い。血清鉄・TIBCとあわせて鉄欠乏性貧血と二次性貧血の鑑別に使う</v>
       </c>
       <c r="M88" t="str">
-        <v>てんかん,抗血小板療法</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="N88" t="str">
-        <v>血小板,Plt,platelet,出血,あざ,紫斑,骨髄抑制</v>
+        <v>UIBC,不飽和鉄結合能,鉄欠乏性貧血</v>
       </c>
       <c r="O88" t="str">
-        <v/>
+        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>RDW-SD</v>
+        <v>トランスフェリン飽和度</v>
       </c>
       <c r="B89" t="str">
-        <v>RDW-SD</v>
+        <v>TSAT</v>
       </c>
       <c r="C89" t="str">
-        <v>39〜46 fL程度（施設差あり）</v>
+        <v>16〜50%程度（施設差あり）</v>
       </c>
       <c r="D89" t="str">
-        <v>赤血球の大きさのばらつきを表す指標(絶対値)。鉄欠乏性貧血などの初期変化を捉えやすい</v>
+        <v>鉄を運ぶ役割のトランスフェリンのうち、実際に鉄を運んでいる割合（血清鉄÷総鉄結合能）</v>
       </c>
       <c r="E89" t="str">
-        <v>RDW-SDは、赤血球の大きさがどれくらいバラバラになっているかを表す数値です。貧血の原因を調べる際、鉄が足りなくなり始めた早い段階での変化を捉えるのに役立ちます。</v>
+        <v>トランスフェリン飽和度は、鉄を運ぶトランスフェリンのうち、実際にどれくらいが鉄を運んでいるかを割合で表したものです。鉄欠乏性貧血では低くなり、鉄が過剰にたまる病気では高くなります。</v>
       </c>
       <c r="F89" t="str">
-        <v>鉄欠乏性貧血の初期、混合性貧血（複数の原因が重なっている状態）、赤血球産生の乱れ</v>
+        <v>鉄過剰症（ヘモクロマトーシスなど）</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -4586,7 +4586,7 @@
         <v/>
       </c>
       <c r="I89" t="str">
-        <v/>
+        <v>鉄欠乏性貧血（＜16%が目安）</v>
       </c>
       <c r="J89" t="str">
         <v/>
@@ -4595,36 +4595,36 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>MCVが正常範囲でもRDWが上昇している場合、鉄欠乏の初期段階を示唆することがある。MCV・MCHと合わせて評価する</v>
+        <v>血清鉄をTIBCで割って計算される。鉄剤補充の効果判定にも使われる</v>
       </c>
       <c r="M89" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
       <c r="N89" t="str">
-        <v>RDW-SD,赤血球分布幅,貧血,鉄欠乏</v>
+        <v>トランスフェリン飽和度,TSAT,鉄欠乏性貧血</v>
       </c>
       <c r="O89" t="str">
-        <v>食事と栄養 p.151-164（第2部 貧血）</v>
+        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>RDW-CV</v>
+        <v>血清フェリチン</v>
       </c>
       <c r="B90" t="str">
-        <v>RDW-CV</v>
+        <v>Ferritin</v>
       </c>
       <c r="C90" t="str">
-        <v>11.5〜14.5%程度（施設差あり）</v>
+        <v>男性 20〜250 ng/mL、女性 10〜120 ng/mL（施設差あり）</v>
       </c>
       <c r="D90" t="str">
-        <v>赤血球の大きさのばらつきを割合(%)で表した指標</v>
+        <v>体に貯蔵されている鉄の量を反映する指標。貧血の症状が出るより早い段階で低下する</v>
       </c>
       <c r="E90" t="str">
-        <v>RDW-CVもRDW-SDと同じく、赤血球の大きさのばらつきを表す数値ですが、こちらは割合(%)で示されます。貧血のタイプを見分ける手がかりになります。</v>
+        <v>フェリチンは、体に蓄えられている鉄の「貯金」の量を見る検査です。この数値が下がるのは、貧血の症状が出るよりも前の、とても早い段階のサインになります。</v>
       </c>
       <c r="F90" t="str">
-        <v>鉄欠乏性貧血、ビタミンB12・葉酸欠乏性貧血、混合性貧血</v>
+        <v>炎症性疾患、肝疾患、悪性腫瘍、鉄過剰症（フェリチンは炎症でも上昇するため、貧血の評価では注意が必要）</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -4633,45 +4633,45 @@
         <v/>
       </c>
       <c r="I90" t="str">
-        <v/>
+        <v>鉄欠乏状態（貧血の症状が出る前の早期段階から低下する）</v>
       </c>
       <c r="J90" t="str">
-        <v/>
+        <v>鉄分の多い食品を意識するとともに、貯蔵鉄を補うため治療は数値が正常化してからも継続が必要なことを伝える</v>
       </c>
       <c r="K90" t="str">
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>RDW-SDと同様の意味を持つ指標。MCVが小さくRDWが高ければ鉄欠乏性貧血、MCVが大きくRDWが高ければビタミンB12・葉酸欠乏を疑う手がかりになる</v>
+        <v>貯蔵鉄の指標で鉄欠乏を最も早期に反映する。ただし炎症があると鉄欠乏があっても正常〜高値に出ることがあり、CRP等の炎症所見と合わせて評価する。二次性貧血との鑑別に重要</v>
       </c>
       <c r="M90" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
       <c r="N90" t="str">
-        <v>RDW-CV,赤血球分布幅,貧血,ビタミンB12,葉酸</v>
+        <v>フェリチン,Ferritin,貯蔵鉄,鉄欠乏</v>
       </c>
       <c r="O90" t="str">
-        <v>食事と栄養 p.151-164（第2部 貧血）</v>
+        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>好中球実数値</v>
+        <v>尿中尿酸/クレアチニン比（UUA/UCr）</v>
       </c>
       <c r="B91" t="str">
-        <v>Neutro#,ANC</v>
+        <v>UUA/UCr</v>
       </c>
       <c r="C91" t="str">
-        <v>2,000〜7,500 /μL程度（施設差あり、白血球数×好中球%で算出）</v>
+        <v>0.4〜0.8程度が混合型の目安</v>
       </c>
       <c r="D91" t="str">
-        <v>好中球の絶対数。感染症リスクを判断する上で割合(%)より重要な指標</v>
+        <v>尿酸が「作られすぎ」か「排泄できていない」かを見分ける比の値</v>
       </c>
       <c r="E91" t="str">
-        <v>これは好中球の実際の数を表す数値です。割合(%)だけでなく、実際の数がどれくらいあるかを見ることで、感染症にかかりやすい状態かどうかをより正確に判断できます。</v>
+        <v>この数値は、体の中で尿酸が「作られすぎている」のか、それとも「うまく排泄できていない」のかを見分けるために使う比の値です。高尿酸血症の治療薬を選ぶときの参考になります。</v>
       </c>
       <c r="F91" t="str">
-        <v>細菌感染症、炎症、ステロイド使用</v>
+        <v>尿酸産生過剰型（0.8以上が目安）</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -4680,51 +4680,51 @@
         <v/>
       </c>
       <c r="I91" t="str">
-        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、メルカゾールなど薬剤性の無顆粒球症（1,000/μL未満で好中球減少症、500/μL未満で重症感染リスクが著しく上昇）</v>
+        <v>尿酸排泄低下型（0.4以下が目安）</v>
       </c>
       <c r="J91" t="str">
-        <v>発熱、のどの痛みなど感染症状の初期サインがないか確認する。人混みを避け、手洗い・うがいを徹底するよう伝える</v>
+        <v/>
       </c>
       <c r="K91" t="str">
-        <v>抗がん剤、メルカゾール(無顆粒球症)、クロザピン、サラゾスルファピリジン</v>
+        <v/>
       </c>
       <c r="L91" t="str">
-        <v>抗がん剤・メルカゾール・カルバマゼピンなど骨髄抑制のリスクがある薬剤使用中は特に重視すべき数値。500/μL未満は発熱性好中球減少症のリスクが高く緊急性が高い</v>
+        <v>高尿酸血症は尿酸産生過剰型・排泄低下型・混合型に分類され、この比が目安になる。病型によって使う薬剤（尿酸生成抑制薬か尿酸排泄促進薬か）の選択が変わる</v>
       </c>
       <c r="M91" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>高尿酸血症</v>
       </c>
       <c r="N91" t="str">
-        <v>好中球実数値,好中球数,ANC,無顆粒球症,発熱性好中球減少症</v>
+        <v>UUA,UCr,尿酸クリアランス,CUA,EUA,尿酸産生過剰型,尿酸排泄低下型</v>
       </c>
       <c r="O91" t="str">
-        <v/>
+        <v>食事と栄養 p.180-189（第2部 痛風・高尿酸血症）</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>好酸球実数値</v>
+        <v>抗甲状腺マイクロゾーム抗体（抗TPO抗体）</v>
       </c>
       <c r="B92" t="str">
-        <v>Eosino#</v>
+        <v>TPOAb</v>
       </c>
       <c r="C92" t="str">
-        <v>100〜500 /μL程度（施設差あり）</v>
+        <v>陰性（16 IU/mL未満程度、施設差あり）</v>
       </c>
       <c r="D92" t="str">
-        <v>好酸球の絶対数。アレルギーや薬剤反応の程度をより正確に評価できる</v>
+        <v>自分の甲状腺を攻撃する抗体が出ていないかを見る検査</v>
       </c>
       <c r="E92" t="str">
-        <v>これは好酸球の実際の数を表す数値です。割合(%)だけでなく実数を見ることで、アレルギー反応の強さをより正確に把握できます。</v>
+        <v>この検査は、体の中に自分の甲状腺を誤って攻撃してしまう抗体がないかを見るものです。陽性の場合、橋本病（慢性甲状腺炎）など甲状腺の自己免疫的な炎症が背景にある可能性があります。</v>
       </c>
       <c r="F92" t="str">
-        <v>アレルギー性疾患、薬剤アレルギー、寄生虫感染</v>
+        <v>橋本病（慢性甲状腺炎）、バセドウ病などの自己免疫性甲状腺疾患</v>
       </c>
       <c r="G92" t="str">
-        <v>新しく始めた薬がないか確認する</v>
+        <v/>
       </c>
       <c r="H92" t="str">
-        <v>薬剤性好酸球増多(抗菌薬・NSAIDs・抗てんかん薬など)。発熱や皮疹を伴う場合はDRESS症候群にも注意</v>
+        <v/>
       </c>
       <c r="I92" t="str">
         <v/>
@@ -4736,36 +4736,36 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>薬剤性過敏症症候群(DIHS)などでは著明な好酸球増多を認めることがあり、原因薬剤の特定に役立つ</v>
+        <v>陽性でも必ずしも甲状腺機能異常があるとは限らない。TSH・FT4など甲状腺ホルモンの数値と合わせて評価する</v>
       </c>
       <c r="M92" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>甲状腺疾患</v>
       </c>
       <c r="N92" t="str">
-        <v>好酸球実数値,好酸球数,アレルギー,DIHS</v>
+        <v>抗TPO抗体,抗甲状腺マイクロゾーム抗体,TPOAb,橋本病</v>
       </c>
       <c r="O92" t="str">
-        <v/>
+        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>好塩基球実数値</v>
+        <v>抗サイログロブリン抗体</v>
       </c>
       <c r="B93" t="str">
-        <v>Baso#</v>
+        <v>TgAb</v>
       </c>
       <c r="C93" t="str">
-        <v>0〜100 /μL程度（施設差あり）</v>
+        <v>陰性（28 IU/mL未満程度、施設差あり）</v>
       </c>
       <c r="D93" t="str">
-        <v>好塩基球の絶対数</v>
+        <v>甲状腺のたんぱく質（サイログロブリン）への抗体が出ていないかを見る検査</v>
       </c>
       <c r="E93" t="str">
-        <v>これは好塩基球の実際の数を表す数値です。数がとても少ない種類の血球なので、通常は大きな変動を示すことは多くありません。</v>
+        <v>この検査も、抗TPO抗体と同じく、甲状腺に対する自己免疫の有無を見るものです。あわせて調べることで橋本病などの診断の参考にします。</v>
       </c>
       <c r="F93" t="str">
-        <v>慢性骨髄性白血病などの血液疾患、アレルギー性疾患</v>
+        <v>橋本病（慢性甲状腺炎）、バセドウ病などの自己免疫性甲状腺疾患</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -4783,60 +4783,60 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>単独での臨床的意義は乏しく、他の血球指標（白血球分画全体）と合わせて評価する</v>
+        <v>抗TPO抗体とあわせて測定されることが多い。単独の高値だけで治療方針が決まるわけではない</v>
       </c>
       <c r="M93" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>甲状腺疾患</v>
       </c>
       <c r="N93" t="str">
-        <v>好塩基球実数値,好塩基球数</v>
+        <v>抗サイログロブリン抗体,TgAb,橋本病</v>
       </c>
       <c r="O93" t="str">
-        <v/>
+        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>リンパ球実数値</v>
+        <v>血中薬物濃度（TDM）</v>
       </c>
       <c r="B94" t="str">
-        <v>Lympho#,ALC</v>
+        <v>TDM</v>
       </c>
       <c r="C94" t="str">
-        <v>1,000〜3,600 /μL程度（施設差あり）</v>
+        <v>薬剤ごとに有効域が異なる（例：フェニトイン 10〜20 μg/mL、ゾニサミド 10〜40 μg/mL、カルバマゼピン 4〜12 μg/mL、バルプロ酸ナトリウム 40〜120 μg/mL、ラモトリギン 1〜10 μg/mL(併用薬により変動)）</v>
       </c>
       <c r="D94" t="str">
-        <v>リンパ球の絶対数。免疫力の目安として使われる</v>
+        <v>治療域が狭い薬剤で、血液中の薬の濃度が効果域・中毒域のどちらにあるかを確認する検査</v>
       </c>
       <c r="E94" t="str">
-        <v>これはリンパ球の実際の数を表す数値です。免疫力の目安の一つとして使われ、抗がん剤や免疫抑制剤の副作用モニタリングにも用いられます。</v>
+        <v>この薬は効く量と副作用が出る量が近いため、血液中の薬の濃度を定期的に測って、ちょうどよい範囲に入っているかを確認します。数値が低いと効果が不十分になり、高いと副作用が出やすくなります。</v>
       </c>
       <c r="F94" t="str">
-        <v>ウイルス感染症、リンパ性白血病などの血液疾患</v>
+        <v>過量投与、代謝を妨げる薬剤との併用、肝機能低下による代謝低下</v>
       </c>
       <c r="G94" t="str">
-        <v/>
+        <v>ふらつき、眠気、めまい、物が二重に見えるなどの中毒症状がないか確認する</v>
       </c>
       <c r="H94" t="str">
         <v/>
       </c>
       <c r="I94" t="str">
-        <v>抗がん剤・免疫抑制剤・ステロイドの使用、強いストレス、AIDSなどの免疫不全</v>
+        <v>飲み忘れ、自己判断による減量、代謝を促進する薬剤との併用（相互作用）</v>
       </c>
       <c r="J94" t="str">
-        <v>感染予防（手洗い・うがい、人混みを避ける）を意識するよう伝える</v>
+        <v>発作やてんかん症状の再発がないか確認し、飲み忘れがないか一緒に確認する</v>
       </c>
       <c r="K94" t="str">
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>免疫抑制剤・抗がん剤治療中のモニタリング指標としても使われる。著明な低下時は日和見感染のリスクが高まる</v>
+        <v>採血のタイミング（トラフ値かどうか）で数値の解釈が変わるため採血時点を確認する。カルバマゼピンは自己誘導により長期使用で濃度が下がることがある点にも注意</v>
       </c>
       <c r="M94" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>てんかん</v>
       </c>
       <c r="N94" t="str">
-        <v>リンパ球実数値,リンパ球数,ALC,免疫抑制剤,日和見感染</v>
+        <v>TDM,血中薬物濃度,治療域,中毒域,カルバマゼピン,フェニトイン,バルプロ酸,抗てんかん薬,ゾニサミド,ラモトリギン</v>
       </c>
       <c r="O94" t="str">
         <v/>
@@ -4844,31 +4844,31 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>単球実数値</v>
+        <v>アミラーゼ（AMY）</v>
       </c>
       <c r="B95" t="str">
-        <v>Mono#</v>
+        <v>AMY</v>
       </c>
       <c r="C95" t="str">
-        <v>200〜600 /μL程度（施設差あり）</v>
+        <v>44〜132 U/L（施設差あり）</v>
       </c>
       <c r="D95" t="str">
-        <v>単球の絶対数</v>
+        <v>膵臓や唾液腺から出る消化酵素。膵炎などで血液中に漏れ出す</v>
       </c>
       <c r="E95" t="str">
-        <v>これは単球の実際の数を表す数値です。慢性的な炎症や感染症の状態を把握する材料の一つになります。</v>
+        <v>アミラーゼは、でんぷんを分解する消化酵素で、主に膵臓と唾液腺から作られます。膵臓に炎症が起きると血液中に漏れ出して数値が上がるため、膵炎の診断や経過観察に使われます。</v>
       </c>
       <c r="F95" t="str">
-        <v>慢性感染症、炎症性疾患、血液疾患</v>
+        <v>急性膵炎、慢性膵炎の急性増悪、耳下腺炎（おたふくかぜ）、腎不全</v>
       </c>
       <c r="G95" t="str">
-        <v/>
+        <v>飲酒を控え、脂っこい食事を避けるよう伝える。強い腹痛・背部痛がある場合は急性膵炎の可能性もあるため早めの受診を勧める</v>
       </c>
       <c r="H95" t="str">
-        <v/>
+        <v>バルプロ酸、アザチオプリン、サイアザイド系・ループ利尿薬、ステロイドなど薬剤性膵炎の原因薬</v>
       </c>
       <c r="I95" t="str">
-        <v/>
+        <v>慢性膵炎の進行期（膵臓の機能低下）</v>
       </c>
       <c r="J95" t="str">
         <v/>
@@ -4877,13 +4877,13 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>単独での臨床的意義は乏しく、他の血球指標と合わせて評価する</v>
+        <v>膵臓由来か唾液腺由来かを区別するには膵型アミラーゼ(P-AMY)を確認する。急性膵炎では強い腹痛・背部痛を伴うことが多く、飲酒歴の確認も重要</v>
       </c>
       <c r="M95" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v/>
       </c>
       <c r="N95" t="str">
-        <v>単球実数値,単球数</v>
+        <v>アミラーゼ,AMY,膵炎,急性膵炎</v>
       </c>
       <c r="O95" t="str">
         <v/>
@@ -4891,46 +4891,46 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>好中球</v>
+        <v>間接ビリルビン</v>
       </c>
       <c r="B96" t="str">
-        <v>Neutro,Neut%</v>
+        <v>I-Bil</v>
       </c>
       <c r="C96" t="str">
-        <v>40〜75%程度（施設差あり）</v>
+        <v>0.2〜0.8 mg/dL程度（施設差あり）</v>
       </c>
       <c r="D96" t="str">
-        <v>白血球の中で最も多くを占め、細菌感染と戦う主力の免疫細胞の割合</v>
+        <v>赤血球が壊れてできるビリルビンのうち、肝臓で処理される前の形</v>
       </c>
       <c r="E96" t="str">
-        <v>好中球は、白血球の中で最も数が多く、細菌が体に入ってきたときに真っ先に戦ってくれる免疫細胞です。感染症や炎症があると増え、逆に薬の副作用などで減ることがあります。</v>
+        <v>間接ビリルビンは、赤血球が壊れてできたビリルビンが、まだ肝臓で処理される前の状態です。この値が高い場合、赤血球が通常より多く壊れている(溶血)か、肝臓での処理能力に生まれつきの体質差(体質性黄疸)がある可能性が考えられます。</v>
       </c>
       <c r="F96" t="str">
-        <v>細菌感染症、炎症、ストレス、ステロイド使用</v>
+        <v>溶血性疾患（自己免疫性溶血性貧血、血液型不適合輸血など）、体質性黄疸（ジルベール症候群）、新生児黄疸</v>
       </c>
       <c r="G96" t="str">
-        <v>発熱や炎症症状がないか確認する</v>
+        <v>皮膚や白目の黄染、尿の色の変化がないか確認する</v>
       </c>
       <c r="H96" t="str">
         <v/>
       </c>
       <c r="I96" t="str">
-        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、ウイルス感染、メルカゾールなど薬剤性の無顆粒球症</v>
+        <v/>
       </c>
       <c r="J96" t="str">
-        <v>発熱やのどの痛みなど感染症状の初期サインがないか確認する</v>
+        <v/>
       </c>
       <c r="K96" t="str">
-        <v>抗がん剤、メルカゾール(無顆粒球症)、クロザピン、サラゾスルファピリジン</v>
+        <v/>
       </c>
       <c r="L96" t="str">
-        <v>好中球の絶対数（好中球実数値）が500/μL未満になると重篤な感染症のリスクが高まる。割合(%)だけでなく実数値も合わせて確認する</v>
+        <v>直接ビリルビンとの比率で原因を推測する（間接優位は溶血・体質性、直接優位は胆道系）。総ビリルビン・AST/ALTと合わせて評価する</v>
       </c>
       <c r="M96" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>肝機能</v>
       </c>
       <c r="N96" t="str">
-        <v>好中球,Neutro,Neut,感染症,無顆粒球症</v>
+        <v>間接ビリルビン,I-Bil,溶血</v>
       </c>
       <c r="O96" t="str">
         <v/>
@@ -4938,28 +4938,28 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>好酸球</v>
+        <v>直接ビリルビン</v>
       </c>
       <c r="B97" t="str">
-        <v>Eosino,Eos%</v>
+        <v>D-Bil</v>
       </c>
       <c r="C97" t="str">
-        <v>1〜5%程度（施設差あり）</v>
+        <v>0.0〜0.3 mg/dL程度（施設差あり）</v>
       </c>
       <c r="D97" t="str">
-        <v>アレルギー反応や寄生虫感染に関わる白血球の一種の割合</v>
+        <v>肝臓で処理された後のビリルビン。胆道の詰まりで血液中に増える</v>
       </c>
       <c r="E97" t="str">
-        <v>好酸球は、アレルギー反応や寄生虫感染と関係が深い免疫細胞です。アレルギー性の病気や薬の副作用（薬疹など）で増えることがあります。</v>
+        <v>直接ビリルビンは、肝臓で処理された後のビリルビンです。胆石や腫瘍などで胆汁の通り道（胆道）が詰まると、行き場を失って血液中に増え、皮膚や白目が黄色くなる黄疸として現れます。</v>
       </c>
       <c r="F97" t="str">
-        <v>アレルギー性疾患（気管支喘息、アトピー性皮膚炎など）、薬剤アレルギー、寄生虫感染</v>
+        <v>肝疾患、胆石など胆道の閉塞</v>
       </c>
       <c r="G97" t="str">
-        <v>新しく始めた薬がないか確認する。皮疹やかゆみなどアレルギー症状の有無を確認する</v>
+        <v>皮膚や白目の黄染、白っぽい便、濃い茶色の尿がないか確認する</v>
       </c>
       <c r="H97" t="str">
-        <v>薬剤性好酸球増多(抗菌薬・NSAIDs・抗てんかん薬など)。発熱や皮疹を伴う場合はDRESS症候群にも注意</v>
+        <v>胆汁うっ滞型の薬剤性肝障害を起こしうる抗菌薬、経口避妊薬</v>
       </c>
       <c r="I97" t="str">
         <v/>
@@ -4971,13 +4971,13 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>薬剤性の好酸球増多は、原因薬剤の中止で改善することが多い。新規薬剤開始後の皮疹・発熱と合わせて薬剤性過敏症症候群(DIHS)を疑う材料になる</v>
+        <v>直接優位の上昇は胆道系（胆石、腫瘍による閉塞）を、間接優位の上昇は溶血・体質性を疑う手がかりになる。γ-GTP・ALPと合わせて胆道系疾患を評価する</v>
       </c>
       <c r="M97" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>肝機能</v>
       </c>
       <c r="N97" t="str">
-        <v>好酸球,Eosino,Eos,アレルギー,薬疹,DIHS</v>
+        <v>直接ビリルビン,D-Bil,胆石,胆道閉塞</v>
       </c>
       <c r="O97" t="str">
         <v/>
@@ -4985,22 +4985,22 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>好塩基球</v>
+        <v>亜鉛（Zn）</v>
       </c>
       <c r="B98" t="str">
-        <v>Baso,Baso%</v>
+        <v>Zn</v>
       </c>
       <c r="C98" t="str">
-        <v>0〜2%程度（施設差あり）</v>
+        <v>80〜130 μg/dL程度（施設差あり）</v>
       </c>
       <c r="D98" t="str">
-        <v>白血球の中で最も数が少なく、アレルギー反応に関わる細胞の割合</v>
+        <v>味覚や皮膚、免疫に関わる微量ミネラル。高齢者や低栄養で不足しやすい</v>
       </c>
       <c r="E98" t="str">
-        <v>好塩基球は白血球の中で最も数が少ない種類で、アレルギー反応や炎症に関わっています。数値の変動が病気の診断に直接使われることは少ない検査です。</v>
+        <v>亜鉛は、味を感じる働きや皮膚・粘膜の健康、免疫の働きに関わる微量ミネラルです。不足すると、味がわかりにくくなったり（味覚障害）、傷が治りにくくなったりすることがあります。</v>
       </c>
       <c r="F98" t="str">
-        <v>慢性骨髄性白血病などの血液疾患、アレルギー性疾患、甲状腺機能低下症</v>
+        <v/>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -5009,72 +5009,72 @@
         <v/>
       </c>
       <c r="I98" t="str">
-        <v/>
+        <v>低栄養、高齢による摂取不足、消化器手術後、亜鉛の吸収を妨げる薬剤（PPI、キレート形成する薬剤など）との併用</v>
       </c>
       <c r="J98" t="str">
-        <v/>
+        <v>味覚の変化（味を感じにくい、金属味がするなど）がないか確認する。牡蠣、赤身肉、レバーなど亜鉛を多く含む食品を意識するとよいことを伝える</v>
       </c>
       <c r="K98" t="str">
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>単独での臨床的意義は乏しいが、著明な増加は血液疾患（慢性骨髄性白血病等）の可能性があり他の血球指標と合わせて評価する</v>
+        <v>薬剤性の亜鉛欠乏（PPI長期使用、D-ペニシラミン、一部の降圧薬など）に注意。亜鉛欠乏による味覚障害は原因薬剤の中止・亜鉛補充で改善することがある</v>
       </c>
       <c r="M98" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v/>
       </c>
       <c r="N98" t="str">
-        <v>好塩基球,Baso,アレルギー,白血病</v>
+        <v>亜鉛,Zn,味覚障害,亜鉛欠乏</v>
       </c>
       <c r="O98" t="str">
-        <v/>
+        <v>食事と栄養 p.78（亜鉛）</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>リンパ球</v>
+        <v>マグネシウム（Mg）</v>
       </c>
       <c r="B99" t="str">
-        <v>Lympho,Lym%</v>
+        <v>Mg</v>
       </c>
       <c r="C99" t="str">
-        <v>18〜49%程度（施設差あり）</v>
+        <v>1.8〜2.6 mg/dL程度（施設差あり）</v>
       </c>
       <c r="D99" t="str">
-        <v>ウイルス感染と戦い、免疫の記憶を担う白血球の割合</v>
+        <v>骨や筋肉、神経の働きに関わるミネラル。低栄養や利尿薬で不足しやすい</v>
       </c>
       <c r="E99" t="str">
-        <v>リンパ球は、ウイルスと戦ったり、一度かかった病気を記憶して免疫をつくったりする細胞です。ウイルス感染で増え、抗がん剤の副作用や強いストレスで減ることがあります。</v>
+        <v>マグネシウムは、骨や筋肉、神経の働きを支えるミネラルです。不足すると、こむら返りや不整脈、だるさなどの症状が出ることがあります。</v>
       </c>
       <c r="F99" t="str">
-        <v>ウイルス感染症、リンパ性白血病などの血液疾患、百日咳</v>
+        <v>腎不全、マグネシウム製剤（酸化マグネシウムなど）の過量投与</v>
       </c>
       <c r="G99" t="str">
-        <v/>
+        <v>腎機能低下がある患者で酸化マグネシウムなどの緩下剤を使用中は、傾眠・血圧低下などの高マグネシウム血症の症状がないか確認する</v>
       </c>
       <c r="H99" t="str">
-        <v/>
+        <v>マグネシウム含有制酸薬・下剤の過量(特に腎機能低下患者)</v>
       </c>
       <c r="I99" t="str">
-        <v>抗がん剤・免疫抑制剤・ステロイドの使用、強いストレス、AIDSなどの免疫不全</v>
+        <v>低栄養、利尿薬の使用、慢性的な下痢、アルコール多飲、PPI長期使用</v>
       </c>
       <c r="J99" t="str">
-        <v>免疫が下がっている可能性があるため、感染予防（手洗い・うがい、人混みを避ける）を意識するよう伝える</v>
+        <v>こむら返りや動悸などの症状がないか確認する</v>
       </c>
       <c r="K99" t="str">
-        <v/>
+        <v>プロトンポンプ阻害薬(PPI)の長期使用、ループ利尿薬、サイアザイド系利尿薬、シスプラチン、アミノグリコシド系</v>
       </c>
       <c r="L99" t="str">
-        <v>ステロイド・免疫抑制剤使用中はリンパ球減少による易感染性に注意。好中球と逆方向に動くことが多い（ウイルス感染ではリンパ球優位、細菌感染では好中球優位になりやすい）</v>
+        <v>腎機能低下患者への酸化マグネシウム投与は高マグネシウム血症のリスクがあるため定期的なモニタリングが必要。PPI長期使用も低マグネシウム血症のリスク因子として知られる</v>
       </c>
       <c r="M99" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>腎機能</v>
       </c>
       <c r="N99" t="str">
-        <v>リンパ球,Lympho,Lym,ウイルス感染,免疫抑制剤,ステロイド</v>
+        <v>マグネシウム,Mg,酸化マグネシウム,こむら返り</v>
       </c>
       <c r="O99" t="str">
-        <v/>
+        <v>食事と栄養 p.84（マグネシウム）</v>
       </c>
     </row>
     <row r="100">

--- a/検査値リファレンス初期データ.xlsx
+++ b/検査値リファレンス初期データ.xlsx
@@ -3434,28 +3434,28 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>尿蛋白（随時尿）</v>
+        <v>単球</v>
       </c>
       <c r="B65" t="str">
-        <v>尿蛋白,U-pro</v>
+        <v>Mono,Mono%</v>
       </c>
       <c r="C65" t="str">
-        <v>陰性（－）〜弱陽性</v>
+        <v>2〜10%程度（施設差あり）</v>
       </c>
       <c r="D65" t="str">
-        <v>腎臓から本来漏れないはずのたんぱくが尿に出ていないかを見る検査</v>
+        <v>感染や炎症の後始末をする白血球の一種の割合</v>
       </c>
       <c r="E65" t="str">
-        <v>この検査は、腎臓のろ過機能に負担がかかっていないかを見るものです。本来、たんぱく質は尿にほとんど出ませんが、腎臓に負担がかかると漏れ出るようになります。</v>
+        <v>単球は、細菌などを取り込んで処理したり、組織の修復に関わったりする免疫細胞です。慢性的な炎症や感染症の回復期に増えることがあります。</v>
       </c>
       <c r="F65" t="str">
-        <v>糖尿病性腎症、腎炎、高血圧性腎硬化症、発熱・運動後の一過性のもの</v>
+        <v>慢性感染症（結核など）、炎症性疾患、血液疾患、感染症の回復期</v>
       </c>
       <c r="G65" t="str">
-        <v>発熱・激しい運動の直後でないか確認する(一過性のことがある)。持続する場合は塩分の摂りすぎに注意し、むくみの有無もあわせて確認する</v>
+        <v/>
       </c>
       <c r="H65" t="str">
-        <v>NSAIDs、造影剤、アミノグリコシド系、バンコマイシン、金製剤</v>
+        <v/>
       </c>
       <c r="I65" t="str">
         <v/>
@@ -3467,13 +3467,13 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>発熱・激しい運動・起立性蛋白尿など生理的な要因でも陽性になることがある。持続する場合に腎症の進行を疑う</v>
+        <v>単独での臨床的意義は乏しく、他の血球指標や炎症マーカー(CRPなど)と合わせて評価する</v>
       </c>
       <c r="M65" t="str">
-        <v>糖尿病,腎機能</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N65" t="str">
-        <v>尿蛋白,U-pro,腎症,たんぱく尿</v>
+        <v>単球,Mono,慢性感染症,結核,炎症</v>
       </c>
       <c r="O65" t="str">
         <v/>
@@ -3481,31 +3481,31 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>尿クレアチニン（随時尿）</v>
+        <v>尿蛋白（随時尿）</v>
       </c>
       <c r="B66" t="str">
-        <v>尿CRE</v>
+        <v>尿蛋白,U-pro</v>
       </c>
       <c r="C66" t="str">
-        <v>随時尿は主に他項目の濃度補正に利用（単独の基準値は設けにくい）</v>
+        <v>陰性（－）〜弱陽性</v>
       </c>
       <c r="D66" t="str">
-        <v>随時尿中のクレアチニン濃度。他の尿検査項目を薄まり具合で補正するための基準として使う</v>
+        <v>腎臓から本来漏れないはずのたんぱくが尿に出ていないかを見る検査</v>
       </c>
       <c r="E66" t="str">
-        <v>この数値は、尿がどれくらい薄まっているかを確認するための基準として使われます。他の尿検査の結果（蛋白やアルブミンなど）をこの値で割って補正することで、水分摂取量による影響を減らして正確に評価できます。</v>
+        <v>この検査は、腎臓のろ過機能に負担がかかっていないかを見るものです。本来、たんぱく質は尿にほとんど出ませんが、腎臓に負担がかかると漏れ出るようになります。</v>
       </c>
       <c r="F66" t="str">
-        <v/>
+        <v>糖尿病性腎症、腎炎、高血圧性腎硬化症、発熱・運動後の一過性のもの</v>
       </c>
       <c r="G66" t="str">
-        <v/>
+        <v>発熱・激しい運動の直後でないか確認する(一過性のことがある)。持続する場合は塩分の摂りすぎに注意し、むくみの有無もあわせて確認する</v>
       </c>
       <c r="H66" t="str">
-        <v/>
+        <v>NSAIDs、造影剤、アミノグリコシド系、バンコマイシン、金製剤</v>
       </c>
       <c r="I66" t="str">
-        <v>尿が薄い（水分摂取が多い、腎機能低下）状態</v>
+        <v/>
       </c>
       <c r="J66" t="str">
         <v/>
@@ -3514,13 +3514,13 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>尿中アルブミン/Cr比、尿蛋白/Cr比など、他項目の補正計算に使われる。単独の高低に臨床的意味は乏しい</v>
+        <v>発熱・激しい運動・起立性蛋白尿など生理的な要因でも陽性になることがある。持続する場合に腎症の進行を疑う</v>
       </c>
       <c r="M66" t="str">
-        <v>腎機能</v>
+        <v>糖尿病,腎機能</v>
       </c>
       <c r="N66" t="str">
-        <v>尿CRE,尿クレアチニン,随時尿,補正,蛋白クレアチニン比</v>
+        <v>尿蛋白,U-pro,腎症,たんぱく尿</v>
       </c>
       <c r="O66" t="str">
         <v/>
@@ -3528,31 +3528,31 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>尿蛋白定量</v>
+        <v>尿クレアチニン（随時尿）</v>
       </c>
       <c r="B67" t="str">
-        <v>U-Pro定量,蛋白/Cr比</v>
+        <v>尿CRE</v>
       </c>
       <c r="C67" t="str">
-        <v>0.15 g/gCr未満</v>
+        <v>随時尿は主に他項目の濃度補正に利用（単独の基準値は設けにくい）</v>
       </c>
       <c r="D67" t="str">
-        <v>随時尿から尿蛋白の量を具体的な数値として評価する検査。ネフローゼ等の重症度判定に使う</v>
+        <v>随時尿中のクレアチニン濃度。他の尿検査項目を薄まり具合で補正するための基準として使う</v>
       </c>
       <c r="E67" t="str">
-        <v>これは、尿に出ているたんぱくの量を具体的な数値で見る検査です。試験紙での陽性・陰性の判定だけでなく、実際にどれくらいの量が出ているかを把握できます。</v>
+        <v>この数値は、尿がどれくらい薄まっているかを確認するための基準として使われます。他の尿検査の結果（蛋白やアルブミンなど）をこの値で割って補正することで、水分摂取量による影響を減らして正確に評価できます。</v>
       </c>
       <c r="F67" t="str">
-        <v>腎症の進行（糖尿病性腎症、慢性腎臓病など）、ネフローゼ症候群（3.5 g/gCr以上が目安）</v>
+        <v/>
       </c>
       <c r="G67" t="str">
-        <v>持続する場合は塩分の摂りすぎに注意し、むくみの有無も確認する。腎臓内科でのフォロー状況もあわせて確認する</v>
+        <v/>
       </c>
       <c r="H67" t="str">
-        <v>NSAIDs、造影剤、アミノグリコシド系、バンコマイシン</v>
+        <v/>
       </c>
       <c r="I67" t="str">
-        <v/>
+        <v>尿が薄い（水分摂取が多い、腎機能低下）状態</v>
       </c>
       <c r="J67" t="str">
         <v/>
@@ -3561,13 +3561,13 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>CKD診療ガイドラインの重症度分類（尿蛋白量による区分）にも使われる定量指標。試験紙法の半定量結果より治療効果判定に適する</v>
+        <v>尿中アルブミン/Cr比、尿蛋白/Cr比など、他項目の補正計算に使われる。単独の高低に臨床的意味は乏しい</v>
       </c>
       <c r="M67" t="str">
-        <v>腎機能,糖尿病</v>
+        <v>腎機能</v>
       </c>
       <c r="N67" t="str">
-        <v>尿蛋白,随時尿,定量,蛋白クレアチニン比,ネフローゼ</v>
+        <v>尿CRE,尿クレアチニン,随時尿,補正,蛋白クレアチニン比</v>
       </c>
       <c r="O67" t="str">
         <v/>
@@ -3575,46 +3575,46 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>尿pH</v>
+        <v>尿蛋白定量</v>
       </c>
       <c r="B68" t="str">
-        <v>尿pH</v>
+        <v>U-Pro定量,蛋白/Cr比</v>
       </c>
       <c r="C68" t="str">
-        <v>4.5〜7.5程度（弱酸性が多い）</v>
+        <v>0.15 g/gCr未満</v>
       </c>
       <c r="D68" t="str">
-        <v>尿の酸性・アルカリ性の度合い。食事や感染症、体の状態を反映する</v>
+        <v>随時尿から尿蛋白の量を具体的な数値として評価する検査。ネフローゼ等の重症度判定に使う</v>
       </c>
       <c r="E68" t="str">
-        <v>尿のpHは酸性・アルカリ性のバランスを表します。食事の内容や感染症、体の代謝状態によって変化します。単独で大きな問題を示すことは少ない検査です。</v>
+        <v>これは、尿に出ているたんぱくの量を具体的な数値で見る検査です。試験紙での陽性・陰性の判定だけでなく、実際にどれくらいの量が出ているかを把握できます。</v>
       </c>
       <c r="F68" t="str">
-        <v>尿路感染症（尿素分解菌によるもの）、野菜中心の食事、過換気</v>
+        <v>腎症の進行（糖尿病性腎症、慢性腎臓病など）、ネフローゼ症候群（3.5 g/gCr以上が目安）</v>
       </c>
       <c r="G68" t="str">
-        <v/>
+        <v>持続する場合は塩分の摂りすぎに注意し、むくみの有無も確認する。腎臓内科でのフォロー状況もあわせて確認する</v>
       </c>
       <c r="H68" t="str">
-        <v/>
+        <v>NSAIDs、造影剤、アミノグリコシド系、バンコマイシン</v>
       </c>
       <c r="I68" t="str">
-        <v>高たんぱく食、糖尿病性ケトアシドーシス、痛風発作時（酸性尿は尿酸結石のリスクを高める）</v>
+        <v/>
       </c>
       <c r="J68" t="str">
-        <v>痛風・尿酸結石がある場合は、野菜など尿をアルカリ化する食品を意識するとよいことを伝える</v>
+        <v/>
       </c>
       <c r="K68" t="str">
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>高尿酸血症・尿酸結石の患者では尿pHが酸性に傾いていないか確認する。尿アルカリ化薬（ウラリットなど）の効果判定にも使う</v>
+        <v>CKD診療ガイドラインの重症度分類（尿蛋白量による区分）にも使われる定量指標。試験紙法の半定量結果より治療効果判定に適する</v>
       </c>
       <c r="M68" t="str">
-        <v>高尿酸血症</v>
+        <v>腎機能,糖尿病</v>
       </c>
       <c r="N68" t="str">
-        <v>尿pH,尿酸性度,尿アルカリ化,ウラリット</v>
+        <v>尿蛋白,随時尿,定量,蛋白クレアチニン比,ネフローゼ</v>
       </c>
       <c r="O68" t="str">
         <v/>
@@ -3622,46 +3622,46 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>尿ケトン体</v>
+        <v>尿pH</v>
       </c>
       <c r="B69" t="str">
-        <v>尿ケトン,Ket</v>
+        <v>尿pH</v>
       </c>
       <c r="C69" t="str">
-        <v>陰性（－）</v>
+        <v>4.5〜7.5程度（弱酸性が多い）</v>
       </c>
       <c r="D69" t="str">
-        <v>体がブドウ糖の代わりに脂肪を分解してエネルギーを作っているサイン</v>
+        <v>尿の酸性・アルカリ性の度合い。食事や感染症、体の状態を反映する</v>
       </c>
       <c r="E69" t="str">
-        <v>この検査は、体が糖の代わりに脂肪を使ってエネルギーを作っていないかを見るものです。陽性が続くときは、食事や水分、インスリンの使い方を確認する必要があります。</v>
+        <v>尿のpHは酸性・アルカリ性のバランスを表します。食事の内容や感染症、体の代謝状態によって変化します。単独で大きな問題を示すことは少ない検査です。</v>
       </c>
       <c r="F69" t="str">
-        <v>糖尿病の血糖コントロール不良（シックデイ・インスリン不足）、極端な糖質制限、絶食、嘔吐・下痢による脱水</v>
+        <v>尿路感染症（尿素分解菌によるもの）、野菜中心の食事、過換気</v>
       </c>
       <c r="G69" t="str">
-        <v>糖尿病治療中の場合はシックデイ時の対応(インスリンを自己中断しない、水分摂取を続けるなど)を確認する。体調不良時の対応方法を事前に説明しておく</v>
+        <v/>
       </c>
       <c r="H69" t="str">
-        <v>SGLT2阻害薬(特に絶食・シックデイ時の正常血糖ケトアシドーシスに注意)</v>
+        <v/>
       </c>
       <c r="I69" t="str">
-        <v/>
+        <v>高たんぱく食、糖尿病性ケトアシドーシス、痛風発作時（酸性尿は尿酸結石のリスクを高める）</v>
       </c>
       <c r="J69" t="str">
-        <v/>
+        <v>痛風・尿酸結石がある場合は、野菜など尿をアルカリ化する食品を意識するとよいことを伝える</v>
       </c>
       <c r="K69" t="str">
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>陽性かつ高血糖・全身倦怠感が強い場合は糖尿病性ケトアシドーシスの可能性があり緊急性が高い。シックデイルールの説明歴を確認する</v>
+        <v>高尿酸血症・尿酸結石の患者では尿pHが酸性に傾いていないか確認する。尿アルカリ化薬（ウラリットなど）の効果判定にも使う</v>
       </c>
       <c r="M69" t="str">
-        <v>糖尿病</v>
+        <v>高尿酸血症</v>
       </c>
       <c r="N69" t="str">
-        <v>尿ケトン体,ケトン体,Ket,シックデイ,ケトアシドーシス</v>
+        <v>尿pH,尿酸性度,尿アルカリ化,ウラリット</v>
       </c>
       <c r="O69" t="str">
         <v/>
@@ -3669,31 +3669,31 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>ウロビリノーゲン</v>
+        <v>尿ケトン体</v>
       </c>
       <c r="B70" t="str">
-        <v>Uro</v>
+        <v>尿ケトン,Ket</v>
       </c>
       <c r="C70" t="str">
-        <v>正常（±）程度</v>
+        <v>陰性（－）</v>
       </c>
       <c r="D70" t="str">
-        <v>肝臓や胆道、赤血球の壊れ方の状態を反映する尿検査項目</v>
+        <v>体がブドウ糖の代わりに脂肪を分解してエネルギーを作っているサイン</v>
       </c>
       <c r="E70" t="str">
-        <v>ウロビリノーゲンは、赤血球やビリルビンが体の中で処理される過程でできる物質です。肝臓の働きが悪くなったり、赤血球が壊れやすくなったりすると、尿の中の量が変化します。</v>
+        <v>この検査は、体が糖の代わりに脂肪を使ってエネルギーを作っていないかを見るものです。陽性が続くときは、食事や水分、インスリンの使い方を確認する必要があります。</v>
       </c>
       <c r="F70" t="str">
-        <v>溶血性疾患（赤血球の破壊亢進）、肝機能障害</v>
+        <v>糖尿病の血糖コントロール不良（シックデイ・インスリン不足）、極端な糖質制限、絶食、嘔吐・下痢による脱水</v>
       </c>
       <c r="G70" t="str">
-        <v/>
+        <v>糖尿病治療中の場合はシックデイ時の対応(インスリンを自己中断しない、水分摂取を続けるなど)を確認する。体調不良時の対応方法を事前に説明しておく</v>
       </c>
       <c r="H70" t="str">
-        <v/>
+        <v>SGLT2阻害薬(特に絶食・シックデイ時の正常血糖ケトアシドーシスに注意)</v>
       </c>
       <c r="I70" t="str">
-        <v>胆道閉塞（胆汁が腸に流れず、ウロビリノーゲンが作られない状態）</v>
+        <v/>
       </c>
       <c r="J70" t="str">
         <v/>
@@ -3702,13 +3702,13 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>完全に陰性の場合は胆道閉塞を疑う所見の一つ。肝機能（AST/ALT/ビリルビン）と合わせて評価する</v>
+        <v>陽性かつ高血糖・全身倦怠感が強い場合は糖尿病性ケトアシドーシスの可能性があり緊急性が高い。シックデイルールの説明歴を確認する</v>
       </c>
       <c r="M70" t="str">
-        <v>肝機能</v>
+        <v>糖尿病</v>
       </c>
       <c r="N70" t="str">
-        <v>ウロビリノーゲン,Uro,溶血,胆道閉塞,肝機能</v>
+        <v>尿ケトン体,ケトン体,Ket,シックデイ,ケトアシドーシス</v>
       </c>
       <c r="O70" t="str">
         <v/>
@@ -3716,31 +3716,31 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>尿潜血反応</v>
+        <v>ウロビリノーゲン</v>
       </c>
       <c r="B71" t="str">
-        <v>尿潜血,U-OB</v>
+        <v>Uro</v>
       </c>
       <c r="C71" t="str">
-        <v>陰性（－）</v>
+        <v>正常（±）程度</v>
       </c>
       <c r="D71" t="str">
-        <v>尿に血液（赤血球）が混じっていないかを見る検査</v>
+        <v>肝臓や胆道、赤血球の壊れ方の状態を反映する尿検査項目</v>
       </c>
       <c r="E71" t="str">
-        <v>この検査は、尿に目に見えないくらいの微量の血液が混じっていないかを調べるものです。陽性の場合、腎臓や膀胱、尿路のどこかに炎症や結石などがある可能性があります。</v>
+        <v>ウロビリノーゲンは、赤血球やビリルビンが体の中で処理される過程でできる物質です。肝臓の働きが悪くなったり、赤血球が壊れやすくなったりすると、尿の中の量が変化します。</v>
       </c>
       <c r="F71" t="str">
-        <v>尿路結石、膀胱炎などの尿路感染症、腎炎、腫瘍、月経血の混入、激しい運動後</v>
+        <v>溶血性疾患（赤血球の破壊亢進）、肝機能障害</v>
       </c>
       <c r="G71" t="str">
-        <v>排尿時の痛みや頻尿、目に見える血尿の有無を確認する。女性は月経の時期と重なっていないか確認する</v>
+        <v/>
       </c>
       <c r="H71" t="str">
-        <v>ワルファリン、DOAC、抗血小板薬など出血傾向を強める薬剤の服用状況を確認</v>
+        <v/>
       </c>
       <c r="I71" t="str">
-        <v/>
+        <v>胆道閉塞（胆汁が腸に流れず、ウロビリノーゲンが作られない状態）</v>
       </c>
       <c r="J71" t="str">
         <v/>
@@ -3749,13 +3749,13 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>陽性でも尿沈渣で赤血球が確認されない場合は偽陽性（ミオグロビン尿など）のこともある。持続する場合は泌尿器科的な精査が必要</v>
+        <v>完全に陰性の場合は胆道閉塞を疑う所見の一つ。肝機能（AST/ALT/ビリルビン）と合わせて評価する</v>
       </c>
       <c r="M71" t="str">
-        <v>腎機能</v>
+        <v>肝機能</v>
       </c>
       <c r="N71" t="str">
-        <v>尿潜血,潜血反応,U-OB,血尿,尿路結石,膀胱炎</v>
+        <v>ウロビリノーゲン,Uro,溶血,胆道閉塞,肝機能</v>
       </c>
       <c r="O71" t="str">
         <v/>
@@ -3763,28 +3763,28 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>尿糖（半定量）</v>
+        <v>尿潜血反応</v>
       </c>
       <c r="B72" t="str">
-        <v>尿糖,U-Glu</v>
+        <v>尿潜血,U-OB</v>
       </c>
       <c r="C72" t="str">
         <v>陰性（－）</v>
       </c>
       <c r="D72" t="str">
-        <v>尿に糖が漏れ出ていないかを見る検査。血糖値がかなり高いと陽性になる</v>
+        <v>尿に血液（赤血球）が混じっていないかを見る検査</v>
       </c>
       <c r="E72" t="str">
-        <v>通常、糖は尿にはほとんど出ませんが、血糖値がかなり高くなると尿にあふれ出るようになります。血糖コントロールの目安の一つです。</v>
+        <v>この検査は、尿に目に見えないくらいの微量の血液が混じっていないかを調べるものです。陽性の場合、腎臓や膀胱、尿路のどこかに炎症や結石などがある可能性があります。</v>
       </c>
       <c r="F72" t="str">
-        <v>糖尿病（血糖値が腎臓で再吸収できる量を超えている状態）、腎性糖尿（血糖値が正常でも体質的に出ることがある）、SGLT2阻害薬服用中（薬の作用で意図的に糖を排泄するため陽性になるのが正常）</v>
+        <v>尿路結石、膀胱炎などの尿路感染症、腎炎、腫瘍、月経血の混入、激しい運動後</v>
       </c>
       <c r="G72" t="str">
-        <v>SGLT2阻害薬（フォシーガ、ジャディアンスなど）服用中は、陽性が薬の効果によるものであることを説明する。脱水や尿路感染の症状がないかも確認する</v>
+        <v>排尿時の痛みや頻尿、目に見える血尿の有無を確認する。女性は月経の時期と重なっていないか確認する</v>
       </c>
       <c r="H72" t="str">
-        <v>SGLT2阻害薬(薬理作用による陽性であれば想定内であることを説明)</v>
+        <v>ワルファリン、DOAC、抗血小板薬など出血傾向を強める薬剤の服用状況を確認</v>
       </c>
       <c r="I72" t="str">
         <v/>
@@ -3796,13 +3796,13 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>SGLT2阻害薬服用中は尿糖陽性が治療効果として想定内であることを患者に伝える。血糖値・HbA1cと合わせて評価する</v>
+        <v>陽性でも尿沈渣で赤血球が確認されない場合は偽陽性（ミオグロビン尿など）のこともある。持続する場合は泌尿器科的な精査が必要</v>
       </c>
       <c r="M72" t="str">
-        <v>糖尿病</v>
+        <v>腎機能</v>
       </c>
       <c r="N72" t="str">
-        <v>尿糖,糖半定量,U-Glu,腎性糖尿,SGLT2</v>
+        <v>尿潜血,潜血反応,U-OB,血尿,尿路結石,膀胱炎</v>
       </c>
       <c r="O72" t="str">
         <v/>
@@ -3810,28 +3810,28 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>尿中微量アルブミン</v>
+        <v>尿糖（半定量）</v>
       </c>
       <c r="B73" t="str">
-        <v>U-Alb,MAU</v>
+        <v>尿糖,U-Glu</v>
       </c>
       <c r="C73" t="str">
-        <v>30 mg/gCr未満（尿中アルブミン/クレアチニン比）</v>
+        <v>陰性（－）</v>
       </c>
       <c r="D73" t="str">
-        <v>通常の尿蛋白検査では見つからない、ごく早期の腎症のサイン</v>
+        <v>尿に糖が漏れ出ていないかを見る検査。血糖値がかなり高いと陽性になる</v>
       </c>
       <c r="E73" t="str">
-        <v>この検査は、通常の尿検査ではまだ分からないくらい早い段階の腎臓の変化を見つけるためのものです。数値が高いと、腎症の初期のサインである可能性があります。</v>
+        <v>通常、糖は尿にはほとんど出ませんが、血糖値がかなり高くなると尿にあふれ出るようになります。血糖コントロールの目安の一つです。</v>
       </c>
       <c r="F73" t="str">
-        <v>糖尿病性腎症の早期段階、高血圧</v>
+        <v>糖尿病（血糖値が腎臓で再吸収できる量を超えている状態）、腎性糖尿（血糖値が正常でも体質的に出ることがある）、SGLT2阻害薬服用中（薬の作用で意図的に糖を排泄するため陽性になるのが正常）</v>
       </c>
       <c r="G73" t="str">
-        <v>血糖・血圧のコントロール状況を確認する。減塩や適正体重の維持など生活習慣の見直しも早期腎症の進行予防に役立つことを伝える</v>
+        <v>SGLT2阻害薬（フォシーガ、ジャディアンスなど）服用中は、陽性が薬の効果によるものであることを説明する。脱水や尿路感染の症状がないかも確認する</v>
       </c>
       <c r="H73" t="str">
-        <v>NSAIDsなど腎機能を悪化させる薬剤。ACE阻害薬・ARB・SGLT2阻害薬は低下させる方向に働く</v>
+        <v>SGLT2阻害薬(薬理作用による陽性であれば想定内であることを説明)</v>
       </c>
       <c r="I73" t="str">
         <v/>
@@ -3843,13 +3843,13 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>糖尿病腎症の早期発見に重要な検査。血糖・血圧コントロールで改善しうる段階なので、早期介入の意義を伝える</v>
+        <v>SGLT2阻害薬服用中は尿糖陽性が治療効果として想定内であることを患者に伝える。血糖値・HbA1cと合わせて評価する</v>
       </c>
       <c r="M73" t="str">
-        <v>糖尿病,腎機能</v>
+        <v>糖尿病</v>
       </c>
       <c r="N73" t="str">
-        <v>微量アルブミン,U-Alb,MAU,糖尿病性腎症,早期腎症</v>
+        <v>尿糖,糖半定量,U-Glu,腎性糖尿,SGLT2</v>
       </c>
       <c r="O73" t="str">
         <v/>
@@ -3857,28 +3857,28 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>C反応性蛋白（CRP）</v>
+        <v>尿中微量アルブミン</v>
       </c>
       <c r="B74" t="str">
-        <v>CRP</v>
+        <v>U-Alb,MAU</v>
       </c>
       <c r="C74" t="str">
-        <v>0.3 mg/dL未満（施設差あり）</v>
+        <v>30 mg/gCr未満（尿中アルブミン/クレアチニン比）</v>
       </c>
       <c r="D74" t="str">
-        <v>体のどこかに炎症や感染が起きていないかを鋭敏に反映する数値</v>
+        <v>通常の尿蛋白検査では見つからない、ごく早期の腎症のサイン</v>
       </c>
       <c r="E74" t="str">
-        <v>CRPは、体に炎症や感染が起きると数時間〜半日程度で急激に上昇する数値です。風邪のようなウイルス感染から細菌感染、体のどこかの炎症まで、幅広く反応するため、体調の変化を早期に捉える手がかりになります。</v>
+        <v>この検査は、通常の尿検査ではまだ分からないくらい早い段階の腎臓の変化を見つけるためのものです。数値が高いと、腎症の初期のサインである可能性があります。</v>
       </c>
       <c r="F74" t="str">
-        <v>細菌感染症、ウイルス感染症、自己免疫疾患（関節リウマチなど）、悪性腫瘍、組織の損傷（術後・心筋梗塞など）</v>
+        <v>糖尿病性腎症の早期段階、高血圧</v>
       </c>
       <c r="G74" t="str">
-        <v>発熱、痛み、腫れなど炎症症状の有無を確認する</v>
+        <v>血糖・血圧のコントロール状況を確認する。減塩や適正体重の維持など生活習慣の見直しも早期腎症の進行予防に役立つことを伝える</v>
       </c>
       <c r="H74" t="str">
-        <v/>
+        <v>NSAIDsなど腎機能を悪化させる薬剤。ACE阻害薬・ARB・SGLT2阻害薬は低下させる方向に働く</v>
       </c>
       <c r="I74" t="str">
         <v/>
@@ -3890,13 +3890,13 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>白血球数と合わせて感染・炎症の程度を評価する。上昇・低下のタイミングは白血球より半日〜1日程度遅れる傾向があるため、経過を追う際は採血のタイミングに注意</v>
+        <v>糖尿病腎症の早期発見に重要な検査。血糖・血圧コントロールで改善しうる段階なので、早期介入の意義を伝える</v>
       </c>
       <c r="M74" t="str">
-        <v/>
+        <v>糖尿病,腎機能</v>
       </c>
       <c r="N74" t="str">
-        <v>CRP,炎症,感染</v>
+        <v>微量アルブミン,U-Alb,MAU,糖尿病性腎症,早期腎症</v>
       </c>
       <c r="O74" t="str">
         <v/>
@@ -3904,125 +3904,125 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>PT-INR（プロトロンビン時間国際標準比）</v>
+        <v>C反応性蛋白（CRP）</v>
       </c>
       <c r="B75" t="str">
-        <v>PT-INR,INR</v>
+        <v>CRP</v>
       </c>
       <c r="C75" t="str">
-        <v>治療域の目安 1.6〜3.0（ワルファリン服用時。年齢・疾患により異なる）</v>
+        <v>0.3 mg/dL未満（施設差あり）</v>
       </c>
       <c r="D75" t="str">
-        <v>血液の固まりやすさを表す数値で、ワルファリンの効き具合を確認するために使う</v>
+        <v>体のどこかに炎症や感染が起きていないかを鋭敏に反映する数値</v>
       </c>
       <c r="E75" t="str">
-        <v>PT-INRは血液が固まるまでの時間をもとにした数値で、ワルファリンというお薬を飲んでいる方の効き具合を確認するために測ります。数値が高いほど血液が固まりにくく出血しやすい状態、低いほど血栓ができやすい状態を示します。</v>
+        <v>CRPは、体に炎症や感染が起きると数時間〜半日程度で急激に上昇する数値です。風邪のようなウイルス感染から細菌感染、体のどこかの炎症まで、幅広く反応するため、体調の変化を早期に捉える手がかりになります。</v>
       </c>
       <c r="F75" t="str">
-        <v>ワルファリンの効きすぎ、肝機能低下、ビタミンK不足、納豆・青汁など摂取量の変化</v>
+        <v>細菌感染症、ウイルス感染症、自己免疫疾患（関節リウマチなど）、悪性腫瘍、組織の損傷（術後・心筋梗塞など）</v>
       </c>
       <c r="G75" t="str">
-        <v>歯ぐきや鼻からの出血、あざ、黒い便などの出血症状がないか確認する。納豆・クロレラ・青汁などビタミンKを多く含む食品の摂取状況を確認する</v>
+        <v>発熱、痛み、腫れなど炎症症状の有無を確認する</v>
       </c>
       <c r="H75" t="str">
-        <v>ワルファリンの過量。ワルファリン服用中はST合剤・マクロライド系・フルコナゾール等の相互作用やビタミンK摂取量の変化にも注意</v>
+        <v/>
       </c>
       <c r="I75" t="str">
-        <v>ワルファリンの効き不足、飲み忘れ、ビタミンK摂取量の急激な増加</v>
+        <v/>
       </c>
       <c r="J75" t="str">
-        <v>服薬状況（飲み忘れ）を確認する。片側のむくみ・しびれ・胸痛など血栓症状がないか確認する</v>
+        <v/>
       </c>
       <c r="K75" t="str">
-        <v>ワルファリン服用中で低値の場合は効果不十分の可能性。ビタミンK摂取量の変化や、リファンピシン・カルバマゼピン・バルビツール酸系など代謝を促進する薬との併用を確認</v>
+        <v/>
       </c>
       <c r="L75" t="str">
-        <v>治療域は疾患・年齢によって異なる（例：非弁膜症性心房細動の高齢者では1.6〜2.6が目安になることが多い）。多くの薬剤・食品と相互作用があるため新規薬剤追加時は必ず確認する。DOAC（エリキュース、リクシアナ、プラザキサなど）ではPT-INRのモニタリングは不要</v>
+        <v>白血球数と合わせて感染・炎症の程度を評価する。上昇・低下のタイミングは白血球より半日〜1日程度遅れる傾向があるため、経過を追う際は採血のタイミングに注意</v>
       </c>
       <c r="M75" t="str">
-        <v>抗凝固療法（心房細動・血栓症）</v>
+        <v/>
       </c>
       <c r="N75" t="str">
-        <v>PT-INR,INR,プロトロンビン時間,ワルファリン,ワーファリン,抗凝固</v>
+        <v>CRP,炎症,感染</v>
       </c>
       <c r="O75" t="str">
-        <v>食事と栄養 p.221（心疾患Q93 ワルファリン服用中のビタミンK摂取）</v>
+        <v/>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>骨型酒石酸抵抗性フォスファターゼ（TRACP-5b）</v>
+        <v>PT-INR（プロトロンビン時間国際標準比）</v>
       </c>
       <c r="B76" t="str">
-        <v>TRACP-5b</v>
+        <v>PT-INR,INR</v>
       </c>
       <c r="C76" t="str">
-        <v>120〜420 mU/dL</v>
+        <v>治療域の目安 1.6〜3.0（ワルファリン服用時。年齢・疾患により異なる）</v>
       </c>
       <c r="D76" t="str">
-        <v>骨がどれくらい壊されているかを見る検査。骨は「古い骨を壊して新しい骨を作る」入れ替えを繰り返しており、骨を壊す細胞が活発だとこの物質が血液中に増える。</v>
+        <v>血液の固まりやすさを表す数値で、ワルファリンの効き具合を確認するために使う</v>
       </c>
       <c r="E76" t="str">
-        <v>この検査は、骨がどれくらい早く減っていないかを見るものです。数値が高いと、骨が弱くなりやすい状態の目安になります。</v>
+        <v>PT-INRは血液が固まるまでの時間をもとにした数値で、ワルファリンというお薬を飲んでいる方の効き具合を確認するために測ります。数値が高いほど血液が固まりにくく出血しやすい状態、低いほど血栓ができやすい状態を示します。</v>
       </c>
       <c r="F76" t="str">
-        <v>骨粗鬆症、骨代謝回転（骨がこわれるスピード）が活発な状態</v>
+        <v>ワルファリンの効きすぎ、肝機能低下、ビタミンK不足、納豆・青汁など摂取量の変化</v>
       </c>
       <c r="G76" t="str">
-        <v>カルシウム・ビタミンDの摂取や、適度な荷重運動（ウォーキングなど）を意識するよう伝える</v>
+        <v>歯ぐきや鼻からの出血、あざ、黒い便などの出血症状がないか確認する。納豆・クロレラ・青汁などビタミンKを多く含む食品の摂取状況を確認する</v>
       </c>
       <c r="H76" t="str">
-        <v/>
+        <v>ワルファリンの過量。ワルファリン服用中はST合剤・マクロライド系・フルコナゾール等の相互作用やビタミンK摂取量の変化にも注意</v>
       </c>
       <c r="I76" t="str">
-        <v/>
+        <v>ワルファリンの効き不足、飲み忘れ、ビタミンK摂取量の急激な増加</v>
       </c>
       <c r="J76" t="str">
-        <v/>
+        <v>服薬状況（飲み忘れ）を確認する。片側のむくみ・しびれ・胸痛など血栓症状がないか確認する</v>
       </c>
       <c r="K76" t="str">
-        <v/>
+        <v>ワルファリン服用中で低値の場合は効果不十分の可能性。ビタミンK摂取量の変化や、リファンピシン・カルバマゼピン・バルビツール酸系など代謝を促進する薬との併用を確認</v>
       </c>
       <c r="L76" t="str">
-        <v>「骨を壊す側」の指標。「骨を作る側」の検査と合わせて評価する。数値だけで診断はしない</v>
+        <v>治療域は疾患・年齢によって異なる（例：非弁膜症性心房細動の高齢者では1.6〜2.6が目安になることが多い）。多くの薬剤・食品と相互作用があるため新規薬剤追加時は必ず確認する。DOAC（エリキュース、リクシアナ、プラザキサなど）ではPT-INRのモニタリングは不要</v>
       </c>
       <c r="M76" t="str">
-        <v>骨粗鬆症</v>
+        <v>抗凝固療法（心房細動・血栓症）</v>
       </c>
       <c r="N76" t="str">
-        <v>TRACP-5b,骨型酒石酸抵抗性フォスファターゼ,骨粗鬆症,骨代謝</v>
+        <v>PT-INR,INR,プロトロンビン時間,ワルファリン,ワーファリン,抗凝固</v>
       </c>
       <c r="O76" t="str">
-        <v/>
+        <v>食事と栄養 p.221（心疾患Q93 ワルファリン服用中のビタミンK摂取）</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>骨型アルカリフォスファターゼ</v>
+        <v>骨型酒石酸抵抗性フォスファターゼ（TRACP-5b）</v>
       </c>
       <c r="B77" t="str">
-        <v>BAP</v>
+        <v>TRACP-5b</v>
       </c>
       <c r="C77" t="str">
-        <v>男性 3.7〜20.9 μg/L、女性（閉経前）2.9〜14.5 μg/L（施設差あり）</v>
+        <v>120〜420 mU/dL</v>
       </c>
       <c r="D77" t="str">
-        <v>ALPのうち骨に由来する成分だけを測定し、骨が作られる勢い（骨形成）を反映する</v>
+        <v>骨がどれくらい壊されているかを見る検査。骨は「古い骨を壊して新しい骨を作る」入れ替えを繰り返しており、骨を壊す細胞が活発だとこの物質が血液中に増える。</v>
       </c>
       <c r="E77" t="str">
-        <v>骨型ALPは、通常のALP（アルカリフォスファターゼ）の中でも、骨で作られる成分だけを選んで測定するものです。骨を新しく作る働きがどれくらい活発かを見る指標として、骨粗鬆症の治療効果判定などに使われます。</v>
+        <v>この検査は、骨がどれくらい早く減っていないかを見るものです。数値が高いと、骨が弱くなりやすい状態の目安になります。</v>
       </c>
       <c r="F77" t="str">
-        <v>骨代謝回転の亢進（骨粗鬆症、骨折治癒過程、骨形成促進薬による治療効果、Paget病、骨転移）</v>
+        <v>骨粗鬆症、骨代謝回転（骨がこわれるスピード）が活発な状態</v>
       </c>
       <c r="G77" t="str">
-        <v/>
+        <v>カルシウム・ビタミンDの摂取や、適度な荷重運動（ウォーキングなど）を意識するよう伝える</v>
       </c>
       <c r="H77" t="str">
         <v/>
       </c>
       <c r="I77" t="str">
-        <v>骨形成の低下</v>
+        <v/>
       </c>
       <c r="J77" t="str">
         <v/>
@@ -4031,13 +4031,13 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>通常のALPと異なり肝臓の影響を受けにくいため、肝機能異常がある患者でも骨代謝を評価しやすい。P1NPと同じ「骨を作る側」の指標で、骨形成促進薬（テリパラチド等）の効果判定に使われる</v>
+        <v>「骨を壊す側」の指標。「骨を作る側」の検査と合わせて評価する。数値だけで診断はしない</v>
       </c>
       <c r="M77" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="N77" t="str">
-        <v>骨型ALP,BAP,骨型アルカリフォスファターゼ,骨形成マーカー</v>
+        <v>TRACP-5b,骨型酒石酸抵抗性フォスファターゼ,骨粗鬆症,骨代謝</v>
       </c>
       <c r="O77" t="str">
         <v/>
@@ -4045,125 +4045,125 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>25-ヒドロキシビタミンD</v>
+        <v>骨型アルカリフォスファターゼ</v>
       </c>
       <c r="B78" t="str">
-        <v>25(OH)D</v>
+        <v>BAP</v>
       </c>
       <c r="C78" t="str">
-        <v>30 ng/mL以上：充足、20〜30 ng/mL：不足、20 ng/mL未満：欠乏（施設差あり）</v>
+        <v>男性 3.7〜20.9 μg/L、女性（閉経前）2.9〜14.5 μg/L（施設差あり）</v>
       </c>
       <c r="D78" t="str">
-        <v>体内のビタミンDの蓄え具合を反映する指標。カルシウムの吸収や骨の健康に関わる</v>
+        <v>ALPのうち骨に由来する成分だけを測定し、骨が作られる勢い（骨形成）を反映する</v>
       </c>
       <c r="E78" t="str">
-        <v>この検査は、体の中にビタミンDがどれくらい蓄えられているかを見るものです。ビタミンDは、食事から摂ったカルシウムを腸で吸収するのを助ける働きがあり、不足すると骨がもろくなりやすくなります。</v>
+        <v>骨型ALPは、通常のALP（アルカリフォスファターゼ）の中でも、骨で作られる成分だけを選んで測定するものです。骨を新しく作る働きがどれくらい活発かを見る指標として、骨粗鬆症の治療効果判定などに使われます。</v>
       </c>
       <c r="F78" t="str">
-        <v>ビタミンD製剤の過剰摂取</v>
+        <v>骨代謝回転の亢進（骨粗鬆症、骨折治癒過程、骨形成促進薬による治療効果、Paget病、骨転移）</v>
       </c>
       <c r="G78" t="str">
-        <v>活性型ビタミンD3製剤やサプリメントの摂取量を確認する。高カルシウム血症の症状（吐き気、便秘、多尿など）がないか確認する</v>
+        <v/>
       </c>
       <c r="H78" t="str">
-        <v>活性型/天然型ビタミンD製剤の過量投与</v>
+        <v/>
       </c>
       <c r="I78" t="str">
-        <v>日光暴露不足、食事摂取不足、高齢、腸疾患による吸収不良、肝・腎機能低下（活性化障害）</v>
+        <v>骨形成の低下</v>
       </c>
       <c r="J78" t="str">
-        <v>適度な日光浴、魚類・きのこ類などビタミンDを多く含む食品の摂取を意識するとよいことを伝える</v>
+        <v/>
       </c>
       <c r="K78" t="str">
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>骨粗鬆症治療における活性型ビタミンD3製剤の効果判定や、投与量調整の参考に用いられる。腎機能低下患者では活性化障害により25(OH)Dが正常でも活性型が不足することがある点に注意</v>
+        <v>通常のALPと異なり肝臓の影響を受けにくいため、肝機能異常がある患者でも骨代謝を評価しやすい。P1NPと同じ「骨を作る側」の指標で、骨形成促進薬（テリパラチド等）の効果判定に使われる</v>
       </c>
       <c r="M78" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="N78" t="str">
-        <v>25(OH)D,ビタミンD,25-ヒドロキシビタミンD,ビタミンD欠乏,骨粗鬆症</v>
+        <v>骨型ALP,BAP,骨型アルカリフォスファターゼ,骨形成マーカー</v>
       </c>
       <c r="O78" t="str">
-        <v>食事と栄養 p.38（ビタミンD）</v>
+        <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>ucOC（低カルボキシル化オステオカルシン）</v>
+        <v>25-ヒドロキシビタミンD</v>
       </c>
       <c r="B79" t="str">
-        <v>ucOC</v>
+        <v>25(OH)D</v>
       </c>
       <c r="C79" t="str">
-        <v>4.5 ng/mL未満（施設差あり）</v>
+        <v>30 ng/mL以上：充足、20〜30 ng/mL：不足、20 ng/mL未満：欠乏（施設差あり）</v>
       </c>
       <c r="D79" t="str">
-        <v>ビタミンKが不足していないかを反映する骨の指標</v>
+        <v>体内のビタミンDの蓄え具合を反映する指標。カルシウムの吸収や骨の健康に関わる</v>
       </c>
       <c r="E79" t="str">
-        <v>ucOCは、骨を作るために必要なビタミンKが体の中で足りているかどうかを反映する検査です。数値が高いとビタミンK不足が疑われます。</v>
+        <v>この検査は、体の中にビタミンDがどれくらい蓄えられているかを見るものです。ビタミンDは、食事から摂ったカルシウムを腸で吸収するのを助ける働きがあり、不足すると骨がもろくなりやすくなります。</v>
       </c>
       <c r="F79" t="str">
-        <v>ビタミンK不足状態</v>
+        <v>ビタミンD製剤の過剰摂取</v>
       </c>
       <c r="G79" t="str">
-        <v>ビタミンK2製剤(骨粗鬆症治療薬)の適応が検討されているか確認する。ワルファリン服用中の患者では、納豆などビタミンKを多く含む食品の急な摂取量の変化を避けるよう説明する</v>
+        <v>活性型ビタミンD3製剤やサプリメントの摂取量を確認する。高カルシウム血症の症状（吐き気、便秘、多尿など）がないか確認する</v>
       </c>
       <c r="H79" t="str">
-        <v/>
+        <v>活性型/天然型ビタミンD製剤の過量投与</v>
       </c>
       <c r="I79" t="str">
-        <v/>
+        <v>日光暴露不足、食事摂取不足、高齢、腸疾患による吸収不良、肝・腎機能低下（活性化障害）</v>
       </c>
       <c r="J79" t="str">
-        <v/>
+        <v>適度な日光浴、魚類・きのこ類などビタミンDを多く含む食品の摂取を意識するとよいことを伝える</v>
       </c>
       <c r="K79" t="str">
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>ビタミンK2製剤（骨粗鬆症治療薬）の適応判断や効果判定に使われる</v>
+        <v>骨粗鬆症治療における活性型ビタミンD3製剤の効果判定や、投与量調整の参考に用いられる。腎機能低下患者では活性化障害により25(OH)Dが正常でも活性型が不足することがある点に注意</v>
       </c>
       <c r="M79" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="N79" t="str">
-        <v>ucOC,オステオカルシン,ビタミンK</v>
+        <v>25(OH)D,ビタミンD,25-ヒドロキシビタミンD,ビタミンD欠乏,骨粗鬆症</v>
       </c>
       <c r="O79" t="str">
-        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
+        <v>食事と栄養 p.38（ビタミンD）</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>PTH（副甲状腺ホルモン）</v>
+        <v>ucOC（低カルボキシル化オステオカルシン）</v>
       </c>
       <c r="B80" t="str">
-        <v>PTH</v>
+        <v>ucOC</v>
       </c>
       <c r="C80" t="str">
-        <v>10〜65 pg/mL（施設差あり）</v>
+        <v>4.5 ng/mL未満（施設差あり）</v>
       </c>
       <c r="D80" t="str">
-        <v>血液中のカルシウム濃度を調節するホルモン</v>
+        <v>ビタミンKが不足していないかを反映する骨の指標</v>
       </c>
       <c r="E80" t="str">
-        <v>PTHは、血液中のカルシウム濃度を一定に保つために働くホルモンです。カルシウムが低くなると分泌が増え、骨からカルシウムを取り出したり、腎臓での再吸収を促したりして数値を戻そうとします。</v>
+        <v>ucOCは、骨を作るために必要なビタミンKが体の中で足りているかどうかを反映する検査です。数値が高いとビタミンK不足が疑われます。</v>
       </c>
       <c r="F80" t="str">
-        <v>原発性・二次性副甲状腺機能亢進症（腎不全に伴うものなど）</v>
+        <v>ビタミンK不足状態</v>
       </c>
       <c r="G80" t="str">
-        <v/>
+        <v>ビタミンK2製剤(骨粗鬆症治療薬)の適応が検討されているか確認する。ワルファリン服用中の患者では、納豆などビタミンKを多く含む食品の急な摂取量の変化を避けるよう説明する</v>
       </c>
       <c r="H80" t="str">
         <v/>
       </c>
       <c r="I80" t="str">
-        <v>副甲状腺機能低下症</v>
+        <v/>
       </c>
       <c r="J80" t="str">
         <v/>
@@ -4172,13 +4172,13 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>骨粗鬆症の二次性原因（副甲状腺機能亢進症）を除外するための検査。カルシウム・リンと合わせて評価する</v>
+        <v>ビタミンK2製剤（骨粗鬆症治療薬）の適応判断や効果判定に使われる</v>
       </c>
       <c r="M80" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="N80" t="str">
-        <v>PTH,副甲状腺ホルモン,パラトルモン</v>
+        <v>ucOC,オステオカルシン,ビタミンK</v>
       </c>
       <c r="O80" t="str">
         <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
@@ -4186,22 +4186,22 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>尿中NTX</v>
+        <v>PTH（副甲状腺ホルモン）</v>
       </c>
       <c r="B81" t="str">
-        <v>NTX</v>
+        <v>PTH</v>
       </c>
       <c r="C81" t="str">
-        <v>施設差が大きく一律の記載が難しい（尿中）</v>
+        <v>10〜65 pg/mL（施設差あり）</v>
       </c>
       <c r="D81" t="str">
-        <v>骨が壊されるときに出る、骨吸収マーカーのひとつ</v>
+        <v>血液中のカルシウム濃度を調節するホルモン</v>
       </c>
       <c r="E81" t="str">
-        <v>NTXは、骨が壊される（吸収される）ときに尿の中に出てくる物質です。骨粗鬆症の治療薬がどれくらい効いているかを確認するために使われます。</v>
+        <v>PTHは、血液中のカルシウム濃度を一定に保つために働くホルモンです。カルシウムが低くなると分泌が増え、骨からカルシウムを取り出したり、腎臓での再吸収を促したりして数値を戻そうとします。</v>
       </c>
       <c r="F81" t="str">
-        <v>骨代謝回転の亢進（骨粗鬆症、閉経後など）</v>
+        <v>原発性・二次性副甲状腺機能亢進症（腎不全に伴うものなど）</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -4210,7 +4210,7 @@
         <v/>
       </c>
       <c r="I81" t="str">
-        <v>骨吸収抑制薬（ビスホスホネート等）による治療効果</v>
+        <v>副甲状腺機能低下症</v>
       </c>
       <c r="J81" t="str">
         <v/>
@@ -4219,13 +4219,13 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>治療開始後3〜6か月で再検し、薬の効果判定に使われる。TRACP-5bと同じ「骨を壊す側」の指標</v>
+        <v>骨粗鬆症の二次性原因（副甲状腺機能亢進症）を除外するための検査。カルシウム・リンと合わせて評価する</v>
       </c>
       <c r="M81" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="N81" t="str">
-        <v>NTX,尿中NTX,骨吸収マーカー</v>
+        <v>PTH,副甲状腺ホルモン,パラトルモン</v>
       </c>
       <c r="O81" t="str">
         <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
@@ -4233,22 +4233,22 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>カルシトニン</v>
+        <v>尿中NTX</v>
       </c>
       <c r="B82" t="str">
-        <v>CT</v>
+        <v>NTX</v>
       </c>
       <c r="C82" t="str">
-        <v>男性 9.52 pg/mL未満、女性 6.40 pg/mL未満（施設差あり）</v>
+        <v>施設差が大きく一律の記載が難しい（尿中）</v>
       </c>
       <c r="D82" t="str">
-        <v>血液中のカルシウムを下げる方向に働くホルモン</v>
+        <v>骨が壊されるときに出る、骨吸収マーカーのひとつ</v>
       </c>
       <c r="E82" t="str">
-        <v>カルシトニンは、PTHとは逆に血液中のカルシウムを下げる方向に働くホルモンです。特定の甲状腺の病気（甲状腺髄様癌）がないかを調べる際にも使われます。</v>
+        <v>NTXは、骨が壊される（吸収される）ときに尿の中に出てくる物質です。骨粗鬆症の治療薬がどれくらい効いているかを確認するために使われます。</v>
       </c>
       <c r="F82" t="str">
-        <v>甲状腺髄様癌、腎不全</v>
+        <v>骨代謝回転の亢進（骨粗鬆症、閉経後など）</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -4257,7 +4257,7 @@
         <v/>
       </c>
       <c r="I82" t="str">
-        <v/>
+        <v>骨吸収抑制薬（ビスホスホネート等）による治療効果</v>
       </c>
       <c r="J82" t="str">
         <v/>
@@ -4266,13 +4266,13 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>骨粗鬆症の二次性原因の除外目的で測定されることがある検査値。同名の薬剤（カルシトニン製剤）と混同しないよう注意</v>
+        <v>治療開始後3〜6か月で再検し、薬の効果判定に使われる。TRACP-5bと同じ「骨を壊す側」の指標</v>
       </c>
       <c r="M82" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="N82" t="str">
-        <v>カルシトニン,CT</v>
+        <v>NTX,尿中NTX,骨吸収マーカー</v>
       </c>
       <c r="O82" t="str">
         <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
@@ -4280,22 +4280,22 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>DPD（デオキシピリジノリン）</v>
+        <v>カルシトニン</v>
       </c>
       <c r="B83" t="str">
-        <v>DPD</v>
+        <v>CT</v>
       </c>
       <c r="C83" t="str">
-        <v>施設差が大きく一律の記載が難しい（尿中）</v>
+        <v>男性 9.52 pg/mL未満、女性 6.40 pg/mL未満（施設差あり）</v>
       </c>
       <c r="D83" t="str">
-        <v>骨のコラーゲンが壊れるときに出る、骨吸収マーカーのひとつ</v>
+        <v>血液中のカルシウムを下げる方向に働くホルモン</v>
       </c>
       <c r="E83" t="str">
-        <v>DPDも、骨が壊されるときに尿に出てくる物質の一つです。NTXと同じように、骨粗鬆症治療薬の効果を確認するために使われます。</v>
+        <v>カルシトニンは、PTHとは逆に血液中のカルシウムを下げる方向に働くホルモンです。特定の甲状腺の病気（甲状腺髄様癌）がないかを調べる際にも使われます。</v>
       </c>
       <c r="F83" t="str">
-        <v>骨代謝回転の亢進（骨粗鬆症など）</v>
+        <v>甲状腺髄様癌、腎不全</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -4304,7 +4304,7 @@
         <v/>
       </c>
       <c r="I83" t="str">
-        <v>骨吸収抑制薬による治療効果</v>
+        <v/>
       </c>
       <c r="J83" t="str">
         <v/>
@@ -4313,13 +4313,13 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>NTX・CTXと同じ「骨を壊す側」の指標。食事の影響を受けにくいとされる</v>
+        <v>骨粗鬆症の二次性原因の除外目的で測定されることがある検査値。同名の薬剤（カルシトニン製剤）と混同しないよう注意</v>
       </c>
       <c r="M83" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="N83" t="str">
-        <v>DPD,デオキシピリジノリン,骨吸収マーカー</v>
+        <v>カルシトニン,CT</v>
       </c>
       <c r="O83" t="str">
         <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
@@ -4327,19 +4327,19 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>CTX</v>
+        <v>DPD（デオキシピリジノリン）</v>
       </c>
       <c r="B84" t="str">
-        <v>CTX</v>
+        <v>DPD</v>
       </c>
       <c r="C84" t="str">
-        <v>施設差が大きく一律の記載が難しい（血清・尿中）</v>
+        <v>施設差が大きく一律の記載が難しい（尿中）</v>
       </c>
       <c r="D84" t="str">
         <v>骨のコラーゲンが壊れるときに出る、骨吸収マーカーのひとつ</v>
       </c>
       <c r="E84" t="str">
-        <v>CTXも、骨が壊されるときに血液や尿に出てくる物質です。骨粗鬆症治療薬（骨を壊すのを抑える薬）の効果を確認するために使われます。</v>
+        <v>DPDも、骨が壊されるときに尿に出てくる物質の一つです。NTXと同じように、骨粗鬆症治療薬の効果を確認するために使われます。</v>
       </c>
       <c r="F84" t="str">
         <v>骨代謝回転の亢進（骨粗鬆症など）</v>
@@ -4360,13 +4360,13 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>NTX・DPDと同じ「骨を壊す側」の指標。血清・尿中いずれでも測定されることがある</v>
+        <v>NTX・CTXと同じ「骨を壊す側」の指標。食事の影響を受けにくいとされる</v>
       </c>
       <c r="M84" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="N84" t="str">
-        <v>CTX,骨吸収マーカー</v>
+        <v>DPD,デオキシピリジノリン,骨吸収マーカー</v>
       </c>
       <c r="O84" t="str">
         <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
@@ -4374,22 +4374,22 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>P1NP</v>
+        <v>CTX</v>
       </c>
       <c r="B85" t="str">
-        <v>P1NP</v>
+        <v>CTX</v>
       </c>
       <c r="C85" t="str">
-        <v>施設差が大きく一律の記載が難しい（血清）</v>
+        <v>施設差が大きく一律の記載が難しい（血清・尿中）</v>
       </c>
       <c r="D85" t="str">
-        <v>骨が新しく作られるときに出る、骨形成マーカーのひとつ</v>
+        <v>骨のコラーゲンが壊れるときに出る、骨吸収マーカーのひとつ</v>
       </c>
       <c r="E85" t="str">
-        <v>P1NPは、CTXなどとは逆に、骨が新しく作られるときに血液中に出てくる物質です。骨を作る力を高める薬（テリパラチドなど）の効果を確認するために使われます。</v>
+        <v>CTXも、骨が壊されるときに血液や尿に出てくる物質です。骨粗鬆症治療薬（骨を壊すのを抑える薬）の効果を確認するために使われます。</v>
       </c>
       <c r="F85" t="str">
-        <v>骨代謝回転の亢進、骨形成促進薬による治療効果</v>
+        <v>骨代謝回転の亢進（骨粗鬆症など）</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -4398,7 +4398,7 @@
         <v/>
       </c>
       <c r="I85" t="str">
-        <v>骨形成の低下</v>
+        <v>骨吸収抑制薬による治療効果</v>
       </c>
       <c r="J85" t="str">
         <v/>
@@ -4407,13 +4407,13 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>TRACP-5b等「骨を壊す側」の指標とは逆の、「骨を作る側」の指標。骨形成促進薬（テリパラチド等）の効果判定に使われる</v>
+        <v>NTX・DPDと同じ「骨を壊す側」の指標。血清・尿中いずれでも測定されることがある</v>
       </c>
       <c r="M85" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="N85" t="str">
-        <v>P1NP,骨形成マーカー</v>
+        <v>CTX,骨吸収マーカー</v>
       </c>
       <c r="O85" t="str">
         <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
@@ -4421,69 +4421,69 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>血清鉄（Fe）</v>
+        <v>P1NP</v>
       </c>
       <c r="B86" t="str">
-        <v>Fe</v>
+        <v>P1NP</v>
       </c>
       <c r="C86" t="str">
-        <v>60〜200 μg/dL（施設差あり）</v>
+        <v>施設差が大きく一律の記載が難しい（血清）</v>
       </c>
       <c r="D86" t="str">
-        <v>血液中を流れている鉄の量</v>
+        <v>骨が新しく作られるときに出る、骨形成マーカーのひとつ</v>
       </c>
       <c r="E86" t="str">
-        <v>この検査は、今血液の中を流れている鉄の量を見るものです。低いと、体の中で鉄が不足している可能性があります。</v>
+        <v>P1NPは、CTXなどとは逆に、骨が新しく作られるときに血液中に出てくる物質です。骨を作る力を高める薬（テリパラチドなど）の効果を確認するために使われます。</v>
       </c>
       <c r="F86" t="str">
-        <v>鉄剤の過剰摂取、溶血、肝疾患</v>
+        <v>骨代謝回転の亢進、骨形成促進薬による治療効果</v>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>鉄剤の過量摂取(小児の誤飲を含む)</v>
+        <v/>
       </c>
       <c r="I86" t="str">
-        <v>鉄欠乏性貧血、慢性炎症、出血</v>
+        <v>骨形成の低下</v>
       </c>
       <c r="J86" t="str">
-        <v>鉄分の多い食品（レバー・赤身肉・魚・ほうれん草など）を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える</v>
+        <v/>
       </c>
       <c r="K86" t="str">
-        <v>プロトンポンプ阻害薬(PPI)・H2ブロッカーは胃酸分泌抑制により鉄の吸収を低下させうる</v>
+        <v/>
       </c>
       <c r="L86" t="str">
-        <v>血清鉄は日内変動が大きい。単独で判断せず総鉄結合能・フェリチンと合わせて評価する</v>
+        <v>TRACP-5b等「骨を壊す側」の指標とは逆の、「骨を作る側」の指標。骨形成促進薬（テリパラチド等）の効果判定に使われる</v>
       </c>
       <c r="M86" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="N86" t="str">
-        <v>血清鉄,Fe,鉄欠乏性貧血</v>
+        <v>P1NP,骨形成マーカー</v>
       </c>
       <c r="O86" t="str">
-        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>総鉄結合能（TIBC）</v>
+        <v>骨密度</v>
       </c>
       <c r="B87" t="str">
-        <v>TIBC</v>
+        <v>BMD,骨密度</v>
       </c>
       <c r="C87" t="str">
-        <v>250〜360 μg/dL（施設差あり）</v>
+        <v>YAM(若年成人平均値)80%以上:正常、70%以上80%未満:骨量減少、70%未満:骨粗鬆症</v>
       </c>
       <c r="D87" t="str">
-        <v>血液中のトランスフェリンが鉄と結合できる総量</v>
+        <v>骨の中にカルシウムなどのミネラルがどれだけ詰まっているかを示す指標。20〜44歳の平均値(YAM)に対する割合(%)で評価する</v>
       </c>
       <c r="E87" t="str">
-        <v>TIBCは、血液中でトランスフェリンという物質が鉄を運べる最大量を表します。体の中の鉄が不足すると、少しでも多く鉄を運ぼうとしてこの数値が上がる性質があります。</v>
+        <v>骨密度は、骨の中にカルシウムなどのミネラルがどれだけしっかり詰まっているかを表す数値です。20〜44歳の若い方の平均値を100%として、ご自身の骨密度が何%かで示されます。70%未満になると「骨粗鬆症」と診断され、骨折しやすい状態と考えられます。</v>
       </c>
       <c r="F87" t="str">
-        <v>鉄欠乏性貧血（＞360 μg/dLが目安）</v>
+        <v>基本的に問題になることは少ない(まれに骨硬化症などの疾患)</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -4492,69 +4492,69 @@
         <v/>
       </c>
       <c r="I87" t="str">
-        <v>慢性炎症、肝疾患、ネフローゼ症候群</v>
+        <v>骨粗鬆症、加齢による骨量減少、閉経後のエストロゲン低下、ステロイド長期使用、カルシウム・ビタミンD不足、運動不足、るいそう</v>
       </c>
       <c r="J87" t="str">
-        <v/>
+        <v>カルシウム・ビタミンD・ビタミンKを意識した食事、荷重運動(ウォーキング等)を勧める。ステロイド長期服用中の場合は骨粗鬆症治療薬の併用が検討されているか確認する</v>
       </c>
       <c r="K87" t="str">
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>鉄が不足すると、体はより多く運ぼうとしてTIBCが上昇する。UIBC・血清鉄と併せて評価する</v>
+        <v>YAM70%未満、または既存の脆弱性骨折がある場合に骨粗鬆症と診断され薬物治療の対象となる(日本骨粗鬆症学会・日本骨代謝学会・厚生労働省合同「原発性骨粗鬆症の診断基準 2012年度改訂版」)。ビスホスホネート製剤は起床時空腹時に十分な水(180mL程度)で服用し、服用後30分は横にならないよう指導する。ステロイドを長期服用中の患者は骨密度によらず骨粗鬆症治療薬の併用が推奨される場合がある(グルココルチコイド誘発性骨粗鬆症: GIOP)</v>
       </c>
       <c r="M87" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="N87" t="str">
-        <v>TIBC,総鉄結合能,鉄欠乏性貧血</v>
+        <v>骨密度,BMD,YAM,若年成人平均値,骨粗鬆症,DXA</v>
       </c>
       <c r="O87" t="str">
-        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
+        <v/>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>不飽和鉄結合能（UIBC）</v>
+        <v>血清鉄（Fe）</v>
       </c>
       <c r="B88" t="str">
-        <v>UIBC</v>
+        <v>Fe</v>
       </c>
       <c r="C88" t="str">
-        <v>170〜300 μg/dL（施設差あり）</v>
+        <v>60〜200 μg/dL（施設差あり）</v>
       </c>
       <c r="D88" t="str">
-        <v>トランスフェリンのうち、まだ鉄と結合していない余力の部分（UIBC＝TIBC－血清鉄）</v>
+        <v>血液中を流れている鉄の量</v>
       </c>
       <c r="E88" t="str">
-        <v>UIBCは、トランスフェリンのうち、まだ鉄と結合していない「空き容量」の部分を表します。鉄が不足しているときほど、この空き容量は大きくなります。</v>
+        <v>この検査は、今血液の中を流れている鉄の量を見るものです。低いと、体の中で鉄が不足している可能性があります。</v>
       </c>
       <c r="F88" t="str">
-        <v>鉄欠乏性貧血（＞300 μg/dLが目安）</v>
+        <v>鉄剤の過剰摂取、溶血、肝疾患</v>
       </c>
       <c r="G88" t="str">
         <v/>
       </c>
       <c r="H88" t="str">
-        <v/>
+        <v>鉄剤の過量摂取(小児の誤飲を含む)</v>
       </c>
       <c r="I88" t="str">
-        <v>慢性炎症、鉄過剰状態</v>
+        <v>鉄欠乏性貧血、慢性炎症、出血</v>
       </c>
       <c r="J88" t="str">
-        <v/>
+        <v>鉄分の多い食品（レバー・赤身肉・魚・ほうれん草など）を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える</v>
       </c>
       <c r="K88" t="str">
-        <v/>
+        <v>プロトンポンプ阻害薬(PPI)・H2ブロッカーは胃酸分泌抑制により鉄の吸収を低下させうる</v>
       </c>
       <c r="L88" t="str">
-        <v>TIBCと同じ方向に動くことが多い。血清鉄・TIBCとあわせて鉄欠乏性貧血と二次性貧血の鑑別に使う</v>
+        <v>血清鉄は日内変動が大きい。単独で判断せず総鉄結合能・フェリチンと合わせて評価する</v>
       </c>
       <c r="M88" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
       <c r="N88" t="str">
-        <v>UIBC,不飽和鉄結合能,鉄欠乏性貧血</v>
+        <v>血清鉄,Fe,鉄欠乏性貧血</v>
       </c>
       <c r="O88" t="str">
         <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
@@ -4562,22 +4562,22 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>トランスフェリン飽和度</v>
+        <v>総鉄結合能（TIBC）</v>
       </c>
       <c r="B89" t="str">
-        <v>TSAT</v>
+        <v>TIBC</v>
       </c>
       <c r="C89" t="str">
-        <v>16〜50%程度（施設差あり）</v>
+        <v>250〜360 μg/dL（施設差あり）</v>
       </c>
       <c r="D89" t="str">
-        <v>鉄を運ぶ役割のトランスフェリンのうち、実際に鉄を運んでいる割合（血清鉄÷総鉄結合能）</v>
+        <v>血液中のトランスフェリンが鉄と結合できる総量</v>
       </c>
       <c r="E89" t="str">
-        <v>トランスフェリン飽和度は、鉄を運ぶトランスフェリンのうち、実際にどれくらいが鉄を運んでいるかを割合で表したものです。鉄欠乏性貧血では低くなり、鉄が過剰にたまる病気では高くなります。</v>
+        <v>TIBCは、血液中でトランスフェリンという物質が鉄を運べる最大量を表します。体の中の鉄が不足すると、少しでも多く鉄を運ぼうとしてこの数値が上がる性質があります。</v>
       </c>
       <c r="F89" t="str">
-        <v>鉄過剰症（ヘモクロマトーシスなど）</v>
+        <v>鉄欠乏性貧血（＞360 μg/dLが目安）</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -4586,7 +4586,7 @@
         <v/>
       </c>
       <c r="I89" t="str">
-        <v>鉄欠乏性貧血（＜16%が目安）</v>
+        <v>慢性炎症、肝疾患、ネフローゼ症候群</v>
       </c>
       <c r="J89" t="str">
         <v/>
@@ -4595,13 +4595,13 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>血清鉄をTIBCで割って計算される。鉄剤補充の効果判定にも使われる</v>
+        <v>鉄が不足すると、体はより多く運ぼうとしてTIBCが上昇する。UIBC・血清鉄と併せて評価する</v>
       </c>
       <c r="M89" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
       <c r="N89" t="str">
-        <v>トランスフェリン飽和度,TSAT,鉄欠乏性貧血</v>
+        <v>TIBC,総鉄結合能,鉄欠乏性貧血</v>
       </c>
       <c r="O89" t="str">
         <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
@@ -4609,22 +4609,22 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>血清フェリチン</v>
+        <v>不飽和鉄結合能（UIBC）</v>
       </c>
       <c r="B90" t="str">
-        <v>Ferritin</v>
+        <v>UIBC</v>
       </c>
       <c r="C90" t="str">
-        <v>男性 20〜250 ng/mL、女性 10〜120 ng/mL（施設差あり）</v>
+        <v>170〜300 μg/dL（施設差あり）</v>
       </c>
       <c r="D90" t="str">
-        <v>体に貯蔵されている鉄の量を反映する指標。貧血の症状が出るより早い段階で低下する</v>
+        <v>トランスフェリンのうち、まだ鉄と結合していない余力の部分（UIBC＝TIBC－血清鉄）</v>
       </c>
       <c r="E90" t="str">
-        <v>フェリチンは、体に蓄えられている鉄の「貯金」の量を見る検査です。この数値が下がるのは、貧血の症状が出るよりも前の、とても早い段階のサインになります。</v>
+        <v>UIBCは、トランスフェリンのうち、まだ鉄と結合していない「空き容量」の部分を表します。鉄が不足しているときほど、この空き容量は大きくなります。</v>
       </c>
       <c r="F90" t="str">
-        <v>炎症性疾患、肝疾患、悪性腫瘍、鉄過剰症（フェリチンは炎症でも上昇するため、貧血の評価では注意が必要）</v>
+        <v>鉄欠乏性貧血（＞300 μg/dLが目安）</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -4633,22 +4633,22 @@
         <v/>
       </c>
       <c r="I90" t="str">
-        <v>鉄欠乏状態（貧血の症状が出る前の早期段階から低下する）</v>
+        <v>慢性炎症、鉄過剰状態</v>
       </c>
       <c r="J90" t="str">
-        <v>鉄分の多い食品を意識するとともに、貯蔵鉄を補うため治療は数値が正常化してからも継続が必要なことを伝える</v>
+        <v/>
       </c>
       <c r="K90" t="str">
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>貯蔵鉄の指標で鉄欠乏を最も早期に反映する。ただし炎症があると鉄欠乏があっても正常〜高値に出ることがあり、CRP等の炎症所見と合わせて評価する。二次性貧血との鑑別に重要</v>
+        <v>TIBCと同じ方向に動くことが多い。血清鉄・TIBCとあわせて鉄欠乏性貧血と二次性貧血の鑑別に使う</v>
       </c>
       <c r="M90" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
       <c r="N90" t="str">
-        <v>フェリチン,Ferritin,貯蔵鉄,鉄欠乏</v>
+        <v>UIBC,不飽和鉄結合能,鉄欠乏性貧血</v>
       </c>
       <c r="O90" t="str">
         <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
@@ -4656,22 +4656,22 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>尿中尿酸/クレアチニン比（UUA/UCr）</v>
+        <v>トランスフェリン飽和度</v>
       </c>
       <c r="B91" t="str">
-        <v>UUA/UCr</v>
+        <v>TSAT</v>
       </c>
       <c r="C91" t="str">
-        <v>0.4〜0.8程度が混合型の目安</v>
+        <v>16〜50%程度（施設差あり）</v>
       </c>
       <c r="D91" t="str">
-        <v>尿酸が「作られすぎ」か「排泄できていない」かを見分ける比の値</v>
+        <v>鉄を運ぶ役割のトランスフェリンのうち、実際に鉄を運んでいる割合（血清鉄÷総鉄結合能）</v>
       </c>
       <c r="E91" t="str">
-        <v>この数値は、体の中で尿酸が「作られすぎている」のか、それとも「うまく排泄できていない」のかを見分けるために使う比の値です。高尿酸血症の治療薬を選ぶときの参考になります。</v>
+        <v>トランスフェリン飽和度は、鉄を運ぶトランスフェリンのうち、実際にどれくらいが鉄を運んでいるかを割合で表したものです。鉄欠乏性貧血では低くなり、鉄が過剰にたまる病気では高くなります。</v>
       </c>
       <c r="F91" t="str">
-        <v>尿酸産生過剰型（0.8以上が目安）</v>
+        <v>鉄過剰症（ヘモクロマトーシスなど）</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -4680,7 +4680,7 @@
         <v/>
       </c>
       <c r="I91" t="str">
-        <v>尿酸排泄低下型（0.4以下が目安）</v>
+        <v>鉄欠乏性貧血（＜16%が目安）</v>
       </c>
       <c r="J91" t="str">
         <v/>
@@ -4689,36 +4689,36 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>高尿酸血症は尿酸産生過剰型・排泄低下型・混合型に分類され、この比が目安になる。病型によって使う薬剤（尿酸生成抑制薬か尿酸排泄促進薬か）の選択が変わる</v>
+        <v>血清鉄をTIBCで割って計算される。鉄剤補充の効果判定にも使われる</v>
       </c>
       <c r="M91" t="str">
-        <v>高尿酸血症</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="N91" t="str">
-        <v>UUA,UCr,尿酸クリアランス,CUA,EUA,尿酸産生過剰型,尿酸排泄低下型</v>
+        <v>トランスフェリン飽和度,TSAT,鉄欠乏性貧血</v>
       </c>
       <c r="O91" t="str">
-        <v>食事と栄養 p.180-189（第2部 痛風・高尿酸血症）</v>
+        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>抗甲状腺マイクロゾーム抗体（抗TPO抗体）</v>
+        <v>血清フェリチン</v>
       </c>
       <c r="B92" t="str">
-        <v>TPOAb</v>
+        <v>Ferritin</v>
       </c>
       <c r="C92" t="str">
-        <v>陰性（16 IU/mL未満程度、施設差あり）</v>
+        <v>男性 20〜250 ng/mL、女性 10〜120 ng/mL（施設差あり）</v>
       </c>
       <c r="D92" t="str">
-        <v>自分の甲状腺を攻撃する抗体が出ていないかを見る検査</v>
+        <v>体に貯蔵されている鉄の量を反映する指標。貧血の症状が出るより早い段階で低下する</v>
       </c>
       <c r="E92" t="str">
-        <v>この検査は、体の中に自分の甲状腺を誤って攻撃してしまう抗体がないかを見るものです。陽性の場合、橋本病（慢性甲状腺炎）など甲状腺の自己免疫的な炎症が背景にある可能性があります。</v>
+        <v>フェリチンは、体に蓄えられている鉄の「貯金」の量を見る検査です。この数値が下がるのは、貧血の症状が出るよりも前の、とても早い段階のサインになります。</v>
       </c>
       <c r="F92" t="str">
-        <v>橋本病（慢性甲状腺炎）、バセドウ病などの自己免疫性甲状腺疾患</v>
+        <v>炎症性疾患、肝疾患、悪性腫瘍、鉄過剰症（フェリチンは炎症でも上昇するため、貧血の評価では注意が必要）</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -4727,45 +4727,45 @@
         <v/>
       </c>
       <c r="I92" t="str">
-        <v/>
+        <v>鉄欠乏状態（貧血の症状が出る前の早期段階から低下する）</v>
       </c>
       <c r="J92" t="str">
-        <v/>
+        <v>鉄分の多い食品を意識するとともに、貯蔵鉄を補うため治療は数値が正常化してからも継続が必要なことを伝える</v>
       </c>
       <c r="K92" t="str">
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>陽性でも必ずしも甲状腺機能異常があるとは限らない。TSH・FT4など甲状腺ホルモンの数値と合わせて評価する</v>
+        <v>貯蔵鉄の指標で鉄欠乏を最も早期に反映する。ただし炎症があると鉄欠乏があっても正常〜高値に出ることがあり、CRP等の炎症所見と合わせて評価する。二次性貧血との鑑別に重要</v>
       </c>
       <c r="M92" t="str">
-        <v>甲状腺疾患</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="N92" t="str">
-        <v>抗TPO抗体,抗甲状腺マイクロゾーム抗体,TPOAb,橋本病</v>
+        <v>フェリチン,Ferritin,貯蔵鉄,鉄欠乏</v>
       </c>
       <c r="O92" t="str">
-        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
+        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>抗サイログロブリン抗体</v>
+        <v>尿中尿酸/クレアチニン比（UUA/UCr）</v>
       </c>
       <c r="B93" t="str">
-        <v>TgAb</v>
+        <v>UUA/UCr</v>
       </c>
       <c r="C93" t="str">
-        <v>陰性（28 IU/mL未満程度、施設差あり）</v>
+        <v>0.4〜0.8程度が混合型の目安</v>
       </c>
       <c r="D93" t="str">
-        <v>甲状腺のたんぱく質（サイログロブリン）への抗体が出ていないかを見る検査</v>
+        <v>尿酸が「作られすぎ」か「排泄できていない」かを見分ける比の値</v>
       </c>
       <c r="E93" t="str">
-        <v>この検査も、抗TPO抗体と同じく、甲状腺に対する自己免疫の有無を見るものです。あわせて調べることで橋本病などの診断の参考にします。</v>
+        <v>この数値は、体の中で尿酸が「作られすぎている」のか、それとも「うまく排泄できていない」のかを見分けるために使う比の値です。高尿酸血症の治療薬を選ぶときの参考になります。</v>
       </c>
       <c r="F93" t="str">
-        <v>橋本病（慢性甲状腺炎）、バセドウ病などの自己免疫性甲状腺疾患</v>
+        <v>尿酸産生過剰型（0.8以上が目安）</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -4774,7 +4774,7 @@
         <v/>
       </c>
       <c r="I93" t="str">
-        <v/>
+        <v>尿酸排泄低下型（0.4以下が目安）</v>
       </c>
       <c r="J93" t="str">
         <v/>
@@ -4783,92 +4783,92 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>抗TPO抗体とあわせて測定されることが多い。単独の高値だけで治療方針が決まるわけではない</v>
+        <v>高尿酸血症は尿酸産生過剰型・排泄低下型・混合型に分類され、この比が目安になる。病型によって使う薬剤（尿酸生成抑制薬か尿酸排泄促進薬か）の選択が変わる</v>
       </c>
       <c r="M93" t="str">
-        <v>甲状腺疾患</v>
+        <v>高尿酸血症</v>
       </c>
       <c r="N93" t="str">
-        <v>抗サイログロブリン抗体,TgAb,橋本病</v>
+        <v>UUA,UCr,尿酸クリアランス,CUA,EUA,尿酸産生過剰型,尿酸排泄低下型</v>
       </c>
       <c r="O93" t="str">
-        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
+        <v>食事と栄養 p.180-189（第2部 痛風・高尿酸血症）</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>血中薬物濃度（TDM）</v>
+        <v>抗甲状腺マイクロゾーム抗体（抗TPO抗体）</v>
       </c>
       <c r="B94" t="str">
-        <v>TDM</v>
+        <v>TPOAb</v>
       </c>
       <c r="C94" t="str">
-        <v>薬剤ごとに有効域が異なる（例：フェニトイン 10〜20 μg/mL、ゾニサミド 10〜40 μg/mL、カルバマゼピン 4〜12 μg/mL、バルプロ酸ナトリウム 40〜120 μg/mL、ラモトリギン 1〜10 μg/mL(併用薬により変動)）</v>
+        <v>陰性（16 IU/mL未満程度、施設差あり）</v>
       </c>
       <c r="D94" t="str">
-        <v>治療域が狭い薬剤で、血液中の薬の濃度が効果域・中毒域のどちらにあるかを確認する検査</v>
+        <v>自分の甲状腺を攻撃する抗体が出ていないかを見る検査</v>
       </c>
       <c r="E94" t="str">
-        <v>この薬は効く量と副作用が出る量が近いため、血液中の薬の濃度を定期的に測って、ちょうどよい範囲に入っているかを確認します。数値が低いと効果が不十分になり、高いと副作用が出やすくなります。</v>
+        <v>この検査は、体の中に自分の甲状腺を誤って攻撃してしまう抗体がないかを見るものです。陽性の場合、橋本病（慢性甲状腺炎）など甲状腺の自己免疫的な炎症が背景にある可能性があります。</v>
       </c>
       <c r="F94" t="str">
-        <v>過量投与、代謝を妨げる薬剤との併用、肝機能低下による代謝低下</v>
+        <v>橋本病（慢性甲状腺炎）、バセドウ病などの自己免疫性甲状腺疾患</v>
       </c>
       <c r="G94" t="str">
-        <v>ふらつき、眠気、めまい、物が二重に見えるなどの中毒症状がないか確認する</v>
+        <v/>
       </c>
       <c r="H94" t="str">
         <v/>
       </c>
       <c r="I94" t="str">
-        <v>飲み忘れ、自己判断による減量、代謝を促進する薬剤との併用（相互作用）</v>
+        <v/>
       </c>
       <c r="J94" t="str">
-        <v>発作やてんかん症状の再発がないか確認し、飲み忘れがないか一緒に確認する</v>
+        <v/>
       </c>
       <c r="K94" t="str">
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>採血のタイミング（トラフ値かどうか）で数値の解釈が変わるため採血時点を確認する。カルバマゼピンは自己誘導により長期使用で濃度が下がることがある点にも注意</v>
+        <v>陽性でも必ずしも甲状腺機能異常があるとは限らない。TSH・FT4など甲状腺ホルモンの数値と合わせて評価する</v>
       </c>
       <c r="M94" t="str">
-        <v>てんかん</v>
+        <v>甲状腺疾患</v>
       </c>
       <c r="N94" t="str">
-        <v>TDM,血中薬物濃度,治療域,中毒域,カルバマゼピン,フェニトイン,バルプロ酸,抗てんかん薬,ゾニサミド,ラモトリギン</v>
+        <v>抗TPO抗体,抗甲状腺マイクロゾーム抗体,TPOAb,橋本病</v>
       </c>
       <c r="O94" t="str">
-        <v/>
+        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>アミラーゼ（AMY）</v>
+        <v>抗サイログロブリン抗体</v>
       </c>
       <c r="B95" t="str">
-        <v>AMY</v>
+        <v>TgAb</v>
       </c>
       <c r="C95" t="str">
-        <v>44〜132 U/L（施設差あり）</v>
+        <v>陰性（28 IU/mL未満程度、施設差あり）</v>
       </c>
       <c r="D95" t="str">
-        <v>膵臓や唾液腺から出る消化酵素。膵炎などで血液中に漏れ出す</v>
+        <v>甲状腺のたんぱく質（サイログロブリン）への抗体が出ていないかを見る検査</v>
       </c>
       <c r="E95" t="str">
-        <v>アミラーゼは、でんぷんを分解する消化酵素で、主に膵臓と唾液腺から作られます。膵臓に炎症が起きると血液中に漏れ出して数値が上がるため、膵炎の診断や経過観察に使われます。</v>
+        <v>この検査も、抗TPO抗体と同じく、甲状腺に対する自己免疫の有無を見るものです。あわせて調べることで橋本病などの診断の参考にします。</v>
       </c>
       <c r="F95" t="str">
-        <v>急性膵炎、慢性膵炎の急性増悪、耳下腺炎（おたふくかぜ）、腎不全</v>
+        <v>橋本病（慢性甲状腺炎）、バセドウ病などの自己免疫性甲状腺疾患</v>
       </c>
       <c r="G95" t="str">
-        <v>飲酒を控え、脂っこい食事を避けるよう伝える。強い腹痛・背部痛がある場合は急性膵炎の可能性もあるため早めの受診を勧める</v>
+        <v/>
       </c>
       <c r="H95" t="str">
-        <v>バルプロ酸、アザチオプリン、サイアザイド系・ループ利尿薬、ステロイドなど薬剤性膵炎の原因薬</v>
+        <v/>
       </c>
       <c r="I95" t="str">
-        <v>慢性膵炎の進行期（膵臓の機能低下）</v>
+        <v/>
       </c>
       <c r="J95" t="str">
         <v/>
@@ -4877,60 +4877,60 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>膵臓由来か唾液腺由来かを区別するには膵型アミラーゼ(P-AMY)を確認する。急性膵炎では強い腹痛・背部痛を伴うことが多く、飲酒歴の確認も重要</v>
+        <v>抗TPO抗体とあわせて測定されることが多い。単独の高値だけで治療方針が決まるわけではない</v>
       </c>
       <c r="M95" t="str">
-        <v/>
+        <v>甲状腺疾患</v>
       </c>
       <c r="N95" t="str">
-        <v>アミラーゼ,AMY,膵炎,急性膵炎</v>
+        <v>抗サイログロブリン抗体,TgAb,橋本病</v>
       </c>
       <c r="O95" t="str">
-        <v/>
+        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>間接ビリルビン</v>
+        <v>血中薬物濃度（TDM）</v>
       </c>
       <c r="B96" t="str">
-        <v>I-Bil</v>
+        <v>TDM</v>
       </c>
       <c r="C96" t="str">
-        <v>0.2〜0.8 mg/dL程度（施設差あり）</v>
+        <v>薬剤ごとに有効域が異なる（例：フェニトイン 10〜20 μg/mL、ゾニサミド 10〜40 μg/mL、カルバマゼピン 4〜12 μg/mL、バルプロ酸ナトリウム 40〜120 μg/mL、ラモトリギン 1〜10 μg/mL(併用薬により変動)）</v>
       </c>
       <c r="D96" t="str">
-        <v>赤血球が壊れてできるビリルビンのうち、肝臓で処理される前の形</v>
+        <v>治療域が狭い薬剤で、血液中の薬の濃度が効果域・中毒域のどちらにあるかを確認する検査</v>
       </c>
       <c r="E96" t="str">
-        <v>間接ビリルビンは、赤血球が壊れてできたビリルビンが、まだ肝臓で処理される前の状態です。この値が高い場合、赤血球が通常より多く壊れている(溶血)か、肝臓での処理能力に生まれつきの体質差(体質性黄疸)がある可能性が考えられます。</v>
+        <v>この薬は効く量と副作用が出る量が近いため、血液中の薬の濃度を定期的に測って、ちょうどよい範囲に入っているかを確認します。数値が低いと効果が不十分になり、高いと副作用が出やすくなります。</v>
       </c>
       <c r="F96" t="str">
-        <v>溶血性疾患（自己免疫性溶血性貧血、血液型不適合輸血など）、体質性黄疸（ジルベール症候群）、新生児黄疸</v>
+        <v>過量投与、代謝を妨げる薬剤との併用、肝機能低下による代謝低下</v>
       </c>
       <c r="G96" t="str">
-        <v>皮膚や白目の黄染、尿の色の変化がないか確認する</v>
+        <v>ふらつき、眠気、めまい、物が二重に見えるなどの中毒症状がないか確認する</v>
       </c>
       <c r="H96" t="str">
         <v/>
       </c>
       <c r="I96" t="str">
-        <v/>
+        <v>飲み忘れ、自己判断による減量、代謝を促進する薬剤との併用（相互作用）</v>
       </c>
       <c r="J96" t="str">
-        <v/>
+        <v>発作やてんかん症状の再発がないか確認し、飲み忘れがないか一緒に確認する</v>
       </c>
       <c r="K96" t="str">
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>直接ビリルビンとの比率で原因を推測する（間接優位は溶血・体質性、直接優位は胆道系）。総ビリルビン・AST/ALTと合わせて評価する</v>
+        <v>採血のタイミング（トラフ値かどうか）で数値の解釈が変わるため採血時点を確認する。カルバマゼピンは自己誘導により長期使用で濃度が下がることがある点にも注意</v>
       </c>
       <c r="M96" t="str">
-        <v>肝機能</v>
+        <v>てんかん</v>
       </c>
       <c r="N96" t="str">
-        <v>間接ビリルビン,I-Bil,溶血</v>
+        <v>TDM,血中薬物濃度,治療域,中毒域,カルバマゼピン,フェニトイン,バルプロ酸,抗てんかん薬,ゾニサミド,ラモトリギン</v>
       </c>
       <c r="O96" t="str">
         <v/>
@@ -4938,31 +4938,31 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>直接ビリルビン</v>
+        <v>アミラーゼ（AMY）</v>
       </c>
       <c r="B97" t="str">
-        <v>D-Bil</v>
+        <v>AMY</v>
       </c>
       <c r="C97" t="str">
-        <v>0.0〜0.3 mg/dL程度（施設差あり）</v>
+        <v>44〜132 U/L（施設差あり）</v>
       </c>
       <c r="D97" t="str">
-        <v>肝臓で処理された後のビリルビン。胆道の詰まりで血液中に増える</v>
+        <v>膵臓や唾液腺から出る消化酵素。膵炎などで血液中に漏れ出す</v>
       </c>
       <c r="E97" t="str">
-        <v>直接ビリルビンは、肝臓で処理された後のビリルビンです。胆石や腫瘍などで胆汁の通り道（胆道）が詰まると、行き場を失って血液中に増え、皮膚や白目が黄色くなる黄疸として現れます。</v>
+        <v>アミラーゼは、でんぷんを分解する消化酵素で、主に膵臓と唾液腺から作られます。膵臓に炎症が起きると血液中に漏れ出して数値が上がるため、膵炎の診断や経過観察に使われます。</v>
       </c>
       <c r="F97" t="str">
-        <v>肝疾患、胆石など胆道の閉塞</v>
+        <v>急性膵炎、慢性膵炎の急性増悪、耳下腺炎（おたふくかぜ）、腎不全</v>
       </c>
       <c r="G97" t="str">
-        <v>皮膚や白目の黄染、白っぽい便、濃い茶色の尿がないか確認する</v>
+        <v>飲酒を控え、脂っこい食事を避けるよう伝える。強い腹痛・背部痛がある場合は急性膵炎の可能性もあるため早めの受診を勧める</v>
       </c>
       <c r="H97" t="str">
-        <v>胆汁うっ滞型の薬剤性肝障害を起こしうる抗菌薬、経口避妊薬</v>
+        <v>バルプロ酸、アザチオプリン、サイアザイド系・ループ利尿薬、ステロイドなど薬剤性膵炎の原因薬</v>
       </c>
       <c r="I97" t="str">
-        <v/>
+        <v>慢性膵炎の進行期（膵臓の機能低下）</v>
       </c>
       <c r="J97" t="str">
         <v/>
@@ -4971,13 +4971,13 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>直接優位の上昇は胆道系（胆石、腫瘍による閉塞）を、間接優位の上昇は溶血・体質性を疑う手がかりになる。γ-GTP・ALPと合わせて胆道系疾患を評価する</v>
+        <v>膵臓由来か唾液腺由来かを区別するには膵型アミラーゼ(P-AMY)を確認する。急性膵炎では強い腹痛・背部痛を伴うことが多く、飲酒歴の確認も重要</v>
       </c>
       <c r="M97" t="str">
-        <v>肝機能</v>
+        <v/>
       </c>
       <c r="N97" t="str">
-        <v>直接ビリルビン,D-Bil,胆石,胆道閉塞</v>
+        <v>アミラーゼ,AMY,膵炎,急性膵炎</v>
       </c>
       <c r="O97" t="str">
         <v/>
@@ -4985,116 +4985,116 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>亜鉛（Zn）</v>
+        <v>間接ビリルビン</v>
       </c>
       <c r="B98" t="str">
-        <v>Zn</v>
+        <v>I-Bil</v>
       </c>
       <c r="C98" t="str">
-        <v>80〜130 μg/dL程度（施設差あり）</v>
+        <v>0.2〜0.8 mg/dL程度（施設差あり）</v>
       </c>
       <c r="D98" t="str">
-        <v>味覚や皮膚、免疫に関わる微量ミネラル。高齢者や低栄養で不足しやすい</v>
+        <v>赤血球が壊れてできるビリルビンのうち、肝臓で処理される前の形</v>
       </c>
       <c r="E98" t="str">
-        <v>亜鉛は、味を感じる働きや皮膚・粘膜の健康、免疫の働きに関わる微量ミネラルです。不足すると、味がわかりにくくなったり（味覚障害）、傷が治りにくくなったりすることがあります。</v>
+        <v>間接ビリルビンは、赤血球が壊れてできたビリルビンが、まだ肝臓で処理される前の状態です。この値が高い場合、赤血球が通常より多く壊れている(溶血)か、肝臓での処理能力に生まれつきの体質差(体質性黄疸)がある可能性が考えられます。</v>
       </c>
       <c r="F98" t="str">
-        <v/>
+        <v>溶血性疾患（自己免疫性溶血性貧血、血液型不適合輸血など）、体質性黄疸（ジルベール症候群）、新生児黄疸</v>
       </c>
       <c r="G98" t="str">
-        <v/>
+        <v>皮膚や白目の黄染、尿の色の変化がないか確認する</v>
       </c>
       <c r="H98" t="str">
         <v/>
       </c>
       <c r="I98" t="str">
-        <v>低栄養、高齢による摂取不足、消化器手術後、亜鉛の吸収を妨げる薬剤（PPI、キレート形成する薬剤など）との併用</v>
+        <v/>
       </c>
       <c r="J98" t="str">
-        <v>味覚の変化（味を感じにくい、金属味がするなど）がないか確認する。牡蠣、赤身肉、レバーなど亜鉛を多く含む食品を意識するとよいことを伝える</v>
+        <v/>
       </c>
       <c r="K98" t="str">
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>薬剤性の亜鉛欠乏（PPI長期使用、D-ペニシラミン、一部の降圧薬など）に注意。亜鉛欠乏による味覚障害は原因薬剤の中止・亜鉛補充で改善することがある</v>
+        <v>直接ビリルビンとの比率で原因を推測する（間接優位は溶血・体質性、直接優位は胆道系）。総ビリルビン・AST/ALTと合わせて評価する</v>
       </c>
       <c r="M98" t="str">
-        <v/>
+        <v>肝機能</v>
       </c>
       <c r="N98" t="str">
-        <v>亜鉛,Zn,味覚障害,亜鉛欠乏</v>
+        <v>間接ビリルビン,I-Bil,溶血</v>
       </c>
       <c r="O98" t="str">
-        <v>食事と栄養 p.78（亜鉛）</v>
+        <v/>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>マグネシウム（Mg）</v>
+        <v>直接ビリルビン</v>
       </c>
       <c r="B99" t="str">
-        <v>Mg</v>
+        <v>D-Bil</v>
       </c>
       <c r="C99" t="str">
-        <v>1.8〜2.6 mg/dL程度（施設差あり）</v>
+        <v>0.0〜0.3 mg/dL程度（施設差あり）</v>
       </c>
       <c r="D99" t="str">
-        <v>骨や筋肉、神経の働きに関わるミネラル。低栄養や利尿薬で不足しやすい</v>
+        <v>肝臓で処理された後のビリルビン。胆道の詰まりで血液中に増える</v>
       </c>
       <c r="E99" t="str">
-        <v>マグネシウムは、骨や筋肉、神経の働きを支えるミネラルです。不足すると、こむら返りや不整脈、だるさなどの症状が出ることがあります。</v>
+        <v>直接ビリルビンは、肝臓で処理された後のビリルビンです。胆石や腫瘍などで胆汁の通り道（胆道）が詰まると、行き場を失って血液中に増え、皮膚や白目が黄色くなる黄疸として現れます。</v>
       </c>
       <c r="F99" t="str">
-        <v>腎不全、マグネシウム製剤（酸化マグネシウムなど）の過量投与</v>
+        <v>肝疾患、胆石など胆道の閉塞</v>
       </c>
       <c r="G99" t="str">
-        <v>腎機能低下がある患者で酸化マグネシウムなどの緩下剤を使用中は、傾眠・血圧低下などの高マグネシウム血症の症状がないか確認する</v>
+        <v>皮膚や白目の黄染、白っぽい便、濃い茶色の尿がないか確認する</v>
       </c>
       <c r="H99" t="str">
-        <v>マグネシウム含有制酸薬・下剤の過量(特に腎機能低下患者)</v>
+        <v>胆汁うっ滞型の薬剤性肝障害を起こしうる抗菌薬、経口避妊薬</v>
       </c>
       <c r="I99" t="str">
-        <v>低栄養、利尿薬の使用、慢性的な下痢、アルコール多飲、PPI長期使用</v>
+        <v/>
       </c>
       <c r="J99" t="str">
-        <v>こむら返りや動悸などの症状がないか確認する</v>
+        <v/>
       </c>
       <c r="K99" t="str">
-        <v>プロトンポンプ阻害薬(PPI)の長期使用、ループ利尿薬、サイアザイド系利尿薬、シスプラチン、アミノグリコシド系</v>
+        <v/>
       </c>
       <c r="L99" t="str">
-        <v>腎機能低下患者への酸化マグネシウム投与は高マグネシウム血症のリスクがあるため定期的なモニタリングが必要。PPI長期使用も低マグネシウム血症のリスク因子として知られる</v>
+        <v>直接優位の上昇は胆道系（胆石、腫瘍による閉塞）を、間接優位の上昇は溶血・体質性を疑う手がかりになる。γ-GTP・ALPと合わせて胆道系疾患を評価する</v>
       </c>
       <c r="M99" t="str">
-        <v>腎機能</v>
+        <v>肝機能</v>
       </c>
       <c r="N99" t="str">
-        <v>マグネシウム,Mg,酸化マグネシウム,こむら返り</v>
+        <v>直接ビリルビン,D-Bil,胆石,胆道閉塞</v>
       </c>
       <c r="O99" t="str">
-        <v>食事と栄養 p.84（マグネシウム）</v>
+        <v/>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>単球</v>
+        <v>亜鉛（Zn）</v>
       </c>
       <c r="B100" t="str">
-        <v>Mono,Mono%</v>
+        <v>Zn</v>
       </c>
       <c r="C100" t="str">
-        <v>2〜10%程度（施設差あり）</v>
+        <v>80〜130 μg/dL程度（施設差あり）</v>
       </c>
       <c r="D100" t="str">
-        <v>感染や炎症の後始末をする白血球の一種の割合</v>
+        <v>味覚や皮膚、免疫に関わる微量ミネラル。高齢者や低栄養で不足しやすい</v>
       </c>
       <c r="E100" t="str">
-        <v>単球は、細菌などを取り込んで処理したり、組織の修復に関わったりする免疫細胞です。慢性的な炎症や感染症の回復期に増えることがあります。</v>
+        <v>亜鉛は、味を感じる働きや皮膚・粘膜の健康、免疫の働きに関わる微量ミネラルです。不足すると、味がわかりにくくなったり（味覚障害）、傷が治りにくくなったりすることがあります。</v>
       </c>
       <c r="F100" t="str">
-        <v>慢性感染症（結核など）、炎症性疾患、血液疾患、感染症の回復期</v>
+        <v/>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -5103,116 +5103,116 @@
         <v/>
       </c>
       <c r="I100" t="str">
-        <v/>
+        <v>低栄養、高齢による摂取不足、消化器手術後、亜鉛の吸収を妨げる薬剤（PPI、キレート形成する薬剤など）との併用</v>
       </c>
       <c r="J100" t="str">
-        <v/>
+        <v>味覚の変化（味を感じにくい、金属味がするなど）がないか確認する。牡蠣、赤身肉、レバーなど亜鉛を多く含む食品を意識するとよいことを伝える</v>
       </c>
       <c r="K100" t="str">
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>単独での臨床的意義は乏しく、他の血球指標や炎症マーカー(CRPなど)と合わせて評価する</v>
+        <v>薬剤性の亜鉛欠乏（PPI長期使用、D-ペニシラミン、一部の降圧薬など）に注意。亜鉛欠乏による味覚障害は原因薬剤の中止・亜鉛補充で改善することがある</v>
       </c>
       <c r="M100" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v/>
       </c>
       <c r="N100" t="str">
-        <v>単球,Mono,慢性感染症,結核,炎症</v>
+        <v>亜鉛,Zn,味覚障害,亜鉛欠乏</v>
       </c>
       <c r="O100" t="str">
-        <v/>
+        <v>食事と栄養 p.78（亜鉛）</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Dダイマー</v>
+        <v>マグネシウム（Mg）</v>
       </c>
       <c r="B101" t="str">
-        <v>D-dimer</v>
+        <v>Mg</v>
       </c>
       <c r="C101" t="str">
-        <v>1.0 μg/mL以下(施設・測定法により異なる)</v>
+        <v>1.8〜2.6 mg/dL程度（施設差あり）</v>
       </c>
       <c r="D101" t="str">
-        <v>体の中で血栓ができて溶けた(線溶)ときにできる分解産物で、血栓症の有無をスクリーニングする指標</v>
+        <v>骨や筋肉、神経の働きに関わるミネラル。低栄養や利尿薬で不足しやすい</v>
       </c>
       <c r="E101" t="str">
-        <v>Dダイマーは、血管の中に血のかたまり(血栓)ができて、それが溶かされるときにできる物質です。この数値が高いと、どこかに血栓ができている可能性を考えます。ただし手術後や妊娠中、高齢の方などでも上がることがあるため、この数値だけで診断が決まるわけではありません。</v>
+        <v>マグネシウムは、骨や筋肉、神経の働きを支えるミネラルです。不足すると、こむら返りや不整脈、だるさなどの症状が出ることがあります。</v>
       </c>
       <c r="F101" t="str">
-        <v>深部静脈血栓症(DVT)・肺血栓塞栓症(PE)、播種性血管内凝固症候群(DIC)、大動脈解離、悪性腫瘍、手術後、妊娠、高齢、感染・炎症</v>
+        <v>腎不全、マグネシウム製剤（酸化マグネシウムなど）の過量投与</v>
       </c>
       <c r="G101" t="str">
-        <v>ふくらはぎの腫れ・痛み、急な息切れ・胸痛など血栓症を疑う症状がないか確認する</v>
+        <v>腎機能低下がある患者で酸化マグネシウムなどの緩下剤を使用中は、傾眠・血圧低下などの高マグネシウム血症の症状がないか確認する</v>
       </c>
       <c r="H101" t="str">
-        <v>経口避妊薬・ホルモン補充療法は血栓リスクを高める。逆にワルファリン・DOAC・ヘパリンなど抗凝固薬の効果不十分で血栓が進行している可能性にも注意</v>
+        <v>マグネシウム含有制酸薬・下剤の過量(特に腎機能低下患者)</v>
       </c>
       <c r="I101" t="str">
-        <v>通常、臨床的意義は乏しい(基準値以下であれば血栓症の可能性は低いとする除外診断に有用)</v>
+        <v>低栄養、利尿薬の使用、慢性的な下痢、アルコール多飲、PPI長期使用</v>
       </c>
       <c r="J101" t="str">
-        <v/>
+        <v>こむら返りや動悸などの症状がないか確認する</v>
       </c>
       <c r="K101" t="str">
-        <v/>
+        <v>プロトンポンプ阻害薬(PPI)の長期使用、ループ利尿薬、サイアザイド系利尿薬、シスプラチン、アミノグリコシド系</v>
       </c>
       <c r="L101" t="str">
-        <v>陰性的中率が高く、基準値以下であれば静脈血栓塞栓症(VTE)の可能性は低いとする除外診断への活用が臨床的に重要。一方で偽陽性が多く、高値のみで血栓症と確定はできない。抗凝固療法中のモニタリングそのものには通常用いない(効果判定はPT-INR/APTT等)</v>
+        <v>腎機能低下患者への酸化マグネシウム投与は高マグネシウム血症のリスクがあるため定期的なモニタリングが必要。PPI長期使用も低マグネシウム血症のリスク因子として知られる</v>
       </c>
       <c r="M101" t="str">
-        <v>抗凝固療法（心房細動・血栓症）</v>
+        <v>腎機能</v>
       </c>
       <c r="N101" t="str">
-        <v>Dダイマー,D-dimer,血栓,DVT,深部静脈血栓症,肺塞栓,DIC</v>
+        <v>マグネシウム,Mg,酸化マグネシウム,こむら返り</v>
       </c>
       <c r="O101" t="str">
-        <v/>
+        <v>食事と栄養 p.84（マグネシウム）</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>骨密度</v>
+        <v>Dダイマー</v>
       </c>
       <c r="B102" t="str">
-        <v>BMD,骨密度</v>
+        <v>D-dimer</v>
       </c>
       <c r="C102" t="str">
-        <v>YAM(若年成人平均値)80%以上:正常、70%以上80%未満:骨量減少、70%未満:骨粗鬆症</v>
+        <v>1.0 μg/mL以下(施設・測定法により異なる)</v>
       </c>
       <c r="D102" t="str">
-        <v>骨の中にカルシウムなどのミネラルがどれだけ詰まっているかを示す指標。20〜44歳の平均値(YAM)に対する割合(%)で評価する</v>
+        <v>体の中で血栓ができて溶けた(線溶)ときにできる分解産物で、血栓症の有無をスクリーニングする指標</v>
       </c>
       <c r="E102" t="str">
-        <v>骨密度は、骨の中にカルシウムなどのミネラルがどれだけしっかり詰まっているかを表す数値です。20〜44歳の若い方の平均値を100%として、ご自身の骨密度が何%かで示されます。70%未満になると「骨粗鬆症」と診断され、骨折しやすい状態と考えられます。</v>
+        <v>Dダイマーは、血管の中に血のかたまり(血栓)ができて、それが溶かされるときにできる物質です。この数値が高いと、どこかに血栓ができている可能性を考えます。ただし手術後や妊娠中、高齢の方などでも上がることがあるため、この数値だけで診断が決まるわけではありません。</v>
       </c>
       <c r="F102" t="str">
-        <v>基本的に問題になることは少ない(まれに骨硬化症などの疾患)</v>
+        <v>深部静脈血栓症(DVT)・肺血栓塞栓症(PE)、播種性血管内凝固症候群(DIC)、大動脈解離、悪性腫瘍、手術後、妊娠、高齢、感染・炎症</v>
       </c>
       <c r="G102" t="str">
-        <v/>
+        <v>ふくらはぎの腫れ・痛み、急な息切れ・胸痛など血栓症を疑う症状がないか確認する</v>
       </c>
       <c r="H102" t="str">
-        <v/>
+        <v>経口避妊薬・ホルモン補充療法は血栓リスクを高める。逆にワルファリン・DOAC・ヘパリンなど抗凝固薬の効果不十分で血栓が進行している可能性にも注意</v>
       </c>
       <c r="I102" t="str">
-        <v>骨粗鬆症、加齢による骨量減少、閉経後のエストロゲン低下、ステロイド長期使用、カルシウム・ビタミンD不足、運動不足、るいそう</v>
+        <v>通常、臨床的意義は乏しい(基準値以下であれば血栓症の可能性は低いとする除外診断に有用)</v>
       </c>
       <c r="J102" t="str">
-        <v>カルシウム・ビタミンD・ビタミンKを意識した食事、荷重運動(ウォーキング等)を勧める。ステロイド長期服用中の場合は骨粗鬆症治療薬の併用が検討されているか確認する</v>
+        <v/>
       </c>
       <c r="K102" t="str">
         <v/>
       </c>
       <c r="L102" t="str">
-        <v>YAM70%未満、または既存の脆弱性骨折がある場合に骨粗鬆症と診断され薬物治療の対象となる(日本骨粗鬆症学会・日本骨代謝学会・厚生労働省合同「原発性骨粗鬆症の診断基準 2012年度改訂版」)。ビスホスホネート製剤は起床時空腹時に十分な水(180mL程度)で服用し、服用後30分は横にならないよう指導する。ステロイドを長期服用中の患者は骨密度によらず骨粗鬆症治療薬の併用が推奨される場合がある(グルココルチコイド誘発性骨粗鬆症: GIOP)</v>
+        <v>陰性的中率が高く、基準値以下であれば静脈血栓塞栓症(VTE)の可能性は低いとする除外診断への活用が臨床的に重要。一方で偽陽性が多く、高値のみで血栓症と確定はできない。抗凝固療法中のモニタリングそのものには通常用いない(効果判定はPT-INR/APTT等)</v>
       </c>
       <c r="M102" t="str">
-        <v>骨粗鬆症</v>
+        <v>抗凝固療法（心房細動・血栓症）</v>
       </c>
       <c r="N102" t="str">
-        <v>骨密度,BMD,YAM,若年成人平均値,骨粗鬆症,DXA</v>
+        <v>Dダイマー,D-dimer,血栓,DVT,深部静脈血栓症,肺塞栓,DIC</v>
       </c>
       <c r="O102" t="str">
         <v/>

--- a/検査値リファレンス初期データ.xlsx
+++ b/検査値リファレンス初期データ.xlsx
@@ -4889,15 +4889,20 @@
         <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" xml:space="preserve">
       <c r="A96" t="str">
         <v>血中薬物濃度（TDM）</v>
       </c>
       <c r="B96" t="str">
         <v>TDM</v>
       </c>
-      <c r="C96" t="str">
-        <v>薬剤ごとに有効域が異なる（例：フェニトイン 10〜20 μg/mL、ゾニサミド 10〜40 μg/mL、カルバマゼピン 4〜12 μg/mL、バルプロ酸ナトリウム 40〜120 μg/mL、ラモトリギン 1〜10 μg/mL(併用薬により変動)）</v>
+      <c r="C96" t="str" xml:space="preserve">
+        <v xml:space="preserve">薬剤ごとに有効域が異なる（代表例）
+フェニトイン 10〜20 μg/mL
+ゾニサミド 10〜40 μg/mL
+カルバマゼピン 4〜12 μg/mL
+バルプロ酸ナトリウム 40〜120 μg/mL
+ラモトリギン 1〜10 μg/mL(併用薬により変動)</v>
       </c>
       <c r="D96" t="str">
         <v>治療域が狭い薬剤で、血液中の薬の濃度が効果域・中毒域のどちらにあるかを確認する検査</v>

--- a/検査値リファレンス初期データ.xlsx
+++ b/検査値リファレンス初期データ.xlsx
@@ -5223,15 +5223,16 @@
         <v/>
       </c>
     </row>
-    <row r="103">
+    <row r="103" xml:space="preserve">
       <c r="A103" t="str">
         <v>収縮期血圧</v>
       </c>
       <c r="B103" t="str">
         <v>SBP,収縮期血圧</v>
       </c>
-      <c r="C103" t="str">
-        <v>診察室血圧 120mmHg未満が正常域、140mmHg以上で高血圧(家庭血圧はそれぞれ5mmHg低い値が基準)</v>
+      <c r="C103" t="str" xml:space="preserve">
+        <v xml:space="preserve">高血圧の診断基準: 診察室血圧140mmHg以上(家庭血圧135mmHg以上)
+降圧目標: 診察室血圧130mmHg未満(家庭血圧125mmHg未満)、患者背景によらず統一</v>
       </c>
       <c r="D103" t="str">
         <v>心臓が収縮して血液を送り出すときの血圧の最高値、いわゆる「上の血圧」</v>
@@ -5258,7 +5259,7 @@
         <v>降圧薬(特に利尿薬・α遮断薬)の効きすぎ、抗うつ薬・抗パーキンソン病薬などによる起立性低血圧</v>
       </c>
       <c r="L103" t="str">
-        <v>診察室血圧と家庭血圧で基準値が異なる(家庭血圧のほうが5mmHg低い基準)。高齢者では収縮期血圧のみが高くなる収縮期高血圧が多く、動脈硬化を反映する。降圧薬開始・増量後はふらつき・立ちくらみの有無を確認する</v>
+        <v>「高血圧管理・治療ガイドライン2025」で、従来75歳以上や両側頸動脈狭窄・脳主幹動脈閉塞のある脳血管障害・蛋白尿陰性CKDなど有害事象リスクのある患者で緩めに設定されていた降圧目標(140/90mmHg未満)が撤廃され、患者背景によらず130/80mmHg未満(家庭血圧125/75mmHg未満)に統一された。高齢者では降圧強化に伴うふらつき・起立性低血圧のリスクにも注意が必要。診断基準(140/90mmHg以上)自体は従来から変更なし</v>
       </c>
       <c r="M103" t="str">
         <v>心不全</v>
@@ -5270,15 +5271,16 @@
         <v/>
       </c>
     </row>
-    <row r="104">
+    <row r="104" xml:space="preserve">
       <c r="A104" t="str">
         <v>拡張期血圧</v>
       </c>
       <c r="B104" t="str">
         <v>DBP,拡張期血圧</v>
       </c>
-      <c r="C104" t="str">
-        <v>診察室血圧 80mmHg未満が正常域、90mmHg以上で高血圧(家庭血圧はそれぞれ5mmHg低い値が基準)</v>
+      <c r="C104" t="str" xml:space="preserve">
+        <v xml:space="preserve">高血圧の診断基準: 診察室血圧90mmHg以上(家庭血圧85mmHg以上)
+降圧目標: 診察室血圧80mmHg未満(家庭血圧75mmHg未満)、患者背景によらず統一</v>
       </c>
       <c r="D104" t="str">
         <v>心臓が拡張して血液をため込むときの血圧の最低値、いわゆる「下の血圧」</v>
@@ -5305,7 +5307,7 @@
         <v>降圧薬(特に血管拡張作用の強いCa拮抗薬)の効きすぎ</v>
       </c>
       <c r="L104" t="str">
-        <v>加齢とともに動脈硬化が進むと拡張期血圧は低下し、収縮期血圧との差(脈圧)が開大する。脈圧の開大は動脈硬化の進行を示唆する所見として重視される</v>
+        <v>「高血圧管理・治療ガイドライン2025」で、従来75歳以上や脳血管障害・CKD等の患者で緩めに設定されていた降圧目標(140/90mmHg未満)が撤廃され、患者背景によらず130/80mmHg未満に統一された(収縮期血圧の項目も参照)。加齢とともに動脈硬化が進むと拡張期血圧は低下し、収縮期血圧との差(脈圧)が開大する</v>
       </c>
       <c r="M104" t="str">
         <v>心不全</v>

--- a/検査値リファレンス初期データ.xlsx
+++ b/検査値リファレンス初期データ.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O106"/>
+  <dimension ref="A1:O116"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -1836,69 +1836,69 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>BUN/CRE比</v>
+        <v>血清鉄（Fe）</v>
       </c>
       <c r="B31" t="str">
-        <v>BUN/Cr</v>
+        <v>Fe</v>
       </c>
       <c r="C31" t="str">
-        <v>10前後が目安（施設差あり）</v>
+        <v>60〜200 μg/dL（施設差あり）</v>
       </c>
       <c r="D31" t="str">
-        <v>BUNとクレアチニンの比率。腎前性（脱水・出血など）か腎性かを見分ける目安になる</v>
+        <v>血液中を流れている鉄の量</v>
       </c>
       <c r="E31" t="str">
-        <v>これは、BUN（尿素窒素）とクレアチニンという2つの腎機能に関わる検査値を比較したもので、腎臓そのものに問題があるのか、それとも脱水や出血など腎臓の外側に原因があるのかを見分ける手がかりになります。</v>
+        <v>この検査は、今血液の中を流れている鉄の量を見るものです。低いと、体の中で鉄が不足している可能性があります。</v>
       </c>
       <c r="F31" t="str">
-        <v>脱水、消化管出血、高たんぱく食、心不全（腎臓への血流低下）</v>
+        <v>鉄剤の過剰摂取、溶血、肝疾患</v>
       </c>
       <c r="G31" t="str">
-        <v>脱水が疑われる場合はこまめな水分摂取を勧める。黒い便など消化管出血を示唆する症状がないか確認する</v>
+        <v/>
       </c>
       <c r="H31" t="str">
-        <v/>
+        <v>鉄剤の過量摂取(小児の誤飲を含む)</v>
       </c>
       <c r="I31" t="str">
-        <v>低たんぱく食、肝不全、妊娠</v>
+        <v>鉄欠乏性貧血、慢性炎症、出血</v>
       </c>
       <c r="J31" t="str">
-        <v/>
+        <v>鉄分の多い食品（レバー・赤身肉・魚・ほうれん草など）を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える</v>
       </c>
       <c r="K31" t="str">
-        <v/>
+        <v>プロトンポンプ阻害薬(PPI)・H2ブロッカーは胃酸分泌抑制により鉄の吸収を低下させうる</v>
       </c>
       <c r="L31" t="str">
-        <v>比が高い（目安20以上）場合は脱水や消化管出血など腎前性の要因を、比が正常範囲で両方高値なら腎性の障害を疑う。BUN単独やクレアチニン単独よりも病態の絞り込みに役立つ</v>
+        <v>血清鉄は日内変動が大きい。単独で判断せず総鉄結合能・フェリチンと合わせて評価する</v>
       </c>
       <c r="M31" t="str">
-        <v>腎機能</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="N31" t="str">
-        <v>BUN/CRE,BUN/Cr,尿素窒素,クレアチニン,脱水,腎前性</v>
+        <v>血清鉄,Fe,鉄欠乏性貧血</v>
       </c>
       <c r="O31" t="str">
-        <v/>
+        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>LDH/AST比</v>
+        <v>血清フェリチン</v>
       </c>
       <c r="B32" t="str">
-        <v>LDH/AST</v>
+        <v>Ferritin</v>
       </c>
       <c r="C32" t="str">
-        <v>目安として使われる比率（施設差・カットオフ値の設定により異なる）</v>
+        <v>男性 20〜250 ng/mL、女性 10〜120 ng/mL（施設差あり）</v>
       </c>
       <c r="D32" t="str">
-        <v>LDHとASTの両方が上昇したときに、原因が肝臓か、それ以外（溶血・心筋・骨格筋）かを見分ける目安になる比</v>
+        <v>体に貯蔵されている鉄の量を反映する指標。貧血の症状が出るより早い段階で低下する</v>
       </c>
       <c r="E32" t="str">
-        <v>これは、肝臓の数値（AST）と、全身に広く分布する酵素（LDH）の比率を見るもので、両方の数値が上がっているときに、原因が肝臓なのか、それとも血液や筋肉など他の場所なのかを見分ける手がかりになります。</v>
+        <v>フェリチンは、体に蓄えられている鉄の「貯金」の量を見る検査です。この数値が下がるのは、貧血の症状が出るよりも前の、とても早い段階のサインになります。</v>
       </c>
       <c r="F32" t="str">
-        <v>溶血性疾患、心筋梗塞、骨格筋の障害（比が高いほど肝臓以外が原因の可能性）</v>
+        <v>炎症性疾患、肝疾患、悪性腫瘍、鉄過剰症（フェリチンは炎症でも上昇するため、貧血の評価では注意が必要）</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1907,54 +1907,54 @@
         <v/>
       </c>
       <c r="I32" t="str">
-        <v>急性肝炎などの肝細胞障害（比が低い、つまりASTに対してLDHが相対的に低い場合は肝性が示唆される）</v>
+        <v>鉄欠乏状態（貧血の症状が出る前の早期段階から低下する）</v>
       </c>
       <c r="J32" t="str">
-        <v/>
+        <v>鉄分の多い食品を意識するとともに、貯蔵鉄を補うため治療は数値が正常化してからも継続が必要なことを伝える</v>
       </c>
       <c r="K32" t="str">
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>AST・LDHが同時に上昇した際の鑑別に使う目安の一つ。単独の検査値ではなく計算上の比率であり、確定診断には他の検査（ビリルビン、CK、心筋マーカーなど）と合わせた評価が必要</v>
+        <v>貯蔵鉄の指標で鉄欠乏を最も早期に反映する。ただし炎症があると鉄欠乏があっても正常〜高値に出ることがあり、CRP等の炎症所見と合わせて評価する。二次性貧血との鑑別に重要</v>
       </c>
       <c r="M32" t="str">
-        <v/>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="N32" t="str">
-        <v>LDH/AST,LDH,AST,溶血,心筋梗塞,肝炎</v>
+        <v>フェリチン,Ferritin,貯蔵鉄,鉄欠乏</v>
       </c>
       <c r="O32" t="str">
-        <v/>
+        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>CK/AST比</v>
+        <v>不飽和鉄結合能（UIBC）</v>
       </c>
       <c r="B33" t="str">
-        <v>CK/AST</v>
+        <v>UIBC</v>
       </c>
       <c r="C33" t="str">
-        <v>目安として使われる比率（施設差・カットオフ値の設定により異なる）</v>
+        <v>170〜300 μg/dL（施設差あり）</v>
       </c>
       <c r="D33" t="str">
-        <v>ASTが上昇したときに、原因が筋肉（CKも上昇）か、それ以外（肝臓など）かを見分ける目安になる比</v>
+        <v>トランスフェリンのうち、まだ鉄と結合していない余力の部分（UIBC＝TIBC－血清鉄）</v>
       </c>
       <c r="E33" t="str">
-        <v>これは、筋肉の数値（CK）と肝臓の数値（AST）を比べることで、ASTの上昇が筋肉由来なのか、肝臓由来なのかを見分ける手がかりになる比率です。</v>
+        <v>UIBCは、トランスフェリンのうち、まだ鉄と結合していない「空き容量」の部分を表します。鉄が不足しているときほど、この空き容量は大きくなります。</v>
       </c>
       <c r="F33" t="str">
-        <v>横紋筋融解症、心筋梗塞、激しい運動など筋肉由来のAST上昇（CKも同時に高値）</v>
+        <v>鉄欠乏性貧血（＞300 μg/dLが目安）</v>
       </c>
       <c r="G33" t="str">
-        <v>筋肉痛や脱力感、褐色尿などの症状がないか確認する</v>
+        <v/>
       </c>
       <c r="H33" t="str">
         <v/>
       </c>
       <c r="I33" t="str">
-        <v/>
+        <v>慢性炎症、鉄過剰状態</v>
       </c>
       <c r="J33" t="str">
         <v/>
@@ -1963,36 +1963,36 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>ASTのみ上昇しCKが正常であれば肝臓由来を、両方上昇していれば筋肉由来を疑う手がかりになる。スタチン系薬剤による横紋筋融解症が疑われる場面での鑑別に有用</v>
+        <v>TIBCと同じ方向に動くことが多い。血清鉄・TIBCとあわせて鉄欠乏性貧血と二次性貧血の鑑別に使う</v>
       </c>
       <c r="M33" t="str">
-        <v/>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="N33" t="str">
-        <v>CK/AST,CK,AST,横紋筋融解症,スタチン</v>
+        <v>UIBC,不飽和鉄結合能,鉄欠乏性貧血</v>
       </c>
       <c r="O33" t="str">
-        <v/>
+        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Na-Cl（ナトリウム・クロール差）</v>
+        <v>総鉄結合能（TIBC）</v>
       </c>
       <c r="B34" t="str">
-        <v>Na-Cl</v>
+        <v>TIBC</v>
       </c>
       <c r="C34" t="str">
-        <v>36前後が目安（施設差あり）</v>
+        <v>250〜360 μg/dL（施設差あり）</v>
       </c>
       <c r="D34" t="str">
-        <v>ナトリウムからクロールを引いた値。アニオンギャップの簡易的な目安として使われる</v>
+        <v>血液中のトランスフェリンが鉄と結合できる総量</v>
       </c>
       <c r="E34" t="str">
-        <v>この数値は、ナトリウムとクロールの検査値の差から計算されるもので、体の中に通常とは違う酸（アニオン）がたまっていないかを大まかに見積もるために使われます。</v>
+        <v>TIBCは、血液中でトランスフェリンという物質が鉄を運べる最大量を表します。体の中の鉄が不足すると、少しでも多く鉄を運ぼうとしてこの数値が上がる性質があります。</v>
       </c>
       <c r="F34" t="str">
-        <v>代謝性アシドーシス（乳酸アシドーシス、糖尿病性ケトアシドーシス、腎不全など、体内に有機酸がたまる病態）</v>
+        <v>鉄欠乏性貧血（＞360 μg/dLが目安）</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -2001,7 +2001,7 @@
         <v/>
       </c>
       <c r="I34" t="str">
-        <v/>
+        <v>慢性炎症、肝疾患、ネフローゼ症候群</v>
       </c>
       <c r="J34" t="str">
         <v/>
@@ -2010,45 +2010,45 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>本来のアニオンギャップ(Na-(Cl+HCO3))の簡易代用として使われることがあるが、重炭酸(HCO3)を用いた計算の方が正確。メトホルミン使用中の乳酸アシドーシスが疑われる場面などで参考にする</v>
+        <v>鉄が不足すると、体はより多く運ぼうとしてTIBCが上昇する。UIBC・血清鉄と併せて評価する</v>
       </c>
       <c r="M34" t="str">
-        <v>電解質</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="N34" t="str">
-        <v>Na-Cl,アニオンギャップ,AG,代謝性アシドーシス,乳酸アシドーシス</v>
+        <v>TIBC,総鉄結合能,鉄欠乏性貧血</v>
       </c>
       <c r="O34" t="str">
-        <v/>
+        <v>食事と栄養 p.69（鉄）／p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>AST/ALT比</v>
+        <v>BUN/CRE比</v>
       </c>
       <c r="B35" t="str">
-        <v>AST/ALT,De Ritis比</v>
+        <v>BUN/Cr</v>
       </c>
       <c r="C35" t="str">
-        <v>1未満が目安（施設・病態により異なる）</v>
+        <v>10前後が目安（施設差あり）</v>
       </c>
       <c r="D35" t="str">
-        <v>ASTとALTの比率（De Ritis比）。肝疾患の種類を推測する手がかりになる</v>
+        <v>BUNとクレアチニンの比率。腎前性（脱水・出血など）か腎性かを見分ける目安になる</v>
       </c>
       <c r="E35" t="str">
-        <v>これは、肝臓に関わる2つの数値（ASTとALT）の比率を見るもので、肝臓のどのようなタイプのトラブルが起きているかを推測する手がかりになります。</v>
+        <v>これは、BUN（尿素窒素）とクレアチニンという2つの腎機能に関わる検査値を比較したもので、腎臓そのものに問題があるのか、それとも脱水や出血など腎臓の外側に原因があるのかを見分ける手がかりになります。</v>
       </c>
       <c r="F35" t="str">
-        <v>アルコール性肝障害、肝硬変、心筋梗塞・筋疾患の合併（比が2以上でアルコール性を強く示唆）</v>
+        <v>脱水、消化管出血、高たんぱく食、心不全（腎臓への血流低下）</v>
       </c>
       <c r="G35" t="str">
-        <v>飲酒量や頻度を確認する</v>
+        <v>脱水が疑われる場合はこまめな水分摂取を勧める。黒い便など消化管出血を示唆する症状がないか確認する</v>
       </c>
       <c r="H35" t="str">
         <v/>
       </c>
       <c r="I35" t="str">
-        <v>急性ウイルス性肝炎、脂肪肝（比が1未満で肝細胞の急性障害を示唆することが多い）</v>
+        <v>低たんぱく食、肝不全、妊娠</v>
       </c>
       <c r="J35" t="str">
         <v/>
@@ -2057,13 +2057,13 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>De Ritis比とも呼ばれる。比が2以上はアルコール性肝障害や肝硬変を、1未満は急性ウイルス性肝炎や脂肪肝を示唆する目安になるが、確定診断には他の検査所見と合わせた評価が必要</v>
+        <v>比が高い（目安20以上）場合は脱水や消化管出血など腎前性の要因を、比が正常範囲で両方高値なら腎性の障害を疑う。BUN単独やクレアチニン単独よりも病態の絞り込みに役立つ</v>
       </c>
       <c r="M35" t="str">
-        <v>肝機能</v>
+        <v>腎機能</v>
       </c>
       <c r="N35" t="str">
-        <v>AST/ALT比,AST/ALT,De Ritis比,デリティス比,アルコール性肝障害,肝硬変</v>
+        <v>BUN/CRE,BUN/Cr,尿素窒素,クレアチニン,脱水,腎前性</v>
       </c>
       <c r="O35" t="str">
         <v/>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>ALT/ALP比</v>
+        <v>LDH/AST比</v>
       </c>
       <c r="B36" t="str">
-        <v>ALT比/ALP比,R比,R-factor</v>
+        <v>LDH/AST</v>
       </c>
       <c r="C36" t="str">
-        <v>R値 5以上：肝細胞障害型、2以下：胆汁うっ滞型、2〜5：混合型</v>
+        <v>目安として使われる比率（施設差・カットオフ値の設定により異なる）</v>
       </c>
       <c r="D36" t="str">
-        <v>薬剤性肝障害(DILI)などで、肝障害のパターンを「肝細胞障害型」か「胆汁うっ滞型」かに分類するための指標(R値)</v>
+        <v>LDHとASTの両方が上昇したときに、原因が肝臓か、それ以外（溶血・心筋・骨格筋）かを見分ける目安になる比</v>
       </c>
       <c r="E36" t="str">
-        <v>肝臓に関する数値はいくつかありますが、その組み合わせ方によって「肝臓の細胞自体が傷んでいるタイプ」か「胆汁の流れが悪くなっているタイプ」かをある程度見分けることができます。この指標はその判定に使われます。</v>
+        <v>これは、肝臓の数値（AST）と、全身に広く分布する酵素（LDH）の比率を見るもので、両方の数値が上がっているときに、原因が肝臓なのか、それとも血液や筋肉など他の場所なのかを見分ける手がかりになります。</v>
       </c>
       <c r="F36" t="str">
-        <v>R値5以上：肝細胞障害型（ウイルス性肝炎、薬剤性肝障害の肝細胞障害型、虚血性肝障害など）</v>
+        <v>溶血性疾患、心筋梗塞、骨格筋の障害（比が高いほど肝臓以外が原因の可能性）</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -2095,7 +2095,7 @@
         <v/>
       </c>
       <c r="I36" t="str">
-        <v>R値2以下：胆汁うっ滞型（閉塞性黄疸、薬剤性肝障害の胆汁うっ滞型など）</v>
+        <v>急性肝炎などの肝細胞障害（比が低い、つまりASTに対してLDHが相対的に低い場合は肝性が示唆される）</v>
       </c>
       <c r="J36" t="str">
         <v/>
@@ -2104,13 +2104,13 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>R値＝(ALTの基準値上限に対する倍率)÷(ALPの基準値上限に対する倍率)で算出する。薬剤性肝障害(DILI)の病型分類(肝細胞障害型/胆汁うっ滞型/混合型)に用いられ、被疑薬の休薬・変更の判断材料になる</v>
+        <v>AST・LDHが同時に上昇した際の鑑別に使う目安の一つ。単独の検査値ではなく計算上の比率であり、確定診断には他の検査（ビリルビン、CK、心筋マーカーなど）と合わせた評価が必要</v>
       </c>
       <c r="M36" t="str">
-        <v>肝機能</v>
+        <v/>
       </c>
       <c r="N36" t="str">
-        <v>ALT/ALP比,R値,R-factor,DILI,薬剤性肝障害</v>
+        <v>LDH/AST,LDH,AST,溶血,心筋梗塞,肝炎</v>
       </c>
       <c r="O36" t="str">
         <v/>
@@ -2118,31 +2118,31 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>BNP</v>
+        <v>CK/AST比</v>
       </c>
       <c r="B37" t="str">
-        <v>BNP</v>
+        <v>CK/AST</v>
       </c>
       <c r="C37" t="str">
-        <v>18.4 pg/mL以下</v>
+        <v>目安として使われる比率（施設差・カットオフ値の設定により異なる）</v>
       </c>
       <c r="D37" t="str">
-        <v>心臓が無理をしているときに出る物質。心臓は血液を送るポンプだが、負担がかかると「少し助けてほしい」というサインとしてBNPを血液中に出す。</v>
+        <v>ASTが上昇したときに、原因が筋肉（CKも上昇）か、それ以外（肝臓など）かを見分ける目安になる比</v>
       </c>
       <c r="E37" t="str">
-        <v>この検査は、心臓がどれくらい頑張りすぎていないかを見るものです。数値が高いと、心臓に少し負担がかかっているサインになります。</v>
+        <v>これは、筋肉の数値（CK）と肝臓の数値（AST）を比べることで、ASTの上昇が筋肉由来なのか、肝臓由来なのかを見分ける手がかりになる比率です。</v>
       </c>
       <c r="F37" t="str">
-        <v>心不全、心臓に負担がかかっている状態、体に水分がたまりやすいとき</v>
+        <v>横紋筋融解症、心筋梗塞、激しい運動など筋肉由来のAST上昇（CKも同時に高値）</v>
       </c>
       <c r="G37" t="str">
-        <v>塩分・水分の摂りすぎに注意し、体重の変化を毎日記録するよう伝える。急な体重増加(2〜3日で2kg以上)や息切れの悪化があれば早めの受診を勧める</v>
+        <v>筋肉痛や脱力感、褐色尿などの症状がないか確認する</v>
       </c>
       <c r="H37" t="str">
         <v/>
       </c>
       <c r="I37" t="str">
-        <v>心臓の負担は少ない状態</v>
+        <v/>
       </c>
       <c r="J37" t="str">
         <v/>
@@ -2151,36 +2151,36 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>腎機能が低いとBNPは高めに出ることがある／数値だけで判断せず、症状と合わせて評価する／息切れ、むくみ、体重増加があれば要注意</v>
+        <v>ASTのみ上昇しCKが正常であれば肝臓由来を、両方上昇していれば筋肉由来を疑う手がかりになる。スタチン系薬剤による横紋筋融解症が疑われる場面での鑑別に有用</v>
       </c>
       <c r="M37" t="str">
-        <v>心不全</v>
+        <v/>
       </c>
       <c r="N37" t="str">
-        <v>BNP,心不全,息切れ,むくみ</v>
+        <v>CK/AST,CK,AST,横紋筋融解症,スタチン</v>
       </c>
       <c r="O37" t="str">
-        <v>食事と栄養 p.216-222（第2部 心疾患）</v>
+        <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>C－ペプチド（血中）</v>
+        <v>Na-Cl（ナトリウム・クロール差）</v>
       </c>
       <c r="B38" t="str">
-        <v>CPR</v>
+        <v>Na-Cl</v>
       </c>
       <c r="C38" t="str">
-        <v>空腹時 0.6〜3.0 ng/mL（施設差あり）</v>
+        <v>36前後が目安（施設差あり）</v>
       </c>
       <c r="D38" t="str">
-        <v>自分の膵臓がどれくらいインスリンを作れているかを表す指標</v>
+        <v>ナトリウムからクロールを引いた値。アニオンギャップの簡易的な目安として使われる</v>
       </c>
       <c r="E38" t="str">
-        <v>この検査は、ご自身の膵臓がどれくらいインスリンを作る力を持っているかを見るものです。数値が低いほど、体の中で作れるインスリンが少ないことを示します。</v>
+        <v>この数値は、ナトリウムとクロールの検査値の差から計算されるもので、体の中に通常とは違う酸（アニオン）がたまっていないかを大まかに見積もるために使われます。</v>
       </c>
       <c r="F38" t="str">
-        <v>インスリン抵抗性が強い状態（初期の2型糖尿病など）</v>
+        <v>代謝性アシドーシス（乳酸アシドーシス、糖尿病性ケトアシドーシス、腎不全など、体内に有機酸がたまる病態）</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -2189,7 +2189,7 @@
         <v/>
       </c>
       <c r="I38" t="str">
-        <v>膵臓のインスリン分泌能低下（1型糖尿病、糖尿病の進行）</v>
+        <v/>
       </c>
       <c r="J38" t="str">
         <v/>
@@ -2198,13 +2198,13 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>インスリン分泌能の評価に使われる。数値が低いほどインスリン治療の必要性が高いと判断される目安になる</v>
+        <v>本来のアニオンギャップ(Na-(Cl+HCO3))の簡易代用として使われることがあるが、重炭酸(HCO3)を用いた計算の方が正確。メトホルミン使用中の乳酸アシドーシスが疑われる場面などで参考にする</v>
       </c>
       <c r="M38" t="str">
-        <v>糖尿病</v>
+        <v>電解質</v>
       </c>
       <c r="N38" t="str">
-        <v>C-ペプチド,Cペプチド,CPR,C-peptide,血中CPR,インスリン分泌</v>
+        <v>Na-Cl,アニオンギャップ,AG,代謝性アシドーシス,乳酸アシドーシス</v>
       </c>
       <c r="O38" t="str">
         <v/>
@@ -2212,46 +2212,46 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>C－ペプチドインデックス</v>
+        <v>AST/ALT比</v>
       </c>
       <c r="B39" t="str">
-        <v>CPI</v>
+        <v>AST/ALT,De Ritis比</v>
       </c>
       <c r="C39" t="str">
-        <v>1.2以上が目安(施設・測定条件により異なる)</v>
+        <v>1未満が目安（施設・病態により異なる）</v>
       </c>
       <c r="D39" t="str">
-        <v>血糖値に対してどれくらいインスリンを分泌できているかを表す指標。低いほどインスリン治療の必要性が高い</v>
+        <v>ASTとALTの比率（De Ritis比）。肝疾患の種類を推測する手がかりになる</v>
       </c>
       <c r="E39" t="str">
-        <v>これは、血糖値の高さに対して、体がどれくらいインスリンを作れているかを見る指標です。数値が低いほど、自分の膵臓だけでは血糖値に見合うインスリンを十分に作れていない可能性が高く、インスリン治療が必要かどうかの判断材料になります。</v>
+        <v>これは、肝臓に関わる2つの数値（ASTとALT）の比率を見るもので、肝臓のどのようなタイプのトラブルが起きているかを推測する手がかりになります。</v>
       </c>
       <c r="F39" t="str">
-        <v>通常、臨床的意義は乏しい</v>
+        <v>アルコール性肝障害、肝硬変、心筋梗塞・筋疾患の合併（比が2以上でアルコール性を強く示唆）</v>
       </c>
       <c r="G39" t="str">
-        <v/>
+        <v>飲酒量や頻度を確認する</v>
       </c>
       <c r="H39" t="str">
         <v/>
       </c>
       <c r="I39" t="str">
-        <v>内因性インスリン分泌能の低下(1.2未満でインスリン治療の適応を検討する目安、0.8未満はインスリン療法が強く推奨される目安)</v>
+        <v>急性ウイルス性肝炎、脂肪肝（比が1未満で肝細胞の急性障害を示唆することが多い）</v>
       </c>
       <c r="J39" t="str">
-        <v>インスリン治療の必要性について医師からどのように説明を受けているか確認する</v>
+        <v/>
       </c>
       <c r="K39" t="str">
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>CPI＝血中Cペプチド(ng/mL)÷血糖値(mg/dL)×100 で算出する。空腹時に測定するのが基本で、境界値付近では食事負荷の影響を受けるため、複数回の評価や随時尿中CPRとあわせて判断することもある</v>
+        <v>De Ritis比とも呼ばれる。比が2以上はアルコール性肝障害や肝硬変を、1未満は急性ウイルス性肝炎や脂肪肝を示唆する目安になるが、確定診断には他の検査所見と合わせた評価が必要</v>
       </c>
       <c r="M39" t="str">
-        <v>糖尿病</v>
+        <v>肝機能</v>
       </c>
       <c r="N39" t="str">
-        <v>CPI,Cペプチドインデックス,C-ペプチドインデックス,インスリン分泌能,インスリン治療</v>
+        <v>AST/ALT比,AST/ALT,De Ritis比,デリティス比,アルコール性肝障害,肝硬変</v>
       </c>
       <c r="O39" t="str">
         <v/>
@@ -2259,31 +2259,31 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>CONUT値</v>
+        <v>ALT/ALP比</v>
       </c>
       <c r="B40" t="str">
-        <v>CONUT</v>
+        <v>ALT比/ALP比,R比,R-factor</v>
       </c>
       <c r="C40" t="str">
-        <v>0〜1点：正常、2〜4点：軽度低栄養、5〜8点：中等度低栄養、9〜12点：高度低栄養</v>
+        <v>R値 5以上：肝細胞障害型、2以下：胆汁うっ滞型、2〜5：混合型</v>
       </c>
       <c r="D40" t="str">
-        <v>アルブミン・総リンパ球数・総コレステロールの3項目から算出する栄養状態の評価スコア</v>
+        <v>薬剤性肝障害(DILI)などで、肝障害のパターンを「肝細胞障害型」か「胆汁うっ滞型」かに分類するための指標(R値)</v>
       </c>
       <c r="E40" t="str">
-        <v>CONUT値は、血液検査（アルブミン、リンパ球数、コレステロール）の結果から計算される、栄養状態を数値化したスコアです。点数が高いほど低栄養の状態が疑われます。</v>
+        <v>肝臓に関する数値はいくつかありますが、その組み合わせ方によって「肝臓の細胞自体が傷んでいるタイプ」か「胆汁の流れが悪くなっているタイプ」かをある程度見分けることができます。この指標はその判定に使われます。</v>
       </c>
       <c r="F40" t="str">
-        <v>低栄養状態（点数が高いほど重度）</v>
+        <v>R値5以上：肝細胞障害型（ウイルス性肝炎、薬剤性肝障害の肝細胞障害型、虚血性肝障害など）</v>
       </c>
       <c r="G40" t="str">
-        <v>食事摂取量や体重の変化を確認する。必要に応じて栄養補助食品の活用を提案する</v>
+        <v/>
       </c>
       <c r="H40" t="str">
         <v/>
       </c>
       <c r="I40" t="str">
-        <v/>
+        <v>R値2以下：胆汁うっ滞型（閉塞性黄疸、薬剤性肝障害の胆汁うっ滞型など）</v>
       </c>
       <c r="J40" t="str">
         <v/>
@@ -2292,45 +2292,45 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>アルブミン・総リンパ球数・総コレステロールの3項目それぞれに配点があり、合計点で評価する客観的栄養指標。フレイル・サルコペニアの評価やポリファーマシー対策の一環としての栄養状態把握に有用</v>
+        <v>R値＝(ALTの基準値上限に対する倍率)÷(ALPの基準値上限に対する倍率)で算出する。薬剤性肝障害(DILI)の病型分類(肝細胞障害型/胆汁うっ滞型/混合型)に用いられ、被疑薬の休薬・変更の判断材料になる</v>
       </c>
       <c r="M40" t="str">
-        <v/>
+        <v>肝機能</v>
       </c>
       <c r="N40" t="str">
-        <v>CONUT,CONUT値,栄養評価,低栄養,フレイル</v>
+        <v>ALT/ALP比,R値,R-factor,DILI,薬剤性肝障害</v>
       </c>
       <c r="O40" t="str">
-        <v>食事と栄養 p.240（フレイルQ108 低栄養や食事量の評価）</v>
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>乳び</v>
+        <v>BNP</v>
       </c>
       <c r="B41" t="str">
-        <v>乳び,Lipemia</v>
+        <v>BNP</v>
       </c>
       <c r="C41" t="str">
-        <v>所見なし（血清が白濁していなければ正常）</v>
+        <v>18.4 pg/mL以下</v>
       </c>
       <c r="D41" t="str">
-        <v>中性脂肪が非常に多いため、血清が白く濁って見える状態。検査値そのものではなく検体の外観所見</v>
+        <v>心臓が無理をしているときに出る物質。心臓は血液を送るポンプだが、負担がかかると「少し助けてほしい」というサインとしてBNPを血液中に出す。</v>
       </c>
       <c r="E41" t="str">
-        <v>乳びとは、血液中の中性脂肪が非常に多いために、採血した血液（血清）が白く濁って見える状態のことです。多くの場合、食後の採血や、著しい脂質異常症が背景にあります。</v>
+        <v>この検査は、心臓がどれくらい頑張りすぎていないかを見るものです。数値が高いと、心臓に少し負担がかかっているサインになります。</v>
       </c>
       <c r="F41" t="str">
-        <v>著しい高中性脂肪血症、食後採血（一時的なもの）、原発性高カイロミクロン血症などの脂質代謝異常</v>
+        <v>心不全、心臓に負担がかかっている状態、体に水分がたまりやすいとき</v>
       </c>
       <c r="G41" t="str">
-        <v>採血が空腹時だったかを確認する。食後採血であれば次回は空腹時の再検を提案する</v>
+        <v>塩分・水分の摂りすぎに注意し、体重の変化を毎日記録するよう伝える。急な体重増加(2〜3日で2kg以上)や息切れの悪化があれば早めの受診を勧める</v>
       </c>
       <c r="H41" t="str">
         <v/>
       </c>
       <c r="I41" t="str">
-        <v/>
+        <v>心臓の負担は少ない状態</v>
       </c>
       <c r="J41" t="str">
         <v/>
@@ -2339,45 +2339,45 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>血清の白濁により一部の検査項目（電解質など）の測定値に誤差が出ることがある（偽性低ナトリウム血症など）。中性脂肪値と合わせて評価する</v>
+        <v>腎機能が低いとBNPは高めに出ることがある／数値だけで判断せず、症状と合わせて評価する／息切れ、むくみ、体重増加があれば要注意</v>
       </c>
       <c r="M41" t="str">
-        <v>脂質異常症</v>
+        <v>心不全</v>
       </c>
       <c r="N41" t="str">
-        <v>乳び,乳び血清,Lipemia,高中性脂肪血症</v>
+        <v>BNP,心不全,息切れ,むくみ</v>
       </c>
       <c r="O41" t="str">
-        <v/>
+        <v>食事と栄養 p.216-222（第2部 心疾患）</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>溶血</v>
+        <v>C－ペプチド（血中）</v>
       </c>
       <c r="B42" t="str">
-        <v>溶血,Hemolysis</v>
+        <v>CPR</v>
       </c>
       <c r="C42" t="str">
-        <v>所見なし（溶血を示唆する検査値異常がなければ正常）</v>
+        <v>空腹時 0.6〜3.0 ng/mL（施設差あり）</v>
       </c>
       <c r="D42" t="str">
-        <v>赤血球が通常より早く壊れる状態。単独の検査値ではなく、複数の検査値の組み合わせで疑う病態</v>
+        <v>自分の膵臓がどれくらいインスリンを作れているかを表す指標</v>
       </c>
       <c r="E42" t="str">
-        <v>溶血とは、赤血球が通常よりも早いペースで壊れてしまう状態のことです。壊れた赤血球からビリルビンなどが放出されるため、貧血や黄疸の原因になることがあります。</v>
+        <v>この検査は、ご自身の膵臓がどれくらいインスリンを作る力を持っているかを見るものです。数値が低いほど、体の中で作れるインスリンが少ないことを示します。</v>
       </c>
       <c r="F42" t="str">
-        <v>自己免疫性溶血性貧血、血液型不適合輸血、G6PD欠損症などの遺伝性疾患、機械弁など人工物による物理的破壊、薬剤性溶血</v>
+        <v>インスリン抵抗性が強い状態（初期の2型糖尿病など）</v>
       </c>
       <c r="G42" t="str">
-        <v>倦怠感、黄疸、尿の色が濃くなるなどの症状がないか確認する</v>
+        <v/>
       </c>
       <c r="H42" t="str">
         <v/>
       </c>
       <c r="I42" t="str">
-        <v/>
+        <v>膵臓のインスリン分泌能低下（1型糖尿病、糖尿病の進行）</v>
       </c>
       <c r="J42" t="str">
         <v/>
@@ -2386,13 +2386,13 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>溶血を疑う際は、間接ビリルビン上昇・LDH上昇・ハプトグロビン低下・網状赤血球増加のパターンを確認する。ヘモグロビン・MCV・MCHCの変化と合わせて総合的に判断する</v>
+        <v>インスリン分泌能の評価に使われる。数値が低いほどインスリン治療の必要性が高いと判断される目安になる</v>
       </c>
       <c r="M42" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>糖尿病</v>
       </c>
       <c r="N42" t="str">
-        <v>溶血,Hemolysis,溶血性貧血,G6PD,ハプトグロビン</v>
+        <v>C-ペプチド,Cペプチド,CPR,C-peptide,血中CPR,インスリン分泌</v>
       </c>
       <c r="O42" t="str">
         <v/>
@@ -2400,46 +2400,46 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>黄疸</v>
+        <v>C－ペプチドインデックス</v>
       </c>
       <c r="B43" t="str">
-        <v>黄疸,Jaundice</v>
+        <v>CPI</v>
       </c>
       <c r="C43" t="str">
-        <v>所見なし（皮膚・眼球結膜の黄染がなければ正常）</v>
+        <v>1.2以上が目安(施設・測定条件により異なる)</v>
       </c>
       <c r="D43" t="str">
-        <v>ビリルビンが体にたまり、皮膚や白目が黄色くなる状態。単独の検査値ではなく、ビリルビン上昇によって表れる身体所見</v>
+        <v>血糖値に対してどれくらいインスリンを分泌できているかを表す指標。低いほどインスリン治療の必要性が高い</v>
       </c>
       <c r="E43" t="str">
-        <v>黄疸は、体の中にビリルビンという黄色い色素がたまることで、皮膚や白目が黄色く見える状態です。肝臓や胆道のトラブル、赤血球が壊れやすくなる病気（溶血）などが原因となります。</v>
+        <v>これは、血糖値の高さに対して、体がどれくらいインスリンを作れているかを見る指標です。数値が低いほど、自分の膵臓だけでは血糖値に見合うインスリンを十分に作れていない可能性が高く、インスリン治療が必要かどうかの判断材料になります。</v>
       </c>
       <c r="F43" t="str">
-        <v>肝炎・肝硬変などの肝疾患、胆石・腫瘍による胆道閉塞、溶血性疾患、体質性黄疸（ジルベール症候群）、新生児黄疸</v>
+        <v>通常、臨床的意義は乏しい</v>
       </c>
       <c r="G43" t="str">
-        <v>白目や皮膚の黄染に気づいたら、尿の色（濃い茶色）や便の色（白っぽい）の変化も確認し、早めの受診を勧める</v>
+        <v/>
       </c>
       <c r="H43" t="str">
         <v/>
       </c>
       <c r="I43" t="str">
-        <v/>
+        <v>内因性インスリン分泌能の低下(1.2未満でインスリン治療の適応を検討する目安、0.8未満はインスリン療法が強く推奨される目安)</v>
       </c>
       <c r="J43" t="str">
-        <v/>
+        <v>インスリン治療の必要性について医師からどのように説明を受けているか確認する</v>
       </c>
       <c r="K43" t="str">
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>黄疸は検査値そのものではなく身体所見。原因を調べる際は総ビリルビン・直接ビリルビン・間接ビリルビンの内訳とAST/ALT/γ-GTPを確認する。直接優位なら胆道系、間接優位なら溶血・体質性を疑う</v>
+        <v>CPI＝血中Cペプチド(ng/mL)÷血糖値(mg/dL)×100 で算出する。空腹時に測定するのが基本で、境界値付近では食事負荷の影響を受けるため、複数回の評価や随時尿中CPRとあわせて判断することもある</v>
       </c>
       <c r="M43" t="str">
-        <v>肝機能</v>
+        <v>糖尿病</v>
       </c>
       <c r="N43" t="str">
-        <v>黄疸,ジョンダイス,Jaundice,ビリルビン,皮膚黄染,白目</v>
+        <v>CPI,Cペプチドインデックス,C-ペプチドインデックス,インスリン分泌能,インスリン治療</v>
       </c>
       <c r="O43" t="str">
         <v/>
@@ -2447,140 +2447,140 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>甲状腺刺激ホルモン（TSH）</v>
+        <v>CONUT値</v>
       </c>
       <c r="B44" t="str">
-        <v>TSH</v>
+        <v>CONUT</v>
       </c>
       <c r="C44" t="str">
-        <v>0.5〜5.0 μIU/mL程度（施設差あり）</v>
+        <v>0〜1点：正常、2〜4点：軽度低栄養、5〜8点：中等度低栄養、9〜12点：高度低栄養</v>
       </c>
       <c r="D44" t="str">
-        <v>甲状腺の働きが多いか少ないかを最も敏感に反映するホルモン</v>
+        <v>アルブミン・総リンパ球数・総コレステロールの3項目から算出する栄養状態の評価スコア</v>
       </c>
       <c r="E44" t="str">
-        <v>TSHは脳の下垂体から出て、甲状腺に「もっと働いて」と指令を送るホルモンです。甲状腺の働きが弱っていると体が指令を強めるためTSHは上がり、逆に甲状腺が働きすぎているとTSHは下がります。甲状腺の状態を最初に確認する数値としてよく使われます。</v>
+        <v>CONUT値は、血液検査（アルブミン、リンパ球数、コレステロール）の結果から計算される、栄養状態を数値化したスコアです。点数が高いほど低栄養の状態が疑われます。</v>
       </c>
       <c r="F44" t="str">
-        <v>甲状腺機能低下症（橋本病など）、チラーヂンSなど甲状腺ホルモン薬の量不足</v>
+        <v>低栄養状態（点数が高いほど重度）</v>
       </c>
       <c r="G44" t="str">
-        <v>だるさ、むくみ、体重増加、寒がりなどの症状がないか確認する。服薬状況（飲み忘れ、他の薬との飲み合わせ）を確認する</v>
+        <v>食事摂取量や体重の変化を確認する。必要に応じて栄養補助食品の活用を提案する</v>
       </c>
       <c r="H44" t="str">
-        <v>アミオダロン、炭酸リチウム、インターフェロン製剤、チロシンキナーゼ阻害薬(スニチニブ等)</v>
+        <v/>
       </c>
       <c r="I44" t="str">
-        <v>甲状腺機能亢進症（バセドウ病など）、チラーヂンSなど甲状腺ホルモン薬の過量</v>
+        <v/>
       </c>
       <c r="J44" t="str">
-        <v>動悸、体重減少、暑がり、手のふるえなどの症状がないか確認する</v>
+        <v/>
       </c>
       <c r="K44" t="str">
-        <v>レボチロキシンの過量投与</v>
+        <v/>
       </c>
       <c r="L44" t="str">
-        <v>チラーヂンS服用中はTSHが治療目標域に収まっているかで用量調整の目安にする。メルカゾール服用中はTSH・FT4に加えて無顆粒球症の初期症状（発熱・のどの痛み）の有無や白血球数も確認する</v>
+        <v>アルブミン・総リンパ球数・総コレステロールの3項目それぞれに配点があり、合計点で評価する客観的栄養指標。フレイル・サルコペニアの評価やポリファーマシー対策の一環としての栄養状態把握に有用</v>
       </c>
       <c r="M44" t="str">
-        <v>甲状腺疾患</v>
+        <v/>
       </c>
       <c r="N44" t="str">
-        <v>TSH,甲状腺刺激ホルモン,甲状腺機能,橋本病,バセドウ病,チラーヂン,メルカゾール</v>
+        <v>CONUT,CONUT値,栄養評価,低栄養,フレイル</v>
       </c>
       <c r="O44" t="str">
-        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
+        <v>食事と栄養 p.240（フレイルQ108 低栄養や食事量の評価）</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>遊離サイロキシン（FT4）</v>
+        <v>マグネシウム（Mg）</v>
       </c>
       <c r="B45" t="str">
-        <v>FT4</v>
+        <v>Mg</v>
       </c>
       <c r="C45" t="str">
-        <v>0.9〜1.7 ng/dL程度（施設差あり）</v>
+        <v>1.8〜2.6 mg/dL程度（施設差あり）</v>
       </c>
       <c r="D45" t="str">
-        <v>甲状腺が実際に分泌しているホルモンの量そのものを表す数値</v>
+        <v>骨や筋肉、神経の働きに関わるミネラル。低栄養や利尿薬で不足しやすい</v>
       </c>
       <c r="E45" t="str">
-        <v>FT4は甲状腺そのものが作っているホルモンの量です。TSHが「指令の強さ」だとすると、FT4は「実際に出ている量」にあたります。2つをあわせて見ることで、甲状腺の働きが今どういう状態かを詳しく判断できます。</v>
+        <v>マグネシウムは、骨や筋肉、神経の働きを支えるミネラルです。不足すると、こむら返りや不整脈、だるさなどの症状が出ることがあります。</v>
       </c>
       <c r="F45" t="str">
-        <v>甲状腺機能亢進症（バセドウ病など）</v>
+        <v>腎不全、マグネシウム製剤（酸化マグネシウムなど）の過量投与</v>
       </c>
       <c r="G45" t="str">
-        <v>動悸、体重減少、暑がり、手のふるえなどの症状がないか確認する</v>
+        <v>腎機能低下がある患者で酸化マグネシウムなどの緩下剤を使用中は、傾眠・血圧低下などの高マグネシウム血症の症状がないか確認する</v>
       </c>
       <c r="H45" t="str">
-        <v>レボチロキシンの過量投与、アミオダロン</v>
+        <v>マグネシウム含有制酸薬・下剤の過量(特に腎機能低下患者)</v>
       </c>
       <c r="I45" t="str">
-        <v>甲状腺機能低下症（橋本病など）</v>
+        <v>低栄養、利尿薬の使用、慢性的な下痢、アルコール多飲、PPI長期使用</v>
       </c>
       <c r="J45" t="str">
-        <v>だるさ、むくみ、体重増加、寒がりなどの症状がないか確認する</v>
+        <v>こむら返りや動悸などの症状がないか確認する</v>
       </c>
       <c r="K45" t="str">
-        <v>抗甲状腺薬(メルカゾール、プロパジール)の効きすぎ</v>
+        <v>プロトンポンプ阻害薬(PPI)の長期使用、ループ利尿薬、サイアザイド系利尿薬、シスプラチン、アミノグリコシド系</v>
       </c>
       <c r="L45" t="str">
-        <v>TSHと逆方向に動くのが基本だが、下垂体性の異常など例外もある。TSHと合わせて評価し、片方だけで判断しない</v>
+        <v>腎機能低下患者への酸化マグネシウム投与は高マグネシウム血症のリスクがあるため定期的なモニタリングが必要。PPI長期使用も低マグネシウム血症のリスク因子として知られる</v>
       </c>
       <c r="M45" t="str">
-        <v>甲状腺疾患</v>
+        <v>腎機能</v>
       </c>
       <c r="N45" t="str">
-        <v>FT4,遊離サイロキシン,甲状腺ホルモン,甲状腺機能</v>
+        <v>マグネシウム,Mg,酸化マグネシウム,こむら返り</v>
       </c>
       <c r="O45" t="str">
-        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
+        <v>食事と栄養 p.84（マグネシウム）</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>白血球数（WBC）</v>
+        <v>乳び</v>
       </c>
       <c r="B46" t="str">
-        <v>WBC</v>
+        <v>乳び,Lipemia</v>
       </c>
       <c r="C46" t="str">
-        <v>3,300〜8,600 /μL程度（施設差あり）</v>
+        <v>所見なし（血清が白濁していなければ正常）</v>
       </c>
       <c r="D46" t="str">
-        <v>体を細菌やウイルスから守る免疫細胞の数で、感染や炎症、薬剤の影響を反映する</v>
+        <v>中性脂肪が非常に多いため、血清が白く濁って見える状態。検査値そのものではなく検体の外観所見</v>
       </c>
       <c r="E46" t="str">
-        <v>白血球は体に入ってきた細菌やウイルスと戦う免疫細胞です。感染症や炎症があると増え、逆に一部のお薬の副作用や骨髄の働きが落ちると減ることがあります。</v>
+        <v>乳びとは、血液中の中性脂肪が非常に多いために、採血した血液（血清）が白く濁って見える状態のことです。多くの場合、食後の採血や、著しい脂質異常症が背景にあります。</v>
       </c>
       <c r="F46" t="str">
-        <v>感染症、炎症、ステロイド使用、喫煙、白血病などの血液疾患</v>
+        <v>著しい高中性脂肪血症、食後採血（一時的なもの）、原発性高カイロミクロン血症などの脂質代謝異常</v>
       </c>
       <c r="G46" t="str">
-        <v>発熱や体の痛みなど感染症状がないか確認する</v>
+        <v>採血が空腹時だったかを確認する。食後採血であれば次回は空腹時の再検を提案する</v>
       </c>
       <c r="H46" t="str">
-        <v>ステロイド、G-CSF製剤、炭酸リチウム</v>
+        <v/>
       </c>
       <c r="I46" t="str">
-        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、メルカゾールなど薬剤性の無顆粒球症、再生不良性貧血、ウイルス感染</v>
+        <v/>
       </c>
       <c r="J46" t="str">
-        <v>発熱、のどの痛みなど感染症状の初期サインがないか確認する。人混みを避け、手洗い・うがいを徹底するよう伝える</v>
+        <v/>
       </c>
       <c r="K46" t="str">
-        <v>抗がん剤、メルカゾール(無顆粒球症)、クロザピン(定期的な血球モニタリング必須)、サラゾスルファピリジン</v>
+        <v/>
       </c>
       <c r="L46" t="str">
-        <v>メルカゾール（チアマゾール）は無顆粒球症の重大な副作用があり、発熱・のどの痛みが出たらすぐ受診するよう指導する。抗がん剤・免疫抑制剤・抗てんかん薬（カルバマゼピンなど）使用中も定期的なモニタリングが必要</v>
+        <v>血清の白濁により一部の検査項目（電解質など）の測定値に誤差が出ることがある（偽性低ナトリウム血症など）。中性脂肪値と合わせて評価する</v>
       </c>
       <c r="M46" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>脂質異常症</v>
       </c>
       <c r="N46" t="str">
-        <v>白血球,WBC,好中球,感染症,白血病,無顆粒球症,骨髄抑制</v>
+        <v>乳び,乳び血清,Lipemia,高中性脂肪血症</v>
       </c>
       <c r="O46" t="str">
         <v/>
@@ -2588,281 +2588,281 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>赤血球数</v>
+        <v>溶血</v>
       </c>
       <c r="B47" t="str">
-        <v>RBC</v>
+        <v>溶血,Hemolysis</v>
       </c>
       <c r="C47" t="str">
-        <v>男性 435〜555万/μL、女性 386〜492万/μL程度（施設差あり）</v>
+        <v>所見なし（溶血を示唆する検査値異常がなければ正常）</v>
       </c>
       <c r="D47" t="str">
-        <v>血液中で酸素を運ぶ細胞の数。ヘモグロビン・ヘマトクリットと合わせて貧血・多血症を評価する</v>
+        <v>赤血球が通常より早く壊れる状態。単独の検査値ではなく、複数の検査値の組み合わせで疑う病態</v>
       </c>
       <c r="E47" t="str">
-        <v>赤血球は、肺で受け取った酸素を全身に運ぶ血液の細胞です。数が少ないと貧血、多いと多血症が疑われます。ヘモグロビンやヘマトクリットと合わせて総合的に評価します。</v>
+        <v>溶血とは、赤血球が通常よりも早いペースで壊れてしまう状態のことです。壊れた赤血球からビリルビンなどが放出されるため、貧血や黄疸の原因になることがあります。</v>
       </c>
       <c r="F47" t="str">
-        <v>脱水、多血症（真性多血症、二次性多血症）、喫煙</v>
+        <v>自己免疫性溶血性貧血、血液型不適合輸血、G6PD欠損症などの遺伝性疾患、機械弁など人工物による物理的破壊、薬剤性溶血</v>
       </c>
       <c r="G47" t="str">
-        <v>脱水が疑われる場合はこまめな水分摂取を勧める（水分制限がある場合を除く）</v>
+        <v>倦怠感、黄疸、尿の色が濃くなるなどの症状がないか確認する</v>
       </c>
       <c r="H47" t="str">
         <v/>
       </c>
       <c r="I47" t="str">
-        <v>貧血（鉄欠乏性貧血、腎性貧血など）、出血</v>
+        <v/>
       </c>
       <c r="J47" t="str">
-        <v>ヘモグロビンと同様に、出血や食事量低下がないか確認する</v>
+        <v/>
       </c>
       <c r="K47" t="str">
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>ヘモグロビン・ヘマトクリットと同じ方向に動くことが多い。赤血球数だけでなくMCV・MCH・MCHCと合わせて貧血のタイプ(小球性・正球性・大球性)を判断する</v>
+        <v>溶血を疑う際は、間接ビリルビン上昇・LDH上昇・ハプトグロビン低下・網状赤血球増加のパターンを確認する。ヘモグロビン・MCV・MCHCの変化と合わせて総合的に判断する</v>
       </c>
       <c r="M47" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
       <c r="N47" t="str">
-        <v>赤血球,RBC,貧血,多血症</v>
+        <v>溶血,Hemolysis,溶血性貧血,G6PD,ハプトグロビン</v>
       </c>
       <c r="O47" t="str">
-        <v>食事と栄養 p.151-164（第2部 貧血）</v>
+        <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ヘモグロビン濃度</v>
+        <v>黄疸</v>
       </c>
       <c r="B48" t="str">
-        <v>Hb</v>
+        <v>黄疸,Jaundice</v>
       </c>
       <c r="C48" t="str">
-        <v>男性 13.5〜17.5 g/dL、女性 11.5〜15.0 g/dL</v>
+        <v>所見なし（皮膚・眼球結膜の黄染がなければ正常）</v>
       </c>
       <c r="D48" t="str">
-        <v>血液の中で酸素を運ぶ役割をしている。この値が低い状態が貧血。</v>
+        <v>ビリルビンが体にたまり、皮膚や白目が黄色くなる状態。単独の検査値ではなく、ビリルビン上昇によって表れる身体所見</v>
       </c>
       <c r="E48" t="str">
-        <v>ヘモグロビンは、血液の中で酸素を全身に運ぶ役割をしている赤い色素です。この値が低い状態が貧血で、体がだるくなったり、階段で息切れしやすくなったりします。</v>
+        <v>黄疸は、体の中にビリルビンという黄色い色素がたまることで、皮膚や白目が黄色く見える状態です。肝臓や胆道のトラブル、赤血球が壊れやすくなる病気（溶血）などが原因となります。</v>
       </c>
       <c r="F48" t="str">
-        <v/>
+        <v>肝炎・肝硬変などの肝疾患、胆石・腫瘍による胆道閉塞、溶血性疾患、体質性黄疸（ジルベール症候群）、新生児黄疸</v>
       </c>
       <c r="G48" t="str">
-        <v/>
+        <v>白目や皮膚の黄染に気づいたら、尿の色（濃い茶色）や便の色（白っぽい）の変化も確認し、早めの受診を勧める</v>
       </c>
       <c r="H48" t="str">
         <v/>
       </c>
       <c r="I48" t="str">
-        <v>鉄欠乏性貧血、出血、腎性貧血、骨髄の造血機能低下</v>
+        <v/>
       </c>
       <c r="J48" t="str">
-        <v>鉄分の多い食品(レバー・赤身肉・魚・ほうれん草など)を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える。鉄剤は数値が正常化した後も体内に鉄を貯蔵するため2〜3か月程度は継続が必要なことを説明する</v>
+        <v/>
       </c>
       <c r="K48" t="str">
-        <v>NSAIDs・抗凝固薬・抗血小板薬(消化管出血のリスク)、抗がん剤、ST合剤</v>
+        <v/>
       </c>
       <c r="L48" t="str">
-        <v>原因（出血・食事量低下など）の確認が重要。腎機能低下がある場合は鉄不足以外が原因のこともある。鉄剤はヘモグロビンが正常化した後も2〜3か月程度は継続することが多い（鉄の貯蔵分を補うため。途中でやめると再び貧血になりやすい）</v>
+        <v>黄疸は検査値そのものではなく身体所見。原因を調べる際は総ビリルビン・直接ビリルビン・間接ビリルビンの内訳とAST/ALT/γ-GTPを確認する。直接優位なら胆道系、間接優位なら溶血・体質性を疑う</v>
       </c>
       <c r="M48" t="str">
-        <v>鉄欠乏性貧血,抗血小板療法,抗凝固療法（心房細動・血栓症）</v>
+        <v>肝機能</v>
       </c>
       <c r="N48" t="str">
-        <v>ヘモグロビン,Hb,貧血,鉄剤,鉄欠乏性貧血</v>
+        <v>黄疸,ジョンダイス,Jaundice,ビリルビン,皮膚黄染,白目</v>
       </c>
       <c r="O48" t="str">
-        <v>食事と栄養 p.151-164（第2部 貧血）</v>
+        <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ヘマトクリット値</v>
+        <v>甲状腺刺激ホルモン（TSH）</v>
       </c>
       <c r="B49" t="str">
-        <v>Ht,Hct</v>
+        <v>TSH</v>
       </c>
       <c r="C49" t="str">
-        <v>男性 40〜50%、女性 35〜45%</v>
+        <v>0.5〜5.0 μIU/mL程度（施設差あり）</v>
       </c>
       <c r="D49" t="str">
-        <v>血液全体のうち赤血球が占める体積の割合。貧血・脱水の指標</v>
+        <v>甲状腺の働きが多いか少ないかを最も敏感に反映するホルモン</v>
       </c>
       <c r="E49" t="str">
-        <v>ヘマトクリットは、血液全体のうち赤血球が占める割合を表す数値です。この値が低いと貧血、高いと脱水や血液が濃くなっている状態が疑われます。</v>
+        <v>TSHは脳の下垂体から出て、甲状腺に「もっと働いて」と指令を送るホルモンです。甲状腺の働きが弱っていると体が指令を強めるためTSHは上がり、逆に甲状腺が働きすぎているとTSHは下がります。甲状腺の状態を最初に確認する数値としてよく使われます。</v>
       </c>
       <c r="F49" t="str">
-        <v>脱水、多血症（真性多血症、二次性多血症）、喫煙</v>
+        <v>甲状腺機能低下症（橋本病など）、チラーヂンSなど甲状腺ホルモン薬の量不足</v>
       </c>
       <c r="G49" t="str">
-        <v>脱水が疑われる場合はこまめな水分摂取を勧める（水分制限がある場合を除く）</v>
+        <v>だるさ、むくみ、体重増加、寒がりなどの症状がないか確認する。服薬状況（飲み忘れ、他の薬との飲み合わせ）を確認する</v>
       </c>
       <c r="H49" t="str">
-        <v/>
+        <v>アミオダロン、炭酸リチウム、インターフェロン製剤、チロシンキナーゼ阻害薬(スニチニブ等)</v>
       </c>
       <c r="I49" t="str">
-        <v>貧血（鉄欠乏性貧血、腎性貧血など）、出血</v>
+        <v>甲状腺機能亢進症（バセドウ病など）、チラーヂンSなど甲状腺ホルモン薬の過量</v>
       </c>
       <c r="J49" t="str">
-        <v>ヘモグロビンと同様に、出血や食事量低下がないか確認する</v>
+        <v>動悸、体重減少、暑がり、手のふるえなどの症状がないか確認する</v>
       </c>
       <c r="K49" t="str">
-        <v/>
+        <v>レボチロキシンの過量投与</v>
       </c>
       <c r="L49" t="str">
-        <v>ヘモグロビン・赤血球数と合わせて評価する。3つの値は同じ方向に動くことが多く、脱水があると貧血が見かけ上隠れることがある</v>
+        <v>チラーヂンS服用中はTSHが治療目標域に収まっているかで用量調整の目安にする。メルカゾール服用中はTSH・FT4に加えて無顆粒球症の初期症状（発熱・のどの痛み）の有無や白血球数も確認する</v>
       </c>
       <c r="M49" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>甲状腺疾患</v>
       </c>
       <c r="N49" t="str">
-        <v>ヘマトクリット,Ht,Hct,貧血,脱水,多血症</v>
+        <v>TSH,甲状腺刺激ホルモン,甲状腺機能,橋本病,バセドウ病,チラーヂン,メルカゾール</v>
       </c>
       <c r="O49" t="str">
-        <v>食事と栄養 p.151-164（第2部 貧血）</v>
+        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>MCV</v>
+        <v>遊離サイロキシン（FT4）</v>
       </c>
       <c r="B50" t="str">
-        <v>MCV</v>
+        <v>FT4</v>
       </c>
       <c r="C50" t="str">
-        <v>79〜100 fL</v>
+        <v>0.9〜1.7 ng/dL程度（施設差あり）</v>
       </c>
       <c r="D50" t="str">
-        <v>赤血球1個の大きさ</v>
+        <v>甲状腺が実際に分泌しているホルモンの量そのものを表す数値</v>
       </c>
       <c r="E50" t="str">
-        <v>MCVは赤血球1個あたりの大きさを表す数値です。貧血があるとき、この数値で「小さい貧血」か「大きい貧血」かを見分けることができ、原因を絞り込む手がかりになります。</v>
+        <v>FT4は甲状腺そのものが作っているホルモンの量です。TSHが「指令の強さ」だとすると、FT4は「実際に出ている量」にあたります。2つをあわせて見ることで、甲状腺の働きが今どういう状態かを詳しく判断できます。</v>
       </c>
       <c r="F50" t="str">
-        <v/>
+        <v>甲状腺機能亢進症（バセドウ病など）</v>
       </c>
       <c r="G50" t="str">
-        <v/>
+        <v>動悸、体重減少、暑がり、手のふるえなどの症状がないか確認する</v>
       </c>
       <c r="H50" t="str">
-        <v/>
+        <v>レボチロキシンの過量投与、アミオダロン</v>
       </c>
       <c r="I50" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>甲状腺機能低下症（橋本病など）</v>
       </c>
       <c r="J50" t="str">
-        <v>鉄分の多い食品(レバー・赤身肉・魚・ほうれん草など)と、吸収を助けるビタミンC(柑橘類・芋類等)を一緒に摂るよう伝える</v>
+        <v>だるさ、むくみ、体重増加、寒がりなどの症状がないか確認する</v>
       </c>
       <c r="K50" t="str">
-        <v/>
+        <v>抗甲状腺薬(メルカゾール、プロパジール)の効きすぎ</v>
       </c>
       <c r="L50" t="str">
-        <v/>
+        <v>TSHと逆方向に動くのが基本だが、下垂体性の異常など例外もある。TSHと合わせて評価し、片方だけで判断しない</v>
       </c>
       <c r="M50" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>甲状腺疾患</v>
       </c>
       <c r="N50" t="str">
-        <v>MCV,赤血球指数,貧血</v>
+        <v>FT4,遊離サイロキシン,甲状腺ホルモン,甲状腺機能</v>
       </c>
       <c r="O50" t="str">
-        <v>食事と栄養 p.151-164（第2部 貧血）</v>
+        <v>食事と栄養 p.224-228（第2部 甲状腺疾患）</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>MCH</v>
+        <v>白血球数（WBC）</v>
       </c>
       <c r="B51" t="str">
-        <v>MCH</v>
+        <v>WBC</v>
       </c>
       <c r="C51" t="str">
-        <v>26.3〜34.3 pg</v>
+        <v>3,300〜8,600 /μL程度（施設差あり）</v>
       </c>
       <c r="D51" t="str">
-        <v>赤血球1個に含まれるヘモグロビン量</v>
+        <v>体を細菌やウイルスから守る免疫細胞の数で、感染や炎症、薬剤の影響を反映する</v>
       </c>
       <c r="E51" t="str">
-        <v>MCHは赤血球1個の中に含まれるヘモグロビン（酸素を運ぶ色素）の量を表す数値です。MCVと同じく、貧血の種類を見分けるのに使われます。</v>
+        <v>白血球は体に入ってきた細菌やウイルスと戦う免疫細胞です。感染症や炎症があると増え、逆に一部のお薬の副作用や骨髄の働きが落ちると減ることがあります。</v>
       </c>
       <c r="F51" t="str">
-        <v/>
+        <v>感染症、炎症、ステロイド使用、喫煙、白血病などの血液疾患</v>
       </c>
       <c r="G51" t="str">
-        <v/>
+        <v>発熱や体の痛みなど感染症状がないか確認する</v>
       </c>
       <c r="H51" t="str">
-        <v/>
+        <v>ステロイド、G-CSF製剤、炭酸リチウム</v>
       </c>
       <c r="I51" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、メルカゾールなど薬剤性の無顆粒球症、再生不良性貧血、ウイルス感染</v>
       </c>
       <c r="J51" t="str">
-        <v>鉄分の多い食品(レバー・赤身肉・魚・ほうれん草など)と、吸収を助けるビタミンC(柑橘類・芋類等)を一緒に摂るよう伝える</v>
+        <v>発熱、のどの痛みなど感染症状の初期サインがないか確認する。人混みを避け、手洗い・うがいを徹底するよう伝える</v>
       </c>
       <c r="K51" t="str">
-        <v/>
+        <v>抗がん剤、メルカゾール(無顆粒球症)、クロザピン(定期的な血球モニタリング必須)、サラゾスルファピリジン</v>
       </c>
       <c r="L51" t="str">
-        <v/>
+        <v>メルカゾール（チアマゾール）は無顆粒球症の重大な副作用があり、発熱・のどの痛みが出たらすぐ受診するよう指導する。抗がん剤・免疫抑制剤・抗てんかん薬（カルバマゼピンなど）使用中も定期的なモニタリングが必要</v>
       </c>
       <c r="M51" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N51" t="str">
-        <v>MCH,赤血球指数,貧血</v>
+        <v>白血球,WBC,好中球,感染症,白血病,無顆粒球症,骨髄抑制</v>
       </c>
       <c r="O51" t="str">
-        <v>食事と栄養 p.151-164（第2部 貧血）</v>
+        <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>MCHC</v>
+        <v>赤血球数</v>
       </c>
       <c r="B52" t="str">
-        <v>MCHC</v>
+        <v>RBC</v>
       </c>
       <c r="C52" t="str">
-        <v>31.6〜36.6 %</v>
+        <v>男性 435〜555万/μL、女性 386〜492万/μL程度（施設差あり）</v>
       </c>
       <c r="D52" t="str">
-        <v>単位容積あたりの赤血球に含まれるヘモグロビン濃度</v>
+        <v>血液中で酸素を運ぶ細胞の数。ヘモグロビン・ヘマトクリットと合わせて貧血・多血症を評価する</v>
       </c>
       <c r="E52" t="str">
-        <v>MCHCは、赤血球の中にヘモグロビンがどれくらい濃く詰まっているかを表す数値です。鉄が不足すると、この濃度も薄くなる傾向があります。</v>
+        <v>赤血球は、肺で受け取った酸素を全身に運ぶ血液の細胞です。数が少ないと貧血、多いと多血症が疑われます。ヘモグロビンやヘマトクリットと合わせて総合的に評価します。</v>
       </c>
       <c r="F52" t="str">
-        <v/>
+        <v>脱水、多血症（真性多血症、二次性多血症）、喫煙</v>
       </c>
       <c r="G52" t="str">
-        <v/>
+        <v>脱水が疑われる場合はこまめな水分摂取を勧める（水分制限がある場合を除く）</v>
       </c>
       <c r="H52" t="str">
         <v/>
       </c>
       <c r="I52" t="str">
-        <v>鉄欠乏性貧血</v>
+        <v>貧血（鉄欠乏性貧血、腎性貧血など）、出血</v>
       </c>
       <c r="J52" t="str">
-        <v>鉄分の多い食品(レバー・赤身肉・魚・ほうれん草など)と、吸収を助けるビタミンC(柑橘類・芋類等)を一緒に摂るよう伝える</v>
+        <v>ヘモグロビンと同様に、出血や食事量低下がないか確認する</v>
       </c>
       <c r="K52" t="str">
         <v/>
       </c>
       <c r="L52" t="str">
-        <v/>
+        <v>ヘモグロビン・ヘマトクリットと同じ方向に動くことが多い。赤血球数だけでなくMCV・MCH・MCHCと合わせて貧血のタイプ(小球性・正球性・大球性)を判断する</v>
       </c>
       <c r="M52" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
       <c r="N52" t="str">
-        <v>MCHC,赤血球指数,貧血</v>
+        <v>赤血球,RBC,貧血,多血症</v>
       </c>
       <c r="O52" t="str">
         <v>食事と栄養 p.151-164（第2部 貧血）</v>
@@ -2870,93 +2870,93 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>血小板数</v>
+        <v>ヘモグロビン濃度</v>
       </c>
       <c r="B53" t="str">
-        <v>Plt</v>
+        <v>Hb</v>
       </c>
       <c r="C53" t="str">
-        <v>15.0〜35.0万/μL程度（施設差あり）</v>
+        <v>男性 13.5〜17.5 g/dL、女性 11.5〜15.0 g/dL</v>
       </c>
       <c r="D53" t="str">
-        <v>出血を止める働きをする血液成分で、少なすぎると出血しやすくなる</v>
+        <v>血液の中で酸素を運ぶ役割をしている。この値が低い状態が貧血。</v>
       </c>
       <c r="E53" t="str">
-        <v>血小板は、血管が傷ついたときに集まって血を止める役割をする血液の成分です。数が少ないとあざができやすくなったり、出血が止まりにくくなったりします。抗血小板薬や抗がん剤を使っている方では、定期的にチェックすることが大切です。</v>
+        <v>ヘモグロビンは、血液の中で酸素を全身に運ぶ役割をしている赤い色素です。この値が低い状態が貧血で、体がだるくなったり、階段で息切れしやすくなったりします。</v>
       </c>
       <c r="F53" t="str">
-        <v>炎症性疾患、鉄欠乏性貧血、脾摘後、骨髄増殖性疾患</v>
+        <v/>
       </c>
       <c r="G53" t="str">
-        <v>出血傾向はなく経過観察でよいことが多いが、片側の腫れ・しびれなど血栓症状がないかも念のため確認する</v>
+        <v/>
       </c>
       <c r="H53" t="str">
         <v/>
       </c>
       <c r="I53" t="str">
-        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、肝硬変・脾機能亢進、再生不良性貧血、抗てんかん薬（バルプロ酸など）の副作用、ITP（特発性血小板減少性紫斑病）</v>
+        <v>鉄欠乏性貧血、出血、腎性貧血、骨髄の造血機能低下</v>
       </c>
       <c r="J53" t="str">
-        <v>あざができやすい、歯ぐきや鼻からの出血が増えていないか確認する。強い運動や転倒によるけがに注意するよう伝え、歯みがきは柔らかめのブラシを勧める</v>
+        <v>鉄分の多い食品(レバー・赤身肉・魚・ほうれん草など)を意識し、吸収を助けるビタミンCと一緒に摂るとよいことを伝える。鉄剤は数値が正常化した後も体内に鉄を貯蔵するため2〜3か月程度は継続が必要なことを説明する</v>
       </c>
       <c r="K53" t="str">
-        <v>ヘパリン(HIT: ヘパリン起因性血小板減少症)、バルプロ酸、抗がん剤、リネゾリド</v>
+        <v>NSAIDs・抗凝固薬・抗血小板薬(消化管出血のリスク)、抗がん剤、ST合剤</v>
       </c>
       <c r="L53" t="str">
-        <v>抗血小板薬・抗凝固薬使用中に血小板減少があると出血リスクがさらに高まる。抗がん剤・バルプロ酸・カルバマゼピンなど骨髄抑制のリスクがある薬剤使用中は定期採血の実施状況を確認する</v>
+        <v>原因（出血・食事量低下など）の確認が重要。腎機能低下がある場合は鉄不足以外が原因のこともある。鉄剤はヘモグロビンが正常化した後も2〜3か月程度は継続することが多い（鉄の貯蔵分を補うため。途中でやめると再び貧血になりやすい）</v>
       </c>
       <c r="M53" t="str">
-        <v>てんかん,抗血小板療法</v>
+        <v>鉄欠乏性貧血,抗血小板療法,抗凝固療法（心房細動・血栓症）</v>
       </c>
       <c r="N53" t="str">
-        <v>血小板,Plt,platelet,出血,あざ,紫斑,骨髄抑制</v>
+        <v>ヘモグロビン,Hb,貧血,鉄剤,鉄欠乏性貧血</v>
       </c>
       <c r="O53" t="str">
-        <v/>
+        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>RDW-SD</v>
+        <v>ヘマトクリット値</v>
       </c>
       <c r="B54" t="str">
-        <v>RDW-SD</v>
+        <v>Ht,Hct</v>
       </c>
       <c r="C54" t="str">
-        <v>39〜46 fL程度（施設差あり）</v>
+        <v>男性 40〜50%、女性 35〜45%</v>
       </c>
       <c r="D54" t="str">
-        <v>赤血球の大きさのばらつきを表す指標(絶対値)。鉄欠乏性貧血などの初期変化を捉えやすい</v>
+        <v>血液全体のうち赤血球が占める体積の割合。貧血・脱水の指標</v>
       </c>
       <c r="E54" t="str">
-        <v>RDW-SDは、赤血球の大きさがどれくらいバラバラになっているかを表す数値です。貧血の原因を調べる際、鉄が足りなくなり始めた早い段階での変化を捉えるのに役立ちます。</v>
+        <v>ヘマトクリットは、血液全体のうち赤血球が占める割合を表す数値です。この値が低いと貧血、高いと脱水や血液が濃くなっている状態が疑われます。</v>
       </c>
       <c r="F54" t="str">
-        <v>鉄欠乏性貧血の初期、混合性貧血（複数の原因が重なっている状態）、赤血球産生の乱れ</v>
+        <v>脱水、多血症（真性多血症、二次性多血症）、喫煙</v>
       </c>
       <c r="G54" t="str">
-        <v/>
+        <v>脱水が疑われる場合はこまめな水分摂取を勧める（水分制限がある場合を除く）</v>
       </c>
       <c r="H54" t="str">
         <v/>
       </c>
       <c r="I54" t="str">
-        <v/>
+        <v>貧血（鉄欠乏性貧血、腎性貧血など）、出血</v>
       </c>
       <c r="J54" t="str">
-        <v/>
+        <v>ヘモグロビンと同様に、出血や食事量低下がないか確認する</v>
       </c>
       <c r="K54" t="str">
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>MCVが正常範囲でもRDWが上昇している場合、鉄欠乏の初期段階を示唆することがある。MCV・MCHと合わせて評価する</v>
+        <v>ヘモグロビン・赤血球数と合わせて評価する。3つの値は同じ方向に動くことが多く、脱水があると貧血が見かけ上隠れることがある</v>
       </c>
       <c r="M54" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
       <c r="N54" t="str">
-        <v>RDW-SD,赤血球分布幅,貧血,鉄欠乏</v>
+        <v>ヘマトクリット,Ht,Hct,貧血,脱水,多血症</v>
       </c>
       <c r="O54" t="str">
         <v>食事と栄養 p.151-164（第2部 貧血）</v>
@@ -2964,22 +2964,22 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>RDW-CV</v>
+        <v>MCV</v>
       </c>
       <c r="B55" t="str">
-        <v>RDW-CV</v>
+        <v>MCV</v>
       </c>
       <c r="C55" t="str">
-        <v>11.5〜14.5%程度（施設差あり）</v>
+        <v>79〜100 fL</v>
       </c>
       <c r="D55" t="str">
-        <v>赤血球の大きさのばらつきを割合(%)で表した指標</v>
+        <v>赤血球1個の大きさ</v>
       </c>
       <c r="E55" t="str">
-        <v>RDW-CVもRDW-SDと同じく、赤血球の大きさのばらつきを表す数値ですが、こちらは割合(%)で示されます。貧血のタイプを見分ける手がかりになります。</v>
+        <v>MCVは赤血球1個あたりの大きさを表す数値です。貧血があるとき、この数値で「小さい貧血」か「大きい貧血」かを見分けることができ、原因を絞り込む手がかりになります。</v>
       </c>
       <c r="F55" t="str">
-        <v>鉄欠乏性貧血、ビタミンB12・葉酸欠乏性貧血、混合性貧血</v>
+        <v/>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2988,22 +2988,22 @@
         <v/>
       </c>
       <c r="I55" t="str">
-        <v/>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="J55" t="str">
-        <v/>
+        <v>鉄分の多い食品(レバー・赤身肉・魚・ほうれん草など)と、吸収を助けるビタミンC(柑橘類・芋類等)を一緒に摂るよう伝える</v>
       </c>
       <c r="K55" t="str">
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>RDW-SDと同様の意味を持つ指標。MCVが小さくRDWが高ければ鉄欠乏性貧血、MCVが大きくRDWが高ければビタミンB12・葉酸欠乏を疑う手がかりになる</v>
+        <v/>
       </c>
       <c r="M55" t="str">
         <v>鉄欠乏性貧血</v>
       </c>
       <c r="N55" t="str">
-        <v>RDW-CV,赤血球分布幅,貧血,ビタミンB12,葉酸</v>
+        <v>MCV,赤血球指数,貧血</v>
       </c>
       <c r="O55" t="str">
         <v>食事と栄養 p.151-164（第2部 貧血）</v>
@@ -3011,22 +3011,22 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>好中球実数値</v>
+        <v>MCH</v>
       </c>
       <c r="B56" t="str">
-        <v>Neutro#,ANC</v>
+        <v>MCH</v>
       </c>
       <c r="C56" t="str">
-        <v>2,000〜7,500 /μL程度（施設差あり、白血球数×好中球%で算出）</v>
+        <v>26.3〜34.3 pg</v>
       </c>
       <c r="D56" t="str">
-        <v>好中球の絶対数。感染症リスクを判断する上で割合(%)より重要な指標</v>
+        <v>赤血球1個に含まれるヘモグロビン量</v>
       </c>
       <c r="E56" t="str">
-        <v>これは好中球の実際の数を表す数値です。割合(%)だけでなく、実際の数がどれくらいあるかを見ることで、感染症にかかりやすい状態かどうかをより正確に判断できます。</v>
+        <v>MCHは赤血球1個の中に含まれるヘモグロビン（酸素を運ぶ色素）の量を表す数値です。MCVと同じく、貧血の種類を見分けるのに使われます。</v>
       </c>
       <c r="F56" t="str">
-        <v>細菌感染症、炎症、ステロイド使用</v>
+        <v/>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -3035,116 +3035,116 @@
         <v/>
       </c>
       <c r="I56" t="str">
-        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、メルカゾールなど薬剤性の無顆粒球症（1,000/μL未満で好中球減少症、500/μL未満で重症感染リスクが著しく上昇）</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="J56" t="str">
-        <v>発熱、のどの痛みなど感染症状の初期サインがないか確認する。人混みを避け、手洗い・うがいを徹底するよう伝える</v>
+        <v>鉄分の多い食品(レバー・赤身肉・魚・ほうれん草など)と、吸収を助けるビタミンC(柑橘類・芋類等)を一緒に摂るよう伝える</v>
       </c>
       <c r="K56" t="str">
-        <v>抗がん剤、メルカゾール(無顆粒球症)、クロザピン、サラゾスルファピリジン</v>
+        <v/>
       </c>
       <c r="L56" t="str">
-        <v>抗がん剤・メルカゾール・カルバマゼピンなど骨髄抑制のリスクがある薬剤使用中は特に重視すべき数値。500/μL未満は発熱性好中球減少症のリスクが高く緊急性が高い</v>
+        <v/>
       </c>
       <c r="M56" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="N56" t="str">
-        <v>好中球実数値,好中球数,ANC,無顆粒球症,発熱性好中球減少症</v>
+        <v>MCH,赤血球指数,貧血</v>
       </c>
       <c r="O56" t="str">
-        <v/>
+        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>好酸球実数値</v>
+        <v>MCHC</v>
       </c>
       <c r="B57" t="str">
-        <v>Eosino#</v>
+        <v>MCHC</v>
       </c>
       <c r="C57" t="str">
-        <v>100〜500 /μL程度（施設差あり）</v>
+        <v>31.6〜36.6 %</v>
       </c>
       <c r="D57" t="str">
-        <v>好酸球の絶対数。アレルギーや薬剤反応の程度をより正確に評価できる</v>
+        <v>単位容積あたりの赤血球に含まれるヘモグロビン濃度</v>
       </c>
       <c r="E57" t="str">
-        <v>これは好酸球の実際の数を表す数値です。割合(%)だけでなく実数を見ることで、アレルギー反応の強さをより正確に把握できます。</v>
+        <v>MCHCは、赤血球の中にヘモグロビンがどれくらい濃く詰まっているかを表す数値です。鉄が不足すると、この濃度も薄くなる傾向があります。</v>
       </c>
       <c r="F57" t="str">
-        <v>アレルギー性疾患、薬剤アレルギー、寄生虫感染</v>
+        <v/>
       </c>
       <c r="G57" t="str">
-        <v>新しく始めた薬がないか確認する</v>
+        <v/>
       </c>
       <c r="H57" t="str">
-        <v>薬剤性好酸球増多(抗菌薬・NSAIDs・抗てんかん薬など)。発熱や皮疹を伴う場合はDRESS症候群にも注意</v>
+        <v/>
       </c>
       <c r="I57" t="str">
-        <v/>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="J57" t="str">
-        <v/>
+        <v>鉄分の多い食品(レバー・赤身肉・魚・ほうれん草など)と、吸収を助けるビタミンC(柑橘類・芋類等)を一緒に摂るよう伝える</v>
       </c>
       <c r="K57" t="str">
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>薬剤性過敏症症候群(DIHS)などでは著明な好酸球増多を認めることがあり、原因薬剤の特定に役立つ</v>
+        <v/>
       </c>
       <c r="M57" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="N57" t="str">
-        <v>好酸球実数値,好酸球数,アレルギー,DIHS</v>
+        <v>MCHC,赤血球指数,貧血</v>
       </c>
       <c r="O57" t="str">
-        <v/>
+        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>好塩基球実数値</v>
+        <v>血小板数</v>
       </c>
       <c r="B58" t="str">
-        <v>Baso#</v>
+        <v>Plt</v>
       </c>
       <c r="C58" t="str">
-        <v>0〜100 /μL程度（施設差あり）</v>
+        <v>15.0〜35.0万/μL程度（施設差あり）</v>
       </c>
       <c r="D58" t="str">
-        <v>好塩基球の絶対数</v>
+        <v>出血を止める働きをする血液成分で、少なすぎると出血しやすくなる</v>
       </c>
       <c r="E58" t="str">
-        <v>これは好塩基球の実際の数を表す数値です。数がとても少ない種類の血球なので、通常は大きな変動を示すことは多くありません。</v>
+        <v>血小板は、血管が傷ついたときに集まって血を止める役割をする血液の成分です。数が少ないとあざができやすくなったり、出血が止まりにくくなったりします。抗血小板薬や抗がん剤を使っている方では、定期的にチェックすることが大切です。</v>
       </c>
       <c r="F58" t="str">
-        <v>慢性骨髄性白血病などの血液疾患、アレルギー性疾患</v>
+        <v>炎症性疾患、鉄欠乏性貧血、脾摘後、骨髄増殖性疾患</v>
       </c>
       <c r="G58" t="str">
-        <v/>
+        <v>出血傾向はなく経過観察でよいことが多いが、片側の腫れ・しびれなど血栓症状がないかも念のため確認する</v>
       </c>
       <c r="H58" t="str">
         <v/>
       </c>
       <c r="I58" t="str">
-        <v/>
+        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、肝硬変・脾機能亢進、再生不良性貧血、抗てんかん薬（バルプロ酸など）の副作用、ITP（特発性血小板減少性紫斑病）</v>
       </c>
       <c r="J58" t="str">
-        <v/>
+        <v>あざができやすい、歯ぐきや鼻からの出血が増えていないか確認する。強い運動や転倒によるけがに注意するよう伝え、歯みがきは柔らかめのブラシを勧める</v>
       </c>
       <c r="K58" t="str">
-        <v/>
+        <v>ヘパリン(HIT: ヘパリン起因性血小板減少症)、バルプロ酸、抗がん剤、リネゾリド</v>
       </c>
       <c r="L58" t="str">
-        <v>単独での臨床的意義は乏しく、他の血球指標（白血球分画全体）と合わせて評価する</v>
+        <v>抗血小板薬・抗凝固薬使用中に血小板減少があると出血リスクがさらに高まる。抗がん剤・バルプロ酸・カルバマゼピンなど骨髄抑制のリスクがある薬剤使用中は定期採血の実施状況を確認する</v>
       </c>
       <c r="M58" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>てんかん,抗血小板療法</v>
       </c>
       <c r="N58" t="str">
-        <v>好塩基球実数値,好塩基球数</v>
+        <v>血小板,Plt,platelet,出血,あざ,紫斑,骨髄抑制</v>
       </c>
       <c r="O58" t="str">
         <v/>
@@ -3152,22 +3152,22 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>リンパ球実数値</v>
+        <v>RDW-SD</v>
       </c>
       <c r="B59" t="str">
-        <v>Lympho#,ALC</v>
+        <v>RDW-SD</v>
       </c>
       <c r="C59" t="str">
-        <v>1,000〜3,600 /μL程度（施設差あり）</v>
+        <v>39〜46 fL程度（施設差あり）</v>
       </c>
       <c r="D59" t="str">
-        <v>リンパ球の絶対数。免疫力の目安として使われる</v>
+        <v>赤血球の大きさのばらつきを表す指標(絶対値)。鉄欠乏性貧血などの初期変化を捉えやすい</v>
       </c>
       <c r="E59" t="str">
-        <v>これはリンパ球の実際の数を表す数値です。免疫力の目安の一つとして使われ、抗がん剤や免疫抑制剤の副作用モニタリングにも用いられます。</v>
+        <v>RDW-SDは、赤血球の大きさがどれくらいバラバラになっているかを表す数値です。貧血の原因を調べる際、鉄が足りなくなり始めた早い段階での変化を捉えるのに役立ちます。</v>
       </c>
       <c r="F59" t="str">
-        <v>ウイルス感染症、リンパ性白血病などの血液疾患</v>
+        <v>鉄欠乏性貧血の初期、混合性貧血（複数の原因が重なっている状態）、赤血球産生の乱れ</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -3176,45 +3176,45 @@
         <v/>
       </c>
       <c r="I59" t="str">
-        <v>抗がん剤・免疫抑制剤・ステロイドの使用、強いストレス、AIDSなどの免疫不全</v>
+        <v/>
       </c>
       <c r="J59" t="str">
-        <v>感染予防（手洗い・うがい、人混みを避ける）を意識するよう伝える</v>
+        <v/>
       </c>
       <c r="K59" t="str">
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>免疫抑制剤・抗がん剤治療中のモニタリング指標としても使われる。著明な低下時は日和見感染のリスクが高まる</v>
+        <v>MCVが正常範囲でもRDWが上昇している場合、鉄欠乏の初期段階を示唆することがある。MCV・MCHと合わせて評価する</v>
       </c>
       <c r="M59" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="N59" t="str">
-        <v>リンパ球実数値,リンパ球数,ALC,免疫抑制剤,日和見感染</v>
+        <v>RDW-SD,赤血球分布幅,貧血,鉄欠乏</v>
       </c>
       <c r="O59" t="str">
-        <v/>
+        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>単球実数値</v>
+        <v>RDW-CV</v>
       </c>
       <c r="B60" t="str">
-        <v>Mono#</v>
+        <v>RDW-CV</v>
       </c>
       <c r="C60" t="str">
-        <v>200〜600 /μL程度（施設差あり）</v>
+        <v>11.5〜14.5%程度（施設差あり）</v>
       </c>
       <c r="D60" t="str">
-        <v>単球の絶対数</v>
+        <v>赤血球の大きさのばらつきを割合(%)で表した指標</v>
       </c>
       <c r="E60" t="str">
-        <v>これは単球の実際の数を表す数値です。慢性的な炎症や感染症の状態を把握する材料の一つになります。</v>
+        <v>RDW-CVもRDW-SDと同じく、赤血球の大きさのばらつきを表す数値ですが、こちらは割合(%)で示されます。貧血のタイプを見分ける手がかりになります。</v>
       </c>
       <c r="F60" t="str">
-        <v>慢性感染症、炎症性疾患、血液疾患</v>
+        <v>鉄欠乏性貧血、ビタミンB12・葉酸欠乏性貧血、混合性貧血</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -3232,60 +3232,60 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>単独での臨床的意義は乏しく、他の血球指標と合わせて評価する</v>
+        <v>RDW-SDと同様の意味を持つ指標。MCVが小さくRDWが高ければ鉄欠乏性貧血、MCVが大きくRDWが高ければビタミンB12・葉酸欠乏を疑う手がかりになる</v>
       </c>
       <c r="M60" t="str">
-        <v>甲状腺疾患,てんかん</v>
+        <v>鉄欠乏性貧血</v>
       </c>
       <c r="N60" t="str">
-        <v>単球実数値,単球数</v>
+        <v>RDW-CV,赤血球分布幅,貧血,ビタミンB12,葉酸</v>
       </c>
       <c r="O60" t="str">
-        <v/>
+        <v>食事と栄養 p.151-164（第2部 貧血）</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>好中球</v>
+        <v>好中球実数値</v>
       </c>
       <c r="B61" t="str">
-        <v>Neutro,Neut%</v>
+        <v>Neutro#,ANC</v>
       </c>
       <c r="C61" t="str">
-        <v>40〜75%程度（施設差あり）</v>
+        <v>2,000〜7,500 /μL程度（施設差あり、白血球数×好中球%で算出）</v>
       </c>
       <c r="D61" t="str">
-        <v>白血球の中で最も多くを占め、細菌感染と戦う主力の免疫細胞の割合</v>
+        <v>好中球の絶対数。感染症リスクを判断する上で割合(%)より重要な指標</v>
       </c>
       <c r="E61" t="str">
-        <v>好中球は、白血球の中で最も数が多く、細菌が体に入ってきたときに真っ先に戦ってくれる免疫細胞です。感染症や炎症があると増え、逆に薬の副作用などで減ることがあります。</v>
+        <v>これは好中球の実際の数を表す数値です。割合(%)だけでなく、実際の数がどれくらいあるかを見ることで、感染症にかかりやすい状態かどうかをより正確に判断できます。</v>
       </c>
       <c r="F61" t="str">
-        <v>細菌感染症、炎症、ストレス、ステロイド使用</v>
+        <v>細菌感染症、炎症、ステロイド使用</v>
       </c>
       <c r="G61" t="str">
-        <v>発熱や炎症症状がないか確認する</v>
+        <v/>
       </c>
       <c r="H61" t="str">
         <v/>
       </c>
       <c r="I61" t="str">
-        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、ウイルス感染、メルカゾールなど薬剤性の無顆粒球症</v>
+        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、メルカゾールなど薬剤性の無顆粒球症（1,000/μL未満で好中球減少症、500/μL未満で重症感染リスクが著しく上昇）</v>
       </c>
       <c r="J61" t="str">
-        <v>発熱やのどの痛みなど感染症状の初期サインがないか確認する</v>
+        <v>発熱、のどの痛みなど感染症状の初期サインがないか確認する。人混みを避け、手洗い・うがいを徹底するよう伝える</v>
       </c>
       <c r="K61" t="str">
         <v>抗がん剤、メルカゾール(無顆粒球症)、クロザピン、サラゾスルファピリジン</v>
       </c>
       <c r="L61" t="str">
-        <v>好中球の絶対数（好中球実数値）が500/μL未満になると重篤な感染症のリスクが高まる。割合(%)だけでなく実数値も合わせて確認する</v>
+        <v>抗がん剤・メルカゾール・カルバマゼピンなど骨髄抑制のリスクがある薬剤使用中は特に重視すべき数値。500/μL未満は発熱性好中球減少症のリスクが高く緊急性が高い</v>
       </c>
       <c r="M61" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N61" t="str">
-        <v>好中球,Neutro,Neut,感染症,無顆粒球症</v>
+        <v>好中球実数値,好中球数,ANC,無顆粒球症,発熱性好中球減少症</v>
       </c>
       <c r="O61" t="str">
         <v/>
@@ -3293,25 +3293,25 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>好酸球</v>
+        <v>好酸球実数値</v>
       </c>
       <c r="B62" t="str">
-        <v>Eosino,Eos%</v>
+        <v>Eosino#</v>
       </c>
       <c r="C62" t="str">
-        <v>1〜5%程度（施設差あり）</v>
+        <v>100〜500 /μL程度（施設差あり）</v>
       </c>
       <c r="D62" t="str">
-        <v>アレルギー反応や寄生虫感染に関わる白血球の一種の割合</v>
+        <v>好酸球の絶対数。アレルギーや薬剤反応の程度をより正確に評価できる</v>
       </c>
       <c r="E62" t="str">
-        <v>好酸球は、アレルギー反応や寄生虫感染と関係が深い免疫細胞です。アレルギー性の病気や薬の副作用（薬疹など）で増えることがあります。</v>
+        <v>これは好酸球の実際の数を表す数値です。割合(%)だけでなく実数を見ることで、アレルギー反応の強さをより正確に把握できます。</v>
       </c>
       <c r="F62" t="str">
-        <v>アレルギー性疾患（気管支喘息、アトピー性皮膚炎など）、薬剤アレルギー、寄生虫感染</v>
+        <v>アレルギー性疾患、薬剤アレルギー、寄生虫感染</v>
       </c>
       <c r="G62" t="str">
-        <v>新しく始めた薬がないか確認する。皮疹やかゆみなどアレルギー症状の有無を確認する</v>
+        <v>新しく始めた薬がないか確認する</v>
       </c>
       <c r="H62" t="str">
         <v>薬剤性好酸球増多(抗菌薬・NSAIDs・抗てんかん薬など)。発熱や皮疹を伴う場合はDRESS症候群にも注意</v>
@@ -3326,13 +3326,13 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>薬剤性の好酸球増多は、原因薬剤の中止で改善することが多い。新規薬剤開始後の皮疹・発熱と合わせて薬剤性過敏症症候群(DIHS)を疑う材料になる</v>
+        <v>薬剤性過敏症症候群(DIHS)などでは著明な好酸球増多を認めることがあり、原因薬剤の特定に役立つ</v>
       </c>
       <c r="M62" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N62" t="str">
-        <v>好酸球,Eosino,Eos,アレルギー,薬疹,DIHS</v>
+        <v>好酸球実数値,好酸球数,アレルギー,DIHS</v>
       </c>
       <c r="O62" t="str">
         <v/>
@@ -3340,22 +3340,22 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>好塩基球</v>
+        <v>好塩基球実数値</v>
       </c>
       <c r="B63" t="str">
-        <v>Baso,Baso%</v>
+        <v>Baso#</v>
       </c>
       <c r="C63" t="str">
-        <v>0〜2%程度（施設差あり）</v>
+        <v>0〜100 /μL程度（施設差あり）</v>
       </c>
       <c r="D63" t="str">
-        <v>白血球の中で最も数が少なく、アレルギー反応に関わる細胞の割合</v>
+        <v>好塩基球の絶対数</v>
       </c>
       <c r="E63" t="str">
-        <v>好塩基球は白血球の中で最も数が少ない種類で、アレルギー反応や炎症に関わっています。数値の変動が病気の診断に直接使われることは少ない検査です。</v>
+        <v>これは好塩基球の実際の数を表す数値です。数がとても少ない種類の血球なので、通常は大きな変動を示すことは多くありません。</v>
       </c>
       <c r="F63" t="str">
-        <v>慢性骨髄性白血病などの血液疾患、アレルギー性疾患、甲状腺機能低下症</v>
+        <v>慢性骨髄性白血病などの血液疾患、アレルギー性疾患</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -3373,13 +3373,13 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>単独での臨床的意義は乏しいが、著明な増加は血液疾患（慢性骨髄性白血病等）の可能性があり他の血球指標と合わせて評価する</v>
+        <v>単独での臨床的意義は乏しく、他の血球指標（白血球分画全体）と合わせて評価する</v>
       </c>
       <c r="M63" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N63" t="str">
-        <v>好塩基球,Baso,アレルギー,白血病</v>
+        <v>好塩基球実数値,好塩基球数</v>
       </c>
       <c r="O63" t="str">
         <v/>
@@ -3387,22 +3387,22 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>リンパ球</v>
+        <v>リンパ球実数値</v>
       </c>
       <c r="B64" t="str">
-        <v>Lympho,Lym%</v>
+        <v>Lympho#,ALC</v>
       </c>
       <c r="C64" t="str">
-        <v>18〜49%程度（施設差あり）</v>
+        <v>1,000〜3,600 /μL程度（施設差あり）</v>
       </c>
       <c r="D64" t="str">
-        <v>ウイルス感染と戦い、免疫の記憶を担う白血球の割合</v>
+        <v>リンパ球の絶対数。免疫力の目安として使われる</v>
       </c>
       <c r="E64" t="str">
-        <v>リンパ球は、ウイルスと戦ったり、一度かかった病気を記憶して免疫をつくったりする細胞です。ウイルス感染で増え、抗がん剤の副作用や強いストレスで減ることがあります。</v>
+        <v>これはリンパ球の実際の数を表す数値です。免疫力の目安の一つとして使われ、抗がん剤や免疫抑制剤の副作用モニタリングにも用いられます。</v>
       </c>
       <c r="F64" t="str">
-        <v>ウイルス感染症、リンパ性白血病などの血液疾患、百日咳</v>
+        <v>ウイルス感染症、リンパ性白血病などの血液疾患</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -3414,19 +3414,19 @@
         <v>抗がん剤・免疫抑制剤・ステロイドの使用、強いストレス、AIDSなどの免疫不全</v>
       </c>
       <c r="J64" t="str">
-        <v>免疫が下がっている可能性があるため、感染予防（手洗い・うがい、人混みを避ける）を意識するよう伝える</v>
+        <v>感染予防（手洗い・うがい、人混みを避ける）を意識するよう伝える</v>
       </c>
       <c r="K64" t="str">
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>ステロイド・免疫抑制剤使用中はリンパ球減少による易感染性に注意。好中球と逆方向に動くことが多い（ウイルス感染ではリンパ球優位、細菌感染では好中球優位になりやすい）</v>
+        <v>免疫抑制剤・抗がん剤治療中のモニタリング指標としても使われる。著明な低下時は日和見感染のリスクが高まる</v>
       </c>
       <c r="M64" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N64" t="str">
-        <v>リンパ球,Lympho,Lym,ウイルス感染,免疫抑制剤,ステロイド</v>
+        <v>リンパ球実数値,リンパ球数,ALC,免疫抑制剤,日和見感染</v>
       </c>
       <c r="O64" t="str">
         <v/>
@@ -3434,22 +3434,22 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>単球</v>
+        <v>単球実数値</v>
       </c>
       <c r="B65" t="str">
-        <v>Mono,Mono%</v>
+        <v>Mono#</v>
       </c>
       <c r="C65" t="str">
-        <v>2〜10%程度（施設差あり）</v>
+        <v>200〜600 /μL程度（施設差あり）</v>
       </c>
       <c r="D65" t="str">
-        <v>感染や炎症の後始末をする白血球の一種の割合</v>
+        <v>単球の絶対数</v>
       </c>
       <c r="E65" t="str">
-        <v>単球は、細菌などを取り込んで処理したり、組織の修復に関わったりする免疫細胞です。慢性的な炎症や感染症の回復期に増えることがあります。</v>
+        <v>これは単球の実際の数を表す数値です。慢性的な炎症や感染症の状態を把握する材料の一つになります。</v>
       </c>
       <c r="F65" t="str">
-        <v>慢性感染症（結核など）、炎症性疾患、血液疾患、感染症の回復期</v>
+        <v>慢性感染症、炎症性疾患、血液疾患</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -3467,13 +3467,13 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>単独での臨床的意義は乏しく、他の血球指標や炎症マーカー(CRPなど)と合わせて評価する</v>
+        <v>単独での臨床的意義は乏しく、他の血球指標と合わせて評価する</v>
       </c>
       <c r="M65" t="str">
         <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N65" t="str">
-        <v>単球,Mono,慢性感染症,結核,炎症</v>
+        <v>単球実数値,単球数</v>
       </c>
       <c r="O65" t="str">
         <v/>
@@ -3481,46 +3481,46 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>尿蛋白（随時尿）</v>
+        <v>好中球</v>
       </c>
       <c r="B66" t="str">
-        <v>尿蛋白,U-pro</v>
+        <v>Neutro,Neut%</v>
       </c>
       <c r="C66" t="str">
-        <v>陰性（－）〜弱陽性</v>
+        <v>40〜75%程度（施設差あり）</v>
       </c>
       <c r="D66" t="str">
-        <v>腎臓から本来漏れないはずのたんぱくが尿に出ていないかを見る検査</v>
+        <v>白血球の中で最も多くを占め、細菌感染と戦う主力の免疫細胞の割合</v>
       </c>
       <c r="E66" t="str">
-        <v>この検査は、腎臓のろ過機能に負担がかかっていないかを見るものです。本来、たんぱく質は尿にほとんど出ませんが、腎臓に負担がかかると漏れ出るようになります。</v>
+        <v>好中球は、白血球の中で最も数が多く、細菌が体に入ってきたときに真っ先に戦ってくれる免疫細胞です。感染症や炎症があると増え、逆に薬の副作用などで減ることがあります。</v>
       </c>
       <c r="F66" t="str">
-        <v>糖尿病性腎症、腎炎、高血圧性腎硬化症、発熱・運動後の一過性のもの</v>
+        <v>細菌感染症、炎症、ストレス、ステロイド使用</v>
       </c>
       <c r="G66" t="str">
-        <v>発熱・激しい運動の直後でないか確認する(一過性のことがある)。持続する場合は塩分の摂りすぎに注意し、むくみの有無もあわせて確認する</v>
+        <v>発熱や炎症症状がないか確認する</v>
       </c>
       <c r="H66" t="str">
-        <v>NSAIDs、造影剤、アミノグリコシド系、バンコマイシン、金製剤</v>
+        <v/>
       </c>
       <c r="I66" t="str">
-        <v/>
+        <v>抗がん剤・免疫抑制剤などによる骨髄抑制、ウイルス感染、メルカゾールなど薬剤性の無顆粒球症</v>
       </c>
       <c r="J66" t="str">
-        <v/>
+        <v>発熱やのどの痛みなど感染症状の初期サインがないか確認する</v>
       </c>
       <c r="K66" t="str">
-        <v/>
+        <v>抗がん剤、メルカゾール(無顆粒球症)、クロザピン、サラゾスルファピリジン</v>
       </c>
       <c r="L66" t="str">
-        <v>発熱・激しい運動・起立性蛋白尿など生理的な要因でも陽性になることがある。持続する場合に腎症の進行を疑う</v>
+        <v>好中球の絶対数（好中球実数値）が500/μL未満になると重篤な感染症のリスクが高まる。割合(%)だけでなく実数値も合わせて確認する</v>
       </c>
       <c r="M66" t="str">
-        <v>糖尿病,腎機能</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N66" t="str">
-        <v>尿蛋白,U-pro,腎症,たんぱく尿</v>
+        <v>好中球,Neutro,Neut,感染症,無顆粒球症</v>
       </c>
       <c r="O66" t="str">
         <v/>
@@ -3528,31 +3528,31 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>尿クレアチニン（随時尿）</v>
+        <v>好酸球</v>
       </c>
       <c r="B67" t="str">
-        <v>尿CRE</v>
+        <v>Eosino,Eos%</v>
       </c>
       <c r="C67" t="str">
-        <v>随時尿は主に他項目の濃度補正に利用（単独の基準値は設けにくい）</v>
+        <v>1〜5%程度（施設差あり）</v>
       </c>
       <c r="D67" t="str">
-        <v>随時尿中のクレアチニン濃度。他の尿検査項目を薄まり具合で補正するための基準として使う</v>
+        <v>アレルギー反応や寄生虫感染に関わる白血球の一種の割合</v>
       </c>
       <c r="E67" t="str">
-        <v>この数値は、尿がどれくらい薄まっているかを確認するための基準として使われます。他の尿検査の結果（蛋白やアルブミンなど）をこの値で割って補正することで、水分摂取量による影響を減らして正確に評価できます。</v>
+        <v>好酸球は、アレルギー反応や寄生虫感染と関係が深い免疫細胞です。アレルギー性の病気や薬の副作用（薬疹など）で増えることがあります。</v>
       </c>
       <c r="F67" t="str">
-        <v/>
+        <v>アレルギー性疾患（気管支喘息、アトピー性皮膚炎など）、薬剤アレルギー、寄生虫感染</v>
       </c>
       <c r="G67" t="str">
-        <v/>
+        <v>新しく始めた薬がないか確認する。皮疹やかゆみなどアレルギー症状の有無を確認する</v>
       </c>
       <c r="H67" t="str">
-        <v/>
+        <v>薬剤性好酸球増多(抗菌薬・NSAIDs・抗てんかん薬など)。発熱や皮疹を伴う場合はDRESS症候群にも注意</v>
       </c>
       <c r="I67" t="str">
-        <v>尿が薄い（水分摂取が多い、腎機能低下）状態</v>
+        <v/>
       </c>
       <c r="J67" t="str">
         <v/>
@@ -3561,13 +3561,13 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>尿中アルブミン/Cr比、尿蛋白/Cr比など、他項目の補正計算に使われる。単独の高低に臨床的意味は乏しい</v>
+        <v>薬剤性の好酸球増多は、原因薬剤の中止で改善することが多い。新規薬剤開始後の皮疹・発熱と合わせて薬剤性過敏症症候群(DIHS)を疑う材料になる</v>
       </c>
       <c r="M67" t="str">
-        <v>腎機能</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N67" t="str">
-        <v>尿CRE,尿クレアチニン,随時尿,補正,蛋白クレアチニン比</v>
+        <v>好酸球,Eosino,Eos,アレルギー,薬疹,DIHS</v>
       </c>
       <c r="O67" t="str">
         <v/>
@@ -3575,28 +3575,28 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>尿蛋白定量</v>
+        <v>好塩基球</v>
       </c>
       <c r="B68" t="str">
-        <v>U-Pro定量,蛋白/Cr比</v>
+        <v>Baso,Baso%</v>
       </c>
       <c r="C68" t="str">
-        <v>0.15 g/gCr未満</v>
+        <v>0〜2%程度（施設差あり）</v>
       </c>
       <c r="D68" t="str">
-        <v>随時尿から尿蛋白の量を具体的な数値として評価する検査。ネフローゼ等の重症度判定に使う</v>
+        <v>白血球の中で最も数が少なく、アレルギー反応に関わる細胞の割合</v>
       </c>
       <c r="E68" t="str">
-        <v>これは、尿に出ているたんぱくの量を具体的な数値で見る検査です。試験紙での陽性・陰性の判定だけでなく、実際にどれくらいの量が出ているかを把握できます。</v>
+        <v>好塩基球は白血球の中で最も数が少ない種類で、アレルギー反応や炎症に関わっています。数値の変動が病気の診断に直接使われることは少ない検査です。</v>
       </c>
       <c r="F68" t="str">
-        <v>腎症の進行（糖尿病性腎症、慢性腎臓病など）、ネフローゼ症候群（3.5 g/gCr以上が目安）</v>
+        <v>慢性骨髄性白血病などの血液疾患、アレルギー性疾患、甲状腺機能低下症</v>
       </c>
       <c r="G68" t="str">
-        <v>持続する場合は塩分の摂りすぎに注意し、むくみの有無も確認する。腎臓内科でのフォロー状況もあわせて確認する</v>
+        <v/>
       </c>
       <c r="H68" t="str">
-        <v>NSAIDs、造影剤、アミノグリコシド系、バンコマイシン</v>
+        <v/>
       </c>
       <c r="I68" t="str">
         <v/>
@@ -3608,13 +3608,13 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>CKD診療ガイドラインの重症度分類（尿蛋白量による区分）にも使われる定量指標。試験紙法の半定量結果より治療効果判定に適する</v>
+        <v>単独での臨床的意義は乏しいが、著明な増加は血液疾患（慢性骨髄性白血病等）の可能性があり他の血球指標と合わせて評価する</v>
       </c>
       <c r="M68" t="str">
-        <v>腎機能,糖尿病</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N68" t="str">
-        <v>尿蛋白,随時尿,定量,蛋白クレアチニン比,ネフローゼ</v>
+        <v>好塩基球,Baso,アレルギー,白血病</v>
       </c>
       <c r="O68" t="str">
         <v/>
@@ -3622,22 +3622,22 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>尿pH</v>
+        <v>リンパ球</v>
       </c>
       <c r="B69" t="str">
-        <v>尿pH</v>
+        <v>Lympho,Lym%</v>
       </c>
       <c r="C69" t="str">
-        <v>4.5〜7.5程度（弱酸性が多い）</v>
+        <v>18〜49%程度（施設差あり）</v>
       </c>
       <c r="D69" t="str">
-        <v>尿の酸性・アルカリ性の度合い。食事や感染症、体の状態を反映する</v>
+        <v>ウイルス感染と戦い、免疫の記憶を担う白血球の割合</v>
       </c>
       <c r="E69" t="str">
-        <v>尿のpHは酸性・アルカリ性のバランスを表します。食事の内容や感染症、体の代謝状態によって変化します。単独で大きな問題を示すことは少ない検査です。</v>
+        <v>リンパ球は、ウイルスと戦ったり、一度かかった病気を記憶して免疫をつくったりする細胞です。ウイルス感染で増え、抗がん剤の副作用や強いストレスで減ることがあります。</v>
       </c>
       <c r="F69" t="str">
-        <v>尿路感染症（尿素分解菌によるもの）、野菜中心の食事、過換気</v>
+        <v>ウイルス感染症、リンパ性白血病などの血液疾患、百日咳</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3646,22 +3646,22 @@
         <v/>
       </c>
       <c r="I69" t="str">
-        <v>高たんぱく食、糖尿病性ケトアシドーシス、痛風発作時（酸性尿は尿酸結石のリスクを高める）</v>
+        <v>抗がん剤・免疫抑制剤・ステロイドの使用、強いストレス、AIDSなどの免疫不全</v>
       </c>
       <c r="J69" t="str">
-        <v>痛風・尿酸結石がある場合は、野菜など尿をアルカリ化する食品を意識するとよいことを伝える</v>
+        <v>免疫が下がっている可能性があるため、感染予防（手洗い・うがい、人混みを避ける）を意識するよう伝える</v>
       </c>
       <c r="K69" t="str">
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>高尿酸血症・尿酸結石の患者では尿pHが酸性に傾いていないか確認する。尿アルカリ化薬（ウラリットなど）の効果判定にも使う</v>
+        <v>ステロイド・免疫抑制剤使用中はリンパ球減少による易感染性に注意。好中球と逆方向に動くことが多い（ウイルス感染ではリンパ球優位、細菌感染では好中球優位になりやすい）</v>
       </c>
       <c r="M69" t="str">
-        <v>高尿酸血症</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N69" t="str">
-        <v>尿pH,尿酸性度,尿アルカリ化,ウラリット</v>
+        <v>リンパ球,Lympho,Lym,ウイルス感染,免疫抑制剤,ステロイド</v>
       </c>
       <c r="O69" t="str">
         <v/>
@@ -3669,28 +3669,28 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>尿ケトン体</v>
+        <v>単球</v>
       </c>
       <c r="B70" t="str">
-        <v>尿ケトン,Ket</v>
+        <v>Mono,Mono%</v>
       </c>
       <c r="C70" t="str">
-        <v>陰性（－）</v>
+        <v>2〜10%程度（施設差あり）</v>
       </c>
       <c r="D70" t="str">
-        <v>体がブドウ糖の代わりに脂肪を分解してエネルギーを作っているサイン</v>
+        <v>感染や炎症の後始末をする白血球の一種の割合</v>
       </c>
       <c r="E70" t="str">
-        <v>この検査は、体が糖の代わりに脂肪を使ってエネルギーを作っていないかを見るものです。陽性が続くときは、食事や水分、インスリンの使い方を確認する必要があります。</v>
+        <v>単球は、細菌などを取り込んで処理したり、組織の修復に関わったりする免疫細胞です。慢性的な炎症や感染症の回復期に増えることがあります。</v>
       </c>
       <c r="F70" t="str">
-        <v>糖尿病の血糖コントロール不良（シックデイ・インスリン不足）、極端な糖質制限、絶食、嘔吐・下痢による脱水</v>
+        <v>慢性感染症（結核など）、炎症性疾患、血液疾患、感染症の回復期</v>
       </c>
       <c r="G70" t="str">
-        <v>糖尿病治療中の場合はシックデイ時の対応(インスリンを自己中断しない、水分摂取を続けるなど)を確認する。体調不良時の対応方法を事前に説明しておく</v>
+        <v/>
       </c>
       <c r="H70" t="str">
-        <v>SGLT2阻害薬(特に絶食・シックデイ時の正常血糖ケトアシドーシスに注意)</v>
+        <v/>
       </c>
       <c r="I70" t="str">
         <v/>
@@ -3702,13 +3702,13 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>陽性かつ高血糖・全身倦怠感が強い場合は糖尿病性ケトアシドーシスの可能性があり緊急性が高い。シックデイルールの説明歴を確認する</v>
+        <v>単独での臨床的意義は乏しく、他の血球指標や炎症マーカー(CRPなど)と合わせて評価する</v>
       </c>
       <c r="M70" t="str">
-        <v>糖尿病</v>
+        <v>甲状腺疾患,てんかん</v>
       </c>
       <c r="N70" t="str">
-        <v>尿ケトン体,ケトン体,Ket,シックデイ,ケトアシドーシス</v>
+        <v>単球,Mono,慢性感染症,結核,炎症</v>
       </c>
       <c r="O70" t="str">
         <v/>
@@ -3716,31 +3716,31 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>ウロビリノーゲン</v>
+        <v>C反応性蛋白（CRP）</v>
       </c>
       <c r="B71" t="str">
-        <v>Uro</v>
+        <v>CRP</v>
       </c>
       <c r="C71" t="str">
-        <v>正常（±）程度</v>
+        <v>0.3 mg/dL未満（施設差あり）</v>
       </c>
       <c r="D71" t="str">
-        <v>肝臓や胆道、赤血球の壊れ方の状態を反映する尿検査項目</v>
+        <v>体のどこかに炎症や感染が起きていないかを鋭敏に反映する数値</v>
       </c>
       <c r="E71" t="str">
-        <v>ウロビリノーゲンは、赤血球やビリルビンが体の中で処理される過程でできる物質です。肝臓の働きが悪くなったり、赤血球が壊れやすくなったりすると、尿の中の量が変化します。</v>
+        <v>CRPは、体に炎症や感染が起きると数時間〜半日程度で急激に上昇する数値です。風邪のようなウイルス感染から細菌感染、体のどこかの炎症まで、幅広く反応するため、体調の変化を早期に捉える手がかりになります。</v>
       </c>
       <c r="F71" t="str">
-        <v>溶血性疾患（赤血球の破壊亢進）、肝機能障害</v>
+        <v>細菌感染症、ウイルス感染症、自己免疫疾患（関節リウマチなど）、悪性腫瘍、組織の損傷（術後・心筋梗塞など）</v>
       </c>
       <c r="G71" t="str">
-        <v/>
+        <v>発熱、痛み、腫れなど炎症症状の有無を確認する</v>
       </c>
       <c r="H71" t="str">
         <v/>
       </c>
       <c r="I71" t="str">
-        <v>胆道閉塞（胆汁が腸に流れず、ウロビリノーゲンが作られない状態）</v>
+        <v/>
       </c>
       <c r="J71" t="str">
         <v/>
@@ -3749,13 +3749,13 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>完全に陰性の場合は胆道閉塞を疑う所見の一つ。肝機能（AST/ALT/ビリルビン）と合わせて評価する</v>
+        <v>白血球数と合わせて感染・炎症の程度を評価する。上昇・低下のタイミングは白血球より半日〜1日程度遅れる傾向があるため、経過を追う際は採血のタイミングに注意</v>
       </c>
       <c r="M71" t="str">
-        <v>肝機能</v>
+        <v/>
       </c>
       <c r="N71" t="str">
-        <v>ウロビリノーゲン,Uro,溶血,胆道閉塞,肝機能</v>
+        <v>CRP,炎症,感染</v>
       </c>
       <c r="O71" t="str">
         <v/>
@@ -3763,28 +3763,28 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>尿潜血反応</v>
+        <v>骨型酒石酸抵抗性フォスファターゼ（TRACP-5b）</v>
       </c>
       <c r="B72" t="str">
-        <v>尿潜血,U-OB</v>
+        <v>TRACP-5b</v>
       </c>
       <c r="C72" t="str">
-        <v>陰性（－）</v>
+        <v>120〜420 mU/dL</v>
       </c>
       <c r="D72" t="str">
-        <v>尿に血液（赤血球）が混じっていないかを見る検査</v>
+        <v>骨がどれくらい壊されているかを見る検査。骨は「古い骨を壊して新しい骨を作る」入れ替えを繰り返しており、骨を壊す細胞が活発だとこの物質が血液中に増える。</v>
       </c>
       <c r="E72" t="str">
-        <v>この検査は、尿に目に見えないくらいの微量の血液が混じっていないかを調べるものです。陽性の場合、腎臓や膀胱、尿路のどこかに炎症や結石などがある可能性があります。</v>
+        <v>この検査は、骨がどれくらい早く減っていないかを見るものです。数値が高いと、骨が弱くなりやすい状態の目安になります。</v>
       </c>
       <c r="F72" t="str">
-        <v>尿路結石、膀胱炎などの尿路感染症、腎炎、腫瘍、月経血の混入、激しい運動後</v>
+        <v>骨粗鬆症、骨代謝回転（骨がこわれるスピード）が活発な状態</v>
       </c>
       <c r="G72" t="str">
-        <v>排尿時の痛みや頻尿、目に見える血尿の有無を確認する。女性は月経の時期と重なっていないか確認する</v>
+        <v>カルシウム・ビタミンDの摂取や、適度な荷重運動（ウォーキングなど）を意識するよう伝える</v>
       </c>
       <c r="H72" t="str">
-        <v>ワルファリン、DOAC、抗血小板薬など出血傾向を強める薬剤の服用状況を確認</v>
+        <v/>
       </c>
       <c r="I72" t="str">
         <v/>
@@ -3796,13 +3796,13 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>陽性でも尿沈渣で赤血球が確認されない場合は偽陽性（ミオグロビン尿など）のこともある。持続する場合は泌尿器科的な精査が必要</v>
+        <v>「骨を壊す側」の指標。「骨を作る側」の検査と合わせて評価する。数値だけで診断はしない</v>
       </c>
       <c r="M72" t="str">
-        <v>腎機能</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="N72" t="str">
-        <v>尿潜血,潜血反応,U-OB,血尿,尿路結石,膀胱炎</v>
+        <v>TRACP-5b,骨型酒石酸抵抗性フォスファターゼ,骨粗鬆症,骨代謝</v>
       </c>
       <c r="O72" t="str">
         <v/>
@@ -3810,31 +3810,31 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>尿糖（半定量）</v>
+        <v>骨型アルカリフォスファターゼ</v>
       </c>
       <c r="B73" t="str">
-        <v>尿糖,U-Glu</v>
+        <v>BAP</v>
       </c>
       <c r="C73" t="str">
-        <v>陰性（－）</v>
+        <v>男性 3.7〜20.9 μg/L、女性（閉経前）2.9〜14.5 μg/L（施設差あり）</v>
       </c>
       <c r="D73" t="str">
-        <v>尿に糖が漏れ出ていないかを見る検査。血糖値がかなり高いと陽性になる</v>
+        <v>ALPのうち骨に由来する成分だけを測定し、骨が作られる勢い（骨形成）を反映する</v>
       </c>
       <c r="E73" t="str">
-        <v>通常、糖は尿にはほとんど出ませんが、血糖値がかなり高くなると尿にあふれ出るようになります。血糖コントロールの目安の一つです。</v>
+        <v>骨型ALPは、通常のALP（アルカリフォスファターゼ）の中でも、骨で作られる成分だけを選んで測定するものです。骨を新しく作る働きがどれくらい活発かを見る指標として、骨粗鬆症の治療効果判定などに使われます。</v>
       </c>
       <c r="F73" t="str">
-        <v>糖尿病（血糖値が腎臓で再吸収できる量を超えている状態）、腎性糖尿（血糖値が正常でも体質的に出ることがある）、SGLT2阻害薬服用中（薬の作用で意図的に糖を排泄するため陽性になるのが正常）</v>
+        <v>骨代謝回転の亢進（骨粗鬆症、骨折治癒過程、骨形成促進薬による治療効果、Paget病、骨転移）</v>
       </c>
       <c r="G73" t="str">
-        <v>SGLT2阻害薬（フォシーガ、ジャディアンスなど）服用中は、陽性が薬の効果によるものであることを説明する。脱水や尿路感染の症状がないかも確認する</v>
+        <v/>
       </c>
       <c r="H73" t="str">
-        <v>SGLT2阻害薬(薬理作用による陽性であれば想定内であることを説明)</v>
+        <v/>
       </c>
       <c r="I73" t="str">
-        <v/>
+        <v>骨形成の低下</v>
       </c>
       <c r="J73" t="str">
         <v/>
@@ -3843,13 +3843,13 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>SGLT2阻害薬服用中は尿糖陽性が治療効果として想定内であることを患者に伝える。血糖値・HbA1cと合わせて評価する</v>
+        <v>通常のALPと異なり肝臓の影響を受けにくいため、肝機能異常がある患者でも骨代謝を評価しやすい。P1NPと同じ「骨を作る側」の指標で、骨形成促進薬（テリパラチド等）の効果判定に使われる</v>
       </c>
       <c r="M73" t="str">
-        <v>糖尿病</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="N73" t="str">
-        <v>尿糖,糖半定量,U-Glu,腎性糖尿,SGLT2</v>
+        <v>骨型ALP,BAP,骨型アルカリフォスファターゼ,骨形成マーカー</v>
       </c>
       <c r="O73" t="str">
         <v/>
@@ -3857,72 +3857,72 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>尿中微量アルブミン</v>
+        <v>25-ヒドロキシビタミンD</v>
       </c>
       <c r="B74" t="str">
-        <v>U-Alb,MAU</v>
+        <v>25(OH)D</v>
       </c>
       <c r="C74" t="str">
-        <v>30 mg/gCr未満（尿中アルブミン/クレアチニン比）</v>
+        <v>30 ng/mL以上：充足、20〜30 ng/mL：不足、20 ng/mL未満：欠乏（施設差あり）</v>
       </c>
       <c r="D74" t="str">
-        <v>通常の尿蛋白検査では見つからない、ごく早期の腎症のサイン</v>
+        <v>体内のビタミンDの蓄え具合を反映する指標。カルシウムの吸収や骨の健康に関わる</v>
       </c>
       <c r="E74" t="str">
-        <v>この検査は、通常の尿検査ではまだ分からないくらい早い段階の腎臓の変化を見つけるためのものです。数値が高いと、腎症の初期のサインである可能性があります。</v>
+        <v>この検査は、体の中にビタミンDがどれくらい蓄えられているかを見るものです。ビタミンDは、食事から摂ったカルシウムを腸で吸収するのを助ける働きがあり、不足すると骨がもろくなりやすくなります。</v>
       </c>
       <c r="F74" t="str">
-        <v>糖尿病性腎症の早期段階、高血圧</v>
+        <v>ビタミンD製剤の過剰摂取</v>
       </c>
       <c r="G74" t="str">
-        <v>血糖・血圧のコントロール状況を確認する。減塩や適正体重の維持など生活習慣の見直しも早期腎症の進行予防に役立つことを伝える</v>
+        <v>活性型ビタミンD3製剤やサプリメントの摂取量を確認する。高カルシウム血症の症状（吐き気、便秘、多尿など）がないか確認する</v>
       </c>
       <c r="H74" t="str">
-        <v>NSAIDsなど腎機能を悪化させる薬剤。ACE阻害薬・ARB・SGLT2阻害薬は低下させる方向に働く</v>
+        <v>活性型/天然型ビタミンD製剤の過量投与</v>
       </c>
       <c r="I74" t="str">
-        <v/>
+        <v>日光暴露不足、食事摂取不足、高齢、腸疾患による吸収不良、肝・腎機能低下（活性化障害）</v>
       </c>
       <c r="J74" t="str">
-        <v/>
+        <v>適度な日光浴、魚類・きのこ類などビタミンDを多く含む食品の摂取を意識するとよいことを伝える</v>
       </c>
       <c r="K74" t="str">
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>糖尿病腎症の早期発見に重要な検査。血糖・血圧コントロールで改善しうる段階なので、早期介入の意義を伝える</v>
+        <v>骨粗鬆症治療における活性型ビタミンD3製剤の効果判定や、投与量調整の参考に用いられる。腎機能低下患者では活性化障害により25(OH)Dが正常でも活性型が不足することがある点に注意</v>
       </c>
       <c r="M74" t="str">
-        <v>糖尿病,腎機能</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="N74" t="str">
-        <v>微量アルブミン,U-Alb,MAU,糖尿病性腎症,早期腎症</v>
+        <v>25(OH)D,ビタミンD,25-ヒドロキシビタミンD,ビタミンD欠乏,骨粗鬆症</v>
       </c>
       <c r="O74" t="str">
-        <v/>
+        <v>食事と栄養 p.38（ビタミンD）</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>C反応性蛋白（CRP）</v>
+        <v>ucOC（低カルボキシル化オステオカルシン）</v>
       </c>
       <c r="B75" t="str">
-        <v>CRP</v>
+        <v>ucOC</v>
       </c>
       <c r="C75" t="str">
-        <v>0.3 mg/dL未満（施設差あり）</v>
+        <v>4.5 ng/mL未満（施設差あり）</v>
       </c>
       <c r="D75" t="str">
-        <v>体のどこかに炎症や感染が起きていないかを鋭敏に反映する数値</v>
+        <v>ビタミンKが不足していないかを反映する骨の指標</v>
       </c>
       <c r="E75" t="str">
-        <v>CRPは、体に炎症や感染が起きると数時間〜半日程度で急激に上昇する数値です。風邪のようなウイルス感染から細菌感染、体のどこかの炎症まで、幅広く反応するため、体調の変化を早期に捉える手がかりになります。</v>
+        <v>ucOCは、骨を作るために必要なビタミンKが体の中で足りているかどうかを反映する検査です。数値が高いとビタミンK不足が疑われます。</v>
       </c>
       <c r="F75" t="str">
-        <v>細菌感染症、ウイルス感染症、自己免疫疾患（関節リウマチなど）、悪性腫瘍、組織の損傷（術後・心筋梗塞など）</v>
+        <v>ビタミンK不足状態</v>
       </c>
       <c r="G75" t="str">
-        <v>発熱、痛み、腫れなど炎症症状の有無を確認する</v>
+        <v>ビタミンK2製剤(骨粗鬆症治療薬)の適応が検討されているか確認する。ワルファリン服用中の患者では、納豆などビタミンKを多く含む食品の急な摂取量の変化を避けるよう説明する</v>
       </c>
       <c r="H75" t="str">
         <v/>
@@ -3937,92 +3937,92 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>白血球数と合わせて感染・炎症の程度を評価する。上昇・低下のタイミングは白血球より半日〜1日程度遅れる傾向があるため、経過を追う際は採血のタイミングに注意</v>
+        <v>ビタミンK2製剤（骨粗鬆症治療薬）の適応判断や効果判定に使われる</v>
       </c>
       <c r="M75" t="str">
-        <v/>
+        <v>骨粗鬆症</v>
       </c>
       <c r="N75" t="str">
-        <v>CRP,炎症,感染</v>
+        <v>ucOC,オステオカルシン,ビタミンK</v>
       </c>
       <c r="O75" t="str">
-        <v/>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>PT-INR（プロトロンビン時間国際標準比）</v>
+        <v>PTH（副甲状腺ホルモン）</v>
       </c>
       <c r="B76" t="str">
-        <v>PT-INR,INR</v>
+        <v>PTH</v>
       </c>
       <c r="C76" t="str">
-        <v>治療域の目安 1.6〜3.0（ワルファリン服用時。年齢・疾患により異なる）</v>
+        <v>10〜65 pg/mL（施設差あり）</v>
       </c>
       <c r="D76" t="str">
-        <v>血液の固まりやすさを表す数値で、ワルファリンの効き具合を確認するために使う</v>
+        <v>血液中のカルシウム濃度を調節するホルモン</v>
       </c>
       <c r="E76" t="str">
-        <v>PT-INRは血液が固まるまでの時間をもとにした数値で、ワルファリンというお薬を飲んでいる方の効き具合を確認するために測ります。数値が高いほど血液が固まりにくく出血しやすい状態、低いほど血栓ができやすい状態を示します。</v>
+        <v>PTHは、血液中のカルシウム濃度を一定に保つために働くホルモンです。カルシウムが低くなると分泌が増え、骨からカルシウムを取り出したり、腎臓での再吸収を促したりして数値を戻そうとします。</v>
       </c>
       <c r="F76" t="str">
-        <v>ワルファリンの効きすぎ、肝機能低下、ビタミンK不足、納豆・青汁など摂取量の変化</v>
+        <v>原発性・二次性副甲状腺機能亢進症（腎不全に伴うものなど）</v>
       </c>
       <c r="G76" t="str">
-        <v>歯ぐきや鼻からの出血、あざ、黒い便などの出血症状がないか確認する。納豆・クロレラ・青汁などビタミンKを多く含む食品の摂取状況を確認する</v>
+        <v/>
       </c>
       <c r="H76" t="str">
-        <v>ワルファリンの過量。ワルファリン服用中はST合剤・マクロライド系・フルコナゾール等の相互作用やビタミンK摂取量の変化にも注意</v>
+        <v/>
       </c>
       <c r="I76" t="str">
-        <v>ワルファリンの効き不足、飲み忘れ、ビタミンK摂取量の急激な増加</v>
+        <v>副甲状腺機能低下症</v>
       </c>
       <c r="J76" t="str">
-        <v>服薬状況（飲み忘れ）を確認する。片側のむくみ・しびれ・胸痛など血栓症状がないか確認する</v>
+        <v/>
       </c>
       <c r="K76" t="str">
-        <v>ワルファリン服用中で低値の場合は効果不十分の可能性。ビタミンK摂取量の変化や、リファンピシン・カルバマゼピン・バルビツール酸系など代謝を促進する薬との併用を確認</v>
+        <v/>
       </c>
       <c r="L76" t="str">
-        <v>治療域は疾患・年齢によって異なる（例：非弁膜症性心房細動の高齢者では1.6〜2.6が目安になることが多い）。多くの薬剤・食品と相互作用があるため新規薬剤追加時は必ず確認する。DOAC（エリキュース、リクシアナ、プラザキサなど）ではPT-INRのモニタリングは不要</v>
+        <v>骨粗鬆症の二次性原因（副甲状腺機能亢進症）を除外するための検査。カルシウム・リンと合わせて評価する</v>
       </c>
       <c r="M76" t="str">
-        <v>抗凝固療法（心房細動・血栓症）</v>
+        <v>骨粗鬆症</v>
       </c>
       <c r="N76" t="str">
-        <v>PT-INR,INR,プロトロンビン時間,ワルファリン,ワーファリン,抗凝固</v>
+        <v>PTH,副甲状腺ホルモン,パラトルモン</v>
       </c>
       <c r="O76" t="str">
-        <v>食事と栄養 p.221（心疾患Q93 ワルファリン服用中のビタミンK摂取）</v>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>骨型酒石酸抵抗性フォスファターゼ（TRACP-5b）</v>
+        <v>尿中NTX</v>
       </c>
       <c r="B77" t="str">
-        <v>TRACP-5b</v>
+        <v>NTX</v>
       </c>
       <c r="C77" t="str">
-        <v>120〜420 mU/dL</v>
+        <v>施設差が大きく一律の記載が難しい（尿中）</v>
       </c>
       <c r="D77" t="str">
-        <v>骨がどれくらい壊されているかを見る検査。骨は「古い骨を壊して新しい骨を作る」入れ替えを繰り返しており、骨を壊す細胞が活発だとこの物質が血液中に増える。</v>
+        <v>骨が壊されるときに出る、骨吸収マーカーのひとつ</v>
       </c>
       <c r="E77" t="str">
-        <v>この検査は、骨がどれくらい早く減っていないかを見るものです。数値が高いと、骨が弱くなりやすい状態の目安になります。</v>
+        <v>NTXは、骨が壊される（吸収される）ときに尿の中に出てくる物質です。骨粗鬆症の治療薬がどれくらい効いているかを確認するために使われます。</v>
       </c>
       <c r="F77" t="str">
-        <v>骨粗鬆症、骨代謝回転（骨がこわれるスピード）が活発な状態</v>
+        <v>骨代謝回転の亢進（骨粗鬆症、閉経後など）</v>
       </c>
       <c r="G77" t="str">
-        <v>カルシウム・ビタミンDの摂取や、適度な荷重運動（ウォーキングなど）を意識するよう伝える</v>
+        <v/>
       </c>
       <c r="H77" t="str">
         <v/>
       </c>
       <c r="I77" t="str">
-        <v/>
+        <v>骨吸収抑制薬（ビスホスホネート等）による治療効果</v>
       </c>
       <c r="J77" t="str">
         <v/>
@@ -4031,36 +4031,36 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>「骨を壊す側」の指標。「骨を作る側」の検査と合わせて評価する。数値だけで診断はしない</v>
+        <v>治療開始後3〜6か月で再検し、薬の効果判定に使われる。TRACP-5bと同じ「骨を壊す側」の指標</v>
       </c>
       <c r="M77" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="N77" t="str">
-        <v>TRACP-5b,骨型酒石酸抵抗性フォスファターゼ,骨粗鬆症,骨代謝</v>
+        <v>NTX,尿中NTX,骨吸収マーカー</v>
       </c>
       <c r="O77" t="str">
-        <v/>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>骨型アルカリフォスファターゼ</v>
+        <v>カルシトニン</v>
       </c>
       <c r="B78" t="str">
-        <v>BAP</v>
+        <v>CT</v>
       </c>
       <c r="C78" t="str">
-        <v>男性 3.7〜20.9 μg/L、女性（閉経前）2.9〜14.5 μg/L（施設差あり）</v>
+        <v>男性 9.52 pg/mL未満、女性 6.40 pg/mL未満（施設差あり）</v>
       </c>
       <c r="D78" t="str">
-        <v>ALPのうち骨に由来する成分だけを測定し、骨が作られる勢い（骨形成）を反映する</v>
+        <v>血液中のカルシウムを下げる方向に働くホルモン</v>
       </c>
       <c r="E78" t="str">
-        <v>骨型ALPは、通常のALP（アルカリフォスファターゼ）の中でも、骨で作られる成分だけを選んで測定するものです。骨を新しく作る働きがどれくらい活発かを見る指標として、骨粗鬆症の治療効果判定などに使われます。</v>
+        <v>カルシトニンは、PTHとは逆に血液中のカルシウムを下げる方向に働くホルモンです。特定の甲状腺の病気（甲状腺髄様癌）がないかを調べる際にも使われます。</v>
       </c>
       <c r="F78" t="str">
-        <v>骨代謝回転の亢進（骨粗鬆症、骨折治癒過程、骨形成促進薬による治療効果、Paget病、骨転移）</v>
+        <v>甲状腺髄様癌、腎不全</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -4069,7 +4069,7 @@
         <v/>
       </c>
       <c r="I78" t="str">
-        <v>骨形成の低下</v>
+        <v/>
       </c>
       <c r="J78" t="str">
         <v/>
@@ -4078,92 +4078,92 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>通常のALPと異なり肝臓の影響を受けにくいため、肝機能異常がある患者でも骨代謝を評価しやすい。P1NPと同じ「骨を作る側」の指標で、骨形成促進薬（テリパラチド等）の効果判定に使われる</v>
+        <v>骨粗鬆症の二次性原因の除外目的で測定されることがある検査値。同名の薬剤（カルシトニン製剤）と混同しないよう注意</v>
       </c>
       <c r="M78" t="str">
         <v>骨粗鬆症</v>
       </c>
       <c r="N78" t="str">
-        <v>骨型ALP,BAP,骨型アルカリフォスファターゼ,骨形成マーカー</v>
+        <v>カルシトニン,CT</v>
       </c>
       <c r="O78" t="str">
-        <v/>
+        <v>食事と栄養 p.165-178（第2部 骨粗鬆症）</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>25-ヒドロキシビタミンD</v>
+        <v>DPD（デオキシピリジノリン）</v>
       </c>
       <c r="B79" t="str">
-        <v>25(OH)D</v>
+        <v>DPD</v>
       </c>
       <c r="C79" t="str">
-        <v>30 ng/mL以上：充足、20〜30 ng/mL：不足、20 ng/mL未満：欠乏（施設差あり）</v>
+        <v>施設差が大きく一律の記載が難しい（尿中）</v>
       </c>
       <c r="D79" t="str">
-        <v>体内のビタミンDの蓄え具合を反映する指標。カルシウムの吸収や骨の健康に関わる</v>
+        <v>骨のコラーゲンが壊れるときに出る、骨吸収マーカーのひとつ</v>
       </c>
       <c r="E79" t="str">
-        <v>この検査は、体の中にビタミンDがどれくらい蓄えられているかを見るものです。ビタミンDは、食事から摂ったカルシウムを腸で吸収するのを助ける働きがあり、不足すると骨がもろくなりやすくなります。</v>
+        <v>DPDも、骨が壊されるときに尿に出てくる物質の一つです。NTXと同じように、骨粗鬆症治療薬の効果を確認するために使われます。</v>
       </c>
       <c r="F79" t="str">
-        <v>ビタミンD製剤の過剰摂取</v>
+        <v>骨代謝回転の亢進（骨粗鬆症など）</v>
       </c>
       <c r="G79" t="str">
-        <v>活性型ビタミンD3製剤やサプリメントの摂取量を確認する。高カルシウム血症の症状（吐き気、便秘、多尿など）がないか確認する</v>
+        <v/>
       </c>
       <c r="H79" t="str">
-        <v>活性型/天然型ビタミンD製剤の過量投与</v>
+        <v/>
       </c>
       <c r="I79" 